--- a/database/XPBR31.xlsx
+++ b/database/XPBR31.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1200"/>
+  <dimension ref="A1:F1201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44473</v>
       </c>
       <c r="B2" t="n">
-        <v>196.6089782714844</v>
+        <v>196.6089630126953</v>
       </c>
       <c r="C2" t="n">
-        <v>203.5755007756201</v>
+        <v>203.5754849761604</v>
       </c>
       <c r="D2" t="n">
-        <v>191.4433762318198</v>
+        <v>191.4433613739322</v>
       </c>
       <c r="E2" t="n">
-        <v>191.9529095912669</v>
+        <v>191.9528946938346</v>
       </c>
       <c r="F2" t="n">
         <v>9950865</v>
@@ -472,16 +472,16 @@
         <v>44474</v>
       </c>
       <c r="B3" t="n">
-        <v>192.5415191650391</v>
+        <v>192.54150390625</v>
       </c>
       <c r="C3" t="n">
-        <v>198.9809483744415</v>
+        <v>198.9809326053319</v>
       </c>
       <c r="D3" t="n">
-        <v>187.727326021756</v>
+        <v>187.7273111444886</v>
       </c>
       <c r="E3" t="n">
-        <v>197.6631937494452</v>
+        <v>197.6631780847668</v>
       </c>
       <c r="F3" t="n">
         <v>2636287</v>
@@ -492,16 +492,16 @@
         <v>44475</v>
       </c>
       <c r="B4" t="n">
-        <v>189.4491577148438</v>
+        <v>189.4491729736328</v>
       </c>
       <c r="C4" t="n">
-        <v>191.0041117053844</v>
+        <v>191.004127089414</v>
       </c>
       <c r="D4" t="n">
-        <v>181.8501124827158</v>
+        <v>181.8501271294555</v>
       </c>
       <c r="E4" t="n">
-        <v>191.0041117053844</v>
+        <v>191.004127089414</v>
       </c>
       <c r="F4" t="n">
         <v>2556665</v>
@@ -572,16 +572,16 @@
         <v>44482</v>
       </c>
       <c r="B8" t="n">
-        <v>169.5510864257812</v>
+        <v>169.5510711669922</v>
       </c>
       <c r="C8" t="n">
-        <v>178.8632239955791</v>
+        <v>178.8632078987421</v>
       </c>
       <c r="D8" t="n">
-        <v>169.5510864257812</v>
+        <v>169.5510711669922</v>
       </c>
       <c r="E8" t="n">
-        <v>174.4092071561597</v>
+        <v>174.4091914601629</v>
       </c>
       <c r="F8" t="n">
         <v>3487621</v>
@@ -592,16 +592,16 @@
         <v>44483</v>
       </c>
       <c r="B9" t="n">
-        <v>164.7632446289062</v>
+        <v>164.7632293701172</v>
       </c>
       <c r="C9" t="n">
-        <v>173.8293888548571</v>
+        <v>173.8293727564489</v>
       </c>
       <c r="D9" t="n">
-        <v>164.2888454897918</v>
+        <v>164.2888302749371</v>
       </c>
       <c r="E9" t="n">
-        <v>171.8351966443599</v>
+        <v>171.8351807306346</v>
       </c>
       <c r="F9" t="n">
         <v>3205420</v>
@@ -632,16 +632,16 @@
         <v>44487</v>
       </c>
       <c r="B11" t="n">
-        <v>179.4166717529297</v>
+        <v>179.4166564941406</v>
       </c>
       <c r="C11" t="n">
-        <v>182.2718066273138</v>
+        <v>182.2717911257051</v>
       </c>
       <c r="D11" t="n">
-        <v>175.0680843944616</v>
+        <v>175.0680695055053</v>
       </c>
       <c r="E11" t="n">
-        <v>176.7548086193568</v>
+        <v>176.7547935869503</v>
       </c>
       <c r="F11" t="n">
         <v>1369949</v>
@@ -672,16 +672,16 @@
         <v>44489</v>
       </c>
       <c r="B13" t="n">
-        <v>174.3828430175781</v>
+        <v>174.3828277587891</v>
       </c>
       <c r="C13" t="n">
-        <v>178.4942305647025</v>
+        <v>178.4942149461601</v>
       </c>
       <c r="D13" t="n">
-        <v>169.8409841808207</v>
+        <v>169.8409693194518</v>
       </c>
       <c r="E13" t="n">
-        <v>176.5791004863134</v>
+        <v>176.5790850353481</v>
       </c>
       <c r="F13" t="n">
         <v>1907987</v>
@@ -712,16 +712,16 @@
         <v>44491</v>
       </c>
       <c r="B15" t="n">
-        <v>166.0546264648438</v>
+        <v>166.0546417236328</v>
       </c>
       <c r="C15" t="n">
-        <v>170.8600385320068</v>
+        <v>170.8600542323661</v>
       </c>
       <c r="D15" t="n">
-        <v>159.8084701383689</v>
+        <v>159.8084848231975</v>
       </c>
       <c r="E15" t="n">
-        <v>169.5510643493521</v>
+        <v>169.5510799294295</v>
       </c>
       <c r="F15" t="n">
         <v>1387914</v>
@@ -732,16 +732,16 @@
         <v>44494</v>
       </c>
       <c r="B16" t="n">
-        <v>169.1205902099609</v>
+        <v>169.12060546875</v>
       </c>
       <c r="C16" t="n">
-        <v>174.5848793771119</v>
+        <v>174.5848951289127</v>
       </c>
       <c r="D16" t="n">
-        <v>167.3635843917102</v>
+        <v>167.3635994919746</v>
       </c>
       <c r="E16" t="n">
-        <v>167.7061999900735</v>
+        <v>167.7062151212502</v>
       </c>
       <c r="F16" t="n">
         <v>1203463</v>
@@ -772,16 +772,16 @@
         <v>44496</v>
       </c>
       <c r="B18" t="n">
-        <v>163.8320159912109</v>
+        <v>163.83203125</v>
       </c>
       <c r="C18" t="n">
-        <v>168.540792225014</v>
+        <v>168.5408079223634</v>
       </c>
       <c r="D18" t="n">
-        <v>163.8320159912109</v>
+        <v>163.83203125</v>
       </c>
       <c r="E18" t="n">
-        <v>166.9155564450402</v>
+        <v>166.9155719910203</v>
       </c>
       <c r="F18" t="n">
         <v>503418</v>
@@ -812,16 +812,16 @@
         <v>44498</v>
       </c>
       <c r="B20" t="n">
-        <v>162.5230560302734</v>
+        <v>162.5230712890625</v>
       </c>
       <c r="C20" t="n">
-        <v>167.337248747422</v>
+        <v>167.3372644582008</v>
       </c>
       <c r="D20" t="n">
-        <v>161.2053015219199</v>
+        <v>161.205316656989</v>
       </c>
       <c r="E20" t="n">
-        <v>166.1249237150633</v>
+        <v>166.1249393120207</v>
       </c>
       <c r="F20" t="n">
         <v>643563</v>
@@ -852,16 +852,16 @@
         <v>44503</v>
       </c>
       <c r="B22" t="n">
-        <v>164.6490325927734</v>
+        <v>164.6490173339844</v>
       </c>
       <c r="C22" t="n">
-        <v>168.6725779888017</v>
+        <v>168.672562357132</v>
       </c>
       <c r="D22" t="n">
-        <v>161.381000321849</v>
+        <v>161.3809853659237</v>
       </c>
       <c r="E22" t="n">
-        <v>168.6725779888017</v>
+        <v>168.672562357132</v>
       </c>
       <c r="F22" t="n">
         <v>834348</v>
@@ -892,16 +892,16 @@
         <v>44505</v>
       </c>
       <c r="B24" t="n">
-        <v>170.4734954833984</v>
+        <v>170.4735107421875</v>
       </c>
       <c r="C24" t="n">
-        <v>171.3080705821796</v>
+        <v>171.30808591567</v>
       </c>
       <c r="D24" t="n">
-        <v>159.1407996942582</v>
+        <v>159.1408139386772</v>
       </c>
       <c r="E24" t="n">
-        <v>160.9417333736644</v>
+        <v>160.9417477792819</v>
       </c>
       <c r="F24" t="n">
         <v>806903</v>
@@ -932,16 +932,16 @@
         <v>44509</v>
       </c>
       <c r="B26" t="n">
-        <v>163.7705383300781</v>
+        <v>163.7705078125</v>
       </c>
       <c r="C26" t="n">
-        <v>169.8497778778882</v>
+        <v>169.8497462274832</v>
       </c>
       <c r="D26" t="n">
-        <v>162.0838140686822</v>
+        <v>162.0837838654142</v>
       </c>
       <c r="E26" t="n">
-        <v>167.3548324123792</v>
+        <v>167.3548012268911</v>
       </c>
       <c r="F26" t="n">
         <v>336270</v>
@@ -1012,16 +1012,16 @@
         <v>44516</v>
       </c>
       <c r="B30" t="n">
-        <v>155.5213775634766</v>
+        <v>155.5213928222656</v>
       </c>
       <c r="C30" t="n">
-        <v>161.6357640485668</v>
+        <v>161.6357799072614</v>
       </c>
       <c r="D30" t="n">
-        <v>154.8976479701114</v>
+        <v>154.897663167704</v>
       </c>
       <c r="E30" t="n">
-        <v>160.9417392050919</v>
+        <v>160.9417549956931</v>
       </c>
       <c r="F30" t="n">
         <v>392032</v>
@@ -1032,16 +1032,16 @@
         <v>44517</v>
       </c>
       <c r="B31" t="n">
-        <v>147.3425140380859</v>
+        <v>147.342529296875</v>
       </c>
       <c r="C31" t="n">
-        <v>157.7088514018402</v>
+        <v>157.708867734167</v>
       </c>
       <c r="D31" t="n">
-        <v>146.6045747863164</v>
+        <v>146.6045899686845</v>
       </c>
       <c r="E31" t="n">
-        <v>156.3735231808589</v>
+        <v>156.3735393748991</v>
       </c>
       <c r="F31" t="n">
         <v>1006563</v>
@@ -1052,16 +1052,16 @@
         <v>44518</v>
       </c>
       <c r="B32" t="n">
-        <v>141.1403045654297</v>
+        <v>141.1402893066406</v>
       </c>
       <c r="C32" t="n">
-        <v>149.7320634033205</v>
+        <v>149.7320472156696</v>
       </c>
       <c r="D32" t="n">
-        <v>141.1403045654297</v>
+        <v>141.1402893066406</v>
       </c>
       <c r="E32" t="n">
-        <v>147.8520673947305</v>
+        <v>147.8520514103275</v>
       </c>
       <c r="F32" t="n">
         <v>1135748</v>
@@ -1072,16 +1072,16 @@
         <v>44519</v>
       </c>
       <c r="B33" t="n">
-        <v>147.1931915283203</v>
+        <v>147.1931762695312</v>
       </c>
       <c r="C33" t="n">
-        <v>149.046833535527</v>
+        <v>149.0468180845801</v>
       </c>
       <c r="D33" t="n">
-        <v>140.5692708976831</v>
+        <v>140.5692563255631</v>
       </c>
       <c r="E33" t="n">
-        <v>142.5722568176638</v>
+        <v>142.5722420379041</v>
       </c>
       <c r="F33" t="n">
         <v>581745</v>
@@ -1092,16 +1092,16 @@
         <v>44522</v>
       </c>
       <c r="B34" t="n">
-        <v>140.0509490966797</v>
+        <v>140.0509338378906</v>
       </c>
       <c r="C34" t="n">
-        <v>150.6632671305561</v>
+        <v>150.6632507155369</v>
       </c>
       <c r="D34" t="n">
-        <v>139.9016051926592</v>
+        <v>139.9015899501414</v>
       </c>
       <c r="E34" t="n">
-        <v>145.9281364140771</v>
+        <v>145.9281205149585</v>
       </c>
       <c r="F34" t="n">
         <v>547961</v>
@@ -1132,16 +1132,16 @@
         <v>44524</v>
       </c>
       <c r="B36" t="n">
-        <v>148.7393341064453</v>
+        <v>148.7393493652344</v>
       </c>
       <c r="C36" t="n">
-        <v>150.2152260507179</v>
+        <v>150.2152414609149</v>
       </c>
       <c r="D36" t="n">
-        <v>144.4171011491115</v>
+        <v>144.4171159644937</v>
       </c>
       <c r="E36" t="n">
-        <v>144.5225172148126</v>
+        <v>144.5225320410092</v>
       </c>
       <c r="F36" t="n">
         <v>231702</v>
@@ -1172,16 +1172,16 @@
         <v>44526</v>
       </c>
       <c r="B38" t="n">
-        <v>146.7363586425781</v>
+        <v>146.7363433837891</v>
       </c>
       <c r="C38" t="n">
-        <v>148.7305642552127</v>
+        <v>148.7305487890506</v>
       </c>
       <c r="D38" t="n">
-        <v>143.3716904608705</v>
+        <v>143.3716755519658</v>
       </c>
       <c r="E38" t="n">
-        <v>148.7305642552127</v>
+        <v>148.7305487890506</v>
       </c>
       <c r="F38" t="n">
         <v>241997</v>
@@ -1192,16 +1192,16 @@
         <v>44529</v>
       </c>
       <c r="B39" t="n">
-        <v>147.0175018310547</v>
+        <v>147.0174865722656</v>
       </c>
       <c r="C39" t="n">
-        <v>150.43487841625</v>
+        <v>150.434862802775</v>
       </c>
       <c r="D39" t="n">
-        <v>146.0247890203648</v>
+        <v>146.0247738646084</v>
       </c>
       <c r="E39" t="n">
-        <v>148.7305802263517</v>
+        <v>148.730564789764</v>
       </c>
       <c r="F39" t="n">
         <v>333389</v>
@@ -1212,16 +1212,16 @@
         <v>44530</v>
       </c>
       <c r="B40" t="n">
-        <v>140.5604705810547</v>
+        <v>140.5604553222656</v>
       </c>
       <c r="C40" t="n">
-        <v>147.3073667345976</v>
+        <v>147.3073507433874</v>
       </c>
       <c r="D40" t="n">
-        <v>139.7610296874511</v>
+        <v>139.7610145154467</v>
       </c>
       <c r="E40" t="n">
-        <v>147.3073667345976</v>
+        <v>147.3073507433874</v>
       </c>
       <c r="F40" t="n">
         <v>711030</v>
@@ -1232,16 +1232,16 @@
         <v>44531</v>
       </c>
       <c r="B41" t="n">
-        <v>144.3116912841797</v>
+        <v>144.3116760253906</v>
       </c>
       <c r="C41" t="n">
-        <v>151.2342857954605</v>
+        <v>151.2342698047112</v>
       </c>
       <c r="D41" t="n">
-        <v>141.4477629305895</v>
+        <v>141.4477479746177</v>
       </c>
       <c r="E41" t="n">
-        <v>142.317485724668</v>
+        <v>142.3174706767361</v>
       </c>
       <c r="F41" t="n">
         <v>941983</v>
@@ -1252,16 +1252,16 @@
         <v>44532</v>
       </c>
       <c r="B42" t="n">
-        <v>143.7845916748047</v>
+        <v>143.7845764160156</v>
       </c>
       <c r="C42" t="n">
-        <v>150.5139282123845</v>
+        <v>150.513912239461</v>
       </c>
       <c r="D42" t="n">
-        <v>143.0466523346498</v>
+        <v>143.0466371541728</v>
       </c>
       <c r="E42" t="n">
-        <v>145.8315053769355</v>
+        <v>145.8314899009227</v>
       </c>
       <c r="F42" t="n">
         <v>584287</v>
@@ -1332,16 +1332,16 @@
         <v>44538</v>
       </c>
       <c r="B46" t="n">
-        <v>146.3498229980469</v>
+        <v>146.3498077392578</v>
       </c>
       <c r="C46" t="n">
-        <v>150.2240247482011</v>
+        <v>150.2240090854783</v>
       </c>
       <c r="D46" t="n">
-        <v>145.9984271325229</v>
+        <v>145.9984119103712</v>
       </c>
       <c r="E46" t="n">
-        <v>148.2473928436195</v>
+        <v>148.2473773869852</v>
       </c>
       <c r="F46" t="n">
         <v>297967</v>
@@ -1372,16 +1372,16 @@
         <v>44540</v>
       </c>
       <c r="B48" t="n">
-        <v>148.2210083007812</v>
+        <v>148.2210235595703</v>
       </c>
       <c r="C48" t="n">
-        <v>150.2239938125575</v>
+        <v>150.2240092775463</v>
       </c>
       <c r="D48" t="n">
-        <v>146.332232453983</v>
+        <v>146.3322475183298</v>
       </c>
       <c r="E48" t="n">
-        <v>148.115592243811</v>
+        <v>148.1156074917479</v>
       </c>
       <c r="F48" t="n">
         <v>506410</v>
@@ -1392,16 +1392,16 @@
         <v>44543</v>
       </c>
       <c r="B49" t="n">
-        <v>155.4950408935547</v>
+        <v>155.4950256347656</v>
       </c>
       <c r="C49" t="n">
-        <v>159.5537207222275</v>
+        <v>159.5537050651586</v>
       </c>
       <c r="D49" t="n">
-        <v>147.1580420673422</v>
+        <v>147.1580276266661</v>
       </c>
       <c r="E49" t="n">
-        <v>148.2034628486411</v>
+        <v>148.2034483053774</v>
       </c>
       <c r="F49" t="n">
         <v>707090</v>
@@ -1412,16 +1412,16 @@
         <v>44544</v>
       </c>
       <c r="B50" t="n">
-        <v>147.2283325195312</v>
+        <v>147.2283172607422</v>
       </c>
       <c r="C50" t="n">
-        <v>150.926836499023</v>
+        <v>150.9268208569199</v>
       </c>
       <c r="D50" t="n">
-        <v>141.1227386054261</v>
+        <v>141.1227239794226</v>
       </c>
       <c r="E50" t="n">
-        <v>150.6632828858824</v>
+        <v>150.663267271094</v>
       </c>
       <c r="F50" t="n">
         <v>995575</v>
@@ -1452,16 +1452,16 @@
         <v>44546</v>
       </c>
       <c r="B52" t="n">
-        <v>145.72607421875</v>
+        <v>145.7260894775391</v>
       </c>
       <c r="C52" t="n">
-        <v>152.8595139117323</v>
+        <v>152.8595299174546</v>
       </c>
       <c r="D52" t="n">
-        <v>144.3028903187285</v>
+        <v>144.3029054284978</v>
       </c>
       <c r="E52" t="n">
-        <v>148.115603324704</v>
+        <v>148.1156188336976</v>
       </c>
       <c r="F52" t="n">
         <v>399045</v>
@@ -1492,16 +1492,16 @@
         <v>44550</v>
       </c>
       <c r="B54" t="n">
-        <v>145.9105682373047</v>
+        <v>145.9105529785156</v>
       </c>
       <c r="C54" t="n">
-        <v>146.2883315190382</v>
+        <v>146.288316220744</v>
       </c>
       <c r="D54" t="n">
-        <v>139.2515135151951</v>
+        <v>139.2514989527854</v>
       </c>
       <c r="E54" t="n">
-        <v>144.6455217015624</v>
+        <v>144.6455065750673</v>
       </c>
       <c r="F54" t="n">
         <v>356146</v>
@@ -1512,16 +1512,16 @@
         <v>44551</v>
       </c>
       <c r="B55" t="n">
-        <v>148.9853057861328</v>
+        <v>148.9853210449219</v>
       </c>
       <c r="C55" t="n">
-        <v>149.6441829708282</v>
+        <v>149.6441982970981</v>
       </c>
       <c r="D55" t="n">
-        <v>144.7948565429918</v>
+        <v>144.7948713726031</v>
       </c>
       <c r="E55" t="n">
-        <v>146.3146628289863</v>
+        <v>146.3146778142533</v>
       </c>
       <c r="F55" t="n">
         <v>221674</v>
@@ -1652,16 +1652,16 @@
         <v>44564</v>
       </c>
       <c r="B62" t="n">
-        <v>144.8124389648438</v>
+        <v>144.8124084472656</v>
       </c>
       <c r="C62" t="n">
-        <v>144.8124389648438</v>
+        <v>144.8124084472656</v>
       </c>
       <c r="D62" t="n">
-        <v>138.7947011393807</v>
+        <v>138.7946718899726</v>
       </c>
       <c r="E62" t="n">
-        <v>142.1769298253991</v>
+        <v>142.1768998632246</v>
       </c>
       <c r="F62" t="n">
         <v>369633</v>
@@ -1672,16 +1672,16 @@
         <v>44565</v>
       </c>
       <c r="B63" t="n">
-        <v>140.2969207763672</v>
+        <v>140.2969055175781</v>
       </c>
       <c r="C63" t="n">
-        <v>146.4991495621347</v>
+        <v>146.499133628787</v>
       </c>
       <c r="D63" t="n">
-        <v>138.6629047258906</v>
+        <v>138.6628896448183</v>
       </c>
       <c r="E63" t="n">
-        <v>144.8124254785607</v>
+        <v>144.8124097286623</v>
       </c>
       <c r="F63" t="n">
         <v>382138</v>
@@ -1712,16 +1712,16 @@
         <v>44567</v>
       </c>
       <c r="B65" t="n">
-        <v>135.2718963623047</v>
+        <v>135.2718811035156</v>
       </c>
       <c r="C65" t="n">
-        <v>137.0289024684961</v>
+        <v>137.0288870115152</v>
       </c>
       <c r="D65" t="n">
-        <v>129.5879805363842</v>
+        <v>129.5879659187458</v>
       </c>
       <c r="E65" t="n">
-        <v>134.8502186501887</v>
+        <v>134.8502034389653</v>
       </c>
       <c r="F65" t="n">
         <v>814212</v>
@@ -1732,16 +1732,16 @@
         <v>44568</v>
       </c>
       <c r="B66" t="n">
-        <v>137.23974609375</v>
+        <v>137.2397308349609</v>
       </c>
       <c r="C66" t="n">
-        <v>142.1857225025721</v>
+        <v>142.1857066938723</v>
       </c>
       <c r="D66" t="n">
-        <v>134.2001196747043</v>
+        <v>134.2001047538714</v>
       </c>
       <c r="E66" t="n">
-        <v>137.9249773931206</v>
+        <v>137.9249620581452</v>
       </c>
       <c r="F66" t="n">
         <v>686988</v>
@@ -1792,16 +1792,16 @@
         <v>44573</v>
       </c>
       <c r="B69" t="n">
-        <v>149.4421539306641</v>
+        <v>149.442138671875</v>
       </c>
       <c r="C69" t="n">
-        <v>150.7950427255186</v>
+        <v>150.7950273285929</v>
       </c>
       <c r="D69" t="n">
-        <v>145.5591720697106</v>
+        <v>145.5591572073933</v>
       </c>
       <c r="E69" t="n">
-        <v>146.4464553218307</v>
+        <v>146.4464403689174</v>
       </c>
       <c r="F69" t="n">
         <v>416574</v>
@@ -1852,16 +1852,16 @@
         <v>44578</v>
       </c>
       <c r="B72" t="n">
-        <v>138.8034820556641</v>
+        <v>138.803466796875</v>
       </c>
       <c r="C72" t="n">
-        <v>140.2705805422223</v>
+        <v>140.2705651221538</v>
       </c>
       <c r="D72" t="n">
-        <v>136.9059122483617</v>
+        <v>136.9058971981742</v>
       </c>
       <c r="E72" t="n">
-        <v>138.0655427100108</v>
+        <v>138.065527532344</v>
       </c>
       <c r="F72" t="n">
         <v>75291</v>
@@ -1872,16 +1872,16 @@
         <v>44579</v>
       </c>
       <c r="B73" t="n">
-        <v>133.1722717285156</v>
+        <v>133.1722564697266</v>
       </c>
       <c r="C73" t="n">
-        <v>138.8034793945444</v>
+        <v>138.8034634905354</v>
       </c>
       <c r="D73" t="n">
-        <v>133.1722717285156</v>
+        <v>133.1722564697266</v>
       </c>
       <c r="E73" t="n">
-        <v>138.1885299516231</v>
+        <v>138.1885141180745</v>
       </c>
       <c r="F73" t="n">
         <v>435258</v>
@@ -1912,16 +1912,16 @@
         <v>44581</v>
       </c>
       <c r="B75" t="n">
-        <v>145.2868194580078</v>
+        <v>145.2868347167969</v>
       </c>
       <c r="C75" t="n">
-        <v>149.2488628630469</v>
+        <v>149.2488785379507</v>
       </c>
       <c r="D75" t="n">
-        <v>138.1094520986048</v>
+        <v>138.1094666035888</v>
       </c>
       <c r="E75" t="n">
-        <v>138.1094520986048</v>
+        <v>138.1094666035888</v>
       </c>
       <c r="F75" t="n">
         <v>666913</v>
@@ -1932,16 +1932,16 @@
         <v>44582</v>
       </c>
       <c r="B76" t="n">
-        <v>143.1872100830078</v>
+        <v>143.1871948242188</v>
       </c>
       <c r="C76" t="n">
-        <v>145.567945727671</v>
+        <v>145.5679302151781</v>
       </c>
       <c r="D76" t="n">
-        <v>140.3320753073403</v>
+        <v>140.3320603528095</v>
       </c>
       <c r="E76" t="n">
-        <v>145.3043921443233</v>
+        <v>145.3043766599161</v>
       </c>
       <c r="F76" t="n">
         <v>292243</v>
@@ -1952,16 +1952,16 @@
         <v>44585</v>
       </c>
       <c r="B77" t="n">
-        <v>143.1696472167969</v>
+        <v>143.1696319580078</v>
       </c>
       <c r="C77" t="n">
-        <v>145.3307572747327</v>
+        <v>145.330741785616</v>
       </c>
       <c r="D77" t="n">
-        <v>136.449104054457</v>
+        <v>136.4490895119325</v>
       </c>
       <c r="E77" t="n">
-        <v>143.0203033026219</v>
+        <v>143.0202880597496</v>
       </c>
       <c r="F77" t="n">
         <v>940613</v>
@@ -1972,16 +1972,16 @@
         <v>44586</v>
       </c>
       <c r="B78" t="n">
-        <v>147.3161773681641</v>
+        <v>147.316162109375</v>
       </c>
       <c r="C78" t="n">
-        <v>149.5212151794752</v>
+        <v>149.5211996922916</v>
       </c>
       <c r="D78" t="n">
-        <v>140.1651631371207</v>
+        <v>140.165148619023</v>
       </c>
       <c r="E78" t="n">
-        <v>140.1651631371207</v>
+        <v>140.165148619023</v>
       </c>
       <c r="F78" t="n">
         <v>456302</v>
@@ -1992,16 +1992,16 @@
         <v>44587</v>
       </c>
       <c r="B79" t="n">
-        <v>151.7789611816406</v>
+        <v>151.7789764404297</v>
       </c>
       <c r="C79" t="n">
-        <v>157.1466148398293</v>
+        <v>157.1466306382445</v>
       </c>
       <c r="D79" t="n">
-        <v>148.2122412846406</v>
+        <v>148.2122561848568</v>
       </c>
       <c r="E79" t="n">
-        <v>148.5987713295526</v>
+        <v>148.5987862686278</v>
       </c>
       <c r="F79" t="n">
         <v>671208</v>
@@ -2012,16 +2012,16 @@
         <v>44588</v>
       </c>
       <c r="B80" t="n">
-        <v>149.486083984375</v>
+        <v>149.4860534667969</v>
       </c>
       <c r="C80" t="n">
-        <v>156.5668165068679</v>
+        <v>156.5667845437585</v>
       </c>
       <c r="D80" t="n">
-        <v>147.3249605575002</v>
+        <v>147.3249304811154</v>
       </c>
       <c r="E80" t="n">
-        <v>151.5417779286678</v>
+        <v>151.5417469914199</v>
       </c>
       <c r="F80" t="n">
         <v>697237</v>
@@ -2032,16 +2032,16 @@
         <v>44589</v>
       </c>
       <c r="B81" t="n">
-        <v>147.5533752441406</v>
+        <v>147.5533599853516</v>
       </c>
       <c r="C81" t="n">
-        <v>149.9253307510293</v>
+        <v>149.9253152469516</v>
       </c>
       <c r="D81" t="n">
-        <v>142.7479625837369</v>
+        <v>142.7479478218851</v>
       </c>
       <c r="E81" t="n">
-        <v>149.4948594393217</v>
+        <v>149.4948439797599</v>
       </c>
       <c r="F81" t="n">
         <v>1084942</v>
@@ -2072,16 +2072,16 @@
         <v>44593</v>
       </c>
       <c r="B83" t="n">
-        <v>155.5828857421875</v>
+        <v>155.5828704833984</v>
       </c>
       <c r="C83" t="n">
-        <v>157.3574521401745</v>
+        <v>157.3574367073448</v>
       </c>
       <c r="D83" t="n">
-        <v>151.1200889199835</v>
+        <v>151.1200740988831</v>
       </c>
       <c r="E83" t="n">
-        <v>152.4378434121932</v>
+        <v>152.4378284618541</v>
       </c>
       <c r="F83" t="n">
         <v>577815</v>
@@ -2092,16 +2092,16 @@
         <v>44594</v>
       </c>
       <c r="B84" t="n">
-        <v>148.9941101074219</v>
+        <v>148.9940948486328</v>
       </c>
       <c r="C84" t="n">
-        <v>158.1305356968381</v>
+        <v>158.1305195023691</v>
       </c>
       <c r="D84" t="n">
-        <v>148.9062544478559</v>
+        <v>148.9062391980643</v>
       </c>
       <c r="E84" t="n">
-        <v>155.8025081721468</v>
+        <v>155.8024922160959</v>
       </c>
       <c r="F84" t="n">
         <v>466282</v>
@@ -2132,16 +2132,16 @@
         <v>44596</v>
       </c>
       <c r="B86" t="n">
-        <v>149.6002655029297</v>
+        <v>149.6002502441406</v>
       </c>
       <c r="C86" t="n">
-        <v>151.0058756228975</v>
+        <v>151.0058602207404</v>
       </c>
       <c r="D86" t="n">
-        <v>143.5825281756291</v>
+        <v>143.5825135306316</v>
       </c>
       <c r="E86" t="n">
-        <v>149.3455055386924</v>
+        <v>149.3454903058881</v>
       </c>
       <c r="F86" t="n">
         <v>455710</v>
@@ -2152,16 +2152,16 @@
         <v>44599</v>
       </c>
       <c r="B87" t="n">
-        <v>147.1229095458984</v>
+        <v>147.1228942871094</v>
       </c>
       <c r="C87" t="n">
-        <v>152.1830823806577</v>
+        <v>152.183066597055</v>
       </c>
       <c r="D87" t="n">
-        <v>146.7100120324576</v>
+        <v>146.709996816492</v>
       </c>
       <c r="E87" t="n">
-        <v>149.5651469971611</v>
+        <v>149.5651314850764</v>
       </c>
       <c r="F87" t="n">
         <v>353300</v>
@@ -2192,16 +2192,16 @@
         <v>44601</v>
       </c>
       <c r="B89" t="n">
-        <v>157.5155792236328</v>
+        <v>157.5155944824219</v>
       </c>
       <c r="C89" t="n">
-        <v>159.7996788160072</v>
+        <v>159.7996942960607</v>
       </c>
       <c r="D89" t="n">
-        <v>151.4275469020544</v>
+        <v>151.4275615710859</v>
       </c>
       <c r="E89" t="n">
-        <v>153.7380139150282</v>
+        <v>153.7380288078784</v>
       </c>
       <c r="F89" t="n">
         <v>1361639</v>
@@ -2232,16 +2232,16 @@
         <v>44603</v>
       </c>
       <c r="B91" t="n">
-        <v>156.0045623779297</v>
+        <v>156.0045471191406</v>
       </c>
       <c r="C91" t="n">
-        <v>160.1510975579418</v>
+        <v>160.1510818935806</v>
       </c>
       <c r="D91" t="n">
-        <v>151.3309200426192</v>
+        <v>151.3309052409586</v>
       </c>
       <c r="E91" t="n">
-        <v>152.3763407441961</v>
+        <v>152.376325840283</v>
       </c>
       <c r="F91" t="n">
         <v>740597</v>
@@ -2252,16 +2252,16 @@
         <v>44606</v>
       </c>
       <c r="B92" t="n">
-        <v>152.9473876953125</v>
+        <v>152.9473724365234</v>
       </c>
       <c r="C92" t="n">
-        <v>157.9197048137788</v>
+        <v>157.9196890589268</v>
       </c>
       <c r="D92" t="n">
-        <v>152.0688846376827</v>
+        <v>152.0688694665374</v>
       </c>
       <c r="E92" t="n">
-        <v>156.0045745824943</v>
+        <v>156.0045590187052</v>
       </c>
       <c r="F92" t="n">
         <v>409040</v>
@@ -2312,16 +2312,16 @@
         <v>44609</v>
       </c>
       <c r="B95" t="n">
-        <v>156.6282958984375</v>
+        <v>156.6282806396484</v>
       </c>
       <c r="C95" t="n">
-        <v>161.1877286693031</v>
+        <v>161.1877129663323</v>
       </c>
       <c r="D95" t="n">
-        <v>156.1626903751017</v>
+        <v>156.1626751616721</v>
       </c>
       <c r="E95" t="n">
-        <v>160.8011851997657</v>
+        <v>160.8011695344521</v>
       </c>
       <c r="F95" t="n">
         <v>315564</v>
@@ -2332,16 +2332,16 @@
         <v>44610</v>
       </c>
       <c r="B96" t="n">
-        <v>155.4950408935547</v>
+        <v>155.4950256347656</v>
       </c>
       <c r="C96" t="n">
-        <v>159.5361603126324</v>
+        <v>159.5361446572868</v>
       </c>
       <c r="D96" t="n">
-        <v>153.4744811840158</v>
+        <v>153.4744661235051</v>
       </c>
       <c r="E96" t="n">
-        <v>156.988493407599</v>
+        <v>156.9884780022568</v>
       </c>
       <c r="F96" t="n">
         <v>742998</v>
@@ -2372,16 +2372,16 @@
         <v>44614</v>
       </c>
       <c r="B98" t="n">
-        <v>150.3557891845703</v>
+        <v>150.3557739257812</v>
       </c>
       <c r="C98" t="n">
-        <v>155.0557857870995</v>
+        <v>155.0557700513334</v>
       </c>
       <c r="D98" t="n">
-        <v>149.6793514986648</v>
+        <v>149.6793363085237</v>
       </c>
       <c r="E98" t="n">
-        <v>150.5315005156085</v>
+        <v>150.5314852389875</v>
       </c>
       <c r="F98" t="n">
         <v>352471</v>
@@ -2392,16 +2392,16 @@
         <v>44615</v>
       </c>
       <c r="B99" t="n">
-        <v>147.2722320556641</v>
+        <v>147.2722473144531</v>
       </c>
       <c r="C99" t="n">
-        <v>153.5623163117172</v>
+        <v>153.5623322222181</v>
       </c>
       <c r="D99" t="n">
-        <v>146.9647506652708</v>
+        <v>146.9647658922019</v>
       </c>
       <c r="E99" t="n">
-        <v>150.3557725436555</v>
+        <v>150.3557881219284</v>
       </c>
       <c r="F99" t="n">
         <v>373832</v>
@@ -2412,16 +2412,16 @@
         <v>44616</v>
       </c>
       <c r="B100" t="n">
-        <v>148.1068115234375</v>
+        <v>148.1067962646484</v>
       </c>
       <c r="C100" t="n">
-        <v>148.1068115234375</v>
+        <v>148.1067962646484</v>
       </c>
       <c r="D100" t="n">
-        <v>139.2427198314664</v>
+        <v>139.2427054859054</v>
       </c>
       <c r="E100" t="n">
-        <v>143.327753253209</v>
+        <v>143.3277384867851</v>
       </c>
       <c r="F100" t="n">
         <v>704723</v>
@@ -2472,16 +2472,16 @@
         <v>44623</v>
       </c>
       <c r="B103" t="n">
-        <v>136.16796875</v>
+        <v>136.1679534912109</v>
       </c>
       <c r="C103" t="n">
-        <v>143.3365566445935</v>
+        <v>143.3365405825027</v>
       </c>
       <c r="D103" t="n">
-        <v>135.4915176680011</v>
+        <v>135.4915024850142</v>
       </c>
       <c r="E103" t="n">
-        <v>142.5107616570688</v>
+        <v>142.5107456875154</v>
       </c>
       <c r="F103" t="n">
         <v>801826</v>
@@ -2492,16 +2492,16 @@
         <v>44624</v>
       </c>
       <c r="B104" t="n">
-        <v>129.4035034179688</v>
+        <v>129.4034729003906</v>
       </c>
       <c r="C104" t="n">
-        <v>139.216380989505</v>
+        <v>139.2163481577294</v>
       </c>
       <c r="D104" t="n">
-        <v>128.5864886016308</v>
+        <v>128.5864582767315</v>
       </c>
       <c r="E104" t="n">
-        <v>134.2440504527695</v>
+        <v>134.2440187936321</v>
       </c>
       <c r="F104" t="n">
         <v>615045</v>
@@ -2512,16 +2512,16 @@
         <v>44627</v>
       </c>
       <c r="B105" t="n">
-        <v>117.0780944824219</v>
+        <v>117.0781097412109</v>
       </c>
       <c r="C105" t="n">
-        <v>130.2644192270299</v>
+        <v>130.2644362043928</v>
       </c>
       <c r="D105" t="n">
-        <v>117.0780944824219</v>
+        <v>117.0781097412109</v>
       </c>
       <c r="E105" t="n">
-        <v>129.5791879833061</v>
+        <v>129.5792048713628</v>
       </c>
       <c r="F105" t="n">
         <v>1053703</v>
@@ -2532,16 +2532,16 @@
         <v>44628</v>
       </c>
       <c r="B106" t="n">
-        <v>124.4399490356445</v>
+        <v>124.4399566650391</v>
       </c>
       <c r="C106" t="n">
-        <v>125.6083596759917</v>
+        <v>125.6083673770213</v>
       </c>
       <c r="D106" t="n">
-        <v>115.8657642749562</v>
+        <v>115.8657713786687</v>
       </c>
       <c r="E106" t="n">
-        <v>118.3431492578484</v>
+        <v>118.3431565134491</v>
       </c>
       <c r="F106" t="n">
         <v>713320</v>
@@ -2552,16 +2552,16 @@
         <v>44629</v>
       </c>
       <c r="B107" t="n">
-        <v>138.6804962158203</v>
+        <v>138.6804809570312</v>
       </c>
       <c r="C107" t="n">
-        <v>138.6804962158203</v>
+        <v>138.6804809570312</v>
       </c>
       <c r="D107" t="n">
-        <v>124.6595812143682</v>
+        <v>124.6595674982775</v>
       </c>
       <c r="E107" t="n">
-        <v>124.7474368839902</v>
+        <v>124.7474231582329</v>
       </c>
       <c r="F107" t="n">
         <v>891534</v>
@@ -2572,16 +2572,16 @@
         <v>44630</v>
       </c>
       <c r="B108" t="n">
-        <v>135.7814331054688</v>
+        <v>135.7814025878906</v>
       </c>
       <c r="C108" t="n">
-        <v>139.1636753056343</v>
+        <v>139.1636440278797</v>
       </c>
       <c r="D108" t="n">
-        <v>133.2425597553211</v>
+        <v>133.2425298083679</v>
       </c>
       <c r="E108" t="n">
-        <v>137.4857312154787</v>
+        <v>137.4857003148507</v>
       </c>
       <c r="F108" t="n">
         <v>543810</v>
@@ -2592,16 +2592,16 @@
         <v>44631</v>
       </c>
       <c r="B109" t="n">
-        <v>131.6173248291016</v>
+        <v>131.6173095703125</v>
       </c>
       <c r="C109" t="n">
-        <v>138.7156172153465</v>
+        <v>138.7156011336312</v>
       </c>
       <c r="D109" t="n">
-        <v>131.1341455020338</v>
+        <v>131.1341302992611</v>
       </c>
       <c r="E109" t="n">
-        <v>135.8077744536639</v>
+        <v>135.8077587090635</v>
       </c>
       <c r="F109" t="n">
         <v>422012</v>
@@ -2652,16 +2652,16 @@
         <v>44636</v>
       </c>
       <c r="B112" t="n">
-        <v>139.4887084960938</v>
+        <v>139.4886932373047</v>
       </c>
       <c r="C112" t="n">
-        <v>142.3438433121762</v>
+        <v>142.3438277410615</v>
       </c>
       <c r="D112" t="n">
-        <v>132.6539560702938</v>
+        <v>132.6539415591642</v>
       </c>
       <c r="E112" t="n">
-        <v>132.6539560702938</v>
+        <v>132.6539415591642</v>
       </c>
       <c r="F112" t="n">
         <v>861619</v>
@@ -2712,16 +2712,16 @@
         <v>44641</v>
       </c>
       <c r="B115" t="n">
-        <v>139.7698364257812</v>
+        <v>139.7698211669922</v>
       </c>
       <c r="C115" t="n">
-        <v>143.0642227644949</v>
+        <v>143.0642071460549</v>
       </c>
       <c r="D115" t="n">
-        <v>138.4169342626098</v>
+        <v>138.4169191515182</v>
       </c>
       <c r="E115" t="n">
-        <v>141.4829146409339</v>
+        <v>141.4828991951266</v>
       </c>
       <c r="F115" t="n">
         <v>351500</v>
@@ -2752,16 +2752,16 @@
         <v>44643</v>
       </c>
       <c r="B117" t="n">
-        <v>132.7418060302734</v>
+        <v>132.7418212890625</v>
       </c>
       <c r="C117" t="n">
-        <v>137.4417889441584</v>
+        <v>137.4418047432147</v>
       </c>
       <c r="D117" t="n">
-        <v>130.5719025909017</v>
+        <v>130.5719176002584</v>
       </c>
       <c r="E117" t="n">
-        <v>134.5075921995046</v>
+        <v>134.5076076612723</v>
       </c>
       <c r="F117" t="n">
         <v>1133860</v>
@@ -2772,16 +2772,16 @@
         <v>44644</v>
       </c>
       <c r="B118" t="n">
-        <v>136.2733764648438</v>
+        <v>136.2733612060547</v>
       </c>
       <c r="C118" t="n">
-        <v>137.2660891108588</v>
+        <v>137.2660737409138</v>
       </c>
       <c r="D118" t="n">
-        <v>132.4870308075925</v>
+        <v>132.4870159727677</v>
       </c>
       <c r="E118" t="n">
-        <v>133.2776915238059</v>
+        <v>133.2776766004494</v>
       </c>
       <c r="F118" t="n">
         <v>438667</v>
@@ -2792,16 +2792,16 @@
         <v>44645</v>
       </c>
       <c r="B119" t="n">
-        <v>133.9277648925781</v>
+        <v>133.9277801513672</v>
       </c>
       <c r="C119" t="n">
-        <v>140.0333573879609</v>
+        <v>140.0333733423783</v>
       </c>
       <c r="D119" t="n">
-        <v>133.4182316002086</v>
+        <v>133.418246800945</v>
       </c>
       <c r="E119" t="n">
-        <v>135.307020884751</v>
+        <v>135.3070363006828</v>
       </c>
       <c r="F119" t="n">
         <v>403765</v>
@@ -2812,16 +2812,16 @@
         <v>44648</v>
       </c>
       <c r="B120" t="n">
-        <v>134.9380798339844</v>
+        <v>134.9380645751953</v>
       </c>
       <c r="C120" t="n">
-        <v>139.8489088843792</v>
+        <v>139.8488930702739</v>
       </c>
       <c r="D120" t="n">
-        <v>132.478268503776</v>
+        <v>132.4782535231423</v>
       </c>
       <c r="E120" t="n">
-        <v>134.7623684922676</v>
+        <v>134.762353253348</v>
       </c>
       <c r="F120" t="n">
         <v>527873</v>
@@ -2832,16 +2832,16 @@
         <v>44649</v>
       </c>
       <c r="B121" t="n">
-        <v>139.5765686035156</v>
+        <v>139.5765533447266</v>
       </c>
       <c r="C121" t="n">
-        <v>140.4638518565375</v>
+        <v>140.4638365007489</v>
       </c>
       <c r="D121" t="n">
-        <v>135.1576993429566</v>
+        <v>135.1576845672471</v>
       </c>
       <c r="E121" t="n">
-        <v>137.9249785831454</v>
+        <v>137.9249635049115</v>
       </c>
       <c r="F121" t="n">
         <v>830631</v>
@@ -2892,16 +2892,16 @@
         <v>44652</v>
       </c>
       <c r="B124" t="n">
-        <v>127.382926940918</v>
+        <v>127.382942199707</v>
       </c>
       <c r="C124" t="n">
-        <v>129.1047986101335</v>
+        <v>129.10481407518</v>
       </c>
       <c r="D124" t="n">
-        <v>124.615648027951</v>
+        <v>124.6156629552567</v>
       </c>
       <c r="E124" t="n">
-        <v>126.5044239964978</v>
+        <v>126.5044391500539</v>
       </c>
       <c r="F124" t="n">
         <v>526406</v>
@@ -2932,16 +2932,16 @@
         <v>44656</v>
       </c>
       <c r="B126" t="n">
-        <v>128.0769500732422</v>
+        <v>128.0769348144531</v>
       </c>
       <c r="C126" t="n">
-        <v>130.1590113571142</v>
+        <v>130.1589958502732</v>
       </c>
       <c r="D126" t="n">
-        <v>125.6347127369603</v>
+        <v>125.6346977691337</v>
       </c>
       <c r="E126" t="n">
-        <v>128.2614416065824</v>
+        <v>128.2614263258134</v>
       </c>
       <c r="F126" t="n">
         <v>767000</v>
@@ -2952,16 +2952,16 @@
         <v>44657</v>
       </c>
       <c r="B127" t="n">
-        <v>125.0197677612305</v>
+        <v>125.0197601318359</v>
       </c>
       <c r="C127" t="n">
-        <v>127.3829431267791</v>
+        <v>127.3829353531706</v>
       </c>
       <c r="D127" t="n">
-        <v>122.6917400246637</v>
+        <v>122.6917325373382</v>
       </c>
       <c r="E127" t="n">
-        <v>127.1720975675664</v>
+        <v>127.1720898068249</v>
       </c>
       <c r="F127" t="n">
         <v>694358</v>
@@ -2972,16 +2972,16 @@
         <v>44658</v>
       </c>
       <c r="B128" t="n">
-        <v>126.9524536132812</v>
+        <v>126.9524612426758</v>
       </c>
       <c r="C128" t="n">
-        <v>128.6040434115682</v>
+        <v>128.6040511402175</v>
       </c>
       <c r="D128" t="n">
-        <v>122.9991904275108</v>
+        <v>122.9991978193282</v>
       </c>
       <c r="E128" t="n">
-        <v>124.7561962878532</v>
+        <v>124.7562037852604</v>
       </c>
       <c r="F128" t="n">
         <v>544395</v>
@@ -2992,16 +2992,16 @@
         <v>44659</v>
       </c>
       <c r="B129" t="n">
-        <v>123.5790252685547</v>
+        <v>123.5790023803711</v>
       </c>
       <c r="C129" t="n">
-        <v>128.0857503079586</v>
+        <v>128.0857265850804</v>
       </c>
       <c r="D129" t="n">
-        <v>123.5790252685547</v>
+        <v>123.5790023803711</v>
       </c>
       <c r="E129" t="n">
-        <v>126.7943497224557</v>
+        <v>126.7943262387589</v>
       </c>
       <c r="F129" t="n">
         <v>403536</v>
@@ -3092,16 +3092,16 @@
         <v>44669</v>
       </c>
       <c r="B134" t="n">
-        <v>112.4483795166016</v>
+        <v>112.4483871459961</v>
       </c>
       <c r="C134" t="n">
-        <v>115.1365964446377</v>
+        <v>115.1366042564223</v>
       </c>
       <c r="D134" t="n">
-        <v>112.0530558633418</v>
+        <v>112.0530634659144</v>
       </c>
       <c r="E134" t="n">
-        <v>114.2053854465485</v>
+        <v>114.2053931951523</v>
       </c>
       <c r="F134" t="n">
         <v>589431</v>
@@ -3112,16 +3112,16 @@
         <v>44670</v>
       </c>
       <c r="B135" t="n">
-        <v>115.2683792114258</v>
+        <v>115.2683868408203</v>
       </c>
       <c r="C135" t="n">
-        <v>116.3137864730974</v>
+        <v>116.3137941716854</v>
       </c>
       <c r="D135" t="n">
-        <v>111.1306243741263</v>
+        <v>111.1306317296507</v>
       </c>
       <c r="E135" t="n">
-        <v>112.5362344712496</v>
+        <v>112.5362419198087</v>
       </c>
       <c r="F135" t="n">
         <v>794893</v>
@@ -3132,16 +3132,16 @@
         <v>44671</v>
       </c>
       <c r="B136" t="n">
-        <v>113.9945526123047</v>
+        <v>113.9945449829102</v>
       </c>
       <c r="C136" t="n">
-        <v>116.5597799472992</v>
+        <v>116.5597721462199</v>
       </c>
       <c r="D136" t="n">
-        <v>112.9754992470936</v>
+        <v>112.975491685902</v>
       </c>
       <c r="E136" t="n">
-        <v>114.5128796071169</v>
+        <v>114.5128719430319</v>
       </c>
       <c r="F136" t="n">
         <v>232622</v>
@@ -3152,16 +3152,16 @@
         <v>44673</v>
       </c>
       <c r="B137" t="n">
-        <v>107.7923202514648</v>
+        <v>107.7923126220703</v>
       </c>
       <c r="C137" t="n">
-        <v>111.5698860017955</v>
+        <v>111.56987810503</v>
       </c>
       <c r="D137" t="n">
-        <v>106.2988677654902</v>
+        <v>106.2988602418002</v>
       </c>
       <c r="E137" t="n">
-        <v>111.5698860017955</v>
+        <v>111.56987810503</v>
       </c>
       <c r="F137" t="n">
         <v>509466</v>
@@ -3172,16 +3172,16 @@
         <v>44676</v>
       </c>
       <c r="B138" t="n">
-        <v>111.5347442626953</v>
+        <v>111.5347366333008</v>
       </c>
       <c r="C138" t="n">
-        <v>111.8334387791802</v>
+        <v>111.8334311293538</v>
       </c>
       <c r="D138" t="n">
-        <v>105.9474644367544</v>
+        <v>105.9474571895508</v>
       </c>
       <c r="E138" t="n">
-        <v>106.2988669904352</v>
+        <v>106.2988597191943</v>
       </c>
       <c r="F138" t="n">
         <v>607459</v>
@@ -3192,16 +3192,16 @@
         <v>44677</v>
       </c>
       <c r="B139" t="n">
-        <v>107.4057769775391</v>
+        <v>107.4057693481445</v>
       </c>
       <c r="C139" t="n">
-        <v>112.6943620057829</v>
+        <v>112.6943540007223</v>
       </c>
       <c r="D139" t="n">
-        <v>106.342789168451</v>
+        <v>106.342781614564</v>
       </c>
       <c r="E139" t="n">
-        <v>109.9270762585565</v>
+        <v>109.9270684500656</v>
       </c>
       <c r="F139" t="n">
         <v>615417</v>
@@ -3212,16 +3212,16 @@
         <v>44678</v>
       </c>
       <c r="B140" t="n">
-        <v>104.541862487793</v>
+        <v>104.5418548583984</v>
       </c>
       <c r="C140" t="n">
-        <v>110.4717580490753</v>
+        <v>110.471749986921</v>
       </c>
       <c r="D140" t="n">
-        <v>104.0938240575889</v>
+        <v>104.0938164608919</v>
       </c>
       <c r="E140" t="n">
-        <v>109.5493271696751</v>
+        <v>109.5493191748392</v>
       </c>
       <c r="F140" t="n">
         <v>1036983</v>
@@ -3232,16 +3232,16 @@
         <v>44679</v>
       </c>
       <c r="B141" t="n">
-        <v>108.4951171875</v>
+        <v>108.4951248168945</v>
       </c>
       <c r="C141" t="n">
-        <v>109.5844589975561</v>
+        <v>109.5844667035533</v>
       </c>
       <c r="D141" t="n">
-        <v>104.0235402711972</v>
+        <v>104.0235475861498</v>
       </c>
       <c r="E141" t="n">
-        <v>104.5418538081984</v>
+        <v>104.5418611595988</v>
       </c>
       <c r="F141" t="n">
         <v>799584</v>
@@ -3272,16 +3272,16 @@
         <v>44683</v>
       </c>
       <c r="B143" t="n">
-        <v>107.168586730957</v>
+        <v>107.1685791015625</v>
       </c>
       <c r="C143" t="n">
-        <v>108.556623178466</v>
+        <v>108.5566154502563</v>
       </c>
       <c r="D143" t="n">
-        <v>104.4628023919814</v>
+        <v>104.4627949552132</v>
       </c>
       <c r="E143" t="n">
-        <v>107.1861605455792</v>
+        <v>107.1861529149336</v>
       </c>
       <c r="F143" t="n">
         <v>497573</v>
@@ -3292,16 +3292,16 @@
         <v>44684</v>
       </c>
       <c r="B144" t="n">
-        <v>102.7848587036133</v>
+        <v>102.7848510742188</v>
       </c>
       <c r="C144" t="n">
-        <v>107.1773740328275</v>
+        <v>107.1773660773905</v>
       </c>
       <c r="D144" t="n">
-        <v>101.809719764332</v>
+        <v>101.8097122073189</v>
       </c>
       <c r="E144" t="n">
-        <v>107.1422331059002</v>
+        <v>107.1422251530716</v>
       </c>
       <c r="F144" t="n">
         <v>541792</v>
@@ -3312,16 +3312,16 @@
         <v>44685</v>
       </c>
       <c r="B145" t="n">
-        <v>94.52692413330078</v>
+        <v>94.52691650390625</v>
       </c>
       <c r="C145" t="n">
-        <v>100.4128984212591</v>
+        <v>100.4128903167997</v>
       </c>
       <c r="D145" t="n">
-        <v>84.54712923481648</v>
+        <v>84.54712241090455</v>
       </c>
       <c r="E145" t="n">
-        <v>100.4128984212591</v>
+        <v>100.4128903167997</v>
       </c>
       <c r="F145" t="n">
         <v>3193940</v>
@@ -3372,16 +3372,16 @@
         <v>44690</v>
       </c>
       <c r="B148" t="n">
-        <v>85.64525604248047</v>
+        <v>85.64524841308594</v>
       </c>
       <c r="C148" t="n">
-        <v>90.7405761501812</v>
+        <v>90.7405680668887</v>
       </c>
       <c r="D148" t="n">
-        <v>83.37872338445261</v>
+        <v>83.37871595696386</v>
       </c>
       <c r="E148" t="n">
-        <v>88.64095450536544</v>
+        <v>88.64094660911006</v>
       </c>
       <c r="F148" t="n">
         <v>1267170</v>
@@ -3392,16 +3392,16 @@
         <v>44691</v>
       </c>
       <c r="B149" t="n">
-        <v>84.51198577880859</v>
+        <v>84.51197814941406</v>
       </c>
       <c r="C149" t="n">
-        <v>89.03627756179158</v>
+        <v>89.03626952396259</v>
       </c>
       <c r="D149" t="n">
-        <v>83.46657176820631</v>
+        <v>83.46656423318744</v>
       </c>
       <c r="E149" t="n">
-        <v>85.83852718329263</v>
+        <v>85.83851943414338</v>
       </c>
       <c r="F149" t="n">
         <v>595901</v>
@@ -3412,16 +3412,16 @@
         <v>44692</v>
       </c>
       <c r="B150" t="n">
-        <v>81.85891723632812</v>
+        <v>81.85890960693359</v>
       </c>
       <c r="C150" t="n">
-        <v>86.58526139233636</v>
+        <v>86.58525332243828</v>
       </c>
       <c r="D150" t="n">
-        <v>81.52508847891562</v>
+        <v>81.52508088063452</v>
       </c>
       <c r="E150" t="n">
-        <v>84.51199358800345</v>
+        <v>84.51198571133756</v>
       </c>
       <c r="F150" t="n">
         <v>624829</v>
@@ -3492,16 +3492,16 @@
         <v>44698</v>
       </c>
       <c r="B154" t="n">
-        <v>86.98058319091797</v>
+        <v>86.98057556152344</v>
       </c>
       <c r="C154" t="n">
-        <v>88.24562294284463</v>
+        <v>88.24561520248869</v>
       </c>
       <c r="D154" t="n">
-        <v>84.59105397819015</v>
+        <v>84.59104655839022</v>
       </c>
       <c r="E154" t="n">
-        <v>85.39048821633966</v>
+        <v>85.39048072641835</v>
       </c>
       <c r="F154" t="n">
         <v>1257850</v>
@@ -3532,16 +3532,16 @@
         <v>44700</v>
       </c>
       <c r="B156" t="n">
-        <v>89.60730743408203</v>
+        <v>89.6072998046875</v>
       </c>
       <c r="C156" t="n">
-        <v>90.45066952328574</v>
+        <v>90.45066182208521</v>
       </c>
       <c r="D156" t="n">
-        <v>82.86040401800625</v>
+        <v>82.86039696306027</v>
       </c>
       <c r="E156" t="n">
-        <v>83.85311001101303</v>
+        <v>83.85310287154553</v>
       </c>
       <c r="F156" t="n">
         <v>889253</v>
@@ -3572,16 +3572,16 @@
         <v>44704</v>
       </c>
       <c r="B158" t="n">
-        <v>91.02169036865234</v>
+        <v>91.02169799804688</v>
       </c>
       <c r="C158" t="n">
-        <v>92.67327348694673</v>
+        <v>92.67328125477616</v>
       </c>
       <c r="D158" t="n">
-        <v>90.09925959845417</v>
+        <v>90.09926715053099</v>
       </c>
       <c r="E158" t="n">
-        <v>90.31010513032238</v>
+        <v>90.31011270007218</v>
       </c>
       <c r="F158" t="n">
         <v>925415</v>
@@ -3592,16 +3592,16 @@
         <v>44705</v>
       </c>
       <c r="B159" t="n">
-        <v>87.67460632324219</v>
+        <v>87.67459869384766</v>
       </c>
       <c r="C159" t="n">
-        <v>90.02020783815051</v>
+        <v>90.02020000464306</v>
       </c>
       <c r="D159" t="n">
-        <v>85.55741077362453</v>
+        <v>85.55740332846713</v>
       </c>
       <c r="E159" t="n">
-        <v>88.43011947599447</v>
+        <v>88.43011178085561</v>
       </c>
       <c r="F159" t="n">
         <v>569845</v>
@@ -3612,16 +3612,16 @@
         <v>44706</v>
       </c>
       <c r="B160" t="n">
-        <v>89.92356872558594</v>
+        <v>89.92357635498047</v>
       </c>
       <c r="C160" t="n">
-        <v>90.73178988696996</v>
+        <v>90.73179758493647</v>
       </c>
       <c r="D160" t="n">
-        <v>85.75067942410486</v>
+        <v>85.75068669945851</v>
       </c>
       <c r="E160" t="n">
-        <v>86.97179807297417</v>
+        <v>86.97180545193132</v>
       </c>
       <c r="F160" t="n">
         <v>958832</v>
@@ -3632,16 +3632,16 @@
         <v>44707</v>
       </c>
       <c r="B161" t="n">
-        <v>94.81683349609375</v>
+        <v>94.81682586669922</v>
       </c>
       <c r="C161" t="n">
-        <v>96.2663648544297</v>
+        <v>96.26635710839928</v>
       </c>
       <c r="D161" t="n">
-        <v>89.0099278581001</v>
+        <v>89.00992069595566</v>
       </c>
       <c r="E161" t="n">
-        <v>89.41403845272137</v>
+        <v>89.41403125806036</v>
       </c>
       <c r="F161" t="n">
         <v>700096</v>
@@ -3652,16 +3652,16 @@
         <v>44708</v>
       </c>
       <c r="B162" t="n">
-        <v>96.65290069580078</v>
+        <v>96.65289306640625</v>
       </c>
       <c r="C162" t="n">
-        <v>97.42598765404017</v>
+        <v>97.42597996362124</v>
       </c>
       <c r="D162" t="n">
-        <v>93.57814008175724</v>
+        <v>93.57813269507206</v>
       </c>
       <c r="E162" t="n">
-        <v>94.5708527981426</v>
+        <v>94.57084533309663</v>
       </c>
       <c r="F162" t="n">
         <v>410015</v>
@@ -3692,16 +3692,16 @@
         <v>44712</v>
       </c>
       <c r="B164" t="n">
-        <v>93.95589447021484</v>
+        <v>93.95588684082031</v>
       </c>
       <c r="C164" t="n">
-        <v>98.17271160959186</v>
+        <v>98.17270363778388</v>
       </c>
       <c r="D164" t="n">
-        <v>93.12131928963522</v>
+        <v>93.12131172800976</v>
       </c>
       <c r="E164" t="n">
-        <v>96.72318029902813</v>
+        <v>96.72317244492481</v>
       </c>
       <c r="F164" t="n">
         <v>435642</v>
@@ -3712,16 +3712,16 @@
         <v>44713</v>
       </c>
       <c r="B165" t="n">
-        <v>92.17253875732422</v>
+        <v>92.17253112792969</v>
       </c>
       <c r="C165" t="n">
-        <v>96.28393331547606</v>
+        <v>96.28392534576922</v>
       </c>
       <c r="D165" t="n">
-        <v>91.18861962704793</v>
+        <v>91.18861207909531</v>
       </c>
       <c r="E165" t="n">
-        <v>95.12430955304588</v>
+        <v>95.12430167932452</v>
       </c>
       <c r="F165" t="n">
         <v>372179</v>
@@ -3732,16 +3732,16 @@
         <v>44714</v>
       </c>
       <c r="B166" t="n">
-        <v>97.39963531494141</v>
+        <v>97.39962768554688</v>
       </c>
       <c r="C166" t="n">
-        <v>97.77739189356407</v>
+        <v>97.77738423457956</v>
       </c>
       <c r="D166" t="n">
-        <v>91.38188407601926</v>
+        <v>91.3818769180002</v>
       </c>
       <c r="E166" t="n">
-        <v>91.38188407601926</v>
+        <v>91.3818769180002</v>
       </c>
       <c r="F166" t="n">
         <v>432233</v>
@@ -3772,16 +3772,16 @@
         <v>44718</v>
       </c>
       <c r="B168" t="n">
-        <v>94.98375701904297</v>
+        <v>94.98374176025391</v>
       </c>
       <c r="C168" t="n">
-        <v>97.48748949863837</v>
+        <v>97.48747383763394</v>
       </c>
       <c r="D168" t="n">
-        <v>94.69384938918279</v>
+        <v>94.69383417696631</v>
       </c>
       <c r="E168" t="n">
-        <v>95.18580897746912</v>
+        <v>95.18579368622116</v>
       </c>
       <c r="F168" t="n">
         <v>540320</v>
@@ -3812,16 +3812,16 @@
         <v>44720</v>
       </c>
       <c r="B170" t="n">
-        <v>97.0745849609375</v>
+        <v>97.07457733154297</v>
       </c>
       <c r="C170" t="n">
-        <v>100.0439227939208</v>
+        <v>100.0439149311568</v>
       </c>
       <c r="D170" t="n">
-        <v>97.0745849609375</v>
+        <v>97.07457733154297</v>
       </c>
       <c r="E170" t="n">
-        <v>98.75252896793423</v>
+        <v>98.75252120666485</v>
       </c>
       <c r="F170" t="n">
         <v>671896</v>
@@ -3892,16 +3892,16 @@
         <v>44726</v>
       </c>
       <c r="B174" t="n">
-        <v>85.73310089111328</v>
+        <v>85.73310852050781</v>
       </c>
       <c r="C174" t="n">
-        <v>86.47104686486708</v>
+        <v>86.47105455993147</v>
       </c>
       <c r="D174" t="n">
-        <v>84.07273082822437</v>
+        <v>84.07273830986246</v>
       </c>
       <c r="E174" t="n">
-        <v>86.10207722921302</v>
+        <v>86.10208489144279</v>
       </c>
       <c r="F174" t="n">
         <v>502449</v>
@@ -3912,16 +3912,16 @@
         <v>44727</v>
       </c>
       <c r="B175" t="n">
-        <v>86.62917327880859</v>
+        <v>86.62918090820312</v>
       </c>
       <c r="C175" t="n">
-        <v>88.47402806609041</v>
+        <v>88.47403585796052</v>
       </c>
       <c r="D175" t="n">
-        <v>85.29384509010026</v>
+        <v>85.29385260189301</v>
       </c>
       <c r="E175" t="n">
-        <v>86.10207286850599</v>
+        <v>86.102080451479</v>
       </c>
       <c r="F175" t="n">
         <v>817586</v>
@@ -3932,16 +3932,16 @@
         <v>44729</v>
       </c>
       <c r="B176" t="n">
-        <v>84.51198577880859</v>
+        <v>84.51197814941406</v>
       </c>
       <c r="C176" t="n">
-        <v>86.43590949039935</v>
+        <v>86.43590168732089</v>
       </c>
       <c r="D176" t="n">
-        <v>83.73011864630146</v>
+        <v>83.73011108749068</v>
       </c>
       <c r="E176" t="n">
-        <v>84.07273427953736</v>
+        <v>84.07272668979664</v>
       </c>
       <c r="F176" t="n">
         <v>418487</v>
@@ -3952,16 +3952,16 @@
         <v>44732</v>
       </c>
       <c r="B177" t="n">
-        <v>83.89703369140625</v>
+        <v>83.89702606201172</v>
       </c>
       <c r="C177" t="n">
-        <v>85.54861686323618</v>
+        <v>85.54860908365065</v>
       </c>
       <c r="D177" t="n">
-        <v>82.53535140601245</v>
+        <v>82.53534390044604</v>
       </c>
       <c r="E177" t="n">
-        <v>84.51198308984139</v>
+        <v>84.51197540452485</v>
       </c>
       <c r="F177" t="n">
         <v>143101</v>
@@ -3972,16 +3972,16 @@
         <v>44733</v>
       </c>
       <c r="B178" t="n">
-        <v>85.99666595458984</v>
+        <v>85.99665069580078</v>
       </c>
       <c r="C178" t="n">
-        <v>87.58675438441436</v>
+        <v>87.5867388434885</v>
       </c>
       <c r="D178" t="n">
-        <v>85.37292957215897</v>
+        <v>85.37291442404235</v>
       </c>
       <c r="E178" t="n">
-        <v>85.57498822961099</v>
+        <v>85.57497304564218</v>
       </c>
       <c r="F178" t="n">
         <v>532289</v>
@@ -3992,16 +3992,16 @@
         <v>44734</v>
       </c>
       <c r="B179" t="n">
-        <v>86.53254699707031</v>
+        <v>86.53253936767578</v>
       </c>
       <c r="C179" t="n">
-        <v>87.41105001226899</v>
+        <v>87.41104230541869</v>
       </c>
       <c r="D179" t="n">
-        <v>84.59105613777476</v>
+        <v>84.59104867955743</v>
       </c>
       <c r="E179" t="n">
-        <v>84.95123888873424</v>
+        <v>84.95123139876036</v>
       </c>
       <c r="F179" t="n">
         <v>352268</v>
@@ -4052,16 +4052,16 @@
         <v>44739</v>
       </c>
       <c r="B182" t="n">
-        <v>91.08319854736328</v>
+        <v>91.08319091796875</v>
       </c>
       <c r="C182" t="n">
-        <v>92.33067129792501</v>
+        <v>92.33066356403852</v>
       </c>
       <c r="D182" t="n">
-        <v>88.45647624527705</v>
+        <v>88.45646883590445</v>
       </c>
       <c r="E182" t="n">
-        <v>91.46095513548509</v>
+        <v>91.46094747444857</v>
       </c>
       <c r="F182" t="n">
         <v>388597</v>
@@ -4072,16 +4072,16 @@
         <v>44740</v>
       </c>
       <c r="B183" t="n">
-        <v>85.97908782958984</v>
+        <v>85.97909545898438</v>
       </c>
       <c r="C183" t="n">
-        <v>92.55907317852221</v>
+        <v>92.55908139179482</v>
       </c>
       <c r="D183" t="n">
-        <v>85.97908782958984</v>
+        <v>85.97909545898438</v>
       </c>
       <c r="E183" t="n">
-        <v>91.55758033191366</v>
+        <v>91.55758845631833</v>
       </c>
       <c r="F183" t="n">
         <v>484787</v>
@@ -4132,16 +4132,16 @@
         <v>44743</v>
       </c>
       <c r="B186" t="n">
-        <v>83.40507507324219</v>
+        <v>83.40506744384766</v>
       </c>
       <c r="C186" t="n">
-        <v>85.39048698245399</v>
+        <v>85.39047917144593</v>
       </c>
       <c r="D186" t="n">
-        <v>81.92918979861589</v>
+        <v>81.92918230422647</v>
       </c>
       <c r="E186" t="n">
-        <v>82.6232079571698</v>
+        <v>82.62320039929577</v>
       </c>
       <c r="F186" t="n">
         <v>500037</v>
@@ -4152,16 +4152,16 @@
         <v>44746</v>
       </c>
       <c r="B187" t="n">
-        <v>82.66713714599609</v>
+        <v>82.66712951660156</v>
       </c>
       <c r="C187" t="n">
-        <v>84.16059637922834</v>
+        <v>84.16058861200165</v>
       </c>
       <c r="D187" t="n">
-        <v>82.21909870578178</v>
+        <v>82.21909111773695</v>
       </c>
       <c r="E187" t="n">
-        <v>82.59685529214944</v>
+        <v>82.59684766924126</v>
       </c>
       <c r="F187" t="n">
         <v>102674</v>
@@ -4172,16 +4172,16 @@
         <v>44747</v>
       </c>
       <c r="B188" t="n">
-        <v>88.54431915283203</v>
+        <v>88.5443115234375</v>
       </c>
       <c r="C188" t="n">
-        <v>88.54431915283203</v>
+        <v>88.5443115234375</v>
       </c>
       <c r="D188" t="n">
-        <v>80.36545827722691</v>
+        <v>80.36545135256145</v>
       </c>
       <c r="E188" t="n">
-        <v>82.56171580149862</v>
+        <v>82.5617086875933</v>
       </c>
       <c r="F188" t="n">
         <v>886458</v>
@@ -4272,16 +4272,16 @@
         <v>44754</v>
       </c>
       <c r="B193" t="n">
-        <v>86.32170867919922</v>
+        <v>86.32169342041016</v>
       </c>
       <c r="C193" t="n">
-        <v>86.32170867919922</v>
+        <v>86.32169342041016</v>
       </c>
       <c r="D193" t="n">
-        <v>81.2966703290714</v>
+        <v>81.29665595854095</v>
       </c>
       <c r="E193" t="n">
-        <v>82.6232117668371</v>
+        <v>82.62319716181851</v>
       </c>
       <c r="F193" t="n">
         <v>730233</v>
@@ -4292,16 +4292,16 @@
         <v>44755</v>
       </c>
       <c r="B194" t="n">
-        <v>84.68769073486328</v>
+        <v>84.68768310546875</v>
       </c>
       <c r="C194" t="n">
-        <v>86.91908916427828</v>
+        <v>86.91908133386021</v>
       </c>
       <c r="D194" t="n">
-        <v>83.45778519155122</v>
+        <v>83.45777767295714</v>
       </c>
       <c r="E194" t="n">
-        <v>84.37142911794173</v>
+        <v>84.37142151703875</v>
       </c>
       <c r="F194" t="n">
         <v>1885043</v>
@@ -4332,16 +4332,16 @@
         <v>44757</v>
       </c>
       <c r="B196" t="n">
-        <v>82.85160827636719</v>
+        <v>82.85161590576172</v>
       </c>
       <c r="C196" t="n">
-        <v>84.72282378634415</v>
+        <v>84.72283158804966</v>
       </c>
       <c r="D196" t="n">
-        <v>81.20881210481942</v>
+        <v>81.20881958293697</v>
       </c>
       <c r="E196" t="n">
-        <v>82.27179983418721</v>
+        <v>82.27180741019004</v>
       </c>
       <c r="F196" t="n">
         <v>1850084</v>
@@ -4352,16 +4352,16 @@
         <v>44760</v>
       </c>
       <c r="B197" t="n">
-        <v>83.74769592285156</v>
+        <v>83.74768829345703</v>
       </c>
       <c r="C197" t="n">
-        <v>86.46226708342914</v>
+        <v>86.46225920673785</v>
       </c>
       <c r="D197" t="n">
-        <v>82.93947473935722</v>
+        <v>82.93946718359145</v>
       </c>
       <c r="E197" t="n">
-        <v>82.93947473935722</v>
+        <v>82.93946718359145</v>
       </c>
       <c r="F197" t="n">
         <v>494919</v>
@@ -4372,16 +4372,16 @@
         <v>44761</v>
       </c>
       <c r="B198" t="n">
-        <v>86.85758972167969</v>
+        <v>86.85759735107422</v>
       </c>
       <c r="C198" t="n">
-        <v>87.15627750971456</v>
+        <v>87.15628516534521</v>
       </c>
       <c r="D198" t="n">
-        <v>83.45778086715818</v>
+        <v>83.45778819792039</v>
       </c>
       <c r="E198" t="n">
-        <v>83.45778086715818</v>
+        <v>83.45778819792039</v>
       </c>
       <c r="F198" t="n">
         <v>493807</v>
@@ -4412,16 +4412,16 @@
         <v>44763</v>
       </c>
       <c r="B200" t="n">
-        <v>91.97047424316406</v>
+        <v>91.97048950195312</v>
       </c>
       <c r="C200" t="n">
-        <v>92.62056453720052</v>
+        <v>92.62057990384585</v>
       </c>
       <c r="D200" t="n">
-        <v>87.41104187399904</v>
+        <v>87.41105637633429</v>
       </c>
       <c r="E200" t="n">
-        <v>87.41104187399904</v>
+        <v>87.41105637633429</v>
       </c>
       <c r="F200" t="n">
         <v>453688</v>
@@ -4492,16 +4492,16 @@
         <v>44769</v>
       </c>
       <c r="B204" t="n">
-        <v>92.2603759765625</v>
+        <v>92.26038360595703</v>
       </c>
       <c r="C204" t="n">
-        <v>92.55907046197431</v>
+        <v>92.55907811606914</v>
       </c>
       <c r="D204" t="n">
-        <v>87.46375071978201</v>
+        <v>87.46375795252364</v>
       </c>
       <c r="E204" t="n">
-        <v>87.46375071978201</v>
+        <v>87.46375795252364</v>
       </c>
       <c r="F204" t="n">
         <v>673546</v>
@@ -4512,16 +4512,16 @@
         <v>44770</v>
       </c>
       <c r="B205" t="n">
-        <v>93.02468872070312</v>
+        <v>93.02468109130859</v>
       </c>
       <c r="C205" t="n">
-        <v>93.68356601735695</v>
+        <v>93.68355833392478</v>
       </c>
       <c r="D205" t="n">
-        <v>89.0274971066913</v>
+        <v>89.02748980512536</v>
       </c>
       <c r="E205" t="n">
-        <v>90.33647149513835</v>
+        <v>90.33646408621723</v>
       </c>
       <c r="F205" t="n">
         <v>529910</v>
@@ -4532,16 +4532,16 @@
         <v>44771</v>
       </c>
       <c r="B206" t="n">
-        <v>95.71291351318359</v>
+        <v>95.712890625</v>
       </c>
       <c r="C206" t="n">
-        <v>96.45964653705067</v>
+        <v>96.45962347029804</v>
       </c>
       <c r="D206" t="n">
-        <v>92.28675666167416</v>
+        <v>92.28673459280013</v>
       </c>
       <c r="E206" t="n">
-        <v>92.28675666167416</v>
+        <v>92.28673459280013</v>
       </c>
       <c r="F206" t="n">
         <v>432249</v>
@@ -4552,16 +4552,16 @@
         <v>44774</v>
       </c>
       <c r="B207" t="n">
-        <v>100.1493453979492</v>
+        <v>100.1493377685547</v>
       </c>
       <c r="C207" t="n">
-        <v>102.284108028477</v>
+        <v>102.2841002364559</v>
       </c>
       <c r="D207" t="n">
-        <v>94.3512267417151</v>
+        <v>94.35121955402224</v>
       </c>
       <c r="E207" t="n">
-        <v>94.3512267417151</v>
+        <v>94.35121955402224</v>
       </c>
       <c r="F207" t="n">
         <v>942663</v>
@@ -4572,16 +4572,16 @@
         <v>44775</v>
       </c>
       <c r="B208" t="n">
-        <v>101.4671020507812</v>
+        <v>101.4670944213867</v>
       </c>
       <c r="C208" t="n">
-        <v>102.2050413939763</v>
+        <v>102.2050337090955</v>
       </c>
       <c r="D208" t="n">
-        <v>98.69981610890704</v>
+        <v>98.69980868758699</v>
       </c>
       <c r="E208" t="n">
-        <v>100.0439247000455</v>
+        <v>100.0439171776608</v>
       </c>
       <c r="F208" t="n">
         <v>737331</v>
@@ -4592,16 +4592,16 @@
         <v>44776</v>
       </c>
       <c r="B209" t="n">
-        <v>106.8523254394531</v>
+        <v>106.8523178100586</v>
       </c>
       <c r="C209" t="n">
-        <v>107.5990584070543</v>
+        <v>107.5990507243421</v>
       </c>
       <c r="D209" t="n">
-        <v>101.4671040610422</v>
+        <v>101.4670968161594</v>
       </c>
       <c r="E209" t="n">
-        <v>101.4671040610422</v>
+        <v>101.4670968161594</v>
       </c>
       <c r="F209" t="n">
         <v>990038</v>
@@ -4632,16 +4632,16 @@
         <v>44778</v>
       </c>
       <c r="B211" t="n">
-        <v>108.0119323730469</v>
+        <v>108.0119476318359</v>
       </c>
       <c r="C211" t="n">
-        <v>108.8728681920126</v>
+        <v>108.8728835724256</v>
       </c>
       <c r="D211" t="n">
-        <v>105.095302918661</v>
+        <v>105.0953177654194</v>
       </c>
       <c r="E211" t="n">
-        <v>107.3969830041038</v>
+        <v>107.3969981760193</v>
       </c>
       <c r="F211" t="n">
         <v>445839</v>
@@ -4652,16 +4652,16 @@
         <v>44781</v>
       </c>
       <c r="B212" t="n">
-        <v>110.4893188476562</v>
+        <v>110.4893112182617</v>
       </c>
       <c r="C212" t="n">
-        <v>113.2829586427765</v>
+        <v>113.2829508204784</v>
       </c>
       <c r="D212" t="n">
-        <v>108.451192165222</v>
+        <v>108.4511846765621</v>
       </c>
       <c r="E212" t="n">
-        <v>108.9343714939558</v>
+        <v>108.9343639719319</v>
       </c>
       <c r="F212" t="n">
         <v>1248783</v>
@@ -4672,16 +4672,16 @@
         <v>44782</v>
       </c>
       <c r="B213" t="n">
-        <v>105.4027938842773</v>
+        <v>105.4027862548828</v>
       </c>
       <c r="C213" t="n">
-        <v>111.0339946821746</v>
+        <v>111.0339866451756</v>
       </c>
       <c r="D213" t="n">
-        <v>104.6999887966631</v>
+        <v>104.6999812181399</v>
       </c>
       <c r="E213" t="n">
-        <v>109.7689482054474</v>
+        <v>109.7689402600166</v>
       </c>
       <c r="F213" t="n">
         <v>927684</v>
@@ -4692,16 +4692,16 @@
         <v>44783</v>
       </c>
       <c r="B214" t="n">
-        <v>90.87236022949219</v>
+        <v>90.87235260009766</v>
       </c>
       <c r="C214" t="n">
-        <v>103.6457957452289</v>
+        <v>103.6457870434117</v>
       </c>
       <c r="D214" t="n">
-        <v>90.32768591007121</v>
+        <v>90.32767832640604</v>
       </c>
       <c r="E214" t="n">
-        <v>103.6457957452289</v>
+        <v>103.6457870434117</v>
       </c>
       <c r="F214" t="n">
         <v>2607483</v>
@@ -4712,16 +4712,16 @@
         <v>44784</v>
       </c>
       <c r="B215" t="n">
-        <v>84.59983062744141</v>
+        <v>84.59983825683594</v>
       </c>
       <c r="C215" t="n">
-        <v>92.06710516061834</v>
+        <v>92.06711346342773</v>
       </c>
       <c r="D215" t="n">
-        <v>83.26450248696285</v>
+        <v>83.26450999593463</v>
       </c>
       <c r="E215" t="n">
-        <v>90.87234069911442</v>
+        <v>90.87234889417739</v>
       </c>
       <c r="F215" t="n">
         <v>3127275</v>
@@ -4752,16 +4752,16 @@
         <v>44788</v>
       </c>
       <c r="B217" t="n">
-        <v>98.17271423339844</v>
+        <v>98.17270660400391</v>
       </c>
       <c r="C217" t="n">
-        <v>98.83159151013265</v>
+        <v>98.83158382953414</v>
       </c>
       <c r="D217" t="n">
-        <v>86.98058743595814</v>
+        <v>86.98058067634858</v>
       </c>
       <c r="E217" t="n">
-        <v>87.40226513969814</v>
+        <v>87.40225834731831</v>
       </c>
       <c r="F217" t="n">
         <v>1427504</v>
@@ -4812,16 +4812,16 @@
         <v>44791</v>
       </c>
       <c r="B220" t="n">
-        <v>96.89888763427734</v>
+        <v>96.89888000488281</v>
       </c>
       <c r="C220" t="n">
-        <v>97.78617087563147</v>
+        <v>97.78616317637614</v>
       </c>
       <c r="D220" t="n">
-        <v>95.80953904294859</v>
+        <v>95.80953149932459</v>
       </c>
       <c r="E220" t="n">
-        <v>96.51234415332544</v>
+        <v>96.51233655436566</v>
       </c>
       <c r="F220" t="n">
         <v>225811</v>
@@ -4832,16 +4832,16 @@
         <v>44792</v>
       </c>
       <c r="B221" t="n">
-        <v>92.8138427734375</v>
+        <v>92.81383514404297</v>
       </c>
       <c r="C221" t="n">
-        <v>96.3542087713233</v>
+        <v>96.35420085090701</v>
       </c>
       <c r="D221" t="n">
-        <v>92.34823725842267</v>
+        <v>92.34822966730141</v>
       </c>
       <c r="E221" t="n">
-        <v>95.79196739065114</v>
+        <v>95.79195951645167</v>
       </c>
       <c r="F221" t="n">
         <v>610732</v>
@@ -4852,16 +4852,16 @@
         <v>44795</v>
       </c>
       <c r="B222" t="n">
-        <v>88.45647430419922</v>
+        <v>88.45646667480469</v>
       </c>
       <c r="C222" t="n">
-        <v>92.04954856375565</v>
+        <v>92.04954062445751</v>
       </c>
       <c r="D222" t="n">
-        <v>88.03478989086102</v>
+        <v>88.03478229783688</v>
       </c>
       <c r="E222" t="n">
-        <v>92.04954856375565</v>
+        <v>92.04954062445751</v>
       </c>
       <c r="F222" t="n">
         <v>1074017</v>
@@ -4912,16 +4912,16 @@
         <v>44798</v>
       </c>
       <c r="B225" t="n">
-        <v>99.56952667236328</v>
+        <v>99.56951904296875</v>
       </c>
       <c r="C225" t="n">
-        <v>103.1362534053532</v>
+        <v>103.1362455026625</v>
       </c>
       <c r="D225" t="n">
-        <v>98.69981058018772</v>
+        <v>98.69980301743414</v>
       </c>
       <c r="E225" t="n">
-        <v>101.9063478664755</v>
+        <v>101.9063400580249</v>
       </c>
       <c r="F225" t="n">
         <v>468543</v>
@@ -4952,16 +4952,16 @@
         <v>44802</v>
       </c>
       <c r="B227" t="n">
-        <v>91.77721405029297</v>
+        <v>91.77720642089844</v>
       </c>
       <c r="C227" t="n">
-        <v>95.84468072985686</v>
+        <v>95.84467276233583</v>
       </c>
       <c r="D227" t="n">
-        <v>91.23253975030309</v>
+        <v>91.23253216618707</v>
       </c>
       <c r="E227" t="n">
-        <v>93.56057415666235</v>
+        <v>93.56056637901798</v>
       </c>
       <c r="F227" t="n">
         <v>661048</v>
@@ -5052,16 +5052,16 @@
         <v>44809</v>
       </c>
       <c r="B232" t="n">
-        <v>89.43160247802734</v>
+        <v>89.43161010742188</v>
       </c>
       <c r="C232" t="n">
-        <v>89.82692612228165</v>
+        <v>89.82693378540118</v>
       </c>
       <c r="D232" t="n">
-        <v>88.03477931026735</v>
+        <v>88.03478682049915</v>
       </c>
       <c r="E232" t="n">
-        <v>88.81664639508718</v>
+        <v>88.81665397201991</v>
       </c>
       <c r="F232" t="n">
         <v>95765</v>
@@ -5092,16 +5092,16 @@
         <v>44812</v>
       </c>
       <c r="B234" t="n">
-        <v>88.28955078125</v>
+        <v>88.28954315185547</v>
       </c>
       <c r="C234" t="n">
-        <v>90.14319263235551</v>
+        <v>90.14318484278159</v>
       </c>
       <c r="D234" t="n">
-        <v>87.12992709878814</v>
+        <v>87.12991956960056</v>
       </c>
       <c r="E234" t="n">
-        <v>88.29833768786334</v>
+        <v>88.29833005770951</v>
       </c>
       <c r="F234" t="n">
         <v>707072</v>
@@ -5172,16 +5172,16 @@
         <v>44818</v>
       </c>
       <c r="B238" t="n">
-        <v>90.13440704345703</v>
+        <v>90.1343994140625</v>
       </c>
       <c r="C238" t="n">
-        <v>91.77721007698068</v>
+        <v>91.77720230853167</v>
       </c>
       <c r="D238" t="n">
-        <v>88.15777528065119</v>
+        <v>88.15776781856795</v>
       </c>
       <c r="E238" t="n">
-        <v>90.17833487472001</v>
+        <v>90.17832724160722</v>
       </c>
       <c r="F238" t="n">
         <v>962834</v>
@@ -5232,16 +5232,16 @@
         <v>44823</v>
       </c>
       <c r="B241" t="n">
-        <v>88.99235534667969</v>
+        <v>88.99234771728516</v>
       </c>
       <c r="C241" t="n">
-        <v>89.82693050412597</v>
+        <v>89.82692280318257</v>
       </c>
       <c r="D241" t="n">
-        <v>86.69946201228579</v>
+        <v>86.69945457946307</v>
       </c>
       <c r="E241" t="n">
-        <v>87.39348017695347</v>
+        <v>87.39347268463194</v>
       </c>
       <c r="F241" t="n">
         <v>601912</v>
@@ -5272,16 +5272,16 @@
         <v>44825</v>
       </c>
       <c r="B243" t="n">
-        <v>89.51067352294922</v>
+        <v>89.51066589355469</v>
       </c>
       <c r="C243" t="n">
-        <v>91.22375175683315</v>
+        <v>91.2237439814253</v>
       </c>
       <c r="D243" t="n">
-        <v>87.51647458651904</v>
+        <v>87.51646712709899</v>
       </c>
       <c r="E243" t="n">
-        <v>90.16955079789631</v>
+        <v>90.16954311234272</v>
       </c>
       <c r="F243" t="n">
         <v>553017</v>
@@ -5372,16 +5372,16 @@
         <v>44832</v>
       </c>
       <c r="B248" t="n">
-        <v>86.94544219970703</v>
+        <v>86.9454345703125</v>
       </c>
       <c r="C248" t="n">
-        <v>88.52674356400453</v>
+        <v>88.52673579585205</v>
       </c>
       <c r="D248" t="n">
-        <v>85.29385228500924</v>
+        <v>85.29384480054043</v>
       </c>
       <c r="E248" t="n">
-        <v>86.5501118317982</v>
+        <v>86.55010423709361</v>
       </c>
       <c r="F248" t="n">
         <v>626382</v>
@@ -5432,16 +5432,16 @@
         <v>44837</v>
       </c>
       <c r="B251" t="n">
-        <v>94.77289581298828</v>
+        <v>94.77290344238281</v>
       </c>
       <c r="C251" t="n">
-        <v>95.68653968508768</v>
+        <v>95.68654738803224</v>
       </c>
       <c r="D251" t="n">
-        <v>90.92505530568604</v>
+        <v>90.92506262532224</v>
       </c>
       <c r="E251" t="n">
-        <v>91.36430678059274</v>
+        <v>91.36431413558951</v>
       </c>
       <c r="F251" t="n">
         <v>814581</v>
@@ -5452,16 +5452,16 @@
         <v>44838</v>
       </c>
       <c r="B252" t="n">
-        <v>94.43907165527344</v>
+        <v>94.43906402587891</v>
       </c>
       <c r="C252" t="n">
-        <v>96.46841142233895</v>
+        <v>96.46840362900132</v>
       </c>
       <c r="D252" t="n">
-        <v>92.77870153632058</v>
+        <v>92.77869404106141</v>
       </c>
       <c r="E252" t="n">
-        <v>93.47271970440633</v>
+        <v>93.47271215307993</v>
       </c>
       <c r="F252" t="n">
         <v>828067</v>
@@ -5472,16 +5472,16 @@
         <v>44839</v>
       </c>
       <c r="B253" t="n">
-        <v>95.75682830810547</v>
+        <v>95.75682067871094</v>
       </c>
       <c r="C253" t="n">
-        <v>97.74224699191255</v>
+        <v>97.74223920433043</v>
       </c>
       <c r="D253" t="n">
-        <v>93.46393491058726</v>
+        <v>93.46392746387826</v>
       </c>
       <c r="E253" t="n">
-        <v>94.30729699781466</v>
+        <v>94.30728948391106</v>
       </c>
       <c r="F253" t="n">
         <v>556734</v>
@@ -5492,16 +5492,16 @@
         <v>44840</v>
       </c>
       <c r="B254" t="n">
-        <v>99.09513854980469</v>
+        <v>99.09514617919922</v>
       </c>
       <c r="C254" t="n">
-        <v>99.89457277411294</v>
+        <v>99.89458046505639</v>
       </c>
       <c r="D254" t="n">
-        <v>94.70262366200211</v>
+        <v>94.70263095321427</v>
       </c>
       <c r="E254" t="n">
-        <v>95.71289672424005</v>
+        <v>95.71290409323375</v>
       </c>
       <c r="F254" t="n">
         <v>1317655</v>
@@ -5552,16 +5552,16 @@
         <v>44845</v>
       </c>
       <c r="B257" t="n">
-        <v>88.64974212646484</v>
+        <v>88.64974975585938</v>
       </c>
       <c r="C257" t="n">
-        <v>96.94280599912264</v>
+        <v>96.94281434223674</v>
       </c>
       <c r="D257" t="n">
-        <v>87.1387158739726</v>
+        <v>87.13872337332482</v>
       </c>
       <c r="E257" t="n">
-        <v>96.5211283068829</v>
+        <v>96.52113661370647</v>
       </c>
       <c r="F257" t="n">
         <v>1649810</v>
@@ -5592,16 +5592,16 @@
         <v>44848</v>
       </c>
       <c r="B259" t="n">
-        <v>82.7198486328125</v>
+        <v>82.71984100341797</v>
       </c>
       <c r="C259" t="n">
-        <v>90.16955058382466</v>
+        <v>90.16954226733124</v>
       </c>
       <c r="D259" t="n">
-        <v>82.66713389327845</v>
+        <v>82.66712626874587</v>
       </c>
       <c r="E259" t="n">
-        <v>86.64675155211943</v>
+        <v>86.64674356053986</v>
       </c>
       <c r="F259" t="n">
         <v>951929</v>
@@ -5632,16 +5632,16 @@
         <v>44852</v>
       </c>
       <c r="B261" t="n">
-        <v>80.54116058349609</v>
+        <v>80.54115295410156</v>
       </c>
       <c r="C261" t="n">
-        <v>85.61012027643372</v>
+        <v>85.61011216687361</v>
       </c>
       <c r="D261" t="n">
-        <v>79.24097310925836</v>
+        <v>79.24096560302623</v>
       </c>
       <c r="E261" t="n">
-        <v>84.42414248924207</v>
+        <v>84.42413449202566</v>
       </c>
       <c r="F261" t="n">
         <v>1514560</v>
@@ -5652,16 +5652,16 @@
         <v>44853</v>
       </c>
       <c r="B262" t="n">
-        <v>80.47087860107422</v>
+        <v>80.47086334228516</v>
       </c>
       <c r="C262" t="n">
-        <v>81.52508628989879</v>
+        <v>81.52507083121216</v>
       </c>
       <c r="D262" t="n">
-        <v>79.10920288553962</v>
+        <v>79.10918788494983</v>
       </c>
       <c r="E262" t="n">
-        <v>80.38302963595044</v>
+        <v>80.3830143938192</v>
       </c>
       <c r="F262" t="n">
         <v>1204425</v>
@@ -5692,16 +5692,16 @@
         <v>44855</v>
       </c>
       <c r="B264" t="n">
-        <v>82.25423431396484</v>
+        <v>82.25422668457031</v>
       </c>
       <c r="C264" t="n">
-        <v>85.73310542506498</v>
+        <v>85.73309747299184</v>
       </c>
       <c r="D264" t="n">
-        <v>75.13836128205794</v>
+        <v>75.13835431268782</v>
       </c>
       <c r="E264" t="n">
-        <v>77.967142043229</v>
+        <v>77.96713481147866</v>
       </c>
       <c r="F264" t="n">
         <v>1421863</v>
@@ -5712,16 +5712,16 @@
         <v>44858</v>
       </c>
       <c r="B265" t="n">
-        <v>82.40357971191406</v>
+        <v>82.40358734130859</v>
       </c>
       <c r="C265" t="n">
-        <v>83.41385274639228</v>
+        <v>83.41386046932367</v>
       </c>
       <c r="D265" t="n">
-        <v>80.20732232836033</v>
+        <v>80.20732975441281</v>
       </c>
       <c r="E265" t="n">
-        <v>81.73591559062895</v>
+        <v>81.73592315820733</v>
       </c>
       <c r="F265" t="n">
         <v>718180</v>
@@ -5732,16 +5732,16 @@
         <v>44859</v>
       </c>
       <c r="B266" t="n">
-        <v>82.92189025878906</v>
+        <v>82.92189788818359</v>
       </c>
       <c r="C266" t="n">
-        <v>85.30263237275399</v>
+        <v>85.30264022119347</v>
       </c>
       <c r="D266" t="n">
-        <v>81.31422830318635</v>
+        <v>81.31423578466473</v>
       </c>
       <c r="E266" t="n">
-        <v>82.03460043101913</v>
+        <v>82.03460797877678</v>
       </c>
       <c r="F266" t="n">
         <v>1189906</v>
@@ -5752,16 +5752,16 @@
         <v>44860</v>
       </c>
       <c r="B267" t="n">
-        <v>80.20732879638672</v>
+        <v>80.20732116699219</v>
       </c>
       <c r="C267" t="n">
-        <v>84.20451353532545</v>
+        <v>84.20450552571505</v>
       </c>
       <c r="D267" t="n">
-        <v>80.07555200225771</v>
+        <v>80.07554438539792</v>
       </c>
       <c r="E267" t="n">
-        <v>82.57928428092416</v>
+        <v>82.57927642590705</v>
       </c>
       <c r="F267" t="n">
         <v>763965</v>
@@ -5772,16 +5772,16 @@
         <v>44861</v>
       </c>
       <c r="B268" t="n">
-        <v>78.95985412597656</v>
+        <v>78.95984649658203</v>
       </c>
       <c r="C268" t="n">
-        <v>81.79742201297594</v>
+        <v>81.79741410940505</v>
       </c>
       <c r="D268" t="n">
-        <v>78.12527888403669</v>
+        <v>78.12527133528192</v>
       </c>
       <c r="E268" t="n">
-        <v>80.63779821975547</v>
+        <v>80.63779042823175</v>
       </c>
       <c r="F268" t="n">
         <v>872704</v>
@@ -5792,16 +5792,16 @@
         <v>44862</v>
       </c>
       <c r="B269" t="n">
-        <v>81.43723297119141</v>
+        <v>81.43721771240234</v>
       </c>
       <c r="C269" t="n">
-        <v>82.14003811734518</v>
+        <v>82.14002272687244</v>
       </c>
       <c r="D269" t="n">
-        <v>78.40640002110223</v>
+        <v>78.40638533019641</v>
       </c>
       <c r="E269" t="n">
-        <v>79.04771021965105</v>
+        <v>79.04769540858378</v>
       </c>
       <c r="F269" t="n">
         <v>705309</v>
@@ -5812,16 +5812,16 @@
         <v>44865</v>
       </c>
       <c r="B270" t="n">
-        <v>83.36993408203125</v>
+        <v>83.36992645263672</v>
       </c>
       <c r="C270" t="n">
-        <v>84.17815521445814</v>
+        <v>84.17814751110124</v>
       </c>
       <c r="D270" t="n">
-        <v>79.07405504914219</v>
+        <v>79.07404781287445</v>
       </c>
       <c r="E270" t="n">
-        <v>79.07405504914219</v>
+        <v>79.07404781287445</v>
       </c>
       <c r="F270" t="n">
         <v>956071</v>
@@ -5832,16 +5832,16 @@
         <v>44866</v>
       </c>
       <c r="B271" t="n">
-        <v>87.10357666015625</v>
+        <v>87.10356903076172</v>
       </c>
       <c r="C271" t="n">
-        <v>87.84151598729392</v>
+        <v>87.84150829326336</v>
       </c>
       <c r="D271" t="n">
-        <v>83.65984639528801</v>
+        <v>83.65983906752952</v>
       </c>
       <c r="E271" t="n">
-        <v>83.65984639528801</v>
+        <v>83.65983906752952</v>
       </c>
       <c r="F271" t="n">
         <v>1461617</v>
@@ -5852,16 +5852,16 @@
         <v>44868</v>
       </c>
       <c r="B272" t="n">
-        <v>86.58525848388672</v>
+        <v>86.58525085449219</v>
       </c>
       <c r="C272" t="n">
-        <v>88.4652544751398</v>
+        <v>88.46524668009084</v>
       </c>
       <c r="D272" t="n">
-        <v>84.04638520497635</v>
+        <v>84.04637779929271</v>
       </c>
       <c r="E272" t="n">
-        <v>85.59255245003042</v>
+        <v>85.59254490810744</v>
       </c>
       <c r="F272" t="n">
         <v>991113</v>
@@ -5872,16 +5872,16 @@
         <v>44869</v>
       </c>
       <c r="B273" t="n">
-        <v>83.48413848876953</v>
+        <v>83.484130859375</v>
       </c>
       <c r="C273" t="n">
-        <v>88.728802437938</v>
+        <v>88.72879432924752</v>
       </c>
       <c r="D273" t="n">
-        <v>82.78134011468907</v>
+        <v>82.78133254952142</v>
       </c>
       <c r="E273" t="n">
-        <v>87.59553277082331</v>
+        <v>87.59552476569932</v>
       </c>
       <c r="F273" t="n">
         <v>612180</v>
@@ -5892,16 +5892,16 @@
         <v>44872</v>
       </c>
       <c r="B274" t="n">
-        <v>83.19423675537109</v>
+        <v>83.19422912597656</v>
       </c>
       <c r="C274" t="n">
-        <v>84.51199133989617</v>
+        <v>84.51198358965588</v>
       </c>
       <c r="D274" t="n">
-        <v>82.28059947491988</v>
+        <v>82.2805919293112</v>
       </c>
       <c r="E274" t="n">
-        <v>83.03610593713023</v>
+        <v>83.03609832223721</v>
       </c>
       <c r="F274" t="n">
         <v>752715</v>
@@ -5952,16 +5952,16 @@
         <v>44875</v>
       </c>
       <c r="B277" t="n">
-        <v>90.49459075927734</v>
+        <v>90.49459838867188</v>
       </c>
       <c r="C277" t="n">
-        <v>94.21944139071987</v>
+        <v>94.21944933414814</v>
       </c>
       <c r="D277" t="n">
-        <v>85.65403762792715</v>
+        <v>85.65404484922558</v>
       </c>
       <c r="E277" t="n">
-        <v>85.67160473785169</v>
+        <v>85.67161196063115</v>
       </c>
       <c r="F277" t="n">
         <v>2820385</v>
@@ -5992,16 +5992,16 @@
         <v>44879</v>
       </c>
       <c r="B279" t="n">
-        <v>88.81664276123047</v>
+        <v>88.816650390625</v>
       </c>
       <c r="C279" t="n">
-        <v>90.38916377266612</v>
+        <v>90.389171537141</v>
       </c>
       <c r="D279" t="n">
-        <v>85.91758718293825</v>
+        <v>85.91759456330244</v>
       </c>
       <c r="E279" t="n">
-        <v>89.08019631491399</v>
+        <v>89.08020396694791</v>
       </c>
       <c r="F279" t="n">
         <v>689741</v>
@@ -6032,16 +6032,16 @@
         <v>44882</v>
       </c>
       <c r="B281" t="n">
-        <v>84.07273864746094</v>
+        <v>84.07273101806641</v>
       </c>
       <c r="C281" t="n">
-        <v>86.65553974214566</v>
+        <v>86.65553187836828</v>
       </c>
       <c r="D281" t="n">
-        <v>78.95107099372555</v>
+        <v>78.95106382910978</v>
       </c>
       <c r="E281" t="n">
-        <v>86.26021605324125</v>
+        <v>86.26020822533852</v>
       </c>
       <c r="F281" t="n">
         <v>1328887</v>
@@ -6052,16 +6052,16 @@
         <v>44883</v>
       </c>
       <c r="B282" t="n">
-        <v>82.07852935791016</v>
+        <v>82.07853698730469</v>
       </c>
       <c r="C282" t="n">
-        <v>86.7082368691072</v>
+        <v>86.70824492884405</v>
       </c>
       <c r="D282" t="n">
-        <v>81.44600617329941</v>
+        <v>81.44601374389941</v>
       </c>
       <c r="E282" t="n">
-        <v>85.21478456290053</v>
+        <v>85.21479248381745</v>
       </c>
       <c r="F282" t="n">
         <v>750376</v>
@@ -6132,16 +6132,16 @@
         <v>44889</v>
       </c>
       <c r="B286" t="n">
-        <v>78.80172729492188</v>
+        <v>78.80171203613281</v>
       </c>
       <c r="C286" t="n">
-        <v>79.50453247289863</v>
+        <v>79.50451707802175</v>
       </c>
       <c r="D286" t="n">
-        <v>77.1940716768986</v>
+        <v>77.19405672940827</v>
       </c>
       <c r="E286" t="n">
-        <v>77.52790045009176</v>
+        <v>77.52788543796044</v>
       </c>
       <c r="F286" t="n">
         <v>618983</v>
@@ -6192,16 +6192,16 @@
         <v>44894</v>
       </c>
       <c r="B289" t="n">
-        <v>76.56153106689453</v>
+        <v>76.56153869628906</v>
       </c>
       <c r="C289" t="n">
-        <v>77.83535762404934</v>
+        <v>77.83536538038132</v>
       </c>
       <c r="D289" t="n">
-        <v>73.80303242534015</v>
+        <v>73.80303977984893</v>
       </c>
       <c r="E289" t="n">
-        <v>75.94657499943207</v>
+        <v>75.94658256754593</v>
       </c>
       <c r="F289" t="n">
         <v>707315</v>
@@ -6212,16 +6212,16 @@
         <v>44895</v>
       </c>
       <c r="B290" t="n">
-        <v>79.53965759277344</v>
+        <v>79.53966522216797</v>
       </c>
       <c r="C290" t="n">
-        <v>80.11946605228191</v>
+        <v>80.11947373729132</v>
       </c>
       <c r="D290" t="n">
-        <v>75.72695131909879</v>
+        <v>75.72695858278091</v>
       </c>
       <c r="E290" t="n">
-        <v>78.18676225065957</v>
+        <v>78.18676975028522</v>
       </c>
       <c r="F290" t="n">
         <v>577266</v>
@@ -6292,16 +6292,16 @@
         <v>44901</v>
       </c>
       <c r="B294" t="n">
-        <v>77.94957733154297</v>
+        <v>77.94956970214844</v>
       </c>
       <c r="C294" t="n">
-        <v>81.69199543905461</v>
+        <v>81.69198744336707</v>
       </c>
       <c r="D294" t="n">
-        <v>77.94957733154297</v>
+        <v>77.94956970214844</v>
       </c>
       <c r="E294" t="n">
-        <v>81.04190506911468</v>
+        <v>81.0418971370554</v>
       </c>
       <c r="F294" t="n">
         <v>575865</v>
@@ -6312,16 +6312,16 @@
         <v>44902</v>
       </c>
       <c r="B295" t="n">
-        <v>76.15743255615234</v>
+        <v>76.15742492675781</v>
       </c>
       <c r="C295" t="n">
-        <v>78.43275226855985</v>
+        <v>78.4327444112255</v>
       </c>
       <c r="D295" t="n">
-        <v>74.76060920291299</v>
+        <v>74.76060171345117</v>
       </c>
       <c r="E295" t="n">
-        <v>77.82658301126293</v>
+        <v>77.82657521465414</v>
       </c>
       <c r="F295" t="n">
         <v>782541</v>
@@ -6332,16 +6332,16 @@
         <v>44903</v>
       </c>
       <c r="B296" t="n">
-        <v>72.38865661621094</v>
+        <v>72.38864898681641</v>
       </c>
       <c r="C296" t="n">
-        <v>76.73724427036358</v>
+        <v>76.73723618265012</v>
       </c>
       <c r="D296" t="n">
-        <v>72.03725403651906</v>
+        <v>72.03724644416056</v>
       </c>
       <c r="E296" t="n">
-        <v>76.73724427036358</v>
+        <v>76.73723618265012</v>
       </c>
       <c r="F296" t="n">
         <v>1116650</v>
@@ -6352,16 +6352,16 @@
         <v>44904</v>
       </c>
       <c r="B297" t="n">
-        <v>72.71369934082031</v>
+        <v>72.71368408203125</v>
       </c>
       <c r="C297" t="n">
-        <v>74.7606131921943</v>
+        <v>74.76059750386545</v>
       </c>
       <c r="D297" t="n">
-        <v>70.9303391029727</v>
+        <v>70.93032421841735</v>
       </c>
       <c r="E297" t="n">
-        <v>72.96846604657665</v>
+        <v>72.96845073432544</v>
       </c>
       <c r="F297" t="n">
         <v>602365</v>
@@ -6412,16 +6412,16 @@
         <v>44909</v>
       </c>
       <c r="B300" t="n">
-        <v>68.19818878173828</v>
+        <v>68.19818115234375</v>
       </c>
       <c r="C300" t="n">
-        <v>70.5174362779243</v>
+        <v>70.51742838907342</v>
       </c>
       <c r="D300" t="n">
-        <v>66.81893927300305</v>
+        <v>66.81893179790644</v>
       </c>
       <c r="E300" t="n">
-        <v>70.43837422126734</v>
+        <v>70.43836634126119</v>
       </c>
       <c r="F300" t="n">
         <v>1355188</v>
@@ -6432,16 +6432,16 @@
         <v>44910</v>
       </c>
       <c r="B301" t="n">
-        <v>65.86137390136719</v>
+        <v>65.86136627197266</v>
       </c>
       <c r="C301" t="n">
-        <v>68.8482855742363</v>
+        <v>68.84827759883733</v>
       </c>
       <c r="D301" t="n">
-        <v>65.81744606844191</v>
+        <v>65.81743844413599</v>
       </c>
       <c r="E301" t="n">
-        <v>68.30361127721578</v>
+        <v>68.30360336491199</v>
       </c>
       <c r="F301" t="n">
         <v>806063</v>
@@ -6472,16 +6472,16 @@
         <v>44914</v>
       </c>
       <c r="B303" t="n">
-        <v>66.36211395263672</v>
+        <v>66.36210632324219</v>
       </c>
       <c r="C303" t="n">
-        <v>66.73108358474747</v>
+        <v>66.73107591293393</v>
       </c>
       <c r="D303" t="n">
-        <v>64.41183632227187</v>
+        <v>64.41182891709317</v>
       </c>
       <c r="E303" t="n">
-        <v>66.09856038544582</v>
+        <v>66.09855278635102</v>
       </c>
       <c r="F303" t="n">
         <v>945079</v>
@@ -6532,16 +6532,16 @@
         <v>44917</v>
       </c>
       <c r="B306" t="n">
-        <v>67.46903991699219</v>
+        <v>67.46903228759766</v>
       </c>
       <c r="C306" t="n">
-        <v>72.45015082309504</v>
+        <v>72.45014263043683</v>
       </c>
       <c r="D306" t="n">
-        <v>64.56997704227857</v>
+        <v>64.56996974070987</v>
       </c>
       <c r="E306" t="n">
-        <v>70.28024712084742</v>
+        <v>70.28023917356177</v>
       </c>
       <c r="F306" t="n">
         <v>477342</v>
@@ -6552,16 +6552,16 @@
         <v>44918</v>
       </c>
       <c r="B307" t="n">
-        <v>70.72827911376953</v>
+        <v>70.728271484375</v>
       </c>
       <c r="C307" t="n">
-        <v>70.85126899880341</v>
+        <v>70.85126135614206</v>
       </c>
       <c r="D307" t="n">
-        <v>68.02248823813217</v>
+        <v>68.02248090060881</v>
       </c>
       <c r="E307" t="n">
-        <v>68.52323468504038</v>
+        <v>68.52322729350198</v>
       </c>
       <c r="F307" t="n">
         <v>762496</v>
@@ -6612,16 +6612,16 @@
         <v>44923</v>
       </c>
       <c r="B310" t="n">
-        <v>68.39145660400391</v>
+        <v>68.39144897460938</v>
       </c>
       <c r="C310" t="n">
-        <v>70.26267226700244</v>
+        <v>70.26266442886484</v>
       </c>
       <c r="D310" t="n">
-        <v>67.17912488761789</v>
+        <v>67.17911739346478</v>
       </c>
       <c r="E310" t="n">
-        <v>67.82042831857034</v>
+        <v>67.82042075287674</v>
       </c>
       <c r="F310" t="n">
         <v>543744</v>
@@ -6652,16 +6652,16 @@
         <v>44928</v>
       </c>
       <c r="B312" t="n">
-        <v>66.42361450195312</v>
+        <v>66.42360687255859</v>
       </c>
       <c r="C312" t="n">
-        <v>69.7707088947915</v>
+        <v>69.77070088095081</v>
       </c>
       <c r="D312" t="n">
-        <v>66.12491998707712</v>
+        <v>66.12491239199053</v>
       </c>
       <c r="E312" t="n">
-        <v>68.88342566202327</v>
+        <v>68.88341775009563</v>
       </c>
       <c r="F312" t="n">
         <v>452524</v>
@@ -6752,16 +6752,16 @@
         <v>44935</v>
       </c>
       <c r="B317" t="n">
-        <v>69.62136840820312</v>
+        <v>69.62136077880859</v>
       </c>
       <c r="C317" t="n">
-        <v>70.95669012764992</v>
+        <v>70.95668235192537</v>
       </c>
       <c r="D317" t="n">
-        <v>66.80137435331271</v>
+        <v>66.80136703294467</v>
       </c>
       <c r="E317" t="n">
-        <v>66.99464610141148</v>
+        <v>66.99463875986392</v>
       </c>
       <c r="F317" t="n">
         <v>604476</v>
@@ -6772,16 +6772,16 @@
         <v>44936</v>
       </c>
       <c r="B318" t="n">
-        <v>71.22023010253906</v>
+        <v>71.22023773193359</v>
       </c>
       <c r="C318" t="n">
-        <v>71.73855030075836</v>
+        <v>71.73855798567742</v>
       </c>
       <c r="D318" t="n">
-        <v>69.26116567910124</v>
+        <v>69.26117309863299</v>
       </c>
       <c r="E318" t="n">
-        <v>69.26116567910124</v>
+        <v>69.26117309863299</v>
       </c>
       <c r="F318" t="n">
         <v>559538</v>
@@ -6792,16 +6792,16 @@
         <v>44937</v>
       </c>
       <c r="B319" t="n">
-        <v>72.90696716308594</v>
+        <v>72.90695953369141</v>
       </c>
       <c r="C319" t="n">
-        <v>73.10902581621284</v>
+        <v>73.10901816567375</v>
       </c>
       <c r="D319" t="n">
-        <v>69.80585242983342</v>
+        <v>69.80584512495696</v>
       </c>
       <c r="E319" t="n">
-        <v>71.22024289438232</v>
+        <v>71.2202354414961</v>
       </c>
       <c r="F319" t="n">
         <v>824670</v>
@@ -6852,16 +6852,16 @@
         <v>44942</v>
       </c>
       <c r="B322" t="n">
-        <v>70.13089752197266</v>
+        <v>70.13088989257812</v>
       </c>
       <c r="C322" t="n">
-        <v>72.91575047990735</v>
+        <v>72.91574254755446</v>
       </c>
       <c r="D322" t="n">
-        <v>69.55108231303058</v>
+        <v>69.55107474671294</v>
       </c>
       <c r="E322" t="n">
-        <v>72.91575047990735</v>
+        <v>72.91574254755446</v>
       </c>
       <c r="F322" t="n">
         <v>636220</v>
@@ -6892,16 +6892,16 @@
         <v>44944</v>
       </c>
       <c r="B324" t="n">
-        <v>73.96995544433594</v>
+        <v>73.96994018554688</v>
       </c>
       <c r="C324" t="n">
-        <v>75.29649695010914</v>
+        <v>75.29648141767632</v>
       </c>
       <c r="D324" t="n">
-        <v>72.48528982109953</v>
+        <v>72.48527486857265</v>
       </c>
       <c r="E324" t="n">
-        <v>72.52043074801796</v>
+        <v>72.52041578824208</v>
       </c>
       <c r="F324" t="n">
         <v>881691</v>
@@ -6932,16 +6932,16 @@
         <v>44946</v>
       </c>
       <c r="B326" t="n">
-        <v>77.02714538574219</v>
+        <v>77.02713775634766</v>
       </c>
       <c r="C326" t="n">
-        <v>78.32733280988822</v>
+        <v>78.32732505171256</v>
       </c>
       <c r="D326" t="n">
-        <v>74.45313125821576</v>
+        <v>74.45312388377251</v>
       </c>
       <c r="E326" t="n">
-        <v>75.12079543290946</v>
+        <v>75.12078799233532</v>
       </c>
       <c r="F326" t="n">
         <v>766265</v>
@@ -6952,16 +6952,16 @@
         <v>44949</v>
       </c>
       <c r="B327" t="n">
-        <v>80.09311676025391</v>
+        <v>80.09310913085938</v>
       </c>
       <c r="C327" t="n">
-        <v>81.2088193216573</v>
+        <v>81.20881158598479</v>
       </c>
       <c r="D327" t="n">
-        <v>77.09742502080553</v>
+        <v>77.09741767677029</v>
       </c>
       <c r="E327" t="n">
-        <v>77.09742502080553</v>
+        <v>77.09741767677029</v>
       </c>
       <c r="F327" t="n">
         <v>1210224</v>
@@ -7052,16 +7052,16 @@
         <v>44956</v>
       </c>
       <c r="B332" t="n">
-        <v>80.8486328125</v>
+        <v>80.84862518310547</v>
       </c>
       <c r="C332" t="n">
-        <v>81.99068943295865</v>
+        <v>81.99068169579233</v>
       </c>
       <c r="D332" t="n">
-        <v>78.90714191967729</v>
+        <v>78.90713447349425</v>
       </c>
       <c r="E332" t="n">
-        <v>81.1736813466173</v>
+        <v>81.17367368654911</v>
       </c>
       <c r="F332" t="n">
         <v>515927</v>
@@ -7072,16 +7072,16 @@
         <v>44957</v>
       </c>
       <c r="B333" t="n">
-        <v>78.84564208984375</v>
+        <v>78.84564971923828</v>
       </c>
       <c r="C333" t="n">
-        <v>81.68320965117834</v>
+        <v>81.68321755514636</v>
       </c>
       <c r="D333" t="n">
-        <v>78.84564208984375</v>
+        <v>78.84564971923828</v>
       </c>
       <c r="E333" t="n">
-        <v>80.83984089613189</v>
+        <v>80.83984871849243</v>
       </c>
       <c r="F333" t="n">
         <v>714873</v>
@@ -7112,16 +7112,16 @@
         <v>44959</v>
       </c>
       <c r="B335" t="n">
-        <v>78.88957977294922</v>
+        <v>78.88956451416016</v>
       </c>
       <c r="C335" t="n">
-        <v>80.39181924512856</v>
+        <v>80.39180369577697</v>
       </c>
       <c r="D335" t="n">
-        <v>77.56303823692257</v>
+        <v>77.5630232347126</v>
       </c>
       <c r="E335" t="n">
-        <v>77.89686699659131</v>
+        <v>77.89685192981234</v>
       </c>
       <c r="F335" t="n">
         <v>645862</v>
@@ -7132,16 +7132,16 @@
         <v>44960</v>
       </c>
       <c r="B336" t="n">
-        <v>78.4327392578125</v>
+        <v>78.43274688720703</v>
       </c>
       <c r="C336" t="n">
-        <v>80.04918810831229</v>
+        <v>80.04919589494379</v>
       </c>
       <c r="D336" t="n">
-        <v>76.42975368198618</v>
+        <v>76.42976111654413</v>
       </c>
       <c r="E336" t="n">
-        <v>79.05647552379735</v>
+        <v>79.05648321386462</v>
       </c>
       <c r="F336" t="n">
         <v>709735</v>
@@ -7152,16 +7152,16 @@
         <v>44963</v>
       </c>
       <c r="B337" t="n">
-        <v>77.33462524414062</v>
+        <v>77.33461761474609</v>
       </c>
       <c r="C337" t="n">
-        <v>79.71536779231553</v>
+        <v>79.71535992805047</v>
       </c>
       <c r="D337" t="n">
-        <v>76.587898964852</v>
+        <v>76.58789140912525</v>
       </c>
       <c r="E337" t="n">
-        <v>77.87929956791825</v>
+        <v>77.87929188478925</v>
       </c>
       <c r="F337" t="n">
         <v>362662</v>
@@ -7172,16 +7172,16 @@
         <v>44964</v>
       </c>
       <c r="B338" t="n">
-        <v>74.67276000976562</v>
+        <v>74.67275238037109</v>
       </c>
       <c r="C338" t="n">
-        <v>78.23948028427274</v>
+        <v>78.23947229046264</v>
       </c>
       <c r="D338" t="n">
-        <v>74.45313424503101</v>
+        <v>74.45312663807589</v>
       </c>
       <c r="E338" t="n">
-        <v>76.98322064189294</v>
+        <v>76.98321277643622</v>
       </c>
       <c r="F338" t="n">
         <v>1089766</v>
@@ -7192,16 +7192,16 @@
         <v>44965</v>
       </c>
       <c r="B339" t="n">
-        <v>74.92751312255859</v>
+        <v>74.92752075195312</v>
       </c>
       <c r="C339" t="n">
-        <v>76.47368010277411</v>
+        <v>76.47368788960505</v>
       </c>
       <c r="D339" t="n">
-        <v>73.99630219362362</v>
+        <v>73.99630972819882</v>
       </c>
       <c r="E339" t="n">
-        <v>74.67274647734247</v>
+        <v>74.67275408079573</v>
       </c>
       <c r="F339" t="n">
         <v>806683</v>
@@ -7212,16 +7212,16 @@
         <v>44966</v>
       </c>
       <c r="B340" t="n">
-        <v>72.64340972900391</v>
+        <v>72.64341735839844</v>
       </c>
       <c r="C340" t="n">
-        <v>76.30676535377293</v>
+        <v>76.30677336791243</v>
       </c>
       <c r="D340" t="n">
-        <v>72.33592834026705</v>
+        <v>72.33593593736826</v>
       </c>
       <c r="E340" t="n">
-        <v>74.92751601602691</v>
+        <v>74.92752388531035</v>
       </c>
       <c r="F340" t="n">
         <v>904775</v>
@@ -7272,16 +7272,16 @@
         <v>44971</v>
       </c>
       <c r="B343" t="n">
-        <v>72.90696716308594</v>
+        <v>72.90695953369141</v>
       </c>
       <c r="C343" t="n">
-        <v>74.53219648561118</v>
+        <v>74.53218868614353</v>
       </c>
       <c r="D343" t="n">
-        <v>71.91426111693616</v>
+        <v>71.91425359142397</v>
       </c>
       <c r="E343" t="n">
-        <v>73.00360303600144</v>
+        <v>73.00359539649439</v>
       </c>
       <c r="F343" t="n">
         <v>472429</v>
@@ -7292,16 +7292,16 @@
         <v>44972</v>
       </c>
       <c r="B344" t="n">
-        <v>73.78546142578125</v>
+        <v>73.78546905517578</v>
       </c>
       <c r="C344" t="n">
-        <v>74.93630485624141</v>
+        <v>74.93631260463282</v>
       </c>
       <c r="D344" t="n">
-        <v>71.65069897379257</v>
+        <v>71.65070638245331</v>
       </c>
       <c r="E344" t="n">
-        <v>72.23930104839484</v>
+        <v>72.23930851791685</v>
       </c>
       <c r="F344" t="n">
         <v>619864</v>
@@ -7352,16 +7352,16 @@
         <v>44979</v>
       </c>
       <c r="B347" t="n">
-        <v>59.92269134521484</v>
+        <v>59.92268753051758</v>
       </c>
       <c r="C347" t="n">
-        <v>60.25652008637044</v>
+        <v>60.25651625042154</v>
       </c>
       <c r="D347" t="n">
-        <v>58.28867516031535</v>
+        <v>58.28867144964006</v>
       </c>
       <c r="E347" t="n">
-        <v>58.85970347481399</v>
+        <v>58.85969972778687</v>
       </c>
       <c r="F347" t="n">
         <v>1166573</v>
@@ -7392,16 +7392,16 @@
         <v>44981</v>
       </c>
       <c r="B349" t="n">
-        <v>58.85091781616211</v>
+        <v>58.85091400146484</v>
       </c>
       <c r="C349" t="n">
-        <v>59.79970272476828</v>
+        <v>59.79969884857108</v>
       </c>
       <c r="D349" t="n">
-        <v>57.98998857507038</v>
+        <v>57.98998481617827</v>
       </c>
       <c r="E349" t="n">
-        <v>59.56250984883994</v>
+        <v>59.56250598801751</v>
       </c>
       <c r="F349" t="n">
         <v>780666</v>
@@ -7452,16 +7452,16 @@
         <v>44986</v>
       </c>
       <c r="B352" t="n">
-        <v>54.14213943481445</v>
+        <v>54.14214324951172</v>
       </c>
       <c r="C352" t="n">
-        <v>57.10269353027231</v>
+        <v>57.10269755356158</v>
       </c>
       <c r="D352" t="n">
-        <v>53.41298035499475</v>
+        <v>53.4129841183176</v>
       </c>
       <c r="E352" t="n">
-        <v>56.48774412707847</v>
+        <v>56.4877481070402</v>
       </c>
       <c r="F352" t="n">
         <v>634515</v>
@@ -7472,16 +7472,16 @@
         <v>44987</v>
       </c>
       <c r="B353" t="n">
-        <v>53.14943313598633</v>
+        <v>53.14942932128906</v>
       </c>
       <c r="C353" t="n">
-        <v>54.59017756413803</v>
+        <v>54.59017364603414</v>
       </c>
       <c r="D353" t="n">
-        <v>52.64868667867075</v>
+        <v>52.64868289991359</v>
       </c>
       <c r="E353" t="n">
-        <v>54.08943110682245</v>
+        <v>54.08942722465866</v>
       </c>
       <c r="F353" t="n">
         <v>1104186</v>
@@ -7492,16 +7492,16 @@
         <v>44988</v>
       </c>
       <c r="B354" t="n">
-        <v>52.35877990722656</v>
+        <v>52.3587760925293</v>
       </c>
       <c r="C354" t="n">
-        <v>54.11578598936467</v>
+        <v>54.11578204665744</v>
       </c>
       <c r="D354" t="n">
-        <v>52.35877990722656</v>
+        <v>52.3587760925293</v>
       </c>
       <c r="E354" t="n">
-        <v>53.14943398467798</v>
+        <v>53.14943011237612</v>
       </c>
       <c r="F354" t="n">
         <v>443497</v>
@@ -7552,16 +7552,16 @@
         <v>44993</v>
       </c>
       <c r="B357" t="n">
-        <v>58.67522048950195</v>
+        <v>58.67521667480469</v>
       </c>
       <c r="C357" t="n">
-        <v>58.67522048950195</v>
+        <v>58.67521667480469</v>
       </c>
       <c r="D357" t="n">
-        <v>53.975227083112</v>
+        <v>53.97522357397903</v>
       </c>
       <c r="E357" t="n">
-        <v>53.975227083112</v>
+        <v>53.97522357397903</v>
       </c>
       <c r="F357" t="n">
         <v>1672249</v>
@@ -7572,16 +7572,16 @@
         <v>44994</v>
       </c>
       <c r="B358" t="n">
-        <v>55.78494644165039</v>
+        <v>55.78494262695312</v>
       </c>
       <c r="C358" t="n">
-        <v>59.46587654848869</v>
+        <v>59.46587248208133</v>
       </c>
       <c r="D358" t="n">
-        <v>55.78494644165039</v>
+        <v>55.78494262695312</v>
       </c>
       <c r="E358" t="n">
-        <v>58.59615366009346</v>
+        <v>58.59614965315966</v>
       </c>
       <c r="F358" t="n">
         <v>905395</v>
@@ -7592,16 +7592,16 @@
         <v>44995</v>
       </c>
       <c r="B359" t="n">
-        <v>52.01616287231445</v>
+        <v>52.01615905761719</v>
       </c>
       <c r="C359" t="n">
-        <v>56.08363278249773</v>
+        <v>56.08362866950537</v>
       </c>
       <c r="D359" t="n">
-        <v>51.7965371178954</v>
+        <v>51.79653331930479</v>
       </c>
       <c r="E359" t="n">
-        <v>55.52139138738065</v>
+        <v>55.52138731562125</v>
       </c>
       <c r="F359" t="n">
         <v>846843</v>
@@ -7632,16 +7632,16 @@
         <v>44999</v>
       </c>
       <c r="B361" t="n">
-        <v>50.32943344116211</v>
+        <v>50.32943725585938</v>
       </c>
       <c r="C361" t="n">
-        <v>52.78924096402687</v>
+        <v>52.78924496516417</v>
       </c>
       <c r="D361" t="n">
-        <v>49.55634992784254</v>
+        <v>49.55635368394428</v>
       </c>
       <c r="E361" t="n">
-        <v>50.84775030161619</v>
+        <v>50.84775415559906</v>
       </c>
       <c r="F361" t="n">
         <v>730632</v>
@@ -7652,16 +7652,16 @@
         <v>45000</v>
       </c>
       <c r="B362" t="n">
-        <v>50.43485641479492</v>
+        <v>50.43486022949219</v>
       </c>
       <c r="C362" t="n">
-        <v>50.90924883268146</v>
+        <v>50.90925268325992</v>
       </c>
       <c r="D362" t="n">
-        <v>48.08925504506086</v>
+        <v>48.08925868234591</v>
       </c>
       <c r="E362" t="n">
-        <v>49.89896905583676</v>
+        <v>49.89897283000158</v>
       </c>
       <c r="F362" t="n">
         <v>1072440</v>
@@ -7692,16 +7692,16 @@
         <v>45002</v>
       </c>
       <c r="B364" t="n">
-        <v>55.06456756591797</v>
+        <v>55.0645637512207</v>
       </c>
       <c r="C364" t="n">
-        <v>55.54774353916095</v>
+        <v>55.5477396909908</v>
       </c>
       <c r="D364" t="n">
-        <v>52.19186239249056</v>
+        <v>52.19185877680513</v>
       </c>
       <c r="E364" t="n">
-        <v>53.58868227771264</v>
+        <v>53.58867856525999</v>
       </c>
       <c r="F364" t="n">
         <v>1415773</v>
@@ -7732,16 +7732,16 @@
         <v>45006</v>
       </c>
       <c r="B366" t="n">
-        <v>54.65167236328125</v>
+        <v>54.65166854858398</v>
       </c>
       <c r="C366" t="n">
-        <v>54.73073776955461</v>
+        <v>54.73073394933856</v>
       </c>
       <c r="D366" t="n">
-        <v>52.65747009502944</v>
+        <v>52.65746641952787</v>
       </c>
       <c r="E366" t="n">
-        <v>52.65747009502944</v>
+        <v>52.65746641952787</v>
       </c>
       <c r="F366" t="n">
         <v>534854</v>
@@ -7792,16 +7792,16 @@
         <v>45009</v>
       </c>
       <c r="B369" t="n">
-        <v>50.40850067138672</v>
+        <v>50.40850448608398</v>
       </c>
       <c r="C369" t="n">
-        <v>51.3660690297127</v>
+        <v>51.3660729168746</v>
       </c>
       <c r="D369" t="n">
-        <v>48.82719601713704</v>
+        <v>48.82719971216801</v>
       </c>
       <c r="E369" t="n">
-        <v>50.05709814767665</v>
+        <v>50.05710193578128</v>
       </c>
       <c r="F369" t="n">
         <v>598427</v>
@@ -7812,16 +7812,16 @@
         <v>45012</v>
       </c>
       <c r="B370" t="n">
-        <v>51.84925079345703</v>
+        <v>51.84924697875977</v>
       </c>
       <c r="C370" t="n">
-        <v>52.5256985490655</v>
+        <v>52.52569468460005</v>
       </c>
       <c r="D370" t="n">
-        <v>50.65448610049781</v>
+        <v>50.6544823737028</v>
       </c>
       <c r="E370" t="n">
-        <v>51.3924288019595</v>
+        <v>51.39242502087193</v>
       </c>
       <c r="F370" t="n">
         <v>634884</v>
@@ -7892,16 +7892,16 @@
         <v>45016</v>
       </c>
       <c r="B374" t="n">
-        <v>52.33242416381836</v>
+        <v>52.33242034912109</v>
       </c>
       <c r="C374" t="n">
-        <v>54.73073698475589</v>
+        <v>54.73073299523703</v>
       </c>
       <c r="D374" t="n">
-        <v>51.94588404492639</v>
+        <v>51.94588025840541</v>
       </c>
       <c r="E374" t="n">
-        <v>54.20363651797383</v>
+        <v>54.20363256687721</v>
       </c>
       <c r="F374" t="n">
         <v>558868</v>
@@ -7912,16 +7912,16 @@
         <v>45019</v>
       </c>
       <c r="B375" t="n">
-        <v>49.41579437255859</v>
+        <v>49.41579055786133</v>
       </c>
       <c r="C375" t="n">
-        <v>52.67503973932627</v>
+        <v>52.67503567302858</v>
       </c>
       <c r="D375" t="n">
-        <v>49.41579437255859</v>
+        <v>49.41579055786133</v>
       </c>
       <c r="E375" t="n">
-        <v>52.34999456357366</v>
+        <v>52.34999052236814</v>
       </c>
       <c r="F375" t="n">
         <v>492395</v>
@@ -7992,16 +7992,16 @@
         <v>45026</v>
       </c>
       <c r="B379" t="n">
-        <v>48.75691986083984</v>
+        <v>48.75691604614258</v>
       </c>
       <c r="C379" t="n">
-        <v>49.21374185447558</v>
+        <v>49.21373800403698</v>
       </c>
       <c r="D379" t="n">
-        <v>48.01019359985681</v>
+        <v>48.01018984358273</v>
       </c>
       <c r="E379" t="n">
-        <v>48.32645188662934</v>
+        <v>48.3264481056115</v>
       </c>
       <c r="F379" t="n">
         <v>441343</v>
@@ -8012,16 +8012,16 @@
         <v>45027</v>
       </c>
       <c r="B380" t="n">
-        <v>54.63410568237305</v>
+        <v>54.63410186767578</v>
       </c>
       <c r="C380" t="n">
-        <v>54.63410568237305</v>
+        <v>54.63410186767578</v>
       </c>
       <c r="D380" t="n">
-        <v>48.85355712225322</v>
+        <v>48.8535537111691</v>
       </c>
       <c r="E380" t="n">
-        <v>48.85355712225322</v>
+        <v>48.8535537111691</v>
       </c>
       <c r="F380" t="n">
         <v>1223134</v>
@@ -8052,16 +8052,16 @@
         <v>45029</v>
       </c>
       <c r="B382" t="n">
-        <v>60.46735763549805</v>
+        <v>60.46736526489258</v>
       </c>
       <c r="C382" t="n">
-        <v>61.46006352292876</v>
+        <v>61.46007127757674</v>
       </c>
       <c r="D382" t="n">
-        <v>55.96063671432766</v>
+        <v>55.96064377509221</v>
       </c>
       <c r="E382" t="n">
-        <v>56.40867172931058</v>
+        <v>56.4086788466054</v>
       </c>
       <c r="F382" t="n">
         <v>2756815</v>
@@ -8072,16 +8072,16 @@
         <v>45030</v>
       </c>
       <c r="B383" t="n">
-        <v>60.44978332519531</v>
+        <v>60.44979476928711</v>
       </c>
       <c r="C383" t="n">
-        <v>62.15408112194347</v>
+        <v>62.15409288868556</v>
       </c>
       <c r="D383" t="n">
-        <v>59.10567494010849</v>
+        <v>59.1056861297395</v>
       </c>
       <c r="E383" t="n">
-        <v>60.45857023101384</v>
+        <v>60.45858167676914</v>
       </c>
       <c r="F383" t="n">
         <v>793877</v>
@@ -8112,16 +8112,16 @@
         <v>45034</v>
       </c>
       <c r="B385" t="n">
-        <v>61.49521255493164</v>
+        <v>61.49520874023438</v>
       </c>
       <c r="C385" t="n">
-        <v>61.49521255493164</v>
+        <v>61.49520874023438</v>
       </c>
       <c r="D385" t="n">
-        <v>59.16717816771997</v>
+        <v>59.16717449743633</v>
       </c>
       <c r="E385" t="n">
-        <v>59.16717816771997</v>
+        <v>59.16717449743633</v>
       </c>
       <c r="F385" t="n">
         <v>581190</v>
@@ -8132,16 +8132,16 @@
         <v>45035</v>
       </c>
       <c r="B386" t="n">
-        <v>58.84212875366211</v>
+        <v>58.84213638305664</v>
       </c>
       <c r="C386" t="n">
-        <v>61.27557890220787</v>
+        <v>61.2755868471204</v>
       </c>
       <c r="D386" t="n">
-        <v>58.3062414342357</v>
+        <v>58.30624899414777</v>
       </c>
       <c r="E386" t="n">
-        <v>61.27557890220787</v>
+        <v>61.2755868471204</v>
       </c>
       <c r="F386" t="n">
         <v>827950</v>
@@ -8152,16 +8152,16 @@
         <v>45036</v>
       </c>
       <c r="B387" t="n">
-        <v>60.80118560791016</v>
+        <v>60.80119323730469</v>
       </c>
       <c r="C387" t="n">
-        <v>60.80118560791016</v>
+        <v>60.80119323730469</v>
       </c>
       <c r="D387" t="n">
-        <v>58.21838490725599</v>
+        <v>58.21839221255807</v>
       </c>
       <c r="E387" t="n">
-        <v>58.78941313934933</v>
+        <v>58.78942051630461</v>
       </c>
       <c r="F387" t="n">
         <v>442904</v>
@@ -8172,16 +8172,16 @@
         <v>45040</v>
       </c>
       <c r="B388" t="n">
-        <v>60.99445724487305</v>
+        <v>60.99446105957031</v>
       </c>
       <c r="C388" t="n">
-        <v>61.27557790767784</v>
+        <v>61.27558173995688</v>
       </c>
       <c r="D388" t="n">
-        <v>59.73819781680421</v>
+        <v>59.73820155293286</v>
       </c>
       <c r="E388" t="n">
-        <v>60.27408512753293</v>
+        <v>60.2740888971769</v>
       </c>
       <c r="F388" t="n">
         <v>315786</v>
@@ -8192,16 +8192,16 @@
         <v>45041</v>
       </c>
       <c r="B389" t="n">
-        <v>60.50250244140625</v>
+        <v>60.50250625610352</v>
       </c>
       <c r="C389" t="n">
-        <v>61.28436955477335</v>
+        <v>61.28437341876753</v>
       </c>
       <c r="D389" t="n">
-        <v>59.00904335897617</v>
+        <v>59.00904707951048</v>
       </c>
       <c r="E389" t="n">
-        <v>61.28436955477335</v>
+        <v>61.28437341876753</v>
       </c>
       <c r="F389" t="n">
         <v>695154</v>
@@ -8252,16 +8252,16 @@
         <v>45044</v>
       </c>
       <c r="B392" t="n">
-        <v>63.67390441894531</v>
+        <v>63.67390060424805</v>
       </c>
       <c r="C392" t="n">
-        <v>63.75296647677501</v>
+        <v>63.75296265734114</v>
       </c>
       <c r="D392" t="n">
-        <v>60.61671083638181</v>
+        <v>60.61670720484071</v>
       </c>
       <c r="E392" t="n">
-        <v>61.50400079922254</v>
+        <v>61.50399711452398</v>
       </c>
       <c r="F392" t="n">
         <v>633625</v>
@@ -8272,16 +8272,16 @@
         <v>45048</v>
       </c>
       <c r="B393" t="n">
-        <v>58.38530731201172</v>
+        <v>58.38531112670898</v>
       </c>
       <c r="C393" t="n">
-        <v>63.16436567335623</v>
+        <v>63.16436980030091</v>
       </c>
       <c r="D393" t="n">
-        <v>58.38530731201172</v>
+        <v>58.38531112670898</v>
       </c>
       <c r="E393" t="n">
-        <v>63.16436567335623</v>
+        <v>63.16436980030091</v>
       </c>
       <c r="F393" t="n">
         <v>808928</v>
@@ -8292,16 +8292,16 @@
         <v>45049</v>
       </c>
       <c r="B394" t="n">
-        <v>58.85091781616211</v>
+        <v>58.85091400146484</v>
       </c>
       <c r="C394" t="n">
-        <v>60.08082343445384</v>
+        <v>60.08081954003449</v>
       </c>
       <c r="D394" t="n">
-        <v>58.7718557583348</v>
+        <v>58.77185194876231</v>
       </c>
       <c r="E394" t="n">
-        <v>59.12325832105335</v>
+        <v>59.12325448870306</v>
       </c>
       <c r="F394" t="n">
         <v>320277</v>
@@ -8312,16 +8312,16 @@
         <v>45050</v>
       </c>
       <c r="B395" t="n">
-        <v>60.79240798950195</v>
+        <v>60.79240417480469</v>
       </c>
       <c r="C395" t="n">
-        <v>61.56549495811417</v>
+        <v>61.56549109490604</v>
       </c>
       <c r="D395" t="n">
-        <v>58.60493728570287</v>
+        <v>58.60493360826845</v>
       </c>
       <c r="E395" t="n">
-        <v>58.60493728570287</v>
+        <v>58.60493360826845</v>
       </c>
       <c r="F395" t="n">
         <v>661928</v>
@@ -8352,16 +8352,16 @@
         <v>45054</v>
       </c>
       <c r="B397" t="n">
-        <v>65.16734313964844</v>
+        <v>65.16735076904297</v>
       </c>
       <c r="C397" t="n">
-        <v>65.74715154835417</v>
+        <v>65.74715924562913</v>
       </c>
       <c r="D397" t="n">
-        <v>63.59482219865949</v>
+        <v>63.59482964395288</v>
       </c>
       <c r="E397" t="n">
-        <v>63.76173988867773</v>
+        <v>63.76174735351282</v>
       </c>
       <c r="F397" t="n">
         <v>685640</v>
@@ -8392,16 +8392,16 @@
         <v>45056</v>
       </c>
       <c r="B399" t="n">
-        <v>68.46173095703125</v>
+        <v>68.46174621582031</v>
       </c>
       <c r="C399" t="n">
-        <v>68.48808497152142</v>
+        <v>68.48810023618428</v>
       </c>
       <c r="D399" t="n">
-        <v>66.18640497099832</v>
+        <v>66.18641972266146</v>
       </c>
       <c r="E399" t="n">
-        <v>66.78378720840801</v>
+        <v>66.78380209321604</v>
       </c>
       <c r="F399" t="n">
         <v>406791</v>
@@ -8432,16 +8432,16 @@
         <v>45058</v>
       </c>
       <c r="B401" t="n">
-        <v>66.23033905029297</v>
+        <v>66.23033142089844</v>
       </c>
       <c r="C401" t="n">
-        <v>67.00341925892872</v>
+        <v>67.00341154047932</v>
       </c>
       <c r="D401" t="n">
-        <v>65.81744157777364</v>
+        <v>65.81743399594278</v>
       </c>
       <c r="E401" t="n">
-        <v>66.79258042065457</v>
+        <v>66.79257272649272</v>
       </c>
       <c r="F401" t="n">
         <v>398348</v>
@@ -8472,16 +8472,16 @@
         <v>45062</v>
       </c>
       <c r="B403" t="n">
-        <v>69.20846557617188</v>
+        <v>69.20845794677734</v>
       </c>
       <c r="C403" t="n">
-        <v>74.04023209771412</v>
+        <v>74.04022393567588</v>
       </c>
       <c r="D403" t="n">
-        <v>67.52174141723872</v>
+        <v>67.52173397378508</v>
       </c>
       <c r="E403" t="n">
-        <v>69.22603938961998</v>
+        <v>69.22603175828814</v>
       </c>
       <c r="F403" t="n">
         <v>1416795</v>
@@ -8492,16 +8492,16 @@
         <v>45063</v>
       </c>
       <c r="B404" t="n">
-        <v>72.32715606689453</v>
+        <v>72.32714080810547</v>
       </c>
       <c r="C404" t="n">
-        <v>73.79425451837514</v>
+        <v>73.79423895007376</v>
       </c>
       <c r="D404" t="n">
-        <v>67.66230042003383</v>
+        <v>67.66228614538477</v>
       </c>
       <c r="E404" t="n">
-        <v>69.4105262754566</v>
+        <v>69.41051163198605</v>
       </c>
       <c r="F404" t="n">
         <v>1084227</v>
@@ -8532,16 +8532,16 @@
         <v>45065</v>
       </c>
       <c r="B406" t="n">
-        <v>75.91145324707031</v>
+        <v>75.91144561767578</v>
       </c>
       <c r="C406" t="n">
-        <v>76.42976683949719</v>
+        <v>76.42975915801013</v>
       </c>
       <c r="D406" t="n">
-        <v>71.19388936375165</v>
+        <v>71.19388220849052</v>
       </c>
       <c r="E406" t="n">
-        <v>71.19388936375165</v>
+        <v>71.19388220849052</v>
       </c>
       <c r="F406" t="n">
         <v>1201246</v>
@@ -8572,16 +8572,16 @@
         <v>45069</v>
       </c>
       <c r="B408" t="n">
-        <v>77.132568359375</v>
+        <v>77.13256072998047</v>
       </c>
       <c r="C408" t="n">
-        <v>80.43573491118516</v>
+        <v>80.43572695506535</v>
       </c>
       <c r="D408" t="n">
-        <v>76.42976325763665</v>
+        <v>76.42975569775851</v>
       </c>
       <c r="E408" t="n">
-        <v>77.74751779656141</v>
+        <v>77.74751010634054</v>
       </c>
       <c r="F408" t="n">
         <v>970823</v>
@@ -8592,16 +8592,16 @@
         <v>45070</v>
       </c>
       <c r="B409" t="n">
-        <v>77.30826568603516</v>
+        <v>77.30825805664062</v>
       </c>
       <c r="C409" t="n">
-        <v>78.27461766662137</v>
+        <v>78.27460994185954</v>
       </c>
       <c r="D409" t="n">
-        <v>75.96415713911252</v>
+        <v>75.96414964236531</v>
       </c>
       <c r="E409" t="n">
-        <v>76.61424749660561</v>
+        <v>76.61423993570233</v>
       </c>
       <c r="F409" t="n">
         <v>567398</v>
@@ -8612,16 +8612,16 @@
         <v>45071</v>
       </c>
       <c r="B410" t="n">
-        <v>81.90283203125</v>
+        <v>81.90283966064453</v>
       </c>
       <c r="C410" t="n">
-        <v>81.90283203125</v>
+        <v>81.90283966064453</v>
       </c>
       <c r="D410" t="n">
-        <v>77.75629708276882</v>
+        <v>77.75630432590624</v>
       </c>
       <c r="E410" t="n">
-        <v>77.75629708276882</v>
+        <v>77.75630432590624</v>
       </c>
       <c r="F410" t="n">
         <v>1153989</v>
@@ -8632,16 +8632,16 @@
         <v>45072</v>
       </c>
       <c r="B411" t="n">
-        <v>82.75498199462891</v>
+        <v>82.75497436523438</v>
       </c>
       <c r="C411" t="n">
-        <v>84.15180528493505</v>
+        <v>84.15179752676379</v>
       </c>
       <c r="D411" t="n">
-        <v>80.38302651611544</v>
+        <v>80.38301910539758</v>
       </c>
       <c r="E411" t="n">
-        <v>81.70078104916651</v>
+        <v>81.70077351696148</v>
       </c>
       <c r="F411" t="n">
         <v>582166</v>
@@ -8652,16 +8652,16 @@
         <v>45075</v>
       </c>
       <c r="B412" t="n">
-        <v>81.52508544921875</v>
+        <v>81.52507781982422</v>
       </c>
       <c r="C412" t="n">
-        <v>83.1678818576769</v>
+        <v>83.1678740745439</v>
       </c>
       <c r="D412" t="n">
-        <v>80.73443136636509</v>
+        <v>80.73442381096265</v>
       </c>
       <c r="E412" t="n">
-        <v>82.66713538894396</v>
+        <v>82.66712765267252</v>
       </c>
       <c r="F412" t="n">
         <v>275309</v>
@@ -8672,16 +8672,16 @@
         <v>45076</v>
       </c>
       <c r="B413" t="n">
-        <v>80.55873107910156</v>
+        <v>80.55872344970703</v>
       </c>
       <c r="C413" t="n">
-        <v>84.13423840537149</v>
+        <v>84.13423043735499</v>
       </c>
       <c r="D413" t="n">
-        <v>79.3991072625396</v>
+        <v>79.3990997429684</v>
       </c>
       <c r="E413" t="n">
-        <v>82.54414994921937</v>
+        <v>82.54414213179378</v>
       </c>
       <c r="F413" t="n">
         <v>664894</v>
@@ -8732,16 +8732,16 @@
         <v>45079</v>
       </c>
       <c r="B416" t="n">
-        <v>82.84284210205078</v>
+        <v>82.84283447265625</v>
       </c>
       <c r="C416" t="n">
-        <v>84.02881990491723</v>
+        <v>84.02881216630033</v>
       </c>
       <c r="D416" t="n">
-        <v>78.89835849579498</v>
+        <v>78.89835122966686</v>
       </c>
       <c r="E416" t="n">
-        <v>78.89835849579498</v>
+        <v>78.89835122966686</v>
       </c>
       <c r="F416" t="n">
         <v>731024</v>
@@ -8772,16 +8772,16 @@
         <v>45083</v>
       </c>
       <c r="B418" t="n">
-        <v>83.89703369140625</v>
+        <v>83.89702606201172</v>
       </c>
       <c r="C418" t="n">
-        <v>86.708240516318</v>
+        <v>86.70823263127907</v>
       </c>
       <c r="D418" t="n">
-        <v>81.92040200757731</v>
+        <v>81.92039455793291</v>
       </c>
       <c r="E418" t="n">
-        <v>82.01703787053793</v>
+        <v>82.01703041210571</v>
       </c>
       <c r="F418" t="n">
         <v>1573579</v>
@@ -8892,16 +8892,16 @@
         <v>45092</v>
       </c>
       <c r="B424" t="n">
-        <v>91.97926330566406</v>
+        <v>91.97925567626953</v>
       </c>
       <c r="C424" t="n">
-        <v>92.26038400333246</v>
+        <v>92.26037635061984</v>
       </c>
       <c r="D424" t="n">
-        <v>89.18562344026418</v>
+        <v>89.18561604259341</v>
       </c>
       <c r="E424" t="n">
-        <v>89.43160991536439</v>
+        <v>89.4316024972898</v>
       </c>
       <c r="F424" t="n">
         <v>844482</v>
@@ -8932,16 +8932,16 @@
         <v>45096</v>
       </c>
       <c r="B426" t="n">
-        <v>98.03215026855469</v>
+        <v>98.03214263916016</v>
       </c>
       <c r="C426" t="n">
-        <v>98.33963169216599</v>
+        <v>98.33962403884159</v>
       </c>
       <c r="D426" t="n">
-        <v>94.14916846996442</v>
+        <v>94.14916114276463</v>
       </c>
       <c r="E426" t="n">
-        <v>94.61477400522099</v>
+        <v>94.61476664178524</v>
       </c>
       <c r="F426" t="n">
         <v>576522</v>
@@ -8992,16 +8992,16 @@
         <v>45099</v>
       </c>
       <c r="B429" t="n">
-        <v>99.27083587646484</v>
+        <v>99.27084350585938</v>
       </c>
       <c r="C429" t="n">
-        <v>104.858115316858</v>
+        <v>104.8581233756592</v>
       </c>
       <c r="D429" t="n">
-        <v>99.18298691971819</v>
+        <v>99.18299454236116</v>
       </c>
       <c r="E429" t="n">
-        <v>102.9605456793905</v>
+        <v>102.9605535923553</v>
       </c>
       <c r="F429" t="n">
         <v>1144936</v>
@@ -9012,16 +9012,16 @@
         <v>45100</v>
       </c>
       <c r="B430" t="n">
-        <v>98.56803131103516</v>
+        <v>98.56803894042969</v>
       </c>
       <c r="C430" t="n">
-        <v>100.544663008736</v>
+        <v>100.5446707911264</v>
       </c>
       <c r="D430" t="n">
-        <v>97.24149664189471</v>
+        <v>97.24150416861238</v>
       </c>
       <c r="E430" t="n">
-        <v>99.71008786179617</v>
+        <v>99.71009557958853</v>
       </c>
       <c r="F430" t="n">
         <v>1883788</v>
@@ -9032,16 +9032,16 @@
         <v>45103</v>
       </c>
       <c r="B431" t="n">
-        <v>97.00430297851562</v>
+        <v>97.00429534912109</v>
       </c>
       <c r="C431" t="n">
-        <v>99.27084240484157</v>
+        <v>99.27083459718358</v>
       </c>
       <c r="D431" t="n">
-        <v>95.75683028431621</v>
+        <v>95.75682275303549</v>
       </c>
       <c r="E431" t="n">
-        <v>98.46262122570784</v>
+        <v>98.46261348161649</v>
       </c>
       <c r="F431" t="n">
         <v>757098</v>
@@ -9092,16 +9092,16 @@
         <v>45106</v>
       </c>
       <c r="B434" t="n">
-        <v>99.08635711669922</v>
+        <v>99.08634948730469</v>
       </c>
       <c r="C434" t="n">
-        <v>99.83308334838433</v>
+        <v>99.83307566149379</v>
       </c>
       <c r="D434" t="n">
-        <v>97.4259869335896</v>
+        <v>97.4259794320393</v>
       </c>
       <c r="E434" t="n">
-        <v>97.53140300715454</v>
+        <v>97.53139549748747</v>
       </c>
       <c r="F434" t="n">
         <v>506881</v>
@@ -9132,16 +9132,16 @@
         <v>45110</v>
       </c>
       <c r="B436" t="n">
-        <v>100.8960723876953</v>
+        <v>100.8960647583008</v>
       </c>
       <c r="C436" t="n">
-        <v>101.4671007018312</v>
+        <v>101.4670930292576</v>
       </c>
       <c r="D436" t="n">
-        <v>98.26056327855684</v>
+        <v>98.26055584844994</v>
       </c>
       <c r="E436" t="n">
-        <v>98.46262192600048</v>
+        <v>98.46261448061463</v>
       </c>
       <c r="F436" t="n">
         <v>512630</v>
@@ -9172,16 +9172,16 @@
         <v>45112</v>
       </c>
       <c r="B438" t="n">
-        <v>101.2386779785156</v>
+        <v>101.2386932373047</v>
       </c>
       <c r="C438" t="n">
-        <v>101.7042834691515</v>
+        <v>101.7042987981171</v>
       </c>
       <c r="D438" t="n">
-        <v>99.13026956016742</v>
+        <v>99.13028450117518</v>
       </c>
       <c r="E438" t="n">
-        <v>99.5343868149092</v>
+        <v>99.53440181682589</v>
       </c>
       <c r="F438" t="n">
         <v>519657</v>
@@ -9212,16 +9212,16 @@
         <v>45114</v>
       </c>
       <c r="B440" t="n">
-        <v>101.2386779785156</v>
+        <v>101.2386932373047</v>
       </c>
       <c r="C440" t="n">
-        <v>102.0820400053658</v>
+        <v>102.0820553912672</v>
       </c>
       <c r="D440" t="n">
-        <v>98.16391765663779</v>
+        <v>98.16393245199608</v>
       </c>
       <c r="E440" t="n">
-        <v>98.73494591404707</v>
+        <v>98.73496079547128</v>
       </c>
       <c r="F440" t="n">
         <v>1239341</v>
@@ -9232,16 +9232,16 @@
         <v>45117</v>
       </c>
       <c r="B441" t="n">
-        <v>98.26055908203125</v>
+        <v>98.26055145263672</v>
       </c>
       <c r="C441" t="n">
-        <v>100.7467241773928</v>
+        <v>100.7467163549612</v>
       </c>
       <c r="D441" t="n">
-        <v>97.19757125770386</v>
+        <v>97.19756371084451</v>
       </c>
       <c r="E441" t="n">
-        <v>100.7467241773928</v>
+        <v>100.7467163549612</v>
       </c>
       <c r="F441" t="n">
         <v>1057552</v>
@@ -9252,16 +9252,16 @@
         <v>45118</v>
       </c>
       <c r="B442" t="n">
-        <v>99.71009826660156</v>
+        <v>99.71009063720703</v>
       </c>
       <c r="C442" t="n">
-        <v>99.71009826660156</v>
+        <v>99.71009063720703</v>
       </c>
       <c r="D442" t="n">
-        <v>94.74655458949289</v>
+        <v>94.7465473398877</v>
       </c>
       <c r="E442" t="n">
-        <v>97.715899250346</v>
+        <v>97.71589177353913</v>
       </c>
       <c r="F442" t="n">
         <v>867229</v>
@@ -9372,16 +9372,16 @@
         <v>45126</v>
       </c>
       <c r="B448" t="n">
-        <v>101.0629959106445</v>
+        <v>101.06298828125</v>
       </c>
       <c r="C448" t="n">
-        <v>101.2650478672402</v>
+        <v>101.2650402225924</v>
       </c>
       <c r="D448" t="n">
-        <v>99.00729520224239</v>
+        <v>99.00728772803575</v>
       </c>
       <c r="E448" t="n">
-        <v>100.8257963238363</v>
+        <v>100.8257887123484</v>
       </c>
       <c r="F448" t="n">
         <v>1189852</v>
@@ -9432,16 +9432,16 @@
         <v>45131</v>
       </c>
       <c r="B451" t="n">
-        <v>112.6240844726562</v>
+        <v>112.6240768432617</v>
       </c>
       <c r="C451" t="n">
-        <v>113.1160440190282</v>
+        <v>113.1160363563073</v>
       </c>
       <c r="D451" t="n">
-        <v>109.3033441297533</v>
+        <v>109.3033367253127</v>
       </c>
       <c r="E451" t="n">
-        <v>110.85829822838</v>
+        <v>110.8582907186036</v>
       </c>
       <c r="F451" t="n">
         <v>870351</v>
@@ -9472,16 +9472,16 @@
         <v>45133</v>
       </c>
       <c r="B453" t="n">
-        <v>113.8891296386719</v>
+        <v>113.8891220092773</v>
       </c>
       <c r="C453" t="n">
-        <v>113.9857655059323</v>
+        <v>113.9857578700642</v>
       </c>
       <c r="D453" t="n">
-        <v>110.5508155209108</v>
+        <v>110.5508081151489</v>
       </c>
       <c r="E453" t="n">
-        <v>111.0427817639948</v>
+        <v>111.0427743252761</v>
       </c>
       <c r="F453" t="n">
         <v>810223</v>
@@ -9512,16 +9512,16 @@
         <v>45135</v>
       </c>
       <c r="B455" t="n">
-        <v>109.8919525146484</v>
+        <v>109.8919372558594</v>
       </c>
       <c r="C455" t="n">
-        <v>111.991581146317</v>
+        <v>111.9915655959889</v>
       </c>
       <c r="D455" t="n">
-        <v>108.0558842034873</v>
+        <v>108.0558691996412</v>
       </c>
       <c r="E455" t="n">
-        <v>110.691393574304</v>
+        <v>110.6913782045105</v>
       </c>
       <c r="F455" t="n">
         <v>651013</v>
@@ -9552,16 +9552,16 @@
         <v>45139</v>
       </c>
       <c r="B457" t="n">
-        <v>113.2302474975586</v>
+        <v>113.2302627563477</v>
       </c>
       <c r="C457" t="n">
-        <v>113.6343647627333</v>
+        <v>113.6343800759808</v>
       </c>
       <c r="D457" t="n">
-        <v>109.1803482614203</v>
+        <v>109.1803629744492</v>
       </c>
       <c r="E457" t="n">
-        <v>111.5698774170749</v>
+        <v>111.5698924521143</v>
       </c>
       <c r="F457" t="n">
         <v>739423</v>
@@ -9572,16 +9572,16 @@
         <v>45140</v>
       </c>
       <c r="B458" t="n">
-        <v>112.2726898193359</v>
+        <v>112.2726821899414</v>
       </c>
       <c r="C458" t="n">
-        <v>112.4220337257216</v>
+        <v>112.4220260861785</v>
       </c>
       <c r="D458" t="n">
-        <v>108.6620418329161</v>
+        <v>108.66203444888</v>
       </c>
       <c r="E458" t="n">
-        <v>111.6928746028557</v>
+        <v>111.692867012862</v>
       </c>
       <c r="F458" t="n">
         <v>921444</v>
@@ -9652,16 +9652,16 @@
         <v>45146</v>
       </c>
       <c r="B462" t="n">
-        <v>113.5904312133789</v>
+        <v>113.590446472168</v>
       </c>
       <c r="C462" t="n">
-        <v>113.5904312133789</v>
+        <v>113.590446472168</v>
       </c>
       <c r="D462" t="n">
-        <v>109.3033326373628</v>
+        <v>109.3033473202589</v>
       </c>
       <c r="E462" t="n">
-        <v>111.8685595772261</v>
+        <v>111.8685746047133</v>
       </c>
       <c r="F462" t="n">
         <v>457201</v>
@@ -9672,16 +9672,16 @@
         <v>45147</v>
       </c>
       <c r="B463" t="n">
-        <v>112.4483795166016</v>
+        <v>112.4483871459961</v>
       </c>
       <c r="C463" t="n">
-        <v>114.1263233968748</v>
+        <v>114.1263311401144</v>
       </c>
       <c r="D463" t="n">
-        <v>110.612311536981</v>
+        <v>110.612319041802</v>
       </c>
       <c r="E463" t="n">
-        <v>113.7397799475038</v>
+        <v>113.7397876645173</v>
       </c>
       <c r="F463" t="n">
         <v>434571</v>
@@ -9692,16 +9692,16 @@
         <v>45148</v>
       </c>
       <c r="B464" t="n">
-        <v>110.5156860351562</v>
+        <v>110.5156784057617</v>
       </c>
       <c r="C464" t="n">
-        <v>114.5919396385741</v>
+        <v>114.5919317277774</v>
       </c>
       <c r="D464" t="n">
-        <v>109.2857804284043</v>
+        <v>109.2857728839157</v>
       </c>
       <c r="E464" t="n">
-        <v>111.7455849394619</v>
+        <v>111.7455772251619</v>
       </c>
       <c r="F464" t="n">
         <v>733254</v>
@@ -9712,16 +9712,16 @@
         <v>45149</v>
       </c>
       <c r="B465" t="n">
-        <v>109.812873840332</v>
+        <v>109.8128814697266</v>
       </c>
       <c r="C465" t="n">
-        <v>111.9915642064004</v>
+        <v>111.9915719871623</v>
       </c>
       <c r="D465" t="n">
-        <v>108.1261497067316</v>
+        <v>108.1261572189387</v>
       </c>
       <c r="E465" t="n">
-        <v>110.7353046615692</v>
+        <v>110.7353123550508</v>
       </c>
       <c r="F465" t="n">
         <v>577766</v>
@@ -9772,16 +9772,16 @@
         <v>45154</v>
       </c>
       <c r="B468" t="n">
-        <v>108.6444702148438</v>
+        <v>108.6444625854492</v>
       </c>
       <c r="C468" t="n">
-        <v>111.8422207697557</v>
+        <v>111.842212915804</v>
       </c>
       <c r="D468" t="n">
-        <v>107.0983096778717</v>
+        <v>107.098302157054</v>
       </c>
       <c r="E468" t="n">
-        <v>108.2403596175138</v>
+        <v>108.2403520164973</v>
       </c>
       <c r="F468" t="n">
         <v>1047832</v>
@@ -9792,16 +9792,16 @@
         <v>45155</v>
       </c>
       <c r="B469" t="n">
-        <v>103.6633529663086</v>
+        <v>103.6633605957031</v>
       </c>
       <c r="C469" t="n">
-        <v>109.7689460744476</v>
+        <v>109.7689541532003</v>
       </c>
       <c r="D469" t="n">
-        <v>103.048403553419</v>
+        <v>103.0484111375546</v>
       </c>
       <c r="E469" t="n">
-        <v>108.9782987442884</v>
+        <v>108.9783067648512</v>
       </c>
       <c r="F469" t="n">
         <v>1841816</v>
@@ -9812,16 +9812,16 @@
         <v>45156</v>
       </c>
       <c r="B470" t="n">
-        <v>109.1540069580078</v>
+        <v>109.1539993286133</v>
       </c>
       <c r="C470" t="n">
-        <v>109.2242888125237</v>
+        <v>109.2242811782168</v>
       </c>
       <c r="D470" t="n">
-        <v>104.6912097329484</v>
+        <v>104.6912024154841</v>
       </c>
       <c r="E470" t="n">
-        <v>106.2549441324704</v>
+        <v>106.2549367057079</v>
       </c>
       <c r="F470" t="n">
         <v>1642163</v>
@@ -9872,16 +9872,16 @@
         <v>45161</v>
       </c>
       <c r="B473" t="n">
-        <v>117.4295043945312</v>
+        <v>117.4294891357422</v>
       </c>
       <c r="C473" t="n">
-        <v>117.939037786479</v>
+        <v>117.9390224614812</v>
       </c>
       <c r="D473" t="n">
-        <v>112.949146756193</v>
+        <v>112.9491320795816</v>
       </c>
       <c r="E473" t="n">
-        <v>114.0297017847773</v>
+        <v>114.0296869677586</v>
       </c>
       <c r="F473" t="n">
         <v>1193312</v>
@@ -9912,16 +9912,16 @@
         <v>45163</v>
       </c>
       <c r="B475" t="n">
-        <v>110.4278182983398</v>
+        <v>110.4278259277344</v>
       </c>
       <c r="C475" t="n">
-        <v>112.7997735858911</v>
+        <v>112.7997813791627</v>
       </c>
       <c r="D475" t="n">
-        <v>108.5917503472816</v>
+        <v>108.5917578498233</v>
       </c>
       <c r="E475" t="n">
-        <v>112.6240756766079</v>
+        <v>112.6240834577406</v>
       </c>
       <c r="F475" t="n">
         <v>1445522</v>
@@ -9952,16 +9952,16 @@
         <v>45167</v>
       </c>
       <c r="B477" t="n">
-        <v>113.3181076049805</v>
+        <v>113.3180999755859</v>
       </c>
       <c r="C477" t="n">
-        <v>113.3620220313805</v>
+        <v>113.3620143990293</v>
       </c>
       <c r="D477" t="n">
-        <v>109.426332316645</v>
+        <v>109.4263249492729</v>
       </c>
       <c r="E477" t="n">
-        <v>112.0091332998718</v>
+        <v>112.0091257586069</v>
       </c>
       <c r="F477" t="n">
         <v>768114</v>
@@ -9972,16 +9972,16 @@
         <v>45168</v>
       </c>
       <c r="B478" t="n">
-        <v>112.4483795166016</v>
+        <v>112.4483871459961</v>
       </c>
       <c r="C478" t="n">
-        <v>113.8539896225157</v>
+        <v>113.853997347278</v>
       </c>
       <c r="D478" t="n">
-        <v>110.8231503718898</v>
+        <v>110.8231578910159</v>
       </c>
       <c r="E478" t="n">
-        <v>113.0721225198849</v>
+        <v>113.0721301915992</v>
       </c>
       <c r="F478" t="n">
         <v>547646</v>
@@ -10072,16 +10072,16 @@
         <v>45175</v>
       </c>
       <c r="B483" t="n">
-        <v>110.331184387207</v>
+        <v>110.3311920166016</v>
       </c>
       <c r="C483" t="n">
-        <v>113.1072569795688</v>
+        <v>113.1072648009286</v>
       </c>
       <c r="D483" t="n">
-        <v>108.3106315849618</v>
+        <v>108.3106390746352</v>
       </c>
       <c r="E483" t="n">
-        <v>110.471748079074</v>
+        <v>110.4717557181885</v>
       </c>
       <c r="F483" t="n">
         <v>1014845</v>
@@ -10092,16 +10092,16 @@
         <v>45177</v>
       </c>
       <c r="B484" t="n">
-        <v>108.5126876831055</v>
+        <v>108.5126953125</v>
       </c>
       <c r="C484" t="n">
-        <v>110.7968008465816</v>
+        <v>110.7968086365694</v>
       </c>
       <c r="D484" t="n">
-        <v>106.7293276643105</v>
+        <v>106.7293351683192</v>
       </c>
       <c r="E484" t="n">
-        <v>109.8128750730466</v>
+        <v>109.8128827938557</v>
       </c>
       <c r="F484" t="n">
         <v>972821</v>
@@ -10132,16 +10132,16 @@
         <v>45181</v>
       </c>
       <c r="B486" t="n">
-        <v>112.4489898681641</v>
+        <v>112.4489974975586</v>
       </c>
       <c r="C486" t="n">
-        <v>113.6994220864307</v>
+        <v>113.6994298006641</v>
       </c>
       <c r="D486" t="n">
-        <v>109.6602562921019</v>
+        <v>109.6602637322876</v>
       </c>
       <c r="E486" t="n">
-        <v>109.7592119522533</v>
+        <v>109.7592193991528</v>
       </c>
       <c r="F486" t="n">
         <v>550963</v>
@@ -10212,16 +10212,16 @@
         <v>45187</v>
       </c>
       <c r="B490" t="n">
-        <v>115.6785125732422</v>
+        <v>115.6785202026367</v>
       </c>
       <c r="C490" t="n">
-        <v>116.2092684697702</v>
+        <v>116.2092761341699</v>
       </c>
       <c r="D490" t="n">
-        <v>112.7188614296512</v>
+        <v>112.7188688638466</v>
       </c>
       <c r="E490" t="n">
-        <v>114.6979607521958</v>
+        <v>114.6979683169196</v>
       </c>
       <c r="F490" t="n">
         <v>402829</v>
@@ -10232,16 +10232,16 @@
         <v>45188</v>
       </c>
       <c r="B491" t="n">
-        <v>111.9991836547852</v>
+        <v>111.9991912841797</v>
       </c>
       <c r="C491" t="n">
-        <v>115.9573822450846</v>
+        <v>115.957390144112</v>
       </c>
       <c r="D491" t="n">
-        <v>111.2705164634207</v>
+        <v>111.2705240431784</v>
       </c>
       <c r="E491" t="n">
-        <v>115.3366754082542</v>
+        <v>115.336683264999</v>
       </c>
       <c r="F491" t="n">
         <v>598810</v>
@@ -10292,16 +10292,16 @@
         <v>45191</v>
       </c>
       <c r="B494" t="n">
-        <v>103.8129043579102</v>
+        <v>103.8128967285156</v>
       </c>
       <c r="C494" t="n">
-        <v>105.8639727468323</v>
+        <v>105.8639649667011</v>
       </c>
       <c r="D494" t="n">
-        <v>103.2011816047806</v>
+        <v>103.2011740203427</v>
       </c>
       <c r="E494" t="n">
-        <v>105.0903231807173</v>
+        <v>105.090315457443</v>
       </c>
       <c r="F494" t="n">
         <v>394595</v>
@@ -10312,16 +10312,16 @@
         <v>45194</v>
       </c>
       <c r="B495" t="n">
-        <v>103.525032043457</v>
+        <v>103.5250396728516</v>
       </c>
       <c r="C495" t="n">
-        <v>104.2986815857532</v>
+        <v>104.2986892721627</v>
       </c>
       <c r="D495" t="n">
-        <v>102.3825465471945</v>
+        <v>102.3825540923923</v>
       </c>
       <c r="E495" t="n">
-        <v>103.8938611340822</v>
+        <v>103.893868790658</v>
       </c>
       <c r="F495" t="n">
         <v>399935</v>
@@ -10372,16 +10372,16 @@
         <v>45197</v>
       </c>
       <c r="B498" t="n">
-        <v>104.352653503418</v>
+        <v>104.3526611328125</v>
       </c>
       <c r="C498" t="n">
-        <v>104.352653503418</v>
+        <v>104.3526611328125</v>
       </c>
       <c r="D498" t="n">
-        <v>99.09904044902891</v>
+        <v>99.09904769432313</v>
       </c>
       <c r="E498" t="n">
-        <v>100.7542861412311</v>
+        <v>100.7542935075431</v>
       </c>
       <c r="F498" t="n">
         <v>896625</v>
@@ -10432,16 +10432,16 @@
         <v>45202</v>
       </c>
       <c r="B501" t="n">
-        <v>99.56683349609375</v>
+        <v>99.56682586669922</v>
       </c>
       <c r="C501" t="n">
-        <v>103.7859217766522</v>
+        <v>103.7859138239664</v>
       </c>
       <c r="D501" t="n">
-        <v>98.79318389958749</v>
+        <v>98.79317632947452</v>
       </c>
       <c r="E501" t="n">
-        <v>103.354114637281</v>
+        <v>103.3541067176828</v>
       </c>
       <c r="F501" t="n">
         <v>596480</v>
@@ -10452,16 +10452,16 @@
         <v>45203</v>
       </c>
       <c r="B502" t="n">
-        <v>101.7978210449219</v>
+        <v>101.7978134155273</v>
       </c>
       <c r="C502" t="n">
-        <v>102.1666501489935</v>
+        <v>102.1666424919565</v>
       </c>
       <c r="D502" t="n">
-        <v>98.96410523328106</v>
+        <v>98.96409781626373</v>
       </c>
       <c r="E502" t="n">
-        <v>99.85469927807969</v>
+        <v>99.85469179431541</v>
       </c>
       <c r="F502" t="n">
         <v>483635</v>
@@ -10492,16 +10492,16 @@
         <v>45205</v>
       </c>
       <c r="B504" t="n">
-        <v>101.6628799438477</v>
+        <v>101.6628875732422</v>
       </c>
       <c r="C504" t="n">
-        <v>102.3015893529314</v>
+        <v>102.3015970302585</v>
       </c>
       <c r="D504" t="n">
-        <v>97.81262780833357</v>
+        <v>97.81263514878201</v>
       </c>
       <c r="E504" t="n">
-        <v>102.1216668595224</v>
+        <v>102.1216745233471</v>
       </c>
       <c r="F504" t="n">
         <v>1185062</v>
@@ -10612,16 +10612,16 @@
         <v>45216</v>
       </c>
       <c r="B510" t="n">
-        <v>97.14692687988281</v>
+        <v>97.14693450927734</v>
       </c>
       <c r="C510" t="n">
-        <v>97.86660314166811</v>
+        <v>97.86661082758212</v>
       </c>
       <c r="D510" t="n">
-        <v>95.20381195440891</v>
+        <v>95.20381943120169</v>
       </c>
       <c r="E510" t="n">
-        <v>96.69713093210238</v>
+        <v>96.69713852617237</v>
       </c>
       <c r="F510" t="n">
         <v>593712</v>
@@ -10632,16 +10632,16 @@
         <v>45217</v>
       </c>
       <c r="B511" t="n">
-        <v>93.6925048828125</v>
+        <v>93.69249725341797</v>
       </c>
       <c r="C511" t="n">
-        <v>96.61617878015257</v>
+        <v>96.61617091268285</v>
       </c>
       <c r="D511" t="n">
-        <v>92.67596156596765</v>
+        <v>92.6759540193504</v>
       </c>
       <c r="E511" t="n">
-        <v>96.61617878015257</v>
+        <v>96.61617091268285</v>
       </c>
       <c r="F511" t="n">
         <v>964239</v>
@@ -10652,16 +10652,16 @@
         <v>45218</v>
       </c>
       <c r="B512" t="n">
-        <v>94.34918975830078</v>
+        <v>94.34919738769531</v>
       </c>
       <c r="C512" t="n">
-        <v>95.99544447357339</v>
+        <v>95.99545223608963</v>
       </c>
       <c r="D512" t="n">
-        <v>92.76591306066892</v>
+        <v>92.76592056203434</v>
       </c>
       <c r="E512" t="n">
-        <v>93.46759359810548</v>
+        <v>93.46760115621116</v>
       </c>
       <c r="F512" t="n">
         <v>760940</v>
@@ -10672,16 +10672,16 @@
         <v>45219</v>
       </c>
       <c r="B513" t="n">
-        <v>96.25634002685547</v>
+        <v>96.25633239746094</v>
       </c>
       <c r="C513" t="n">
-        <v>96.43625567409222</v>
+        <v>96.43624803043737</v>
       </c>
       <c r="D513" t="n">
-        <v>93.06278581333794</v>
+        <v>93.0627784370684</v>
       </c>
       <c r="E513" t="n">
-        <v>93.27869282603245</v>
+        <v>93.27868543264987</v>
       </c>
       <c r="F513" t="n">
         <v>605848</v>
@@ -10692,16 +10692,16 @@
         <v>45222</v>
       </c>
       <c r="B514" t="n">
-        <v>96.25634002685547</v>
+        <v>96.25633239746094</v>
       </c>
       <c r="C514" t="n">
-        <v>97.29087215682185</v>
+        <v>97.29086444542904</v>
       </c>
       <c r="D514" t="n">
-        <v>93.93539111545444</v>
+        <v>93.93538367002114</v>
       </c>
       <c r="E514" t="n">
-        <v>96.0764243796187</v>
+        <v>96.07641676448451</v>
       </c>
       <c r="F514" t="n">
         <v>469364</v>
@@ -10712,16 +10712,16 @@
         <v>45223</v>
       </c>
       <c r="B515" t="n">
-        <v>93.5125732421875</v>
+        <v>93.51258087158203</v>
       </c>
       <c r="C515" t="n">
-        <v>98.39735742833496</v>
+        <v>98.39736545626356</v>
       </c>
       <c r="D515" t="n">
-        <v>93.38663092797195</v>
+        <v>93.38663854709125</v>
       </c>
       <c r="E515" t="n">
-        <v>96.71512500416665</v>
+        <v>96.71513289484724</v>
       </c>
       <c r="F515" t="n">
         <v>956700</v>
@@ -10852,16 +10852,16 @@
         <v>45233</v>
       </c>
       <c r="B522" t="n">
-        <v>94.61007690429688</v>
+        <v>94.61006927490234</v>
       </c>
       <c r="C522" t="n">
-        <v>97.14692574562541</v>
+        <v>97.14691791165838</v>
       </c>
       <c r="D522" t="n">
-        <v>92.08222590355452</v>
+        <v>92.08221847800689</v>
       </c>
       <c r="E522" t="n">
-        <v>92.70294650051345</v>
+        <v>92.70293902491068</v>
       </c>
       <c r="F522" t="n">
         <v>760712</v>
@@ -10872,16 +10872,16 @@
         <v>45236</v>
       </c>
       <c r="B523" t="n">
-        <v>92.21717071533203</v>
+        <v>92.2171630859375</v>
       </c>
       <c r="C523" t="n">
-        <v>95.98645623697459</v>
+        <v>95.9864482957361</v>
       </c>
       <c r="D523" t="n">
-        <v>91.38954092314988</v>
+        <v>91.38953336222757</v>
       </c>
       <c r="E523" t="n">
-        <v>95.13184664835444</v>
+        <v>95.13183877782029</v>
       </c>
       <c r="F523" t="n">
         <v>393989</v>
@@ -10892,16 +10892,16 @@
         <v>45237</v>
       </c>
       <c r="B524" t="n">
-        <v>97.12894439697266</v>
+        <v>97.12893676757812</v>
       </c>
       <c r="C524" t="n">
-        <v>97.12894439697266</v>
+        <v>97.12893676757812</v>
       </c>
       <c r="D524" t="n">
-        <v>91.57846368653991</v>
+        <v>91.57845649313083</v>
       </c>
       <c r="E524" t="n">
-        <v>92.02825966365781</v>
+        <v>92.02825243491765</v>
       </c>
       <c r="F524" t="n">
         <v>722184</v>
@@ -10912,16 +10912,16 @@
         <v>45238</v>
       </c>
       <c r="B525" t="n">
-        <v>96.40926361083984</v>
+        <v>96.40927124023438</v>
       </c>
       <c r="C525" t="n">
-        <v>98.50531441406719</v>
+        <v>98.50532220933374</v>
       </c>
       <c r="D525" t="n">
-        <v>95.54565619848189</v>
+        <v>95.54566375953443</v>
       </c>
       <c r="E525" t="n">
-        <v>97.11094420442183</v>
+        <v>97.11095188934421</v>
       </c>
       <c r="F525" t="n">
         <v>449324</v>
@@ -10972,16 +10972,16 @@
         <v>45243</v>
       </c>
       <c r="B528" t="n">
-        <v>98.83817291259766</v>
+        <v>98.83816528320312</v>
       </c>
       <c r="C528" t="n">
-        <v>100.3135032047476</v>
+        <v>100.3134954614712</v>
       </c>
       <c r="D528" t="n">
-        <v>96.80509312430634</v>
+        <v>96.80508565184681</v>
       </c>
       <c r="E528" t="n">
-        <v>98.95511739872026</v>
+        <v>98.9551097602987</v>
       </c>
       <c r="F528" t="n">
         <v>702632</v>
@@ -11052,16 +11052,16 @@
         <v>45250</v>
       </c>
       <c r="B532" t="n">
-        <v>102.5534820556641</v>
+        <v>102.5534744262695</v>
       </c>
       <c r="C532" t="n">
-        <v>104.5685660971273</v>
+        <v>104.5685583178221</v>
       </c>
       <c r="D532" t="n">
-        <v>100.9881939881291</v>
+        <v>100.9881864751831</v>
       </c>
       <c r="E532" t="n">
-        <v>103.6329896477554</v>
+        <v>103.6329819380516</v>
       </c>
       <c r="F532" t="n">
         <v>946377</v>
@@ -11072,16 +11072,16 @@
         <v>45251</v>
       </c>
       <c r="B533" t="n">
-        <v>100.2595062255859</v>
+        <v>100.2595138549805</v>
       </c>
       <c r="C533" t="n">
-        <v>103.0932218491147</v>
+        <v>103.0932296941449</v>
       </c>
       <c r="D533" t="n">
-        <v>99.13501644349843</v>
+        <v>99.13502398732325</v>
       </c>
       <c r="E533" t="n">
-        <v>102.5804547830164</v>
+        <v>102.5804625890269</v>
       </c>
       <c r="F533" t="n">
         <v>1091156</v>
@@ -11132,16 +11132,16 @@
         <v>45254</v>
       </c>
       <c r="B536" t="n">
-        <v>103.5430221557617</v>
+        <v>103.5430297851562</v>
       </c>
       <c r="C536" t="n">
-        <v>104.3526562058894</v>
+        <v>104.3526638949405</v>
       </c>
       <c r="D536" t="n">
-        <v>100.9522000586942</v>
+        <v>100.9522074971883</v>
       </c>
       <c r="E536" t="n">
-        <v>103.2731487146133</v>
+        <v>103.2731563241227</v>
       </c>
       <c r="F536" t="n">
         <v>447021</v>
@@ -11152,16 +11152,16 @@
         <v>45257</v>
       </c>
       <c r="B537" t="n">
-        <v>102.1036834716797</v>
+        <v>102.1036758422852</v>
       </c>
       <c r="C537" t="n">
-        <v>103.9028673214009</v>
+        <v>103.9028595575677</v>
       </c>
       <c r="D537" t="n">
-        <v>101.4739718696139</v>
+        <v>101.4739642872727</v>
       </c>
       <c r="E537" t="n">
-        <v>102.8233597569049</v>
+        <v>102.8233520737347</v>
       </c>
       <c r="F537" t="n">
         <v>311562</v>
@@ -11352,16 +11352,16 @@
         <v>45271</v>
       </c>
       <c r="B547" t="n">
-        <v>103.1921920776367</v>
+        <v>103.1921844482422</v>
       </c>
       <c r="C547" t="n">
-        <v>106.4127329157239</v>
+        <v>106.4127250482224</v>
       </c>
       <c r="D547" t="n">
-        <v>103.1921920776367</v>
+        <v>103.1921844482422</v>
       </c>
       <c r="E547" t="n">
-        <v>105.3782007973801</v>
+        <v>105.3781930063656</v>
       </c>
       <c r="F547" t="n">
         <v>558243</v>
@@ -11372,16 +11372,16 @@
         <v>45272</v>
       </c>
       <c r="B548" t="n">
-        <v>104.2786865234375</v>
+        <v>104.278694152832</v>
       </c>
       <c r="C548" t="n">
-        <v>106.2836923282544</v>
+        <v>106.2837001043422</v>
       </c>
       <c r="D548" t="n">
-        <v>102.0787578609517</v>
+        <v>102.0787653293918</v>
       </c>
       <c r="E548" t="n">
-        <v>105.7267486320019</v>
+        <v>105.7267563673418</v>
       </c>
       <c r="F548" t="n">
         <v>686347</v>
@@ -11432,16 +11432,16 @@
         <v>45275</v>
       </c>
       <c r="B551" t="n">
-        <v>114.2387237548828</v>
+        <v>114.2387313842773</v>
       </c>
       <c r="C551" t="n">
-        <v>118.8149563409803</v>
+        <v>118.814964275997</v>
       </c>
       <c r="D551" t="n">
-        <v>110.9341850478647</v>
+        <v>110.9341924565668</v>
       </c>
       <c r="E551" t="n">
-        <v>115.4640027088722</v>
+        <v>115.4640104200966</v>
       </c>
       <c r="F551" t="n">
         <v>3143296</v>
@@ -11492,16 +11492,16 @@
         <v>45280</v>
       </c>
       <c r="B554" t="n">
-        <v>119.1769714355469</v>
+        <v>119.1769790649414</v>
       </c>
       <c r="C554" t="n">
-        <v>122.5186477857772</v>
+        <v>122.518655629097</v>
       </c>
       <c r="D554" t="n">
-        <v>118.0352379174876</v>
+        <v>118.0352454737914</v>
       </c>
       <c r="E554" t="n">
-        <v>121.5996832485022</v>
+        <v>121.5996910329923</v>
       </c>
       <c r="F554" t="n">
         <v>920819</v>
@@ -11512,16 +11512,16 @@
         <v>45281</v>
       </c>
       <c r="B555" t="n">
-        <v>118.4436569213867</v>
+        <v>118.4436645507812</v>
       </c>
       <c r="C555" t="n">
-        <v>120.485793210847</v>
+        <v>120.4858009717831</v>
       </c>
       <c r="D555" t="n">
-        <v>116.55004272509</v>
+        <v>116.5500502325098</v>
       </c>
       <c r="E555" t="n">
-        <v>119.8360267580643</v>
+        <v>119.8360344771465</v>
       </c>
       <c r="F555" t="n">
         <v>410768</v>
@@ -11632,16 +11632,16 @@
         <v>45294</v>
       </c>
       <c r="B561" t="n">
-        <v>113.2455139160156</v>
+        <v>113.2455062866211</v>
       </c>
       <c r="C561" t="n">
-        <v>116.2437384250845</v>
+        <v>116.2437305936984</v>
       </c>
       <c r="D561" t="n">
-        <v>113.2455139160156</v>
+        <v>113.2455062866211</v>
       </c>
       <c r="E561" t="n">
-        <v>115.7517642600759</v>
+        <v>115.7517564618344</v>
       </c>
       <c r="F561" t="n">
         <v>798887</v>
@@ -11652,16 +11652,16 @@
         <v>45295</v>
       </c>
       <c r="B562" t="n">
-        <v>109.9688262939453</v>
+        <v>109.9688186645508</v>
       </c>
       <c r="C562" t="n">
-        <v>114.2387378997589</v>
+        <v>114.2387299741274</v>
       </c>
       <c r="D562" t="n">
-        <v>109.9688262939453</v>
+        <v>109.9688186645508</v>
       </c>
       <c r="E562" t="n">
-        <v>113.338342064144</v>
+        <v>113.3383342009799</v>
       </c>
       <c r="F562" t="n">
         <v>1652695</v>
@@ -11672,16 +11672,16 @@
         <v>45296</v>
       </c>
       <c r="B563" t="n">
-        <v>115.6310958862305</v>
+        <v>115.6310882568359</v>
       </c>
       <c r="C563" t="n">
-        <v>115.6310958862305</v>
+        <v>115.6310882568359</v>
       </c>
       <c r="D563" t="n">
-        <v>109.7181922963609</v>
+        <v>109.7181850571025</v>
       </c>
       <c r="E563" t="n">
-        <v>110.182313257144</v>
+        <v>110.1823059872627</v>
       </c>
       <c r="F563" t="n">
         <v>1732820</v>
@@ -11732,16 +11732,16 @@
         <v>45301</v>
       </c>
       <c r="B566" t="n">
-        <v>113.9788284301758</v>
+        <v>113.9788208007812</v>
       </c>
       <c r="C566" t="n">
-        <v>114.5172104539405</v>
+        <v>114.5172027885083</v>
       </c>
       <c r="D566" t="n">
-        <v>111.9738224445379</v>
+        <v>111.9738149493523</v>
       </c>
       <c r="E566" t="n">
-        <v>114.1737583873477</v>
+        <v>114.1737507449051</v>
       </c>
       <c r="F566" t="n">
         <v>497776</v>
@@ -11792,16 +11792,16 @@
         <v>45306</v>
       </c>
       <c r="B569" t="n">
-        <v>118.2580184936523</v>
+        <v>118.2580261230469</v>
       </c>
       <c r="C569" t="n">
-        <v>120.5786161424443</v>
+        <v>120.5786239215518</v>
       </c>
       <c r="D569" t="n">
-        <v>115.6589383624814</v>
+        <v>115.6589458241968</v>
       </c>
       <c r="E569" t="n">
-        <v>116.6707257076737</v>
+        <v>116.6707332346643</v>
       </c>
       <c r="F569" t="n">
         <v>875695</v>
@@ -11812,16 +11812,16 @@
         <v>45307</v>
       </c>
       <c r="B570" t="n">
-        <v>116.5871810913086</v>
+        <v>116.5871734619141</v>
       </c>
       <c r="C570" t="n">
-        <v>118.2487349402539</v>
+        <v>118.2487272021283</v>
       </c>
       <c r="D570" t="n">
-        <v>115.2969254183267</v>
+        <v>115.2969178733657</v>
       </c>
       <c r="E570" t="n">
-        <v>118.2487349402539</v>
+        <v>118.2487272021283</v>
       </c>
       <c r="F570" t="n">
         <v>641403</v>
@@ -11872,16 +11872,16 @@
         <v>45310</v>
       </c>
       <c r="B573" t="n">
-        <v>115.9281311035156</v>
+        <v>115.9281234741211</v>
       </c>
       <c r="C573" t="n">
-        <v>115.9281311035156</v>
+        <v>115.9281234741211</v>
       </c>
       <c r="D573" t="n">
-        <v>112.7628298858442</v>
+        <v>112.7628224647626</v>
       </c>
       <c r="E573" t="n">
-        <v>113.7838945663213</v>
+        <v>113.783887078042</v>
       </c>
       <c r="F573" t="n">
         <v>461986</v>
@@ -11892,16 +11892,16 @@
         <v>45313</v>
       </c>
       <c r="B574" t="n">
-        <v>116.9677581787109</v>
+        <v>116.9677658081055</v>
       </c>
       <c r="C574" t="n">
-        <v>118.313706036235</v>
+        <v>118.313713753421</v>
       </c>
       <c r="D574" t="n">
-        <v>114.8792140041177</v>
+        <v>114.8792214972839</v>
       </c>
       <c r="E574" t="n">
-        <v>115.7331948114009</v>
+        <v>115.7332023602692</v>
       </c>
       <c r="F574" t="n">
         <v>856226</v>
@@ -11912,16 +11912,16 @@
         <v>45314</v>
       </c>
       <c r="B575" t="n">
-        <v>115.8445892333984</v>
+        <v>115.8445816040039</v>
       </c>
       <c r="C575" t="n">
-        <v>119.5111418195592</v>
+        <v>119.5111339486896</v>
       </c>
       <c r="D575" t="n">
-        <v>115.3526150891313</v>
+        <v>115.3526074921376</v>
       </c>
       <c r="E575" t="n">
-        <v>117.0605838276382</v>
+        <v>117.0605761181597</v>
       </c>
       <c r="F575" t="n">
         <v>383026</v>
@@ -11972,16 +11972,16 @@
         <v>45317</v>
       </c>
       <c r="B578" t="n">
-        <v>116.6614456176758</v>
+        <v>116.6614379882812</v>
       </c>
       <c r="C578" t="n">
-        <v>119.0841505307175</v>
+        <v>119.0841427428836</v>
       </c>
       <c r="D578" t="n">
-        <v>113.3383378208057</v>
+        <v>113.3383304087349</v>
       </c>
       <c r="E578" t="n">
-        <v>113.6817898831383</v>
+        <v>113.6817824486065</v>
       </c>
       <c r="F578" t="n">
         <v>753916</v>
@@ -12012,16 +12012,16 @@
         <v>45321</v>
       </c>
       <c r="B580" t="n">
-        <v>115.1205520629883</v>
+        <v>115.1205596923828</v>
       </c>
       <c r="C580" t="n">
-        <v>120.3743972943805</v>
+        <v>120.3744052719636</v>
       </c>
       <c r="D580" t="n">
-        <v>114.8235149518346</v>
+        <v>114.8235225615435</v>
       </c>
       <c r="E580" t="n">
-        <v>119.7524769494529</v>
+        <v>119.7524848858194</v>
       </c>
       <c r="F580" t="n">
         <v>678468</v>
@@ -12092,16 +12092,16 @@
         <v>45327</v>
       </c>
       <c r="B584" t="n">
-        <v>117.5711212158203</v>
+        <v>117.5711135864258</v>
       </c>
       <c r="C584" t="n">
-        <v>121.3026434165738</v>
+        <v>121.3026355450343</v>
       </c>
       <c r="D584" t="n">
-        <v>116.2066045040748</v>
+        <v>116.2065969632262</v>
       </c>
       <c r="E584" t="n">
-        <v>119.7246350359527</v>
+        <v>119.7246272668129</v>
       </c>
       <c r="F584" t="n">
         <v>563930</v>
@@ -12132,16 +12132,16 @@
         <v>45329</v>
       </c>
       <c r="B586" t="n">
-        <v>114.9070663452148</v>
+        <v>114.9070587158203</v>
       </c>
       <c r="C586" t="n">
-        <v>116.3179909256947</v>
+        <v>116.3179832026201</v>
       </c>
       <c r="D586" t="n">
-        <v>111.816019099874</v>
+        <v>111.8160116757133</v>
       </c>
       <c r="E586" t="n">
-        <v>115.101996295562</v>
+        <v>115.1019886532248</v>
       </c>
       <c r="F586" t="n">
         <v>998662</v>
@@ -12152,16 +12152,16 @@
         <v>45330</v>
       </c>
       <c r="B587" t="n">
-        <v>114.4058074951172</v>
+        <v>114.4058151245117</v>
       </c>
       <c r="C587" t="n">
-        <v>115.4361565105115</v>
+        <v>115.436164208617</v>
       </c>
       <c r="D587" t="n">
-        <v>113.0412908486803</v>
+        <v>113.0412983870791</v>
       </c>
       <c r="E587" t="n">
-        <v>115.1019888794688</v>
+        <v>115.1019965552897</v>
       </c>
       <c r="F587" t="n">
         <v>662990</v>
@@ -12212,16 +12212,16 @@
         <v>45337</v>
       </c>
       <c r="B590" t="n">
-        <v>115.7517547607422</v>
+        <v>115.7517623901367</v>
       </c>
       <c r="C590" t="n">
-        <v>116.4015282987129</v>
+        <v>116.4015359709352</v>
       </c>
       <c r="D590" t="n">
-        <v>114.4986296915515</v>
+        <v>114.4986372383505</v>
       </c>
       <c r="E590" t="n">
-        <v>115.6589319930101</v>
+        <v>115.6589396162866</v>
       </c>
       <c r="F590" t="n">
         <v>464925</v>
@@ -12232,16 +12232,16 @@
         <v>45338</v>
       </c>
       <c r="B591" t="n">
-        <v>114.2387237548828</v>
+        <v>114.2387313842773</v>
       </c>
       <c r="C591" t="n">
-        <v>116.0302308017386</v>
+        <v>116.0302385507783</v>
       </c>
       <c r="D591" t="n">
-        <v>113.3568968335589</v>
+        <v>113.3569044040609</v>
       </c>
       <c r="E591" t="n">
-        <v>115.7517554150451</v>
+        <v>115.7517631454869</v>
       </c>
       <c r="F591" t="n">
         <v>476906</v>
@@ -12412,16 +12412,16 @@
         <v>45351</v>
       </c>
       <c r="B600" t="n">
-        <v>108.5021896362305</v>
+        <v>108.502197265625</v>
       </c>
       <c r="C600" t="n">
-        <v>111.5189756586366</v>
+        <v>111.5189835001582</v>
       </c>
       <c r="D600" t="n">
-        <v>108.5021896362305</v>
+        <v>108.502197265625</v>
       </c>
       <c r="E600" t="n">
-        <v>109.4397158907475</v>
+        <v>109.4397235860647</v>
       </c>
       <c r="F600" t="n">
         <v>462606</v>
@@ -12432,16 +12432,16 @@
         <v>45352</v>
       </c>
       <c r="B601" t="n">
-        <v>109.0869827270508</v>
+        <v>109.0869903564453</v>
       </c>
       <c r="C601" t="n">
-        <v>110.2008772332821</v>
+        <v>110.2008849405809</v>
       </c>
       <c r="D601" t="n">
-        <v>108.1958713712198</v>
+        <v>108.1958789382912</v>
       </c>
       <c r="E601" t="n">
-        <v>108.8642066585739</v>
+        <v>108.8642142723878</v>
       </c>
       <c r="F601" t="n">
         <v>370372</v>
@@ -12472,16 +12472,16 @@
         <v>45356</v>
       </c>
       <c r="B603" t="n">
-        <v>109.6624984741211</v>
+        <v>109.6624908447266</v>
       </c>
       <c r="C603" t="n">
-        <v>109.6624984741211</v>
+        <v>109.6624908447266</v>
       </c>
       <c r="D603" t="n">
-        <v>106.5157589717069</v>
+        <v>106.5157515612361</v>
       </c>
       <c r="E603" t="n">
-        <v>107.9730984843827</v>
+        <v>107.9730909725224</v>
       </c>
       <c r="F603" t="n">
         <v>2890717</v>
@@ -12612,16 +12612,16 @@
         <v>45365</v>
       </c>
       <c r="B610" t="n">
-        <v>117.5711212158203</v>
+        <v>117.5711135864258</v>
       </c>
       <c r="C610" t="n">
-        <v>120.7642755844261</v>
+        <v>120.7642677478222</v>
       </c>
       <c r="D610" t="n">
-        <v>115.9374135060774</v>
+        <v>115.937405982697</v>
       </c>
       <c r="E610" t="n">
-        <v>120.662168409947</v>
+        <v>120.662160579969</v>
       </c>
       <c r="F610" t="n">
         <v>644367</v>
@@ -12812,16 +12812,16 @@
         <v>45379</v>
       </c>
       <c r="B620" t="n">
-        <v>118.9077911376953</v>
+        <v>118.9077835083008</v>
       </c>
       <c r="C620" t="n">
-        <v>120.5693378798037</v>
+        <v>120.5693301438005</v>
       </c>
       <c r="D620" t="n">
-        <v>116.5964637449893</v>
+        <v>116.5964562638948</v>
       </c>
       <c r="E620" t="n">
-        <v>117.0698690892924</v>
+        <v>117.0698615778232</v>
       </c>
       <c r="F620" t="n">
         <v>712173</v>
@@ -12892,16 +12892,16 @@
         <v>45386</v>
       </c>
       <c r="B624" t="n">
-        <v>117.4225997924805</v>
+        <v>117.4225921630859</v>
       </c>
       <c r="C624" t="n">
-        <v>118.7964009140041</v>
+        <v>118.7963931953485</v>
       </c>
       <c r="D624" t="n">
-        <v>116.1044980004005</v>
+        <v>116.104490456648</v>
       </c>
       <c r="E624" t="n">
-        <v>117.5525530913096</v>
+        <v>117.5525454534715</v>
       </c>
       <c r="F624" t="n">
         <v>491773</v>
@@ -12992,16 +12992,16 @@
         <v>45393</v>
       </c>
       <c r="B629" t="n">
-        <v>113.9509735107422</v>
+        <v>113.9509811401367</v>
       </c>
       <c r="C629" t="n">
-        <v>114.4522249684666</v>
+        <v>114.4522326314215</v>
       </c>
       <c r="D629" t="n">
-        <v>112.3915268917964</v>
+        <v>112.3915344167808</v>
       </c>
       <c r="E629" t="n">
-        <v>114.025227477798</v>
+        <v>114.025235112164</v>
       </c>
       <c r="F629" t="n">
         <v>445667</v>
@@ -13132,16 +13132,16 @@
         <v>45404</v>
       </c>
       <c r="B636" t="n">
-        <v>100.9463043212891</v>
+        <v>100.9462966918945</v>
       </c>
       <c r="C636" t="n">
-        <v>102.5243126825076</v>
+        <v>102.5243049338492</v>
       </c>
       <c r="D636" t="n">
-        <v>100.4357684551706</v>
+        <v>100.4357608643617</v>
       </c>
       <c r="E636" t="n">
-        <v>101.1783647909932</v>
+        <v>101.1783571440598</v>
       </c>
       <c r="F636" t="n">
         <v>363945</v>
@@ -13292,16 +13292,16 @@
         <v>45418</v>
       </c>
       <c r="B644" t="n">
-        <v>105.7267456054688</v>
+        <v>105.7267532348633</v>
       </c>
       <c r="C644" t="n">
-        <v>107.1655161894411</v>
+        <v>107.1655239226594</v>
       </c>
       <c r="D644" t="n">
-        <v>105.2254941686134</v>
+        <v>105.2255017618369</v>
       </c>
       <c r="E644" t="n">
-        <v>105.8195683718665</v>
+        <v>105.8195760079592</v>
       </c>
       <c r="F644" t="n">
         <v>262476</v>
@@ -13332,16 +13332,16 @@
         <v>45420</v>
       </c>
       <c r="B646" t="n">
-        <v>105.9495315551758</v>
+        <v>105.9495239257812</v>
       </c>
       <c r="C646" t="n">
-        <v>105.9959464836706</v>
+        <v>105.9959388509337</v>
       </c>
       <c r="D646" t="n">
-        <v>102.3015405478897</v>
+        <v>102.301533181186</v>
       </c>
       <c r="E646" t="n">
-        <v>103.6846190175652</v>
+        <v>103.6846115512664</v>
       </c>
       <c r="F646" t="n">
         <v>426813</v>
@@ -13412,16 +13412,16 @@
         <v>45426</v>
       </c>
       <c r="B650" t="n">
-        <v>103.6660461425781</v>
+        <v>103.6660537719727</v>
       </c>
       <c r="C650" t="n">
-        <v>104.6314184796373</v>
+        <v>104.6314261800793</v>
       </c>
       <c r="D650" t="n">
-        <v>103.0348414253441</v>
+        <v>103.0348490082846</v>
       </c>
       <c r="E650" t="n">
-        <v>103.0348414253441</v>
+        <v>103.0348490082846</v>
       </c>
       <c r="F650" t="n">
         <v>247200</v>
@@ -13452,16 +13452,16 @@
         <v>45428</v>
       </c>
       <c r="B652" t="n">
-        <v>104.6407089233398</v>
+        <v>104.6407012939453</v>
       </c>
       <c r="C652" t="n">
-        <v>104.9377460379014</v>
+        <v>104.9377383868498</v>
       </c>
       <c r="D652" t="n">
-        <v>103.3226000881697</v>
+        <v>103.322592554879</v>
       </c>
       <c r="E652" t="n">
-        <v>104.1487347843541</v>
+        <v>104.1487271908296</v>
       </c>
       <c r="F652" t="n">
         <v>283646</v>
@@ -13492,16 +13492,16 @@
         <v>45432</v>
       </c>
       <c r="B654" t="n">
-        <v>102.5243148803711</v>
+        <v>102.5243072509766</v>
       </c>
       <c r="C654" t="n">
-        <v>103.3504496036741</v>
+        <v>103.3504419128024</v>
       </c>
       <c r="D654" t="n">
-        <v>101.2340592077103</v>
+        <v>101.2340516743307</v>
       </c>
       <c r="E654" t="n">
-        <v>103.0162890355063</v>
+        <v>103.0162813695012</v>
       </c>
       <c r="F654" t="n">
         <v>409635</v>
@@ -13672,16 +13672,16 @@
         <v>45446</v>
       </c>
       <c r="B663" t="n">
-        <v>92.434326171875</v>
+        <v>92.43431854248047</v>
       </c>
       <c r="C663" t="n">
-        <v>93.60390581716601</v>
+        <v>93.60389809123609</v>
       </c>
       <c r="D663" t="n">
-        <v>90.53142752500605</v>
+        <v>90.53142005267401</v>
       </c>
       <c r="E663" t="n">
-        <v>92.64781783392128</v>
+        <v>92.64781018690546</v>
       </c>
       <c r="F663" t="n">
         <v>373105</v>
@@ -13752,16 +13752,16 @@
         <v>45450</v>
       </c>
       <c r="B667" t="n">
-        <v>92.82418060302734</v>
+        <v>92.82418823242188</v>
       </c>
       <c r="C667" t="n">
-        <v>94.03089778363588</v>
+        <v>94.03090551221278</v>
       </c>
       <c r="D667" t="n">
-        <v>91.53392505919909</v>
+        <v>91.53393258254509</v>
       </c>
       <c r="E667" t="n">
-        <v>92.7313578388089</v>
+        <v>92.73136546057417</v>
       </c>
       <c r="F667" t="n">
         <v>795802</v>
@@ -13772,16 +13772,16 @@
         <v>45453</v>
       </c>
       <c r="B668" t="n">
-        <v>92.53643035888672</v>
+        <v>92.53643798828125</v>
       </c>
       <c r="C668" t="n">
-        <v>93.24188905115926</v>
+        <v>93.24189673871706</v>
       </c>
       <c r="D668" t="n">
-        <v>90.78205386560359</v>
+        <v>90.78206135035421</v>
       </c>
       <c r="E668" t="n">
-        <v>92.0351789205311</v>
+        <v>92.0351865085987</v>
       </c>
       <c r="F668" t="n">
         <v>279796</v>
@@ -13792,16 +13792,16 @@
         <v>45454</v>
       </c>
       <c r="B669" t="n">
-        <v>92.84275817871094</v>
+        <v>92.84275054931641</v>
       </c>
       <c r="C669" t="n">
-        <v>93.01912641819206</v>
+        <v>93.01911877430439</v>
       </c>
       <c r="D669" t="n">
-        <v>91.69174012560192</v>
+        <v>91.69173259079281</v>
       </c>
       <c r="E669" t="n">
-        <v>92.52715931008595</v>
+        <v>92.5271517066259</v>
       </c>
       <c r="F669" t="n">
         <v>406022</v>
@@ -13852,16 +13852,16 @@
         <v>45457</v>
       </c>
       <c r="B672" t="n">
-        <v>85.38896179199219</v>
+        <v>85.38896942138672</v>
       </c>
       <c r="C672" t="n">
-        <v>86.81845502374917</v>
+        <v>86.81846278086709</v>
       </c>
       <c r="D672" t="n">
-        <v>84.95268700985508</v>
+        <v>84.95269460026903</v>
       </c>
       <c r="E672" t="n">
-        <v>86.81845502374917</v>
+        <v>86.81846278086709</v>
       </c>
       <c r="F672" t="n">
         <v>481131</v>
@@ -13892,16 +13892,16 @@
         <v>45461</v>
       </c>
       <c r="B674" t="n">
-        <v>87.54248809814453</v>
+        <v>87.54248046875</v>
       </c>
       <c r="C674" t="n">
-        <v>87.54248809814453</v>
+        <v>87.54248046875</v>
       </c>
       <c r="D674" t="n">
-        <v>84.97126124590245</v>
+        <v>84.9712538405923</v>
       </c>
       <c r="E674" t="n">
-        <v>85.57461987506238</v>
+        <v>85.57461241716906</v>
       </c>
       <c r="F674" t="n">
         <v>348422</v>
@@ -13912,16 +13912,16 @@
         <v>45462</v>
       </c>
       <c r="B675" t="n">
-        <v>86.95770263671875</v>
+        <v>86.95769500732422</v>
       </c>
       <c r="C675" t="n">
-        <v>88.3036505769263</v>
+        <v>88.30364282944254</v>
       </c>
       <c r="D675" t="n">
-        <v>84.89700445808745</v>
+        <v>84.89699700949208</v>
       </c>
       <c r="E675" t="n">
-        <v>86.80918053141167</v>
+        <v>86.80917291504799</v>
       </c>
       <c r="F675" t="n">
         <v>247119</v>
@@ -13932,16 +13932,16 @@
         <v>45463</v>
       </c>
       <c r="B676" t="n">
-        <v>90.61498260498047</v>
+        <v>90.61497497558594</v>
       </c>
       <c r="C676" t="n">
-        <v>91.32972579750511</v>
+        <v>91.32971810793224</v>
       </c>
       <c r="D676" t="n">
-        <v>86.61425494519142</v>
+        <v>86.61424765264107</v>
       </c>
       <c r="E676" t="n">
-        <v>86.61425494519142</v>
+        <v>86.61424765264107</v>
       </c>
       <c r="F676" t="n">
         <v>965986</v>
@@ -13972,16 +13972,16 @@
         <v>45467</v>
       </c>
       <c r="B678" t="n">
-        <v>89.74242401123047</v>
+        <v>89.74241638183594</v>
       </c>
       <c r="C678" t="n">
-        <v>90.6056892310713</v>
+        <v>90.60568152828682</v>
       </c>
       <c r="D678" t="n">
-        <v>88.23866963675577</v>
+        <v>88.23866213520195</v>
       </c>
       <c r="E678" t="n">
-        <v>88.92557371752265</v>
+        <v>88.92556615757213</v>
       </c>
       <c r="F678" t="n">
         <v>235914</v>
@@ -14012,16 +14012,16 @@
         <v>45469</v>
       </c>
       <c r="B680" t="n">
-        <v>91.09766387939453</v>
+        <v>91.09765625</v>
       </c>
       <c r="C680" t="n">
-        <v>91.68245375501853</v>
+        <v>91.68244607664806</v>
       </c>
       <c r="D680" t="n">
-        <v>89.57534765675591</v>
+        <v>89.57534015485479</v>
       </c>
       <c r="E680" t="n">
-        <v>90.03946862907071</v>
+        <v>90.03946108829963</v>
       </c>
       <c r="F680" t="n">
         <v>524346</v>
@@ -14072,16 +14072,16 @@
         <v>45474</v>
       </c>
       <c r="B683" t="n">
-        <v>87.96947479248047</v>
+        <v>87.969482421875</v>
       </c>
       <c r="C683" t="n">
-        <v>91.70101090135917</v>
+        <v>91.70101885438143</v>
       </c>
       <c r="D683" t="n">
-        <v>87.85809030571718</v>
+        <v>87.85809792545159</v>
       </c>
       <c r="E683" t="n">
-        <v>90.31793256263779</v>
+        <v>90.31794039570877</v>
       </c>
       <c r="F683" t="n">
         <v>154542</v>
@@ -14232,16 +14232,16 @@
         <v>45484</v>
       </c>
       <c r="B691" t="n">
-        <v>92.32293701171875</v>
+        <v>92.32294464111328</v>
       </c>
       <c r="C691" t="n">
-        <v>92.60141240992618</v>
+        <v>92.6014200623334</v>
       </c>
       <c r="D691" t="n">
-        <v>89.85381728076861</v>
+        <v>89.85382470611971</v>
       </c>
       <c r="E691" t="n">
-        <v>90.12300119526596</v>
+        <v>90.12300864286192</v>
       </c>
       <c r="F691" t="n">
         <v>274684</v>
@@ -14292,16 +14292,16 @@
         <v>45489</v>
       </c>
       <c r="B694" t="n">
-        <v>93.74314880371094</v>
+        <v>93.74314117431641</v>
       </c>
       <c r="C694" t="n">
-        <v>95.46039492624392</v>
+        <v>95.46038715708933</v>
       </c>
       <c r="D694" t="n">
-        <v>92.92629846982642</v>
+        <v>92.9262909069122</v>
       </c>
       <c r="E694" t="n">
-        <v>92.92629846982642</v>
+        <v>92.9262909069122</v>
       </c>
       <c r="F694" t="n">
         <v>218776</v>
@@ -14332,16 +14332,16 @@
         <v>45491</v>
       </c>
       <c r="B696" t="n">
-        <v>91.96092987060547</v>
+        <v>91.96092224121094</v>
       </c>
       <c r="C696" t="n">
-        <v>94.96843181114083</v>
+        <v>94.96842393223361</v>
       </c>
       <c r="D696" t="n">
-        <v>91.20905615595265</v>
+        <v>91.20904858893614</v>
       </c>
       <c r="E696" t="n">
-        <v>94.88489343481233</v>
+        <v>94.88488556283573</v>
       </c>
       <c r="F696" t="n">
         <v>265514</v>
@@ -14412,16 +14412,16 @@
         <v>45497</v>
       </c>
       <c r="B700" t="n">
-        <v>91.80312347412109</v>
+        <v>91.80311584472656</v>
       </c>
       <c r="C700" t="n">
-        <v>94.77349466141999</v>
+        <v>94.77348678516967</v>
       </c>
       <c r="D700" t="n">
-        <v>91.78455467061849</v>
+        <v>91.78454704276713</v>
       </c>
       <c r="E700" t="n">
-        <v>94.3650730493686</v>
+        <v>94.36506520706058</v>
       </c>
       <c r="F700" t="n">
         <v>387734</v>
@@ -14472,16 +14472,16 @@
         <v>45502</v>
       </c>
       <c r="B703" t="n">
-        <v>91.94235992431641</v>
+        <v>91.94235229492188</v>
       </c>
       <c r="C703" t="n">
-        <v>94.07731197309832</v>
+        <v>94.07730416654506</v>
       </c>
       <c r="D703" t="n">
-        <v>91.71957677685126</v>
+        <v>91.71956916594331</v>
       </c>
       <c r="E703" t="n">
-        <v>93.10266226015118</v>
+        <v>93.10265453447454</v>
       </c>
       <c r="F703" t="n">
         <v>142991</v>
@@ -14512,16 +14512,16 @@
         <v>45504</v>
       </c>
       <c r="B705" t="n">
-        <v>90.49430084228516</v>
+        <v>90.49430847167969</v>
       </c>
       <c r="C705" t="n">
-        <v>91.80312532052498</v>
+        <v>91.8031330602639</v>
       </c>
       <c r="D705" t="n">
-        <v>89.90022659287696</v>
+        <v>89.90023417218629</v>
       </c>
       <c r="E705" t="n">
-        <v>90.59640801783253</v>
+        <v>90.59641565583551</v>
       </c>
       <c r="F705" t="n">
         <v>210335</v>
@@ -14712,16 +14712,16 @@
         <v>45518</v>
       </c>
       <c r="B715" t="n">
-        <v>100.2501220703125</v>
+        <v>100.250129699707</v>
       </c>
       <c r="C715" t="n">
-        <v>101.4382705321122</v>
+        <v>101.4382782519291</v>
       </c>
       <c r="D715" t="n">
-        <v>98.41220004964379</v>
+        <v>98.41220753916585</v>
       </c>
       <c r="E715" t="n">
-        <v>100.0644765288776</v>
+        <v>100.0644841441438</v>
       </c>
       <c r="F715" t="n">
         <v>1420295</v>
@@ -14832,16 +14832,16 @@
         <v>45526</v>
       </c>
       <c r="B721" t="n">
-        <v>99.97164154052734</v>
+        <v>99.97164916992188</v>
       </c>
       <c r="C721" t="n">
-        <v>101.0112749321561</v>
+        <v>101.0112826408908</v>
       </c>
       <c r="D721" t="n">
-        <v>98.57927880552322</v>
+        <v>98.57928632865877</v>
       </c>
       <c r="E721" t="n">
-        <v>98.87631590571384</v>
+        <v>98.87632345151795</v>
       </c>
       <c r="F721" t="n">
         <v>499264</v>
@@ -14992,16 +14992,16 @@
         <v>45538</v>
       </c>
       <c r="B729" t="n">
-        <v>96.24939727783203</v>
+        <v>96.24940490722656</v>
       </c>
       <c r="C729" t="n">
-        <v>97.25189306841784</v>
+        <v>97.25190077727714</v>
       </c>
       <c r="D729" t="n">
-        <v>94.5414286340846</v>
+        <v>94.54143612809369</v>
       </c>
       <c r="E729" t="n">
-        <v>95.51608538489992</v>
+        <v>95.51609295616707</v>
       </c>
       <c r="F729" t="n">
         <v>703523</v>
@@ -15012,16 +15012,16 @@
         <v>45539</v>
       </c>
       <c r="B730" t="n">
-        <v>95.59035491943359</v>
+        <v>95.59034729003906</v>
       </c>
       <c r="C730" t="n">
-        <v>96.91774113278282</v>
+        <v>96.91773339744505</v>
       </c>
       <c r="D730" t="n">
-        <v>94.91273520971389</v>
+        <v>94.9127276344025</v>
       </c>
       <c r="E730" t="n">
-        <v>95.74815434432594</v>
+        <v>95.7481467023369</v>
       </c>
       <c r="F730" t="n">
         <v>802363</v>
@@ -15032,16 +15032,16 @@
         <v>45540</v>
       </c>
       <c r="B731" t="n">
-        <v>96.58358001708984</v>
+        <v>96.58357238769531</v>
       </c>
       <c r="C731" t="n">
-        <v>96.95487114034169</v>
+        <v>96.95486348161789</v>
       </c>
       <c r="D731" t="n">
-        <v>94.83848057733952</v>
+        <v>94.83847308579506</v>
       </c>
       <c r="E731" t="n">
-        <v>96.72281064734717</v>
+        <v>96.72280300695445</v>
       </c>
       <c r="F731" t="n">
         <v>616217</v>
@@ -15052,16 +15052,16 @@
         <v>45541</v>
       </c>
       <c r="B732" t="n">
-        <v>93.76171875</v>
+        <v>93.76171112060547</v>
       </c>
       <c r="C732" t="n">
-        <v>96.95486615366303</v>
+        <v>96.95485826444198</v>
       </c>
       <c r="D732" t="n">
-        <v>93.10266783362343</v>
+        <v>93.10266025785589</v>
       </c>
       <c r="E732" t="n">
-        <v>96.58357504950779</v>
+        <v>96.5835671904987</v>
       </c>
       <c r="F732" t="n">
         <v>627234</v>
@@ -15072,16 +15072,16 @@
         <v>45544</v>
       </c>
       <c r="B733" t="n">
-        <v>93.68744659423828</v>
+        <v>93.68745422363281</v>
       </c>
       <c r="C733" t="n">
-        <v>95.05196319427465</v>
+        <v>95.05197093478797</v>
       </c>
       <c r="D733" t="n">
-        <v>93.37184069479765</v>
+        <v>93.37184829849096</v>
       </c>
       <c r="E733" t="n">
-        <v>93.77098495819658</v>
+        <v>93.77099259439402</v>
       </c>
       <c r="F733" t="n">
         <v>200739</v>
@@ -15152,16 +15152,16 @@
         <v>45548</v>
       </c>
       <c r="B737" t="n">
-        <v>98.87631988525391</v>
+        <v>98.87632751464844</v>
       </c>
       <c r="C737" t="n">
-        <v>99.46111678992312</v>
+        <v>99.46112446444116</v>
       </c>
       <c r="D737" t="n">
-        <v>96.32365476834089</v>
+        <v>96.32366220076925</v>
       </c>
       <c r="E737" t="n">
-        <v>96.32365476834089</v>
+        <v>96.32366220076925</v>
       </c>
       <c r="F737" t="n">
         <v>344396</v>
@@ -15192,16 +15192,16 @@
         <v>45552</v>
       </c>
       <c r="B739" t="n">
-        <v>100.3151016235352</v>
+        <v>100.3150939941406</v>
       </c>
       <c r="C739" t="n">
-        <v>100.7977842944004</v>
+        <v>100.7977766282958</v>
       </c>
       <c r="D739" t="n">
-        <v>98.70924002410959</v>
+        <v>98.70923251684773</v>
       </c>
       <c r="E739" t="n">
-        <v>99.17336097306311</v>
+        <v>99.17335343050286</v>
       </c>
       <c r="F739" t="n">
         <v>287351</v>
@@ -15312,16 +15312,16 @@
         <v>45560</v>
       </c>
       <c r="B745" t="n">
-        <v>90.49430084228516</v>
+        <v>90.49430847167969</v>
       </c>
       <c r="C745" t="n">
-        <v>92.0630319194006</v>
+        <v>92.06303968105173</v>
       </c>
       <c r="D745" t="n">
-        <v>89.42682124096855</v>
+        <v>89.42682878036601</v>
       </c>
       <c r="E745" t="n">
-        <v>91.89594809413431</v>
+        <v>91.89595584169895</v>
       </c>
       <c r="F745" t="n">
         <v>511811</v>
@@ -15392,16 +15392,16 @@
         <v>45566</v>
       </c>
       <c r="B749" t="n">
-        <v>90.82846069335938</v>
+        <v>90.82846832275391</v>
       </c>
       <c r="C749" t="n">
-        <v>91.7845486350911</v>
+        <v>91.78455634479495</v>
       </c>
       <c r="D749" t="n">
-        <v>89.77026558484825</v>
+        <v>89.77027312535667</v>
       </c>
       <c r="E749" t="n">
-        <v>90.50357747266264</v>
+        <v>90.50358507476767</v>
       </c>
       <c r="F749" t="n">
         <v>321109</v>
@@ -15472,16 +15472,16 @@
         <v>45572</v>
       </c>
       <c r="B753" t="n">
-        <v>90.48502349853516</v>
+        <v>90.48501586914062</v>
       </c>
       <c r="C753" t="n">
-        <v>90.75420741735454</v>
+        <v>90.75419976526331</v>
       </c>
       <c r="D753" t="n">
-        <v>89.1205067728724</v>
+        <v>89.12049925852935</v>
       </c>
       <c r="E753" t="n">
-        <v>89.80740379570975</v>
+        <v>89.80739622344984</v>
       </c>
       <c r="F753" t="n">
         <v>295051</v>
@@ -15532,16 +15532,16 @@
         <v>45575</v>
       </c>
       <c r="B756" t="n">
-        <v>89.9930419921875</v>
+        <v>89.99304962158203</v>
       </c>
       <c r="C756" t="n">
-        <v>90.42003946326363</v>
+        <v>90.42004712885797</v>
       </c>
       <c r="D756" t="n">
-        <v>88.55427141433071</v>
+        <v>88.5542789217497</v>
       </c>
       <c r="E756" t="n">
-        <v>88.8327397123402</v>
+        <v>88.83274724336708</v>
       </c>
       <c r="F756" t="n">
         <v>262199</v>
@@ -15552,16 +15552,16 @@
         <v>45576</v>
       </c>
       <c r="B757" t="n">
-        <v>91.21833038330078</v>
+        <v>91.21832275390625</v>
       </c>
       <c r="C757" t="n">
-        <v>91.71030454982977</v>
+        <v>91.7102968792871</v>
       </c>
       <c r="D757" t="n">
-        <v>89.11122434046339</v>
+        <v>89.11121688730475</v>
       </c>
       <c r="E757" t="n">
-        <v>89.11122434046339</v>
+        <v>89.11121688730475</v>
       </c>
       <c r="F757" t="n">
         <v>354987</v>
@@ -15612,16 +15612,16 @@
         <v>45581</v>
       </c>
       <c r="B760" t="n">
-        <v>95.37685394287109</v>
+        <v>95.37684631347656</v>
       </c>
       <c r="C760" t="n">
-        <v>95.37685394287109</v>
+        <v>95.37684631347656</v>
       </c>
       <c r="D760" t="n">
-        <v>91.53393309508448</v>
+        <v>91.53392577309324</v>
       </c>
       <c r="E760" t="n">
-        <v>91.53393309508448</v>
+        <v>91.53392577309324</v>
       </c>
       <c r="F760" t="n">
         <v>473040</v>
@@ -15632,16 +15632,16 @@
         <v>45582</v>
       </c>
       <c r="B761" t="n">
-        <v>95.03339385986328</v>
+        <v>95.03340148925781</v>
       </c>
       <c r="C761" t="n">
-        <v>96.48145589767088</v>
+        <v>96.48146364331757</v>
       </c>
       <c r="D761" t="n">
-        <v>94.06802152863254</v>
+        <v>94.06802908052583</v>
       </c>
       <c r="E761" t="n">
-        <v>94.42075794849787</v>
+        <v>94.42076552870925</v>
       </c>
       <c r="F761" t="n">
         <v>511946</v>
@@ -15752,16 +15752,16 @@
         <v>45590</v>
       </c>
       <c r="B767" t="n">
-        <v>93.17691802978516</v>
+        <v>93.17691040039062</v>
       </c>
       <c r="C767" t="n">
-        <v>93.91022997004863</v>
+        <v>93.91022228060997</v>
       </c>
       <c r="D767" t="n">
-        <v>92.02590007331048</v>
+        <v>92.02589253816214</v>
       </c>
       <c r="E767" t="n">
-        <v>93.29759400747731</v>
+        <v>93.29758636820173</v>
       </c>
       <c r="F767" t="n">
         <v>563664</v>
@@ -15852,16 +15852,16 @@
         <v>45597</v>
       </c>
       <c r="B772" t="n">
-        <v>91.89595031738281</v>
+        <v>91.89594268798828</v>
       </c>
       <c r="C772" t="n">
-        <v>94.99627493886804</v>
+        <v>94.99626705207805</v>
       </c>
       <c r="D772" t="n">
-        <v>91.41326763378245</v>
+        <v>91.41326004446124</v>
       </c>
       <c r="E772" t="n">
-        <v>93.85454134019609</v>
+        <v>93.85453354819522</v>
       </c>
       <c r="F772" t="n">
         <v>397099</v>
@@ -15912,16 +15912,16 @@
         <v>45602</v>
       </c>
       <c r="B775" t="n">
-        <v>94.72708892822266</v>
+        <v>94.72709655761719</v>
       </c>
       <c r="C775" t="n">
-        <v>95.38613982878644</v>
+        <v>95.38614751126146</v>
       </c>
       <c r="D775" t="n">
-        <v>91.81240992260877</v>
+        <v>91.81241731725275</v>
       </c>
       <c r="E775" t="n">
-        <v>94.21655304937283</v>
+        <v>94.2165606376484</v>
       </c>
       <c r="F775" t="n">
         <v>484922</v>
@@ -15972,16 +15972,16 @@
         <v>45607</v>
       </c>
       <c r="B778" t="n">
-        <v>92.10944366455078</v>
+        <v>92.10945129394531</v>
       </c>
       <c r="C778" t="n">
-        <v>93.48323766311775</v>
+        <v>93.48324540630318</v>
       </c>
       <c r="D778" t="n">
-        <v>90.58712048587832</v>
+        <v>90.58712798917934</v>
       </c>
       <c r="E778" t="n">
-        <v>91.52464675536318</v>
+        <v>91.52465433631919</v>
       </c>
       <c r="F778" t="n">
         <v>447451</v>
@@ -16012,16 +16012,16 @@
         <v>45609</v>
       </c>
       <c r="B780" t="n">
-        <v>90.29007720947266</v>
+        <v>90.29008483886719</v>
       </c>
       <c r="C780" t="n">
-        <v>91.10693452987967</v>
+        <v>91.10694222829758</v>
       </c>
       <c r="D780" t="n">
-        <v>89.34327368490983</v>
+        <v>89.3432812343007</v>
       </c>
       <c r="E780" t="n">
-        <v>90.84702795772213</v>
+        <v>90.8470356341783</v>
       </c>
       <c r="F780" t="n">
         <v>352617</v>
@@ -16092,16 +16092,16 @@
         <v>45617</v>
       </c>
       <c r="B784" t="n">
-        <v>83.69029235839844</v>
+        <v>83.69029998779297</v>
       </c>
       <c r="C784" t="n">
-        <v>85.30543126708351</v>
+        <v>85.30543904371771</v>
       </c>
       <c r="D784" t="n">
-        <v>83.30042538160664</v>
+        <v>83.30043297546001</v>
       </c>
       <c r="E784" t="n">
-        <v>85.16619356693812</v>
+        <v>85.1662013308791</v>
       </c>
       <c r="F784" t="n">
         <v>1016945</v>
@@ -16132,16 +16132,16 @@
         <v>45621</v>
       </c>
       <c r="B786" t="n">
-        <v>85.59318542480469</v>
+        <v>85.59317779541016</v>
       </c>
       <c r="C786" t="n">
-        <v>86.31721297941206</v>
+        <v>86.31720528548094</v>
       </c>
       <c r="D786" t="n">
-        <v>84.42359863863385</v>
+        <v>84.42359111349106</v>
       </c>
       <c r="E786" t="n">
-        <v>85.32399442184897</v>
+        <v>85.32398681644892</v>
       </c>
       <c r="F786" t="n">
         <v>384525</v>
@@ -16272,16 +16272,16 @@
         <v>45630</v>
       </c>
       <c r="B793" t="n">
-        <v>75.22472381591797</v>
+        <v>75.2247314453125</v>
       </c>
       <c r="C793" t="n">
-        <v>76.09727346105902</v>
+        <v>76.09728117894873</v>
       </c>
       <c r="D793" t="n">
-        <v>74.39858909817006</v>
+        <v>74.39859664377688</v>
       </c>
       <c r="E793" t="n">
-        <v>75.41965376350666</v>
+        <v>75.41966141267126</v>
       </c>
       <c r="F793" t="n">
         <v>411810</v>
@@ -16292,16 +16292,16 @@
         <v>45631</v>
       </c>
       <c r="B794" t="n">
-        <v>75.51247406005859</v>
+        <v>75.51248168945312</v>
       </c>
       <c r="C794" t="n">
-        <v>77.5731721268812</v>
+        <v>77.57317996447813</v>
       </c>
       <c r="D794" t="n">
-        <v>74.09226514425474</v>
+        <v>74.09227263015862</v>
       </c>
       <c r="E794" t="n">
-        <v>75.65171175574832</v>
+        <v>75.65171939921073</v>
       </c>
       <c r="F794" t="n">
         <v>973742</v>
@@ -16312,16 +16312,16 @@
         <v>45632</v>
       </c>
       <c r="B795" t="n">
-        <v>75.78166961669922</v>
+        <v>75.78166198730469</v>
       </c>
       <c r="C795" t="n">
-        <v>75.78166961669922</v>
+        <v>75.78166198730469</v>
       </c>
       <c r="D795" t="n">
-        <v>74.25935343777866</v>
+        <v>74.25934596164483</v>
       </c>
       <c r="E795" t="n">
-        <v>75.651716314737</v>
+        <v>75.65170869842567</v>
       </c>
       <c r="F795" t="n">
         <v>1017781</v>
@@ -16332,16 +16332,16 @@
         <v>45635</v>
       </c>
       <c r="B796" t="n">
-        <v>75.51247406005859</v>
+        <v>75.51248168945312</v>
       </c>
       <c r="C796" t="n">
-        <v>78.06513918065133</v>
+        <v>78.0651470679541</v>
       </c>
       <c r="D796" t="n">
-        <v>75.51247406005859</v>
+        <v>75.51248168945312</v>
       </c>
       <c r="E796" t="n">
-        <v>76.11583268676519</v>
+        <v>76.11584037711999</v>
       </c>
       <c r="F796" t="n">
         <v>291521</v>
@@ -16452,16 +16452,16 @@
         <v>45643</v>
       </c>
       <c r="B802" t="n">
-        <v>77.18951416015625</v>
+        <v>77.18950653076172</v>
       </c>
       <c r="C802" t="n">
-        <v>78.91917327583685</v>
+        <v>78.9191654754832</v>
       </c>
       <c r="D802" t="n">
-        <v>75.78234232905898</v>
+        <v>75.78233483874901</v>
       </c>
       <c r="E802" t="n">
-        <v>76.12436300135722</v>
+        <v>76.12435547724201</v>
       </c>
       <c r="F802" t="n">
         <v>713503</v>
@@ -16492,16 +16492,16 @@
         <v>45645</v>
       </c>
       <c r="B804" t="n">
-        <v>72.45983123779297</v>
+        <v>72.4598388671875</v>
       </c>
       <c r="C804" t="n">
-        <v>73.96472947311145</v>
+        <v>73.96473726095877</v>
       </c>
       <c r="D804" t="n">
-        <v>71.17968622243332</v>
+        <v>71.17969371703964</v>
       </c>
       <c r="E804" t="n">
-        <v>72.37187881505514</v>
+        <v>72.37188643518905</v>
       </c>
       <c r="F804" t="n">
         <v>633891</v>
@@ -16532,16 +16532,16 @@
         <v>45649</v>
       </c>
       <c r="B806" t="n">
-        <v>72.79208374023438</v>
+        <v>72.79207611083984</v>
       </c>
       <c r="C806" t="n">
-        <v>73.45658421784569</v>
+        <v>73.45657651880434</v>
       </c>
       <c r="D806" t="n">
-        <v>71.07220629093905</v>
+        <v>71.0721988418062</v>
       </c>
       <c r="E806" t="n">
-        <v>72.32302896515064</v>
+        <v>72.32302138491811</v>
       </c>
       <c r="F806" t="n">
         <v>510211</v>
@@ -16572,16 +16572,16 @@
         <v>45653</v>
       </c>
       <c r="B808" t="n">
-        <v>72.35234069824219</v>
+        <v>72.35234832763672</v>
       </c>
       <c r="C808" t="n">
-        <v>73.83769069310235</v>
+        <v>73.83769847912376</v>
       </c>
       <c r="D808" t="n">
-        <v>72.35234069824219</v>
+        <v>72.35234832763672</v>
       </c>
       <c r="E808" t="n">
-        <v>73.29045766165243</v>
+        <v>73.29046538996933</v>
       </c>
       <c r="F808" t="n">
         <v>193425</v>
@@ -16612,16 +16612,16 @@
         <v>45659</v>
       </c>
       <c r="B810" t="n">
-        <v>70.56404876708984</v>
+        <v>70.56405639648438</v>
       </c>
       <c r="C810" t="n">
-        <v>72.74322156344115</v>
+        <v>72.74322942844815</v>
       </c>
       <c r="D810" t="n">
-        <v>69.733425106374</v>
+        <v>69.73343264596139</v>
       </c>
       <c r="E810" t="n">
-        <v>71.8832754582845</v>
+        <v>71.88328323031399</v>
       </c>
       <c r="F810" t="n">
         <v>241349</v>
@@ -16732,16 +16732,16 @@
         <v>45667</v>
       </c>
       <c r="B816" t="n">
-        <v>66.62590789794922</v>
+        <v>66.62591552734375</v>
       </c>
       <c r="C816" t="n">
-        <v>67.14382590465797</v>
+        <v>67.14383359335977</v>
       </c>
       <c r="D816" t="n">
-        <v>65.19918797865081</v>
+        <v>65.19919544467032</v>
       </c>
       <c r="E816" t="n">
-        <v>65.58029773662483</v>
+        <v>65.58030524628556</v>
       </c>
       <c r="F816" t="n">
         <v>598954</v>
@@ -16752,16 +16752,16 @@
         <v>45670</v>
       </c>
       <c r="B817" t="n">
-        <v>67.87673950195312</v>
+        <v>67.87673187255859</v>
       </c>
       <c r="C817" t="n">
-        <v>68.63895911974765</v>
+        <v>68.63895140467909</v>
       </c>
       <c r="D817" t="n">
-        <v>65.75620390773163</v>
+        <v>65.75619651668684</v>
       </c>
       <c r="E817" t="n">
-        <v>66.5770535098207</v>
+        <v>66.57704602651182</v>
       </c>
       <c r="F817" t="n">
         <v>512624</v>
@@ -16792,16 +16792,16 @@
         <v>45672</v>
       </c>
       <c r="B819" t="n">
-        <v>69.77252197265625</v>
+        <v>69.77251434326172</v>
       </c>
       <c r="C819" t="n">
-        <v>69.96796022430158</v>
+        <v>69.96795257353654</v>
       </c>
       <c r="D819" t="n">
-        <v>66.75295103294337</v>
+        <v>66.75294373372894</v>
       </c>
       <c r="E819" t="n">
-        <v>66.75295103294337</v>
+        <v>66.75294373372894</v>
       </c>
       <c r="F819" t="n">
         <v>444557</v>
@@ -17032,16 +17032,16 @@
         <v>45688</v>
       </c>
       <c r="B831" t="n">
-        <v>77.98105621337891</v>
+        <v>77.98104858398438</v>
       </c>
       <c r="C831" t="n">
-        <v>80.18953681412769</v>
+        <v>80.18952896866313</v>
       </c>
       <c r="D831" t="n">
-        <v>77.37518569728</v>
+        <v>77.37517812716173</v>
       </c>
       <c r="E831" t="n">
-        <v>79.7400228655994</v>
+        <v>79.74001506411371</v>
       </c>
       <c r="F831" t="n">
         <v>229217</v>
@@ -17072,16 +17072,16 @@
         <v>45692</v>
       </c>
       <c r="B833" t="n">
-        <v>78.51850891113281</v>
+        <v>78.51851654052734</v>
       </c>
       <c r="C833" t="n">
-        <v>79.76933153051134</v>
+        <v>79.76933928144435</v>
       </c>
       <c r="D833" t="n">
-        <v>77.01361061735211</v>
+        <v>77.01361810052045</v>
       </c>
       <c r="E833" t="n">
-        <v>78.95825613092398</v>
+        <v>78.95826380304736</v>
       </c>
       <c r="F833" t="n">
         <v>404279</v>
@@ -17252,16 +17252,16 @@
         <v>45705</v>
       </c>
       <c r="B842" t="n">
-        <v>81.79214477539062</v>
+        <v>81.79215240478516</v>
       </c>
       <c r="C842" t="n">
-        <v>84.23515994138785</v>
+        <v>84.23516779866155</v>
       </c>
       <c r="D842" t="n">
-        <v>80.99083609916316</v>
+        <v>80.99084365381336</v>
       </c>
       <c r="E842" t="n">
-        <v>82.28074780859008</v>
+        <v>82.28075548356044</v>
       </c>
       <c r="F842" t="n">
         <v>317686</v>
@@ -17412,16 +17412,16 @@
         <v>45715</v>
       </c>
       <c r="B850" t="n">
-        <v>82.19280242919922</v>
+        <v>82.19281005859375</v>
       </c>
       <c r="C850" t="n">
-        <v>84.69444756088208</v>
+        <v>84.69445542248718</v>
       </c>
       <c r="D850" t="n">
-        <v>81.93872676567187</v>
+        <v>81.9387343714823</v>
       </c>
       <c r="E850" t="n">
-        <v>82.2612065552846</v>
+        <v>82.2612141910286</v>
       </c>
       <c r="F850" t="n">
         <v>386526</v>
@@ -17492,16 +17492,16 @@
         <v>45723</v>
       </c>
       <c r="B854" t="n">
-        <v>86.96156311035156</v>
+        <v>86.96157073974609</v>
       </c>
       <c r="C854" t="n">
-        <v>87.20586461950396</v>
+        <v>87.2058722703318</v>
       </c>
       <c r="D854" t="n">
-        <v>81.63579319302536</v>
+        <v>81.6358003551744</v>
       </c>
       <c r="E854" t="n">
-        <v>82.23188947179645</v>
+        <v>82.23189668624276</v>
       </c>
       <c r="F854" t="n">
         <v>477946</v>
@@ -17512,16 +17512,16 @@
         <v>45726</v>
       </c>
       <c r="B855" t="n">
-        <v>86.60977172851562</v>
+        <v>86.60977935791016</v>
       </c>
       <c r="C855" t="n">
-        <v>87.33290959184569</v>
+        <v>87.33291728494093</v>
       </c>
       <c r="D855" t="n">
-        <v>85.90618961724768</v>
+        <v>85.90619718466415</v>
       </c>
       <c r="E855" t="n">
-        <v>85.90618961724768</v>
+        <v>85.90619718466415</v>
       </c>
       <c r="F855" t="n">
         <v>418727</v>
@@ -17552,16 +17552,16 @@
         <v>45728</v>
       </c>
       <c r="B857" t="n">
-        <v>80.08203125</v>
+        <v>80.08203887939453</v>
       </c>
       <c r="C857" t="n">
-        <v>84.72375989677158</v>
+        <v>84.72376796838242</v>
       </c>
       <c r="D857" t="n">
-        <v>77.38494797267103</v>
+        <v>77.38495534511513</v>
       </c>
       <c r="E857" t="n">
-        <v>84.29379431290934</v>
+        <v>84.29380234355746</v>
       </c>
       <c r="F857" t="n">
         <v>1616980</v>
@@ -17732,16 +17732,16 @@
         <v>45741</v>
       </c>
       <c r="B866" t="n">
-        <v>82.01690673828125</v>
+        <v>82.01691436767578</v>
       </c>
       <c r="C866" t="n">
-        <v>84.42083280469173</v>
+        <v>84.42084065770479</v>
       </c>
       <c r="D866" t="n">
-        <v>80.61950174317984</v>
+        <v>80.61950924258466</v>
       </c>
       <c r="E866" t="n">
-        <v>83.0820577887374</v>
+        <v>83.08206551721464</v>
       </c>
       <c r="F866" t="n">
         <v>769467</v>
@@ -17752,16 +17752,16 @@
         <v>45742</v>
       </c>
       <c r="B867" t="n">
-        <v>82.81821441650391</v>
+        <v>82.81822204589844</v>
       </c>
       <c r="C867" t="n">
-        <v>83.15046090160423</v>
+        <v>83.15046856160603</v>
       </c>
       <c r="D867" t="n">
-        <v>81.10810379433421</v>
+        <v>81.10811126618962</v>
       </c>
       <c r="E867" t="n">
-        <v>81.59670682923984</v>
+        <v>81.59671434610642</v>
       </c>
       <c r="F867" t="n">
         <v>621808</v>
@@ -17792,16 +17792,16 @@
         <v>45744</v>
       </c>
       <c r="B869" t="n">
-        <v>83.47293853759766</v>
+        <v>83.47294616699219</v>
       </c>
       <c r="C869" t="n">
-        <v>83.74655503719795</v>
+        <v>83.74656269160093</v>
       </c>
       <c r="D869" t="n">
-        <v>80.22861476785475</v>
+        <v>80.22862210071933</v>
       </c>
       <c r="E869" t="n">
-        <v>81.59670472134668</v>
+        <v>81.59671217925415</v>
       </c>
       <c r="F869" t="n">
         <v>1013438</v>
@@ -17832,16 +17832,16 @@
         <v>45748</v>
       </c>
       <c r="B871" t="n">
-        <v>78.28398895263672</v>
+        <v>78.28398132324219</v>
       </c>
       <c r="C871" t="n">
-        <v>79.3882292700641</v>
+        <v>79.3882215330526</v>
       </c>
       <c r="D871" t="n">
-        <v>76.88658379423278</v>
+        <v>76.88657630102644</v>
       </c>
       <c r="E871" t="n">
-        <v>77.5608584551839</v>
+        <v>77.56085089626417</v>
       </c>
       <c r="F871" t="n">
         <v>960198</v>
@@ -17852,16 +17852,16 @@
         <v>45749</v>
       </c>
       <c r="B872" t="n">
-        <v>78.16671752929688</v>
+        <v>78.16670989990234</v>
       </c>
       <c r="C872" t="n">
-        <v>78.76281387478318</v>
+        <v>78.76280618720718</v>
       </c>
       <c r="D872" t="n">
-        <v>76.86703902131858</v>
+        <v>76.86703151877802</v>
       </c>
       <c r="E872" t="n">
-        <v>78.09831339729801</v>
+        <v>78.09830577458001</v>
       </c>
       <c r="F872" t="n">
         <v>373719</v>
@@ -17872,16 +17872,16 @@
         <v>45750</v>
       </c>
       <c r="B873" t="n">
-        <v>78.32306671142578</v>
+        <v>78.32307434082031</v>
       </c>
       <c r="C873" t="n">
-        <v>79.06574539992943</v>
+        <v>79.06575310166777</v>
       </c>
       <c r="D873" t="n">
-        <v>75.82141414370047</v>
+        <v>75.8214215294108</v>
       </c>
       <c r="E873" t="n">
-        <v>77.10155914404699</v>
+        <v>77.10156665445534</v>
       </c>
       <c r="F873" t="n">
         <v>721024</v>
@@ -17892,16 +17892,16 @@
         <v>45751</v>
       </c>
       <c r="B874" t="n">
-        <v>73.78884124755859</v>
+        <v>73.78883361816406</v>
       </c>
       <c r="C874" t="n">
-        <v>77.65857685235244</v>
+        <v>77.65856882284673</v>
       </c>
       <c r="D874" t="n">
-        <v>72.9386691811261</v>
+        <v>72.93866163963507</v>
       </c>
       <c r="E874" t="n">
-        <v>76.7106856583452</v>
+        <v>76.71067772684667</v>
       </c>
       <c r="F874" t="n">
         <v>1192804</v>
@@ -17912,16 +17912,16 @@
         <v>45754</v>
       </c>
       <c r="B875" t="n">
-        <v>73.09502410888672</v>
+        <v>73.09501647949219</v>
       </c>
       <c r="C875" t="n">
-        <v>76.01686845408716</v>
+        <v>76.01686051972106</v>
       </c>
       <c r="D875" t="n">
-        <v>70.59337125727656</v>
+        <v>70.59336388899551</v>
       </c>
       <c r="E875" t="n">
-        <v>72.17644792822188</v>
+        <v>72.17644039470501</v>
       </c>
       <c r="F875" t="n">
         <v>726435</v>
@@ -17932,16 +17932,16 @@
         <v>45755</v>
       </c>
       <c r="B876" t="n">
-        <v>75.04943084716797</v>
+        <v>75.0494384765625</v>
       </c>
       <c r="C876" t="n">
-        <v>77.47289778023283</v>
+        <v>77.47290565599279</v>
       </c>
       <c r="D876" t="n">
-        <v>74.10153974505738</v>
+        <v>74.10154727809095</v>
       </c>
       <c r="E876" t="n">
-        <v>76.22207517536182</v>
+        <v>76.22208292396535</v>
       </c>
       <c r="F876" t="n">
         <v>1315177</v>
@@ -18052,16 +18052,16 @@
         <v>45763</v>
       </c>
       <c r="B882" t="n">
-        <v>78.49896240234375</v>
+        <v>78.49897003173828</v>
       </c>
       <c r="C882" t="n">
-        <v>79.83772989573525</v>
+        <v>79.83773765524597</v>
       </c>
       <c r="D882" t="n">
-        <v>77.92240696614996</v>
+        <v>77.92241453950848</v>
       </c>
       <c r="E882" t="n">
-        <v>79.15368865498706</v>
+        <v>79.15369634801512</v>
       </c>
       <c r="F882" t="n">
         <v>449643</v>
@@ -18112,16 +18112,16 @@
         <v>45770</v>
       </c>
       <c r="B885" t="n">
-        <v>84.33289337158203</v>
+        <v>84.3328857421875</v>
       </c>
       <c r="C885" t="n">
-        <v>85.00716054250474</v>
+        <v>85.00715285211088</v>
       </c>
       <c r="D885" t="n">
-        <v>81.96804883238075</v>
+        <v>81.96804141692802</v>
       </c>
       <c r="E885" t="n">
-        <v>82.60323431830055</v>
+        <v>82.60322684538413</v>
       </c>
       <c r="F885" t="n">
         <v>698539</v>
@@ -18192,16 +18192,16 @@
         <v>45776</v>
       </c>
       <c r="B889" t="n">
-        <v>88.58373260498047</v>
+        <v>88.583740234375</v>
       </c>
       <c r="C889" t="n">
-        <v>90.62608973266609</v>
+        <v>90.62609753796141</v>
       </c>
       <c r="D889" t="n">
-        <v>88.58373260498047</v>
+        <v>88.583740234375</v>
       </c>
       <c r="E889" t="n">
-        <v>89.4143562815249</v>
+        <v>89.41436398245803</v>
       </c>
       <c r="F889" t="n">
         <v>288735</v>
@@ -18272,16 +18272,16 @@
         <v>45783</v>
       </c>
       <c r="B893" t="n">
-        <v>88.32965850830078</v>
+        <v>88.32966613769531</v>
       </c>
       <c r="C893" t="n">
-        <v>90.02999502948387</v>
+        <v>90.03000280574344</v>
       </c>
       <c r="D893" t="n">
-        <v>87.94854872692339</v>
+        <v>87.9485563233999</v>
       </c>
       <c r="E893" t="n">
-        <v>87.94854872692339</v>
+        <v>87.9485563233999</v>
       </c>
       <c r="F893" t="n">
         <v>191886</v>
@@ -18292,16 +18292,16 @@
         <v>45784</v>
       </c>
       <c r="B894" t="n">
-        <v>89.1602783203125</v>
+        <v>89.16028594970703</v>
       </c>
       <c r="C894" t="n">
-        <v>89.26777158274103</v>
+        <v>89.26777922133371</v>
       </c>
       <c r="D894" t="n">
-        <v>87.09837294898765</v>
+        <v>87.0983804019461</v>
       </c>
       <c r="E894" t="n">
-        <v>88.43714792755821</v>
+        <v>88.43715549507488</v>
       </c>
       <c r="F894" t="n">
         <v>251191</v>
@@ -18312,16 +18312,16 @@
         <v>45785</v>
       </c>
       <c r="B895" t="n">
-        <v>97.71083831787109</v>
+        <v>97.71083068847656</v>
       </c>
       <c r="C895" t="n">
-        <v>97.71083831787109</v>
+        <v>97.71083068847656</v>
       </c>
       <c r="D895" t="n">
-        <v>88.50555841283003</v>
+        <v>88.50555150219621</v>
       </c>
       <c r="E895" t="n">
-        <v>88.50555841283003</v>
+        <v>88.50555150219621</v>
       </c>
       <c r="F895" t="n">
         <v>1207326</v>
@@ -18332,16 +18332,16 @@
         <v>45786</v>
       </c>
       <c r="B896" t="n">
-        <v>98.40465545654297</v>
+        <v>98.40464782714844</v>
       </c>
       <c r="C896" t="n">
-        <v>99.07893007986451</v>
+        <v>99.0789223981929</v>
       </c>
       <c r="D896" t="n">
-        <v>97.23201106906231</v>
+        <v>97.23200353058388</v>
       </c>
       <c r="E896" t="n">
-        <v>97.67175085049476</v>
+        <v>97.67174327792293</v>
       </c>
       <c r="F896" t="n">
         <v>488440</v>
@@ -18372,16 +18372,16 @@
         <v>45790</v>
       </c>
       <c r="B898" t="n">
-        <v>101.4242172241211</v>
+        <v>101.4242248535156</v>
       </c>
       <c r="C898" t="n">
-        <v>102.2548408787985</v>
+        <v>102.2548485706747</v>
       </c>
       <c r="D898" t="n">
-        <v>99.13755118124867</v>
+        <v>99.1375586386342</v>
       </c>
       <c r="E898" t="n">
-        <v>99.62615420817545</v>
+        <v>99.62616170231497</v>
       </c>
       <c r="F898" t="n">
         <v>527476</v>
@@ -18392,16 +18392,16 @@
         <v>45791</v>
       </c>
       <c r="B899" t="n">
-        <v>103.1538772583008</v>
+        <v>103.1538696289062</v>
       </c>
       <c r="C899" t="n">
-        <v>104.5610564789144</v>
+        <v>104.561048745443</v>
       </c>
       <c r="D899" t="n">
-        <v>100.359067114855</v>
+        <v>100.3590596921682</v>
       </c>
       <c r="E899" t="n">
-        <v>101.3362732501719</v>
+        <v>101.3362657552098</v>
       </c>
       <c r="F899" t="n">
         <v>818733</v>
@@ -18432,16 +18432,16 @@
         <v>45793</v>
       </c>
       <c r="B901" t="n">
-        <v>103.5936279296875</v>
+        <v>103.593620300293</v>
       </c>
       <c r="C901" t="n">
-        <v>104.0235935737591</v>
+        <v>104.0235859126987</v>
       </c>
       <c r="D901" t="n">
-        <v>102.3721202200121</v>
+        <v>102.3721126805784</v>
       </c>
       <c r="E901" t="n">
-        <v>103.2906889479539</v>
+        <v>103.29068134087</v>
       </c>
       <c r="F901" t="n">
         <v>726672</v>
@@ -18452,16 +18452,16 @@
         <v>45796</v>
       </c>
       <c r="B902" t="n">
-        <v>102.2157516479492</v>
+        <v>102.2157592773438</v>
       </c>
       <c r="C902" t="n">
-        <v>103.7499648528683</v>
+        <v>103.7499725967766</v>
       </c>
       <c r="D902" t="n">
-        <v>101.6685186440516</v>
+        <v>101.6685262326006</v>
       </c>
       <c r="E902" t="n">
-        <v>103.5643007725404</v>
+        <v>103.5643085025908</v>
       </c>
       <c r="F902" t="n">
         <v>1026194</v>
@@ -18512,16 +18512,16 @@
         <v>45799</v>
       </c>
       <c r="B905" t="n">
-        <v>103.8770141601562</v>
+        <v>103.8770065307617</v>
       </c>
       <c r="C905" t="n">
-        <v>104.6099187545445</v>
+        <v>104.6099110713208</v>
       </c>
       <c r="D905" t="n">
-        <v>102.3232525431978</v>
+        <v>102.3232450279215</v>
       </c>
       <c r="E905" t="n">
-        <v>103.5838493402045</v>
+        <v>103.5838417323419</v>
       </c>
       <c r="F905" t="n">
         <v>1088124</v>
@@ -18532,16 +18532,16 @@
         <v>45800</v>
       </c>
       <c r="B906" t="n">
-        <v>103.2906875610352</v>
+        <v>103.2906799316406</v>
       </c>
       <c r="C906" t="n">
-        <v>104.3851611381853</v>
+        <v>104.3851534279493</v>
       </c>
       <c r="D906" t="n">
-        <v>100.8769946217388</v>
+        <v>100.8769871706277</v>
       </c>
       <c r="E906" t="n">
-        <v>102.704365359362</v>
+        <v>102.7043577732752</v>
       </c>
       <c r="F906" t="n">
         <v>895232</v>
@@ -18552,16 +18552,16 @@
         <v>45803</v>
       </c>
       <c r="B907" t="n">
-        <v>103.7988357543945</v>
+        <v>103.798828125</v>
       </c>
       <c r="C907" t="n">
-        <v>104.6587744601196</v>
+        <v>104.6587667675181</v>
       </c>
       <c r="D907" t="n">
-        <v>102.997527030392</v>
+        <v>102.997519459895</v>
       </c>
       <c r="E907" t="n">
-        <v>102.997527030392</v>
+        <v>102.997519459895</v>
       </c>
       <c r="F907" t="n">
         <v>188218</v>
@@ -18612,16 +18612,16 @@
         <v>45806</v>
       </c>
       <c r="B910" t="n">
-        <v>107.2679138183594</v>
+        <v>107.2679061889648</v>
       </c>
       <c r="C910" t="n">
-        <v>108.8021271472243</v>
+        <v>108.8021194087094</v>
       </c>
       <c r="D910" t="n">
-        <v>106.3982009574068</v>
+        <v>106.3981933898703</v>
       </c>
       <c r="E910" t="n">
-        <v>108.235353256895</v>
+        <v>108.2353455586916</v>
       </c>
       <c r="F910" t="n">
         <v>645105</v>
@@ -18652,16 +18652,16 @@
         <v>45810</v>
       </c>
       <c r="B912" t="n">
-        <v>107.4047241210938</v>
+        <v>107.4047317504883</v>
       </c>
       <c r="C912" t="n">
-        <v>109.2027797345073</v>
+        <v>109.2027874916251</v>
       </c>
       <c r="D912" t="n">
-        <v>106.740223686682</v>
+        <v>106.7402312688744</v>
       </c>
       <c r="E912" t="n">
-        <v>108.5480534484594</v>
+        <v>108.5480611590693</v>
       </c>
       <c r="F912" t="n">
         <v>325434</v>
@@ -18712,16 +18712,16 @@
         <v>45813</v>
       </c>
       <c r="B915" t="n">
-        <v>108.3916931152344</v>
+        <v>108.3917007446289</v>
       </c>
       <c r="C915" t="n">
-        <v>108.7532620371724</v>
+        <v>108.7532696920168</v>
       </c>
       <c r="D915" t="n">
-        <v>107.0529256002424</v>
+        <v>107.0529331354047</v>
       </c>
       <c r="E915" t="n">
-        <v>107.8835492504071</v>
+        <v>107.8835568440347</v>
       </c>
       <c r="F915" t="n">
         <v>989620</v>
@@ -18732,16 +18732,16 @@
         <v>45814</v>
       </c>
       <c r="B916" t="n">
-        <v>107.5513000488281</v>
+        <v>107.5513076782227</v>
       </c>
       <c r="C916" t="n">
-        <v>108.9584792063988</v>
+        <v>108.9584869356147</v>
       </c>
       <c r="D916" t="n">
-        <v>106.4861489876882</v>
+        <v>106.4861565415238</v>
       </c>
       <c r="E916" t="n">
-        <v>108.3721570425746</v>
+        <v>108.3721647301985</v>
       </c>
       <c r="F916" t="n">
         <v>400888</v>
@@ -18752,16 +18752,16 @@
         <v>45817</v>
       </c>
       <c r="B917" t="n">
-        <v>106.2809448242188</v>
+        <v>106.2809371948242</v>
       </c>
       <c r="C917" t="n">
-        <v>108.2744462998158</v>
+        <v>108.2744385273175</v>
       </c>
       <c r="D917" t="n">
-        <v>105.7727934422378</v>
+        <v>105.772785849321</v>
       </c>
       <c r="E917" t="n">
-        <v>107.1995135515835</v>
+        <v>107.1995058562494</v>
       </c>
       <c r="F917" t="n">
         <v>436201</v>
@@ -18772,16 +18772,16 @@
         <v>45818</v>
       </c>
       <c r="B918" t="n">
-        <v>108.6848602294922</v>
+        <v>108.6848678588867</v>
       </c>
       <c r="C918" t="n">
-        <v>109.7109221290484</v>
+        <v>109.7109298304698</v>
       </c>
       <c r="D918" t="n">
-        <v>106.8086263655974</v>
+        <v>106.8086338632852</v>
       </c>
       <c r="E918" t="n">
-        <v>106.8086263655974</v>
+        <v>106.8086338632852</v>
       </c>
       <c r="F918" t="n">
         <v>299047</v>
@@ -18872,16 +18872,16 @@
         <v>45825</v>
       </c>
       <c r="B923" t="n">
-        <v>107.5903854370117</v>
+        <v>107.5903930664062</v>
       </c>
       <c r="C923" t="n">
-        <v>107.8444610994928</v>
+        <v>107.8444687469043</v>
       </c>
       <c r="D923" t="n">
-        <v>105.7630148810455</v>
+        <v>105.7630223808585</v>
       </c>
       <c r="E923" t="n">
-        <v>107.7858311218013</v>
+        <v>107.7858387650551</v>
       </c>
       <c r="F923" t="n">
         <v>359643</v>
@@ -18892,16 +18892,16 @@
         <v>45826</v>
       </c>
       <c r="B924" t="n">
-        <v>106.9845352172852</v>
+        <v>106.9845275878906</v>
       </c>
       <c r="C924" t="n">
-        <v>107.6881174000007</v>
+        <v>107.6881097204315</v>
       </c>
       <c r="D924" t="n">
-        <v>105.8314316336663</v>
+        <v>105.8314240865031</v>
       </c>
       <c r="E924" t="n">
-        <v>107.0040760603503</v>
+        <v>107.0040684295622</v>
       </c>
       <c r="F924" t="n">
         <v>439989</v>
@@ -18912,16 +18912,16 @@
         <v>45828</v>
       </c>
       <c r="B925" t="n">
-        <v>104.707633972168</v>
+        <v>104.7076416015625</v>
       </c>
       <c r="C925" t="n">
-        <v>107.0040667912006</v>
+        <v>107.0040745879219</v>
       </c>
       <c r="D925" t="n">
-        <v>104.6294556956968</v>
+        <v>104.629463319395</v>
       </c>
       <c r="E925" t="n">
-        <v>107.0040667912006</v>
+        <v>107.0040745879219</v>
       </c>
       <c r="F925" t="n">
         <v>336419</v>
@@ -18952,16 +18952,16 @@
         <v>45832</v>
       </c>
       <c r="B927" t="n">
-        <v>103.5936279296875</v>
+        <v>103.593620300293</v>
       </c>
       <c r="C927" t="n">
-        <v>106.0854991841304</v>
+        <v>106.0854913712162</v>
       </c>
       <c r="D927" t="n">
-        <v>103.1050248458173</v>
+        <v>103.1050172524071</v>
       </c>
       <c r="E927" t="n">
-        <v>103.1050248458173</v>
+        <v>103.1050172524071</v>
       </c>
       <c r="F927" t="n">
         <v>471744</v>
@@ -19072,16 +19072,16 @@
         <v>45840</v>
       </c>
       <c r="B933" t="n">
-        <v>103.3004608154297</v>
+        <v>103.3004531860352</v>
       </c>
       <c r="C933" t="n">
-        <v>106.0952709898735</v>
+        <v>106.0952631540645</v>
       </c>
       <c r="D933" t="n">
-        <v>103.2418308324176</v>
+        <v>103.2418232073532</v>
       </c>
       <c r="E933" t="n">
-        <v>106.0561818493683</v>
+        <v>106.0561740164463</v>
       </c>
       <c r="F933" t="n">
         <v>463221</v>
@@ -19112,16 +19112,16 @@
         <v>45842</v>
       </c>
       <c r="B935" t="n">
-        <v>103.5936279296875</v>
+        <v>103.593620300293</v>
       </c>
       <c r="C935" t="n">
-        <v>104.7369573566257</v>
+        <v>104.736949643028</v>
       </c>
       <c r="D935" t="n">
-        <v>102.8998124452508</v>
+        <v>102.899804866954</v>
       </c>
       <c r="E935" t="n">
-        <v>102.9095791389745</v>
+        <v>102.9095715599583</v>
       </c>
       <c r="F935" t="n">
         <v>75389</v>
@@ -19132,16 +19132,16 @@
         <v>45845</v>
       </c>
       <c r="B936" t="n">
-        <v>104.4535598754883</v>
+        <v>104.4535675048828</v>
       </c>
       <c r="C936" t="n">
-        <v>104.844443808244</v>
+        <v>104.8444514661891</v>
       </c>
       <c r="D936" t="n">
-        <v>103.5740728906607</v>
+        <v>103.5740804558166</v>
       </c>
       <c r="E936" t="n">
-        <v>104.3167516173474</v>
+        <v>104.3167592367493</v>
       </c>
       <c r="F936" t="n">
         <v>614814</v>
@@ -19152,16 +19152,16 @@
         <v>45846</v>
       </c>
       <c r="B937" t="n">
-        <v>102.8998107910156</v>
+        <v>102.8998031616211</v>
       </c>
       <c r="C937" t="n">
-        <v>104.9323939210659</v>
+        <v>104.9323861409677</v>
       </c>
       <c r="D937" t="n">
-        <v>102.6164201122678</v>
+        <v>102.616412503885</v>
       </c>
       <c r="E937" t="n">
-        <v>103.5936262642984</v>
+        <v>103.5936185834616</v>
       </c>
       <c r="F937" t="n">
         <v>319689</v>
@@ -19192,16 +19192,16 @@
         <v>45848</v>
       </c>
       <c r="B939" t="n">
-        <v>100.8378982543945</v>
+        <v>100.8379058837891</v>
       </c>
       <c r="C939" t="n">
-        <v>103.2222760310556</v>
+        <v>103.2222838408521</v>
       </c>
       <c r="D939" t="n">
-        <v>99.47958239325645</v>
+        <v>99.47958991988082</v>
       </c>
       <c r="E939" t="n">
-        <v>102.8802553925479</v>
+        <v>102.8802631764672</v>
       </c>
       <c r="F939" t="n">
         <v>532452</v>
@@ -19232,16 +19232,16 @@
         <v>45852</v>
       </c>
       <c r="B941" t="n">
-        <v>98.11149597167969</v>
+        <v>98.11148834228516</v>
       </c>
       <c r="C941" t="n">
-        <v>99.43072274301957</v>
+        <v>99.43071501103869</v>
       </c>
       <c r="D941" t="n">
-        <v>97.74992702318283</v>
+        <v>97.74991942190482</v>
       </c>
       <c r="E941" t="n">
-        <v>98.94211968285731</v>
+        <v>98.94211198887142</v>
       </c>
       <c r="F941" t="n">
         <v>223357</v>
@@ -19252,16 +19252,16 @@
         <v>45853</v>
       </c>
       <c r="B942" t="n">
-        <v>98.70759582519531</v>
+        <v>98.70758819580078</v>
       </c>
       <c r="C942" t="n">
-        <v>99.33300716808975</v>
+        <v>99.33299949035536</v>
       </c>
       <c r="D942" t="n">
-        <v>97.82810879440898</v>
+        <v>97.82810123299254</v>
       </c>
       <c r="E942" t="n">
-        <v>98.12127362316819</v>
+        <v>98.12126603909219</v>
       </c>
       <c r="F942" t="n">
         <v>259679</v>
@@ -19272,16 +19272,16 @@
         <v>45854</v>
       </c>
       <c r="B943" t="n">
-        <v>99.80206298828125</v>
+        <v>99.80205535888672</v>
       </c>
       <c r="C943" t="n">
-        <v>100.0365978359309</v>
+        <v>100.0365901886073</v>
       </c>
       <c r="D943" t="n">
-        <v>97.96491808130695</v>
+        <v>97.96491059235345</v>
       </c>
       <c r="E943" t="n">
-        <v>98.71736354824841</v>
+        <v>98.71735600177402</v>
       </c>
       <c r="F943" t="n">
         <v>444283</v>
@@ -19332,16 +19332,16 @@
         <v>45859</v>
       </c>
       <c r="B946" t="n">
-        <v>92.29711151123047</v>
+        <v>92.297119140625</v>
       </c>
       <c r="C946" t="n">
-        <v>93.63588652825102</v>
+        <v>93.63589426831037</v>
       </c>
       <c r="D946" t="n">
-        <v>91.88668674589246</v>
+        <v>91.88669434136077</v>
       </c>
       <c r="E946" t="n">
-        <v>93.0300160731158</v>
+        <v>93.03002376309314</v>
       </c>
       <c r="F946" t="n">
         <v>459254</v>
@@ -19372,16 +19372,16 @@
         <v>45861</v>
       </c>
       <c r="B948" t="n">
-        <v>91.75965118408203</v>
+        <v>91.75965881347656</v>
       </c>
       <c r="C948" t="n">
-        <v>92.32643249227019</v>
+        <v>92.32644016878999</v>
       </c>
       <c r="D948" t="n">
-        <v>91.0756024638751</v>
+        <v>91.07561003639412</v>
       </c>
       <c r="E948" t="n">
-        <v>92.26779505851549</v>
+        <v>92.26780273015984</v>
       </c>
       <c r="F948" t="n">
         <v>201915</v>
@@ -19392,16 +19392,16 @@
         <v>45862</v>
       </c>
       <c r="B949" t="n">
-        <v>90.00067901611328</v>
+        <v>90.00068664550781</v>
       </c>
       <c r="C949" t="n">
-        <v>92.0332694640087</v>
+        <v>92.03327726570676</v>
       </c>
       <c r="D949" t="n">
-        <v>89.64888422876635</v>
+        <v>89.64889182833909</v>
       </c>
       <c r="E949" t="n">
-        <v>92.0332694640087</v>
+        <v>92.03327726570676</v>
       </c>
       <c r="F949" t="n">
         <v>148443</v>
@@ -19412,16 +19412,16 @@
         <v>45863</v>
       </c>
       <c r="B950" t="n">
-        <v>89.61957550048828</v>
+        <v>89.61956787109375</v>
       </c>
       <c r="C950" t="n">
-        <v>90.68473408534409</v>
+        <v>90.68472636527164</v>
       </c>
       <c r="D950" t="n">
-        <v>89.27755483764147</v>
+        <v>89.27754723736346</v>
       </c>
       <c r="E950" t="n">
-        <v>89.46322639268315</v>
+        <v>89.46321877659875</v>
       </c>
       <c r="F950" t="n">
         <v>133512</v>
@@ -19572,16 +19572,16 @@
         <v>45875</v>
       </c>
       <c r="B958" t="n">
-        <v>91.05606079101562</v>
+        <v>91.05606842041016</v>
       </c>
       <c r="C958" t="n">
-        <v>91.3101364536563</v>
+        <v>91.3101441043393</v>
       </c>
       <c r="D958" t="n">
-        <v>90.09839557367191</v>
+        <v>90.09840312282569</v>
       </c>
       <c r="E958" t="n">
-        <v>90.09839557367191</v>
+        <v>90.09840312282569</v>
       </c>
       <c r="F958" t="n">
         <v>142081</v>
@@ -19752,16 +19752,16 @@
         <v>45888</v>
       </c>
       <c r="B967" t="n">
-        <v>85.65212249755859</v>
+        <v>85.65211486816406</v>
       </c>
       <c r="C967" t="n">
-        <v>90.97789315466845</v>
+        <v>90.97788505088515</v>
       </c>
       <c r="D967" t="n">
-        <v>85.40782095447115</v>
+        <v>85.40781334683759</v>
       </c>
       <c r="E967" t="n">
-        <v>90.97789315466845</v>
+        <v>90.97788505088515</v>
       </c>
       <c r="F967" t="n">
         <v>1451209</v>
@@ -19772,16 +19772,16 @@
         <v>45889</v>
       </c>
       <c r="B968" t="n">
-        <v>86.38501739501953</v>
+        <v>86.38502502441406</v>
       </c>
       <c r="C968" t="n">
-        <v>87.58697667652652</v>
+        <v>87.58698441207628</v>
       </c>
       <c r="D968" t="n">
-        <v>85.41758548091796</v>
+        <v>85.41759302487036</v>
       </c>
       <c r="E968" t="n">
-        <v>86.15049002761413</v>
+        <v>86.15049763629555</v>
       </c>
       <c r="F968" t="n">
         <v>1048687</v>
@@ -19832,16 +19832,16 @@
         <v>45894</v>
       </c>
       <c r="B971" t="n">
-        <v>88.92575836181641</v>
+        <v>88.92575073242188</v>
       </c>
       <c r="C971" t="n">
-        <v>89.5413955434214</v>
+        <v>89.54138786120821</v>
       </c>
       <c r="D971" t="n">
-        <v>87.15701764169569</v>
+        <v>87.15701016405045</v>
       </c>
       <c r="E971" t="n">
-        <v>87.15701764169569</v>
+        <v>87.15701016405045</v>
       </c>
       <c r="F971" t="n">
         <v>788338</v>
@@ -19872,16 +19872,16 @@
         <v>45896</v>
       </c>
       <c r="B973" t="n">
-        <v>90.80198669433594</v>
+        <v>90.80199432373047</v>
       </c>
       <c r="C973" t="n">
-        <v>90.80198669433594</v>
+        <v>90.80199432373047</v>
       </c>
       <c r="D973" t="n">
-        <v>88.61304717400222</v>
+        <v>88.61305461947694</v>
       </c>
       <c r="E973" t="n">
-        <v>88.91597867147736</v>
+        <v>88.91598614240509</v>
       </c>
       <c r="F973" t="n">
         <v>1220015</v>
@@ -19932,16 +19932,16 @@
         <v>45901</v>
       </c>
       <c r="B976" t="n">
-        <v>96.01050567626953</v>
+        <v>96.010498046875</v>
       </c>
       <c r="C976" t="n">
-        <v>96.44047877447011</v>
+        <v>96.44047111090812</v>
       </c>
       <c r="D976" t="n">
-        <v>95.27760105278657</v>
+        <v>95.27759348163168</v>
       </c>
       <c r="E976" t="n">
-        <v>95.28737520197058</v>
+        <v>95.287367630039</v>
       </c>
       <c r="F976" t="n">
         <v>152929</v>
@@ -19952,16 +19952,16 @@
         <v>45902</v>
       </c>
       <c r="B977" t="n">
-        <v>95.76619720458984</v>
+        <v>95.76620483398438</v>
       </c>
       <c r="C977" t="n">
-        <v>95.76619720458984</v>
+        <v>95.76620483398438</v>
       </c>
       <c r="D977" t="n">
-        <v>93.7140658984468</v>
+        <v>93.71407336435442</v>
       </c>
       <c r="E977" t="n">
-        <v>95.75642305611316</v>
+        <v>95.75643068472903</v>
       </c>
       <c r="F977" t="n">
         <v>684271</v>
@@ -19972,16 +19972,16 @@
         <v>45903</v>
       </c>
       <c r="B978" t="n">
-        <v>95.60984802246094</v>
+        <v>95.60984039306641</v>
       </c>
       <c r="C978" t="n">
-        <v>96.16686269621496</v>
+        <v>96.16685502237223</v>
       </c>
       <c r="D978" t="n">
-        <v>94.76945757594329</v>
+        <v>94.76945001360953</v>
       </c>
       <c r="E978" t="n">
-        <v>95.75643043894929</v>
+        <v>95.75642279785789</v>
       </c>
       <c r="F978" t="n">
         <v>439208</v>
@@ -20052,16 +20052,16 @@
         <v>45909</v>
       </c>
       <c r="B982" t="n">
-        <v>96.98770904541016</v>
+        <v>96.98770141601562</v>
       </c>
       <c r="C982" t="n">
-        <v>99.0887037299354</v>
+        <v>99.08869593526924</v>
       </c>
       <c r="D982" t="n">
-        <v>96.87044162505602</v>
+        <v>96.87043400488615</v>
       </c>
       <c r="E982" t="n">
-        <v>97.8671960593383</v>
+        <v>97.86718836076022</v>
       </c>
       <c r="F982" t="n">
         <v>316824</v>
@@ -20112,16 +20112,16 @@
         <v>45912</v>
       </c>
       <c r="B985" t="n">
-        <v>98.69782257080078</v>
+        <v>98.69781494140625</v>
       </c>
       <c r="C985" t="n">
-        <v>100.2027209581235</v>
+        <v>100.2027132123995</v>
       </c>
       <c r="D985" t="n">
-        <v>97.80856138286366</v>
+        <v>97.80855382220949</v>
       </c>
       <c r="E985" t="n">
-        <v>99.1180215195694</v>
+        <v>99.11801385769326</v>
       </c>
       <c r="F985" t="n">
         <v>599879</v>
@@ -20132,16 +20132,16 @@
         <v>45915</v>
       </c>
       <c r="B986" t="n">
-        <v>98.02353668212891</v>
+        <v>98.02354431152344</v>
       </c>
       <c r="C986" t="n">
-        <v>99.6457023069481</v>
+        <v>99.64571006259945</v>
       </c>
       <c r="D986" t="n">
-        <v>97.52516696360394</v>
+        <v>97.52517455420922</v>
       </c>
       <c r="E986" t="n">
-        <v>98.69781124370924</v>
+        <v>98.69781892558407</v>
       </c>
       <c r="F986" t="n">
         <v>461876</v>
@@ -20152,16 +20152,16 @@
         <v>45916</v>
       </c>
       <c r="B987" t="n">
-        <v>99.60662078857422</v>
+        <v>99.60661315917969</v>
       </c>
       <c r="C987" t="n">
-        <v>100.4861077936656</v>
+        <v>100.4861000969065</v>
       </c>
       <c r="D987" t="n">
-        <v>97.60334524672678</v>
+        <v>97.60333777077366</v>
       </c>
       <c r="E987" t="n">
-        <v>98.11149660766448</v>
+        <v>98.11148909278937</v>
       </c>
       <c r="F987" t="n">
         <v>502898</v>
@@ -20172,16 +20172,16 @@
         <v>45917</v>
       </c>
       <c r="B988" t="n">
-        <v>102.8998107910156</v>
+        <v>102.8998031616211</v>
       </c>
       <c r="C988" t="n">
-        <v>104.8444489460189</v>
+        <v>104.8444411724413</v>
       </c>
       <c r="D988" t="n">
-        <v>98.7466846448857</v>
+        <v>98.74667732342019</v>
       </c>
       <c r="E988" t="n">
-        <v>99.22551357184312</v>
+        <v>99.22550621487537</v>
       </c>
       <c r="F988" t="n">
         <v>607209</v>
@@ -20192,16 +20192,16 @@
         <v>45918</v>
       </c>
       <c r="B989" t="n">
-        <v>104.0919952392578</v>
+        <v>104.0919876098633</v>
       </c>
       <c r="C989" t="n">
-        <v>104.7858181627353</v>
+        <v>104.7858104824872</v>
       </c>
       <c r="D989" t="n">
-        <v>102.069178818216</v>
+        <v>102.0691713370833</v>
       </c>
       <c r="E989" t="n">
-        <v>103.5936254734804</v>
+        <v>103.5936178806138</v>
       </c>
       <c r="F989" t="n">
         <v>323487</v>
@@ -20212,16 +20212,16 @@
         <v>45919</v>
       </c>
       <c r="B990" t="n">
-        <v>102.118034362793</v>
+        <v>102.1180419921875</v>
       </c>
       <c r="C990" t="n">
-        <v>105.0203375849298</v>
+        <v>105.0203454311598</v>
       </c>
       <c r="D990" t="n">
-        <v>101.4437597884204</v>
+        <v>101.4437673674388</v>
       </c>
       <c r="E990" t="n">
-        <v>104.3753779997924</v>
+        <v>104.3753857978366</v>
       </c>
       <c r="F990" t="n">
         <v>805829</v>
@@ -20252,16 +20252,16 @@
         <v>45923</v>
       </c>
       <c r="B992" t="n">
-        <v>101.2385482788086</v>
+        <v>101.2385559082031</v>
       </c>
       <c r="C992" t="n">
-        <v>102.5577749941716</v>
+        <v>102.5577827229838</v>
       </c>
       <c r="D992" t="n">
-        <v>100.4079246028757</v>
+        <v>100.4079321696739</v>
       </c>
       <c r="E992" t="n">
-        <v>101.2287741304826</v>
+        <v>101.2287817591405</v>
       </c>
       <c r="F992" t="n">
         <v>578829</v>
@@ -20372,16 +20372,16 @@
         <v>45931</v>
       </c>
       <c r="B998" t="n">
-        <v>95.22873687744141</v>
+        <v>95.22872924804688</v>
       </c>
       <c r="C998" t="n">
-        <v>99.3623221958901</v>
+        <v>99.3623142353271</v>
       </c>
       <c r="D998" t="n">
-        <v>95.01375778583019</v>
+        <v>95.01375017365902</v>
       </c>
       <c r="E998" t="n">
-        <v>97.55449229919635</v>
+        <v>97.5544844834704</v>
       </c>
       <c r="F998" t="n">
         <v>911140</v>
@@ -20392,16 +20392,16 @@
         <v>45932</v>
       </c>
       <c r="B999" t="n">
-        <v>92.09190368652344</v>
+        <v>92.09189605712891</v>
       </c>
       <c r="C999" t="n">
-        <v>96.53819456422049</v>
+        <v>96.53818656647101</v>
       </c>
       <c r="D999" t="n">
-        <v>91.47626650804631</v>
+        <v>91.47625892965451</v>
       </c>
       <c r="E999" t="n">
-        <v>95.22873447198691</v>
+        <v>95.22872658272024</v>
       </c>
       <c r="F999" t="n">
         <v>1326713</v>
@@ -20452,16 +20452,16 @@
         <v>45937</v>
       </c>
       <c r="B1002" t="n">
-        <v>85.99413299560547</v>
+        <v>85.994140625</v>
       </c>
       <c r="C1002" t="n">
-        <v>88.4957781151752</v>
+        <v>88.49578596651554</v>
       </c>
       <c r="D1002" t="n">
-        <v>85.55439325225598</v>
+        <v>85.55440084263682</v>
       </c>
       <c r="E1002" t="n">
-        <v>88.24170990836865</v>
+        <v>88.24171773716807</v>
       </c>
       <c r="F1002" t="n">
         <v>845675</v>
@@ -20512,16 +20512,16 @@
         <v>45940</v>
       </c>
       <c r="B1005" t="n">
-        <v>85.34918212890625</v>
+        <v>85.34917449951172</v>
       </c>
       <c r="C1005" t="n">
-        <v>86.74658723090178</v>
+        <v>86.7465794765927</v>
       </c>
       <c r="D1005" t="n">
-        <v>84.66514080156213</v>
+        <v>84.66513323331431</v>
       </c>
       <c r="E1005" t="n">
-        <v>85.31010044347914</v>
+        <v>85.31009281757814</v>
       </c>
       <c r="F1005" t="n">
         <v>848390</v>
@@ -20572,16 +20572,16 @@
         <v>45945</v>
       </c>
       <c r="B1008" t="n">
-        <v>88.33943939208984</v>
+        <v>88.33943176269531</v>
       </c>
       <c r="C1008" t="n">
-        <v>89.01370658067076</v>
+        <v>89.01369889304345</v>
       </c>
       <c r="D1008" t="n">
-        <v>85.47622501145973</v>
+        <v>85.47621762934537</v>
       </c>
       <c r="E1008" t="n">
-        <v>85.85733482189416</v>
+        <v>85.85732740686544</v>
       </c>
       <c r="F1008" t="n">
         <v>892096</v>
@@ -20672,16 +20672,16 @@
         <v>45952</v>
       </c>
       <c r="B1013" t="n">
-        <v>88.34921264648438</v>
+        <v>88.34920501708984</v>
       </c>
       <c r="C1013" t="n">
-        <v>90.32316581244639</v>
+        <v>90.32315801259118</v>
       </c>
       <c r="D1013" t="n">
-        <v>88.06582196496913</v>
+        <v>88.0658143600468</v>
       </c>
       <c r="E1013" t="n">
-        <v>89.41436378396349</v>
+        <v>89.41435606258787</v>
       </c>
       <c r="F1013" t="n">
         <v>342955</v>
@@ -20812,16 +20812,16 @@
         <v>45961</v>
       </c>
       <c r="B1020" t="n">
-        <v>95.01375579833984</v>
+        <v>95.01374816894531</v>
       </c>
       <c r="C1020" t="n">
-        <v>95.64893382177631</v>
+        <v>95.64892614137838</v>
       </c>
       <c r="D1020" t="n">
-        <v>94.12449463674297</v>
+        <v>94.12448707875414</v>
       </c>
       <c r="E1020" t="n">
-        <v>94.39811116169858</v>
+        <v>94.39810358173895</v>
       </c>
       <c r="F1020" t="n">
         <v>181142</v>
@@ -20872,16 +20872,16 @@
         <v>45966</v>
       </c>
       <c r="B1023" t="n">
-        <v>96.76294708251953</v>
+        <v>96.762939453125</v>
       </c>
       <c r="C1023" t="n">
-        <v>97.7108382153299</v>
+        <v>97.71083051119773</v>
       </c>
       <c r="D1023" t="n">
-        <v>95.0137546820342</v>
+        <v>95.01374719055691</v>
       </c>
       <c r="E1023" t="n">
-        <v>95.33622703666254</v>
+        <v>95.33621951975952</v>
       </c>
       <c r="F1023" t="n">
         <v>404214</v>
@@ -20892,16 +20892,16 @@
         <v>45967</v>
       </c>
       <c r="B1024" t="n">
-        <v>97.857421875</v>
+        <v>97.85741424560547</v>
       </c>
       <c r="C1024" t="n">
-        <v>98.36557324085943</v>
+        <v>98.36556557184718</v>
       </c>
       <c r="D1024" t="n">
-        <v>96.3720718285079</v>
+        <v>96.37206431491778</v>
       </c>
       <c r="E1024" t="n">
-        <v>96.76294831856451</v>
+        <v>96.76294077449994</v>
       </c>
       <c r="F1024" t="n">
         <v>244412</v>
@@ -20972,16 +20972,16 @@
         <v>45973</v>
       </c>
       <c r="B1028" t="n">
-        <v>99.68479919433594</v>
+        <v>99.68479156494141</v>
       </c>
       <c r="C1028" t="n">
-        <v>103.0659315022015</v>
+        <v>103.0659236140314</v>
       </c>
       <c r="D1028" t="n">
-        <v>98.06263344339078</v>
+        <v>98.06262593814901</v>
       </c>
       <c r="E1028" t="n">
-        <v>101.629437301314</v>
+        <v>101.6294295230862</v>
       </c>
       <c r="F1028" t="n">
         <v>452005</v>
@@ -21032,16 +21032,16 @@
         <v>45978</v>
       </c>
       <c r="B1031" t="n">
-        <v>94.49582672119141</v>
+        <v>94.49583435058594</v>
       </c>
       <c r="C1031" t="n">
-        <v>97.72060982770191</v>
+        <v>97.72061771745865</v>
       </c>
       <c r="D1031" t="n">
-        <v>94.08540194923286</v>
+        <v>94.08540954549056</v>
       </c>
       <c r="E1031" t="n">
-        <v>96.85089699667463</v>
+        <v>96.85090481621259</v>
       </c>
       <c r="F1031" t="n">
         <v>742213</v>
@@ -21132,16 +21132,16 @@
         <v>45986</v>
       </c>
       <c r="B1036" t="n">
-        <v>95.07238006591797</v>
+        <v>95.0723876953125</v>
       </c>
       <c r="C1036" t="n">
-        <v>95.32645573331483</v>
+        <v>95.32646338309848</v>
       </c>
       <c r="D1036" t="n">
-        <v>93.23523532629541</v>
+        <v>93.23524280826224</v>
       </c>
       <c r="E1036" t="n">
-        <v>93.61634509964536</v>
+        <v>93.61635261219558</v>
       </c>
       <c r="F1036" t="n">
         <v>322148</v>
@@ -21292,16 +21292,16 @@
         <v>45996</v>
       </c>
       <c r="B1044" t="n">
-        <v>95.47303009033203</v>
+        <v>95.47303771972656</v>
       </c>
       <c r="C1044" t="n">
-        <v>104.336288850125</v>
+        <v>104.336297187796</v>
       </c>
       <c r="D1044" t="n">
-        <v>94.21244082042111</v>
+        <v>94.21244834908003</v>
       </c>
       <c r="E1044" t="n">
-        <v>101.6392054639311</v>
+        <v>101.6392135860741</v>
       </c>
       <c r="F1044" t="n">
         <v>1178496</v>
@@ -24412,19 +24412,39 @@
         <v>46230</v>
       </c>
       <c r="B1200" t="n">
-        <v>84.95999999999999</v>
+        <v>84.95999908447266</v>
       </c>
       <c r="C1200" t="n">
-        <v>86.45999999999999</v>
+        <v>86.45999908447266</v>
       </c>
       <c r="D1200" t="n">
-        <v>84.95999999999999</v>
+        <v>84.95999908447266</v>
       </c>
       <c r="E1200" t="n">
-        <v>85.77</v>
+        <v>85.76999664306641</v>
       </c>
       <c r="F1200" t="n">
         <v>287063</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B1201" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="C1201" t="n">
+        <v>87.11</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>85.04000000000001</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>85.04000000000001</v>
+      </c>
+      <c r="F1201" t="n">
+        <v>52988</v>
       </c>
     </row>
   </sheetData>

--- a/database/XPBR31.xlsx
+++ b/database/XPBR31.xlsx
@@ -452,16 +452,16 @@
         <v>44473</v>
       </c>
       <c r="B2" t="n">
-        <v>196.6089630126953</v>
+        <v>196.6089782714844</v>
       </c>
       <c r="C2" t="n">
-        <v>203.5754849761604</v>
+        <v>203.5755007756201</v>
       </c>
       <c r="D2" t="n">
-        <v>191.4433613739322</v>
+        <v>191.4433762318198</v>
       </c>
       <c r="E2" t="n">
-        <v>191.9528946938346</v>
+        <v>191.9529095912669</v>
       </c>
       <c r="F2" t="n">
         <v>9950865</v>
@@ -472,16 +472,16 @@
         <v>44474</v>
       </c>
       <c r="B3" t="n">
-        <v>192.54150390625</v>
+        <v>192.5414886474609</v>
       </c>
       <c r="C3" t="n">
-        <v>198.9809326053319</v>
+        <v>198.9809168362223</v>
       </c>
       <c r="D3" t="n">
-        <v>187.7273111444886</v>
+        <v>187.7272962672212</v>
       </c>
       <c r="E3" t="n">
-        <v>197.6631780847668</v>
+        <v>197.6631624200884</v>
       </c>
       <c r="F3" t="n">
         <v>2636287</v>
@@ -532,16 +532,16 @@
         <v>44477</v>
       </c>
       <c r="B6" t="n">
-        <v>193.8241119384766</v>
+        <v>193.8241271972656</v>
       </c>
       <c r="C6" t="n">
-        <v>204.8668871514385</v>
+        <v>204.8669032795693</v>
       </c>
       <c r="D6" t="n">
-        <v>191.7947722500135</v>
+        <v>191.794787349043</v>
       </c>
       <c r="E6" t="n">
-        <v>200.9926858889775</v>
+        <v>200.9927017121121</v>
       </c>
       <c r="F6" t="n">
         <v>4982319</v>
@@ -552,16 +552,16 @@
         <v>44480</v>
       </c>
       <c r="B7" t="n">
-        <v>180.0931243896484</v>
+        <v>180.0931091308594</v>
       </c>
       <c r="C7" t="n">
-        <v>193.1125459627998</v>
+        <v>193.1125296009114</v>
       </c>
       <c r="D7" t="n">
-        <v>180.0931243896484</v>
+        <v>180.0931091308594</v>
       </c>
       <c r="E7" t="n">
-        <v>191.8738534510431</v>
+        <v>191.8738371941056</v>
       </c>
       <c r="F7" t="n">
         <v>2006205</v>
@@ -612,16 +612,16 @@
         <v>44484</v>
       </c>
       <c r="B10" t="n">
-        <v>175.7005920410156</v>
+        <v>175.7005767822266</v>
       </c>
       <c r="C10" t="n">
-        <v>178.977404329211</v>
+        <v>178.9773887858458</v>
       </c>
       <c r="D10" t="n">
-        <v>166.9155624389649</v>
+        <v>166.9155479431152</v>
       </c>
       <c r="E10" t="n">
-        <v>166.9155624389649</v>
+        <v>166.9155479431152</v>
       </c>
       <c r="F10" t="n">
         <v>2643581</v>
@@ -632,16 +632,16 @@
         <v>44487</v>
       </c>
       <c r="B11" t="n">
-        <v>179.4166564941406</v>
+        <v>179.4166717529297</v>
       </c>
       <c r="C11" t="n">
-        <v>182.2717911257051</v>
+        <v>182.2718066273138</v>
       </c>
       <c r="D11" t="n">
-        <v>175.0680695055053</v>
+        <v>175.0680843944616</v>
       </c>
       <c r="E11" t="n">
-        <v>176.7547935869503</v>
+        <v>176.7548086193568</v>
       </c>
       <c r="F11" t="n">
         <v>1369949</v>
@@ -652,16 +652,16 @@
         <v>44488</v>
       </c>
       <c r="B12" t="n">
-        <v>175.0856475830078</v>
+        <v>175.0856628417969</v>
       </c>
       <c r="C12" t="n">
-        <v>179.4078806604117</v>
+        <v>179.4078962958852</v>
       </c>
       <c r="D12" t="n">
-        <v>174.3828425140635</v>
+        <v>174.3828577116028</v>
       </c>
       <c r="E12" t="n">
-        <v>177.5454586218672</v>
+        <v>177.5454740950298</v>
       </c>
       <c r="F12" t="n">
         <v>722779</v>
@@ -672,16 +672,16 @@
         <v>44489</v>
       </c>
       <c r="B13" t="n">
-        <v>174.3828277587891</v>
+        <v>174.3828582763672</v>
       </c>
       <c r="C13" t="n">
-        <v>178.4942149461601</v>
+        <v>178.4942461832448</v>
       </c>
       <c r="D13" t="n">
-        <v>169.8409693194518</v>
+        <v>169.8409990421895</v>
       </c>
       <c r="E13" t="n">
-        <v>176.5790850353481</v>
+        <v>176.5791159372786</v>
       </c>
       <c r="F13" t="n">
         <v>1907987</v>
@@ -692,16 +692,16 @@
         <v>44490</v>
       </c>
       <c r="B14" t="n">
-        <v>169.4193115234375</v>
+        <v>169.4192962646484</v>
       </c>
       <c r="C14" t="n">
-        <v>176.2189162691178</v>
+        <v>176.2189003979208</v>
       </c>
       <c r="D14" t="n">
-        <v>167.1615523442876</v>
+        <v>167.1615372888441</v>
       </c>
       <c r="E14" t="n">
-        <v>173.3989291023892</v>
+        <v>173.3989134851749</v>
       </c>
       <c r="F14" t="n">
         <v>1852525</v>
@@ -732,16 +732,16 @@
         <v>44494</v>
       </c>
       <c r="B16" t="n">
-        <v>169.12060546875</v>
+        <v>169.1206207275391</v>
       </c>
       <c r="C16" t="n">
-        <v>174.5848951289127</v>
+        <v>174.5849108807135</v>
       </c>
       <c r="D16" t="n">
-        <v>167.3635994919746</v>
+        <v>167.3636145922391</v>
       </c>
       <c r="E16" t="n">
-        <v>167.7062151212502</v>
+        <v>167.7062302524268</v>
       </c>
       <c r="F16" t="n">
         <v>1203463</v>
@@ -752,16 +752,16 @@
         <v>44495</v>
       </c>
       <c r="B17" t="n">
-        <v>163.9637908935547</v>
+        <v>163.9638061523438</v>
       </c>
       <c r="C17" t="n">
-        <v>170.2538752650204</v>
+        <v>170.2538911091769</v>
       </c>
       <c r="D17" t="n">
-        <v>159.9051115332836</v>
+        <v>159.9051264143641</v>
       </c>
       <c r="E17" t="n">
-        <v>168.7604229233316</v>
+        <v>168.7604386285045</v>
       </c>
       <c r="F17" t="n">
         <v>810455</v>
@@ -792,16 +792,16 @@
         <v>44497</v>
       </c>
       <c r="B19" t="n">
-        <v>165.1673278808594</v>
+        <v>165.1673431396484</v>
       </c>
       <c r="C19" t="n">
-        <v>166.8101374438281</v>
+        <v>166.8101528543862</v>
       </c>
       <c r="D19" t="n">
-        <v>158.6664116852975</v>
+        <v>158.6664263435071</v>
       </c>
       <c r="E19" t="n">
-        <v>163.4103220545031</v>
+        <v>163.4103371509733</v>
       </c>
       <c r="F19" t="n">
         <v>1047427</v>
@@ -832,16 +832,16 @@
         <v>44501</v>
       </c>
       <c r="B21" t="n">
-        <v>169.7267761230469</v>
+        <v>169.7267913818359</v>
       </c>
       <c r="C21" t="n">
-        <v>171.2026681266692</v>
+        <v>171.2026835181439</v>
       </c>
       <c r="D21" t="n">
-        <v>161.9344588391563</v>
+        <v>161.9344733973998</v>
       </c>
       <c r="E21" t="n">
-        <v>162.5230542378089</v>
+        <v>162.5230688489684</v>
       </c>
       <c r="F21" t="n">
         <v>466029</v>
@@ -852,16 +852,16 @@
         <v>44503</v>
       </c>
       <c r="B22" t="n">
-        <v>164.6490173339844</v>
+        <v>164.6490325927734</v>
       </c>
       <c r="C22" t="n">
-        <v>168.672562357132</v>
+        <v>168.6725779888017</v>
       </c>
       <c r="D22" t="n">
-        <v>161.3809853659237</v>
+        <v>161.381000321849</v>
       </c>
       <c r="E22" t="n">
-        <v>168.672562357132</v>
+        <v>168.6725779888017</v>
       </c>
       <c r="F22" t="n">
         <v>834348</v>
@@ -892,16 +892,16 @@
         <v>44505</v>
       </c>
       <c r="B24" t="n">
-        <v>170.4735107421875</v>
+        <v>170.4735260009766</v>
       </c>
       <c r="C24" t="n">
-        <v>171.30808591567</v>
+        <v>171.3081012491605</v>
       </c>
       <c r="D24" t="n">
-        <v>159.1408139386772</v>
+        <v>159.1408281830961</v>
       </c>
       <c r="E24" t="n">
-        <v>160.9417477792819</v>
+        <v>160.9417621848993</v>
       </c>
       <c r="F24" t="n">
         <v>806903</v>
@@ -932,16 +932,16 @@
         <v>44509</v>
       </c>
       <c r="B26" t="n">
-        <v>163.7705078125</v>
+        <v>163.7705230712891</v>
       </c>
       <c r="C26" t="n">
-        <v>169.8497462274832</v>
+        <v>169.8497620526857</v>
       </c>
       <c r="D26" t="n">
-        <v>162.0837838654142</v>
+        <v>162.0837989670482</v>
       </c>
       <c r="E26" t="n">
-        <v>167.3548012268911</v>
+        <v>167.3548168196352</v>
       </c>
       <c r="F26" t="n">
         <v>336270</v>
@@ -972,16 +972,16 @@
         <v>44511</v>
       </c>
       <c r="B28" t="n">
-        <v>162.1804351806641</v>
+        <v>162.180419921875</v>
       </c>
       <c r="C28" t="n">
-        <v>165.5099555665838</v>
+        <v>165.5099399945359</v>
       </c>
       <c r="D28" t="n">
-        <v>159.4658641978954</v>
+        <v>159.4658491945075</v>
       </c>
       <c r="E28" t="n">
-        <v>161.5566921686091</v>
+        <v>161.556676968505</v>
       </c>
       <c r="F28" t="n">
         <v>479646</v>
@@ -992,16 +992,16 @@
         <v>44512</v>
       </c>
       <c r="B29" t="n">
-        <v>161.6533355712891</v>
+        <v>161.6533508300781</v>
       </c>
       <c r="C29" t="n">
-        <v>162.5230583851655</v>
+        <v>162.5230737260495</v>
       </c>
       <c r="D29" t="n">
-        <v>157.4277381980575</v>
+        <v>157.4277530579838</v>
       </c>
       <c r="E29" t="n">
-        <v>162.1804427442249</v>
+        <v>162.1804580527687</v>
       </c>
       <c r="F29" t="n">
         <v>339439</v>
@@ -1052,16 +1052,16 @@
         <v>44518</v>
       </c>
       <c r="B32" t="n">
-        <v>141.1402893066406</v>
+        <v>141.1403045654297</v>
       </c>
       <c r="C32" t="n">
-        <v>149.7320472156696</v>
+        <v>149.7320634033205</v>
       </c>
       <c r="D32" t="n">
-        <v>141.1402893066406</v>
+        <v>141.1403045654297</v>
       </c>
       <c r="E32" t="n">
-        <v>147.8520514103275</v>
+        <v>147.8520673947305</v>
       </c>
       <c r="F32" t="n">
         <v>1135748</v>
@@ -1072,16 +1072,16 @@
         <v>44519</v>
       </c>
       <c r="B33" t="n">
-        <v>147.1931762695312</v>
+        <v>147.1931610107422</v>
       </c>
       <c r="C33" t="n">
-        <v>149.0468180845801</v>
+        <v>149.0468026336331</v>
       </c>
       <c r="D33" t="n">
-        <v>140.5692563255631</v>
+        <v>140.5692417534431</v>
       </c>
       <c r="E33" t="n">
-        <v>142.5722420379041</v>
+        <v>142.5722272581445</v>
       </c>
       <c r="F33" t="n">
         <v>581745</v>
@@ -1132,16 +1132,16 @@
         <v>44524</v>
       </c>
       <c r="B36" t="n">
-        <v>148.7393493652344</v>
+        <v>148.7393341064453</v>
       </c>
       <c r="C36" t="n">
-        <v>150.2152414609149</v>
+        <v>150.2152260507179</v>
       </c>
       <c r="D36" t="n">
-        <v>144.4171159644937</v>
+        <v>144.4171011491115</v>
       </c>
       <c r="E36" t="n">
-        <v>144.5225320410092</v>
+        <v>144.5225172148126</v>
       </c>
       <c r="F36" t="n">
         <v>231702</v>
@@ -1152,16 +1152,16 @@
         <v>44525</v>
       </c>
       <c r="B37" t="n">
-        <v>151.3133544921875</v>
+        <v>151.3133850097656</v>
       </c>
       <c r="C37" t="n">
-        <v>152.8507346705215</v>
+        <v>152.8507654981656</v>
       </c>
       <c r="D37" t="n">
-        <v>148.0716764285178</v>
+        <v>148.0717062922993</v>
       </c>
       <c r="E37" t="n">
-        <v>148.0716764285178</v>
+        <v>148.0717062922993</v>
       </c>
       <c r="F37" t="n">
         <v>222385</v>
@@ -1172,16 +1172,16 @@
         <v>44526</v>
       </c>
       <c r="B38" t="n">
-        <v>146.7363433837891</v>
+        <v>146.7363739013672</v>
       </c>
       <c r="C38" t="n">
-        <v>148.7305487890506</v>
+        <v>148.7305797213747</v>
       </c>
       <c r="D38" t="n">
-        <v>143.3716755519658</v>
+        <v>143.3717053697751</v>
       </c>
       <c r="E38" t="n">
-        <v>148.7305487890506</v>
+        <v>148.7305797213747</v>
       </c>
       <c r="F38" t="n">
         <v>241997</v>
@@ -1212,16 +1212,16 @@
         <v>44530</v>
       </c>
       <c r="B40" t="n">
-        <v>140.5604553222656</v>
+        <v>140.5604858398438</v>
       </c>
       <c r="C40" t="n">
-        <v>147.3073507433874</v>
+        <v>147.3073827258078</v>
       </c>
       <c r="D40" t="n">
-        <v>139.7610145154467</v>
+        <v>139.7610448594554</v>
       </c>
       <c r="E40" t="n">
-        <v>147.3073507433874</v>
+        <v>147.3073827258078</v>
       </c>
       <c r="F40" t="n">
         <v>711030</v>
@@ -1232,16 +1232,16 @@
         <v>44531</v>
       </c>
       <c r="B41" t="n">
-        <v>144.3116760253906</v>
+        <v>144.3116912841797</v>
       </c>
       <c r="C41" t="n">
-        <v>151.2342698047112</v>
+        <v>151.2342857954605</v>
       </c>
       <c r="D41" t="n">
-        <v>141.4477479746177</v>
+        <v>141.4477629305895</v>
       </c>
       <c r="E41" t="n">
-        <v>142.3174706767361</v>
+        <v>142.317485724668</v>
       </c>
       <c r="F41" t="n">
         <v>941983</v>
@@ -1292,16 +1292,16 @@
         <v>44536</v>
       </c>
       <c r="B44" t="n">
-        <v>147.7642059326172</v>
+        <v>147.7641906738281</v>
       </c>
       <c r="C44" t="n">
-        <v>149.3279402427002</v>
+        <v>149.327924822433</v>
       </c>
       <c r="D44" t="n">
-        <v>139.2427292821338</v>
+        <v>139.2427149033103</v>
       </c>
       <c r="E44" t="n">
-        <v>144.9617791417145</v>
+        <v>144.9617641723165</v>
       </c>
       <c r="F44" t="n">
         <v>521095</v>
@@ -1312,16 +1312,16 @@
         <v>44537</v>
       </c>
       <c r="B45" t="n">
-        <v>148.0277557373047</v>
+        <v>148.0277404785156</v>
       </c>
       <c r="C45" t="n">
-        <v>153.0440137734988</v>
+        <v>153.0439979976308</v>
       </c>
       <c r="D45" t="n">
-        <v>147.8871920399053</v>
+        <v>147.8871767956056</v>
       </c>
       <c r="E45" t="n">
-        <v>150.2240132408255</v>
+        <v>150.2239977556449</v>
       </c>
       <c r="F45" t="n">
         <v>560968</v>
@@ -1332,16 +1332,16 @@
         <v>44538</v>
       </c>
       <c r="B46" t="n">
-        <v>146.3498077392578</v>
+        <v>146.3497924804688</v>
       </c>
       <c r="C46" t="n">
-        <v>150.2240090854783</v>
+        <v>150.2239934227556</v>
       </c>
       <c r="D46" t="n">
-        <v>145.9984119103712</v>
+        <v>145.9983966882195</v>
       </c>
       <c r="E46" t="n">
-        <v>148.2473773869852</v>
+        <v>148.2473619303509</v>
       </c>
       <c r="F46" t="n">
         <v>297967</v>
@@ -1352,16 +1352,16 @@
         <v>44539</v>
       </c>
       <c r="B47" t="n">
-        <v>146.6836547851562</v>
+        <v>146.6836395263672</v>
       </c>
       <c r="C47" t="n">
-        <v>148.8974862162897</v>
+        <v>148.8974707272065</v>
       </c>
       <c r="D47" t="n">
-        <v>143.7318840119426</v>
+        <v>143.7318690602119</v>
       </c>
       <c r="E47" t="n">
-        <v>146.4464552091688</v>
+        <v>146.4464399750544</v>
       </c>
       <c r="F47" t="n">
         <v>319045</v>
@@ -1392,16 +1392,16 @@
         <v>44543</v>
       </c>
       <c r="B49" t="n">
-        <v>155.4950256347656</v>
+        <v>155.4950408935547</v>
       </c>
       <c r="C49" t="n">
-        <v>159.5537050651586</v>
+        <v>159.5537207222275</v>
       </c>
       <c r="D49" t="n">
-        <v>147.1580276266661</v>
+        <v>147.1580420673422</v>
       </c>
       <c r="E49" t="n">
-        <v>148.2034483053774</v>
+        <v>148.2034628486411</v>
       </c>
       <c r="F49" t="n">
         <v>707090</v>
@@ -1412,16 +1412,16 @@
         <v>44544</v>
       </c>
       <c r="B50" t="n">
-        <v>147.2283172607422</v>
+        <v>147.2283020019531</v>
       </c>
       <c r="C50" t="n">
-        <v>150.9268208569199</v>
+        <v>150.9268052148167</v>
       </c>
       <c r="D50" t="n">
-        <v>141.1227239794226</v>
+        <v>141.1227093534192</v>
       </c>
       <c r="E50" t="n">
-        <v>150.663267271094</v>
+        <v>150.6632516563057</v>
       </c>
       <c r="F50" t="n">
         <v>995575</v>
@@ -1452,16 +1452,16 @@
         <v>44546</v>
       </c>
       <c r="B52" t="n">
-        <v>145.7260894775391</v>
+        <v>145.72607421875</v>
       </c>
       <c r="C52" t="n">
-        <v>152.8595299174546</v>
+        <v>152.8595139117323</v>
       </c>
       <c r="D52" t="n">
-        <v>144.3029054284978</v>
+        <v>144.3028903187285</v>
       </c>
       <c r="E52" t="n">
-        <v>148.1156188336976</v>
+        <v>148.115603324704</v>
       </c>
       <c r="F52" t="n">
         <v>399045</v>
@@ -1512,16 +1512,16 @@
         <v>44551</v>
       </c>
       <c r="B55" t="n">
-        <v>148.9853210449219</v>
+        <v>148.9853363037109</v>
       </c>
       <c r="C55" t="n">
-        <v>149.6441982970981</v>
+        <v>149.6442136233681</v>
       </c>
       <c r="D55" t="n">
-        <v>144.7948713726031</v>
+        <v>144.7948862022144</v>
       </c>
       <c r="E55" t="n">
-        <v>146.3146778142533</v>
+        <v>146.3146927995202</v>
       </c>
       <c r="F55" t="n">
         <v>221674</v>
@@ -1572,16 +1572,16 @@
         <v>44557</v>
       </c>
       <c r="B58" t="n">
-        <v>150.0483245849609</v>
+        <v>150.0482940673828</v>
       </c>
       <c r="C58" t="n">
-        <v>153.6941069039261</v>
+        <v>153.6940756448505</v>
       </c>
       <c r="D58" t="n">
-        <v>147.0438457432459</v>
+        <v>147.0438158367336</v>
       </c>
       <c r="E58" t="n">
-        <v>147.0438457432459</v>
+        <v>147.0438158367336</v>
       </c>
       <c r="F58" t="n">
         <v>232495</v>
@@ -1652,16 +1652,16 @@
         <v>44564</v>
       </c>
       <c r="B62" t="n">
-        <v>144.8124084472656</v>
+        <v>144.8124237060547</v>
       </c>
       <c r="C62" t="n">
-        <v>144.8124084472656</v>
+        <v>144.8124237060547</v>
       </c>
       <c r="D62" t="n">
-        <v>138.7946718899726</v>
+        <v>138.7946865146767</v>
       </c>
       <c r="E62" t="n">
-        <v>142.1768998632246</v>
+        <v>142.1769148443119</v>
       </c>
       <c r="F62" t="n">
         <v>369633</v>
@@ -1672,16 +1672,16 @@
         <v>44565</v>
       </c>
       <c r="B63" t="n">
-        <v>140.2969055175781</v>
+        <v>140.2969360351562</v>
       </c>
       <c r="C63" t="n">
-        <v>146.499133628787</v>
+        <v>146.4991654954824</v>
       </c>
       <c r="D63" t="n">
-        <v>138.6628896448183</v>
+        <v>138.662919806963</v>
       </c>
       <c r="E63" t="n">
-        <v>144.8124097286623</v>
+        <v>144.8124412284592</v>
       </c>
       <c r="F63" t="n">
         <v>382138</v>
@@ -1732,16 +1732,16 @@
         <v>44568</v>
       </c>
       <c r="B66" t="n">
-        <v>137.2397308349609</v>
+        <v>137.23974609375</v>
       </c>
       <c r="C66" t="n">
-        <v>142.1857066938723</v>
+        <v>142.1857225025721</v>
       </c>
       <c r="D66" t="n">
-        <v>134.2001047538714</v>
+        <v>134.2001196747043</v>
       </c>
       <c r="E66" t="n">
-        <v>137.9249620581452</v>
+        <v>137.9249773931206</v>
       </c>
       <c r="F66" t="n">
         <v>686988</v>
@@ -1752,16 +1752,16 @@
         <v>44571</v>
       </c>
       <c r="B67" t="n">
-        <v>137.5208435058594</v>
+        <v>137.5208587646484</v>
       </c>
       <c r="C67" t="n">
-        <v>138.4696282839642</v>
+        <v>138.4696436480268</v>
       </c>
       <c r="D67" t="n">
-        <v>131.9072102890741</v>
+        <v>131.9072249249958</v>
       </c>
       <c r="E67" t="n">
-        <v>137.2309493336996</v>
+        <v>137.2309645603231</v>
       </c>
       <c r="F67" t="n">
         <v>730000</v>
@@ -1772,16 +1772,16 @@
         <v>44572</v>
       </c>
       <c r="B68" t="n">
-        <v>146.3849639892578</v>
+        <v>146.3849487304688</v>
       </c>
       <c r="C68" t="n">
-        <v>149.0116794664315</v>
+        <v>149.0116639338405</v>
       </c>
       <c r="D68" t="n">
-        <v>133.6290962567753</v>
+        <v>133.6290823276248</v>
       </c>
       <c r="E68" t="n">
-        <v>137.5735796821382</v>
+        <v>137.573565341825</v>
       </c>
       <c r="F68" t="n">
         <v>715197</v>
@@ -1872,16 +1872,16 @@
         <v>44579</v>
       </c>
       <c r="B73" t="n">
-        <v>133.1722564697266</v>
+        <v>133.1722717285156</v>
       </c>
       <c r="C73" t="n">
-        <v>138.8034634905354</v>
+        <v>138.8034793945444</v>
       </c>
       <c r="D73" t="n">
-        <v>133.1722564697266</v>
+        <v>133.1722717285156</v>
       </c>
       <c r="E73" t="n">
-        <v>138.1885141180745</v>
+        <v>138.1885299516231</v>
       </c>
       <c r="F73" t="n">
         <v>435258</v>
@@ -1892,16 +1892,16 @@
         <v>44580</v>
       </c>
       <c r="B74" t="n">
-        <v>139.6116943359375</v>
+        <v>139.6116790771484</v>
       </c>
       <c r="C74" t="n">
-        <v>141.6937421442108</v>
+        <v>141.6937266578653</v>
       </c>
       <c r="D74" t="n">
-        <v>133.0492758918774</v>
+        <v>133.0492613503245</v>
       </c>
       <c r="E74" t="n">
-        <v>133.5324552200335</v>
+        <v>133.5324406256718</v>
       </c>
       <c r="F74" t="n">
         <v>381153</v>
@@ -1972,16 +1972,16 @@
         <v>44586</v>
       </c>
       <c r="B78" t="n">
-        <v>147.316162109375</v>
+        <v>147.3161773681641</v>
       </c>
       <c r="C78" t="n">
-        <v>149.5211996922916</v>
+        <v>149.5212151794752</v>
       </c>
       <c r="D78" t="n">
-        <v>140.165148619023</v>
+        <v>140.1651631371207</v>
       </c>
       <c r="E78" t="n">
-        <v>140.165148619023</v>
+        <v>140.1651631371207</v>
       </c>
       <c r="F78" t="n">
         <v>456302</v>
@@ -2012,16 +2012,16 @@
         <v>44588</v>
       </c>
       <c r="B80" t="n">
-        <v>149.4860534667969</v>
+        <v>149.486083984375</v>
       </c>
       <c r="C80" t="n">
-        <v>156.5667845437585</v>
+        <v>156.5668165068679</v>
       </c>
       <c r="D80" t="n">
-        <v>147.3249304811154</v>
+        <v>147.3249605575002</v>
       </c>
       <c r="E80" t="n">
-        <v>151.5417469914199</v>
+        <v>151.5417779286678</v>
       </c>
       <c r="F80" t="n">
         <v>697237</v>
@@ -2052,16 +2052,16 @@
         <v>44592</v>
       </c>
       <c r="B82" t="n">
-        <v>155.0557708740234</v>
+        <v>155.0558013916016</v>
       </c>
       <c r="C82" t="n">
-        <v>155.31932444034</v>
+        <v>155.3193550097899</v>
       </c>
       <c r="D82" t="n">
-        <v>145.8666241070765</v>
+        <v>145.8666528160763</v>
       </c>
       <c r="E82" t="n">
-        <v>147.0174742331623</v>
+        <v>147.0175031686687</v>
       </c>
       <c r="F82" t="n">
         <v>286473</v>
@@ -2092,16 +2092,16 @@
         <v>44594</v>
       </c>
       <c r="B84" t="n">
-        <v>148.9940948486328</v>
+        <v>148.9941253662109</v>
       </c>
       <c r="C84" t="n">
-        <v>158.1305195023691</v>
+        <v>158.1305518913071</v>
       </c>
       <c r="D84" t="n">
-        <v>148.9062391980643</v>
+        <v>148.9062696976475</v>
       </c>
       <c r="E84" t="n">
-        <v>155.8024922160959</v>
+        <v>155.8025241281978</v>
       </c>
       <c r="F84" t="n">
         <v>466282</v>
@@ -2112,16 +2112,16 @@
         <v>44595</v>
       </c>
       <c r="B85" t="n">
-        <v>146.270751953125</v>
+        <v>146.2707366943359</v>
       </c>
       <c r="C85" t="n">
-        <v>149.9604619340272</v>
+        <v>149.960446290332</v>
       </c>
       <c r="D85" t="n">
-        <v>145.5415928423091</v>
+        <v>145.5415776595851</v>
       </c>
       <c r="E85" t="n">
-        <v>149.2137424144391</v>
+        <v>149.2137268486408</v>
       </c>
       <c r="F85" t="n">
         <v>228387</v>
@@ -2132,16 +2132,16 @@
         <v>44596</v>
       </c>
       <c r="B86" t="n">
-        <v>149.6002502441406</v>
+        <v>149.6002807617188</v>
       </c>
       <c r="C86" t="n">
-        <v>151.0058602207404</v>
+        <v>151.0058910250547</v>
       </c>
       <c r="D86" t="n">
-        <v>143.5825135306316</v>
+        <v>143.5825428206266</v>
       </c>
       <c r="E86" t="n">
-        <v>149.3454903058881</v>
+        <v>149.3455207714968</v>
       </c>
       <c r="F86" t="n">
         <v>455710</v>
@@ -2192,16 +2192,16 @@
         <v>44601</v>
       </c>
       <c r="B89" t="n">
-        <v>157.5155944824219</v>
+        <v>157.5156097412109</v>
       </c>
       <c r="C89" t="n">
-        <v>159.7996942960607</v>
+        <v>159.7997097761142</v>
       </c>
       <c r="D89" t="n">
-        <v>151.4275615710859</v>
+        <v>151.4275762401174</v>
       </c>
       <c r="E89" t="n">
-        <v>153.7380288078784</v>
+        <v>153.7380437007286</v>
       </c>
       <c r="F89" t="n">
         <v>1361639</v>
@@ -2232,16 +2232,16 @@
         <v>44603</v>
       </c>
       <c r="B91" t="n">
-        <v>156.0045471191406</v>
+        <v>156.0045623779297</v>
       </c>
       <c r="C91" t="n">
-        <v>160.1510818935806</v>
+        <v>160.1510975579418</v>
       </c>
       <c r="D91" t="n">
-        <v>151.3309052409586</v>
+        <v>151.3309200426192</v>
       </c>
       <c r="E91" t="n">
-        <v>152.376325840283</v>
+        <v>152.3763407441961</v>
       </c>
       <c r="F91" t="n">
         <v>740597</v>
@@ -2252,16 +2252,16 @@
         <v>44606</v>
       </c>
       <c r="B92" t="n">
-        <v>152.9473724365234</v>
+        <v>152.9473876953125</v>
       </c>
       <c r="C92" t="n">
-        <v>157.9196890589268</v>
+        <v>157.9197048137788</v>
       </c>
       <c r="D92" t="n">
-        <v>152.0688694665374</v>
+        <v>152.0688846376827</v>
       </c>
       <c r="E92" t="n">
-        <v>156.0045590187052</v>
+        <v>156.0045745824943</v>
       </c>
       <c r="F92" t="n">
         <v>409040</v>
@@ -2272,16 +2272,16 @@
         <v>44607</v>
       </c>
       <c r="B93" t="n">
-        <v>161.1437835693359</v>
+        <v>161.143798828125</v>
       </c>
       <c r="C93" t="n">
-        <v>161.8202345685366</v>
+        <v>161.8202498913792</v>
       </c>
       <c r="D93" t="n">
-        <v>154.6252935362757</v>
+        <v>154.6253081778255</v>
       </c>
       <c r="E93" t="n">
-        <v>156.2768833091691</v>
+        <v>156.2768981071088</v>
       </c>
       <c r="F93" t="n">
         <v>501987</v>
@@ -2292,16 +2292,16 @@
         <v>44608</v>
       </c>
       <c r="B94" t="n">
-        <v>160.8099822998047</v>
+        <v>160.8099975585938</v>
       </c>
       <c r="C94" t="n">
-        <v>164.6841838787326</v>
+        <v>164.6841995051333</v>
       </c>
       <c r="D94" t="n">
-        <v>158.0690437312643</v>
+        <v>158.0690587299737</v>
       </c>
       <c r="E94" t="n">
-        <v>161.1438043358308</v>
+        <v>161.1438196262952</v>
       </c>
       <c r="F94" t="n">
         <v>383335</v>
@@ -2312,16 +2312,16 @@
         <v>44609</v>
       </c>
       <c r="B95" t="n">
-        <v>156.6282806396484</v>
+        <v>156.6282958984375</v>
       </c>
       <c r="C95" t="n">
-        <v>161.1877129663323</v>
+        <v>161.1877286693031</v>
       </c>
       <c r="D95" t="n">
-        <v>156.1626751616721</v>
+        <v>156.1626903751017</v>
       </c>
       <c r="E95" t="n">
-        <v>160.8011695344521</v>
+        <v>160.8011851997657</v>
       </c>
       <c r="F95" t="n">
         <v>315564</v>
@@ -2332,16 +2332,16 @@
         <v>44610</v>
       </c>
       <c r="B96" t="n">
-        <v>155.4950256347656</v>
+        <v>155.4950408935547</v>
       </c>
       <c r="C96" t="n">
-        <v>159.5361446572868</v>
+        <v>159.5361603126324</v>
       </c>
       <c r="D96" t="n">
-        <v>153.4744661235051</v>
+        <v>153.4744811840158</v>
       </c>
       <c r="E96" t="n">
-        <v>156.9884780022568</v>
+        <v>156.988493407599</v>
       </c>
       <c r="F96" t="n">
         <v>742998</v>
@@ -2352,16 +2352,16 @@
         <v>44613</v>
       </c>
       <c r="B97" t="n">
-        <v>150.3118591308594</v>
+        <v>150.3118743896484</v>
       </c>
       <c r="C97" t="n">
-        <v>155.6882928603806</v>
+        <v>155.6883086649541</v>
       </c>
       <c r="D97" t="n">
-        <v>149.5827000785075</v>
+        <v>149.5827152632765</v>
       </c>
       <c r="E97" t="n">
-        <v>154.6165181959493</v>
+        <v>154.6165338917224</v>
       </c>
       <c r="F97" t="n">
         <v>185476</v>
@@ -2372,16 +2372,16 @@
         <v>44614</v>
       </c>
       <c r="B98" t="n">
-        <v>150.3557739257812</v>
+        <v>150.3557891845703</v>
       </c>
       <c r="C98" t="n">
-        <v>155.0557700513334</v>
+        <v>155.0557857870995</v>
       </c>
       <c r="D98" t="n">
-        <v>149.6793363085237</v>
+        <v>149.6793514986648</v>
       </c>
       <c r="E98" t="n">
-        <v>150.5314852389875</v>
+        <v>150.5315005156085</v>
       </c>
       <c r="F98" t="n">
         <v>352471</v>
@@ -2412,16 +2412,16 @@
         <v>44616</v>
       </c>
       <c r="B100" t="n">
-        <v>148.1067962646484</v>
+        <v>148.1068115234375</v>
       </c>
       <c r="C100" t="n">
-        <v>148.1067962646484</v>
+        <v>148.1068115234375</v>
       </c>
       <c r="D100" t="n">
-        <v>139.2427054859054</v>
+        <v>139.2427198314664</v>
       </c>
       <c r="E100" t="n">
-        <v>143.3277384867851</v>
+        <v>143.327753253209</v>
       </c>
       <c r="F100" t="n">
         <v>704723</v>
@@ -2452,16 +2452,16 @@
         <v>44622</v>
       </c>
       <c r="B102" t="n">
-        <v>141.6410217285156</v>
+        <v>141.6410369873047</v>
       </c>
       <c r="C102" t="n">
-        <v>145.8314844011221</v>
+        <v>145.8315001113438</v>
       </c>
       <c r="D102" t="n">
-        <v>141.6410217285156</v>
+        <v>141.6410369873047</v>
       </c>
       <c r="E102" t="n">
-        <v>144.952981483043</v>
+        <v>144.9529970986249</v>
       </c>
       <c r="F102" t="n">
         <v>220670</v>
@@ -2472,16 +2472,16 @@
         <v>44623</v>
       </c>
       <c r="B103" t="n">
-        <v>136.1679534912109</v>
+        <v>136.16796875</v>
       </c>
       <c r="C103" t="n">
-        <v>143.3365405825027</v>
+        <v>143.3365566445935</v>
       </c>
       <c r="D103" t="n">
-        <v>135.4915024850142</v>
+        <v>135.4915176680011</v>
       </c>
       <c r="E103" t="n">
-        <v>142.5107456875154</v>
+        <v>142.5107616570688</v>
       </c>
       <c r="F103" t="n">
         <v>801826</v>
@@ -2492,16 +2492,16 @@
         <v>44624</v>
       </c>
       <c r="B104" t="n">
-        <v>129.4034729003906</v>
+        <v>129.4034881591797</v>
       </c>
       <c r="C104" t="n">
-        <v>139.2163481577294</v>
+        <v>139.2163645736173</v>
       </c>
       <c r="D104" t="n">
-        <v>128.5864582767315</v>
+        <v>128.5864734391812</v>
       </c>
       <c r="E104" t="n">
-        <v>134.2440187936321</v>
+        <v>134.2440346232008</v>
       </c>
       <c r="F104" t="n">
         <v>615045</v>
@@ -2512,16 +2512,16 @@
         <v>44627</v>
       </c>
       <c r="B105" t="n">
-        <v>117.0781097412109</v>
+        <v>117.0781021118164</v>
       </c>
       <c r="C105" t="n">
-        <v>130.2644362043928</v>
+        <v>130.2644277157113</v>
       </c>
       <c r="D105" t="n">
-        <v>117.0781097412109</v>
+        <v>117.0781021118164</v>
       </c>
       <c r="E105" t="n">
-        <v>129.5792048713628</v>
+        <v>129.5791964273345</v>
       </c>
       <c r="F105" t="n">
         <v>1053703</v>
@@ -2532,16 +2532,16 @@
         <v>44628</v>
       </c>
       <c r="B106" t="n">
-        <v>124.4399566650391</v>
+        <v>124.43994140625</v>
       </c>
       <c r="C106" t="n">
-        <v>125.6083673770213</v>
+        <v>125.6083519749621</v>
       </c>
       <c r="D106" t="n">
-        <v>115.8657713786687</v>
+        <v>115.8657571712436</v>
       </c>
       <c r="E106" t="n">
-        <v>118.3431565134491</v>
+        <v>118.3431420022477</v>
       </c>
       <c r="F106" t="n">
         <v>713320</v>
@@ -2572,16 +2572,16 @@
         <v>44630</v>
       </c>
       <c r="B108" t="n">
-        <v>135.7814025878906</v>
+        <v>135.7814331054688</v>
       </c>
       <c r="C108" t="n">
-        <v>139.1636440278797</v>
+        <v>139.1636753056343</v>
       </c>
       <c r="D108" t="n">
-        <v>133.2425298083679</v>
+        <v>133.2425597553211</v>
       </c>
       <c r="E108" t="n">
-        <v>137.4857003148507</v>
+        <v>137.4857312154787</v>
       </c>
       <c r="F108" t="n">
         <v>543810</v>
@@ -2592,16 +2592,16 @@
         <v>44631</v>
       </c>
       <c r="B109" t="n">
-        <v>131.6173095703125</v>
+        <v>131.6173400878906</v>
       </c>
       <c r="C109" t="n">
-        <v>138.7156011336312</v>
+        <v>138.7156332970618</v>
       </c>
       <c r="D109" t="n">
-        <v>131.1341302992611</v>
+        <v>131.1341607048064</v>
       </c>
       <c r="E109" t="n">
-        <v>135.8077587090635</v>
+        <v>135.8077901982643</v>
       </c>
       <c r="F109" t="n">
         <v>422012</v>
@@ -2612,16 +2612,16 @@
         <v>44634</v>
       </c>
       <c r="B110" t="n">
-        <v>126.6801223754883</v>
+        <v>126.6801376342773</v>
       </c>
       <c r="C110" t="n">
-        <v>133.8311358334649</v>
+        <v>133.831151953603</v>
       </c>
       <c r="D110" t="n">
-        <v>126.6801223754883</v>
+        <v>126.6801376342773</v>
       </c>
       <c r="E110" t="n">
-        <v>131.6173180568153</v>
+        <v>131.6173339102961</v>
       </c>
       <c r="F110" t="n">
         <v>265850</v>
@@ -2632,16 +2632,16 @@
         <v>44635</v>
       </c>
       <c r="B111" t="n">
-        <v>131.4855346679688</v>
+        <v>131.4855499267578</v>
       </c>
       <c r="C111" t="n">
-        <v>132.1971199113335</v>
+        <v>132.1971352527014</v>
       </c>
       <c r="D111" t="n">
-        <v>124.3520950170941</v>
+        <v>124.3521094480533</v>
       </c>
       <c r="E111" t="n">
-        <v>126.9876038620842</v>
+        <v>126.987618598892</v>
       </c>
       <c r="F111" t="n">
         <v>302237</v>
@@ -2652,16 +2652,16 @@
         <v>44636</v>
       </c>
       <c r="B112" t="n">
-        <v>139.4886932373047</v>
+        <v>139.4887084960938</v>
       </c>
       <c r="C112" t="n">
-        <v>142.3438277410615</v>
+        <v>142.3438433121762</v>
       </c>
       <c r="D112" t="n">
-        <v>132.6539415591642</v>
+        <v>132.6539560702938</v>
       </c>
       <c r="E112" t="n">
-        <v>132.6539415591642</v>
+        <v>132.6539560702938</v>
       </c>
       <c r="F112" t="n">
         <v>861619</v>
@@ -2692,16 +2692,16 @@
         <v>44638</v>
       </c>
       <c r="B114" t="n">
-        <v>142.3174743652344</v>
+        <v>142.3174896240234</v>
       </c>
       <c r="C114" t="n">
-        <v>145.1199008509126</v>
+        <v>145.1199164101681</v>
       </c>
       <c r="D114" t="n">
-        <v>137.1518728579682</v>
+        <v>137.1518875629193</v>
       </c>
       <c r="E114" t="n">
-        <v>138.6189711394427</v>
+        <v>138.618986001691</v>
       </c>
       <c r="F114" t="n">
         <v>570545</v>
@@ -2712,16 +2712,16 @@
         <v>44641</v>
       </c>
       <c r="B115" t="n">
-        <v>139.7698211669922</v>
+        <v>139.7698364257812</v>
       </c>
       <c r="C115" t="n">
-        <v>143.0642071460549</v>
+        <v>143.0642227644949</v>
       </c>
       <c r="D115" t="n">
-        <v>138.4169191515182</v>
+        <v>138.4169342626098</v>
       </c>
       <c r="E115" t="n">
-        <v>141.4828991951266</v>
+        <v>141.4829146409339</v>
       </c>
       <c r="F115" t="n">
         <v>351500</v>
@@ -2732,16 +2732,16 @@
         <v>44642</v>
       </c>
       <c r="B116" t="n">
-        <v>143.4683227539062</v>
+        <v>143.4683380126953</v>
       </c>
       <c r="C116" t="n">
-        <v>146.832990851759</v>
+        <v>146.8330064684024</v>
       </c>
       <c r="D116" t="n">
-        <v>139.7698326314529</v>
+        <v>139.7698474968835</v>
       </c>
       <c r="E116" t="n">
-        <v>139.7698326314529</v>
+        <v>139.7698474968835</v>
       </c>
       <c r="F116" t="n">
         <v>384464</v>
@@ -2752,16 +2752,16 @@
         <v>44643</v>
       </c>
       <c r="B117" t="n">
-        <v>132.7418212890625</v>
+        <v>132.7418060302734</v>
       </c>
       <c r="C117" t="n">
-        <v>137.4418047432147</v>
+        <v>137.4417889441584</v>
       </c>
       <c r="D117" t="n">
-        <v>130.5719176002584</v>
+        <v>130.5719025909017</v>
       </c>
       <c r="E117" t="n">
-        <v>134.5076076612723</v>
+        <v>134.5075921995046</v>
       </c>
       <c r="F117" t="n">
         <v>1133860</v>
@@ -2772,16 +2772,16 @@
         <v>44644</v>
       </c>
       <c r="B118" t="n">
-        <v>136.2733612060547</v>
+        <v>136.2734069824219</v>
       </c>
       <c r="C118" t="n">
-        <v>137.2660737409138</v>
+        <v>137.2661198507487</v>
       </c>
       <c r="D118" t="n">
-        <v>132.4870159727677</v>
+        <v>132.487060477242</v>
       </c>
       <c r="E118" t="n">
-        <v>133.2776766004494</v>
+        <v>133.277721370519</v>
       </c>
       <c r="F118" t="n">
         <v>438667</v>
@@ -2792,16 +2792,16 @@
         <v>44645</v>
       </c>
       <c r="B119" t="n">
-        <v>133.9277801513672</v>
+        <v>133.9277648925781</v>
       </c>
       <c r="C119" t="n">
-        <v>140.0333733423783</v>
+        <v>140.0333573879609</v>
       </c>
       <c r="D119" t="n">
-        <v>133.418246800945</v>
+        <v>133.4182316002086</v>
       </c>
       <c r="E119" t="n">
-        <v>135.3070363006828</v>
+        <v>135.307020884751</v>
       </c>
       <c r="F119" t="n">
         <v>403765</v>
@@ -2872,16 +2872,16 @@
         <v>44651</v>
       </c>
       <c r="B123" t="n">
-        <v>126.065185546875</v>
+        <v>126.0651702880859</v>
       </c>
       <c r="C123" t="n">
-        <v>132.170778960327</v>
+        <v>132.1707629625238</v>
       </c>
       <c r="D123" t="n">
-        <v>123.4736042741024</v>
+        <v>123.4735893289954</v>
       </c>
       <c r="E123" t="n">
-        <v>131.6788194054147</v>
+        <v>131.6788034671577</v>
       </c>
       <c r="F123" t="n">
         <v>791956</v>
@@ -2892,16 +2892,16 @@
         <v>44652</v>
       </c>
       <c r="B124" t="n">
-        <v>127.382942199707</v>
+        <v>127.382926940918</v>
       </c>
       <c r="C124" t="n">
-        <v>129.10481407518</v>
+        <v>129.1047986101335</v>
       </c>
       <c r="D124" t="n">
-        <v>124.6156629552567</v>
+        <v>124.615648027951</v>
       </c>
       <c r="E124" t="n">
-        <v>126.5044391500539</v>
+        <v>126.5044239964978</v>
       </c>
       <c r="F124" t="n">
         <v>526406</v>
@@ -2912,16 +2912,16 @@
         <v>44655</v>
       </c>
       <c r="B125" t="n">
-        <v>129.0872344970703</v>
+        <v>129.0872192382812</v>
       </c>
       <c r="C125" t="n">
-        <v>129.0872344970703</v>
+        <v>129.0872192382812</v>
       </c>
       <c r="D125" t="n">
-        <v>125.6347106955444</v>
+        <v>125.6346958448618</v>
       </c>
       <c r="E125" t="n">
-        <v>127.3829365120573</v>
+        <v>127.3829214547252</v>
       </c>
       <c r="F125" t="n">
         <v>325077</v>
@@ -2952,16 +2952,16 @@
         <v>44657</v>
       </c>
       <c r="B127" t="n">
-        <v>125.0197601318359</v>
+        <v>125.019775390625</v>
       </c>
       <c r="C127" t="n">
-        <v>127.3829353531706</v>
+        <v>127.3829509003876</v>
       </c>
       <c r="D127" t="n">
-        <v>122.6917325373382</v>
+        <v>122.6917475119892</v>
       </c>
       <c r="E127" t="n">
-        <v>127.1720898068249</v>
+        <v>127.172105328308</v>
       </c>
       <c r="F127" t="n">
         <v>694358</v>
@@ -2972,16 +2972,16 @@
         <v>44658</v>
       </c>
       <c r="B128" t="n">
-        <v>126.9524612426758</v>
+        <v>126.9524536132812</v>
       </c>
       <c r="C128" t="n">
-        <v>128.6040511402175</v>
+        <v>128.6040434115682</v>
       </c>
       <c r="D128" t="n">
-        <v>122.9991978193282</v>
+        <v>122.9991904275108</v>
       </c>
       <c r="E128" t="n">
-        <v>124.7562037852604</v>
+        <v>124.7561962878532</v>
       </c>
       <c r="F128" t="n">
         <v>544395</v>
@@ -3012,16 +3012,16 @@
         <v>44662</v>
       </c>
       <c r="B130" t="n">
-        <v>121.8659439086914</v>
+        <v>121.8659210205078</v>
       </c>
       <c r="C130" t="n">
-        <v>123.5702419668423</v>
+        <v>123.570218758567</v>
       </c>
       <c r="D130" t="n">
-        <v>119.3622048595699</v>
+        <v>119.3621824416246</v>
       </c>
       <c r="E130" t="n">
-        <v>122.9904267379037</v>
+        <v>122.990403638526</v>
       </c>
       <c r="F130" t="n">
         <v>348006</v>
@@ -3032,16 +3032,16 @@
         <v>44663</v>
       </c>
       <c r="B131" t="n">
-        <v>118.2025756835938</v>
+        <v>118.2025833129883</v>
       </c>
       <c r="C131" t="n">
-        <v>125.1690977064049</v>
+        <v>125.1691057854541</v>
       </c>
       <c r="D131" t="n">
-        <v>118.1762216672442</v>
+        <v>118.1762292949377</v>
       </c>
       <c r="E131" t="n">
-        <v>122.990414123866</v>
+        <v>122.9904220622919</v>
       </c>
       <c r="F131" t="n">
         <v>576598</v>
@@ -3052,16 +3052,16 @@
         <v>44664</v>
       </c>
       <c r="B132" t="n">
-        <v>119.7751007080078</v>
+        <v>119.7750930786133</v>
       </c>
       <c r="C132" t="n">
-        <v>120.794167446916</v>
+        <v>120.7941597526093</v>
       </c>
       <c r="D132" t="n">
-        <v>117.7545410442809</v>
+        <v>117.7545335435913</v>
       </c>
       <c r="E132" t="n">
-        <v>118.8351094300559</v>
+        <v>118.8351018605366</v>
       </c>
       <c r="F132" t="n">
         <v>714435</v>
@@ -3072,16 +3072,16 @@
         <v>44665</v>
       </c>
       <c r="B133" t="n">
-        <v>115.6022109985352</v>
+        <v>115.6022033691406</v>
       </c>
       <c r="C133" t="n">
-        <v>120.003519776927</v>
+        <v>120.0035118570594</v>
       </c>
       <c r="D133" t="n">
-        <v>114.7061475555975</v>
+        <v>114.7061399853404</v>
       </c>
       <c r="E133" t="n">
-        <v>119.7751004090118</v>
+        <v>119.7750925042192</v>
       </c>
       <c r="F133" t="n">
         <v>497156</v>
@@ -3192,16 +3192,16 @@
         <v>44677</v>
       </c>
       <c r="B139" t="n">
-        <v>107.4057693481445</v>
+        <v>107.4057769775391</v>
       </c>
       <c r="C139" t="n">
-        <v>112.6943540007223</v>
+        <v>112.6943620057829</v>
       </c>
       <c r="D139" t="n">
-        <v>106.342781614564</v>
+        <v>106.342789168451</v>
       </c>
       <c r="E139" t="n">
-        <v>109.9270684500656</v>
+        <v>109.9270762585565</v>
       </c>
       <c r="F139" t="n">
         <v>615417</v>
@@ -3212,16 +3212,16 @@
         <v>44678</v>
       </c>
       <c r="B140" t="n">
-        <v>104.5418548583984</v>
+        <v>104.541862487793</v>
       </c>
       <c r="C140" t="n">
-        <v>110.471749986921</v>
+        <v>110.4717580490753</v>
       </c>
       <c r="D140" t="n">
-        <v>104.0938164608919</v>
+        <v>104.0938240575889</v>
       </c>
       <c r="E140" t="n">
-        <v>109.5493191748392</v>
+        <v>109.5493271696751</v>
       </c>
       <c r="F140" t="n">
         <v>1036983</v>
@@ -3292,16 +3292,16 @@
         <v>44684</v>
       </c>
       <c r="B144" t="n">
-        <v>102.7848510742188</v>
+        <v>102.7848434448242</v>
       </c>
       <c r="C144" t="n">
-        <v>107.1773660773905</v>
+        <v>107.1773581219535</v>
       </c>
       <c r="D144" t="n">
-        <v>101.8097122073189</v>
+        <v>101.8097046503059</v>
       </c>
       <c r="E144" t="n">
-        <v>107.1422251530716</v>
+        <v>107.142217200243</v>
       </c>
       <c r="F144" t="n">
         <v>541792</v>
@@ -3312,16 +3312,16 @@
         <v>44685</v>
       </c>
       <c r="B145" t="n">
-        <v>94.52691650390625</v>
+        <v>94.52693176269531</v>
       </c>
       <c r="C145" t="n">
-        <v>100.4128903167997</v>
+        <v>100.4129065257185</v>
       </c>
       <c r="D145" t="n">
-        <v>84.54712241090455</v>
+        <v>84.54713605872841</v>
       </c>
       <c r="E145" t="n">
-        <v>100.4128903167997</v>
+        <v>100.4129065257185</v>
       </c>
       <c r="F145" t="n">
         <v>3193940</v>
@@ -3372,16 +3372,16 @@
         <v>44690</v>
       </c>
       <c r="B148" t="n">
-        <v>85.64524841308594</v>
+        <v>85.64525604248047</v>
       </c>
       <c r="C148" t="n">
-        <v>90.7405680668887</v>
+        <v>90.7405761501812</v>
       </c>
       <c r="D148" t="n">
-        <v>83.37871595696386</v>
+        <v>83.37872338445261</v>
       </c>
       <c r="E148" t="n">
-        <v>88.64094660911006</v>
+        <v>88.64095450536544</v>
       </c>
       <c r="F148" t="n">
         <v>1267170</v>
@@ -3392,16 +3392,16 @@
         <v>44691</v>
       </c>
       <c r="B149" t="n">
-        <v>84.51197814941406</v>
+        <v>84.51199340820312</v>
       </c>
       <c r="C149" t="n">
-        <v>89.03626952396259</v>
+        <v>89.03628559962057</v>
       </c>
       <c r="D149" t="n">
-        <v>83.46656423318744</v>
+        <v>83.46657930322515</v>
       </c>
       <c r="E149" t="n">
-        <v>85.83851943414338</v>
+        <v>85.83853493244185</v>
       </c>
       <c r="F149" t="n">
         <v>595901</v>
@@ -3452,16 +3452,16 @@
         <v>44694</v>
       </c>
       <c r="B152" t="n">
-        <v>89.78300476074219</v>
+        <v>89.78299713134766</v>
       </c>
       <c r="C152" t="n">
-        <v>92.42730069221749</v>
+        <v>92.42729283812145</v>
       </c>
       <c r="D152" t="n">
-        <v>87.90300885931281</v>
+        <v>87.90300138967268</v>
       </c>
       <c r="E152" t="n">
-        <v>90.57365880864381</v>
+        <v>90.57365111206272</v>
       </c>
       <c r="F152" t="n">
         <v>780406</v>
@@ -3492,16 +3492,16 @@
         <v>44698</v>
       </c>
       <c r="B154" t="n">
-        <v>86.98057556152344</v>
+        <v>86.98058319091797</v>
       </c>
       <c r="C154" t="n">
-        <v>88.24561520248869</v>
+        <v>88.24562294284463</v>
       </c>
       <c r="D154" t="n">
-        <v>84.59104655839022</v>
+        <v>84.59105397819015</v>
       </c>
       <c r="E154" t="n">
-        <v>85.39048072641835</v>
+        <v>85.39048821633966</v>
       </c>
       <c r="F154" t="n">
         <v>1257850</v>
@@ -3532,16 +3532,16 @@
         <v>44700</v>
       </c>
       <c r="B156" t="n">
-        <v>89.6072998046875</v>
+        <v>89.60730743408203</v>
       </c>
       <c r="C156" t="n">
-        <v>90.45066182208521</v>
+        <v>90.45066952328574</v>
       </c>
       <c r="D156" t="n">
-        <v>82.86039696306027</v>
+        <v>82.86040401800625</v>
       </c>
       <c r="E156" t="n">
-        <v>83.85310287154553</v>
+        <v>83.85311001101303</v>
       </c>
       <c r="F156" t="n">
         <v>889253</v>
@@ -3592,16 +3592,16 @@
         <v>44705</v>
       </c>
       <c r="B159" t="n">
-        <v>87.67459869384766</v>
+        <v>87.67460632324219</v>
       </c>
       <c r="C159" t="n">
-        <v>90.02020000464306</v>
+        <v>90.02020783815051</v>
       </c>
       <c r="D159" t="n">
-        <v>85.55740332846713</v>
+        <v>85.55741077362453</v>
       </c>
       <c r="E159" t="n">
-        <v>88.43011178085561</v>
+        <v>88.43011947599447</v>
       </c>
       <c r="F159" t="n">
         <v>569845</v>
@@ -3612,16 +3612,16 @@
         <v>44706</v>
       </c>
       <c r="B160" t="n">
-        <v>89.92357635498047</v>
+        <v>89.92356872558594</v>
       </c>
       <c r="C160" t="n">
-        <v>90.73179758493647</v>
+        <v>90.73178988696996</v>
       </c>
       <c r="D160" t="n">
-        <v>85.75068669945851</v>
+        <v>85.75067942410486</v>
       </c>
       <c r="E160" t="n">
-        <v>86.97180545193132</v>
+        <v>86.97179807297417</v>
       </c>
       <c r="F160" t="n">
         <v>958832</v>
@@ -3632,16 +3632,16 @@
         <v>44707</v>
       </c>
       <c r="B161" t="n">
-        <v>94.81682586669922</v>
+        <v>94.81683349609375</v>
       </c>
       <c r="C161" t="n">
-        <v>96.26635710839928</v>
+        <v>96.2663648544297</v>
       </c>
       <c r="D161" t="n">
-        <v>89.00992069595566</v>
+        <v>89.0099278581001</v>
       </c>
       <c r="E161" t="n">
-        <v>89.41403125806036</v>
+        <v>89.41403845272137</v>
       </c>
       <c r="F161" t="n">
         <v>700096</v>
@@ -3672,16 +3672,16 @@
         <v>44711</v>
       </c>
       <c r="B163" t="n">
-        <v>96.5474853515625</v>
+        <v>96.54747772216797</v>
       </c>
       <c r="C163" t="n">
-        <v>99.64860000764324</v>
+        <v>99.64859213319181</v>
       </c>
       <c r="D163" t="n">
-        <v>94.96617719997496</v>
+        <v>94.96616969553888</v>
       </c>
       <c r="E163" t="n">
-        <v>94.96617719997496</v>
+        <v>94.96616969553888</v>
       </c>
       <c r="F163" t="n">
         <v>123810</v>
@@ -3692,16 +3692,16 @@
         <v>44712</v>
       </c>
       <c r="B164" t="n">
-        <v>93.95588684082031</v>
+        <v>93.95589447021484</v>
       </c>
       <c r="C164" t="n">
-        <v>98.17270363778388</v>
+        <v>98.17271160959186</v>
       </c>
       <c r="D164" t="n">
-        <v>93.12131172800976</v>
+        <v>93.12131928963522</v>
       </c>
       <c r="E164" t="n">
-        <v>96.72317244492481</v>
+        <v>96.72318029902813</v>
       </c>
       <c r="F164" t="n">
         <v>435642</v>
@@ -3772,16 +3772,16 @@
         <v>44718</v>
       </c>
       <c r="B168" t="n">
-        <v>94.98374176025391</v>
+        <v>94.98374938964844</v>
       </c>
       <c r="C168" t="n">
-        <v>97.48747383763394</v>
+        <v>97.48748166813617</v>
       </c>
       <c r="D168" t="n">
-        <v>94.69383417696631</v>
+        <v>94.69384178307456</v>
       </c>
       <c r="E168" t="n">
-        <v>95.18579368622116</v>
+        <v>95.18580133184516</v>
       </c>
       <c r="F168" t="n">
         <v>540320</v>
@@ -3792,16 +3792,16 @@
         <v>44719</v>
       </c>
       <c r="B169" t="n">
-        <v>100.5710220336914</v>
+        <v>100.5710296630859</v>
       </c>
       <c r="C169" t="n">
-        <v>101.2035385362447</v>
+        <v>101.2035462136224</v>
       </c>
       <c r="D169" t="n">
-        <v>93.36729372419249</v>
+        <v>93.36730080710669</v>
       </c>
       <c r="E169" t="n">
-        <v>94.36000636076696</v>
+        <v>94.36001351898909</v>
       </c>
       <c r="F169" t="n">
         <v>669503</v>
@@ -3812,16 +3812,16 @@
         <v>44720</v>
       </c>
       <c r="B170" t="n">
-        <v>97.07457733154297</v>
+        <v>97.0745849609375</v>
       </c>
       <c r="C170" t="n">
-        <v>100.0439149311568</v>
+        <v>100.0439227939208</v>
       </c>
       <c r="D170" t="n">
-        <v>97.07457733154297</v>
+        <v>97.0745849609375</v>
       </c>
       <c r="E170" t="n">
-        <v>98.75252120666485</v>
+        <v>98.75252896793423</v>
       </c>
       <c r="F170" t="n">
         <v>671896</v>
@@ -3872,16 +3872,16 @@
         <v>44725</v>
       </c>
       <c r="B173" t="n">
-        <v>85.03909301757812</v>
+        <v>85.03908538818359</v>
       </c>
       <c r="C173" t="n">
-        <v>87.61310707375694</v>
+        <v>87.61309921343133</v>
       </c>
       <c r="D173" t="n">
-        <v>84.30993391953471</v>
+        <v>84.30992635555765</v>
       </c>
       <c r="E173" t="n">
-        <v>87.41104843483134</v>
+        <v>87.4110405926337</v>
       </c>
       <c r="F173" t="n">
         <v>846744</v>
@@ -3892,16 +3892,16 @@
         <v>44726</v>
       </c>
       <c r="B174" t="n">
-        <v>85.73310852050781</v>
+        <v>85.73310089111328</v>
       </c>
       <c r="C174" t="n">
-        <v>86.47105455993147</v>
+        <v>86.47104686486708</v>
       </c>
       <c r="D174" t="n">
-        <v>84.07273830986246</v>
+        <v>84.07273082822437</v>
       </c>
       <c r="E174" t="n">
-        <v>86.10208489144279</v>
+        <v>86.10207722921302</v>
       </c>
       <c r="F174" t="n">
         <v>502449</v>
@@ -3912,16 +3912,16 @@
         <v>44727</v>
       </c>
       <c r="B175" t="n">
-        <v>86.62918090820312</v>
+        <v>86.62918853759766</v>
       </c>
       <c r="C175" t="n">
-        <v>88.47403585796052</v>
+        <v>88.47404364983063</v>
       </c>
       <c r="D175" t="n">
-        <v>85.29385260189301</v>
+        <v>85.29386011368575</v>
       </c>
       <c r="E175" t="n">
-        <v>86.102080451479</v>
+        <v>86.10208803445202</v>
       </c>
       <c r="F175" t="n">
         <v>817586</v>
@@ -3932,16 +3932,16 @@
         <v>44729</v>
       </c>
       <c r="B176" t="n">
-        <v>84.51197814941406</v>
+        <v>84.51199340820312</v>
       </c>
       <c r="C176" t="n">
-        <v>86.43590168732089</v>
+        <v>86.4359172934778</v>
       </c>
       <c r="D176" t="n">
-        <v>83.73011108749068</v>
+        <v>83.73012620511224</v>
       </c>
       <c r="E176" t="n">
-        <v>84.07272668979664</v>
+        <v>84.07274186927806</v>
       </c>
       <c r="F176" t="n">
         <v>418487</v>
@@ -3952,16 +3952,16 @@
         <v>44732</v>
       </c>
       <c r="B177" t="n">
-        <v>83.89702606201172</v>
+        <v>83.89703369140625</v>
       </c>
       <c r="C177" t="n">
-        <v>85.54860908365065</v>
+        <v>85.54861686323618</v>
       </c>
       <c r="D177" t="n">
-        <v>82.53534390044604</v>
+        <v>82.53535140601245</v>
       </c>
       <c r="E177" t="n">
-        <v>84.51197540452485</v>
+        <v>84.51198308984139</v>
       </c>
       <c r="F177" t="n">
         <v>143101</v>
@@ -3972,16 +3972,16 @@
         <v>44733</v>
       </c>
       <c r="B178" t="n">
-        <v>85.99665069580078</v>
+        <v>85.99665832519531</v>
       </c>
       <c r="C178" t="n">
-        <v>87.5867388434885</v>
+        <v>87.58674661395143</v>
       </c>
       <c r="D178" t="n">
-        <v>85.37291442404235</v>
+        <v>85.37292199810067</v>
       </c>
       <c r="E178" t="n">
-        <v>85.57497304564218</v>
+        <v>85.5749806376266</v>
       </c>
       <c r="F178" t="n">
         <v>532289</v>
@@ -3992,16 +3992,16 @@
         <v>44734</v>
       </c>
       <c r="B179" t="n">
-        <v>86.53253936767578</v>
+        <v>86.53254699707031</v>
       </c>
       <c r="C179" t="n">
-        <v>87.41104230541869</v>
+        <v>87.41105001226899</v>
       </c>
       <c r="D179" t="n">
-        <v>84.59104867955743</v>
+        <v>84.59105613777476</v>
       </c>
       <c r="E179" t="n">
-        <v>84.95123139876036</v>
+        <v>84.95123888873424</v>
       </c>
       <c r="F179" t="n">
         <v>352268</v>
@@ -4072,16 +4072,16 @@
         <v>44740</v>
       </c>
       <c r="B183" t="n">
-        <v>85.97909545898438</v>
+        <v>85.97908782958984</v>
       </c>
       <c r="C183" t="n">
-        <v>92.55908139179482</v>
+        <v>92.55907317852221</v>
       </c>
       <c r="D183" t="n">
-        <v>85.97909545898438</v>
+        <v>85.97908782958984</v>
       </c>
       <c r="E183" t="n">
-        <v>91.55758845631833</v>
+        <v>91.55758033191366</v>
       </c>
       <c r="F183" t="n">
         <v>484787</v>
@@ -4092,16 +4092,16 @@
         <v>44741</v>
       </c>
       <c r="B184" t="n">
-        <v>83.28208160400391</v>
+        <v>83.28208923339844</v>
       </c>
       <c r="C184" t="n">
-        <v>86.92786345228541</v>
+        <v>86.92787141566664</v>
       </c>
       <c r="D184" t="n">
-        <v>82.57927656924488</v>
+        <v>82.57928413425608</v>
       </c>
       <c r="E184" t="n">
-        <v>85.9878655722014</v>
+        <v>85.9878734494703</v>
       </c>
       <c r="F184" t="n">
         <v>504091</v>
@@ -4112,16 +4112,16 @@
         <v>44742</v>
       </c>
       <c r="B185" t="n">
-        <v>82.6934814453125</v>
+        <v>82.69349670410156</v>
       </c>
       <c r="C185" t="n">
-        <v>84.46806118289064</v>
+        <v>84.46807676912917</v>
       </c>
       <c r="D185" t="n">
-        <v>79.82077970708073</v>
+        <v>79.82079443579234</v>
       </c>
       <c r="E185" t="n">
-        <v>82.49142951731181</v>
+        <v>82.49144473881779</v>
       </c>
       <c r="F185" t="n">
         <v>710009</v>
@@ -4132,16 +4132,16 @@
         <v>44743</v>
       </c>
       <c r="B186" t="n">
-        <v>83.40506744384766</v>
+        <v>83.40507507324219</v>
       </c>
       <c r="C186" t="n">
-        <v>85.39047917144593</v>
+        <v>85.39048698245399</v>
       </c>
       <c r="D186" t="n">
-        <v>81.92918230422647</v>
+        <v>81.92918979861589</v>
       </c>
       <c r="E186" t="n">
-        <v>82.62320039929577</v>
+        <v>82.6232079571698</v>
       </c>
       <c r="F186" t="n">
         <v>500037</v>
@@ -4152,16 +4152,16 @@
         <v>44746</v>
       </c>
       <c r="B187" t="n">
-        <v>82.66712951660156</v>
+        <v>82.66713714599609</v>
       </c>
       <c r="C187" t="n">
-        <v>84.16058861200165</v>
+        <v>84.16059637922834</v>
       </c>
       <c r="D187" t="n">
-        <v>82.21909111773695</v>
+        <v>82.21909870578178</v>
       </c>
       <c r="E187" t="n">
-        <v>82.59684766924126</v>
+        <v>82.59685529214944</v>
       </c>
       <c r="F187" t="n">
         <v>102674</v>
@@ -4172,16 +4172,16 @@
         <v>44747</v>
       </c>
       <c r="B188" t="n">
-        <v>88.5443115234375</v>
+        <v>88.54431915283203</v>
       </c>
       <c r="C188" t="n">
-        <v>88.5443115234375</v>
+        <v>88.54431915283203</v>
       </c>
       <c r="D188" t="n">
-        <v>80.36545135256145</v>
+        <v>80.36545827722691</v>
       </c>
       <c r="E188" t="n">
-        <v>82.5617086875933</v>
+        <v>82.56171580149862</v>
       </c>
       <c r="F188" t="n">
         <v>886458</v>
@@ -4232,16 +4232,16 @@
         <v>44750</v>
       </c>
       <c r="B191" t="n">
-        <v>85.69796752929688</v>
+        <v>85.69797515869141</v>
       </c>
       <c r="C191" t="n">
-        <v>88.1489849210145</v>
+        <v>88.14899276861466</v>
       </c>
       <c r="D191" t="n">
-        <v>84.96880845454787</v>
+        <v>84.9688160190279</v>
       </c>
       <c r="E191" t="n">
-        <v>86.35684475775652</v>
+        <v>86.35685244580863</v>
       </c>
       <c r="F191" t="n">
         <v>710031</v>
@@ -4252,16 +4252,16 @@
         <v>44753</v>
       </c>
       <c r="B192" t="n">
-        <v>81.78862762451172</v>
+        <v>81.78861999511719</v>
       </c>
       <c r="C192" t="n">
-        <v>85.20600374431876</v>
+        <v>85.20599579614506</v>
       </c>
       <c r="D192" t="n">
-        <v>81.43722508546183</v>
+        <v>81.43721748884678</v>
       </c>
       <c r="E192" t="n">
-        <v>85.0303058260168</v>
+        <v>85.03029789423252</v>
       </c>
       <c r="F192" t="n">
         <v>432674</v>
@@ -4272,16 +4272,16 @@
         <v>44754</v>
       </c>
       <c r="B193" t="n">
-        <v>86.32169342041016</v>
+        <v>86.32170867919922</v>
       </c>
       <c r="C193" t="n">
-        <v>86.32169342041016</v>
+        <v>86.32170867919922</v>
       </c>
       <c r="D193" t="n">
-        <v>81.29665595854095</v>
+        <v>81.2966703290714</v>
       </c>
       <c r="E193" t="n">
-        <v>82.62319716181851</v>
+        <v>82.6232117668371</v>
       </c>
       <c r="F193" t="n">
         <v>730233</v>
@@ -4372,16 +4372,16 @@
         <v>44761</v>
       </c>
       <c r="B198" t="n">
-        <v>86.85759735107422</v>
+        <v>86.85758209228516</v>
       </c>
       <c r="C198" t="n">
-        <v>87.15628516534521</v>
+        <v>87.15626985408389</v>
       </c>
       <c r="D198" t="n">
-        <v>83.45778819792039</v>
+        <v>83.45777353639596</v>
       </c>
       <c r="E198" t="n">
-        <v>83.45778819792039</v>
+        <v>83.45777353639596</v>
       </c>
       <c r="F198" t="n">
         <v>493807</v>
@@ -4392,16 +4392,16 @@
         <v>44762</v>
       </c>
       <c r="B199" t="n">
-        <v>88.29833984375</v>
+        <v>88.29834747314453</v>
       </c>
       <c r="C199" t="n">
-        <v>88.90450236595208</v>
+        <v>88.90451004772193</v>
       </c>
       <c r="D199" t="n">
-        <v>86.09329540117778</v>
+        <v>86.09330284004604</v>
       </c>
       <c r="E199" t="n">
-        <v>86.09329540117778</v>
+        <v>86.09330284004604</v>
       </c>
       <c r="F199" t="n">
         <v>780872</v>
@@ -4412,16 +4412,16 @@
         <v>44763</v>
       </c>
       <c r="B200" t="n">
-        <v>91.97048950195312</v>
+        <v>91.97047424316406</v>
       </c>
       <c r="C200" t="n">
-        <v>92.62057990384585</v>
+        <v>92.62056453720052</v>
       </c>
       <c r="D200" t="n">
-        <v>87.41105637633429</v>
+        <v>87.41104187399904</v>
       </c>
       <c r="E200" t="n">
-        <v>87.41105637633429</v>
+        <v>87.41104187399904</v>
       </c>
       <c r="F200" t="n">
         <v>453688</v>
@@ -4432,16 +4432,16 @@
         <v>44764</v>
       </c>
       <c r="B201" t="n">
-        <v>89.78300476074219</v>
+        <v>89.78299713134766</v>
       </c>
       <c r="C201" t="n">
-        <v>92.24281586478145</v>
+        <v>92.24280802636217</v>
       </c>
       <c r="D201" t="n">
-        <v>89.22076337166682</v>
+        <v>89.22075579004928</v>
       </c>
       <c r="E201" t="n">
-        <v>91.97048207701101</v>
+        <v>91.97047426173357</v>
       </c>
       <c r="F201" t="n">
         <v>566897</v>
@@ -4532,16 +4532,16 @@
         <v>44771</v>
       </c>
       <c r="B206" t="n">
-        <v>95.712890625</v>
+        <v>95.71289825439453</v>
       </c>
       <c r="C206" t="n">
-        <v>96.45962347029804</v>
+        <v>96.45963115921559</v>
       </c>
       <c r="D206" t="n">
-        <v>92.28673459280013</v>
+        <v>92.28674194909148</v>
       </c>
       <c r="E206" t="n">
-        <v>92.28673459280013</v>
+        <v>92.28674194909148</v>
       </c>
       <c r="F206" t="n">
         <v>432249</v>
@@ -4552,16 +4552,16 @@
         <v>44774</v>
       </c>
       <c r="B207" t="n">
-        <v>100.1493377685547</v>
+        <v>100.1493453979492</v>
       </c>
       <c r="C207" t="n">
-        <v>102.2841002364559</v>
+        <v>102.284108028477</v>
       </c>
       <c r="D207" t="n">
-        <v>94.35121955402224</v>
+        <v>94.3512267417151</v>
       </c>
       <c r="E207" t="n">
-        <v>94.35121955402224</v>
+        <v>94.3512267417151</v>
       </c>
       <c r="F207" t="n">
         <v>942663</v>
@@ -4592,16 +4592,16 @@
         <v>44776</v>
       </c>
       <c r="B209" t="n">
-        <v>106.8523178100586</v>
+        <v>106.8523101806641</v>
       </c>
       <c r="C209" t="n">
-        <v>107.5990507243421</v>
+        <v>107.5990430416299</v>
       </c>
       <c r="D209" t="n">
-        <v>101.4670968161594</v>
+        <v>101.4670895712767</v>
       </c>
       <c r="E209" t="n">
-        <v>101.4670968161594</v>
+        <v>101.4670895712767</v>
       </c>
       <c r="F209" t="n">
         <v>990038</v>
@@ -4612,16 +4612,16 @@
         <v>44777</v>
       </c>
       <c r="B210" t="n">
-        <v>107.695671081543</v>
+        <v>107.6956787109375</v>
       </c>
       <c r="C210" t="n">
-        <v>114.1966008131186</v>
+        <v>114.196608903053</v>
       </c>
       <c r="D210" t="n">
-        <v>104.9811002422437</v>
+        <v>104.9811076793322</v>
       </c>
       <c r="E210" t="n">
-        <v>106.8610959781686</v>
+        <v>106.86110354844</v>
       </c>
       <c r="F210" t="n">
         <v>1242592</v>
@@ -4652,16 +4652,16 @@
         <v>44781</v>
       </c>
       <c r="B212" t="n">
-        <v>110.4893112182617</v>
+        <v>110.4893188476562</v>
       </c>
       <c r="C212" t="n">
-        <v>113.2829508204784</v>
+        <v>113.2829586427765</v>
       </c>
       <c r="D212" t="n">
-        <v>108.4511846765621</v>
+        <v>108.451192165222</v>
       </c>
       <c r="E212" t="n">
-        <v>108.9343639719319</v>
+        <v>108.9343714939558</v>
       </c>
       <c r="F212" t="n">
         <v>1248783</v>
@@ -4672,16 +4672,16 @@
         <v>44782</v>
       </c>
       <c r="B213" t="n">
-        <v>105.4027862548828</v>
+        <v>105.4027938842773</v>
       </c>
       <c r="C213" t="n">
-        <v>111.0339866451756</v>
+        <v>111.0339946821746</v>
       </c>
       <c r="D213" t="n">
-        <v>104.6999812181399</v>
+        <v>104.6999887966631</v>
       </c>
       <c r="E213" t="n">
-        <v>109.7689402600166</v>
+        <v>109.7689482054474</v>
       </c>
       <c r="F213" t="n">
         <v>927684</v>
@@ -4752,16 +4752,16 @@
         <v>44788</v>
       </c>
       <c r="B217" t="n">
-        <v>98.17270660400391</v>
+        <v>98.17271423339844</v>
       </c>
       <c r="C217" t="n">
-        <v>98.83158382953414</v>
+        <v>98.83159151013265</v>
       </c>
       <c r="D217" t="n">
-        <v>86.98058067634858</v>
+        <v>86.98058743595814</v>
       </c>
       <c r="E217" t="n">
-        <v>87.40225834731831</v>
+        <v>87.40226513969814</v>
       </c>
       <c r="F217" t="n">
         <v>1427504</v>
@@ -4792,16 +4792,16 @@
         <v>44790</v>
       </c>
       <c r="B219" t="n">
-        <v>96.52112579345703</v>
+        <v>96.5211181640625</v>
       </c>
       <c r="C219" t="n">
-        <v>96.67046969296776</v>
+        <v>96.67046205176851</v>
       </c>
       <c r="D219" t="n">
-        <v>93.29701473066473</v>
+        <v>93.29700735611611</v>
       </c>
       <c r="E219" t="n">
-        <v>93.29701473066473</v>
+        <v>93.29700735611611</v>
       </c>
       <c r="F219" t="n">
         <v>484266</v>
@@ -4832,16 +4832,16 @@
         <v>44792</v>
       </c>
       <c r="B221" t="n">
-        <v>92.81383514404297</v>
+        <v>92.8138427734375</v>
       </c>
       <c r="C221" t="n">
-        <v>96.35420085090701</v>
+        <v>96.3542087713233</v>
       </c>
       <c r="D221" t="n">
-        <v>92.34822966730141</v>
+        <v>92.34823725842267</v>
       </c>
       <c r="E221" t="n">
-        <v>95.79195951645167</v>
+        <v>95.79196739065114</v>
       </c>
       <c r="F221" t="n">
         <v>610732</v>
@@ -4912,16 +4912,16 @@
         <v>44798</v>
       </c>
       <c r="B225" t="n">
-        <v>99.56951904296875</v>
+        <v>99.56952667236328</v>
       </c>
       <c r="C225" t="n">
-        <v>103.1362455026625</v>
+        <v>103.1362534053532</v>
       </c>
       <c r="D225" t="n">
-        <v>98.69980301743414</v>
+        <v>98.69981058018772</v>
       </c>
       <c r="E225" t="n">
-        <v>101.9063400580249</v>
+        <v>101.9063478664755</v>
       </c>
       <c r="F225" t="n">
         <v>468543</v>
@@ -5032,16 +5032,16 @@
         <v>44806</v>
       </c>
       <c r="B231" t="n">
-        <v>88.0260009765625</v>
+        <v>88.02600860595703</v>
       </c>
       <c r="C231" t="n">
-        <v>91.19739745291511</v>
+        <v>91.1974053571811</v>
       </c>
       <c r="D231" t="n">
-        <v>86.98936713245767</v>
+        <v>86.98937467200503</v>
       </c>
       <c r="E231" t="n">
-        <v>89.50188633592451</v>
+        <v>89.50189409323706</v>
       </c>
       <c r="F231" t="n">
         <v>344726</v>
@@ -5092,16 +5092,16 @@
         <v>44812</v>
       </c>
       <c r="B234" t="n">
-        <v>88.28954315185547</v>
+        <v>88.28955078125</v>
       </c>
       <c r="C234" t="n">
-        <v>90.14318484278159</v>
+        <v>90.14319263235551</v>
       </c>
       <c r="D234" t="n">
-        <v>87.12991956960056</v>
+        <v>87.12992709878814</v>
       </c>
       <c r="E234" t="n">
-        <v>88.29833005770951</v>
+        <v>88.29833768786334</v>
       </c>
       <c r="F234" t="n">
         <v>707072</v>
@@ -5132,16 +5132,16 @@
         <v>44816</v>
       </c>
       <c r="B236" t="n">
-        <v>94.79047393798828</v>
+        <v>94.79048156738281</v>
       </c>
       <c r="C236" t="n">
-        <v>94.79047393798828</v>
+        <v>94.79048156738281</v>
       </c>
       <c r="D236" t="n">
-        <v>91.34674382662909</v>
+        <v>91.34675117884834</v>
       </c>
       <c r="E236" t="n">
-        <v>91.34674382662909</v>
+        <v>91.34675117884834</v>
       </c>
       <c r="F236" t="n">
         <v>423751</v>
@@ -5152,16 +5152,16 @@
         <v>44817</v>
       </c>
       <c r="B237" t="n">
-        <v>90.74935913085938</v>
+        <v>90.74936676025391</v>
       </c>
       <c r="C237" t="n">
-        <v>92.94561654736182</v>
+        <v>92.94562436139803</v>
       </c>
       <c r="D237" t="n">
-        <v>90.4858055599008</v>
+        <v>90.48581316713809</v>
       </c>
       <c r="E237" t="n">
-        <v>91.36430852650177</v>
+        <v>91.36431620759575</v>
       </c>
       <c r="F237" t="n">
         <v>548480</v>
@@ -5172,16 +5172,16 @@
         <v>44818</v>
       </c>
       <c r="B238" t="n">
-        <v>90.1343994140625</v>
+        <v>90.13442230224609</v>
       </c>
       <c r="C238" t="n">
-        <v>91.77720230853167</v>
+        <v>91.77722561387868</v>
       </c>
       <c r="D238" t="n">
-        <v>88.15776781856795</v>
+        <v>88.15779020481769</v>
       </c>
       <c r="E238" t="n">
-        <v>90.17832724160722</v>
+        <v>90.17835014094558</v>
       </c>
       <c r="F238" t="n">
         <v>962834</v>
@@ -5232,16 +5232,16 @@
         <v>44823</v>
       </c>
       <c r="B241" t="n">
-        <v>88.99234771728516</v>
+        <v>88.99235534667969</v>
       </c>
       <c r="C241" t="n">
-        <v>89.82692280318257</v>
+        <v>89.82693050412597</v>
       </c>
       <c r="D241" t="n">
-        <v>86.69945457946307</v>
+        <v>86.69946201228579</v>
       </c>
       <c r="E241" t="n">
-        <v>87.39347268463194</v>
+        <v>87.39348017695347</v>
       </c>
       <c r="F241" t="n">
         <v>601912</v>
@@ -5332,16 +5332,16 @@
         <v>44830</v>
       </c>
       <c r="B246" t="n">
-        <v>84.33628845214844</v>
+        <v>84.33628082275391</v>
       </c>
       <c r="C246" t="n">
-        <v>89.18562208907072</v>
+        <v>89.18561402098628</v>
       </c>
       <c r="D246" t="n">
-        <v>84.24843949216665</v>
+        <v>84.24843187071929</v>
       </c>
       <c r="E246" t="n">
-        <v>88.13142116439727</v>
+        <v>88.13141319168002</v>
       </c>
       <c r="F246" t="n">
         <v>548585</v>
@@ -5372,16 +5372,16 @@
         <v>44832</v>
       </c>
       <c r="B248" t="n">
-        <v>86.9454345703125</v>
+        <v>86.94544219970703</v>
       </c>
       <c r="C248" t="n">
-        <v>88.52673579585205</v>
+        <v>88.52674356400453</v>
       </c>
       <c r="D248" t="n">
-        <v>85.29384480054043</v>
+        <v>85.29385228500924</v>
       </c>
       <c r="E248" t="n">
-        <v>86.55010423709361</v>
+        <v>86.5501118317982</v>
       </c>
       <c r="F248" t="n">
         <v>626382</v>
@@ -5392,16 +5392,16 @@
         <v>44833</v>
       </c>
       <c r="B249" t="n">
-        <v>87.27047729492188</v>
+        <v>87.27049255371094</v>
       </c>
       <c r="C249" t="n">
-        <v>87.79758441153149</v>
+        <v>87.79759976248249</v>
       </c>
       <c r="D249" t="n">
-        <v>84.51197864843198</v>
+        <v>84.51199342491191</v>
       </c>
       <c r="E249" t="n">
-        <v>85.39926847878306</v>
+        <v>85.399283410401</v>
       </c>
       <c r="F249" t="n">
         <v>546314</v>
@@ -5452,16 +5452,16 @@
         <v>44838</v>
       </c>
       <c r="B252" t="n">
-        <v>94.43906402587891</v>
+        <v>94.43907165527344</v>
       </c>
       <c r="C252" t="n">
-        <v>96.46840362900132</v>
+        <v>96.46841142233895</v>
       </c>
       <c r="D252" t="n">
-        <v>92.77869404106141</v>
+        <v>92.77870153632058</v>
       </c>
       <c r="E252" t="n">
-        <v>93.47271215307993</v>
+        <v>93.47271970440633</v>
       </c>
       <c r="F252" t="n">
         <v>828067</v>
@@ -5472,16 +5472,16 @@
         <v>44839</v>
       </c>
       <c r="B253" t="n">
-        <v>95.75682067871094</v>
+        <v>95.75682830810547</v>
       </c>
       <c r="C253" t="n">
-        <v>97.74223920433043</v>
+        <v>97.74224699191255</v>
       </c>
       <c r="D253" t="n">
-        <v>93.46392746387826</v>
+        <v>93.46393491058726</v>
       </c>
       <c r="E253" t="n">
-        <v>94.30728948391106</v>
+        <v>94.30729699781466</v>
       </c>
       <c r="F253" t="n">
         <v>556734</v>
@@ -5492,16 +5492,16 @@
         <v>44840</v>
       </c>
       <c r="B254" t="n">
-        <v>99.09514617919922</v>
+        <v>99.09513854980469</v>
       </c>
       <c r="C254" t="n">
-        <v>99.89458046505639</v>
+        <v>99.89457277411294</v>
       </c>
       <c r="D254" t="n">
-        <v>94.70263095321427</v>
+        <v>94.70262366200211</v>
       </c>
       <c r="E254" t="n">
-        <v>95.71290409323375</v>
+        <v>95.71289672424005</v>
       </c>
       <c r="F254" t="n">
         <v>1317655</v>
@@ -5532,16 +5532,16 @@
         <v>44844</v>
       </c>
       <c r="B256" t="n">
-        <v>96.52112579345703</v>
+        <v>96.5211181640625</v>
       </c>
       <c r="C256" t="n">
-        <v>97.95308325233714</v>
+        <v>97.95307550975528</v>
       </c>
       <c r="D256" t="n">
-        <v>94.96617174989328</v>
+        <v>94.96616424340819</v>
       </c>
       <c r="E256" t="n">
-        <v>97.16242922191877</v>
+        <v>97.1624215418332</v>
       </c>
       <c r="F256" t="n">
         <v>391665</v>
@@ -5552,16 +5552,16 @@
         <v>44845</v>
       </c>
       <c r="B257" t="n">
-        <v>88.64974975585938</v>
+        <v>88.64974212646484</v>
       </c>
       <c r="C257" t="n">
-        <v>96.94281434223674</v>
+        <v>96.94280599912264</v>
       </c>
       <c r="D257" t="n">
-        <v>87.13872337332482</v>
+        <v>87.1387158739726</v>
       </c>
       <c r="E257" t="n">
-        <v>96.52113661370647</v>
+        <v>96.5211283068829</v>
       </c>
       <c r="F257" t="n">
         <v>1649810</v>
@@ -5632,16 +5632,16 @@
         <v>44852</v>
       </c>
       <c r="B261" t="n">
-        <v>80.54115295410156</v>
+        <v>80.54116058349609</v>
       </c>
       <c r="C261" t="n">
-        <v>85.61011216687361</v>
+        <v>85.61012027643372</v>
       </c>
       <c r="D261" t="n">
-        <v>79.24096560302623</v>
+        <v>79.24097310925836</v>
       </c>
       <c r="E261" t="n">
-        <v>84.42413449202566</v>
+        <v>84.42414248924207</v>
       </c>
       <c r="F261" t="n">
         <v>1514560</v>
@@ -5652,16 +5652,16 @@
         <v>44853</v>
       </c>
       <c r="B262" t="n">
-        <v>80.47086334228516</v>
+        <v>80.47087860107422</v>
       </c>
       <c r="C262" t="n">
-        <v>81.52507083121216</v>
+        <v>81.52508628989879</v>
       </c>
       <c r="D262" t="n">
-        <v>79.10918788494983</v>
+        <v>79.10920288553962</v>
       </c>
       <c r="E262" t="n">
-        <v>80.3830143938192</v>
+        <v>80.38302963595044</v>
       </c>
       <c r="F262" t="n">
         <v>1204425</v>
@@ -5672,16 +5672,16 @@
         <v>44854</v>
       </c>
       <c r="B263" t="n">
-        <v>77.81779479980469</v>
+        <v>77.81778717041016</v>
       </c>
       <c r="C263" t="n">
-        <v>80.72563748978079</v>
+        <v>80.72562957529622</v>
       </c>
       <c r="D263" t="n">
-        <v>76.50004034296538</v>
+        <v>76.50003284276583</v>
       </c>
       <c r="E263" t="n">
-        <v>80.4708708238317</v>
+        <v>80.4708629343249</v>
       </c>
       <c r="F263" t="n">
         <v>1064344</v>
@@ -5692,16 +5692,16 @@
         <v>44855</v>
       </c>
       <c r="B264" t="n">
-        <v>82.25422668457031</v>
+        <v>82.25423431396484</v>
       </c>
       <c r="C264" t="n">
-        <v>85.73309747299184</v>
+        <v>85.73310542506498</v>
       </c>
       <c r="D264" t="n">
-        <v>75.13835431268782</v>
+        <v>75.13836128205794</v>
       </c>
       <c r="E264" t="n">
-        <v>77.96713481147866</v>
+        <v>77.967142043229</v>
       </c>
       <c r="F264" t="n">
         <v>1421863</v>
@@ -5732,16 +5732,16 @@
         <v>44859</v>
       </c>
       <c r="B266" t="n">
-        <v>82.92189788818359</v>
+        <v>82.92189025878906</v>
       </c>
       <c r="C266" t="n">
-        <v>85.30264022119347</v>
+        <v>85.30263237275399</v>
       </c>
       <c r="D266" t="n">
-        <v>81.31423578466473</v>
+        <v>81.31422830318635</v>
       </c>
       <c r="E266" t="n">
-        <v>82.03460797877678</v>
+        <v>82.03460043101913</v>
       </c>
       <c r="F266" t="n">
         <v>1189906</v>
@@ -5752,16 +5752,16 @@
         <v>44860</v>
       </c>
       <c r="B267" t="n">
-        <v>80.20732116699219</v>
+        <v>80.20732879638672</v>
       </c>
       <c r="C267" t="n">
-        <v>84.20450552571505</v>
+        <v>84.20451353532545</v>
       </c>
       <c r="D267" t="n">
-        <v>80.07554438539792</v>
+        <v>80.07555200225771</v>
       </c>
       <c r="E267" t="n">
-        <v>82.57927642590705</v>
+        <v>82.57928428092416</v>
       </c>
       <c r="F267" t="n">
         <v>763965</v>
@@ -5772,16 +5772,16 @@
         <v>44861</v>
       </c>
       <c r="B268" t="n">
-        <v>78.95984649658203</v>
+        <v>78.95985412597656</v>
       </c>
       <c r="C268" t="n">
-        <v>81.79741410940505</v>
+        <v>81.79742201297594</v>
       </c>
       <c r="D268" t="n">
-        <v>78.12527133528192</v>
+        <v>78.12527888403669</v>
       </c>
       <c r="E268" t="n">
-        <v>80.63779042823175</v>
+        <v>80.63779821975547</v>
       </c>
       <c r="F268" t="n">
         <v>872704</v>
@@ -5792,16 +5792,16 @@
         <v>44862</v>
       </c>
       <c r="B269" t="n">
-        <v>81.43721771240234</v>
+        <v>81.43722534179688</v>
       </c>
       <c r="C269" t="n">
-        <v>82.14002272687244</v>
+        <v>82.14003042210881</v>
       </c>
       <c r="D269" t="n">
-        <v>78.40638533019641</v>
+        <v>78.40639267564933</v>
       </c>
       <c r="E269" t="n">
-        <v>79.04769540858378</v>
+        <v>79.04770281411741</v>
       </c>
       <c r="F269" t="n">
         <v>705309</v>
@@ -5812,16 +5812,16 @@
         <v>44865</v>
       </c>
       <c r="B270" t="n">
-        <v>83.36992645263672</v>
+        <v>83.36994171142578</v>
       </c>
       <c r="C270" t="n">
-        <v>84.17814751110124</v>
+        <v>84.17816291781504</v>
       </c>
       <c r="D270" t="n">
-        <v>79.07404781287445</v>
+        <v>79.07406228540991</v>
       </c>
       <c r="E270" t="n">
-        <v>79.07404781287445</v>
+        <v>79.07406228540991</v>
       </c>
       <c r="F270" t="n">
         <v>956071</v>
@@ -5852,16 +5852,16 @@
         <v>44868</v>
       </c>
       <c r="B272" t="n">
-        <v>86.58525085449219</v>
+        <v>86.58524322509766</v>
       </c>
       <c r="C272" t="n">
-        <v>88.46524668009084</v>
+        <v>88.4652388850419</v>
       </c>
       <c r="D272" t="n">
-        <v>84.04637779929271</v>
+        <v>84.0463703936091</v>
       </c>
       <c r="E272" t="n">
-        <v>85.59254490810744</v>
+        <v>85.59253736618446</v>
       </c>
       <c r="F272" t="n">
         <v>991113</v>
@@ -5872,16 +5872,16 @@
         <v>44869</v>
       </c>
       <c r="B273" t="n">
-        <v>83.484130859375</v>
+        <v>83.48413848876953</v>
       </c>
       <c r="C273" t="n">
-        <v>88.72879432924752</v>
+        <v>88.728802437938</v>
       </c>
       <c r="D273" t="n">
-        <v>82.78133254952142</v>
+        <v>82.78134011468907</v>
       </c>
       <c r="E273" t="n">
-        <v>87.59552476569932</v>
+        <v>87.59553277082331</v>
       </c>
       <c r="F273" t="n">
         <v>612180</v>
@@ -5912,16 +5912,16 @@
         <v>44873</v>
       </c>
       <c r="B275" t="n">
-        <v>83.45778656005859</v>
+        <v>83.45777893066406</v>
       </c>
       <c r="C275" t="n">
-        <v>84.66133810543688</v>
+        <v>84.66133036601822</v>
       </c>
       <c r="D275" t="n">
-        <v>81.31423705520696</v>
+        <v>81.31422962176761</v>
       </c>
       <c r="E275" t="n">
-        <v>82.7110603365894</v>
+        <v>82.71105277545774</v>
       </c>
       <c r="F275" t="n">
         <v>953385</v>
@@ -5952,16 +5952,16 @@
         <v>44875</v>
       </c>
       <c r="B277" t="n">
-        <v>90.49459838867188</v>
+        <v>90.49459075927734</v>
       </c>
       <c r="C277" t="n">
-        <v>94.21944933414814</v>
+        <v>94.21944139071987</v>
       </c>
       <c r="D277" t="n">
-        <v>85.65404484922558</v>
+        <v>85.65403762792715</v>
       </c>
       <c r="E277" t="n">
-        <v>85.67161196063115</v>
+        <v>85.67160473785169</v>
       </c>
       <c r="F277" t="n">
         <v>2820385</v>
@@ -5972,16 +5972,16 @@
         <v>44876</v>
       </c>
       <c r="B278" t="n">
-        <v>89.57216644287109</v>
+        <v>89.57217407226562</v>
       </c>
       <c r="C278" t="n">
-        <v>91.51365729821109</v>
+        <v>91.51366509297395</v>
       </c>
       <c r="D278" t="n">
-        <v>88.06114018741653</v>
+        <v>88.06114768810795</v>
       </c>
       <c r="E278" t="n">
-        <v>90.4858103811098</v>
+        <v>90.48581808832483</v>
       </c>
       <c r="F278" t="n">
         <v>1123849</v>
@@ -6032,16 +6032,16 @@
         <v>44882</v>
       </c>
       <c r="B281" t="n">
-        <v>84.07273101806641</v>
+        <v>84.07273864746094</v>
       </c>
       <c r="C281" t="n">
-        <v>86.65553187836828</v>
+        <v>86.65553974214566</v>
       </c>
       <c r="D281" t="n">
-        <v>78.95106382910978</v>
+        <v>78.95107099372555</v>
       </c>
       <c r="E281" t="n">
-        <v>86.26020822533852</v>
+        <v>86.26021605324125</v>
       </c>
       <c r="F281" t="n">
         <v>1328887</v>
@@ -6212,16 +6212,16 @@
         <v>44895</v>
       </c>
       <c r="B290" t="n">
-        <v>79.53966522216797</v>
+        <v>79.53965759277344</v>
       </c>
       <c r="C290" t="n">
-        <v>80.11947373729132</v>
+        <v>80.11946605228191</v>
       </c>
       <c r="D290" t="n">
-        <v>75.72695858278091</v>
+        <v>75.72695131909879</v>
       </c>
       <c r="E290" t="n">
-        <v>78.18676975028522</v>
+        <v>78.18676225065957</v>
       </c>
       <c r="F290" t="n">
         <v>577266</v>
@@ -6312,16 +6312,16 @@
         <v>44902</v>
       </c>
       <c r="B295" t="n">
-        <v>76.15742492675781</v>
+        <v>76.15741729736328</v>
       </c>
       <c r="C295" t="n">
-        <v>78.4327444112255</v>
+        <v>78.43273655389115</v>
       </c>
       <c r="D295" t="n">
-        <v>74.76060171345117</v>
+        <v>74.76059422398934</v>
       </c>
       <c r="E295" t="n">
-        <v>77.82657521465414</v>
+        <v>77.82656741804537</v>
       </c>
       <c r="F295" t="n">
         <v>782541</v>
@@ -6332,16 +6332,16 @@
         <v>44903</v>
       </c>
       <c r="B296" t="n">
-        <v>72.38864898681641</v>
+        <v>72.38865661621094</v>
       </c>
       <c r="C296" t="n">
-        <v>76.73723618265012</v>
+        <v>76.73724427036358</v>
       </c>
       <c r="D296" t="n">
-        <v>72.03724644416056</v>
+        <v>72.03725403651906</v>
       </c>
       <c r="E296" t="n">
-        <v>76.73723618265012</v>
+        <v>76.73724427036358</v>
       </c>
       <c r="F296" t="n">
         <v>1116650</v>
@@ -6352,16 +6352,16 @@
         <v>44904</v>
       </c>
       <c r="B297" t="n">
-        <v>72.71368408203125</v>
+        <v>72.71369934082031</v>
       </c>
       <c r="C297" t="n">
-        <v>74.76059750386545</v>
+        <v>74.7606131921943</v>
       </c>
       <c r="D297" t="n">
-        <v>70.93032421841735</v>
+        <v>70.9303391029727</v>
       </c>
       <c r="E297" t="n">
-        <v>72.96845073432544</v>
+        <v>72.96846604657665</v>
       </c>
       <c r="F297" t="n">
         <v>602365</v>
@@ -6392,16 +6392,16 @@
         <v>44908</v>
       </c>
       <c r="B299" t="n">
-        <v>70.42079925537109</v>
+        <v>70.42080688476562</v>
       </c>
       <c r="C299" t="n">
-        <v>74.92751694822861</v>
+        <v>74.92752506588127</v>
       </c>
       <c r="D299" t="n">
-        <v>69.92883304873867</v>
+        <v>69.92884062483354</v>
       </c>
       <c r="E299" t="n">
-        <v>71.9581794084006</v>
+        <v>71.958187204355</v>
       </c>
       <c r="F299" t="n">
         <v>758036</v>
@@ -6412,16 +6412,16 @@
         <v>44909</v>
       </c>
       <c r="B300" t="n">
-        <v>68.19818115234375</v>
+        <v>68.19818878173828</v>
       </c>
       <c r="C300" t="n">
-        <v>70.51742838907342</v>
+        <v>70.5174362779243</v>
       </c>
       <c r="D300" t="n">
-        <v>66.81893179790644</v>
+        <v>66.81893927300305</v>
       </c>
       <c r="E300" t="n">
-        <v>70.43836634126119</v>
+        <v>70.43837422126734</v>
       </c>
       <c r="F300" t="n">
         <v>1355188</v>
@@ -6432,16 +6432,16 @@
         <v>44910</v>
       </c>
       <c r="B301" t="n">
-        <v>65.86136627197266</v>
+        <v>65.86137390136719</v>
       </c>
       <c r="C301" t="n">
-        <v>68.84827759883733</v>
+        <v>68.8482855742363</v>
       </c>
       <c r="D301" t="n">
-        <v>65.81743844413599</v>
+        <v>65.81744606844191</v>
       </c>
       <c r="E301" t="n">
-        <v>68.30360336491199</v>
+        <v>68.30361127721578</v>
       </c>
       <c r="F301" t="n">
         <v>806063</v>
@@ -6472,16 +6472,16 @@
         <v>44914</v>
       </c>
       <c r="B303" t="n">
-        <v>66.36210632324219</v>
+        <v>66.36211395263672</v>
       </c>
       <c r="C303" t="n">
-        <v>66.73107591293393</v>
+        <v>66.73108358474747</v>
       </c>
       <c r="D303" t="n">
-        <v>64.41182891709317</v>
+        <v>64.41183632227187</v>
       </c>
       <c r="E303" t="n">
-        <v>66.09855278635102</v>
+        <v>66.09856038544582</v>
       </c>
       <c r="F303" t="n">
         <v>945079</v>
@@ -6552,16 +6552,16 @@
         <v>44918</v>
       </c>
       <c r="B307" t="n">
-        <v>70.728271484375</v>
+        <v>70.72827911376953</v>
       </c>
       <c r="C307" t="n">
-        <v>70.85126135614206</v>
+        <v>70.85126899880341</v>
       </c>
       <c r="D307" t="n">
-        <v>68.02248090060881</v>
+        <v>68.02248823813217</v>
       </c>
       <c r="E307" t="n">
-        <v>68.52322729350198</v>
+        <v>68.52323468504038</v>
       </c>
       <c r="F307" t="n">
         <v>762496</v>
@@ -6572,16 +6572,16 @@
         <v>44921</v>
       </c>
       <c r="B308" t="n">
-        <v>68.78679656982422</v>
+        <v>68.78678894042969</v>
       </c>
       <c r="C308" t="n">
-        <v>71.15875229880567</v>
+        <v>71.15874440632886</v>
       </c>
       <c r="D308" t="n">
-        <v>68.39146614669608</v>
+        <v>68.39145856114908</v>
       </c>
       <c r="E308" t="n">
-        <v>71.15875229880567</v>
+        <v>71.15874440632886</v>
       </c>
       <c r="F308" t="n">
         <v>122344</v>
@@ -6672,16 +6672,16 @@
         <v>44929</v>
       </c>
       <c r="B313" t="n">
-        <v>66.99463653564453</v>
+        <v>66.99462890625</v>
       </c>
       <c r="C313" t="n">
-        <v>69.74434834362098</v>
+        <v>69.74434040108741</v>
       </c>
       <c r="D313" t="n">
-        <v>65.50117750604407</v>
+        <v>65.50117004672566</v>
       </c>
       <c r="E313" t="n">
-        <v>66.60809309463926</v>
+        <v>66.60808550926455</v>
       </c>
       <c r="F313" t="n">
         <v>913081</v>
@@ -6712,16 +6712,16 @@
         <v>44931</v>
       </c>
       <c r="B315" t="n">
-        <v>65.422119140625</v>
+        <v>65.42211151123047</v>
       </c>
       <c r="C315" t="n">
-        <v>68.18061801001888</v>
+        <v>68.18061005893381</v>
       </c>
       <c r="D315" t="n">
-        <v>65.07071660197154</v>
+        <v>65.07070901355685</v>
       </c>
       <c r="E315" t="n">
-        <v>67.19669224227836</v>
+        <v>67.19668440593672</v>
       </c>
       <c r="F315" t="n">
         <v>721996</v>
@@ -6812,16 +6812,16 @@
         <v>44938</v>
       </c>
       <c r="B320" t="n">
-        <v>74.93630981445312</v>
+        <v>74.93631744384766</v>
       </c>
       <c r="C320" t="n">
-        <v>75.89387488304087</v>
+        <v>75.89388260992675</v>
       </c>
       <c r="D320" t="n">
-        <v>71.29052096395313</v>
+        <v>71.29052822216363</v>
       </c>
       <c r="E320" t="n">
-        <v>72.90696329338618</v>
+        <v>72.90697071616947</v>
       </c>
       <c r="F320" t="n">
         <v>1386963</v>
@@ -6872,16 +6872,16 @@
         <v>44943</v>
       </c>
       <c r="B323" t="n">
-        <v>72.37985992431641</v>
+        <v>72.37985229492188</v>
       </c>
       <c r="C323" t="n">
-        <v>72.69612153304253</v>
+        <v>72.69611387031159</v>
       </c>
       <c r="D323" t="n">
-        <v>70.11332062926112</v>
+        <v>70.11331323877729</v>
       </c>
       <c r="E323" t="n">
-        <v>71.02696453197595</v>
+        <v>71.026957045187</v>
       </c>
       <c r="F323" t="n">
         <v>1038524</v>
@@ -6892,16 +6892,16 @@
         <v>44944</v>
       </c>
       <c r="B324" t="n">
-        <v>73.96994018554688</v>
+        <v>73.96994781494141</v>
       </c>
       <c r="C324" t="n">
-        <v>75.29648141767632</v>
+        <v>75.29648918389273</v>
       </c>
       <c r="D324" t="n">
-        <v>72.48527486857265</v>
+        <v>72.48528234483609</v>
       </c>
       <c r="E324" t="n">
-        <v>72.52041578824208</v>
+        <v>72.52042326813002</v>
       </c>
       <c r="F324" t="n">
         <v>881691</v>
@@ -6932,16 +6932,16 @@
         <v>44946</v>
       </c>
       <c r="B326" t="n">
-        <v>77.02713775634766</v>
+        <v>77.02714538574219</v>
       </c>
       <c r="C326" t="n">
-        <v>78.32732505171256</v>
+        <v>78.32733280988822</v>
       </c>
       <c r="D326" t="n">
-        <v>74.45312388377251</v>
+        <v>74.45313125821576</v>
       </c>
       <c r="E326" t="n">
-        <v>75.12078799233532</v>
+        <v>75.12079543290946</v>
       </c>
       <c r="F326" t="n">
         <v>766265</v>
@@ -7012,16 +7012,16 @@
         <v>44952</v>
       </c>
       <c r="B330" t="n">
-        <v>79.52208709716797</v>
+        <v>79.52207946777344</v>
       </c>
       <c r="C330" t="n">
-        <v>80.04919424909092</v>
+        <v>80.04918656912542</v>
       </c>
       <c r="D330" t="n">
-        <v>77.41368529925958</v>
+        <v>77.41367787214632</v>
       </c>
       <c r="E330" t="n">
-        <v>77.87929080800512</v>
+        <v>77.87928333622141</v>
       </c>
       <c r="F330" t="n">
         <v>392968</v>
@@ -7032,16 +7032,16 @@
         <v>44953</v>
       </c>
       <c r="B331" t="n">
-        <v>81.18247222900391</v>
+        <v>81.18246459960938</v>
       </c>
       <c r="C331" t="n">
-        <v>81.18247222900391</v>
+        <v>81.18246459960938</v>
       </c>
       <c r="D331" t="n">
-        <v>75.7357491525274</v>
+        <v>75.73574203500689</v>
       </c>
       <c r="E331" t="n">
-        <v>78.99499475050509</v>
+        <v>78.99498732668607</v>
       </c>
       <c r="F331" t="n">
         <v>1276572</v>
@@ -7052,16 +7052,16 @@
         <v>44956</v>
       </c>
       <c r="B332" t="n">
-        <v>80.84862518310547</v>
+        <v>80.8486328125</v>
       </c>
       <c r="C332" t="n">
-        <v>81.99068169579233</v>
+        <v>81.99068943295865</v>
       </c>
       <c r="D332" t="n">
-        <v>78.90713447349425</v>
+        <v>78.90714191967729</v>
       </c>
       <c r="E332" t="n">
-        <v>81.17367368654911</v>
+        <v>81.1736813466173</v>
       </c>
       <c r="F332" t="n">
         <v>515927</v>
@@ -7072,16 +7072,16 @@
         <v>44957</v>
       </c>
       <c r="B333" t="n">
-        <v>78.84564971923828</v>
+        <v>78.84564208984375</v>
       </c>
       <c r="C333" t="n">
-        <v>81.68321755514636</v>
+        <v>81.68320965117834</v>
       </c>
       <c r="D333" t="n">
-        <v>78.84564971923828</v>
+        <v>78.84564208984375</v>
       </c>
       <c r="E333" t="n">
-        <v>80.83984871849243</v>
+        <v>80.83984089613189</v>
       </c>
       <c r="F333" t="n">
         <v>714873</v>
@@ -7092,16 +7092,16 @@
         <v>44958</v>
       </c>
       <c r="B334" t="n">
-        <v>77.84415435791016</v>
+        <v>77.84414672851562</v>
       </c>
       <c r="C334" t="n">
-        <v>79.74171742556558</v>
+        <v>79.74170961019361</v>
       </c>
       <c r="D334" t="n">
-        <v>76.97443823117001</v>
+        <v>76.97443068701511</v>
       </c>
       <c r="E334" t="n">
-        <v>78.62602152176328</v>
+        <v>78.62601381573906</v>
       </c>
       <c r="F334" t="n">
         <v>624239</v>
@@ -7112,16 +7112,16 @@
         <v>44959</v>
       </c>
       <c r="B335" t="n">
-        <v>78.88956451416016</v>
+        <v>78.88957214355469</v>
       </c>
       <c r="C335" t="n">
-        <v>80.39180369577697</v>
+        <v>80.39181147045277</v>
       </c>
       <c r="D335" t="n">
-        <v>77.5630232347126</v>
+        <v>77.56303073581758</v>
       </c>
       <c r="E335" t="n">
-        <v>77.89685192981234</v>
+        <v>77.89685946320182</v>
       </c>
       <c r="F335" t="n">
         <v>645862</v>
@@ -7312,16 +7312,16 @@
         <v>44973</v>
       </c>
       <c r="B345" t="n">
-        <v>71.15873718261719</v>
+        <v>71.15874481201172</v>
       </c>
       <c r="C345" t="n">
-        <v>73.96994387181648</v>
+        <v>73.96995180261891</v>
       </c>
       <c r="D345" t="n">
-        <v>70.32416208182393</v>
+        <v>70.32416962173819</v>
       </c>
       <c r="E345" t="n">
-        <v>73.30228647216005</v>
+        <v>73.30229433137855</v>
       </c>
       <c r="F345" t="n">
         <v>1330447</v>
@@ -7372,16 +7372,16 @@
         <v>44980</v>
       </c>
       <c r="B348" t="n">
-        <v>59.61521530151367</v>
+        <v>59.61521911621094</v>
       </c>
       <c r="C348" t="n">
-        <v>60.55521326210563</v>
+        <v>60.5552171369521</v>
       </c>
       <c r="D348" t="n">
-        <v>58.94755113155375</v>
+        <v>58.94755490352809</v>
       </c>
       <c r="E348" t="n">
-        <v>60.00175877398195</v>
+        <v>60.00176261341363</v>
       </c>
       <c r="F348" t="n">
         <v>572076</v>
@@ -7432,16 +7432,16 @@
         <v>44985</v>
       </c>
       <c r="B351" t="n">
-        <v>56.48774719238281</v>
+        <v>56.48774337768555</v>
       </c>
       <c r="C351" t="n">
-        <v>57.19933249789922</v>
+        <v>57.19932863514759</v>
       </c>
       <c r="D351" t="n">
-        <v>55.53017540979462</v>
+        <v>55.53017165976352</v>
       </c>
       <c r="E351" t="n">
-        <v>56.82157592902526</v>
+        <v>56.82157209178407</v>
       </c>
       <c r="F351" t="n">
         <v>573942</v>
@@ -7452,16 +7452,16 @@
         <v>44986</v>
       </c>
       <c r="B352" t="n">
-        <v>54.14214324951172</v>
+        <v>54.14213943481445</v>
       </c>
       <c r="C352" t="n">
-        <v>57.10269755356158</v>
+        <v>57.10269353027231</v>
       </c>
       <c r="D352" t="n">
-        <v>53.4129841183176</v>
+        <v>53.41298035499475</v>
       </c>
       <c r="E352" t="n">
-        <v>56.4877481070402</v>
+        <v>56.48774412707847</v>
       </c>
       <c r="F352" t="n">
         <v>634515</v>
@@ -7472,16 +7472,16 @@
         <v>44987</v>
       </c>
       <c r="B353" t="n">
-        <v>53.14942932128906</v>
+        <v>53.14943313598633</v>
       </c>
       <c r="C353" t="n">
-        <v>54.59017364603414</v>
+        <v>54.59017756413803</v>
       </c>
       <c r="D353" t="n">
-        <v>52.64868289991359</v>
+        <v>52.64868667867075</v>
       </c>
       <c r="E353" t="n">
-        <v>54.08942722465866</v>
+        <v>54.08943110682245</v>
       </c>
       <c r="F353" t="n">
         <v>1104186</v>
@@ -7492,16 +7492,16 @@
         <v>44988</v>
       </c>
       <c r="B354" t="n">
-        <v>52.3587760925293</v>
+        <v>52.35877227783203</v>
       </c>
       <c r="C354" t="n">
-        <v>54.11578204665744</v>
+        <v>54.11577810395019</v>
       </c>
       <c r="D354" t="n">
-        <v>52.3587760925293</v>
+        <v>52.35877227783203</v>
       </c>
       <c r="E354" t="n">
-        <v>53.14943011237612</v>
+        <v>53.14942624007427</v>
       </c>
       <c r="F354" t="n">
         <v>443497</v>
@@ -7552,16 +7552,16 @@
         <v>44993</v>
       </c>
       <c r="B357" t="n">
-        <v>58.67521667480469</v>
+        <v>58.67521286010742</v>
       </c>
       <c r="C357" t="n">
-        <v>58.67521667480469</v>
+        <v>58.67521286010742</v>
       </c>
       <c r="D357" t="n">
-        <v>53.97522357397903</v>
+        <v>53.97522006484605</v>
       </c>
       <c r="E357" t="n">
-        <v>53.97522357397903</v>
+        <v>53.97522006484605</v>
       </c>
       <c r="F357" t="n">
         <v>1672249</v>
@@ -7592,16 +7592,16 @@
         <v>44995</v>
       </c>
       <c r="B359" t="n">
-        <v>52.01615905761719</v>
+        <v>52.01616287231445</v>
       </c>
       <c r="C359" t="n">
-        <v>56.08362866950537</v>
+        <v>56.08363278249773</v>
       </c>
       <c r="D359" t="n">
-        <v>51.79653331930479</v>
+        <v>51.7965371178954</v>
       </c>
       <c r="E359" t="n">
-        <v>55.52138731562125</v>
+        <v>55.52139138738065</v>
       </c>
       <c r="F359" t="n">
         <v>846843</v>
@@ -7632,16 +7632,16 @@
         <v>44999</v>
       </c>
       <c r="B361" t="n">
-        <v>50.32943725585938</v>
+        <v>50.32943344116211</v>
       </c>
       <c r="C361" t="n">
-        <v>52.78924496516417</v>
+        <v>52.78924096402687</v>
       </c>
       <c r="D361" t="n">
-        <v>49.55635368394428</v>
+        <v>49.55634992784254</v>
       </c>
       <c r="E361" t="n">
-        <v>50.84775415559906</v>
+        <v>50.84775030161619</v>
       </c>
       <c r="F361" t="n">
         <v>730632</v>
@@ -7692,16 +7692,16 @@
         <v>45002</v>
       </c>
       <c r="B364" t="n">
-        <v>55.0645637512207</v>
+        <v>55.06457138061523</v>
       </c>
       <c r="C364" t="n">
-        <v>55.5477396909908</v>
+        <v>55.5477473873311</v>
       </c>
       <c r="D364" t="n">
-        <v>52.19185877680513</v>
+        <v>52.19186600817599</v>
       </c>
       <c r="E364" t="n">
-        <v>53.58867856525999</v>
+        <v>53.58868599016529</v>
       </c>
       <c r="F364" t="n">
         <v>1415773</v>
@@ -7712,16 +7712,16 @@
         <v>45005</v>
       </c>
       <c r="B365" t="n">
-        <v>52.49055480957031</v>
+        <v>52.49055099487305</v>
       </c>
       <c r="C365" t="n">
-        <v>55.60923982257214</v>
+        <v>55.60923578122764</v>
       </c>
       <c r="D365" t="n">
-        <v>52.18308009678171</v>
+        <v>52.18307630442985</v>
       </c>
       <c r="E365" t="n">
-        <v>54.03671863151492</v>
+        <v>54.03671470445178</v>
       </c>
       <c r="F365" t="n">
         <v>714391</v>
@@ -7732,16 +7732,16 @@
         <v>45006</v>
       </c>
       <c r="B366" t="n">
-        <v>54.65166854858398</v>
+        <v>54.65167617797852</v>
       </c>
       <c r="C366" t="n">
-        <v>54.73073394933856</v>
+        <v>54.73074158977065</v>
       </c>
       <c r="D366" t="n">
-        <v>52.65746641952787</v>
+        <v>52.657473770531</v>
       </c>
       <c r="E366" t="n">
-        <v>52.65746641952787</v>
+        <v>52.657473770531</v>
       </c>
       <c r="F366" t="n">
         <v>534854</v>
@@ -7752,16 +7752,16 @@
         <v>45007</v>
       </c>
       <c r="B367" t="n">
-        <v>52.56962203979492</v>
+        <v>52.56961822509766</v>
       </c>
       <c r="C367" t="n">
-        <v>55.12606575176405</v>
+        <v>55.1260617515593</v>
       </c>
       <c r="D367" t="n">
-        <v>52.56962203979492</v>
+        <v>52.56961822509766</v>
       </c>
       <c r="E367" t="n">
-        <v>53.85223567370974</v>
+        <v>53.85223176594004</v>
       </c>
       <c r="F367" t="n">
         <v>930770</v>
@@ -7792,16 +7792,16 @@
         <v>45009</v>
       </c>
       <c r="B369" t="n">
-        <v>50.40850448608398</v>
+        <v>50.40850067138672</v>
       </c>
       <c r="C369" t="n">
-        <v>51.3660729168746</v>
+        <v>51.3660690297127</v>
       </c>
       <c r="D369" t="n">
-        <v>48.82719971216801</v>
+        <v>48.82719601713704</v>
       </c>
       <c r="E369" t="n">
-        <v>50.05710193578128</v>
+        <v>50.05709814767665</v>
       </c>
       <c r="F369" t="n">
         <v>598427</v>
@@ -7812,16 +7812,16 @@
         <v>45012</v>
       </c>
       <c r="B370" t="n">
-        <v>51.84924697875977</v>
+        <v>51.84925079345703</v>
       </c>
       <c r="C370" t="n">
-        <v>52.52569468460005</v>
+        <v>52.5256985490655</v>
       </c>
       <c r="D370" t="n">
-        <v>50.6544823737028</v>
+        <v>50.65448610049781</v>
       </c>
       <c r="E370" t="n">
-        <v>51.39242502087193</v>
+        <v>51.3924288019595</v>
       </c>
       <c r="F370" t="n">
         <v>634884</v>
@@ -7832,16 +7832,16 @@
         <v>45013</v>
       </c>
       <c r="B371" t="n">
-        <v>54.30905532836914</v>
+        <v>54.30905151367188</v>
       </c>
       <c r="C371" t="n">
-        <v>54.44961567467342</v>
+        <v>54.44961185010312</v>
       </c>
       <c r="D371" t="n">
-        <v>51.11130493652956</v>
+        <v>51.111301346444</v>
       </c>
       <c r="E371" t="n">
-        <v>51.83167713024186</v>
+        <v>51.83167348955698</v>
       </c>
       <c r="F371" t="n">
         <v>854484</v>
@@ -7892,16 +7892,16 @@
         <v>45016</v>
       </c>
       <c r="B374" t="n">
-        <v>52.33242034912109</v>
+        <v>52.33242416381836</v>
       </c>
       <c r="C374" t="n">
-        <v>54.73073299523703</v>
+        <v>54.73073698475589</v>
       </c>
       <c r="D374" t="n">
-        <v>51.94588025840541</v>
+        <v>51.94588404492639</v>
       </c>
       <c r="E374" t="n">
-        <v>54.20363256687721</v>
+        <v>54.20363651797383</v>
       </c>
       <c r="F374" t="n">
         <v>558868</v>
@@ -7912,16 +7912,16 @@
         <v>45019</v>
       </c>
       <c r="B375" t="n">
-        <v>49.41579055786133</v>
+        <v>49.41579437255859</v>
       </c>
       <c r="C375" t="n">
-        <v>52.67503567302858</v>
+        <v>52.67503973932627</v>
       </c>
       <c r="D375" t="n">
-        <v>49.41579055786133</v>
+        <v>49.41579437255859</v>
       </c>
       <c r="E375" t="n">
-        <v>52.34999052236814</v>
+        <v>52.34999456357366</v>
       </c>
       <c r="F375" t="n">
         <v>492395</v>
@@ -7972,16 +7972,16 @@
         <v>45022</v>
       </c>
       <c r="B378" t="n">
-        <v>48.04532623291016</v>
+        <v>48.04533004760742</v>
       </c>
       <c r="C378" t="n">
-        <v>49.56513596918133</v>
+        <v>49.56513990454828</v>
       </c>
       <c r="D378" t="n">
-        <v>47.88719543017925</v>
+        <v>47.88719923232127</v>
       </c>
       <c r="E378" t="n">
-        <v>48.64270852073295</v>
+        <v>48.64271238286111</v>
       </c>
       <c r="F378" t="n">
         <v>483494</v>
@@ -8012,16 +8012,16 @@
         <v>45027</v>
       </c>
       <c r="B380" t="n">
-        <v>54.63410186767578</v>
+        <v>54.63409805297852</v>
       </c>
       <c r="C380" t="n">
-        <v>54.63410186767578</v>
+        <v>54.63409805297852</v>
       </c>
       <c r="D380" t="n">
-        <v>48.8535537111691</v>
+        <v>48.85355030008497</v>
       </c>
       <c r="E380" t="n">
-        <v>48.8535537111691</v>
+        <v>48.85355030008497</v>
       </c>
       <c r="F380" t="n">
         <v>1223134</v>
@@ -8032,16 +8032,16 @@
         <v>45028</v>
       </c>
       <c r="B381" t="n">
-        <v>56.73372650146484</v>
+        <v>56.73372268676758</v>
       </c>
       <c r="C381" t="n">
-        <v>57.69129157374931</v>
+        <v>57.69128769466669</v>
       </c>
       <c r="D381" t="n">
-        <v>54.3090562955086</v>
+        <v>54.3090526438428</v>
       </c>
       <c r="E381" t="n">
-        <v>54.55503606811576</v>
+        <v>54.55503239991062</v>
       </c>
       <c r="F381" t="n">
         <v>1443641</v>
@@ -8052,16 +8052,16 @@
         <v>45029</v>
       </c>
       <c r="B382" t="n">
-        <v>60.46736526489258</v>
+        <v>60.46736145019531</v>
       </c>
       <c r="C382" t="n">
-        <v>61.46007127757674</v>
+        <v>61.46006740025275</v>
       </c>
       <c r="D382" t="n">
-        <v>55.96064377509221</v>
+        <v>55.96064024470993</v>
       </c>
       <c r="E382" t="n">
-        <v>56.4086788466054</v>
+        <v>56.408675287958</v>
       </c>
       <c r="F382" t="n">
         <v>2756815</v>
@@ -8092,16 +8092,16 @@
         <v>45033</v>
       </c>
       <c r="B384" t="n">
-        <v>59.95782852172852</v>
+        <v>59.95782089233398</v>
       </c>
       <c r="C384" t="n">
-        <v>60.72212852895193</v>
+        <v>60.72212080230327</v>
       </c>
       <c r="D384" t="n">
-        <v>59.16717449743633</v>
+        <v>59.16716696864937</v>
       </c>
       <c r="E384" t="n">
-        <v>60.35315218265168</v>
+        <v>60.35314450295379</v>
       </c>
       <c r="F384" t="n">
         <v>288592</v>
@@ -8112,16 +8112,16 @@
         <v>45034</v>
       </c>
       <c r="B385" t="n">
-        <v>61.49520874023438</v>
+        <v>61.49520492553711</v>
       </c>
       <c r="C385" t="n">
-        <v>61.49520874023438</v>
+        <v>61.49520492553711</v>
       </c>
       <c r="D385" t="n">
-        <v>59.16717449743633</v>
+        <v>59.16717082715269</v>
       </c>
       <c r="E385" t="n">
-        <v>59.16717449743633</v>
+        <v>59.16717082715269</v>
       </c>
       <c r="F385" t="n">
         <v>581190</v>
@@ -8132,16 +8132,16 @@
         <v>45035</v>
       </c>
       <c r="B386" t="n">
-        <v>58.84213638305664</v>
+        <v>58.84213256835938</v>
       </c>
       <c r="C386" t="n">
-        <v>61.2755868471204</v>
+        <v>61.27558287466414</v>
       </c>
       <c r="D386" t="n">
-        <v>58.30624899414777</v>
+        <v>58.30624521419173</v>
       </c>
       <c r="E386" t="n">
-        <v>61.2755868471204</v>
+        <v>61.27558287466414</v>
       </c>
       <c r="F386" t="n">
         <v>827950</v>
@@ -8172,16 +8172,16 @@
         <v>45040</v>
       </c>
       <c r="B388" t="n">
-        <v>60.99446105957031</v>
+        <v>60.99446868896484</v>
       </c>
       <c r="C388" t="n">
-        <v>61.27558173995688</v>
+        <v>61.27558940451494</v>
       </c>
       <c r="D388" t="n">
-        <v>59.73820155293286</v>
+        <v>59.73820902519019</v>
       </c>
       <c r="E388" t="n">
-        <v>60.2740888971769</v>
+        <v>60.27409643646482</v>
       </c>
       <c r="F388" t="n">
         <v>315786</v>
@@ -8192,16 +8192,16 @@
         <v>45041</v>
       </c>
       <c r="B389" t="n">
-        <v>60.50250625610352</v>
+        <v>60.50250244140625</v>
       </c>
       <c r="C389" t="n">
-        <v>61.28437341876753</v>
+        <v>61.28436955477335</v>
       </c>
       <c r="D389" t="n">
-        <v>59.00904707951048</v>
+        <v>59.00904335897617</v>
       </c>
       <c r="E389" t="n">
-        <v>61.28437341876753</v>
+        <v>61.28436955477335</v>
       </c>
       <c r="F389" t="n">
         <v>695154</v>
@@ -8212,16 +8212,16 @@
         <v>45042</v>
       </c>
       <c r="B390" t="n">
-        <v>59.3165168762207</v>
+        <v>59.31652069091797</v>
       </c>
       <c r="C390" t="n">
-        <v>60.01932192479727</v>
+        <v>60.01932578469255</v>
       </c>
       <c r="D390" t="n">
-        <v>56.95334847283447</v>
+        <v>56.9533521355543</v>
       </c>
       <c r="E390" t="n">
-        <v>59.30773667238661</v>
+        <v>59.30774048651921</v>
       </c>
       <c r="F390" t="n">
         <v>963997</v>
@@ -8232,16 +8232,16 @@
         <v>45043</v>
       </c>
       <c r="B391" t="n">
-        <v>61.50399780273438</v>
+        <v>61.50399398803711</v>
       </c>
       <c r="C391" t="n">
-        <v>62.82175232193269</v>
+        <v>62.82174842550359</v>
       </c>
       <c r="D391" t="n">
-        <v>58.446804369118</v>
+        <v>58.44680074403878</v>
       </c>
       <c r="E391" t="n">
-        <v>58.59614827270675</v>
+        <v>58.59614463836468</v>
       </c>
       <c r="F391" t="n">
         <v>723893</v>
@@ -8252,16 +8252,16 @@
         <v>45044</v>
       </c>
       <c r="B392" t="n">
-        <v>63.67390060424805</v>
+        <v>63.67390441894531</v>
       </c>
       <c r="C392" t="n">
-        <v>63.75296265734114</v>
+        <v>63.75296647677501</v>
       </c>
       <c r="D392" t="n">
-        <v>60.61670720484071</v>
+        <v>60.61671083638181</v>
       </c>
       <c r="E392" t="n">
-        <v>61.50399711452398</v>
+        <v>61.50400079922254</v>
       </c>
       <c r="F392" t="n">
         <v>633625</v>
@@ -8312,16 +8312,16 @@
         <v>45050</v>
       </c>
       <c r="B395" t="n">
-        <v>60.79240417480469</v>
+        <v>60.79240036010742</v>
       </c>
       <c r="C395" t="n">
-        <v>61.56549109490604</v>
+        <v>61.5654872316979</v>
       </c>
       <c r="D395" t="n">
-        <v>58.60493360826845</v>
+        <v>58.60492993083402</v>
       </c>
       <c r="E395" t="n">
-        <v>58.60493360826845</v>
+        <v>58.60492993083402</v>
       </c>
       <c r="F395" t="n">
         <v>661928</v>
@@ -8332,16 +8332,16 @@
         <v>45051</v>
       </c>
       <c r="B396" t="n">
-        <v>64.07801055908203</v>
+        <v>64.07801818847656</v>
       </c>
       <c r="C396" t="n">
-        <v>64.75445491572299</v>
+        <v>64.75446262565779</v>
       </c>
       <c r="D396" t="n">
-        <v>60.79240453412326</v>
+        <v>60.79241177231987</v>
       </c>
       <c r="E396" t="n">
-        <v>60.79240453412326</v>
+        <v>60.79241177231987</v>
       </c>
       <c r="F396" t="n">
         <v>739601</v>
@@ -8372,16 +8372,16 @@
         <v>45055</v>
       </c>
       <c r="B398" t="n">
-        <v>66.17762756347656</v>
+        <v>66.17763519287109</v>
       </c>
       <c r="C398" t="n">
-        <v>67.59201782205866</v>
+        <v>67.59202561451346</v>
       </c>
       <c r="D398" t="n">
-        <v>64.157068136232</v>
+        <v>64.15707553268307</v>
       </c>
       <c r="E398" t="n">
-        <v>65.00921705378778</v>
+        <v>65.00922454848022</v>
       </c>
       <c r="F398" t="n">
         <v>730723</v>
@@ -8392,16 +8392,16 @@
         <v>45056</v>
       </c>
       <c r="B399" t="n">
-        <v>68.46174621582031</v>
+        <v>68.46173858642578</v>
       </c>
       <c r="C399" t="n">
-        <v>68.48810023618428</v>
+        <v>68.48809260385286</v>
       </c>
       <c r="D399" t="n">
-        <v>66.18641972266146</v>
+        <v>66.1864123468299</v>
       </c>
       <c r="E399" t="n">
-        <v>66.78380209321604</v>
+        <v>66.78379465081203</v>
       </c>
       <c r="F399" t="n">
         <v>406791</v>
@@ -8432,16 +8432,16 @@
         <v>45058</v>
       </c>
       <c r="B401" t="n">
-        <v>66.23033142089844</v>
+        <v>66.23033905029297</v>
       </c>
       <c r="C401" t="n">
-        <v>67.00341154047932</v>
+        <v>67.00341925892872</v>
       </c>
       <c r="D401" t="n">
-        <v>65.81743399594278</v>
+        <v>65.81744157777364</v>
       </c>
       <c r="E401" t="n">
-        <v>66.79257272649272</v>
+        <v>66.79258042065457</v>
       </c>
       <c r="F401" t="n">
         <v>398348</v>
@@ -8472,16 +8472,16 @@
         <v>45062</v>
       </c>
       <c r="B403" t="n">
-        <v>69.20845794677734</v>
+        <v>69.20846557617188</v>
       </c>
       <c r="C403" t="n">
-        <v>74.04022393567588</v>
+        <v>74.04023209771412</v>
       </c>
       <c r="D403" t="n">
-        <v>67.52173397378508</v>
+        <v>67.52174141723872</v>
       </c>
       <c r="E403" t="n">
-        <v>69.22603175828814</v>
+        <v>69.22603938961998</v>
       </c>
       <c r="F403" t="n">
         <v>1416795</v>
@@ -8492,16 +8492,16 @@
         <v>45063</v>
       </c>
       <c r="B404" t="n">
-        <v>72.32714080810547</v>
+        <v>72.3271484375</v>
       </c>
       <c r="C404" t="n">
-        <v>73.79423895007376</v>
+        <v>73.79424673422444</v>
       </c>
       <c r="D404" t="n">
-        <v>67.66228614538477</v>
+        <v>67.6622932827093</v>
       </c>
       <c r="E404" t="n">
-        <v>69.41051163198605</v>
+        <v>69.41051895372132</v>
       </c>
       <c r="F404" t="n">
         <v>1084227</v>
@@ -8512,16 +8512,16 @@
         <v>45064</v>
       </c>
       <c r="B405" t="n">
-        <v>71.18509674072266</v>
+        <v>71.18508911132812</v>
       </c>
       <c r="C405" t="n">
-        <v>71.99331788899191</v>
+        <v>71.99331017297479</v>
       </c>
       <c r="D405" t="n">
-        <v>69.86734224584828</v>
+        <v>69.86733475768652</v>
       </c>
       <c r="E405" t="n">
-        <v>71.15874272321652</v>
+        <v>71.15873509664654</v>
       </c>
       <c r="F405" t="n">
         <v>796674</v>
@@ -8532,16 +8532,16 @@
         <v>45065</v>
       </c>
       <c r="B406" t="n">
-        <v>75.91144561767578</v>
+        <v>75.91145324707031</v>
       </c>
       <c r="C406" t="n">
-        <v>76.42975915801013</v>
+        <v>76.42976683949719</v>
       </c>
       <c r="D406" t="n">
-        <v>71.19388220849052</v>
+        <v>71.19388936375165</v>
       </c>
       <c r="E406" t="n">
-        <v>71.19388220849052</v>
+        <v>71.19388936375165</v>
       </c>
       <c r="F406" t="n">
         <v>1201246</v>
@@ -8592,16 +8592,16 @@
         <v>45070</v>
       </c>
       <c r="B409" t="n">
-        <v>77.30825805664062</v>
+        <v>77.30827331542969</v>
       </c>
       <c r="C409" t="n">
-        <v>78.27460994185954</v>
+        <v>78.2746253913832</v>
       </c>
       <c r="D409" t="n">
-        <v>75.96414964236531</v>
+        <v>75.96416463585973</v>
       </c>
       <c r="E409" t="n">
-        <v>76.61423993570233</v>
+        <v>76.61425505750891</v>
       </c>
       <c r="F409" t="n">
         <v>567398</v>
@@ -8632,16 +8632,16 @@
         <v>45072</v>
       </c>
       <c r="B411" t="n">
-        <v>82.75497436523438</v>
+        <v>82.75498199462891</v>
       </c>
       <c r="C411" t="n">
-        <v>84.15179752676379</v>
+        <v>84.15180528493505</v>
       </c>
       <c r="D411" t="n">
-        <v>80.38301910539758</v>
+        <v>80.38302651611544</v>
       </c>
       <c r="E411" t="n">
-        <v>81.70077351696148</v>
+        <v>81.70078104916651</v>
       </c>
       <c r="F411" t="n">
         <v>582166</v>
@@ -8652,16 +8652,16 @@
         <v>45075</v>
       </c>
       <c r="B412" t="n">
-        <v>81.52507781982422</v>
+        <v>81.52508544921875</v>
       </c>
       <c r="C412" t="n">
-        <v>83.1678740745439</v>
+        <v>83.1678818576769</v>
       </c>
       <c r="D412" t="n">
-        <v>80.73442381096265</v>
+        <v>80.73443136636509</v>
       </c>
       <c r="E412" t="n">
-        <v>82.66712765267252</v>
+        <v>82.66713538894396</v>
       </c>
       <c r="F412" t="n">
         <v>275309</v>
@@ -8672,16 +8672,16 @@
         <v>45076</v>
       </c>
       <c r="B413" t="n">
-        <v>80.55872344970703</v>
+        <v>80.55873107910156</v>
       </c>
       <c r="C413" t="n">
-        <v>84.13423043735499</v>
+        <v>84.13423840537149</v>
       </c>
       <c r="D413" t="n">
-        <v>79.3990997429684</v>
+        <v>79.3991072625396</v>
       </c>
       <c r="E413" t="n">
-        <v>82.54414213179378</v>
+        <v>82.54414994921937</v>
       </c>
       <c r="F413" t="n">
         <v>664894</v>
@@ -8692,16 +8692,16 @@
         <v>45077</v>
       </c>
       <c r="B414" t="n">
-        <v>78.81928253173828</v>
+        <v>78.81929016113281</v>
       </c>
       <c r="C414" t="n">
-        <v>80.38301664656991</v>
+        <v>80.38302442732773</v>
       </c>
       <c r="D414" t="n">
-        <v>78.53816186730164</v>
+        <v>78.53816946948481</v>
       </c>
       <c r="E414" t="n">
-        <v>79.97890611034508</v>
+        <v>79.97891385198659</v>
       </c>
       <c r="F414" t="n">
         <v>527775</v>
@@ -8772,16 +8772,16 @@
         <v>45083</v>
       </c>
       <c r="B418" t="n">
-        <v>83.89702606201172</v>
+        <v>83.89703369140625</v>
       </c>
       <c r="C418" t="n">
-        <v>86.70823263127907</v>
+        <v>86.708240516318</v>
       </c>
       <c r="D418" t="n">
-        <v>81.92039455793291</v>
+        <v>81.92040200757731</v>
       </c>
       <c r="E418" t="n">
-        <v>82.01703041210571</v>
+        <v>82.01703787053793</v>
       </c>
       <c r="F418" t="n">
         <v>1573579</v>
@@ -8832,16 +8832,16 @@
         <v>45089</v>
       </c>
       <c r="B421" t="n">
-        <v>90.35403442382812</v>
+        <v>90.35404205322266</v>
       </c>
       <c r="C421" t="n">
-        <v>91.34674712772208</v>
+        <v>91.34675484094018</v>
       </c>
       <c r="D421" t="n">
-        <v>87.95572492842221</v>
+        <v>87.95573235530614</v>
       </c>
       <c r="E421" t="n">
-        <v>87.95572492842221</v>
+        <v>87.95573235530614</v>
       </c>
       <c r="F421" t="n">
         <v>1071620</v>
@@ -8852,16 +8852,16 @@
         <v>45090</v>
       </c>
       <c r="B422" t="n">
-        <v>86.91908264160156</v>
+        <v>86.91909027099609</v>
       </c>
       <c r="C422" t="n">
-        <v>91.17982054115261</v>
+        <v>91.17982854453695</v>
       </c>
       <c r="D422" t="n">
-        <v>86.91908264160156</v>
+        <v>86.91909027099609</v>
       </c>
       <c r="E422" t="n">
-        <v>90.48580241734746</v>
+        <v>90.48581035981377</v>
       </c>
       <c r="F422" t="n">
         <v>519950</v>
@@ -8872,16 +8872,16 @@
         <v>45091</v>
       </c>
       <c r="B423" t="n">
-        <v>89.40525054931641</v>
+        <v>89.40524291992188</v>
       </c>
       <c r="C423" t="n">
-        <v>89.44039147486313</v>
+        <v>89.44038384246984</v>
       </c>
       <c r="D423" t="n">
-        <v>87.26170771053611</v>
+        <v>87.26170026406075</v>
       </c>
       <c r="E423" t="n">
-        <v>87.54282841246366</v>
+        <v>87.54282094199888</v>
       </c>
       <c r="F423" t="n">
         <v>605932</v>
@@ -8892,16 +8892,16 @@
         <v>45092</v>
       </c>
       <c r="B424" t="n">
-        <v>91.97925567626953</v>
+        <v>91.97927093505859</v>
       </c>
       <c r="C424" t="n">
-        <v>92.26037635061984</v>
+        <v>92.26039165604509</v>
       </c>
       <c r="D424" t="n">
-        <v>89.18561604259341</v>
+        <v>89.18563083793495</v>
       </c>
       <c r="E424" t="n">
-        <v>89.4316024972898</v>
+        <v>89.43161733343898</v>
       </c>
       <c r="F424" t="n">
         <v>844482</v>
@@ -8992,16 +8992,16 @@
         <v>45099</v>
       </c>
       <c r="B429" t="n">
-        <v>99.27084350585938</v>
+        <v>99.27083587646484</v>
       </c>
       <c r="C429" t="n">
-        <v>104.8581233756592</v>
+        <v>104.858115316858</v>
       </c>
       <c r="D429" t="n">
-        <v>99.18299454236116</v>
+        <v>99.18298691971819</v>
       </c>
       <c r="E429" t="n">
-        <v>102.9605535923553</v>
+        <v>102.9605456793905</v>
       </c>
       <c r="F429" t="n">
         <v>1144936</v>
@@ -9012,16 +9012,16 @@
         <v>45100</v>
       </c>
       <c r="B430" t="n">
-        <v>98.56803894042969</v>
+        <v>98.56803131103516</v>
       </c>
       <c r="C430" t="n">
-        <v>100.5446707911264</v>
+        <v>100.544663008736</v>
       </c>
       <c r="D430" t="n">
-        <v>97.24150416861238</v>
+        <v>97.24149664189471</v>
       </c>
       <c r="E430" t="n">
-        <v>99.71009557958853</v>
+        <v>99.71008786179617</v>
       </c>
       <c r="F430" t="n">
         <v>1883788</v>
@@ -9032,16 +9032,16 @@
         <v>45103</v>
       </c>
       <c r="B431" t="n">
-        <v>97.00429534912109</v>
+        <v>97.00428771972656</v>
       </c>
       <c r="C431" t="n">
-        <v>99.27083459718358</v>
+        <v>99.27082678952559</v>
       </c>
       <c r="D431" t="n">
-        <v>95.75682275303549</v>
+        <v>95.75681522175476</v>
       </c>
       <c r="E431" t="n">
-        <v>98.46261348161649</v>
+        <v>98.46260573752514</v>
       </c>
       <c r="F431" t="n">
         <v>757098</v>
@@ -9072,16 +9072,16 @@
         <v>45105</v>
       </c>
       <c r="B433" t="n">
-        <v>97.09214782714844</v>
+        <v>97.09215545654297</v>
       </c>
       <c r="C433" t="n">
-        <v>98.19027656828381</v>
+        <v>98.19028428396808</v>
       </c>
       <c r="D433" t="n">
-        <v>94.29850804160222</v>
+        <v>94.29851545147561</v>
       </c>
       <c r="E433" t="n">
-        <v>94.47421266165144</v>
+        <v>94.4742200853315</v>
       </c>
       <c r="F433" t="n">
         <v>538862</v>
@@ -9112,16 +9112,16 @@
         <v>45107</v>
       </c>
       <c r="B435" t="n">
-        <v>98.43625640869141</v>
+        <v>98.43626403808594</v>
       </c>
       <c r="C435" t="n">
-        <v>101.4758757552046</v>
+        <v>101.4758836201877</v>
       </c>
       <c r="D435" t="n">
-        <v>98.40111548704759</v>
+        <v>98.40112311371848</v>
       </c>
       <c r="E435" t="n">
-        <v>100.67643486831</v>
+        <v>100.6764426713316</v>
       </c>
       <c r="F435" t="n">
         <v>851232</v>
@@ -9172,16 +9172,16 @@
         <v>45112</v>
       </c>
       <c r="B438" t="n">
-        <v>101.2386932373047</v>
+        <v>101.2386779785156</v>
       </c>
       <c r="C438" t="n">
-        <v>101.7042987981171</v>
+        <v>101.7042834691515</v>
       </c>
       <c r="D438" t="n">
-        <v>99.13028450117518</v>
+        <v>99.13026956016742</v>
       </c>
       <c r="E438" t="n">
-        <v>99.53440181682589</v>
+        <v>99.5343868149092</v>
       </c>
       <c r="F438" t="n">
         <v>519657</v>
@@ -9212,16 +9212,16 @@
         <v>45114</v>
       </c>
       <c r="B440" t="n">
-        <v>101.2386932373047</v>
+        <v>101.2386779785156</v>
       </c>
       <c r="C440" t="n">
-        <v>102.0820553912672</v>
+        <v>102.0820400053658</v>
       </c>
       <c r="D440" t="n">
-        <v>98.16393245199608</v>
+        <v>98.16391765663779</v>
       </c>
       <c r="E440" t="n">
-        <v>98.73496079547128</v>
+        <v>98.73494591404707</v>
       </c>
       <c r="F440" t="n">
         <v>1239341</v>
@@ -9232,16 +9232,16 @@
         <v>45117</v>
       </c>
       <c r="B441" t="n">
-        <v>98.26055145263672</v>
+        <v>98.26055908203125</v>
       </c>
       <c r="C441" t="n">
-        <v>100.7467163549612</v>
+        <v>100.7467241773928</v>
       </c>
       <c r="D441" t="n">
-        <v>97.19756371084451</v>
+        <v>97.19757125770386</v>
       </c>
       <c r="E441" t="n">
-        <v>100.7467163549612</v>
+        <v>100.7467241773928</v>
       </c>
       <c r="F441" t="n">
         <v>1057552</v>
@@ -9272,16 +9272,16 @@
         <v>45119</v>
       </c>
       <c r="B443" t="n">
-        <v>99.29718780517578</v>
+        <v>99.29719543457031</v>
       </c>
       <c r="C443" t="n">
-        <v>102.0644734504011</v>
+        <v>102.0644812924171</v>
       </c>
       <c r="D443" t="n">
-        <v>98.57681565108831</v>
+        <v>98.57682322513379</v>
       </c>
       <c r="E443" t="n">
-        <v>99.10391608292989</v>
+        <v>99.10392369747458</v>
       </c>
       <c r="F443" t="n">
         <v>690662</v>
@@ -9292,16 +9292,16 @@
         <v>45120</v>
       </c>
       <c r="B444" t="n">
-        <v>97.98822021484375</v>
+        <v>97.98822784423828</v>
       </c>
       <c r="C444" t="n">
-        <v>101.0893345675846</v>
+        <v>101.0893424384329</v>
       </c>
       <c r="D444" t="n">
-        <v>97.21514002882437</v>
+        <v>97.21514759802663</v>
       </c>
       <c r="E444" t="n">
-        <v>99.32354175477643</v>
+        <v>99.32354948813953</v>
       </c>
       <c r="F444" t="n">
         <v>738822</v>
@@ -9352,16 +9352,16 @@
         <v>45125</v>
       </c>
       <c r="B447" t="n">
-        <v>101.4231643676758</v>
+        <v>101.4231719970703</v>
       </c>
       <c r="C447" t="n">
-        <v>103.6633496036482</v>
+        <v>103.663357401557</v>
       </c>
       <c r="D447" t="n">
-        <v>98.74373435277772</v>
+        <v>98.74374178061643</v>
       </c>
       <c r="E447" t="n">
-        <v>99.27083478993424</v>
+        <v>99.27084225742324</v>
       </c>
       <c r="F447" t="n">
         <v>594813</v>
@@ -9372,16 +9372,16 @@
         <v>45126</v>
       </c>
       <c r="B448" t="n">
-        <v>101.06298828125</v>
+        <v>101.0629806518555</v>
       </c>
       <c r="C448" t="n">
-        <v>101.2650402225924</v>
+        <v>101.2650325779447</v>
       </c>
       <c r="D448" t="n">
-        <v>99.00728772803575</v>
+        <v>99.00728025382909</v>
       </c>
       <c r="E448" t="n">
-        <v>100.8257887123484</v>
+        <v>100.8257811008604</v>
       </c>
       <c r="F448" t="n">
         <v>1189852</v>
@@ -9392,16 +9392,16 @@
         <v>45127</v>
       </c>
       <c r="B449" t="n">
-        <v>106.9138107299805</v>
+        <v>106.913818359375</v>
       </c>
       <c r="C449" t="n">
-        <v>107.2740001714642</v>
+        <v>107.2740078265619</v>
       </c>
       <c r="D449" t="n">
-        <v>100.3601792578093</v>
+        <v>100.3601864195351</v>
       </c>
       <c r="E449" t="n">
-        <v>100.4919560462166</v>
+        <v>100.4919632173461</v>
       </c>
       <c r="F449" t="n">
         <v>1906043</v>
@@ -9412,16 +9412,16 @@
         <v>45128</v>
       </c>
       <c r="B450" t="n">
-        <v>111.3941802978516</v>
+        <v>111.3941879272461</v>
       </c>
       <c r="C450" t="n">
-        <v>111.3941802978516</v>
+        <v>111.3941879272461</v>
       </c>
       <c r="D450" t="n">
-        <v>106.0353067697835</v>
+        <v>106.0353140321484</v>
       </c>
       <c r="E450" t="n">
-        <v>106.7556789436875</v>
+        <v>106.7556862553908</v>
       </c>
       <c r="F450" t="n">
         <v>688364</v>
@@ -9432,16 +9432,16 @@
         <v>45131</v>
       </c>
       <c r="B451" t="n">
-        <v>112.6240768432617</v>
+        <v>112.6240844726562</v>
       </c>
       <c r="C451" t="n">
-        <v>113.1160363563073</v>
+        <v>113.1160440190282</v>
       </c>
       <c r="D451" t="n">
-        <v>109.3033367253127</v>
+        <v>109.3033441297533</v>
       </c>
       <c r="E451" t="n">
-        <v>110.8582907186036</v>
+        <v>110.85829822838</v>
       </c>
       <c r="F451" t="n">
         <v>870351</v>
@@ -9452,16 +9452,16 @@
         <v>45132</v>
       </c>
       <c r="B452" t="n">
-        <v>112.1584777832031</v>
+        <v>112.1584701538086</v>
       </c>
       <c r="C452" t="n">
-        <v>115.3298741884703</v>
+        <v>115.3298663433468</v>
       </c>
       <c r="D452" t="n">
-        <v>110.5859565895362</v>
+        <v>110.5859490671098</v>
       </c>
       <c r="E452" t="n">
-        <v>112.9491385358792</v>
+        <v>112.9491308527013</v>
       </c>
       <c r="F452" t="n">
         <v>603712</v>
@@ -9492,16 +9492,16 @@
         <v>45134</v>
       </c>
       <c r="B454" t="n">
-        <v>110.7440795898438</v>
+        <v>110.7440872192383</v>
       </c>
       <c r="C454" t="n">
-        <v>114.6446348276118</v>
+        <v>114.6446427257238</v>
       </c>
       <c r="D454" t="n">
-        <v>109.7074458420786</v>
+        <v>109.7074534000573</v>
       </c>
       <c r="E454" t="n">
-        <v>113.5025783131018</v>
+        <v>113.5025861325351</v>
       </c>
       <c r="F454" t="n">
         <v>678181</v>
@@ -9512,16 +9512,16 @@
         <v>45135</v>
       </c>
       <c r="B455" t="n">
-        <v>109.8919372558594</v>
+        <v>109.8919448852539</v>
       </c>
       <c r="C455" t="n">
-        <v>111.9915655959889</v>
+        <v>111.9915733711529</v>
       </c>
       <c r="D455" t="n">
-        <v>108.0558691996412</v>
+        <v>108.0558767015642</v>
       </c>
       <c r="E455" t="n">
-        <v>110.6913782045105</v>
+        <v>110.6913858894073</v>
       </c>
       <c r="F455" t="n">
         <v>651013</v>
@@ -9532,16 +9532,16 @@
         <v>45138</v>
       </c>
       <c r="B456" t="n">
-        <v>111.8246459960938</v>
+        <v>111.8246536254883</v>
       </c>
       <c r="C456" t="n">
-        <v>115.0838912728874</v>
+        <v>115.0838991246485</v>
       </c>
       <c r="D456" t="n">
-        <v>110.7792252970001</v>
+        <v>110.7792328550693</v>
       </c>
       <c r="E456" t="n">
-        <v>112.6416540419304</v>
+        <v>112.6416617270665</v>
       </c>
       <c r="F456" t="n">
         <v>524630</v>
@@ -9552,16 +9552,16 @@
         <v>45139</v>
       </c>
       <c r="B457" t="n">
-        <v>113.2302627563477</v>
+        <v>113.2302551269531</v>
       </c>
       <c r="C457" t="n">
-        <v>113.6343800759808</v>
+        <v>113.6343724193571</v>
       </c>
       <c r="D457" t="n">
-        <v>109.1803629744492</v>
+        <v>109.1803556179347</v>
       </c>
       <c r="E457" t="n">
-        <v>111.5698924521143</v>
+        <v>111.5698849345946</v>
       </c>
       <c r="F457" t="n">
         <v>739423</v>
@@ -9592,16 +9592,16 @@
         <v>45141</v>
       </c>
       <c r="B459" t="n">
-        <v>114.7939834594727</v>
+        <v>114.7939910888672</v>
       </c>
       <c r="C459" t="n">
-        <v>117.3065025331647</v>
+        <v>117.3065103295453</v>
       </c>
       <c r="D459" t="n">
-        <v>111.8597867062838</v>
+        <v>111.8597941406668</v>
       </c>
       <c r="E459" t="n">
-        <v>112.9227678115621</v>
+        <v>112.9227753165926</v>
       </c>
       <c r="F459" t="n">
         <v>1277901</v>
@@ -9612,16 +9612,16 @@
         <v>45142</v>
       </c>
       <c r="B460" t="n">
-        <v>113.1336212158203</v>
+        <v>113.1336135864258</v>
       </c>
       <c r="C460" t="n">
-        <v>114.6007196943687</v>
+        <v>114.6007119660374</v>
       </c>
       <c r="D460" t="n">
-        <v>110.9900716383365</v>
+        <v>110.9900641534965</v>
       </c>
       <c r="E460" t="n">
-        <v>114.2053960045622</v>
+        <v>114.2053883028904</v>
       </c>
       <c r="F460" t="n">
         <v>805649</v>
@@ -9652,16 +9652,16 @@
         <v>45146</v>
       </c>
       <c r="B462" t="n">
-        <v>113.590446472168</v>
+        <v>113.5904388427734</v>
       </c>
       <c r="C462" t="n">
-        <v>113.590446472168</v>
+        <v>113.5904388427734</v>
       </c>
       <c r="D462" t="n">
-        <v>109.3033473202589</v>
+        <v>109.3033399788109</v>
       </c>
       <c r="E462" t="n">
-        <v>111.8685746047133</v>
+        <v>111.8685670909697</v>
       </c>
       <c r="F462" t="n">
         <v>457201</v>
@@ -9692,16 +9692,16 @@
         <v>45148</v>
       </c>
       <c r="B464" t="n">
-        <v>110.5156784057617</v>
+        <v>110.5156860351562</v>
       </c>
       <c r="C464" t="n">
-        <v>114.5919317277774</v>
+        <v>114.5919396385741</v>
       </c>
       <c r="D464" t="n">
-        <v>109.2857728839157</v>
+        <v>109.2857804284043</v>
       </c>
       <c r="E464" t="n">
-        <v>111.7455772251619</v>
+        <v>111.7455849394619</v>
       </c>
       <c r="F464" t="n">
         <v>733254</v>
@@ -9712,16 +9712,16 @@
         <v>45149</v>
       </c>
       <c r="B465" t="n">
-        <v>109.8128814697266</v>
+        <v>109.812873840332</v>
       </c>
       <c r="C465" t="n">
-        <v>111.9915719871623</v>
+        <v>111.9915642064004</v>
       </c>
       <c r="D465" t="n">
-        <v>108.1261572189387</v>
+        <v>108.1261497067316</v>
       </c>
       <c r="E465" t="n">
-        <v>110.7353123550508</v>
+        <v>110.7353046615692</v>
       </c>
       <c r="F465" t="n">
         <v>577766</v>
@@ -9792,16 +9792,16 @@
         <v>45155</v>
       </c>
       <c r="B469" t="n">
-        <v>103.6633605957031</v>
+        <v>103.6633529663086</v>
       </c>
       <c r="C469" t="n">
-        <v>109.7689541532003</v>
+        <v>109.7689460744476</v>
       </c>
       <c r="D469" t="n">
-        <v>103.0484111375546</v>
+        <v>103.048403553419</v>
       </c>
       <c r="E469" t="n">
-        <v>108.9783067648512</v>
+        <v>108.9782987442884</v>
       </c>
       <c r="F469" t="n">
         <v>1841816</v>
@@ -9812,16 +9812,16 @@
         <v>45156</v>
       </c>
       <c r="B470" t="n">
-        <v>109.1539993286133</v>
+        <v>109.1539916992188</v>
       </c>
       <c r="C470" t="n">
-        <v>109.2242811782168</v>
+        <v>109.2242735439098</v>
       </c>
       <c r="D470" t="n">
-        <v>104.6912024154841</v>
+        <v>104.6911950980199</v>
       </c>
       <c r="E470" t="n">
-        <v>106.2549367057079</v>
+        <v>106.2549292789454</v>
       </c>
       <c r="F470" t="n">
         <v>1642163</v>
@@ -9832,16 +9832,16 @@
         <v>45159</v>
       </c>
       <c r="B471" t="n">
-        <v>111.3941802978516</v>
+        <v>111.3941879272461</v>
       </c>
       <c r="C471" t="n">
-        <v>111.4556752382173</v>
+        <v>111.4556828718236</v>
       </c>
       <c r="D471" t="n">
-        <v>108.0997941301601</v>
+        <v>108.0998015339219</v>
       </c>
       <c r="E471" t="n">
-        <v>109.153995022843</v>
+        <v>109.1540024988072</v>
       </c>
       <c r="F471" t="n">
         <v>967109</v>
@@ -9852,16 +9852,16 @@
         <v>45160</v>
       </c>
       <c r="B472" t="n">
-        <v>113.9594116210938</v>
+        <v>113.9594192504883</v>
       </c>
       <c r="C472" t="n">
-        <v>114.0033394526074</v>
+        <v>114.0033470849429</v>
       </c>
       <c r="D472" t="n">
-        <v>111.1745586857447</v>
+        <v>111.174566128698</v>
       </c>
       <c r="E472" t="n">
-        <v>111.534741434862</v>
+        <v>111.5347489019289</v>
       </c>
       <c r="F472" t="n">
         <v>933012</v>
@@ -9932,16 +9932,16 @@
         <v>45166</v>
       </c>
       <c r="B476" t="n">
-        <v>110.9549331665039</v>
+        <v>110.9549255371094</v>
       </c>
       <c r="C476" t="n">
-        <v>111.4820336335469</v>
+        <v>111.4820259679083</v>
       </c>
       <c r="D476" t="n">
-        <v>109.5493229844612</v>
+        <v>109.5493154517181</v>
       </c>
       <c r="E476" t="n">
-        <v>110.3399770362487</v>
+        <v>110.3399694491393</v>
       </c>
       <c r="F476" t="n">
         <v>1603475</v>
@@ -9952,16 +9952,16 @@
         <v>45167</v>
       </c>
       <c r="B477" t="n">
-        <v>113.3180999755859</v>
+        <v>113.3181076049805</v>
       </c>
       <c r="C477" t="n">
-        <v>113.3620143990293</v>
+        <v>113.3620220313805</v>
       </c>
       <c r="D477" t="n">
-        <v>109.4263249492729</v>
+        <v>109.426332316645</v>
       </c>
       <c r="E477" t="n">
-        <v>112.0091257586069</v>
+        <v>112.0091332998718</v>
       </c>
       <c r="F477" t="n">
         <v>768114</v>
@@ -10012,16 +10012,16 @@
         <v>45170</v>
       </c>
       <c r="B480" t="n">
-        <v>113.7397842407227</v>
+        <v>113.7397918701172</v>
       </c>
       <c r="C480" t="n">
-        <v>115.5670720854272</v>
+        <v>115.5670798373918</v>
       </c>
       <c r="D480" t="n">
-        <v>109.320915232503</v>
+        <v>109.3209225654903</v>
       </c>
       <c r="E480" t="n">
-        <v>110.2609131724079</v>
+        <v>110.260920568448</v>
       </c>
       <c r="F480" t="n">
         <v>5149038</v>
@@ -10032,16 +10032,16 @@
         <v>45173</v>
       </c>
       <c r="B481" t="n">
-        <v>113.3268890380859</v>
+        <v>113.3268814086914</v>
       </c>
       <c r="C481" t="n">
-        <v>115.4704385414185</v>
+        <v>115.4704307677159</v>
       </c>
       <c r="D481" t="n">
-        <v>112.711939608005</v>
+        <v>112.7119320200101</v>
       </c>
       <c r="E481" t="n">
-        <v>114.3020279218186</v>
+        <v>114.3020202267758</v>
       </c>
       <c r="F481" t="n">
         <v>279175</v>
@@ -10092,16 +10092,16 @@
         <v>45177</v>
       </c>
       <c r="B484" t="n">
-        <v>108.5126953125</v>
+        <v>108.5126876831055</v>
       </c>
       <c r="C484" t="n">
-        <v>110.7968086365694</v>
+        <v>110.7968008465816</v>
       </c>
       <c r="D484" t="n">
-        <v>106.7293351683192</v>
+        <v>106.7293276643105</v>
       </c>
       <c r="E484" t="n">
-        <v>109.8128827938557</v>
+        <v>109.8128750730466</v>
       </c>
       <c r="F484" t="n">
         <v>972821</v>
@@ -10132,16 +10132,16 @@
         <v>45181</v>
       </c>
       <c r="B486" t="n">
-        <v>112.4489974975586</v>
+        <v>112.4489898681641</v>
       </c>
       <c r="C486" t="n">
-        <v>113.6994298006641</v>
+        <v>113.6994220864307</v>
       </c>
       <c r="D486" t="n">
-        <v>109.6602637322876</v>
+        <v>109.6602562921019</v>
       </c>
       <c r="E486" t="n">
-        <v>109.7592193991528</v>
+        <v>109.7592119522533</v>
       </c>
       <c r="F486" t="n">
         <v>550963</v>
@@ -10192,16 +10192,16 @@
         <v>45184</v>
       </c>
       <c r="B489" t="n">
-        <v>114.455078125</v>
+        <v>114.4550857543945</v>
       </c>
       <c r="C489" t="n">
-        <v>117.9365011778736</v>
+        <v>117.9365090393343</v>
       </c>
       <c r="D489" t="n">
-        <v>111.6573468239327</v>
+        <v>111.6573542668349</v>
       </c>
       <c r="E489" t="n">
-        <v>113.0697058036241</v>
+        <v>113.0697133406719</v>
       </c>
       <c r="F489" t="n">
         <v>1700134</v>
@@ -10232,16 +10232,16 @@
         <v>45188</v>
       </c>
       <c r="B491" t="n">
-        <v>111.9991912841797</v>
+        <v>111.9991836547852</v>
       </c>
       <c r="C491" t="n">
-        <v>115.957390144112</v>
+        <v>115.9573822450846</v>
       </c>
       <c r="D491" t="n">
-        <v>111.2705240431784</v>
+        <v>111.2705164634207</v>
       </c>
       <c r="E491" t="n">
-        <v>115.336683264999</v>
+        <v>115.3366754082542</v>
       </c>
       <c r="F491" t="n">
         <v>598810</v>
@@ -10252,16 +10252,16 @@
         <v>45189</v>
       </c>
       <c r="B492" t="n">
-        <v>110.0200958251953</v>
+        <v>110.0200881958008</v>
       </c>
       <c r="C492" t="n">
-        <v>112.5479469531647</v>
+        <v>112.5479391484752</v>
       </c>
       <c r="D492" t="n">
-        <v>110.0200958251953</v>
+        <v>110.0200881958008</v>
       </c>
       <c r="E492" t="n">
-        <v>111.7113261834204</v>
+        <v>111.7113184367467</v>
       </c>
       <c r="F492" t="n">
         <v>472827</v>
@@ -10292,16 +10292,16 @@
         <v>45191</v>
       </c>
       <c r="B494" t="n">
-        <v>103.8128967285156</v>
+        <v>103.8129043579102</v>
       </c>
       <c r="C494" t="n">
-        <v>105.8639649667011</v>
+        <v>105.8639727468323</v>
       </c>
       <c r="D494" t="n">
-        <v>103.2011740203427</v>
+        <v>103.2011816047806</v>
       </c>
       <c r="E494" t="n">
-        <v>105.090315457443</v>
+        <v>105.0903231807173</v>
       </c>
       <c r="F494" t="n">
         <v>394595</v>
@@ -10312,16 +10312,16 @@
         <v>45194</v>
       </c>
       <c r="B495" t="n">
-        <v>103.5250396728516</v>
+        <v>103.525032043457</v>
       </c>
       <c r="C495" t="n">
-        <v>104.2986892721627</v>
+        <v>104.2986815857532</v>
       </c>
       <c r="D495" t="n">
-        <v>102.3825540923923</v>
+        <v>102.3825465471945</v>
       </c>
       <c r="E495" t="n">
-        <v>103.893868790658</v>
+        <v>103.8938611340822</v>
       </c>
       <c r="F495" t="n">
         <v>399935</v>
@@ -10432,16 +10432,16 @@
         <v>45202</v>
       </c>
       <c r="B501" t="n">
-        <v>99.56682586669922</v>
+        <v>99.56683349609375</v>
       </c>
       <c r="C501" t="n">
-        <v>103.7859138239664</v>
+        <v>103.7859217766522</v>
       </c>
       <c r="D501" t="n">
-        <v>98.79317632947452</v>
+        <v>98.79318389958749</v>
       </c>
       <c r="E501" t="n">
-        <v>103.3541067176828</v>
+        <v>103.354114637281</v>
       </c>
       <c r="F501" t="n">
         <v>596480</v>
@@ -10472,16 +10472,16 @@
         <v>45204</v>
       </c>
       <c r="B503" t="n">
-        <v>102.8683319091797</v>
+        <v>102.8683395385742</v>
       </c>
       <c r="C503" t="n">
-        <v>103.4170835146696</v>
+        <v>103.4170911847632</v>
       </c>
       <c r="D503" t="n">
-        <v>100.7542923267772</v>
+        <v>100.7542997993806</v>
       </c>
       <c r="E503" t="n">
-        <v>101.24907061479</v>
+        <v>101.2490781240894</v>
       </c>
       <c r="F503" t="n">
         <v>554198</v>
@@ -10552,16 +10552,16 @@
         <v>45210</v>
       </c>
       <c r="B507" t="n">
-        <v>99.23397827148438</v>
+        <v>99.23398590087891</v>
       </c>
       <c r="C507" t="n">
-        <v>102.9852816342156</v>
+        <v>102.9852895520211</v>
       </c>
       <c r="D507" t="n">
-        <v>98.40635538754377</v>
+        <v>98.40636295330827</v>
       </c>
       <c r="E507" t="n">
-        <v>102.3735588801418</v>
+        <v>102.3735667509163</v>
       </c>
       <c r="F507" t="n">
         <v>598551</v>
@@ -10592,16 +10592,16 @@
         <v>45215</v>
       </c>
       <c r="B509" t="n">
-        <v>96.91303253173828</v>
+        <v>96.91304016113281</v>
       </c>
       <c r="C509" t="n">
-        <v>98.87414302938409</v>
+        <v>98.87415081316534</v>
       </c>
       <c r="D509" t="n">
-        <v>96.44524092862584</v>
+        <v>96.44524852119388</v>
       </c>
       <c r="E509" t="n">
-        <v>97.20989262460226</v>
+        <v>97.20990027736684</v>
       </c>
       <c r="F509" t="n">
         <v>1010350</v>
@@ -10612,16 +10612,16 @@
         <v>45216</v>
       </c>
       <c r="B510" t="n">
-        <v>97.14693450927734</v>
+        <v>97.14692687988281</v>
       </c>
       <c r="C510" t="n">
-        <v>97.86661082758212</v>
+        <v>97.86660314166811</v>
       </c>
       <c r="D510" t="n">
-        <v>95.20381943120169</v>
+        <v>95.20381195440891</v>
       </c>
       <c r="E510" t="n">
-        <v>96.69713852617237</v>
+        <v>96.69713093210238</v>
       </c>
       <c r="F510" t="n">
         <v>593712</v>
@@ -10652,16 +10652,16 @@
         <v>45218</v>
       </c>
       <c r="B512" t="n">
-        <v>94.34919738769531</v>
+        <v>94.34920501708984</v>
       </c>
       <c r="C512" t="n">
-        <v>95.99545223608963</v>
+        <v>95.9954599986059</v>
       </c>
       <c r="D512" t="n">
-        <v>92.76592056203434</v>
+        <v>92.76592806339976</v>
       </c>
       <c r="E512" t="n">
-        <v>93.46760115621116</v>
+        <v>93.46760871431685</v>
       </c>
       <c r="F512" t="n">
         <v>760940</v>
@@ -10712,16 +10712,16 @@
         <v>45223</v>
       </c>
       <c r="B515" t="n">
-        <v>93.51258087158203</v>
+        <v>93.5125732421875</v>
       </c>
       <c r="C515" t="n">
-        <v>98.39736545626356</v>
+        <v>98.39735742833496</v>
       </c>
       <c r="D515" t="n">
-        <v>93.38663854709125</v>
+        <v>93.38663092797195</v>
       </c>
       <c r="E515" t="n">
-        <v>96.71513289484724</v>
+        <v>96.71512500416665</v>
       </c>
       <c r="F515" t="n">
         <v>956700</v>
@@ -10812,16 +10812,16 @@
         <v>45230</v>
       </c>
       <c r="B520" t="n">
-        <v>91.32656860351562</v>
+        <v>91.32656097412109</v>
       </c>
       <c r="C520" t="n">
-        <v>91.32656860351562</v>
+        <v>91.32656097412109</v>
       </c>
       <c r="D520" t="n">
-        <v>88.72674850648775</v>
+        <v>88.72674109428142</v>
       </c>
       <c r="E520" t="n">
-        <v>89.94120308789761</v>
+        <v>89.94119557423609</v>
       </c>
       <c r="F520" t="n">
         <v>382337</v>
@@ -10832,16 +10832,16 @@
         <v>45231</v>
       </c>
       <c r="B521" t="n">
-        <v>90.28304290771484</v>
+        <v>90.28305053710938</v>
       </c>
       <c r="C521" t="n">
-        <v>92.37909366507671</v>
+        <v>92.37910147159862</v>
       </c>
       <c r="D521" t="n">
-        <v>89.68031798675922</v>
+        <v>89.68032556522031</v>
       </c>
       <c r="E521" t="n">
-        <v>91.74038424480922</v>
+        <v>91.7403919973568</v>
       </c>
       <c r="F521" t="n">
         <v>488304</v>
@@ -10852,16 +10852,16 @@
         <v>45233</v>
       </c>
       <c r="B522" t="n">
-        <v>94.61006927490234</v>
+        <v>94.61008453369141</v>
       </c>
       <c r="C522" t="n">
-        <v>97.14691791165838</v>
+        <v>97.14693357959244</v>
       </c>
       <c r="D522" t="n">
-        <v>92.08221847800689</v>
+        <v>92.08223332910212</v>
       </c>
       <c r="E522" t="n">
-        <v>92.70293902491068</v>
+        <v>92.70295397611622</v>
       </c>
       <c r="F522" t="n">
         <v>760712</v>
@@ -10872,16 +10872,16 @@
         <v>45236</v>
       </c>
       <c r="B523" t="n">
-        <v>92.2171630859375</v>
+        <v>92.21717071533203</v>
       </c>
       <c r="C523" t="n">
-        <v>95.9864482957361</v>
+        <v>95.98645623697459</v>
       </c>
       <c r="D523" t="n">
-        <v>91.38953336222757</v>
+        <v>91.38954092314988</v>
       </c>
       <c r="E523" t="n">
-        <v>95.13183877782029</v>
+        <v>95.13184664835444</v>
       </c>
       <c r="F523" t="n">
         <v>393989</v>
@@ -10912,16 +10912,16 @@
         <v>45238</v>
       </c>
       <c r="B525" t="n">
-        <v>96.40927124023438</v>
+        <v>96.40926361083984</v>
       </c>
       <c r="C525" t="n">
-        <v>98.50532220933374</v>
+        <v>98.50531441406719</v>
       </c>
       <c r="D525" t="n">
-        <v>95.54566375953443</v>
+        <v>95.54565619848189</v>
       </c>
       <c r="E525" t="n">
-        <v>97.11095188934421</v>
+        <v>97.11094420442183</v>
       </c>
       <c r="F525" t="n">
         <v>449324</v>
@@ -10932,16 +10932,16 @@
         <v>45239</v>
       </c>
       <c r="B526" t="n">
-        <v>95.28477478027344</v>
+        <v>95.28476715087891</v>
       </c>
       <c r="C526" t="n">
-        <v>97.73166590751246</v>
+        <v>97.73165808219684</v>
       </c>
       <c r="D526" t="n">
-        <v>94.73602315850255</v>
+        <v>94.73601557304625</v>
       </c>
       <c r="E526" t="n">
-        <v>97.21889878624117</v>
+        <v>97.2188910019825</v>
       </c>
       <c r="F526" t="n">
         <v>493995</v>
@@ -10952,16 +10952,16 @@
         <v>45240</v>
       </c>
       <c r="B527" t="n">
-        <v>98.95510864257812</v>
+        <v>98.95511627197266</v>
       </c>
       <c r="C527" t="n">
-        <v>99.84570269862571</v>
+        <v>99.84571039668464</v>
       </c>
       <c r="D527" t="n">
-        <v>95.04188526438084</v>
+        <v>95.0418925920676</v>
       </c>
       <c r="E527" t="n">
-        <v>95.04188526438084</v>
+        <v>95.0418925920676</v>
       </c>
       <c r="F527" t="n">
         <v>655787</v>
@@ -10972,16 +10972,16 @@
         <v>45243</v>
       </c>
       <c r="B528" t="n">
-        <v>98.83816528320312</v>
+        <v>98.83815765380859</v>
       </c>
       <c r="C528" t="n">
-        <v>100.3134954614712</v>
+        <v>100.3134877181948</v>
       </c>
       <c r="D528" t="n">
-        <v>96.80508565184681</v>
+        <v>96.80507817938725</v>
       </c>
       <c r="E528" t="n">
-        <v>98.9551097602987</v>
+        <v>98.95510212187712</v>
       </c>
       <c r="F528" t="n">
         <v>702632</v>
@@ -11012,16 +11012,16 @@
         <v>45246</v>
       </c>
       <c r="B530" t="n">
-        <v>101.6538925170898</v>
+        <v>101.6538772583008</v>
       </c>
       <c r="C530" t="n">
-        <v>103.6599856282268</v>
+        <v>103.6599700683125</v>
       </c>
       <c r="D530" t="n">
-        <v>99.45888591602659</v>
+        <v>99.45887098671967</v>
       </c>
       <c r="E530" t="n">
-        <v>100.4214490485131</v>
+        <v>100.4214339747204</v>
       </c>
       <c r="F530" t="n">
         <v>1796629</v>
@@ -11032,16 +11032,16 @@
         <v>45247</v>
       </c>
       <c r="B531" t="n">
-        <v>103.8578796386719</v>
+        <v>103.8578872680664</v>
       </c>
       <c r="C531" t="n">
-        <v>105.3062231122801</v>
+        <v>105.3062308480699</v>
       </c>
       <c r="D531" t="n">
-        <v>101.6538822814461</v>
+        <v>101.6538897489351</v>
       </c>
       <c r="E531" t="n">
-        <v>102.4725141853731</v>
+        <v>102.4725217129987</v>
       </c>
       <c r="F531" t="n">
         <v>1423714</v>
@@ -11052,16 +11052,16 @@
         <v>45250</v>
       </c>
       <c r="B532" t="n">
-        <v>102.5534744262695</v>
+        <v>102.5534820556641</v>
       </c>
       <c r="C532" t="n">
-        <v>104.5685583178221</v>
+        <v>104.5685660971273</v>
       </c>
       <c r="D532" t="n">
-        <v>100.9881864751831</v>
+        <v>100.9881939881291</v>
       </c>
       <c r="E532" t="n">
-        <v>103.6329819380516</v>
+        <v>103.6329896477554</v>
       </c>
       <c r="F532" t="n">
         <v>946377</v>
@@ -11072,16 +11072,16 @@
         <v>45251</v>
       </c>
       <c r="B533" t="n">
-        <v>100.2595138549805</v>
+        <v>100.259521484375</v>
       </c>
       <c r="C533" t="n">
-        <v>103.0932296941449</v>
+        <v>103.0932375391752</v>
       </c>
       <c r="D533" t="n">
-        <v>99.13502398732325</v>
+        <v>99.13503153114809</v>
       </c>
       <c r="E533" t="n">
-        <v>102.5804625890269</v>
+        <v>102.5804703950374</v>
       </c>
       <c r="F533" t="n">
         <v>1091156</v>
@@ -11132,16 +11132,16 @@
         <v>45254</v>
       </c>
       <c r="B536" t="n">
-        <v>103.5430297851562</v>
+        <v>103.5430221557617</v>
       </c>
       <c r="C536" t="n">
-        <v>104.3526638949405</v>
+        <v>104.3526562058894</v>
       </c>
       <c r="D536" t="n">
-        <v>100.9522074971883</v>
+        <v>100.9522000586942</v>
       </c>
       <c r="E536" t="n">
-        <v>103.2731563241227</v>
+        <v>103.2731487146133</v>
       </c>
       <c r="F536" t="n">
         <v>447021</v>
@@ -11152,16 +11152,16 @@
         <v>45257</v>
       </c>
       <c r="B537" t="n">
-        <v>102.1036758422852</v>
+        <v>102.1036834716797</v>
       </c>
       <c r="C537" t="n">
-        <v>103.9028595575677</v>
+        <v>103.9028673214009</v>
       </c>
       <c r="D537" t="n">
-        <v>101.4739642872727</v>
+        <v>101.4739718696139</v>
       </c>
       <c r="E537" t="n">
-        <v>102.8233520737347</v>
+        <v>102.8233597569049</v>
       </c>
       <c r="F537" t="n">
         <v>311562</v>
@@ -11172,16 +11172,16 @@
         <v>45258</v>
       </c>
       <c r="B538" t="n">
-        <v>102.9852828979492</v>
+        <v>102.9852905273438</v>
       </c>
       <c r="C538" t="n">
-        <v>105.4501627622543</v>
+        <v>105.450170574253</v>
       </c>
       <c r="D538" t="n">
-        <v>101.8337995100664</v>
+        <v>101.8338070541564</v>
       </c>
       <c r="E538" t="n">
-        <v>102.0946819825549</v>
+        <v>102.0946895459716</v>
       </c>
       <c r="F538" t="n">
         <v>492581</v>
@@ -11252,16 +11252,16 @@
         <v>45264</v>
       </c>
       <c r="B542" t="n">
-        <v>101.1591110229492</v>
+        <v>101.1591033935547</v>
       </c>
       <c r="C542" t="n">
-        <v>105.2972394423387</v>
+        <v>105.2972315008476</v>
       </c>
       <c r="D542" t="n">
-        <v>100.3674725856501</v>
+        <v>100.3674650159607</v>
       </c>
       <c r="E542" t="n">
-        <v>105.2522570999507</v>
+        <v>105.2522491618521</v>
       </c>
       <c r="F542" t="n">
         <v>887105</v>
@@ -11312,16 +11312,16 @@
         <v>45267</v>
       </c>
       <c r="B545" t="n">
-        <v>106.6016387939453</v>
+        <v>106.6016464233398</v>
       </c>
       <c r="C545" t="n">
-        <v>107.0514347382236</v>
+        <v>107.0514423998096</v>
       </c>
       <c r="D545" t="n">
-        <v>103.6959539740376</v>
+        <v>103.6959613954746</v>
       </c>
       <c r="E545" t="n">
-        <v>105.4231756162056</v>
+        <v>105.4231831612584</v>
       </c>
       <c r="F545" t="n">
         <v>599154</v>
@@ -11352,16 +11352,16 @@
         <v>45271</v>
       </c>
       <c r="B547" t="n">
-        <v>103.1921844482422</v>
+        <v>103.1921920776367</v>
       </c>
       <c r="C547" t="n">
-        <v>106.4127250482224</v>
+        <v>106.4127329157239</v>
       </c>
       <c r="D547" t="n">
-        <v>103.1921844482422</v>
+        <v>103.1921920776367</v>
       </c>
       <c r="E547" t="n">
-        <v>105.3781930063656</v>
+        <v>105.3782007973801</v>
       </c>
       <c r="F547" t="n">
         <v>558243</v>
@@ -11372,16 +11372,16 @@
         <v>45272</v>
       </c>
       <c r="B548" t="n">
-        <v>104.278694152832</v>
+        <v>104.2786865234375</v>
       </c>
       <c r="C548" t="n">
-        <v>106.2837001043422</v>
+        <v>106.2836923282544</v>
       </c>
       <c r="D548" t="n">
-        <v>102.0787653293918</v>
+        <v>102.0787578609517</v>
       </c>
       <c r="E548" t="n">
-        <v>105.7267563673418</v>
+        <v>105.7267486320019</v>
       </c>
       <c r="F548" t="n">
         <v>686347</v>
@@ -11432,16 +11432,16 @@
         <v>45275</v>
       </c>
       <c r="B551" t="n">
-        <v>114.2387313842773</v>
+        <v>114.2387237548828</v>
       </c>
       <c r="C551" t="n">
-        <v>118.814964275997</v>
+        <v>118.8149563409803</v>
       </c>
       <c r="D551" t="n">
-        <v>110.9341924565668</v>
+        <v>110.9341850478647</v>
       </c>
       <c r="E551" t="n">
-        <v>115.4640104200966</v>
+        <v>115.4640027088722</v>
       </c>
       <c r="F551" t="n">
         <v>3143296</v>
@@ -11492,16 +11492,16 @@
         <v>45280</v>
       </c>
       <c r="B554" t="n">
-        <v>119.1769790649414</v>
+        <v>119.1769714355469</v>
       </c>
       <c r="C554" t="n">
-        <v>122.518655629097</v>
+        <v>122.5186477857772</v>
       </c>
       <c r="D554" t="n">
-        <v>118.0352454737914</v>
+        <v>118.0352379174876</v>
       </c>
       <c r="E554" t="n">
-        <v>121.5996910329923</v>
+        <v>121.5996832485022</v>
       </c>
       <c r="F554" t="n">
         <v>920819</v>
@@ -11512,16 +11512,16 @@
         <v>45281</v>
       </c>
       <c r="B555" t="n">
-        <v>118.4436645507812</v>
+        <v>118.4436569213867</v>
       </c>
       <c r="C555" t="n">
-        <v>120.4858009717831</v>
+        <v>120.485793210847</v>
       </c>
       <c r="D555" t="n">
-        <v>116.5500502325098</v>
+        <v>116.55004272509</v>
       </c>
       <c r="E555" t="n">
-        <v>119.8360344771465</v>
+        <v>119.8360267580643</v>
       </c>
       <c r="F555" t="n">
         <v>410768</v>
@@ -11632,16 +11632,16 @@
         <v>45294</v>
       </c>
       <c r="B561" t="n">
-        <v>113.2455062866211</v>
+        <v>113.2455139160156</v>
       </c>
       <c r="C561" t="n">
-        <v>116.2437305936984</v>
+        <v>116.2437384250845</v>
       </c>
       <c r="D561" t="n">
-        <v>113.2455062866211</v>
+        <v>113.2455139160156</v>
       </c>
       <c r="E561" t="n">
-        <v>115.7517564618344</v>
+        <v>115.7517642600759</v>
       </c>
       <c r="F561" t="n">
         <v>798887</v>
@@ -11652,16 +11652,16 @@
         <v>45295</v>
       </c>
       <c r="B562" t="n">
-        <v>109.9688186645508</v>
+        <v>109.9688262939453</v>
       </c>
       <c r="C562" t="n">
-        <v>114.2387299741274</v>
+        <v>114.2387378997589</v>
       </c>
       <c r="D562" t="n">
-        <v>109.9688186645508</v>
+        <v>109.9688262939453</v>
       </c>
       <c r="E562" t="n">
-        <v>113.3383342009799</v>
+        <v>113.338342064144</v>
       </c>
       <c r="F562" t="n">
         <v>1652695</v>
@@ -11672,16 +11672,16 @@
         <v>45296</v>
       </c>
       <c r="B563" t="n">
-        <v>115.6310882568359</v>
+        <v>115.6310958862305</v>
       </c>
       <c r="C563" t="n">
-        <v>115.6310882568359</v>
+        <v>115.6310958862305</v>
       </c>
       <c r="D563" t="n">
-        <v>109.7181850571025</v>
+        <v>109.7181922963609</v>
       </c>
       <c r="E563" t="n">
-        <v>110.1823059872627</v>
+        <v>110.182313257144</v>
       </c>
       <c r="F563" t="n">
         <v>1732820</v>
@@ -11732,16 +11732,16 @@
         <v>45301</v>
       </c>
       <c r="B566" t="n">
-        <v>113.9788208007812</v>
+        <v>113.9788284301758</v>
       </c>
       <c r="C566" t="n">
-        <v>114.5172027885083</v>
+        <v>114.5172104539405</v>
       </c>
       <c r="D566" t="n">
-        <v>111.9738149493523</v>
+        <v>111.9738224445379</v>
       </c>
       <c r="E566" t="n">
-        <v>114.1737507449051</v>
+        <v>114.1737583873477</v>
       </c>
       <c r="F566" t="n">
         <v>497776</v>
@@ -11792,16 +11792,16 @@
         <v>45306</v>
       </c>
       <c r="B569" t="n">
-        <v>118.2580261230469</v>
+        <v>118.2580184936523</v>
       </c>
       <c r="C569" t="n">
-        <v>120.5786239215518</v>
+        <v>120.5786161424443</v>
       </c>
       <c r="D569" t="n">
-        <v>115.6589458241968</v>
+        <v>115.6589383624814</v>
       </c>
       <c r="E569" t="n">
-        <v>116.6707332346643</v>
+        <v>116.6707257076737</v>
       </c>
       <c r="F569" t="n">
         <v>875695</v>
@@ -11812,16 +11812,16 @@
         <v>45307</v>
       </c>
       <c r="B570" t="n">
-        <v>116.5871734619141</v>
+        <v>116.5871810913086</v>
       </c>
       <c r="C570" t="n">
-        <v>118.2487272021283</v>
+        <v>118.2487349402539</v>
       </c>
       <c r="D570" t="n">
-        <v>115.2969178733657</v>
+        <v>115.2969254183267</v>
       </c>
       <c r="E570" t="n">
-        <v>118.2487272021283</v>
+        <v>118.2487349402539</v>
       </c>
       <c r="F570" t="n">
         <v>641403</v>
@@ -11872,16 +11872,16 @@
         <v>45310</v>
       </c>
       <c r="B573" t="n">
-        <v>115.9281234741211</v>
+        <v>115.9281311035156</v>
       </c>
       <c r="C573" t="n">
-        <v>115.9281234741211</v>
+        <v>115.9281311035156</v>
       </c>
       <c r="D573" t="n">
-        <v>112.7628224647626</v>
+        <v>112.7628298858442</v>
       </c>
       <c r="E573" t="n">
-        <v>113.783887078042</v>
+        <v>113.7838945663213</v>
       </c>
       <c r="F573" t="n">
         <v>461986</v>
@@ -11892,16 +11892,16 @@
         <v>45313</v>
       </c>
       <c r="B574" t="n">
-        <v>116.9677658081055</v>
+        <v>116.9677581787109</v>
       </c>
       <c r="C574" t="n">
-        <v>118.313713753421</v>
+        <v>118.313706036235</v>
       </c>
       <c r="D574" t="n">
-        <v>114.8792214972839</v>
+        <v>114.8792140041177</v>
       </c>
       <c r="E574" t="n">
-        <v>115.7332023602692</v>
+        <v>115.7331948114009</v>
       </c>
       <c r="F574" t="n">
         <v>856226</v>
@@ -11912,16 +11912,16 @@
         <v>45314</v>
       </c>
       <c r="B575" t="n">
-        <v>115.8445816040039</v>
+        <v>115.8445892333984</v>
       </c>
       <c r="C575" t="n">
-        <v>119.5111339486896</v>
+        <v>119.5111418195592</v>
       </c>
       <c r="D575" t="n">
-        <v>115.3526074921376</v>
+        <v>115.3526150891313</v>
       </c>
       <c r="E575" t="n">
-        <v>117.0605761181597</v>
+        <v>117.0605838276382</v>
       </c>
       <c r="F575" t="n">
         <v>383026</v>
@@ -11972,16 +11972,16 @@
         <v>45317</v>
       </c>
       <c r="B578" t="n">
-        <v>116.6614379882812</v>
+        <v>116.6614456176758</v>
       </c>
       <c r="C578" t="n">
-        <v>119.0841427428836</v>
+        <v>119.0841505307175</v>
       </c>
       <c r="D578" t="n">
-        <v>113.3383304087349</v>
+        <v>113.3383378208057</v>
       </c>
       <c r="E578" t="n">
-        <v>113.6817824486065</v>
+        <v>113.6817898831383</v>
       </c>
       <c r="F578" t="n">
         <v>753916</v>
@@ -12012,16 +12012,16 @@
         <v>45321</v>
       </c>
       <c r="B580" t="n">
-        <v>115.1205596923828</v>
+        <v>115.1205520629883</v>
       </c>
       <c r="C580" t="n">
-        <v>120.3744052719636</v>
+        <v>120.3743972943805</v>
       </c>
       <c r="D580" t="n">
-        <v>114.8235225615435</v>
+        <v>114.8235149518346</v>
       </c>
       <c r="E580" t="n">
-        <v>119.7524848858194</v>
+        <v>119.7524769494529</v>
       </c>
       <c r="F580" t="n">
         <v>678468</v>
@@ -12092,16 +12092,16 @@
         <v>45327</v>
       </c>
       <c r="B584" t="n">
-        <v>117.5711135864258</v>
+        <v>117.5711212158203</v>
       </c>
       <c r="C584" t="n">
-        <v>121.3026355450343</v>
+        <v>121.3026434165738</v>
       </c>
       <c r="D584" t="n">
-        <v>116.2065969632262</v>
+        <v>116.2066045040748</v>
       </c>
       <c r="E584" t="n">
-        <v>119.7246272668129</v>
+        <v>119.7246350359527</v>
       </c>
       <c r="F584" t="n">
         <v>563930</v>
@@ -12132,16 +12132,16 @@
         <v>45329</v>
       </c>
       <c r="B586" t="n">
-        <v>114.9070587158203</v>
+        <v>114.9070663452148</v>
       </c>
       <c r="C586" t="n">
-        <v>116.3179832026201</v>
+        <v>116.3179909256947</v>
       </c>
       <c r="D586" t="n">
-        <v>111.8160116757133</v>
+        <v>111.816019099874</v>
       </c>
       <c r="E586" t="n">
-        <v>115.1019886532248</v>
+        <v>115.101996295562</v>
       </c>
       <c r="F586" t="n">
         <v>998662</v>
@@ -12152,16 +12152,16 @@
         <v>45330</v>
       </c>
       <c r="B587" t="n">
-        <v>114.4058151245117</v>
+        <v>114.4058074951172</v>
       </c>
       <c r="C587" t="n">
-        <v>115.436164208617</v>
+        <v>115.4361565105115</v>
       </c>
       <c r="D587" t="n">
-        <v>113.0412983870791</v>
+        <v>113.0412908486803</v>
       </c>
       <c r="E587" t="n">
-        <v>115.1019965552897</v>
+        <v>115.1019888794688</v>
       </c>
       <c r="F587" t="n">
         <v>662990</v>
@@ -12212,16 +12212,16 @@
         <v>45337</v>
       </c>
       <c r="B590" t="n">
-        <v>115.7517623901367</v>
+        <v>115.7517547607422</v>
       </c>
       <c r="C590" t="n">
-        <v>116.4015359709352</v>
+        <v>116.4015282987129</v>
       </c>
       <c r="D590" t="n">
-        <v>114.4986372383505</v>
+        <v>114.4986296915515</v>
       </c>
       <c r="E590" t="n">
-        <v>115.6589396162866</v>
+        <v>115.6589319930101</v>
       </c>
       <c r="F590" t="n">
         <v>464925</v>
@@ -12232,16 +12232,16 @@
         <v>45338</v>
       </c>
       <c r="B591" t="n">
-        <v>114.2387313842773</v>
+        <v>114.2387237548828</v>
       </c>
       <c r="C591" t="n">
-        <v>116.0302385507783</v>
+        <v>116.0302308017386</v>
       </c>
       <c r="D591" t="n">
-        <v>113.3569044040609</v>
+        <v>113.3568968335589</v>
       </c>
       <c r="E591" t="n">
-        <v>115.7517631454869</v>
+        <v>115.7517554150451</v>
       </c>
       <c r="F591" t="n">
         <v>476906</v>
@@ -12412,16 +12412,16 @@
         <v>45351</v>
       </c>
       <c r="B600" t="n">
-        <v>108.502197265625</v>
+        <v>108.5021896362305</v>
       </c>
       <c r="C600" t="n">
-        <v>111.5189835001582</v>
+        <v>111.5189756586366</v>
       </c>
       <c r="D600" t="n">
-        <v>108.502197265625</v>
+        <v>108.5021896362305</v>
       </c>
       <c r="E600" t="n">
-        <v>109.4397235860647</v>
+        <v>109.4397158907475</v>
       </c>
       <c r="F600" t="n">
         <v>462606</v>
@@ -12432,16 +12432,16 @@
         <v>45352</v>
       </c>
       <c r="B601" t="n">
-        <v>109.0869903564453</v>
+        <v>109.0869827270508</v>
       </c>
       <c r="C601" t="n">
-        <v>110.2008849405809</v>
+        <v>110.2008772332821</v>
       </c>
       <c r="D601" t="n">
-        <v>108.1958789382912</v>
+        <v>108.1958713712198</v>
       </c>
       <c r="E601" t="n">
-        <v>108.8642142723878</v>
+        <v>108.8642066585739</v>
       </c>
       <c r="F601" t="n">
         <v>370372</v>
@@ -12472,16 +12472,16 @@
         <v>45356</v>
       </c>
       <c r="B603" t="n">
-        <v>109.6624908447266</v>
+        <v>109.6624984741211</v>
       </c>
       <c r="C603" t="n">
-        <v>109.6624908447266</v>
+        <v>109.6624984741211</v>
       </c>
       <c r="D603" t="n">
-        <v>106.5157515612361</v>
+        <v>106.5157589717069</v>
       </c>
       <c r="E603" t="n">
-        <v>107.9730909725224</v>
+        <v>107.9730984843827</v>
       </c>
       <c r="F603" t="n">
         <v>2890717</v>
@@ -12612,16 +12612,16 @@
         <v>45365</v>
       </c>
       <c r="B610" t="n">
-        <v>117.5711135864258</v>
+        <v>117.5711212158203</v>
       </c>
       <c r="C610" t="n">
-        <v>120.7642677478222</v>
+        <v>120.7642755844261</v>
       </c>
       <c r="D610" t="n">
-        <v>115.937405982697</v>
+        <v>115.9374135060774</v>
       </c>
       <c r="E610" t="n">
-        <v>120.662160579969</v>
+        <v>120.662168409947</v>
       </c>
       <c r="F610" t="n">
         <v>644367</v>
@@ -12812,16 +12812,16 @@
         <v>45379</v>
       </c>
       <c r="B620" t="n">
-        <v>118.9077835083008</v>
+        <v>118.9077911376953</v>
       </c>
       <c r="C620" t="n">
-        <v>120.5693301438005</v>
+        <v>120.5693378798037</v>
       </c>
       <c r="D620" t="n">
-        <v>116.5964562638948</v>
+        <v>116.5964637449893</v>
       </c>
       <c r="E620" t="n">
-        <v>117.0698615778232</v>
+        <v>117.0698690892924</v>
       </c>
       <c r="F620" t="n">
         <v>712173</v>
@@ -12892,16 +12892,16 @@
         <v>45386</v>
       </c>
       <c r="B624" t="n">
-        <v>117.4225921630859</v>
+        <v>117.4225997924805</v>
       </c>
       <c r="C624" t="n">
-        <v>118.7963931953485</v>
+        <v>118.7964009140041</v>
       </c>
       <c r="D624" t="n">
-        <v>116.104490456648</v>
+        <v>116.1044980004005</v>
       </c>
       <c r="E624" t="n">
-        <v>117.5525454534715</v>
+        <v>117.5525530913096</v>
       </c>
       <c r="F624" t="n">
         <v>491773</v>
@@ -12992,16 +12992,16 @@
         <v>45393</v>
       </c>
       <c r="B629" t="n">
-        <v>113.9509811401367</v>
+        <v>113.9509735107422</v>
       </c>
       <c r="C629" t="n">
-        <v>114.4522326314215</v>
+        <v>114.4522249684666</v>
       </c>
       <c r="D629" t="n">
-        <v>112.3915344167808</v>
+        <v>112.3915268917964</v>
       </c>
       <c r="E629" t="n">
-        <v>114.025235112164</v>
+        <v>114.025227477798</v>
       </c>
       <c r="F629" t="n">
         <v>445667</v>
@@ -13132,16 +13132,16 @@
         <v>45404</v>
       </c>
       <c r="B636" t="n">
-        <v>100.9462966918945</v>
+        <v>100.9463043212891</v>
       </c>
       <c r="C636" t="n">
-        <v>102.5243049338492</v>
+        <v>102.5243126825076</v>
       </c>
       <c r="D636" t="n">
-        <v>100.4357608643617</v>
+        <v>100.4357684551706</v>
       </c>
       <c r="E636" t="n">
-        <v>101.1783571440598</v>
+        <v>101.1783647909932</v>
       </c>
       <c r="F636" t="n">
         <v>363945</v>
@@ -13292,16 +13292,16 @@
         <v>45418</v>
       </c>
       <c r="B644" t="n">
-        <v>105.7267532348633</v>
+        <v>105.7267456054688</v>
       </c>
       <c r="C644" t="n">
-        <v>107.1655239226594</v>
+        <v>107.1655161894411</v>
       </c>
       <c r="D644" t="n">
-        <v>105.2255017618369</v>
+        <v>105.2254941686134</v>
       </c>
       <c r="E644" t="n">
-        <v>105.8195760079592</v>
+        <v>105.8195683718665</v>
       </c>
       <c r="F644" t="n">
         <v>262476</v>
@@ -13332,16 +13332,16 @@
         <v>45420</v>
       </c>
       <c r="B646" t="n">
-        <v>105.9495239257812</v>
+        <v>105.9495315551758</v>
       </c>
       <c r="C646" t="n">
-        <v>105.9959388509337</v>
+        <v>105.9959464836706</v>
       </c>
       <c r="D646" t="n">
-        <v>102.301533181186</v>
+        <v>102.3015405478897</v>
       </c>
       <c r="E646" t="n">
-        <v>103.6846115512664</v>
+        <v>103.6846190175652</v>
       </c>
       <c r="F646" t="n">
         <v>426813</v>
@@ -13412,16 +13412,16 @@
         <v>45426</v>
       </c>
       <c r="B650" t="n">
-        <v>103.6660537719727</v>
+        <v>103.6660461425781</v>
       </c>
       <c r="C650" t="n">
-        <v>104.6314261800793</v>
+        <v>104.6314184796373</v>
       </c>
       <c r="D650" t="n">
-        <v>103.0348490082846</v>
+        <v>103.0348414253441</v>
       </c>
       <c r="E650" t="n">
-        <v>103.0348490082846</v>
+        <v>103.0348414253441</v>
       </c>
       <c r="F650" t="n">
         <v>247200</v>
@@ -13452,16 +13452,16 @@
         <v>45428</v>
       </c>
       <c r="B652" t="n">
-        <v>104.6407012939453</v>
+        <v>104.6407089233398</v>
       </c>
       <c r="C652" t="n">
-        <v>104.9377383868498</v>
+        <v>104.9377460379014</v>
       </c>
       <c r="D652" t="n">
-        <v>103.322592554879</v>
+        <v>103.3226000881697</v>
       </c>
       <c r="E652" t="n">
-        <v>104.1487271908296</v>
+        <v>104.1487347843541</v>
       </c>
       <c r="F652" t="n">
         <v>283646</v>
@@ -13492,16 +13492,16 @@
         <v>45432</v>
       </c>
       <c r="B654" t="n">
-        <v>102.5243072509766</v>
+        <v>102.5243148803711</v>
       </c>
       <c r="C654" t="n">
-        <v>103.3504419128024</v>
+        <v>103.3504496036741</v>
       </c>
       <c r="D654" t="n">
-        <v>101.2340516743307</v>
+        <v>101.2340592077103</v>
       </c>
       <c r="E654" t="n">
-        <v>103.0162813695012</v>
+        <v>103.0162890355063</v>
       </c>
       <c r="F654" t="n">
         <v>409635</v>
@@ -13672,16 +13672,16 @@
         <v>45446</v>
       </c>
       <c r="B663" t="n">
-        <v>92.43431854248047</v>
+        <v>92.434326171875</v>
       </c>
       <c r="C663" t="n">
-        <v>93.60389809123609</v>
+        <v>93.60390581716601</v>
       </c>
       <c r="D663" t="n">
-        <v>90.53142005267401</v>
+        <v>90.53142752500605</v>
       </c>
       <c r="E663" t="n">
-        <v>92.64781018690546</v>
+        <v>92.64781783392128</v>
       </c>
       <c r="F663" t="n">
         <v>373105</v>
@@ -13752,16 +13752,16 @@
         <v>45450</v>
       </c>
       <c r="B667" t="n">
-        <v>92.82418823242188</v>
+        <v>92.82418060302734</v>
       </c>
       <c r="C667" t="n">
-        <v>94.03090551221278</v>
+        <v>94.03089778363588</v>
       </c>
       <c r="D667" t="n">
-        <v>91.53393258254509</v>
+        <v>91.53392505919909</v>
       </c>
       <c r="E667" t="n">
-        <v>92.73136546057417</v>
+        <v>92.7313578388089</v>
       </c>
       <c r="F667" t="n">
         <v>795802</v>
@@ -13772,16 +13772,16 @@
         <v>45453</v>
       </c>
       <c r="B668" t="n">
-        <v>92.53643798828125</v>
+        <v>92.53643035888672</v>
       </c>
       <c r="C668" t="n">
-        <v>93.24189673871706</v>
+        <v>93.24188905115926</v>
       </c>
       <c r="D668" t="n">
-        <v>90.78206135035421</v>
+        <v>90.78205386560359</v>
       </c>
       <c r="E668" t="n">
-        <v>92.0351865085987</v>
+        <v>92.0351789205311</v>
       </c>
       <c r="F668" t="n">
         <v>279796</v>
@@ -13792,16 +13792,16 @@
         <v>45454</v>
       </c>
       <c r="B669" t="n">
-        <v>92.84275054931641</v>
+        <v>92.84275817871094</v>
       </c>
       <c r="C669" t="n">
-        <v>93.01911877430439</v>
+        <v>93.01912641819206</v>
       </c>
       <c r="D669" t="n">
-        <v>91.69173259079281</v>
+        <v>91.69174012560192</v>
       </c>
       <c r="E669" t="n">
-        <v>92.5271517066259</v>
+        <v>92.52715931008595</v>
       </c>
       <c r="F669" t="n">
         <v>406022</v>
@@ -13852,16 +13852,16 @@
         <v>45457</v>
       </c>
       <c r="B672" t="n">
-        <v>85.38896942138672</v>
+        <v>85.38896179199219</v>
       </c>
       <c r="C672" t="n">
-        <v>86.81846278086709</v>
+        <v>86.81845502374917</v>
       </c>
       <c r="D672" t="n">
-        <v>84.95269460026903</v>
+        <v>84.95268700985508</v>
       </c>
       <c r="E672" t="n">
-        <v>86.81846278086709</v>
+        <v>86.81845502374917</v>
       </c>
       <c r="F672" t="n">
         <v>481131</v>
@@ -13892,16 +13892,16 @@
         <v>45461</v>
       </c>
       <c r="B674" t="n">
-        <v>87.54248046875</v>
+        <v>87.54248809814453</v>
       </c>
       <c r="C674" t="n">
-        <v>87.54248046875</v>
+        <v>87.54248809814453</v>
       </c>
       <c r="D674" t="n">
-        <v>84.9712538405923</v>
+        <v>84.97126124590245</v>
       </c>
       <c r="E674" t="n">
-        <v>85.57461241716906</v>
+        <v>85.57461987506238</v>
       </c>
       <c r="F674" t="n">
         <v>348422</v>
@@ -13912,16 +13912,16 @@
         <v>45462</v>
       </c>
       <c r="B675" t="n">
-        <v>86.95769500732422</v>
+        <v>86.95770263671875</v>
       </c>
       <c r="C675" t="n">
-        <v>88.30364282944254</v>
+        <v>88.3036505769263</v>
       </c>
       <c r="D675" t="n">
-        <v>84.89699700949208</v>
+        <v>84.89700445808745</v>
       </c>
       <c r="E675" t="n">
-        <v>86.80917291504799</v>
+        <v>86.80918053141167</v>
       </c>
       <c r="F675" t="n">
         <v>247119</v>
@@ -13932,16 +13932,16 @@
         <v>45463</v>
       </c>
       <c r="B676" t="n">
-        <v>90.61497497558594</v>
+        <v>90.61498260498047</v>
       </c>
       <c r="C676" t="n">
-        <v>91.32971810793224</v>
+        <v>91.32972579750511</v>
       </c>
       <c r="D676" t="n">
-        <v>86.61424765264107</v>
+        <v>86.61425494519142</v>
       </c>
       <c r="E676" t="n">
-        <v>86.61424765264107</v>
+        <v>86.61425494519142</v>
       </c>
       <c r="F676" t="n">
         <v>965986</v>
@@ -13972,16 +13972,16 @@
         <v>45467</v>
       </c>
       <c r="B678" t="n">
-        <v>89.74241638183594</v>
+        <v>89.74242401123047</v>
       </c>
       <c r="C678" t="n">
-        <v>90.60568152828682</v>
+        <v>90.6056892310713</v>
       </c>
       <c r="D678" t="n">
-        <v>88.23866213520195</v>
+        <v>88.23866963675577</v>
       </c>
       <c r="E678" t="n">
-        <v>88.92556615757213</v>
+        <v>88.92557371752265</v>
       </c>
       <c r="F678" t="n">
         <v>235914</v>
@@ -14012,16 +14012,16 @@
         <v>45469</v>
       </c>
       <c r="B680" t="n">
-        <v>91.09765625</v>
+        <v>91.09766387939453</v>
       </c>
       <c r="C680" t="n">
-        <v>91.68244607664806</v>
+        <v>91.68245375501853</v>
       </c>
       <c r="D680" t="n">
-        <v>89.57534015485479</v>
+        <v>89.57534765675591</v>
       </c>
       <c r="E680" t="n">
-        <v>90.03946108829963</v>
+        <v>90.03946862907071</v>
       </c>
       <c r="F680" t="n">
         <v>524346</v>
@@ -14072,16 +14072,16 @@
         <v>45474</v>
       </c>
       <c r="B683" t="n">
-        <v>87.969482421875</v>
+        <v>87.96947479248047</v>
       </c>
       <c r="C683" t="n">
-        <v>91.70101885438143</v>
+        <v>91.70101090135917</v>
       </c>
       <c r="D683" t="n">
-        <v>87.85809792545159</v>
+        <v>87.85809030571718</v>
       </c>
       <c r="E683" t="n">
-        <v>90.31794039570877</v>
+        <v>90.31793256263779</v>
       </c>
       <c r="F683" t="n">
         <v>154542</v>
@@ -14232,16 +14232,16 @@
         <v>45484</v>
       </c>
       <c r="B691" t="n">
-        <v>92.32294464111328</v>
+        <v>92.32293701171875</v>
       </c>
       <c r="C691" t="n">
-        <v>92.6014200623334</v>
+        <v>92.60141240992618</v>
       </c>
       <c r="D691" t="n">
-        <v>89.85382470611971</v>
+        <v>89.85381728076861</v>
       </c>
       <c r="E691" t="n">
-        <v>90.12300864286192</v>
+        <v>90.12300119526596</v>
       </c>
       <c r="F691" t="n">
         <v>274684</v>
@@ -14292,16 +14292,16 @@
         <v>45489</v>
       </c>
       <c r="B694" t="n">
-        <v>93.74314117431641</v>
+        <v>93.74314880371094</v>
       </c>
       <c r="C694" t="n">
-        <v>95.46038715708933</v>
+        <v>95.46039492624392</v>
       </c>
       <c r="D694" t="n">
-        <v>92.9262909069122</v>
+        <v>92.92629846982642</v>
       </c>
       <c r="E694" t="n">
-        <v>92.9262909069122</v>
+        <v>92.92629846982642</v>
       </c>
       <c r="F694" t="n">
         <v>218776</v>
@@ -14332,16 +14332,16 @@
         <v>45491</v>
       </c>
       <c r="B696" t="n">
-        <v>91.96092224121094</v>
+        <v>91.96092987060547</v>
       </c>
       <c r="C696" t="n">
-        <v>94.96842393223361</v>
+        <v>94.96843181114083</v>
       </c>
       <c r="D696" t="n">
-        <v>91.20904858893614</v>
+        <v>91.20905615595265</v>
       </c>
       <c r="E696" t="n">
-        <v>94.88488556283573</v>
+        <v>94.88489343481233</v>
       </c>
       <c r="F696" t="n">
         <v>265514</v>
@@ -14412,16 +14412,16 @@
         <v>45497</v>
       </c>
       <c r="B700" t="n">
-        <v>91.80311584472656</v>
+        <v>91.80312347412109</v>
       </c>
       <c r="C700" t="n">
-        <v>94.77348678516967</v>
+        <v>94.77349466141999</v>
       </c>
       <c r="D700" t="n">
-        <v>91.78454704276713</v>
+        <v>91.78455467061849</v>
       </c>
       <c r="E700" t="n">
-        <v>94.36506520706058</v>
+        <v>94.3650730493686</v>
       </c>
       <c r="F700" t="n">
         <v>387734</v>
@@ -14472,16 +14472,16 @@
         <v>45502</v>
       </c>
       <c r="B703" t="n">
-        <v>91.94235229492188</v>
+        <v>91.94235992431641</v>
       </c>
       <c r="C703" t="n">
-        <v>94.07730416654506</v>
+        <v>94.07731197309832</v>
       </c>
       <c r="D703" t="n">
-        <v>91.71956916594331</v>
+        <v>91.71957677685126</v>
       </c>
       <c r="E703" t="n">
-        <v>93.10265453447454</v>
+        <v>93.10266226015118</v>
       </c>
       <c r="F703" t="n">
         <v>142991</v>
@@ -14512,16 +14512,16 @@
         <v>45504</v>
       </c>
       <c r="B705" t="n">
-        <v>90.49430847167969</v>
+        <v>90.49430084228516</v>
       </c>
       <c r="C705" t="n">
-        <v>91.8031330602639</v>
+        <v>91.80312532052498</v>
       </c>
       <c r="D705" t="n">
-        <v>89.90023417218629</v>
+        <v>89.90022659287696</v>
       </c>
       <c r="E705" t="n">
-        <v>90.59641565583551</v>
+        <v>90.59640801783253</v>
       </c>
       <c r="F705" t="n">
         <v>210335</v>
@@ -14712,16 +14712,16 @@
         <v>45518</v>
       </c>
       <c r="B715" t="n">
-        <v>100.250129699707</v>
+        <v>100.2501220703125</v>
       </c>
       <c r="C715" t="n">
-        <v>101.4382782519291</v>
+        <v>101.4382705321122</v>
       </c>
       <c r="D715" t="n">
-        <v>98.41220753916585</v>
+        <v>98.41220004964379</v>
       </c>
       <c r="E715" t="n">
-        <v>100.0644841441438</v>
+        <v>100.0644765288776</v>
       </c>
       <c r="F715" t="n">
         <v>1420295</v>
@@ -14832,16 +14832,16 @@
         <v>45526</v>
       </c>
       <c r="B721" t="n">
-        <v>99.97164916992188</v>
+        <v>99.97164154052734</v>
       </c>
       <c r="C721" t="n">
-        <v>101.0112826408908</v>
+        <v>101.0112749321561</v>
       </c>
       <c r="D721" t="n">
-        <v>98.57928632865877</v>
+        <v>98.57927880552322</v>
       </c>
       <c r="E721" t="n">
-        <v>98.87632345151795</v>
+        <v>98.87631590571384</v>
       </c>
       <c r="F721" t="n">
         <v>499264</v>
@@ -14992,16 +14992,16 @@
         <v>45538</v>
       </c>
       <c r="B729" t="n">
-        <v>96.24940490722656</v>
+        <v>96.24939727783203</v>
       </c>
       <c r="C729" t="n">
-        <v>97.25190077727714</v>
+        <v>97.25189306841784</v>
       </c>
       <c r="D729" t="n">
-        <v>94.54143612809369</v>
+        <v>94.5414286340846</v>
       </c>
       <c r="E729" t="n">
-        <v>95.51609295616707</v>
+        <v>95.51608538489992</v>
       </c>
       <c r="F729" t="n">
         <v>703523</v>
@@ -15012,16 +15012,16 @@
         <v>45539</v>
       </c>
       <c r="B730" t="n">
-        <v>95.59034729003906</v>
+        <v>95.59035491943359</v>
       </c>
       <c r="C730" t="n">
-        <v>96.91773339744505</v>
+        <v>96.91774113278282</v>
       </c>
       <c r="D730" t="n">
-        <v>94.9127276344025</v>
+        <v>94.91273520971389</v>
       </c>
       <c r="E730" t="n">
-        <v>95.7481467023369</v>
+        <v>95.74815434432594</v>
       </c>
       <c r="F730" t="n">
         <v>802363</v>
@@ -15032,16 +15032,16 @@
         <v>45540</v>
       </c>
       <c r="B731" t="n">
-        <v>96.58357238769531</v>
+        <v>96.58358001708984</v>
       </c>
       <c r="C731" t="n">
-        <v>96.95486348161789</v>
+        <v>96.95487114034169</v>
       </c>
       <c r="D731" t="n">
-        <v>94.83847308579506</v>
+        <v>94.83848057733952</v>
       </c>
       <c r="E731" t="n">
-        <v>96.72280300695445</v>
+        <v>96.72281064734717</v>
       </c>
       <c r="F731" t="n">
         <v>616217</v>
@@ -15052,16 +15052,16 @@
         <v>45541</v>
       </c>
       <c r="B732" t="n">
-        <v>93.76171112060547</v>
+        <v>93.76171875</v>
       </c>
       <c r="C732" t="n">
-        <v>96.95485826444198</v>
+        <v>96.95486615366303</v>
       </c>
       <c r="D732" t="n">
-        <v>93.10266025785589</v>
+        <v>93.10266783362343</v>
       </c>
       <c r="E732" t="n">
-        <v>96.5835671904987</v>
+        <v>96.58357504950779</v>
       </c>
       <c r="F732" t="n">
         <v>627234</v>
@@ -15072,16 +15072,16 @@
         <v>45544</v>
       </c>
       <c r="B733" t="n">
-        <v>93.68745422363281</v>
+        <v>93.68744659423828</v>
       </c>
       <c r="C733" t="n">
-        <v>95.05197093478797</v>
+        <v>95.05196319427465</v>
       </c>
       <c r="D733" t="n">
-        <v>93.37184829849096</v>
+        <v>93.37184069479765</v>
       </c>
       <c r="E733" t="n">
-        <v>93.77099259439402</v>
+        <v>93.77098495819658</v>
       </c>
       <c r="F733" t="n">
         <v>200739</v>
@@ -15152,16 +15152,16 @@
         <v>45548</v>
       </c>
       <c r="B737" t="n">
-        <v>98.87632751464844</v>
+        <v>98.87631988525391</v>
       </c>
       <c r="C737" t="n">
-        <v>99.46112446444116</v>
+        <v>99.46111678992312</v>
       </c>
       <c r="D737" t="n">
-        <v>96.32366220076925</v>
+        <v>96.32365476834089</v>
       </c>
       <c r="E737" t="n">
-        <v>96.32366220076925</v>
+        <v>96.32365476834089</v>
       </c>
       <c r="F737" t="n">
         <v>344396</v>
@@ -15192,16 +15192,16 @@
         <v>45552</v>
       </c>
       <c r="B739" t="n">
-        <v>100.3150939941406</v>
+        <v>100.3151016235352</v>
       </c>
       <c r="C739" t="n">
-        <v>100.7977766282958</v>
+        <v>100.7977842944004</v>
       </c>
       <c r="D739" t="n">
-        <v>98.70923251684773</v>
+        <v>98.70924002410959</v>
       </c>
       <c r="E739" t="n">
-        <v>99.17335343050286</v>
+        <v>99.17336097306311</v>
       </c>
       <c r="F739" t="n">
         <v>287351</v>
@@ -15312,16 +15312,16 @@
         <v>45560</v>
       </c>
       <c r="B745" t="n">
-        <v>90.49430847167969</v>
+        <v>90.49430084228516</v>
       </c>
       <c r="C745" t="n">
-        <v>92.06303968105173</v>
+        <v>92.0630319194006</v>
       </c>
       <c r="D745" t="n">
-        <v>89.42682878036601</v>
+        <v>89.42682124096855</v>
       </c>
       <c r="E745" t="n">
-        <v>91.89595584169895</v>
+        <v>91.89594809413431</v>
       </c>
       <c r="F745" t="n">
         <v>511811</v>
@@ -15392,16 +15392,16 @@
         <v>45566</v>
       </c>
       <c r="B749" t="n">
-        <v>90.82846832275391</v>
+        <v>90.82846069335938</v>
       </c>
       <c r="C749" t="n">
-        <v>91.78455634479495</v>
+        <v>91.7845486350911</v>
       </c>
       <c r="D749" t="n">
-        <v>89.77027312535667</v>
+        <v>89.77026558484825</v>
       </c>
       <c r="E749" t="n">
-        <v>90.50358507476767</v>
+        <v>90.50357747266264</v>
       </c>
       <c r="F749" t="n">
         <v>321109</v>
@@ -15472,16 +15472,16 @@
         <v>45572</v>
       </c>
       <c r="B753" t="n">
-        <v>90.48501586914062</v>
+        <v>90.48502349853516</v>
       </c>
       <c r="C753" t="n">
-        <v>90.75419976526331</v>
+        <v>90.75420741735454</v>
       </c>
       <c r="D753" t="n">
-        <v>89.12049925852935</v>
+        <v>89.1205067728724</v>
       </c>
       <c r="E753" t="n">
-        <v>89.80739622344984</v>
+        <v>89.80740379570975</v>
       </c>
       <c r="F753" t="n">
         <v>295051</v>
@@ -15532,16 +15532,16 @@
         <v>45575</v>
       </c>
       <c r="B756" t="n">
-        <v>89.99304962158203</v>
+        <v>89.9930419921875</v>
       </c>
       <c r="C756" t="n">
-        <v>90.42004712885797</v>
+        <v>90.42003946326363</v>
       </c>
       <c r="D756" t="n">
-        <v>88.5542789217497</v>
+        <v>88.55427141433071</v>
       </c>
       <c r="E756" t="n">
-        <v>88.83274724336708</v>
+        <v>88.8327397123402</v>
       </c>
       <c r="F756" t="n">
         <v>262199</v>
@@ -15552,16 +15552,16 @@
         <v>45576</v>
       </c>
       <c r="B757" t="n">
-        <v>91.21832275390625</v>
+        <v>91.21833038330078</v>
       </c>
       <c r="C757" t="n">
-        <v>91.7102968792871</v>
+        <v>91.71030454982977</v>
       </c>
       <c r="D757" t="n">
-        <v>89.11121688730475</v>
+        <v>89.11122434046339</v>
       </c>
       <c r="E757" t="n">
-        <v>89.11121688730475</v>
+        <v>89.11122434046339</v>
       </c>
       <c r="F757" t="n">
         <v>354987</v>
@@ -15612,16 +15612,16 @@
         <v>45581</v>
       </c>
       <c r="B760" t="n">
-        <v>95.37684631347656</v>
+        <v>95.37685394287109</v>
       </c>
       <c r="C760" t="n">
-        <v>95.37684631347656</v>
+        <v>95.37685394287109</v>
       </c>
       <c r="D760" t="n">
-        <v>91.53392577309324</v>
+        <v>91.53393309508448</v>
       </c>
       <c r="E760" t="n">
-        <v>91.53392577309324</v>
+        <v>91.53393309508448</v>
       </c>
       <c r="F760" t="n">
         <v>473040</v>
@@ -15632,16 +15632,16 @@
         <v>45582</v>
       </c>
       <c r="B761" t="n">
-        <v>95.03340148925781</v>
+        <v>95.03339385986328</v>
       </c>
       <c r="C761" t="n">
-        <v>96.48146364331757</v>
+        <v>96.48145589767088</v>
       </c>
       <c r="D761" t="n">
-        <v>94.06802908052583</v>
+        <v>94.06802152863254</v>
       </c>
       <c r="E761" t="n">
-        <v>94.42076552870925</v>
+        <v>94.42075794849787</v>
       </c>
       <c r="F761" t="n">
         <v>511946</v>
@@ -15752,16 +15752,16 @@
         <v>45590</v>
       </c>
       <c r="B767" t="n">
-        <v>93.17691040039062</v>
+        <v>93.17691802978516</v>
       </c>
       <c r="C767" t="n">
-        <v>93.91022228060997</v>
+        <v>93.91022997004863</v>
       </c>
       <c r="D767" t="n">
-        <v>92.02589253816214</v>
+        <v>92.02590007331048</v>
       </c>
       <c r="E767" t="n">
-        <v>93.29758636820173</v>
+        <v>93.29759400747731</v>
       </c>
       <c r="F767" t="n">
         <v>563664</v>
@@ -15852,16 +15852,16 @@
         <v>45597</v>
       </c>
       <c r="B772" t="n">
-        <v>91.89594268798828</v>
+        <v>91.89595031738281</v>
       </c>
       <c r="C772" t="n">
-        <v>94.99626705207805</v>
+        <v>94.99627493886804</v>
       </c>
       <c r="D772" t="n">
-        <v>91.41326004446124</v>
+        <v>91.41326763378245</v>
       </c>
       <c r="E772" t="n">
-        <v>93.85453354819522</v>
+        <v>93.85454134019609</v>
       </c>
       <c r="F772" t="n">
         <v>397099</v>
@@ -15912,16 +15912,16 @@
         <v>45602</v>
       </c>
       <c r="B775" t="n">
-        <v>94.72709655761719</v>
+        <v>94.72708892822266</v>
       </c>
       <c r="C775" t="n">
-        <v>95.38614751126146</v>
+        <v>95.38613982878644</v>
       </c>
       <c r="D775" t="n">
-        <v>91.81241731725275</v>
+        <v>91.81240992260877</v>
       </c>
       <c r="E775" t="n">
-        <v>94.2165606376484</v>
+        <v>94.21655304937283</v>
       </c>
       <c r="F775" t="n">
         <v>484922</v>
@@ -15972,16 +15972,16 @@
         <v>45607</v>
       </c>
       <c r="B778" t="n">
-        <v>92.10945129394531</v>
+        <v>92.10944366455078</v>
       </c>
       <c r="C778" t="n">
-        <v>93.48324540630318</v>
+        <v>93.48323766311775</v>
       </c>
       <c r="D778" t="n">
-        <v>90.58712798917934</v>
+        <v>90.58712048587832</v>
       </c>
       <c r="E778" t="n">
-        <v>91.52465433631919</v>
+        <v>91.52464675536318</v>
       </c>
       <c r="F778" t="n">
         <v>447451</v>
@@ -16012,16 +16012,16 @@
         <v>45609</v>
       </c>
       <c r="B780" t="n">
-        <v>90.29008483886719</v>
+        <v>90.29007720947266</v>
       </c>
       <c r="C780" t="n">
-        <v>91.10694222829758</v>
+        <v>91.10693452987967</v>
       </c>
       <c r="D780" t="n">
-        <v>89.3432812343007</v>
+        <v>89.34327368490983</v>
       </c>
       <c r="E780" t="n">
-        <v>90.8470356341783</v>
+        <v>90.84702795772213</v>
       </c>
       <c r="F780" t="n">
         <v>352617</v>
@@ -16092,16 +16092,16 @@
         <v>45617</v>
       </c>
       <c r="B784" t="n">
-        <v>83.69029998779297</v>
+        <v>83.69029235839844</v>
       </c>
       <c r="C784" t="n">
-        <v>85.30543904371771</v>
+        <v>85.30543126708351</v>
       </c>
       <c r="D784" t="n">
-        <v>83.30043297546001</v>
+        <v>83.30042538160664</v>
       </c>
       <c r="E784" t="n">
-        <v>85.1662013308791</v>
+        <v>85.16619356693812</v>
       </c>
       <c r="F784" t="n">
         <v>1016945</v>
@@ -16132,16 +16132,16 @@
         <v>45621</v>
       </c>
       <c r="B786" t="n">
-        <v>85.59317779541016</v>
+        <v>85.59318542480469</v>
       </c>
       <c r="C786" t="n">
-        <v>86.31720528548094</v>
+        <v>86.31721297941206</v>
       </c>
       <c r="D786" t="n">
-        <v>84.42359111349106</v>
+        <v>84.42359863863385</v>
       </c>
       <c r="E786" t="n">
-        <v>85.32398681644892</v>
+        <v>85.32399442184897</v>
       </c>
       <c r="F786" t="n">
         <v>384525</v>
@@ -16272,16 +16272,16 @@
         <v>45630</v>
       </c>
       <c r="B793" t="n">
-        <v>75.2247314453125</v>
+        <v>75.22472381591797</v>
       </c>
       <c r="C793" t="n">
-        <v>76.09728117894873</v>
+        <v>76.09727346105902</v>
       </c>
       <c r="D793" t="n">
-        <v>74.39859664377688</v>
+        <v>74.39858909817006</v>
       </c>
       <c r="E793" t="n">
-        <v>75.41966141267126</v>
+        <v>75.41965376350666</v>
       </c>
       <c r="F793" t="n">
         <v>411810</v>
@@ -16292,16 +16292,16 @@
         <v>45631</v>
       </c>
       <c r="B794" t="n">
-        <v>75.51248168945312</v>
+        <v>75.51247406005859</v>
       </c>
       <c r="C794" t="n">
-        <v>77.57317996447813</v>
+        <v>77.5731721268812</v>
       </c>
       <c r="D794" t="n">
-        <v>74.09227263015862</v>
+        <v>74.09226514425474</v>
       </c>
       <c r="E794" t="n">
-        <v>75.65171939921073</v>
+        <v>75.65171175574832</v>
       </c>
       <c r="F794" t="n">
         <v>973742</v>
@@ -16312,16 +16312,16 @@
         <v>45632</v>
       </c>
       <c r="B795" t="n">
-        <v>75.78166198730469</v>
+        <v>75.78166961669922</v>
       </c>
       <c r="C795" t="n">
-        <v>75.78166198730469</v>
+        <v>75.78166961669922</v>
       </c>
       <c r="D795" t="n">
-        <v>74.25934596164483</v>
+        <v>74.25935343777866</v>
       </c>
       <c r="E795" t="n">
-        <v>75.65170869842567</v>
+        <v>75.651716314737</v>
       </c>
       <c r="F795" t="n">
         <v>1017781</v>
@@ -16332,16 +16332,16 @@
         <v>45635</v>
       </c>
       <c r="B796" t="n">
-        <v>75.51248168945312</v>
+        <v>75.51247406005859</v>
       </c>
       <c r="C796" t="n">
-        <v>78.0651470679541</v>
+        <v>78.06513918065133</v>
       </c>
       <c r="D796" t="n">
-        <v>75.51248168945312</v>
+        <v>75.51247406005859</v>
       </c>
       <c r="E796" t="n">
-        <v>76.11584037711999</v>
+        <v>76.11583268676519</v>
       </c>
       <c r="F796" t="n">
         <v>291521</v>
@@ -16452,16 +16452,16 @@
         <v>45643</v>
       </c>
       <c r="B802" t="n">
-        <v>77.18950653076172</v>
+        <v>77.18951416015625</v>
       </c>
       <c r="C802" t="n">
-        <v>78.9191654754832</v>
+        <v>78.91917327583685</v>
       </c>
       <c r="D802" t="n">
-        <v>75.78233483874901</v>
+        <v>75.78234232905898</v>
       </c>
       <c r="E802" t="n">
-        <v>76.12435547724201</v>
+        <v>76.12436300135722</v>
       </c>
       <c r="F802" t="n">
         <v>713503</v>
@@ -16492,16 +16492,16 @@
         <v>45645</v>
       </c>
       <c r="B804" t="n">
-        <v>72.4598388671875</v>
+        <v>72.45983123779297</v>
       </c>
       <c r="C804" t="n">
-        <v>73.96473726095877</v>
+        <v>73.96472947311145</v>
       </c>
       <c r="D804" t="n">
-        <v>71.17969371703964</v>
+        <v>71.17968622243332</v>
       </c>
       <c r="E804" t="n">
-        <v>72.37188643518905</v>
+        <v>72.37187881505514</v>
       </c>
       <c r="F804" t="n">
         <v>633891</v>
@@ -16532,16 +16532,16 @@
         <v>45649</v>
       </c>
       <c r="B806" t="n">
-        <v>72.79207611083984</v>
+        <v>72.79208374023438</v>
       </c>
       <c r="C806" t="n">
-        <v>73.45657651880434</v>
+        <v>73.45658421784569</v>
       </c>
       <c r="D806" t="n">
-        <v>71.0721988418062</v>
+        <v>71.07220629093905</v>
       </c>
       <c r="E806" t="n">
-        <v>72.32302138491811</v>
+        <v>72.32302896515064</v>
       </c>
       <c r="F806" t="n">
         <v>510211</v>
@@ -16572,16 +16572,16 @@
         <v>45653</v>
       </c>
       <c r="B808" t="n">
-        <v>72.35234832763672</v>
+        <v>72.35234069824219</v>
       </c>
       <c r="C808" t="n">
-        <v>73.83769847912376</v>
+        <v>73.83769069310235</v>
       </c>
       <c r="D808" t="n">
-        <v>72.35234832763672</v>
+        <v>72.35234069824219</v>
       </c>
       <c r="E808" t="n">
-        <v>73.29046538996933</v>
+        <v>73.29045766165243</v>
       </c>
       <c r="F808" t="n">
         <v>193425</v>
@@ -16612,16 +16612,16 @@
         <v>45659</v>
       </c>
       <c r="B810" t="n">
-        <v>70.56405639648438</v>
+        <v>70.56404876708984</v>
       </c>
       <c r="C810" t="n">
-        <v>72.74322942844815</v>
+        <v>72.74322156344115</v>
       </c>
       <c r="D810" t="n">
-        <v>69.73343264596139</v>
+        <v>69.733425106374</v>
       </c>
       <c r="E810" t="n">
-        <v>71.88328323031399</v>
+        <v>71.8832754582845</v>
       </c>
       <c r="F810" t="n">
         <v>241349</v>
@@ -16732,16 +16732,16 @@
         <v>45667</v>
       </c>
       <c r="B816" t="n">
-        <v>66.62591552734375</v>
+        <v>66.62590789794922</v>
       </c>
       <c r="C816" t="n">
-        <v>67.14383359335977</v>
+        <v>67.14382590465797</v>
       </c>
       <c r="D816" t="n">
-        <v>65.19919544467032</v>
+        <v>65.19918797865081</v>
       </c>
       <c r="E816" t="n">
-        <v>65.58030524628556</v>
+        <v>65.58029773662483</v>
       </c>
       <c r="F816" t="n">
         <v>598954</v>
@@ -16752,16 +16752,16 @@
         <v>45670</v>
       </c>
       <c r="B817" t="n">
-        <v>67.87673187255859</v>
+        <v>67.87673950195312</v>
       </c>
       <c r="C817" t="n">
-        <v>68.63895140467909</v>
+        <v>68.63895911974765</v>
       </c>
       <c r="D817" t="n">
-        <v>65.75619651668684</v>
+        <v>65.75620390773163</v>
       </c>
       <c r="E817" t="n">
-        <v>66.57704602651182</v>
+        <v>66.5770535098207</v>
       </c>
       <c r="F817" t="n">
         <v>512624</v>
@@ -16792,16 +16792,16 @@
         <v>45672</v>
       </c>
       <c r="B819" t="n">
-        <v>69.77251434326172</v>
+        <v>69.77252197265625</v>
       </c>
       <c r="C819" t="n">
-        <v>69.96795257353654</v>
+        <v>69.96796022430158</v>
       </c>
       <c r="D819" t="n">
-        <v>66.75294373372894</v>
+        <v>66.75295103294337</v>
       </c>
       <c r="E819" t="n">
-        <v>66.75294373372894</v>
+        <v>66.75295103294337</v>
       </c>
       <c r="F819" t="n">
         <v>444557</v>
@@ -17032,16 +17032,16 @@
         <v>45688</v>
       </c>
       <c r="B831" t="n">
-        <v>77.98104858398438</v>
+        <v>77.98105621337891</v>
       </c>
       <c r="C831" t="n">
-        <v>80.18952896866313</v>
+        <v>80.18953681412769</v>
       </c>
       <c r="D831" t="n">
-        <v>77.37517812716173</v>
+        <v>77.37518569728</v>
       </c>
       <c r="E831" t="n">
-        <v>79.74001506411371</v>
+        <v>79.7400228655994</v>
       </c>
       <c r="F831" t="n">
         <v>229217</v>
@@ -17072,16 +17072,16 @@
         <v>45692</v>
       </c>
       <c r="B833" t="n">
-        <v>78.51851654052734</v>
+        <v>78.51850891113281</v>
       </c>
       <c r="C833" t="n">
-        <v>79.76933928144435</v>
+        <v>79.76933153051134</v>
       </c>
       <c r="D833" t="n">
-        <v>77.01361810052045</v>
+        <v>77.01361061735211</v>
       </c>
       <c r="E833" t="n">
-        <v>78.95826380304736</v>
+        <v>78.95825613092398</v>
       </c>
       <c r="F833" t="n">
         <v>404279</v>
@@ -17252,16 +17252,16 @@
         <v>45705</v>
       </c>
       <c r="B842" t="n">
-        <v>81.79215240478516</v>
+        <v>81.79214477539062</v>
       </c>
       <c r="C842" t="n">
-        <v>84.23516779866155</v>
+        <v>84.23515994138785</v>
       </c>
       <c r="D842" t="n">
-        <v>80.99084365381336</v>
+        <v>80.99083609916316</v>
       </c>
       <c r="E842" t="n">
-        <v>82.28075548356044</v>
+        <v>82.28074780859008</v>
       </c>
       <c r="F842" t="n">
         <v>317686</v>
@@ -17412,16 +17412,16 @@
         <v>45715</v>
       </c>
       <c r="B850" t="n">
-        <v>82.19281005859375</v>
+        <v>82.19280242919922</v>
       </c>
       <c r="C850" t="n">
-        <v>84.69445542248718</v>
+        <v>84.69444756088208</v>
       </c>
       <c r="D850" t="n">
-        <v>81.9387343714823</v>
+        <v>81.93872676567187</v>
       </c>
       <c r="E850" t="n">
-        <v>82.2612141910286</v>
+        <v>82.2612065552846</v>
       </c>
       <c r="F850" t="n">
         <v>386526</v>
@@ -17492,16 +17492,16 @@
         <v>45723</v>
       </c>
       <c r="B854" t="n">
-        <v>86.96157073974609</v>
+        <v>86.96156311035156</v>
       </c>
       <c r="C854" t="n">
-        <v>87.2058722703318</v>
+        <v>87.20586461950396</v>
       </c>
       <c r="D854" t="n">
-        <v>81.6358003551744</v>
+        <v>81.63579319302536</v>
       </c>
       <c r="E854" t="n">
-        <v>82.23189668624276</v>
+        <v>82.23188947179645</v>
       </c>
       <c r="F854" t="n">
         <v>477946</v>
@@ -17512,16 +17512,16 @@
         <v>45726</v>
       </c>
       <c r="B855" t="n">
-        <v>86.60977935791016</v>
+        <v>86.60977172851562</v>
       </c>
       <c r="C855" t="n">
-        <v>87.33291728494093</v>
+        <v>87.33290959184569</v>
       </c>
       <c r="D855" t="n">
-        <v>85.90619718466415</v>
+        <v>85.90618961724768</v>
       </c>
       <c r="E855" t="n">
-        <v>85.90619718466415</v>
+        <v>85.90618961724768</v>
       </c>
       <c r="F855" t="n">
         <v>418727</v>
@@ -17552,16 +17552,16 @@
         <v>45728</v>
       </c>
       <c r="B857" t="n">
-        <v>80.08203887939453</v>
+        <v>80.08203125</v>
       </c>
       <c r="C857" t="n">
-        <v>84.72376796838242</v>
+        <v>84.72375989677158</v>
       </c>
       <c r="D857" t="n">
-        <v>77.38495534511513</v>
+        <v>77.38494797267103</v>
       </c>
       <c r="E857" t="n">
-        <v>84.29380234355746</v>
+        <v>84.29379431290934</v>
       </c>
       <c r="F857" t="n">
         <v>1616980</v>
@@ -17732,16 +17732,16 @@
         <v>45741</v>
       </c>
       <c r="B866" t="n">
-        <v>82.01691436767578</v>
+        <v>82.01690673828125</v>
       </c>
       <c r="C866" t="n">
-        <v>84.42084065770479</v>
+        <v>84.42083280469173</v>
       </c>
       <c r="D866" t="n">
-        <v>80.61950924258466</v>
+        <v>80.61950174317984</v>
       </c>
       <c r="E866" t="n">
-        <v>83.08206551721464</v>
+        <v>83.0820577887374</v>
       </c>
       <c r="F866" t="n">
         <v>769467</v>
@@ -17752,16 +17752,16 @@
         <v>45742</v>
       </c>
       <c r="B867" t="n">
-        <v>82.81822204589844</v>
+        <v>82.81821441650391</v>
       </c>
       <c r="C867" t="n">
-        <v>83.15046856160603</v>
+        <v>83.15046090160423</v>
       </c>
       <c r="D867" t="n">
-        <v>81.10811126618962</v>
+        <v>81.10810379433421</v>
       </c>
       <c r="E867" t="n">
-        <v>81.59671434610642</v>
+        <v>81.59670682923984</v>
       </c>
       <c r="F867" t="n">
         <v>621808</v>
@@ -17792,16 +17792,16 @@
         <v>45744</v>
       </c>
       <c r="B869" t="n">
-        <v>83.47294616699219</v>
+        <v>83.47293853759766</v>
       </c>
       <c r="C869" t="n">
-        <v>83.74656269160093</v>
+        <v>83.74655503719795</v>
       </c>
       <c r="D869" t="n">
-        <v>80.22862210071933</v>
+        <v>80.22861476785475</v>
       </c>
       <c r="E869" t="n">
-        <v>81.59671217925415</v>
+        <v>81.59670472134668</v>
       </c>
       <c r="F869" t="n">
         <v>1013438</v>
@@ -17832,16 +17832,16 @@
         <v>45748</v>
       </c>
       <c r="B871" t="n">
-        <v>78.28398132324219</v>
+        <v>78.28398895263672</v>
       </c>
       <c r="C871" t="n">
-        <v>79.3882215330526</v>
+        <v>79.3882292700641</v>
       </c>
       <c r="D871" t="n">
-        <v>76.88657630102644</v>
+        <v>76.88658379423278</v>
       </c>
       <c r="E871" t="n">
-        <v>77.56085089626417</v>
+        <v>77.5608584551839</v>
       </c>
       <c r="F871" t="n">
         <v>960198</v>
@@ -17852,16 +17852,16 @@
         <v>45749</v>
       </c>
       <c r="B872" t="n">
-        <v>78.16670989990234</v>
+        <v>78.16671752929688</v>
       </c>
       <c r="C872" t="n">
-        <v>78.76280618720718</v>
+        <v>78.76281387478318</v>
       </c>
       <c r="D872" t="n">
-        <v>76.86703151877802</v>
+        <v>76.86703902131858</v>
       </c>
       <c r="E872" t="n">
-        <v>78.09830577458001</v>
+        <v>78.09831339729801</v>
       </c>
       <c r="F872" t="n">
         <v>373719</v>
@@ -17872,16 +17872,16 @@
         <v>45750</v>
       </c>
       <c r="B873" t="n">
-        <v>78.32307434082031</v>
+        <v>78.32306671142578</v>
       </c>
       <c r="C873" t="n">
-        <v>79.06575310166777</v>
+        <v>79.06574539992943</v>
       </c>
       <c r="D873" t="n">
-        <v>75.8214215294108</v>
+        <v>75.82141414370047</v>
       </c>
       <c r="E873" t="n">
-        <v>77.10156665445534</v>
+        <v>77.10155914404699</v>
       </c>
       <c r="F873" t="n">
         <v>721024</v>
@@ -17892,16 +17892,16 @@
         <v>45751</v>
       </c>
       <c r="B874" t="n">
-        <v>73.78883361816406</v>
+        <v>73.78884124755859</v>
       </c>
       <c r="C874" t="n">
-        <v>77.65856882284673</v>
+        <v>77.65857685235244</v>
       </c>
       <c r="D874" t="n">
-        <v>72.93866163963507</v>
+        <v>72.9386691811261</v>
       </c>
       <c r="E874" t="n">
-        <v>76.71067772684667</v>
+        <v>76.7106856583452</v>
       </c>
       <c r="F874" t="n">
         <v>1192804</v>
@@ -17912,16 +17912,16 @@
         <v>45754</v>
       </c>
       <c r="B875" t="n">
-        <v>73.09501647949219</v>
+        <v>73.09502410888672</v>
       </c>
       <c r="C875" t="n">
-        <v>76.01686051972106</v>
+        <v>76.01686845408716</v>
       </c>
       <c r="D875" t="n">
-        <v>70.59336388899551</v>
+        <v>70.59337125727656</v>
       </c>
       <c r="E875" t="n">
-        <v>72.17644039470501</v>
+        <v>72.17644792822188</v>
       </c>
       <c r="F875" t="n">
         <v>726435</v>
@@ -17932,16 +17932,16 @@
         <v>45755</v>
       </c>
       <c r="B876" t="n">
-        <v>75.0494384765625</v>
+        <v>75.04943084716797</v>
       </c>
       <c r="C876" t="n">
-        <v>77.47290565599279</v>
+        <v>77.47289778023283</v>
       </c>
       <c r="D876" t="n">
-        <v>74.10154727809095</v>
+        <v>74.10153974505738</v>
       </c>
       <c r="E876" t="n">
-        <v>76.22208292396535</v>
+        <v>76.22207517536182</v>
       </c>
       <c r="F876" t="n">
         <v>1315177</v>
@@ -18052,16 +18052,16 @@
         <v>45763</v>
       </c>
       <c r="B882" t="n">
-        <v>78.49897003173828</v>
+        <v>78.49896240234375</v>
       </c>
       <c r="C882" t="n">
-        <v>79.83773765524597</v>
+        <v>79.83772989573525</v>
       </c>
       <c r="D882" t="n">
-        <v>77.92241453950848</v>
+        <v>77.92240696614996</v>
       </c>
       <c r="E882" t="n">
-        <v>79.15369634801512</v>
+        <v>79.15368865498706</v>
       </c>
       <c r="F882" t="n">
         <v>449643</v>
@@ -18112,16 +18112,16 @@
         <v>45770</v>
       </c>
       <c r="B885" t="n">
-        <v>84.3328857421875</v>
+        <v>84.33289337158203</v>
       </c>
       <c r="C885" t="n">
-        <v>85.00715285211088</v>
+        <v>85.00716054250474</v>
       </c>
       <c r="D885" t="n">
-        <v>81.96804141692802</v>
+        <v>81.96804883238075</v>
       </c>
       <c r="E885" t="n">
-        <v>82.60322684538413</v>
+        <v>82.60323431830055</v>
       </c>
       <c r="F885" t="n">
         <v>698539</v>
@@ -18192,16 +18192,16 @@
         <v>45776</v>
       </c>
       <c r="B889" t="n">
-        <v>88.583740234375</v>
+        <v>88.58373260498047</v>
       </c>
       <c r="C889" t="n">
-        <v>90.62609753796141</v>
+        <v>90.62608973266609</v>
       </c>
       <c r="D889" t="n">
-        <v>88.583740234375</v>
+        <v>88.58373260498047</v>
       </c>
       <c r="E889" t="n">
-        <v>89.41436398245803</v>
+        <v>89.4143562815249</v>
       </c>
       <c r="F889" t="n">
         <v>288735</v>
@@ -18272,16 +18272,16 @@
         <v>45783</v>
       </c>
       <c r="B893" t="n">
-        <v>88.32966613769531</v>
+        <v>88.32965850830078</v>
       </c>
       <c r="C893" t="n">
-        <v>90.03000280574344</v>
+        <v>90.02999502948387</v>
       </c>
       <c r="D893" t="n">
-        <v>87.9485563233999</v>
+        <v>87.94854872692339</v>
       </c>
       <c r="E893" t="n">
-        <v>87.9485563233999</v>
+        <v>87.94854872692339</v>
       </c>
       <c r="F893" t="n">
         <v>191886</v>
@@ -18292,16 +18292,16 @@
         <v>45784</v>
       </c>
       <c r="B894" t="n">
-        <v>89.16028594970703</v>
+        <v>89.1602783203125</v>
       </c>
       <c r="C894" t="n">
-        <v>89.26777922133371</v>
+        <v>89.26777158274103</v>
       </c>
       <c r="D894" t="n">
-        <v>87.0983804019461</v>
+        <v>87.09837294898765</v>
       </c>
       <c r="E894" t="n">
-        <v>88.43715549507488</v>
+        <v>88.43714792755821</v>
       </c>
       <c r="F894" t="n">
         <v>251191</v>
@@ -18312,16 +18312,16 @@
         <v>45785</v>
       </c>
       <c r="B895" t="n">
-        <v>97.71083068847656</v>
+        <v>97.71083831787109</v>
       </c>
       <c r="C895" t="n">
-        <v>97.71083068847656</v>
+        <v>97.71083831787109</v>
       </c>
       <c r="D895" t="n">
-        <v>88.50555150219621</v>
+        <v>88.50555841283003</v>
       </c>
       <c r="E895" t="n">
-        <v>88.50555150219621</v>
+        <v>88.50555841283003</v>
       </c>
       <c r="F895" t="n">
         <v>1207326</v>
@@ -18332,16 +18332,16 @@
         <v>45786</v>
       </c>
       <c r="B896" t="n">
-        <v>98.40464782714844</v>
+        <v>98.40465545654297</v>
       </c>
       <c r="C896" t="n">
-        <v>99.0789223981929</v>
+        <v>99.07893007986451</v>
       </c>
       <c r="D896" t="n">
-        <v>97.23200353058388</v>
+        <v>97.23201106906231</v>
       </c>
       <c r="E896" t="n">
-        <v>97.67174327792293</v>
+        <v>97.67175085049476</v>
       </c>
       <c r="F896" t="n">
         <v>488440</v>
@@ -18372,16 +18372,16 @@
         <v>45790</v>
       </c>
       <c r="B898" t="n">
-        <v>101.4242248535156</v>
+        <v>101.4242172241211</v>
       </c>
       <c r="C898" t="n">
-        <v>102.2548485706747</v>
+        <v>102.2548408787985</v>
       </c>
       <c r="D898" t="n">
-        <v>99.1375586386342</v>
+        <v>99.13755118124867</v>
       </c>
       <c r="E898" t="n">
-        <v>99.62616170231497</v>
+        <v>99.62615420817545</v>
       </c>
       <c r="F898" t="n">
         <v>527476</v>
@@ -18392,16 +18392,16 @@
         <v>45791</v>
       </c>
       <c r="B899" t="n">
-        <v>103.1538696289062</v>
+        <v>103.1538772583008</v>
       </c>
       <c r="C899" t="n">
-        <v>104.561048745443</v>
+        <v>104.5610564789144</v>
       </c>
       <c r="D899" t="n">
-        <v>100.3590596921682</v>
+        <v>100.359067114855</v>
       </c>
       <c r="E899" t="n">
-        <v>101.3362657552098</v>
+        <v>101.3362732501719</v>
       </c>
       <c r="F899" t="n">
         <v>818733</v>
@@ -18432,16 +18432,16 @@
         <v>45793</v>
       </c>
       <c r="B901" t="n">
-        <v>103.593620300293</v>
+        <v>103.5936279296875</v>
       </c>
       <c r="C901" t="n">
-        <v>104.0235859126987</v>
+        <v>104.0235935737591</v>
       </c>
       <c r="D901" t="n">
-        <v>102.3721126805784</v>
+        <v>102.3721202200121</v>
       </c>
       <c r="E901" t="n">
-        <v>103.29068134087</v>
+        <v>103.2906889479539</v>
       </c>
       <c r="F901" t="n">
         <v>726672</v>
@@ -18452,16 +18452,16 @@
         <v>45796</v>
       </c>
       <c r="B902" t="n">
-        <v>102.2157592773438</v>
+        <v>102.2157516479492</v>
       </c>
       <c r="C902" t="n">
-        <v>103.7499725967766</v>
+        <v>103.7499648528683</v>
       </c>
       <c r="D902" t="n">
-        <v>101.6685262326006</v>
+        <v>101.6685186440516</v>
       </c>
       <c r="E902" t="n">
-        <v>103.5643085025908</v>
+        <v>103.5643007725404</v>
       </c>
       <c r="F902" t="n">
         <v>1026194</v>
@@ -18512,16 +18512,16 @@
         <v>45799</v>
       </c>
       <c r="B905" t="n">
-        <v>103.8770065307617</v>
+        <v>103.8770141601562</v>
       </c>
       <c r="C905" t="n">
-        <v>104.6099110713208</v>
+        <v>104.6099187545445</v>
       </c>
       <c r="D905" t="n">
-        <v>102.3232450279215</v>
+        <v>102.3232525431978</v>
       </c>
       <c r="E905" t="n">
-        <v>103.5838417323419</v>
+        <v>103.5838493402045</v>
       </c>
       <c r="F905" t="n">
         <v>1088124</v>
@@ -18532,16 +18532,16 @@
         <v>45800</v>
       </c>
       <c r="B906" t="n">
-        <v>103.2906799316406</v>
+        <v>103.2906875610352</v>
       </c>
       <c r="C906" t="n">
-        <v>104.3851534279493</v>
+        <v>104.3851611381853</v>
       </c>
       <c r="D906" t="n">
-        <v>100.8769871706277</v>
+        <v>100.8769946217388</v>
       </c>
       <c r="E906" t="n">
-        <v>102.7043577732752</v>
+        <v>102.704365359362</v>
       </c>
       <c r="F906" t="n">
         <v>895232</v>
@@ -18552,16 +18552,16 @@
         <v>45803</v>
       </c>
       <c r="B907" t="n">
-        <v>103.798828125</v>
+        <v>103.7988357543945</v>
       </c>
       <c r="C907" t="n">
-        <v>104.6587667675181</v>
+        <v>104.6587744601196</v>
       </c>
       <c r="D907" t="n">
-        <v>102.997519459895</v>
+        <v>102.997527030392</v>
       </c>
       <c r="E907" t="n">
-        <v>102.997519459895</v>
+        <v>102.997527030392</v>
       </c>
       <c r="F907" t="n">
         <v>188218</v>
@@ -18612,16 +18612,16 @@
         <v>45806</v>
       </c>
       <c r="B910" t="n">
-        <v>107.2679061889648</v>
+        <v>107.2679138183594</v>
       </c>
       <c r="C910" t="n">
-        <v>108.8021194087094</v>
+        <v>108.8021271472243</v>
       </c>
       <c r="D910" t="n">
-        <v>106.3981933898703</v>
+        <v>106.3982009574068</v>
       </c>
       <c r="E910" t="n">
-        <v>108.2353455586916</v>
+        <v>108.235353256895</v>
       </c>
       <c r="F910" t="n">
         <v>645105</v>
@@ -18652,16 +18652,16 @@
         <v>45810</v>
       </c>
       <c r="B912" t="n">
-        <v>107.4047317504883</v>
+        <v>107.4047241210938</v>
       </c>
       <c r="C912" t="n">
-        <v>109.2027874916251</v>
+        <v>109.2027797345073</v>
       </c>
       <c r="D912" t="n">
-        <v>106.7402312688744</v>
+        <v>106.740223686682</v>
       </c>
       <c r="E912" t="n">
-        <v>108.5480611590693</v>
+        <v>108.5480534484594</v>
       </c>
       <c r="F912" t="n">
         <v>325434</v>
@@ -18712,16 +18712,16 @@
         <v>45813</v>
       </c>
       <c r="B915" t="n">
-        <v>108.3917007446289</v>
+        <v>108.3916931152344</v>
       </c>
       <c r="C915" t="n">
-        <v>108.7532696920168</v>
+        <v>108.7532620371724</v>
       </c>
       <c r="D915" t="n">
-        <v>107.0529331354047</v>
+        <v>107.0529256002424</v>
       </c>
       <c r="E915" t="n">
-        <v>107.8835568440347</v>
+        <v>107.8835492504071</v>
       </c>
       <c r="F915" t="n">
         <v>989620</v>
@@ -18732,16 +18732,16 @@
         <v>45814</v>
       </c>
       <c r="B916" t="n">
-        <v>107.5513076782227</v>
+        <v>107.5513000488281</v>
       </c>
       <c r="C916" t="n">
-        <v>108.9584869356147</v>
+        <v>108.9584792063988</v>
       </c>
       <c r="D916" t="n">
-        <v>106.4861565415238</v>
+        <v>106.4861489876882</v>
       </c>
       <c r="E916" t="n">
-        <v>108.3721647301985</v>
+        <v>108.3721570425746</v>
       </c>
       <c r="F916" t="n">
         <v>400888</v>
@@ -18752,16 +18752,16 @@
         <v>45817</v>
       </c>
       <c r="B917" t="n">
-        <v>106.2809371948242</v>
+        <v>106.2809448242188</v>
       </c>
       <c r="C917" t="n">
-        <v>108.2744385273175</v>
+        <v>108.2744462998158</v>
       </c>
       <c r="D917" t="n">
-        <v>105.772785849321</v>
+        <v>105.7727934422378</v>
       </c>
       <c r="E917" t="n">
-        <v>107.1995058562494</v>
+        <v>107.1995135515835</v>
       </c>
       <c r="F917" t="n">
         <v>436201</v>
@@ -18772,16 +18772,16 @@
         <v>45818</v>
       </c>
       <c r="B918" t="n">
-        <v>108.6848678588867</v>
+        <v>108.6848602294922</v>
       </c>
       <c r="C918" t="n">
-        <v>109.7109298304698</v>
+        <v>109.7109221290484</v>
       </c>
       <c r="D918" t="n">
-        <v>106.8086338632852</v>
+        <v>106.8086263655974</v>
       </c>
       <c r="E918" t="n">
-        <v>106.8086338632852</v>
+        <v>106.8086263655974</v>
       </c>
       <c r="F918" t="n">
         <v>299047</v>
@@ -18872,16 +18872,16 @@
         <v>45825</v>
       </c>
       <c r="B923" t="n">
-        <v>107.5903930664062</v>
+        <v>107.5903854370117</v>
       </c>
       <c r="C923" t="n">
-        <v>107.8444687469043</v>
+        <v>107.8444610994928</v>
       </c>
       <c r="D923" t="n">
-        <v>105.7630223808585</v>
+        <v>105.7630148810455</v>
       </c>
       <c r="E923" t="n">
-        <v>107.7858387650551</v>
+        <v>107.7858311218013</v>
       </c>
       <c r="F923" t="n">
         <v>359643</v>
@@ -18892,16 +18892,16 @@
         <v>45826</v>
       </c>
       <c r="B924" t="n">
-        <v>106.9845275878906</v>
+        <v>106.9845352172852</v>
       </c>
       <c r="C924" t="n">
-        <v>107.6881097204315</v>
+        <v>107.6881174000007</v>
       </c>
       <c r="D924" t="n">
-        <v>105.8314240865031</v>
+        <v>105.8314316336663</v>
       </c>
       <c r="E924" t="n">
-        <v>107.0040684295622</v>
+        <v>107.0040760603503</v>
       </c>
       <c r="F924" t="n">
         <v>439989</v>
@@ -18912,16 +18912,16 @@
         <v>45828</v>
       </c>
       <c r="B925" t="n">
-        <v>104.7076416015625</v>
+        <v>104.707633972168</v>
       </c>
       <c r="C925" t="n">
-        <v>107.0040745879219</v>
+        <v>107.0040667912006</v>
       </c>
       <c r="D925" t="n">
-        <v>104.629463319395</v>
+        <v>104.6294556956968</v>
       </c>
       <c r="E925" t="n">
-        <v>107.0040745879219</v>
+        <v>107.0040667912006</v>
       </c>
       <c r="F925" t="n">
         <v>336419</v>
@@ -18952,16 +18952,16 @@
         <v>45832</v>
       </c>
       <c r="B927" t="n">
-        <v>103.593620300293</v>
+        <v>103.5936279296875</v>
       </c>
       <c r="C927" t="n">
-        <v>106.0854913712162</v>
+        <v>106.0854991841304</v>
       </c>
       <c r="D927" t="n">
-        <v>103.1050172524071</v>
+        <v>103.1050248458173</v>
       </c>
       <c r="E927" t="n">
-        <v>103.1050172524071</v>
+        <v>103.1050248458173</v>
       </c>
       <c r="F927" t="n">
         <v>471744</v>
@@ -19072,16 +19072,16 @@
         <v>45840</v>
       </c>
       <c r="B933" t="n">
-        <v>103.3004531860352</v>
+        <v>103.3004608154297</v>
       </c>
       <c r="C933" t="n">
-        <v>106.0952631540645</v>
+        <v>106.0952709898735</v>
       </c>
       <c r="D933" t="n">
-        <v>103.2418232073532</v>
+        <v>103.2418308324176</v>
       </c>
       <c r="E933" t="n">
-        <v>106.0561740164463</v>
+        <v>106.0561818493683</v>
       </c>
       <c r="F933" t="n">
         <v>463221</v>
@@ -19112,16 +19112,16 @@
         <v>45842</v>
       </c>
       <c r="B935" t="n">
-        <v>103.593620300293</v>
+        <v>103.5936279296875</v>
       </c>
       <c r="C935" t="n">
-        <v>104.736949643028</v>
+        <v>104.7369573566257</v>
       </c>
       <c r="D935" t="n">
-        <v>102.899804866954</v>
+        <v>102.8998124452508</v>
       </c>
       <c r="E935" t="n">
-        <v>102.9095715599583</v>
+        <v>102.9095791389745</v>
       </c>
       <c r="F935" t="n">
         <v>75389</v>
@@ -19132,16 +19132,16 @@
         <v>45845</v>
       </c>
       <c r="B936" t="n">
-        <v>104.4535675048828</v>
+        <v>104.4535598754883</v>
       </c>
       <c r="C936" t="n">
-        <v>104.8444514661891</v>
+        <v>104.844443808244</v>
       </c>
       <c r="D936" t="n">
-        <v>103.5740804558166</v>
+        <v>103.5740728906607</v>
       </c>
       <c r="E936" t="n">
-        <v>104.3167592367493</v>
+        <v>104.3167516173474</v>
       </c>
       <c r="F936" t="n">
         <v>614814</v>
@@ -19152,16 +19152,16 @@
         <v>45846</v>
       </c>
       <c r="B937" t="n">
-        <v>102.8998031616211</v>
+        <v>102.8998107910156</v>
       </c>
       <c r="C937" t="n">
-        <v>104.9323861409677</v>
+        <v>104.9323939210659</v>
       </c>
       <c r="D937" t="n">
-        <v>102.616412503885</v>
+        <v>102.6164201122678</v>
       </c>
       <c r="E937" t="n">
-        <v>103.5936185834616</v>
+        <v>103.5936262642984</v>
       </c>
       <c r="F937" t="n">
         <v>319689</v>
@@ -19192,16 +19192,16 @@
         <v>45848</v>
       </c>
       <c r="B939" t="n">
-        <v>100.8379058837891</v>
+        <v>100.8378982543945</v>
       </c>
       <c r="C939" t="n">
-        <v>103.2222838408521</v>
+        <v>103.2222760310556</v>
       </c>
       <c r="D939" t="n">
-        <v>99.47958991988082</v>
+        <v>99.47958239325645</v>
       </c>
       <c r="E939" t="n">
-        <v>102.8802631764672</v>
+        <v>102.8802553925479</v>
       </c>
       <c r="F939" t="n">
         <v>532452</v>
@@ -19232,16 +19232,16 @@
         <v>45852</v>
       </c>
       <c r="B941" t="n">
-        <v>98.11148834228516</v>
+        <v>98.11149597167969</v>
       </c>
       <c r="C941" t="n">
-        <v>99.43071501103869</v>
+        <v>99.43072274301957</v>
       </c>
       <c r="D941" t="n">
-        <v>97.74991942190482</v>
+        <v>97.74992702318283</v>
       </c>
       <c r="E941" t="n">
-        <v>98.94211198887142</v>
+        <v>98.94211968285731</v>
       </c>
       <c r="F941" t="n">
         <v>223357</v>
@@ -19252,16 +19252,16 @@
         <v>45853</v>
       </c>
       <c r="B942" t="n">
-        <v>98.70758819580078</v>
+        <v>98.70759582519531</v>
       </c>
       <c r="C942" t="n">
-        <v>99.33299949035536</v>
+        <v>99.33300716808975</v>
       </c>
       <c r="D942" t="n">
-        <v>97.82810123299254</v>
+        <v>97.82810879440898</v>
       </c>
       <c r="E942" t="n">
-        <v>98.12126603909219</v>
+        <v>98.12127362316819</v>
       </c>
       <c r="F942" t="n">
         <v>259679</v>
@@ -19272,16 +19272,16 @@
         <v>45854</v>
       </c>
       <c r="B943" t="n">
-        <v>99.80205535888672</v>
+        <v>99.80206298828125</v>
       </c>
       <c r="C943" t="n">
-        <v>100.0365901886073</v>
+        <v>100.0365978359309</v>
       </c>
       <c r="D943" t="n">
-        <v>97.96491059235345</v>
+        <v>97.96491808130695</v>
       </c>
       <c r="E943" t="n">
-        <v>98.71735600177402</v>
+        <v>98.71736354824841</v>
       </c>
       <c r="F943" t="n">
         <v>444283</v>
@@ -19332,16 +19332,16 @@
         <v>45859</v>
       </c>
       <c r="B946" t="n">
-        <v>92.297119140625</v>
+        <v>92.29711151123047</v>
       </c>
       <c r="C946" t="n">
-        <v>93.63589426831037</v>
+        <v>93.63588652825102</v>
       </c>
       <c r="D946" t="n">
-        <v>91.88669434136077</v>
+        <v>91.88668674589246</v>
       </c>
       <c r="E946" t="n">
-        <v>93.03002376309314</v>
+        <v>93.0300160731158</v>
       </c>
       <c r="F946" t="n">
         <v>459254</v>
@@ -19372,16 +19372,16 @@
         <v>45861</v>
       </c>
       <c r="B948" t="n">
-        <v>91.75965881347656</v>
+        <v>91.75965118408203</v>
       </c>
       <c r="C948" t="n">
-        <v>92.32644016878999</v>
+        <v>92.32643249227019</v>
       </c>
       <c r="D948" t="n">
-        <v>91.07561003639412</v>
+        <v>91.0756024638751</v>
       </c>
       <c r="E948" t="n">
-        <v>92.26780273015984</v>
+        <v>92.26779505851549</v>
       </c>
       <c r="F948" t="n">
         <v>201915</v>
@@ -19392,16 +19392,16 @@
         <v>45862</v>
       </c>
       <c r="B949" t="n">
-        <v>90.00068664550781</v>
+        <v>90.00067901611328</v>
       </c>
       <c r="C949" t="n">
-        <v>92.03327726570676</v>
+        <v>92.0332694640087</v>
       </c>
       <c r="D949" t="n">
-        <v>89.64889182833909</v>
+        <v>89.64888422876635</v>
       </c>
       <c r="E949" t="n">
-        <v>92.03327726570676</v>
+        <v>92.0332694640087</v>
       </c>
       <c r="F949" t="n">
         <v>148443</v>
@@ -19412,16 +19412,16 @@
         <v>45863</v>
       </c>
       <c r="B950" t="n">
-        <v>89.61956787109375</v>
+        <v>89.61957550048828</v>
       </c>
       <c r="C950" t="n">
-        <v>90.68472636527164</v>
+        <v>90.68473408534409</v>
       </c>
       <c r="D950" t="n">
-        <v>89.27754723736346</v>
+        <v>89.27755483764147</v>
       </c>
       <c r="E950" t="n">
-        <v>89.46321877659875</v>
+        <v>89.46322639268315</v>
       </c>
       <c r="F950" t="n">
         <v>133512</v>
@@ -19572,16 +19572,16 @@
         <v>45875</v>
       </c>
       <c r="B958" t="n">
-        <v>91.05606842041016</v>
+        <v>91.05606079101562</v>
       </c>
       <c r="C958" t="n">
-        <v>91.3101441043393</v>
+        <v>91.3101364536563</v>
       </c>
       <c r="D958" t="n">
-        <v>90.09840312282569</v>
+        <v>90.09839557367191</v>
       </c>
       <c r="E958" t="n">
-        <v>90.09840312282569</v>
+        <v>90.09839557367191</v>
       </c>
       <c r="F958" t="n">
         <v>142081</v>
@@ -19752,16 +19752,16 @@
         <v>45888</v>
       </c>
       <c r="B967" t="n">
-        <v>85.65211486816406</v>
+        <v>85.65212249755859</v>
       </c>
       <c r="C967" t="n">
-        <v>90.97788505088515</v>
+        <v>90.97789315466845</v>
       </c>
       <c r="D967" t="n">
-        <v>85.40781334683759</v>
+        <v>85.40782095447115</v>
       </c>
       <c r="E967" t="n">
-        <v>90.97788505088515</v>
+        <v>90.97789315466845</v>
       </c>
       <c r="F967" t="n">
         <v>1451209</v>
@@ -19772,16 +19772,16 @@
         <v>45889</v>
       </c>
       <c r="B968" t="n">
-        <v>86.38502502441406</v>
+        <v>86.38501739501953</v>
       </c>
       <c r="C968" t="n">
-        <v>87.58698441207628</v>
+        <v>87.58697667652652</v>
       </c>
       <c r="D968" t="n">
-        <v>85.41759302487036</v>
+        <v>85.41758548091796</v>
       </c>
       <c r="E968" t="n">
-        <v>86.15049763629555</v>
+        <v>86.15049002761413</v>
       </c>
       <c r="F968" t="n">
         <v>1048687</v>
@@ -19832,16 +19832,16 @@
         <v>45894</v>
       </c>
       <c r="B971" t="n">
-        <v>88.92575073242188</v>
+        <v>88.92575836181641</v>
       </c>
       <c r="C971" t="n">
-        <v>89.54138786120821</v>
+        <v>89.5413955434214</v>
       </c>
       <c r="D971" t="n">
-        <v>87.15701016405045</v>
+        <v>87.15701764169569</v>
       </c>
       <c r="E971" t="n">
-        <v>87.15701016405045</v>
+        <v>87.15701764169569</v>
       </c>
       <c r="F971" t="n">
         <v>788338</v>
@@ -19872,16 +19872,16 @@
         <v>45896</v>
       </c>
       <c r="B973" t="n">
-        <v>90.80199432373047</v>
+        <v>90.80198669433594</v>
       </c>
       <c r="C973" t="n">
-        <v>90.80199432373047</v>
+        <v>90.80198669433594</v>
       </c>
       <c r="D973" t="n">
-        <v>88.61305461947694</v>
+        <v>88.61304717400222</v>
       </c>
       <c r="E973" t="n">
-        <v>88.91598614240509</v>
+        <v>88.91597867147736</v>
       </c>
       <c r="F973" t="n">
         <v>1220015</v>
@@ -19932,16 +19932,16 @@
         <v>45901</v>
       </c>
       <c r="B976" t="n">
-        <v>96.010498046875</v>
+        <v>96.01050567626953</v>
       </c>
       <c r="C976" t="n">
-        <v>96.44047111090812</v>
+        <v>96.44047877447011</v>
       </c>
       <c r="D976" t="n">
-        <v>95.27759348163168</v>
+        <v>95.27760105278657</v>
       </c>
       <c r="E976" t="n">
-        <v>95.287367630039</v>
+        <v>95.28737520197058</v>
       </c>
       <c r="F976" t="n">
         <v>152929</v>
@@ -19952,16 +19952,16 @@
         <v>45902</v>
       </c>
       <c r="B977" t="n">
-        <v>95.76620483398438</v>
+        <v>95.76619720458984</v>
       </c>
       <c r="C977" t="n">
-        <v>95.76620483398438</v>
+        <v>95.76619720458984</v>
       </c>
       <c r="D977" t="n">
-        <v>93.71407336435442</v>
+        <v>93.7140658984468</v>
       </c>
       <c r="E977" t="n">
-        <v>95.75643068472903</v>
+        <v>95.75642305611316</v>
       </c>
       <c r="F977" t="n">
         <v>684271</v>
@@ -19972,16 +19972,16 @@
         <v>45903</v>
       </c>
       <c r="B978" t="n">
-        <v>95.60984039306641</v>
+        <v>95.60984802246094</v>
       </c>
       <c r="C978" t="n">
-        <v>96.16685502237223</v>
+        <v>96.16686269621496</v>
       </c>
       <c r="D978" t="n">
-        <v>94.76945001360953</v>
+        <v>94.76945757594329</v>
       </c>
       <c r="E978" t="n">
-        <v>95.75642279785789</v>
+        <v>95.75643043894929</v>
       </c>
       <c r="F978" t="n">
         <v>439208</v>
@@ -20052,16 +20052,16 @@
         <v>45909</v>
       </c>
       <c r="B982" t="n">
-        <v>96.98770141601562</v>
+        <v>96.98770904541016</v>
       </c>
       <c r="C982" t="n">
-        <v>99.08869593526924</v>
+        <v>99.0887037299354</v>
       </c>
       <c r="D982" t="n">
-        <v>96.87043400488615</v>
+        <v>96.87044162505602</v>
       </c>
       <c r="E982" t="n">
-        <v>97.86718836076022</v>
+        <v>97.8671960593383</v>
       </c>
       <c r="F982" t="n">
         <v>316824</v>
@@ -20112,16 +20112,16 @@
         <v>45912</v>
       </c>
       <c r="B985" t="n">
-        <v>98.69781494140625</v>
+        <v>98.69782257080078</v>
       </c>
       <c r="C985" t="n">
-        <v>100.2027132123995</v>
+        <v>100.2027209581235</v>
       </c>
       <c r="D985" t="n">
-        <v>97.80855382220949</v>
+        <v>97.80856138286366</v>
       </c>
       <c r="E985" t="n">
-        <v>99.11801385769326</v>
+        <v>99.1180215195694</v>
       </c>
       <c r="F985" t="n">
         <v>599879</v>
@@ -20132,16 +20132,16 @@
         <v>45915</v>
       </c>
       <c r="B986" t="n">
-        <v>98.02354431152344</v>
+        <v>98.02353668212891</v>
       </c>
       <c r="C986" t="n">
-        <v>99.64571006259945</v>
+        <v>99.6457023069481</v>
       </c>
       <c r="D986" t="n">
-        <v>97.52517455420922</v>
+        <v>97.52516696360394</v>
       </c>
       <c r="E986" t="n">
-        <v>98.69781892558407</v>
+        <v>98.69781124370924</v>
       </c>
       <c r="F986" t="n">
         <v>461876</v>
@@ -20152,16 +20152,16 @@
         <v>45916</v>
       </c>
       <c r="B987" t="n">
-        <v>99.60661315917969</v>
+        <v>99.60662078857422</v>
       </c>
       <c r="C987" t="n">
-        <v>100.4861000969065</v>
+        <v>100.4861077936656</v>
       </c>
       <c r="D987" t="n">
-        <v>97.60333777077366</v>
+        <v>97.60334524672678</v>
       </c>
       <c r="E987" t="n">
-        <v>98.11148909278937</v>
+        <v>98.11149660766448</v>
       </c>
       <c r="F987" t="n">
         <v>502898</v>
@@ -20172,16 +20172,16 @@
         <v>45917</v>
       </c>
       <c r="B988" t="n">
-        <v>102.8998031616211</v>
+        <v>102.8998107910156</v>
       </c>
       <c r="C988" t="n">
-        <v>104.8444411724413</v>
+        <v>104.8444489460189</v>
       </c>
       <c r="D988" t="n">
-        <v>98.74667732342019</v>
+        <v>98.7466846448857</v>
       </c>
       <c r="E988" t="n">
-        <v>99.22550621487537</v>
+        <v>99.22551357184312</v>
       </c>
       <c r="F988" t="n">
         <v>607209</v>
@@ -20192,16 +20192,16 @@
         <v>45918</v>
       </c>
       <c r="B989" t="n">
-        <v>104.0919876098633</v>
+        <v>104.0919952392578</v>
       </c>
       <c r="C989" t="n">
-        <v>104.7858104824872</v>
+        <v>104.7858181627353</v>
       </c>
       <c r="D989" t="n">
-        <v>102.0691713370833</v>
+        <v>102.069178818216</v>
       </c>
       <c r="E989" t="n">
-        <v>103.5936178806138</v>
+        <v>103.5936254734804</v>
       </c>
       <c r="F989" t="n">
         <v>323487</v>
@@ -20212,16 +20212,16 @@
         <v>45919</v>
       </c>
       <c r="B990" t="n">
-        <v>102.1180419921875</v>
+        <v>102.118034362793</v>
       </c>
       <c r="C990" t="n">
-        <v>105.0203454311598</v>
+        <v>105.0203375849298</v>
       </c>
       <c r="D990" t="n">
-        <v>101.4437673674388</v>
+        <v>101.4437597884204</v>
       </c>
       <c r="E990" t="n">
-        <v>104.3753857978366</v>
+        <v>104.3753779997924</v>
       </c>
       <c r="F990" t="n">
         <v>805829</v>
@@ -20252,16 +20252,16 @@
         <v>45923</v>
       </c>
       <c r="B992" t="n">
-        <v>101.2385559082031</v>
+        <v>101.2385482788086</v>
       </c>
       <c r="C992" t="n">
-        <v>102.5577827229838</v>
+        <v>102.5577749941716</v>
       </c>
       <c r="D992" t="n">
-        <v>100.4079321696739</v>
+        <v>100.4079246028757</v>
       </c>
       <c r="E992" t="n">
-        <v>101.2287817591405</v>
+        <v>101.2287741304826</v>
       </c>
       <c r="F992" t="n">
         <v>578829</v>
@@ -20372,16 +20372,16 @@
         <v>45931</v>
       </c>
       <c r="B998" t="n">
-        <v>95.22872924804688</v>
+        <v>95.22873687744141</v>
       </c>
       <c r="C998" t="n">
-        <v>99.3623142353271</v>
+        <v>99.3623221958901</v>
       </c>
       <c r="D998" t="n">
-        <v>95.01375017365902</v>
+        <v>95.01375778583019</v>
       </c>
       <c r="E998" t="n">
-        <v>97.5544844834704</v>
+        <v>97.55449229919635</v>
       </c>
       <c r="F998" t="n">
         <v>911140</v>
@@ -20392,16 +20392,16 @@
         <v>45932</v>
       </c>
       <c r="B999" t="n">
-        <v>92.09189605712891</v>
+        <v>92.09190368652344</v>
       </c>
       <c r="C999" t="n">
-        <v>96.53818656647101</v>
+        <v>96.53819456422049</v>
       </c>
       <c r="D999" t="n">
-        <v>91.47625892965451</v>
+        <v>91.47626650804631</v>
       </c>
       <c r="E999" t="n">
-        <v>95.22872658272024</v>
+        <v>95.22873447198691</v>
       </c>
       <c r="F999" t="n">
         <v>1326713</v>
@@ -20452,16 +20452,16 @@
         <v>45937</v>
       </c>
       <c r="B1002" t="n">
-        <v>85.994140625</v>
+        <v>85.99413299560547</v>
       </c>
       <c r="C1002" t="n">
-        <v>88.49578596651554</v>
+        <v>88.4957781151752</v>
       </c>
       <c r="D1002" t="n">
-        <v>85.55440084263682</v>
+        <v>85.55439325225598</v>
       </c>
       <c r="E1002" t="n">
-        <v>88.24171773716807</v>
+        <v>88.24170990836865</v>
       </c>
       <c r="F1002" t="n">
         <v>845675</v>
@@ -20512,16 +20512,16 @@
         <v>45940</v>
       </c>
       <c r="B1005" t="n">
-        <v>85.34917449951172</v>
+        <v>85.34918212890625</v>
       </c>
       <c r="C1005" t="n">
-        <v>86.7465794765927</v>
+        <v>86.74658723090178</v>
       </c>
       <c r="D1005" t="n">
-        <v>84.66513323331431</v>
+        <v>84.66514080156213</v>
       </c>
       <c r="E1005" t="n">
-        <v>85.31009281757814</v>
+        <v>85.31010044347914</v>
       </c>
       <c r="F1005" t="n">
         <v>848390</v>
@@ -20572,16 +20572,16 @@
         <v>45945</v>
       </c>
       <c r="B1008" t="n">
-        <v>88.33943176269531</v>
+        <v>88.33943939208984</v>
       </c>
       <c r="C1008" t="n">
-        <v>89.01369889304345</v>
+        <v>89.01370658067076</v>
       </c>
       <c r="D1008" t="n">
-        <v>85.47621762934537</v>
+        <v>85.47622501145973</v>
       </c>
       <c r="E1008" t="n">
-        <v>85.85732740686544</v>
+        <v>85.85733482189416</v>
       </c>
       <c r="F1008" t="n">
         <v>892096</v>
@@ -20672,16 +20672,16 @@
         <v>45952</v>
       </c>
       <c r="B1013" t="n">
-        <v>88.34920501708984</v>
+        <v>88.34921264648438</v>
       </c>
       <c r="C1013" t="n">
-        <v>90.32315801259118</v>
+        <v>90.32316581244639</v>
       </c>
       <c r="D1013" t="n">
-        <v>88.0658143600468</v>
+        <v>88.06582196496913</v>
       </c>
       <c r="E1013" t="n">
-        <v>89.41435606258787</v>
+        <v>89.41436378396349</v>
       </c>
       <c r="F1013" t="n">
         <v>342955</v>
@@ -20812,16 +20812,16 @@
         <v>45961</v>
       </c>
       <c r="B1020" t="n">
-        <v>95.01374816894531</v>
+        <v>95.01375579833984</v>
       </c>
       <c r="C1020" t="n">
-        <v>95.64892614137838</v>
+        <v>95.64893382177631</v>
       </c>
       <c r="D1020" t="n">
-        <v>94.12448707875414</v>
+        <v>94.12449463674297</v>
       </c>
       <c r="E1020" t="n">
-        <v>94.39810358173895</v>
+        <v>94.39811116169858</v>
       </c>
       <c r="F1020" t="n">
         <v>181142</v>
@@ -20872,16 +20872,16 @@
         <v>45966</v>
       </c>
       <c r="B1023" t="n">
-        <v>96.762939453125</v>
+        <v>96.76294708251953</v>
       </c>
       <c r="C1023" t="n">
-        <v>97.71083051119773</v>
+        <v>97.7108382153299</v>
       </c>
       <c r="D1023" t="n">
-        <v>95.01374719055691</v>
+        <v>95.0137546820342</v>
       </c>
       <c r="E1023" t="n">
-        <v>95.33621951975952</v>
+        <v>95.33622703666254</v>
       </c>
       <c r="F1023" t="n">
         <v>404214</v>
@@ -20892,16 +20892,16 @@
         <v>45967</v>
       </c>
       <c r="B1024" t="n">
-        <v>97.85741424560547</v>
+        <v>97.857421875</v>
       </c>
       <c r="C1024" t="n">
-        <v>98.36556557184718</v>
+        <v>98.36557324085943</v>
       </c>
       <c r="D1024" t="n">
-        <v>96.37206431491778</v>
+        <v>96.3720718285079</v>
       </c>
       <c r="E1024" t="n">
-        <v>96.76294077449994</v>
+        <v>96.76294831856451</v>
       </c>
       <c r="F1024" t="n">
         <v>244412</v>
@@ -20972,16 +20972,16 @@
         <v>45973</v>
       </c>
       <c r="B1028" t="n">
-        <v>99.68479156494141</v>
+        <v>99.68479919433594</v>
       </c>
       <c r="C1028" t="n">
-        <v>103.0659236140314</v>
+        <v>103.0659315022015</v>
       </c>
       <c r="D1028" t="n">
-        <v>98.06262593814901</v>
+        <v>98.06263344339078</v>
       </c>
       <c r="E1028" t="n">
-        <v>101.6294295230862</v>
+        <v>101.629437301314</v>
       </c>
       <c r="F1028" t="n">
         <v>452005</v>
@@ -21032,16 +21032,16 @@
         <v>45978</v>
       </c>
       <c r="B1031" t="n">
-        <v>94.49583435058594</v>
+        <v>94.49582672119141</v>
       </c>
       <c r="C1031" t="n">
-        <v>97.72061771745865</v>
+        <v>97.72060982770191</v>
       </c>
       <c r="D1031" t="n">
-        <v>94.08540954549056</v>
+        <v>94.08540194923286</v>
       </c>
       <c r="E1031" t="n">
-        <v>96.85090481621259</v>
+        <v>96.85089699667463</v>
       </c>
       <c r="F1031" t="n">
         <v>742213</v>
@@ -21132,16 +21132,16 @@
         <v>45986</v>
       </c>
       <c r="B1036" t="n">
-        <v>95.0723876953125</v>
+        <v>95.07238006591797</v>
       </c>
       <c r="C1036" t="n">
-        <v>95.32646338309848</v>
+        <v>95.32645573331483</v>
       </c>
       <c r="D1036" t="n">
-        <v>93.23524280826224</v>
+        <v>93.23523532629541</v>
       </c>
       <c r="E1036" t="n">
-        <v>93.61635261219558</v>
+        <v>93.61634509964536</v>
       </c>
       <c r="F1036" t="n">
         <v>322148</v>
@@ -21292,16 +21292,16 @@
         <v>45996</v>
       </c>
       <c r="B1044" t="n">
-        <v>95.47303771972656</v>
+        <v>95.47303009033203</v>
       </c>
       <c r="C1044" t="n">
-        <v>104.336297187796</v>
+        <v>104.336288850125</v>
       </c>
       <c r="D1044" t="n">
-        <v>94.21244834908003</v>
+        <v>94.21244082042111</v>
       </c>
       <c r="E1044" t="n">
-        <v>101.6392135860741</v>
+        <v>101.6392054639311</v>
       </c>
       <c r="F1044" t="n">
         <v>1178496</v>
@@ -24432,7 +24432,7 @@
         <v>46231</v>
       </c>
       <c r="B1201" t="n">
-        <v>85.56999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="C1201" t="n">
         <v>87.11</v>
@@ -24444,7 +24444,7 @@
         <v>85.04000000000001</v>
       </c>
       <c r="F1201" t="n">
-        <v>52988</v>
+        <v>344769</v>
       </c>
     </row>
   </sheetData>

--- a/database/XPBR31.xlsx
+++ b/database/XPBR31.xlsx
@@ -512,16 +512,16 @@
         <v>44476</v>
       </c>
       <c r="B5" t="n">
-        <v>203.3734436035156</v>
+        <v>203.3734283447266</v>
       </c>
       <c r="C5" t="n">
-        <v>203.3734436035156</v>
+        <v>203.3734283447266</v>
       </c>
       <c r="D5" t="n">
-        <v>190.9426315702683</v>
+        <v>190.9426172441435</v>
       </c>
       <c r="E5" t="n">
-        <v>190.9426315702683</v>
+        <v>190.9426172441435</v>
       </c>
       <c r="F5" t="n">
         <v>12157101</v>
@@ -532,16 +532,16 @@
         <v>44477</v>
       </c>
       <c r="B6" t="n">
-        <v>193.8241271972656</v>
+        <v>193.8241119384766</v>
       </c>
       <c r="C6" t="n">
-        <v>204.8669032795693</v>
+        <v>204.8668871514385</v>
       </c>
       <c r="D6" t="n">
-        <v>191.794787349043</v>
+        <v>191.7947722500135</v>
       </c>
       <c r="E6" t="n">
-        <v>200.9927017121121</v>
+        <v>200.9926858889775</v>
       </c>
       <c r="F6" t="n">
         <v>4982319</v>
@@ -552,16 +552,16 @@
         <v>44480</v>
       </c>
       <c r="B7" t="n">
-        <v>180.0931091308594</v>
+        <v>180.0931243896484</v>
       </c>
       <c r="C7" t="n">
-        <v>193.1125296009114</v>
+        <v>193.1125459627998</v>
       </c>
       <c r="D7" t="n">
-        <v>180.0931091308594</v>
+        <v>180.0931243896484</v>
       </c>
       <c r="E7" t="n">
-        <v>191.8738371941056</v>
+        <v>191.8738534510431</v>
       </c>
       <c r="F7" t="n">
         <v>2006205</v>
@@ -612,16 +612,16 @@
         <v>44484</v>
       </c>
       <c r="B10" t="n">
-        <v>175.7005767822266</v>
+        <v>175.7005920410156</v>
       </c>
       <c r="C10" t="n">
-        <v>178.9773887858458</v>
+        <v>178.977404329211</v>
       </c>
       <c r="D10" t="n">
-        <v>166.9155479431152</v>
+        <v>166.9155624389649</v>
       </c>
       <c r="E10" t="n">
-        <v>166.9155479431152</v>
+        <v>166.9155624389649</v>
       </c>
       <c r="F10" t="n">
         <v>2643581</v>
@@ -632,16 +632,16 @@
         <v>44487</v>
       </c>
       <c r="B11" t="n">
-        <v>179.4166717529297</v>
+        <v>179.4166564941406</v>
       </c>
       <c r="C11" t="n">
-        <v>182.2718066273138</v>
+        <v>182.2717911257051</v>
       </c>
       <c r="D11" t="n">
-        <v>175.0680843944616</v>
+        <v>175.0680695055053</v>
       </c>
       <c r="E11" t="n">
-        <v>176.7548086193568</v>
+        <v>176.7547935869503</v>
       </c>
       <c r="F11" t="n">
         <v>1369949</v>
@@ -652,16 +652,16 @@
         <v>44488</v>
       </c>
       <c r="B12" t="n">
-        <v>175.0856628417969</v>
+        <v>175.0856475830078</v>
       </c>
       <c r="C12" t="n">
-        <v>179.4078962958852</v>
+        <v>179.4078806604117</v>
       </c>
       <c r="D12" t="n">
-        <v>174.3828577116028</v>
+        <v>174.3828425140635</v>
       </c>
       <c r="E12" t="n">
-        <v>177.5454740950298</v>
+        <v>177.5454586218672</v>
       </c>
       <c r="F12" t="n">
         <v>722779</v>
@@ -672,16 +672,16 @@
         <v>44489</v>
       </c>
       <c r="B13" t="n">
-        <v>174.3828582763672</v>
+        <v>174.3828430175781</v>
       </c>
       <c r="C13" t="n">
-        <v>178.4942461832448</v>
+        <v>178.4942305647025</v>
       </c>
       <c r="D13" t="n">
-        <v>169.8409990421895</v>
+        <v>169.8409841808207</v>
       </c>
       <c r="E13" t="n">
-        <v>176.5791159372786</v>
+        <v>176.5791004863134</v>
       </c>
       <c r="F13" t="n">
         <v>1907987</v>
@@ -692,16 +692,16 @@
         <v>44490</v>
       </c>
       <c r="B14" t="n">
-        <v>169.4192962646484</v>
+        <v>169.4193115234375</v>
       </c>
       <c r="C14" t="n">
-        <v>176.2189003979208</v>
+        <v>176.2189162691178</v>
       </c>
       <c r="D14" t="n">
-        <v>167.1615372888441</v>
+        <v>167.1615523442876</v>
       </c>
       <c r="E14" t="n">
-        <v>173.3989134851749</v>
+        <v>173.3989291023892</v>
       </c>
       <c r="F14" t="n">
         <v>1852525</v>
@@ -732,16 +732,16 @@
         <v>44494</v>
       </c>
       <c r="B16" t="n">
-        <v>169.1206207275391</v>
+        <v>169.12060546875</v>
       </c>
       <c r="C16" t="n">
-        <v>174.5849108807135</v>
+        <v>174.5848951289127</v>
       </c>
       <c r="D16" t="n">
-        <v>167.3636145922391</v>
+        <v>167.3635994919746</v>
       </c>
       <c r="E16" t="n">
-        <v>167.7062302524268</v>
+        <v>167.7062151212502</v>
       </c>
       <c r="F16" t="n">
         <v>1203463</v>
@@ -752,16 +752,16 @@
         <v>44495</v>
       </c>
       <c r="B17" t="n">
-        <v>163.9638061523438</v>
+        <v>163.9637756347656</v>
       </c>
       <c r="C17" t="n">
-        <v>170.2538911091769</v>
+        <v>170.2538594208638</v>
       </c>
       <c r="D17" t="n">
-        <v>159.9051264143641</v>
+        <v>159.9050966522031</v>
       </c>
       <c r="E17" t="n">
-        <v>168.7604386285045</v>
+        <v>168.7604072181586</v>
       </c>
       <c r="F17" t="n">
         <v>810455</v>
@@ -832,16 +832,16 @@
         <v>44501</v>
       </c>
       <c r="B21" t="n">
-        <v>169.7267913818359</v>
+        <v>169.7267761230469</v>
       </c>
       <c r="C21" t="n">
-        <v>171.2026835181439</v>
+        <v>171.2026681266692</v>
       </c>
       <c r="D21" t="n">
-        <v>161.9344733973998</v>
+        <v>161.9344588391563</v>
       </c>
       <c r="E21" t="n">
-        <v>162.5230688489684</v>
+        <v>162.5230542378089</v>
       </c>
       <c r="F21" t="n">
         <v>466029</v>
@@ -872,16 +872,16 @@
         <v>44504</v>
       </c>
       <c r="B23" t="n">
-        <v>160.3707275390625</v>
+        <v>160.3707122802734</v>
       </c>
       <c r="C23" t="n">
-        <v>170.4208041422209</v>
+        <v>170.4207879271975</v>
       </c>
       <c r="D23" t="n">
-        <v>158.7630654183402</v>
+        <v>158.7630503125153</v>
       </c>
       <c r="E23" t="n">
-        <v>168.2333268163413</v>
+        <v>168.2333108094497</v>
       </c>
       <c r="F23" t="n">
         <v>1051127</v>
@@ -912,16 +912,16 @@
         <v>44508</v>
       </c>
       <c r="B25" t="n">
-        <v>166.99462890625</v>
+        <v>166.9946441650391</v>
       </c>
       <c r="C25" t="n">
-        <v>173.0650877390422</v>
+        <v>173.0651035525069</v>
       </c>
       <c r="D25" t="n">
-        <v>165.58903217567</v>
+        <v>165.5890473060255</v>
       </c>
       <c r="E25" t="n">
-        <v>173.0211599088915</v>
+        <v>173.0211757183424</v>
       </c>
       <c r="F25" t="n">
         <v>352216</v>
@@ -932,16 +932,16 @@
         <v>44509</v>
       </c>
       <c r="B26" t="n">
-        <v>163.7705230712891</v>
+        <v>163.7705383300781</v>
       </c>
       <c r="C26" t="n">
-        <v>169.8497620526857</v>
+        <v>169.8497778778882</v>
       </c>
       <c r="D26" t="n">
-        <v>162.0837989670482</v>
+        <v>162.0838140686822</v>
       </c>
       <c r="E26" t="n">
-        <v>167.3548168196352</v>
+        <v>167.3548324123792</v>
       </c>
       <c r="F26" t="n">
         <v>336270</v>
@@ -972,16 +972,16 @@
         <v>44511</v>
       </c>
       <c r="B28" t="n">
-        <v>162.180419921875</v>
+        <v>162.1804351806641</v>
       </c>
       <c r="C28" t="n">
-        <v>165.5099399945359</v>
+        <v>165.5099555665838</v>
       </c>
       <c r="D28" t="n">
-        <v>159.4658491945075</v>
+        <v>159.4658641978954</v>
       </c>
       <c r="E28" t="n">
-        <v>161.556676968505</v>
+        <v>161.5566921686091</v>
       </c>
       <c r="F28" t="n">
         <v>479646</v>
@@ -992,16 +992,16 @@
         <v>44512</v>
       </c>
       <c r="B29" t="n">
-        <v>161.6533508300781</v>
+        <v>161.6533355712891</v>
       </c>
       <c r="C29" t="n">
-        <v>162.5230737260495</v>
+        <v>162.5230583851655</v>
       </c>
       <c r="D29" t="n">
-        <v>157.4277530579838</v>
+        <v>157.4277381980575</v>
       </c>
       <c r="E29" t="n">
-        <v>162.1804580527687</v>
+        <v>162.1804427442249</v>
       </c>
       <c r="F29" t="n">
         <v>339439</v>
@@ -1072,16 +1072,16 @@
         <v>44519</v>
       </c>
       <c r="B33" t="n">
-        <v>147.1931610107422</v>
+        <v>147.1931762695312</v>
       </c>
       <c r="C33" t="n">
-        <v>149.0468026336331</v>
+        <v>149.0468180845801</v>
       </c>
       <c r="D33" t="n">
-        <v>140.5692417534431</v>
+        <v>140.5692563255631</v>
       </c>
       <c r="E33" t="n">
-        <v>142.5722272581445</v>
+        <v>142.5722420379041</v>
       </c>
       <c r="F33" t="n">
         <v>581745</v>
@@ -1152,16 +1152,16 @@
         <v>44525</v>
       </c>
       <c r="B37" t="n">
-        <v>151.3133850097656</v>
+        <v>151.3133697509766</v>
       </c>
       <c r="C37" t="n">
-        <v>152.8507654981656</v>
+        <v>152.8507500843435</v>
       </c>
       <c r="D37" t="n">
-        <v>148.0717062922993</v>
+        <v>148.0716913604085</v>
       </c>
       <c r="E37" t="n">
-        <v>148.0717062922993</v>
+        <v>148.0716913604085</v>
       </c>
       <c r="F37" t="n">
         <v>222385</v>
@@ -1232,16 +1232,16 @@
         <v>44531</v>
       </c>
       <c r="B41" t="n">
-        <v>144.3116912841797</v>
+        <v>144.3116760253906</v>
       </c>
       <c r="C41" t="n">
-        <v>151.2342857954605</v>
+        <v>151.2342698047112</v>
       </c>
       <c r="D41" t="n">
-        <v>141.4477629305895</v>
+        <v>141.4477479746177</v>
       </c>
       <c r="E41" t="n">
-        <v>142.317485724668</v>
+        <v>142.3174706767361</v>
       </c>
       <c r="F41" t="n">
         <v>941983</v>
@@ -1252,16 +1252,16 @@
         <v>44532</v>
       </c>
       <c r="B42" t="n">
-        <v>143.7845764160156</v>
+        <v>143.7845916748047</v>
       </c>
       <c r="C42" t="n">
-        <v>150.513912239461</v>
+        <v>150.5139282123845</v>
       </c>
       <c r="D42" t="n">
-        <v>143.0466371541728</v>
+        <v>143.0466523346498</v>
       </c>
       <c r="E42" t="n">
-        <v>145.8314899009227</v>
+        <v>145.8315053769355</v>
       </c>
       <c r="F42" t="n">
         <v>584287</v>
@@ -1312,16 +1312,16 @@
         <v>44537</v>
       </c>
       <c r="B45" t="n">
-        <v>148.0277404785156</v>
+        <v>148.0277557373047</v>
       </c>
       <c r="C45" t="n">
-        <v>153.0439979976308</v>
+        <v>153.0440137734988</v>
       </c>
       <c r="D45" t="n">
-        <v>147.8871767956056</v>
+        <v>147.8871920399053</v>
       </c>
       <c r="E45" t="n">
-        <v>150.2239977556449</v>
+        <v>150.2240132408255</v>
       </c>
       <c r="F45" t="n">
         <v>560968</v>
@@ -1332,16 +1332,16 @@
         <v>44538</v>
       </c>
       <c r="B46" t="n">
-        <v>146.3497924804688</v>
+        <v>146.3498077392578</v>
       </c>
       <c r="C46" t="n">
-        <v>150.2239934227556</v>
+        <v>150.2240090854783</v>
       </c>
       <c r="D46" t="n">
-        <v>145.9983966882195</v>
+        <v>145.9984119103712</v>
       </c>
       <c r="E46" t="n">
-        <v>148.2473619303509</v>
+        <v>148.2473773869852</v>
       </c>
       <c r="F46" t="n">
         <v>297967</v>
@@ -1352,16 +1352,16 @@
         <v>44539</v>
       </c>
       <c r="B47" t="n">
-        <v>146.6836395263672</v>
+        <v>146.6836547851562</v>
       </c>
       <c r="C47" t="n">
-        <v>148.8974707272065</v>
+        <v>148.8974862162897</v>
       </c>
       <c r="D47" t="n">
-        <v>143.7318690602119</v>
+        <v>143.7318840119426</v>
       </c>
       <c r="E47" t="n">
-        <v>146.4464399750544</v>
+        <v>146.4464552091688</v>
       </c>
       <c r="F47" t="n">
         <v>319045</v>
@@ -1572,16 +1572,16 @@
         <v>44557</v>
       </c>
       <c r="B58" t="n">
-        <v>150.0482940673828</v>
+        <v>150.0483093261719</v>
       </c>
       <c r="C58" t="n">
-        <v>153.6940756448505</v>
+        <v>153.6940912743883</v>
       </c>
       <c r="D58" t="n">
-        <v>147.0438158367336</v>
+        <v>147.0438307899898</v>
       </c>
       <c r="E58" t="n">
-        <v>147.0438158367336</v>
+        <v>147.0438307899898</v>
       </c>
       <c r="F58" t="n">
         <v>232495</v>
@@ -1592,16 +1592,16 @@
         <v>44558</v>
       </c>
       <c r="B59" t="n">
-        <v>141.7025299072266</v>
+        <v>141.7025451660156</v>
       </c>
       <c r="C59" t="n">
-        <v>151.4539047050317</v>
+        <v>151.4539210138668</v>
       </c>
       <c r="D59" t="n">
-        <v>141.0963607209925</v>
+        <v>141.0963759145082</v>
       </c>
       <c r="E59" t="n">
-        <v>150.4875594934788</v>
+        <v>150.487575698256</v>
       </c>
       <c r="F59" t="n">
         <v>577682</v>
@@ -1632,16 +1632,16 @@
         <v>44560</v>
       </c>
       <c r="B61" t="n">
-        <v>140.9909362792969</v>
+        <v>140.9909515380859</v>
       </c>
       <c r="C61" t="n">
-        <v>141.2632700355088</v>
+        <v>141.2632853237713</v>
       </c>
       <c r="D61" t="n">
-        <v>136.7126180096394</v>
+        <v>136.7126328054061</v>
       </c>
       <c r="E61" t="n">
-        <v>140.0333579235674</v>
+        <v>140.0333730787222</v>
       </c>
       <c r="F61" t="n">
         <v>445854</v>
@@ -1752,16 +1752,16 @@
         <v>44571</v>
       </c>
       <c r="B67" t="n">
-        <v>137.5208587646484</v>
+        <v>137.5208435058594</v>
       </c>
       <c r="C67" t="n">
-        <v>138.4696436480268</v>
+        <v>138.4696282839642</v>
       </c>
       <c r="D67" t="n">
-        <v>131.9072249249958</v>
+        <v>131.9072102890741</v>
       </c>
       <c r="E67" t="n">
-        <v>137.2309645603231</v>
+        <v>137.2309493336996</v>
       </c>
       <c r="F67" t="n">
         <v>730000</v>
@@ -1872,16 +1872,16 @@
         <v>44579</v>
       </c>
       <c r="B73" t="n">
-        <v>133.1722717285156</v>
+        <v>133.1722412109375</v>
       </c>
       <c r="C73" t="n">
-        <v>138.8034793945444</v>
+        <v>138.8034475865263</v>
       </c>
       <c r="D73" t="n">
-        <v>133.1722717285156</v>
+        <v>133.1722412109375</v>
       </c>
       <c r="E73" t="n">
-        <v>138.1885299516231</v>
+        <v>138.188498284526</v>
       </c>
       <c r="F73" t="n">
         <v>435258</v>
@@ -1992,16 +1992,16 @@
         <v>44587</v>
       </c>
       <c r="B79" t="n">
-        <v>151.7789764404297</v>
+        <v>151.7789611816406</v>
       </c>
       <c r="C79" t="n">
-        <v>157.1466306382445</v>
+        <v>157.1466148398293</v>
       </c>
       <c r="D79" t="n">
-        <v>148.2122561848568</v>
+        <v>148.2122412846406</v>
       </c>
       <c r="E79" t="n">
-        <v>148.5987862686278</v>
+        <v>148.5987713295526</v>
       </c>
       <c r="F79" t="n">
         <v>671208</v>
@@ -2052,16 +2052,16 @@
         <v>44592</v>
       </c>
       <c r="B82" t="n">
-        <v>155.0558013916016</v>
+        <v>155.0557708740234</v>
       </c>
       <c r="C82" t="n">
-        <v>155.3193550097899</v>
+        <v>155.31932444034</v>
       </c>
       <c r="D82" t="n">
-        <v>145.8666528160763</v>
+        <v>145.8666241070765</v>
       </c>
       <c r="E82" t="n">
-        <v>147.0175031686687</v>
+        <v>147.0174742331623</v>
       </c>
       <c r="F82" t="n">
         <v>286473</v>
@@ -2092,16 +2092,16 @@
         <v>44594</v>
       </c>
       <c r="B84" t="n">
-        <v>148.9941253662109</v>
+        <v>148.9941101074219</v>
       </c>
       <c r="C84" t="n">
-        <v>158.1305518913071</v>
+        <v>158.1305356968381</v>
       </c>
       <c r="D84" t="n">
-        <v>148.9062696976475</v>
+        <v>148.9062544478559</v>
       </c>
       <c r="E84" t="n">
-        <v>155.8025241281978</v>
+        <v>155.8025081721468</v>
       </c>
       <c r="F84" t="n">
         <v>466282</v>
@@ -2132,16 +2132,16 @@
         <v>44596</v>
       </c>
       <c r="B86" t="n">
-        <v>149.6002807617188</v>
+        <v>149.6002655029297</v>
       </c>
       <c r="C86" t="n">
-        <v>151.0058910250547</v>
+        <v>151.0058756228975</v>
       </c>
       <c r="D86" t="n">
-        <v>143.5825428206266</v>
+        <v>143.5825281756291</v>
       </c>
       <c r="E86" t="n">
-        <v>149.3455207714968</v>
+        <v>149.3455055386924</v>
       </c>
       <c r="F86" t="n">
         <v>455710</v>
@@ -2172,16 +2172,16 @@
         <v>44600</v>
       </c>
       <c r="B88" t="n">
-        <v>149.3191680908203</v>
+        <v>149.3191528320312</v>
       </c>
       <c r="C88" t="n">
-        <v>149.3191680908203</v>
+        <v>149.3191528320312</v>
       </c>
       <c r="D88" t="n">
-        <v>144.2326278016086</v>
+        <v>144.2326130626084</v>
       </c>
       <c r="E88" t="n">
-        <v>147.6763716371699</v>
+        <v>147.6763565462567</v>
       </c>
       <c r="F88" t="n">
         <v>326666</v>
@@ -2192,16 +2192,16 @@
         <v>44601</v>
       </c>
       <c r="B89" t="n">
-        <v>157.5156097412109</v>
+        <v>157.5155792236328</v>
       </c>
       <c r="C89" t="n">
-        <v>159.7997097761142</v>
+        <v>159.7996788160072</v>
       </c>
       <c r="D89" t="n">
-        <v>151.4275762401174</v>
+        <v>151.4275469020544</v>
       </c>
       <c r="E89" t="n">
-        <v>153.7380437007286</v>
+        <v>153.7380139150282</v>
       </c>
       <c r="F89" t="n">
         <v>1361639</v>
@@ -2212,16 +2212,16 @@
         <v>44602</v>
       </c>
       <c r="B90" t="n">
-        <v>152.6311187744141</v>
+        <v>152.631103515625</v>
       </c>
       <c r="C90" t="n">
-        <v>163.1380073355108</v>
+        <v>163.1379910263304</v>
       </c>
       <c r="D90" t="n">
-        <v>151.2870102327762</v>
+        <v>151.2869951083599</v>
       </c>
       <c r="E90" t="n">
-        <v>157.5155933969532</v>
+        <v>157.515577649855</v>
       </c>
       <c r="F90" t="n">
         <v>704053</v>
@@ -2232,16 +2232,16 @@
         <v>44603</v>
       </c>
       <c r="B91" t="n">
-        <v>156.0045623779297</v>
+        <v>156.0045471191406</v>
       </c>
       <c r="C91" t="n">
-        <v>160.1510975579418</v>
+        <v>160.1510818935806</v>
       </c>
       <c r="D91" t="n">
-        <v>151.3309200426192</v>
+        <v>151.3309052409586</v>
       </c>
       <c r="E91" t="n">
-        <v>152.3763407441961</v>
+        <v>152.376325840283</v>
       </c>
       <c r="F91" t="n">
         <v>740597</v>
@@ -2252,16 +2252,16 @@
         <v>44606</v>
       </c>
       <c r="B92" t="n">
-        <v>152.9473876953125</v>
+        <v>152.9473724365234</v>
       </c>
       <c r="C92" t="n">
-        <v>157.9197048137788</v>
+        <v>157.9196890589268</v>
       </c>
       <c r="D92" t="n">
-        <v>152.0688846376827</v>
+        <v>152.0688694665374</v>
       </c>
       <c r="E92" t="n">
-        <v>156.0045745824943</v>
+        <v>156.0045590187052</v>
       </c>
       <c r="F92" t="n">
         <v>409040</v>
@@ -2272,16 +2272,16 @@
         <v>44607</v>
       </c>
       <c r="B93" t="n">
-        <v>161.143798828125</v>
+        <v>161.1437835693359</v>
       </c>
       <c r="C93" t="n">
-        <v>161.8202498913792</v>
+        <v>161.8202345685366</v>
       </c>
       <c r="D93" t="n">
-        <v>154.6253081778255</v>
+        <v>154.6252935362757</v>
       </c>
       <c r="E93" t="n">
-        <v>156.2768981071088</v>
+        <v>156.2768833091691</v>
       </c>
       <c r="F93" t="n">
         <v>501987</v>
@@ -2292,16 +2292,16 @@
         <v>44608</v>
       </c>
       <c r="B94" t="n">
-        <v>160.8099975585938</v>
+        <v>160.8099822998047</v>
       </c>
       <c r="C94" t="n">
-        <v>164.6841995051333</v>
+        <v>164.6841838787326</v>
       </c>
       <c r="D94" t="n">
-        <v>158.0690587299737</v>
+        <v>158.0690437312643</v>
       </c>
       <c r="E94" t="n">
-        <v>161.1438196262952</v>
+        <v>161.1438043358308</v>
       </c>
       <c r="F94" t="n">
         <v>383335</v>
@@ -2312,16 +2312,16 @@
         <v>44609</v>
       </c>
       <c r="B95" t="n">
-        <v>156.6282958984375</v>
+        <v>156.6282806396484</v>
       </c>
       <c r="C95" t="n">
-        <v>161.1877286693031</v>
+        <v>161.1877129663323</v>
       </c>
       <c r="D95" t="n">
-        <v>156.1626903751017</v>
+        <v>156.1626751616721</v>
       </c>
       <c r="E95" t="n">
-        <v>160.8011851997657</v>
+        <v>160.8011695344521</v>
       </c>
       <c r="F95" t="n">
         <v>315564</v>
@@ -2392,16 +2392,16 @@
         <v>44615</v>
       </c>
       <c r="B99" t="n">
-        <v>147.2722473144531</v>
+        <v>147.2722320556641</v>
       </c>
       <c r="C99" t="n">
-        <v>153.5623322222181</v>
+        <v>153.5623163117172</v>
       </c>
       <c r="D99" t="n">
-        <v>146.9647658922019</v>
+        <v>146.9647506652708</v>
       </c>
       <c r="E99" t="n">
-        <v>150.3557881219284</v>
+        <v>150.3557725436555</v>
       </c>
       <c r="F99" t="n">
         <v>373832</v>
@@ -2472,16 +2472,16 @@
         <v>44623</v>
       </c>
       <c r="B103" t="n">
-        <v>136.16796875</v>
+        <v>136.1679840087891</v>
       </c>
       <c r="C103" t="n">
-        <v>143.3365566445935</v>
+        <v>143.3365727066843</v>
       </c>
       <c r="D103" t="n">
-        <v>135.4915176680011</v>
+        <v>135.491532850988</v>
       </c>
       <c r="E103" t="n">
-        <v>142.5107616570688</v>
+        <v>142.5107776266222</v>
       </c>
       <c r="F103" t="n">
         <v>801826</v>
@@ -2492,16 +2492,16 @@
         <v>44624</v>
       </c>
       <c r="B104" t="n">
-        <v>129.4034881591797</v>
+        <v>129.4035034179688</v>
       </c>
       <c r="C104" t="n">
-        <v>139.2163645736173</v>
+        <v>139.216380989505</v>
       </c>
       <c r="D104" t="n">
-        <v>128.5864734391812</v>
+        <v>128.5864886016308</v>
       </c>
       <c r="E104" t="n">
-        <v>134.2440346232008</v>
+        <v>134.2440504527695</v>
       </c>
       <c r="F104" t="n">
         <v>615045</v>
@@ -2512,16 +2512,16 @@
         <v>44627</v>
       </c>
       <c r="B105" t="n">
-        <v>117.0781021118164</v>
+        <v>117.0780944824219</v>
       </c>
       <c r="C105" t="n">
-        <v>130.2644277157113</v>
+        <v>130.2644192270299</v>
       </c>
       <c r="D105" t="n">
-        <v>117.0781021118164</v>
+        <v>117.0780944824219</v>
       </c>
       <c r="E105" t="n">
-        <v>129.5791964273345</v>
+        <v>129.5791879833061</v>
       </c>
       <c r="F105" t="n">
         <v>1053703</v>
@@ -2612,16 +2612,16 @@
         <v>44634</v>
       </c>
       <c r="B110" t="n">
-        <v>126.6801376342773</v>
+        <v>126.6801223754883</v>
       </c>
       <c r="C110" t="n">
-        <v>133.831151953603</v>
+        <v>133.8311358334649</v>
       </c>
       <c r="D110" t="n">
-        <v>126.6801376342773</v>
+        <v>126.6801223754883</v>
       </c>
       <c r="E110" t="n">
-        <v>131.6173339102961</v>
+        <v>131.6173180568153</v>
       </c>
       <c r="F110" t="n">
         <v>265850</v>
@@ -2652,16 +2652,16 @@
         <v>44636</v>
       </c>
       <c r="B112" t="n">
-        <v>139.4887084960938</v>
+        <v>139.4886932373047</v>
       </c>
       <c r="C112" t="n">
-        <v>142.3438433121762</v>
+        <v>142.3438277410615</v>
       </c>
       <c r="D112" t="n">
-        <v>132.6539560702938</v>
+        <v>132.6539415591642</v>
       </c>
       <c r="E112" t="n">
-        <v>132.6539560702938</v>
+        <v>132.6539415591642</v>
       </c>
       <c r="F112" t="n">
         <v>861619</v>
@@ -2692,16 +2692,16 @@
         <v>44638</v>
       </c>
       <c r="B114" t="n">
-        <v>142.3174896240234</v>
+        <v>142.3174743652344</v>
       </c>
       <c r="C114" t="n">
-        <v>145.1199164101681</v>
+        <v>145.1199008509126</v>
       </c>
       <c r="D114" t="n">
-        <v>137.1518875629193</v>
+        <v>137.1518728579682</v>
       </c>
       <c r="E114" t="n">
-        <v>138.618986001691</v>
+        <v>138.6189711394427</v>
       </c>
       <c r="F114" t="n">
         <v>570545</v>
@@ -2712,16 +2712,16 @@
         <v>44641</v>
       </c>
       <c r="B115" t="n">
-        <v>139.7698364257812</v>
+        <v>139.7698211669922</v>
       </c>
       <c r="C115" t="n">
-        <v>143.0642227644949</v>
+        <v>143.0642071460549</v>
       </c>
       <c r="D115" t="n">
-        <v>138.4169342626098</v>
+        <v>138.4169191515182</v>
       </c>
       <c r="E115" t="n">
-        <v>141.4829146409339</v>
+        <v>141.4828991951266</v>
       </c>
       <c r="F115" t="n">
         <v>351500</v>
@@ -2732,16 +2732,16 @@
         <v>44642</v>
       </c>
       <c r="B116" t="n">
-        <v>143.4683380126953</v>
+        <v>143.4683227539062</v>
       </c>
       <c r="C116" t="n">
-        <v>146.8330064684024</v>
+        <v>146.832990851759</v>
       </c>
       <c r="D116" t="n">
-        <v>139.7698474968835</v>
+        <v>139.7698326314529</v>
       </c>
       <c r="E116" t="n">
-        <v>139.7698474968835</v>
+        <v>139.7698326314529</v>
       </c>
       <c r="F116" t="n">
         <v>384464</v>
@@ -2772,16 +2772,16 @@
         <v>44644</v>
       </c>
       <c r="B118" t="n">
-        <v>136.2734069824219</v>
+        <v>136.2733917236328</v>
       </c>
       <c r="C118" t="n">
-        <v>137.2661198507487</v>
+        <v>137.2661044808038</v>
       </c>
       <c r="D118" t="n">
-        <v>132.487060477242</v>
+        <v>132.4870456424172</v>
       </c>
       <c r="E118" t="n">
-        <v>133.277721370519</v>
+        <v>133.2777064471624</v>
       </c>
       <c r="F118" t="n">
         <v>438667</v>
@@ -2952,16 +2952,16 @@
         <v>44657</v>
       </c>
       <c r="B127" t="n">
-        <v>125.019775390625</v>
+        <v>125.0197601318359</v>
       </c>
       <c r="C127" t="n">
-        <v>127.3829509003876</v>
+        <v>127.3829353531706</v>
       </c>
       <c r="D127" t="n">
-        <v>122.6917475119892</v>
+        <v>122.6917325373382</v>
       </c>
       <c r="E127" t="n">
-        <v>127.172105328308</v>
+        <v>127.1720898068249</v>
       </c>
       <c r="F127" t="n">
         <v>694358</v>
@@ -3012,16 +3012,16 @@
         <v>44662</v>
       </c>
       <c r="B130" t="n">
-        <v>121.8659210205078</v>
+        <v>121.8659286499023</v>
       </c>
       <c r="C130" t="n">
-        <v>123.570218758567</v>
+        <v>123.5702264946588</v>
       </c>
       <c r="D130" t="n">
-        <v>119.3621824416246</v>
+        <v>119.362189914273</v>
       </c>
       <c r="E130" t="n">
-        <v>122.990403638526</v>
+        <v>122.9904113383186</v>
       </c>
       <c r="F130" t="n">
         <v>348006</v>
@@ -3052,16 +3052,16 @@
         <v>44664</v>
       </c>
       <c r="B132" t="n">
-        <v>119.7750930786133</v>
+        <v>119.7751007080078</v>
       </c>
       <c r="C132" t="n">
-        <v>120.7941597526093</v>
+        <v>120.794167446916</v>
       </c>
       <c r="D132" t="n">
-        <v>117.7545335435913</v>
+        <v>117.7545410442809</v>
       </c>
       <c r="E132" t="n">
-        <v>118.8351018605366</v>
+        <v>118.8351094300559</v>
       </c>
       <c r="F132" t="n">
         <v>714435</v>
@@ -3072,16 +3072,16 @@
         <v>44665</v>
       </c>
       <c r="B133" t="n">
-        <v>115.6022033691406</v>
+        <v>115.6022109985352</v>
       </c>
       <c r="C133" t="n">
-        <v>120.0035118570594</v>
+        <v>120.003519776927</v>
       </c>
       <c r="D133" t="n">
-        <v>114.7061399853404</v>
+        <v>114.7061475555975</v>
       </c>
       <c r="E133" t="n">
-        <v>119.7750925042192</v>
+        <v>119.7751004090118</v>
       </c>
       <c r="F133" t="n">
         <v>497156</v>
@@ -3092,16 +3092,16 @@
         <v>44669</v>
       </c>
       <c r="B134" t="n">
-        <v>112.4483871459961</v>
+        <v>112.4483795166016</v>
       </c>
       <c r="C134" t="n">
-        <v>115.1366042564223</v>
+        <v>115.1365964446377</v>
       </c>
       <c r="D134" t="n">
-        <v>112.0530634659144</v>
+        <v>112.0530558633418</v>
       </c>
       <c r="E134" t="n">
-        <v>114.2053931951523</v>
+        <v>114.2053854465485</v>
       </c>
       <c r="F134" t="n">
         <v>589431</v>
@@ -3132,16 +3132,16 @@
         <v>44671</v>
       </c>
       <c r="B136" t="n">
-        <v>113.9945449829102</v>
+        <v>113.9945373535156</v>
       </c>
       <c r="C136" t="n">
-        <v>116.5597721462199</v>
+        <v>116.5597643451405</v>
       </c>
       <c r="D136" t="n">
-        <v>112.975491685902</v>
+        <v>112.9754841247104</v>
       </c>
       <c r="E136" t="n">
-        <v>114.5128719430319</v>
+        <v>114.5128642789469</v>
       </c>
       <c r="F136" t="n">
         <v>232622</v>
@@ -3152,16 +3152,16 @@
         <v>44673</v>
       </c>
       <c r="B137" t="n">
-        <v>107.7923126220703</v>
+        <v>107.7923049926758</v>
       </c>
       <c r="C137" t="n">
-        <v>111.56987810503</v>
+        <v>111.5698702082644</v>
       </c>
       <c r="D137" t="n">
-        <v>106.2988602418002</v>
+        <v>106.2988527181102</v>
       </c>
       <c r="E137" t="n">
-        <v>111.56987810503</v>
+        <v>111.5698702082644</v>
       </c>
       <c r="F137" t="n">
         <v>509466</v>
@@ -3172,16 +3172,16 @@
         <v>44676</v>
       </c>
       <c r="B138" t="n">
-        <v>111.5347366333008</v>
+        <v>111.5347442626953</v>
       </c>
       <c r="C138" t="n">
-        <v>111.8334311293538</v>
+        <v>111.8334387791802</v>
       </c>
       <c r="D138" t="n">
-        <v>105.9474571895508</v>
+        <v>105.9474644367544</v>
       </c>
       <c r="E138" t="n">
-        <v>106.2988597191943</v>
+        <v>106.2988669904352</v>
       </c>
       <c r="F138" t="n">
         <v>607459</v>
@@ -3192,16 +3192,16 @@
         <v>44677</v>
       </c>
       <c r="B139" t="n">
-        <v>107.4057769775391</v>
+        <v>107.4057846069336</v>
       </c>
       <c r="C139" t="n">
-        <v>112.6943620057829</v>
+        <v>112.6943700108434</v>
       </c>
       <c r="D139" t="n">
-        <v>106.342789168451</v>
+        <v>106.3427967223379</v>
       </c>
       <c r="E139" t="n">
-        <v>109.9270762585565</v>
+        <v>109.9270840670474</v>
       </c>
       <c r="F139" t="n">
         <v>615417</v>
@@ -3232,16 +3232,16 @@
         <v>44679</v>
       </c>
       <c r="B141" t="n">
-        <v>108.4951248168945</v>
+        <v>108.4951171875</v>
       </c>
       <c r="C141" t="n">
-        <v>109.5844667035533</v>
+        <v>109.5844589975561</v>
       </c>
       <c r="D141" t="n">
-        <v>104.0235475861498</v>
+        <v>104.0235402711972</v>
       </c>
       <c r="E141" t="n">
-        <v>104.5418611595988</v>
+        <v>104.5418538081984</v>
       </c>
       <c r="F141" t="n">
         <v>799584</v>
@@ -3252,16 +3252,16 @@
         <v>44680</v>
       </c>
       <c r="B142" t="n">
-        <v>107.6341857910156</v>
+        <v>107.6341781616211</v>
       </c>
       <c r="C142" t="n">
-        <v>112.0969826885324</v>
+        <v>112.0969747428031</v>
       </c>
       <c r="D142" t="n">
-        <v>107.1773671750833</v>
+        <v>107.1773595780693</v>
       </c>
       <c r="E142" t="n">
-        <v>108.1173651272915</v>
+        <v>108.117357463648</v>
       </c>
       <c r="F142" t="n">
         <v>762051</v>
@@ -3292,16 +3292,16 @@
         <v>44684</v>
       </c>
       <c r="B144" t="n">
-        <v>102.7848434448242</v>
+        <v>102.7848510742188</v>
       </c>
       <c r="C144" t="n">
-        <v>107.1773581219535</v>
+        <v>107.1773660773905</v>
       </c>
       <c r="D144" t="n">
-        <v>101.8097046503059</v>
+        <v>101.8097122073189</v>
       </c>
       <c r="E144" t="n">
-        <v>107.142217200243</v>
+        <v>107.1422251530716</v>
       </c>
       <c r="F144" t="n">
         <v>541792</v>
@@ -3312,16 +3312,16 @@
         <v>44685</v>
       </c>
       <c r="B145" t="n">
-        <v>94.52693176269531</v>
+        <v>94.52692413330078</v>
       </c>
       <c r="C145" t="n">
-        <v>100.4129065257185</v>
+        <v>100.4128984212591</v>
       </c>
       <c r="D145" t="n">
-        <v>84.54713605872841</v>
+        <v>84.54712923481648</v>
       </c>
       <c r="E145" t="n">
-        <v>100.4129065257185</v>
+        <v>100.4128984212591</v>
       </c>
       <c r="F145" t="n">
         <v>3193940</v>
@@ -3332,16 +3332,16 @@
         <v>44686</v>
       </c>
       <c r="B146" t="n">
-        <v>93.73626708984375</v>
+        <v>93.73627471923828</v>
       </c>
       <c r="C146" t="n">
-        <v>95.51084689698163</v>
+        <v>95.51085467081299</v>
       </c>
       <c r="D146" t="n">
-        <v>91.46094754500817</v>
+        <v>91.4609549892096</v>
       </c>
       <c r="E146" t="n">
-        <v>94.43907216835407</v>
+        <v>94.4390798549514</v>
       </c>
       <c r="F146" t="n">
         <v>1265698</v>
@@ -3452,16 +3452,16 @@
         <v>44694</v>
       </c>
       <c r="B152" t="n">
-        <v>89.78299713134766</v>
+        <v>89.78300476074219</v>
       </c>
       <c r="C152" t="n">
-        <v>92.42729283812145</v>
+        <v>92.42730069221749</v>
       </c>
       <c r="D152" t="n">
-        <v>87.90300138967268</v>
+        <v>87.90300885931281</v>
       </c>
       <c r="E152" t="n">
-        <v>90.57365111206272</v>
+        <v>90.57365880864381</v>
       </c>
       <c r="F152" t="n">
         <v>780406</v>
@@ -3612,16 +3612,16 @@
         <v>44706</v>
       </c>
       <c r="B160" t="n">
-        <v>89.92356872558594</v>
+        <v>89.92357635498047</v>
       </c>
       <c r="C160" t="n">
-        <v>90.73178988696996</v>
+        <v>90.73179758493647</v>
       </c>
       <c r="D160" t="n">
-        <v>85.75067942410486</v>
+        <v>85.75068669945851</v>
       </c>
       <c r="E160" t="n">
-        <v>86.97179807297417</v>
+        <v>86.97180545193132</v>
       </c>
       <c r="F160" t="n">
         <v>958832</v>
@@ -3732,16 +3732,16 @@
         <v>44714</v>
       </c>
       <c r="B166" t="n">
-        <v>97.39962768554688</v>
+        <v>97.39963531494141</v>
       </c>
       <c r="C166" t="n">
-        <v>97.77738423457956</v>
+        <v>97.77739189356407</v>
       </c>
       <c r="D166" t="n">
-        <v>91.3818769180002</v>
+        <v>91.38188407601926</v>
       </c>
       <c r="E166" t="n">
-        <v>91.3818769180002</v>
+        <v>91.38188407601926</v>
       </c>
       <c r="F166" t="n">
         <v>432233</v>
@@ -3752,16 +3752,16 @@
         <v>44715</v>
       </c>
       <c r="B167" t="n">
-        <v>94.96617126464844</v>
+        <v>94.96617889404297</v>
       </c>
       <c r="C167" t="n">
-        <v>97.28541860706112</v>
+        <v>97.28542642277941</v>
       </c>
       <c r="D167" t="n">
-        <v>93.93832438157946</v>
+        <v>93.93833192839882</v>
       </c>
       <c r="E167" t="n">
-        <v>96.63532827534817</v>
+        <v>96.63533603883948</v>
       </c>
       <c r="F167" t="n">
         <v>452357</v>
@@ -3892,16 +3892,16 @@
         <v>44726</v>
       </c>
       <c r="B174" t="n">
-        <v>85.73310089111328</v>
+        <v>85.73310852050781</v>
       </c>
       <c r="C174" t="n">
-        <v>86.47104686486708</v>
+        <v>86.47105455993147</v>
       </c>
       <c r="D174" t="n">
-        <v>84.07273082822437</v>
+        <v>84.07273830986246</v>
       </c>
       <c r="E174" t="n">
-        <v>86.10207722921302</v>
+        <v>86.10208489144279</v>
       </c>
       <c r="F174" t="n">
         <v>502449</v>
@@ -3912,16 +3912,16 @@
         <v>44727</v>
       </c>
       <c r="B175" t="n">
-        <v>86.62918853759766</v>
+        <v>86.62918090820312</v>
       </c>
       <c r="C175" t="n">
-        <v>88.47404364983063</v>
+        <v>88.47403585796052</v>
       </c>
       <c r="D175" t="n">
-        <v>85.29386011368575</v>
+        <v>85.29385260189301</v>
       </c>
       <c r="E175" t="n">
-        <v>86.10208803445202</v>
+        <v>86.102080451479</v>
       </c>
       <c r="F175" t="n">
         <v>817586</v>
@@ -3952,16 +3952,16 @@
         <v>44732</v>
       </c>
       <c r="B177" t="n">
-        <v>83.89703369140625</v>
+        <v>83.89704132080078</v>
       </c>
       <c r="C177" t="n">
-        <v>85.54861686323618</v>
+        <v>85.54862464282172</v>
       </c>
       <c r="D177" t="n">
-        <v>82.53535140601245</v>
+        <v>82.53535891157887</v>
       </c>
       <c r="E177" t="n">
-        <v>84.51198308984139</v>
+        <v>84.51199077515794</v>
       </c>
       <c r="F177" t="n">
         <v>143101</v>
@@ -3972,16 +3972,16 @@
         <v>44733</v>
       </c>
       <c r="B178" t="n">
-        <v>85.99665832519531</v>
+        <v>85.99666595458984</v>
       </c>
       <c r="C178" t="n">
-        <v>87.58674661395143</v>
+        <v>87.58675438441436</v>
       </c>
       <c r="D178" t="n">
-        <v>85.37292199810067</v>
+        <v>85.37292957215897</v>
       </c>
       <c r="E178" t="n">
-        <v>85.5749806376266</v>
+        <v>85.57498822961099</v>
       </c>
       <c r="F178" t="n">
         <v>532289</v>
@@ -3992,16 +3992,16 @@
         <v>44734</v>
       </c>
       <c r="B179" t="n">
-        <v>86.53254699707031</v>
+        <v>86.53253936767578</v>
       </c>
       <c r="C179" t="n">
-        <v>87.41105001226899</v>
+        <v>87.41104230541869</v>
       </c>
       <c r="D179" t="n">
-        <v>84.59105613777476</v>
+        <v>84.59104867955743</v>
       </c>
       <c r="E179" t="n">
-        <v>84.95123888873424</v>
+        <v>84.95123139876036</v>
       </c>
       <c r="F179" t="n">
         <v>352268</v>
@@ -4012,16 +4012,16 @@
         <v>44735</v>
       </c>
       <c r="B180" t="n">
-        <v>89.34375</v>
+        <v>89.34375762939453</v>
       </c>
       <c r="C180" t="n">
-        <v>90.31888883979336</v>
+        <v>90.31889655245861</v>
       </c>
       <c r="D180" t="n">
-        <v>86.62039211422531</v>
+        <v>86.6203995110622</v>
       </c>
       <c r="E180" t="n">
-        <v>86.84001785827886</v>
+        <v>86.8400252738704</v>
       </c>
       <c r="F180" t="n">
         <v>839900</v>
@@ -4112,16 +4112,16 @@
         <v>44742</v>
       </c>
       <c r="B185" t="n">
-        <v>82.69349670410156</v>
+        <v>82.69348907470703</v>
       </c>
       <c r="C185" t="n">
-        <v>84.46807676912917</v>
+        <v>84.4680689760099</v>
       </c>
       <c r="D185" t="n">
-        <v>79.82079443579234</v>
+        <v>79.82078707143653</v>
       </c>
       <c r="E185" t="n">
-        <v>82.49144473881779</v>
+        <v>82.4914371280648</v>
       </c>
       <c r="F185" t="n">
         <v>710009</v>
@@ -4192,16 +4192,16 @@
         <v>44748</v>
       </c>
       <c r="B189" t="n">
-        <v>86.62039184570312</v>
+        <v>86.62039947509766</v>
       </c>
       <c r="C189" t="n">
-        <v>88.46524674954465</v>
+        <v>88.46525454143122</v>
       </c>
       <c r="D189" t="n">
-        <v>84.60861923211571</v>
+        <v>84.60862668431632</v>
       </c>
       <c r="E189" t="n">
-        <v>87.84151044265967</v>
+        <v>87.8415181796085</v>
       </c>
       <c r="F189" t="n">
         <v>788696</v>
@@ -4212,16 +4212,16 @@
         <v>44749</v>
       </c>
       <c r="B190" t="n">
-        <v>86.40076446533203</v>
+        <v>86.40077209472656</v>
       </c>
       <c r="C190" t="n">
-        <v>88.54431382481931</v>
+        <v>88.54432164349438</v>
       </c>
       <c r="D190" t="n">
-        <v>86.18992563237374</v>
+        <v>86.18993324315069</v>
       </c>
       <c r="E190" t="n">
-        <v>87.14749063816215</v>
+        <v>87.14749833349438</v>
       </c>
       <c r="F190" t="n">
         <v>483378</v>
@@ -4252,16 +4252,16 @@
         <v>44753</v>
       </c>
       <c r="B192" t="n">
-        <v>81.78861999511719</v>
+        <v>81.78863525390625</v>
       </c>
       <c r="C192" t="n">
-        <v>85.20599579614506</v>
+        <v>85.20601169249247</v>
       </c>
       <c r="D192" t="n">
-        <v>81.43721748884678</v>
+        <v>81.4372326820769</v>
       </c>
       <c r="E192" t="n">
-        <v>85.03029789423252</v>
+        <v>85.03031375780108</v>
       </c>
       <c r="F192" t="n">
         <v>432674</v>
@@ -4292,16 +4292,16 @@
         <v>44755</v>
       </c>
       <c r="B194" t="n">
-        <v>84.68768310546875</v>
+        <v>84.68769073486328</v>
       </c>
       <c r="C194" t="n">
-        <v>86.91908133386021</v>
+        <v>86.91908916427828</v>
       </c>
       <c r="D194" t="n">
-        <v>83.45777767295714</v>
+        <v>83.45778519155122</v>
       </c>
       <c r="E194" t="n">
-        <v>84.37142151703875</v>
+        <v>84.37142911794173</v>
       </c>
       <c r="F194" t="n">
         <v>1885043</v>
@@ -4312,16 +4312,16 @@
         <v>44756</v>
       </c>
       <c r="B195" t="n">
-        <v>81.44600677490234</v>
+        <v>81.44601440429688</v>
       </c>
       <c r="C195" t="n">
-        <v>85.20599828625562</v>
+        <v>85.20600626786458</v>
       </c>
       <c r="D195" t="n">
-        <v>81.35815782137873</v>
+        <v>81.35816544254408</v>
       </c>
       <c r="E195" t="n">
-        <v>84.3362822522144</v>
+        <v>84.33629015235336</v>
       </c>
       <c r="F195" t="n">
         <v>647308</v>
@@ -4372,16 +4372,16 @@
         <v>44761</v>
       </c>
       <c r="B198" t="n">
-        <v>86.85758209228516</v>
+        <v>86.85758972167969</v>
       </c>
       <c r="C198" t="n">
-        <v>87.15626985408389</v>
+        <v>87.15627750971456</v>
       </c>
       <c r="D198" t="n">
-        <v>83.45777353639596</v>
+        <v>83.45778086715818</v>
       </c>
       <c r="E198" t="n">
-        <v>83.45777353639596</v>
+        <v>83.45778086715818</v>
       </c>
       <c r="F198" t="n">
         <v>493807</v>
@@ -4392,16 +4392,16 @@
         <v>44762</v>
       </c>
       <c r="B199" t="n">
-        <v>88.29834747314453</v>
+        <v>88.29833984375</v>
       </c>
       <c r="C199" t="n">
-        <v>88.90451004772193</v>
+        <v>88.90450236595208</v>
       </c>
       <c r="D199" t="n">
-        <v>86.09330284004604</v>
+        <v>86.09329540117778</v>
       </c>
       <c r="E199" t="n">
-        <v>86.09330284004604</v>
+        <v>86.09329540117778</v>
       </c>
       <c r="F199" t="n">
         <v>780872</v>
@@ -4412,16 +4412,16 @@
         <v>44763</v>
       </c>
       <c r="B200" t="n">
-        <v>91.97047424316406</v>
+        <v>91.97048187255859</v>
       </c>
       <c r="C200" t="n">
-        <v>92.62056453720052</v>
+        <v>92.62057222052319</v>
       </c>
       <c r="D200" t="n">
-        <v>87.41104187399904</v>
+        <v>87.41104912516667</v>
       </c>
       <c r="E200" t="n">
-        <v>87.41104187399904</v>
+        <v>87.41104912516667</v>
       </c>
       <c r="F200" t="n">
         <v>453688</v>
@@ -4432,16 +4432,16 @@
         <v>44764</v>
       </c>
       <c r="B201" t="n">
-        <v>89.78299713134766</v>
+        <v>89.78300476074219</v>
       </c>
       <c r="C201" t="n">
-        <v>92.24280802636217</v>
+        <v>92.24281586478145</v>
       </c>
       <c r="D201" t="n">
-        <v>89.22075579004928</v>
+        <v>89.22076337166682</v>
       </c>
       <c r="E201" t="n">
-        <v>91.97047426173357</v>
+        <v>91.97048207701101</v>
       </c>
       <c r="F201" t="n">
         <v>566897</v>
@@ -4532,16 +4532,16 @@
         <v>44771</v>
       </c>
       <c r="B206" t="n">
-        <v>95.71289825439453</v>
+        <v>95.71290588378906</v>
       </c>
       <c r="C206" t="n">
-        <v>96.45963115921559</v>
+        <v>96.45963884813312</v>
       </c>
       <c r="D206" t="n">
-        <v>92.28674194909148</v>
+        <v>92.28674930538281</v>
       </c>
       <c r="E206" t="n">
-        <v>92.28674194909148</v>
+        <v>92.28674930538281</v>
       </c>
       <c r="F206" t="n">
         <v>432249</v>
@@ -4592,16 +4592,16 @@
         <v>44776</v>
       </c>
       <c r="B209" t="n">
-        <v>106.8523101806641</v>
+        <v>106.8523178100586</v>
       </c>
       <c r="C209" t="n">
-        <v>107.5990430416299</v>
+        <v>107.5990507243421</v>
       </c>
       <c r="D209" t="n">
-        <v>101.4670895712767</v>
+        <v>101.4670968161594</v>
       </c>
       <c r="E209" t="n">
-        <v>101.4670895712767</v>
+        <v>101.4670968161594</v>
       </c>
       <c r="F209" t="n">
         <v>990038</v>
@@ -4692,16 +4692,16 @@
         <v>44783</v>
       </c>
       <c r="B214" t="n">
-        <v>90.87235260009766</v>
+        <v>90.87236022949219</v>
       </c>
       <c r="C214" t="n">
-        <v>103.6457870434117</v>
+        <v>103.6457957452289</v>
       </c>
       <c r="D214" t="n">
-        <v>90.32767832640604</v>
+        <v>90.32768591007121</v>
       </c>
       <c r="E214" t="n">
-        <v>103.6457870434117</v>
+        <v>103.6457957452289</v>
       </c>
       <c r="F214" t="n">
         <v>2607483</v>
@@ -4712,16 +4712,16 @@
         <v>44784</v>
       </c>
       <c r="B215" t="n">
-        <v>84.59983825683594</v>
+        <v>84.59984588623047</v>
       </c>
       <c r="C215" t="n">
-        <v>92.06711346342773</v>
+        <v>92.06712176623714</v>
       </c>
       <c r="D215" t="n">
-        <v>83.26450999593463</v>
+        <v>83.26451750490639</v>
       </c>
       <c r="E215" t="n">
-        <v>90.87234889417739</v>
+        <v>90.87235708924037</v>
       </c>
       <c r="F215" t="n">
         <v>3127275</v>
@@ -4732,16 +4732,16 @@
         <v>44785</v>
       </c>
       <c r="B216" t="n">
-        <v>88.11385345458984</v>
+        <v>88.11386108398438</v>
       </c>
       <c r="C216" t="n">
-        <v>88.11385345458984</v>
+        <v>88.11386108398438</v>
       </c>
       <c r="D216" t="n">
-        <v>84.52077270447177</v>
+        <v>84.52078002275709</v>
       </c>
       <c r="E216" t="n">
-        <v>84.52077270447177</v>
+        <v>84.52078002275709</v>
       </c>
       <c r="F216" t="n">
         <v>1008211</v>
@@ -4772,16 +4772,16 @@
         <v>44789</v>
       </c>
       <c r="B218" t="n">
-        <v>94.96617126464844</v>
+        <v>94.96617889404297</v>
       </c>
       <c r="C218" t="n">
-        <v>98.40112115051892</v>
+        <v>98.40112905587054</v>
       </c>
       <c r="D218" t="n">
-        <v>92.85776276178804</v>
+        <v>92.8577702217972</v>
       </c>
       <c r="E218" t="n">
-        <v>98.18149540443858</v>
+        <v>98.1815032921459</v>
       </c>
       <c r="F218" t="n">
         <v>844810</v>
@@ -4792,16 +4792,16 @@
         <v>44790</v>
       </c>
       <c r="B219" t="n">
-        <v>96.5211181640625</v>
+        <v>96.52112579345703</v>
       </c>
       <c r="C219" t="n">
-        <v>96.67046205176851</v>
+        <v>96.67046969296776</v>
       </c>
       <c r="D219" t="n">
-        <v>93.29700735611611</v>
+        <v>93.29701473066473</v>
       </c>
       <c r="E219" t="n">
-        <v>93.29700735611611</v>
+        <v>93.29701473066473</v>
       </c>
       <c r="F219" t="n">
         <v>484266</v>
@@ -4872,16 +4872,16 @@
         <v>44796</v>
       </c>
       <c r="B223" t="n">
-        <v>96.42449188232422</v>
+        <v>96.42449951171875</v>
       </c>
       <c r="C223" t="n">
-        <v>97.50504682708615</v>
+        <v>97.50505454197742</v>
       </c>
       <c r="D223" t="n">
-        <v>87.49889811798089</v>
+        <v>87.49890504115571</v>
       </c>
       <c r="E223" t="n">
-        <v>89.51945771416493</v>
+        <v>89.51946479721248</v>
       </c>
       <c r="F223" t="n">
         <v>1305076</v>
@@ -4952,16 +4952,16 @@
         <v>44802</v>
       </c>
       <c r="B227" t="n">
-        <v>91.77720642089844</v>
+        <v>91.77721405029297</v>
       </c>
       <c r="C227" t="n">
-        <v>95.84467276233583</v>
+        <v>95.84468072985686</v>
       </c>
       <c r="D227" t="n">
-        <v>91.23253216618707</v>
+        <v>91.23253975030309</v>
       </c>
       <c r="E227" t="n">
-        <v>93.56056637901798</v>
+        <v>93.56057415666235</v>
       </c>
       <c r="F227" t="n">
         <v>661048</v>
@@ -4972,16 +4972,16 @@
         <v>44803</v>
       </c>
       <c r="B228" t="n">
-        <v>89.34375</v>
+        <v>89.34375762939453</v>
       </c>
       <c r="C228" t="n">
-        <v>93.80654672775484</v>
+        <v>93.80655473824415</v>
       </c>
       <c r="D228" t="n">
-        <v>88.50038794712792</v>
+        <v>88.50039550450462</v>
       </c>
       <c r="E228" t="n">
-        <v>92.65570997369696</v>
+        <v>92.65571788591205</v>
       </c>
       <c r="F228" t="n">
         <v>477437</v>
@@ -5012,16 +5012,16 @@
         <v>44805</v>
       </c>
       <c r="B230" t="n">
-        <v>88.58823394775391</v>
+        <v>88.58824157714844</v>
       </c>
       <c r="C230" t="n">
-        <v>89.21197693820172</v>
+        <v>89.21198462131423</v>
       </c>
       <c r="D230" t="n">
-        <v>84.33628290195425</v>
+        <v>84.33629016516232</v>
       </c>
       <c r="E230" t="n">
-        <v>87.39347610622615</v>
+        <v>87.39348363272576</v>
       </c>
       <c r="F230" t="n">
         <v>1016578</v>
@@ -5032,16 +5032,16 @@
         <v>44806</v>
       </c>
       <c r="B231" t="n">
-        <v>88.02600860595703</v>
+        <v>88.0260009765625</v>
       </c>
       <c r="C231" t="n">
-        <v>91.1974053571811</v>
+        <v>91.19739745291511</v>
       </c>
       <c r="D231" t="n">
-        <v>86.98937467200503</v>
+        <v>86.98936713245767</v>
       </c>
       <c r="E231" t="n">
-        <v>89.50189409323706</v>
+        <v>89.50188633592451</v>
       </c>
       <c r="F231" t="n">
         <v>344726</v>
@@ -5072,16 +5072,16 @@
         <v>44810</v>
       </c>
       <c r="B233" t="n">
-        <v>86.71702575683594</v>
+        <v>86.71703338623047</v>
       </c>
       <c r="C233" t="n">
-        <v>89.31739369553651</v>
+        <v>89.31740155371233</v>
       </c>
       <c r="D233" t="n">
-        <v>85.2059996040562</v>
+        <v>85.20600710051012</v>
       </c>
       <c r="E233" t="n">
-        <v>88.73758523135686</v>
+        <v>88.73759303852093</v>
       </c>
       <c r="F233" t="n">
         <v>519096</v>
@@ -5112,16 +5112,16 @@
         <v>44813</v>
       </c>
       <c r="B235" t="n">
-        <v>91.80355834960938</v>
+        <v>91.80356597900391</v>
       </c>
       <c r="C235" t="n">
-        <v>92.14617396419217</v>
+        <v>92.14618162206</v>
       </c>
       <c r="D235" t="n">
-        <v>88.81664697669278</v>
+        <v>88.81665435785808</v>
       </c>
       <c r="E235" t="n">
-        <v>88.81664697669278</v>
+        <v>88.81665435785808</v>
       </c>
       <c r="F235" t="n">
         <v>540504</v>
@@ -5152,16 +5152,16 @@
         <v>44817</v>
       </c>
       <c r="B237" t="n">
-        <v>90.74936676025391</v>
+        <v>90.74937438964844</v>
       </c>
       <c r="C237" t="n">
-        <v>92.94562436139803</v>
+        <v>92.94563217543426</v>
       </c>
       <c r="D237" t="n">
-        <v>90.48581316713809</v>
+        <v>90.4858207743754</v>
       </c>
       <c r="E237" t="n">
-        <v>91.36431620759575</v>
+        <v>91.36432388868973</v>
       </c>
       <c r="F237" t="n">
         <v>548480</v>
@@ -5172,16 +5172,16 @@
         <v>44818</v>
       </c>
       <c r="B238" t="n">
-        <v>90.13442230224609</v>
+        <v>90.13441467285156</v>
       </c>
       <c r="C238" t="n">
-        <v>91.77722561387868</v>
+        <v>91.77721784542967</v>
       </c>
       <c r="D238" t="n">
-        <v>88.15779020481769</v>
+        <v>88.15778274273444</v>
       </c>
       <c r="E238" t="n">
-        <v>90.17835014094558</v>
+        <v>90.1783425078328</v>
       </c>
       <c r="F238" t="n">
         <v>962834</v>
@@ -5192,16 +5192,16 @@
         <v>44819</v>
       </c>
       <c r="B239" t="n">
-        <v>90.22225189208984</v>
+        <v>90.22225952148438</v>
       </c>
       <c r="C239" t="n">
-        <v>93.36729411773216</v>
+        <v>93.36730201307846</v>
       </c>
       <c r="D239" t="n">
-        <v>89.21197884353981</v>
+        <v>89.2119863875034</v>
       </c>
       <c r="E239" t="n">
-        <v>89.60730249710758</v>
+        <v>89.60731007450063</v>
       </c>
       <c r="F239" t="n">
         <v>512054</v>
@@ -5212,16 +5212,16 @@
         <v>44820</v>
       </c>
       <c r="B240" t="n">
-        <v>87.80637359619141</v>
+        <v>87.80636596679688</v>
       </c>
       <c r="C240" t="n">
-        <v>89.46674375698272</v>
+        <v>89.46673598332055</v>
       </c>
       <c r="D240" t="n">
-        <v>86.15479034222778</v>
+        <v>86.15478285633742</v>
       </c>
       <c r="E240" t="n">
-        <v>89.33497366679777</v>
+        <v>89.33496590458495</v>
       </c>
       <c r="F240" t="n">
         <v>454254</v>
@@ -5312,16 +5312,16 @@
         <v>44827</v>
       </c>
       <c r="B245" t="n">
-        <v>88.11385345458984</v>
+        <v>88.11386108398438</v>
       </c>
       <c r="C245" t="n">
-        <v>89.37011301088573</v>
+        <v>89.37012074905431</v>
       </c>
       <c r="D245" t="n">
-        <v>86.19871664923903</v>
+        <v>86.19872411281021</v>
       </c>
       <c r="E245" t="n">
-        <v>87.85029987398948</v>
+        <v>87.85030748056406</v>
       </c>
       <c r="F245" t="n">
         <v>433707</v>
@@ -5352,16 +5352,16 @@
         <v>44831</v>
       </c>
       <c r="B247" t="n">
-        <v>86.48861694335938</v>
+        <v>86.48860931396484</v>
       </c>
       <c r="C247" t="n">
-        <v>88.90450017308949</v>
+        <v>88.90449233058337</v>
       </c>
       <c r="D247" t="n">
-        <v>84.68768982993723</v>
+        <v>84.68768235940733</v>
       </c>
       <c r="E247" t="n">
-        <v>85.22357719163666</v>
+        <v>85.2235696738347</v>
       </c>
       <c r="F247" t="n">
         <v>891547</v>
@@ -5372,16 +5372,16 @@
         <v>44832</v>
       </c>
       <c r="B248" t="n">
-        <v>86.94544219970703</v>
+        <v>86.94544982910156</v>
       </c>
       <c r="C248" t="n">
-        <v>88.52674356400453</v>
+        <v>88.52675133215702</v>
       </c>
       <c r="D248" t="n">
-        <v>85.29385228500924</v>
+        <v>85.29385976947805</v>
       </c>
       <c r="E248" t="n">
-        <v>86.5501118317982</v>
+        <v>86.5501194265028</v>
       </c>
       <c r="F248" t="n">
         <v>626382</v>
@@ -5452,16 +5452,16 @@
         <v>44838</v>
       </c>
       <c r="B252" t="n">
-        <v>94.43907165527344</v>
+        <v>94.43907928466797</v>
       </c>
       <c r="C252" t="n">
-        <v>96.46841142233895</v>
+        <v>96.46841921567656</v>
       </c>
       <c r="D252" t="n">
-        <v>92.77870153632058</v>
+        <v>92.77870903157975</v>
       </c>
       <c r="E252" t="n">
-        <v>93.47271970440633</v>
+        <v>93.47272725573275</v>
       </c>
       <c r="F252" t="n">
         <v>828067</v>
@@ -5492,16 +5492,16 @@
         <v>44840</v>
       </c>
       <c r="B254" t="n">
-        <v>99.09513854980469</v>
+        <v>99.09514617919922</v>
       </c>
       <c r="C254" t="n">
-        <v>99.89457277411294</v>
+        <v>99.89458046505639</v>
       </c>
       <c r="D254" t="n">
-        <v>94.70262366200211</v>
+        <v>94.70263095321427</v>
       </c>
       <c r="E254" t="n">
-        <v>95.71289672424005</v>
+        <v>95.71290409323375</v>
       </c>
       <c r="F254" t="n">
         <v>1317655</v>
@@ -5512,16 +5512,16 @@
         <v>44841</v>
       </c>
       <c r="B255" t="n">
-        <v>96.81102752685547</v>
+        <v>96.81101989746094</v>
       </c>
       <c r="C255" t="n">
-        <v>98.87551493044936</v>
+        <v>98.87550713835859</v>
       </c>
       <c r="D255" t="n">
-        <v>95.87102958876109</v>
+        <v>95.87102203344506</v>
       </c>
       <c r="E255" t="n">
-        <v>97.69831742994607</v>
+        <v>97.69830973062682</v>
       </c>
       <c r="F255" t="n">
         <v>390672</v>
@@ -5532,16 +5532,16 @@
         <v>44844</v>
       </c>
       <c r="B256" t="n">
-        <v>96.5211181640625</v>
+        <v>96.52112579345703</v>
       </c>
       <c r="C256" t="n">
-        <v>97.95307550975528</v>
+        <v>97.95308325233714</v>
       </c>
       <c r="D256" t="n">
-        <v>94.96616424340819</v>
+        <v>94.96617174989328</v>
       </c>
       <c r="E256" t="n">
-        <v>97.1624215418332</v>
+        <v>97.16242922191877</v>
       </c>
       <c r="F256" t="n">
         <v>391665</v>
@@ -5552,16 +5552,16 @@
         <v>44845</v>
       </c>
       <c r="B257" t="n">
-        <v>88.64974212646484</v>
+        <v>88.64973449707031</v>
       </c>
       <c r="C257" t="n">
-        <v>96.94280599912264</v>
+        <v>96.94279765600854</v>
       </c>
       <c r="D257" t="n">
-        <v>87.1387158739726</v>
+        <v>87.13870837462035</v>
       </c>
       <c r="E257" t="n">
-        <v>96.5211283068829</v>
+        <v>96.52112000005931</v>
       </c>
       <c r="F257" t="n">
         <v>1649810</v>
@@ -5572,16 +5572,16 @@
         <v>44847</v>
       </c>
       <c r="B258" t="n">
-        <v>86.48861694335938</v>
+        <v>86.48860931396484</v>
       </c>
       <c r="C258" t="n">
-        <v>88.29833766583862</v>
+        <v>88.29832987680373</v>
       </c>
       <c r="D258" t="n">
-        <v>84.9073155780945</v>
+        <v>84.90730808819083</v>
       </c>
       <c r="E258" t="n">
-        <v>86.97179627028378</v>
+        <v>86.97178859826668</v>
       </c>
       <c r="F258" t="n">
         <v>1120971</v>
@@ -5592,16 +5592,16 @@
         <v>44848</v>
       </c>
       <c r="B259" t="n">
-        <v>82.71984100341797</v>
+        <v>82.7198486328125</v>
       </c>
       <c r="C259" t="n">
-        <v>90.16954226733124</v>
+        <v>90.16955058382466</v>
       </c>
       <c r="D259" t="n">
-        <v>82.66712626874587</v>
+        <v>82.66713389327845</v>
       </c>
       <c r="E259" t="n">
-        <v>86.64674356053986</v>
+        <v>86.64675155211943</v>
       </c>
       <c r="F259" t="n">
         <v>951929</v>
@@ -5612,16 +5612,16 @@
         <v>44851</v>
       </c>
       <c r="B260" t="n">
-        <v>83.01853179931641</v>
+        <v>83.01853942871094</v>
       </c>
       <c r="C260" t="n">
-        <v>85.90880741440093</v>
+        <v>85.90881530941148</v>
       </c>
       <c r="D260" t="n">
-        <v>82.82526007088433</v>
+        <v>82.82526768251721</v>
       </c>
       <c r="E260" t="n">
-        <v>84.32749936581655</v>
+        <v>84.32750711550507</v>
       </c>
       <c r="F260" t="n">
         <v>630186</v>
@@ -5632,16 +5632,16 @@
         <v>44852</v>
       </c>
       <c r="B261" t="n">
-        <v>80.54116058349609</v>
+        <v>80.54115295410156</v>
       </c>
       <c r="C261" t="n">
-        <v>85.61012027643372</v>
+        <v>85.61011216687361</v>
       </c>
       <c r="D261" t="n">
-        <v>79.24097310925836</v>
+        <v>79.24096560302623</v>
       </c>
       <c r="E261" t="n">
-        <v>84.42414248924207</v>
+        <v>84.42413449202566</v>
       </c>
       <c r="F261" t="n">
         <v>1514560</v>
@@ -5652,16 +5652,16 @@
         <v>44853</v>
       </c>
       <c r="B262" t="n">
-        <v>80.47087860107422</v>
+        <v>80.47087097167969</v>
       </c>
       <c r="C262" t="n">
-        <v>81.52508628989879</v>
+        <v>81.52507856055549</v>
       </c>
       <c r="D262" t="n">
-        <v>79.10920288553962</v>
+        <v>79.10919538524473</v>
       </c>
       <c r="E262" t="n">
-        <v>80.38302963595044</v>
+        <v>80.38302201488482</v>
       </c>
       <c r="F262" t="n">
         <v>1204425</v>
@@ -5672,16 +5672,16 @@
         <v>44854</v>
       </c>
       <c r="B263" t="n">
-        <v>77.81778717041016</v>
+        <v>77.81779479980469</v>
       </c>
       <c r="C263" t="n">
-        <v>80.72562957529622</v>
+        <v>80.72563748978079</v>
       </c>
       <c r="D263" t="n">
-        <v>76.50003284276583</v>
+        <v>76.50004034296538</v>
       </c>
       <c r="E263" t="n">
-        <v>80.4708629343249</v>
+        <v>80.4708708238317</v>
       </c>
       <c r="F263" t="n">
         <v>1064344</v>
@@ -5712,16 +5712,16 @@
         <v>44858</v>
       </c>
       <c r="B265" t="n">
-        <v>82.40358734130859</v>
+        <v>82.40357971191406</v>
       </c>
       <c r="C265" t="n">
-        <v>83.41386046932367</v>
+        <v>83.41385274639228</v>
       </c>
       <c r="D265" t="n">
-        <v>80.20732975441281</v>
+        <v>80.20732232836033</v>
       </c>
       <c r="E265" t="n">
-        <v>81.73592315820733</v>
+        <v>81.73591559062895</v>
       </c>
       <c r="F265" t="n">
         <v>718180</v>
@@ -5772,16 +5772,16 @@
         <v>44861</v>
       </c>
       <c r="B268" t="n">
-        <v>78.95985412597656</v>
+        <v>78.95984649658203</v>
       </c>
       <c r="C268" t="n">
-        <v>81.79742201297594</v>
+        <v>81.79741410940505</v>
       </c>
       <c r="D268" t="n">
-        <v>78.12527888403669</v>
+        <v>78.12527133528192</v>
       </c>
       <c r="E268" t="n">
-        <v>80.63779821975547</v>
+        <v>80.63779042823175</v>
       </c>
       <c r="F268" t="n">
         <v>872704</v>
@@ -5852,16 +5852,16 @@
         <v>44868</v>
       </c>
       <c r="B272" t="n">
-        <v>86.58524322509766</v>
+        <v>86.58525085449219</v>
       </c>
       <c r="C272" t="n">
-        <v>88.4652388850419</v>
+        <v>88.46524668009084</v>
       </c>
       <c r="D272" t="n">
-        <v>84.0463703936091</v>
+        <v>84.04637779929271</v>
       </c>
       <c r="E272" t="n">
-        <v>85.59253736618446</v>
+        <v>85.59254490810744</v>
       </c>
       <c r="F272" t="n">
         <v>991113</v>
@@ -5892,16 +5892,16 @@
         <v>44872</v>
       </c>
       <c r="B274" t="n">
-        <v>83.19422912597656</v>
+        <v>83.19423675537109</v>
       </c>
       <c r="C274" t="n">
-        <v>84.51198358965588</v>
+        <v>84.51199133989617</v>
       </c>
       <c r="D274" t="n">
-        <v>82.2805919293112</v>
+        <v>82.28059947491988</v>
       </c>
       <c r="E274" t="n">
-        <v>83.03609832223721</v>
+        <v>83.03610593713023</v>
       </c>
       <c r="F274" t="n">
         <v>752715</v>
@@ -5912,16 +5912,16 @@
         <v>44873</v>
       </c>
       <c r="B275" t="n">
-        <v>83.45777893066406</v>
+        <v>83.45778656005859</v>
       </c>
       <c r="C275" t="n">
-        <v>84.66133036601822</v>
+        <v>84.66133810543688</v>
       </c>
       <c r="D275" t="n">
-        <v>81.31422962176761</v>
+        <v>81.31423705520696</v>
       </c>
       <c r="E275" t="n">
-        <v>82.71105277545774</v>
+        <v>82.7110603365894</v>
       </c>
       <c r="F275" t="n">
         <v>953385</v>
@@ -5932,16 +5932,16 @@
         <v>44874</v>
       </c>
       <c r="B276" t="n">
-        <v>90.18711853027344</v>
+        <v>90.18712615966797</v>
       </c>
       <c r="C276" t="n">
-        <v>93.10374813592868</v>
+        <v>93.10375601205598</v>
       </c>
       <c r="D276" t="n">
-        <v>83.4665694385159</v>
+        <v>83.46657649938446</v>
       </c>
       <c r="E276" t="n">
-        <v>83.89703401910188</v>
+        <v>83.89704111638565</v>
       </c>
       <c r="F276" t="n">
         <v>2468383</v>
@@ -5952,16 +5952,16 @@
         <v>44875</v>
       </c>
       <c r="B277" t="n">
-        <v>90.49459075927734</v>
+        <v>90.49459838867188</v>
       </c>
       <c r="C277" t="n">
-        <v>94.21944139071987</v>
+        <v>94.21944933414814</v>
       </c>
       <c r="D277" t="n">
-        <v>85.65403762792715</v>
+        <v>85.65404484922558</v>
       </c>
       <c r="E277" t="n">
-        <v>85.67160473785169</v>
+        <v>85.67161196063115</v>
       </c>
       <c r="F277" t="n">
         <v>2820385</v>
@@ -5992,16 +5992,16 @@
         <v>44879</v>
       </c>
       <c r="B279" t="n">
-        <v>88.816650390625</v>
+        <v>88.81665802001953</v>
       </c>
       <c r="C279" t="n">
-        <v>90.389171537141</v>
+        <v>90.38917930161588</v>
       </c>
       <c r="D279" t="n">
-        <v>85.91759456330244</v>
+        <v>85.91760194366664</v>
       </c>
       <c r="E279" t="n">
-        <v>89.08020396694791</v>
+        <v>89.08021161898182</v>
       </c>
       <c r="F279" t="n">
         <v>689741</v>
@@ -6012,16 +6012,16 @@
         <v>44881</v>
       </c>
       <c r="B280" t="n">
-        <v>86.34806823730469</v>
+        <v>86.34806060791016</v>
       </c>
       <c r="C280" t="n">
-        <v>90.38918105076644</v>
+        <v>90.38917306431421</v>
       </c>
       <c r="D280" t="n">
-        <v>85.75947278433812</v>
+        <v>85.7594652069497</v>
       </c>
       <c r="E280" t="n">
-        <v>88.90450870594499</v>
+        <v>88.90450085067289</v>
       </c>
       <c r="F280" t="n">
         <v>1097230</v>
@@ -6072,16 +6072,16 @@
         <v>44886</v>
       </c>
       <c r="B283" t="n">
-        <v>80.0404052734375</v>
+        <v>80.04041290283203</v>
       </c>
       <c r="C283" t="n">
-        <v>82.56171118314468</v>
+        <v>82.5617190528683</v>
       </c>
       <c r="D283" t="n">
-        <v>79.6275078095798</v>
+        <v>79.62751539961722</v>
       </c>
       <c r="E283" t="n">
-        <v>82.0697449675642</v>
+        <v>82.06975279039395</v>
       </c>
       <c r="F283" t="n">
         <v>597582</v>
@@ -6092,16 +6092,16 @@
         <v>44887</v>
       </c>
       <c r="B284" t="n">
-        <v>78.23069763183594</v>
+        <v>78.23069000244141</v>
       </c>
       <c r="C284" t="n">
-        <v>80.67293498688288</v>
+        <v>80.67292711931084</v>
       </c>
       <c r="D284" t="n">
-        <v>76.6493894942427</v>
+        <v>76.64938201906415</v>
       </c>
       <c r="E284" t="n">
-        <v>80.04919863884506</v>
+        <v>80.04919083210247</v>
       </c>
       <c r="F284" t="n">
         <v>724710</v>
@@ -6112,16 +6112,16 @@
         <v>44888</v>
       </c>
       <c r="B285" t="n">
-        <v>77.27311706542969</v>
+        <v>77.27312469482422</v>
       </c>
       <c r="C285" t="n">
-        <v>78.72264824317485</v>
+        <v>78.7226560156857</v>
       </c>
       <c r="D285" t="n">
-        <v>75.99929049548588</v>
+        <v>75.99929799911189</v>
       </c>
       <c r="E285" t="n">
-        <v>78.02863012286181</v>
+        <v>78.0286378268503</v>
       </c>
       <c r="F285" t="n">
         <v>751617</v>
@@ -6132,16 +6132,16 @@
         <v>44889</v>
       </c>
       <c r="B286" t="n">
-        <v>78.80171203613281</v>
+        <v>78.80171966552734</v>
       </c>
       <c r="C286" t="n">
-        <v>79.50451707802175</v>
+        <v>79.5045247754602</v>
       </c>
       <c r="D286" t="n">
-        <v>77.19405672940827</v>
+        <v>77.19406420315345</v>
       </c>
       <c r="E286" t="n">
-        <v>77.52788543796044</v>
+        <v>77.52789294402611</v>
       </c>
       <c r="F286" t="n">
         <v>618983</v>
@@ -6212,16 +6212,16 @@
         <v>44895</v>
       </c>
       <c r="B290" t="n">
-        <v>79.53965759277344</v>
+        <v>79.53966522216797</v>
       </c>
       <c r="C290" t="n">
-        <v>80.11946605228191</v>
+        <v>80.11947373729132</v>
       </c>
       <c r="D290" t="n">
-        <v>75.72695131909879</v>
+        <v>75.72695858278091</v>
       </c>
       <c r="E290" t="n">
-        <v>78.18676225065957</v>
+        <v>78.18676975028522</v>
       </c>
       <c r="F290" t="n">
         <v>577266</v>
@@ -6252,16 +6252,16 @@
         <v>44897</v>
       </c>
       <c r="B292" t="n">
-        <v>83.99366760253906</v>
+        <v>83.99367523193359</v>
       </c>
       <c r="C292" t="n">
-        <v>84.95123260105719</v>
+        <v>84.95124031743019</v>
       </c>
       <c r="D292" t="n">
-        <v>77.90564188972039</v>
+        <v>77.90564896612145</v>
       </c>
       <c r="E292" t="n">
-        <v>79.21460940879811</v>
+        <v>79.21461660409658</v>
       </c>
       <c r="F292" t="n">
         <v>680539</v>
@@ -6292,16 +6292,16 @@
         <v>44901</v>
       </c>
       <c r="B294" t="n">
-        <v>77.94956970214844</v>
+        <v>77.94956207275391</v>
       </c>
       <c r="C294" t="n">
-        <v>81.69198744336707</v>
+        <v>81.69197944767954</v>
       </c>
       <c r="D294" t="n">
-        <v>77.94956970214844</v>
+        <v>77.94956207275391</v>
       </c>
       <c r="E294" t="n">
-        <v>81.0418971370554</v>
+        <v>81.04188920499614</v>
       </c>
       <c r="F294" t="n">
         <v>575865</v>
@@ -6312,16 +6312,16 @@
         <v>44902</v>
       </c>
       <c r="B295" t="n">
-        <v>76.15741729736328</v>
+        <v>76.15742492675781</v>
       </c>
       <c r="C295" t="n">
-        <v>78.43273655389115</v>
+        <v>78.4327444112255</v>
       </c>
       <c r="D295" t="n">
-        <v>74.76059422398934</v>
+        <v>74.76060171345117</v>
       </c>
       <c r="E295" t="n">
-        <v>77.82656741804537</v>
+        <v>77.82657521465414</v>
       </c>
       <c r="F295" t="n">
         <v>782541</v>
@@ -6332,16 +6332,16 @@
         <v>44903</v>
       </c>
       <c r="B296" t="n">
-        <v>72.38865661621094</v>
+        <v>72.38864898681641</v>
       </c>
       <c r="C296" t="n">
-        <v>76.73724427036358</v>
+        <v>76.73723618265012</v>
       </c>
       <c r="D296" t="n">
-        <v>72.03725403651906</v>
+        <v>72.03724644416056</v>
       </c>
       <c r="E296" t="n">
-        <v>76.73724427036358</v>
+        <v>76.73723618265012</v>
       </c>
       <c r="F296" t="n">
         <v>1116650</v>
@@ -6352,16 +6352,16 @@
         <v>44904</v>
       </c>
       <c r="B297" t="n">
-        <v>72.71369934082031</v>
+        <v>72.71369171142578</v>
       </c>
       <c r="C297" t="n">
-        <v>74.7606131921943</v>
+        <v>74.76060534802988</v>
       </c>
       <c r="D297" t="n">
-        <v>70.9303391029727</v>
+        <v>70.93033166069503</v>
       </c>
       <c r="E297" t="n">
-        <v>72.96846604657665</v>
+        <v>72.96845839045105</v>
       </c>
       <c r="F297" t="n">
         <v>602365</v>
@@ -6412,16 +6412,16 @@
         <v>44909</v>
       </c>
       <c r="B300" t="n">
-        <v>68.19818878173828</v>
+        <v>68.19818115234375</v>
       </c>
       <c r="C300" t="n">
-        <v>70.5174362779243</v>
+        <v>70.51742838907342</v>
       </c>
       <c r="D300" t="n">
-        <v>66.81893927300305</v>
+        <v>66.81893179790644</v>
       </c>
       <c r="E300" t="n">
-        <v>70.43837422126734</v>
+        <v>70.43836634126119</v>
       </c>
       <c r="F300" t="n">
         <v>1355188</v>
@@ -6472,16 +6472,16 @@
         <v>44914</v>
       </c>
       <c r="B303" t="n">
-        <v>66.36211395263672</v>
+        <v>66.36210632324219</v>
       </c>
       <c r="C303" t="n">
-        <v>66.73108358474747</v>
+        <v>66.73107591293393</v>
       </c>
       <c r="D303" t="n">
-        <v>64.41183632227187</v>
+        <v>64.41182891709317</v>
       </c>
       <c r="E303" t="n">
-        <v>66.09856038544582</v>
+        <v>66.09855278635102</v>
       </c>
       <c r="F303" t="n">
         <v>945079</v>
@@ -6572,16 +6572,16 @@
         <v>44921</v>
       </c>
       <c r="B308" t="n">
-        <v>68.78678894042969</v>
+        <v>68.78679656982422</v>
       </c>
       <c r="C308" t="n">
-        <v>71.15874440632886</v>
+        <v>71.15875229880567</v>
       </c>
       <c r="D308" t="n">
-        <v>68.39145856114908</v>
+        <v>68.39146614669608</v>
       </c>
       <c r="E308" t="n">
-        <v>71.15874440632886</v>
+        <v>71.15875229880567</v>
       </c>
       <c r="F308" t="n">
         <v>122344</v>
@@ -6612,16 +6612,16 @@
         <v>44923</v>
       </c>
       <c r="B310" t="n">
-        <v>68.39144897460938</v>
+        <v>68.39145660400391</v>
       </c>
       <c r="C310" t="n">
-        <v>70.26266442886484</v>
+        <v>70.26267226700244</v>
       </c>
       <c r="D310" t="n">
-        <v>67.17911739346478</v>
+        <v>67.17912488761789</v>
       </c>
       <c r="E310" t="n">
-        <v>67.82042075287674</v>
+        <v>67.82042831857034</v>
       </c>
       <c r="F310" t="n">
         <v>543744</v>
@@ -6632,16 +6632,16 @@
         <v>44924</v>
       </c>
       <c r="B311" t="n">
-        <v>70.66677856445312</v>
+        <v>70.66678619384766</v>
       </c>
       <c r="C311" t="n">
-        <v>70.66677856445312</v>
+        <v>70.66678619384766</v>
       </c>
       <c r="D311" t="n">
-        <v>67.35481873074851</v>
+        <v>67.35482600257404</v>
       </c>
       <c r="E311" t="n">
-        <v>68.52322924831307</v>
+        <v>68.52323664628368</v>
       </c>
       <c r="F311" t="n">
         <v>1109758</v>
@@ -6672,16 +6672,16 @@
         <v>44929</v>
       </c>
       <c r="B313" t="n">
-        <v>66.99462890625</v>
+        <v>66.99463653564453</v>
       </c>
       <c r="C313" t="n">
-        <v>69.74434040108741</v>
+        <v>69.74434834362098</v>
       </c>
       <c r="D313" t="n">
-        <v>65.50117004672566</v>
+        <v>65.50117750604407</v>
       </c>
       <c r="E313" t="n">
-        <v>66.60808550926455</v>
+        <v>66.60809309463926</v>
       </c>
       <c r="F313" t="n">
         <v>913081</v>
@@ -6752,16 +6752,16 @@
         <v>44935</v>
       </c>
       <c r="B317" t="n">
-        <v>69.62136077880859</v>
+        <v>69.62136840820312</v>
       </c>
       <c r="C317" t="n">
-        <v>70.95668235192537</v>
+        <v>70.95669012764992</v>
       </c>
       <c r="D317" t="n">
-        <v>66.80136703294467</v>
+        <v>66.80137435331271</v>
       </c>
       <c r="E317" t="n">
-        <v>66.99463875986392</v>
+        <v>66.99464610141148</v>
       </c>
       <c r="F317" t="n">
         <v>604476</v>
@@ -6952,16 +6952,16 @@
         <v>44949</v>
       </c>
       <c r="B327" t="n">
-        <v>80.09310913085938</v>
+        <v>80.09311676025391</v>
       </c>
       <c r="C327" t="n">
-        <v>81.20881158598479</v>
+        <v>81.2088193216573</v>
       </c>
       <c r="D327" t="n">
-        <v>77.09741767677029</v>
+        <v>77.09742502080553</v>
       </c>
       <c r="E327" t="n">
-        <v>77.09741767677029</v>
+        <v>77.09742502080553</v>
       </c>
       <c r="F327" t="n">
         <v>1210224</v>
@@ -6992,16 +6992,16 @@
         <v>44951</v>
       </c>
       <c r="B329" t="n">
-        <v>77.85293579101562</v>
+        <v>77.85294342041016</v>
       </c>
       <c r="C329" t="n">
-        <v>79.94377045148158</v>
+        <v>79.94377828577274</v>
       </c>
       <c r="D329" t="n">
-        <v>77.15891763884663</v>
+        <v>77.15892520022911</v>
       </c>
       <c r="E329" t="n">
-        <v>79.94377045148158</v>
+        <v>79.94377828577274</v>
       </c>
       <c r="F329" t="n">
         <v>568888</v>
@@ -7112,16 +7112,16 @@
         <v>44959</v>
       </c>
       <c r="B335" t="n">
-        <v>78.88957214355469</v>
+        <v>78.88956451416016</v>
       </c>
       <c r="C335" t="n">
-        <v>80.39181147045277</v>
+        <v>80.39180369577697</v>
       </c>
       <c r="D335" t="n">
-        <v>77.56303073581758</v>
+        <v>77.5630232347126</v>
       </c>
       <c r="E335" t="n">
-        <v>77.89685946320182</v>
+        <v>77.89685192981234</v>
       </c>
       <c r="F335" t="n">
         <v>645862</v>
@@ -7132,16 +7132,16 @@
         <v>44960</v>
       </c>
       <c r="B336" t="n">
-        <v>78.43274688720703</v>
+        <v>78.4327392578125</v>
       </c>
       <c r="C336" t="n">
-        <v>80.04919589494379</v>
+        <v>80.04918810831229</v>
       </c>
       <c r="D336" t="n">
-        <v>76.42976111654413</v>
+        <v>76.42975368198618</v>
       </c>
       <c r="E336" t="n">
-        <v>79.05648321386462</v>
+        <v>79.05647552379735</v>
       </c>
       <c r="F336" t="n">
         <v>709735</v>
@@ -7152,16 +7152,16 @@
         <v>44963</v>
       </c>
       <c r="B337" t="n">
-        <v>77.33461761474609</v>
+        <v>77.33462524414062</v>
       </c>
       <c r="C337" t="n">
-        <v>79.71535992805047</v>
+        <v>79.71536779231553</v>
       </c>
       <c r="D337" t="n">
-        <v>76.58789140912525</v>
+        <v>76.587898964852</v>
       </c>
       <c r="E337" t="n">
-        <v>77.87929188478925</v>
+        <v>77.87929956791825</v>
       </c>
       <c r="F337" t="n">
         <v>362662</v>
@@ -7292,16 +7292,16 @@
         <v>44972</v>
       </c>
       <c r="B344" t="n">
-        <v>73.78546905517578</v>
+        <v>73.78546142578125</v>
       </c>
       <c r="C344" t="n">
-        <v>74.93631260463282</v>
+        <v>74.93630485624141</v>
       </c>
       <c r="D344" t="n">
-        <v>71.65070638245331</v>
+        <v>71.65069897379257</v>
       </c>
       <c r="E344" t="n">
-        <v>72.23930851791685</v>
+        <v>72.23930104839484</v>
       </c>
       <c r="F344" t="n">
         <v>619864</v>
@@ -7312,16 +7312,16 @@
         <v>44973</v>
       </c>
       <c r="B345" t="n">
-        <v>71.15874481201172</v>
+        <v>71.15873718261719</v>
       </c>
       <c r="C345" t="n">
-        <v>73.96995180261891</v>
+        <v>73.96994387181648</v>
       </c>
       <c r="D345" t="n">
-        <v>70.32416962173819</v>
+        <v>70.32416208182393</v>
       </c>
       <c r="E345" t="n">
-        <v>73.30229433137855</v>
+        <v>73.30228647216005</v>
       </c>
       <c r="F345" t="n">
         <v>1330447</v>
@@ -7332,16 +7332,16 @@
         <v>44974</v>
       </c>
       <c r="B346" t="n">
-        <v>58.25353240966797</v>
+        <v>58.25353622436523</v>
       </c>
       <c r="C346" t="n">
-        <v>64.91258682963696</v>
+        <v>64.91259108039837</v>
       </c>
       <c r="D346" t="n">
-        <v>57.36624919591782</v>
+        <v>57.36625295251188</v>
       </c>
       <c r="E346" t="n">
-        <v>64.68417417050361</v>
+        <v>64.68417840630755</v>
       </c>
       <c r="F346" t="n">
         <v>4993765</v>
@@ -7372,16 +7372,16 @@
         <v>44980</v>
       </c>
       <c r="B348" t="n">
-        <v>59.61521911621094</v>
+        <v>59.61521530151367</v>
       </c>
       <c r="C348" t="n">
-        <v>60.5552171369521</v>
+        <v>60.55521326210563</v>
       </c>
       <c r="D348" t="n">
-        <v>58.94755490352809</v>
+        <v>58.94755113155375</v>
       </c>
       <c r="E348" t="n">
-        <v>60.00176261341363</v>
+        <v>60.00175877398195</v>
       </c>
       <c r="F348" t="n">
         <v>572076</v>
@@ -7432,16 +7432,16 @@
         <v>44985</v>
       </c>
       <c r="B351" t="n">
-        <v>56.48774337768555</v>
+        <v>56.48774719238281</v>
       </c>
       <c r="C351" t="n">
-        <v>57.19932863514759</v>
+        <v>57.19933249789922</v>
       </c>
       <c r="D351" t="n">
-        <v>55.53017165976352</v>
+        <v>55.53017540979462</v>
       </c>
       <c r="E351" t="n">
-        <v>56.82157209178407</v>
+        <v>56.82157592902526</v>
       </c>
       <c r="F351" t="n">
         <v>573942</v>
@@ -7452,16 +7452,16 @@
         <v>44986</v>
       </c>
       <c r="B352" t="n">
-        <v>54.14213943481445</v>
+        <v>54.14214324951172</v>
       </c>
       <c r="C352" t="n">
-        <v>57.10269353027231</v>
+        <v>57.10269755356158</v>
       </c>
       <c r="D352" t="n">
-        <v>53.41298035499475</v>
+        <v>53.4129841183176</v>
       </c>
       <c r="E352" t="n">
-        <v>56.48774412707847</v>
+        <v>56.4877481070402</v>
       </c>
       <c r="F352" t="n">
         <v>634515</v>
@@ -7492,16 +7492,16 @@
         <v>44988</v>
       </c>
       <c r="B354" t="n">
-        <v>52.35877227783203</v>
+        <v>52.3587760925293</v>
       </c>
       <c r="C354" t="n">
-        <v>54.11577810395019</v>
+        <v>54.11578204665744</v>
       </c>
       <c r="D354" t="n">
-        <v>52.35877227783203</v>
+        <v>52.3587760925293</v>
       </c>
       <c r="E354" t="n">
-        <v>53.14942624007427</v>
+        <v>53.14943011237612</v>
       </c>
       <c r="F354" t="n">
         <v>443497</v>
@@ -7512,16 +7512,16 @@
         <v>44991</v>
       </c>
       <c r="B355" t="n">
-        <v>54.28269958496094</v>
+        <v>54.2827033996582</v>
       </c>
       <c r="C355" t="n">
-        <v>55.26662197781043</v>
+        <v>55.26662586165249</v>
       </c>
       <c r="D355" t="n">
-        <v>52.38513329456833</v>
+        <v>52.3851369759148</v>
       </c>
       <c r="E355" t="n">
-        <v>52.71017845670896</v>
+        <v>52.71018216089787</v>
       </c>
       <c r="F355" t="n">
         <v>1320672</v>
@@ -7552,16 +7552,16 @@
         <v>44993</v>
       </c>
       <c r="B357" t="n">
-        <v>58.67521286010742</v>
+        <v>58.67521667480469</v>
       </c>
       <c r="C357" t="n">
-        <v>58.67521286010742</v>
+        <v>58.67521667480469</v>
       </c>
       <c r="D357" t="n">
-        <v>53.97522006484605</v>
+        <v>53.97522357397903</v>
       </c>
       <c r="E357" t="n">
-        <v>53.97522006484605</v>
+        <v>53.97522357397903</v>
       </c>
       <c r="F357" t="n">
         <v>1672249</v>
@@ -7672,16 +7672,16 @@
         <v>45001</v>
       </c>
       <c r="B363" t="n">
-        <v>53.81709289550781</v>
+        <v>53.81708908081055</v>
       </c>
       <c r="C363" t="n">
-        <v>54.24756084476554</v>
+        <v>54.24755699955558</v>
       </c>
       <c r="D363" t="n">
-        <v>50.10981247369315</v>
+        <v>50.10980892177768</v>
       </c>
       <c r="E363" t="n">
-        <v>50.68962432600123</v>
+        <v>50.68962073298718</v>
       </c>
       <c r="F363" t="n">
         <v>1144994</v>
@@ -7692,16 +7692,16 @@
         <v>45002</v>
       </c>
       <c r="B364" t="n">
-        <v>55.06457138061523</v>
+        <v>55.06456756591797</v>
       </c>
       <c r="C364" t="n">
-        <v>55.5477473873311</v>
+        <v>55.54774353916095</v>
       </c>
       <c r="D364" t="n">
-        <v>52.19186600817599</v>
+        <v>52.19186239249056</v>
       </c>
       <c r="E364" t="n">
-        <v>53.58868599016529</v>
+        <v>53.58868227771264</v>
       </c>
       <c r="F364" t="n">
         <v>1415773</v>
@@ -7732,16 +7732,16 @@
         <v>45006</v>
       </c>
       <c r="B366" t="n">
-        <v>54.65167617797852</v>
+        <v>54.65167236328125</v>
       </c>
       <c r="C366" t="n">
-        <v>54.73074158977065</v>
+        <v>54.73073776955461</v>
       </c>
       <c r="D366" t="n">
-        <v>52.657473770531</v>
+        <v>52.65747009502944</v>
       </c>
       <c r="E366" t="n">
-        <v>52.657473770531</v>
+        <v>52.65747009502944</v>
       </c>
       <c r="F366" t="n">
         <v>534854</v>
@@ -7752,16 +7752,16 @@
         <v>45007</v>
       </c>
       <c r="B367" t="n">
-        <v>52.56961822509766</v>
+        <v>52.56962203979492</v>
       </c>
       <c r="C367" t="n">
-        <v>55.1260617515593</v>
+        <v>55.12606575176405</v>
       </c>
       <c r="D367" t="n">
-        <v>52.56961822509766</v>
+        <v>52.56962203979492</v>
       </c>
       <c r="E367" t="n">
-        <v>53.85223176594004</v>
+        <v>53.85223567370974</v>
       </c>
       <c r="F367" t="n">
         <v>930770</v>
@@ -7772,16 +7772,16 @@
         <v>45008</v>
       </c>
       <c r="B368" t="n">
-        <v>49.1961669921875</v>
+        <v>49.19617080688477</v>
       </c>
       <c r="C368" t="n">
-        <v>53.29877430955613</v>
+        <v>53.29877844237178</v>
       </c>
       <c r="D368" t="n">
-        <v>48.85355136540186</v>
+        <v>48.85355515353253</v>
       </c>
       <c r="E368" t="n">
-        <v>52.56961857712928</v>
+        <v>52.56962265340579</v>
       </c>
       <c r="F368" t="n">
         <v>1208098</v>
@@ -7792,16 +7792,16 @@
         <v>45009</v>
       </c>
       <c r="B369" t="n">
-        <v>50.40850067138672</v>
+        <v>50.40850448608398</v>
       </c>
       <c r="C369" t="n">
-        <v>51.3660690297127</v>
+        <v>51.3660729168746</v>
       </c>
       <c r="D369" t="n">
-        <v>48.82719601713704</v>
+        <v>48.82719971216801</v>
       </c>
       <c r="E369" t="n">
-        <v>50.05709814767665</v>
+        <v>50.05710193578128</v>
       </c>
       <c r="F369" t="n">
         <v>598427</v>
@@ -7812,16 +7812,16 @@
         <v>45012</v>
       </c>
       <c r="B370" t="n">
-        <v>51.84925079345703</v>
+        <v>51.84924697875977</v>
       </c>
       <c r="C370" t="n">
-        <v>52.5256985490655</v>
+        <v>52.52569468460005</v>
       </c>
       <c r="D370" t="n">
-        <v>50.65448610049781</v>
+        <v>50.6544823737028</v>
       </c>
       <c r="E370" t="n">
-        <v>51.3924288019595</v>
+        <v>51.39242502087193</v>
       </c>
       <c r="F370" t="n">
         <v>634884</v>
@@ -7912,16 +7912,16 @@
         <v>45019</v>
       </c>
       <c r="B375" t="n">
-        <v>49.41579437255859</v>
+        <v>49.41579818725586</v>
       </c>
       <c r="C375" t="n">
-        <v>52.67503973932627</v>
+        <v>52.67504380562394</v>
       </c>
       <c r="D375" t="n">
-        <v>49.41579437255859</v>
+        <v>49.41579818725586</v>
       </c>
       <c r="E375" t="n">
-        <v>52.34999456357366</v>
+        <v>52.34999860477918</v>
       </c>
       <c r="F375" t="n">
         <v>492395</v>
@@ -7992,16 +7992,16 @@
         <v>45026</v>
       </c>
       <c r="B379" t="n">
-        <v>48.75691604614258</v>
+        <v>48.75691223144531</v>
       </c>
       <c r="C379" t="n">
-        <v>49.21373800403698</v>
+        <v>49.21373415359837</v>
       </c>
       <c r="D379" t="n">
-        <v>48.01018984358273</v>
+        <v>48.01018608730865</v>
       </c>
       <c r="E379" t="n">
-        <v>48.3264481056115</v>
+        <v>48.32644432459367</v>
       </c>
       <c r="F379" t="n">
         <v>441343</v>
@@ -8012,16 +8012,16 @@
         <v>45027</v>
       </c>
       <c r="B380" t="n">
-        <v>54.63409805297852</v>
+        <v>54.63410186767578</v>
       </c>
       <c r="C380" t="n">
-        <v>54.63409805297852</v>
+        <v>54.63410186767578</v>
       </c>
       <c r="D380" t="n">
-        <v>48.85355030008497</v>
+        <v>48.8535537111691</v>
       </c>
       <c r="E380" t="n">
-        <v>48.85355030008497</v>
+        <v>48.8535537111691</v>
       </c>
       <c r="F380" t="n">
         <v>1223134</v>
@@ -8092,16 +8092,16 @@
         <v>45033</v>
       </c>
       <c r="B384" t="n">
-        <v>59.95782089233398</v>
+        <v>59.95782470703125</v>
       </c>
       <c r="C384" t="n">
-        <v>60.72212080230327</v>
+        <v>60.7221246656276</v>
       </c>
       <c r="D384" t="n">
-        <v>59.16716696864937</v>
+        <v>59.16717073304285</v>
       </c>
       <c r="E384" t="n">
-        <v>60.35314450295379</v>
+        <v>60.35314834280274</v>
       </c>
       <c r="F384" t="n">
         <v>288592</v>
@@ -8112,16 +8112,16 @@
         <v>45034</v>
       </c>
       <c r="B385" t="n">
-        <v>61.49520492553711</v>
+        <v>61.49520874023438</v>
       </c>
       <c r="C385" t="n">
-        <v>61.49520492553711</v>
+        <v>61.49520874023438</v>
       </c>
       <c r="D385" t="n">
-        <v>59.16717082715269</v>
+        <v>59.16717449743633</v>
       </c>
       <c r="E385" t="n">
-        <v>59.16717082715269</v>
+        <v>59.16717449743633</v>
       </c>
       <c r="F385" t="n">
         <v>581190</v>
@@ -8132,16 +8132,16 @@
         <v>45035</v>
       </c>
       <c r="B386" t="n">
-        <v>58.84213256835938</v>
+        <v>58.84212875366211</v>
       </c>
       <c r="C386" t="n">
-        <v>61.27558287466414</v>
+        <v>61.27557890220787</v>
       </c>
       <c r="D386" t="n">
-        <v>58.30624521419173</v>
+        <v>58.3062414342357</v>
       </c>
       <c r="E386" t="n">
-        <v>61.27558287466414</v>
+        <v>61.27557890220787</v>
       </c>
       <c r="F386" t="n">
         <v>827950</v>
@@ -8152,16 +8152,16 @@
         <v>45036</v>
       </c>
       <c r="B387" t="n">
-        <v>60.80119323730469</v>
+        <v>60.80119705200195</v>
       </c>
       <c r="C387" t="n">
-        <v>60.80119323730469</v>
+        <v>60.80119705200195</v>
       </c>
       <c r="D387" t="n">
-        <v>58.21839221255807</v>
+        <v>58.2183958652091</v>
       </c>
       <c r="E387" t="n">
-        <v>58.78942051630461</v>
+        <v>58.78942420478224</v>
       </c>
       <c r="F387" t="n">
         <v>442904</v>
@@ -8192,16 +8192,16 @@
         <v>45041</v>
       </c>
       <c r="B389" t="n">
-        <v>60.50250244140625</v>
+        <v>60.50251007080078</v>
       </c>
       <c r="C389" t="n">
-        <v>61.28436955477335</v>
+        <v>61.2843772827617</v>
       </c>
       <c r="D389" t="n">
-        <v>59.00904335897617</v>
+        <v>59.0090508000448</v>
       </c>
       <c r="E389" t="n">
-        <v>61.28436955477335</v>
+        <v>61.2843772827617</v>
       </c>
       <c r="F389" t="n">
         <v>695154</v>
@@ -8212,16 +8212,16 @@
         <v>45042</v>
       </c>
       <c r="B390" t="n">
-        <v>59.31652069091797</v>
+        <v>59.3165168762207</v>
       </c>
       <c r="C390" t="n">
-        <v>60.01932578469255</v>
+        <v>60.01932192479727</v>
       </c>
       <c r="D390" t="n">
-        <v>56.9533521355543</v>
+        <v>56.95334847283447</v>
       </c>
       <c r="E390" t="n">
-        <v>59.30774048651921</v>
+        <v>59.30773667238661</v>
       </c>
       <c r="F390" t="n">
         <v>963997</v>
@@ -8232,16 +8232,16 @@
         <v>45043</v>
       </c>
       <c r="B391" t="n">
-        <v>61.50399398803711</v>
+        <v>61.50399780273438</v>
       </c>
       <c r="C391" t="n">
-        <v>62.82174842550359</v>
+        <v>62.82175232193269</v>
       </c>
       <c r="D391" t="n">
-        <v>58.44680074403878</v>
+        <v>58.446804369118</v>
       </c>
       <c r="E391" t="n">
-        <v>58.59614463836468</v>
+        <v>58.59614827270675</v>
       </c>
       <c r="F391" t="n">
         <v>723893</v>
@@ -8312,16 +8312,16 @@
         <v>45050</v>
       </c>
       <c r="B395" t="n">
-        <v>60.79240036010742</v>
+        <v>60.79240417480469</v>
       </c>
       <c r="C395" t="n">
-        <v>61.5654872316979</v>
+        <v>61.56549109490604</v>
       </c>
       <c r="D395" t="n">
-        <v>58.60492993083402</v>
+        <v>58.60493360826845</v>
       </c>
       <c r="E395" t="n">
-        <v>58.60492993083402</v>
+        <v>58.60493360826845</v>
       </c>
       <c r="F395" t="n">
         <v>661928</v>
@@ -8332,16 +8332,16 @@
         <v>45051</v>
       </c>
       <c r="B396" t="n">
-        <v>64.07801818847656</v>
+        <v>64.07801055908203</v>
       </c>
       <c r="C396" t="n">
-        <v>64.75446262565779</v>
+        <v>64.75445491572299</v>
       </c>
       <c r="D396" t="n">
-        <v>60.79241177231987</v>
+        <v>60.79240453412326</v>
       </c>
       <c r="E396" t="n">
-        <v>60.79241177231987</v>
+        <v>60.79240453412326</v>
       </c>
       <c r="F396" t="n">
         <v>739601</v>
@@ -8352,16 +8352,16 @@
         <v>45054</v>
       </c>
       <c r="B397" t="n">
-        <v>65.16735076904297</v>
+        <v>65.1673583984375</v>
       </c>
       <c r="C397" t="n">
-        <v>65.74715924562913</v>
+        <v>65.74716694290409</v>
       </c>
       <c r="D397" t="n">
-        <v>63.59482964395288</v>
+        <v>63.59483708924626</v>
       </c>
       <c r="E397" t="n">
-        <v>63.76174735351282</v>
+        <v>63.7617548183479</v>
       </c>
       <c r="F397" t="n">
         <v>685640</v>
@@ -8372,16 +8372,16 @@
         <v>45055</v>
       </c>
       <c r="B398" t="n">
-        <v>66.17763519287109</v>
+        <v>66.17762756347656</v>
       </c>
       <c r="C398" t="n">
-        <v>67.59202561451346</v>
+        <v>67.59201782205866</v>
       </c>
       <c r="D398" t="n">
-        <v>64.15707553268307</v>
+        <v>64.157068136232</v>
       </c>
       <c r="E398" t="n">
-        <v>65.00922454848022</v>
+        <v>65.00921705378778</v>
       </c>
       <c r="F398" t="n">
         <v>730723</v>
@@ -8452,16 +8452,16 @@
         <v>45061</v>
       </c>
       <c r="B402" t="n">
-        <v>68.41781616210938</v>
+        <v>68.41780853271484</v>
       </c>
       <c r="C402" t="n">
-        <v>69.17332933280035</v>
+        <v>69.17332161915719</v>
       </c>
       <c r="D402" t="n">
-        <v>66.23913231833025</v>
+        <v>66.2391249318847</v>
       </c>
       <c r="E402" t="n">
-        <v>66.23913231833025</v>
+        <v>66.2391249318847</v>
       </c>
       <c r="F402" t="n">
         <v>689284</v>
@@ -8472,16 +8472,16 @@
         <v>45062</v>
       </c>
       <c r="B403" t="n">
-        <v>69.20846557617188</v>
+        <v>69.20847320556641</v>
       </c>
       <c r="C403" t="n">
-        <v>74.04023209771412</v>
+        <v>74.04024025975235</v>
       </c>
       <c r="D403" t="n">
-        <v>67.52174141723872</v>
+        <v>67.52174886069236</v>
       </c>
       <c r="E403" t="n">
-        <v>69.22603938961998</v>
+        <v>69.22604702095181</v>
       </c>
       <c r="F403" t="n">
         <v>1416795</v>
@@ -8492,16 +8492,16 @@
         <v>45063</v>
       </c>
       <c r="B404" t="n">
-        <v>72.3271484375</v>
+        <v>72.32714080810547</v>
       </c>
       <c r="C404" t="n">
-        <v>73.79424673422444</v>
+        <v>73.79423895007376</v>
       </c>
       <c r="D404" t="n">
-        <v>67.6622932827093</v>
+        <v>67.66228614538477</v>
       </c>
       <c r="E404" t="n">
-        <v>69.41051895372132</v>
+        <v>69.41051163198605</v>
       </c>
       <c r="F404" t="n">
         <v>1084227</v>
@@ -8512,16 +8512,16 @@
         <v>45064</v>
       </c>
       <c r="B405" t="n">
-        <v>71.18508911132812</v>
+        <v>71.18510437011719</v>
       </c>
       <c r="C405" t="n">
-        <v>71.99331017297479</v>
+        <v>71.99332560500903</v>
       </c>
       <c r="D405" t="n">
-        <v>69.86733475768652</v>
+        <v>69.86734973401003</v>
       </c>
       <c r="E405" t="n">
-        <v>71.15873509664654</v>
+        <v>71.15875034978652</v>
       </c>
       <c r="F405" t="n">
         <v>796674</v>
@@ -8532,16 +8532,16 @@
         <v>45065</v>
       </c>
       <c r="B406" t="n">
-        <v>75.91145324707031</v>
+        <v>75.91144561767578</v>
       </c>
       <c r="C406" t="n">
-        <v>76.42976683949719</v>
+        <v>76.42975915801013</v>
       </c>
       <c r="D406" t="n">
-        <v>71.19388936375165</v>
+        <v>71.19388220849052</v>
       </c>
       <c r="E406" t="n">
-        <v>71.19388936375165</v>
+        <v>71.19388220849052</v>
       </c>
       <c r="F406" t="n">
         <v>1201246</v>
@@ -8552,16 +8552,16 @@
         <v>45068</v>
       </c>
       <c r="B407" t="n">
-        <v>77.76508331298828</v>
+        <v>77.76507568359375</v>
       </c>
       <c r="C407" t="n">
-        <v>78.30975759078616</v>
+        <v>78.3097499079546</v>
       </c>
       <c r="D407" t="n">
-        <v>75.07686625350173</v>
+        <v>75.0768588878434</v>
       </c>
       <c r="E407" t="n">
-        <v>75.45462281500996</v>
+        <v>75.45461541229061</v>
       </c>
       <c r="F407" t="n">
         <v>873661</v>
@@ -8572,16 +8572,16 @@
         <v>45069</v>
       </c>
       <c r="B408" t="n">
-        <v>77.13256072998047</v>
+        <v>77.132568359375</v>
       </c>
       <c r="C408" t="n">
-        <v>80.43572695506535</v>
+        <v>80.43573491118516</v>
       </c>
       <c r="D408" t="n">
-        <v>76.42975569775851</v>
+        <v>76.42976325763665</v>
       </c>
       <c r="E408" t="n">
-        <v>77.74751010634054</v>
+        <v>77.74751779656141</v>
       </c>
       <c r="F408" t="n">
         <v>970823</v>
@@ -8592,16 +8592,16 @@
         <v>45070</v>
       </c>
       <c r="B409" t="n">
-        <v>77.30827331542969</v>
+        <v>77.30825805664062</v>
       </c>
       <c r="C409" t="n">
-        <v>78.2746253913832</v>
+        <v>78.27460994185954</v>
       </c>
       <c r="D409" t="n">
-        <v>75.96416463585973</v>
+        <v>75.96414964236531</v>
       </c>
       <c r="E409" t="n">
-        <v>76.61425505750891</v>
+        <v>76.61423993570233</v>
       </c>
       <c r="F409" t="n">
         <v>567398</v>
@@ -8652,16 +8652,16 @@
         <v>45075</v>
       </c>
       <c r="B412" t="n">
-        <v>81.52508544921875</v>
+        <v>81.52507781982422</v>
       </c>
       <c r="C412" t="n">
-        <v>83.1678818576769</v>
+        <v>83.1678740745439</v>
       </c>
       <c r="D412" t="n">
-        <v>80.73443136636509</v>
+        <v>80.73442381096265</v>
       </c>
       <c r="E412" t="n">
-        <v>82.66713538894396</v>
+        <v>82.66712765267252</v>
       </c>
       <c r="F412" t="n">
         <v>275309</v>
@@ -8692,16 +8692,16 @@
         <v>45077</v>
       </c>
       <c r="B414" t="n">
-        <v>78.81929016113281</v>
+        <v>78.81928253173828</v>
       </c>
       <c r="C414" t="n">
-        <v>80.38302442732773</v>
+        <v>80.38301664656991</v>
       </c>
       <c r="D414" t="n">
-        <v>78.53816946948481</v>
+        <v>78.53816186730164</v>
       </c>
       <c r="E414" t="n">
-        <v>79.97891385198659</v>
+        <v>79.97890611034508</v>
       </c>
       <c r="F414" t="n">
         <v>527775</v>
@@ -8752,16 +8752,16 @@
         <v>45082</v>
       </c>
       <c r="B417" t="n">
-        <v>82.02582550048828</v>
+        <v>82.02584075927734</v>
       </c>
       <c r="C417" t="n">
-        <v>82.88675466589184</v>
+        <v>82.88677008483457</v>
       </c>
       <c r="D417" t="n">
-        <v>79.88227608855597</v>
+        <v>79.88229094859295</v>
       </c>
       <c r="E417" t="n">
-        <v>82.88675466589184</v>
+        <v>82.88677008483457</v>
       </c>
       <c r="F417" t="n">
         <v>409729</v>
@@ -8772,16 +8772,16 @@
         <v>45083</v>
       </c>
       <c r="B418" t="n">
-        <v>83.89703369140625</v>
+        <v>83.89704132080078</v>
       </c>
       <c r="C418" t="n">
-        <v>86.708240516318</v>
+        <v>86.70824840135691</v>
       </c>
       <c r="D418" t="n">
-        <v>81.92040200757731</v>
+        <v>81.92040945722171</v>
       </c>
       <c r="E418" t="n">
-        <v>82.01703787053793</v>
+        <v>82.01704532897017</v>
       </c>
       <c r="F418" t="n">
         <v>1573579</v>
@@ -8792,16 +8792,16 @@
         <v>45084</v>
       </c>
       <c r="B419" t="n">
-        <v>86.52375793457031</v>
+        <v>86.52376556396484</v>
       </c>
       <c r="C419" t="n">
-        <v>86.60282668924023</v>
+        <v>86.60283432560681</v>
       </c>
       <c r="D419" t="n">
-        <v>82.88675607845614</v>
+        <v>82.88676338715122</v>
       </c>
       <c r="E419" t="n">
-        <v>84.3362873579094</v>
+        <v>84.33629479441962</v>
       </c>
       <c r="F419" t="n">
         <v>2805750</v>
@@ -8812,16 +8812,16 @@
         <v>45086</v>
       </c>
       <c r="B420" t="n">
-        <v>87.92935943603516</v>
+        <v>87.92936706542969</v>
       </c>
       <c r="C420" t="n">
-        <v>90.98655273412886</v>
+        <v>90.98656062878784</v>
       </c>
       <c r="D420" t="n">
-        <v>86.98058131812988</v>
+        <v>86.98058886520148</v>
       </c>
       <c r="E420" t="n">
-        <v>86.98058131812988</v>
+        <v>86.98058886520148</v>
       </c>
       <c r="F420" t="n">
         <v>1309381</v>
@@ -8832,16 +8832,16 @@
         <v>45089</v>
       </c>
       <c r="B421" t="n">
-        <v>90.35404205322266</v>
+        <v>90.35403442382812</v>
       </c>
       <c r="C421" t="n">
-        <v>91.34675484094018</v>
+        <v>91.34674712772208</v>
       </c>
       <c r="D421" t="n">
-        <v>87.95573235530614</v>
+        <v>87.95572492842221</v>
       </c>
       <c r="E421" t="n">
-        <v>87.95573235530614</v>
+        <v>87.95572492842221</v>
       </c>
       <c r="F421" t="n">
         <v>1071620</v>
@@ -8852,16 +8852,16 @@
         <v>45090</v>
       </c>
       <c r="B422" t="n">
-        <v>86.91909027099609</v>
+        <v>86.91908264160156</v>
       </c>
       <c r="C422" t="n">
-        <v>91.17982854453695</v>
+        <v>91.17982054115261</v>
       </c>
       <c r="D422" t="n">
-        <v>86.91909027099609</v>
+        <v>86.91908264160156</v>
       </c>
       <c r="E422" t="n">
-        <v>90.48581035981377</v>
+        <v>90.48580241734746</v>
       </c>
       <c r="F422" t="n">
         <v>519950</v>
@@ -8872,16 +8872,16 @@
         <v>45091</v>
       </c>
       <c r="B423" t="n">
-        <v>89.40524291992188</v>
+        <v>89.40525054931641</v>
       </c>
       <c r="C423" t="n">
-        <v>89.44038384246984</v>
+        <v>89.44039147486313</v>
       </c>
       <c r="D423" t="n">
-        <v>87.26170026406075</v>
+        <v>87.26170771053611</v>
       </c>
       <c r="E423" t="n">
-        <v>87.54282094199888</v>
+        <v>87.54282841246366</v>
       </c>
       <c r="F423" t="n">
         <v>605932</v>
@@ -9012,16 +9012,16 @@
         <v>45100</v>
       </c>
       <c r="B430" t="n">
-        <v>98.56803131103516</v>
+        <v>98.56803894042969</v>
       </c>
       <c r="C430" t="n">
-        <v>100.544663008736</v>
+        <v>100.5446707911264</v>
       </c>
       <c r="D430" t="n">
-        <v>97.24149664189471</v>
+        <v>97.24150416861238</v>
       </c>
       <c r="E430" t="n">
-        <v>99.71008786179617</v>
+        <v>99.71009557958853</v>
       </c>
       <c r="F430" t="n">
         <v>1883788</v>
@@ -9032,16 +9032,16 @@
         <v>45103</v>
       </c>
       <c r="B431" t="n">
-        <v>97.00428771972656</v>
+        <v>97.00429534912109</v>
       </c>
       <c r="C431" t="n">
-        <v>99.27082678952559</v>
+        <v>99.27083459718358</v>
       </c>
       <c r="D431" t="n">
-        <v>95.75681522175476</v>
+        <v>95.75682275303549</v>
       </c>
       <c r="E431" t="n">
-        <v>98.46260573752514</v>
+        <v>98.46261348161649</v>
       </c>
       <c r="F431" t="n">
         <v>757098</v>
@@ -9072,16 +9072,16 @@
         <v>45105</v>
       </c>
       <c r="B433" t="n">
-        <v>97.09215545654297</v>
+        <v>97.09214782714844</v>
       </c>
       <c r="C433" t="n">
-        <v>98.19028428396808</v>
+        <v>98.19027656828381</v>
       </c>
       <c r="D433" t="n">
-        <v>94.29851545147561</v>
+        <v>94.29850804160222</v>
       </c>
       <c r="E433" t="n">
-        <v>94.4742200853315</v>
+        <v>94.47421266165144</v>
       </c>
       <c r="F433" t="n">
         <v>538862</v>
@@ -9232,16 +9232,16 @@
         <v>45117</v>
       </c>
       <c r="B441" t="n">
-        <v>98.26055908203125</v>
+        <v>98.26055145263672</v>
       </c>
       <c r="C441" t="n">
-        <v>100.7467241773928</v>
+        <v>100.7467163549612</v>
       </c>
       <c r="D441" t="n">
-        <v>97.19757125770386</v>
+        <v>97.19756371084451</v>
       </c>
       <c r="E441" t="n">
-        <v>100.7467241773928</v>
+        <v>100.7467163549612</v>
       </c>
       <c r="F441" t="n">
         <v>1057552</v>
@@ -9332,16 +9332,16 @@
         <v>45124</v>
       </c>
       <c r="B446" t="n">
-        <v>99.48168182373047</v>
+        <v>99.48167419433594</v>
       </c>
       <c r="C446" t="n">
-        <v>99.48168182373047</v>
+        <v>99.48167419433594</v>
       </c>
       <c r="D446" t="n">
-        <v>95.75683083137832</v>
+        <v>95.75682348764802</v>
       </c>
       <c r="E446" t="n">
-        <v>96.44206212640412</v>
+        <v>96.44205473012244</v>
       </c>
       <c r="F446" t="n">
         <v>395417</v>
@@ -9352,16 +9352,16 @@
         <v>45125</v>
       </c>
       <c r="B447" t="n">
-        <v>101.4231719970703</v>
+        <v>101.4231643676758</v>
       </c>
       <c r="C447" t="n">
-        <v>103.663357401557</v>
+        <v>103.6633496036482</v>
       </c>
       <c r="D447" t="n">
-        <v>98.74374178061643</v>
+        <v>98.74373435277772</v>
       </c>
       <c r="E447" t="n">
-        <v>99.27084225742324</v>
+        <v>99.27083478993424</v>
       </c>
       <c r="F447" t="n">
         <v>594813</v>
@@ -9412,16 +9412,16 @@
         <v>45128</v>
       </c>
       <c r="B450" t="n">
-        <v>111.3941879272461</v>
+        <v>111.3941802978516</v>
       </c>
       <c r="C450" t="n">
-        <v>111.3941879272461</v>
+        <v>111.3941802978516</v>
       </c>
       <c r="D450" t="n">
-        <v>106.0353140321484</v>
+        <v>106.0353067697835</v>
       </c>
       <c r="E450" t="n">
-        <v>106.7556862553908</v>
+        <v>106.7556789436875</v>
       </c>
       <c r="F450" t="n">
         <v>688364</v>
@@ -9532,16 +9532,16 @@
         <v>45138</v>
       </c>
       <c r="B456" t="n">
-        <v>111.8246536254883</v>
+        <v>111.8246459960938</v>
       </c>
       <c r="C456" t="n">
-        <v>115.0838991246485</v>
+        <v>115.0838912728874</v>
       </c>
       <c r="D456" t="n">
-        <v>110.7792328550693</v>
+        <v>110.7792252970001</v>
       </c>
       <c r="E456" t="n">
-        <v>112.6416617270665</v>
+        <v>112.6416540419304</v>
       </c>
       <c r="F456" t="n">
         <v>524630</v>
@@ -9572,16 +9572,16 @@
         <v>45140</v>
       </c>
       <c r="B458" t="n">
-        <v>112.2726821899414</v>
+        <v>112.2726898193359</v>
       </c>
       <c r="C458" t="n">
-        <v>112.4220260861785</v>
+        <v>112.4220337257216</v>
       </c>
       <c r="D458" t="n">
-        <v>108.66203444888</v>
+        <v>108.6620418329161</v>
       </c>
       <c r="E458" t="n">
-        <v>111.692867012862</v>
+        <v>111.6928746028557</v>
       </c>
       <c r="F458" t="n">
         <v>921444</v>
@@ -9612,16 +9612,16 @@
         <v>45142</v>
       </c>
       <c r="B460" t="n">
-        <v>113.1336135864258</v>
+        <v>113.1336059570312</v>
       </c>
       <c r="C460" t="n">
-        <v>114.6007119660374</v>
+        <v>114.6007042377062</v>
       </c>
       <c r="D460" t="n">
-        <v>110.9900641534965</v>
+        <v>110.9900566686566</v>
       </c>
       <c r="E460" t="n">
-        <v>114.2053883028904</v>
+        <v>114.2053806012186</v>
       </c>
       <c r="F460" t="n">
         <v>805649</v>
@@ -9672,16 +9672,16 @@
         <v>45147</v>
       </c>
       <c r="B463" t="n">
-        <v>112.4483871459961</v>
+        <v>112.4483795166016</v>
       </c>
       <c r="C463" t="n">
-        <v>114.1263311401144</v>
+        <v>114.1263233968748</v>
       </c>
       <c r="D463" t="n">
-        <v>110.612319041802</v>
+        <v>110.612311536981</v>
       </c>
       <c r="E463" t="n">
-        <v>113.7397876645173</v>
+        <v>113.7397799475038</v>
       </c>
       <c r="F463" t="n">
         <v>434571</v>
@@ -9692,16 +9692,16 @@
         <v>45148</v>
       </c>
       <c r="B464" t="n">
-        <v>110.5156860351562</v>
+        <v>110.5156784057617</v>
       </c>
       <c r="C464" t="n">
-        <v>114.5919396385741</v>
+        <v>114.5919317277774</v>
       </c>
       <c r="D464" t="n">
-        <v>109.2857804284043</v>
+        <v>109.2857728839157</v>
       </c>
       <c r="E464" t="n">
-        <v>111.7455849394619</v>
+        <v>111.7455772251619</v>
       </c>
       <c r="F464" t="n">
         <v>733254</v>
@@ -9712,16 +9712,16 @@
         <v>45149</v>
       </c>
       <c r="B465" t="n">
-        <v>109.812873840332</v>
+        <v>109.8128814697266</v>
       </c>
       <c r="C465" t="n">
-        <v>111.9915642064004</v>
+        <v>111.9915719871623</v>
       </c>
       <c r="D465" t="n">
-        <v>108.1261497067316</v>
+        <v>108.1261572189387</v>
       </c>
       <c r="E465" t="n">
-        <v>110.7353046615692</v>
+        <v>110.7353123550508</v>
       </c>
       <c r="F465" t="n">
         <v>577766</v>
@@ -9752,16 +9752,16 @@
         <v>45153</v>
       </c>
       <c r="B467" t="n">
-        <v>107.7396087646484</v>
+        <v>107.7396011352539</v>
       </c>
       <c r="C467" t="n">
-        <v>113.3268884524535</v>
+        <v>113.3268804274053</v>
       </c>
       <c r="D467" t="n">
-        <v>104.9898967522873</v>
+        <v>104.9898893176089</v>
       </c>
       <c r="E467" t="n">
-        <v>112.7910010793896</v>
+        <v>112.7909930922894</v>
       </c>
       <c r="F467" t="n">
         <v>1563395</v>
@@ -9792,16 +9792,16 @@
         <v>45155</v>
       </c>
       <c r="B469" t="n">
-        <v>103.6633529663086</v>
+        <v>103.6633453369141</v>
       </c>
       <c r="C469" t="n">
-        <v>109.7689460744476</v>
+        <v>109.7689379956948</v>
       </c>
       <c r="D469" t="n">
-        <v>103.048403553419</v>
+        <v>103.0483959692834</v>
       </c>
       <c r="E469" t="n">
-        <v>108.9782987442884</v>
+        <v>108.9782907237255</v>
       </c>
       <c r="F469" t="n">
         <v>1841816</v>
@@ -9832,16 +9832,16 @@
         <v>45159</v>
       </c>
       <c r="B471" t="n">
-        <v>111.3941879272461</v>
+        <v>111.3941802978516</v>
       </c>
       <c r="C471" t="n">
-        <v>111.4556828718236</v>
+        <v>111.4556752382173</v>
       </c>
       <c r="D471" t="n">
-        <v>108.0998015339219</v>
+        <v>108.0997941301601</v>
       </c>
       <c r="E471" t="n">
-        <v>109.1540024988072</v>
+        <v>109.153995022843</v>
       </c>
       <c r="F471" t="n">
         <v>967109</v>
@@ -9852,16 +9852,16 @@
         <v>45160</v>
       </c>
       <c r="B472" t="n">
-        <v>113.9594192504883</v>
+        <v>113.9594116210938</v>
       </c>
       <c r="C472" t="n">
-        <v>114.0033470849429</v>
+        <v>114.0033394526074</v>
       </c>
       <c r="D472" t="n">
-        <v>111.174566128698</v>
+        <v>111.1745586857447</v>
       </c>
       <c r="E472" t="n">
-        <v>111.5347489019289</v>
+        <v>111.534741434862</v>
       </c>
       <c r="F472" t="n">
         <v>933012</v>
@@ -9872,16 +9872,16 @@
         <v>45161</v>
       </c>
       <c r="B473" t="n">
-        <v>117.4294891357422</v>
+        <v>117.4294967651367</v>
       </c>
       <c r="C473" t="n">
-        <v>117.9390224614812</v>
+        <v>117.9390301239801</v>
       </c>
       <c r="D473" t="n">
-        <v>112.9491320795816</v>
+        <v>112.9491394178873</v>
       </c>
       <c r="E473" t="n">
-        <v>114.0296869677586</v>
+        <v>114.0296943762679</v>
       </c>
       <c r="F473" t="n">
         <v>1193312</v>
@@ -9912,16 +9912,16 @@
         <v>45163</v>
       </c>
       <c r="B475" t="n">
-        <v>110.4278259277344</v>
+        <v>110.4278182983398</v>
       </c>
       <c r="C475" t="n">
-        <v>112.7997813791627</v>
+        <v>112.7997735858911</v>
       </c>
       <c r="D475" t="n">
-        <v>108.5917578498233</v>
+        <v>108.5917503472816</v>
       </c>
       <c r="E475" t="n">
-        <v>112.6240834577406</v>
+        <v>112.6240756766079</v>
       </c>
       <c r="F475" t="n">
         <v>1445522</v>
@@ -9972,16 +9972,16 @@
         <v>45168</v>
       </c>
       <c r="B478" t="n">
-        <v>112.4483871459961</v>
+        <v>112.4483795166016</v>
       </c>
       <c r="C478" t="n">
-        <v>113.853997347278</v>
+        <v>113.8539896225157</v>
       </c>
       <c r="D478" t="n">
-        <v>110.8231578910159</v>
+        <v>110.8231503718898</v>
       </c>
       <c r="E478" t="n">
-        <v>113.0721301915992</v>
+        <v>113.0721225198849</v>
       </c>
       <c r="F478" t="n">
         <v>547646</v>
@@ -9992,16 +9992,16 @@
         <v>45169</v>
       </c>
       <c r="B479" t="n">
-        <v>110.4102630615234</v>
+        <v>110.4102554321289</v>
       </c>
       <c r="C479" t="n">
-        <v>112.4396029524886</v>
+        <v>112.4395951828659</v>
       </c>
       <c r="D479" t="n">
-        <v>108.8465287124293</v>
+        <v>108.8465211910895</v>
       </c>
       <c r="E479" t="n">
-        <v>111.7455847420302</v>
+        <v>111.7455770203644</v>
       </c>
       <c r="F479" t="n">
         <v>854216</v>
@@ -10012,16 +10012,16 @@
         <v>45170</v>
       </c>
       <c r="B480" t="n">
-        <v>113.7397918701172</v>
+        <v>113.7397842407227</v>
       </c>
       <c r="C480" t="n">
-        <v>115.5670798373918</v>
+        <v>115.5670720854272</v>
       </c>
       <c r="D480" t="n">
-        <v>109.3209225654903</v>
+        <v>109.320915232503</v>
       </c>
       <c r="E480" t="n">
-        <v>110.260920568448</v>
+        <v>110.2609131724079</v>
       </c>
       <c r="F480" t="n">
         <v>5149038</v>
@@ -10072,16 +10072,16 @@
         <v>45175</v>
       </c>
       <c r="B483" t="n">
-        <v>110.3311920166016</v>
+        <v>110.331184387207</v>
       </c>
       <c r="C483" t="n">
-        <v>113.1072648009286</v>
+        <v>113.1072569795688</v>
       </c>
       <c r="D483" t="n">
-        <v>108.3106390746352</v>
+        <v>108.3106315849618</v>
       </c>
       <c r="E483" t="n">
-        <v>110.4717557181885</v>
+        <v>110.471748079074</v>
       </c>
       <c r="F483" t="n">
         <v>1014845</v>
@@ -24432,7 +24432,7 @@
         <v>46231</v>
       </c>
       <c r="B1201" t="n">
-        <v>86.7</v>
+        <v>85.44</v>
       </c>
       <c r="C1201" t="n">
         <v>87.11</v>
@@ -24444,7 +24444,7 @@
         <v>85.04000000000001</v>
       </c>
       <c r="F1201" t="n">
-        <v>344769</v>
+        <v>455564</v>
       </c>
     </row>
   </sheetData>

--- a/database/XPBR31.xlsx
+++ b/database/XPBR31.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1202"/>
+  <dimension ref="A1:F1203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44473</v>
       </c>
       <c r="B2" t="n">
-        <v>196.6089782714844</v>
+        <v>196.6089477539062</v>
       </c>
       <c r="C2" t="n">
-        <v>203.5755007756201</v>
+        <v>203.5754691767007</v>
       </c>
       <c r="D2" t="n">
-        <v>191.4433762318198</v>
+        <v>191.4433465160446</v>
       </c>
       <c r="E2" t="n">
-        <v>191.9529095912669</v>
+        <v>191.9528797964022</v>
       </c>
       <c r="F2" t="n">
         <v>9950865</v>
@@ -512,16 +512,16 @@
         <v>44476</v>
       </c>
       <c r="B5" t="n">
-        <v>203.3734283447266</v>
+        <v>203.3734436035156</v>
       </c>
       <c r="C5" t="n">
-        <v>203.3734283447266</v>
+        <v>203.3734436035156</v>
       </c>
       <c r="D5" t="n">
-        <v>190.9426172441435</v>
+        <v>190.9426315702683</v>
       </c>
       <c r="E5" t="n">
-        <v>190.9426172441435</v>
+        <v>190.9426315702683</v>
       </c>
       <c r="F5" t="n">
         <v>12157101</v>
@@ -552,16 +552,16 @@
         <v>44480</v>
       </c>
       <c r="B7" t="n">
-        <v>180.0931091308594</v>
+        <v>180.0931243896484</v>
       </c>
       <c r="C7" t="n">
-        <v>193.1125296009114</v>
+        <v>193.1125459627998</v>
       </c>
       <c r="D7" t="n">
-        <v>180.0931091308594</v>
+        <v>180.0931243896484</v>
       </c>
       <c r="E7" t="n">
-        <v>191.8738371941056</v>
+        <v>191.8738534510431</v>
       </c>
       <c r="F7" t="n">
         <v>2006205</v>
@@ -572,16 +572,16 @@
         <v>44482</v>
       </c>
       <c r="B8" t="n">
-        <v>169.5510864257812</v>
+        <v>169.5510711669922</v>
       </c>
       <c r="C8" t="n">
-        <v>178.8632239955791</v>
+        <v>178.8632078987421</v>
       </c>
       <c r="D8" t="n">
-        <v>169.5510864257812</v>
+        <v>169.5510711669922</v>
       </c>
       <c r="E8" t="n">
-        <v>174.4092071561597</v>
+        <v>174.4091914601629</v>
       </c>
       <c r="F8" t="n">
         <v>3487621</v>
@@ -592,16 +592,16 @@
         <v>44483</v>
       </c>
       <c r="B9" t="n">
-        <v>164.7632446289062</v>
+        <v>164.7632293701172</v>
       </c>
       <c r="C9" t="n">
-        <v>173.8293888548571</v>
+        <v>173.8293727564489</v>
       </c>
       <c r="D9" t="n">
-        <v>164.2888454897918</v>
+        <v>164.2888302749371</v>
       </c>
       <c r="E9" t="n">
-        <v>171.8351966443599</v>
+        <v>171.8351807306346</v>
       </c>
       <c r="F9" t="n">
         <v>3205420</v>
@@ -612,16 +612,16 @@
         <v>44484</v>
       </c>
       <c r="B10" t="n">
-        <v>175.7006072998047</v>
+        <v>175.7005920410156</v>
       </c>
       <c r="C10" t="n">
-        <v>178.9774198725761</v>
+        <v>178.977404329211</v>
       </c>
       <c r="D10" t="n">
-        <v>166.9155769348145</v>
+        <v>166.9155624389649</v>
       </c>
       <c r="E10" t="n">
-        <v>166.9155769348145</v>
+        <v>166.9155624389649</v>
       </c>
       <c r="F10" t="n">
         <v>2643581</v>
@@ -652,16 +652,16 @@
         <v>44488</v>
       </c>
       <c r="B12" t="n">
-        <v>175.0856475830078</v>
+        <v>175.0856628417969</v>
       </c>
       <c r="C12" t="n">
-        <v>179.4078806604117</v>
+        <v>179.4078962958852</v>
       </c>
       <c r="D12" t="n">
-        <v>174.3828425140635</v>
+        <v>174.3828577116028</v>
       </c>
       <c r="E12" t="n">
-        <v>177.5454586218672</v>
+        <v>177.5454740950298</v>
       </c>
       <c r="F12" t="n">
         <v>722779</v>
@@ -672,16 +672,16 @@
         <v>44489</v>
       </c>
       <c r="B13" t="n">
-        <v>174.3828277587891</v>
+        <v>174.3828430175781</v>
       </c>
       <c r="C13" t="n">
-        <v>178.4942149461601</v>
+        <v>178.4942305647025</v>
       </c>
       <c r="D13" t="n">
-        <v>169.8409693194518</v>
+        <v>169.8409841808207</v>
       </c>
       <c r="E13" t="n">
-        <v>176.5790850353481</v>
+        <v>176.5791004863134</v>
       </c>
       <c r="F13" t="n">
         <v>1907987</v>
@@ -692,16 +692,16 @@
         <v>44490</v>
       </c>
       <c r="B14" t="n">
-        <v>169.4192962646484</v>
+        <v>169.4193115234375</v>
       </c>
       <c r="C14" t="n">
-        <v>176.2189003979208</v>
+        <v>176.2189162691178</v>
       </c>
       <c r="D14" t="n">
-        <v>167.1615372888441</v>
+        <v>167.1615523442876</v>
       </c>
       <c r="E14" t="n">
-        <v>173.3989134851749</v>
+        <v>173.3989291023892</v>
       </c>
       <c r="F14" t="n">
         <v>1852525</v>
@@ -732,16 +732,16 @@
         <v>44494</v>
       </c>
       <c r="B16" t="n">
-        <v>169.1206207275391</v>
+        <v>169.12060546875</v>
       </c>
       <c r="C16" t="n">
-        <v>174.5849108807135</v>
+        <v>174.5848951289127</v>
       </c>
       <c r="D16" t="n">
-        <v>167.3636145922391</v>
+        <v>167.3635994919746</v>
       </c>
       <c r="E16" t="n">
-        <v>167.7062302524268</v>
+        <v>167.7062151212502</v>
       </c>
       <c r="F16" t="n">
         <v>1203463</v>
@@ -752,16 +752,16 @@
         <v>44495</v>
       </c>
       <c r="B17" t="n">
-        <v>163.9638061523438</v>
+        <v>163.9637908935547</v>
       </c>
       <c r="C17" t="n">
-        <v>170.2538911091769</v>
+        <v>170.2538752650204</v>
       </c>
       <c r="D17" t="n">
-        <v>159.9051264143641</v>
+        <v>159.9051115332836</v>
       </c>
       <c r="E17" t="n">
-        <v>168.7604386285045</v>
+        <v>168.7604229233316</v>
       </c>
       <c r="F17" t="n">
         <v>810455</v>
@@ -792,16 +792,16 @@
         <v>44497</v>
       </c>
       <c r="B19" t="n">
-        <v>165.1673583984375</v>
+        <v>165.1673278808594</v>
       </c>
       <c r="C19" t="n">
-        <v>166.8101682649443</v>
+        <v>166.8101374438281</v>
       </c>
       <c r="D19" t="n">
-        <v>158.6664410017166</v>
+        <v>158.6664116852975</v>
       </c>
       <c r="E19" t="n">
-        <v>163.4103522474434</v>
+        <v>163.4103220545031</v>
       </c>
       <c r="F19" t="n">
         <v>1047427</v>
@@ -812,16 +812,16 @@
         <v>44498</v>
       </c>
       <c r="B20" t="n">
-        <v>162.5230560302734</v>
+        <v>162.5230712890625</v>
       </c>
       <c r="C20" t="n">
-        <v>167.337248747422</v>
+        <v>167.3372644582008</v>
       </c>
       <c r="D20" t="n">
-        <v>161.2053015219199</v>
+        <v>161.205316656989</v>
       </c>
       <c r="E20" t="n">
-        <v>166.1249237150633</v>
+        <v>166.1249393120207</v>
       </c>
       <c r="F20" t="n">
         <v>643563</v>
@@ -832,16 +832,16 @@
         <v>44501</v>
       </c>
       <c r="B21" t="n">
-        <v>169.7267913818359</v>
+        <v>169.7267761230469</v>
       </c>
       <c r="C21" t="n">
-        <v>171.2026835181439</v>
+        <v>171.2026681266692</v>
       </c>
       <c r="D21" t="n">
-        <v>161.9344733973998</v>
+        <v>161.9344588391563</v>
       </c>
       <c r="E21" t="n">
-        <v>162.5230688489684</v>
+        <v>162.5230542378089</v>
       </c>
       <c r="F21" t="n">
         <v>466029</v>
@@ -852,16 +852,16 @@
         <v>44503</v>
       </c>
       <c r="B22" t="n">
-        <v>164.6490478515625</v>
+        <v>164.6490325927734</v>
       </c>
       <c r="C22" t="n">
-        <v>168.6725936204714</v>
+        <v>168.6725779888017</v>
       </c>
       <c r="D22" t="n">
-        <v>161.3810152777744</v>
+        <v>161.381000321849</v>
       </c>
       <c r="E22" t="n">
-        <v>168.6725936204714</v>
+        <v>168.6725779888017</v>
       </c>
       <c r="F22" t="n">
         <v>834348</v>
@@ -932,16 +932,16 @@
         <v>44509</v>
       </c>
       <c r="B26" t="n">
-        <v>163.7705230712891</v>
+        <v>163.7705078125</v>
       </c>
       <c r="C26" t="n">
-        <v>169.8497620526857</v>
+        <v>169.8497462274832</v>
       </c>
       <c r="D26" t="n">
-        <v>162.0837989670482</v>
+        <v>162.0837838654142</v>
       </c>
       <c r="E26" t="n">
-        <v>167.3548168196352</v>
+        <v>167.3548012268911</v>
       </c>
       <c r="F26" t="n">
         <v>336270</v>
@@ -952,16 +952,16 @@
         <v>44510</v>
       </c>
       <c r="B27" t="n">
-        <v>158.5697784423828</v>
+        <v>158.5697937011719</v>
       </c>
       <c r="C27" t="n">
-        <v>165.9931255001201</v>
+        <v>165.99314147324</v>
       </c>
       <c r="D27" t="n">
-        <v>157.9109012466388</v>
+        <v>157.9109164420257</v>
       </c>
       <c r="E27" t="n">
-        <v>162.8305230034835</v>
+        <v>162.8305386722738</v>
       </c>
       <c r="F27" t="n">
         <v>596401</v>
@@ -972,16 +972,16 @@
         <v>44511</v>
       </c>
       <c r="B28" t="n">
-        <v>162.1804504394531</v>
+        <v>162.1804351806641</v>
       </c>
       <c r="C28" t="n">
-        <v>165.5099711386316</v>
+        <v>165.5099555665838</v>
       </c>
       <c r="D28" t="n">
-        <v>159.4658792012834</v>
+        <v>159.4658641978954</v>
       </c>
       <c r="E28" t="n">
-        <v>161.5567073687131</v>
+        <v>161.5566921686091</v>
       </c>
       <c r="F28" t="n">
         <v>479646</v>
@@ -1032,16 +1032,16 @@
         <v>44517</v>
       </c>
       <c r="B31" t="n">
-        <v>147.3425140380859</v>
+        <v>147.342529296875</v>
       </c>
       <c r="C31" t="n">
-        <v>157.7088514018402</v>
+        <v>157.708867734167</v>
       </c>
       <c r="D31" t="n">
-        <v>146.6045747863164</v>
+        <v>146.6045899686845</v>
       </c>
       <c r="E31" t="n">
-        <v>156.3735231808589</v>
+        <v>156.3735393748991</v>
       </c>
       <c r="F31" t="n">
         <v>1006563</v>
@@ -1072,16 +1072,16 @@
         <v>44519</v>
       </c>
       <c r="B33" t="n">
-        <v>147.1931762695312</v>
+        <v>147.1931610107422</v>
       </c>
       <c r="C33" t="n">
-        <v>149.0468180845801</v>
+        <v>149.0468026336331</v>
       </c>
       <c r="D33" t="n">
-        <v>140.5692563255631</v>
+        <v>140.5692417534431</v>
       </c>
       <c r="E33" t="n">
-        <v>142.5722420379041</v>
+        <v>142.5722272581445</v>
       </c>
       <c r="F33" t="n">
         <v>581745</v>
@@ -1092,16 +1092,16 @@
         <v>44522</v>
       </c>
       <c r="B34" t="n">
-        <v>140.0509338378906</v>
+        <v>140.0509185791016</v>
       </c>
       <c r="C34" t="n">
-        <v>150.6632507155369</v>
+        <v>150.6632343005178</v>
       </c>
       <c r="D34" t="n">
-        <v>139.9015899501414</v>
+        <v>139.9015747076236</v>
       </c>
       <c r="E34" t="n">
-        <v>145.9281205149585</v>
+        <v>145.9281046158399</v>
       </c>
       <c r="F34" t="n">
         <v>547961</v>
@@ -1112,16 +1112,16 @@
         <v>44523</v>
       </c>
       <c r="B35" t="n">
-        <v>144.9529876708984</v>
+        <v>144.9530029296875</v>
       </c>
       <c r="C35" t="n">
-        <v>147.2107467010899</v>
+        <v>147.2107621975469</v>
       </c>
       <c r="D35" t="n">
-        <v>136.3524496339106</v>
+        <v>136.3524639873455</v>
       </c>
       <c r="E35" t="n">
-        <v>142.3174788041548</v>
+        <v>142.3174937855114</v>
       </c>
       <c r="F35" t="n">
         <v>809322</v>
@@ -1132,16 +1132,16 @@
         <v>44524</v>
       </c>
       <c r="B36" t="n">
-        <v>148.7393646240234</v>
+        <v>148.7393493652344</v>
       </c>
       <c r="C36" t="n">
-        <v>150.215256871112</v>
+        <v>150.2152414609149</v>
       </c>
       <c r="D36" t="n">
-        <v>144.4171307798759</v>
+        <v>144.4171159644937</v>
       </c>
       <c r="E36" t="n">
-        <v>144.5225468672058</v>
+        <v>144.5225320410092</v>
       </c>
       <c r="F36" t="n">
         <v>231702</v>
@@ -1172,16 +1172,16 @@
         <v>44526</v>
       </c>
       <c r="B38" t="n">
-        <v>146.7363586425781</v>
+        <v>146.7363433837891</v>
       </c>
       <c r="C38" t="n">
-        <v>148.7305642552127</v>
+        <v>148.7305487890506</v>
       </c>
       <c r="D38" t="n">
-        <v>143.3716904608705</v>
+        <v>143.3716755519658</v>
       </c>
       <c r="E38" t="n">
-        <v>148.7305642552127</v>
+        <v>148.7305487890506</v>
       </c>
       <c r="F38" t="n">
         <v>241997</v>
@@ -1212,16 +1212,16 @@
         <v>44530</v>
       </c>
       <c r="B40" t="n">
-        <v>140.5604858398438</v>
+        <v>140.5604705810547</v>
       </c>
       <c r="C40" t="n">
-        <v>147.3073827258078</v>
+        <v>147.3073667345976</v>
       </c>
       <c r="D40" t="n">
-        <v>139.7610448594554</v>
+        <v>139.7610296874511</v>
       </c>
       <c r="E40" t="n">
-        <v>147.3073827258078</v>
+        <v>147.3073667345976</v>
       </c>
       <c r="F40" t="n">
         <v>711030</v>
@@ -1252,16 +1252,16 @@
         <v>44532</v>
       </c>
       <c r="B42" t="n">
-        <v>143.7845764160156</v>
+        <v>143.7845611572266</v>
       </c>
       <c r="C42" t="n">
-        <v>150.513912239461</v>
+        <v>150.5138962665375</v>
       </c>
       <c r="D42" t="n">
-        <v>143.0466371541728</v>
+        <v>143.0466219736957</v>
       </c>
       <c r="E42" t="n">
-        <v>145.8314899009227</v>
+        <v>145.83147442491</v>
       </c>
       <c r="F42" t="n">
         <v>584287</v>
@@ -1272,16 +1272,16 @@
         <v>44533</v>
       </c>
       <c r="B43" t="n">
-        <v>144.0657043457031</v>
+        <v>144.0657196044922</v>
       </c>
       <c r="C43" t="n">
-        <v>149.3455022769083</v>
+        <v>149.3455180949097</v>
       </c>
       <c r="D43" t="n">
-        <v>142.6776680688955</v>
+        <v>142.67768318067</v>
       </c>
       <c r="E43" t="n">
-        <v>143.5649512272504</v>
+        <v>143.564966433002</v>
       </c>
       <c r="F43" t="n">
         <v>471453</v>
@@ -1292,16 +1292,16 @@
         <v>44536</v>
       </c>
       <c r="B44" t="n">
-        <v>147.7642059326172</v>
+        <v>147.7641906738281</v>
       </c>
       <c r="C44" t="n">
-        <v>149.3279402427002</v>
+        <v>149.327924822433</v>
       </c>
       <c r="D44" t="n">
-        <v>139.2427292821338</v>
+        <v>139.2427149033103</v>
       </c>
       <c r="E44" t="n">
-        <v>144.9617791417145</v>
+        <v>144.9617641723165</v>
       </c>
       <c r="F44" t="n">
         <v>521095</v>
@@ -1372,16 +1372,16 @@
         <v>44540</v>
       </c>
       <c r="B48" t="n">
-        <v>148.2210388183594</v>
+        <v>148.2210083007812</v>
       </c>
       <c r="C48" t="n">
-        <v>150.2240247425351</v>
+        <v>150.2239938125575</v>
       </c>
       <c r="D48" t="n">
-        <v>146.3322625826765</v>
+        <v>146.332232453983</v>
       </c>
       <c r="E48" t="n">
-        <v>148.1156227396848</v>
+        <v>148.115592243811</v>
       </c>
       <c r="F48" t="n">
         <v>506410</v>
@@ -1412,16 +1412,16 @@
         <v>44544</v>
       </c>
       <c r="B50" t="n">
-        <v>147.2283325195312</v>
+        <v>147.2283020019531</v>
       </c>
       <c r="C50" t="n">
-        <v>150.926836499023</v>
+        <v>150.9268052148167</v>
       </c>
       <c r="D50" t="n">
-        <v>141.1227386054261</v>
+        <v>141.1227093534192</v>
       </c>
       <c r="E50" t="n">
-        <v>150.6632828858824</v>
+        <v>150.6632516563057</v>
       </c>
       <c r="F50" t="n">
         <v>995575</v>
@@ -1432,16 +1432,16 @@
         <v>44545</v>
       </c>
       <c r="B51" t="n">
-        <v>150.6984100341797</v>
+        <v>150.6983947753906</v>
       </c>
       <c r="C51" t="n">
-        <v>151.5417788756405</v>
+        <v>151.5417635314571</v>
       </c>
       <c r="D51" t="n">
-        <v>142.2296410146585</v>
+        <v>142.2296266133646</v>
       </c>
       <c r="E51" t="n">
-        <v>145.8402891518912</v>
+        <v>145.8402743850054</v>
       </c>
       <c r="F51" t="n">
         <v>314440</v>
@@ -1452,16 +1452,16 @@
         <v>44546</v>
       </c>
       <c r="B52" t="n">
-        <v>145.7260894775391</v>
+        <v>145.72607421875</v>
       </c>
       <c r="C52" t="n">
-        <v>152.8595299174546</v>
+        <v>152.8595139117323</v>
       </c>
       <c r="D52" t="n">
-        <v>144.3029054284978</v>
+        <v>144.3028903187285</v>
       </c>
       <c r="E52" t="n">
-        <v>148.1156188336976</v>
+        <v>148.115603324704</v>
       </c>
       <c r="F52" t="n">
         <v>399045</v>
@@ -1472,16 +1472,16 @@
         <v>44547</v>
       </c>
       <c r="B53" t="n">
-        <v>144.9529876708984</v>
+        <v>144.9530029296875</v>
       </c>
       <c r="C53" t="n">
-        <v>147.4127986275041</v>
+        <v>147.4128141452304</v>
       </c>
       <c r="D53" t="n">
-        <v>141.825519293812</v>
+        <v>141.8255342233813</v>
       </c>
       <c r="E53" t="n">
-        <v>144.0744847153172</v>
+        <v>144.0744998816288</v>
       </c>
       <c r="F53" t="n">
         <v>507335</v>
@@ -1492,16 +1492,16 @@
         <v>44550</v>
       </c>
       <c r="B54" t="n">
-        <v>145.9105682373047</v>
+        <v>145.9105529785156</v>
       </c>
       <c r="C54" t="n">
-        <v>146.2883315190382</v>
+        <v>146.288316220744</v>
       </c>
       <c r="D54" t="n">
-        <v>139.2515135151951</v>
+        <v>139.2514989527854</v>
       </c>
       <c r="E54" t="n">
-        <v>144.6455217015624</v>
+        <v>144.6455065750673</v>
       </c>
       <c r="F54" t="n">
         <v>356146</v>
@@ -1512,16 +1512,16 @@
         <v>44551</v>
       </c>
       <c r="B55" t="n">
-        <v>148.9853210449219</v>
+        <v>148.9853363037109</v>
       </c>
       <c r="C55" t="n">
-        <v>149.6441982970981</v>
+        <v>149.6442136233681</v>
       </c>
       <c r="D55" t="n">
-        <v>144.7948713726031</v>
+        <v>144.7948862022144</v>
       </c>
       <c r="E55" t="n">
-        <v>146.3146778142533</v>
+        <v>146.3146927995202</v>
       </c>
       <c r="F55" t="n">
         <v>221674</v>
@@ -1552,16 +1552,16 @@
         <v>44553</v>
       </c>
       <c r="B57" t="n">
-        <v>148.923828125</v>
+        <v>148.9238128662109</v>
       </c>
       <c r="C57" t="n">
-        <v>149.7759770834253</v>
+        <v>149.7759617373248</v>
       </c>
       <c r="D57" t="n">
-        <v>144.0832681520062</v>
+        <v>144.0832533891827</v>
       </c>
       <c r="E57" t="n">
-        <v>146.2268175565032</v>
+        <v>146.2268025740509</v>
       </c>
       <c r="F57" t="n">
         <v>381841</v>
@@ -1572,16 +1572,16 @@
         <v>44557</v>
       </c>
       <c r="B58" t="n">
-        <v>150.0483093261719</v>
+        <v>150.0483245849609</v>
       </c>
       <c r="C58" t="n">
-        <v>153.6940912743883</v>
+        <v>153.6941069039261</v>
       </c>
       <c r="D58" t="n">
-        <v>147.0438307899898</v>
+        <v>147.0438457432459</v>
       </c>
       <c r="E58" t="n">
-        <v>147.0438307899898</v>
+        <v>147.0438457432459</v>
       </c>
       <c r="F58" t="n">
         <v>232495</v>
@@ -1632,16 +1632,16 @@
         <v>44560</v>
       </c>
       <c r="B61" t="n">
-        <v>140.990966796875</v>
+        <v>140.9909362792969</v>
       </c>
       <c r="C61" t="n">
-        <v>141.2633006120338</v>
+        <v>141.2632700355088</v>
       </c>
       <c r="D61" t="n">
-        <v>136.7126476011728</v>
+        <v>136.7126180096394</v>
       </c>
       <c r="E61" t="n">
-        <v>140.0333882338771</v>
+        <v>140.0333579235674</v>
       </c>
       <c r="F61" t="n">
         <v>445854</v>
@@ -1652,16 +1652,16 @@
         <v>44564</v>
       </c>
       <c r="B62" t="n">
-        <v>144.8124389648438</v>
+        <v>144.8124084472656</v>
       </c>
       <c r="C62" t="n">
-        <v>144.8124389648438</v>
+        <v>144.8124084472656</v>
       </c>
       <c r="D62" t="n">
-        <v>138.7947011393807</v>
+        <v>138.7946718899726</v>
       </c>
       <c r="E62" t="n">
-        <v>142.1769298253991</v>
+        <v>142.1768998632246</v>
       </c>
       <c r="F62" t="n">
         <v>369633</v>
@@ -1672,16 +1672,16 @@
         <v>44565</v>
       </c>
       <c r="B63" t="n">
-        <v>140.2969207763672</v>
+        <v>140.2969055175781</v>
       </c>
       <c r="C63" t="n">
-        <v>146.4991495621347</v>
+        <v>146.499133628787</v>
       </c>
       <c r="D63" t="n">
-        <v>138.6629047258906</v>
+        <v>138.6628896448183</v>
       </c>
       <c r="E63" t="n">
-        <v>144.8124254785607</v>
+        <v>144.8124097286623</v>
       </c>
       <c r="F63" t="n">
         <v>382138</v>
@@ -1692,16 +1692,16 @@
         <v>44566</v>
       </c>
       <c r="B64" t="n">
-        <v>134.8502197265625</v>
+        <v>134.8502044677734</v>
       </c>
       <c r="C64" t="n">
-        <v>142.2296400695117</v>
+        <v>142.2296239757146</v>
       </c>
       <c r="D64" t="n">
-        <v>133.1019938111863</v>
+        <v>133.1019787502154</v>
       </c>
       <c r="E64" t="n">
-        <v>140.2969360182529</v>
+        <v>140.2969201431482</v>
       </c>
       <c r="F64" t="n">
         <v>1366948</v>
@@ -1712,16 +1712,16 @@
         <v>44567</v>
       </c>
       <c r="B65" t="n">
-        <v>135.2718963623047</v>
+        <v>135.2718811035156</v>
       </c>
       <c r="C65" t="n">
-        <v>137.0289024684961</v>
+        <v>137.0288870115152</v>
       </c>
       <c r="D65" t="n">
-        <v>129.5879805363842</v>
+        <v>129.5879659187458</v>
       </c>
       <c r="E65" t="n">
-        <v>134.8502186501887</v>
+        <v>134.8502034389653</v>
       </c>
       <c r="F65" t="n">
         <v>814212</v>
@@ -1752,16 +1752,16 @@
         <v>44571</v>
       </c>
       <c r="B67" t="n">
-        <v>137.5208587646484</v>
+        <v>137.5208435058594</v>
       </c>
       <c r="C67" t="n">
-        <v>138.4696436480268</v>
+        <v>138.4696282839642</v>
       </c>
       <c r="D67" t="n">
-        <v>131.9072249249958</v>
+        <v>131.9072102890741</v>
       </c>
       <c r="E67" t="n">
-        <v>137.2309645603231</v>
+        <v>137.2309493336996</v>
       </c>
       <c r="F67" t="n">
         <v>730000</v>
@@ -1772,16 +1772,16 @@
         <v>44572</v>
       </c>
       <c r="B68" t="n">
-        <v>146.3849639892578</v>
+        <v>146.3849487304688</v>
       </c>
       <c r="C68" t="n">
-        <v>149.0116794664315</v>
+        <v>149.0116639338405</v>
       </c>
       <c r="D68" t="n">
-        <v>133.6290962567753</v>
+        <v>133.6290823276248</v>
       </c>
       <c r="E68" t="n">
-        <v>137.5735796821382</v>
+        <v>137.573565341825</v>
       </c>
       <c r="F68" t="n">
         <v>715197</v>
@@ -1792,16 +1792,16 @@
         <v>44573</v>
       </c>
       <c r="B69" t="n">
-        <v>149.4421539306641</v>
+        <v>149.442138671875</v>
       </c>
       <c r="C69" t="n">
-        <v>150.7950427255186</v>
+        <v>150.7950273285929</v>
       </c>
       <c r="D69" t="n">
-        <v>145.5591720697106</v>
+        <v>145.5591572073933</v>
       </c>
       <c r="E69" t="n">
-        <v>146.4464553218307</v>
+        <v>146.4464403689174</v>
       </c>
       <c r="F69" t="n">
         <v>416574</v>
@@ -1852,16 +1852,16 @@
         <v>44578</v>
       </c>
       <c r="B72" t="n">
-        <v>138.8034820556641</v>
+        <v>138.803466796875</v>
       </c>
       <c r="C72" t="n">
-        <v>140.2705805422223</v>
+        <v>140.2705651221538</v>
       </c>
       <c r="D72" t="n">
-        <v>136.9059122483617</v>
+        <v>136.9058971981742</v>
       </c>
       <c r="E72" t="n">
-        <v>138.0655427100108</v>
+        <v>138.065527532344</v>
       </c>
       <c r="F72" t="n">
         <v>75291</v>
@@ -1872,16 +1872,16 @@
         <v>44579</v>
       </c>
       <c r="B73" t="n">
-        <v>133.1722717285156</v>
+        <v>133.1722564697266</v>
       </c>
       <c r="C73" t="n">
-        <v>138.8034793945444</v>
+        <v>138.8034634905354</v>
       </c>
       <c r="D73" t="n">
-        <v>133.1722717285156</v>
+        <v>133.1722564697266</v>
       </c>
       <c r="E73" t="n">
-        <v>138.1885299516231</v>
+        <v>138.1885141180745</v>
       </c>
       <c r="F73" t="n">
         <v>435258</v>
@@ -1892,16 +1892,16 @@
         <v>44580</v>
       </c>
       <c r="B74" t="n">
-        <v>139.6116790771484</v>
+        <v>139.6116943359375</v>
       </c>
       <c r="C74" t="n">
-        <v>141.6937266578653</v>
+        <v>141.6937421442108</v>
       </c>
       <c r="D74" t="n">
-        <v>133.0492613503245</v>
+        <v>133.0492758918774</v>
       </c>
       <c r="E74" t="n">
-        <v>133.5324406256718</v>
+        <v>133.5324552200335</v>
       </c>
       <c r="F74" t="n">
         <v>381153</v>
@@ -1952,16 +1952,16 @@
         <v>44585</v>
       </c>
       <c r="B77" t="n">
-        <v>143.1696319580078</v>
+        <v>143.1696166992188</v>
       </c>
       <c r="C77" t="n">
-        <v>145.330741785616</v>
+        <v>145.3307262964993</v>
       </c>
       <c r="D77" t="n">
-        <v>136.4490895119325</v>
+        <v>136.4490749694081</v>
       </c>
       <c r="E77" t="n">
-        <v>143.0202880597496</v>
+        <v>143.0202728168774</v>
       </c>
       <c r="F77" t="n">
         <v>940613</v>
@@ -1972,16 +1972,16 @@
         <v>44586</v>
       </c>
       <c r="B78" t="n">
-        <v>147.3161773681641</v>
+        <v>147.316162109375</v>
       </c>
       <c r="C78" t="n">
-        <v>149.5212151794752</v>
+        <v>149.5211996922916</v>
       </c>
       <c r="D78" t="n">
-        <v>140.1651631371207</v>
+        <v>140.165148619023</v>
       </c>
       <c r="E78" t="n">
-        <v>140.1651631371207</v>
+        <v>140.165148619023</v>
       </c>
       <c r="F78" t="n">
         <v>456302</v>
@@ -2012,16 +2012,16 @@
         <v>44588</v>
       </c>
       <c r="B80" t="n">
-        <v>149.486083984375</v>
+        <v>149.4860534667969</v>
       </c>
       <c r="C80" t="n">
-        <v>156.5668165068679</v>
+        <v>156.5667845437585</v>
       </c>
       <c r="D80" t="n">
-        <v>147.3249605575002</v>
+        <v>147.3249304811154</v>
       </c>
       <c r="E80" t="n">
-        <v>151.5417779286678</v>
+        <v>151.5417469914199</v>
       </c>
       <c r="F80" t="n">
         <v>697237</v>
@@ -2072,16 +2072,16 @@
         <v>44593</v>
       </c>
       <c r="B83" t="n">
-        <v>155.5829010009766</v>
+        <v>155.5828704833984</v>
       </c>
       <c r="C83" t="n">
-        <v>157.3574675730041</v>
+        <v>157.3574367073448</v>
       </c>
       <c r="D83" t="n">
-        <v>151.1201037410838</v>
+        <v>151.1200740988831</v>
       </c>
       <c r="E83" t="n">
-        <v>152.4378583625323</v>
+        <v>152.4378284618541</v>
       </c>
       <c r="F83" t="n">
         <v>577815</v>
@@ -2092,16 +2092,16 @@
         <v>44594</v>
       </c>
       <c r="B84" t="n">
-        <v>148.9941253662109</v>
+        <v>148.9940948486328</v>
       </c>
       <c r="C84" t="n">
-        <v>158.1305518913071</v>
+        <v>158.1305195023691</v>
       </c>
       <c r="D84" t="n">
-        <v>148.9062696976475</v>
+        <v>148.9062391980643</v>
       </c>
       <c r="E84" t="n">
-        <v>155.8025241281978</v>
+        <v>155.8024922160959</v>
       </c>
       <c r="F84" t="n">
         <v>466282</v>
@@ -2112,16 +2112,16 @@
         <v>44595</v>
       </c>
       <c r="B85" t="n">
-        <v>146.2707366943359</v>
+        <v>146.270751953125</v>
       </c>
       <c r="C85" t="n">
-        <v>149.960446290332</v>
+        <v>149.9604619340272</v>
       </c>
       <c r="D85" t="n">
-        <v>145.5415776595851</v>
+        <v>145.5415928423091</v>
       </c>
       <c r="E85" t="n">
-        <v>149.2137268486408</v>
+        <v>149.2137424144391</v>
       </c>
       <c r="F85" t="n">
         <v>228387</v>
@@ -2132,16 +2132,16 @@
         <v>44596</v>
       </c>
       <c r="B86" t="n">
-        <v>149.6002807617188</v>
+        <v>149.6002655029297</v>
       </c>
       <c r="C86" t="n">
-        <v>151.0058910250547</v>
+        <v>151.0058756228975</v>
       </c>
       <c r="D86" t="n">
-        <v>143.5825428206266</v>
+        <v>143.5825281756291</v>
       </c>
       <c r="E86" t="n">
-        <v>149.3455207714968</v>
+        <v>149.3455055386924</v>
       </c>
       <c r="F86" t="n">
         <v>455710</v>
@@ -2152,16 +2152,16 @@
         <v>44599</v>
       </c>
       <c r="B87" t="n">
-        <v>147.1229095458984</v>
+        <v>147.1228942871094</v>
       </c>
       <c r="C87" t="n">
-        <v>152.1830823806577</v>
+        <v>152.183066597055</v>
       </c>
       <c r="D87" t="n">
-        <v>146.7100120324576</v>
+        <v>146.709996816492</v>
       </c>
       <c r="E87" t="n">
-        <v>149.5651469971611</v>
+        <v>149.5651314850764</v>
       </c>
       <c r="F87" t="n">
         <v>353300</v>
@@ -2172,16 +2172,16 @@
         <v>44600</v>
       </c>
       <c r="B88" t="n">
-        <v>149.3191375732422</v>
+        <v>149.3191528320312</v>
       </c>
       <c r="C88" t="n">
-        <v>149.3191375732422</v>
+        <v>149.3191528320312</v>
       </c>
       <c r="D88" t="n">
-        <v>144.2325983236082</v>
+        <v>144.2326130626084</v>
       </c>
       <c r="E88" t="n">
-        <v>147.6763414553435</v>
+        <v>147.6763565462567</v>
       </c>
       <c r="F88" t="n">
         <v>326666</v>
@@ -2272,16 +2272,16 @@
         <v>44607</v>
       </c>
       <c r="B93" t="n">
-        <v>161.1438140869141</v>
+        <v>161.1437835693359</v>
       </c>
       <c r="C93" t="n">
-        <v>161.8202652142218</v>
+        <v>161.8202345685366</v>
       </c>
       <c r="D93" t="n">
-        <v>154.6253228193754</v>
+        <v>154.6252935362757</v>
       </c>
       <c r="E93" t="n">
-        <v>156.2769129050486</v>
+        <v>156.2768833091691</v>
       </c>
       <c r="F93" t="n">
         <v>501987</v>
@@ -2292,16 +2292,16 @@
         <v>44608</v>
       </c>
       <c r="B94" t="n">
-        <v>160.8099975585938</v>
+        <v>160.8099822998047</v>
       </c>
       <c r="C94" t="n">
-        <v>164.6841995051333</v>
+        <v>164.6841838787326</v>
       </c>
       <c r="D94" t="n">
-        <v>158.0690587299737</v>
+        <v>158.0690437312643</v>
       </c>
       <c r="E94" t="n">
-        <v>161.1438196262952</v>
+        <v>161.1438043358308</v>
       </c>
       <c r="F94" t="n">
         <v>383335</v>
@@ -2312,16 +2312,16 @@
         <v>44609</v>
       </c>
       <c r="B95" t="n">
-        <v>156.6282958984375</v>
+        <v>156.6282806396484</v>
       </c>
       <c r="C95" t="n">
-        <v>161.1877286693031</v>
+        <v>161.1877129663323</v>
       </c>
       <c r="D95" t="n">
-        <v>156.1626903751017</v>
+        <v>156.1626751616721</v>
       </c>
       <c r="E95" t="n">
-        <v>160.8011851997657</v>
+        <v>160.8011695344521</v>
       </c>
       <c r="F95" t="n">
         <v>315564</v>
@@ -2352,16 +2352,16 @@
         <v>44613</v>
       </c>
       <c r="B97" t="n">
-        <v>150.3118743896484</v>
+        <v>150.3118591308594</v>
       </c>
       <c r="C97" t="n">
-        <v>155.6883086649541</v>
+        <v>155.6882928603806</v>
       </c>
       <c r="D97" t="n">
-        <v>149.5827152632765</v>
+        <v>149.5827000785075</v>
       </c>
       <c r="E97" t="n">
-        <v>154.6165338917224</v>
+        <v>154.6165181959493</v>
       </c>
       <c r="F97" t="n">
         <v>185476</v>
@@ -2372,16 +2372,16 @@
         <v>44614</v>
       </c>
       <c r="B98" t="n">
-        <v>150.3558044433594</v>
+        <v>150.3557739257812</v>
       </c>
       <c r="C98" t="n">
-        <v>155.0558015228655</v>
+        <v>155.0557700513334</v>
       </c>
       <c r="D98" t="n">
-        <v>149.6793666888059</v>
+        <v>149.6793363085237</v>
       </c>
       <c r="E98" t="n">
-        <v>150.5315157922296</v>
+        <v>150.5314852389875</v>
       </c>
       <c r="F98" t="n">
         <v>352471</v>
@@ -2392,16 +2392,16 @@
         <v>44615</v>
       </c>
       <c r="B99" t="n">
-        <v>147.2722473144531</v>
+        <v>147.2722320556641</v>
       </c>
       <c r="C99" t="n">
-        <v>153.5623322222181</v>
+        <v>153.5623163117172</v>
       </c>
       <c r="D99" t="n">
-        <v>146.9647658922019</v>
+        <v>146.9647506652708</v>
       </c>
       <c r="E99" t="n">
-        <v>150.3557881219284</v>
+        <v>150.3557725436555</v>
       </c>
       <c r="F99" t="n">
         <v>373832</v>
@@ -2412,16 +2412,16 @@
         <v>44616</v>
       </c>
       <c r="B100" t="n">
-        <v>148.1068115234375</v>
+        <v>148.1067962646484</v>
       </c>
       <c r="C100" t="n">
-        <v>148.1068115234375</v>
+        <v>148.1067962646484</v>
       </c>
       <c r="D100" t="n">
-        <v>139.2427198314664</v>
+        <v>139.2427054859054</v>
       </c>
       <c r="E100" t="n">
-        <v>143.327753253209</v>
+        <v>143.3277384867851</v>
       </c>
       <c r="F100" t="n">
         <v>704723</v>
@@ -2432,16 +2432,16 @@
         <v>44617</v>
       </c>
       <c r="B101" t="n">
-        <v>145.1374816894531</v>
+        <v>145.1374664306641</v>
       </c>
       <c r="C101" t="n">
-        <v>149.1698071078465</v>
+        <v>149.1697914251255</v>
       </c>
       <c r="D101" t="n">
-        <v>141.2457065586561</v>
+        <v>141.2456917090224</v>
       </c>
       <c r="E101" t="n">
-        <v>145.8754209676771</v>
+        <v>145.875405631306</v>
       </c>
       <c r="F101" t="n">
         <v>765160</v>
@@ -2512,16 +2512,16 @@
         <v>44627</v>
       </c>
       <c r="B105" t="n">
-        <v>117.0780868530273</v>
+        <v>117.0781021118164</v>
       </c>
       <c r="C105" t="n">
-        <v>130.2644107383485</v>
+        <v>130.2644277157113</v>
       </c>
       <c r="D105" t="n">
-        <v>117.0780868530273</v>
+        <v>117.0781021118164</v>
       </c>
       <c r="E105" t="n">
-        <v>129.5791795392778</v>
+        <v>129.5791964273345</v>
       </c>
       <c r="F105" t="n">
         <v>1053703</v>
@@ -2532,16 +2532,16 @@
         <v>44628</v>
       </c>
       <c r="B106" t="n">
-        <v>124.43994140625</v>
+        <v>124.4399566650391</v>
       </c>
       <c r="C106" t="n">
-        <v>125.6083519749621</v>
+        <v>125.6083673770213</v>
       </c>
       <c r="D106" t="n">
-        <v>115.8657571712436</v>
+        <v>115.8657713786687</v>
       </c>
       <c r="E106" t="n">
-        <v>118.3431420022477</v>
+        <v>118.3431565134491</v>
       </c>
       <c r="F106" t="n">
         <v>713320</v>
@@ -2612,16 +2612,16 @@
         <v>44634</v>
       </c>
       <c r="B110" t="n">
-        <v>126.6801376342773</v>
+        <v>126.6801071166992</v>
       </c>
       <c r="C110" t="n">
-        <v>133.831151953603</v>
+        <v>133.8311197133267</v>
       </c>
       <c r="D110" t="n">
-        <v>126.6801376342773</v>
+        <v>126.6801071166992</v>
       </c>
       <c r="E110" t="n">
-        <v>131.6173339102961</v>
+        <v>131.6173022033344</v>
       </c>
       <c r="F110" t="n">
         <v>265850</v>
@@ -2632,16 +2632,16 @@
         <v>44635</v>
       </c>
       <c r="B111" t="n">
-        <v>131.4855499267578</v>
+        <v>131.4855346679688</v>
       </c>
       <c r="C111" t="n">
-        <v>132.1971352527014</v>
+        <v>132.1971199113335</v>
       </c>
       <c r="D111" t="n">
-        <v>124.3521094480533</v>
+        <v>124.3520950170941</v>
       </c>
       <c r="E111" t="n">
-        <v>126.987618598892</v>
+        <v>126.9876038620842</v>
       </c>
       <c r="F111" t="n">
         <v>302237</v>
@@ -2652,16 +2652,16 @@
         <v>44636</v>
       </c>
       <c r="B112" t="n">
-        <v>139.4887084960938</v>
+        <v>139.4886932373047</v>
       </c>
       <c r="C112" t="n">
-        <v>142.3438433121762</v>
+        <v>142.3438277410615</v>
       </c>
       <c r="D112" t="n">
-        <v>132.6539560702938</v>
+        <v>132.6539415591642</v>
       </c>
       <c r="E112" t="n">
-        <v>132.6539560702938</v>
+        <v>132.6539415591642</v>
       </c>
       <c r="F112" t="n">
         <v>861619</v>
@@ -2672,16 +2672,16 @@
         <v>44637</v>
       </c>
       <c r="B113" t="n">
-        <v>138.6102142333984</v>
+        <v>138.6101989746094</v>
       </c>
       <c r="C113" t="n">
-        <v>142.0978725168685</v>
+        <v>142.0978568741435</v>
       </c>
       <c r="D113" t="n">
-        <v>135.799007071694</v>
+        <v>135.7989921223744</v>
       </c>
       <c r="E113" t="n">
-        <v>140.0333849266909</v>
+        <v>140.0333695112333</v>
       </c>
       <c r="F113" t="n">
         <v>600068</v>
@@ -2692,16 +2692,16 @@
         <v>44638</v>
       </c>
       <c r="B114" t="n">
-        <v>142.3174896240234</v>
+        <v>142.3174743652344</v>
       </c>
       <c r="C114" t="n">
-        <v>145.1199164101681</v>
+        <v>145.1199008509126</v>
       </c>
       <c r="D114" t="n">
-        <v>137.1518875629193</v>
+        <v>137.1518728579682</v>
       </c>
       <c r="E114" t="n">
-        <v>138.618986001691</v>
+        <v>138.6189711394427</v>
       </c>
       <c r="F114" t="n">
         <v>570545</v>
@@ -2712,16 +2712,16 @@
         <v>44641</v>
       </c>
       <c r="B115" t="n">
-        <v>139.7698364257812</v>
+        <v>139.7698211669922</v>
       </c>
       <c r="C115" t="n">
-        <v>143.0642227644949</v>
+        <v>143.0642071460549</v>
       </c>
       <c r="D115" t="n">
-        <v>138.4169342626098</v>
+        <v>138.4169191515182</v>
       </c>
       <c r="E115" t="n">
-        <v>141.4829146409339</v>
+        <v>141.4828991951266</v>
       </c>
       <c r="F115" t="n">
         <v>351500</v>
@@ -2752,16 +2752,16 @@
         <v>44643</v>
       </c>
       <c r="B117" t="n">
-        <v>132.7418212890625</v>
+        <v>132.7418060302734</v>
       </c>
       <c r="C117" t="n">
-        <v>137.4418047432147</v>
+        <v>137.4417889441584</v>
       </c>
       <c r="D117" t="n">
-        <v>130.5719176002584</v>
+        <v>130.5719025909017</v>
       </c>
       <c r="E117" t="n">
-        <v>134.5076076612723</v>
+        <v>134.5075921995046</v>
       </c>
       <c r="F117" t="n">
         <v>1133860</v>
@@ -2792,16 +2792,16 @@
         <v>44645</v>
       </c>
       <c r="B119" t="n">
-        <v>133.9277954101562</v>
+        <v>133.9277648925781</v>
       </c>
       <c r="C119" t="n">
-        <v>140.0333892967957</v>
+        <v>140.0333573879609</v>
       </c>
       <c r="D119" t="n">
-        <v>133.4182620016815</v>
+        <v>133.4182316002086</v>
       </c>
       <c r="E119" t="n">
-        <v>135.3070517166146</v>
+        <v>135.307020884751</v>
       </c>
       <c r="F119" t="n">
         <v>403765</v>
@@ -2812,16 +2812,16 @@
         <v>44648</v>
       </c>
       <c r="B120" t="n">
-        <v>134.9380798339844</v>
+        <v>134.9380645751953</v>
       </c>
       <c r="C120" t="n">
-        <v>139.8489088843792</v>
+        <v>139.8488930702739</v>
       </c>
       <c r="D120" t="n">
-        <v>132.478268503776</v>
+        <v>132.4782535231423</v>
       </c>
       <c r="E120" t="n">
-        <v>134.7623684922676</v>
+        <v>134.762353253348</v>
       </c>
       <c r="F120" t="n">
         <v>527873</v>
@@ -2832,16 +2832,16 @@
         <v>44649</v>
       </c>
       <c r="B121" t="n">
-        <v>139.5765686035156</v>
+        <v>139.5765533447266</v>
       </c>
       <c r="C121" t="n">
-        <v>140.4638518565375</v>
+        <v>140.4638365007489</v>
       </c>
       <c r="D121" t="n">
-        <v>135.1576993429566</v>
+        <v>135.1576845672471</v>
       </c>
       <c r="E121" t="n">
-        <v>137.9249785831454</v>
+        <v>137.9249635049115</v>
       </c>
       <c r="F121" t="n">
         <v>830631</v>
@@ -2892,16 +2892,16 @@
         <v>44652</v>
       </c>
       <c r="B124" t="n">
-        <v>127.3829345703125</v>
+        <v>127.382926940918</v>
       </c>
       <c r="C124" t="n">
-        <v>129.1048063426568</v>
+        <v>129.1047986101335</v>
       </c>
       <c r="D124" t="n">
-        <v>124.6156554916039</v>
+        <v>124.615648027951</v>
       </c>
       <c r="E124" t="n">
-        <v>126.5044315732759</v>
+        <v>126.5044239964978</v>
       </c>
       <c r="F124" t="n">
         <v>526406</v>
@@ -2912,16 +2912,16 @@
         <v>44655</v>
       </c>
       <c r="B125" t="n">
-        <v>129.0872344970703</v>
+        <v>129.0872192382812</v>
       </c>
       <c r="C125" t="n">
-        <v>129.0872344970703</v>
+        <v>129.0872192382812</v>
       </c>
       <c r="D125" t="n">
-        <v>125.6347106955444</v>
+        <v>125.6346958448618</v>
       </c>
       <c r="E125" t="n">
-        <v>127.3829365120573</v>
+        <v>127.3829214547252</v>
       </c>
       <c r="F125" t="n">
         <v>325077</v>
@@ -2932,16 +2932,16 @@
         <v>44656</v>
       </c>
       <c r="B126" t="n">
-        <v>128.0769500732422</v>
+        <v>128.0769348144531</v>
       </c>
       <c r="C126" t="n">
-        <v>130.1590113571142</v>
+        <v>130.1589958502732</v>
       </c>
       <c r="D126" t="n">
-        <v>125.6347127369603</v>
+        <v>125.6346977691337</v>
       </c>
       <c r="E126" t="n">
-        <v>128.2614416065824</v>
+        <v>128.2614263258134</v>
       </c>
       <c r="F126" t="n">
         <v>767000</v>
@@ -2952,16 +2952,16 @@
         <v>44657</v>
       </c>
       <c r="B127" t="n">
-        <v>125.0197448730469</v>
+        <v>125.0197601318359</v>
       </c>
       <c r="C127" t="n">
-        <v>127.3829198059536</v>
+        <v>127.3829353531706</v>
       </c>
       <c r="D127" t="n">
-        <v>122.6917175626873</v>
+        <v>122.6917325373382</v>
       </c>
       <c r="E127" t="n">
-        <v>127.1720742853418</v>
+        <v>127.1720898068249</v>
       </c>
       <c r="F127" t="n">
         <v>694358</v>
@@ -2972,16 +2972,16 @@
         <v>44658</v>
       </c>
       <c r="B128" t="n">
-        <v>126.9524765014648</v>
+        <v>126.9524459838867</v>
       </c>
       <c r="C128" t="n">
-        <v>128.604066597516</v>
+        <v>128.604035682919</v>
       </c>
       <c r="D128" t="n">
-        <v>122.9992126029629</v>
+        <v>122.9991830356934</v>
       </c>
       <c r="E128" t="n">
-        <v>124.7562187800749</v>
+        <v>124.756188790446</v>
       </c>
       <c r="F128" t="n">
         <v>544395</v>
@@ -2992,16 +2992,16 @@
         <v>44659</v>
       </c>
       <c r="B129" t="n">
-        <v>123.5790100097656</v>
+        <v>123.5790176391602</v>
       </c>
       <c r="C129" t="n">
-        <v>128.0857344927065</v>
+        <v>128.0857424003326</v>
       </c>
       <c r="D129" t="n">
-        <v>123.5790100097656</v>
+        <v>123.5790176391602</v>
       </c>
       <c r="E129" t="n">
-        <v>126.7943340666578</v>
+        <v>126.7943418945568</v>
       </c>
       <c r="F129" t="n">
         <v>403536</v>
@@ -3012,16 +3012,16 @@
         <v>44662</v>
       </c>
       <c r="B130" t="n">
-        <v>121.8659286499023</v>
+        <v>121.8659362792969</v>
       </c>
       <c r="C130" t="n">
-        <v>123.5702264946588</v>
+        <v>123.5702342307505</v>
       </c>
       <c r="D130" t="n">
-        <v>119.362189914273</v>
+        <v>119.3621973869214</v>
       </c>
       <c r="E130" t="n">
-        <v>122.9904113383186</v>
+        <v>122.9904190381111</v>
       </c>
       <c r="F130" t="n">
         <v>348006</v>
@@ -3032,16 +3032,16 @@
         <v>44663</v>
       </c>
       <c r="B131" t="n">
-        <v>118.2025756835938</v>
+        <v>118.2025833129883</v>
       </c>
       <c r="C131" t="n">
-        <v>125.1690977064049</v>
+        <v>125.1691057854541</v>
       </c>
       <c r="D131" t="n">
-        <v>118.1762216672442</v>
+        <v>118.1762292949377</v>
       </c>
       <c r="E131" t="n">
-        <v>122.990414123866</v>
+        <v>122.9904220622919</v>
       </c>
       <c r="F131" t="n">
         <v>576598</v>
@@ -3052,16 +3052,16 @@
         <v>44664</v>
       </c>
       <c r="B132" t="n">
-        <v>119.7751083374023</v>
+        <v>119.7750930786133</v>
       </c>
       <c r="C132" t="n">
-        <v>120.7941751412227</v>
+        <v>120.7941597526093</v>
       </c>
       <c r="D132" t="n">
-        <v>117.7545485449705</v>
+        <v>117.7545335435913</v>
       </c>
       <c r="E132" t="n">
-        <v>118.8351169995752</v>
+        <v>118.8351018605366</v>
       </c>
       <c r="F132" t="n">
         <v>714435</v>
@@ -3092,16 +3092,16 @@
         <v>44669</v>
       </c>
       <c r="B134" t="n">
-        <v>112.4483795166016</v>
+        <v>112.4483871459961</v>
       </c>
       <c r="C134" t="n">
-        <v>115.1365964446377</v>
+        <v>115.1366042564223</v>
       </c>
       <c r="D134" t="n">
-        <v>112.0530558633418</v>
+        <v>112.0530634659144</v>
       </c>
       <c r="E134" t="n">
-        <v>114.2053854465485</v>
+        <v>114.2053931951523</v>
       </c>
       <c r="F134" t="n">
         <v>589431</v>
@@ -3172,16 +3172,16 @@
         <v>44676</v>
       </c>
       <c r="B138" t="n">
-        <v>111.5347442626953</v>
+        <v>111.5347366333008</v>
       </c>
       <c r="C138" t="n">
-        <v>111.8334387791802</v>
+        <v>111.8334311293538</v>
       </c>
       <c r="D138" t="n">
-        <v>105.9474644367544</v>
+        <v>105.9474571895508</v>
       </c>
       <c r="E138" t="n">
-        <v>106.2988669904352</v>
+        <v>106.2988597191943</v>
       </c>
       <c r="F138" t="n">
         <v>607459</v>
@@ -3272,16 +3272,16 @@
         <v>44683</v>
       </c>
       <c r="B143" t="n">
-        <v>107.168586730957</v>
+        <v>107.1685791015625</v>
       </c>
       <c r="C143" t="n">
-        <v>108.556623178466</v>
+        <v>108.5566154502563</v>
       </c>
       <c r="D143" t="n">
-        <v>104.4628023919814</v>
+        <v>104.4627949552132</v>
       </c>
       <c r="E143" t="n">
-        <v>107.1861605455792</v>
+        <v>107.1861529149336</v>
       </c>
       <c r="F143" t="n">
         <v>497573</v>
@@ -3332,16 +3332,16 @@
         <v>44686</v>
       </c>
       <c r="B146" t="n">
-        <v>93.73626708984375</v>
+        <v>93.73627471923828</v>
       </c>
       <c r="C146" t="n">
-        <v>95.51084689698163</v>
+        <v>95.51085467081299</v>
       </c>
       <c r="D146" t="n">
-        <v>91.46094754500817</v>
+        <v>91.4609549892096</v>
       </c>
       <c r="E146" t="n">
-        <v>94.43907216835407</v>
+        <v>94.4390798549514</v>
       </c>
       <c r="F146" t="n">
         <v>1265698</v>
@@ -3352,16 +3352,16 @@
         <v>44687</v>
       </c>
       <c r="B147" t="n">
-        <v>90.31010437011719</v>
+        <v>90.31011199951172</v>
       </c>
       <c r="C147" t="n">
-        <v>95.44055829170378</v>
+        <v>95.44056635451888</v>
       </c>
       <c r="D147" t="n">
-        <v>90.31010437011719</v>
+        <v>90.31011199951172</v>
       </c>
       <c r="E147" t="n">
-        <v>93.73626045356588</v>
+        <v>93.73626837240195</v>
       </c>
       <c r="F147" t="n">
         <v>602571</v>
@@ -3392,16 +3392,16 @@
         <v>44691</v>
       </c>
       <c r="B149" t="n">
-        <v>84.51198577880859</v>
+        <v>84.51197814941406</v>
       </c>
       <c r="C149" t="n">
-        <v>89.03627756179158</v>
+        <v>89.03626952396259</v>
       </c>
       <c r="D149" t="n">
-        <v>83.46657176820631</v>
+        <v>83.46656423318744</v>
       </c>
       <c r="E149" t="n">
-        <v>85.83852718329263</v>
+        <v>85.83851943414338</v>
       </c>
       <c r="F149" t="n">
         <v>595901</v>
@@ -3432,16 +3432,16 @@
         <v>44693</v>
       </c>
       <c r="B151" t="n">
-        <v>89.44918060302734</v>
+        <v>89.44917297363281</v>
       </c>
       <c r="C151" t="n">
-        <v>96.81103377549363</v>
+        <v>96.8110255181841</v>
       </c>
       <c r="D151" t="n">
-        <v>80.67293697880346</v>
+        <v>80.67293009796164</v>
       </c>
       <c r="E151" t="n">
-        <v>80.98041170691459</v>
+        <v>80.98040479984731</v>
       </c>
       <c r="F151" t="n">
         <v>2304224</v>
@@ -3452,16 +3452,16 @@
         <v>44694</v>
       </c>
       <c r="B152" t="n">
-        <v>89.78299713134766</v>
+        <v>89.78300476074219</v>
       </c>
       <c r="C152" t="n">
-        <v>92.42729283812145</v>
+        <v>92.42730069221749</v>
       </c>
       <c r="D152" t="n">
-        <v>87.90300138967268</v>
+        <v>87.90300885931281</v>
       </c>
       <c r="E152" t="n">
-        <v>90.57365111206272</v>
+        <v>90.57365880864381</v>
       </c>
       <c r="F152" t="n">
         <v>780406</v>
@@ -3492,16 +3492,16 @@
         <v>44698</v>
       </c>
       <c r="B154" t="n">
-        <v>86.98058319091797</v>
+        <v>86.98057556152344</v>
       </c>
       <c r="C154" t="n">
-        <v>88.24562294284463</v>
+        <v>88.24561520248869</v>
       </c>
       <c r="D154" t="n">
-        <v>84.59105397819015</v>
+        <v>84.59104655839022</v>
       </c>
       <c r="E154" t="n">
-        <v>85.39048821633966</v>
+        <v>85.39048072641835</v>
       </c>
       <c r="F154" t="n">
         <v>1257850</v>
@@ -3532,16 +3532,16 @@
         <v>44700</v>
       </c>
       <c r="B156" t="n">
-        <v>89.60730743408203</v>
+        <v>89.6072998046875</v>
       </c>
       <c r="C156" t="n">
-        <v>90.45066952328574</v>
+        <v>90.45066182208521</v>
       </c>
       <c r="D156" t="n">
-        <v>82.86040401800625</v>
+        <v>82.86039696306027</v>
       </c>
       <c r="E156" t="n">
-        <v>83.85311001101303</v>
+        <v>83.85310287154553</v>
       </c>
       <c r="F156" t="n">
         <v>889253</v>
@@ -3552,16 +3552,16 @@
         <v>44701</v>
       </c>
       <c r="B157" t="n">
-        <v>91.24132537841797</v>
+        <v>91.24131774902344</v>
       </c>
       <c r="C157" t="n">
-        <v>92.66450270218249</v>
+        <v>92.66449495378507</v>
       </c>
       <c r="D157" t="n">
-        <v>87.70095923422785</v>
+        <v>87.70095190087078</v>
       </c>
       <c r="E157" t="n">
-        <v>89.60730920380003</v>
+        <v>89.60730171103826</v>
       </c>
       <c r="F157" t="n">
         <v>709088</v>
@@ -3612,16 +3612,16 @@
         <v>44706</v>
       </c>
       <c r="B160" t="n">
-        <v>89.92356872558594</v>
+        <v>89.92357635498047</v>
       </c>
       <c r="C160" t="n">
-        <v>90.73178988696996</v>
+        <v>90.73179758493647</v>
       </c>
       <c r="D160" t="n">
-        <v>85.75067942410486</v>
+        <v>85.75068669945851</v>
       </c>
       <c r="E160" t="n">
-        <v>86.97179807297417</v>
+        <v>86.97180545193132</v>
       </c>
       <c r="F160" t="n">
         <v>958832</v>
@@ -3632,16 +3632,16 @@
         <v>44707</v>
       </c>
       <c r="B161" t="n">
-        <v>94.81683349609375</v>
+        <v>94.81682586669922</v>
       </c>
       <c r="C161" t="n">
-        <v>96.2663648544297</v>
+        <v>96.26635710839928</v>
       </c>
       <c r="D161" t="n">
-        <v>89.0099278581001</v>
+        <v>89.00992069595566</v>
       </c>
       <c r="E161" t="n">
-        <v>89.41403845272137</v>
+        <v>89.41403125806036</v>
       </c>
       <c r="F161" t="n">
         <v>700096</v>
@@ -3652,16 +3652,16 @@
         <v>44708</v>
       </c>
       <c r="B162" t="n">
-        <v>96.65290069580078</v>
+        <v>96.65289306640625</v>
       </c>
       <c r="C162" t="n">
-        <v>97.42598765404017</v>
+        <v>97.42597996362124</v>
       </c>
       <c r="D162" t="n">
-        <v>93.57814008175724</v>
+        <v>93.57813269507206</v>
       </c>
       <c r="E162" t="n">
-        <v>94.5708527981426</v>
+        <v>94.57084533309663</v>
       </c>
       <c r="F162" t="n">
         <v>410015</v>
@@ -3692,16 +3692,16 @@
         <v>44712</v>
       </c>
       <c r="B164" t="n">
-        <v>93.95589447021484</v>
+        <v>93.95588684082031</v>
       </c>
       <c r="C164" t="n">
-        <v>98.17271160959186</v>
+        <v>98.17270363778388</v>
       </c>
       <c r="D164" t="n">
-        <v>93.12131928963522</v>
+        <v>93.12131172800976</v>
       </c>
       <c r="E164" t="n">
-        <v>96.72318029902813</v>
+        <v>96.72317244492481</v>
       </c>
       <c r="F164" t="n">
         <v>435642</v>
@@ -3712,16 +3712,16 @@
         <v>44713</v>
       </c>
       <c r="B165" t="n">
-        <v>92.17252349853516</v>
+        <v>92.17253112792969</v>
       </c>
       <c r="C165" t="n">
-        <v>96.28391737606235</v>
+        <v>96.28392534576922</v>
       </c>
       <c r="D165" t="n">
-        <v>91.18860453114267</v>
+        <v>91.18861207909531</v>
       </c>
       <c r="E165" t="n">
-        <v>95.12429380560316</v>
+        <v>95.12430167932452</v>
       </c>
       <c r="F165" t="n">
         <v>372179</v>
@@ -3752,16 +3752,16 @@
         <v>44715</v>
       </c>
       <c r="B167" t="n">
-        <v>94.96617889404297</v>
+        <v>94.96617126464844</v>
       </c>
       <c r="C167" t="n">
-        <v>97.28542642277941</v>
+        <v>97.28541860706112</v>
       </c>
       <c r="D167" t="n">
-        <v>93.93833192839882</v>
+        <v>93.93832438157946</v>
       </c>
       <c r="E167" t="n">
-        <v>96.63533603883948</v>
+        <v>96.63532827534817</v>
       </c>
       <c r="F167" t="n">
         <v>452357</v>
@@ -3772,16 +3772,16 @@
         <v>44718</v>
       </c>
       <c r="B168" t="n">
-        <v>94.98374938964844</v>
+        <v>94.98374176025391</v>
       </c>
       <c r="C168" t="n">
-        <v>97.48748166813617</v>
+        <v>97.48747383763394</v>
       </c>
       <c r="D168" t="n">
-        <v>94.69384178307456</v>
+        <v>94.69383417696631</v>
       </c>
       <c r="E168" t="n">
-        <v>95.18580133184516</v>
+        <v>95.18579368622116</v>
       </c>
       <c r="F168" t="n">
         <v>540320</v>
@@ -3792,16 +3792,16 @@
         <v>44719</v>
       </c>
       <c r="B169" t="n">
-        <v>100.5710296630859</v>
+        <v>100.5710220336914</v>
       </c>
       <c r="C169" t="n">
-        <v>101.2035462136224</v>
+        <v>101.2035385362447</v>
       </c>
       <c r="D169" t="n">
-        <v>93.36730080710669</v>
+        <v>93.36729372419249</v>
       </c>
       <c r="E169" t="n">
-        <v>94.36001351898909</v>
+        <v>94.36000636076696</v>
       </c>
       <c r="F169" t="n">
         <v>669503</v>
@@ -3812,16 +3812,16 @@
         <v>44720</v>
       </c>
       <c r="B170" t="n">
-        <v>97.0745849609375</v>
+        <v>97.07457733154297</v>
       </c>
       <c r="C170" t="n">
-        <v>100.0439227939208</v>
+        <v>100.0439149311568</v>
       </c>
       <c r="D170" t="n">
-        <v>97.0745849609375</v>
+        <v>97.07457733154297</v>
       </c>
       <c r="E170" t="n">
-        <v>98.75252896793423</v>
+        <v>98.75252120666485</v>
       </c>
       <c r="F170" t="n">
         <v>671896</v>
@@ -3852,16 +3852,16 @@
         <v>44722</v>
       </c>
       <c r="B172" t="n">
-        <v>88.72879791259766</v>
+        <v>88.72880554199219</v>
       </c>
       <c r="C172" t="n">
-        <v>95.22972108034641</v>
+        <v>95.2297292687264</v>
       </c>
       <c r="D172" t="n">
-        <v>88.72879791259766</v>
+        <v>88.72880554199219</v>
       </c>
       <c r="E172" t="n">
-        <v>93.59570505783955</v>
+        <v>93.59571310571778</v>
       </c>
       <c r="F172" t="n">
         <v>588546</v>
@@ -3872,16 +3872,16 @@
         <v>44725</v>
       </c>
       <c r="B173" t="n">
-        <v>85.03910064697266</v>
+        <v>85.03909301757812</v>
       </c>
       <c r="C173" t="n">
-        <v>87.61311493408253</v>
+        <v>87.61310707375694</v>
       </c>
       <c r="D173" t="n">
-        <v>84.30994148351176</v>
+        <v>84.30993391953471</v>
       </c>
       <c r="E173" t="n">
-        <v>87.41105627702898</v>
+        <v>87.41104843483134</v>
       </c>
       <c r="F173" t="n">
         <v>846744</v>
@@ -3892,16 +3892,16 @@
         <v>44726</v>
       </c>
       <c r="B174" t="n">
-        <v>85.73310089111328</v>
+        <v>85.73310852050781</v>
       </c>
       <c r="C174" t="n">
-        <v>86.47104686486708</v>
+        <v>86.47105455993147</v>
       </c>
       <c r="D174" t="n">
-        <v>84.07273082822437</v>
+        <v>84.07273830986246</v>
       </c>
       <c r="E174" t="n">
-        <v>86.10207722921302</v>
+        <v>86.10208489144279</v>
       </c>
       <c r="F174" t="n">
         <v>502449</v>
@@ -3932,16 +3932,16 @@
         <v>44729</v>
       </c>
       <c r="B176" t="n">
-        <v>84.51198577880859</v>
+        <v>84.51197814941406</v>
       </c>
       <c r="C176" t="n">
-        <v>86.43590949039935</v>
+        <v>86.43590168732089</v>
       </c>
       <c r="D176" t="n">
-        <v>83.73011864630146</v>
+        <v>83.73011108749068</v>
       </c>
       <c r="E176" t="n">
-        <v>84.07273427953736</v>
+        <v>84.07272668979664</v>
       </c>
       <c r="F176" t="n">
         <v>418487</v>
@@ -3952,16 +3952,16 @@
         <v>44732</v>
       </c>
       <c r="B177" t="n">
-        <v>83.89703369140625</v>
+        <v>83.89702606201172</v>
       </c>
       <c r="C177" t="n">
-        <v>85.54861686323618</v>
+        <v>85.54860908365065</v>
       </c>
       <c r="D177" t="n">
-        <v>82.53535140601245</v>
+        <v>82.53534390044604</v>
       </c>
       <c r="E177" t="n">
-        <v>84.51198308984139</v>
+        <v>84.51197540452485</v>
       </c>
       <c r="F177" t="n">
         <v>143101</v>
@@ -4032,16 +4032,16 @@
         <v>44736</v>
       </c>
       <c r="B181" t="n">
-        <v>91.10076141357422</v>
+        <v>91.10075378417969</v>
       </c>
       <c r="C181" t="n">
-        <v>92.33066699449137</v>
+        <v>92.33065926209622</v>
       </c>
       <c r="D181" t="n">
-        <v>89.34375535582006</v>
+        <v>89.34374787356913</v>
       </c>
       <c r="E181" t="n">
-        <v>89.34375535582006</v>
+        <v>89.34374787356913</v>
       </c>
       <c r="F181" t="n">
         <v>487883</v>
@@ -4072,16 +4072,16 @@
         <v>44740</v>
       </c>
       <c r="B183" t="n">
-        <v>85.97908782958984</v>
+        <v>85.97909545898438</v>
       </c>
       <c r="C183" t="n">
-        <v>92.55907317852221</v>
+        <v>92.55908139179482</v>
       </c>
       <c r="D183" t="n">
-        <v>85.97908782958984</v>
+        <v>85.97909545898438</v>
       </c>
       <c r="E183" t="n">
-        <v>91.55758033191366</v>
+        <v>91.55758845631833</v>
       </c>
       <c r="F183" t="n">
         <v>484787</v>
@@ -4092,16 +4092,16 @@
         <v>44741</v>
       </c>
       <c r="B184" t="n">
-        <v>83.28208160400391</v>
+        <v>83.28207397460938</v>
       </c>
       <c r="C184" t="n">
-        <v>86.92786345228541</v>
+        <v>86.92785548890417</v>
       </c>
       <c r="D184" t="n">
-        <v>82.57927656924488</v>
+        <v>82.57926900423368</v>
       </c>
       <c r="E184" t="n">
-        <v>85.9878655722014</v>
+        <v>85.9878576949325</v>
       </c>
       <c r="F184" t="n">
         <v>504091</v>
@@ -4112,16 +4112,16 @@
         <v>44742</v>
       </c>
       <c r="B185" t="n">
-        <v>82.6934814453125</v>
+        <v>82.69348907470703</v>
       </c>
       <c r="C185" t="n">
-        <v>84.46806118289064</v>
+        <v>84.4680689760099</v>
       </c>
       <c r="D185" t="n">
-        <v>79.82077970708073</v>
+        <v>79.82078707143653</v>
       </c>
       <c r="E185" t="n">
-        <v>82.49142951731181</v>
+        <v>82.4914371280648</v>
       </c>
       <c r="F185" t="n">
         <v>710009</v>
@@ -4132,16 +4132,16 @@
         <v>44743</v>
       </c>
       <c r="B186" t="n">
-        <v>83.40508270263672</v>
+        <v>83.40506744384766</v>
       </c>
       <c r="C186" t="n">
-        <v>85.39049479346207</v>
+        <v>85.39047917144593</v>
       </c>
       <c r="D186" t="n">
-        <v>81.92919729300532</v>
+        <v>81.92918230422647</v>
       </c>
       <c r="E186" t="n">
-        <v>82.62321551504384</v>
+        <v>82.62320039929577</v>
       </c>
       <c r="F186" t="n">
         <v>500037</v>
@@ -4192,16 +4192,16 @@
         <v>44748</v>
       </c>
       <c r="B189" t="n">
-        <v>86.62039184570312</v>
+        <v>86.62039947509766</v>
       </c>
       <c r="C189" t="n">
-        <v>88.46524674954465</v>
+        <v>88.46525454143122</v>
       </c>
       <c r="D189" t="n">
-        <v>84.60861923211571</v>
+        <v>84.60862668431632</v>
       </c>
       <c r="E189" t="n">
-        <v>87.84151044265967</v>
+        <v>87.8415181796085</v>
       </c>
       <c r="F189" t="n">
         <v>788696</v>
@@ -4212,16 +4212,16 @@
         <v>44749</v>
       </c>
       <c r="B190" t="n">
-        <v>86.4007568359375</v>
+        <v>86.40076446533203</v>
       </c>
       <c r="C190" t="n">
-        <v>88.54430600614423</v>
+        <v>88.54431382481931</v>
       </c>
       <c r="D190" t="n">
-        <v>86.18991802159677</v>
+        <v>86.18992563237374</v>
       </c>
       <c r="E190" t="n">
-        <v>87.14748294282991</v>
+        <v>87.14749063816215</v>
       </c>
       <c r="F190" t="n">
         <v>483378</v>
@@ -4272,16 +4272,16 @@
         <v>44754</v>
       </c>
       <c r="B193" t="n">
-        <v>86.32170867919922</v>
+        <v>86.32170104980469</v>
       </c>
       <c r="C193" t="n">
-        <v>86.32170867919922</v>
+        <v>86.32170104980469</v>
       </c>
       <c r="D193" t="n">
-        <v>81.2966703290714</v>
+        <v>81.29666314380617</v>
       </c>
       <c r="E193" t="n">
-        <v>82.6232117668371</v>
+        <v>82.6232044643278</v>
       </c>
       <c r="F193" t="n">
         <v>730233</v>
@@ -4292,16 +4292,16 @@
         <v>44755</v>
       </c>
       <c r="B194" t="n">
-        <v>84.68769073486328</v>
+        <v>84.68768310546875</v>
       </c>
       <c r="C194" t="n">
-        <v>86.91908916427828</v>
+        <v>86.91908133386021</v>
       </c>
       <c r="D194" t="n">
-        <v>83.45778519155122</v>
+        <v>83.45777767295714</v>
       </c>
       <c r="E194" t="n">
-        <v>84.37142911794173</v>
+        <v>84.37142151703875</v>
       </c>
       <c r="F194" t="n">
         <v>1885043</v>
@@ -4332,16 +4332,16 @@
         <v>44757</v>
       </c>
       <c r="B196" t="n">
-        <v>82.85162353515625</v>
+        <v>82.85160827636719</v>
       </c>
       <c r="C196" t="n">
-        <v>84.72283938975517</v>
+        <v>84.72282378634415</v>
       </c>
       <c r="D196" t="n">
-        <v>81.20882706105454</v>
+        <v>81.20881210481942</v>
       </c>
       <c r="E196" t="n">
-        <v>82.27181498619288</v>
+        <v>82.27179983418721</v>
       </c>
       <c r="F196" t="n">
         <v>1850084</v>
@@ -4372,16 +4372,16 @@
         <v>44761</v>
       </c>
       <c r="B198" t="n">
-        <v>86.85759735107422</v>
+        <v>86.85758972167969</v>
       </c>
       <c r="C198" t="n">
-        <v>87.15628516534521</v>
+        <v>87.15627750971456</v>
       </c>
       <c r="D198" t="n">
-        <v>83.45778819792039</v>
+        <v>83.45778086715818</v>
       </c>
       <c r="E198" t="n">
-        <v>83.45778819792039</v>
+        <v>83.45778086715818</v>
       </c>
       <c r="F198" t="n">
         <v>493807</v>
@@ -4432,16 +4432,16 @@
         <v>44764</v>
       </c>
       <c r="B201" t="n">
-        <v>89.78299713134766</v>
+        <v>89.78300476074219</v>
       </c>
       <c r="C201" t="n">
-        <v>92.24280802636217</v>
+        <v>92.24281586478145</v>
       </c>
       <c r="D201" t="n">
-        <v>89.22075579004928</v>
+        <v>89.22076337166682</v>
       </c>
       <c r="E201" t="n">
-        <v>91.97047426173357</v>
+        <v>91.97048207701101</v>
       </c>
       <c r="F201" t="n">
         <v>566897</v>
@@ -4452,16 +4452,16 @@
         <v>44767</v>
       </c>
       <c r="B202" t="n">
-        <v>89.08021545410156</v>
+        <v>89.08020782470703</v>
       </c>
       <c r="C202" t="n">
-        <v>90.58245494699018</v>
+        <v>90.58244718893432</v>
       </c>
       <c r="D202" t="n">
-        <v>88.15778452046713</v>
+        <v>88.15777697007543</v>
       </c>
       <c r="E202" t="n">
-        <v>89.17685133105172</v>
+        <v>89.17684369338068</v>
       </c>
       <c r="F202" t="n">
         <v>343259</v>
@@ -4492,16 +4492,16 @@
         <v>44769</v>
       </c>
       <c r="B204" t="n">
-        <v>92.2603759765625</v>
+        <v>92.26038360595703</v>
       </c>
       <c r="C204" t="n">
-        <v>92.55907046197431</v>
+        <v>92.55907811606914</v>
       </c>
       <c r="D204" t="n">
-        <v>87.46375071978201</v>
+        <v>87.46375795252364</v>
       </c>
       <c r="E204" t="n">
-        <v>87.46375071978201</v>
+        <v>87.46375795252364</v>
       </c>
       <c r="F204" t="n">
         <v>673546</v>
@@ -4552,16 +4552,16 @@
         <v>44774</v>
       </c>
       <c r="B207" t="n">
-        <v>100.1493377685547</v>
+        <v>100.1493453979492</v>
       </c>
       <c r="C207" t="n">
-        <v>102.2841002364559</v>
+        <v>102.284108028477</v>
       </c>
       <c r="D207" t="n">
-        <v>94.35121955402224</v>
+        <v>94.3512267417151</v>
       </c>
       <c r="E207" t="n">
-        <v>94.35121955402224</v>
+        <v>94.3512267417151</v>
       </c>
       <c r="F207" t="n">
         <v>942663</v>
@@ -4572,16 +4572,16 @@
         <v>44775</v>
       </c>
       <c r="B208" t="n">
-        <v>101.4670944213867</v>
+        <v>101.4670867919922</v>
       </c>
       <c r="C208" t="n">
-        <v>102.2050337090955</v>
+        <v>102.2050260242147</v>
       </c>
       <c r="D208" t="n">
-        <v>98.69980868758699</v>
+        <v>98.69980126626697</v>
       </c>
       <c r="E208" t="n">
-        <v>100.0439171776608</v>
+        <v>100.0439096552761</v>
       </c>
       <c r="F208" t="n">
         <v>737331</v>
@@ -4592,16 +4592,16 @@
         <v>44776</v>
       </c>
       <c r="B209" t="n">
-        <v>106.8523254394531</v>
+        <v>106.8523178100586</v>
       </c>
       <c r="C209" t="n">
-        <v>107.5990584070543</v>
+        <v>107.5990507243421</v>
       </c>
       <c r="D209" t="n">
-        <v>101.4671040610422</v>
+        <v>101.4670968161594</v>
       </c>
       <c r="E209" t="n">
-        <v>101.4671040610422</v>
+        <v>101.4670968161594</v>
       </c>
       <c r="F209" t="n">
         <v>990038</v>
@@ -4612,16 +4612,16 @@
         <v>44777</v>
       </c>
       <c r="B210" t="n">
-        <v>107.6956787109375</v>
+        <v>107.695671081543</v>
       </c>
       <c r="C210" t="n">
-        <v>114.196608903053</v>
+        <v>114.1966008131186</v>
       </c>
       <c r="D210" t="n">
-        <v>104.9811076793322</v>
+        <v>104.9811002422437</v>
       </c>
       <c r="E210" t="n">
-        <v>106.86110354844</v>
+        <v>106.8610959781686</v>
       </c>
       <c r="F210" t="n">
         <v>1242592</v>
@@ -4632,16 +4632,16 @@
         <v>44778</v>
       </c>
       <c r="B211" t="n">
-        <v>108.0119323730469</v>
+        <v>108.0119400024414</v>
       </c>
       <c r="C211" t="n">
-        <v>108.8728681920126</v>
+        <v>108.8728758822191</v>
       </c>
       <c r="D211" t="n">
-        <v>105.095302918661</v>
+        <v>105.0953103420402</v>
       </c>
       <c r="E211" t="n">
-        <v>107.3969830041038</v>
+        <v>107.3969905900615</v>
       </c>
       <c r="F211" t="n">
         <v>445839</v>
@@ -4652,16 +4652,16 @@
         <v>44781</v>
       </c>
       <c r="B212" t="n">
-        <v>110.4893264770508</v>
+        <v>110.4893188476562</v>
       </c>
       <c r="C212" t="n">
-        <v>113.2829664650746</v>
+        <v>113.2829586427765</v>
       </c>
       <c r="D212" t="n">
-        <v>108.4511996538819</v>
+        <v>108.451192165222</v>
       </c>
       <c r="E212" t="n">
-        <v>108.9343790159798</v>
+        <v>108.9343714939558</v>
       </c>
       <c r="F212" t="n">
         <v>1248783</v>
@@ -4712,16 +4712,16 @@
         <v>44784</v>
       </c>
       <c r="B215" t="n">
-        <v>84.59984588623047</v>
+        <v>84.59983825683594</v>
       </c>
       <c r="C215" t="n">
-        <v>92.06712176623714</v>
+        <v>92.06711346342773</v>
       </c>
       <c r="D215" t="n">
-        <v>83.26451750490639</v>
+        <v>83.26450999593463</v>
       </c>
       <c r="E215" t="n">
-        <v>90.87235708924037</v>
+        <v>90.87234889417739</v>
       </c>
       <c r="F215" t="n">
         <v>3127275</v>
@@ -4772,16 +4772,16 @@
         <v>44789</v>
       </c>
       <c r="B218" t="n">
-        <v>94.96617889404297</v>
+        <v>94.96617126464844</v>
       </c>
       <c r="C218" t="n">
-        <v>98.40112905587054</v>
+        <v>98.40112115051892</v>
       </c>
       <c r="D218" t="n">
-        <v>92.8577702217972</v>
+        <v>92.85776276178804</v>
       </c>
       <c r="E218" t="n">
-        <v>98.1815032921459</v>
+        <v>98.18149540443858</v>
       </c>
       <c r="F218" t="n">
         <v>844810</v>
@@ -4792,16 +4792,16 @@
         <v>44790</v>
       </c>
       <c r="B219" t="n">
-        <v>96.52112579345703</v>
+        <v>96.5211181640625</v>
       </c>
       <c r="C219" t="n">
-        <v>96.67046969296776</v>
+        <v>96.67046205176851</v>
       </c>
       <c r="D219" t="n">
-        <v>93.29701473066473</v>
+        <v>93.29700735611611</v>
       </c>
       <c r="E219" t="n">
-        <v>93.29701473066473</v>
+        <v>93.29700735611611</v>
       </c>
       <c r="F219" t="n">
         <v>484266</v>
@@ -4812,16 +4812,16 @@
         <v>44791</v>
       </c>
       <c r="B220" t="n">
-        <v>96.89888763427734</v>
+        <v>96.89888000488281</v>
       </c>
       <c r="C220" t="n">
-        <v>97.78617087563147</v>
+        <v>97.78616317637614</v>
       </c>
       <c r="D220" t="n">
-        <v>95.80953904294859</v>
+        <v>95.80953149932459</v>
       </c>
       <c r="E220" t="n">
-        <v>96.51234415332544</v>
+        <v>96.51233655436566</v>
       </c>
       <c r="F220" t="n">
         <v>225811</v>
@@ -4832,16 +4832,16 @@
         <v>44792</v>
       </c>
       <c r="B221" t="n">
-        <v>92.8138427734375</v>
+        <v>92.81383514404297</v>
       </c>
       <c r="C221" t="n">
-        <v>96.3542087713233</v>
+        <v>96.35420085090701</v>
       </c>
       <c r="D221" t="n">
-        <v>92.34823725842267</v>
+        <v>92.34822966730141</v>
       </c>
       <c r="E221" t="n">
-        <v>95.79196739065114</v>
+        <v>95.79195951645167</v>
       </c>
       <c r="F221" t="n">
         <v>610732</v>
@@ -4852,16 +4852,16 @@
         <v>44795</v>
       </c>
       <c r="B222" t="n">
-        <v>88.45647430419922</v>
+        <v>88.45645904541016</v>
       </c>
       <c r="C222" t="n">
-        <v>92.04954856375565</v>
+        <v>92.04953268515936</v>
       </c>
       <c r="D222" t="n">
-        <v>88.03478989086102</v>
+        <v>88.03477470481275</v>
       </c>
       <c r="E222" t="n">
-        <v>92.04954856375565</v>
+        <v>92.04953268515936</v>
       </c>
       <c r="F222" t="n">
         <v>1074017</v>
@@ -4892,16 +4892,16 @@
         <v>44797</v>
       </c>
       <c r="B224" t="n">
-        <v>101.0278396606445</v>
+        <v>101.0278472900391</v>
       </c>
       <c r="C224" t="n">
-        <v>102.8551274126588</v>
+        <v>102.855135180046</v>
       </c>
       <c r="D224" t="n">
-        <v>96.94279958605108</v>
+        <v>96.94280690695261</v>
       </c>
       <c r="E224" t="n">
-        <v>96.98672741470787</v>
+        <v>96.98673473892673</v>
       </c>
       <c r="F224" t="n">
         <v>1291806</v>
@@ -4912,16 +4912,16 @@
         <v>44798</v>
       </c>
       <c r="B225" t="n">
-        <v>99.56953430175781</v>
+        <v>99.56951904296875</v>
       </c>
       <c r="C225" t="n">
-        <v>103.1362613080438</v>
+        <v>103.1362455026625</v>
       </c>
       <c r="D225" t="n">
-        <v>98.6998181429413</v>
+        <v>98.69980301743414</v>
       </c>
       <c r="E225" t="n">
-        <v>101.9063556749261</v>
+        <v>101.9063400580249</v>
       </c>
       <c r="F225" t="n">
         <v>468543</v>
@@ -4952,16 +4952,16 @@
         <v>44802</v>
       </c>
       <c r="B227" t="n">
-        <v>91.77720642089844</v>
+        <v>91.77719879150391</v>
       </c>
       <c r="C227" t="n">
-        <v>95.84467276233583</v>
+        <v>95.8446647948148</v>
       </c>
       <c r="D227" t="n">
-        <v>91.23253216618707</v>
+        <v>91.23252458207104</v>
       </c>
       <c r="E227" t="n">
-        <v>93.56056637901798</v>
+        <v>93.5605586013736</v>
       </c>
       <c r="F227" t="n">
         <v>661048</v>
@@ -5012,16 +5012,16 @@
         <v>44805</v>
       </c>
       <c r="B230" t="n">
-        <v>88.58824920654297</v>
+        <v>88.58823394775391</v>
       </c>
       <c r="C230" t="n">
-        <v>89.21199230442676</v>
+        <v>89.21197693820172</v>
       </c>
       <c r="D230" t="n">
-        <v>84.3362974283704</v>
+        <v>84.33628290195425</v>
       </c>
       <c r="E230" t="n">
-        <v>87.39349115922539</v>
+        <v>87.39347610622615</v>
       </c>
       <c r="F230" t="n">
         <v>1016578</v>
@@ -5032,16 +5032,16 @@
         <v>44806</v>
       </c>
       <c r="B231" t="n">
-        <v>88.02600860595703</v>
+        <v>88.0260009765625</v>
       </c>
       <c r="C231" t="n">
-        <v>91.1974053571811</v>
+        <v>91.19739745291511</v>
       </c>
       <c r="D231" t="n">
-        <v>86.98937467200503</v>
+        <v>86.98936713245767</v>
       </c>
       <c r="E231" t="n">
-        <v>89.50189409323706</v>
+        <v>89.50188633592451</v>
       </c>
       <c r="F231" t="n">
         <v>344726</v>
@@ -5052,16 +5052,16 @@
         <v>44809</v>
       </c>
       <c r="B232" t="n">
-        <v>89.43161010742188</v>
+        <v>89.43161773681641</v>
       </c>
       <c r="C232" t="n">
-        <v>89.82693378540118</v>
+        <v>89.8269414485207</v>
       </c>
       <c r="D232" t="n">
-        <v>88.03478682049915</v>
+        <v>88.03479433073093</v>
       </c>
       <c r="E232" t="n">
-        <v>88.81665397201991</v>
+        <v>88.81666154895264</v>
       </c>
       <c r="F232" t="n">
         <v>95765</v>
@@ -5092,16 +5092,16 @@
         <v>44812</v>
       </c>
       <c r="B234" t="n">
-        <v>88.28955078125</v>
+        <v>88.28954315185547</v>
       </c>
       <c r="C234" t="n">
-        <v>90.14319263235551</v>
+        <v>90.14318484278159</v>
       </c>
       <c r="D234" t="n">
-        <v>87.12992709878814</v>
+        <v>87.12991956960056</v>
       </c>
       <c r="E234" t="n">
-        <v>88.29833768786334</v>
+        <v>88.29833005770951</v>
       </c>
       <c r="F234" t="n">
         <v>707072</v>
@@ -5112,16 +5112,16 @@
         <v>44813</v>
       </c>
       <c r="B235" t="n">
-        <v>91.80357360839844</v>
+        <v>91.80355834960938</v>
       </c>
       <c r="C235" t="n">
-        <v>92.14618927992782</v>
+        <v>92.14617396419217</v>
       </c>
       <c r="D235" t="n">
-        <v>88.8166617390234</v>
+        <v>88.81664697669278</v>
       </c>
       <c r="E235" t="n">
-        <v>88.8166617390234</v>
+        <v>88.81664697669278</v>
       </c>
       <c r="F235" t="n">
         <v>540504</v>
@@ -5132,16 +5132,16 @@
         <v>44816</v>
       </c>
       <c r="B236" t="n">
-        <v>94.79047393798828</v>
+        <v>94.79048156738281</v>
       </c>
       <c r="C236" t="n">
-        <v>94.79047393798828</v>
+        <v>94.79048156738281</v>
       </c>
       <c r="D236" t="n">
-        <v>91.34674382662909</v>
+        <v>91.34675117884834</v>
       </c>
       <c r="E236" t="n">
-        <v>91.34674382662909</v>
+        <v>91.34675117884834</v>
       </c>
       <c r="F236" t="n">
         <v>423751</v>
@@ -5152,16 +5152,16 @@
         <v>44817</v>
       </c>
       <c r="B237" t="n">
-        <v>90.74936676025391</v>
+        <v>90.74935913085938</v>
       </c>
       <c r="C237" t="n">
-        <v>92.94562436139803</v>
+        <v>92.94561654736182</v>
       </c>
       <c r="D237" t="n">
-        <v>90.48581316713809</v>
+        <v>90.4858055599008</v>
       </c>
       <c r="E237" t="n">
-        <v>91.36431620759575</v>
+        <v>91.36430852650177</v>
       </c>
       <c r="F237" t="n">
         <v>548480</v>
@@ -5172,16 +5172,16 @@
         <v>44818</v>
       </c>
       <c r="B238" t="n">
-        <v>90.13440704345703</v>
+        <v>90.1343994140625</v>
       </c>
       <c r="C238" t="n">
-        <v>91.77721007698068</v>
+        <v>91.77720230853167</v>
       </c>
       <c r="D238" t="n">
-        <v>88.15777528065119</v>
+        <v>88.15776781856795</v>
       </c>
       <c r="E238" t="n">
-        <v>90.17833487472001</v>
+        <v>90.17832724160722</v>
       </c>
       <c r="F238" t="n">
         <v>962834</v>
@@ -5192,16 +5192,16 @@
         <v>44819</v>
       </c>
       <c r="B239" t="n">
-        <v>90.22225952148438</v>
+        <v>90.22225189208984</v>
       </c>
       <c r="C239" t="n">
-        <v>93.36730201307846</v>
+        <v>93.36729411773216</v>
       </c>
       <c r="D239" t="n">
-        <v>89.2119863875034</v>
+        <v>89.21197884353981</v>
       </c>
       <c r="E239" t="n">
-        <v>89.60731007450063</v>
+        <v>89.60730249710758</v>
       </c>
       <c r="F239" t="n">
         <v>512054</v>
@@ -5212,16 +5212,16 @@
         <v>44820</v>
       </c>
       <c r="B240" t="n">
-        <v>87.80637359619141</v>
+        <v>87.80636596679688</v>
       </c>
       <c r="C240" t="n">
-        <v>89.46674375698272</v>
+        <v>89.46673598332055</v>
       </c>
       <c r="D240" t="n">
-        <v>86.15479034222778</v>
+        <v>86.15478285633742</v>
       </c>
       <c r="E240" t="n">
-        <v>89.33497366679777</v>
+        <v>89.33496590458495</v>
       </c>
       <c r="F240" t="n">
         <v>454254</v>
@@ -5232,16 +5232,16 @@
         <v>44823</v>
       </c>
       <c r="B241" t="n">
-        <v>88.99235534667969</v>
+        <v>88.99234771728516</v>
       </c>
       <c r="C241" t="n">
-        <v>89.82693050412597</v>
+        <v>89.82692280318257</v>
       </c>
       <c r="D241" t="n">
-        <v>86.69946201228579</v>
+        <v>86.69945457946307</v>
       </c>
       <c r="E241" t="n">
-        <v>87.39348017695347</v>
+        <v>87.39347268463194</v>
       </c>
       <c r="F241" t="n">
         <v>601912</v>
@@ -5252,16 +5252,16 @@
         <v>44824</v>
       </c>
       <c r="B242" t="n">
-        <v>89.88843536376953</v>
+        <v>89.88841247558594</v>
       </c>
       <c r="C242" t="n">
-        <v>91.25011782611443</v>
+        <v>91.25009459120727</v>
       </c>
       <c r="D242" t="n">
-        <v>88.50918578880611</v>
+        <v>88.50916325181916</v>
       </c>
       <c r="E242" t="n">
-        <v>88.77273939521048</v>
+        <v>88.7727167911152</v>
       </c>
       <c r="F242" t="n">
         <v>415549</v>
@@ -5292,16 +5292,16 @@
         <v>44826</v>
       </c>
       <c r="B244" t="n">
-        <v>89.08021545410156</v>
+        <v>89.08020782470703</v>
       </c>
       <c r="C244" t="n">
-        <v>91.53123990116616</v>
+        <v>91.53123206185035</v>
       </c>
       <c r="D244" t="n">
-        <v>86.27778842744067</v>
+        <v>86.27778103806376</v>
       </c>
       <c r="E244" t="n">
-        <v>89.43161803369786</v>
+        <v>89.43161037420698</v>
       </c>
       <c r="F244" t="n">
         <v>985794</v>
@@ -5392,16 +5392,16 @@
         <v>44833</v>
       </c>
       <c r="B249" t="n">
-        <v>87.27049255371094</v>
+        <v>87.27048492431641</v>
       </c>
       <c r="C249" t="n">
-        <v>87.79759976248249</v>
+        <v>87.79759208700698</v>
       </c>
       <c r="D249" t="n">
-        <v>84.51199342491191</v>
+        <v>84.51198603667193</v>
       </c>
       <c r="E249" t="n">
-        <v>85.399283410401</v>
+        <v>85.39927594459202</v>
       </c>
       <c r="F249" t="n">
         <v>546314</v>
@@ -5412,16 +5412,16 @@
         <v>44834</v>
       </c>
       <c r="B250" t="n">
-        <v>90.31010437011719</v>
+        <v>90.31011199951172</v>
       </c>
       <c r="C250" t="n">
-        <v>91.18860730483644</v>
+        <v>91.18861500844686</v>
       </c>
       <c r="D250" t="n">
-        <v>85.89122897842515</v>
+        <v>85.89123623451323</v>
       </c>
       <c r="E250" t="n">
-        <v>86.97179053720583</v>
+        <v>86.97179788457973</v>
       </c>
       <c r="F250" t="n">
         <v>846019</v>
@@ -5452,16 +5452,16 @@
         <v>44838</v>
       </c>
       <c r="B252" t="n">
-        <v>94.43906402587891</v>
+        <v>94.43907165527344</v>
       </c>
       <c r="C252" t="n">
-        <v>96.46840362900132</v>
+        <v>96.46841142233895</v>
       </c>
       <c r="D252" t="n">
-        <v>92.77869404106141</v>
+        <v>92.77870153632058</v>
       </c>
       <c r="E252" t="n">
-        <v>93.47271215307993</v>
+        <v>93.47271970440633</v>
       </c>
       <c r="F252" t="n">
         <v>828067</v>
@@ -5472,16 +5472,16 @@
         <v>44839</v>
       </c>
       <c r="B253" t="n">
-        <v>95.75682830810547</v>
+        <v>95.75682067871094</v>
       </c>
       <c r="C253" t="n">
-        <v>97.74224699191255</v>
+        <v>97.74223920433043</v>
       </c>
       <c r="D253" t="n">
-        <v>93.46393491058726</v>
+        <v>93.46392746387826</v>
       </c>
       <c r="E253" t="n">
-        <v>94.30729699781466</v>
+        <v>94.30728948391106</v>
       </c>
       <c r="F253" t="n">
         <v>556734</v>
@@ -5492,16 +5492,16 @@
         <v>44840</v>
       </c>
       <c r="B254" t="n">
-        <v>99.09513854980469</v>
+        <v>99.09514617919922</v>
       </c>
       <c r="C254" t="n">
-        <v>99.89457277411294</v>
+        <v>99.89458046505639</v>
       </c>
       <c r="D254" t="n">
-        <v>94.70262366200211</v>
+        <v>94.70263095321427</v>
       </c>
       <c r="E254" t="n">
-        <v>95.71289672424005</v>
+        <v>95.71290409323375</v>
       </c>
       <c r="F254" t="n">
         <v>1317655</v>
@@ -5532,16 +5532,16 @@
         <v>44844</v>
       </c>
       <c r="B256" t="n">
-        <v>96.52112579345703</v>
+        <v>96.5211181640625</v>
       </c>
       <c r="C256" t="n">
-        <v>97.95308325233714</v>
+        <v>97.95307550975528</v>
       </c>
       <c r="D256" t="n">
-        <v>94.96617174989328</v>
+        <v>94.96616424340819</v>
       </c>
       <c r="E256" t="n">
-        <v>97.16242922191877</v>
+        <v>97.1624215418332</v>
       </c>
       <c r="F256" t="n">
         <v>391665</v>
@@ -5552,16 +5552,16 @@
         <v>44845</v>
       </c>
       <c r="B257" t="n">
-        <v>88.64974212646484</v>
+        <v>88.64974975585938</v>
       </c>
       <c r="C257" t="n">
-        <v>96.94280599912264</v>
+        <v>96.94281434223674</v>
       </c>
       <c r="D257" t="n">
-        <v>87.1387158739726</v>
+        <v>87.13872337332482</v>
       </c>
       <c r="E257" t="n">
-        <v>96.5211283068829</v>
+        <v>96.52113661370647</v>
       </c>
       <c r="F257" t="n">
         <v>1649810</v>
@@ -5592,16 +5592,16 @@
         <v>44848</v>
       </c>
       <c r="B259" t="n">
-        <v>82.7198486328125</v>
+        <v>82.71984100341797</v>
       </c>
       <c r="C259" t="n">
-        <v>90.16955058382466</v>
+        <v>90.16954226733124</v>
       </c>
       <c r="D259" t="n">
-        <v>82.66713389327845</v>
+        <v>82.66712626874587</v>
       </c>
       <c r="E259" t="n">
-        <v>86.64675155211943</v>
+        <v>86.64674356053986</v>
       </c>
       <c r="F259" t="n">
         <v>951929</v>
@@ -5652,16 +5652,16 @@
         <v>44853</v>
       </c>
       <c r="B262" t="n">
-        <v>80.47087860107422</v>
+        <v>80.47086334228516</v>
       </c>
       <c r="C262" t="n">
-        <v>81.52508628989879</v>
+        <v>81.52507083121216</v>
       </c>
       <c r="D262" t="n">
-        <v>79.10920288553962</v>
+        <v>79.10918788494983</v>
       </c>
       <c r="E262" t="n">
-        <v>80.38302963595044</v>
+        <v>80.3830143938192</v>
       </c>
       <c r="F262" t="n">
         <v>1204425</v>
@@ -5692,16 +5692,16 @@
         <v>44855</v>
       </c>
       <c r="B264" t="n">
-        <v>82.25422668457031</v>
+        <v>82.25421905517578</v>
       </c>
       <c r="C264" t="n">
-        <v>85.73309747299184</v>
+        <v>85.73308952091872</v>
       </c>
       <c r="D264" t="n">
-        <v>75.13835431268782</v>
+        <v>75.1383473433177</v>
       </c>
       <c r="E264" t="n">
-        <v>77.96713481147866</v>
+        <v>77.96712757972831</v>
       </c>
       <c r="F264" t="n">
         <v>1421863</v>
@@ -5712,16 +5712,16 @@
         <v>44858</v>
       </c>
       <c r="B265" t="n">
-        <v>82.40357971191406</v>
+        <v>82.40358734130859</v>
       </c>
       <c r="C265" t="n">
-        <v>83.41385274639228</v>
+        <v>83.41386046932367</v>
       </c>
       <c r="D265" t="n">
-        <v>80.20732232836033</v>
+        <v>80.20732975441281</v>
       </c>
       <c r="E265" t="n">
-        <v>81.73591559062895</v>
+        <v>81.73592315820733</v>
       </c>
       <c r="F265" t="n">
         <v>718180</v>
@@ -5732,16 +5732,16 @@
         <v>44859</v>
       </c>
       <c r="B266" t="n">
-        <v>82.92189025878906</v>
+        <v>82.92189788818359</v>
       </c>
       <c r="C266" t="n">
-        <v>85.30263237275399</v>
+        <v>85.30264022119347</v>
       </c>
       <c r="D266" t="n">
-        <v>81.31422830318635</v>
+        <v>81.31423578466473</v>
       </c>
       <c r="E266" t="n">
-        <v>82.03460043101913</v>
+        <v>82.03460797877678</v>
       </c>
       <c r="F266" t="n">
         <v>1189906</v>
@@ -5772,16 +5772,16 @@
         <v>44861</v>
       </c>
       <c r="B268" t="n">
-        <v>78.95985412597656</v>
+        <v>78.95984649658203</v>
       </c>
       <c r="C268" t="n">
-        <v>81.79742201297594</v>
+        <v>81.79741410940505</v>
       </c>
       <c r="D268" t="n">
-        <v>78.12527888403669</v>
+        <v>78.12527133528192</v>
       </c>
       <c r="E268" t="n">
-        <v>80.63779821975547</v>
+        <v>80.63779042823175</v>
       </c>
       <c r="F268" t="n">
         <v>872704</v>
@@ -5792,16 +5792,16 @@
         <v>44862</v>
       </c>
       <c r="B269" t="n">
-        <v>81.43723297119141</v>
+        <v>81.43721771240234</v>
       </c>
       <c r="C269" t="n">
-        <v>82.14003811734518</v>
+        <v>82.14002272687244</v>
       </c>
       <c r="D269" t="n">
-        <v>78.40640002110223</v>
+        <v>78.40638533019641</v>
       </c>
       <c r="E269" t="n">
-        <v>79.04771021965105</v>
+        <v>79.04769540858378</v>
       </c>
       <c r="F269" t="n">
         <v>705309</v>
@@ -5832,16 +5832,16 @@
         <v>44866</v>
       </c>
       <c r="B271" t="n">
-        <v>87.10357666015625</v>
+        <v>87.10356140136719</v>
       </c>
       <c r="C271" t="n">
-        <v>87.84151598729392</v>
+        <v>87.84150059923279</v>
       </c>
       <c r="D271" t="n">
-        <v>83.65984639528801</v>
+        <v>83.65983173977101</v>
       </c>
       <c r="E271" t="n">
-        <v>83.65984639528801</v>
+        <v>83.65983173977101</v>
       </c>
       <c r="F271" t="n">
         <v>1461617</v>
@@ -5852,16 +5852,16 @@
         <v>44868</v>
       </c>
       <c r="B272" t="n">
-        <v>86.58525085449219</v>
+        <v>86.58524322509766</v>
       </c>
       <c r="C272" t="n">
-        <v>88.46524668009084</v>
+        <v>88.4652388850419</v>
       </c>
       <c r="D272" t="n">
-        <v>84.04637779929271</v>
+        <v>84.0463703936091</v>
       </c>
       <c r="E272" t="n">
-        <v>85.59254490810744</v>
+        <v>85.59253736618446</v>
       </c>
       <c r="F272" t="n">
         <v>991113</v>
@@ -5872,16 +5872,16 @@
         <v>44869</v>
       </c>
       <c r="B273" t="n">
-        <v>83.484130859375</v>
+        <v>83.48413848876953</v>
       </c>
       <c r="C273" t="n">
-        <v>88.72879432924752</v>
+        <v>88.728802437938</v>
       </c>
       <c r="D273" t="n">
-        <v>82.78133254952142</v>
+        <v>82.78134011468907</v>
       </c>
       <c r="E273" t="n">
-        <v>87.59552476569932</v>
+        <v>87.59553277082331</v>
       </c>
       <c r="F273" t="n">
         <v>612180</v>
@@ -5892,16 +5892,16 @@
         <v>44872</v>
       </c>
       <c r="B274" t="n">
-        <v>83.19422912597656</v>
+        <v>83.19423675537109</v>
       </c>
       <c r="C274" t="n">
-        <v>84.51198358965588</v>
+        <v>84.51199133989617</v>
       </c>
       <c r="D274" t="n">
-        <v>82.2805919293112</v>
+        <v>82.28059947491988</v>
       </c>
       <c r="E274" t="n">
-        <v>83.03609832223721</v>
+        <v>83.03610593713023</v>
       </c>
       <c r="F274" t="n">
         <v>752715</v>
@@ -5912,16 +5912,16 @@
         <v>44873</v>
       </c>
       <c r="B275" t="n">
-        <v>83.45777893066406</v>
+        <v>83.45778656005859</v>
       </c>
       <c r="C275" t="n">
-        <v>84.66133036601822</v>
+        <v>84.66133810543688</v>
       </c>
       <c r="D275" t="n">
-        <v>81.31422962176761</v>
+        <v>81.31423705520696</v>
       </c>
       <c r="E275" t="n">
-        <v>82.71105277545774</v>
+        <v>82.7110603365894</v>
       </c>
       <c r="F275" t="n">
         <v>953385</v>
@@ -5932,16 +5932,16 @@
         <v>44874</v>
       </c>
       <c r="B276" t="n">
-        <v>90.18712615966797</v>
+        <v>90.18711853027344</v>
       </c>
       <c r="C276" t="n">
-        <v>93.10375601205598</v>
+        <v>93.10374813592868</v>
       </c>
       <c r="D276" t="n">
-        <v>83.46657649938446</v>
+        <v>83.4665694385159</v>
       </c>
       <c r="E276" t="n">
-        <v>83.89704111638565</v>
+        <v>83.89703401910188</v>
       </c>
       <c r="F276" t="n">
         <v>2468383</v>
@@ -5952,16 +5952,16 @@
         <v>44875</v>
       </c>
       <c r="B277" t="n">
-        <v>90.49459075927734</v>
+        <v>90.49459838867188</v>
       </c>
       <c r="C277" t="n">
-        <v>94.21944139071987</v>
+        <v>94.21944933414814</v>
       </c>
       <c r="D277" t="n">
-        <v>85.65403762792715</v>
+        <v>85.65404484922558</v>
       </c>
       <c r="E277" t="n">
-        <v>85.67160473785169</v>
+        <v>85.67161196063115</v>
       </c>
       <c r="F277" t="n">
         <v>2820385</v>
@@ -5972,16 +5972,16 @@
         <v>44876</v>
       </c>
       <c r="B278" t="n">
-        <v>89.57217407226562</v>
+        <v>89.57216644287109</v>
       </c>
       <c r="C278" t="n">
-        <v>91.51366509297395</v>
+        <v>91.51365729821109</v>
       </c>
       <c r="D278" t="n">
-        <v>88.06114768810795</v>
+        <v>88.06114018741653</v>
       </c>
       <c r="E278" t="n">
-        <v>90.48581808832483</v>
+        <v>90.4858103811098</v>
       </c>
       <c r="F278" t="n">
         <v>1123849</v>
@@ -6012,16 +6012,16 @@
         <v>44881</v>
       </c>
       <c r="B280" t="n">
-        <v>86.34806060791016</v>
+        <v>86.34806823730469</v>
       </c>
       <c r="C280" t="n">
-        <v>90.38917306431421</v>
+        <v>90.38918105076644</v>
       </c>
       <c r="D280" t="n">
-        <v>85.7594652069497</v>
+        <v>85.75947278433812</v>
       </c>
       <c r="E280" t="n">
-        <v>88.90450085067289</v>
+        <v>88.90450870594499</v>
       </c>
       <c r="F280" t="n">
         <v>1097230</v>
@@ -6032,16 +6032,16 @@
         <v>44882</v>
       </c>
       <c r="B281" t="n">
-        <v>84.07273101806641</v>
+        <v>84.07273864746094</v>
       </c>
       <c r="C281" t="n">
-        <v>86.65553187836828</v>
+        <v>86.65553974214566</v>
       </c>
       <c r="D281" t="n">
-        <v>78.95106382910978</v>
+        <v>78.95107099372555</v>
       </c>
       <c r="E281" t="n">
-        <v>86.26020822533852</v>
+        <v>86.26021605324125</v>
       </c>
       <c r="F281" t="n">
         <v>1328887</v>
@@ -6132,16 +6132,16 @@
         <v>44889</v>
       </c>
       <c r="B286" t="n">
-        <v>78.80171203613281</v>
+        <v>78.80171966552734</v>
       </c>
       <c r="C286" t="n">
-        <v>79.50451707802175</v>
+        <v>79.5045247754602</v>
       </c>
       <c r="D286" t="n">
-        <v>77.19405672940827</v>
+        <v>77.19406420315345</v>
       </c>
       <c r="E286" t="n">
-        <v>77.52788543796044</v>
+        <v>77.52789294402611</v>
       </c>
       <c r="F286" t="n">
         <v>618983</v>
@@ -6152,16 +6152,16 @@
         <v>44890</v>
       </c>
       <c r="B287" t="n">
-        <v>77.44882202148438</v>
+        <v>77.44883728027344</v>
       </c>
       <c r="C287" t="n">
-        <v>78.80171064418803</v>
+        <v>78.80172616952011</v>
       </c>
       <c r="D287" t="n">
-        <v>76.73723008596878</v>
+        <v>76.73724520456162</v>
       </c>
       <c r="E287" t="n">
-        <v>78.37124608241869</v>
+        <v>78.37126152294162</v>
       </c>
       <c r="F287" t="n">
         <v>602409</v>
@@ -6172,16 +6172,16 @@
         <v>44893</v>
       </c>
       <c r="B288" t="n">
-        <v>75.56884002685547</v>
+        <v>75.56881713867188</v>
       </c>
       <c r="C288" t="n">
-        <v>78.24827738670668</v>
+        <v>78.24825368697887</v>
       </c>
       <c r="D288" t="n">
-        <v>75.28771927946512</v>
+        <v>75.28769647642699</v>
       </c>
       <c r="E288" t="n">
-        <v>77.14136151153649</v>
+        <v>77.1413381470698</v>
       </c>
       <c r="F288" t="n">
         <v>519110</v>
@@ -6192,16 +6192,16 @@
         <v>44894</v>
       </c>
       <c r="B289" t="n">
-        <v>76.56153106689453</v>
+        <v>76.56153869628906</v>
       </c>
       <c r="C289" t="n">
-        <v>77.83535762404934</v>
+        <v>77.83536538038132</v>
       </c>
       <c r="D289" t="n">
-        <v>73.80303242534015</v>
+        <v>73.80303977984893</v>
       </c>
       <c r="E289" t="n">
-        <v>75.94657499943207</v>
+        <v>75.94658256754593</v>
       </c>
       <c r="F289" t="n">
         <v>707315</v>
@@ -6232,16 +6232,16 @@
         <v>44896</v>
       </c>
       <c r="B291" t="n">
-        <v>79.21460723876953</v>
+        <v>79.21461486816406</v>
       </c>
       <c r="C291" t="n">
-        <v>81.06824894905768</v>
+        <v>81.06825675698197</v>
       </c>
       <c r="D291" t="n">
-        <v>78.69629372953831</v>
+        <v>78.69630130901254</v>
       </c>
       <c r="E291" t="n">
-        <v>79.07405025586351</v>
+        <v>79.0740578717206</v>
       </c>
       <c r="F291" t="n">
         <v>741238</v>
@@ -6252,16 +6252,16 @@
         <v>44897</v>
       </c>
       <c r="B292" t="n">
-        <v>83.99366760253906</v>
+        <v>83.99367523193359</v>
       </c>
       <c r="C292" t="n">
-        <v>84.95123260105719</v>
+        <v>84.95124031743019</v>
       </c>
       <c r="D292" t="n">
-        <v>77.90564188972039</v>
+        <v>77.90564896612145</v>
       </c>
       <c r="E292" t="n">
-        <v>79.21460940879811</v>
+        <v>79.21461660409658</v>
       </c>
       <c r="F292" t="n">
         <v>680539</v>
@@ -6272,16 +6272,16 @@
         <v>44900</v>
       </c>
       <c r="B293" t="n">
-        <v>81.08583068847656</v>
+        <v>81.08582305908203</v>
       </c>
       <c r="C293" t="n">
-        <v>84.30993513392545</v>
+        <v>84.30992720117379</v>
       </c>
       <c r="D293" t="n">
-        <v>80.1546129380944</v>
+        <v>80.15460539631847</v>
       </c>
       <c r="E293" t="n">
-        <v>81.88526494412361</v>
+        <v>81.88525723951001</v>
       </c>
       <c r="F293" t="n">
         <v>633863</v>
@@ -6292,16 +6292,16 @@
         <v>44901</v>
       </c>
       <c r="B294" t="n">
-        <v>77.94957733154297</v>
+        <v>77.94956970214844</v>
       </c>
       <c r="C294" t="n">
-        <v>81.69199543905461</v>
+        <v>81.69198744336707</v>
       </c>
       <c r="D294" t="n">
-        <v>77.94957733154297</v>
+        <v>77.94956970214844</v>
       </c>
       <c r="E294" t="n">
-        <v>81.04190506911468</v>
+        <v>81.0418971370554</v>
       </c>
       <c r="F294" t="n">
         <v>575865</v>
@@ -6312,16 +6312,16 @@
         <v>44902</v>
       </c>
       <c r="B295" t="n">
-        <v>76.15743255615234</v>
+        <v>76.15741729736328</v>
       </c>
       <c r="C295" t="n">
-        <v>78.43275226855985</v>
+        <v>78.43273655389115</v>
       </c>
       <c r="D295" t="n">
-        <v>74.76060920291299</v>
+        <v>74.76059422398934</v>
       </c>
       <c r="E295" t="n">
-        <v>77.82658301126293</v>
+        <v>77.82656741804537</v>
       </c>
       <c r="F295" t="n">
         <v>782541</v>
@@ -6352,16 +6352,16 @@
         <v>44904</v>
       </c>
       <c r="B297" t="n">
-        <v>72.71369171142578</v>
+        <v>72.71368408203125</v>
       </c>
       <c r="C297" t="n">
-        <v>74.76060534802988</v>
+        <v>74.76059750386545</v>
       </c>
       <c r="D297" t="n">
-        <v>70.93033166069503</v>
+        <v>70.93032421841735</v>
       </c>
       <c r="E297" t="n">
-        <v>72.96845839045105</v>
+        <v>72.96845073432544</v>
       </c>
       <c r="F297" t="n">
         <v>602365</v>
@@ -6372,16 +6372,16 @@
         <v>44907</v>
       </c>
       <c r="B298" t="n">
-        <v>72.23931121826172</v>
+        <v>72.23930358886719</v>
       </c>
       <c r="C298" t="n">
-        <v>74.02267139828965</v>
+        <v>74.02266358054949</v>
       </c>
       <c r="D298" t="n">
-        <v>70.51743928329</v>
+        <v>70.51743183574715</v>
       </c>
       <c r="E298" t="n">
-        <v>72.73127079828416</v>
+        <v>72.73126311693241</v>
       </c>
       <c r="F298" t="n">
         <v>769701</v>
@@ -6392,16 +6392,16 @@
         <v>44908</v>
       </c>
       <c r="B299" t="n">
-        <v>70.42080688476562</v>
+        <v>70.42079925537109</v>
       </c>
       <c r="C299" t="n">
-        <v>74.92752506588127</v>
+        <v>74.92751694822861</v>
       </c>
       <c r="D299" t="n">
-        <v>69.92884062483354</v>
+        <v>69.92883304873867</v>
       </c>
       <c r="E299" t="n">
-        <v>71.958187204355</v>
+        <v>71.9581794084006</v>
       </c>
       <c r="F299" t="n">
         <v>758036</v>
@@ -6412,16 +6412,16 @@
         <v>44909</v>
       </c>
       <c r="B300" t="n">
-        <v>68.19818878173828</v>
+        <v>68.19818115234375</v>
       </c>
       <c r="C300" t="n">
-        <v>70.5174362779243</v>
+        <v>70.51742838907342</v>
       </c>
       <c r="D300" t="n">
-        <v>66.81893927300305</v>
+        <v>66.81893179790644</v>
       </c>
       <c r="E300" t="n">
-        <v>70.43837422126734</v>
+        <v>70.43836634126119</v>
       </c>
       <c r="F300" t="n">
         <v>1355188</v>
@@ -6512,16 +6512,16 @@
         <v>44916</v>
       </c>
       <c r="B305" t="n">
-        <v>69.76193237304688</v>
+        <v>69.76192474365234</v>
       </c>
       <c r="C305" t="n">
-        <v>70.19239700292748</v>
+        <v>70.19238932645592</v>
       </c>
       <c r="D305" t="n">
-        <v>66.63445686972265</v>
+        <v>66.63444958235912</v>
       </c>
       <c r="E305" t="n">
-        <v>69.57744082922292</v>
+        <v>69.57743322000499</v>
       </c>
       <c r="F305" t="n">
         <v>349356</v>
@@ -6532,16 +6532,16 @@
         <v>44917</v>
       </c>
       <c r="B306" t="n">
-        <v>67.46903991699219</v>
+        <v>67.46903228759766</v>
       </c>
       <c r="C306" t="n">
-        <v>72.45015082309504</v>
+        <v>72.45014263043683</v>
       </c>
       <c r="D306" t="n">
-        <v>64.56997704227857</v>
+        <v>64.56996974070987</v>
       </c>
       <c r="E306" t="n">
-        <v>70.28024712084742</v>
+        <v>70.28023917356177</v>
       </c>
       <c r="F306" t="n">
         <v>477342</v>
@@ -6552,16 +6552,16 @@
         <v>44918</v>
       </c>
       <c r="B307" t="n">
-        <v>70.72827911376953</v>
+        <v>70.728271484375</v>
       </c>
       <c r="C307" t="n">
-        <v>70.85126899880341</v>
+        <v>70.85126135614206</v>
       </c>
       <c r="D307" t="n">
-        <v>68.02248823813217</v>
+        <v>68.02248090060881</v>
       </c>
       <c r="E307" t="n">
-        <v>68.52323468504038</v>
+        <v>68.52322729350198</v>
       </c>
       <c r="F307" t="n">
         <v>762496</v>
@@ -6572,16 +6572,16 @@
         <v>44921</v>
       </c>
       <c r="B308" t="n">
-        <v>68.78678131103516</v>
+        <v>68.78679656982422</v>
       </c>
       <c r="C308" t="n">
-        <v>71.15873651385208</v>
+        <v>71.15875229880567</v>
       </c>
       <c r="D308" t="n">
-        <v>68.39145097560208</v>
+        <v>68.39146614669608</v>
       </c>
       <c r="E308" t="n">
-        <v>71.15873651385208</v>
+        <v>71.15875229880567</v>
       </c>
       <c r="F308" t="n">
         <v>122344</v>
@@ -6612,16 +6612,16 @@
         <v>44923</v>
       </c>
       <c r="B310" t="n">
-        <v>68.39145660400391</v>
+        <v>68.39144897460938</v>
       </c>
       <c r="C310" t="n">
-        <v>70.26267226700244</v>
+        <v>70.26266442886484</v>
       </c>
       <c r="D310" t="n">
-        <v>67.17912488761789</v>
+        <v>67.17911739346478</v>
       </c>
       <c r="E310" t="n">
-        <v>67.82042831857034</v>
+        <v>67.82042075287674</v>
       </c>
       <c r="F310" t="n">
         <v>543744</v>
@@ -6632,16 +6632,16 @@
         <v>44924</v>
       </c>
       <c r="B311" t="n">
-        <v>70.66678619384766</v>
+        <v>70.66677856445312</v>
       </c>
       <c r="C311" t="n">
-        <v>70.66678619384766</v>
+        <v>70.66677856445312</v>
       </c>
       <c r="D311" t="n">
-        <v>67.35482600257404</v>
+        <v>67.35481873074851</v>
       </c>
       <c r="E311" t="n">
-        <v>68.52323664628368</v>
+        <v>68.52322924831307</v>
       </c>
       <c r="F311" t="n">
         <v>1109758</v>
@@ -6672,16 +6672,16 @@
         <v>44929</v>
       </c>
       <c r="B313" t="n">
-        <v>66.99464416503906</v>
+        <v>66.99462890625</v>
       </c>
       <c r="C313" t="n">
-        <v>69.74435628615456</v>
+        <v>69.74434040108741</v>
       </c>
       <c r="D313" t="n">
-        <v>65.50118496536248</v>
+        <v>65.50117004672566</v>
       </c>
       <c r="E313" t="n">
-        <v>66.60810068001396</v>
+        <v>66.60808550926455</v>
       </c>
       <c r="F313" t="n">
         <v>913081</v>
@@ -6732,16 +6732,16 @@
         <v>44932</v>
       </c>
       <c r="B316" t="n">
-        <v>68.31240081787109</v>
+        <v>68.31239318847656</v>
       </c>
       <c r="C316" t="n">
-        <v>68.31240081787109</v>
+        <v>68.31239318847656</v>
       </c>
       <c r="D316" t="n">
-        <v>65.62417685742929</v>
+        <v>65.62416952826607</v>
       </c>
       <c r="E316" t="n">
-        <v>65.99315324186605</v>
+        <v>65.99314587149411</v>
       </c>
       <c r="F316" t="n">
         <v>775272</v>
@@ -6792,16 +6792,16 @@
         <v>44937</v>
       </c>
       <c r="B319" t="n">
-        <v>72.90696716308594</v>
+        <v>72.90695953369141</v>
       </c>
       <c r="C319" t="n">
-        <v>73.10902581621284</v>
+        <v>73.10901816567375</v>
       </c>
       <c r="D319" t="n">
-        <v>69.80585242983342</v>
+        <v>69.80584512495696</v>
       </c>
       <c r="E319" t="n">
-        <v>71.22024289438232</v>
+        <v>71.2202354414961</v>
       </c>
       <c r="F319" t="n">
         <v>824670</v>
@@ -6832,16 +6832,16 @@
         <v>44939</v>
       </c>
       <c r="B321" t="n">
-        <v>74.85724639892578</v>
+        <v>74.85723876953125</v>
       </c>
       <c r="C321" t="n">
-        <v>76.07836513995662</v>
+        <v>76.07835738610657</v>
       </c>
       <c r="D321" t="n">
-        <v>73.63612765789495</v>
+        <v>73.63612015295593</v>
       </c>
       <c r="E321" t="n">
-        <v>74.82210547154654</v>
+        <v>74.82209784573354</v>
       </c>
       <c r="F321" t="n">
         <v>628080</v>
@@ -6872,16 +6872,16 @@
         <v>44943</v>
       </c>
       <c r="B323" t="n">
-        <v>72.37985229492188</v>
+        <v>72.37985992431641</v>
       </c>
       <c r="C323" t="n">
-        <v>72.69611387031159</v>
+        <v>72.69612153304253</v>
       </c>
       <c r="D323" t="n">
-        <v>70.11331323877729</v>
+        <v>70.11332062926112</v>
       </c>
       <c r="E323" t="n">
-        <v>71.026957045187</v>
+        <v>71.02696453197595</v>
       </c>
       <c r="F323" t="n">
         <v>1038524</v>
@@ -6892,16 +6892,16 @@
         <v>44944</v>
       </c>
       <c r="B324" t="n">
-        <v>73.96994781494141</v>
+        <v>73.96994018554688</v>
       </c>
       <c r="C324" t="n">
-        <v>75.29648918389273</v>
+        <v>75.29648141767632</v>
       </c>
       <c r="D324" t="n">
-        <v>72.48528234483609</v>
+        <v>72.48527486857265</v>
       </c>
       <c r="E324" t="n">
-        <v>72.52042326813002</v>
+        <v>72.52041578824208</v>
       </c>
       <c r="F324" t="n">
         <v>881691</v>
@@ -6932,16 +6932,16 @@
         <v>44946</v>
       </c>
       <c r="B326" t="n">
-        <v>77.02714538574219</v>
+        <v>77.02713775634766</v>
       </c>
       <c r="C326" t="n">
-        <v>78.32733280988822</v>
+        <v>78.32732505171256</v>
       </c>
       <c r="D326" t="n">
-        <v>74.45313125821576</v>
+        <v>74.45312388377251</v>
       </c>
       <c r="E326" t="n">
-        <v>75.12079543290946</v>
+        <v>75.12078799233532</v>
       </c>
       <c r="F326" t="n">
         <v>766265</v>
@@ -6952,16 +6952,16 @@
         <v>44949</v>
       </c>
       <c r="B327" t="n">
-        <v>80.09311676025391</v>
+        <v>80.09310913085938</v>
       </c>
       <c r="C327" t="n">
-        <v>81.2088193216573</v>
+        <v>81.20881158598479</v>
       </c>
       <c r="D327" t="n">
-        <v>77.09742502080553</v>
+        <v>77.09741767677029</v>
       </c>
       <c r="E327" t="n">
-        <v>77.09742502080553</v>
+        <v>77.09741767677029</v>
       </c>
       <c r="F327" t="n">
         <v>1210224</v>
@@ -6972,16 +6972,16 @@
         <v>44950</v>
       </c>
       <c r="B328" t="n">
-        <v>80.330322265625</v>
+        <v>80.33030700683594</v>
       </c>
       <c r="C328" t="n">
-        <v>81.29667429491836</v>
+        <v>81.2966588525702</v>
       </c>
       <c r="D328" t="n">
-        <v>78.64359128996323</v>
+        <v>78.64357635156964</v>
       </c>
       <c r="E328" t="n">
-        <v>81.29667429491836</v>
+        <v>81.2966588525702</v>
       </c>
       <c r="F328" t="n">
         <v>788120</v>
@@ -6992,16 +6992,16 @@
         <v>44951</v>
       </c>
       <c r="B329" t="n">
-        <v>77.85293579101562</v>
+        <v>77.85294342041016</v>
       </c>
       <c r="C329" t="n">
-        <v>79.94377045148158</v>
+        <v>79.94377828577274</v>
       </c>
       <c r="D329" t="n">
-        <v>77.15891763884663</v>
+        <v>77.15892520022911</v>
       </c>
       <c r="E329" t="n">
-        <v>79.94377045148158</v>
+        <v>79.94377828577274</v>
       </c>
       <c r="F329" t="n">
         <v>568888</v>
@@ -7012,16 +7012,16 @@
         <v>44952</v>
       </c>
       <c r="B330" t="n">
-        <v>79.5220947265625</v>
+        <v>79.52208709716797</v>
       </c>
       <c r="C330" t="n">
-        <v>80.04920192905641</v>
+        <v>80.04919424909092</v>
       </c>
       <c r="D330" t="n">
-        <v>77.41369272637284</v>
+        <v>77.41368529925958</v>
       </c>
       <c r="E330" t="n">
-        <v>77.87929827978883</v>
+        <v>77.87929080800512</v>
       </c>
       <c r="F330" t="n">
         <v>392968</v>
@@ -7052,16 +7052,16 @@
         <v>44956</v>
       </c>
       <c r="B332" t="n">
-        <v>80.8486328125</v>
+        <v>80.84862518310547</v>
       </c>
       <c r="C332" t="n">
-        <v>81.99068943295865</v>
+        <v>81.99068169579233</v>
       </c>
       <c r="D332" t="n">
-        <v>78.90714191967729</v>
+        <v>78.90713447349425</v>
       </c>
       <c r="E332" t="n">
-        <v>81.1736813466173</v>
+        <v>81.17367368654911</v>
       </c>
       <c r="F332" t="n">
         <v>515927</v>
@@ -7092,16 +7092,16 @@
         <v>44958</v>
       </c>
       <c r="B334" t="n">
-        <v>77.84415435791016</v>
+        <v>77.84414672851562</v>
       </c>
       <c r="C334" t="n">
-        <v>79.74171742556558</v>
+        <v>79.74170961019361</v>
       </c>
       <c r="D334" t="n">
-        <v>76.97443823117001</v>
+        <v>76.97443068701511</v>
       </c>
       <c r="E334" t="n">
-        <v>78.62602152176328</v>
+        <v>78.62601381573906</v>
       </c>
       <c r="F334" t="n">
         <v>624239</v>
@@ -7112,16 +7112,16 @@
         <v>44959</v>
       </c>
       <c r="B335" t="n">
-        <v>78.88957214355469</v>
+        <v>78.88956451416016</v>
       </c>
       <c r="C335" t="n">
-        <v>80.39181147045277</v>
+        <v>80.39180369577697</v>
       </c>
       <c r="D335" t="n">
-        <v>77.56303073581758</v>
+        <v>77.5630232347126</v>
       </c>
       <c r="E335" t="n">
-        <v>77.89685946320182</v>
+        <v>77.89685192981234</v>
       </c>
       <c r="F335" t="n">
         <v>645862</v>
@@ -7132,16 +7132,16 @@
         <v>44960</v>
       </c>
       <c r="B336" t="n">
-        <v>78.4327392578125</v>
+        <v>78.43274688720703</v>
       </c>
       <c r="C336" t="n">
-        <v>80.04918810831229</v>
+        <v>80.04919589494379</v>
       </c>
       <c r="D336" t="n">
-        <v>76.42975368198618</v>
+        <v>76.42976111654413</v>
       </c>
       <c r="E336" t="n">
-        <v>79.05647552379735</v>
+        <v>79.05648321386462</v>
       </c>
       <c r="F336" t="n">
         <v>709735</v>
@@ -7172,16 +7172,16 @@
         <v>44964</v>
       </c>
       <c r="B338" t="n">
-        <v>74.67276000976562</v>
+        <v>74.67275238037109</v>
       </c>
       <c r="C338" t="n">
-        <v>78.23948028427274</v>
+        <v>78.23947229046264</v>
       </c>
       <c r="D338" t="n">
-        <v>74.45313424503101</v>
+        <v>74.45312663807589</v>
       </c>
       <c r="E338" t="n">
-        <v>76.98322064189294</v>
+        <v>76.98321277643622</v>
       </c>
       <c r="F338" t="n">
         <v>1089766</v>
@@ -7192,16 +7192,16 @@
         <v>44965</v>
       </c>
       <c r="B339" t="n">
-        <v>74.92751312255859</v>
+        <v>74.92752075195312</v>
       </c>
       <c r="C339" t="n">
-        <v>76.47368010277411</v>
+        <v>76.47368788960505</v>
       </c>
       <c r="D339" t="n">
-        <v>73.99630219362362</v>
+        <v>73.99630972819882</v>
       </c>
       <c r="E339" t="n">
-        <v>74.67274647734247</v>
+        <v>74.67275408079573</v>
       </c>
       <c r="F339" t="n">
         <v>806683</v>
@@ -7252,16 +7252,16 @@
         <v>44970</v>
       </c>
       <c r="B342" t="n">
-        <v>73.79425048828125</v>
+        <v>73.79425811767578</v>
       </c>
       <c r="C342" t="n">
-        <v>74.05780406386059</v>
+        <v>74.05781172050324</v>
       </c>
       <c r="D342" t="n">
-        <v>70.90397487319673</v>
+        <v>70.90398220377323</v>
       </c>
       <c r="E342" t="n">
-        <v>71.35201327070328</v>
+        <v>71.35202064760129</v>
       </c>
       <c r="F342" t="n">
         <v>400048</v>
@@ -7272,16 +7272,16 @@
         <v>44971</v>
       </c>
       <c r="B343" t="n">
-        <v>72.90696716308594</v>
+        <v>72.90695953369141</v>
       </c>
       <c r="C343" t="n">
-        <v>74.53219648561118</v>
+        <v>74.53218868614353</v>
       </c>
       <c r="D343" t="n">
-        <v>71.91426111693616</v>
+        <v>71.91425359142397</v>
       </c>
       <c r="E343" t="n">
-        <v>73.00360303600144</v>
+        <v>73.00359539649439</v>
       </c>
       <c r="F343" t="n">
         <v>472429</v>
@@ -7292,16 +7292,16 @@
         <v>44972</v>
       </c>
       <c r="B344" t="n">
-        <v>73.78546905517578</v>
+        <v>73.78546142578125</v>
       </c>
       <c r="C344" t="n">
-        <v>74.93631260463282</v>
+        <v>74.93630485624141</v>
       </c>
       <c r="D344" t="n">
-        <v>71.65070638245331</v>
+        <v>71.65069897379257</v>
       </c>
       <c r="E344" t="n">
-        <v>72.23930851791685</v>
+        <v>72.23930104839484</v>
       </c>
       <c r="F344" t="n">
         <v>619864</v>
@@ -7312,16 +7312,16 @@
         <v>44973</v>
       </c>
       <c r="B345" t="n">
-        <v>71.15874481201172</v>
+        <v>71.15873718261719</v>
       </c>
       <c r="C345" t="n">
-        <v>73.96995180261891</v>
+        <v>73.96994387181648</v>
       </c>
       <c r="D345" t="n">
-        <v>70.32416962173819</v>
+        <v>70.32416208182393</v>
       </c>
       <c r="E345" t="n">
-        <v>73.30229433137855</v>
+        <v>73.30228647216005</v>
       </c>
       <c r="F345" t="n">
         <v>1330447</v>
@@ -7352,16 +7352,16 @@
         <v>44979</v>
       </c>
       <c r="B347" t="n">
-        <v>59.92269134521484</v>
+        <v>59.92268753051758</v>
       </c>
       <c r="C347" t="n">
-        <v>60.25652008637044</v>
+        <v>60.25651625042154</v>
       </c>
       <c r="D347" t="n">
-        <v>58.28867516031535</v>
+        <v>58.28867144964006</v>
       </c>
       <c r="E347" t="n">
-        <v>58.85970347481399</v>
+        <v>58.85969972778687</v>
       </c>
       <c r="F347" t="n">
         <v>1166573</v>
@@ -7432,16 +7432,16 @@
         <v>44985</v>
       </c>
       <c r="B351" t="n">
-        <v>56.48774337768555</v>
+        <v>56.48774719238281</v>
       </c>
       <c r="C351" t="n">
-        <v>57.19932863514759</v>
+        <v>57.19933249789922</v>
       </c>
       <c r="D351" t="n">
-        <v>55.53017165976352</v>
+        <v>55.53017540979462</v>
       </c>
       <c r="E351" t="n">
-        <v>56.82157209178407</v>
+        <v>56.82157592902526</v>
       </c>
       <c r="F351" t="n">
         <v>573942</v>
@@ -7472,16 +7472,16 @@
         <v>44987</v>
       </c>
       <c r="B353" t="n">
-        <v>53.14943313598633</v>
+        <v>53.14942932128906</v>
       </c>
       <c r="C353" t="n">
-        <v>54.59017756413803</v>
+        <v>54.59017364603414</v>
       </c>
       <c r="D353" t="n">
-        <v>52.64868667867075</v>
+        <v>52.64868289991359</v>
       </c>
       <c r="E353" t="n">
-        <v>54.08943110682245</v>
+        <v>54.08942722465866</v>
       </c>
       <c r="F353" t="n">
         <v>1104186</v>
@@ -7512,16 +7512,16 @@
         <v>44991</v>
       </c>
       <c r="B355" t="n">
-        <v>54.2827033996582</v>
+        <v>54.28269958496094</v>
       </c>
       <c r="C355" t="n">
-        <v>55.26662586165249</v>
+        <v>55.26662197781043</v>
       </c>
       <c r="D355" t="n">
-        <v>52.3851369759148</v>
+        <v>52.38513329456833</v>
       </c>
       <c r="E355" t="n">
-        <v>52.71018216089787</v>
+        <v>52.71017845670896</v>
       </c>
       <c r="F355" t="n">
         <v>1320672</v>
@@ -7552,16 +7552,16 @@
         <v>44993</v>
       </c>
       <c r="B357" t="n">
-        <v>58.67522048950195</v>
+        <v>58.67521286010742</v>
       </c>
       <c r="C357" t="n">
-        <v>58.67522048950195</v>
+        <v>58.67521286010742</v>
       </c>
       <c r="D357" t="n">
-        <v>53.975227083112</v>
+        <v>53.97522006484605</v>
       </c>
       <c r="E357" t="n">
-        <v>53.975227083112</v>
+        <v>53.97522006484605</v>
       </c>
       <c r="F357" t="n">
         <v>1672249</v>
@@ -7592,16 +7592,16 @@
         <v>44995</v>
       </c>
       <c r="B359" t="n">
-        <v>52.01616668701172</v>
+        <v>52.01615905761719</v>
       </c>
       <c r="C359" t="n">
-        <v>56.08363689549009</v>
+        <v>56.08362866950537</v>
       </c>
       <c r="D359" t="n">
-        <v>51.79654091648602</v>
+        <v>51.79653331930479</v>
       </c>
       <c r="E359" t="n">
-        <v>55.52139545914005</v>
+        <v>55.52138731562125</v>
       </c>
       <c r="F359" t="n">
         <v>846843</v>
@@ -7632,16 +7632,16 @@
         <v>44999</v>
       </c>
       <c r="B361" t="n">
-        <v>50.32944107055664</v>
+        <v>50.32943725585938</v>
       </c>
       <c r="C361" t="n">
-        <v>52.78924896630146</v>
+        <v>52.78924496516417</v>
       </c>
       <c r="D361" t="n">
-        <v>49.55635744004602</v>
+        <v>49.55635368394428</v>
       </c>
       <c r="E361" t="n">
-        <v>50.84775800958192</v>
+        <v>50.84775415559906</v>
       </c>
       <c r="F361" t="n">
         <v>730632</v>
@@ -7652,16 +7652,16 @@
         <v>45000</v>
       </c>
       <c r="B362" t="n">
-        <v>50.43486022949219</v>
+        <v>50.43485641479492</v>
       </c>
       <c r="C362" t="n">
-        <v>50.90925268325992</v>
+        <v>50.90924883268146</v>
       </c>
       <c r="D362" t="n">
-        <v>48.08925868234591</v>
+        <v>48.08925504506086</v>
       </c>
       <c r="E362" t="n">
-        <v>49.89897283000158</v>
+        <v>49.89896905583676</v>
       </c>
       <c r="F362" t="n">
         <v>1072440</v>
@@ -7692,16 +7692,16 @@
         <v>45002</v>
       </c>
       <c r="B364" t="n">
-        <v>55.06457138061523</v>
+        <v>55.0645637512207</v>
       </c>
       <c r="C364" t="n">
-        <v>55.5477473873311</v>
+        <v>55.5477396909908</v>
       </c>
       <c r="D364" t="n">
-        <v>52.19186600817599</v>
+        <v>52.19185877680513</v>
       </c>
       <c r="E364" t="n">
-        <v>53.58868599016529</v>
+        <v>53.58867856525999</v>
       </c>
       <c r="F364" t="n">
         <v>1415773</v>
@@ -7712,16 +7712,16 @@
         <v>45005</v>
       </c>
       <c r="B365" t="n">
-        <v>52.49055099487305</v>
+        <v>52.49055480957031</v>
       </c>
       <c r="C365" t="n">
-        <v>55.60923578122764</v>
+        <v>55.60923982257214</v>
       </c>
       <c r="D365" t="n">
-        <v>52.18307630442985</v>
+        <v>52.18308009678171</v>
       </c>
       <c r="E365" t="n">
-        <v>54.03671470445178</v>
+        <v>54.03671863151492</v>
       </c>
       <c r="F365" t="n">
         <v>714391</v>
@@ -7752,16 +7752,16 @@
         <v>45007</v>
       </c>
       <c r="B367" t="n">
-        <v>52.56962203979492</v>
+        <v>52.56961822509766</v>
       </c>
       <c r="C367" t="n">
-        <v>55.12606575176405</v>
+        <v>55.1260617515593</v>
       </c>
       <c r="D367" t="n">
-        <v>52.56962203979492</v>
+        <v>52.56961822509766</v>
       </c>
       <c r="E367" t="n">
-        <v>53.85223567370974</v>
+        <v>53.85223176594004</v>
       </c>
       <c r="F367" t="n">
         <v>930770</v>
@@ -7772,16 +7772,16 @@
         <v>45008</v>
       </c>
       <c r="B368" t="n">
-        <v>49.19617080688477</v>
+        <v>49.1961669921875</v>
       </c>
       <c r="C368" t="n">
-        <v>53.29877844237178</v>
+        <v>53.29877430955613</v>
       </c>
       <c r="D368" t="n">
-        <v>48.85355515353253</v>
+        <v>48.85355136540186</v>
       </c>
       <c r="E368" t="n">
-        <v>52.56962265340579</v>
+        <v>52.56961857712928</v>
       </c>
       <c r="F368" t="n">
         <v>1208098</v>
@@ -7792,16 +7792,16 @@
         <v>45009</v>
       </c>
       <c r="B369" t="n">
-        <v>50.40850448608398</v>
+        <v>50.40850067138672</v>
       </c>
       <c r="C369" t="n">
-        <v>51.3660729168746</v>
+        <v>51.3660690297127</v>
       </c>
       <c r="D369" t="n">
-        <v>48.82719971216801</v>
+        <v>48.82719601713704</v>
       </c>
       <c r="E369" t="n">
-        <v>50.05710193578128</v>
+        <v>50.05709814767665</v>
       </c>
       <c r="F369" t="n">
         <v>598427</v>
@@ -7812,16 +7812,16 @@
         <v>45012</v>
       </c>
       <c r="B370" t="n">
-        <v>51.84924697875977</v>
+        <v>51.84925079345703</v>
       </c>
       <c r="C370" t="n">
-        <v>52.52569468460005</v>
+        <v>52.5256985490655</v>
       </c>
       <c r="D370" t="n">
-        <v>50.6544823737028</v>
+        <v>50.65448610049781</v>
       </c>
       <c r="E370" t="n">
-        <v>51.39242502087193</v>
+        <v>51.3924288019595</v>
       </c>
       <c r="F370" t="n">
         <v>634884</v>
@@ -7832,16 +7832,16 @@
         <v>45013</v>
       </c>
       <c r="B371" t="n">
-        <v>54.30905914306641</v>
+        <v>54.30905532836914</v>
       </c>
       <c r="C371" t="n">
-        <v>54.44961949924372</v>
+        <v>54.44961567467342</v>
       </c>
       <c r="D371" t="n">
-        <v>51.11130852661512</v>
+        <v>51.11130493652956</v>
       </c>
       <c r="E371" t="n">
-        <v>51.83168077092675</v>
+        <v>51.83167713024186</v>
       </c>
       <c r="F371" t="n">
         <v>854484</v>
@@ -7852,16 +7852,16 @@
         <v>45014</v>
       </c>
       <c r="B372" t="n">
-        <v>53.88737869262695</v>
+        <v>53.88737487792969</v>
       </c>
       <c r="C372" t="n">
-        <v>54.64289187245452</v>
+        <v>54.64288800427434</v>
       </c>
       <c r="D372" t="n">
-        <v>52.91223974430176</v>
+        <v>52.91223599863476</v>
       </c>
       <c r="E372" t="n">
-        <v>54.38812517670369</v>
+        <v>54.38812132655848</v>
       </c>
       <c r="F372" t="n">
         <v>332515</v>
@@ -7872,16 +7872,16 @@
         <v>45015</v>
       </c>
       <c r="B373" t="n">
-        <v>54.20363235473633</v>
+        <v>54.20363616943359</v>
       </c>
       <c r="C373" t="n">
-        <v>56.3998863651218</v>
+        <v>56.39989033438518</v>
       </c>
       <c r="D373" t="n">
-        <v>53.72923996033548</v>
+        <v>53.72924374164636</v>
       </c>
       <c r="E373" t="n">
-        <v>54.03671465047152</v>
+        <v>54.0367184534216</v>
       </c>
       <c r="F373" t="n">
         <v>990197</v>
@@ -7912,16 +7912,16 @@
         <v>45019</v>
       </c>
       <c r="B375" t="n">
-        <v>49.41579055786133</v>
+        <v>49.41579437255859</v>
       </c>
       <c r="C375" t="n">
-        <v>52.67503567302858</v>
+        <v>52.67503973932627</v>
       </c>
       <c r="D375" t="n">
-        <v>49.41579055786133</v>
+        <v>49.41579437255859</v>
       </c>
       <c r="E375" t="n">
-        <v>52.34999052236814</v>
+        <v>52.34999456357366</v>
       </c>
       <c r="F375" t="n">
         <v>492395</v>
@@ -7932,16 +7932,16 @@
         <v>45020</v>
       </c>
       <c r="B376" t="n">
-        <v>48.9062614440918</v>
+        <v>48.90625762939453</v>
       </c>
       <c r="C376" t="n">
-        <v>50.48756955878359</v>
+        <v>50.48756562074401</v>
       </c>
       <c r="D376" t="n">
-        <v>48.55486224733378</v>
+        <v>48.55485846004571</v>
       </c>
       <c r="E376" t="n">
-        <v>49.5914960775326</v>
+        <v>49.59149220938691</v>
       </c>
       <c r="F376" t="n">
         <v>366364</v>
@@ -7952,16 +7952,16 @@
         <v>45021</v>
       </c>
       <c r="B377" t="n">
-        <v>48.9062614440918</v>
+        <v>48.90625762939453</v>
       </c>
       <c r="C377" t="n">
-        <v>49.2049526045088</v>
+        <v>49.20494876651357</v>
       </c>
       <c r="D377" t="n">
-        <v>47.2810321999312</v>
+        <v>47.2810285120021</v>
       </c>
       <c r="E377" t="n">
-        <v>48.94140236913452</v>
+        <v>48.94139855169625</v>
       </c>
       <c r="F377" t="n">
         <v>464516</v>
@@ -7972,16 +7972,16 @@
         <v>45022</v>
       </c>
       <c r="B378" t="n">
-        <v>48.04533004760742</v>
+        <v>48.04532623291016</v>
       </c>
       <c r="C378" t="n">
-        <v>49.56513990454828</v>
+        <v>49.56513596918133</v>
       </c>
       <c r="D378" t="n">
-        <v>47.88719923232127</v>
+        <v>47.88719543017925</v>
       </c>
       <c r="E378" t="n">
-        <v>48.64271238286111</v>
+        <v>48.64270852073295</v>
       </c>
       <c r="F378" t="n">
         <v>483494</v>
@@ -7992,16 +7992,16 @@
         <v>45026</v>
       </c>
       <c r="B379" t="n">
-        <v>48.75691223144531</v>
+        <v>48.75691604614258</v>
       </c>
       <c r="C379" t="n">
-        <v>49.21373415359837</v>
+        <v>49.21373800403698</v>
       </c>
       <c r="D379" t="n">
-        <v>48.01018608730865</v>
+        <v>48.01018984358273</v>
       </c>
       <c r="E379" t="n">
-        <v>48.32644432459367</v>
+        <v>48.3264481056115</v>
       </c>
       <c r="F379" t="n">
         <v>441343</v>
@@ -8012,16 +8012,16 @@
         <v>45027</v>
       </c>
       <c r="B380" t="n">
-        <v>54.63409805297852</v>
+        <v>54.63410186767578</v>
       </c>
       <c r="C380" t="n">
-        <v>54.63409805297852</v>
+        <v>54.63410186767578</v>
       </c>
       <c r="D380" t="n">
-        <v>48.85355030008497</v>
+        <v>48.8535537111691</v>
       </c>
       <c r="E380" t="n">
-        <v>48.85355030008497</v>
+        <v>48.8535537111691</v>
       </c>
       <c r="F380" t="n">
         <v>1223134</v>
@@ -8032,16 +8032,16 @@
         <v>45028</v>
       </c>
       <c r="B381" t="n">
-        <v>56.73372268676758</v>
+        <v>56.73373031616211</v>
       </c>
       <c r="C381" t="n">
-        <v>57.69128769466669</v>
+        <v>57.69129545283193</v>
       </c>
       <c r="D381" t="n">
-        <v>54.3090526438428</v>
+        <v>54.30905994717439</v>
       </c>
       <c r="E381" t="n">
-        <v>54.55503239991062</v>
+        <v>54.55503973632089</v>
       </c>
       <c r="F381" t="n">
         <v>1443641</v>
@@ -8052,16 +8052,16 @@
         <v>45029</v>
       </c>
       <c r="B382" t="n">
-        <v>60.46736907958984</v>
+        <v>60.46736145019531</v>
       </c>
       <c r="C382" t="n">
-        <v>61.46007515490073</v>
+        <v>61.46006740025275</v>
       </c>
       <c r="D382" t="n">
-        <v>55.96064730547449</v>
+        <v>55.96064024470993</v>
       </c>
       <c r="E382" t="n">
-        <v>56.40868240525283</v>
+        <v>56.408675287958</v>
       </c>
       <c r="F382" t="n">
         <v>2756815</v>
@@ -8092,16 +8092,16 @@
         <v>45033</v>
       </c>
       <c r="B384" t="n">
-        <v>59.95783233642578</v>
+        <v>59.95782852172852</v>
       </c>
       <c r="C384" t="n">
-        <v>60.72213239227627</v>
+        <v>60.72212852895193</v>
       </c>
       <c r="D384" t="n">
-        <v>59.16717826182981</v>
+        <v>59.16717449743633</v>
       </c>
       <c r="E384" t="n">
-        <v>60.35315602250063</v>
+        <v>60.35315218265168</v>
       </c>
       <c r="F384" t="n">
         <v>288592</v>
@@ -8112,16 +8112,16 @@
         <v>45034</v>
       </c>
       <c r="B385" t="n">
-        <v>61.49520492553711</v>
+        <v>61.49520874023438</v>
       </c>
       <c r="C385" t="n">
-        <v>61.49520492553711</v>
+        <v>61.49520874023438</v>
       </c>
       <c r="D385" t="n">
-        <v>59.16717082715269</v>
+        <v>59.16717449743633</v>
       </c>
       <c r="E385" t="n">
-        <v>59.16717082715269</v>
+        <v>59.16717449743633</v>
       </c>
       <c r="F385" t="n">
         <v>581190</v>
@@ -8132,16 +8132,16 @@
         <v>45035</v>
       </c>
       <c r="B386" t="n">
-        <v>58.84213638305664</v>
+        <v>58.84213256835938</v>
       </c>
       <c r="C386" t="n">
-        <v>61.2755868471204</v>
+        <v>61.27558287466414</v>
       </c>
       <c r="D386" t="n">
-        <v>58.30624899414777</v>
+        <v>58.30624521419173</v>
       </c>
       <c r="E386" t="n">
-        <v>61.2755868471204</v>
+        <v>61.27558287466414</v>
       </c>
       <c r="F386" t="n">
         <v>827950</v>
@@ -8152,16 +8152,16 @@
         <v>45036</v>
       </c>
       <c r="B387" t="n">
-        <v>60.80118560791016</v>
+        <v>60.80119705200195</v>
       </c>
       <c r="C387" t="n">
-        <v>60.80118560791016</v>
+        <v>60.80119705200195</v>
       </c>
       <c r="D387" t="n">
-        <v>58.21838490725599</v>
+        <v>58.2183958652091</v>
       </c>
       <c r="E387" t="n">
-        <v>58.78941313934933</v>
+        <v>58.78942420478224</v>
       </c>
       <c r="F387" t="n">
         <v>442904</v>
@@ -8212,16 +8212,16 @@
         <v>45042</v>
       </c>
       <c r="B390" t="n">
-        <v>59.31651306152344</v>
+        <v>59.31652069091797</v>
       </c>
       <c r="C390" t="n">
-        <v>60.019318064902</v>
+        <v>60.01932578469255</v>
       </c>
       <c r="D390" t="n">
-        <v>56.95334481011464</v>
+        <v>56.9533521355543</v>
       </c>
       <c r="E390" t="n">
-        <v>59.30773285825401</v>
+        <v>59.30774048651921</v>
       </c>
       <c r="F390" t="n">
         <v>963997</v>
@@ -8252,16 +8252,16 @@
         <v>45044</v>
       </c>
       <c r="B392" t="n">
-        <v>63.67389297485352</v>
+        <v>63.67390060424805</v>
       </c>
       <c r="C392" t="n">
-        <v>63.75295501847341</v>
+        <v>63.75296265734114</v>
       </c>
       <c r="D392" t="n">
-        <v>60.6166999417585</v>
+        <v>60.61670720484071</v>
       </c>
       <c r="E392" t="n">
-        <v>61.50398974512687</v>
+        <v>61.50399711452398</v>
       </c>
       <c r="F392" t="n">
         <v>633625</v>
@@ -8312,16 +8312,16 @@
         <v>45050</v>
       </c>
       <c r="B395" t="n">
-        <v>60.79240417480469</v>
+        <v>60.79240036010742</v>
       </c>
       <c r="C395" t="n">
-        <v>61.56549109490604</v>
+        <v>61.5654872316979</v>
       </c>
       <c r="D395" t="n">
-        <v>58.60493360826845</v>
+        <v>58.60492993083402</v>
       </c>
       <c r="E395" t="n">
-        <v>58.60493360826845</v>
+        <v>58.60492993083402</v>
       </c>
       <c r="F395" t="n">
         <v>661928</v>
@@ -8352,16 +8352,16 @@
         <v>45054</v>
       </c>
       <c r="B397" t="n">
-        <v>65.1673583984375</v>
+        <v>65.16735076904297</v>
       </c>
       <c r="C397" t="n">
-        <v>65.74716694290409</v>
+        <v>65.74715924562913</v>
       </c>
       <c r="D397" t="n">
-        <v>63.59483708924626</v>
+        <v>63.59482964395288</v>
       </c>
       <c r="E397" t="n">
-        <v>63.7617548183479</v>
+        <v>63.76174735351282</v>
       </c>
       <c r="F397" t="n">
         <v>685640</v>
@@ -8392,16 +8392,16 @@
         <v>45056</v>
       </c>
       <c r="B399" t="n">
-        <v>68.46174621582031</v>
+        <v>68.46173858642578</v>
       </c>
       <c r="C399" t="n">
-        <v>68.48810023618428</v>
+        <v>68.48809260385286</v>
       </c>
       <c r="D399" t="n">
-        <v>66.18641972266146</v>
+        <v>66.1864123468299</v>
       </c>
       <c r="E399" t="n">
-        <v>66.78380209321604</v>
+        <v>66.78379465081203</v>
       </c>
       <c r="F399" t="n">
         <v>406791</v>
@@ -8432,16 +8432,16 @@
         <v>45058</v>
       </c>
       <c r="B401" t="n">
-        <v>66.23033905029297</v>
+        <v>66.23033142089844</v>
       </c>
       <c r="C401" t="n">
-        <v>67.00341925892872</v>
+        <v>67.00341154047932</v>
       </c>
       <c r="D401" t="n">
-        <v>65.81744157777364</v>
+        <v>65.81743399594278</v>
       </c>
       <c r="E401" t="n">
-        <v>66.79258042065457</v>
+        <v>66.79257272649272</v>
       </c>
       <c r="F401" t="n">
         <v>398348</v>
@@ -8472,16 +8472,16 @@
         <v>45062</v>
       </c>
       <c r="B403" t="n">
-        <v>69.20846557617188</v>
+        <v>69.20845794677734</v>
       </c>
       <c r="C403" t="n">
-        <v>74.04023209771412</v>
+        <v>74.04022393567588</v>
       </c>
       <c r="D403" t="n">
-        <v>67.52174141723872</v>
+        <v>67.52173397378508</v>
       </c>
       <c r="E403" t="n">
-        <v>69.22603938961998</v>
+        <v>69.22603175828814</v>
       </c>
       <c r="F403" t="n">
         <v>1416795</v>
@@ -8492,16 +8492,16 @@
         <v>45063</v>
       </c>
       <c r="B404" t="n">
-        <v>72.3271484375</v>
+        <v>72.32714080810547</v>
       </c>
       <c r="C404" t="n">
-        <v>73.79424673422444</v>
+        <v>73.79423895007376</v>
       </c>
       <c r="D404" t="n">
-        <v>67.6622932827093</v>
+        <v>67.66228614538477</v>
       </c>
       <c r="E404" t="n">
-        <v>69.41051895372132</v>
+        <v>69.41051163198605</v>
       </c>
       <c r="F404" t="n">
         <v>1084227</v>
@@ -8512,16 +8512,16 @@
         <v>45064</v>
       </c>
       <c r="B405" t="n">
-        <v>71.18509674072266</v>
+        <v>71.18508911132812</v>
       </c>
       <c r="C405" t="n">
-        <v>71.99331788899191</v>
+        <v>71.99331017297479</v>
       </c>
       <c r="D405" t="n">
-        <v>69.86734224584828</v>
+        <v>69.86733475768652</v>
       </c>
       <c r="E405" t="n">
-        <v>71.15874272321652</v>
+        <v>71.15873509664654</v>
       </c>
       <c r="F405" t="n">
         <v>796674</v>
@@ -8532,16 +8532,16 @@
         <v>45065</v>
       </c>
       <c r="B406" t="n">
-        <v>75.91145324707031</v>
+        <v>75.91144561767578</v>
       </c>
       <c r="C406" t="n">
-        <v>76.42976683949719</v>
+        <v>76.42975915801013</v>
       </c>
       <c r="D406" t="n">
-        <v>71.19388936375165</v>
+        <v>71.19388220849052</v>
       </c>
       <c r="E406" t="n">
-        <v>71.19388936375165</v>
+        <v>71.19388220849052</v>
       </c>
       <c r="F406" t="n">
         <v>1201246</v>
@@ -8572,16 +8572,16 @@
         <v>45069</v>
       </c>
       <c r="B408" t="n">
-        <v>77.132568359375</v>
+        <v>77.13256072998047</v>
       </c>
       <c r="C408" t="n">
-        <v>80.43573491118516</v>
+        <v>80.43572695506535</v>
       </c>
       <c r="D408" t="n">
-        <v>76.42976325763665</v>
+        <v>76.42975569775851</v>
       </c>
       <c r="E408" t="n">
-        <v>77.74751779656141</v>
+        <v>77.74751010634054</v>
       </c>
       <c r="F408" t="n">
         <v>970823</v>
@@ -8592,16 +8592,16 @@
         <v>45070</v>
       </c>
       <c r="B409" t="n">
-        <v>77.30826568603516</v>
+        <v>77.30825805664062</v>
       </c>
       <c r="C409" t="n">
-        <v>78.27461766662137</v>
+        <v>78.27460994185954</v>
       </c>
       <c r="D409" t="n">
-        <v>75.96415713911252</v>
+        <v>75.96414964236531</v>
       </c>
       <c r="E409" t="n">
-        <v>76.61424749660561</v>
+        <v>76.61423993570233</v>
       </c>
       <c r="F409" t="n">
         <v>567398</v>
@@ -8612,16 +8612,16 @@
         <v>45071</v>
       </c>
       <c r="B410" t="n">
-        <v>81.90283203125</v>
+        <v>81.90283966064453</v>
       </c>
       <c r="C410" t="n">
-        <v>81.90283203125</v>
+        <v>81.90283966064453</v>
       </c>
       <c r="D410" t="n">
-        <v>77.75629708276882</v>
+        <v>77.75630432590624</v>
       </c>
       <c r="E410" t="n">
-        <v>77.75629708276882</v>
+        <v>77.75630432590624</v>
       </c>
       <c r="F410" t="n">
         <v>1153989</v>
@@ -8632,16 +8632,16 @@
         <v>45072</v>
       </c>
       <c r="B411" t="n">
-        <v>82.75498199462891</v>
+        <v>82.75497436523438</v>
       </c>
       <c r="C411" t="n">
-        <v>84.15180528493505</v>
+        <v>84.15179752676379</v>
       </c>
       <c r="D411" t="n">
-        <v>80.38302651611544</v>
+        <v>80.38301910539758</v>
       </c>
       <c r="E411" t="n">
-        <v>81.70078104916651</v>
+        <v>81.70077351696148</v>
       </c>
       <c r="F411" t="n">
         <v>582166</v>
@@ -8712,16 +8712,16 @@
         <v>45078</v>
       </c>
       <c r="B415" t="n">
-        <v>79.15311431884766</v>
+        <v>79.15312194824219</v>
       </c>
       <c r="C415" t="n">
-        <v>80.05797128340549</v>
+        <v>80.0579790000172</v>
       </c>
       <c r="D415" t="n">
-        <v>78.45909618524368</v>
+        <v>78.45910374774334</v>
       </c>
       <c r="E415" t="n">
-        <v>79.07405227065705</v>
+        <v>79.07405989243097</v>
       </c>
       <c r="F415" t="n">
         <v>974431</v>
@@ -8772,16 +8772,16 @@
         <v>45083</v>
       </c>
       <c r="B418" t="n">
-        <v>83.89703369140625</v>
+        <v>83.89702606201172</v>
       </c>
       <c r="C418" t="n">
-        <v>86.708240516318</v>
+        <v>86.70823263127907</v>
       </c>
       <c r="D418" t="n">
-        <v>81.92040200757731</v>
+        <v>81.92039455793291</v>
       </c>
       <c r="E418" t="n">
-        <v>82.01703787053793</v>
+        <v>82.01703041210571</v>
       </c>
       <c r="F418" t="n">
         <v>1573579</v>
@@ -8792,16 +8792,16 @@
         <v>45084</v>
       </c>
       <c r="B419" t="n">
-        <v>86.52375793457031</v>
+        <v>86.52375030517578</v>
       </c>
       <c r="C419" t="n">
-        <v>86.60282668924023</v>
+        <v>86.60281905287367</v>
       </c>
       <c r="D419" t="n">
-        <v>82.88675607845614</v>
+        <v>82.88674876976107</v>
       </c>
       <c r="E419" t="n">
-        <v>84.3362873579094</v>
+        <v>84.33627992139918</v>
       </c>
       <c r="F419" t="n">
         <v>2805750</v>
@@ -8812,16 +8812,16 @@
         <v>45086</v>
       </c>
       <c r="B420" t="n">
-        <v>87.92936706542969</v>
+        <v>87.92935943603516</v>
       </c>
       <c r="C420" t="n">
-        <v>90.98656062878784</v>
+        <v>90.98655273412886</v>
       </c>
       <c r="D420" t="n">
-        <v>86.98058886520148</v>
+        <v>86.98058131812988</v>
       </c>
       <c r="E420" t="n">
-        <v>86.98058886520148</v>
+        <v>86.98058131812988</v>
       </c>
       <c r="F420" t="n">
         <v>1309381</v>
@@ -8932,16 +8932,16 @@
         <v>45096</v>
       </c>
       <c r="B426" t="n">
-        <v>98.03215789794922</v>
+        <v>98.03214263916016</v>
       </c>
       <c r="C426" t="n">
-        <v>98.3396393454904</v>
+        <v>98.33962403884159</v>
       </c>
       <c r="D426" t="n">
-        <v>94.14917579716422</v>
+        <v>94.14916114276463</v>
       </c>
       <c r="E426" t="n">
-        <v>94.61478136865674</v>
+        <v>94.61476664178524</v>
       </c>
       <c r="F426" t="n">
         <v>576522</v>
@@ -8952,16 +8952,16 @@
         <v>45097</v>
       </c>
       <c r="B427" t="n">
-        <v>99.66616821289062</v>
+        <v>99.66616058349609</v>
       </c>
       <c r="C427" t="n">
-        <v>100.1493475707456</v>
+        <v>100.1493399043639</v>
       </c>
       <c r="D427" t="n">
-        <v>95.20337781850962</v>
+        <v>95.20337053073942</v>
       </c>
       <c r="E427" t="n">
-        <v>97.8564540770091</v>
+        <v>97.85644658614729</v>
       </c>
       <c r="F427" t="n">
         <v>1047570</v>
@@ -8992,16 +8992,16 @@
         <v>45099</v>
       </c>
       <c r="B429" t="n">
-        <v>99.27084350585938</v>
+        <v>99.27083587646484</v>
       </c>
       <c r="C429" t="n">
-        <v>104.8581233756592</v>
+        <v>104.858115316858</v>
       </c>
       <c r="D429" t="n">
-        <v>99.18299454236116</v>
+        <v>99.18298691971819</v>
       </c>
       <c r="E429" t="n">
-        <v>102.9605535923553</v>
+        <v>102.9605456793905</v>
       </c>
       <c r="F429" t="n">
         <v>1144936</v>
@@ -9012,16 +9012,16 @@
         <v>45100</v>
       </c>
       <c r="B430" t="n">
-        <v>98.56803131103516</v>
+        <v>98.56803894042969</v>
       </c>
       <c r="C430" t="n">
-        <v>100.544663008736</v>
+        <v>100.5446707911264</v>
       </c>
       <c r="D430" t="n">
-        <v>97.24149664189471</v>
+        <v>97.24150416861238</v>
       </c>
       <c r="E430" t="n">
-        <v>99.71008786179617</v>
+        <v>99.71009557958853</v>
       </c>
       <c r="F430" t="n">
         <v>1883788</v>
@@ -9032,16 +9032,16 @@
         <v>45103</v>
       </c>
       <c r="B431" t="n">
-        <v>97.00430297851562</v>
+        <v>97.00429534912109</v>
       </c>
       <c r="C431" t="n">
-        <v>99.27084240484157</v>
+        <v>99.27083459718358</v>
       </c>
       <c r="D431" t="n">
-        <v>95.75683028431621</v>
+        <v>95.75682275303549</v>
       </c>
       <c r="E431" t="n">
-        <v>98.46262122570784</v>
+        <v>98.46261348161649</v>
       </c>
       <c r="F431" t="n">
         <v>757098</v>
@@ -9052,16 +9052,16 @@
         <v>45104</v>
       </c>
       <c r="B432" t="n">
-        <v>94.86954498291016</v>
+        <v>94.86952972412109</v>
       </c>
       <c r="C432" t="n">
-        <v>98.37477707017537</v>
+        <v>98.37476124760583</v>
       </c>
       <c r="D432" t="n">
-        <v>91.40824743272303</v>
+        <v>91.40823273064802</v>
       </c>
       <c r="E432" t="n">
-        <v>96.97795369874004</v>
+        <v>96.97793810083515</v>
       </c>
       <c r="F432" t="n">
         <v>1484061</v>
@@ -9092,16 +9092,16 @@
         <v>45106</v>
       </c>
       <c r="B434" t="n">
-        <v>99.08635711669922</v>
+        <v>99.08634948730469</v>
       </c>
       <c r="C434" t="n">
-        <v>99.83308334838433</v>
+        <v>99.83307566149379</v>
       </c>
       <c r="D434" t="n">
-        <v>97.4259869335896</v>
+        <v>97.4259794320393</v>
       </c>
       <c r="E434" t="n">
-        <v>97.53140300715454</v>
+        <v>97.53139549748747</v>
       </c>
       <c r="F434" t="n">
         <v>506881</v>
@@ -9112,16 +9112,16 @@
         <v>45107</v>
       </c>
       <c r="B435" t="n">
-        <v>98.43626403808594</v>
+        <v>98.43625640869141</v>
       </c>
       <c r="C435" t="n">
-        <v>101.4758836201877</v>
+        <v>101.4758757552046</v>
       </c>
       <c r="D435" t="n">
-        <v>98.40112311371848</v>
+        <v>98.40111548704759</v>
       </c>
       <c r="E435" t="n">
-        <v>100.6764426713316</v>
+        <v>100.67643486831</v>
       </c>
       <c r="F435" t="n">
         <v>851232</v>
@@ -9252,16 +9252,16 @@
         <v>45118</v>
       </c>
       <c r="B442" t="n">
-        <v>99.7100830078125</v>
+        <v>99.71009063720703</v>
       </c>
       <c r="C442" t="n">
-        <v>99.7100830078125</v>
+        <v>99.71009063720703</v>
       </c>
       <c r="D442" t="n">
-        <v>94.74654009028252</v>
+        <v>94.7465473398877</v>
       </c>
       <c r="E442" t="n">
-        <v>97.71588429673227</v>
+        <v>97.71589177353913</v>
       </c>
       <c r="F442" t="n">
         <v>867229</v>
@@ -9332,16 +9332,16 @@
         <v>45124</v>
       </c>
       <c r="B446" t="n">
-        <v>99.48167419433594</v>
+        <v>99.48168182373047</v>
       </c>
       <c r="C446" t="n">
-        <v>99.48167419433594</v>
+        <v>99.48168182373047</v>
       </c>
       <c r="D446" t="n">
-        <v>95.75682348764802</v>
+        <v>95.75683083137832</v>
       </c>
       <c r="E446" t="n">
-        <v>96.44205473012244</v>
+        <v>96.44206212640412</v>
       </c>
       <c r="F446" t="n">
         <v>395417</v>
@@ -9452,16 +9452,16 @@
         <v>45132</v>
       </c>
       <c r="B452" t="n">
-        <v>112.1584777832031</v>
+        <v>112.1584701538086</v>
       </c>
       <c r="C452" t="n">
-        <v>115.3298741884703</v>
+        <v>115.3298663433468</v>
       </c>
       <c r="D452" t="n">
-        <v>110.5859565895362</v>
+        <v>110.5859490671098</v>
       </c>
       <c r="E452" t="n">
-        <v>112.9491385358792</v>
+        <v>112.9491308527013</v>
       </c>
       <c r="F452" t="n">
         <v>603712</v>
@@ -9472,16 +9472,16 @@
         <v>45133</v>
       </c>
       <c r="B453" t="n">
-        <v>113.8891372680664</v>
+        <v>113.8891220092773</v>
       </c>
       <c r="C453" t="n">
-        <v>113.9857731418005</v>
+        <v>113.9857578700642</v>
       </c>
       <c r="D453" t="n">
-        <v>110.5508229266728</v>
+        <v>110.5508081151489</v>
       </c>
       <c r="E453" t="n">
-        <v>111.0427892027134</v>
+        <v>111.0427743252761</v>
       </c>
       <c r="F453" t="n">
         <v>810223</v>
@@ -9492,16 +9492,16 @@
         <v>45134</v>
       </c>
       <c r="B454" t="n">
-        <v>110.7440872192383</v>
+        <v>110.7440795898438</v>
       </c>
       <c r="C454" t="n">
-        <v>114.6446427257238</v>
+        <v>114.6446348276118</v>
       </c>
       <c r="D454" t="n">
-        <v>109.7074534000573</v>
+        <v>109.7074458420786</v>
       </c>
       <c r="E454" t="n">
-        <v>113.5025861325351</v>
+        <v>113.5025783131018</v>
       </c>
       <c r="F454" t="n">
         <v>678181</v>
@@ -9512,16 +9512,16 @@
         <v>45135</v>
       </c>
       <c r="B455" t="n">
-        <v>109.8919372558594</v>
+        <v>109.8919448852539</v>
       </c>
       <c r="C455" t="n">
-        <v>111.9915655959889</v>
+        <v>111.9915733711529</v>
       </c>
       <c r="D455" t="n">
-        <v>108.0558691996412</v>
+        <v>108.0558767015642</v>
       </c>
       <c r="E455" t="n">
-        <v>110.6913782045105</v>
+        <v>110.6913858894073</v>
       </c>
       <c r="F455" t="n">
         <v>651013</v>
@@ -9532,16 +9532,16 @@
         <v>45138</v>
       </c>
       <c r="B456" t="n">
-        <v>111.8246459960938</v>
+        <v>111.8246536254883</v>
       </c>
       <c r="C456" t="n">
-        <v>115.0838912728874</v>
+        <v>115.0838991246485</v>
       </c>
       <c r="D456" t="n">
-        <v>110.7792252970001</v>
+        <v>110.7792328550693</v>
       </c>
       <c r="E456" t="n">
-        <v>112.6416540419304</v>
+        <v>112.6416617270665</v>
       </c>
       <c r="F456" t="n">
         <v>524630</v>
@@ -9632,16 +9632,16 @@
         <v>45145</v>
       </c>
       <c r="B461" t="n">
-        <v>112.9930419921875</v>
+        <v>112.993049621582</v>
       </c>
       <c r="C461" t="n">
-        <v>117.7193920211075</v>
+        <v>117.7193999696295</v>
       </c>
       <c r="D461" t="n">
-        <v>111.6225795731422</v>
+        <v>111.6225871100018</v>
       </c>
       <c r="E461" t="n">
-        <v>113.3268773934542</v>
+        <v>113.3268850453896</v>
       </c>
       <c r="F461" t="n">
         <v>579696</v>
@@ -9652,16 +9652,16 @@
         <v>45146</v>
       </c>
       <c r="B462" t="n">
-        <v>113.5904388427734</v>
+        <v>113.590446472168</v>
       </c>
       <c r="C462" t="n">
-        <v>113.5904388427734</v>
+        <v>113.590446472168</v>
       </c>
       <c r="D462" t="n">
-        <v>109.3033399788109</v>
+        <v>109.3033473202589</v>
       </c>
       <c r="E462" t="n">
-        <v>111.8685670909697</v>
+        <v>111.8685746047133</v>
       </c>
       <c r="F462" t="n">
         <v>457201</v>
@@ -9672,16 +9672,16 @@
         <v>45147</v>
       </c>
       <c r="B463" t="n">
-        <v>112.4483795166016</v>
+        <v>112.4483871459961</v>
       </c>
       <c r="C463" t="n">
-        <v>114.1263233968748</v>
+        <v>114.1263311401144</v>
       </c>
       <c r="D463" t="n">
-        <v>110.612311536981</v>
+        <v>110.612319041802</v>
       </c>
       <c r="E463" t="n">
-        <v>113.7397799475038</v>
+        <v>113.7397876645173</v>
       </c>
       <c r="F463" t="n">
         <v>434571</v>
@@ -9712,16 +9712,16 @@
         <v>45149</v>
       </c>
       <c r="B465" t="n">
-        <v>109.812873840332</v>
+        <v>109.8128814697266</v>
       </c>
       <c r="C465" t="n">
-        <v>111.9915642064004</v>
+        <v>111.9915719871623</v>
       </c>
       <c r="D465" t="n">
-        <v>108.1261497067316</v>
+        <v>108.1261572189387</v>
       </c>
       <c r="E465" t="n">
-        <v>110.7353046615692</v>
+        <v>110.7353123550508</v>
       </c>
       <c r="F465" t="n">
         <v>577766</v>
@@ -9872,16 +9872,16 @@
         <v>45161</v>
       </c>
       <c r="B473" t="n">
-        <v>117.4294891357422</v>
+        <v>117.4294967651367</v>
       </c>
       <c r="C473" t="n">
-        <v>117.9390224614812</v>
+        <v>117.9390301239801</v>
       </c>
       <c r="D473" t="n">
-        <v>112.9491320795816</v>
+        <v>112.9491394178873</v>
       </c>
       <c r="E473" t="n">
-        <v>114.0296869677586</v>
+        <v>114.0296943762679</v>
       </c>
       <c r="F473" t="n">
         <v>1193312</v>
@@ -9972,16 +9972,16 @@
         <v>45168</v>
       </c>
       <c r="B478" t="n">
-        <v>112.4483795166016</v>
+        <v>112.4483871459961</v>
       </c>
       <c r="C478" t="n">
-        <v>113.8539896225157</v>
+        <v>113.853997347278</v>
       </c>
       <c r="D478" t="n">
-        <v>110.8231503718898</v>
+        <v>110.8231578910159</v>
       </c>
       <c r="E478" t="n">
-        <v>113.0721225198849</v>
+        <v>113.0721301915992</v>
       </c>
       <c r="F478" t="n">
         <v>547646</v>
@@ -9992,16 +9992,16 @@
         <v>45169</v>
       </c>
       <c r="B479" t="n">
-        <v>110.4102554321289</v>
+        <v>110.4102630615234</v>
       </c>
       <c r="C479" t="n">
-        <v>112.4395951828659</v>
+        <v>112.4396029524886</v>
       </c>
       <c r="D479" t="n">
-        <v>108.8465211910895</v>
+        <v>108.8465287124293</v>
       </c>
       <c r="E479" t="n">
-        <v>111.7455770203644</v>
+        <v>111.7455847420302</v>
       </c>
       <c r="F479" t="n">
         <v>854216</v>
@@ -10052,16 +10052,16 @@
         <v>45174</v>
       </c>
       <c r="B482" t="n">
-        <v>110.4717483520508</v>
+        <v>110.4717559814453</v>
       </c>
       <c r="C482" t="n">
-        <v>114.2053859703109</v>
+        <v>114.2053938575578</v>
       </c>
       <c r="D482" t="n">
-        <v>110.3838993956397</v>
+        <v>110.3839070189672</v>
       </c>
       <c r="E482" t="n">
-        <v>114.2053859703109</v>
+        <v>114.2053938575578</v>
       </c>
       <c r="F482" t="n">
         <v>645307</v>
@@ -10072,16 +10072,16 @@
         <v>45175</v>
       </c>
       <c r="B483" t="n">
-        <v>110.3311996459961</v>
+        <v>110.331184387207</v>
       </c>
       <c r="C483" t="n">
-        <v>113.1072726222884</v>
+        <v>113.1072569795688</v>
       </c>
       <c r="D483" t="n">
-        <v>108.3106465643086</v>
+        <v>108.3106315849618</v>
       </c>
       <c r="E483" t="n">
-        <v>110.471763357303</v>
+        <v>110.471748079074</v>
       </c>
       <c r="F483" t="n">
         <v>1014845</v>
@@ -10092,16 +10092,16 @@
         <v>45177</v>
       </c>
       <c r="B484" t="n">
-        <v>108.5126876831055</v>
+        <v>108.5126953125</v>
       </c>
       <c r="C484" t="n">
-        <v>110.7968008465816</v>
+        <v>110.7968086365694</v>
       </c>
       <c r="D484" t="n">
-        <v>106.7293276643105</v>
+        <v>106.7293351683192</v>
       </c>
       <c r="E484" t="n">
-        <v>109.8128750730466</v>
+        <v>109.8128827938557</v>
       </c>
       <c r="F484" t="n">
         <v>972821</v>
@@ -10112,16 +10112,16 @@
         <v>45180</v>
       </c>
       <c r="B485" t="n">
-        <v>110.2899703979492</v>
+        <v>110.2899627685547</v>
       </c>
       <c r="C485" t="n">
-        <v>111.0096466948071</v>
+        <v>111.0096390156284</v>
       </c>
       <c r="D485" t="n">
-        <v>106.9614829675006</v>
+        <v>106.9614755683568</v>
       </c>
       <c r="E485" t="n">
-        <v>109.7502166069767</v>
+        <v>109.7502090149201</v>
       </c>
       <c r="F485" t="n">
         <v>846938</v>
@@ -10132,16 +10132,16 @@
         <v>45181</v>
       </c>
       <c r="B486" t="n">
-        <v>112.4489898681641</v>
+        <v>112.4489974975586</v>
       </c>
       <c r="C486" t="n">
-        <v>113.6994220864307</v>
+        <v>113.6994298006641</v>
       </c>
       <c r="D486" t="n">
-        <v>109.6602562921019</v>
+        <v>109.6602637322876</v>
       </c>
       <c r="E486" t="n">
-        <v>109.7592119522533</v>
+        <v>109.7592193991528</v>
       </c>
       <c r="F486" t="n">
         <v>550963</v>
@@ -10172,16 +10172,16 @@
         <v>45183</v>
       </c>
       <c r="B488" t="n">
-        <v>112.4759826660156</v>
+        <v>112.4759750366211</v>
       </c>
       <c r="C488" t="n">
-        <v>114.2481799411909</v>
+        <v>114.2481721915859</v>
       </c>
       <c r="D488" t="n">
-        <v>110.6048297252885</v>
+        <v>110.6048222228168</v>
       </c>
       <c r="E488" t="n">
-        <v>114.2481799411909</v>
+        <v>114.2481721915859</v>
       </c>
       <c r="F488" t="n">
         <v>682177</v>
@@ -10192,16 +10192,16 @@
         <v>45184</v>
       </c>
       <c r="B489" t="n">
-        <v>114.4550857543945</v>
+        <v>114.455078125</v>
       </c>
       <c r="C489" t="n">
-        <v>117.9365090393343</v>
+        <v>117.9365011778736</v>
       </c>
       <c r="D489" t="n">
-        <v>111.6573542668349</v>
+        <v>111.6573468239327</v>
       </c>
       <c r="E489" t="n">
-        <v>113.0697133406719</v>
+        <v>113.0697058036241</v>
       </c>
       <c r="F489" t="n">
         <v>1700134</v>
@@ -10232,16 +10232,16 @@
         <v>45188</v>
       </c>
       <c r="B491" t="n">
-        <v>111.9991989135742</v>
+        <v>111.9991912841797</v>
       </c>
       <c r="C491" t="n">
-        <v>115.9573980431394</v>
+        <v>115.957390144112</v>
       </c>
       <c r="D491" t="n">
-        <v>111.2705316229361</v>
+        <v>111.2705240431784</v>
       </c>
       <c r="E491" t="n">
-        <v>115.3366911217438</v>
+        <v>115.336683264999</v>
       </c>
       <c r="F491" t="n">
         <v>598810</v>
@@ -10292,16 +10292,16 @@
         <v>45191</v>
       </c>
       <c r="B494" t="n">
-        <v>103.8129119873047</v>
+        <v>103.8129043579102</v>
       </c>
       <c r="C494" t="n">
-        <v>105.8639805269635</v>
+        <v>105.8639727468323</v>
       </c>
       <c r="D494" t="n">
-        <v>103.2011891892186</v>
+        <v>103.2011816047806</v>
       </c>
       <c r="E494" t="n">
-        <v>105.0903309039916</v>
+        <v>105.0903231807173</v>
       </c>
       <c r="F494" t="n">
         <v>394595</v>
@@ -10452,16 +10452,16 @@
         <v>45203</v>
       </c>
       <c r="B502" t="n">
-        <v>101.7978286743164</v>
+        <v>101.7978134155273</v>
       </c>
       <c r="C502" t="n">
-        <v>102.1666578060305</v>
+        <v>102.1666424919565</v>
       </c>
       <c r="D502" t="n">
-        <v>98.96411265029839</v>
+        <v>98.96409781626373</v>
       </c>
       <c r="E502" t="n">
-        <v>99.85470676184396</v>
+        <v>99.85469179431541</v>
       </c>
       <c r="F502" t="n">
         <v>483635</v>
@@ -10512,16 +10512,16 @@
         <v>45208</v>
       </c>
       <c r="B505" t="n">
-        <v>100.9612045288086</v>
+        <v>100.9611968994141</v>
       </c>
       <c r="C505" t="n">
-        <v>101.6718761081721</v>
+        <v>101.6718684250738</v>
       </c>
       <c r="D505" t="n">
-        <v>99.18900734252807</v>
+        <v>99.18899984705422</v>
       </c>
       <c r="E505" t="n">
-        <v>101.1051356675376</v>
+        <v>101.1051280272665</v>
       </c>
       <c r="F505" t="n">
         <v>728058</v>
@@ -10612,16 +10612,16 @@
         <v>45216</v>
       </c>
       <c r="B510" t="n">
-        <v>97.14693450927734</v>
+        <v>97.14692687988281</v>
       </c>
       <c r="C510" t="n">
-        <v>97.86661082758212</v>
+        <v>97.86660314166811</v>
       </c>
       <c r="D510" t="n">
-        <v>95.20381943120169</v>
+        <v>95.20381195440891</v>
       </c>
       <c r="E510" t="n">
-        <v>96.69713852617237</v>
+        <v>96.69713093210238</v>
       </c>
       <c r="F510" t="n">
         <v>593712</v>
@@ -10652,16 +10652,16 @@
         <v>45218</v>
       </c>
       <c r="B512" t="n">
-        <v>94.34918975830078</v>
+        <v>94.34920501708984</v>
       </c>
       <c r="C512" t="n">
-        <v>95.99544447357339</v>
+        <v>95.9954599986059</v>
       </c>
       <c r="D512" t="n">
-        <v>92.76591306066892</v>
+        <v>92.76592806339976</v>
       </c>
       <c r="E512" t="n">
-        <v>93.46759359810548</v>
+        <v>93.46760871431685</v>
       </c>
       <c r="F512" t="n">
         <v>760940</v>
@@ -10672,16 +10672,16 @@
         <v>45219</v>
       </c>
       <c r="B513" t="n">
-        <v>96.25633239746094</v>
+        <v>96.25632476806641</v>
       </c>
       <c r="C513" t="n">
-        <v>96.43624803043737</v>
+        <v>96.4362403867825</v>
       </c>
       <c r="D513" t="n">
-        <v>93.0627784370684</v>
+        <v>93.06277106079887</v>
       </c>
       <c r="E513" t="n">
-        <v>93.27868543264987</v>
+        <v>93.27867803926728</v>
       </c>
       <c r="F513" t="n">
         <v>605848</v>
@@ -10692,16 +10692,16 @@
         <v>45222</v>
       </c>
       <c r="B514" t="n">
-        <v>96.25633239746094</v>
+        <v>96.25632476806641</v>
       </c>
       <c r="C514" t="n">
-        <v>97.29086444542904</v>
+        <v>97.29085673403624</v>
       </c>
       <c r="D514" t="n">
-        <v>93.93538367002114</v>
+        <v>93.93537622458784</v>
       </c>
       <c r="E514" t="n">
-        <v>96.07641676448451</v>
+        <v>96.07640914935031</v>
       </c>
       <c r="F514" t="n">
         <v>469364</v>
@@ -10712,16 +10712,16 @@
         <v>45223</v>
       </c>
       <c r="B515" t="n">
-        <v>93.5125732421875</v>
+        <v>93.51258087158203</v>
       </c>
       <c r="C515" t="n">
-        <v>98.39735742833496</v>
+        <v>98.39736545626356</v>
       </c>
       <c r="D515" t="n">
-        <v>93.38663092797195</v>
+        <v>93.38663854709125</v>
       </c>
       <c r="E515" t="n">
-        <v>96.71512500416665</v>
+        <v>96.71513289484724</v>
       </c>
       <c r="F515" t="n">
         <v>956700</v>
@@ -10752,16 +10752,16 @@
         <v>45225</v>
       </c>
       <c r="B517" t="n">
-        <v>92.35211181640625</v>
+        <v>92.35210418701172</v>
       </c>
       <c r="C517" t="n">
-        <v>92.90085658530361</v>
+        <v>92.90084891057617</v>
       </c>
       <c r="D517" t="n">
-        <v>89.23951766555959</v>
+        <v>89.23951029330274</v>
       </c>
       <c r="E517" t="n">
-        <v>89.23951766555959</v>
+        <v>89.23951029330274</v>
       </c>
       <c r="F517" t="n">
         <v>731795</v>
@@ -10772,16 +10772,16 @@
         <v>45226</v>
       </c>
       <c r="B518" t="n">
-        <v>90.64289093017578</v>
+        <v>90.64288330078125</v>
       </c>
       <c r="C518" t="n">
-        <v>93.41362904617142</v>
+        <v>93.4136211835644</v>
       </c>
       <c r="D518" t="n">
-        <v>90.64289093017578</v>
+        <v>90.64288330078125</v>
       </c>
       <c r="E518" t="n">
-        <v>92.37010590560371</v>
+        <v>92.37009813082983</v>
       </c>
       <c r="F518" t="n">
         <v>492223</v>
@@ -10792,16 +10792,16 @@
         <v>45229</v>
       </c>
       <c r="B519" t="n">
-        <v>89.12256622314453</v>
+        <v>89.12257385253906</v>
       </c>
       <c r="C519" t="n">
-        <v>92.43306457692978</v>
+        <v>92.43307248972164</v>
       </c>
       <c r="D519" t="n">
-        <v>88.60979913214193</v>
+        <v>88.60980671764069</v>
       </c>
       <c r="E519" t="n">
-        <v>91.38054373697832</v>
+        <v>91.38055155966848</v>
       </c>
       <c r="F519" t="n">
         <v>688103</v>
@@ -10852,16 +10852,16 @@
         <v>45233</v>
       </c>
       <c r="B522" t="n">
-        <v>94.61007690429688</v>
+        <v>94.61006927490234</v>
       </c>
       <c r="C522" t="n">
-        <v>97.14692574562541</v>
+        <v>97.14691791165838</v>
       </c>
       <c r="D522" t="n">
-        <v>92.08222590355452</v>
+        <v>92.08221847800689</v>
       </c>
       <c r="E522" t="n">
-        <v>92.70294650051345</v>
+        <v>92.70293902491068</v>
       </c>
       <c r="F522" t="n">
         <v>760712</v>
@@ -10872,16 +10872,16 @@
         <v>45236</v>
       </c>
       <c r="B523" t="n">
-        <v>92.21717071533203</v>
+        <v>92.2171630859375</v>
       </c>
       <c r="C523" t="n">
-        <v>95.98645623697459</v>
+        <v>95.9864482957361</v>
       </c>
       <c r="D523" t="n">
-        <v>91.38954092314988</v>
+        <v>91.38953336222757</v>
       </c>
       <c r="E523" t="n">
-        <v>95.13184664835444</v>
+        <v>95.13183877782029</v>
       </c>
       <c r="F523" t="n">
         <v>393989</v>
@@ -10892,16 +10892,16 @@
         <v>45237</v>
       </c>
       <c r="B524" t="n">
-        <v>97.12894439697266</v>
+        <v>97.12893676757812</v>
       </c>
       <c r="C524" t="n">
-        <v>97.12894439697266</v>
+        <v>97.12893676757812</v>
       </c>
       <c r="D524" t="n">
-        <v>91.57846368653991</v>
+        <v>91.57845649313083</v>
       </c>
       <c r="E524" t="n">
-        <v>92.02825966365781</v>
+        <v>92.02825243491765</v>
       </c>
       <c r="F524" t="n">
         <v>722184</v>
@@ -10912,16 +10912,16 @@
         <v>45238</v>
       </c>
       <c r="B525" t="n">
-        <v>96.40926361083984</v>
+        <v>96.40927124023438</v>
       </c>
       <c r="C525" t="n">
-        <v>98.50531441406719</v>
+        <v>98.50532220933374</v>
       </c>
       <c r="D525" t="n">
-        <v>95.54565619848189</v>
+        <v>95.54566375953443</v>
       </c>
       <c r="E525" t="n">
-        <v>97.11094420442183</v>
+        <v>97.11095188934421</v>
       </c>
       <c r="F525" t="n">
         <v>449324</v>
@@ -10932,16 +10932,16 @@
         <v>45239</v>
       </c>
       <c r="B526" t="n">
-        <v>95.28478240966797</v>
+        <v>95.28476715087891</v>
       </c>
       <c r="C526" t="n">
-        <v>97.73167373282809</v>
+        <v>97.73165808219684</v>
       </c>
       <c r="D526" t="n">
-        <v>94.73603074395886</v>
+        <v>94.73601557304625</v>
       </c>
       <c r="E526" t="n">
-        <v>97.21890657049985</v>
+        <v>97.2188910019825</v>
       </c>
       <c r="F526" t="n">
         <v>493995</v>
@@ -10952,16 +10952,16 @@
         <v>45240</v>
       </c>
       <c r="B527" t="n">
-        <v>98.95510864257812</v>
+        <v>98.95511627197266</v>
       </c>
       <c r="C527" t="n">
-        <v>99.84570269862571</v>
+        <v>99.84571039668464</v>
       </c>
       <c r="D527" t="n">
-        <v>95.04188526438084</v>
+        <v>95.0418925920676</v>
       </c>
       <c r="E527" t="n">
-        <v>95.04188526438084</v>
+        <v>95.0418925920676</v>
       </c>
       <c r="F527" t="n">
         <v>655787</v>
@@ -10972,16 +10972,16 @@
         <v>45243</v>
       </c>
       <c r="B528" t="n">
-        <v>98.83816528320312</v>
+        <v>98.83815765380859</v>
       </c>
       <c r="C528" t="n">
-        <v>100.3134954614712</v>
+        <v>100.3134877181948</v>
       </c>
       <c r="D528" t="n">
-        <v>96.80508565184681</v>
+        <v>96.80507817938725</v>
       </c>
       <c r="E528" t="n">
-        <v>98.9551097602987</v>
+        <v>98.95510212187712</v>
       </c>
       <c r="F528" t="n">
         <v>702632</v>
@@ -11012,16 +11012,16 @@
         <v>45246</v>
       </c>
       <c r="B530" t="n">
-        <v>101.6538925170898</v>
+        <v>101.6538848876953</v>
       </c>
       <c r="C530" t="n">
-        <v>103.6599856282268</v>
+        <v>103.6599778482697</v>
       </c>
       <c r="D530" t="n">
-        <v>99.45888591602659</v>
+        <v>99.45887845137312</v>
       </c>
       <c r="E530" t="n">
-        <v>100.4214490485131</v>
+        <v>100.4214415116168</v>
       </c>
       <c r="F530" t="n">
         <v>1796629</v>
@@ -11052,16 +11052,16 @@
         <v>45250</v>
       </c>
       <c r="B532" t="n">
-        <v>102.5534744262695</v>
+        <v>102.5534820556641</v>
       </c>
       <c r="C532" t="n">
-        <v>104.5685583178221</v>
+        <v>104.5685660971273</v>
       </c>
       <c r="D532" t="n">
-        <v>100.9881864751831</v>
+        <v>100.9881939881291</v>
       </c>
       <c r="E532" t="n">
-        <v>103.6329819380516</v>
+        <v>103.6329896477554</v>
       </c>
       <c r="F532" t="n">
         <v>946377</v>
@@ -11072,16 +11072,16 @@
         <v>45251</v>
       </c>
       <c r="B533" t="n">
-        <v>100.2595062255859</v>
+        <v>100.259521484375</v>
       </c>
       <c r="C533" t="n">
-        <v>103.0932218491147</v>
+        <v>103.0932375391752</v>
       </c>
       <c r="D533" t="n">
-        <v>99.13501644349843</v>
+        <v>99.13503153114809</v>
       </c>
       <c r="E533" t="n">
-        <v>102.5804547830164</v>
+        <v>102.5804703950374</v>
       </c>
       <c r="F533" t="n">
         <v>1091156</v>
@@ -11092,16 +11092,16 @@
         <v>45252</v>
       </c>
       <c r="B534" t="n">
-        <v>102.9403076171875</v>
+        <v>102.940299987793</v>
       </c>
       <c r="C534" t="n">
-        <v>103.5700192399348</v>
+        <v>103.5700115638693</v>
       </c>
       <c r="D534" t="n">
-        <v>100.2775162557474</v>
+        <v>100.277508823705</v>
       </c>
       <c r="E534" t="n">
-        <v>100.3045029162449</v>
+        <v>100.3044954822023</v>
       </c>
       <c r="F534" t="n">
         <v>622704</v>
@@ -11112,16 +11112,16 @@
         <v>45253</v>
       </c>
       <c r="B535" t="n">
-        <v>103.4440765380859</v>
+        <v>103.4440689086914</v>
       </c>
       <c r="C535" t="n">
-        <v>104.5955531373908</v>
+        <v>104.5955454230704</v>
       </c>
       <c r="D535" t="n">
-        <v>101.9327617856629</v>
+        <v>101.9327542677336</v>
       </c>
       <c r="E535" t="n">
-        <v>102.8683382384335</v>
+        <v>102.8683306515019</v>
       </c>
       <c r="F535" t="n">
         <v>270469</v>
@@ -11132,16 +11132,16 @@
         <v>45254</v>
       </c>
       <c r="B536" t="n">
-        <v>103.5430297851562</v>
+        <v>103.5430221557617</v>
       </c>
       <c r="C536" t="n">
-        <v>104.3526638949405</v>
+        <v>104.3526562058894</v>
       </c>
       <c r="D536" t="n">
-        <v>100.9522074971883</v>
+        <v>100.9522000586942</v>
       </c>
       <c r="E536" t="n">
-        <v>103.2731563241227</v>
+        <v>103.2731487146133</v>
       </c>
       <c r="F536" t="n">
         <v>447021</v>
@@ -11172,16 +11172,16 @@
         <v>45258</v>
       </c>
       <c r="B538" t="n">
-        <v>102.9852905273438</v>
+        <v>102.9852828979492</v>
       </c>
       <c r="C538" t="n">
-        <v>105.450170574253</v>
+        <v>105.4501627622543</v>
       </c>
       <c r="D538" t="n">
-        <v>101.8338070541564</v>
+        <v>101.8337995100664</v>
       </c>
       <c r="E538" t="n">
-        <v>102.0946895459716</v>
+        <v>102.0946819825549</v>
       </c>
       <c r="F538" t="n">
         <v>492581</v>
@@ -11212,16 +11212,16 @@
         <v>45260</v>
       </c>
       <c r="B540" t="n">
-        <v>103.2731552124023</v>
+        <v>103.2731475830078</v>
       </c>
       <c r="C540" t="n">
-        <v>103.5250398519922</v>
+        <v>103.5250322039895</v>
       </c>
       <c r="D540" t="n">
-        <v>101.2310777095213</v>
+        <v>101.231070230987</v>
       </c>
       <c r="E540" t="n">
-        <v>102.643436750086</v>
+        <v>102.6434291672124</v>
       </c>
       <c r="F540" t="n">
         <v>702061</v>
@@ -11272,16 +11272,16 @@
         <v>45265</v>
       </c>
       <c r="B543" t="n">
-        <v>106.1338500976562</v>
+        <v>106.1338577270508</v>
       </c>
       <c r="C543" t="n">
-        <v>107.82508031465</v>
+        <v>107.825088065618</v>
       </c>
       <c r="D543" t="n">
-        <v>103.0212562388862</v>
+        <v>103.021263644533</v>
       </c>
       <c r="E543" t="n">
-        <v>103.4260766917358</v>
+        <v>103.426084126483</v>
       </c>
       <c r="F543" t="n">
         <v>1056803</v>
@@ -11292,16 +11292,16 @@
         <v>45266</v>
       </c>
       <c r="B544" t="n">
-        <v>104.0737915039062</v>
+        <v>104.0737838745117</v>
       </c>
       <c r="C544" t="n">
-        <v>106.4217269660424</v>
+        <v>106.4217191645265</v>
       </c>
       <c r="D544" t="n">
-        <v>102.9043192616387</v>
+        <v>102.9043117179754</v>
       </c>
       <c r="E544" t="n">
-        <v>106.1608444854338</v>
+        <v>106.1608367030425</v>
       </c>
       <c r="F544" t="n">
         <v>811001</v>
@@ -11312,16 +11312,16 @@
         <v>45267</v>
       </c>
       <c r="B545" t="n">
-        <v>106.6016387939453</v>
+        <v>106.6016464233398</v>
       </c>
       <c r="C545" t="n">
-        <v>107.0514347382236</v>
+        <v>107.0514423998096</v>
       </c>
       <c r="D545" t="n">
-        <v>103.6959539740376</v>
+        <v>103.6959613954746</v>
       </c>
       <c r="E545" t="n">
-        <v>105.4231756162056</v>
+        <v>105.4231831612584</v>
       </c>
       <c r="F545" t="n">
         <v>599154</v>
@@ -11352,16 +11352,16 @@
         <v>45271</v>
       </c>
       <c r="B547" t="n">
-        <v>103.1921920776367</v>
+        <v>103.1921844482422</v>
       </c>
       <c r="C547" t="n">
-        <v>106.4127329157239</v>
+        <v>106.4127250482224</v>
       </c>
       <c r="D547" t="n">
-        <v>103.1921920776367</v>
+        <v>103.1921844482422</v>
       </c>
       <c r="E547" t="n">
-        <v>105.3782007973801</v>
+        <v>105.3781930063656</v>
       </c>
       <c r="F547" t="n">
         <v>558243</v>
@@ -11452,16 +11452,16 @@
         <v>45278</v>
       </c>
       <c r="B552" t="n">
-        <v>118.3415603637695</v>
+        <v>118.341552734375</v>
       </c>
       <c r="C552" t="n">
-        <v>120.671449565237</v>
+        <v>120.6714417856362</v>
       </c>
       <c r="D552" t="n">
-        <v>114.5543387135227</v>
+        <v>114.5543313282876</v>
       </c>
       <c r="E552" t="n">
-        <v>114.804960915804</v>
+        <v>114.8049535144115</v>
       </c>
       <c r="F552" t="n">
         <v>1013443</v>
@@ -11632,16 +11632,16 @@
         <v>45294</v>
       </c>
       <c r="B561" t="n">
-        <v>113.2455139160156</v>
+        <v>113.2455062866211</v>
       </c>
       <c r="C561" t="n">
-        <v>116.2437384250845</v>
+        <v>116.2437305936984</v>
       </c>
       <c r="D561" t="n">
-        <v>113.2455139160156</v>
+        <v>113.2455062866211</v>
       </c>
       <c r="E561" t="n">
-        <v>115.7517642600759</v>
+        <v>115.7517564618344</v>
       </c>
       <c r="F561" t="n">
         <v>798887</v>
@@ -11672,16 +11672,16 @@
         <v>45296</v>
       </c>
       <c r="B563" t="n">
-        <v>115.6310958862305</v>
+        <v>115.6310882568359</v>
       </c>
       <c r="C563" t="n">
-        <v>115.6310958862305</v>
+        <v>115.6310882568359</v>
       </c>
       <c r="D563" t="n">
-        <v>109.7181922963609</v>
+        <v>109.7181850571025</v>
       </c>
       <c r="E563" t="n">
-        <v>110.182313257144</v>
+        <v>110.1823059872627</v>
       </c>
       <c r="F563" t="n">
         <v>1732820</v>
@@ -11712,16 +11712,16 @@
         <v>45300</v>
       </c>
       <c r="B565" t="n">
-        <v>114.0345077514648</v>
+        <v>114.0345153808594</v>
       </c>
       <c r="C565" t="n">
-        <v>117.79389000735</v>
+        <v>117.7938978882632</v>
       </c>
       <c r="D565" t="n">
-        <v>113.3847413012264</v>
+        <v>113.3847488871488</v>
       </c>
       <c r="E565" t="n">
-        <v>117.79389000735</v>
+        <v>117.7938978882632</v>
       </c>
       <c r="F565" t="n">
         <v>842892</v>
@@ -11772,16 +11772,16 @@
         <v>45303</v>
       </c>
       <c r="B568" t="n">
-        <v>116.6800079345703</v>
+        <v>116.6800003051758</v>
       </c>
       <c r="C568" t="n">
-        <v>117.7010797245651</v>
+        <v>117.7010720284054</v>
       </c>
       <c r="D568" t="n">
-        <v>112.8649330302776</v>
+        <v>112.8649256503406</v>
       </c>
       <c r="E568" t="n">
-        <v>114.6378785184286</v>
+        <v>114.6378710225635</v>
       </c>
       <c r="F568" t="n">
         <v>693991</v>
@@ -11792,16 +11792,16 @@
         <v>45306</v>
       </c>
       <c r="B569" t="n">
-        <v>118.2580108642578</v>
+        <v>118.2580261230469</v>
       </c>
       <c r="C569" t="n">
-        <v>120.5786083633369</v>
+        <v>120.5786239215518</v>
       </c>
       <c r="D569" t="n">
-        <v>115.6589309007661</v>
+        <v>115.6589458241968</v>
       </c>
       <c r="E569" t="n">
-        <v>116.6707181806831</v>
+        <v>116.6707332346643</v>
       </c>
       <c r="F569" t="n">
         <v>875695</v>
@@ -11832,16 +11832,16 @@
         <v>45308</v>
       </c>
       <c r="B571" t="n">
-        <v>115.8167419433594</v>
+        <v>115.8167343139648</v>
       </c>
       <c r="C571" t="n">
-        <v>117.292650287693</v>
+        <v>117.2926425610734</v>
       </c>
       <c r="D571" t="n">
-        <v>114.0530879502235</v>
+        <v>114.0530804370092</v>
       </c>
       <c r="E571" t="n">
-        <v>116.5686227188185</v>
+        <v>116.568615039894</v>
       </c>
       <c r="F571" t="n">
         <v>474098</v>
@@ -11892,16 +11892,16 @@
         <v>45313</v>
       </c>
       <c r="B574" t="n">
-        <v>116.9677581787109</v>
+        <v>116.9677658081055</v>
       </c>
       <c r="C574" t="n">
-        <v>118.313706036235</v>
+        <v>118.313713753421</v>
       </c>
       <c r="D574" t="n">
-        <v>114.8792140041177</v>
+        <v>114.8792214972839</v>
       </c>
       <c r="E574" t="n">
-        <v>115.7331948114009</v>
+        <v>115.7332023602692</v>
       </c>
       <c r="F574" t="n">
         <v>856226</v>
@@ -11912,16 +11912,16 @@
         <v>45314</v>
       </c>
       <c r="B575" t="n">
-        <v>115.844596862793</v>
+        <v>115.8445816040039</v>
       </c>
       <c r="C575" t="n">
-        <v>119.5111496904288</v>
+        <v>119.5111339486896</v>
       </c>
       <c r="D575" t="n">
-        <v>115.352622686125</v>
+        <v>115.3526074921376</v>
       </c>
       <c r="E575" t="n">
-        <v>117.0605915371168</v>
+        <v>117.0605761181597</v>
       </c>
       <c r="F575" t="n">
         <v>383026</v>
@@ -11992,16 +11992,16 @@
         <v>45320</v>
       </c>
       <c r="B579" t="n">
-        <v>120.5507659912109</v>
+        <v>120.5507736206055</v>
       </c>
       <c r="C579" t="n">
-        <v>120.9963322825921</v>
+        <v>120.9963399401855</v>
       </c>
       <c r="D579" t="n">
-        <v>115.668218899895</v>
+        <v>115.6682262202838</v>
       </c>
       <c r="E579" t="n">
-        <v>116.9213439962301</v>
+        <v>116.9213513959265</v>
       </c>
       <c r="F579" t="n">
         <v>917694</v>
@@ -12032,16 +12032,16 @@
         <v>45322</v>
       </c>
       <c r="B581" t="n">
-        <v>112.725700378418</v>
+        <v>112.7256927490234</v>
       </c>
       <c r="C581" t="n">
-        <v>117.5618399037895</v>
+        <v>117.5618319470799</v>
       </c>
       <c r="D581" t="n">
-        <v>112.25229501902</v>
+        <v>112.252287421666</v>
       </c>
       <c r="E581" t="n">
-        <v>115.1205591358914</v>
+        <v>115.1205513444103</v>
       </c>
       <c r="F581" t="n">
         <v>967870</v>
@@ -12072,16 +12072,16 @@
         <v>45324</v>
       </c>
       <c r="B583" t="n">
-        <v>119.7432022094727</v>
+        <v>119.7431945800781</v>
       </c>
       <c r="C583" t="n">
-        <v>120.7642739403636</v>
+        <v>120.7642662459118</v>
       </c>
       <c r="D583" t="n">
-        <v>114.2758581170049</v>
+        <v>114.2758508359602</v>
       </c>
       <c r="E583" t="n">
-        <v>114.7492634575158</v>
+        <v>114.7492561463083</v>
       </c>
       <c r="F583" t="n">
         <v>1061152</v>
@@ -12112,16 +12112,16 @@
         <v>45328</v>
       </c>
       <c r="B585" t="n">
-        <v>115.9374160766602</v>
+        <v>115.9374084472656</v>
       </c>
       <c r="C585" t="n">
-        <v>119.5946843895468</v>
+        <v>119.5946765194815</v>
       </c>
       <c r="D585" t="n">
-        <v>115.1205586627154</v>
+        <v>115.1205510870751</v>
       </c>
       <c r="E585" t="n">
-        <v>117.8867226729782</v>
+        <v>117.8867149153073</v>
       </c>
       <c r="F585" t="n">
         <v>714734</v>
@@ -12132,16 +12132,16 @@
         <v>45329</v>
       </c>
       <c r="B586" t="n">
-        <v>114.9070663452148</v>
+        <v>114.9070587158203</v>
       </c>
       <c r="C586" t="n">
-        <v>116.3179909256947</v>
+        <v>116.3179832026201</v>
       </c>
       <c r="D586" t="n">
-        <v>111.816019099874</v>
+        <v>111.8160116757133</v>
       </c>
       <c r="E586" t="n">
-        <v>115.101996295562</v>
+        <v>115.1019886532248</v>
       </c>
       <c r="F586" t="n">
         <v>998662</v>
@@ -12152,16 +12152,16 @@
         <v>45330</v>
       </c>
       <c r="B587" t="n">
-        <v>114.4058074951172</v>
+        <v>114.4058151245117</v>
       </c>
       <c r="C587" t="n">
-        <v>115.4361565105115</v>
+        <v>115.436164208617</v>
       </c>
       <c r="D587" t="n">
-        <v>113.0412908486803</v>
+        <v>113.0412983870791</v>
       </c>
       <c r="E587" t="n">
-        <v>115.1019888794688</v>
+        <v>115.1019965552897</v>
       </c>
       <c r="F587" t="n">
         <v>662990</v>
@@ -12172,16 +12172,16 @@
         <v>45331</v>
       </c>
       <c r="B588" t="n">
-        <v>114.2201690673828</v>
+        <v>114.2201614379883</v>
       </c>
       <c r="C588" t="n">
-        <v>115.8445923986349</v>
+        <v>115.8445846607362</v>
       </c>
       <c r="D588" t="n">
-        <v>113.5611110837534</v>
+        <v>113.561103498381</v>
       </c>
       <c r="E588" t="n">
-        <v>114.9070660930879</v>
+        <v>114.9070584178118</v>
       </c>
       <c r="F588" t="n">
         <v>354486</v>
@@ -12212,16 +12212,16 @@
         <v>45337</v>
       </c>
       <c r="B590" t="n">
-        <v>115.7517547607422</v>
+        <v>115.7517623901367</v>
       </c>
       <c r="C590" t="n">
-        <v>116.4015282987129</v>
+        <v>116.4015359709352</v>
       </c>
       <c r="D590" t="n">
-        <v>114.4986296915515</v>
+        <v>114.4986372383505</v>
       </c>
       <c r="E590" t="n">
-        <v>115.6589319930101</v>
+        <v>115.6589396162866</v>
       </c>
       <c r="F590" t="n">
         <v>464925</v>
@@ -12352,16 +12352,16 @@
         <v>45348</v>
       </c>
       <c r="B597" t="n">
-        <v>111.2776336669922</v>
+        <v>111.2776260375977</v>
       </c>
       <c r="C597" t="n">
-        <v>113.0227329282103</v>
+        <v>113.0227251791686</v>
       </c>
       <c r="D597" t="n">
-        <v>110.5164756111173</v>
+        <v>110.5164680339092</v>
       </c>
       <c r="E597" t="n">
-        <v>111.6675006376001</v>
+        <v>111.6674929814756</v>
       </c>
       <c r="F597" t="n">
         <v>306480</v>
@@ -12372,16 +12372,16 @@
         <v>45349</v>
       </c>
       <c r="B598" t="n">
-        <v>112.9763259887695</v>
+        <v>112.976318359375</v>
       </c>
       <c r="C598" t="n">
-        <v>113.941698458945</v>
+        <v>113.941690764358</v>
       </c>
       <c r="D598" t="n">
-        <v>107.7039114713027</v>
+        <v>107.7039041979591</v>
       </c>
       <c r="E598" t="n">
-        <v>111.8717158108134</v>
+        <v>111.8717082560142</v>
       </c>
       <c r="F598" t="n">
         <v>631455</v>
@@ -12392,16 +12392,16 @@
         <v>45350</v>
       </c>
       <c r="B599" t="n">
-        <v>110.5072021484375</v>
+        <v>110.507194519043</v>
       </c>
       <c r="C599" t="n">
-        <v>112.8556530461457</v>
+        <v>112.8556452546146</v>
       </c>
       <c r="D599" t="n">
-        <v>103.03485194489</v>
+        <v>103.0348448313849</v>
       </c>
       <c r="E599" t="n">
-        <v>112.8556530461457</v>
+        <v>112.8556452546146</v>
       </c>
       <c r="F599" t="n">
         <v>1284448</v>
@@ -12512,16 +12512,16 @@
         <v>45358</v>
       </c>
       <c r="B605" t="n">
-        <v>114.6378784179688</v>
+        <v>114.6378707885742</v>
       </c>
       <c r="C605" t="n">
-        <v>115.4640131695686</v>
+        <v>115.4640054851931</v>
       </c>
       <c r="D605" t="n">
-        <v>111.8531526264392</v>
+        <v>111.853145182374</v>
       </c>
       <c r="E605" t="n">
-        <v>114.5543400435463</v>
+        <v>114.5543324197115</v>
       </c>
       <c r="F605" t="n">
         <v>408472</v>
@@ -12552,16 +12552,16 @@
         <v>45362</v>
       </c>
       <c r="B607" t="n">
-        <v>116.9120635986328</v>
+        <v>116.9120559692383</v>
       </c>
       <c r="C607" t="n">
-        <v>117.9052821409343</v>
+        <v>117.9052744467247</v>
       </c>
       <c r="D607" t="n">
-        <v>116.1044976840983</v>
+        <v>116.1044901074035</v>
       </c>
       <c r="E607" t="n">
-        <v>116.1230594059132</v>
+        <v>116.1230518280071</v>
       </c>
       <c r="F607" t="n">
         <v>387232</v>
@@ -12572,16 +12572,16 @@
         <v>45363</v>
       </c>
       <c r="B608" t="n">
-        <v>118.4715042114258</v>
+        <v>118.4715118408203</v>
       </c>
       <c r="C608" t="n">
-        <v>119.4368765807375</v>
+        <v>119.4368842723006</v>
       </c>
       <c r="D608" t="n">
-        <v>117.3854629516713</v>
+        <v>117.3854705111263</v>
       </c>
       <c r="E608" t="n">
-        <v>117.5154162435091</v>
+        <v>117.5154238113329</v>
       </c>
       <c r="F608" t="n">
         <v>411262</v>
@@ -12652,16 +12652,16 @@
         <v>45369</v>
       </c>
       <c r="B612" t="n">
-        <v>117.88671875</v>
+        <v>117.8867263793945</v>
       </c>
       <c r="C612" t="n">
-        <v>119.5946804097318</v>
+        <v>119.5946881496622</v>
       </c>
       <c r="D612" t="n">
-        <v>116.364402633483</v>
+        <v>116.3644101643563</v>
       </c>
       <c r="E612" t="n">
-        <v>118.8799443601623</v>
+        <v>118.8799520538364</v>
       </c>
       <c r="F612" t="n">
         <v>649560</v>
@@ -12692,16 +12692,16 @@
         <v>45371</v>
       </c>
       <c r="B614" t="n">
-        <v>118.1744689941406</v>
+        <v>118.1744766235352</v>
       </c>
       <c r="C614" t="n">
-        <v>119.5854005879789</v>
+        <v>119.5854083084638</v>
       </c>
       <c r="D614" t="n">
-        <v>115.1019907020985</v>
+        <v>115.1019981331325</v>
       </c>
       <c r="E614" t="n">
-        <v>115.9374097929339</v>
+        <v>115.9374172779029</v>
       </c>
       <c r="F614" t="n">
         <v>596704</v>
@@ -12792,16 +12792,16 @@
         <v>45378</v>
       </c>
       <c r="B619" t="n">
-        <v>116.8099517822266</v>
+        <v>116.8099594116211</v>
       </c>
       <c r="C619" t="n">
-        <v>118.6571581750073</v>
+        <v>118.6571659250514</v>
       </c>
       <c r="D619" t="n">
-        <v>116.7821056596489</v>
+        <v>116.7821132872247</v>
       </c>
       <c r="E619" t="n">
-        <v>116.9399121574611</v>
+        <v>116.9399197953439</v>
       </c>
       <c r="F619" t="n">
         <v>350637</v>
@@ -12812,16 +12812,16 @@
         <v>45379</v>
       </c>
       <c r="B620" t="n">
-        <v>118.9077911376953</v>
+        <v>118.9077835083008</v>
       </c>
       <c r="C620" t="n">
-        <v>120.5693378798037</v>
+        <v>120.5693301438005</v>
       </c>
       <c r="D620" t="n">
-        <v>116.5964637449893</v>
+        <v>116.5964562638948</v>
       </c>
       <c r="E620" t="n">
-        <v>117.0698690892924</v>
+        <v>117.0698615778232</v>
       </c>
       <c r="F620" t="n">
         <v>712173</v>
@@ -12992,16 +12992,16 @@
         <v>45393</v>
       </c>
       <c r="B629" t="n">
-        <v>113.9509735107422</v>
+        <v>113.9509811401367</v>
       </c>
       <c r="C629" t="n">
-        <v>114.4522249684666</v>
+        <v>114.4522326314215</v>
       </c>
       <c r="D629" t="n">
-        <v>112.3915268917964</v>
+        <v>112.3915344167808</v>
       </c>
       <c r="E629" t="n">
-        <v>114.025227477798</v>
+        <v>114.025235112164</v>
       </c>
       <c r="F629" t="n">
         <v>445667</v>
@@ -13132,16 +13132,16 @@
         <v>45404</v>
       </c>
       <c r="B636" t="n">
-        <v>100.9463043212891</v>
+        <v>100.9462966918945</v>
       </c>
       <c r="C636" t="n">
-        <v>102.5243126825076</v>
+        <v>102.5243049338492</v>
       </c>
       <c r="D636" t="n">
-        <v>100.4357684551706</v>
+        <v>100.4357608643617</v>
       </c>
       <c r="E636" t="n">
-        <v>101.1783647909932</v>
+        <v>101.1783571440598</v>
       </c>
       <c r="F636" t="n">
         <v>363945</v>
@@ -13232,16 +13232,16 @@
         <v>45412</v>
       </c>
       <c r="B641" t="n">
-        <v>98.46790313720703</v>
+        <v>98.4678955078125</v>
       </c>
       <c r="C641" t="n">
-        <v>100.482186374569</v>
+        <v>100.4821785891058</v>
       </c>
       <c r="D641" t="n">
-        <v>96.7692187487189</v>
+        <v>96.76921125094019</v>
       </c>
       <c r="E641" t="n">
-        <v>99.3125995894876</v>
+        <v>99.31259189464512</v>
       </c>
       <c r="F641" t="n">
         <v>1108924</v>
@@ -13392,16 +13392,16 @@
         <v>45425</v>
       </c>
       <c r="B649" t="n">
-        <v>103.5732269287109</v>
+        <v>103.5732345581055</v>
       </c>
       <c r="C649" t="n">
-        <v>105.0955429903668</v>
+        <v>105.0955507318979</v>
       </c>
       <c r="D649" t="n">
-        <v>102.8027844964798</v>
+        <v>102.8027920691221</v>
       </c>
       <c r="E649" t="n">
-        <v>102.8027844964798</v>
+        <v>102.8027920691221</v>
       </c>
       <c r="F649" t="n">
         <v>135742</v>
@@ -13452,16 +13452,16 @@
         <v>45428</v>
       </c>
       <c r="B652" t="n">
-        <v>104.6407089233398</v>
+        <v>104.6407012939453</v>
       </c>
       <c r="C652" t="n">
-        <v>104.9377460379014</v>
+        <v>104.9377383868498</v>
       </c>
       <c r="D652" t="n">
-        <v>103.3226000881697</v>
+        <v>103.322592554879</v>
       </c>
       <c r="E652" t="n">
-        <v>104.1487347843541</v>
+        <v>104.1487271908296</v>
       </c>
       <c r="F652" t="n">
         <v>283646</v>
@@ -13492,16 +13492,16 @@
         <v>45432</v>
       </c>
       <c r="B654" t="n">
-        <v>102.5243148803711</v>
+        <v>102.5243072509766</v>
       </c>
       <c r="C654" t="n">
-        <v>103.3504496036741</v>
+        <v>103.3504419128024</v>
       </c>
       <c r="D654" t="n">
-        <v>101.2340592077103</v>
+        <v>101.2340516743307</v>
       </c>
       <c r="E654" t="n">
-        <v>103.0162890355063</v>
+        <v>103.0162813695012</v>
       </c>
       <c r="F654" t="n">
         <v>409635</v>
@@ -13552,16 +13552,16 @@
         <v>45435</v>
       </c>
       <c r="B657" t="n">
-        <v>88.36862945556641</v>
+        <v>88.36862182617188</v>
       </c>
       <c r="C657" t="n">
-        <v>90.96770970858115</v>
+        <v>90.96770185479242</v>
       </c>
       <c r="D657" t="n">
-        <v>87.70957853097796</v>
+        <v>87.70957095848325</v>
       </c>
       <c r="E657" t="n">
-        <v>88.18298390117562</v>
+        <v>88.18297628780898</v>
       </c>
       <c r="F657" t="n">
         <v>1960163</v>
@@ -13572,16 +13572,16 @@
         <v>45436</v>
       </c>
       <c r="B658" t="n">
-        <v>90.03945922851562</v>
+        <v>90.03946685791016</v>
       </c>
       <c r="C658" t="n">
-        <v>91.0605238446193</v>
+        <v>91.06053156053261</v>
       </c>
       <c r="D658" t="n">
-        <v>88.15512941075855</v>
+        <v>88.15513688048645</v>
       </c>
       <c r="E658" t="n">
-        <v>89.29686291757299</v>
+        <v>89.29687048404443</v>
       </c>
       <c r="F658" t="n">
         <v>574555</v>
@@ -13592,16 +13592,16 @@
         <v>45439</v>
       </c>
       <c r="B659" t="n">
-        <v>90.40148162841797</v>
+        <v>90.40147399902344</v>
       </c>
       <c r="C659" t="n">
-        <v>90.78206422170325</v>
+        <v>90.78205656018962</v>
       </c>
       <c r="D659" t="n">
-        <v>89.2040486805122</v>
+        <v>89.20404115217451</v>
       </c>
       <c r="E659" t="n">
-        <v>90.08588276933413</v>
+        <v>90.08587516657443</v>
       </c>
       <c r="F659" t="n">
         <v>176378</v>
@@ -13612,16 +13612,16 @@
         <v>45440</v>
       </c>
       <c r="B660" t="n">
-        <v>90.68923187255859</v>
+        <v>90.68922424316406</v>
       </c>
       <c r="C660" t="n">
-        <v>92.44360851780684</v>
+        <v>92.44360074082222</v>
       </c>
       <c r="D660" t="n">
-        <v>90.07659589389471</v>
+        <v>90.07658831603928</v>
       </c>
       <c r="E660" t="n">
-        <v>90.96770727863003</v>
+        <v>90.96769962580825</v>
       </c>
       <c r="F660" t="n">
         <v>449350</v>
@@ -13632,16 +13632,16 @@
         <v>45441</v>
       </c>
       <c r="B661" t="n">
-        <v>88.13655853271484</v>
+        <v>88.13656616210938</v>
       </c>
       <c r="C661" t="n">
-        <v>90.68922355383208</v>
+        <v>90.68923140419381</v>
       </c>
       <c r="D661" t="n">
-        <v>87.62602977764526</v>
+        <v>87.62603736284672</v>
       </c>
       <c r="E661" t="n">
-        <v>90.68922355383208</v>
+        <v>90.68923140419381</v>
       </c>
       <c r="F661" t="n">
         <v>430434</v>
@@ -13672,16 +13672,16 @@
         <v>45446</v>
       </c>
       <c r="B663" t="n">
-        <v>92.434326171875</v>
+        <v>92.43431854248047</v>
       </c>
       <c r="C663" t="n">
-        <v>93.60390581716601</v>
+        <v>93.60389809123609</v>
       </c>
       <c r="D663" t="n">
-        <v>90.53142752500605</v>
+        <v>90.53142005267401</v>
       </c>
       <c r="E663" t="n">
-        <v>92.64781783392128</v>
+        <v>92.64781018690546</v>
       </c>
       <c r="F663" t="n">
         <v>373105</v>
@@ -13712,16 +13712,16 @@
         <v>45448</v>
       </c>
       <c r="B665" t="n">
-        <v>92.92629241943359</v>
+        <v>92.92630004882812</v>
       </c>
       <c r="C665" t="n">
-        <v>93.79884202699066</v>
+        <v>93.79884972802287</v>
       </c>
       <c r="D665" t="n">
-        <v>92.39719484679063</v>
+        <v>92.39720243274542</v>
       </c>
       <c r="E665" t="n">
-        <v>93.18619900502337</v>
+        <v>93.18620665575664</v>
       </c>
       <c r="F665" t="n">
         <v>402887</v>
@@ -13792,16 +13792,16 @@
         <v>45454</v>
       </c>
       <c r="B669" t="n">
-        <v>92.84275817871094</v>
+        <v>92.84275054931641</v>
       </c>
       <c r="C669" t="n">
-        <v>93.01912641819206</v>
+        <v>93.01911877430439</v>
       </c>
       <c r="D669" t="n">
-        <v>91.69174012560192</v>
+        <v>91.69173259079281</v>
       </c>
       <c r="E669" t="n">
-        <v>92.52715931008595</v>
+        <v>92.5271517066259</v>
       </c>
       <c r="F669" t="n">
         <v>406022</v>
@@ -13812,16 +13812,16 @@
         <v>45455</v>
       </c>
       <c r="B670" t="n">
-        <v>90.15084838867188</v>
+        <v>90.15085601806641</v>
       </c>
       <c r="C670" t="n">
-        <v>93.8638156802361</v>
+        <v>93.86382362385611</v>
       </c>
       <c r="D670" t="n">
-        <v>90.1415639875045</v>
+        <v>90.1415716161133</v>
       </c>
       <c r="E670" t="n">
-        <v>93.15834991190043</v>
+        <v>93.15835779581742</v>
       </c>
       <c r="F670" t="n">
         <v>421382</v>
@@ -13872,16 +13872,16 @@
         <v>45460</v>
       </c>
       <c r="B673" t="n">
-        <v>85.58389282226562</v>
+        <v>85.58390045166016</v>
       </c>
       <c r="C673" t="n">
-        <v>86.70707165460294</v>
+        <v>86.70707938412349</v>
       </c>
       <c r="D673" t="n">
-        <v>83.36539544288092</v>
+        <v>83.36540287450703</v>
       </c>
       <c r="E673" t="n">
-        <v>85.12905631419575</v>
+        <v>85.12906390304379</v>
       </c>
       <c r="F673" t="n">
         <v>650145</v>
@@ -13892,16 +13892,16 @@
         <v>45461</v>
       </c>
       <c r="B674" t="n">
-        <v>87.54249572753906</v>
+        <v>87.54248046875</v>
       </c>
       <c r="C674" t="n">
-        <v>87.54249572753906</v>
+        <v>87.54248046875</v>
       </c>
       <c r="D674" t="n">
-        <v>84.97126865121261</v>
+        <v>84.9712538405923</v>
       </c>
       <c r="E674" t="n">
-        <v>85.5746273329557</v>
+        <v>85.57461241716906</v>
       </c>
       <c r="F674" t="n">
         <v>348422</v>
@@ -13952,16 +13952,16 @@
         <v>45464</v>
       </c>
       <c r="B677" t="n">
-        <v>88.75848388671875</v>
+        <v>88.75849151611328</v>
       </c>
       <c r="C677" t="n">
-        <v>91.33899496985757</v>
+        <v>91.33900282106455</v>
       </c>
       <c r="D677" t="n">
-        <v>86.98553864098177</v>
+        <v>86.98554611797962</v>
       </c>
       <c r="E677" t="n">
-        <v>91.33899496985757</v>
+        <v>91.33900282106455</v>
       </c>
       <c r="F677" t="n">
         <v>813524</v>
@@ -13972,16 +13972,16 @@
         <v>45467</v>
       </c>
       <c r="B678" t="n">
-        <v>89.74242401123047</v>
+        <v>89.74241638183594</v>
       </c>
       <c r="C678" t="n">
-        <v>90.6056892310713</v>
+        <v>90.60568152828682</v>
       </c>
       <c r="D678" t="n">
-        <v>88.23866963675577</v>
+        <v>88.23866213520195</v>
       </c>
       <c r="E678" t="n">
-        <v>88.92557371752265</v>
+        <v>88.92556615757213</v>
       </c>
       <c r="F678" t="n">
         <v>235914</v>
@@ -13992,16 +13992,16 @@
         <v>45468</v>
       </c>
       <c r="B679" t="n">
-        <v>90.97698974609375</v>
+        <v>90.97698211669922</v>
       </c>
       <c r="C679" t="n">
-        <v>90.97698974609375</v>
+        <v>90.97698211669922</v>
       </c>
       <c r="D679" t="n">
-        <v>89.1112215617069</v>
+        <v>89.11121408877702</v>
       </c>
       <c r="E679" t="n">
-        <v>90.0301790511234</v>
+        <v>90.03017150112908</v>
       </c>
       <c r="F679" t="n">
         <v>300759</v>
@@ -14032,16 +14032,16 @@
         <v>45470</v>
       </c>
       <c r="B681" t="n">
-        <v>91.58034515380859</v>
+        <v>91.58035278320312</v>
       </c>
       <c r="C681" t="n">
-        <v>92.01661287846356</v>
+        <v>92.01662054420278</v>
       </c>
       <c r="D681" t="n">
-        <v>90.22510580838188</v>
+        <v>90.22511332487385</v>
       </c>
       <c r="E681" t="n">
-        <v>90.22510580838188</v>
+        <v>90.22511332487385</v>
       </c>
       <c r="F681" t="n">
         <v>136324</v>
@@ -14052,16 +14052,16 @@
         <v>45471</v>
       </c>
       <c r="B682" t="n">
-        <v>90.78205871582031</v>
+        <v>90.78206634521484</v>
       </c>
       <c r="C682" t="n">
-        <v>92.44360544927629</v>
+        <v>92.4436132183085</v>
       </c>
       <c r="D682" t="n">
-        <v>89.58462584053821</v>
+        <v>89.58463336929955</v>
       </c>
       <c r="E682" t="n">
-        <v>91.15334980235941</v>
+        <v>91.15335746295753</v>
       </c>
       <c r="F682" t="n">
         <v>273815</v>
@@ -14072,16 +14072,16 @@
         <v>45474</v>
       </c>
       <c r="B683" t="n">
-        <v>87.96947479248047</v>
+        <v>87.969482421875</v>
       </c>
       <c r="C683" t="n">
-        <v>91.70101090135917</v>
+        <v>91.70101885438143</v>
       </c>
       <c r="D683" t="n">
-        <v>87.85809030571718</v>
+        <v>87.85809792545159</v>
       </c>
       <c r="E683" t="n">
-        <v>90.31793256263779</v>
+        <v>90.31794039570877</v>
       </c>
       <c r="F683" t="n">
         <v>154542</v>
@@ -14092,16 +14092,16 @@
         <v>45475</v>
       </c>
       <c r="B684" t="n">
-        <v>87.69100952148438</v>
+        <v>87.69101715087891</v>
       </c>
       <c r="C684" t="n">
-        <v>88.6470975028048</v>
+        <v>88.647105215382</v>
       </c>
       <c r="D684" t="n">
-        <v>87.28258083745493</v>
+        <v>87.28258843131488</v>
       </c>
       <c r="E684" t="n">
-        <v>88.03445447676063</v>
+        <v>88.03446213603596</v>
       </c>
       <c r="F684" t="n">
         <v>181372</v>
@@ -14172,16 +14172,16 @@
         <v>45481</v>
       </c>
       <c r="B688" t="n">
-        <v>87.11550140380859</v>
+        <v>87.11549377441406</v>
       </c>
       <c r="C688" t="n">
-        <v>88.26651938354486</v>
+        <v>88.26651165334657</v>
       </c>
       <c r="D688" t="n">
-        <v>86.17797509643314</v>
+        <v>86.17796754914521</v>
       </c>
       <c r="E688" t="n">
-        <v>86.32649720061781</v>
+        <v>86.32648964032262</v>
       </c>
       <c r="F688" t="n">
         <v>189187</v>
@@ -14212,16 +14212,16 @@
         <v>45483</v>
       </c>
       <c r="B690" t="n">
-        <v>91.15334320068359</v>
+        <v>91.15335083007812</v>
       </c>
       <c r="C690" t="n">
-        <v>92.08158501365153</v>
+        <v>92.08159272073848</v>
       </c>
       <c r="D690" t="n">
-        <v>86.83702443592102</v>
+        <v>86.83703170404632</v>
       </c>
       <c r="E690" t="n">
-        <v>86.83702443592102</v>
+        <v>86.83703170404632</v>
       </c>
       <c r="F690" t="n">
         <v>604684</v>
@@ -14252,16 +14252,16 @@
         <v>45485</v>
       </c>
       <c r="B692" t="n">
-        <v>92.93558502197266</v>
+        <v>92.93557739257812</v>
       </c>
       <c r="C692" t="n">
-        <v>93.67817432034111</v>
+        <v>93.67816662998491</v>
       </c>
       <c r="D692" t="n">
-        <v>91.43183053874634</v>
+        <v>91.43182303280007</v>
       </c>
       <c r="E692" t="n">
-        <v>91.90523590823084</v>
+        <v>91.90522836342113</v>
       </c>
       <c r="F692" t="n">
         <v>527149</v>
@@ -14272,16 +14272,16 @@
         <v>45488</v>
       </c>
       <c r="B693" t="n">
-        <v>93.75242614746094</v>
+        <v>93.75243377685547</v>
       </c>
       <c r="C693" t="n">
-        <v>94.87559792771359</v>
+        <v>94.8756056485097</v>
       </c>
       <c r="D693" t="n">
-        <v>92.54570891873422</v>
+        <v>92.54571644992839</v>
       </c>
       <c r="E693" t="n">
-        <v>92.83346870578572</v>
+        <v>92.83347626039723</v>
       </c>
       <c r="F693" t="n">
         <v>284490</v>
@@ -14292,16 +14292,16 @@
         <v>45489</v>
       </c>
       <c r="B694" t="n">
-        <v>93.74314880371094</v>
+        <v>93.74314117431641</v>
       </c>
       <c r="C694" t="n">
-        <v>95.46039492624392</v>
+        <v>95.46038715708933</v>
       </c>
       <c r="D694" t="n">
-        <v>92.92629846982642</v>
+        <v>92.9262909069122</v>
       </c>
       <c r="E694" t="n">
-        <v>92.92629846982642</v>
+        <v>92.9262909069122</v>
       </c>
       <c r="F694" t="n">
         <v>218776</v>
@@ -14392,16 +14392,16 @@
         <v>45496</v>
       </c>
       <c r="B699" t="n">
-        <v>94.27223968505859</v>
+        <v>94.27224731445312</v>
       </c>
       <c r="C699" t="n">
-        <v>94.94057494779331</v>
+        <v>94.9405826312758</v>
       </c>
       <c r="D699" t="n">
-        <v>93.76171091852527</v>
+        <v>93.76171850660302</v>
       </c>
       <c r="E699" t="n">
-        <v>93.76171091852527</v>
+        <v>93.76171850660302</v>
       </c>
       <c r="F699" t="n">
         <v>121190</v>
@@ -14412,16 +14412,16 @@
         <v>45497</v>
       </c>
       <c r="B700" t="n">
-        <v>91.80313110351562</v>
+        <v>91.80311584472656</v>
       </c>
       <c r="C700" t="n">
-        <v>94.77350253767032</v>
+        <v>94.77348678516967</v>
       </c>
       <c r="D700" t="n">
-        <v>91.78456229846984</v>
+        <v>91.78454704276713</v>
       </c>
       <c r="E700" t="n">
-        <v>94.36508089167664</v>
+        <v>94.36506520706058</v>
       </c>
       <c r="F700" t="n">
         <v>387734</v>
@@ -14452,16 +14452,16 @@
         <v>45499</v>
       </c>
       <c r="B702" t="n">
-        <v>93.10266876220703</v>
+        <v>93.1026611328125</v>
       </c>
       <c r="C702" t="n">
-        <v>94.9312994223739</v>
+        <v>94.93129164313034</v>
       </c>
       <c r="D702" t="n">
-        <v>92.04447352457791</v>
+        <v>92.04446598189828</v>
       </c>
       <c r="E702" t="n">
-        <v>93.00056158296879</v>
+        <v>93.00055396194153</v>
       </c>
       <c r="F702" t="n">
         <v>291332</v>
@@ -14472,16 +14472,16 @@
         <v>45502</v>
       </c>
       <c r="B703" t="n">
-        <v>91.94236755371094</v>
+        <v>91.94235229492188</v>
       </c>
       <c r="C703" t="n">
-        <v>94.07731977965157</v>
+        <v>94.07730416654506</v>
       </c>
       <c r="D703" t="n">
-        <v>91.7195843877592</v>
+        <v>91.71956916594331</v>
       </c>
       <c r="E703" t="n">
-        <v>93.1026699858278</v>
+        <v>93.10265453447454</v>
       </c>
       <c r="F703" t="n">
         <v>142991</v>
@@ -14512,16 +14512,16 @@
         <v>45504</v>
       </c>
       <c r="B705" t="n">
-        <v>90.49430084228516</v>
+        <v>90.49430847167969</v>
       </c>
       <c r="C705" t="n">
-        <v>91.80312532052498</v>
+        <v>91.8031330602639</v>
       </c>
       <c r="D705" t="n">
-        <v>89.90022659287696</v>
+        <v>89.90023417218629</v>
       </c>
       <c r="E705" t="n">
-        <v>90.59640801783253</v>
+        <v>90.59641565583551</v>
       </c>
       <c r="F705" t="n">
         <v>210335</v>
@@ -14552,16 +14552,16 @@
         <v>45506</v>
       </c>
       <c r="B707" t="n">
-        <v>86.47501373291016</v>
+        <v>86.47502136230469</v>
       </c>
       <c r="C707" t="n">
-        <v>88.6656579730932</v>
+        <v>88.66566579576077</v>
       </c>
       <c r="D707" t="n">
-        <v>85.23116597724216</v>
+        <v>85.23117349689625</v>
       </c>
       <c r="E707" t="n">
-        <v>87.72813880804915</v>
+        <v>87.72814654800261</v>
       </c>
       <c r="F707" t="n">
         <v>556592</v>
@@ -14592,16 +14592,16 @@
         <v>45510</v>
       </c>
       <c r="B709" t="n">
-        <v>85.0455322265625</v>
+        <v>85.04552459716797</v>
       </c>
       <c r="C709" t="n">
-        <v>86.18726588896256</v>
+        <v>86.18725815714363</v>
       </c>
       <c r="D709" t="n">
-        <v>83.79239989584035</v>
+        <v>83.79239237886372</v>
       </c>
       <c r="E709" t="n">
-        <v>85.21261606519718</v>
+        <v>85.21260842081362</v>
       </c>
       <c r="F709" t="n">
         <v>246819</v>
@@ -14692,16 +14692,16 @@
         <v>45517</v>
       </c>
       <c r="B714" t="n">
-        <v>93.46468353271484</v>
+        <v>93.46467590332031</v>
       </c>
       <c r="C714" t="n">
-        <v>94.6806782121652</v>
+        <v>94.6806704835107</v>
       </c>
       <c r="D714" t="n">
-        <v>92.62926436739917</v>
+        <v>92.62925680619877</v>
       </c>
       <c r="E714" t="n">
-        <v>92.62926436739917</v>
+        <v>92.62925680619877</v>
       </c>
       <c r="F714" t="n">
         <v>783941</v>
@@ -14712,16 +14712,16 @@
         <v>45518</v>
       </c>
       <c r="B715" t="n">
-        <v>100.2501220703125</v>
+        <v>100.250129699707</v>
       </c>
       <c r="C715" t="n">
-        <v>101.4382705321122</v>
+        <v>101.4382782519291</v>
       </c>
       <c r="D715" t="n">
-        <v>98.41220004964379</v>
+        <v>98.41220753916585</v>
       </c>
       <c r="E715" t="n">
-        <v>100.0644765288776</v>
+        <v>100.0644841441438</v>
       </c>
       <c r="F715" t="n">
         <v>1420295</v>
@@ -14772,16 +14772,16 @@
         <v>45523</v>
       </c>
       <c r="B718" t="n">
-        <v>100.5471649169922</v>
+        <v>100.5471572875977</v>
       </c>
       <c r="C718" t="n">
-        <v>102.0787655078641</v>
+        <v>102.0787577622536</v>
       </c>
       <c r="D718" t="n">
-        <v>99.8602678762215</v>
+        <v>99.86026029894786</v>
       </c>
       <c r="E718" t="n">
-        <v>101.3640152605594</v>
+        <v>101.3640075691833</v>
       </c>
       <c r="F718" t="n">
         <v>372762</v>
@@ -14792,16 +14792,16 @@
         <v>45524</v>
       </c>
       <c r="B719" t="n">
-        <v>99.72103118896484</v>
+        <v>99.72102355957031</v>
       </c>
       <c r="C719" t="n">
-        <v>101.0948323664506</v>
+        <v>101.0948246319502</v>
       </c>
       <c r="D719" t="n">
-        <v>99.31260247205103</v>
+        <v>99.31259487390432</v>
       </c>
       <c r="E719" t="n">
-        <v>100.5935808725811</v>
+        <v>100.5935731764301</v>
       </c>
       <c r="F719" t="n">
         <v>300080</v>
@@ -14892,16 +14892,16 @@
         <v>45531</v>
       </c>
       <c r="B724" t="n">
-        <v>99.32188415527344</v>
+        <v>99.32187652587891</v>
       </c>
       <c r="C724" t="n">
-        <v>100.7977853896593</v>
+        <v>100.7977776468936</v>
       </c>
       <c r="D724" t="n">
-        <v>99.15480032855771</v>
+        <v>99.1547927119977</v>
       </c>
       <c r="E724" t="n">
-        <v>99.40542252766943</v>
+        <v>99.40541489185792</v>
       </c>
       <c r="F724" t="n">
         <v>203544</v>
@@ -14972,16 +14972,16 @@
         <v>45537</v>
       </c>
       <c r="B728" t="n">
-        <v>95.3304443359375</v>
+        <v>95.33043670654297</v>
       </c>
       <c r="C728" t="n">
-        <v>95.77600358286018</v>
+        <v>95.77599591780708</v>
       </c>
       <c r="D728" t="n">
-        <v>93.65032869197439</v>
+        <v>93.65032119704127</v>
       </c>
       <c r="E728" t="n">
-        <v>95.61820415283664</v>
+        <v>95.6181965004124</v>
       </c>
       <c r="F728" t="n">
         <v>425330</v>
@@ -14992,16 +14992,16 @@
         <v>45538</v>
       </c>
       <c r="B729" t="n">
-        <v>96.24939727783203</v>
+        <v>96.24940490722656</v>
       </c>
       <c r="C729" t="n">
-        <v>97.25189306841784</v>
+        <v>97.25190077727714</v>
       </c>
       <c r="D729" t="n">
-        <v>94.5414286340846</v>
+        <v>94.54143612809369</v>
       </c>
       <c r="E729" t="n">
-        <v>95.51608538489992</v>
+        <v>95.51609295616707</v>
       </c>
       <c r="F729" t="n">
         <v>703523</v>
@@ -15072,16 +15072,16 @@
         <v>45544</v>
       </c>
       <c r="B733" t="n">
-        <v>93.68744659423828</v>
+        <v>93.68745422363281</v>
       </c>
       <c r="C733" t="n">
-        <v>95.05196319427465</v>
+        <v>95.05197093478797</v>
       </c>
       <c r="D733" t="n">
-        <v>93.37184069479765</v>
+        <v>93.37184829849096</v>
       </c>
       <c r="E733" t="n">
-        <v>93.77098495819658</v>
+        <v>93.77099259439402</v>
       </c>
       <c r="F733" t="n">
         <v>200739</v>
@@ -15092,16 +15092,16 @@
         <v>45545</v>
       </c>
       <c r="B734" t="n">
-        <v>94.43932342529297</v>
+        <v>94.4393310546875</v>
       </c>
       <c r="C734" t="n">
-        <v>94.89416702879937</v>
+        <v>94.894174694939</v>
       </c>
       <c r="D734" t="n">
-        <v>92.19297985772515</v>
+        <v>92.1929873056461</v>
       </c>
       <c r="E734" t="n">
-        <v>93.78027256449035</v>
+        <v>93.78028014064265</v>
       </c>
       <c r="F734" t="n">
         <v>481370</v>
@@ -15152,16 +15152,16 @@
         <v>45548</v>
       </c>
       <c r="B737" t="n">
-        <v>98.87631988525391</v>
+        <v>98.87632751464844</v>
       </c>
       <c r="C737" t="n">
-        <v>99.46111678992312</v>
+        <v>99.46112446444116</v>
       </c>
       <c r="D737" t="n">
-        <v>96.32365476834089</v>
+        <v>96.32366220076925</v>
       </c>
       <c r="E737" t="n">
-        <v>96.32365476834089</v>
+        <v>96.32366220076925</v>
       </c>
       <c r="F737" t="n">
         <v>344396</v>
@@ -15192,16 +15192,16 @@
         <v>45552</v>
       </c>
       <c r="B739" t="n">
-        <v>100.3151016235352</v>
+        <v>100.3150939941406</v>
       </c>
       <c r="C739" t="n">
-        <v>100.7977842944004</v>
+        <v>100.7977766282958</v>
       </c>
       <c r="D739" t="n">
-        <v>98.70924002410959</v>
+        <v>98.70923251684773</v>
       </c>
       <c r="E739" t="n">
-        <v>99.17336097306311</v>
+        <v>99.17335343050286</v>
       </c>
       <c r="F739" t="n">
         <v>287351</v>
@@ -15272,16 +15272,16 @@
         <v>45558</v>
       </c>
       <c r="B743" t="n">
-        <v>90.16012573242188</v>
+        <v>90.16013336181641</v>
       </c>
       <c r="C743" t="n">
-        <v>93.88237742616521</v>
+        <v>93.8823853705385</v>
       </c>
       <c r="D743" t="n">
-        <v>89.63102817650709</v>
+        <v>89.63103576112911</v>
       </c>
       <c r="E743" t="n">
-        <v>93.10265769404786</v>
+        <v>93.1026655724409</v>
       </c>
       <c r="F743" t="n">
         <v>500884</v>
@@ -15312,16 +15312,16 @@
         <v>45560</v>
       </c>
       <c r="B745" t="n">
-        <v>90.49430084228516</v>
+        <v>90.49430847167969</v>
       </c>
       <c r="C745" t="n">
-        <v>92.0630319194006</v>
+        <v>92.06303968105173</v>
       </c>
       <c r="D745" t="n">
-        <v>89.42682124096855</v>
+        <v>89.42682878036601</v>
       </c>
       <c r="E745" t="n">
-        <v>91.89594809413431</v>
+        <v>91.89595584169895</v>
       </c>
       <c r="F745" t="n">
         <v>511811</v>
@@ -15332,16 +15332,16 @@
         <v>45561</v>
       </c>
       <c r="B746" t="n">
-        <v>91.32042694091797</v>
+        <v>91.3204345703125</v>
       </c>
       <c r="C746" t="n">
-        <v>92.21153823085946</v>
+        <v>92.21154593470217</v>
       </c>
       <c r="D746" t="n">
-        <v>90.4850149754199</v>
+        <v>90.48502253501967</v>
       </c>
       <c r="E746" t="n">
-        <v>91.07908916871422</v>
+        <v>91.07909677794611</v>
       </c>
       <c r="F746" t="n">
         <v>433745</v>
@@ -15432,16 +15432,16 @@
         <v>45568</v>
       </c>
       <c r="B751" t="n">
-        <v>90.16012573242188</v>
+        <v>90.16013336181641</v>
       </c>
       <c r="C751" t="n">
-        <v>90.9120064248757</v>
+        <v>90.91201411789474</v>
       </c>
       <c r="D751" t="n">
-        <v>88.60996358743401</v>
+        <v>88.60997108565304</v>
       </c>
       <c r="E751" t="n">
-        <v>90.49429335530733</v>
+        <v>90.49430101297929</v>
       </c>
       <c r="F751" t="n">
         <v>420486</v>
@@ -15452,16 +15452,16 @@
         <v>45569</v>
       </c>
       <c r="B752" t="n">
-        <v>89.85382080078125</v>
+        <v>89.85381317138672</v>
       </c>
       <c r="C752" t="n">
-        <v>90.30865735920958</v>
+        <v>90.30864969119534</v>
       </c>
       <c r="D752" t="n">
-        <v>87.72814595150052</v>
+        <v>87.72813850259483</v>
       </c>
       <c r="E752" t="n">
-        <v>90.17870405680148</v>
+        <v>90.17869639982145</v>
       </c>
       <c r="F752" t="n">
         <v>695884</v>
@@ -15472,16 +15472,16 @@
         <v>45572</v>
       </c>
       <c r="B753" t="n">
-        <v>90.48502349853516</v>
+        <v>90.48501586914062</v>
       </c>
       <c r="C753" t="n">
-        <v>90.75420741735454</v>
+        <v>90.75419976526331</v>
       </c>
       <c r="D753" t="n">
-        <v>89.1205067728724</v>
+        <v>89.12049925852935</v>
       </c>
       <c r="E753" t="n">
-        <v>89.80740379570975</v>
+        <v>89.80739622344984</v>
       </c>
       <c r="F753" t="n">
         <v>295051</v>
@@ -15492,16 +15492,16 @@
         <v>45573</v>
       </c>
       <c r="B754" t="n">
-        <v>90.68923187255859</v>
+        <v>90.68922424316406</v>
       </c>
       <c r="C754" t="n">
-        <v>91.33900545941735</v>
+        <v>91.33899777535945</v>
       </c>
       <c r="D754" t="n">
-        <v>90.68923187255859</v>
+        <v>90.68922424316406</v>
       </c>
       <c r="E754" t="n">
-        <v>91.12550670383942</v>
+        <v>91.12549903774249</v>
       </c>
       <c r="F754" t="n">
         <v>183628</v>
@@ -15512,16 +15512,16 @@
         <v>45574</v>
       </c>
       <c r="B755" t="n">
-        <v>89.48252105712891</v>
+        <v>89.48251342773438</v>
       </c>
       <c r="C755" t="n">
-        <v>90.68923128445775</v>
+        <v>90.68922355217755</v>
       </c>
       <c r="D755" t="n">
-        <v>87.85809772340171</v>
+        <v>87.85809023250759</v>
       </c>
       <c r="E755" t="n">
-        <v>90.42004736410439</v>
+        <v>90.42003965477517</v>
       </c>
       <c r="F755" t="n">
         <v>305833</v>
@@ -15592,16 +15592,16 @@
         <v>45580</v>
       </c>
       <c r="B759" t="n">
-        <v>92.22083282470703</v>
+        <v>92.2208251953125</v>
       </c>
       <c r="C759" t="n">
-        <v>94.20726995594816</v>
+        <v>94.20726216221644</v>
       </c>
       <c r="D759" t="n">
-        <v>91.71030402068969</v>
+        <v>91.71029643353101</v>
       </c>
       <c r="E759" t="n">
-        <v>93.52965732397952</v>
+        <v>93.52964958630643</v>
       </c>
       <c r="F759" t="n">
         <v>238514</v>
@@ -15652,16 +15652,16 @@
         <v>45583</v>
       </c>
       <c r="B762" t="n">
-        <v>95.56249237060547</v>
+        <v>95.5625</v>
       </c>
       <c r="C762" t="n">
-        <v>96.35150358177644</v>
+        <v>96.35151127416302</v>
       </c>
       <c r="D762" t="n">
-        <v>94.81061876392397</v>
+        <v>94.81062633329138</v>
       </c>
       <c r="E762" t="n">
-        <v>95.59962289317188</v>
+        <v>95.5996305255308</v>
       </c>
       <c r="F762" t="n">
         <v>405254</v>
@@ -15712,16 +15712,16 @@
         <v>45588</v>
       </c>
       <c r="B765" t="n">
-        <v>92.425048828125</v>
+        <v>92.42504119873047</v>
       </c>
       <c r="C765" t="n">
-        <v>95.40470457814952</v>
+        <v>95.40469670279386</v>
       </c>
       <c r="D765" t="n">
-        <v>92.36007217620262</v>
+        <v>92.36006455217171</v>
       </c>
       <c r="E765" t="n">
-        <v>93.76171947558419</v>
+        <v>93.76171173585173</v>
       </c>
       <c r="F765" t="n">
         <v>357512</v>
@@ -15752,16 +15752,16 @@
         <v>45590</v>
       </c>
       <c r="B767" t="n">
-        <v>93.17691802978516</v>
+        <v>93.17691040039062</v>
       </c>
       <c r="C767" t="n">
-        <v>93.91022997004863</v>
+        <v>93.91022228060997</v>
       </c>
       <c r="D767" t="n">
-        <v>92.02590007331048</v>
+        <v>92.02589253816214</v>
       </c>
       <c r="E767" t="n">
-        <v>93.29759400747731</v>
+        <v>93.29758636820173</v>
       </c>
       <c r="F767" t="n">
         <v>563664</v>
@@ -15812,16 +15812,16 @@
         <v>45595</v>
       </c>
       <c r="B770" t="n">
-        <v>95.72957611083984</v>
+        <v>95.72958374023438</v>
       </c>
       <c r="C770" t="n">
-        <v>96.24011194334904</v>
+        <v>96.24011961343192</v>
       </c>
       <c r="D770" t="n">
-        <v>94.58784264093464</v>
+        <v>94.58785017933603</v>
       </c>
       <c r="E770" t="n">
-        <v>94.58784264093464</v>
+        <v>94.58785017933603</v>
       </c>
       <c r="F770" t="n">
         <v>154247</v>
@@ -15852,16 +15852,16 @@
         <v>45597</v>
       </c>
       <c r="B772" t="n">
-        <v>91.89595031738281</v>
+        <v>91.89594268798828</v>
       </c>
       <c r="C772" t="n">
-        <v>94.99627493886804</v>
+        <v>94.99626705207805</v>
       </c>
       <c r="D772" t="n">
-        <v>91.41326763378245</v>
+        <v>91.41326004446124</v>
       </c>
       <c r="E772" t="n">
-        <v>93.85454134019609</v>
+        <v>93.85453354819522</v>
       </c>
       <c r="F772" t="n">
         <v>397099</v>
@@ -15912,16 +15912,16 @@
         <v>45602</v>
       </c>
       <c r="B775" t="n">
-        <v>94.72708129882812</v>
+        <v>94.72709655761719</v>
       </c>
       <c r="C775" t="n">
-        <v>95.38613214631143</v>
+        <v>95.38614751126146</v>
       </c>
       <c r="D775" t="n">
-        <v>91.81240252796478</v>
+        <v>91.81241731725275</v>
       </c>
       <c r="E775" t="n">
-        <v>94.21654546109727</v>
+        <v>94.2165606376484</v>
       </c>
       <c r="F775" t="n">
         <v>484922</v>
@@ -15932,16 +15932,16 @@
         <v>45603</v>
       </c>
       <c r="B776" t="n">
-        <v>93.40897369384766</v>
+        <v>93.40898132324219</v>
       </c>
       <c r="C776" t="n">
-        <v>96.03589979745092</v>
+        <v>96.03590764140573</v>
       </c>
       <c r="D776" t="n">
-        <v>92.91700665236559</v>
+        <v>92.91701424157758</v>
       </c>
       <c r="E776" t="n">
-        <v>94.72708248727439</v>
+        <v>94.72709022432851</v>
       </c>
       <c r="F776" t="n">
         <v>397597</v>
@@ -15952,16 +15952,16 @@
         <v>45604</v>
       </c>
       <c r="B777" t="n">
-        <v>91.02339935302734</v>
+        <v>91.02339172363281</v>
       </c>
       <c r="C777" t="n">
-        <v>93.79884776061469</v>
+        <v>93.79883989858776</v>
       </c>
       <c r="D777" t="n">
-        <v>89.98377294711923</v>
+        <v>89.98376540486406</v>
       </c>
       <c r="E777" t="n">
-        <v>93.39970345636819</v>
+        <v>93.39969562779672</v>
       </c>
       <c r="F777" t="n">
         <v>477120</v>
@@ -16032,16 +16032,16 @@
         <v>45610</v>
       </c>
       <c r="B781" t="n">
-        <v>90.15084838867188</v>
+        <v>90.15085601806641</v>
       </c>
       <c r="C781" t="n">
-        <v>91.79383329914289</v>
+        <v>91.79384106758192</v>
       </c>
       <c r="D781" t="n">
-        <v>89.28758321010626</v>
+        <v>89.28759076644334</v>
       </c>
       <c r="E781" t="n">
-        <v>90.22510235224161</v>
+        <v>90.22510998792019</v>
       </c>
       <c r="F781" t="n">
         <v>249817</v>
@@ -16132,16 +16132,16 @@
         <v>45621</v>
       </c>
       <c r="B786" t="n">
-        <v>85.59318542480469</v>
+        <v>85.59317779541016</v>
       </c>
       <c r="C786" t="n">
-        <v>86.31721297941206</v>
+        <v>86.31720528548094</v>
       </c>
       <c r="D786" t="n">
-        <v>84.42359863863385</v>
+        <v>84.42359111349106</v>
       </c>
       <c r="E786" t="n">
-        <v>85.32399442184897</v>
+        <v>85.32398681644892</v>
       </c>
       <c r="F786" t="n">
         <v>384525</v>
@@ -16212,16 +16212,16 @@
         <v>45625</v>
       </c>
       <c r="B790" t="n">
-        <v>76.31076049804688</v>
+        <v>76.31076812744141</v>
       </c>
       <c r="C790" t="n">
-        <v>79.70812901758936</v>
+        <v>79.70813698664587</v>
       </c>
       <c r="D790" t="n">
-        <v>73.81378769265385</v>
+        <v>73.81379507240612</v>
       </c>
       <c r="E790" t="n">
-        <v>78.53854232113272</v>
+        <v>78.53855017325635</v>
       </c>
       <c r="F790" t="n">
         <v>1718056</v>
@@ -16272,16 +16272,16 @@
         <v>45630</v>
       </c>
       <c r="B793" t="n">
-        <v>75.22472381591797</v>
+        <v>75.2247314453125</v>
       </c>
       <c r="C793" t="n">
-        <v>76.09727346105902</v>
+        <v>76.09728117894873</v>
       </c>
       <c r="D793" t="n">
-        <v>74.39858909817006</v>
+        <v>74.39859664377688</v>
       </c>
       <c r="E793" t="n">
-        <v>75.41965376350666</v>
+        <v>75.41966141267126</v>
       </c>
       <c r="F793" t="n">
         <v>411810</v>
@@ -16312,16 +16312,16 @@
         <v>45632</v>
       </c>
       <c r="B795" t="n">
-        <v>75.78166961669922</v>
+        <v>75.78166198730469</v>
       </c>
       <c r="C795" t="n">
-        <v>75.78166961669922</v>
+        <v>75.78166198730469</v>
       </c>
       <c r="D795" t="n">
-        <v>74.25935343777866</v>
+        <v>74.25934596164483</v>
       </c>
       <c r="E795" t="n">
-        <v>75.651716314737</v>
+        <v>75.65170869842567</v>
       </c>
       <c r="F795" t="n">
         <v>1017781</v>
@@ -24452,19 +24452,39 @@
         <v>46232</v>
       </c>
       <c r="B1202" t="n">
-        <v>83.93000000000001</v>
+        <v>83.93000030517578</v>
       </c>
       <c r="C1202" t="n">
-        <v>85.58</v>
+        <v>85.58000183105469</v>
       </c>
       <c r="D1202" t="n">
-        <v>83.04000000000001</v>
+        <v>83.04000091552734</v>
       </c>
       <c r="E1202" t="n">
-        <v>85.45</v>
+        <v>85.44999694824219</v>
       </c>
       <c r="F1202" t="n">
         <v>359528</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B1203" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="C1203" t="n">
+        <v>87.42</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>83.48999999999999</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>83.70999999999999</v>
+      </c>
+      <c r="F1203" t="n">
+        <v>452487</v>
       </c>
     </row>
   </sheetData>

--- a/database/XPBR31.xlsx
+++ b/database/XPBR31.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1203"/>
+  <dimension ref="A1:F1204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44473</v>
       </c>
       <c r="B2" t="n">
-        <v>196.6089477539062</v>
+        <v>196.6089630126953</v>
       </c>
       <c r="C2" t="n">
-        <v>203.5754691767007</v>
+        <v>203.5754849761604</v>
       </c>
       <c r="D2" t="n">
-        <v>191.4433465160446</v>
+        <v>191.4433613739322</v>
       </c>
       <c r="E2" t="n">
-        <v>191.9528797964022</v>
+        <v>191.9528946938346</v>
       </c>
       <c r="F2" t="n">
         <v>9950865</v>
@@ -472,16 +472,16 @@
         <v>44474</v>
       </c>
       <c r="B3" t="n">
-        <v>192.54150390625</v>
+        <v>192.5414886474609</v>
       </c>
       <c r="C3" t="n">
-        <v>198.9809326053319</v>
+        <v>198.9809168362223</v>
       </c>
       <c r="D3" t="n">
-        <v>187.7273111444886</v>
+        <v>187.7272962672212</v>
       </c>
       <c r="E3" t="n">
-        <v>197.6631780847668</v>
+        <v>197.6631624200884</v>
       </c>
       <c r="F3" t="n">
         <v>2636287</v>
@@ -512,16 +512,16 @@
         <v>44476</v>
       </c>
       <c r="B5" t="n">
-        <v>203.3734436035156</v>
+        <v>203.3734283447266</v>
       </c>
       <c r="C5" t="n">
-        <v>203.3734436035156</v>
+        <v>203.3734283447266</v>
       </c>
       <c r="D5" t="n">
-        <v>190.9426315702683</v>
+        <v>190.9426172441435</v>
       </c>
       <c r="E5" t="n">
-        <v>190.9426315702683</v>
+        <v>190.9426172441435</v>
       </c>
       <c r="F5" t="n">
         <v>12157101</v>
@@ -532,16 +532,16 @@
         <v>44477</v>
       </c>
       <c r="B6" t="n">
-        <v>193.8241119384766</v>
+        <v>193.8240966796875</v>
       </c>
       <c r="C6" t="n">
-        <v>204.8668871514385</v>
+        <v>204.8668710233078</v>
       </c>
       <c r="D6" t="n">
-        <v>191.7947722500135</v>
+        <v>191.7947571509841</v>
       </c>
       <c r="E6" t="n">
-        <v>200.9926858889775</v>
+        <v>200.992670065843</v>
       </c>
       <c r="F6" t="n">
         <v>4982319</v>
@@ -592,16 +592,16 @@
         <v>44483</v>
       </c>
       <c r="B9" t="n">
-        <v>164.7632293701172</v>
+        <v>164.7632446289062</v>
       </c>
       <c r="C9" t="n">
-        <v>173.8293727564489</v>
+        <v>173.8293888548571</v>
       </c>
       <c r="D9" t="n">
-        <v>164.2888302749371</v>
+        <v>164.2888454897918</v>
       </c>
       <c r="E9" t="n">
-        <v>171.8351807306346</v>
+        <v>171.8351966443599</v>
       </c>
       <c r="F9" t="n">
         <v>3205420</v>
@@ -612,16 +612,16 @@
         <v>44484</v>
       </c>
       <c r="B10" t="n">
-        <v>175.7005920410156</v>
+        <v>175.7005767822266</v>
       </c>
       <c r="C10" t="n">
-        <v>178.977404329211</v>
+        <v>178.9773887858458</v>
       </c>
       <c r="D10" t="n">
-        <v>166.9155624389649</v>
+        <v>166.9155479431152</v>
       </c>
       <c r="E10" t="n">
-        <v>166.9155624389649</v>
+        <v>166.9155479431152</v>
       </c>
       <c r="F10" t="n">
         <v>2643581</v>
@@ -632,16 +632,16 @@
         <v>44487</v>
       </c>
       <c r="B11" t="n">
-        <v>179.4166564941406</v>
+        <v>179.4166717529297</v>
       </c>
       <c r="C11" t="n">
-        <v>182.2717911257051</v>
+        <v>182.2718066273138</v>
       </c>
       <c r="D11" t="n">
-        <v>175.0680695055053</v>
+        <v>175.0680843944616</v>
       </c>
       <c r="E11" t="n">
-        <v>176.7547935869503</v>
+        <v>176.7548086193568</v>
       </c>
       <c r="F11" t="n">
         <v>1369949</v>
@@ -672,16 +672,16 @@
         <v>44489</v>
       </c>
       <c r="B13" t="n">
-        <v>174.3828430175781</v>
+        <v>174.3828582763672</v>
       </c>
       <c r="C13" t="n">
-        <v>178.4942305647025</v>
+        <v>178.4942461832448</v>
       </c>
       <c r="D13" t="n">
-        <v>169.8409841808207</v>
+        <v>169.8409990421895</v>
       </c>
       <c r="E13" t="n">
-        <v>176.5791004863134</v>
+        <v>176.5791159372786</v>
       </c>
       <c r="F13" t="n">
         <v>1907987</v>
@@ -752,16 +752,16 @@
         <v>44495</v>
       </c>
       <c r="B17" t="n">
-        <v>163.9637908935547</v>
+        <v>163.9638061523438</v>
       </c>
       <c r="C17" t="n">
-        <v>170.2538752650204</v>
+        <v>170.2538911091769</v>
       </c>
       <c r="D17" t="n">
-        <v>159.9051115332836</v>
+        <v>159.9051264143641</v>
       </c>
       <c r="E17" t="n">
-        <v>168.7604229233316</v>
+        <v>168.7604386285045</v>
       </c>
       <c r="F17" t="n">
         <v>810455</v>
@@ -772,16 +772,16 @@
         <v>44496</v>
       </c>
       <c r="B18" t="n">
-        <v>163.83203125</v>
+        <v>163.8320159912109</v>
       </c>
       <c r="C18" t="n">
-        <v>168.5408079223634</v>
+        <v>168.540792225014</v>
       </c>
       <c r="D18" t="n">
-        <v>163.83203125</v>
+        <v>163.8320159912109</v>
       </c>
       <c r="E18" t="n">
-        <v>166.9155719910203</v>
+        <v>166.9155564450402</v>
       </c>
       <c r="F18" t="n">
         <v>503418</v>
@@ -792,16 +792,16 @@
         <v>44497</v>
       </c>
       <c r="B19" t="n">
-        <v>165.1673278808594</v>
+        <v>165.1673431396484</v>
       </c>
       <c r="C19" t="n">
-        <v>166.8101374438281</v>
+        <v>166.8101528543862</v>
       </c>
       <c r="D19" t="n">
-        <v>158.6664116852975</v>
+        <v>158.6664263435071</v>
       </c>
       <c r="E19" t="n">
-        <v>163.4103220545031</v>
+        <v>163.4103371509733</v>
       </c>
       <c r="F19" t="n">
         <v>1047427</v>
@@ -812,16 +812,16 @@
         <v>44498</v>
       </c>
       <c r="B20" t="n">
-        <v>162.5230712890625</v>
+        <v>162.5230560302734</v>
       </c>
       <c r="C20" t="n">
-        <v>167.3372644582008</v>
+        <v>167.337248747422</v>
       </c>
       <c r="D20" t="n">
-        <v>161.205316656989</v>
+        <v>161.2053015219199</v>
       </c>
       <c r="E20" t="n">
-        <v>166.1249393120207</v>
+        <v>166.1249237150633</v>
       </c>
       <c r="F20" t="n">
         <v>643563</v>
@@ -852,16 +852,16 @@
         <v>44503</v>
       </c>
       <c r="B22" t="n">
-        <v>164.6490325927734</v>
+        <v>164.6490173339844</v>
       </c>
       <c r="C22" t="n">
-        <v>168.6725779888017</v>
+        <v>168.672562357132</v>
       </c>
       <c r="D22" t="n">
-        <v>161.381000321849</v>
+        <v>161.3809853659237</v>
       </c>
       <c r="E22" t="n">
-        <v>168.6725779888017</v>
+        <v>168.672562357132</v>
       </c>
       <c r="F22" t="n">
         <v>834348</v>
@@ -872,16 +872,16 @@
         <v>44504</v>
       </c>
       <c r="B23" t="n">
-        <v>160.3707275390625</v>
+        <v>160.3707122802734</v>
       </c>
       <c r="C23" t="n">
-        <v>170.4208041422209</v>
+        <v>170.4207879271975</v>
       </c>
       <c r="D23" t="n">
-        <v>158.7630654183402</v>
+        <v>158.7630503125153</v>
       </c>
       <c r="E23" t="n">
-        <v>168.2333268163413</v>
+        <v>168.2333108094497</v>
       </c>
       <c r="F23" t="n">
         <v>1051127</v>
@@ -932,16 +932,16 @@
         <v>44509</v>
       </c>
       <c r="B26" t="n">
-        <v>163.7705078125</v>
+        <v>163.7705230712891</v>
       </c>
       <c r="C26" t="n">
-        <v>169.8497462274832</v>
+        <v>169.8497620526857</v>
       </c>
       <c r="D26" t="n">
-        <v>162.0837838654142</v>
+        <v>162.0837989670482</v>
       </c>
       <c r="E26" t="n">
-        <v>167.3548012268911</v>
+        <v>167.3548168196352</v>
       </c>
       <c r="F26" t="n">
         <v>336270</v>
@@ -952,16 +952,16 @@
         <v>44510</v>
       </c>
       <c r="B27" t="n">
-        <v>158.5697937011719</v>
+        <v>158.5697784423828</v>
       </c>
       <c r="C27" t="n">
-        <v>165.99314147324</v>
+        <v>165.9931255001201</v>
       </c>
       <c r="D27" t="n">
-        <v>157.9109164420257</v>
+        <v>157.9109012466388</v>
       </c>
       <c r="E27" t="n">
-        <v>162.8305386722738</v>
+        <v>162.8305230034835</v>
       </c>
       <c r="F27" t="n">
         <v>596401</v>
@@ -972,16 +972,16 @@
         <v>44511</v>
       </c>
       <c r="B28" t="n">
-        <v>162.1804351806641</v>
+        <v>162.1804504394531</v>
       </c>
       <c r="C28" t="n">
-        <v>165.5099555665838</v>
+        <v>165.5099711386316</v>
       </c>
       <c r="D28" t="n">
-        <v>159.4658641978954</v>
+        <v>159.4658792012834</v>
       </c>
       <c r="E28" t="n">
-        <v>161.5566921686091</v>
+        <v>161.5567073687131</v>
       </c>
       <c r="F28" t="n">
         <v>479646</v>
@@ -992,16 +992,16 @@
         <v>44512</v>
       </c>
       <c r="B29" t="n">
-        <v>161.6533355712891</v>
+        <v>161.6533203125</v>
       </c>
       <c r="C29" t="n">
-        <v>162.5230583851655</v>
+        <v>162.5230430442815</v>
       </c>
       <c r="D29" t="n">
-        <v>157.4277381980575</v>
+        <v>157.4277233381312</v>
       </c>
       <c r="E29" t="n">
-        <v>162.1804427442249</v>
+        <v>162.1804274356811</v>
       </c>
       <c r="F29" t="n">
         <v>339439</v>
@@ -1072,16 +1072,16 @@
         <v>44519</v>
       </c>
       <c r="B33" t="n">
-        <v>147.1931610107422</v>
+        <v>147.1931915283203</v>
       </c>
       <c r="C33" t="n">
-        <v>149.0468026336331</v>
+        <v>149.046833535527</v>
       </c>
       <c r="D33" t="n">
-        <v>140.5692417534431</v>
+        <v>140.5692708976831</v>
       </c>
       <c r="E33" t="n">
-        <v>142.5722272581445</v>
+        <v>142.5722568176638</v>
       </c>
       <c r="F33" t="n">
         <v>581745</v>
@@ -1092,16 +1092,16 @@
         <v>44522</v>
       </c>
       <c r="B34" t="n">
-        <v>140.0509185791016</v>
+        <v>140.0509490966797</v>
       </c>
       <c r="C34" t="n">
-        <v>150.6632343005178</v>
+        <v>150.6632671305561</v>
       </c>
       <c r="D34" t="n">
-        <v>139.9015747076236</v>
+        <v>139.9016051926592</v>
       </c>
       <c r="E34" t="n">
-        <v>145.9281046158399</v>
+        <v>145.9281364140771</v>
       </c>
       <c r="F34" t="n">
         <v>547961</v>
@@ -1152,16 +1152,16 @@
         <v>44525</v>
       </c>
       <c r="B37" t="n">
-        <v>151.3133544921875</v>
+        <v>151.3133850097656</v>
       </c>
       <c r="C37" t="n">
-        <v>152.8507346705215</v>
+        <v>152.8507654981656</v>
       </c>
       <c r="D37" t="n">
-        <v>148.0716764285178</v>
+        <v>148.0717062922993</v>
       </c>
       <c r="E37" t="n">
-        <v>148.0716764285178</v>
+        <v>148.0717062922993</v>
       </c>
       <c r="F37" t="n">
         <v>222385</v>
@@ -1172,16 +1172,16 @@
         <v>44526</v>
       </c>
       <c r="B38" t="n">
-        <v>146.7363433837891</v>
+        <v>146.7363739013672</v>
       </c>
       <c r="C38" t="n">
-        <v>148.7305487890506</v>
+        <v>148.7305797213747</v>
       </c>
       <c r="D38" t="n">
-        <v>143.3716755519658</v>
+        <v>143.3717053697751</v>
       </c>
       <c r="E38" t="n">
-        <v>148.7305487890506</v>
+        <v>148.7305797213747</v>
       </c>
       <c r="F38" t="n">
         <v>241997</v>
@@ -1212,16 +1212,16 @@
         <v>44530</v>
       </c>
       <c r="B40" t="n">
-        <v>140.5604705810547</v>
+        <v>140.5604858398438</v>
       </c>
       <c r="C40" t="n">
-        <v>147.3073667345976</v>
+        <v>147.3073827258078</v>
       </c>
       <c r="D40" t="n">
-        <v>139.7610296874511</v>
+        <v>139.7610448594554</v>
       </c>
       <c r="E40" t="n">
-        <v>147.3073667345976</v>
+        <v>147.3073827258078</v>
       </c>
       <c r="F40" t="n">
         <v>711030</v>
@@ -1232,16 +1232,16 @@
         <v>44531</v>
       </c>
       <c r="B41" t="n">
-        <v>144.3116760253906</v>
+        <v>144.3116912841797</v>
       </c>
       <c r="C41" t="n">
-        <v>151.2342698047112</v>
+        <v>151.2342857954605</v>
       </c>
       <c r="D41" t="n">
-        <v>141.4477479746177</v>
+        <v>141.4477629305895</v>
       </c>
       <c r="E41" t="n">
-        <v>142.3174706767361</v>
+        <v>142.317485724668</v>
       </c>
       <c r="F41" t="n">
         <v>941983</v>
@@ -1252,16 +1252,16 @@
         <v>44532</v>
       </c>
       <c r="B42" t="n">
-        <v>143.7845611572266</v>
+        <v>143.7845916748047</v>
       </c>
       <c r="C42" t="n">
-        <v>150.5138962665375</v>
+        <v>150.5139282123845</v>
       </c>
       <c r="D42" t="n">
-        <v>143.0466219736957</v>
+        <v>143.0466523346498</v>
       </c>
       <c r="E42" t="n">
-        <v>145.83147442491</v>
+        <v>145.8315053769355</v>
       </c>
       <c r="F42" t="n">
         <v>584287</v>
@@ -1292,16 +1292,16 @@
         <v>44536</v>
       </c>
       <c r="B44" t="n">
-        <v>147.7641906738281</v>
+        <v>147.7642059326172</v>
       </c>
       <c r="C44" t="n">
-        <v>149.327924822433</v>
+        <v>149.3279402427002</v>
       </c>
       <c r="D44" t="n">
-        <v>139.2427149033103</v>
+        <v>139.2427292821338</v>
       </c>
       <c r="E44" t="n">
-        <v>144.9617641723165</v>
+        <v>144.9617791417145</v>
       </c>
       <c r="F44" t="n">
         <v>521095</v>
@@ -1372,16 +1372,16 @@
         <v>44540</v>
       </c>
       <c r="B48" t="n">
-        <v>148.2210083007812</v>
+        <v>148.2210235595703</v>
       </c>
       <c r="C48" t="n">
-        <v>150.2239938125575</v>
+        <v>150.2240092775463</v>
       </c>
       <c r="D48" t="n">
-        <v>146.332232453983</v>
+        <v>146.3322475183298</v>
       </c>
       <c r="E48" t="n">
-        <v>148.115592243811</v>
+        <v>148.1156074917479</v>
       </c>
       <c r="F48" t="n">
         <v>506410</v>
@@ -1492,16 +1492,16 @@
         <v>44550</v>
       </c>
       <c r="B54" t="n">
-        <v>145.9105529785156</v>
+        <v>145.9105682373047</v>
       </c>
       <c r="C54" t="n">
-        <v>146.288316220744</v>
+        <v>146.2883315190382</v>
       </c>
       <c r="D54" t="n">
-        <v>139.2514989527854</v>
+        <v>139.2515135151951</v>
       </c>
       <c r="E54" t="n">
-        <v>144.6455065750673</v>
+        <v>144.6455217015624</v>
       </c>
       <c r="F54" t="n">
         <v>356146</v>
@@ -1512,16 +1512,16 @@
         <v>44551</v>
       </c>
       <c r="B55" t="n">
-        <v>148.9853363037109</v>
+        <v>148.9853210449219</v>
       </c>
       <c r="C55" t="n">
-        <v>149.6442136233681</v>
+        <v>149.6441982970981</v>
       </c>
       <c r="D55" t="n">
-        <v>144.7948862022144</v>
+        <v>144.7948713726031</v>
       </c>
       <c r="E55" t="n">
-        <v>146.3146927995202</v>
+        <v>146.3146778142533</v>
       </c>
       <c r="F55" t="n">
         <v>221674</v>
@@ -1532,16 +1532,16 @@
         <v>44552</v>
       </c>
       <c r="B56" t="n">
-        <v>146.2268218994141</v>
+        <v>146.2268371582031</v>
       </c>
       <c r="C56" t="n">
-        <v>148.9501865656617</v>
+        <v>148.9502021086343</v>
       </c>
       <c r="D56" t="n">
-        <v>144.0744922270013</v>
+        <v>144.0745072611944</v>
       </c>
       <c r="E56" t="n">
-        <v>147.7202743207887</v>
+        <v>147.7202897354198</v>
       </c>
       <c r="F56" t="n">
         <v>439793</v>
@@ -1552,16 +1552,16 @@
         <v>44553</v>
       </c>
       <c r="B57" t="n">
-        <v>148.9238128662109</v>
+        <v>148.923828125</v>
       </c>
       <c r="C57" t="n">
-        <v>149.7759617373248</v>
+        <v>149.7759770834253</v>
       </c>
       <c r="D57" t="n">
-        <v>144.0832533891827</v>
+        <v>144.0832681520062</v>
       </c>
       <c r="E57" t="n">
-        <v>146.2268025740509</v>
+        <v>146.2268175565032</v>
       </c>
       <c r="F57" t="n">
         <v>381841</v>
@@ -1572,16 +1572,16 @@
         <v>44557</v>
       </c>
       <c r="B58" t="n">
-        <v>150.0483245849609</v>
+        <v>150.0482940673828</v>
       </c>
       <c r="C58" t="n">
-        <v>153.6941069039261</v>
+        <v>153.6940756448505</v>
       </c>
       <c r="D58" t="n">
-        <v>147.0438457432459</v>
+        <v>147.0438158367336</v>
       </c>
       <c r="E58" t="n">
-        <v>147.0438457432459</v>
+        <v>147.0438158367336</v>
       </c>
       <c r="F58" t="n">
         <v>232495</v>
@@ -1612,16 +1612,16 @@
         <v>44559</v>
       </c>
       <c r="B60" t="n">
-        <v>139.9894561767578</v>
+        <v>139.9894714355469</v>
       </c>
       <c r="C60" t="n">
-        <v>143.1696326964148</v>
+        <v>143.1696483018417</v>
       </c>
       <c r="D60" t="n">
-        <v>138.4169283251267</v>
+        <v>138.4169434125109</v>
       </c>
       <c r="E60" t="n">
-        <v>142.1857136416904</v>
+        <v>142.1857291398705</v>
       </c>
       <c r="F60" t="n">
         <v>277505</v>
@@ -1652,16 +1652,16 @@
         <v>44564</v>
       </c>
       <c r="B62" t="n">
-        <v>144.8124084472656</v>
+        <v>144.8124389648438</v>
       </c>
       <c r="C62" t="n">
-        <v>144.8124084472656</v>
+        <v>144.8124389648438</v>
       </c>
       <c r="D62" t="n">
-        <v>138.7946718899726</v>
+        <v>138.7947011393807</v>
       </c>
       <c r="E62" t="n">
-        <v>142.1768998632246</v>
+        <v>142.1769298253991</v>
       </c>
       <c r="F62" t="n">
         <v>369633</v>
@@ -1672,16 +1672,16 @@
         <v>44565</v>
       </c>
       <c r="B63" t="n">
-        <v>140.2969055175781</v>
+        <v>140.2969360351562</v>
       </c>
       <c r="C63" t="n">
-        <v>146.499133628787</v>
+        <v>146.4991654954824</v>
       </c>
       <c r="D63" t="n">
-        <v>138.6628896448183</v>
+        <v>138.662919806963</v>
       </c>
       <c r="E63" t="n">
-        <v>144.8124097286623</v>
+        <v>144.8124412284592</v>
       </c>
       <c r="F63" t="n">
         <v>382138</v>
@@ -1712,16 +1712,16 @@
         <v>44567</v>
       </c>
       <c r="B65" t="n">
-        <v>135.2718811035156</v>
+        <v>135.2718963623047</v>
       </c>
       <c r="C65" t="n">
-        <v>137.0288870115152</v>
+        <v>137.0289024684961</v>
       </c>
       <c r="D65" t="n">
-        <v>129.5879659187458</v>
+        <v>129.5879805363842</v>
       </c>
       <c r="E65" t="n">
-        <v>134.8502034389653</v>
+        <v>134.8502186501887</v>
       </c>
       <c r="F65" t="n">
         <v>814212</v>
@@ -1732,16 +1732,16 @@
         <v>44568</v>
       </c>
       <c r="B66" t="n">
-        <v>137.23974609375</v>
+        <v>137.2397308349609</v>
       </c>
       <c r="C66" t="n">
-        <v>142.1857225025721</v>
+        <v>142.1857066938723</v>
       </c>
       <c r="D66" t="n">
-        <v>134.2001196747043</v>
+        <v>134.2001047538714</v>
       </c>
       <c r="E66" t="n">
-        <v>137.9249773931206</v>
+        <v>137.9249620581452</v>
       </c>
       <c r="F66" t="n">
         <v>686988</v>
@@ -1752,16 +1752,16 @@
         <v>44571</v>
       </c>
       <c r="B67" t="n">
-        <v>137.5208435058594</v>
+        <v>137.5208740234375</v>
       </c>
       <c r="C67" t="n">
-        <v>138.4696282839642</v>
+        <v>138.4696590120894</v>
       </c>
       <c r="D67" t="n">
-        <v>131.9072102890741</v>
+        <v>131.9072395609175</v>
       </c>
       <c r="E67" t="n">
-        <v>137.2309493336996</v>
+        <v>137.2309797869466</v>
       </c>
       <c r="F67" t="n">
         <v>730000</v>
@@ -1772,16 +1772,16 @@
         <v>44572</v>
       </c>
       <c r="B68" t="n">
-        <v>146.3849487304688</v>
+        <v>146.3849639892578</v>
       </c>
       <c r="C68" t="n">
-        <v>149.0116639338405</v>
+        <v>149.0116794664315</v>
       </c>
       <c r="D68" t="n">
-        <v>133.6290823276248</v>
+        <v>133.6290962567753</v>
       </c>
       <c r="E68" t="n">
-        <v>137.573565341825</v>
+        <v>137.5735796821382</v>
       </c>
       <c r="F68" t="n">
         <v>715197</v>
@@ -1812,16 +1812,16 @@
         <v>44574</v>
       </c>
       <c r="B70" t="n">
-        <v>142.9675750732422</v>
+        <v>142.9675903320312</v>
       </c>
       <c r="C70" t="n">
-        <v>149.6529830666293</v>
+        <v>149.6529990389454</v>
       </c>
       <c r="D70" t="n">
-        <v>141.7201024913939</v>
+        <v>141.7201176170415</v>
       </c>
       <c r="E70" t="n">
-        <v>149.4860653611546</v>
+        <v>149.4860813156558</v>
       </c>
       <c r="F70" t="n">
         <v>401557</v>
@@ -1852,16 +1852,16 @@
         <v>44578</v>
       </c>
       <c r="B72" t="n">
-        <v>138.803466796875</v>
+        <v>138.8034820556641</v>
       </c>
       <c r="C72" t="n">
-        <v>140.2705651221538</v>
+        <v>140.2705805422223</v>
       </c>
       <c r="D72" t="n">
-        <v>136.9058971981742</v>
+        <v>136.9059122483617</v>
       </c>
       <c r="E72" t="n">
-        <v>138.065527532344</v>
+        <v>138.0655427100108</v>
       </c>
       <c r="F72" t="n">
         <v>75291</v>
@@ -1872,16 +1872,16 @@
         <v>44579</v>
       </c>
       <c r="B73" t="n">
-        <v>133.1722564697266</v>
+        <v>133.1722717285156</v>
       </c>
       <c r="C73" t="n">
-        <v>138.8034634905354</v>
+        <v>138.8034793945444</v>
       </c>
       <c r="D73" t="n">
-        <v>133.1722564697266</v>
+        <v>133.1722717285156</v>
       </c>
       <c r="E73" t="n">
-        <v>138.1885141180745</v>
+        <v>138.1885299516231</v>
       </c>
       <c r="F73" t="n">
         <v>435258</v>
@@ -1892,16 +1892,16 @@
         <v>44580</v>
       </c>
       <c r="B74" t="n">
-        <v>139.6116943359375</v>
+        <v>139.6116790771484</v>
       </c>
       <c r="C74" t="n">
-        <v>141.6937421442108</v>
+        <v>141.6937266578653</v>
       </c>
       <c r="D74" t="n">
-        <v>133.0492758918774</v>
+        <v>133.0492613503245</v>
       </c>
       <c r="E74" t="n">
-        <v>133.5324552200335</v>
+        <v>133.5324406256718</v>
       </c>
       <c r="F74" t="n">
         <v>381153</v>
@@ -1952,16 +1952,16 @@
         <v>44585</v>
       </c>
       <c r="B77" t="n">
-        <v>143.1696166992188</v>
+        <v>143.1696319580078</v>
       </c>
       <c r="C77" t="n">
-        <v>145.3307262964993</v>
+        <v>145.330741785616</v>
       </c>
       <c r="D77" t="n">
-        <v>136.4490749694081</v>
+        <v>136.4490895119325</v>
       </c>
       <c r="E77" t="n">
-        <v>143.0202728168774</v>
+        <v>143.0202880597496</v>
       </c>
       <c r="F77" t="n">
         <v>940613</v>
@@ -1972,16 +1972,16 @@
         <v>44586</v>
       </c>
       <c r="B78" t="n">
-        <v>147.316162109375</v>
+        <v>147.3161773681641</v>
       </c>
       <c r="C78" t="n">
-        <v>149.5211996922916</v>
+        <v>149.5212151794752</v>
       </c>
       <c r="D78" t="n">
-        <v>140.165148619023</v>
+        <v>140.1651631371207</v>
       </c>
       <c r="E78" t="n">
-        <v>140.165148619023</v>
+        <v>140.1651631371207</v>
       </c>
       <c r="F78" t="n">
         <v>456302</v>
@@ -2012,16 +2012,16 @@
         <v>44588</v>
       </c>
       <c r="B80" t="n">
-        <v>149.4860534667969</v>
+        <v>149.486083984375</v>
       </c>
       <c r="C80" t="n">
-        <v>156.5667845437585</v>
+        <v>156.5668165068679</v>
       </c>
       <c r="D80" t="n">
-        <v>147.3249304811154</v>
+        <v>147.3249605575002</v>
       </c>
       <c r="E80" t="n">
-        <v>151.5417469914199</v>
+        <v>151.5417779286678</v>
       </c>
       <c r="F80" t="n">
         <v>697237</v>
@@ -2072,16 +2072,16 @@
         <v>44593</v>
       </c>
       <c r="B83" t="n">
-        <v>155.5828704833984</v>
+        <v>155.5828857421875</v>
       </c>
       <c r="C83" t="n">
-        <v>157.3574367073448</v>
+        <v>157.3574521401745</v>
       </c>
       <c r="D83" t="n">
-        <v>151.1200740988831</v>
+        <v>151.1200889199835</v>
       </c>
       <c r="E83" t="n">
-        <v>152.4378284618541</v>
+        <v>152.4378434121932</v>
       </c>
       <c r="F83" t="n">
         <v>577815</v>
@@ -2092,16 +2092,16 @@
         <v>44594</v>
       </c>
       <c r="B84" t="n">
-        <v>148.9940948486328</v>
+        <v>148.9941101074219</v>
       </c>
       <c r="C84" t="n">
-        <v>158.1305195023691</v>
+        <v>158.1305356968381</v>
       </c>
       <c r="D84" t="n">
-        <v>148.9062391980643</v>
+        <v>148.9062544478559</v>
       </c>
       <c r="E84" t="n">
-        <v>155.8024922160959</v>
+        <v>155.8025081721468</v>
       </c>
       <c r="F84" t="n">
         <v>466282</v>
@@ -2112,16 +2112,16 @@
         <v>44595</v>
       </c>
       <c r="B85" t="n">
-        <v>146.270751953125</v>
+        <v>146.2707366943359</v>
       </c>
       <c r="C85" t="n">
-        <v>149.9604619340272</v>
+        <v>149.960446290332</v>
       </c>
       <c r="D85" t="n">
-        <v>145.5415928423091</v>
+        <v>145.5415776595851</v>
       </c>
       <c r="E85" t="n">
-        <v>149.2137424144391</v>
+        <v>149.2137268486408</v>
       </c>
       <c r="F85" t="n">
         <v>228387</v>
@@ -2152,16 +2152,16 @@
         <v>44599</v>
       </c>
       <c r="B87" t="n">
-        <v>147.1228942871094</v>
+        <v>147.1229095458984</v>
       </c>
       <c r="C87" t="n">
-        <v>152.183066597055</v>
+        <v>152.1830823806577</v>
       </c>
       <c r="D87" t="n">
-        <v>146.709996816492</v>
+        <v>146.7100120324576</v>
       </c>
       <c r="E87" t="n">
-        <v>149.5651314850764</v>
+        <v>149.5651469971611</v>
       </c>
       <c r="F87" t="n">
         <v>353300</v>
@@ -2192,16 +2192,16 @@
         <v>44601</v>
       </c>
       <c r="B89" t="n">
-        <v>157.5155944824219</v>
+        <v>157.5156097412109</v>
       </c>
       <c r="C89" t="n">
-        <v>159.7996942960607</v>
+        <v>159.7997097761142</v>
       </c>
       <c r="D89" t="n">
-        <v>151.4275615710859</v>
+        <v>151.4275762401174</v>
       </c>
       <c r="E89" t="n">
-        <v>153.7380288078784</v>
+        <v>153.7380437007286</v>
       </c>
       <c r="F89" t="n">
         <v>1361639</v>
@@ -2252,16 +2252,16 @@
         <v>44606</v>
       </c>
       <c r="B92" t="n">
-        <v>152.9473724365234</v>
+        <v>152.9473876953125</v>
       </c>
       <c r="C92" t="n">
-        <v>157.9196890589268</v>
+        <v>157.9197048137788</v>
       </c>
       <c r="D92" t="n">
-        <v>152.0688694665374</v>
+        <v>152.0688846376827</v>
       </c>
       <c r="E92" t="n">
-        <v>156.0045590187052</v>
+        <v>156.0045745824943</v>
       </c>
       <c r="F92" t="n">
         <v>409040</v>
@@ -2272,16 +2272,16 @@
         <v>44607</v>
       </c>
       <c r="B93" t="n">
-        <v>161.1437835693359</v>
+        <v>161.143798828125</v>
       </c>
       <c r="C93" t="n">
-        <v>161.8202345685366</v>
+        <v>161.8202498913792</v>
       </c>
       <c r="D93" t="n">
-        <v>154.6252935362757</v>
+        <v>154.6253081778255</v>
       </c>
       <c r="E93" t="n">
-        <v>156.2768833091691</v>
+        <v>156.2768981071088</v>
       </c>
       <c r="F93" t="n">
         <v>501987</v>
@@ -2292,16 +2292,16 @@
         <v>44608</v>
       </c>
       <c r="B94" t="n">
-        <v>160.8099822998047</v>
+        <v>160.8099670410156</v>
       </c>
       <c r="C94" t="n">
-        <v>164.6841838787326</v>
+        <v>164.6841682523319</v>
       </c>
       <c r="D94" t="n">
-        <v>158.0690437312643</v>
+        <v>158.0690287325549</v>
       </c>
       <c r="E94" t="n">
-        <v>161.1438043358308</v>
+        <v>161.1437890453663</v>
       </c>
       <c r="F94" t="n">
         <v>383335</v>
@@ -2352,16 +2352,16 @@
         <v>44613</v>
       </c>
       <c r="B97" t="n">
-        <v>150.3118591308594</v>
+        <v>150.3118743896484</v>
       </c>
       <c r="C97" t="n">
-        <v>155.6882928603806</v>
+        <v>155.6883086649541</v>
       </c>
       <c r="D97" t="n">
-        <v>149.5827000785075</v>
+        <v>149.5827152632765</v>
       </c>
       <c r="E97" t="n">
-        <v>154.6165181959493</v>
+        <v>154.6165338917224</v>
       </c>
       <c r="F97" t="n">
         <v>185476</v>
@@ -2392,16 +2392,16 @@
         <v>44615</v>
       </c>
       <c r="B99" t="n">
-        <v>147.2722320556641</v>
+        <v>147.2722473144531</v>
       </c>
       <c r="C99" t="n">
-        <v>153.5623163117172</v>
+        <v>153.5623322222181</v>
       </c>
       <c r="D99" t="n">
-        <v>146.9647506652708</v>
+        <v>146.9647658922019</v>
       </c>
       <c r="E99" t="n">
-        <v>150.3557725436555</v>
+        <v>150.3557881219284</v>
       </c>
       <c r="F99" t="n">
         <v>373832</v>
@@ -2412,16 +2412,16 @@
         <v>44616</v>
       </c>
       <c r="B100" t="n">
-        <v>148.1067962646484</v>
+        <v>148.1068267822266</v>
       </c>
       <c r="C100" t="n">
-        <v>148.1067962646484</v>
+        <v>148.1068267822266</v>
       </c>
       <c r="D100" t="n">
-        <v>139.2427054859054</v>
+        <v>139.2427341770273</v>
       </c>
       <c r="E100" t="n">
-        <v>143.3277384867851</v>
+        <v>143.3277680196328</v>
       </c>
       <c r="F100" t="n">
         <v>704723</v>
@@ -2432,16 +2432,16 @@
         <v>44617</v>
       </c>
       <c r="B101" t="n">
-        <v>145.1374664306641</v>
+        <v>145.1374969482422</v>
       </c>
       <c r="C101" t="n">
-        <v>149.1697914251255</v>
+        <v>149.1698227905674</v>
       </c>
       <c r="D101" t="n">
-        <v>141.2456917090224</v>
+        <v>141.2457214082899</v>
       </c>
       <c r="E101" t="n">
-        <v>145.875405631306</v>
+        <v>145.8754363040482</v>
       </c>
       <c r="F101" t="n">
         <v>765160</v>
@@ -2472,16 +2472,16 @@
         <v>44623</v>
       </c>
       <c r="B103" t="n">
-        <v>136.16796875</v>
+        <v>136.1679534912109</v>
       </c>
       <c r="C103" t="n">
-        <v>143.3365566445935</v>
+        <v>143.3365405825027</v>
       </c>
       <c r="D103" t="n">
-        <v>135.4915176680011</v>
+        <v>135.4915024850142</v>
       </c>
       <c r="E103" t="n">
-        <v>142.5107616570688</v>
+        <v>142.5107456875154</v>
       </c>
       <c r="F103" t="n">
         <v>801826</v>
@@ -2492,16 +2492,16 @@
         <v>44624</v>
       </c>
       <c r="B104" t="n">
-        <v>129.4034881591797</v>
+        <v>129.4035034179688</v>
       </c>
       <c r="C104" t="n">
-        <v>139.2163645736173</v>
+        <v>139.216380989505</v>
       </c>
       <c r="D104" t="n">
-        <v>128.5864734391812</v>
+        <v>128.5864886016308</v>
       </c>
       <c r="E104" t="n">
-        <v>134.2440346232008</v>
+        <v>134.2440504527695</v>
       </c>
       <c r="F104" t="n">
         <v>615045</v>
@@ -2512,16 +2512,16 @@
         <v>44627</v>
       </c>
       <c r="B105" t="n">
-        <v>117.0781021118164</v>
+        <v>117.0780868530273</v>
       </c>
       <c r="C105" t="n">
-        <v>130.2644277157113</v>
+        <v>130.2644107383485</v>
       </c>
       <c r="D105" t="n">
-        <v>117.0781021118164</v>
+        <v>117.0780868530273</v>
       </c>
       <c r="E105" t="n">
-        <v>129.5791964273345</v>
+        <v>129.5791795392778</v>
       </c>
       <c r="F105" t="n">
         <v>1053703</v>
@@ -2532,16 +2532,16 @@
         <v>44628</v>
       </c>
       <c r="B106" t="n">
-        <v>124.4399566650391</v>
+        <v>124.43994140625</v>
       </c>
       <c r="C106" t="n">
-        <v>125.6083673770213</v>
+        <v>125.6083519749621</v>
       </c>
       <c r="D106" t="n">
-        <v>115.8657713786687</v>
+        <v>115.8657571712436</v>
       </c>
       <c r="E106" t="n">
-        <v>118.3431565134491</v>
+        <v>118.3431420022477</v>
       </c>
       <c r="F106" t="n">
         <v>713320</v>
@@ -2552,16 +2552,16 @@
         <v>44629</v>
       </c>
       <c r="B107" t="n">
-        <v>138.6804809570312</v>
+        <v>138.6804962158203</v>
       </c>
       <c r="C107" t="n">
-        <v>138.6804809570312</v>
+        <v>138.6804962158203</v>
       </c>
       <c r="D107" t="n">
-        <v>124.6595674982775</v>
+        <v>124.6595812143682</v>
       </c>
       <c r="E107" t="n">
-        <v>124.7474231582329</v>
+        <v>124.7474368839902</v>
       </c>
       <c r="F107" t="n">
         <v>891534</v>
@@ -2572,16 +2572,16 @@
         <v>44630</v>
       </c>
       <c r="B108" t="n">
-        <v>135.7814025878906</v>
+        <v>135.7814178466797</v>
       </c>
       <c r="C108" t="n">
-        <v>139.1636440278797</v>
+        <v>139.163659666757</v>
       </c>
       <c r="D108" t="n">
-        <v>133.2425298083679</v>
+        <v>133.2425447818445</v>
       </c>
       <c r="E108" t="n">
-        <v>137.4857003148507</v>
+        <v>137.4857157651647</v>
       </c>
       <c r="F108" t="n">
         <v>543810</v>
@@ -2612,16 +2612,16 @@
         <v>44634</v>
       </c>
       <c r="B110" t="n">
-        <v>126.6801071166992</v>
+        <v>126.6801223754883</v>
       </c>
       <c r="C110" t="n">
-        <v>133.8311197133267</v>
+        <v>133.8311358334649</v>
       </c>
       <c r="D110" t="n">
-        <v>126.6801071166992</v>
+        <v>126.6801223754883</v>
       </c>
       <c r="E110" t="n">
-        <v>131.6173022033344</v>
+        <v>131.6173180568153</v>
       </c>
       <c r="F110" t="n">
         <v>265850</v>
@@ -2652,16 +2652,16 @@
         <v>44636</v>
       </c>
       <c r="B112" t="n">
-        <v>139.4886932373047</v>
+        <v>139.4887084960938</v>
       </c>
       <c r="C112" t="n">
-        <v>142.3438277410615</v>
+        <v>142.3438433121762</v>
       </c>
       <c r="D112" t="n">
-        <v>132.6539415591642</v>
+        <v>132.6539560702938</v>
       </c>
       <c r="E112" t="n">
-        <v>132.6539415591642</v>
+        <v>132.6539560702938</v>
       </c>
       <c r="F112" t="n">
         <v>861619</v>
@@ -2692,16 +2692,16 @@
         <v>44638</v>
       </c>
       <c r="B114" t="n">
-        <v>142.3174743652344</v>
+        <v>142.3174896240234</v>
       </c>
       <c r="C114" t="n">
-        <v>145.1199008509126</v>
+        <v>145.1199164101681</v>
       </c>
       <c r="D114" t="n">
-        <v>137.1518728579682</v>
+        <v>137.1518875629193</v>
       </c>
       <c r="E114" t="n">
-        <v>138.6189711394427</v>
+        <v>138.618986001691</v>
       </c>
       <c r="F114" t="n">
         <v>570545</v>
@@ -2712,16 +2712,16 @@
         <v>44641</v>
       </c>
       <c r="B115" t="n">
-        <v>139.7698211669922</v>
+        <v>139.7698364257812</v>
       </c>
       <c r="C115" t="n">
-        <v>143.0642071460549</v>
+        <v>143.0642227644949</v>
       </c>
       <c r="D115" t="n">
-        <v>138.4169191515182</v>
+        <v>138.4169342626098</v>
       </c>
       <c r="E115" t="n">
-        <v>141.4828991951266</v>
+        <v>141.4829146409339</v>
       </c>
       <c r="F115" t="n">
         <v>351500</v>
@@ -2772,16 +2772,16 @@
         <v>44644</v>
       </c>
       <c r="B118" t="n">
-        <v>136.2733612060547</v>
+        <v>136.2733764648438</v>
       </c>
       <c r="C118" t="n">
-        <v>137.2660737409138</v>
+        <v>137.2660891108588</v>
       </c>
       <c r="D118" t="n">
-        <v>132.4870159727677</v>
+        <v>132.4870308075925</v>
       </c>
       <c r="E118" t="n">
-        <v>133.2776766004494</v>
+        <v>133.2776915238059</v>
       </c>
       <c r="F118" t="n">
         <v>438667</v>
@@ -2792,16 +2792,16 @@
         <v>44645</v>
       </c>
       <c r="B119" t="n">
-        <v>133.9277648925781</v>
+        <v>133.9277496337891</v>
       </c>
       <c r="C119" t="n">
-        <v>140.0333573879609</v>
+        <v>140.0333414335435</v>
       </c>
       <c r="D119" t="n">
-        <v>133.4182316002086</v>
+        <v>133.4182163994722</v>
       </c>
       <c r="E119" t="n">
-        <v>135.307020884751</v>
+        <v>135.3070054688192</v>
       </c>
       <c r="F119" t="n">
         <v>403765</v>
@@ -2812,16 +2812,16 @@
         <v>44648</v>
       </c>
       <c r="B120" t="n">
-        <v>134.9380645751953</v>
+        <v>134.9380798339844</v>
       </c>
       <c r="C120" t="n">
-        <v>139.8488930702739</v>
+        <v>139.8489088843792</v>
       </c>
       <c r="D120" t="n">
-        <v>132.4782535231423</v>
+        <v>132.478268503776</v>
       </c>
       <c r="E120" t="n">
-        <v>134.762353253348</v>
+        <v>134.7623684922676</v>
       </c>
       <c r="F120" t="n">
         <v>527873</v>
@@ -2832,16 +2832,16 @@
         <v>44649</v>
       </c>
       <c r="B121" t="n">
-        <v>139.5765533447266</v>
+        <v>139.5765686035156</v>
       </c>
       <c r="C121" t="n">
-        <v>140.4638365007489</v>
+        <v>140.4638518565375</v>
       </c>
       <c r="D121" t="n">
-        <v>135.1576845672471</v>
+        <v>135.1576993429566</v>
       </c>
       <c r="E121" t="n">
-        <v>137.9249635049115</v>
+        <v>137.9249785831454</v>
       </c>
       <c r="F121" t="n">
         <v>830631</v>
@@ -2912,16 +2912,16 @@
         <v>44655</v>
       </c>
       <c r="B125" t="n">
-        <v>129.0872192382812</v>
+        <v>129.0872344970703</v>
       </c>
       <c r="C125" t="n">
-        <v>129.0872192382812</v>
+        <v>129.0872344970703</v>
       </c>
       <c r="D125" t="n">
-        <v>125.6346958448618</v>
+        <v>125.6347106955444</v>
       </c>
       <c r="E125" t="n">
-        <v>127.3829214547252</v>
+        <v>127.3829365120573</v>
       </c>
       <c r="F125" t="n">
         <v>325077</v>
@@ -2972,16 +2972,16 @@
         <v>44658</v>
       </c>
       <c r="B128" t="n">
-        <v>126.9524459838867</v>
+        <v>126.9524536132812</v>
       </c>
       <c r="C128" t="n">
-        <v>128.604035682919</v>
+        <v>128.6040434115682</v>
       </c>
       <c r="D128" t="n">
-        <v>122.9991830356934</v>
+        <v>122.9991904275108</v>
       </c>
       <c r="E128" t="n">
-        <v>124.756188790446</v>
+        <v>124.7561962878532</v>
       </c>
       <c r="F128" t="n">
         <v>544395</v>
@@ -3012,16 +3012,16 @@
         <v>44662</v>
       </c>
       <c r="B130" t="n">
-        <v>121.8659362792969</v>
+        <v>121.8659286499023</v>
       </c>
       <c r="C130" t="n">
-        <v>123.5702342307505</v>
+        <v>123.5702264946588</v>
       </c>
       <c r="D130" t="n">
-        <v>119.3621973869214</v>
+        <v>119.362189914273</v>
       </c>
       <c r="E130" t="n">
-        <v>122.9904190381111</v>
+        <v>122.9904113383186</v>
       </c>
       <c r="F130" t="n">
         <v>348006</v>
@@ -3032,16 +3032,16 @@
         <v>44663</v>
       </c>
       <c r="B131" t="n">
-        <v>118.2025833129883</v>
+        <v>118.2025909423828</v>
       </c>
       <c r="C131" t="n">
-        <v>125.1691057854541</v>
+        <v>125.1691138645034</v>
       </c>
       <c r="D131" t="n">
-        <v>118.1762292949377</v>
+        <v>118.1762369226312</v>
       </c>
       <c r="E131" t="n">
-        <v>122.9904220622919</v>
+        <v>122.9904300007179</v>
       </c>
       <c r="F131" t="n">
         <v>576598</v>
@@ -3092,16 +3092,16 @@
         <v>44669</v>
       </c>
       <c r="B134" t="n">
-        <v>112.4483871459961</v>
+        <v>112.4483795166016</v>
       </c>
       <c r="C134" t="n">
-        <v>115.1366042564223</v>
+        <v>115.1365964446377</v>
       </c>
       <c r="D134" t="n">
-        <v>112.0530634659144</v>
+        <v>112.0530558633418</v>
       </c>
       <c r="E134" t="n">
-        <v>114.2053931951523</v>
+        <v>114.2053854465485</v>
       </c>
       <c r="F134" t="n">
         <v>589431</v>
@@ -3112,16 +3112,16 @@
         <v>44670</v>
       </c>
       <c r="B135" t="n">
-        <v>115.2683868408203</v>
+        <v>115.2683792114258</v>
       </c>
       <c r="C135" t="n">
-        <v>116.3137941716854</v>
+        <v>116.3137864730974</v>
       </c>
       <c r="D135" t="n">
-        <v>111.1306317296507</v>
+        <v>111.1306243741263</v>
       </c>
       <c r="E135" t="n">
-        <v>112.5362419198087</v>
+        <v>112.5362344712496</v>
       </c>
       <c r="F135" t="n">
         <v>794893</v>
@@ -3192,16 +3192,16 @@
         <v>44677</v>
       </c>
       <c r="B139" t="n">
-        <v>107.4057769775391</v>
+        <v>107.4057693481445</v>
       </c>
       <c r="C139" t="n">
-        <v>112.6943620057829</v>
+        <v>112.6943540007223</v>
       </c>
       <c r="D139" t="n">
-        <v>106.342789168451</v>
+        <v>106.342781614564</v>
       </c>
       <c r="E139" t="n">
-        <v>109.9270762585565</v>
+        <v>109.9270684500656</v>
       </c>
       <c r="F139" t="n">
         <v>615417</v>
@@ -3272,16 +3272,16 @@
         <v>44683</v>
       </c>
       <c r="B143" t="n">
-        <v>107.1685791015625</v>
+        <v>107.168571472168</v>
       </c>
       <c r="C143" t="n">
-        <v>108.5566154502563</v>
+        <v>108.5566077220467</v>
       </c>
       <c r="D143" t="n">
-        <v>104.4627949552132</v>
+        <v>104.4627875184451</v>
       </c>
       <c r="E143" t="n">
-        <v>107.1861529149336</v>
+        <v>107.186145284288</v>
       </c>
       <c r="F143" t="n">
         <v>497573</v>
@@ -3292,16 +3292,16 @@
         <v>44684</v>
       </c>
       <c r="B144" t="n">
-        <v>102.7848510742188</v>
+        <v>102.7848587036133</v>
       </c>
       <c r="C144" t="n">
-        <v>107.1773660773905</v>
+        <v>107.1773740328275</v>
       </c>
       <c r="D144" t="n">
-        <v>101.8097122073189</v>
+        <v>101.809719764332</v>
       </c>
       <c r="E144" t="n">
-        <v>107.1422251530716</v>
+        <v>107.1422331059002</v>
       </c>
       <c r="F144" t="n">
         <v>541792</v>
@@ -3312,16 +3312,16 @@
         <v>44685</v>
       </c>
       <c r="B145" t="n">
-        <v>94.52691650390625</v>
+        <v>94.52692413330078</v>
       </c>
       <c r="C145" t="n">
-        <v>100.4128903167997</v>
+        <v>100.4128984212591</v>
       </c>
       <c r="D145" t="n">
-        <v>84.54712241090455</v>
+        <v>84.54712923481648</v>
       </c>
       <c r="E145" t="n">
-        <v>100.4128903167997</v>
+        <v>100.4128984212591</v>
       </c>
       <c r="F145" t="n">
         <v>3193940</v>
@@ -3332,16 +3332,16 @@
         <v>44686</v>
       </c>
       <c r="B146" t="n">
-        <v>93.73627471923828</v>
+        <v>93.73625946044922</v>
       </c>
       <c r="C146" t="n">
-        <v>95.51085467081299</v>
+        <v>95.51083912315028</v>
       </c>
       <c r="D146" t="n">
-        <v>91.4609549892096</v>
+        <v>91.46094010080674</v>
       </c>
       <c r="E146" t="n">
-        <v>94.4390798549514</v>
+        <v>94.43906448175674</v>
       </c>
       <c r="F146" t="n">
         <v>1265698</v>
@@ -3352,16 +3352,16 @@
         <v>44687</v>
       </c>
       <c r="B147" t="n">
-        <v>90.31011199951172</v>
+        <v>90.31011962890625</v>
       </c>
       <c r="C147" t="n">
-        <v>95.44056635451888</v>
+        <v>95.44057441733399</v>
       </c>
       <c r="D147" t="n">
-        <v>90.31011199951172</v>
+        <v>90.31011962890625</v>
       </c>
       <c r="E147" t="n">
-        <v>93.73626837240195</v>
+        <v>93.73627629123804</v>
       </c>
       <c r="F147" t="n">
         <v>602571</v>
@@ -3392,16 +3392,16 @@
         <v>44691</v>
       </c>
       <c r="B149" t="n">
-        <v>84.51197814941406</v>
+        <v>84.51198577880859</v>
       </c>
       <c r="C149" t="n">
-        <v>89.03626952396259</v>
+        <v>89.03627756179158</v>
       </c>
       <c r="D149" t="n">
-        <v>83.46656423318744</v>
+        <v>83.46657176820631</v>
       </c>
       <c r="E149" t="n">
-        <v>85.83851943414338</v>
+        <v>85.83852718329263</v>
       </c>
       <c r="F149" t="n">
         <v>595901</v>
@@ -3452,16 +3452,16 @@
         <v>44694</v>
       </c>
       <c r="B152" t="n">
-        <v>89.78300476074219</v>
+        <v>89.78299713134766</v>
       </c>
       <c r="C152" t="n">
-        <v>92.42730069221749</v>
+        <v>92.42729283812145</v>
       </c>
       <c r="D152" t="n">
-        <v>87.90300885931281</v>
+        <v>87.90300138967268</v>
       </c>
       <c r="E152" t="n">
-        <v>90.57365880864381</v>
+        <v>90.57365111206272</v>
       </c>
       <c r="F152" t="n">
         <v>780406</v>
@@ -3492,16 +3492,16 @@
         <v>44698</v>
       </c>
       <c r="B154" t="n">
-        <v>86.98057556152344</v>
+        <v>86.98058319091797</v>
       </c>
       <c r="C154" t="n">
-        <v>88.24561520248869</v>
+        <v>88.24562294284463</v>
       </c>
       <c r="D154" t="n">
-        <v>84.59104655839022</v>
+        <v>84.59105397819015</v>
       </c>
       <c r="E154" t="n">
-        <v>85.39048072641835</v>
+        <v>85.39048821633966</v>
       </c>
       <c r="F154" t="n">
         <v>1257850</v>
@@ -3512,16 +3512,16 @@
         <v>44699</v>
       </c>
       <c r="B155" t="n">
-        <v>84.09909057617188</v>
+        <v>84.09909820556641</v>
       </c>
       <c r="C155" t="n">
-        <v>87.19141801931744</v>
+        <v>87.19142592924517</v>
       </c>
       <c r="D155" t="n">
-        <v>83.82675010328479</v>
+        <v>83.82675770797285</v>
       </c>
       <c r="E155" t="n">
-        <v>86.83122859168591</v>
+        <v>86.83123646893756</v>
       </c>
       <c r="F155" t="n">
         <v>617555</v>
@@ -3552,16 +3552,16 @@
         <v>44701</v>
       </c>
       <c r="B157" t="n">
-        <v>91.24131774902344</v>
+        <v>91.24132537841797</v>
       </c>
       <c r="C157" t="n">
-        <v>92.66449495378507</v>
+        <v>92.66450270218249</v>
       </c>
       <c r="D157" t="n">
-        <v>87.70095190087078</v>
+        <v>87.70095923422785</v>
       </c>
       <c r="E157" t="n">
-        <v>89.60730171103826</v>
+        <v>89.60730920380003</v>
       </c>
       <c r="F157" t="n">
         <v>709088</v>
@@ -3572,16 +3572,16 @@
         <v>44704</v>
       </c>
       <c r="B158" t="n">
-        <v>91.02169036865234</v>
+        <v>91.02169799804688</v>
       </c>
       <c r="C158" t="n">
-        <v>92.67327348694673</v>
+        <v>92.67328125477616</v>
       </c>
       <c r="D158" t="n">
-        <v>90.09925959845417</v>
+        <v>90.09926715053099</v>
       </c>
       <c r="E158" t="n">
-        <v>90.31010513032238</v>
+        <v>90.31011270007218</v>
       </c>
       <c r="F158" t="n">
         <v>925415</v>
@@ -3592,16 +3592,16 @@
         <v>44705</v>
       </c>
       <c r="B159" t="n">
-        <v>87.67459869384766</v>
+        <v>87.67461395263672</v>
       </c>
       <c r="C159" t="n">
-        <v>90.02020000464306</v>
+        <v>90.02021567165795</v>
       </c>
       <c r="D159" t="n">
-        <v>85.55740332846713</v>
+        <v>85.55741821878189</v>
       </c>
       <c r="E159" t="n">
-        <v>88.43011178085561</v>
+        <v>88.43012717113334</v>
       </c>
       <c r="F159" t="n">
         <v>569845</v>
@@ -3632,16 +3632,16 @@
         <v>44707</v>
       </c>
       <c r="B161" t="n">
-        <v>94.81682586669922</v>
+        <v>94.81683349609375</v>
       </c>
       <c r="C161" t="n">
-        <v>96.26635710839928</v>
+        <v>96.2663648544297</v>
       </c>
       <c r="D161" t="n">
-        <v>89.00992069595566</v>
+        <v>89.0099278581001</v>
       </c>
       <c r="E161" t="n">
-        <v>89.41403125806036</v>
+        <v>89.41403845272137</v>
       </c>
       <c r="F161" t="n">
         <v>700096</v>
@@ -3652,16 +3652,16 @@
         <v>44708</v>
       </c>
       <c r="B162" t="n">
-        <v>96.65289306640625</v>
+        <v>96.65290069580078</v>
       </c>
       <c r="C162" t="n">
-        <v>97.42597996362124</v>
+        <v>97.42598765404017</v>
       </c>
       <c r="D162" t="n">
-        <v>93.57813269507206</v>
+        <v>93.57814008175724</v>
       </c>
       <c r="E162" t="n">
-        <v>94.57084533309663</v>
+        <v>94.5708527981426</v>
       </c>
       <c r="F162" t="n">
         <v>410015</v>
@@ -3712,16 +3712,16 @@
         <v>44713</v>
       </c>
       <c r="B165" t="n">
-        <v>92.17253112792969</v>
+        <v>92.17253875732422</v>
       </c>
       <c r="C165" t="n">
-        <v>96.28392534576922</v>
+        <v>96.28393331547606</v>
       </c>
       <c r="D165" t="n">
-        <v>91.18861207909531</v>
+        <v>91.18861962704793</v>
       </c>
       <c r="E165" t="n">
-        <v>95.12430167932452</v>
+        <v>95.12430955304588</v>
       </c>
       <c r="F165" t="n">
         <v>372179</v>
@@ -3752,16 +3752,16 @@
         <v>44715</v>
       </c>
       <c r="B167" t="n">
-        <v>94.96617126464844</v>
+        <v>94.96616363525391</v>
       </c>
       <c r="C167" t="n">
-        <v>97.28541860706112</v>
+        <v>97.28541079134285</v>
       </c>
       <c r="D167" t="n">
-        <v>93.93832438157946</v>
+        <v>93.93831683476013</v>
       </c>
       <c r="E167" t="n">
-        <v>96.63532827534817</v>
+        <v>96.63532051185686</v>
       </c>
       <c r="F167" t="n">
         <v>452357</v>
@@ -3792,16 +3792,16 @@
         <v>44719</v>
       </c>
       <c r="B169" t="n">
-        <v>100.5710220336914</v>
+        <v>100.5710296630859</v>
       </c>
       <c r="C169" t="n">
-        <v>101.2035385362447</v>
+        <v>101.2035462136224</v>
       </c>
       <c r="D169" t="n">
-        <v>93.36729372419249</v>
+        <v>93.36730080710669</v>
       </c>
       <c r="E169" t="n">
-        <v>94.36000636076696</v>
+        <v>94.36001351898909</v>
       </c>
       <c r="F169" t="n">
         <v>669503</v>
@@ -3812,16 +3812,16 @@
         <v>44720</v>
       </c>
       <c r="B170" t="n">
-        <v>97.07457733154297</v>
+        <v>97.0745849609375</v>
       </c>
       <c r="C170" t="n">
-        <v>100.0439149311568</v>
+        <v>100.0439227939208</v>
       </c>
       <c r="D170" t="n">
-        <v>97.07457733154297</v>
+        <v>97.0745849609375</v>
       </c>
       <c r="E170" t="n">
-        <v>98.75252120666485</v>
+        <v>98.75252896793423</v>
       </c>
       <c r="F170" t="n">
         <v>671896</v>
@@ -3892,16 +3892,16 @@
         <v>44726</v>
       </c>
       <c r="B174" t="n">
-        <v>85.73310852050781</v>
+        <v>85.73310089111328</v>
       </c>
       <c r="C174" t="n">
-        <v>86.47105455993147</v>
+        <v>86.47104686486708</v>
       </c>
       <c r="D174" t="n">
-        <v>84.07273830986246</v>
+        <v>84.07273082822437</v>
       </c>
       <c r="E174" t="n">
-        <v>86.10208489144279</v>
+        <v>86.10207722921302</v>
       </c>
       <c r="F174" t="n">
         <v>502449</v>
@@ -3932,16 +3932,16 @@
         <v>44729</v>
       </c>
       <c r="B176" t="n">
-        <v>84.51197814941406</v>
+        <v>84.51198577880859</v>
       </c>
       <c r="C176" t="n">
-        <v>86.43590168732089</v>
+        <v>86.43590949039935</v>
       </c>
       <c r="D176" t="n">
-        <v>83.73011108749068</v>
+        <v>83.73011864630146</v>
       </c>
       <c r="E176" t="n">
-        <v>84.07272668979664</v>
+        <v>84.07273427953736</v>
       </c>
       <c r="F176" t="n">
         <v>418487</v>
@@ -3952,16 +3952,16 @@
         <v>44732</v>
       </c>
       <c r="B177" t="n">
-        <v>83.89702606201172</v>
+        <v>83.89704132080078</v>
       </c>
       <c r="C177" t="n">
-        <v>85.54860908365065</v>
+        <v>85.54862464282172</v>
       </c>
       <c r="D177" t="n">
-        <v>82.53534390044604</v>
+        <v>82.53535891157887</v>
       </c>
       <c r="E177" t="n">
-        <v>84.51197540452485</v>
+        <v>84.51199077515794</v>
       </c>
       <c r="F177" t="n">
         <v>143101</v>
@@ -4012,16 +4012,16 @@
         <v>44735</v>
       </c>
       <c r="B180" t="n">
-        <v>89.34375</v>
+        <v>89.34375762939453</v>
       </c>
       <c r="C180" t="n">
-        <v>90.31888883979336</v>
+        <v>90.31889655245861</v>
       </c>
       <c r="D180" t="n">
-        <v>86.62039211422531</v>
+        <v>86.6203995110622</v>
       </c>
       <c r="E180" t="n">
-        <v>86.84001785827886</v>
+        <v>86.8400252738704</v>
       </c>
       <c r="F180" t="n">
         <v>839900</v>
@@ -4072,16 +4072,16 @@
         <v>44740</v>
       </c>
       <c r="B183" t="n">
-        <v>85.97909545898438</v>
+        <v>85.97908782958984</v>
       </c>
       <c r="C183" t="n">
-        <v>92.55908139179482</v>
+        <v>92.55907317852221</v>
       </c>
       <c r="D183" t="n">
-        <v>85.97909545898438</v>
+        <v>85.97908782958984</v>
       </c>
       <c r="E183" t="n">
-        <v>91.55758845631833</v>
+        <v>91.55758033191366</v>
       </c>
       <c r="F183" t="n">
         <v>484787</v>
@@ -4092,16 +4092,16 @@
         <v>44741</v>
       </c>
       <c r="B184" t="n">
-        <v>83.28207397460938</v>
+        <v>83.28208923339844</v>
       </c>
       <c r="C184" t="n">
-        <v>86.92785548890417</v>
+        <v>86.92787141566664</v>
       </c>
       <c r="D184" t="n">
-        <v>82.57926900423368</v>
+        <v>82.57928413425608</v>
       </c>
       <c r="E184" t="n">
-        <v>85.9878576949325</v>
+        <v>85.9878734494703</v>
       </c>
       <c r="F184" t="n">
         <v>504091</v>
@@ -4132,16 +4132,16 @@
         <v>44743</v>
       </c>
       <c r="B186" t="n">
-        <v>83.40506744384766</v>
+        <v>83.40507507324219</v>
       </c>
       <c r="C186" t="n">
-        <v>85.39047917144593</v>
+        <v>85.39048698245399</v>
       </c>
       <c r="D186" t="n">
-        <v>81.92918230422647</v>
+        <v>81.92918979861589</v>
       </c>
       <c r="E186" t="n">
-        <v>82.62320039929577</v>
+        <v>82.6232079571698</v>
       </c>
       <c r="F186" t="n">
         <v>500037</v>
@@ -4152,16 +4152,16 @@
         <v>44746</v>
       </c>
       <c r="B187" t="n">
-        <v>82.66712951660156</v>
+        <v>82.66713714599609</v>
       </c>
       <c r="C187" t="n">
-        <v>84.16058861200165</v>
+        <v>84.16059637922834</v>
       </c>
       <c r="D187" t="n">
-        <v>82.21909111773695</v>
+        <v>82.21909870578178</v>
       </c>
       <c r="E187" t="n">
-        <v>82.59684766924126</v>
+        <v>82.59685529214944</v>
       </c>
       <c r="F187" t="n">
         <v>102674</v>
@@ -4192,16 +4192,16 @@
         <v>44748</v>
       </c>
       <c r="B189" t="n">
-        <v>86.62039947509766</v>
+        <v>86.62039184570312</v>
       </c>
       <c r="C189" t="n">
-        <v>88.46525454143122</v>
+        <v>88.46524674954465</v>
       </c>
       <c r="D189" t="n">
-        <v>84.60862668431632</v>
+        <v>84.60861923211571</v>
       </c>
       <c r="E189" t="n">
-        <v>87.8415181796085</v>
+        <v>87.84151044265967</v>
       </c>
       <c r="F189" t="n">
         <v>788696</v>
@@ -4212,16 +4212,16 @@
         <v>44749</v>
       </c>
       <c r="B190" t="n">
-        <v>86.40076446533203</v>
+        <v>86.4007568359375</v>
       </c>
       <c r="C190" t="n">
-        <v>88.54431382481931</v>
+        <v>88.54430600614423</v>
       </c>
       <c r="D190" t="n">
-        <v>86.18992563237374</v>
+        <v>86.18991802159677</v>
       </c>
       <c r="E190" t="n">
-        <v>87.14749063816215</v>
+        <v>87.14748294282991</v>
       </c>
       <c r="F190" t="n">
         <v>483378</v>
@@ -4232,16 +4232,16 @@
         <v>44750</v>
       </c>
       <c r="B191" t="n">
-        <v>85.69797515869141</v>
+        <v>85.69796752929688</v>
       </c>
       <c r="C191" t="n">
-        <v>88.14899276861466</v>
+        <v>88.1489849210145</v>
       </c>
       <c r="D191" t="n">
-        <v>84.9688160190279</v>
+        <v>84.96880845454787</v>
       </c>
       <c r="E191" t="n">
-        <v>86.35685244580863</v>
+        <v>86.35684475775652</v>
       </c>
       <c r="F191" t="n">
         <v>710031</v>
@@ -4252,16 +4252,16 @@
         <v>44753</v>
       </c>
       <c r="B192" t="n">
-        <v>81.78862762451172</v>
+        <v>81.78863525390625</v>
       </c>
       <c r="C192" t="n">
-        <v>85.20600374431876</v>
+        <v>85.20601169249247</v>
       </c>
       <c r="D192" t="n">
-        <v>81.43722508546183</v>
+        <v>81.4372326820769</v>
       </c>
       <c r="E192" t="n">
-        <v>85.0303058260168</v>
+        <v>85.03031375780108</v>
       </c>
       <c r="F192" t="n">
         <v>432674</v>
@@ -4292,16 +4292,16 @@
         <v>44755</v>
       </c>
       <c r="B194" t="n">
-        <v>84.68768310546875</v>
+        <v>84.68769073486328</v>
       </c>
       <c r="C194" t="n">
-        <v>86.91908133386021</v>
+        <v>86.91908916427828</v>
       </c>
       <c r="D194" t="n">
-        <v>83.45777767295714</v>
+        <v>83.45778519155122</v>
       </c>
       <c r="E194" t="n">
-        <v>84.37142151703875</v>
+        <v>84.37142911794173</v>
       </c>
       <c r="F194" t="n">
         <v>1885043</v>
@@ -4312,16 +4312,16 @@
         <v>44756</v>
       </c>
       <c r="B195" t="n">
-        <v>81.44600677490234</v>
+        <v>81.44601440429688</v>
       </c>
       <c r="C195" t="n">
-        <v>85.20599828625562</v>
+        <v>85.20600626786458</v>
       </c>
       <c r="D195" t="n">
-        <v>81.35815782137873</v>
+        <v>81.35816544254408</v>
       </c>
       <c r="E195" t="n">
-        <v>84.3362822522144</v>
+        <v>84.33629015235336</v>
       </c>
       <c r="F195" t="n">
         <v>647308</v>
@@ -4332,16 +4332,16 @@
         <v>44757</v>
       </c>
       <c r="B196" t="n">
-        <v>82.85160827636719</v>
+        <v>82.85161590576172</v>
       </c>
       <c r="C196" t="n">
-        <v>84.72282378634415</v>
+        <v>84.72283158804966</v>
       </c>
       <c r="D196" t="n">
-        <v>81.20881210481942</v>
+        <v>81.20881958293697</v>
       </c>
       <c r="E196" t="n">
-        <v>82.27179983418721</v>
+        <v>82.27180741019004</v>
       </c>
       <c r="F196" t="n">
         <v>1850084</v>
@@ -4352,16 +4352,16 @@
         <v>44760</v>
       </c>
       <c r="B197" t="n">
-        <v>83.74768829345703</v>
+        <v>83.74769592285156</v>
       </c>
       <c r="C197" t="n">
-        <v>86.46225920673785</v>
+        <v>86.46226708342914</v>
       </c>
       <c r="D197" t="n">
-        <v>82.93946718359145</v>
+        <v>82.93947473935722</v>
       </c>
       <c r="E197" t="n">
-        <v>82.93946718359145</v>
+        <v>82.93947473935722</v>
       </c>
       <c r="F197" t="n">
         <v>494919</v>
@@ -4432,16 +4432,16 @@
         <v>44764</v>
       </c>
       <c r="B201" t="n">
-        <v>89.78300476074219</v>
+        <v>89.78299713134766</v>
       </c>
       <c r="C201" t="n">
-        <v>92.24281586478145</v>
+        <v>92.24280802636217</v>
       </c>
       <c r="D201" t="n">
-        <v>89.22076337166682</v>
+        <v>89.22075579004928</v>
       </c>
       <c r="E201" t="n">
-        <v>91.97048207701101</v>
+        <v>91.97047426173357</v>
       </c>
       <c r="F201" t="n">
         <v>566897</v>
@@ -4452,16 +4452,16 @@
         <v>44767</v>
       </c>
       <c r="B202" t="n">
-        <v>89.08020782470703</v>
+        <v>89.0802001953125</v>
       </c>
       <c r="C202" t="n">
-        <v>90.58244718893432</v>
+        <v>90.58243943087848</v>
       </c>
       <c r="D202" t="n">
-        <v>88.15777697007543</v>
+        <v>88.15776941968373</v>
       </c>
       <c r="E202" t="n">
-        <v>89.17684369338068</v>
+        <v>89.17683605570963</v>
       </c>
       <c r="F202" t="n">
         <v>343259</v>
@@ -4492,16 +4492,16 @@
         <v>44769</v>
       </c>
       <c r="B204" t="n">
-        <v>92.26038360595703</v>
+        <v>92.2603759765625</v>
       </c>
       <c r="C204" t="n">
-        <v>92.55907811606914</v>
+        <v>92.55907046197431</v>
       </c>
       <c r="D204" t="n">
-        <v>87.46375795252364</v>
+        <v>87.46375071978201</v>
       </c>
       <c r="E204" t="n">
-        <v>87.46375795252364</v>
+        <v>87.46375071978201</v>
       </c>
       <c r="F204" t="n">
         <v>673546</v>
@@ -4572,16 +4572,16 @@
         <v>44775</v>
       </c>
       <c r="B208" t="n">
-        <v>101.4670867919922</v>
+        <v>101.4671020507812</v>
       </c>
       <c r="C208" t="n">
-        <v>102.2050260242147</v>
+        <v>102.2050413939763</v>
       </c>
       <c r="D208" t="n">
-        <v>98.69980126626697</v>
+        <v>98.69981610890704</v>
       </c>
       <c r="E208" t="n">
-        <v>100.0439096552761</v>
+        <v>100.0439247000455</v>
       </c>
       <c r="F208" t="n">
         <v>737331</v>
@@ -4612,16 +4612,16 @@
         <v>44777</v>
       </c>
       <c r="B210" t="n">
-        <v>107.695671081543</v>
+        <v>107.6956787109375</v>
       </c>
       <c r="C210" t="n">
-        <v>114.1966008131186</v>
+        <v>114.196608903053</v>
       </c>
       <c r="D210" t="n">
-        <v>104.9811002422437</v>
+        <v>104.9811076793322</v>
       </c>
       <c r="E210" t="n">
-        <v>106.8610959781686</v>
+        <v>106.86110354844</v>
       </c>
       <c r="F210" t="n">
         <v>1242592</v>
@@ -4652,16 +4652,16 @@
         <v>44781</v>
       </c>
       <c r="B212" t="n">
-        <v>110.4893188476562</v>
+        <v>110.4893264770508</v>
       </c>
       <c r="C212" t="n">
-        <v>113.2829586427765</v>
+        <v>113.2829664650746</v>
       </c>
       <c r="D212" t="n">
-        <v>108.451192165222</v>
+        <v>108.4511996538819</v>
       </c>
       <c r="E212" t="n">
-        <v>108.9343714939558</v>
+        <v>108.9343790159798</v>
       </c>
       <c r="F212" t="n">
         <v>1248783</v>
@@ -4692,16 +4692,16 @@
         <v>44783</v>
       </c>
       <c r="B214" t="n">
-        <v>90.87235260009766</v>
+        <v>90.87234497070312</v>
       </c>
       <c r="C214" t="n">
-        <v>103.6457870434117</v>
+        <v>103.6457783415945</v>
       </c>
       <c r="D214" t="n">
-        <v>90.32767832640604</v>
+        <v>90.32767074274088</v>
       </c>
       <c r="E214" t="n">
-        <v>103.6457870434117</v>
+        <v>103.6457783415945</v>
       </c>
       <c r="F214" t="n">
         <v>2607483</v>
@@ -4772,16 +4772,16 @@
         <v>44789</v>
       </c>
       <c r="B218" t="n">
-        <v>94.96617126464844</v>
+        <v>94.96616363525391</v>
       </c>
       <c r="C218" t="n">
-        <v>98.40112115051892</v>
+        <v>98.40111324516731</v>
       </c>
       <c r="D218" t="n">
-        <v>92.85776276178804</v>
+        <v>92.85775530177888</v>
       </c>
       <c r="E218" t="n">
-        <v>98.18149540443858</v>
+        <v>98.18148751673127</v>
       </c>
       <c r="F218" t="n">
         <v>844810</v>
@@ -4792,16 +4792,16 @@
         <v>44790</v>
       </c>
       <c r="B219" t="n">
-        <v>96.5211181640625</v>
+        <v>96.52112579345703</v>
       </c>
       <c r="C219" t="n">
-        <v>96.67046205176851</v>
+        <v>96.67046969296776</v>
       </c>
       <c r="D219" t="n">
-        <v>93.29700735611611</v>
+        <v>93.29701473066473</v>
       </c>
       <c r="E219" t="n">
-        <v>93.29700735611611</v>
+        <v>93.29701473066473</v>
       </c>
       <c r="F219" t="n">
         <v>484266</v>
@@ -4812,16 +4812,16 @@
         <v>44791</v>
       </c>
       <c r="B220" t="n">
-        <v>96.89888000488281</v>
+        <v>96.89888763427734</v>
       </c>
       <c r="C220" t="n">
-        <v>97.78616317637614</v>
+        <v>97.78617087563147</v>
       </c>
       <c r="D220" t="n">
-        <v>95.80953149932459</v>
+        <v>95.80953904294859</v>
       </c>
       <c r="E220" t="n">
-        <v>96.51233655436566</v>
+        <v>96.51234415332544</v>
       </c>
       <c r="F220" t="n">
         <v>225811</v>
@@ -4832,16 +4832,16 @@
         <v>44792</v>
       </c>
       <c r="B221" t="n">
-        <v>92.81383514404297</v>
+        <v>92.8138427734375</v>
       </c>
       <c r="C221" t="n">
-        <v>96.35420085090701</v>
+        <v>96.3542087713233</v>
       </c>
       <c r="D221" t="n">
-        <v>92.34822966730141</v>
+        <v>92.34823725842267</v>
       </c>
       <c r="E221" t="n">
-        <v>95.79195951645167</v>
+        <v>95.79196739065114</v>
       </c>
       <c r="F221" t="n">
         <v>610732</v>
@@ -4852,16 +4852,16 @@
         <v>44795</v>
       </c>
       <c r="B222" t="n">
-        <v>88.45645904541016</v>
+        <v>88.45646667480469</v>
       </c>
       <c r="C222" t="n">
-        <v>92.04953268515936</v>
+        <v>92.04954062445751</v>
       </c>
       <c r="D222" t="n">
-        <v>88.03477470481275</v>
+        <v>88.03478229783688</v>
       </c>
       <c r="E222" t="n">
-        <v>92.04953268515936</v>
+        <v>92.04954062445751</v>
       </c>
       <c r="F222" t="n">
         <v>1074017</v>
@@ -4872,16 +4872,16 @@
         <v>44796</v>
       </c>
       <c r="B223" t="n">
-        <v>96.42449188232422</v>
+        <v>96.42449951171875</v>
       </c>
       <c r="C223" t="n">
-        <v>97.50504682708615</v>
+        <v>97.50505454197742</v>
       </c>
       <c r="D223" t="n">
-        <v>87.49889811798089</v>
+        <v>87.49890504115571</v>
       </c>
       <c r="E223" t="n">
-        <v>89.51945771416493</v>
+        <v>89.51946479721248</v>
       </c>
       <c r="F223" t="n">
         <v>1305076</v>
@@ -4912,16 +4912,16 @@
         <v>44798</v>
       </c>
       <c r="B225" t="n">
-        <v>99.56951904296875</v>
+        <v>99.56952667236328</v>
       </c>
       <c r="C225" t="n">
-        <v>103.1362455026625</v>
+        <v>103.1362534053532</v>
       </c>
       <c r="D225" t="n">
-        <v>98.69980301743414</v>
+        <v>98.69981058018772</v>
       </c>
       <c r="E225" t="n">
-        <v>101.9063400580249</v>
+        <v>101.9063478664755</v>
       </c>
       <c r="F225" t="n">
         <v>468543</v>
@@ -4952,16 +4952,16 @@
         <v>44802</v>
       </c>
       <c r="B227" t="n">
-        <v>91.77719879150391</v>
+        <v>91.77720642089844</v>
       </c>
       <c r="C227" t="n">
-        <v>95.8446647948148</v>
+        <v>95.84467276233583</v>
       </c>
       <c r="D227" t="n">
-        <v>91.23252458207104</v>
+        <v>91.23253216618707</v>
       </c>
       <c r="E227" t="n">
-        <v>93.5605586013736</v>
+        <v>93.56056637901798</v>
       </c>
       <c r="F227" t="n">
         <v>661048</v>
@@ -4972,16 +4972,16 @@
         <v>44803</v>
       </c>
       <c r="B228" t="n">
-        <v>89.34375</v>
+        <v>89.34375762939453</v>
       </c>
       <c r="C228" t="n">
-        <v>93.80654672775484</v>
+        <v>93.80655473824415</v>
       </c>
       <c r="D228" t="n">
-        <v>88.50038794712792</v>
+        <v>88.50039550450462</v>
       </c>
       <c r="E228" t="n">
-        <v>92.65570997369696</v>
+        <v>92.65571788591205</v>
       </c>
       <c r="F228" t="n">
         <v>477437</v>
@@ -4992,16 +4992,16 @@
         <v>44804</v>
       </c>
       <c r="B229" t="n">
-        <v>87.36711883544922</v>
+        <v>87.36711120605469</v>
       </c>
       <c r="C229" t="n">
-        <v>91.33795606548307</v>
+        <v>91.33794808933241</v>
       </c>
       <c r="D229" t="n">
-        <v>87.36711883544922</v>
+        <v>87.36711120605469</v>
       </c>
       <c r="E229" t="n">
-        <v>89.35253745046614</v>
+        <v>89.35252964769354</v>
       </c>
       <c r="F229" t="n">
         <v>588012</v>
@@ -5012,16 +5012,16 @@
         <v>44805</v>
       </c>
       <c r="B230" t="n">
-        <v>88.58823394775391</v>
+        <v>88.58824157714844</v>
       </c>
       <c r="C230" t="n">
-        <v>89.21197693820172</v>
+        <v>89.21198462131423</v>
       </c>
       <c r="D230" t="n">
-        <v>84.33628290195425</v>
+        <v>84.33629016516232</v>
       </c>
       <c r="E230" t="n">
-        <v>87.39347610622615</v>
+        <v>87.39348363272576</v>
       </c>
       <c r="F230" t="n">
         <v>1016578</v>
@@ -5052,16 +5052,16 @@
         <v>44809</v>
       </c>
       <c r="B232" t="n">
-        <v>89.43161773681641</v>
+        <v>89.43160247802734</v>
       </c>
       <c r="C232" t="n">
-        <v>89.8269414485207</v>
+        <v>89.82692612228165</v>
       </c>
       <c r="D232" t="n">
-        <v>88.03479433073093</v>
+        <v>88.03477931026735</v>
       </c>
       <c r="E232" t="n">
-        <v>88.81666154895264</v>
+        <v>88.81664639508718</v>
       </c>
       <c r="F232" t="n">
         <v>95765</v>
@@ -5072,16 +5072,16 @@
         <v>44810</v>
       </c>
       <c r="B233" t="n">
-        <v>86.71702575683594</v>
+        <v>86.71703338623047</v>
       </c>
       <c r="C233" t="n">
-        <v>89.31739369553651</v>
+        <v>89.31740155371233</v>
       </c>
       <c r="D233" t="n">
-        <v>85.2059996040562</v>
+        <v>85.20600710051012</v>
       </c>
       <c r="E233" t="n">
-        <v>88.73758523135686</v>
+        <v>88.73759303852093</v>
       </c>
       <c r="F233" t="n">
         <v>519096</v>
@@ -5092,16 +5092,16 @@
         <v>44812</v>
       </c>
       <c r="B234" t="n">
-        <v>88.28954315185547</v>
+        <v>88.28955841064453</v>
       </c>
       <c r="C234" t="n">
-        <v>90.14318484278159</v>
+        <v>90.14320042192941</v>
       </c>
       <c r="D234" t="n">
-        <v>87.12991956960056</v>
+        <v>87.12993462797571</v>
       </c>
       <c r="E234" t="n">
-        <v>88.29833005770951</v>
+        <v>88.29834531801718</v>
       </c>
       <c r="F234" t="n">
         <v>707072</v>
@@ -5112,16 +5112,16 @@
         <v>44813</v>
       </c>
       <c r="B235" t="n">
-        <v>91.80355834960938</v>
+        <v>91.80356597900391</v>
       </c>
       <c r="C235" t="n">
-        <v>92.14617396419217</v>
+        <v>92.14618162206</v>
       </c>
       <c r="D235" t="n">
-        <v>88.81664697669278</v>
+        <v>88.81665435785808</v>
       </c>
       <c r="E235" t="n">
-        <v>88.81664697669278</v>
+        <v>88.81665435785808</v>
       </c>
       <c r="F235" t="n">
         <v>540504</v>
@@ -5152,16 +5152,16 @@
         <v>44817</v>
       </c>
       <c r="B237" t="n">
-        <v>90.74935913085938</v>
+        <v>90.74936676025391</v>
       </c>
       <c r="C237" t="n">
-        <v>92.94561654736182</v>
+        <v>92.94562436139803</v>
       </c>
       <c r="D237" t="n">
-        <v>90.4858055599008</v>
+        <v>90.48581316713809</v>
       </c>
       <c r="E237" t="n">
-        <v>91.36430852650177</v>
+        <v>91.36431620759575</v>
       </c>
       <c r="F237" t="n">
         <v>548480</v>
@@ -5172,16 +5172,16 @@
         <v>44818</v>
       </c>
       <c r="B238" t="n">
-        <v>90.1343994140625</v>
+        <v>90.13440704345703</v>
       </c>
       <c r="C238" t="n">
-        <v>91.77720230853167</v>
+        <v>91.77721007698068</v>
       </c>
       <c r="D238" t="n">
-        <v>88.15776781856795</v>
+        <v>88.15777528065119</v>
       </c>
       <c r="E238" t="n">
-        <v>90.17832724160722</v>
+        <v>90.17833487472001</v>
       </c>
       <c r="F238" t="n">
         <v>962834</v>
@@ -5212,16 +5212,16 @@
         <v>44820</v>
       </c>
       <c r="B240" t="n">
-        <v>87.80636596679688</v>
+        <v>87.80637359619141</v>
       </c>
       <c r="C240" t="n">
-        <v>89.46673598332055</v>
+        <v>89.46674375698272</v>
       </c>
       <c r="D240" t="n">
-        <v>86.15478285633742</v>
+        <v>86.15479034222778</v>
       </c>
       <c r="E240" t="n">
-        <v>89.33496590458495</v>
+        <v>89.33497366679777</v>
       </c>
       <c r="F240" t="n">
         <v>454254</v>
@@ -5232,16 +5232,16 @@
         <v>44823</v>
       </c>
       <c r="B241" t="n">
-        <v>88.99234771728516</v>
+        <v>88.99236297607422</v>
       </c>
       <c r="C241" t="n">
-        <v>89.82692280318257</v>
+        <v>89.82693820506938</v>
       </c>
       <c r="D241" t="n">
-        <v>86.69945457946307</v>
+        <v>86.69946944510852</v>
       </c>
       <c r="E241" t="n">
-        <v>87.39347268463194</v>
+        <v>87.393487669275</v>
       </c>
       <c r="F241" t="n">
         <v>601912</v>
@@ -5252,16 +5252,16 @@
         <v>44824</v>
       </c>
       <c r="B242" t="n">
-        <v>89.88841247558594</v>
+        <v>89.88842010498047</v>
       </c>
       <c r="C242" t="n">
-        <v>91.25009459120727</v>
+        <v>91.25010233617633</v>
       </c>
       <c r="D242" t="n">
-        <v>88.50916325181916</v>
+        <v>88.50917076414814</v>
       </c>
       <c r="E242" t="n">
-        <v>88.7727167911152</v>
+        <v>88.77272432581363</v>
       </c>
       <c r="F242" t="n">
         <v>415549</v>
@@ -5272,16 +5272,16 @@
         <v>44825</v>
       </c>
       <c r="B243" t="n">
-        <v>89.51066589355469</v>
+        <v>89.51067352294922</v>
       </c>
       <c r="C243" t="n">
-        <v>91.2237439814253</v>
+        <v>91.22375175683315</v>
       </c>
       <c r="D243" t="n">
-        <v>87.51646712709899</v>
+        <v>87.51647458651904</v>
       </c>
       <c r="E243" t="n">
-        <v>90.16954311234272</v>
+        <v>90.16955079789631</v>
       </c>
       <c r="F243" t="n">
         <v>553017</v>
@@ -5292,16 +5292,16 @@
         <v>44826</v>
       </c>
       <c r="B244" t="n">
-        <v>89.08020782470703</v>
+        <v>89.0802001953125</v>
       </c>
       <c r="C244" t="n">
-        <v>91.53123206185035</v>
+        <v>91.53122422253455</v>
       </c>
       <c r="D244" t="n">
-        <v>86.27778103806376</v>
+        <v>86.27777364868685</v>
       </c>
       <c r="E244" t="n">
-        <v>89.43161037420698</v>
+        <v>89.43160271471611</v>
       </c>
       <c r="F244" t="n">
         <v>985794</v>
@@ -5392,16 +5392,16 @@
         <v>44833</v>
       </c>
       <c r="B249" t="n">
-        <v>87.27048492431641</v>
+        <v>87.27049255371094</v>
       </c>
       <c r="C249" t="n">
-        <v>87.79759208700698</v>
+        <v>87.79759976248249</v>
       </c>
       <c r="D249" t="n">
-        <v>84.51198603667193</v>
+        <v>84.51199342491191</v>
       </c>
       <c r="E249" t="n">
-        <v>85.39927594459202</v>
+        <v>85.399283410401</v>
       </c>
       <c r="F249" t="n">
         <v>546314</v>
@@ -5412,16 +5412,16 @@
         <v>44834</v>
       </c>
       <c r="B250" t="n">
-        <v>90.31011199951172</v>
+        <v>90.31011962890625</v>
       </c>
       <c r="C250" t="n">
-        <v>91.18861500844686</v>
+        <v>91.1886227120573</v>
       </c>
       <c r="D250" t="n">
-        <v>85.89123623451323</v>
+        <v>85.89124349060133</v>
       </c>
       <c r="E250" t="n">
-        <v>86.97179788457973</v>
+        <v>86.97180523195362</v>
       </c>
       <c r="F250" t="n">
         <v>846019</v>
@@ -5432,16 +5432,16 @@
         <v>44837</v>
       </c>
       <c r="B251" t="n">
-        <v>94.77290344238281</v>
+        <v>94.77289581298828</v>
       </c>
       <c r="C251" t="n">
-        <v>95.68654738803224</v>
+        <v>95.68653968508768</v>
       </c>
       <c r="D251" t="n">
-        <v>90.92506262532224</v>
+        <v>90.92505530568604</v>
       </c>
       <c r="E251" t="n">
-        <v>91.36431413558951</v>
+        <v>91.36430678059274</v>
       </c>
       <c r="F251" t="n">
         <v>814581</v>
@@ -5472,16 +5472,16 @@
         <v>44839</v>
       </c>
       <c r="B253" t="n">
-        <v>95.75682067871094</v>
+        <v>95.75682830810547</v>
       </c>
       <c r="C253" t="n">
-        <v>97.74223920433043</v>
+        <v>97.74224699191255</v>
       </c>
       <c r="D253" t="n">
-        <v>93.46392746387826</v>
+        <v>93.46393491058726</v>
       </c>
       <c r="E253" t="n">
-        <v>94.30728948391106</v>
+        <v>94.30729699781466</v>
       </c>
       <c r="F253" t="n">
         <v>556734</v>
@@ -5532,16 +5532,16 @@
         <v>44844</v>
       </c>
       <c r="B256" t="n">
-        <v>96.5211181640625</v>
+        <v>96.52112579345703</v>
       </c>
       <c r="C256" t="n">
-        <v>97.95307550975528</v>
+        <v>97.95308325233714</v>
       </c>
       <c r="D256" t="n">
-        <v>94.96616424340819</v>
+        <v>94.96617174989328</v>
       </c>
       <c r="E256" t="n">
-        <v>97.1624215418332</v>
+        <v>97.16242922191877</v>
       </c>
       <c r="F256" t="n">
         <v>391665</v>
@@ -5552,16 +5552,16 @@
         <v>44845</v>
       </c>
       <c r="B257" t="n">
-        <v>88.64974975585938</v>
+        <v>88.64973449707031</v>
       </c>
       <c r="C257" t="n">
-        <v>96.94281434223674</v>
+        <v>96.94279765600854</v>
       </c>
       <c r="D257" t="n">
-        <v>87.13872337332482</v>
+        <v>87.13870837462035</v>
       </c>
       <c r="E257" t="n">
-        <v>96.52113661370647</v>
+        <v>96.52112000005931</v>
       </c>
       <c r="F257" t="n">
         <v>1649810</v>
@@ -5592,16 +5592,16 @@
         <v>44848</v>
       </c>
       <c r="B259" t="n">
-        <v>82.71984100341797</v>
+        <v>82.7198486328125</v>
       </c>
       <c r="C259" t="n">
-        <v>90.16954226733124</v>
+        <v>90.16955058382466</v>
       </c>
       <c r="D259" t="n">
-        <v>82.66712626874587</v>
+        <v>82.66713389327845</v>
       </c>
       <c r="E259" t="n">
-        <v>86.64674356053986</v>
+        <v>86.64675155211943</v>
       </c>
       <c r="F259" t="n">
         <v>951929</v>
@@ -5612,16 +5612,16 @@
         <v>44851</v>
       </c>
       <c r="B260" t="n">
-        <v>83.01853179931641</v>
+        <v>83.01853942871094</v>
       </c>
       <c r="C260" t="n">
-        <v>85.90880741440093</v>
+        <v>85.90881530941148</v>
       </c>
       <c r="D260" t="n">
-        <v>82.82526007088433</v>
+        <v>82.82526768251721</v>
       </c>
       <c r="E260" t="n">
-        <v>84.32749936581655</v>
+        <v>84.32750711550507</v>
       </c>
       <c r="F260" t="n">
         <v>630186</v>
@@ -5632,16 +5632,16 @@
         <v>44852</v>
       </c>
       <c r="B261" t="n">
-        <v>80.54115295410156</v>
+        <v>80.54116058349609</v>
       </c>
       <c r="C261" t="n">
-        <v>85.61011216687361</v>
+        <v>85.61012027643372</v>
       </c>
       <c r="D261" t="n">
-        <v>79.24096560302623</v>
+        <v>79.24097310925836</v>
       </c>
       <c r="E261" t="n">
-        <v>84.42413449202566</v>
+        <v>84.42414248924207</v>
       </c>
       <c r="F261" t="n">
         <v>1514560</v>
@@ -5652,16 +5652,16 @@
         <v>44853</v>
       </c>
       <c r="B262" t="n">
-        <v>80.47086334228516</v>
+        <v>80.47087097167969</v>
       </c>
       <c r="C262" t="n">
-        <v>81.52507083121216</v>
+        <v>81.52507856055549</v>
       </c>
       <c r="D262" t="n">
-        <v>79.10918788494983</v>
+        <v>79.10919538524473</v>
       </c>
       <c r="E262" t="n">
-        <v>80.3830143938192</v>
+        <v>80.38302201488482</v>
       </c>
       <c r="F262" t="n">
         <v>1204425</v>
@@ -5692,16 +5692,16 @@
         <v>44855</v>
       </c>
       <c r="B264" t="n">
-        <v>82.25421905517578</v>
+        <v>82.25423431396484</v>
       </c>
       <c r="C264" t="n">
-        <v>85.73308952091872</v>
+        <v>85.73310542506498</v>
       </c>
       <c r="D264" t="n">
-        <v>75.1383473433177</v>
+        <v>75.13836128205794</v>
       </c>
       <c r="E264" t="n">
-        <v>77.96712757972831</v>
+        <v>77.967142043229</v>
       </c>
       <c r="F264" t="n">
         <v>1421863</v>
@@ -5732,16 +5732,16 @@
         <v>44859</v>
       </c>
       <c r="B266" t="n">
-        <v>82.92189788818359</v>
+        <v>82.92189025878906</v>
       </c>
       <c r="C266" t="n">
-        <v>85.30264022119347</v>
+        <v>85.30263237275399</v>
       </c>
       <c r="D266" t="n">
-        <v>81.31423578466473</v>
+        <v>81.31422830318635</v>
       </c>
       <c r="E266" t="n">
-        <v>82.03460797877678</v>
+        <v>82.03460043101913</v>
       </c>
       <c r="F266" t="n">
         <v>1189906</v>
@@ -5752,16 +5752,16 @@
         <v>44860</v>
       </c>
       <c r="B267" t="n">
-        <v>80.20732116699219</v>
+        <v>80.20732879638672</v>
       </c>
       <c r="C267" t="n">
-        <v>84.20450552571505</v>
+        <v>84.20451353532545</v>
       </c>
       <c r="D267" t="n">
-        <v>80.07554438539792</v>
+        <v>80.07555200225771</v>
       </c>
       <c r="E267" t="n">
-        <v>82.57927642590705</v>
+        <v>82.57928428092416</v>
       </c>
       <c r="F267" t="n">
         <v>763965</v>
@@ -5792,16 +5792,16 @@
         <v>44862</v>
       </c>
       <c r="B269" t="n">
-        <v>81.43721771240234</v>
+        <v>81.43722534179688</v>
       </c>
       <c r="C269" t="n">
-        <v>82.14002272687244</v>
+        <v>82.14003042210881</v>
       </c>
       <c r="D269" t="n">
-        <v>78.40638533019641</v>
+        <v>78.40639267564933</v>
       </c>
       <c r="E269" t="n">
-        <v>79.04769540858378</v>
+        <v>79.04770281411741</v>
       </c>
       <c r="F269" t="n">
         <v>705309</v>
@@ -5832,16 +5832,16 @@
         <v>44866</v>
       </c>
       <c r="B271" t="n">
-        <v>87.10356140136719</v>
+        <v>87.10357666015625</v>
       </c>
       <c r="C271" t="n">
-        <v>87.84150059923279</v>
+        <v>87.84151598729392</v>
       </c>
       <c r="D271" t="n">
-        <v>83.65983173977101</v>
+        <v>83.65984639528801</v>
       </c>
       <c r="E271" t="n">
-        <v>83.65983173977101</v>
+        <v>83.65984639528801</v>
       </c>
       <c r="F271" t="n">
         <v>1461617</v>
@@ -5852,16 +5852,16 @@
         <v>44868</v>
       </c>
       <c r="B272" t="n">
-        <v>86.58524322509766</v>
+        <v>86.58525085449219</v>
       </c>
       <c r="C272" t="n">
-        <v>88.4652388850419</v>
+        <v>88.46524668009084</v>
       </c>
       <c r="D272" t="n">
-        <v>84.0463703936091</v>
+        <v>84.04637779929271</v>
       </c>
       <c r="E272" t="n">
-        <v>85.59253736618446</v>
+        <v>85.59254490810744</v>
       </c>
       <c r="F272" t="n">
         <v>991113</v>
@@ -5892,16 +5892,16 @@
         <v>44872</v>
       </c>
       <c r="B274" t="n">
-        <v>83.19423675537109</v>
+        <v>83.19422912597656</v>
       </c>
       <c r="C274" t="n">
-        <v>84.51199133989617</v>
+        <v>84.51198358965588</v>
       </c>
       <c r="D274" t="n">
-        <v>82.28059947491988</v>
+        <v>82.2805919293112</v>
       </c>
       <c r="E274" t="n">
-        <v>83.03610593713023</v>
+        <v>83.03609832223721</v>
       </c>
       <c r="F274" t="n">
         <v>752715</v>
@@ -5932,16 +5932,16 @@
         <v>44874</v>
       </c>
       <c r="B276" t="n">
-        <v>90.18711853027344</v>
+        <v>90.18712615966797</v>
       </c>
       <c r="C276" t="n">
-        <v>93.10374813592868</v>
+        <v>93.10375601205598</v>
       </c>
       <c r="D276" t="n">
-        <v>83.4665694385159</v>
+        <v>83.46657649938446</v>
       </c>
       <c r="E276" t="n">
-        <v>83.89703401910188</v>
+        <v>83.89704111638565</v>
       </c>
       <c r="F276" t="n">
         <v>2468383</v>
@@ -5952,16 +5952,16 @@
         <v>44875</v>
       </c>
       <c r="B277" t="n">
-        <v>90.49459838867188</v>
+        <v>90.49458312988281</v>
       </c>
       <c r="C277" t="n">
-        <v>94.21944933414814</v>
+        <v>94.21943344729159</v>
       </c>
       <c r="D277" t="n">
-        <v>85.65404484922558</v>
+        <v>85.65403040662872</v>
       </c>
       <c r="E277" t="n">
-        <v>85.67161196063115</v>
+        <v>85.67159751507221</v>
       </c>
       <c r="F277" t="n">
         <v>2820385</v>
@@ -5992,16 +5992,16 @@
         <v>44879</v>
       </c>
       <c r="B279" t="n">
-        <v>88.81665802001953</v>
+        <v>88.81664276123047</v>
       </c>
       <c r="C279" t="n">
-        <v>90.38917930161588</v>
+        <v>90.38916377266612</v>
       </c>
       <c r="D279" t="n">
-        <v>85.91760194366664</v>
+        <v>85.91758718293825</v>
       </c>
       <c r="E279" t="n">
-        <v>89.08021161898182</v>
+        <v>89.08019631491399</v>
       </c>
       <c r="F279" t="n">
         <v>689741</v>
@@ -6012,16 +6012,16 @@
         <v>44881</v>
       </c>
       <c r="B280" t="n">
-        <v>86.34806823730469</v>
+        <v>86.34806060791016</v>
       </c>
       <c r="C280" t="n">
-        <v>90.38918105076644</v>
+        <v>90.38917306431421</v>
       </c>
       <c r="D280" t="n">
-        <v>85.75947278433812</v>
+        <v>85.7594652069497</v>
       </c>
       <c r="E280" t="n">
-        <v>88.90450870594499</v>
+        <v>88.90450085067289</v>
       </c>
       <c r="F280" t="n">
         <v>1097230</v>
@@ -6072,16 +6072,16 @@
         <v>44886</v>
       </c>
       <c r="B283" t="n">
-        <v>80.0404052734375</v>
+        <v>80.04039764404297</v>
       </c>
       <c r="C283" t="n">
-        <v>82.56171118314468</v>
+        <v>82.56170331342106</v>
       </c>
       <c r="D283" t="n">
-        <v>79.6275078095798</v>
+        <v>79.62750021954236</v>
       </c>
       <c r="E283" t="n">
-        <v>82.0697449675642</v>
+        <v>82.06973714473446</v>
       </c>
       <c r="F283" t="n">
         <v>597582</v>
@@ -6112,16 +6112,16 @@
         <v>44888</v>
       </c>
       <c r="B285" t="n">
-        <v>77.27311706542969</v>
+        <v>77.27312469482422</v>
       </c>
       <c r="C285" t="n">
-        <v>78.72264824317485</v>
+        <v>78.7226560156857</v>
       </c>
       <c r="D285" t="n">
-        <v>75.99929049548588</v>
+        <v>75.99929799911189</v>
       </c>
       <c r="E285" t="n">
-        <v>78.02863012286181</v>
+        <v>78.0286378268503</v>
       </c>
       <c r="F285" t="n">
         <v>751617</v>
@@ -6132,16 +6132,16 @@
         <v>44889</v>
       </c>
       <c r="B286" t="n">
-        <v>78.80171966552734</v>
+        <v>78.80171203613281</v>
       </c>
       <c r="C286" t="n">
-        <v>79.5045247754602</v>
+        <v>79.50451707802175</v>
       </c>
       <c r="D286" t="n">
-        <v>77.19406420315345</v>
+        <v>77.19405672940827</v>
       </c>
       <c r="E286" t="n">
-        <v>77.52789294402611</v>
+        <v>77.52788543796044</v>
       </c>
       <c r="F286" t="n">
         <v>618983</v>
@@ -6152,16 +6152,16 @@
         <v>44890</v>
       </c>
       <c r="B287" t="n">
-        <v>77.44883728027344</v>
+        <v>77.44882965087891</v>
       </c>
       <c r="C287" t="n">
-        <v>78.80172616952011</v>
+        <v>78.80171840685408</v>
       </c>
       <c r="D287" t="n">
-        <v>76.73724520456162</v>
+        <v>76.7372376452652</v>
       </c>
       <c r="E287" t="n">
-        <v>78.37126152294162</v>
+        <v>78.37125380268016</v>
       </c>
       <c r="F287" t="n">
         <v>602409</v>
@@ -6212,16 +6212,16 @@
         <v>44895</v>
       </c>
       <c r="B290" t="n">
-        <v>79.53966522216797</v>
+        <v>79.5396728515625</v>
       </c>
       <c r="C290" t="n">
-        <v>80.11947373729132</v>
+        <v>80.11948142230071</v>
       </c>
       <c r="D290" t="n">
-        <v>75.72695858278091</v>
+        <v>75.72696584646302</v>
       </c>
       <c r="E290" t="n">
-        <v>78.18676975028522</v>
+        <v>78.18677724991088</v>
       </c>
       <c r="F290" t="n">
         <v>577266</v>
@@ -6232,16 +6232,16 @@
         <v>44896</v>
       </c>
       <c r="B291" t="n">
-        <v>79.21461486816406</v>
+        <v>79.21462249755859</v>
       </c>
       <c r="C291" t="n">
-        <v>81.06825675698197</v>
+        <v>81.06826456490624</v>
       </c>
       <c r="D291" t="n">
-        <v>78.69630130901254</v>
+        <v>78.69630888848674</v>
       </c>
       <c r="E291" t="n">
-        <v>79.0740578717206</v>
+        <v>79.07406548757766</v>
       </c>
       <c r="F291" t="n">
         <v>741238</v>
@@ -6272,16 +6272,16 @@
         <v>44900</v>
       </c>
       <c r="B293" t="n">
-        <v>81.08582305908203</v>
+        <v>81.08583068847656</v>
       </c>
       <c r="C293" t="n">
-        <v>84.30992720117379</v>
+        <v>84.30993513392545</v>
       </c>
       <c r="D293" t="n">
-        <v>80.15460539631847</v>
+        <v>80.1546129380944</v>
       </c>
       <c r="E293" t="n">
-        <v>81.88525723951001</v>
+        <v>81.88526494412361</v>
       </c>
       <c r="F293" t="n">
         <v>633863</v>
@@ -6312,16 +6312,16 @@
         <v>44902</v>
       </c>
       <c r="B295" t="n">
-        <v>76.15741729736328</v>
+        <v>76.15742492675781</v>
       </c>
       <c r="C295" t="n">
-        <v>78.43273655389115</v>
+        <v>78.4327444112255</v>
       </c>
       <c r="D295" t="n">
-        <v>74.76059422398934</v>
+        <v>74.76060171345117</v>
       </c>
       <c r="E295" t="n">
-        <v>77.82656741804537</v>
+        <v>77.82657521465414</v>
       </c>
       <c r="F295" t="n">
         <v>782541</v>
@@ -6332,16 +6332,16 @@
         <v>44903</v>
       </c>
       <c r="B296" t="n">
-        <v>72.38864898681641</v>
+        <v>72.38865661621094</v>
       </c>
       <c r="C296" t="n">
-        <v>76.73723618265012</v>
+        <v>76.73724427036358</v>
       </c>
       <c r="D296" t="n">
-        <v>72.03724644416056</v>
+        <v>72.03725403651906</v>
       </c>
       <c r="E296" t="n">
-        <v>76.73723618265012</v>
+        <v>76.73724427036358</v>
       </c>
       <c r="F296" t="n">
         <v>1116650</v>
@@ -6352,16 +6352,16 @@
         <v>44904</v>
       </c>
       <c r="B297" t="n">
-        <v>72.71368408203125</v>
+        <v>72.71369171142578</v>
       </c>
       <c r="C297" t="n">
-        <v>74.76059750386545</v>
+        <v>74.76060534802988</v>
       </c>
       <c r="D297" t="n">
-        <v>70.93032421841735</v>
+        <v>70.93033166069503</v>
       </c>
       <c r="E297" t="n">
-        <v>72.96845073432544</v>
+        <v>72.96845839045105</v>
       </c>
       <c r="F297" t="n">
         <v>602365</v>
@@ -6372,16 +6372,16 @@
         <v>44907</v>
       </c>
       <c r="B298" t="n">
-        <v>72.23930358886719</v>
+        <v>72.23931121826172</v>
       </c>
       <c r="C298" t="n">
-        <v>74.02266358054949</v>
+        <v>74.02267139828965</v>
       </c>
       <c r="D298" t="n">
-        <v>70.51743183574715</v>
+        <v>70.51743928329</v>
       </c>
       <c r="E298" t="n">
-        <v>72.73126311693241</v>
+        <v>72.73127079828416</v>
       </c>
       <c r="F298" t="n">
         <v>769701</v>
@@ -6412,16 +6412,16 @@
         <v>44909</v>
       </c>
       <c r="B300" t="n">
-        <v>68.19818115234375</v>
+        <v>68.19818878173828</v>
       </c>
       <c r="C300" t="n">
-        <v>70.51742838907342</v>
+        <v>70.5174362779243</v>
       </c>
       <c r="D300" t="n">
-        <v>66.81893179790644</v>
+        <v>66.81893927300305</v>
       </c>
       <c r="E300" t="n">
-        <v>70.43836634126119</v>
+        <v>70.43837422126734</v>
       </c>
       <c r="F300" t="n">
         <v>1355188</v>
@@ -6492,16 +6492,16 @@
         <v>44915</v>
       </c>
       <c r="B304" t="n">
-        <v>69.59500885009766</v>
+        <v>69.59501647949219</v>
       </c>
       <c r="C304" t="n">
-        <v>69.88491644917501</v>
+        <v>69.88492411035084</v>
       </c>
       <c r="D304" t="n">
-        <v>65.0004352032506</v>
+        <v>65.00044232896225</v>
       </c>
       <c r="E304" t="n">
-        <v>65.79987615177677</v>
+        <v>65.79988336512761</v>
       </c>
       <c r="F304" t="n">
         <v>691729</v>
@@ -6512,16 +6512,16 @@
         <v>44916</v>
       </c>
       <c r="B305" t="n">
-        <v>69.76192474365234</v>
+        <v>69.76193237304688</v>
       </c>
       <c r="C305" t="n">
-        <v>70.19238932645592</v>
+        <v>70.19239700292748</v>
       </c>
       <c r="D305" t="n">
-        <v>66.63444958235912</v>
+        <v>66.63445686972265</v>
       </c>
       <c r="E305" t="n">
-        <v>69.57743322000499</v>
+        <v>69.57744082922292</v>
       </c>
       <c r="F305" t="n">
         <v>349356</v>
@@ -6532,16 +6532,16 @@
         <v>44917</v>
       </c>
       <c r="B306" t="n">
-        <v>67.46903228759766</v>
+        <v>67.46903991699219</v>
       </c>
       <c r="C306" t="n">
-        <v>72.45014263043683</v>
+        <v>72.45015082309504</v>
       </c>
       <c r="D306" t="n">
-        <v>64.56996974070987</v>
+        <v>64.56997704227857</v>
       </c>
       <c r="E306" t="n">
-        <v>70.28023917356177</v>
+        <v>70.28024712084742</v>
       </c>
       <c r="F306" t="n">
         <v>477342</v>
@@ -6552,16 +6552,16 @@
         <v>44918</v>
       </c>
       <c r="B307" t="n">
-        <v>70.728271484375</v>
+        <v>70.72827911376953</v>
       </c>
       <c r="C307" t="n">
-        <v>70.85126135614206</v>
+        <v>70.85126899880341</v>
       </c>
       <c r="D307" t="n">
-        <v>68.02248090060881</v>
+        <v>68.02248823813217</v>
       </c>
       <c r="E307" t="n">
-        <v>68.52322729350198</v>
+        <v>68.52323468504038</v>
       </c>
       <c r="F307" t="n">
         <v>762496</v>
@@ -6592,16 +6592,16 @@
         <v>44922</v>
       </c>
       <c r="B309" t="n">
-        <v>67.82042694091797</v>
+        <v>67.8204345703125</v>
       </c>
       <c r="C309" t="n">
-        <v>70.45593586404866</v>
+        <v>70.45594378992226</v>
       </c>
       <c r="D309" t="n">
-        <v>67.38117545372953</v>
+        <v>67.38118303371087</v>
       </c>
       <c r="E309" t="n">
-        <v>68.96248348858624</v>
+        <v>68.96249124645534</v>
       </c>
       <c r="F309" t="n">
         <v>436455</v>
@@ -6612,16 +6612,16 @@
         <v>44923</v>
       </c>
       <c r="B310" t="n">
-        <v>68.39144897460938</v>
+        <v>68.39145660400391</v>
       </c>
       <c r="C310" t="n">
-        <v>70.26266442886484</v>
+        <v>70.26267226700244</v>
       </c>
       <c r="D310" t="n">
-        <v>67.17911739346478</v>
+        <v>67.17912488761789</v>
       </c>
       <c r="E310" t="n">
-        <v>67.82042075287674</v>
+        <v>67.82042831857034</v>
       </c>
       <c r="F310" t="n">
         <v>543744</v>
@@ -6652,16 +6652,16 @@
         <v>44928</v>
       </c>
       <c r="B312" t="n">
-        <v>66.42360687255859</v>
+        <v>66.42361450195312</v>
       </c>
       <c r="C312" t="n">
-        <v>69.77070088095081</v>
+        <v>69.7707088947915</v>
       </c>
       <c r="D312" t="n">
-        <v>66.12491239199053</v>
+        <v>66.12491998707712</v>
       </c>
       <c r="E312" t="n">
-        <v>68.88341775009563</v>
+        <v>68.88342566202327</v>
       </c>
       <c r="F312" t="n">
         <v>452524</v>
@@ -6672,16 +6672,16 @@
         <v>44929</v>
       </c>
       <c r="B313" t="n">
-        <v>66.99462890625</v>
+        <v>66.99464416503906</v>
       </c>
       <c r="C313" t="n">
-        <v>69.74434040108741</v>
+        <v>69.74435628615456</v>
       </c>
       <c r="D313" t="n">
-        <v>65.50117004672566</v>
+        <v>65.50118496536248</v>
       </c>
       <c r="E313" t="n">
-        <v>66.60808550926455</v>
+        <v>66.60810068001396</v>
       </c>
       <c r="F313" t="n">
         <v>913081</v>
@@ -6692,16 +6692,16 @@
         <v>44930</v>
       </c>
       <c r="B314" t="n">
-        <v>67.00341796875</v>
+        <v>67.00341033935547</v>
       </c>
       <c r="C314" t="n">
-        <v>68.40902807003422</v>
+        <v>68.40902028058885</v>
       </c>
       <c r="D314" t="n">
-        <v>66.33576054333025</v>
+        <v>66.33575298995903</v>
       </c>
       <c r="E314" t="n">
-        <v>66.52024536107352</v>
+        <v>66.52023778669582</v>
       </c>
       <c r="F314" t="n">
         <v>669125</v>
@@ -6752,16 +6752,16 @@
         <v>44935</v>
       </c>
       <c r="B317" t="n">
-        <v>69.62136077880859</v>
+        <v>69.62136840820312</v>
       </c>
       <c r="C317" t="n">
-        <v>70.95668235192537</v>
+        <v>70.95669012764992</v>
       </c>
       <c r="D317" t="n">
-        <v>66.80136703294467</v>
+        <v>66.80137435331271</v>
       </c>
       <c r="E317" t="n">
-        <v>66.99463875986392</v>
+        <v>66.99464610141148</v>
       </c>
       <c r="F317" t="n">
         <v>604476</v>
@@ -6792,16 +6792,16 @@
         <v>44937</v>
       </c>
       <c r="B319" t="n">
-        <v>72.90695953369141</v>
+        <v>72.90696716308594</v>
       </c>
       <c r="C319" t="n">
-        <v>73.10901816567375</v>
+        <v>73.10902581621284</v>
       </c>
       <c r="D319" t="n">
-        <v>69.80584512495696</v>
+        <v>69.80585242983342</v>
       </c>
       <c r="E319" t="n">
-        <v>71.2202354414961</v>
+        <v>71.22024289438232</v>
       </c>
       <c r="F319" t="n">
         <v>824670</v>
@@ -6872,16 +6872,16 @@
         <v>44943</v>
       </c>
       <c r="B323" t="n">
-        <v>72.37985992431641</v>
+        <v>72.37985229492188</v>
       </c>
       <c r="C323" t="n">
-        <v>72.69612153304253</v>
+        <v>72.69611387031159</v>
       </c>
       <c r="D323" t="n">
-        <v>70.11332062926112</v>
+        <v>70.11331323877729</v>
       </c>
       <c r="E323" t="n">
-        <v>71.02696453197595</v>
+        <v>71.026957045187</v>
       </c>
       <c r="F323" t="n">
         <v>1038524</v>
@@ -6892,16 +6892,16 @@
         <v>44944</v>
       </c>
       <c r="B324" t="n">
-        <v>73.96994018554688</v>
+        <v>73.96995544433594</v>
       </c>
       <c r="C324" t="n">
-        <v>75.29648141767632</v>
+        <v>75.29649695010914</v>
       </c>
       <c r="D324" t="n">
-        <v>72.48527486857265</v>
+        <v>72.48528982109953</v>
       </c>
       <c r="E324" t="n">
-        <v>72.52041578824208</v>
+        <v>72.52043074801796</v>
       </c>
       <c r="F324" t="n">
         <v>881691</v>
@@ -6972,16 +6972,16 @@
         <v>44950</v>
       </c>
       <c r="B328" t="n">
-        <v>80.33030700683594</v>
+        <v>80.33031463623047</v>
       </c>
       <c r="C328" t="n">
-        <v>81.2966588525702</v>
+        <v>81.29666657374428</v>
       </c>
       <c r="D328" t="n">
-        <v>78.64357635156964</v>
+        <v>78.64358382076644</v>
       </c>
       <c r="E328" t="n">
-        <v>81.2966588525702</v>
+        <v>81.29666657374428</v>
       </c>
       <c r="F328" t="n">
         <v>788120</v>
@@ -6992,16 +6992,16 @@
         <v>44951</v>
       </c>
       <c r="B329" t="n">
-        <v>77.85294342041016</v>
+        <v>77.85293579101562</v>
       </c>
       <c r="C329" t="n">
-        <v>79.94377828577274</v>
+        <v>79.94377045148158</v>
       </c>
       <c r="D329" t="n">
-        <v>77.15892520022911</v>
+        <v>77.15891763884663</v>
       </c>
       <c r="E329" t="n">
-        <v>79.94377828577274</v>
+        <v>79.94377045148158</v>
       </c>
       <c r="F329" t="n">
         <v>568888</v>
@@ -7052,16 +7052,16 @@
         <v>44956</v>
       </c>
       <c r="B332" t="n">
-        <v>80.84862518310547</v>
+        <v>80.8486328125</v>
       </c>
       <c r="C332" t="n">
-        <v>81.99068169579233</v>
+        <v>81.99068943295865</v>
       </c>
       <c r="D332" t="n">
-        <v>78.90713447349425</v>
+        <v>78.90714191967729</v>
       </c>
       <c r="E332" t="n">
-        <v>81.17367368654911</v>
+        <v>81.1736813466173</v>
       </c>
       <c r="F332" t="n">
         <v>515927</v>
@@ -7072,16 +7072,16 @@
         <v>44957</v>
       </c>
       <c r="B333" t="n">
-        <v>78.84564971923828</v>
+        <v>78.84564208984375</v>
       </c>
       <c r="C333" t="n">
-        <v>81.68321755514636</v>
+        <v>81.68320965117834</v>
       </c>
       <c r="D333" t="n">
-        <v>78.84564971923828</v>
+        <v>78.84564208984375</v>
       </c>
       <c r="E333" t="n">
-        <v>80.83984871849243</v>
+        <v>80.83984089613189</v>
       </c>
       <c r="F333" t="n">
         <v>714873</v>
@@ -7112,16 +7112,16 @@
         <v>44959</v>
       </c>
       <c r="B335" t="n">
-        <v>78.88956451416016</v>
+        <v>78.88957214355469</v>
       </c>
       <c r="C335" t="n">
-        <v>80.39180369577697</v>
+        <v>80.39181147045277</v>
       </c>
       <c r="D335" t="n">
-        <v>77.5630232347126</v>
+        <v>77.56303073581758</v>
       </c>
       <c r="E335" t="n">
-        <v>77.89685192981234</v>
+        <v>77.89685946320182</v>
       </c>
       <c r="F335" t="n">
         <v>645862</v>
@@ -7132,16 +7132,16 @@
         <v>44960</v>
       </c>
       <c r="B336" t="n">
-        <v>78.43274688720703</v>
+        <v>78.4327392578125</v>
       </c>
       <c r="C336" t="n">
-        <v>80.04919589494379</v>
+        <v>80.04918810831229</v>
       </c>
       <c r="D336" t="n">
-        <v>76.42976111654413</v>
+        <v>76.42975368198618</v>
       </c>
       <c r="E336" t="n">
-        <v>79.05648321386462</v>
+        <v>79.05647552379735</v>
       </c>
       <c r="F336" t="n">
         <v>709735</v>
@@ -7172,16 +7172,16 @@
         <v>44964</v>
       </c>
       <c r="B338" t="n">
-        <v>74.67275238037109</v>
+        <v>74.67276000976562</v>
       </c>
       <c r="C338" t="n">
-        <v>78.23947229046264</v>
+        <v>78.23948028427274</v>
       </c>
       <c r="D338" t="n">
-        <v>74.45312663807589</v>
+        <v>74.45313424503101</v>
       </c>
       <c r="E338" t="n">
-        <v>76.98321277643622</v>
+        <v>76.98322064189294</v>
       </c>
       <c r="F338" t="n">
         <v>1089766</v>
@@ -7252,16 +7252,16 @@
         <v>44970</v>
       </c>
       <c r="B342" t="n">
-        <v>73.79425811767578</v>
+        <v>73.79424285888672</v>
       </c>
       <c r="C342" t="n">
-        <v>74.05781172050324</v>
+        <v>74.05779640721795</v>
       </c>
       <c r="D342" t="n">
-        <v>70.90398220377323</v>
+        <v>70.90396754262024</v>
       </c>
       <c r="E342" t="n">
-        <v>71.35202064760129</v>
+        <v>71.35200589380526</v>
       </c>
       <c r="F342" t="n">
         <v>400048</v>
@@ -7272,16 +7272,16 @@
         <v>44971</v>
       </c>
       <c r="B343" t="n">
-        <v>72.90695953369141</v>
+        <v>72.90696716308594</v>
       </c>
       <c r="C343" t="n">
-        <v>74.53218868614353</v>
+        <v>74.53219648561118</v>
       </c>
       <c r="D343" t="n">
-        <v>71.91425359142397</v>
+        <v>71.91426111693616</v>
       </c>
       <c r="E343" t="n">
-        <v>73.00359539649439</v>
+        <v>73.00360303600144</v>
       </c>
       <c r="F343" t="n">
         <v>472429</v>
@@ -7312,16 +7312,16 @@
         <v>44973</v>
       </c>
       <c r="B345" t="n">
-        <v>71.15873718261719</v>
+        <v>71.15874481201172</v>
       </c>
       <c r="C345" t="n">
-        <v>73.96994387181648</v>
+        <v>73.96995180261891</v>
       </c>
       <c r="D345" t="n">
-        <v>70.32416208182393</v>
+        <v>70.32416962173819</v>
       </c>
       <c r="E345" t="n">
-        <v>73.30228647216005</v>
+        <v>73.30229433137855</v>
       </c>
       <c r="F345" t="n">
         <v>1330447</v>
@@ -7332,16 +7332,16 @@
         <v>44974</v>
       </c>
       <c r="B346" t="n">
-        <v>58.25353240966797</v>
+        <v>58.2535285949707</v>
       </c>
       <c r="C346" t="n">
-        <v>64.91258682963696</v>
+        <v>64.91258257887556</v>
       </c>
       <c r="D346" t="n">
-        <v>57.36624919591782</v>
+        <v>57.36624543932376</v>
       </c>
       <c r="E346" t="n">
-        <v>64.68417417050361</v>
+        <v>64.68416993469967</v>
       </c>
       <c r="F346" t="n">
         <v>4993765</v>
@@ -7392,16 +7392,16 @@
         <v>44981</v>
       </c>
       <c r="B349" t="n">
-        <v>58.85091400146484</v>
+        <v>58.85091781616211</v>
       </c>
       <c r="C349" t="n">
-        <v>59.79969884857108</v>
+        <v>59.79970272476828</v>
       </c>
       <c r="D349" t="n">
-        <v>57.98998481617827</v>
+        <v>57.98998857507038</v>
       </c>
       <c r="E349" t="n">
-        <v>59.56250598801751</v>
+        <v>59.56250984883994</v>
       </c>
       <c r="F349" t="n">
         <v>780666</v>
@@ -7432,16 +7432,16 @@
         <v>44985</v>
       </c>
       <c r="B351" t="n">
-        <v>56.48774719238281</v>
+        <v>56.48774337768555</v>
       </c>
       <c r="C351" t="n">
-        <v>57.19933249789922</v>
+        <v>57.19932863514759</v>
       </c>
       <c r="D351" t="n">
-        <v>55.53017540979462</v>
+        <v>55.53017165976352</v>
       </c>
       <c r="E351" t="n">
-        <v>56.82157592902526</v>
+        <v>56.82157209178407</v>
       </c>
       <c r="F351" t="n">
         <v>573942</v>
@@ -7452,16 +7452,16 @@
         <v>44986</v>
       </c>
       <c r="B352" t="n">
-        <v>54.14213943481445</v>
+        <v>54.14214706420898</v>
       </c>
       <c r="C352" t="n">
-        <v>57.10269353027231</v>
+        <v>57.10270157685085</v>
       </c>
       <c r="D352" t="n">
-        <v>53.41298035499475</v>
+        <v>53.41298788164043</v>
       </c>
       <c r="E352" t="n">
-        <v>56.48774412707847</v>
+        <v>56.48775208700194</v>
       </c>
       <c r="F352" t="n">
         <v>634515</v>
@@ -7472,16 +7472,16 @@
         <v>44987</v>
       </c>
       <c r="B353" t="n">
-        <v>53.14942932128906</v>
+        <v>53.14943313598633</v>
       </c>
       <c r="C353" t="n">
-        <v>54.59017364603414</v>
+        <v>54.59017756413803</v>
       </c>
       <c r="D353" t="n">
-        <v>52.64868289991359</v>
+        <v>52.64868667867075</v>
       </c>
       <c r="E353" t="n">
-        <v>54.08942722465866</v>
+        <v>54.08943110682245</v>
       </c>
       <c r="F353" t="n">
         <v>1104186</v>
@@ -7552,16 +7552,16 @@
         <v>44993</v>
       </c>
       <c r="B357" t="n">
-        <v>58.67521286010742</v>
+        <v>58.67520904541016</v>
       </c>
       <c r="C357" t="n">
-        <v>58.67521286010742</v>
+        <v>58.67520904541016</v>
       </c>
       <c r="D357" t="n">
-        <v>53.97522006484605</v>
+        <v>53.97521655571307</v>
       </c>
       <c r="E357" t="n">
-        <v>53.97522006484605</v>
+        <v>53.97521655571307</v>
       </c>
       <c r="F357" t="n">
         <v>1672249</v>
@@ -7592,16 +7592,16 @@
         <v>44995</v>
       </c>
       <c r="B359" t="n">
-        <v>52.01615905761719</v>
+        <v>52.01616287231445</v>
       </c>
       <c r="C359" t="n">
-        <v>56.08362866950537</v>
+        <v>56.08363278249773</v>
       </c>
       <c r="D359" t="n">
-        <v>51.79653331930479</v>
+        <v>51.7965371178954</v>
       </c>
       <c r="E359" t="n">
-        <v>55.52138731562125</v>
+        <v>55.52139138738065</v>
       </c>
       <c r="F359" t="n">
         <v>846843</v>
@@ -7612,16 +7612,16 @@
         <v>44998</v>
       </c>
       <c r="B360" t="n">
-        <v>50.39093399047852</v>
+        <v>50.39093017578125</v>
       </c>
       <c r="C360" t="n">
-        <v>51.9634552076585</v>
+        <v>51.96345127391815</v>
       </c>
       <c r="D360" t="n">
-        <v>49.46850648556628</v>
+        <v>49.46850274069867</v>
       </c>
       <c r="E360" t="n">
-        <v>51.9634552076585</v>
+        <v>51.96345127391815</v>
       </c>
       <c r="F360" t="n">
         <v>1066340</v>
@@ -7652,16 +7652,16 @@
         <v>45000</v>
       </c>
       <c r="B362" t="n">
-        <v>50.43485641479492</v>
+        <v>50.43486022949219</v>
       </c>
       <c r="C362" t="n">
-        <v>50.90924883268146</v>
+        <v>50.90925268325992</v>
       </c>
       <c r="D362" t="n">
-        <v>48.08925504506086</v>
+        <v>48.08925868234591</v>
       </c>
       <c r="E362" t="n">
-        <v>49.89896905583676</v>
+        <v>49.89897283000158</v>
       </c>
       <c r="F362" t="n">
         <v>1072440</v>
@@ -7692,16 +7692,16 @@
         <v>45002</v>
       </c>
       <c r="B364" t="n">
-        <v>55.0645637512207</v>
+        <v>55.06456756591797</v>
       </c>
       <c r="C364" t="n">
-        <v>55.5477396909908</v>
+        <v>55.54774353916095</v>
       </c>
       <c r="D364" t="n">
-        <v>52.19185877680513</v>
+        <v>52.19186239249056</v>
       </c>
       <c r="E364" t="n">
-        <v>53.58867856525999</v>
+        <v>53.58868227771264</v>
       </c>
       <c r="F364" t="n">
         <v>1415773</v>
@@ -7792,16 +7792,16 @@
         <v>45009</v>
       </c>
       <c r="B369" t="n">
-        <v>50.40850067138672</v>
+        <v>50.40850448608398</v>
       </c>
       <c r="C369" t="n">
-        <v>51.3660690297127</v>
+        <v>51.3660729168746</v>
       </c>
       <c r="D369" t="n">
-        <v>48.82719601713704</v>
+        <v>48.82719971216801</v>
       </c>
       <c r="E369" t="n">
-        <v>50.05709814767665</v>
+        <v>50.05710193578128</v>
       </c>
       <c r="F369" t="n">
         <v>598427</v>
@@ -7812,16 +7812,16 @@
         <v>45012</v>
       </c>
       <c r="B370" t="n">
-        <v>51.84925079345703</v>
+        <v>51.84924697875977</v>
       </c>
       <c r="C370" t="n">
-        <v>52.5256985490655</v>
+        <v>52.52569468460005</v>
       </c>
       <c r="D370" t="n">
-        <v>50.65448610049781</v>
+        <v>50.6544823737028</v>
       </c>
       <c r="E370" t="n">
-        <v>51.3924288019595</v>
+        <v>51.39242502087193</v>
       </c>
       <c r="F370" t="n">
         <v>634884</v>
@@ -7832,16 +7832,16 @@
         <v>45013</v>
       </c>
       <c r="B371" t="n">
-        <v>54.30905532836914</v>
+        <v>54.30905151367188</v>
       </c>
       <c r="C371" t="n">
-        <v>54.44961567467342</v>
+        <v>54.44961185010312</v>
       </c>
       <c r="D371" t="n">
-        <v>51.11130493652956</v>
+        <v>51.111301346444</v>
       </c>
       <c r="E371" t="n">
-        <v>51.83167713024186</v>
+        <v>51.83167348955698</v>
       </c>
       <c r="F371" t="n">
         <v>854484</v>
@@ -7872,16 +7872,16 @@
         <v>45015</v>
       </c>
       <c r="B373" t="n">
-        <v>54.20363616943359</v>
+        <v>54.20362854003906</v>
       </c>
       <c r="C373" t="n">
-        <v>56.39989033438518</v>
+        <v>56.39988239585843</v>
       </c>
       <c r="D373" t="n">
-        <v>53.72924374164636</v>
+        <v>53.7292361790246</v>
       </c>
       <c r="E373" t="n">
-        <v>54.0367184534216</v>
+        <v>54.03671084752145</v>
       </c>
       <c r="F373" t="n">
         <v>990197</v>
@@ -7892,16 +7892,16 @@
         <v>45016</v>
       </c>
       <c r="B374" t="n">
-        <v>52.33242034912109</v>
+        <v>52.33242416381836</v>
       </c>
       <c r="C374" t="n">
-        <v>54.73073299523703</v>
+        <v>54.73073698475589</v>
       </c>
       <c r="D374" t="n">
-        <v>51.94588025840541</v>
+        <v>51.94588404492639</v>
       </c>
       <c r="E374" t="n">
-        <v>54.20363256687721</v>
+        <v>54.20363651797383</v>
       </c>
       <c r="F374" t="n">
         <v>558868</v>
@@ -8012,16 +8012,16 @@
         <v>45027</v>
       </c>
       <c r="B380" t="n">
-        <v>54.63410186767578</v>
+        <v>54.63409805297852</v>
       </c>
       <c r="C380" t="n">
-        <v>54.63410186767578</v>
+        <v>54.63409805297852</v>
       </c>
       <c r="D380" t="n">
-        <v>48.8535537111691</v>
+        <v>48.85355030008497</v>
       </c>
       <c r="E380" t="n">
-        <v>48.8535537111691</v>
+        <v>48.85355030008497</v>
       </c>
       <c r="F380" t="n">
         <v>1223134</v>
@@ -8032,16 +8032,16 @@
         <v>45028</v>
       </c>
       <c r="B381" t="n">
-        <v>56.73373031616211</v>
+        <v>56.73372268676758</v>
       </c>
       <c r="C381" t="n">
-        <v>57.69129545283193</v>
+        <v>57.69128769466669</v>
       </c>
       <c r="D381" t="n">
-        <v>54.30905994717439</v>
+        <v>54.3090526438428</v>
       </c>
       <c r="E381" t="n">
-        <v>54.55503973632089</v>
+        <v>54.55503239991062</v>
       </c>
       <c r="F381" t="n">
         <v>1443641</v>
@@ -8052,16 +8052,16 @@
         <v>45029</v>
       </c>
       <c r="B382" t="n">
-        <v>60.46736145019531</v>
+        <v>60.46735763549805</v>
       </c>
       <c r="C382" t="n">
-        <v>61.46006740025275</v>
+        <v>61.46006352292876</v>
       </c>
       <c r="D382" t="n">
-        <v>55.96064024470993</v>
+        <v>55.96063671432766</v>
       </c>
       <c r="E382" t="n">
-        <v>56.408675287958</v>
+        <v>56.40867172931058</v>
       </c>
       <c r="F382" t="n">
         <v>2756815</v>
@@ -8072,16 +8072,16 @@
         <v>45030</v>
       </c>
       <c r="B383" t="n">
-        <v>60.44979476928711</v>
+        <v>60.44978713989258</v>
       </c>
       <c r="C383" t="n">
-        <v>62.15409288868556</v>
+        <v>62.15408504419084</v>
       </c>
       <c r="D383" t="n">
-        <v>59.1056861297395</v>
+        <v>59.10567866998549</v>
       </c>
       <c r="E383" t="n">
-        <v>60.45858167676914</v>
+        <v>60.45857404626561</v>
       </c>
       <c r="F383" t="n">
         <v>793877</v>
@@ -8092,16 +8092,16 @@
         <v>45033</v>
       </c>
       <c r="B384" t="n">
-        <v>59.95782852172852</v>
+        <v>59.95782470703125</v>
       </c>
       <c r="C384" t="n">
-        <v>60.72212852895193</v>
+        <v>60.7221246656276</v>
       </c>
       <c r="D384" t="n">
-        <v>59.16717449743633</v>
+        <v>59.16717073304285</v>
       </c>
       <c r="E384" t="n">
-        <v>60.35315218265168</v>
+        <v>60.35314834280274</v>
       </c>
       <c r="F384" t="n">
         <v>288592</v>
@@ -8112,16 +8112,16 @@
         <v>45034</v>
       </c>
       <c r="B385" t="n">
-        <v>61.49520874023438</v>
+        <v>61.49521255493164</v>
       </c>
       <c r="C385" t="n">
-        <v>61.49520874023438</v>
+        <v>61.49521255493164</v>
       </c>
       <c r="D385" t="n">
-        <v>59.16717449743633</v>
+        <v>59.16717816771997</v>
       </c>
       <c r="E385" t="n">
-        <v>59.16717449743633</v>
+        <v>59.16717816771997</v>
       </c>
       <c r="F385" t="n">
         <v>581190</v>
@@ -8152,16 +8152,16 @@
         <v>45036</v>
       </c>
       <c r="B387" t="n">
-        <v>60.80119705200195</v>
+        <v>60.80118942260742</v>
       </c>
       <c r="C387" t="n">
-        <v>60.80119705200195</v>
+        <v>60.80118942260742</v>
       </c>
       <c r="D387" t="n">
-        <v>58.2183958652091</v>
+        <v>58.21838855990702</v>
       </c>
       <c r="E387" t="n">
-        <v>58.78942420478224</v>
+        <v>58.78941682782696</v>
       </c>
       <c r="F387" t="n">
         <v>442904</v>
@@ -8212,16 +8212,16 @@
         <v>45042</v>
       </c>
       <c r="B390" t="n">
-        <v>59.31652069091797</v>
+        <v>59.31651306152344</v>
       </c>
       <c r="C390" t="n">
-        <v>60.01932578469255</v>
+        <v>60.019318064902</v>
       </c>
       <c r="D390" t="n">
-        <v>56.9533521355543</v>
+        <v>56.95334481011464</v>
       </c>
       <c r="E390" t="n">
-        <v>59.30774048651921</v>
+        <v>59.30773285825401</v>
       </c>
       <c r="F390" t="n">
         <v>963997</v>
@@ -8252,16 +8252,16 @@
         <v>45044</v>
       </c>
       <c r="B392" t="n">
-        <v>63.67390060424805</v>
+        <v>63.67390441894531</v>
       </c>
       <c r="C392" t="n">
-        <v>63.75296265734114</v>
+        <v>63.75296647677501</v>
       </c>
       <c r="D392" t="n">
-        <v>60.61670720484071</v>
+        <v>60.61671083638181</v>
       </c>
       <c r="E392" t="n">
-        <v>61.50399711452398</v>
+        <v>61.50400079922254</v>
       </c>
       <c r="F392" t="n">
         <v>633625</v>
@@ -8292,16 +8292,16 @@
         <v>45049</v>
       </c>
       <c r="B394" t="n">
-        <v>58.85091400146484</v>
+        <v>58.85091781616211</v>
       </c>
       <c r="C394" t="n">
-        <v>60.08081954003449</v>
+        <v>60.08082343445384</v>
       </c>
       <c r="D394" t="n">
-        <v>58.77185194876231</v>
+        <v>58.7718557583348</v>
       </c>
       <c r="E394" t="n">
-        <v>59.12325448870306</v>
+        <v>59.12325832105335</v>
       </c>
       <c r="F394" t="n">
         <v>320277</v>
@@ -8312,16 +8312,16 @@
         <v>45050</v>
       </c>
       <c r="B395" t="n">
-        <v>60.79240036010742</v>
+        <v>60.79240798950195</v>
       </c>
       <c r="C395" t="n">
-        <v>61.5654872316979</v>
+        <v>61.56549495811417</v>
       </c>
       <c r="D395" t="n">
-        <v>58.60492993083402</v>
+        <v>58.60493728570287</v>
       </c>
       <c r="E395" t="n">
-        <v>58.60492993083402</v>
+        <v>58.60493728570287</v>
       </c>
       <c r="F395" t="n">
         <v>661928</v>
@@ -8372,16 +8372,16 @@
         <v>45055</v>
       </c>
       <c r="B398" t="n">
-        <v>66.17762756347656</v>
+        <v>66.17763519287109</v>
       </c>
       <c r="C398" t="n">
-        <v>67.59201782205866</v>
+        <v>67.59202561451346</v>
       </c>
       <c r="D398" t="n">
-        <v>64.157068136232</v>
+        <v>64.15707553268307</v>
       </c>
       <c r="E398" t="n">
-        <v>65.00921705378778</v>
+        <v>65.00922454848022</v>
       </c>
       <c r="F398" t="n">
         <v>730723</v>
@@ -8412,16 +8412,16 @@
         <v>45057</v>
       </c>
       <c r="B400" t="n">
-        <v>67.00341796875</v>
+        <v>67.00341033935547</v>
       </c>
       <c r="C400" t="n">
-        <v>68.69892895366183</v>
+        <v>68.69892113120667</v>
       </c>
       <c r="D400" t="n">
-        <v>67.00341796875</v>
+        <v>67.00341033935547</v>
       </c>
       <c r="E400" t="n">
-        <v>67.38117451054214</v>
+        <v>67.38116683813408</v>
       </c>
       <c r="F400" t="n">
         <v>282491</v>
@@ -8432,16 +8432,16 @@
         <v>45058</v>
       </c>
       <c r="B401" t="n">
-        <v>66.23033142089844</v>
+        <v>66.23033905029297</v>
       </c>
       <c r="C401" t="n">
-        <v>67.00341154047932</v>
+        <v>67.00341925892872</v>
       </c>
       <c r="D401" t="n">
-        <v>65.81743399594278</v>
+        <v>65.81744157777364</v>
       </c>
       <c r="E401" t="n">
-        <v>66.79257272649272</v>
+        <v>66.79258042065457</v>
       </c>
       <c r="F401" t="n">
         <v>398348</v>
@@ -8452,16 +8452,16 @@
         <v>45061</v>
       </c>
       <c r="B402" t="n">
-        <v>68.41781616210938</v>
+        <v>68.41780853271484</v>
       </c>
       <c r="C402" t="n">
-        <v>69.17332933280035</v>
+        <v>69.17332161915719</v>
       </c>
       <c r="D402" t="n">
-        <v>66.23913231833025</v>
+        <v>66.2391249318847</v>
       </c>
       <c r="E402" t="n">
-        <v>66.23913231833025</v>
+        <v>66.2391249318847</v>
       </c>
       <c r="F402" t="n">
         <v>689284</v>
@@ -8472,16 +8472,16 @@
         <v>45062</v>
       </c>
       <c r="B403" t="n">
-        <v>69.20845794677734</v>
+        <v>69.20846557617188</v>
       </c>
       <c r="C403" t="n">
-        <v>74.04022393567588</v>
+        <v>74.04023209771412</v>
       </c>
       <c r="D403" t="n">
-        <v>67.52173397378508</v>
+        <v>67.52174141723872</v>
       </c>
       <c r="E403" t="n">
-        <v>69.22603175828814</v>
+        <v>69.22603938961998</v>
       </c>
       <c r="F403" t="n">
         <v>1416795</v>
@@ -8492,16 +8492,16 @@
         <v>45063</v>
       </c>
       <c r="B404" t="n">
-        <v>72.32714080810547</v>
+        <v>72.32715606689453</v>
       </c>
       <c r="C404" t="n">
-        <v>73.79423895007376</v>
+        <v>73.79425451837514</v>
       </c>
       <c r="D404" t="n">
-        <v>67.66228614538477</v>
+        <v>67.66230042003383</v>
       </c>
       <c r="E404" t="n">
-        <v>69.41051163198605</v>
+        <v>69.4105262754566</v>
       </c>
       <c r="F404" t="n">
         <v>1084227</v>
@@ -8512,16 +8512,16 @@
         <v>45064</v>
       </c>
       <c r="B405" t="n">
-        <v>71.18508911132812</v>
+        <v>71.18510437011719</v>
       </c>
       <c r="C405" t="n">
-        <v>71.99331017297479</v>
+        <v>71.99332560500903</v>
       </c>
       <c r="D405" t="n">
-        <v>69.86733475768652</v>
+        <v>69.86734973401003</v>
       </c>
       <c r="E405" t="n">
-        <v>71.15873509664654</v>
+        <v>71.15875034978652</v>
       </c>
       <c r="F405" t="n">
         <v>796674</v>
@@ -8552,16 +8552,16 @@
         <v>45068</v>
       </c>
       <c r="B407" t="n">
-        <v>77.76507568359375</v>
+        <v>77.76508331298828</v>
       </c>
       <c r="C407" t="n">
-        <v>78.3097499079546</v>
+        <v>78.30975759078616</v>
       </c>
       <c r="D407" t="n">
-        <v>75.0768588878434</v>
+        <v>75.07686625350173</v>
       </c>
       <c r="E407" t="n">
-        <v>75.45461541229061</v>
+        <v>75.45462281500996</v>
       </c>
       <c r="F407" t="n">
         <v>873661</v>
@@ -8572,16 +8572,16 @@
         <v>45069</v>
       </c>
       <c r="B408" t="n">
-        <v>77.13256072998047</v>
+        <v>77.132568359375</v>
       </c>
       <c r="C408" t="n">
-        <v>80.43572695506535</v>
+        <v>80.43573491118516</v>
       </c>
       <c r="D408" t="n">
-        <v>76.42975569775851</v>
+        <v>76.42976325763665</v>
       </c>
       <c r="E408" t="n">
-        <v>77.74751010634054</v>
+        <v>77.74751779656141</v>
       </c>
       <c r="F408" t="n">
         <v>970823</v>
@@ -8592,16 +8592,16 @@
         <v>45070</v>
       </c>
       <c r="B409" t="n">
-        <v>77.30825805664062</v>
+        <v>77.30826568603516</v>
       </c>
       <c r="C409" t="n">
-        <v>78.27460994185954</v>
+        <v>78.27461766662137</v>
       </c>
       <c r="D409" t="n">
-        <v>75.96414964236531</v>
+        <v>75.96415713911252</v>
       </c>
       <c r="E409" t="n">
-        <v>76.61423993570233</v>
+        <v>76.61424749660561</v>
       </c>
       <c r="F409" t="n">
         <v>567398</v>
@@ -8612,16 +8612,16 @@
         <v>45071</v>
       </c>
       <c r="B410" t="n">
-        <v>81.90283966064453</v>
+        <v>81.90283203125</v>
       </c>
       <c r="C410" t="n">
-        <v>81.90283966064453</v>
+        <v>81.90283203125</v>
       </c>
       <c r="D410" t="n">
-        <v>77.75630432590624</v>
+        <v>77.75629708276882</v>
       </c>
       <c r="E410" t="n">
-        <v>77.75630432590624</v>
+        <v>77.75629708276882</v>
       </c>
       <c r="F410" t="n">
         <v>1153989</v>
@@ -8672,16 +8672,16 @@
         <v>45076</v>
       </c>
       <c r="B413" t="n">
-        <v>80.55872344970703</v>
+        <v>80.55873107910156</v>
       </c>
       <c r="C413" t="n">
-        <v>84.13423043735499</v>
+        <v>84.13423840537149</v>
       </c>
       <c r="D413" t="n">
-        <v>79.3990997429684</v>
+        <v>79.3991072625396</v>
       </c>
       <c r="E413" t="n">
-        <v>82.54414213179378</v>
+        <v>82.54414994921937</v>
       </c>
       <c r="F413" t="n">
         <v>664894</v>
@@ -8692,16 +8692,16 @@
         <v>45077</v>
       </c>
       <c r="B414" t="n">
-        <v>78.81928253173828</v>
+        <v>78.81929016113281</v>
       </c>
       <c r="C414" t="n">
-        <v>80.38301664656991</v>
+        <v>80.38302442732773</v>
       </c>
       <c r="D414" t="n">
-        <v>78.53816186730164</v>
+        <v>78.53816946948481</v>
       </c>
       <c r="E414" t="n">
-        <v>79.97890611034508</v>
+        <v>79.97891385198659</v>
       </c>
       <c r="F414" t="n">
         <v>527775</v>
@@ -8712,16 +8712,16 @@
         <v>45078</v>
       </c>
       <c r="B415" t="n">
-        <v>79.15312194824219</v>
+        <v>79.15311431884766</v>
       </c>
       <c r="C415" t="n">
-        <v>80.0579790000172</v>
+        <v>80.05797128340549</v>
       </c>
       <c r="D415" t="n">
-        <v>78.45910374774334</v>
+        <v>78.45909618524368</v>
       </c>
       <c r="E415" t="n">
-        <v>79.07405989243097</v>
+        <v>79.07405227065705</v>
       </c>
       <c r="F415" t="n">
         <v>974431</v>
@@ -8772,16 +8772,16 @@
         <v>45083</v>
       </c>
       <c r="B418" t="n">
-        <v>83.89702606201172</v>
+        <v>83.89704132080078</v>
       </c>
       <c r="C418" t="n">
-        <v>86.70823263127907</v>
+        <v>86.70824840135691</v>
       </c>
       <c r="D418" t="n">
-        <v>81.92039455793291</v>
+        <v>81.92040945722171</v>
       </c>
       <c r="E418" t="n">
-        <v>82.01703041210571</v>
+        <v>82.01704532897017</v>
       </c>
       <c r="F418" t="n">
         <v>1573579</v>
@@ -8792,16 +8792,16 @@
         <v>45084</v>
       </c>
       <c r="B419" t="n">
-        <v>86.52375030517578</v>
+        <v>86.52375793457031</v>
       </c>
       <c r="C419" t="n">
-        <v>86.60281905287367</v>
+        <v>86.60282668924023</v>
       </c>
       <c r="D419" t="n">
-        <v>82.88674876976107</v>
+        <v>82.88675607845614</v>
       </c>
       <c r="E419" t="n">
-        <v>84.33627992139918</v>
+        <v>84.3362873579094</v>
       </c>
       <c r="F419" t="n">
         <v>2805750</v>
@@ -8892,16 +8892,16 @@
         <v>45092</v>
       </c>
       <c r="B424" t="n">
-        <v>91.97926330566406</v>
+        <v>91.97927093505859</v>
       </c>
       <c r="C424" t="n">
-        <v>92.26038400333246</v>
+        <v>92.26039165604509</v>
       </c>
       <c r="D424" t="n">
-        <v>89.18562344026418</v>
+        <v>89.18563083793495</v>
       </c>
       <c r="E424" t="n">
-        <v>89.43160991536439</v>
+        <v>89.43161733343898</v>
       </c>
       <c r="F424" t="n">
         <v>844482</v>
@@ -8912,16 +8912,16 @@
         <v>45093</v>
       </c>
       <c r="B425" t="n">
-        <v>94.66748809814453</v>
+        <v>94.66748046875</v>
       </c>
       <c r="C425" t="n">
-        <v>95.72168904992172</v>
+        <v>95.72168133556757</v>
       </c>
       <c r="D425" t="n">
-        <v>91.39066885725265</v>
+        <v>91.39066149194188</v>
       </c>
       <c r="E425" t="n">
-        <v>91.84749418481664</v>
+        <v>91.84748678268964</v>
       </c>
       <c r="F425" t="n">
         <v>1238876</v>
@@ -8952,16 +8952,16 @@
         <v>45097</v>
       </c>
       <c r="B427" t="n">
-        <v>99.66616058349609</v>
+        <v>99.66616821289062</v>
       </c>
       <c r="C427" t="n">
-        <v>100.1493399043639</v>
+        <v>100.1493475707456</v>
       </c>
       <c r="D427" t="n">
-        <v>95.20337053073942</v>
+        <v>95.20337781850962</v>
       </c>
       <c r="E427" t="n">
-        <v>97.85644658614729</v>
+        <v>97.8564540770091</v>
       </c>
       <c r="F427" t="n">
         <v>1047570</v>
@@ -9012,16 +9012,16 @@
         <v>45100</v>
       </c>
       <c r="B430" t="n">
-        <v>98.56803894042969</v>
+        <v>98.56803131103516</v>
       </c>
       <c r="C430" t="n">
-        <v>100.5446707911264</v>
+        <v>100.544663008736</v>
       </c>
       <c r="D430" t="n">
-        <v>97.24150416861238</v>
+        <v>97.24149664189471</v>
       </c>
       <c r="E430" t="n">
-        <v>99.71009557958853</v>
+        <v>99.71008786179617</v>
       </c>
       <c r="F430" t="n">
         <v>1883788</v>
@@ -9052,16 +9052,16 @@
         <v>45104</v>
       </c>
       <c r="B432" t="n">
-        <v>94.86952972412109</v>
+        <v>94.86953735351562</v>
       </c>
       <c r="C432" t="n">
-        <v>98.37476124760583</v>
+        <v>98.3747691588906</v>
       </c>
       <c r="D432" t="n">
-        <v>91.40823273064802</v>
+        <v>91.40824008168553</v>
       </c>
       <c r="E432" t="n">
-        <v>96.97793810083515</v>
+        <v>96.9779458997876</v>
       </c>
       <c r="F432" t="n">
         <v>1484061</v>
@@ -9092,16 +9092,16 @@
         <v>45106</v>
       </c>
       <c r="B434" t="n">
-        <v>99.08634948730469</v>
+        <v>99.08635711669922</v>
       </c>
       <c r="C434" t="n">
-        <v>99.83307566149379</v>
+        <v>99.83308334838433</v>
       </c>
       <c r="D434" t="n">
-        <v>97.4259794320393</v>
+        <v>97.4259869335896</v>
       </c>
       <c r="E434" t="n">
-        <v>97.53139549748747</v>
+        <v>97.53140300715454</v>
       </c>
       <c r="F434" t="n">
         <v>506881</v>
@@ -9132,16 +9132,16 @@
         <v>45110</v>
       </c>
       <c r="B436" t="n">
-        <v>100.8960647583008</v>
+        <v>100.8960800170898</v>
       </c>
       <c r="C436" t="n">
-        <v>101.4670930292576</v>
+        <v>101.4671083744049</v>
       </c>
       <c r="D436" t="n">
-        <v>98.26055584844994</v>
+        <v>98.26057070866375</v>
       </c>
       <c r="E436" t="n">
-        <v>98.46261448061463</v>
+        <v>98.46262937138633</v>
       </c>
       <c r="F436" t="n">
         <v>512630</v>
@@ -9172,16 +9172,16 @@
         <v>45112</v>
       </c>
       <c r="B438" t="n">
-        <v>101.2386856079102</v>
+        <v>101.2386779785156</v>
       </c>
       <c r="C438" t="n">
-        <v>101.7042911336343</v>
+        <v>101.7042834691515</v>
       </c>
       <c r="D438" t="n">
-        <v>99.13027703067131</v>
+        <v>99.13026956016742</v>
       </c>
       <c r="E438" t="n">
-        <v>99.53439431586756</v>
+        <v>99.5343868149092</v>
       </c>
       <c r="F438" t="n">
         <v>519657</v>
@@ -9212,16 +9212,16 @@
         <v>45114</v>
       </c>
       <c r="B440" t="n">
-        <v>101.2386856079102</v>
+        <v>101.2386779785156</v>
       </c>
       <c r="C440" t="n">
-        <v>102.0820476983165</v>
+        <v>102.0820400053658</v>
       </c>
       <c r="D440" t="n">
-        <v>98.16392505431695</v>
+        <v>98.16391765663779</v>
       </c>
       <c r="E440" t="n">
-        <v>98.73495335475918</v>
+        <v>98.73494591404707</v>
       </c>
       <c r="F440" t="n">
         <v>1239341</v>
@@ -9232,16 +9232,16 @@
         <v>45117</v>
       </c>
       <c r="B441" t="n">
-        <v>98.26055908203125</v>
+        <v>98.26056671142578</v>
       </c>
       <c r="C441" t="n">
-        <v>100.7467241773928</v>
+        <v>100.7467319998245</v>
       </c>
       <c r="D441" t="n">
-        <v>97.19757125770386</v>
+        <v>97.19757880456319</v>
       </c>
       <c r="E441" t="n">
-        <v>100.7467241773928</v>
+        <v>100.7467319998245</v>
       </c>
       <c r="F441" t="n">
         <v>1057552</v>
@@ -9272,16 +9272,16 @@
         <v>45119</v>
       </c>
       <c r="B443" t="n">
-        <v>99.29718780517578</v>
+        <v>99.29719543457031</v>
       </c>
       <c r="C443" t="n">
-        <v>102.0644734504011</v>
+        <v>102.0644812924171</v>
       </c>
       <c r="D443" t="n">
-        <v>98.57681565108831</v>
+        <v>98.57682322513379</v>
       </c>
       <c r="E443" t="n">
-        <v>99.10391608292989</v>
+        <v>99.10392369747458</v>
       </c>
       <c r="F443" t="n">
         <v>690662</v>
@@ -9292,16 +9292,16 @@
         <v>45120</v>
       </c>
       <c r="B444" t="n">
-        <v>97.98822784423828</v>
+        <v>97.98822021484375</v>
       </c>
       <c r="C444" t="n">
-        <v>101.0893424384329</v>
+        <v>101.0893345675846</v>
       </c>
       <c r="D444" t="n">
-        <v>97.21514759802663</v>
+        <v>97.21514002882437</v>
       </c>
       <c r="E444" t="n">
-        <v>99.32354948813953</v>
+        <v>99.32354175477643</v>
       </c>
       <c r="F444" t="n">
         <v>738822</v>
@@ -9312,16 +9312,16 @@
         <v>45121</v>
       </c>
       <c r="B445" t="n">
-        <v>96.74075317382812</v>
+        <v>96.74074554443359</v>
       </c>
       <c r="C445" t="n">
-        <v>98.69981111857781</v>
+        <v>98.69980333468348</v>
       </c>
       <c r="D445" t="n">
-        <v>95.02766829526057</v>
+        <v>95.02766080096731</v>
       </c>
       <c r="E445" t="n">
-        <v>98.69981111857781</v>
+        <v>98.69980333468348</v>
       </c>
       <c r="F445" t="n">
         <v>461646</v>
@@ -9372,16 +9372,16 @@
         <v>45126</v>
       </c>
       <c r="B448" t="n">
-        <v>101.0629806518555</v>
+        <v>101.06298828125</v>
       </c>
       <c r="C448" t="n">
-        <v>101.2650325779447</v>
+        <v>101.2650402225924</v>
       </c>
       <c r="D448" t="n">
-        <v>99.00728025382909</v>
+        <v>99.00728772803575</v>
       </c>
       <c r="E448" t="n">
-        <v>100.8257811008604</v>
+        <v>100.8257887123484</v>
       </c>
       <c r="F448" t="n">
         <v>1189852</v>
@@ -9392,16 +9392,16 @@
         <v>45127</v>
       </c>
       <c r="B449" t="n">
-        <v>106.9138107299805</v>
+        <v>106.913818359375</v>
       </c>
       <c r="C449" t="n">
-        <v>107.2740001714642</v>
+        <v>107.2740078265619</v>
       </c>
       <c r="D449" t="n">
-        <v>100.3601792578093</v>
+        <v>100.3601864195351</v>
       </c>
       <c r="E449" t="n">
-        <v>100.4919560462166</v>
+        <v>100.4919632173461</v>
       </c>
       <c r="F449" t="n">
         <v>1906043</v>
@@ -9432,16 +9432,16 @@
         <v>45131</v>
       </c>
       <c r="B451" t="n">
-        <v>112.6240844726562</v>
+        <v>112.6240768432617</v>
       </c>
       <c r="C451" t="n">
-        <v>113.1160440190282</v>
+        <v>113.1160363563073</v>
       </c>
       <c r="D451" t="n">
-        <v>109.3033441297533</v>
+        <v>109.3033367253127</v>
       </c>
       <c r="E451" t="n">
-        <v>110.85829822838</v>
+        <v>110.8582907186036</v>
       </c>
       <c r="F451" t="n">
         <v>870351</v>
@@ -9452,16 +9452,16 @@
         <v>45132</v>
       </c>
       <c r="B452" t="n">
-        <v>112.1584701538086</v>
+        <v>112.1584777832031</v>
       </c>
       <c r="C452" t="n">
-        <v>115.3298663433468</v>
+        <v>115.3298741884703</v>
       </c>
       <c r="D452" t="n">
-        <v>110.5859490671098</v>
+        <v>110.5859565895362</v>
       </c>
       <c r="E452" t="n">
-        <v>112.9491308527013</v>
+        <v>112.9491385358792</v>
       </c>
       <c r="F452" t="n">
         <v>603712</v>
@@ -9472,16 +9472,16 @@
         <v>45133</v>
       </c>
       <c r="B453" t="n">
-        <v>113.8891220092773</v>
+        <v>113.8891296386719</v>
       </c>
       <c r="C453" t="n">
-        <v>113.9857578700642</v>
+        <v>113.9857655059323</v>
       </c>
       <c r="D453" t="n">
-        <v>110.5508081151489</v>
+        <v>110.5508155209108</v>
       </c>
       <c r="E453" t="n">
-        <v>111.0427743252761</v>
+        <v>111.0427817639948</v>
       </c>
       <c r="F453" t="n">
         <v>810223</v>
@@ -9492,16 +9492,16 @@
         <v>45134</v>
       </c>
       <c r="B454" t="n">
-        <v>110.7440795898438</v>
+        <v>110.7440872192383</v>
       </c>
       <c r="C454" t="n">
-        <v>114.6446348276118</v>
+        <v>114.6446427257238</v>
       </c>
       <c r="D454" t="n">
-        <v>109.7074458420786</v>
+        <v>109.7074534000573</v>
       </c>
       <c r="E454" t="n">
-        <v>113.5025783131018</v>
+        <v>113.5025861325351</v>
       </c>
       <c r="F454" t="n">
         <v>678181</v>
@@ -9532,16 +9532,16 @@
         <v>45138</v>
       </c>
       <c r="B456" t="n">
-        <v>111.8246536254883</v>
+        <v>111.8246459960938</v>
       </c>
       <c r="C456" t="n">
-        <v>115.0838991246485</v>
+        <v>115.0838912728874</v>
       </c>
       <c r="D456" t="n">
-        <v>110.7792328550693</v>
+        <v>110.7792252970001</v>
       </c>
       <c r="E456" t="n">
-        <v>112.6416617270665</v>
+        <v>112.6416540419304</v>
       </c>
       <c r="F456" t="n">
         <v>524630</v>
@@ -9552,16 +9552,16 @@
         <v>45139</v>
       </c>
       <c r="B457" t="n">
-        <v>113.2302551269531</v>
+        <v>113.2302474975586</v>
       </c>
       <c r="C457" t="n">
-        <v>113.6343724193571</v>
+        <v>113.6343647627333</v>
       </c>
       <c r="D457" t="n">
-        <v>109.1803556179347</v>
+        <v>109.1803482614203</v>
       </c>
       <c r="E457" t="n">
-        <v>111.5698849345946</v>
+        <v>111.5698774170749</v>
       </c>
       <c r="F457" t="n">
         <v>739423</v>
@@ -9572,16 +9572,16 @@
         <v>45140</v>
       </c>
       <c r="B458" t="n">
-        <v>112.2726821899414</v>
+        <v>112.2726898193359</v>
       </c>
       <c r="C458" t="n">
-        <v>112.4220260861785</v>
+        <v>112.4220337257216</v>
       </c>
       <c r="D458" t="n">
-        <v>108.66203444888</v>
+        <v>108.6620418329161</v>
       </c>
       <c r="E458" t="n">
-        <v>111.692867012862</v>
+        <v>111.6928746028557</v>
       </c>
       <c r="F458" t="n">
         <v>921444</v>
@@ -9612,16 +9612,16 @@
         <v>45142</v>
       </c>
       <c r="B460" t="n">
-        <v>113.1336135864258</v>
+        <v>113.1336212158203</v>
       </c>
       <c r="C460" t="n">
-        <v>114.6007119660374</v>
+        <v>114.6007196943687</v>
       </c>
       <c r="D460" t="n">
-        <v>110.9900641534965</v>
+        <v>110.9900716383365</v>
       </c>
       <c r="E460" t="n">
-        <v>114.2053883028904</v>
+        <v>114.2053960045622</v>
       </c>
       <c r="F460" t="n">
         <v>805649</v>
@@ -9632,16 +9632,16 @@
         <v>45145</v>
       </c>
       <c r="B461" t="n">
-        <v>112.993049621582</v>
+        <v>112.9930572509766</v>
       </c>
       <c r="C461" t="n">
-        <v>117.7193999696295</v>
+        <v>117.7194079181516</v>
       </c>
       <c r="D461" t="n">
-        <v>111.6225871100018</v>
+        <v>111.6225946468615</v>
       </c>
       <c r="E461" t="n">
-        <v>113.3268850453896</v>
+        <v>113.326892697325</v>
       </c>
       <c r="F461" t="n">
         <v>579696</v>
@@ -9652,16 +9652,16 @@
         <v>45146</v>
       </c>
       <c r="B462" t="n">
-        <v>113.590446472168</v>
+        <v>113.5904388427734</v>
       </c>
       <c r="C462" t="n">
-        <v>113.590446472168</v>
+        <v>113.5904388427734</v>
       </c>
       <c r="D462" t="n">
-        <v>109.3033473202589</v>
+        <v>109.3033399788109</v>
       </c>
       <c r="E462" t="n">
-        <v>111.8685746047133</v>
+        <v>111.8685670909697</v>
       </c>
       <c r="F462" t="n">
         <v>457201</v>
@@ -9672,16 +9672,16 @@
         <v>45147</v>
       </c>
       <c r="B463" t="n">
-        <v>112.4483871459961</v>
+        <v>112.4483795166016</v>
       </c>
       <c r="C463" t="n">
-        <v>114.1263311401144</v>
+        <v>114.1263233968748</v>
       </c>
       <c r="D463" t="n">
-        <v>110.612319041802</v>
+        <v>110.612311536981</v>
       </c>
       <c r="E463" t="n">
-        <v>113.7397876645173</v>
+        <v>113.7397799475038</v>
       </c>
       <c r="F463" t="n">
         <v>434571</v>
@@ -9692,16 +9692,16 @@
         <v>45148</v>
       </c>
       <c r="B464" t="n">
-        <v>110.5156784057617</v>
+        <v>110.5156860351562</v>
       </c>
       <c r="C464" t="n">
-        <v>114.5919317277774</v>
+        <v>114.5919396385741</v>
       </c>
       <c r="D464" t="n">
-        <v>109.2857728839157</v>
+        <v>109.2857804284043</v>
       </c>
       <c r="E464" t="n">
-        <v>111.7455772251619</v>
+        <v>111.7455849394619</v>
       </c>
       <c r="F464" t="n">
         <v>733254</v>
@@ -9712,16 +9712,16 @@
         <v>45149</v>
       </c>
       <c r="B465" t="n">
-        <v>109.8128814697266</v>
+        <v>109.812873840332</v>
       </c>
       <c r="C465" t="n">
-        <v>111.9915719871623</v>
+        <v>111.9915642064004</v>
       </c>
       <c r="D465" t="n">
-        <v>108.1261572189387</v>
+        <v>108.1261497067316</v>
       </c>
       <c r="E465" t="n">
-        <v>110.7353123550508</v>
+        <v>110.7353046615692</v>
       </c>
       <c r="F465" t="n">
         <v>577766</v>
@@ -9732,16 +9732,16 @@
         <v>45152</v>
       </c>
       <c r="B466" t="n">
-        <v>113.0633316040039</v>
+        <v>113.0633239746094</v>
       </c>
       <c r="C466" t="n">
-        <v>113.0633316040039</v>
+        <v>113.0633239746094</v>
       </c>
       <c r="D466" t="n">
-        <v>106.3779233451298</v>
+        <v>106.3779161668596</v>
       </c>
       <c r="E466" t="n">
-        <v>108.9431571578088</v>
+        <v>108.9431498064393</v>
       </c>
       <c r="F466" t="n">
         <v>1213584</v>
@@ -9772,16 +9772,16 @@
         <v>45154</v>
       </c>
       <c r="B468" t="n">
-        <v>108.6444625854492</v>
+        <v>108.6444702148438</v>
       </c>
       <c r="C468" t="n">
-        <v>111.842212915804</v>
+        <v>111.8422207697557</v>
       </c>
       <c r="D468" t="n">
-        <v>107.098302157054</v>
+        <v>107.0983096778717</v>
       </c>
       <c r="E468" t="n">
-        <v>108.2403520164973</v>
+        <v>108.2403596175138</v>
       </c>
       <c r="F468" t="n">
         <v>1047832</v>
@@ -9872,16 +9872,16 @@
         <v>45161</v>
       </c>
       <c r="B473" t="n">
-        <v>117.4294967651367</v>
+        <v>117.4294891357422</v>
       </c>
       <c r="C473" t="n">
-        <v>117.9390301239801</v>
+        <v>117.9390224614812</v>
       </c>
       <c r="D473" t="n">
-        <v>112.9491394178873</v>
+        <v>112.9491320795816</v>
       </c>
       <c r="E473" t="n">
-        <v>114.0296943762679</v>
+        <v>114.0296869677586</v>
       </c>
       <c r="F473" t="n">
         <v>1193312</v>
@@ -9912,16 +9912,16 @@
         <v>45163</v>
       </c>
       <c r="B475" t="n">
-        <v>110.4278259277344</v>
+        <v>110.4278182983398</v>
       </c>
       <c r="C475" t="n">
-        <v>112.7997813791627</v>
+        <v>112.7997735858911</v>
       </c>
       <c r="D475" t="n">
-        <v>108.5917578498233</v>
+        <v>108.5917503472816</v>
       </c>
       <c r="E475" t="n">
-        <v>112.6240834577406</v>
+        <v>112.6240756766079</v>
       </c>
       <c r="F475" t="n">
         <v>1445522</v>
@@ -9952,16 +9952,16 @@
         <v>45167</v>
       </c>
       <c r="B477" t="n">
-        <v>113.3180999755859</v>
+        <v>113.318115234375</v>
       </c>
       <c r="C477" t="n">
-        <v>113.3620143990293</v>
+        <v>113.3620296637317</v>
       </c>
       <c r="D477" t="n">
-        <v>109.4263249492729</v>
+        <v>109.426339684017</v>
       </c>
       <c r="E477" t="n">
-        <v>112.0091257586069</v>
+        <v>112.0091408411367</v>
       </c>
       <c r="F477" t="n">
         <v>768114</v>
@@ -9972,16 +9972,16 @@
         <v>45168</v>
       </c>
       <c r="B478" t="n">
-        <v>112.4483871459961</v>
+        <v>112.4483795166016</v>
       </c>
       <c r="C478" t="n">
-        <v>113.853997347278</v>
+        <v>113.8539896225157</v>
       </c>
       <c r="D478" t="n">
-        <v>110.8231578910159</v>
+        <v>110.8231503718898</v>
       </c>
       <c r="E478" t="n">
-        <v>113.0721301915992</v>
+        <v>113.0721225198849</v>
       </c>
       <c r="F478" t="n">
         <v>547646</v>
@@ -9992,16 +9992,16 @@
         <v>45169</v>
       </c>
       <c r="B479" t="n">
-        <v>110.4102630615234</v>
+        <v>110.4102554321289</v>
       </c>
       <c r="C479" t="n">
-        <v>112.4396029524886</v>
+        <v>112.4395951828659</v>
       </c>
       <c r="D479" t="n">
-        <v>108.8465287124293</v>
+        <v>108.8465211910895</v>
       </c>
       <c r="E479" t="n">
-        <v>111.7455847420302</v>
+        <v>111.7455770203644</v>
       </c>
       <c r="F479" t="n">
         <v>854216</v>
@@ -10092,16 +10092,16 @@
         <v>45177</v>
       </c>
       <c r="B484" t="n">
-        <v>108.5126953125</v>
+        <v>108.5126876831055</v>
       </c>
       <c r="C484" t="n">
-        <v>110.7968086365694</v>
+        <v>110.7968008465816</v>
       </c>
       <c r="D484" t="n">
-        <v>106.7293351683192</v>
+        <v>106.7293276643105</v>
       </c>
       <c r="E484" t="n">
-        <v>109.8128827938557</v>
+        <v>109.8128750730466</v>
       </c>
       <c r="F484" t="n">
         <v>972821</v>
@@ -10112,16 +10112,16 @@
         <v>45180</v>
       </c>
       <c r="B485" t="n">
-        <v>110.2899627685547</v>
+        <v>110.2899703979492</v>
       </c>
       <c r="C485" t="n">
-        <v>111.0096390156284</v>
+        <v>111.0096466948071</v>
       </c>
       <c r="D485" t="n">
-        <v>106.9614755683568</v>
+        <v>106.9614829675006</v>
       </c>
       <c r="E485" t="n">
-        <v>109.7502090149201</v>
+        <v>109.7502166069767</v>
       </c>
       <c r="F485" t="n">
         <v>846938</v>
@@ -10132,16 +10132,16 @@
         <v>45181</v>
       </c>
       <c r="B486" t="n">
-        <v>112.4489974975586</v>
+        <v>112.4489898681641</v>
       </c>
       <c r="C486" t="n">
-        <v>113.6994298006641</v>
+        <v>113.6994220864307</v>
       </c>
       <c r="D486" t="n">
-        <v>109.6602637322876</v>
+        <v>109.6602562921019</v>
       </c>
       <c r="E486" t="n">
-        <v>109.7592193991528</v>
+        <v>109.7592119522533</v>
       </c>
       <c r="F486" t="n">
         <v>550963</v>
@@ -10172,16 +10172,16 @@
         <v>45183</v>
       </c>
       <c r="B488" t="n">
-        <v>112.4759750366211</v>
+        <v>112.4759826660156</v>
       </c>
       <c r="C488" t="n">
-        <v>114.2481721915859</v>
+        <v>114.2481799411909</v>
       </c>
       <c r="D488" t="n">
-        <v>110.6048222228168</v>
+        <v>110.6048297252885</v>
       </c>
       <c r="E488" t="n">
-        <v>114.2481721915859</v>
+        <v>114.2481799411909</v>
       </c>
       <c r="F488" t="n">
         <v>682177</v>
@@ -10192,16 +10192,16 @@
         <v>45184</v>
       </c>
       <c r="B489" t="n">
-        <v>114.455078125</v>
+        <v>114.4550857543945</v>
       </c>
       <c r="C489" t="n">
-        <v>117.9365011778736</v>
+        <v>117.9365090393343</v>
       </c>
       <c r="D489" t="n">
-        <v>111.6573468239327</v>
+        <v>111.6573542668349</v>
       </c>
       <c r="E489" t="n">
-        <v>113.0697058036241</v>
+        <v>113.0697133406719</v>
       </c>
       <c r="F489" t="n">
         <v>1700134</v>
@@ -10272,16 +10272,16 @@
         <v>45190</v>
       </c>
       <c r="B493" t="n">
-        <v>104.118766784668</v>
+        <v>104.1187591552734</v>
       </c>
       <c r="C493" t="n">
-        <v>109.5343139805892</v>
+        <v>109.5343059543656</v>
       </c>
       <c r="D493" t="n">
-        <v>103.6509820066523</v>
+        <v>103.6509744115351</v>
       </c>
       <c r="E493" t="n">
-        <v>109.4353583204306</v>
+        <v>109.4353503014581</v>
       </c>
       <c r="F493" t="n">
         <v>1919322</v>
@@ -10292,16 +10292,16 @@
         <v>45191</v>
       </c>
       <c r="B494" t="n">
-        <v>103.8129043579102</v>
+        <v>103.8129119873047</v>
       </c>
       <c r="C494" t="n">
-        <v>105.8639727468323</v>
+        <v>105.8639805269635</v>
       </c>
       <c r="D494" t="n">
-        <v>103.2011816047806</v>
+        <v>103.2011891892186</v>
       </c>
       <c r="E494" t="n">
-        <v>105.0903231807173</v>
+        <v>105.0903309039916</v>
       </c>
       <c r="F494" t="n">
         <v>394595</v>
@@ -10312,16 +10312,16 @@
         <v>45194</v>
       </c>
       <c r="B495" t="n">
-        <v>103.5250396728516</v>
+        <v>103.525032043457</v>
       </c>
       <c r="C495" t="n">
-        <v>104.2986892721627</v>
+        <v>104.2986815857532</v>
       </c>
       <c r="D495" t="n">
-        <v>102.3825540923923</v>
+        <v>102.3825465471945</v>
       </c>
       <c r="E495" t="n">
-        <v>103.893868790658</v>
+        <v>103.8938611340822</v>
       </c>
       <c r="F495" t="n">
         <v>399935</v>
@@ -10332,16 +10332,16 @@
         <v>45195</v>
       </c>
       <c r="B496" t="n">
-        <v>101.554931640625</v>
+        <v>101.5549240112305</v>
       </c>
       <c r="C496" t="n">
-        <v>103.8129092891401</v>
+        <v>103.8129014901132</v>
       </c>
       <c r="D496" t="n">
-        <v>100.8622488797702</v>
+        <v>100.862241302414</v>
       </c>
       <c r="E496" t="n">
-        <v>101.6538873012245</v>
+        <v>101.6538796643958</v>
       </c>
       <c r="F496" t="n">
         <v>1664293</v>
@@ -10392,16 +10392,16 @@
         <v>45198</v>
       </c>
       <c r="B499" t="n">
-        <v>104.2177200317383</v>
+        <v>104.2177124023438</v>
       </c>
       <c r="C499" t="n">
-        <v>107.0514358836805</v>
+        <v>107.0514280468401</v>
       </c>
       <c r="D499" t="n">
-        <v>103.408085950706</v>
+        <v>103.4080783805818</v>
       </c>
       <c r="E499" t="n">
-        <v>107.0514358836805</v>
+        <v>107.0514280468401</v>
       </c>
       <c r="F499" t="n">
         <v>323662</v>
@@ -10452,16 +10452,16 @@
         <v>45203</v>
       </c>
       <c r="B502" t="n">
-        <v>101.7978134155273</v>
+        <v>101.7978210449219</v>
       </c>
       <c r="C502" t="n">
-        <v>102.1666424919565</v>
+        <v>102.1666501489935</v>
       </c>
       <c r="D502" t="n">
-        <v>98.96409781626373</v>
+        <v>98.96410523328106</v>
       </c>
       <c r="E502" t="n">
-        <v>99.85469179431541</v>
+        <v>99.85469927807969</v>
       </c>
       <c r="F502" t="n">
         <v>483635</v>
@@ -10512,16 +10512,16 @@
         <v>45208</v>
       </c>
       <c r="B505" t="n">
-        <v>100.9611968994141</v>
+        <v>100.9612045288086</v>
       </c>
       <c r="C505" t="n">
-        <v>101.6718684250738</v>
+        <v>101.6718761081721</v>
       </c>
       <c r="D505" t="n">
-        <v>99.18899984705422</v>
+        <v>99.18900734252807</v>
       </c>
       <c r="E505" t="n">
-        <v>101.1051280272665</v>
+        <v>101.1051356675376</v>
       </c>
       <c r="F505" t="n">
         <v>728058</v>
@@ -10592,16 +10592,16 @@
         <v>45215</v>
       </c>
       <c r="B509" t="n">
-        <v>96.91304016113281</v>
+        <v>96.91303253173828</v>
       </c>
       <c r="C509" t="n">
-        <v>98.87415081316534</v>
+        <v>98.87414302938409</v>
       </c>
       <c r="D509" t="n">
-        <v>96.44524852119388</v>
+        <v>96.44524092862584</v>
       </c>
       <c r="E509" t="n">
-        <v>97.20990027736684</v>
+        <v>97.20989262460226</v>
       </c>
       <c r="F509" t="n">
         <v>1010350</v>
@@ -10612,16 +10612,16 @@
         <v>45216</v>
       </c>
       <c r="B510" t="n">
-        <v>97.14692687988281</v>
+        <v>97.14693450927734</v>
       </c>
       <c r="C510" t="n">
-        <v>97.86660314166811</v>
+        <v>97.86661082758212</v>
       </c>
       <c r="D510" t="n">
-        <v>95.20381195440891</v>
+        <v>95.20381943120169</v>
       </c>
       <c r="E510" t="n">
-        <v>96.69713093210238</v>
+        <v>96.69713852617237</v>
       </c>
       <c r="F510" t="n">
         <v>593712</v>
@@ -10652,16 +10652,16 @@
         <v>45218</v>
       </c>
       <c r="B512" t="n">
-        <v>94.34920501708984</v>
+        <v>94.34919738769531</v>
       </c>
       <c r="C512" t="n">
-        <v>95.9954599986059</v>
+        <v>95.99545223608963</v>
       </c>
       <c r="D512" t="n">
-        <v>92.76592806339976</v>
+        <v>92.76592056203434</v>
       </c>
       <c r="E512" t="n">
-        <v>93.46760871431685</v>
+        <v>93.46760115621116</v>
       </c>
       <c r="F512" t="n">
         <v>760940</v>
@@ -10672,16 +10672,16 @@
         <v>45219</v>
       </c>
       <c r="B513" t="n">
-        <v>96.25632476806641</v>
+        <v>96.25634002685547</v>
       </c>
       <c r="C513" t="n">
-        <v>96.4362403867825</v>
+        <v>96.43625567409222</v>
       </c>
       <c r="D513" t="n">
-        <v>93.06277106079887</v>
+        <v>93.06278581333794</v>
       </c>
       <c r="E513" t="n">
-        <v>93.27867803926728</v>
+        <v>93.27869282603245</v>
       </c>
       <c r="F513" t="n">
         <v>605848</v>
@@ -10692,16 +10692,16 @@
         <v>45222</v>
       </c>
       <c r="B514" t="n">
-        <v>96.25632476806641</v>
+        <v>96.25634002685547</v>
       </c>
       <c r="C514" t="n">
-        <v>97.29085673403624</v>
+        <v>97.29087215682185</v>
       </c>
       <c r="D514" t="n">
-        <v>93.93537622458784</v>
+        <v>93.93539111545444</v>
       </c>
       <c r="E514" t="n">
-        <v>96.07640914935031</v>
+        <v>96.0764243796187</v>
       </c>
       <c r="F514" t="n">
         <v>469364</v>
@@ -10712,16 +10712,16 @@
         <v>45223</v>
       </c>
       <c r="B515" t="n">
-        <v>93.51258087158203</v>
+        <v>93.5125732421875</v>
       </c>
       <c r="C515" t="n">
-        <v>98.39736545626356</v>
+        <v>98.39735742833496</v>
       </c>
       <c r="D515" t="n">
-        <v>93.38663854709125</v>
+        <v>93.38663092797195</v>
       </c>
       <c r="E515" t="n">
-        <v>96.71513289484724</v>
+        <v>96.71512500416665</v>
       </c>
       <c r="F515" t="n">
         <v>956700</v>
@@ -10732,16 +10732,16 @@
         <v>45224</v>
       </c>
       <c r="B516" t="n">
-        <v>89.44642639160156</v>
+        <v>89.44641876220703</v>
       </c>
       <c r="C516" t="n">
-        <v>92.42407350084858</v>
+        <v>92.42406561747359</v>
       </c>
       <c r="D516" t="n">
-        <v>87.28740437445002</v>
+        <v>87.28739692921076</v>
       </c>
       <c r="E516" t="n">
-        <v>92.42407350084858</v>
+        <v>92.42406561747359</v>
       </c>
       <c r="F516" t="n">
         <v>1619426</v>
@@ -10752,16 +10752,16 @@
         <v>45225</v>
       </c>
       <c r="B517" t="n">
-        <v>92.35210418701172</v>
+        <v>92.35211181640625</v>
       </c>
       <c r="C517" t="n">
-        <v>92.90084891057617</v>
+        <v>92.90085658530361</v>
       </c>
       <c r="D517" t="n">
-        <v>89.23951029330274</v>
+        <v>89.23951766555959</v>
       </c>
       <c r="E517" t="n">
-        <v>89.23951029330274</v>
+        <v>89.23951766555959</v>
       </c>
       <c r="F517" t="n">
         <v>731795</v>
@@ -10792,16 +10792,16 @@
         <v>45229</v>
       </c>
       <c r="B519" t="n">
-        <v>89.12257385253906</v>
+        <v>89.12256622314453</v>
       </c>
       <c r="C519" t="n">
-        <v>92.43307248972164</v>
+        <v>92.43306457692978</v>
       </c>
       <c r="D519" t="n">
-        <v>88.60980671764069</v>
+        <v>88.60979913214193</v>
       </c>
       <c r="E519" t="n">
-        <v>91.38055155966848</v>
+        <v>91.38054373697832</v>
       </c>
       <c r="F519" t="n">
         <v>688103</v>
@@ -10812,16 +10812,16 @@
         <v>45230</v>
       </c>
       <c r="B520" t="n">
-        <v>91.32656860351562</v>
+        <v>91.32656097412109</v>
       </c>
       <c r="C520" t="n">
-        <v>91.32656860351562</v>
+        <v>91.32656097412109</v>
       </c>
       <c r="D520" t="n">
-        <v>88.72674850648775</v>
+        <v>88.72674109428142</v>
       </c>
       <c r="E520" t="n">
-        <v>89.94120308789761</v>
+        <v>89.94119557423609</v>
       </c>
       <c r="F520" t="n">
         <v>382337</v>
@@ -10852,16 +10852,16 @@
         <v>45233</v>
       </c>
       <c r="B522" t="n">
-        <v>94.61006927490234</v>
+        <v>94.61008453369141</v>
       </c>
       <c r="C522" t="n">
-        <v>97.14691791165838</v>
+        <v>97.14693357959244</v>
       </c>
       <c r="D522" t="n">
-        <v>92.08221847800689</v>
+        <v>92.08223332910212</v>
       </c>
       <c r="E522" t="n">
-        <v>92.70293902491068</v>
+        <v>92.70295397611622</v>
       </c>
       <c r="F522" t="n">
         <v>760712</v>
@@ -10892,16 +10892,16 @@
         <v>45237</v>
       </c>
       <c r="B524" t="n">
-        <v>97.12893676757812</v>
+        <v>97.12894439697266</v>
       </c>
       <c r="C524" t="n">
-        <v>97.12893676757812</v>
+        <v>97.12894439697266</v>
       </c>
       <c r="D524" t="n">
-        <v>91.57845649313083</v>
+        <v>91.57846368653991</v>
       </c>
       <c r="E524" t="n">
-        <v>92.02825243491765</v>
+        <v>92.02825966365781</v>
       </c>
       <c r="F524" t="n">
         <v>722184</v>
@@ -10912,16 +10912,16 @@
         <v>45238</v>
       </c>
       <c r="B525" t="n">
-        <v>96.40927124023438</v>
+        <v>96.40926361083984</v>
       </c>
       <c r="C525" t="n">
-        <v>98.50532220933374</v>
+        <v>98.50531441406719</v>
       </c>
       <c r="D525" t="n">
-        <v>95.54566375953443</v>
+        <v>95.54565619848189</v>
       </c>
       <c r="E525" t="n">
-        <v>97.11095188934421</v>
+        <v>97.11094420442183</v>
       </c>
       <c r="F525" t="n">
         <v>449324</v>
@@ -10932,16 +10932,16 @@
         <v>45239</v>
       </c>
       <c r="B526" t="n">
-        <v>95.28476715087891</v>
+        <v>95.28477478027344</v>
       </c>
       <c r="C526" t="n">
-        <v>97.73165808219684</v>
+        <v>97.73166590751246</v>
       </c>
       <c r="D526" t="n">
-        <v>94.73601557304625</v>
+        <v>94.73602315850255</v>
       </c>
       <c r="E526" t="n">
-        <v>97.2188910019825</v>
+        <v>97.21889878624117</v>
       </c>
       <c r="F526" t="n">
         <v>493995</v>
@@ -10952,16 +10952,16 @@
         <v>45240</v>
       </c>
       <c r="B527" t="n">
-        <v>98.95511627197266</v>
+        <v>98.95510864257812</v>
       </c>
       <c r="C527" t="n">
-        <v>99.84571039668464</v>
+        <v>99.84570269862571</v>
       </c>
       <c r="D527" t="n">
-        <v>95.0418925920676</v>
+        <v>95.04188526438084</v>
       </c>
       <c r="E527" t="n">
-        <v>95.0418925920676</v>
+        <v>95.04188526438084</v>
       </c>
       <c r="F527" t="n">
         <v>655787</v>
@@ -10972,16 +10972,16 @@
         <v>45243</v>
       </c>
       <c r="B528" t="n">
-        <v>98.83815765380859</v>
+        <v>98.83816528320312</v>
       </c>
       <c r="C528" t="n">
-        <v>100.3134877181948</v>
+        <v>100.3134954614712</v>
       </c>
       <c r="D528" t="n">
-        <v>96.80507817938725</v>
+        <v>96.80508565184681</v>
       </c>
       <c r="E528" t="n">
-        <v>98.95510212187712</v>
+        <v>98.9551097602987</v>
       </c>
       <c r="F528" t="n">
         <v>702632</v>
@@ -11052,16 +11052,16 @@
         <v>45250</v>
       </c>
       <c r="B532" t="n">
-        <v>102.5534820556641</v>
+        <v>102.5534744262695</v>
       </c>
       <c r="C532" t="n">
-        <v>104.5685660971273</v>
+        <v>104.5685583178221</v>
       </c>
       <c r="D532" t="n">
-        <v>100.9881939881291</v>
+        <v>100.9881864751831</v>
       </c>
       <c r="E532" t="n">
-        <v>103.6329896477554</v>
+        <v>103.6329819380516</v>
       </c>
       <c r="F532" t="n">
         <v>946377</v>
@@ -11072,16 +11072,16 @@
         <v>45251</v>
       </c>
       <c r="B533" t="n">
-        <v>100.259521484375</v>
+        <v>100.2595138549805</v>
       </c>
       <c r="C533" t="n">
-        <v>103.0932375391752</v>
+        <v>103.0932296941449</v>
       </c>
       <c r="D533" t="n">
-        <v>99.13503153114809</v>
+        <v>99.13502398732325</v>
       </c>
       <c r="E533" t="n">
-        <v>102.5804703950374</v>
+        <v>102.5804625890269</v>
       </c>
       <c r="F533" t="n">
         <v>1091156</v>
@@ -11092,16 +11092,16 @@
         <v>45252</v>
       </c>
       <c r="B534" t="n">
-        <v>102.940299987793</v>
+        <v>102.9403076171875</v>
       </c>
       <c r="C534" t="n">
-        <v>103.5700115638693</v>
+        <v>103.5700192399348</v>
       </c>
       <c r="D534" t="n">
-        <v>100.277508823705</v>
+        <v>100.2775162557474</v>
       </c>
       <c r="E534" t="n">
-        <v>100.3044954822023</v>
+        <v>100.3045029162449</v>
       </c>
       <c r="F534" t="n">
         <v>622704</v>
@@ -11112,16 +11112,16 @@
         <v>45253</v>
       </c>
       <c r="B535" t="n">
-        <v>103.4440689086914</v>
+        <v>103.4440765380859</v>
       </c>
       <c r="C535" t="n">
-        <v>104.5955454230704</v>
+        <v>104.5955531373908</v>
       </c>
       <c r="D535" t="n">
-        <v>101.9327542677336</v>
+        <v>101.9327617856629</v>
       </c>
       <c r="E535" t="n">
-        <v>102.8683306515019</v>
+        <v>102.8683382384335</v>
       </c>
       <c r="F535" t="n">
         <v>270469</v>
@@ -11132,16 +11132,16 @@
         <v>45254</v>
       </c>
       <c r="B536" t="n">
-        <v>103.5430221557617</v>
+        <v>103.5430297851562</v>
       </c>
       <c r="C536" t="n">
-        <v>104.3526562058894</v>
+        <v>104.3526638949405</v>
       </c>
       <c r="D536" t="n">
-        <v>100.9522000586942</v>
+        <v>100.9522074971883</v>
       </c>
       <c r="E536" t="n">
-        <v>103.2731487146133</v>
+        <v>103.2731563241227</v>
       </c>
       <c r="F536" t="n">
         <v>447021</v>
@@ -11172,16 +11172,16 @@
         <v>45258</v>
       </c>
       <c r="B538" t="n">
-        <v>102.9852828979492</v>
+        <v>102.9852905273438</v>
       </c>
       <c r="C538" t="n">
-        <v>105.4501627622543</v>
+        <v>105.450170574253</v>
       </c>
       <c r="D538" t="n">
-        <v>101.8337995100664</v>
+        <v>101.8338070541564</v>
       </c>
       <c r="E538" t="n">
-        <v>102.0946819825549</v>
+        <v>102.0946895459716</v>
       </c>
       <c r="F538" t="n">
         <v>492581</v>
@@ -11212,16 +11212,16 @@
         <v>45260</v>
       </c>
       <c r="B540" t="n">
-        <v>103.2731475830078</v>
+        <v>103.2731552124023</v>
       </c>
       <c r="C540" t="n">
-        <v>103.5250322039895</v>
+        <v>103.5250398519922</v>
       </c>
       <c r="D540" t="n">
-        <v>101.231070230987</v>
+        <v>101.2310777095213</v>
       </c>
       <c r="E540" t="n">
-        <v>102.6434291672124</v>
+        <v>102.643436750086</v>
       </c>
       <c r="F540" t="n">
         <v>702061</v>
@@ -11272,16 +11272,16 @@
         <v>45265</v>
       </c>
       <c r="B543" t="n">
-        <v>106.1338577270508</v>
+        <v>106.1338500976562</v>
       </c>
       <c r="C543" t="n">
-        <v>107.825088065618</v>
+        <v>107.82508031465</v>
       </c>
       <c r="D543" t="n">
-        <v>103.021263644533</v>
+        <v>103.0212562388862</v>
       </c>
       <c r="E543" t="n">
-        <v>103.426084126483</v>
+        <v>103.4260766917358</v>
       </c>
       <c r="F543" t="n">
         <v>1056803</v>
@@ -11292,16 +11292,16 @@
         <v>45266</v>
       </c>
       <c r="B544" t="n">
-        <v>104.0737838745117</v>
+        <v>104.0737915039062</v>
       </c>
       <c r="C544" t="n">
-        <v>106.4217191645265</v>
+        <v>106.4217269660424</v>
       </c>
       <c r="D544" t="n">
-        <v>102.9043117179754</v>
+        <v>102.9043192616387</v>
       </c>
       <c r="E544" t="n">
-        <v>106.1608367030425</v>
+        <v>106.1608444854338</v>
       </c>
       <c r="F544" t="n">
         <v>811001</v>
@@ -11312,16 +11312,16 @@
         <v>45267</v>
       </c>
       <c r="B545" t="n">
-        <v>106.6016464233398</v>
+        <v>106.6016387939453</v>
       </c>
       <c r="C545" t="n">
-        <v>107.0514423998096</v>
+        <v>107.0514347382236</v>
       </c>
       <c r="D545" t="n">
-        <v>103.6959613954746</v>
+        <v>103.6959539740376</v>
       </c>
       <c r="E545" t="n">
-        <v>105.4231831612584</v>
+        <v>105.4231756162056</v>
       </c>
       <c r="F545" t="n">
         <v>599154</v>
@@ -11332,16 +11332,16 @@
         <v>45268</v>
       </c>
       <c r="B546" t="n">
-        <v>105.4321670532227</v>
+        <v>105.4321594238281</v>
       </c>
       <c r="C546" t="n">
-        <v>108.7156788334399</v>
+        <v>108.7156709664404</v>
       </c>
       <c r="D546" t="n">
-        <v>105.2522514200634</v>
+        <v>105.2522438036881</v>
       </c>
       <c r="E546" t="n">
-        <v>106.9614773884421</v>
+        <v>106.961469648382</v>
       </c>
       <c r="F546" t="n">
         <v>678575</v>
@@ -11352,16 +11352,16 @@
         <v>45271</v>
       </c>
       <c r="B547" t="n">
-        <v>103.1921844482422</v>
+        <v>103.1921920776367</v>
       </c>
       <c r="C547" t="n">
-        <v>106.4127250482224</v>
+        <v>106.4127329157239</v>
       </c>
       <c r="D547" t="n">
-        <v>103.1921844482422</v>
+        <v>103.1921920776367</v>
       </c>
       <c r="E547" t="n">
-        <v>105.3781930063656</v>
+        <v>105.3782007973801</v>
       </c>
       <c r="F547" t="n">
         <v>558243</v>
@@ -11452,16 +11452,16 @@
         <v>45278</v>
       </c>
       <c r="B552" t="n">
-        <v>118.341552734375</v>
+        <v>118.3415603637695</v>
       </c>
       <c r="C552" t="n">
-        <v>120.6714417856362</v>
+        <v>120.671449565237</v>
       </c>
       <c r="D552" t="n">
-        <v>114.5543313282876</v>
+        <v>114.5543387135227</v>
       </c>
       <c r="E552" t="n">
-        <v>114.8049535144115</v>
+        <v>114.804960915804</v>
       </c>
       <c r="F552" t="n">
         <v>1013443</v>
@@ -11632,16 +11632,16 @@
         <v>45294</v>
       </c>
       <c r="B561" t="n">
-        <v>113.2455062866211</v>
+        <v>113.2455139160156</v>
       </c>
       <c r="C561" t="n">
-        <v>116.2437305936984</v>
+        <v>116.2437384250845</v>
       </c>
       <c r="D561" t="n">
-        <v>113.2455062866211</v>
+        <v>113.2455139160156</v>
       </c>
       <c r="E561" t="n">
-        <v>115.7517564618344</v>
+        <v>115.7517642600759</v>
       </c>
       <c r="F561" t="n">
         <v>798887</v>
@@ -11672,16 +11672,16 @@
         <v>45296</v>
       </c>
       <c r="B563" t="n">
-        <v>115.6310882568359</v>
+        <v>115.6310958862305</v>
       </c>
       <c r="C563" t="n">
-        <v>115.6310882568359</v>
+        <v>115.6310958862305</v>
       </c>
       <c r="D563" t="n">
-        <v>109.7181850571025</v>
+        <v>109.7181922963609</v>
       </c>
       <c r="E563" t="n">
-        <v>110.1823059872627</v>
+        <v>110.182313257144</v>
       </c>
       <c r="F563" t="n">
         <v>1732820</v>
@@ -11712,16 +11712,16 @@
         <v>45300</v>
       </c>
       <c r="B565" t="n">
-        <v>114.0345153808594</v>
+        <v>114.0345077514648</v>
       </c>
       <c r="C565" t="n">
-        <v>117.7938978882632</v>
+        <v>117.79389000735</v>
       </c>
       <c r="D565" t="n">
-        <v>113.3847488871488</v>
+        <v>113.3847413012264</v>
       </c>
       <c r="E565" t="n">
-        <v>117.7938978882632</v>
+        <v>117.79389000735</v>
       </c>
       <c r="F565" t="n">
         <v>842892</v>
@@ -11772,16 +11772,16 @@
         <v>45303</v>
       </c>
       <c r="B568" t="n">
-        <v>116.6800003051758</v>
+        <v>116.6800079345703</v>
       </c>
       <c r="C568" t="n">
-        <v>117.7010720284054</v>
+        <v>117.7010797245651</v>
       </c>
       <c r="D568" t="n">
-        <v>112.8649256503406</v>
+        <v>112.8649330302776</v>
       </c>
       <c r="E568" t="n">
-        <v>114.6378710225635</v>
+        <v>114.6378785184286</v>
       </c>
       <c r="F568" t="n">
         <v>693991</v>
@@ -11792,16 +11792,16 @@
         <v>45306</v>
       </c>
       <c r="B569" t="n">
-        <v>118.2580261230469</v>
+        <v>118.2580108642578</v>
       </c>
       <c r="C569" t="n">
-        <v>120.5786239215518</v>
+        <v>120.5786083633369</v>
       </c>
       <c r="D569" t="n">
-        <v>115.6589458241968</v>
+        <v>115.6589309007661</v>
       </c>
       <c r="E569" t="n">
-        <v>116.6707332346643</v>
+        <v>116.6707181806831</v>
       </c>
       <c r="F569" t="n">
         <v>875695</v>
@@ -11832,16 +11832,16 @@
         <v>45308</v>
       </c>
       <c r="B571" t="n">
-        <v>115.8167343139648</v>
+        <v>115.8167419433594</v>
       </c>
       <c r="C571" t="n">
-        <v>117.2926425610734</v>
+        <v>117.292650287693</v>
       </c>
       <c r="D571" t="n">
-        <v>114.0530804370092</v>
+        <v>114.0530879502235</v>
       </c>
       <c r="E571" t="n">
-        <v>116.568615039894</v>
+        <v>116.5686227188185</v>
       </c>
       <c r="F571" t="n">
         <v>474098</v>
@@ -11892,16 +11892,16 @@
         <v>45313</v>
       </c>
       <c r="B574" t="n">
-        <v>116.9677658081055</v>
+        <v>116.9677581787109</v>
       </c>
       <c r="C574" t="n">
-        <v>118.313713753421</v>
+        <v>118.313706036235</v>
       </c>
       <c r="D574" t="n">
-        <v>114.8792214972839</v>
+        <v>114.8792140041177</v>
       </c>
       <c r="E574" t="n">
-        <v>115.7332023602692</v>
+        <v>115.7331948114009</v>
       </c>
       <c r="F574" t="n">
         <v>856226</v>
@@ -11912,16 +11912,16 @@
         <v>45314</v>
       </c>
       <c r="B575" t="n">
-        <v>115.8445816040039</v>
+        <v>115.844596862793</v>
       </c>
       <c r="C575" t="n">
-        <v>119.5111339486896</v>
+        <v>119.5111496904288</v>
       </c>
       <c r="D575" t="n">
-        <v>115.3526074921376</v>
+        <v>115.352622686125</v>
       </c>
       <c r="E575" t="n">
-        <v>117.0605761181597</v>
+        <v>117.0605915371168</v>
       </c>
       <c r="F575" t="n">
         <v>383026</v>
@@ -11992,16 +11992,16 @@
         <v>45320</v>
       </c>
       <c r="B579" t="n">
-        <v>120.5507736206055</v>
+        <v>120.5507659912109</v>
       </c>
       <c r="C579" t="n">
-        <v>120.9963399401855</v>
+        <v>120.9963322825921</v>
       </c>
       <c r="D579" t="n">
-        <v>115.6682262202838</v>
+        <v>115.668218899895</v>
       </c>
       <c r="E579" t="n">
-        <v>116.9213513959265</v>
+        <v>116.9213439962301</v>
       </c>
       <c r="F579" t="n">
         <v>917694</v>
@@ -12032,16 +12032,16 @@
         <v>45322</v>
       </c>
       <c r="B581" t="n">
-        <v>112.7256927490234</v>
+        <v>112.725700378418</v>
       </c>
       <c r="C581" t="n">
-        <v>117.5618319470799</v>
+        <v>117.5618399037895</v>
       </c>
       <c r="D581" t="n">
-        <v>112.252287421666</v>
+        <v>112.25229501902</v>
       </c>
       <c r="E581" t="n">
-        <v>115.1205513444103</v>
+        <v>115.1205591358914</v>
       </c>
       <c r="F581" t="n">
         <v>967870</v>
@@ -12072,16 +12072,16 @@
         <v>45324</v>
       </c>
       <c r="B583" t="n">
-        <v>119.7431945800781</v>
+        <v>119.7432022094727</v>
       </c>
       <c r="C583" t="n">
-        <v>120.7642662459118</v>
+        <v>120.7642739403636</v>
       </c>
       <c r="D583" t="n">
-        <v>114.2758508359602</v>
+        <v>114.2758581170049</v>
       </c>
       <c r="E583" t="n">
-        <v>114.7492561463083</v>
+        <v>114.7492634575158</v>
       </c>
       <c r="F583" t="n">
         <v>1061152</v>
@@ -12112,16 +12112,16 @@
         <v>45328</v>
       </c>
       <c r="B585" t="n">
-        <v>115.9374084472656</v>
+        <v>115.9374160766602</v>
       </c>
       <c r="C585" t="n">
-        <v>119.5946765194815</v>
+        <v>119.5946843895468</v>
       </c>
       <c r="D585" t="n">
-        <v>115.1205510870751</v>
+        <v>115.1205586627154</v>
       </c>
       <c r="E585" t="n">
-        <v>117.8867149153073</v>
+        <v>117.8867226729782</v>
       </c>
       <c r="F585" t="n">
         <v>714734</v>
@@ -12132,16 +12132,16 @@
         <v>45329</v>
       </c>
       <c r="B586" t="n">
-        <v>114.9070587158203</v>
+        <v>114.9070663452148</v>
       </c>
       <c r="C586" t="n">
-        <v>116.3179832026201</v>
+        <v>116.3179909256947</v>
       </c>
       <c r="D586" t="n">
-        <v>111.8160116757133</v>
+        <v>111.816019099874</v>
       </c>
       <c r="E586" t="n">
-        <v>115.1019886532248</v>
+        <v>115.101996295562</v>
       </c>
       <c r="F586" t="n">
         <v>998662</v>
@@ -12152,16 +12152,16 @@
         <v>45330</v>
       </c>
       <c r="B587" t="n">
-        <v>114.4058151245117</v>
+        <v>114.4058074951172</v>
       </c>
       <c r="C587" t="n">
-        <v>115.436164208617</v>
+        <v>115.4361565105115</v>
       </c>
       <c r="D587" t="n">
-        <v>113.0412983870791</v>
+        <v>113.0412908486803</v>
       </c>
       <c r="E587" t="n">
-        <v>115.1019965552897</v>
+        <v>115.1019888794688</v>
       </c>
       <c r="F587" t="n">
         <v>662990</v>
@@ -12172,16 +12172,16 @@
         <v>45331</v>
       </c>
       <c r="B588" t="n">
-        <v>114.2201614379883</v>
+        <v>114.2201690673828</v>
       </c>
       <c r="C588" t="n">
-        <v>115.8445846607362</v>
+        <v>115.8445923986349</v>
       </c>
       <c r="D588" t="n">
-        <v>113.561103498381</v>
+        <v>113.5611110837534</v>
       </c>
       <c r="E588" t="n">
-        <v>114.9070584178118</v>
+        <v>114.9070660930879</v>
       </c>
       <c r="F588" t="n">
         <v>354486</v>
@@ -12212,16 +12212,16 @@
         <v>45337</v>
       </c>
       <c r="B590" t="n">
-        <v>115.7517623901367</v>
+        <v>115.7517547607422</v>
       </c>
       <c r="C590" t="n">
-        <v>116.4015359709352</v>
+        <v>116.4015282987129</v>
       </c>
       <c r="D590" t="n">
-        <v>114.4986372383505</v>
+        <v>114.4986296915515</v>
       </c>
       <c r="E590" t="n">
-        <v>115.6589396162866</v>
+        <v>115.6589319930101</v>
       </c>
       <c r="F590" t="n">
         <v>464925</v>
@@ -12352,16 +12352,16 @@
         <v>45348</v>
       </c>
       <c r="B597" t="n">
-        <v>111.2776260375977</v>
+        <v>111.2776336669922</v>
       </c>
       <c r="C597" t="n">
-        <v>113.0227251791686</v>
+        <v>113.0227329282103</v>
       </c>
       <c r="D597" t="n">
-        <v>110.5164680339092</v>
+        <v>110.5164756111173</v>
       </c>
       <c r="E597" t="n">
-        <v>111.6674929814756</v>
+        <v>111.6675006376001</v>
       </c>
       <c r="F597" t="n">
         <v>306480</v>
@@ -12372,16 +12372,16 @@
         <v>45349</v>
       </c>
       <c r="B598" t="n">
-        <v>112.976318359375</v>
+        <v>112.9763259887695</v>
       </c>
       <c r="C598" t="n">
-        <v>113.941690764358</v>
+        <v>113.941698458945</v>
       </c>
       <c r="D598" t="n">
-        <v>107.7039041979591</v>
+        <v>107.7039114713027</v>
       </c>
       <c r="E598" t="n">
-        <v>111.8717082560142</v>
+        <v>111.8717158108134</v>
       </c>
       <c r="F598" t="n">
         <v>631455</v>
@@ -12392,16 +12392,16 @@
         <v>45350</v>
       </c>
       <c r="B599" t="n">
-        <v>110.507194519043</v>
+        <v>110.5072021484375</v>
       </c>
       <c r="C599" t="n">
-        <v>112.8556452546146</v>
+        <v>112.8556530461457</v>
       </c>
       <c r="D599" t="n">
-        <v>103.0348448313849</v>
+        <v>103.03485194489</v>
       </c>
       <c r="E599" t="n">
-        <v>112.8556452546146</v>
+        <v>112.8556530461457</v>
       </c>
       <c r="F599" t="n">
         <v>1284448</v>
@@ -12512,16 +12512,16 @@
         <v>45358</v>
       </c>
       <c r="B605" t="n">
-        <v>114.6378707885742</v>
+        <v>114.6378784179688</v>
       </c>
       <c r="C605" t="n">
-        <v>115.4640054851931</v>
+        <v>115.4640131695686</v>
       </c>
       <c r="D605" t="n">
-        <v>111.853145182374</v>
+        <v>111.8531526264392</v>
       </c>
       <c r="E605" t="n">
-        <v>114.5543324197115</v>
+        <v>114.5543400435463</v>
       </c>
       <c r="F605" t="n">
         <v>408472</v>
@@ -12552,16 +12552,16 @@
         <v>45362</v>
       </c>
       <c r="B607" t="n">
-        <v>116.9120559692383</v>
+        <v>116.9120635986328</v>
       </c>
       <c r="C607" t="n">
-        <v>117.9052744467247</v>
+        <v>117.9052821409343</v>
       </c>
       <c r="D607" t="n">
-        <v>116.1044901074035</v>
+        <v>116.1044976840983</v>
       </c>
       <c r="E607" t="n">
-        <v>116.1230518280071</v>
+        <v>116.1230594059132</v>
       </c>
       <c r="F607" t="n">
         <v>387232</v>
@@ -12572,16 +12572,16 @@
         <v>45363</v>
       </c>
       <c r="B608" t="n">
-        <v>118.4715118408203</v>
+        <v>118.4715042114258</v>
       </c>
       <c r="C608" t="n">
-        <v>119.4368842723006</v>
+        <v>119.4368765807375</v>
       </c>
       <c r="D608" t="n">
-        <v>117.3854705111263</v>
+        <v>117.3854629516713</v>
       </c>
       <c r="E608" t="n">
-        <v>117.5154238113329</v>
+        <v>117.5154162435091</v>
       </c>
       <c r="F608" t="n">
         <v>411262</v>
@@ -12652,16 +12652,16 @@
         <v>45369</v>
       </c>
       <c r="B612" t="n">
-        <v>117.8867263793945</v>
+        <v>117.88671875</v>
       </c>
       <c r="C612" t="n">
-        <v>119.5946881496622</v>
+        <v>119.5946804097318</v>
       </c>
       <c r="D612" t="n">
-        <v>116.3644101643563</v>
+        <v>116.364402633483</v>
       </c>
       <c r="E612" t="n">
-        <v>118.8799520538364</v>
+        <v>118.8799443601623</v>
       </c>
       <c r="F612" t="n">
         <v>649560</v>
@@ -12692,16 +12692,16 @@
         <v>45371</v>
       </c>
       <c r="B614" t="n">
-        <v>118.1744766235352</v>
+        <v>118.1744689941406</v>
       </c>
       <c r="C614" t="n">
-        <v>119.5854083084638</v>
+        <v>119.5854005879789</v>
       </c>
       <c r="D614" t="n">
-        <v>115.1019981331325</v>
+        <v>115.1019907020985</v>
       </c>
       <c r="E614" t="n">
-        <v>115.9374172779029</v>
+        <v>115.9374097929339</v>
       </c>
       <c r="F614" t="n">
         <v>596704</v>
@@ -12792,16 +12792,16 @@
         <v>45378</v>
       </c>
       <c r="B619" t="n">
-        <v>116.8099594116211</v>
+        <v>116.8099517822266</v>
       </c>
       <c r="C619" t="n">
-        <v>118.6571659250514</v>
+        <v>118.6571581750073</v>
       </c>
       <c r="D619" t="n">
-        <v>116.7821132872247</v>
+        <v>116.7821056596489</v>
       </c>
       <c r="E619" t="n">
-        <v>116.9399197953439</v>
+        <v>116.9399121574611</v>
       </c>
       <c r="F619" t="n">
         <v>350637</v>
@@ -12812,16 +12812,16 @@
         <v>45379</v>
       </c>
       <c r="B620" t="n">
-        <v>118.9077835083008</v>
+        <v>118.9077911376953</v>
       </c>
       <c r="C620" t="n">
-        <v>120.5693301438005</v>
+        <v>120.5693378798037</v>
       </c>
       <c r="D620" t="n">
-        <v>116.5964562638948</v>
+        <v>116.5964637449893</v>
       </c>
       <c r="E620" t="n">
-        <v>117.0698615778232</v>
+        <v>117.0698690892924</v>
       </c>
       <c r="F620" t="n">
         <v>712173</v>
@@ -12992,16 +12992,16 @@
         <v>45393</v>
       </c>
       <c r="B629" t="n">
-        <v>113.9509811401367</v>
+        <v>113.9509735107422</v>
       </c>
       <c r="C629" t="n">
-        <v>114.4522326314215</v>
+        <v>114.4522249684666</v>
       </c>
       <c r="D629" t="n">
-        <v>112.3915344167808</v>
+        <v>112.3915268917964</v>
       </c>
       <c r="E629" t="n">
-        <v>114.025235112164</v>
+        <v>114.025227477798</v>
       </c>
       <c r="F629" t="n">
         <v>445667</v>
@@ -13132,16 +13132,16 @@
         <v>45404</v>
       </c>
       <c r="B636" t="n">
-        <v>100.9462966918945</v>
+        <v>100.9463043212891</v>
       </c>
       <c r="C636" t="n">
-        <v>102.5243049338492</v>
+        <v>102.5243126825076</v>
       </c>
       <c r="D636" t="n">
-        <v>100.4357608643617</v>
+        <v>100.4357684551706</v>
       </c>
       <c r="E636" t="n">
-        <v>101.1783571440598</v>
+        <v>101.1783647909932</v>
       </c>
       <c r="F636" t="n">
         <v>363945</v>
@@ -13232,16 +13232,16 @@
         <v>45412</v>
       </c>
       <c r="B641" t="n">
-        <v>98.4678955078125</v>
+        <v>98.46790313720703</v>
       </c>
       <c r="C641" t="n">
-        <v>100.4821785891058</v>
+        <v>100.482186374569</v>
       </c>
       <c r="D641" t="n">
-        <v>96.76921125094019</v>
+        <v>96.7692187487189</v>
       </c>
       <c r="E641" t="n">
-        <v>99.31259189464512</v>
+        <v>99.3125995894876</v>
       </c>
       <c r="F641" t="n">
         <v>1108924</v>
@@ -13392,16 +13392,16 @@
         <v>45425</v>
       </c>
       <c r="B649" t="n">
-        <v>103.5732345581055</v>
+        <v>103.5732269287109</v>
       </c>
       <c r="C649" t="n">
-        <v>105.0955507318979</v>
+        <v>105.0955429903668</v>
       </c>
       <c r="D649" t="n">
-        <v>102.8027920691221</v>
+        <v>102.8027844964798</v>
       </c>
       <c r="E649" t="n">
-        <v>102.8027920691221</v>
+        <v>102.8027844964798</v>
       </c>
       <c r="F649" t="n">
         <v>135742</v>
@@ -13452,16 +13452,16 @@
         <v>45428</v>
       </c>
       <c r="B652" t="n">
-        <v>104.6407012939453</v>
+        <v>104.6407089233398</v>
       </c>
       <c r="C652" t="n">
-        <v>104.9377383868498</v>
+        <v>104.9377460379014</v>
       </c>
       <c r="D652" t="n">
-        <v>103.322592554879</v>
+        <v>103.3226000881697</v>
       </c>
       <c r="E652" t="n">
-        <v>104.1487271908296</v>
+        <v>104.1487347843541</v>
       </c>
       <c r="F652" t="n">
         <v>283646</v>
@@ -13492,16 +13492,16 @@
         <v>45432</v>
       </c>
       <c r="B654" t="n">
-        <v>102.5243072509766</v>
+        <v>102.5243148803711</v>
       </c>
       <c r="C654" t="n">
-        <v>103.3504419128024</v>
+        <v>103.3504496036741</v>
       </c>
       <c r="D654" t="n">
-        <v>101.2340516743307</v>
+        <v>101.2340592077103</v>
       </c>
       <c r="E654" t="n">
-        <v>103.0162813695012</v>
+        <v>103.0162890355063</v>
       </c>
       <c r="F654" t="n">
         <v>409635</v>
@@ -13552,16 +13552,16 @@
         <v>45435</v>
       </c>
       <c r="B657" t="n">
-        <v>88.36862182617188</v>
+        <v>88.36862945556641</v>
       </c>
       <c r="C657" t="n">
-        <v>90.96770185479242</v>
+        <v>90.96770970858115</v>
       </c>
       <c r="D657" t="n">
-        <v>87.70957095848325</v>
+        <v>87.70957853097796</v>
       </c>
       <c r="E657" t="n">
-        <v>88.18297628780898</v>
+        <v>88.18298390117562</v>
       </c>
       <c r="F657" t="n">
         <v>1960163</v>
@@ -13572,16 +13572,16 @@
         <v>45436</v>
       </c>
       <c r="B658" t="n">
-        <v>90.03946685791016</v>
+        <v>90.03945922851562</v>
       </c>
       <c r="C658" t="n">
-        <v>91.06053156053261</v>
+        <v>91.0605238446193</v>
       </c>
       <c r="D658" t="n">
-        <v>88.15513688048645</v>
+        <v>88.15512941075855</v>
       </c>
       <c r="E658" t="n">
-        <v>89.29687048404443</v>
+        <v>89.29686291757299</v>
       </c>
       <c r="F658" t="n">
         <v>574555</v>
@@ -13592,16 +13592,16 @@
         <v>45439</v>
       </c>
       <c r="B659" t="n">
-        <v>90.40147399902344</v>
+        <v>90.40148162841797</v>
       </c>
       <c r="C659" t="n">
-        <v>90.78205656018962</v>
+        <v>90.78206422170325</v>
       </c>
       <c r="D659" t="n">
-        <v>89.20404115217451</v>
+        <v>89.2040486805122</v>
       </c>
       <c r="E659" t="n">
-        <v>90.08587516657443</v>
+        <v>90.08588276933413</v>
       </c>
       <c r="F659" t="n">
         <v>176378</v>
@@ -13612,16 +13612,16 @@
         <v>45440</v>
       </c>
       <c r="B660" t="n">
-        <v>90.68922424316406</v>
+        <v>90.68923187255859</v>
       </c>
       <c r="C660" t="n">
-        <v>92.44360074082222</v>
+        <v>92.44360851780684</v>
       </c>
       <c r="D660" t="n">
-        <v>90.07658831603928</v>
+        <v>90.07659589389471</v>
       </c>
       <c r="E660" t="n">
-        <v>90.96769962580825</v>
+        <v>90.96770727863003</v>
       </c>
       <c r="F660" t="n">
         <v>449350</v>
@@ -13632,16 +13632,16 @@
         <v>45441</v>
       </c>
       <c r="B661" t="n">
-        <v>88.13656616210938</v>
+        <v>88.13655853271484</v>
       </c>
       <c r="C661" t="n">
-        <v>90.68923140419381</v>
+        <v>90.68922355383208</v>
       </c>
       <c r="D661" t="n">
-        <v>87.62603736284672</v>
+        <v>87.62602977764526</v>
       </c>
       <c r="E661" t="n">
-        <v>90.68923140419381</v>
+        <v>90.68922355383208</v>
       </c>
       <c r="F661" t="n">
         <v>430434</v>
@@ -13672,16 +13672,16 @@
         <v>45446</v>
       </c>
       <c r="B663" t="n">
-        <v>92.43431854248047</v>
+        <v>92.434326171875</v>
       </c>
       <c r="C663" t="n">
-        <v>93.60389809123609</v>
+        <v>93.60390581716601</v>
       </c>
       <c r="D663" t="n">
-        <v>90.53142005267401</v>
+        <v>90.53142752500605</v>
       </c>
       <c r="E663" t="n">
-        <v>92.64781018690546</v>
+        <v>92.64781783392128</v>
       </c>
       <c r="F663" t="n">
         <v>373105</v>
@@ -13712,16 +13712,16 @@
         <v>45448</v>
       </c>
       <c r="B665" t="n">
-        <v>92.92630004882812</v>
+        <v>92.92629241943359</v>
       </c>
       <c r="C665" t="n">
-        <v>93.79884972802287</v>
+        <v>93.79884202699066</v>
       </c>
       <c r="D665" t="n">
-        <v>92.39720243274542</v>
+        <v>92.39719484679063</v>
       </c>
       <c r="E665" t="n">
-        <v>93.18620665575664</v>
+        <v>93.18619900502337</v>
       </c>
       <c r="F665" t="n">
         <v>402887</v>
@@ -13792,16 +13792,16 @@
         <v>45454</v>
       </c>
       <c r="B669" t="n">
-        <v>92.84275054931641</v>
+        <v>92.84275817871094</v>
       </c>
       <c r="C669" t="n">
-        <v>93.01911877430439</v>
+        <v>93.01912641819206</v>
       </c>
       <c r="D669" t="n">
-        <v>91.69173259079281</v>
+        <v>91.69174012560192</v>
       </c>
       <c r="E669" t="n">
-        <v>92.5271517066259</v>
+        <v>92.52715931008595</v>
       </c>
       <c r="F669" t="n">
         <v>406022</v>
@@ -13812,16 +13812,16 @@
         <v>45455</v>
       </c>
       <c r="B670" t="n">
-        <v>90.15085601806641</v>
+        <v>90.15084838867188</v>
       </c>
       <c r="C670" t="n">
-        <v>93.86382362385611</v>
+        <v>93.8638156802361</v>
       </c>
       <c r="D670" t="n">
-        <v>90.1415716161133</v>
+        <v>90.1415639875045</v>
       </c>
       <c r="E670" t="n">
-        <v>93.15835779581742</v>
+        <v>93.15834991190043</v>
       </c>
       <c r="F670" t="n">
         <v>421382</v>
@@ -13872,16 +13872,16 @@
         <v>45460</v>
       </c>
       <c r="B673" t="n">
-        <v>85.58390045166016</v>
+        <v>85.58389282226562</v>
       </c>
       <c r="C673" t="n">
-        <v>86.70707938412349</v>
+        <v>86.70707165460294</v>
       </c>
       <c r="D673" t="n">
-        <v>83.36540287450703</v>
+        <v>83.36539544288092</v>
       </c>
       <c r="E673" t="n">
-        <v>85.12906390304379</v>
+        <v>85.12905631419575</v>
       </c>
       <c r="F673" t="n">
         <v>650145</v>
@@ -13892,16 +13892,16 @@
         <v>45461</v>
       </c>
       <c r="B674" t="n">
-        <v>87.54248046875</v>
+        <v>87.54249572753906</v>
       </c>
       <c r="C674" t="n">
-        <v>87.54248046875</v>
+        <v>87.54249572753906</v>
       </c>
       <c r="D674" t="n">
-        <v>84.9712538405923</v>
+        <v>84.97126865121261</v>
       </c>
       <c r="E674" t="n">
-        <v>85.57461241716906</v>
+        <v>85.5746273329557</v>
       </c>
       <c r="F674" t="n">
         <v>348422</v>
@@ -13952,16 +13952,16 @@
         <v>45464</v>
       </c>
       <c r="B677" t="n">
-        <v>88.75849151611328</v>
+        <v>88.75848388671875</v>
       </c>
       <c r="C677" t="n">
-        <v>91.33900282106455</v>
+        <v>91.33899496985757</v>
       </c>
       <c r="D677" t="n">
-        <v>86.98554611797962</v>
+        <v>86.98553864098177</v>
       </c>
       <c r="E677" t="n">
-        <v>91.33900282106455</v>
+        <v>91.33899496985757</v>
       </c>
       <c r="F677" t="n">
         <v>813524</v>
@@ -13972,16 +13972,16 @@
         <v>45467</v>
       </c>
       <c r="B678" t="n">
-        <v>89.74241638183594</v>
+        <v>89.74242401123047</v>
       </c>
       <c r="C678" t="n">
-        <v>90.60568152828682</v>
+        <v>90.6056892310713</v>
       </c>
       <c r="D678" t="n">
-        <v>88.23866213520195</v>
+        <v>88.23866963675577</v>
       </c>
       <c r="E678" t="n">
-        <v>88.92556615757213</v>
+        <v>88.92557371752265</v>
       </c>
       <c r="F678" t="n">
         <v>235914</v>
@@ -13992,16 +13992,16 @@
         <v>45468</v>
       </c>
       <c r="B679" t="n">
-        <v>90.97698211669922</v>
+        <v>90.97698974609375</v>
       </c>
       <c r="C679" t="n">
-        <v>90.97698211669922</v>
+        <v>90.97698974609375</v>
       </c>
       <c r="D679" t="n">
-        <v>89.11121408877702</v>
+        <v>89.1112215617069</v>
       </c>
       <c r="E679" t="n">
-        <v>90.03017150112908</v>
+        <v>90.0301790511234</v>
       </c>
       <c r="F679" t="n">
         <v>300759</v>
@@ -14032,16 +14032,16 @@
         <v>45470</v>
       </c>
       <c r="B681" t="n">
-        <v>91.58035278320312</v>
+        <v>91.58034515380859</v>
       </c>
       <c r="C681" t="n">
-        <v>92.01662054420278</v>
+        <v>92.01661287846356</v>
       </c>
       <c r="D681" t="n">
-        <v>90.22511332487385</v>
+        <v>90.22510580838188</v>
       </c>
       <c r="E681" t="n">
-        <v>90.22511332487385</v>
+        <v>90.22510580838188</v>
       </c>
       <c r="F681" t="n">
         <v>136324</v>
@@ -14052,16 +14052,16 @@
         <v>45471</v>
       </c>
       <c r="B682" t="n">
-        <v>90.78206634521484</v>
+        <v>90.78205871582031</v>
       </c>
       <c r="C682" t="n">
-        <v>92.4436132183085</v>
+        <v>92.44360544927629</v>
       </c>
       <c r="D682" t="n">
-        <v>89.58463336929955</v>
+        <v>89.58462584053821</v>
       </c>
       <c r="E682" t="n">
-        <v>91.15335746295753</v>
+        <v>91.15334980235941</v>
       </c>
       <c r="F682" t="n">
         <v>273815</v>
@@ -14072,16 +14072,16 @@
         <v>45474</v>
       </c>
       <c r="B683" t="n">
-        <v>87.969482421875</v>
+        <v>87.96947479248047</v>
       </c>
       <c r="C683" t="n">
-        <v>91.70101885438143</v>
+        <v>91.70101090135917</v>
       </c>
       <c r="D683" t="n">
-        <v>87.85809792545159</v>
+        <v>87.85809030571718</v>
       </c>
       <c r="E683" t="n">
-        <v>90.31794039570877</v>
+        <v>90.31793256263779</v>
       </c>
       <c r="F683" t="n">
         <v>154542</v>
@@ -14092,16 +14092,16 @@
         <v>45475</v>
       </c>
       <c r="B684" t="n">
-        <v>87.69101715087891</v>
+        <v>87.69100952148438</v>
       </c>
       <c r="C684" t="n">
-        <v>88.647105215382</v>
+        <v>88.6470975028048</v>
       </c>
       <c r="D684" t="n">
-        <v>87.28258843131488</v>
+        <v>87.28258083745493</v>
       </c>
       <c r="E684" t="n">
-        <v>88.03446213603596</v>
+        <v>88.03445447676063</v>
       </c>
       <c r="F684" t="n">
         <v>181372</v>
@@ -14172,16 +14172,16 @@
         <v>45481</v>
       </c>
       <c r="B688" t="n">
-        <v>87.11549377441406</v>
+        <v>87.11550140380859</v>
       </c>
       <c r="C688" t="n">
-        <v>88.26651165334657</v>
+        <v>88.26651938354486</v>
       </c>
       <c r="D688" t="n">
-        <v>86.17796754914521</v>
+        <v>86.17797509643314</v>
       </c>
       <c r="E688" t="n">
-        <v>86.32648964032262</v>
+        <v>86.32649720061781</v>
       </c>
       <c r="F688" t="n">
         <v>189187</v>
@@ -14212,16 +14212,16 @@
         <v>45483</v>
       </c>
       <c r="B690" t="n">
-        <v>91.15335083007812</v>
+        <v>91.15334320068359</v>
       </c>
       <c r="C690" t="n">
-        <v>92.08159272073848</v>
+        <v>92.08158501365153</v>
       </c>
       <c r="D690" t="n">
-        <v>86.83703170404632</v>
+        <v>86.83702443592102</v>
       </c>
       <c r="E690" t="n">
-        <v>86.83703170404632</v>
+        <v>86.83702443592102</v>
       </c>
       <c r="F690" t="n">
         <v>604684</v>
@@ -14252,16 +14252,16 @@
         <v>45485</v>
       </c>
       <c r="B692" t="n">
-        <v>92.93557739257812</v>
+        <v>92.93558502197266</v>
       </c>
       <c r="C692" t="n">
-        <v>93.67816662998491</v>
+        <v>93.67817432034111</v>
       </c>
       <c r="D692" t="n">
-        <v>91.43182303280007</v>
+        <v>91.43183053874634</v>
       </c>
       <c r="E692" t="n">
-        <v>91.90522836342113</v>
+        <v>91.90523590823084</v>
       </c>
       <c r="F692" t="n">
         <v>527149</v>
@@ -14272,16 +14272,16 @@
         <v>45488</v>
       </c>
       <c r="B693" t="n">
-        <v>93.75243377685547</v>
+        <v>93.75242614746094</v>
       </c>
       <c r="C693" t="n">
-        <v>94.8756056485097</v>
+        <v>94.87559792771359</v>
       </c>
       <c r="D693" t="n">
-        <v>92.54571644992839</v>
+        <v>92.54570891873422</v>
       </c>
       <c r="E693" t="n">
-        <v>92.83347626039723</v>
+        <v>92.83346870578572</v>
       </c>
       <c r="F693" t="n">
         <v>284490</v>
@@ -14292,16 +14292,16 @@
         <v>45489</v>
       </c>
       <c r="B694" t="n">
-        <v>93.74314117431641</v>
+        <v>93.74314880371094</v>
       </c>
       <c r="C694" t="n">
-        <v>95.46038715708933</v>
+        <v>95.46039492624392</v>
       </c>
       <c r="D694" t="n">
-        <v>92.9262909069122</v>
+        <v>92.92629846982642</v>
       </c>
       <c r="E694" t="n">
-        <v>92.9262909069122</v>
+        <v>92.92629846982642</v>
       </c>
       <c r="F694" t="n">
         <v>218776</v>
@@ -14392,16 +14392,16 @@
         <v>45496</v>
       </c>
       <c r="B699" t="n">
-        <v>94.27224731445312</v>
+        <v>94.27223968505859</v>
       </c>
       <c r="C699" t="n">
-        <v>94.9405826312758</v>
+        <v>94.94057494779331</v>
       </c>
       <c r="D699" t="n">
-        <v>93.76171850660302</v>
+        <v>93.76171091852527</v>
       </c>
       <c r="E699" t="n">
-        <v>93.76171850660302</v>
+        <v>93.76171091852527</v>
       </c>
       <c r="F699" t="n">
         <v>121190</v>
@@ -14412,16 +14412,16 @@
         <v>45497</v>
       </c>
       <c r="B700" t="n">
-        <v>91.80311584472656</v>
+        <v>91.80313110351562</v>
       </c>
       <c r="C700" t="n">
-        <v>94.77348678516967</v>
+        <v>94.77350253767032</v>
       </c>
       <c r="D700" t="n">
-        <v>91.78454704276713</v>
+        <v>91.78456229846984</v>
       </c>
       <c r="E700" t="n">
-        <v>94.36506520706058</v>
+        <v>94.36508089167664</v>
       </c>
       <c r="F700" t="n">
         <v>387734</v>
@@ -14452,16 +14452,16 @@
         <v>45499</v>
       </c>
       <c r="B702" t="n">
-        <v>93.1026611328125</v>
+        <v>93.10266876220703</v>
       </c>
       <c r="C702" t="n">
-        <v>94.93129164313034</v>
+        <v>94.9312994223739</v>
       </c>
       <c r="D702" t="n">
-        <v>92.04446598189828</v>
+        <v>92.04447352457791</v>
       </c>
       <c r="E702" t="n">
-        <v>93.00055396194153</v>
+        <v>93.00056158296879</v>
       </c>
       <c r="F702" t="n">
         <v>291332</v>
@@ -14472,16 +14472,16 @@
         <v>45502</v>
       </c>
       <c r="B703" t="n">
-        <v>91.94235229492188</v>
+        <v>91.94236755371094</v>
       </c>
       <c r="C703" t="n">
-        <v>94.07730416654506</v>
+        <v>94.07731977965157</v>
       </c>
       <c r="D703" t="n">
-        <v>91.71956916594331</v>
+        <v>91.7195843877592</v>
       </c>
       <c r="E703" t="n">
-        <v>93.10265453447454</v>
+        <v>93.1026699858278</v>
       </c>
       <c r="F703" t="n">
         <v>142991</v>
@@ -14512,16 +14512,16 @@
         <v>45504</v>
       </c>
       <c r="B705" t="n">
-        <v>90.49430847167969</v>
+        <v>90.49430084228516</v>
       </c>
       <c r="C705" t="n">
-        <v>91.8031330602639</v>
+        <v>91.80312532052498</v>
       </c>
       <c r="D705" t="n">
-        <v>89.90023417218629</v>
+        <v>89.90022659287696</v>
       </c>
       <c r="E705" t="n">
-        <v>90.59641565583551</v>
+        <v>90.59640801783253</v>
       </c>
       <c r="F705" t="n">
         <v>210335</v>
@@ -14552,16 +14552,16 @@
         <v>45506</v>
       </c>
       <c r="B707" t="n">
-        <v>86.47502136230469</v>
+        <v>86.47501373291016</v>
       </c>
       <c r="C707" t="n">
-        <v>88.66566579576077</v>
+        <v>88.6656579730932</v>
       </c>
       <c r="D707" t="n">
-        <v>85.23117349689625</v>
+        <v>85.23116597724216</v>
       </c>
       <c r="E707" t="n">
-        <v>87.72814654800261</v>
+        <v>87.72813880804915</v>
       </c>
       <c r="F707" t="n">
         <v>556592</v>
@@ -14592,16 +14592,16 @@
         <v>45510</v>
       </c>
       <c r="B709" t="n">
-        <v>85.04552459716797</v>
+        <v>85.0455322265625</v>
       </c>
       <c r="C709" t="n">
-        <v>86.18725815714363</v>
+        <v>86.18726588896256</v>
       </c>
       <c r="D709" t="n">
-        <v>83.79239237886372</v>
+        <v>83.79239989584035</v>
       </c>
       <c r="E709" t="n">
-        <v>85.21260842081362</v>
+        <v>85.21261606519718</v>
       </c>
       <c r="F709" t="n">
         <v>246819</v>
@@ -14692,16 +14692,16 @@
         <v>45517</v>
       </c>
       <c r="B714" t="n">
-        <v>93.46467590332031</v>
+        <v>93.46468353271484</v>
       </c>
       <c r="C714" t="n">
-        <v>94.6806704835107</v>
+        <v>94.6806782121652</v>
       </c>
       <c r="D714" t="n">
-        <v>92.62925680619877</v>
+        <v>92.62926436739917</v>
       </c>
       <c r="E714" t="n">
-        <v>92.62925680619877</v>
+        <v>92.62926436739917</v>
       </c>
       <c r="F714" t="n">
         <v>783941</v>
@@ -14712,16 +14712,16 @@
         <v>45518</v>
       </c>
       <c r="B715" t="n">
-        <v>100.250129699707</v>
+        <v>100.2501220703125</v>
       </c>
       <c r="C715" t="n">
-        <v>101.4382782519291</v>
+        <v>101.4382705321122</v>
       </c>
       <c r="D715" t="n">
-        <v>98.41220753916585</v>
+        <v>98.41220004964379</v>
       </c>
       <c r="E715" t="n">
-        <v>100.0644841441438</v>
+        <v>100.0644765288776</v>
       </c>
       <c r="F715" t="n">
         <v>1420295</v>
@@ -14772,16 +14772,16 @@
         <v>45523</v>
       </c>
       <c r="B718" t="n">
-        <v>100.5471572875977</v>
+        <v>100.5471649169922</v>
       </c>
       <c r="C718" t="n">
-        <v>102.0787577622536</v>
+        <v>102.0787655078641</v>
       </c>
       <c r="D718" t="n">
-        <v>99.86026029894786</v>
+        <v>99.8602678762215</v>
       </c>
       <c r="E718" t="n">
-        <v>101.3640075691833</v>
+        <v>101.3640152605594</v>
       </c>
       <c r="F718" t="n">
         <v>372762</v>
@@ -14792,16 +14792,16 @@
         <v>45524</v>
       </c>
       <c r="B719" t="n">
-        <v>99.72102355957031</v>
+        <v>99.72103118896484</v>
       </c>
       <c r="C719" t="n">
-        <v>101.0948246319502</v>
+        <v>101.0948323664506</v>
       </c>
       <c r="D719" t="n">
-        <v>99.31259487390432</v>
+        <v>99.31260247205103</v>
       </c>
       <c r="E719" t="n">
-        <v>100.5935731764301</v>
+        <v>100.5935808725811</v>
       </c>
       <c r="F719" t="n">
         <v>300080</v>
@@ -14892,16 +14892,16 @@
         <v>45531</v>
       </c>
       <c r="B724" t="n">
-        <v>99.32187652587891</v>
+        <v>99.32188415527344</v>
       </c>
       <c r="C724" t="n">
-        <v>100.7977776468936</v>
+        <v>100.7977853896593</v>
       </c>
       <c r="D724" t="n">
-        <v>99.1547927119977</v>
+        <v>99.15480032855771</v>
       </c>
       <c r="E724" t="n">
-        <v>99.40541489185792</v>
+        <v>99.40542252766943</v>
       </c>
       <c r="F724" t="n">
         <v>203544</v>
@@ -14972,16 +14972,16 @@
         <v>45537</v>
       </c>
       <c r="B728" t="n">
-        <v>95.33043670654297</v>
+        <v>95.3304443359375</v>
       </c>
       <c r="C728" t="n">
-        <v>95.77599591780708</v>
+        <v>95.77600358286018</v>
       </c>
       <c r="D728" t="n">
-        <v>93.65032119704127</v>
+        <v>93.65032869197439</v>
       </c>
       <c r="E728" t="n">
-        <v>95.6181965004124</v>
+        <v>95.61820415283664</v>
       </c>
       <c r="F728" t="n">
         <v>425330</v>
@@ -14992,16 +14992,16 @@
         <v>45538</v>
       </c>
       <c r="B729" t="n">
-        <v>96.24940490722656</v>
+        <v>96.24939727783203</v>
       </c>
       <c r="C729" t="n">
-        <v>97.25190077727714</v>
+        <v>97.25189306841784</v>
       </c>
       <c r="D729" t="n">
-        <v>94.54143612809369</v>
+        <v>94.5414286340846</v>
       </c>
       <c r="E729" t="n">
-        <v>95.51609295616707</v>
+        <v>95.51608538489992</v>
       </c>
       <c r="F729" t="n">
         <v>703523</v>
@@ -15072,16 +15072,16 @@
         <v>45544</v>
       </c>
       <c r="B733" t="n">
-        <v>93.68745422363281</v>
+        <v>93.68744659423828</v>
       </c>
       <c r="C733" t="n">
-        <v>95.05197093478797</v>
+        <v>95.05196319427465</v>
       </c>
       <c r="D733" t="n">
-        <v>93.37184829849096</v>
+        <v>93.37184069479765</v>
       </c>
       <c r="E733" t="n">
-        <v>93.77099259439402</v>
+        <v>93.77098495819658</v>
       </c>
       <c r="F733" t="n">
         <v>200739</v>
@@ -15092,16 +15092,16 @@
         <v>45545</v>
       </c>
       <c r="B734" t="n">
-        <v>94.4393310546875</v>
+        <v>94.43932342529297</v>
       </c>
       <c r="C734" t="n">
-        <v>94.894174694939</v>
+        <v>94.89416702879937</v>
       </c>
       <c r="D734" t="n">
-        <v>92.1929873056461</v>
+        <v>92.19297985772515</v>
       </c>
       <c r="E734" t="n">
-        <v>93.78028014064265</v>
+        <v>93.78027256449035</v>
       </c>
       <c r="F734" t="n">
         <v>481370</v>
@@ -15152,16 +15152,16 @@
         <v>45548</v>
       </c>
       <c r="B737" t="n">
-        <v>98.87632751464844</v>
+        <v>98.87631988525391</v>
       </c>
       <c r="C737" t="n">
-        <v>99.46112446444116</v>
+        <v>99.46111678992312</v>
       </c>
       <c r="D737" t="n">
-        <v>96.32366220076925</v>
+        <v>96.32365476834089</v>
       </c>
       <c r="E737" t="n">
-        <v>96.32366220076925</v>
+        <v>96.32365476834089</v>
       </c>
       <c r="F737" t="n">
         <v>344396</v>
@@ -15192,16 +15192,16 @@
         <v>45552</v>
       </c>
       <c r="B739" t="n">
-        <v>100.3150939941406</v>
+        <v>100.3151016235352</v>
       </c>
       <c r="C739" t="n">
-        <v>100.7977766282958</v>
+        <v>100.7977842944004</v>
       </c>
       <c r="D739" t="n">
-        <v>98.70923251684773</v>
+        <v>98.70924002410959</v>
       </c>
       <c r="E739" t="n">
-        <v>99.17335343050286</v>
+        <v>99.17336097306311</v>
       </c>
       <c r="F739" t="n">
         <v>287351</v>
@@ -15272,16 +15272,16 @@
         <v>45558</v>
       </c>
       <c r="B743" t="n">
-        <v>90.16013336181641</v>
+        <v>90.16012573242188</v>
       </c>
       <c r="C743" t="n">
-        <v>93.8823853705385</v>
+        <v>93.88237742616521</v>
       </c>
       <c r="D743" t="n">
-        <v>89.63103576112911</v>
+        <v>89.63102817650709</v>
       </c>
       <c r="E743" t="n">
-        <v>93.1026655724409</v>
+        <v>93.10265769404786</v>
       </c>
       <c r="F743" t="n">
         <v>500884</v>
@@ -15312,16 +15312,16 @@
         <v>45560</v>
       </c>
       <c r="B745" t="n">
-        <v>90.49430847167969</v>
+        <v>90.49430084228516</v>
       </c>
       <c r="C745" t="n">
-        <v>92.06303968105173</v>
+        <v>92.0630319194006</v>
       </c>
       <c r="D745" t="n">
-        <v>89.42682878036601</v>
+        <v>89.42682124096855</v>
       </c>
       <c r="E745" t="n">
-        <v>91.89595584169895</v>
+        <v>91.89594809413431</v>
       </c>
       <c r="F745" t="n">
         <v>511811</v>
@@ -15332,16 +15332,16 @@
         <v>45561</v>
       </c>
       <c r="B746" t="n">
-        <v>91.3204345703125</v>
+        <v>91.32042694091797</v>
       </c>
       <c r="C746" t="n">
-        <v>92.21154593470217</v>
+        <v>92.21153823085946</v>
       </c>
       <c r="D746" t="n">
-        <v>90.48502253501967</v>
+        <v>90.4850149754199</v>
       </c>
       <c r="E746" t="n">
-        <v>91.07909677794611</v>
+        <v>91.07908916871422</v>
       </c>
       <c r="F746" t="n">
         <v>433745</v>
@@ -15432,16 +15432,16 @@
         <v>45568</v>
       </c>
       <c r="B751" t="n">
-        <v>90.16013336181641</v>
+        <v>90.16012573242188</v>
       </c>
       <c r="C751" t="n">
-        <v>90.91201411789474</v>
+        <v>90.9120064248757</v>
       </c>
       <c r="D751" t="n">
-        <v>88.60997108565304</v>
+        <v>88.60996358743401</v>
       </c>
       <c r="E751" t="n">
-        <v>90.49430101297929</v>
+        <v>90.49429335530733</v>
       </c>
       <c r="F751" t="n">
         <v>420486</v>
@@ -15452,16 +15452,16 @@
         <v>45569</v>
       </c>
       <c r="B752" t="n">
-        <v>89.85381317138672</v>
+        <v>89.85382080078125</v>
       </c>
       <c r="C752" t="n">
-        <v>90.30864969119534</v>
+        <v>90.30865735920958</v>
       </c>
       <c r="D752" t="n">
-        <v>87.72813850259483</v>
+        <v>87.72814595150052</v>
       </c>
       <c r="E752" t="n">
-        <v>90.17869639982145</v>
+        <v>90.17870405680148</v>
       </c>
       <c r="F752" t="n">
         <v>695884</v>
@@ -15472,16 +15472,16 @@
         <v>45572</v>
       </c>
       <c r="B753" t="n">
-        <v>90.48501586914062</v>
+        <v>90.48502349853516</v>
       </c>
       <c r="C753" t="n">
-        <v>90.75419976526331</v>
+        <v>90.75420741735454</v>
       </c>
       <c r="D753" t="n">
-        <v>89.12049925852935</v>
+        <v>89.1205067728724</v>
       </c>
       <c r="E753" t="n">
-        <v>89.80739622344984</v>
+        <v>89.80740379570975</v>
       </c>
       <c r="F753" t="n">
         <v>295051</v>
@@ -15492,16 +15492,16 @@
         <v>45573</v>
       </c>
       <c r="B754" t="n">
-        <v>90.68922424316406</v>
+        <v>90.68923187255859</v>
       </c>
       <c r="C754" t="n">
-        <v>91.33899777535945</v>
+        <v>91.33900545941735</v>
       </c>
       <c r="D754" t="n">
-        <v>90.68922424316406</v>
+        <v>90.68923187255859</v>
       </c>
       <c r="E754" t="n">
-        <v>91.12549903774249</v>
+        <v>91.12550670383942</v>
       </c>
       <c r="F754" t="n">
         <v>183628</v>
@@ -15512,16 +15512,16 @@
         <v>45574</v>
       </c>
       <c r="B755" t="n">
-        <v>89.48251342773438</v>
+        <v>89.48252105712891</v>
       </c>
       <c r="C755" t="n">
-        <v>90.68922355217755</v>
+        <v>90.68923128445775</v>
       </c>
       <c r="D755" t="n">
-        <v>87.85809023250759</v>
+        <v>87.85809772340171</v>
       </c>
       <c r="E755" t="n">
-        <v>90.42003965477517</v>
+        <v>90.42004736410439</v>
       </c>
       <c r="F755" t="n">
         <v>305833</v>
@@ -15592,16 +15592,16 @@
         <v>45580</v>
       </c>
       <c r="B759" t="n">
-        <v>92.2208251953125</v>
+        <v>92.22083282470703</v>
       </c>
       <c r="C759" t="n">
-        <v>94.20726216221644</v>
+        <v>94.20726995594816</v>
       </c>
       <c r="D759" t="n">
-        <v>91.71029643353101</v>
+        <v>91.71030402068969</v>
       </c>
       <c r="E759" t="n">
-        <v>93.52964958630643</v>
+        <v>93.52965732397952</v>
       </c>
       <c r="F759" t="n">
         <v>238514</v>
@@ -15652,16 +15652,16 @@
         <v>45583</v>
       </c>
       <c r="B762" t="n">
-        <v>95.5625</v>
+        <v>95.56249237060547</v>
       </c>
       <c r="C762" t="n">
-        <v>96.35151127416302</v>
+        <v>96.35150358177644</v>
       </c>
       <c r="D762" t="n">
-        <v>94.81062633329138</v>
+        <v>94.81061876392397</v>
       </c>
       <c r="E762" t="n">
-        <v>95.5996305255308</v>
+        <v>95.59962289317188</v>
       </c>
       <c r="F762" t="n">
         <v>405254</v>
@@ -15712,16 +15712,16 @@
         <v>45588</v>
       </c>
       <c r="B765" t="n">
-        <v>92.42504119873047</v>
+        <v>92.425048828125</v>
       </c>
       <c r="C765" t="n">
-        <v>95.40469670279386</v>
+        <v>95.40470457814952</v>
       </c>
       <c r="D765" t="n">
-        <v>92.36006455217171</v>
+        <v>92.36007217620262</v>
       </c>
       <c r="E765" t="n">
-        <v>93.76171173585173</v>
+        <v>93.76171947558419</v>
       </c>
       <c r="F765" t="n">
         <v>357512</v>
@@ -15752,16 +15752,16 @@
         <v>45590</v>
       </c>
       <c r="B767" t="n">
-        <v>93.17691040039062</v>
+        <v>93.17691802978516</v>
       </c>
       <c r="C767" t="n">
-        <v>93.91022228060997</v>
+        <v>93.91022997004863</v>
       </c>
       <c r="D767" t="n">
-        <v>92.02589253816214</v>
+        <v>92.02590007331048</v>
       </c>
       <c r="E767" t="n">
-        <v>93.29758636820173</v>
+        <v>93.29759400747731</v>
       </c>
       <c r="F767" t="n">
         <v>563664</v>
@@ -15812,16 +15812,16 @@
         <v>45595</v>
       </c>
       <c r="B770" t="n">
-        <v>95.72958374023438</v>
+        <v>95.72957611083984</v>
       </c>
       <c r="C770" t="n">
-        <v>96.24011961343192</v>
+        <v>96.24011194334904</v>
       </c>
       <c r="D770" t="n">
-        <v>94.58785017933603</v>
+        <v>94.58784264093464</v>
       </c>
       <c r="E770" t="n">
-        <v>94.58785017933603</v>
+        <v>94.58784264093464</v>
       </c>
       <c r="F770" t="n">
         <v>154247</v>
@@ -15852,16 +15852,16 @@
         <v>45597</v>
       </c>
       <c r="B772" t="n">
-        <v>91.89594268798828</v>
+        <v>91.89595031738281</v>
       </c>
       <c r="C772" t="n">
-        <v>94.99626705207805</v>
+        <v>94.99627493886804</v>
       </c>
       <c r="D772" t="n">
-        <v>91.41326004446124</v>
+        <v>91.41326763378245</v>
       </c>
       <c r="E772" t="n">
-        <v>93.85453354819522</v>
+        <v>93.85454134019609</v>
       </c>
       <c r="F772" t="n">
         <v>397099</v>
@@ -15912,16 +15912,16 @@
         <v>45602</v>
       </c>
       <c r="B775" t="n">
-        <v>94.72709655761719</v>
+        <v>94.72708129882812</v>
       </c>
       <c r="C775" t="n">
-        <v>95.38614751126146</v>
+        <v>95.38613214631143</v>
       </c>
       <c r="D775" t="n">
-        <v>91.81241731725275</v>
+        <v>91.81240252796478</v>
       </c>
       <c r="E775" t="n">
-        <v>94.2165606376484</v>
+        <v>94.21654546109727</v>
       </c>
       <c r="F775" t="n">
         <v>484922</v>
@@ -15932,16 +15932,16 @@
         <v>45603</v>
       </c>
       <c r="B776" t="n">
-        <v>93.40898132324219</v>
+        <v>93.40897369384766</v>
       </c>
       <c r="C776" t="n">
-        <v>96.03590764140573</v>
+        <v>96.03589979745092</v>
       </c>
       <c r="D776" t="n">
-        <v>92.91701424157758</v>
+        <v>92.91700665236559</v>
       </c>
       <c r="E776" t="n">
-        <v>94.72709022432851</v>
+        <v>94.72708248727439</v>
       </c>
       <c r="F776" t="n">
         <v>397597</v>
@@ -15952,16 +15952,16 @@
         <v>45604</v>
       </c>
       <c r="B777" t="n">
-        <v>91.02339172363281</v>
+        <v>91.02339935302734</v>
       </c>
       <c r="C777" t="n">
-        <v>93.79883989858776</v>
+        <v>93.79884776061469</v>
       </c>
       <c r="D777" t="n">
-        <v>89.98376540486406</v>
+        <v>89.98377294711923</v>
       </c>
       <c r="E777" t="n">
-        <v>93.39969562779672</v>
+        <v>93.39970345636819</v>
       </c>
       <c r="F777" t="n">
         <v>477120</v>
@@ -16032,16 +16032,16 @@
         <v>45610</v>
       </c>
       <c r="B781" t="n">
-        <v>90.15085601806641</v>
+        <v>90.15084838867188</v>
       </c>
       <c r="C781" t="n">
-        <v>91.79384106758192</v>
+        <v>91.79383329914289</v>
       </c>
       <c r="D781" t="n">
-        <v>89.28759076644334</v>
+        <v>89.28758321010626</v>
       </c>
       <c r="E781" t="n">
-        <v>90.22510998792019</v>
+        <v>90.22510235224161</v>
       </c>
       <c r="F781" t="n">
         <v>249817</v>
@@ -16132,16 +16132,16 @@
         <v>45621</v>
       </c>
       <c r="B786" t="n">
-        <v>85.59317779541016</v>
+        <v>85.59318542480469</v>
       </c>
       <c r="C786" t="n">
-        <v>86.31720528548094</v>
+        <v>86.31721297941206</v>
       </c>
       <c r="D786" t="n">
-        <v>84.42359111349106</v>
+        <v>84.42359863863385</v>
       </c>
       <c r="E786" t="n">
-        <v>85.32398681644892</v>
+        <v>85.32399442184897</v>
       </c>
       <c r="F786" t="n">
         <v>384525</v>
@@ -16212,16 +16212,16 @@
         <v>45625</v>
       </c>
       <c r="B790" t="n">
-        <v>76.31076812744141</v>
+        <v>76.31076049804688</v>
       </c>
       <c r="C790" t="n">
-        <v>79.70813698664587</v>
+        <v>79.70812901758936</v>
       </c>
       <c r="D790" t="n">
-        <v>73.81379507240612</v>
+        <v>73.81378769265385</v>
       </c>
       <c r="E790" t="n">
-        <v>78.53855017325635</v>
+        <v>78.53854232113272</v>
       </c>
       <c r="F790" t="n">
         <v>1718056</v>
@@ -16272,16 +16272,16 @@
         <v>45630</v>
       </c>
       <c r="B793" t="n">
-        <v>75.2247314453125</v>
+        <v>75.22472381591797</v>
       </c>
       <c r="C793" t="n">
-        <v>76.09728117894873</v>
+        <v>76.09727346105902</v>
       </c>
       <c r="D793" t="n">
-        <v>74.39859664377688</v>
+        <v>74.39858909817006</v>
       </c>
       <c r="E793" t="n">
-        <v>75.41966141267126</v>
+        <v>75.41965376350666</v>
       </c>
       <c r="F793" t="n">
         <v>411810</v>
@@ -16312,16 +16312,16 @@
         <v>45632</v>
       </c>
       <c r="B795" t="n">
-        <v>75.78166198730469</v>
+        <v>75.78166961669922</v>
       </c>
       <c r="C795" t="n">
-        <v>75.78166198730469</v>
+        <v>75.78166961669922</v>
       </c>
       <c r="D795" t="n">
-        <v>74.25934596164483</v>
+        <v>74.25935343777866</v>
       </c>
       <c r="E795" t="n">
-        <v>75.65170869842567</v>
+        <v>75.651716314737</v>
       </c>
       <c r="F795" t="n">
         <v>1017781</v>
@@ -24472,19 +24472,39 @@
         <v>46233</v>
       </c>
       <c r="B1203" t="n">
-        <v>86.26000000000001</v>
+        <v>86.26000213623047</v>
       </c>
       <c r="C1203" t="n">
-        <v>87.42</v>
+        <v>87.41999816894531</v>
       </c>
       <c r="D1203" t="n">
-        <v>83.48999999999999</v>
+        <v>83.48999786376953</v>
       </c>
       <c r="E1203" t="n">
-        <v>83.70999999999999</v>
+        <v>83.70999908447266</v>
       </c>
       <c r="F1203" t="n">
         <v>452487</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B1204" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="C1204" t="n">
+        <v>87</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>86.19</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>86.31</v>
+      </c>
+      <c r="F1204" t="n">
+        <v>256130</v>
       </c>
     </row>
   </sheetData>

--- a/database/XPBR31.xlsx
+++ b/database/XPBR31.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1204"/>
+  <dimension ref="A1:F1205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>44474</v>
       </c>
       <c r="B3" t="n">
-        <v>192.5414886474609</v>
+        <v>192.5415191650391</v>
       </c>
       <c r="C3" t="n">
-        <v>198.9809168362223</v>
+        <v>198.9809483744415</v>
       </c>
       <c r="D3" t="n">
-        <v>187.7272962672212</v>
+        <v>187.727326021756</v>
       </c>
       <c r="E3" t="n">
-        <v>197.6631624200884</v>
+        <v>197.6631937494452</v>
       </c>
       <c r="F3" t="n">
         <v>2636287</v>
@@ -512,16 +512,16 @@
         <v>44476</v>
       </c>
       <c r="B5" t="n">
-        <v>203.3734283447266</v>
+        <v>203.3734436035156</v>
       </c>
       <c r="C5" t="n">
-        <v>203.3734283447266</v>
+        <v>203.3734436035156</v>
       </c>
       <c r="D5" t="n">
-        <v>190.9426172441435</v>
+        <v>190.9426315702683</v>
       </c>
       <c r="E5" t="n">
-        <v>190.9426172441435</v>
+        <v>190.9426315702683</v>
       </c>
       <c r="F5" t="n">
         <v>12157101</v>
@@ -532,16 +532,16 @@
         <v>44477</v>
       </c>
       <c r="B6" t="n">
-        <v>193.8240966796875</v>
+        <v>193.8241119384766</v>
       </c>
       <c r="C6" t="n">
-        <v>204.8668710233078</v>
+        <v>204.8668871514385</v>
       </c>
       <c r="D6" t="n">
-        <v>191.7947571509841</v>
+        <v>191.7947722500135</v>
       </c>
       <c r="E6" t="n">
-        <v>200.992670065843</v>
+        <v>200.9926858889775</v>
       </c>
       <c r="F6" t="n">
         <v>4982319</v>
@@ -572,16 +572,16 @@
         <v>44482</v>
       </c>
       <c r="B8" t="n">
-        <v>169.5510711669922</v>
+        <v>169.5510864257812</v>
       </c>
       <c r="C8" t="n">
-        <v>178.8632078987421</v>
+        <v>178.8632239955791</v>
       </c>
       <c r="D8" t="n">
-        <v>169.5510711669922</v>
+        <v>169.5510864257812</v>
       </c>
       <c r="E8" t="n">
-        <v>174.4091914601629</v>
+        <v>174.4092071561597</v>
       </c>
       <c r="F8" t="n">
         <v>3487621</v>
@@ -612,16 +612,16 @@
         <v>44484</v>
       </c>
       <c r="B10" t="n">
-        <v>175.7005767822266</v>
+        <v>175.7006072998047</v>
       </c>
       <c r="C10" t="n">
-        <v>178.9773887858458</v>
+        <v>178.9774198725761</v>
       </c>
       <c r="D10" t="n">
-        <v>166.9155479431152</v>
+        <v>166.9155769348145</v>
       </c>
       <c r="E10" t="n">
-        <v>166.9155479431152</v>
+        <v>166.9155769348145</v>
       </c>
       <c r="F10" t="n">
         <v>2643581</v>
@@ -632,16 +632,16 @@
         <v>44487</v>
       </c>
       <c r="B11" t="n">
-        <v>179.4166717529297</v>
+        <v>179.4166564941406</v>
       </c>
       <c r="C11" t="n">
-        <v>182.2718066273138</v>
+        <v>182.2717911257051</v>
       </c>
       <c r="D11" t="n">
-        <v>175.0680843944616</v>
+        <v>175.0680695055053</v>
       </c>
       <c r="E11" t="n">
-        <v>176.7548086193568</v>
+        <v>176.7547935869503</v>
       </c>
       <c r="F11" t="n">
         <v>1369949</v>
@@ -652,16 +652,16 @@
         <v>44488</v>
       </c>
       <c r="B12" t="n">
-        <v>175.0856628417969</v>
+        <v>175.0856323242188</v>
       </c>
       <c r="C12" t="n">
-        <v>179.4078962958852</v>
+        <v>179.4078650249382</v>
       </c>
       <c r="D12" t="n">
-        <v>174.3828577116028</v>
+        <v>174.3828273165242</v>
       </c>
       <c r="E12" t="n">
-        <v>177.5454740950298</v>
+        <v>177.5454431487045</v>
       </c>
       <c r="F12" t="n">
         <v>722779</v>
@@ -672,16 +672,16 @@
         <v>44489</v>
       </c>
       <c r="B13" t="n">
-        <v>174.3828582763672</v>
+        <v>174.3828277587891</v>
       </c>
       <c r="C13" t="n">
-        <v>178.4942461832448</v>
+        <v>178.4942149461601</v>
       </c>
       <c r="D13" t="n">
-        <v>169.8409990421895</v>
+        <v>169.8409693194518</v>
       </c>
       <c r="E13" t="n">
-        <v>176.5791159372786</v>
+        <v>176.5790850353481</v>
       </c>
       <c r="F13" t="n">
         <v>1907987</v>
@@ -712,16 +712,16 @@
         <v>44491</v>
       </c>
       <c r="B15" t="n">
-        <v>166.0546417236328</v>
+        <v>166.0546264648438</v>
       </c>
       <c r="C15" t="n">
-        <v>170.8600542323661</v>
+        <v>170.8600385320068</v>
       </c>
       <c r="D15" t="n">
-        <v>159.8084848231975</v>
+        <v>159.8084701383689</v>
       </c>
       <c r="E15" t="n">
-        <v>169.5510799294295</v>
+        <v>169.5510643493521</v>
       </c>
       <c r="F15" t="n">
         <v>1387914</v>
@@ -732,16 +732,16 @@
         <v>44494</v>
       </c>
       <c r="B16" t="n">
-        <v>169.12060546875</v>
+        <v>169.1206207275391</v>
       </c>
       <c r="C16" t="n">
-        <v>174.5848951289127</v>
+        <v>174.5849108807135</v>
       </c>
       <c r="D16" t="n">
-        <v>167.3635994919746</v>
+        <v>167.3636145922391</v>
       </c>
       <c r="E16" t="n">
-        <v>167.7062151212502</v>
+        <v>167.7062302524268</v>
       </c>
       <c r="F16" t="n">
         <v>1203463</v>
@@ -752,16 +752,16 @@
         <v>44495</v>
       </c>
       <c r="B17" t="n">
-        <v>163.9638061523438</v>
+        <v>163.9637908935547</v>
       </c>
       <c r="C17" t="n">
-        <v>170.2538911091769</v>
+        <v>170.2538752650204</v>
       </c>
       <c r="D17" t="n">
-        <v>159.9051264143641</v>
+        <v>159.9051115332836</v>
       </c>
       <c r="E17" t="n">
-        <v>168.7604386285045</v>
+        <v>168.7604229233316</v>
       </c>
       <c r="F17" t="n">
         <v>810455</v>
@@ -772,16 +772,16 @@
         <v>44496</v>
       </c>
       <c r="B18" t="n">
-        <v>163.8320159912109</v>
+        <v>163.8320465087891</v>
       </c>
       <c r="C18" t="n">
-        <v>168.540792225014</v>
+        <v>168.5408236197128</v>
       </c>
       <c r="D18" t="n">
-        <v>163.8320159912109</v>
+        <v>163.8320465087891</v>
       </c>
       <c r="E18" t="n">
-        <v>166.9155564450402</v>
+        <v>166.9155875370005</v>
       </c>
       <c r="F18" t="n">
         <v>503418</v>
@@ -792,16 +792,16 @@
         <v>44497</v>
       </c>
       <c r="B19" t="n">
-        <v>165.1673431396484</v>
+        <v>165.1673583984375</v>
       </c>
       <c r="C19" t="n">
-        <v>166.8101528543862</v>
+        <v>166.8101682649443</v>
       </c>
       <c r="D19" t="n">
-        <v>158.6664263435071</v>
+        <v>158.6664410017166</v>
       </c>
       <c r="E19" t="n">
-        <v>163.4103371509733</v>
+        <v>163.4103522474434</v>
       </c>
       <c r="F19" t="n">
         <v>1047427</v>
@@ -832,16 +832,16 @@
         <v>44501</v>
       </c>
       <c r="B21" t="n">
-        <v>169.7267761230469</v>
+        <v>169.7267913818359</v>
       </c>
       <c r="C21" t="n">
-        <v>171.2026681266692</v>
+        <v>171.2026835181439</v>
       </c>
       <c r="D21" t="n">
-        <v>161.9344588391563</v>
+        <v>161.9344733973998</v>
       </c>
       <c r="E21" t="n">
-        <v>162.5230542378089</v>
+        <v>162.5230688489684</v>
       </c>
       <c r="F21" t="n">
         <v>466029</v>
@@ -852,16 +852,16 @@
         <v>44503</v>
       </c>
       <c r="B22" t="n">
-        <v>164.6490173339844</v>
+        <v>164.6490325927734</v>
       </c>
       <c r="C22" t="n">
-        <v>168.672562357132</v>
+        <v>168.6725779888017</v>
       </c>
       <c r="D22" t="n">
-        <v>161.3809853659237</v>
+        <v>161.381000321849</v>
       </c>
       <c r="E22" t="n">
-        <v>168.672562357132</v>
+        <v>168.6725779888017</v>
       </c>
       <c r="F22" t="n">
         <v>834348</v>
@@ -872,16 +872,16 @@
         <v>44504</v>
       </c>
       <c r="B23" t="n">
-        <v>160.3707122802734</v>
+        <v>160.3707275390625</v>
       </c>
       <c r="C23" t="n">
-        <v>170.4207879271975</v>
+        <v>170.4208041422209</v>
       </c>
       <c r="D23" t="n">
-        <v>158.7630503125153</v>
+        <v>158.7630654183402</v>
       </c>
       <c r="E23" t="n">
-        <v>168.2333108094497</v>
+        <v>168.2333268163413</v>
       </c>
       <c r="F23" t="n">
         <v>1051127</v>
@@ -972,16 +972,16 @@
         <v>44511</v>
       </c>
       <c r="B28" t="n">
-        <v>162.1804504394531</v>
+        <v>162.1804351806641</v>
       </c>
       <c r="C28" t="n">
-        <v>165.5099711386316</v>
+        <v>165.5099555665838</v>
       </c>
       <c r="D28" t="n">
-        <v>159.4658792012834</v>
+        <v>159.4658641978954</v>
       </c>
       <c r="E28" t="n">
-        <v>161.5567073687131</v>
+        <v>161.5566921686091</v>
       </c>
       <c r="F28" t="n">
         <v>479646</v>
@@ -992,16 +992,16 @@
         <v>44512</v>
       </c>
       <c r="B29" t="n">
-        <v>161.6533203125</v>
+        <v>161.6533355712891</v>
       </c>
       <c r="C29" t="n">
-        <v>162.5230430442815</v>
+        <v>162.5230583851655</v>
       </c>
       <c r="D29" t="n">
-        <v>157.4277233381312</v>
+        <v>157.4277381980575</v>
       </c>
       <c r="E29" t="n">
-        <v>162.1804274356811</v>
+        <v>162.1804427442249</v>
       </c>
       <c r="F29" t="n">
         <v>339439</v>
@@ -1012,16 +1012,16 @@
         <v>44516</v>
       </c>
       <c r="B30" t="n">
-        <v>155.5213775634766</v>
+        <v>155.5213928222656</v>
       </c>
       <c r="C30" t="n">
-        <v>161.6357640485668</v>
+        <v>161.6357799072614</v>
       </c>
       <c r="D30" t="n">
-        <v>154.8976479701114</v>
+        <v>154.897663167704</v>
       </c>
       <c r="E30" t="n">
-        <v>160.9417392050919</v>
+        <v>160.9417549956931</v>
       </c>
       <c r="F30" t="n">
         <v>392032</v>
@@ -1072,16 +1072,16 @@
         <v>44519</v>
       </c>
       <c r="B33" t="n">
-        <v>147.1931915283203</v>
+        <v>147.1931762695312</v>
       </c>
       <c r="C33" t="n">
-        <v>149.046833535527</v>
+        <v>149.0468180845801</v>
       </c>
       <c r="D33" t="n">
-        <v>140.5692708976831</v>
+        <v>140.5692563255631</v>
       </c>
       <c r="E33" t="n">
-        <v>142.5722568176638</v>
+        <v>142.5722420379041</v>
       </c>
       <c r="F33" t="n">
         <v>581745</v>
@@ -1112,16 +1112,16 @@
         <v>44523</v>
       </c>
       <c r="B35" t="n">
-        <v>144.9530029296875</v>
+        <v>144.9529876708984</v>
       </c>
       <c r="C35" t="n">
-        <v>147.2107621975469</v>
+        <v>147.2107467010899</v>
       </c>
       <c r="D35" t="n">
-        <v>136.3524639873455</v>
+        <v>136.3524496339106</v>
       </c>
       <c r="E35" t="n">
-        <v>142.3174937855114</v>
+        <v>142.3174788041548</v>
       </c>
       <c r="F35" t="n">
         <v>809322</v>
@@ -1152,16 +1152,16 @@
         <v>44525</v>
       </c>
       <c r="B37" t="n">
-        <v>151.3133850097656</v>
+        <v>151.3133544921875</v>
       </c>
       <c r="C37" t="n">
-        <v>152.8507654981656</v>
+        <v>152.8507346705215</v>
       </c>
       <c r="D37" t="n">
-        <v>148.0717062922993</v>
+        <v>148.0716764285178</v>
       </c>
       <c r="E37" t="n">
-        <v>148.0717062922993</v>
+        <v>148.0716764285178</v>
       </c>
       <c r="F37" t="n">
         <v>222385</v>
@@ -1172,16 +1172,16 @@
         <v>44526</v>
       </c>
       <c r="B38" t="n">
-        <v>146.7363739013672</v>
+        <v>146.7363586425781</v>
       </c>
       <c r="C38" t="n">
-        <v>148.7305797213747</v>
+        <v>148.7305642552127</v>
       </c>
       <c r="D38" t="n">
-        <v>143.3717053697751</v>
+        <v>143.3716904608705</v>
       </c>
       <c r="E38" t="n">
-        <v>148.7305797213747</v>
+        <v>148.7305642552127</v>
       </c>
       <c r="F38" t="n">
         <v>241997</v>
@@ -1212,16 +1212,16 @@
         <v>44530</v>
       </c>
       <c r="B40" t="n">
-        <v>140.5604858398438</v>
+        <v>140.5604705810547</v>
       </c>
       <c r="C40" t="n">
-        <v>147.3073827258078</v>
+        <v>147.3073667345976</v>
       </c>
       <c r="D40" t="n">
-        <v>139.7610448594554</v>
+        <v>139.7610296874511</v>
       </c>
       <c r="E40" t="n">
-        <v>147.3073827258078</v>
+        <v>147.3073667345976</v>
       </c>
       <c r="F40" t="n">
         <v>711030</v>
@@ -1232,16 +1232,16 @@
         <v>44531</v>
       </c>
       <c r="B41" t="n">
-        <v>144.3116912841797</v>
+        <v>144.3116760253906</v>
       </c>
       <c r="C41" t="n">
-        <v>151.2342857954605</v>
+        <v>151.2342698047112</v>
       </c>
       <c r="D41" t="n">
-        <v>141.4477629305895</v>
+        <v>141.4477479746177</v>
       </c>
       <c r="E41" t="n">
-        <v>142.317485724668</v>
+        <v>142.3174706767361</v>
       </c>
       <c r="F41" t="n">
         <v>941983</v>
@@ -1252,16 +1252,16 @@
         <v>44532</v>
       </c>
       <c r="B42" t="n">
-        <v>143.7845916748047</v>
+        <v>143.7845764160156</v>
       </c>
       <c r="C42" t="n">
-        <v>150.5139282123845</v>
+        <v>150.513912239461</v>
       </c>
       <c r="D42" t="n">
-        <v>143.0466523346498</v>
+        <v>143.0466371541728</v>
       </c>
       <c r="E42" t="n">
-        <v>145.8315053769355</v>
+        <v>145.8314899009227</v>
       </c>
       <c r="F42" t="n">
         <v>584287</v>
@@ -1292,16 +1292,16 @@
         <v>44536</v>
       </c>
       <c r="B44" t="n">
-        <v>147.7642059326172</v>
+        <v>147.7641906738281</v>
       </c>
       <c r="C44" t="n">
-        <v>149.3279402427002</v>
+        <v>149.327924822433</v>
       </c>
       <c r="D44" t="n">
-        <v>139.2427292821338</v>
+        <v>139.2427149033103</v>
       </c>
       <c r="E44" t="n">
-        <v>144.9617791417145</v>
+        <v>144.9617641723165</v>
       </c>
       <c r="F44" t="n">
         <v>521095</v>
@@ -1372,16 +1372,16 @@
         <v>44540</v>
       </c>
       <c r="B48" t="n">
-        <v>148.2210235595703</v>
+        <v>148.2210388183594</v>
       </c>
       <c r="C48" t="n">
-        <v>150.2240092775463</v>
+        <v>150.2240247425351</v>
       </c>
       <c r="D48" t="n">
-        <v>146.3322475183298</v>
+        <v>146.3322625826765</v>
       </c>
       <c r="E48" t="n">
-        <v>148.1156074917479</v>
+        <v>148.1156227396848</v>
       </c>
       <c r="F48" t="n">
         <v>506410</v>
@@ -1412,16 +1412,16 @@
         <v>44544</v>
       </c>
       <c r="B50" t="n">
-        <v>147.2283020019531</v>
+        <v>147.2283325195312</v>
       </c>
       <c r="C50" t="n">
-        <v>150.9268052148167</v>
+        <v>150.926836499023</v>
       </c>
       <c r="D50" t="n">
-        <v>141.1227093534192</v>
+        <v>141.1227386054261</v>
       </c>
       <c r="E50" t="n">
-        <v>150.6632516563057</v>
+        <v>150.6632828858824</v>
       </c>
       <c r="F50" t="n">
         <v>995575</v>
@@ -1432,16 +1432,16 @@
         <v>44545</v>
       </c>
       <c r="B51" t="n">
-        <v>150.6983947753906</v>
+        <v>150.6984100341797</v>
       </c>
       <c r="C51" t="n">
-        <v>151.5417635314571</v>
+        <v>151.5417788756405</v>
       </c>
       <c r="D51" t="n">
-        <v>142.2296266133646</v>
+        <v>142.2296410146585</v>
       </c>
       <c r="E51" t="n">
-        <v>145.8402743850054</v>
+        <v>145.8402891518912</v>
       </c>
       <c r="F51" t="n">
         <v>314440</v>
@@ -1452,16 +1452,16 @@
         <v>44546</v>
       </c>
       <c r="B52" t="n">
-        <v>145.72607421875</v>
+        <v>145.7260894775391</v>
       </c>
       <c r="C52" t="n">
-        <v>152.8595139117323</v>
+        <v>152.8595299174546</v>
       </c>
       <c r="D52" t="n">
-        <v>144.3028903187285</v>
+        <v>144.3029054284978</v>
       </c>
       <c r="E52" t="n">
-        <v>148.115603324704</v>
+        <v>148.1156188336976</v>
       </c>
       <c r="F52" t="n">
         <v>399045</v>
@@ -1472,16 +1472,16 @@
         <v>44547</v>
       </c>
       <c r="B53" t="n">
-        <v>144.9530029296875</v>
+        <v>144.9529876708984</v>
       </c>
       <c r="C53" t="n">
-        <v>147.4128141452304</v>
+        <v>147.4127986275041</v>
       </c>
       <c r="D53" t="n">
-        <v>141.8255342233813</v>
+        <v>141.825519293812</v>
       </c>
       <c r="E53" t="n">
-        <v>144.0744998816288</v>
+        <v>144.0744847153172</v>
       </c>
       <c r="F53" t="n">
         <v>507335</v>
@@ -1572,16 +1572,16 @@
         <v>44557</v>
       </c>
       <c r="B58" t="n">
-        <v>150.0482940673828</v>
+        <v>150.0483093261719</v>
       </c>
       <c r="C58" t="n">
-        <v>153.6940756448505</v>
+        <v>153.6940912743883</v>
       </c>
       <c r="D58" t="n">
-        <v>147.0438158367336</v>
+        <v>147.0438307899898</v>
       </c>
       <c r="E58" t="n">
-        <v>147.0438158367336</v>
+        <v>147.0438307899898</v>
       </c>
       <c r="F58" t="n">
         <v>232495</v>
@@ -1612,16 +1612,16 @@
         <v>44559</v>
       </c>
       <c r="B60" t="n">
-        <v>139.9894714355469</v>
+        <v>139.9894561767578</v>
       </c>
       <c r="C60" t="n">
-        <v>143.1696483018417</v>
+        <v>143.1696326964148</v>
       </c>
       <c r="D60" t="n">
-        <v>138.4169434125109</v>
+        <v>138.4169283251267</v>
       </c>
       <c r="E60" t="n">
-        <v>142.1857291398705</v>
+        <v>142.1857136416904</v>
       </c>
       <c r="F60" t="n">
         <v>277505</v>
@@ -1632,16 +1632,16 @@
         <v>44560</v>
       </c>
       <c r="B61" t="n">
-        <v>140.9909362792969</v>
+        <v>140.9909515380859</v>
       </c>
       <c r="C61" t="n">
-        <v>141.2632700355088</v>
+        <v>141.2632853237713</v>
       </c>
       <c r="D61" t="n">
-        <v>136.7126180096394</v>
+        <v>136.7126328054061</v>
       </c>
       <c r="E61" t="n">
-        <v>140.0333579235674</v>
+        <v>140.0333730787222</v>
       </c>
       <c r="F61" t="n">
         <v>445854</v>
@@ -1652,16 +1652,16 @@
         <v>44564</v>
       </c>
       <c r="B62" t="n">
-        <v>144.8124389648438</v>
+        <v>144.8124237060547</v>
       </c>
       <c r="C62" t="n">
-        <v>144.8124389648438</v>
+        <v>144.8124237060547</v>
       </c>
       <c r="D62" t="n">
-        <v>138.7947011393807</v>
+        <v>138.7946865146767</v>
       </c>
       <c r="E62" t="n">
-        <v>142.1769298253991</v>
+        <v>142.1769148443119</v>
       </c>
       <c r="F62" t="n">
         <v>369633</v>
@@ -1672,16 +1672,16 @@
         <v>44565</v>
       </c>
       <c r="B63" t="n">
-        <v>140.2969360351562</v>
+        <v>140.2969207763672</v>
       </c>
       <c r="C63" t="n">
-        <v>146.4991654954824</v>
+        <v>146.4991495621347</v>
       </c>
       <c r="D63" t="n">
-        <v>138.662919806963</v>
+        <v>138.6629047258906</v>
       </c>
       <c r="E63" t="n">
-        <v>144.8124412284592</v>
+        <v>144.8124254785607</v>
       </c>
       <c r="F63" t="n">
         <v>382138</v>
@@ -1692,16 +1692,16 @@
         <v>44566</v>
       </c>
       <c r="B64" t="n">
-        <v>134.8502044677734</v>
+        <v>134.8502349853516</v>
       </c>
       <c r="C64" t="n">
-        <v>142.2296239757146</v>
+        <v>142.2296561633088</v>
       </c>
       <c r="D64" t="n">
-        <v>133.1019787502154</v>
+        <v>133.1020088721573</v>
       </c>
       <c r="E64" t="n">
-        <v>140.2969201431482</v>
+        <v>140.2969518933576</v>
       </c>
       <c r="F64" t="n">
         <v>1366948</v>
@@ -1732,16 +1732,16 @@
         <v>44568</v>
       </c>
       <c r="B66" t="n">
-        <v>137.2397308349609</v>
+        <v>137.23974609375</v>
       </c>
       <c r="C66" t="n">
-        <v>142.1857066938723</v>
+        <v>142.1857225025721</v>
       </c>
       <c r="D66" t="n">
-        <v>134.2001047538714</v>
+        <v>134.2001196747043</v>
       </c>
       <c r="E66" t="n">
-        <v>137.9249620581452</v>
+        <v>137.9249773931206</v>
       </c>
       <c r="F66" t="n">
         <v>686988</v>
@@ -1752,16 +1752,16 @@
         <v>44571</v>
       </c>
       <c r="B67" t="n">
-        <v>137.5208740234375</v>
+        <v>137.5208435058594</v>
       </c>
       <c r="C67" t="n">
-        <v>138.4696590120894</v>
+        <v>138.4696282839642</v>
       </c>
       <c r="D67" t="n">
-        <v>131.9072395609175</v>
+        <v>131.9072102890741</v>
       </c>
       <c r="E67" t="n">
-        <v>137.2309797869466</v>
+        <v>137.2309493336996</v>
       </c>
       <c r="F67" t="n">
         <v>730000</v>
@@ -1792,16 +1792,16 @@
         <v>44573</v>
       </c>
       <c r="B69" t="n">
-        <v>149.442138671875</v>
+        <v>149.4421539306641</v>
       </c>
       <c r="C69" t="n">
-        <v>150.7950273285929</v>
+        <v>150.7950427255186</v>
       </c>
       <c r="D69" t="n">
-        <v>145.5591572073933</v>
+        <v>145.5591720697106</v>
       </c>
       <c r="E69" t="n">
-        <v>146.4464403689174</v>
+        <v>146.4464553218307</v>
       </c>
       <c r="F69" t="n">
         <v>416574</v>
@@ -1812,16 +1812,16 @@
         <v>44574</v>
       </c>
       <c r="B70" t="n">
-        <v>142.9675903320312</v>
+        <v>142.9675750732422</v>
       </c>
       <c r="C70" t="n">
-        <v>149.6529990389454</v>
+        <v>149.6529830666293</v>
       </c>
       <c r="D70" t="n">
-        <v>141.7201176170415</v>
+        <v>141.7201024913939</v>
       </c>
       <c r="E70" t="n">
-        <v>149.4860813156558</v>
+        <v>149.4860653611546</v>
       </c>
       <c r="F70" t="n">
         <v>401557</v>
@@ -1892,16 +1892,16 @@
         <v>44580</v>
       </c>
       <c r="B74" t="n">
-        <v>139.6116790771484</v>
+        <v>139.6116943359375</v>
       </c>
       <c r="C74" t="n">
-        <v>141.6937266578653</v>
+        <v>141.6937421442108</v>
       </c>
       <c r="D74" t="n">
-        <v>133.0492613503245</v>
+        <v>133.0492758918774</v>
       </c>
       <c r="E74" t="n">
-        <v>133.5324406256718</v>
+        <v>133.5324552200335</v>
       </c>
       <c r="F74" t="n">
         <v>381153</v>
@@ -1912,16 +1912,16 @@
         <v>44581</v>
       </c>
       <c r="B75" t="n">
-        <v>145.2868347167969</v>
+        <v>145.2868194580078</v>
       </c>
       <c r="C75" t="n">
-        <v>149.2488785379507</v>
+        <v>149.2488628630469</v>
       </c>
       <c r="D75" t="n">
-        <v>138.1094666035888</v>
+        <v>138.1094520986048</v>
       </c>
       <c r="E75" t="n">
-        <v>138.1094666035888</v>
+        <v>138.1094520986048</v>
       </c>
       <c r="F75" t="n">
         <v>666913</v>
@@ -1932,16 +1932,16 @@
         <v>44582</v>
       </c>
       <c r="B76" t="n">
-        <v>143.1871948242188</v>
+        <v>143.1872100830078</v>
       </c>
       <c r="C76" t="n">
-        <v>145.5679302151781</v>
+        <v>145.567945727671</v>
       </c>
       <c r="D76" t="n">
-        <v>140.3320603528095</v>
+        <v>140.3320753073403</v>
       </c>
       <c r="E76" t="n">
-        <v>145.3043766599161</v>
+        <v>145.3043921443233</v>
       </c>
       <c r="F76" t="n">
         <v>292243</v>
@@ -1972,16 +1972,16 @@
         <v>44586</v>
       </c>
       <c r="B78" t="n">
-        <v>147.3161773681641</v>
+        <v>147.316162109375</v>
       </c>
       <c r="C78" t="n">
-        <v>149.5212151794752</v>
+        <v>149.5211996922916</v>
       </c>
       <c r="D78" t="n">
-        <v>140.1651631371207</v>
+        <v>140.165148619023</v>
       </c>
       <c r="E78" t="n">
-        <v>140.1651631371207</v>
+        <v>140.165148619023</v>
       </c>
       <c r="F78" t="n">
         <v>456302</v>
@@ -1992,16 +1992,16 @@
         <v>44587</v>
       </c>
       <c r="B79" t="n">
-        <v>151.7789764404297</v>
+        <v>151.7789611816406</v>
       </c>
       <c r="C79" t="n">
-        <v>157.1466306382445</v>
+        <v>157.1466148398293</v>
       </c>
       <c r="D79" t="n">
-        <v>148.2122561848568</v>
+        <v>148.2122412846406</v>
       </c>
       <c r="E79" t="n">
-        <v>148.5987862686278</v>
+        <v>148.5987713295526</v>
       </c>
       <c r="F79" t="n">
         <v>671208</v>
@@ -2072,16 +2072,16 @@
         <v>44593</v>
       </c>
       <c r="B83" t="n">
-        <v>155.5828857421875</v>
+        <v>155.5829010009766</v>
       </c>
       <c r="C83" t="n">
-        <v>157.3574521401745</v>
+        <v>157.3574675730041</v>
       </c>
       <c r="D83" t="n">
-        <v>151.1200889199835</v>
+        <v>151.1201037410838</v>
       </c>
       <c r="E83" t="n">
-        <v>152.4378434121932</v>
+        <v>152.4378583625323</v>
       </c>
       <c r="F83" t="n">
         <v>577815</v>
@@ -2112,16 +2112,16 @@
         <v>44595</v>
       </c>
       <c r="B85" t="n">
-        <v>146.2707366943359</v>
+        <v>146.270751953125</v>
       </c>
       <c r="C85" t="n">
-        <v>149.960446290332</v>
+        <v>149.9604619340272</v>
       </c>
       <c r="D85" t="n">
-        <v>145.5415776595851</v>
+        <v>145.5415928423091</v>
       </c>
       <c r="E85" t="n">
-        <v>149.2137268486408</v>
+        <v>149.2137424144391</v>
       </c>
       <c r="F85" t="n">
         <v>228387</v>
@@ -2132,16 +2132,16 @@
         <v>44596</v>
       </c>
       <c r="B86" t="n">
-        <v>149.6002655029297</v>
+        <v>149.6002807617188</v>
       </c>
       <c r="C86" t="n">
-        <v>151.0058756228975</v>
+        <v>151.0058910250547</v>
       </c>
       <c r="D86" t="n">
-        <v>143.5825281756291</v>
+        <v>143.5825428206266</v>
       </c>
       <c r="E86" t="n">
-        <v>149.3455055386924</v>
+        <v>149.3455207714968</v>
       </c>
       <c r="F86" t="n">
         <v>455710</v>
@@ -2152,16 +2152,16 @@
         <v>44599</v>
       </c>
       <c r="B87" t="n">
-        <v>147.1229095458984</v>
+        <v>147.1228942871094</v>
       </c>
       <c r="C87" t="n">
-        <v>152.1830823806577</v>
+        <v>152.183066597055</v>
       </c>
       <c r="D87" t="n">
-        <v>146.7100120324576</v>
+        <v>146.709996816492</v>
       </c>
       <c r="E87" t="n">
-        <v>149.5651469971611</v>
+        <v>149.5651314850764</v>
       </c>
       <c r="F87" t="n">
         <v>353300</v>
@@ -2192,16 +2192,16 @@
         <v>44601</v>
       </c>
       <c r="B89" t="n">
-        <v>157.5156097412109</v>
+        <v>157.5155944824219</v>
       </c>
       <c r="C89" t="n">
-        <v>159.7997097761142</v>
+        <v>159.7996942960607</v>
       </c>
       <c r="D89" t="n">
-        <v>151.4275762401174</v>
+        <v>151.4275615710859</v>
       </c>
       <c r="E89" t="n">
-        <v>153.7380437007286</v>
+        <v>153.7380288078784</v>
       </c>
       <c r="F89" t="n">
         <v>1361639</v>
@@ -2272,16 +2272,16 @@
         <v>44607</v>
       </c>
       <c r="B93" t="n">
-        <v>161.143798828125</v>
+        <v>161.1438140869141</v>
       </c>
       <c r="C93" t="n">
-        <v>161.8202498913792</v>
+        <v>161.8202652142218</v>
       </c>
       <c r="D93" t="n">
-        <v>154.6253081778255</v>
+        <v>154.6253228193754</v>
       </c>
       <c r="E93" t="n">
-        <v>156.2768981071088</v>
+        <v>156.2769129050486</v>
       </c>
       <c r="F93" t="n">
         <v>501987</v>
@@ -2292,16 +2292,16 @@
         <v>44608</v>
       </c>
       <c r="B94" t="n">
-        <v>160.8099670410156</v>
+        <v>160.8099975585938</v>
       </c>
       <c r="C94" t="n">
-        <v>164.6841682523319</v>
+        <v>164.6841995051333</v>
       </c>
       <c r="D94" t="n">
-        <v>158.0690287325549</v>
+        <v>158.0690587299737</v>
       </c>
       <c r="E94" t="n">
-        <v>161.1437890453663</v>
+        <v>161.1438196262952</v>
       </c>
       <c r="F94" t="n">
         <v>383335</v>
@@ -2372,16 +2372,16 @@
         <v>44614</v>
       </c>
       <c r="B98" t="n">
-        <v>150.3557739257812</v>
+        <v>150.3557891845703</v>
       </c>
       <c r="C98" t="n">
-        <v>155.0557700513334</v>
+        <v>155.0557857870995</v>
       </c>
       <c r="D98" t="n">
-        <v>149.6793363085237</v>
+        <v>149.6793514986648</v>
       </c>
       <c r="E98" t="n">
-        <v>150.5314852389875</v>
+        <v>150.5315005156085</v>
       </c>
       <c r="F98" t="n">
         <v>352471</v>
@@ -2412,16 +2412,16 @@
         <v>44616</v>
       </c>
       <c r="B100" t="n">
-        <v>148.1068267822266</v>
+        <v>148.1068115234375</v>
       </c>
       <c r="C100" t="n">
-        <v>148.1068267822266</v>
+        <v>148.1068115234375</v>
       </c>
       <c r="D100" t="n">
-        <v>139.2427341770273</v>
+        <v>139.2427198314664</v>
       </c>
       <c r="E100" t="n">
-        <v>143.3277680196328</v>
+        <v>143.327753253209</v>
       </c>
       <c r="F100" t="n">
         <v>704723</v>
@@ -2472,16 +2472,16 @@
         <v>44623</v>
       </c>
       <c r="B103" t="n">
-        <v>136.1679534912109</v>
+        <v>136.16796875</v>
       </c>
       <c r="C103" t="n">
-        <v>143.3365405825027</v>
+        <v>143.3365566445935</v>
       </c>
       <c r="D103" t="n">
-        <v>135.4915024850142</v>
+        <v>135.4915176680011</v>
       </c>
       <c r="E103" t="n">
-        <v>142.5107456875154</v>
+        <v>142.5107616570688</v>
       </c>
       <c r="F103" t="n">
         <v>801826</v>
@@ -2492,16 +2492,16 @@
         <v>44624</v>
       </c>
       <c r="B104" t="n">
-        <v>129.4035034179688</v>
+        <v>129.4034881591797</v>
       </c>
       <c r="C104" t="n">
-        <v>139.216380989505</v>
+        <v>139.2163645736173</v>
       </c>
       <c r="D104" t="n">
-        <v>128.5864886016308</v>
+        <v>128.5864734391812</v>
       </c>
       <c r="E104" t="n">
-        <v>134.2440504527695</v>
+        <v>134.2440346232008</v>
       </c>
       <c r="F104" t="n">
         <v>615045</v>
@@ -2552,16 +2552,16 @@
         <v>44629</v>
       </c>
       <c r="B107" t="n">
-        <v>138.6804962158203</v>
+        <v>138.6804809570312</v>
       </c>
       <c r="C107" t="n">
-        <v>138.6804962158203</v>
+        <v>138.6804809570312</v>
       </c>
       <c r="D107" t="n">
-        <v>124.6595812143682</v>
+        <v>124.6595674982775</v>
       </c>
       <c r="E107" t="n">
-        <v>124.7474368839902</v>
+        <v>124.7474231582329</v>
       </c>
       <c r="F107" t="n">
         <v>891534</v>
@@ -2572,16 +2572,16 @@
         <v>44630</v>
       </c>
       <c r="B108" t="n">
-        <v>135.7814178466797</v>
+        <v>135.7814025878906</v>
       </c>
       <c r="C108" t="n">
-        <v>139.163659666757</v>
+        <v>139.1636440278797</v>
       </c>
       <c r="D108" t="n">
-        <v>133.2425447818445</v>
+        <v>133.2425298083679</v>
       </c>
       <c r="E108" t="n">
-        <v>137.4857157651647</v>
+        <v>137.4857003148507</v>
       </c>
       <c r="F108" t="n">
         <v>543810</v>
@@ -2592,16 +2592,16 @@
         <v>44631</v>
       </c>
       <c r="B109" t="n">
-        <v>131.6173248291016</v>
+        <v>131.6173400878906</v>
       </c>
       <c r="C109" t="n">
-        <v>138.7156172153465</v>
+        <v>138.7156332970618</v>
       </c>
       <c r="D109" t="n">
-        <v>131.1341455020338</v>
+        <v>131.1341607048064</v>
       </c>
       <c r="E109" t="n">
-        <v>135.8077744536639</v>
+        <v>135.8077901982643</v>
       </c>
       <c r="F109" t="n">
         <v>422012</v>
@@ -2612,16 +2612,16 @@
         <v>44634</v>
       </c>
       <c r="B110" t="n">
-        <v>126.6801223754883</v>
+        <v>126.6801376342773</v>
       </c>
       <c r="C110" t="n">
-        <v>133.8311358334649</v>
+        <v>133.831151953603</v>
       </c>
       <c r="D110" t="n">
-        <v>126.6801223754883</v>
+        <v>126.6801376342773</v>
       </c>
       <c r="E110" t="n">
-        <v>131.6173180568153</v>
+        <v>131.6173339102961</v>
       </c>
       <c r="F110" t="n">
         <v>265850</v>
@@ -2652,16 +2652,16 @@
         <v>44636</v>
       </c>
       <c r="B112" t="n">
-        <v>139.4887084960938</v>
+        <v>139.4886932373047</v>
       </c>
       <c r="C112" t="n">
-        <v>142.3438433121762</v>
+        <v>142.3438277410615</v>
       </c>
       <c r="D112" t="n">
-        <v>132.6539560702938</v>
+        <v>132.6539415591642</v>
       </c>
       <c r="E112" t="n">
-        <v>132.6539560702938</v>
+        <v>132.6539415591642</v>
       </c>
       <c r="F112" t="n">
         <v>861619</v>
@@ -2692,16 +2692,16 @@
         <v>44638</v>
       </c>
       <c r="B114" t="n">
-        <v>142.3174896240234</v>
+        <v>142.3174743652344</v>
       </c>
       <c r="C114" t="n">
-        <v>145.1199164101681</v>
+        <v>145.1199008509126</v>
       </c>
       <c r="D114" t="n">
-        <v>137.1518875629193</v>
+        <v>137.1518728579682</v>
       </c>
       <c r="E114" t="n">
-        <v>138.618986001691</v>
+        <v>138.6189711394427</v>
       </c>
       <c r="F114" t="n">
         <v>570545</v>
@@ -2752,16 +2752,16 @@
         <v>44643</v>
       </c>
       <c r="B117" t="n">
-        <v>132.7418060302734</v>
+        <v>132.7418212890625</v>
       </c>
       <c r="C117" t="n">
-        <v>137.4417889441584</v>
+        <v>137.4418047432147</v>
       </c>
       <c r="D117" t="n">
-        <v>130.5719025909017</v>
+        <v>130.5719176002584</v>
       </c>
       <c r="E117" t="n">
-        <v>134.5075921995046</v>
+        <v>134.5076076612723</v>
       </c>
       <c r="F117" t="n">
         <v>1133860</v>
@@ -2792,16 +2792,16 @@
         <v>44645</v>
       </c>
       <c r="B119" t="n">
-        <v>133.9277496337891</v>
+        <v>133.9277801513672</v>
       </c>
       <c r="C119" t="n">
-        <v>140.0333414335435</v>
+        <v>140.0333733423783</v>
       </c>
       <c r="D119" t="n">
-        <v>133.4182163994722</v>
+        <v>133.418246800945</v>
       </c>
       <c r="E119" t="n">
-        <v>135.3070054688192</v>
+        <v>135.3070363006828</v>
       </c>
       <c r="F119" t="n">
         <v>403765</v>
@@ -2872,16 +2872,16 @@
         <v>44651</v>
       </c>
       <c r="B123" t="n">
-        <v>126.065185546875</v>
+        <v>126.0651779174805</v>
       </c>
       <c r="C123" t="n">
-        <v>132.170778960327</v>
+        <v>132.1707709614254</v>
       </c>
       <c r="D123" t="n">
-        <v>123.4736042741024</v>
+        <v>123.4735968015489</v>
       </c>
       <c r="E123" t="n">
-        <v>131.6788194054147</v>
+        <v>131.6788114362862</v>
       </c>
       <c r="F123" t="n">
         <v>791956</v>
@@ -2892,16 +2892,16 @@
         <v>44652</v>
       </c>
       <c r="B124" t="n">
-        <v>127.382926940918</v>
+        <v>127.3829345703125</v>
       </c>
       <c r="C124" t="n">
-        <v>129.1047986101335</v>
+        <v>129.1048063426568</v>
       </c>
       <c r="D124" t="n">
-        <v>124.615648027951</v>
+        <v>124.6156554916039</v>
       </c>
       <c r="E124" t="n">
-        <v>126.5044239964978</v>
+        <v>126.5044315732759</v>
       </c>
       <c r="F124" t="n">
         <v>526406</v>
@@ -2912,16 +2912,16 @@
         <v>44655</v>
       </c>
       <c r="B125" t="n">
-        <v>129.0872344970703</v>
+        <v>129.0872192382812</v>
       </c>
       <c r="C125" t="n">
-        <v>129.0872344970703</v>
+        <v>129.0872192382812</v>
       </c>
       <c r="D125" t="n">
-        <v>125.6347106955444</v>
+        <v>125.6346958448618</v>
       </c>
       <c r="E125" t="n">
-        <v>127.3829365120573</v>
+        <v>127.3829214547252</v>
       </c>
       <c r="F125" t="n">
         <v>325077</v>
@@ -2932,16 +2932,16 @@
         <v>44656</v>
       </c>
       <c r="B126" t="n">
-        <v>128.0769348144531</v>
+        <v>128.0769653320312</v>
       </c>
       <c r="C126" t="n">
-        <v>130.1589958502732</v>
+        <v>130.1590268639552</v>
       </c>
       <c r="D126" t="n">
-        <v>125.6346977691337</v>
+        <v>125.6347277047869</v>
       </c>
       <c r="E126" t="n">
-        <v>128.2614263258134</v>
+        <v>128.2614568873513</v>
       </c>
       <c r="F126" t="n">
         <v>767000</v>
@@ -2952,16 +2952,16 @@
         <v>44657</v>
       </c>
       <c r="B127" t="n">
-        <v>125.0197601318359</v>
+        <v>125.0197525024414</v>
       </c>
       <c r="C127" t="n">
-        <v>127.3829353531706</v>
+        <v>127.3829275795621</v>
       </c>
       <c r="D127" t="n">
-        <v>122.6917325373382</v>
+        <v>122.6917250500128</v>
       </c>
       <c r="E127" t="n">
-        <v>127.1720898068249</v>
+        <v>127.1720820460833</v>
       </c>
       <c r="F127" t="n">
         <v>694358</v>
@@ -2972,16 +2972,16 @@
         <v>44658</v>
       </c>
       <c r="B128" t="n">
-        <v>126.9524536132812</v>
+        <v>126.9524688720703</v>
       </c>
       <c r="C128" t="n">
-        <v>128.6040434115682</v>
+        <v>128.6040588688667</v>
       </c>
       <c r="D128" t="n">
-        <v>122.9991904275108</v>
+        <v>122.9992052111455</v>
       </c>
       <c r="E128" t="n">
-        <v>124.7561962878532</v>
+        <v>124.7562112826676</v>
       </c>
       <c r="F128" t="n">
         <v>544395</v>
@@ -2992,16 +2992,16 @@
         <v>44659</v>
       </c>
       <c r="B129" t="n">
-        <v>123.5790176391602</v>
+        <v>123.5790100097656</v>
       </c>
       <c r="C129" t="n">
-        <v>128.0857424003326</v>
+        <v>128.0857344927065</v>
       </c>
       <c r="D129" t="n">
-        <v>123.5790176391602</v>
+        <v>123.5790100097656</v>
       </c>
       <c r="E129" t="n">
-        <v>126.7943418945568</v>
+        <v>126.7943340666578</v>
       </c>
       <c r="F129" t="n">
         <v>403536</v>
@@ -3012,16 +3012,16 @@
         <v>44662</v>
       </c>
       <c r="B130" t="n">
-        <v>121.8659286499023</v>
+        <v>121.8659210205078</v>
       </c>
       <c r="C130" t="n">
-        <v>123.5702264946588</v>
+        <v>123.570218758567</v>
       </c>
       <c r="D130" t="n">
-        <v>119.362189914273</v>
+        <v>119.3621824416246</v>
       </c>
       <c r="E130" t="n">
-        <v>122.9904113383186</v>
+        <v>122.990403638526</v>
       </c>
       <c r="F130" t="n">
         <v>348006</v>
@@ -3032,16 +3032,16 @@
         <v>44663</v>
       </c>
       <c r="B131" t="n">
-        <v>118.2025909423828</v>
+        <v>118.2025756835938</v>
       </c>
       <c r="C131" t="n">
-        <v>125.1691138645034</v>
+        <v>125.1690977064049</v>
       </c>
       <c r="D131" t="n">
-        <v>118.1762369226312</v>
+        <v>118.1762216672442</v>
       </c>
       <c r="E131" t="n">
-        <v>122.9904300007179</v>
+        <v>122.990414123866</v>
       </c>
       <c r="F131" t="n">
         <v>576598</v>
@@ -3052,16 +3052,16 @@
         <v>44664</v>
       </c>
       <c r="B132" t="n">
-        <v>119.7750930786133</v>
+        <v>119.7751007080078</v>
       </c>
       <c r="C132" t="n">
-        <v>120.7941597526093</v>
+        <v>120.794167446916</v>
       </c>
       <c r="D132" t="n">
-        <v>117.7545335435913</v>
+        <v>117.7545410442809</v>
       </c>
       <c r="E132" t="n">
-        <v>118.8351018605366</v>
+        <v>118.8351094300559</v>
       </c>
       <c r="F132" t="n">
         <v>714435</v>
@@ -3072,16 +3072,16 @@
         <v>44665</v>
       </c>
       <c r="B133" t="n">
-        <v>115.6022109985352</v>
+        <v>115.6022033691406</v>
       </c>
       <c r="C133" t="n">
-        <v>120.003519776927</v>
+        <v>120.0035118570594</v>
       </c>
       <c r="D133" t="n">
-        <v>114.7061475555975</v>
+        <v>114.7061399853404</v>
       </c>
       <c r="E133" t="n">
-        <v>119.7751004090118</v>
+        <v>119.7750925042192</v>
       </c>
       <c r="F133" t="n">
         <v>497156</v>
@@ -3112,16 +3112,16 @@
         <v>44670</v>
       </c>
       <c r="B135" t="n">
-        <v>115.2683792114258</v>
+        <v>115.2683868408203</v>
       </c>
       <c r="C135" t="n">
-        <v>116.3137864730974</v>
+        <v>116.3137941716854</v>
       </c>
       <c r="D135" t="n">
-        <v>111.1306243741263</v>
+        <v>111.1306317296507</v>
       </c>
       <c r="E135" t="n">
-        <v>112.5362344712496</v>
+        <v>112.5362419198087</v>
       </c>
       <c r="F135" t="n">
         <v>794893</v>
@@ -3172,16 +3172,16 @@
         <v>44676</v>
       </c>
       <c r="B138" t="n">
-        <v>111.5347366333008</v>
+        <v>111.5347442626953</v>
       </c>
       <c r="C138" t="n">
-        <v>111.8334311293538</v>
+        <v>111.8334387791802</v>
       </c>
       <c r="D138" t="n">
-        <v>105.9474571895508</v>
+        <v>105.9474644367544</v>
       </c>
       <c r="E138" t="n">
-        <v>106.2988597191943</v>
+        <v>106.2988669904352</v>
       </c>
       <c r="F138" t="n">
         <v>607459</v>
@@ -3192,16 +3192,16 @@
         <v>44677</v>
       </c>
       <c r="B139" t="n">
-        <v>107.4057693481445</v>
+        <v>107.4057769775391</v>
       </c>
       <c r="C139" t="n">
-        <v>112.6943540007223</v>
+        <v>112.6943620057829</v>
       </c>
       <c r="D139" t="n">
-        <v>106.342781614564</v>
+        <v>106.342789168451</v>
       </c>
       <c r="E139" t="n">
-        <v>109.9270684500656</v>
+        <v>109.9270762585565</v>
       </c>
       <c r="F139" t="n">
         <v>615417</v>
@@ -3252,16 +3252,16 @@
         <v>44680</v>
       </c>
       <c r="B142" t="n">
-        <v>107.6341857910156</v>
+        <v>107.6341781616211</v>
       </c>
       <c r="C142" t="n">
-        <v>112.0969826885324</v>
+        <v>112.0969747428031</v>
       </c>
       <c r="D142" t="n">
-        <v>107.1773671750833</v>
+        <v>107.1773595780693</v>
       </c>
       <c r="E142" t="n">
-        <v>108.1173651272915</v>
+        <v>108.117357463648</v>
       </c>
       <c r="F142" t="n">
         <v>762051</v>
@@ -3272,16 +3272,16 @@
         <v>44683</v>
       </c>
       <c r="B143" t="n">
-        <v>107.168571472168</v>
+        <v>107.1685791015625</v>
       </c>
       <c r="C143" t="n">
-        <v>108.5566077220467</v>
+        <v>108.5566154502563</v>
       </c>
       <c r="D143" t="n">
-        <v>104.4627875184451</v>
+        <v>104.4627949552132</v>
       </c>
       <c r="E143" t="n">
-        <v>107.186145284288</v>
+        <v>107.1861529149336</v>
       </c>
       <c r="F143" t="n">
         <v>497573</v>
@@ -3292,16 +3292,16 @@
         <v>44684</v>
       </c>
       <c r="B144" t="n">
-        <v>102.7848587036133</v>
+        <v>102.7848434448242</v>
       </c>
       <c r="C144" t="n">
-        <v>107.1773740328275</v>
+        <v>107.1773581219535</v>
       </c>
       <c r="D144" t="n">
-        <v>101.809719764332</v>
+        <v>101.8097046503059</v>
       </c>
       <c r="E144" t="n">
-        <v>107.1422331059002</v>
+        <v>107.142217200243</v>
       </c>
       <c r="F144" t="n">
         <v>541792</v>
@@ -3312,16 +3312,16 @@
         <v>44685</v>
       </c>
       <c r="B145" t="n">
-        <v>94.52692413330078</v>
+        <v>94.52690887451172</v>
       </c>
       <c r="C145" t="n">
-        <v>100.4128984212591</v>
+        <v>100.4128822123403</v>
       </c>
       <c r="D145" t="n">
-        <v>84.54712923481648</v>
+        <v>84.54711558699262</v>
       </c>
       <c r="E145" t="n">
-        <v>100.4128984212591</v>
+        <v>100.4128822123403</v>
       </c>
       <c r="F145" t="n">
         <v>3193940</v>
@@ -3332,16 +3332,16 @@
         <v>44686</v>
       </c>
       <c r="B146" t="n">
-        <v>93.73625946044922</v>
+        <v>93.73626708984375</v>
       </c>
       <c r="C146" t="n">
-        <v>95.51083912315028</v>
+        <v>95.51084689698163</v>
       </c>
       <c r="D146" t="n">
-        <v>91.46094010080674</v>
+        <v>91.46094754500817</v>
       </c>
       <c r="E146" t="n">
-        <v>94.43906448175674</v>
+        <v>94.43907216835407</v>
       </c>
       <c r="F146" t="n">
         <v>1265698</v>
@@ -3352,16 +3352,16 @@
         <v>44687</v>
       </c>
       <c r="B147" t="n">
-        <v>90.31011962890625</v>
+        <v>90.31010437011719</v>
       </c>
       <c r="C147" t="n">
-        <v>95.44057441733399</v>
+        <v>95.44055829170378</v>
       </c>
       <c r="D147" t="n">
-        <v>90.31011962890625</v>
+        <v>90.31010437011719</v>
       </c>
       <c r="E147" t="n">
-        <v>93.73627629123804</v>
+        <v>93.73626045356588</v>
       </c>
       <c r="F147" t="n">
         <v>602571</v>
@@ -3412,16 +3412,16 @@
         <v>44692</v>
       </c>
       <c r="B150" t="n">
-        <v>81.85890960693359</v>
+        <v>81.85891723632812</v>
       </c>
       <c r="C150" t="n">
-        <v>86.58525332243828</v>
+        <v>86.58526139233636</v>
       </c>
       <c r="D150" t="n">
-        <v>81.52508088063452</v>
+        <v>81.52508847891562</v>
       </c>
       <c r="E150" t="n">
-        <v>84.51198571133756</v>
+        <v>84.51199358800345</v>
       </c>
       <c r="F150" t="n">
         <v>624829</v>
@@ -3432,16 +3432,16 @@
         <v>44693</v>
       </c>
       <c r="B151" t="n">
-        <v>89.44917297363281</v>
+        <v>89.44918060302734</v>
       </c>
       <c r="C151" t="n">
-        <v>96.8110255181841</v>
+        <v>96.81103377549363</v>
       </c>
       <c r="D151" t="n">
-        <v>80.67293009796164</v>
+        <v>80.67293697880346</v>
       </c>
       <c r="E151" t="n">
-        <v>80.98040479984731</v>
+        <v>80.98041170691459</v>
       </c>
       <c r="F151" t="n">
         <v>2304224</v>
@@ -3452,16 +3452,16 @@
         <v>44694</v>
       </c>
       <c r="B152" t="n">
-        <v>89.78299713134766</v>
+        <v>89.78300476074219</v>
       </c>
       <c r="C152" t="n">
-        <v>92.42729283812145</v>
+        <v>92.42730069221749</v>
       </c>
       <c r="D152" t="n">
-        <v>87.90300138967268</v>
+        <v>87.90300885931281</v>
       </c>
       <c r="E152" t="n">
-        <v>90.57365111206272</v>
+        <v>90.57365880864381</v>
       </c>
       <c r="F152" t="n">
         <v>780406</v>
@@ -3492,16 +3492,16 @@
         <v>44698</v>
       </c>
       <c r="B154" t="n">
-        <v>86.98058319091797</v>
+        <v>86.9805908203125</v>
       </c>
       <c r="C154" t="n">
-        <v>88.24562294284463</v>
+        <v>88.24563068320056</v>
       </c>
       <c r="D154" t="n">
-        <v>84.59105397819015</v>
+        <v>84.59106139799007</v>
       </c>
       <c r="E154" t="n">
-        <v>85.39048821633966</v>
+        <v>85.39049570626096</v>
       </c>
       <c r="F154" t="n">
         <v>1257850</v>
@@ -3512,16 +3512,16 @@
         <v>44699</v>
       </c>
       <c r="B155" t="n">
-        <v>84.09909820556641</v>
+        <v>84.09909057617188</v>
       </c>
       <c r="C155" t="n">
-        <v>87.19142592924517</v>
+        <v>87.19141801931744</v>
       </c>
       <c r="D155" t="n">
-        <v>83.82675770797285</v>
+        <v>83.82675010328479</v>
       </c>
       <c r="E155" t="n">
-        <v>86.83123646893756</v>
+        <v>86.83122859168591</v>
       </c>
       <c r="F155" t="n">
         <v>617555</v>
@@ -3532,16 +3532,16 @@
         <v>44700</v>
       </c>
       <c r="B156" t="n">
-        <v>89.6072998046875</v>
+        <v>89.60730743408203</v>
       </c>
       <c r="C156" t="n">
-        <v>90.45066182208521</v>
+        <v>90.45066952328574</v>
       </c>
       <c r="D156" t="n">
-        <v>82.86039696306027</v>
+        <v>82.86040401800625</v>
       </c>
       <c r="E156" t="n">
-        <v>83.85310287154553</v>
+        <v>83.85311001101303</v>
       </c>
       <c r="F156" t="n">
         <v>889253</v>
@@ -3572,16 +3572,16 @@
         <v>44704</v>
       </c>
       <c r="B158" t="n">
-        <v>91.02169799804688</v>
+        <v>91.02169036865234</v>
       </c>
       <c r="C158" t="n">
-        <v>92.67328125477616</v>
+        <v>92.67327348694673</v>
       </c>
       <c r="D158" t="n">
-        <v>90.09926715053099</v>
+        <v>90.09925959845417</v>
       </c>
       <c r="E158" t="n">
-        <v>90.31011270007218</v>
+        <v>90.31010513032238</v>
       </c>
       <c r="F158" t="n">
         <v>925415</v>
@@ -3592,16 +3592,16 @@
         <v>44705</v>
       </c>
       <c r="B159" t="n">
-        <v>87.67461395263672</v>
+        <v>87.67459869384766</v>
       </c>
       <c r="C159" t="n">
-        <v>90.02021567165795</v>
+        <v>90.02020000464306</v>
       </c>
       <c r="D159" t="n">
-        <v>85.55741821878189</v>
+        <v>85.55740332846713</v>
       </c>
       <c r="E159" t="n">
-        <v>88.43012717113334</v>
+        <v>88.43011178085561</v>
       </c>
       <c r="F159" t="n">
         <v>569845</v>
@@ -3612,16 +3612,16 @@
         <v>44706</v>
       </c>
       <c r="B160" t="n">
-        <v>89.92357635498047</v>
+        <v>89.92356872558594</v>
       </c>
       <c r="C160" t="n">
-        <v>90.73179758493647</v>
+        <v>90.73178988696996</v>
       </c>
       <c r="D160" t="n">
-        <v>85.75068669945851</v>
+        <v>85.75067942410486</v>
       </c>
       <c r="E160" t="n">
-        <v>86.97180545193132</v>
+        <v>86.97179807297417</v>
       </c>
       <c r="F160" t="n">
         <v>958832</v>
@@ -3652,16 +3652,16 @@
         <v>44708</v>
       </c>
       <c r="B162" t="n">
-        <v>96.65290069580078</v>
+        <v>96.65289306640625</v>
       </c>
       <c r="C162" t="n">
-        <v>97.42598765404017</v>
+        <v>97.42597996362124</v>
       </c>
       <c r="D162" t="n">
-        <v>93.57814008175724</v>
+        <v>93.57813269507206</v>
       </c>
       <c r="E162" t="n">
-        <v>94.5708527981426</v>
+        <v>94.57084533309663</v>
       </c>
       <c r="F162" t="n">
         <v>410015</v>
@@ -3692,16 +3692,16 @@
         <v>44712</v>
       </c>
       <c r="B164" t="n">
-        <v>93.95588684082031</v>
+        <v>93.95589447021484</v>
       </c>
       <c r="C164" t="n">
-        <v>98.17270363778388</v>
+        <v>98.17271160959186</v>
       </c>
       <c r="D164" t="n">
-        <v>93.12131172800976</v>
+        <v>93.12131928963522</v>
       </c>
       <c r="E164" t="n">
-        <v>96.72317244492481</v>
+        <v>96.72318029902813</v>
       </c>
       <c r="F164" t="n">
         <v>435642</v>
@@ -3712,16 +3712,16 @@
         <v>44713</v>
       </c>
       <c r="B165" t="n">
-        <v>92.17253875732422</v>
+        <v>92.17253112792969</v>
       </c>
       <c r="C165" t="n">
-        <v>96.28393331547606</v>
+        <v>96.28392534576922</v>
       </c>
       <c r="D165" t="n">
-        <v>91.18861962704793</v>
+        <v>91.18861207909531</v>
       </c>
       <c r="E165" t="n">
-        <v>95.12430955304588</v>
+        <v>95.12430167932452</v>
       </c>
       <c r="F165" t="n">
         <v>372179</v>
@@ -3752,16 +3752,16 @@
         <v>44715</v>
       </c>
       <c r="B167" t="n">
-        <v>94.96616363525391</v>
+        <v>94.96617126464844</v>
       </c>
       <c r="C167" t="n">
-        <v>97.28541079134285</v>
+        <v>97.28541860706112</v>
       </c>
       <c r="D167" t="n">
-        <v>93.93831683476013</v>
+        <v>93.93832438157946</v>
       </c>
       <c r="E167" t="n">
-        <v>96.63532051185686</v>
+        <v>96.63532827534817</v>
       </c>
       <c r="F167" t="n">
         <v>452357</v>
@@ -3772,16 +3772,16 @@
         <v>44718</v>
       </c>
       <c r="B168" t="n">
-        <v>94.98374176025391</v>
+        <v>94.98375701904297</v>
       </c>
       <c r="C168" t="n">
-        <v>97.48747383763394</v>
+        <v>97.48748949863837</v>
       </c>
       <c r="D168" t="n">
-        <v>94.69383417696631</v>
+        <v>94.69384938918279</v>
       </c>
       <c r="E168" t="n">
-        <v>95.18579368622116</v>
+        <v>95.18580897746912</v>
       </c>
       <c r="F168" t="n">
         <v>540320</v>
@@ -3852,16 +3852,16 @@
         <v>44722</v>
       </c>
       <c r="B172" t="n">
-        <v>88.72880554199219</v>
+        <v>88.72879791259766</v>
       </c>
       <c r="C172" t="n">
-        <v>95.2297292687264</v>
+        <v>95.22972108034641</v>
       </c>
       <c r="D172" t="n">
-        <v>88.72880554199219</v>
+        <v>88.72879791259766</v>
       </c>
       <c r="E172" t="n">
-        <v>93.59571310571778</v>
+        <v>93.59570505783955</v>
       </c>
       <c r="F172" t="n">
         <v>588546</v>
@@ -3872,16 +3872,16 @@
         <v>44725</v>
       </c>
       <c r="B173" t="n">
-        <v>85.03909301757812</v>
+        <v>85.03910064697266</v>
       </c>
       <c r="C173" t="n">
-        <v>87.61310707375694</v>
+        <v>87.61311493408253</v>
       </c>
       <c r="D173" t="n">
-        <v>84.30993391953471</v>
+        <v>84.30994148351176</v>
       </c>
       <c r="E173" t="n">
-        <v>87.41104843483134</v>
+        <v>87.41105627702898</v>
       </c>
       <c r="F173" t="n">
         <v>846744</v>
@@ -3892,16 +3892,16 @@
         <v>44726</v>
       </c>
       <c r="B174" t="n">
-        <v>85.73310089111328</v>
+        <v>85.73310852050781</v>
       </c>
       <c r="C174" t="n">
-        <v>86.47104686486708</v>
+        <v>86.47105455993147</v>
       </c>
       <c r="D174" t="n">
-        <v>84.07273082822437</v>
+        <v>84.07273830986246</v>
       </c>
       <c r="E174" t="n">
-        <v>86.10207722921302</v>
+        <v>86.10208489144279</v>
       </c>
       <c r="F174" t="n">
         <v>502449</v>
@@ -4032,16 +4032,16 @@
         <v>44736</v>
       </c>
       <c r="B181" t="n">
-        <v>91.10075378417969</v>
+        <v>91.10076141357422</v>
       </c>
       <c r="C181" t="n">
-        <v>92.33065926209622</v>
+        <v>92.33066699449137</v>
       </c>
       <c r="D181" t="n">
-        <v>89.34374787356913</v>
+        <v>89.34375535582006</v>
       </c>
       <c r="E181" t="n">
-        <v>89.34374787356913</v>
+        <v>89.34375535582006</v>
       </c>
       <c r="F181" t="n">
         <v>487883</v>
@@ -4112,16 +4112,16 @@
         <v>44742</v>
       </c>
       <c r="B185" t="n">
-        <v>82.69348907470703</v>
+        <v>82.6934814453125</v>
       </c>
       <c r="C185" t="n">
-        <v>84.4680689760099</v>
+        <v>84.46806118289064</v>
       </c>
       <c r="D185" t="n">
-        <v>79.82078707143653</v>
+        <v>79.82077970708073</v>
       </c>
       <c r="E185" t="n">
-        <v>82.4914371280648</v>
+        <v>82.49142951731181</v>
       </c>
       <c r="F185" t="n">
         <v>710009</v>
@@ -4132,16 +4132,16 @@
         <v>44743</v>
       </c>
       <c r="B186" t="n">
-        <v>83.40507507324219</v>
+        <v>83.40508270263672</v>
       </c>
       <c r="C186" t="n">
-        <v>85.39048698245399</v>
+        <v>85.39049479346207</v>
       </c>
       <c r="D186" t="n">
-        <v>81.92918979861589</v>
+        <v>81.92919729300532</v>
       </c>
       <c r="E186" t="n">
-        <v>82.6232079571698</v>
+        <v>82.62321551504384</v>
       </c>
       <c r="F186" t="n">
         <v>500037</v>
@@ -4192,16 +4192,16 @@
         <v>44748</v>
       </c>
       <c r="B189" t="n">
-        <v>86.62039184570312</v>
+        <v>86.62039947509766</v>
       </c>
       <c r="C189" t="n">
-        <v>88.46524674954465</v>
+        <v>88.46525454143122</v>
       </c>
       <c r="D189" t="n">
-        <v>84.60861923211571</v>
+        <v>84.60862668431632</v>
       </c>
       <c r="E189" t="n">
-        <v>87.84151044265967</v>
+        <v>87.8415181796085</v>
       </c>
       <c r="F189" t="n">
         <v>788696</v>
@@ -4232,16 +4232,16 @@
         <v>44750</v>
       </c>
       <c r="B191" t="n">
-        <v>85.69796752929688</v>
+        <v>85.69797515869141</v>
       </c>
       <c r="C191" t="n">
-        <v>88.1489849210145</v>
+        <v>88.14899276861466</v>
       </c>
       <c r="D191" t="n">
-        <v>84.96880845454787</v>
+        <v>84.9688160190279</v>
       </c>
       <c r="E191" t="n">
-        <v>86.35684475775652</v>
+        <v>86.35685244580863</v>
       </c>
       <c r="F191" t="n">
         <v>710031</v>
@@ -4272,16 +4272,16 @@
         <v>44754</v>
       </c>
       <c r="B193" t="n">
-        <v>86.32170104980469</v>
+        <v>86.32170867919922</v>
       </c>
       <c r="C193" t="n">
-        <v>86.32170104980469</v>
+        <v>86.32170867919922</v>
       </c>
       <c r="D193" t="n">
-        <v>81.29666314380617</v>
+        <v>81.2966703290714</v>
       </c>
       <c r="E193" t="n">
-        <v>82.6232044643278</v>
+        <v>82.6232117668371</v>
       </c>
       <c r="F193" t="n">
         <v>730233</v>
@@ -4292,16 +4292,16 @@
         <v>44755</v>
       </c>
       <c r="B194" t="n">
-        <v>84.68769073486328</v>
+        <v>84.68769836425781</v>
       </c>
       <c r="C194" t="n">
-        <v>86.91908916427828</v>
+        <v>86.91909699469635</v>
       </c>
       <c r="D194" t="n">
-        <v>83.45778519155122</v>
+        <v>83.4577927101453</v>
       </c>
       <c r="E194" t="n">
-        <v>84.37142911794173</v>
+        <v>84.37143671884469</v>
       </c>
       <c r="F194" t="n">
         <v>1885043</v>
@@ -4312,16 +4312,16 @@
         <v>44756</v>
       </c>
       <c r="B195" t="n">
-        <v>81.44601440429688</v>
+        <v>81.44600677490234</v>
       </c>
       <c r="C195" t="n">
-        <v>85.20600626786458</v>
+        <v>85.20599828625562</v>
       </c>
       <c r="D195" t="n">
-        <v>81.35816544254408</v>
+        <v>81.35815782137873</v>
       </c>
       <c r="E195" t="n">
-        <v>84.33629015235336</v>
+        <v>84.3362822522144</v>
       </c>
       <c r="F195" t="n">
         <v>647308</v>
@@ -4352,16 +4352,16 @@
         <v>44760</v>
       </c>
       <c r="B197" t="n">
-        <v>83.74769592285156</v>
+        <v>83.74768829345703</v>
       </c>
       <c r="C197" t="n">
-        <v>86.46226708342914</v>
+        <v>86.46225920673785</v>
       </c>
       <c r="D197" t="n">
-        <v>82.93947473935722</v>
+        <v>82.93946718359145</v>
       </c>
       <c r="E197" t="n">
-        <v>82.93947473935722</v>
+        <v>82.93946718359145</v>
       </c>
       <c r="F197" t="n">
         <v>494919</v>
@@ -4372,16 +4372,16 @@
         <v>44761</v>
       </c>
       <c r="B198" t="n">
-        <v>86.85758972167969</v>
+        <v>86.85759735107422</v>
       </c>
       <c r="C198" t="n">
-        <v>87.15627750971456</v>
+        <v>87.15628516534521</v>
       </c>
       <c r="D198" t="n">
-        <v>83.45778086715818</v>
+        <v>83.45778819792039</v>
       </c>
       <c r="E198" t="n">
-        <v>83.45778086715818</v>
+        <v>83.45778819792039</v>
       </c>
       <c r="F198" t="n">
         <v>493807</v>
@@ -4432,16 +4432,16 @@
         <v>44764</v>
       </c>
       <c r="B201" t="n">
-        <v>89.78299713134766</v>
+        <v>89.78300476074219</v>
       </c>
       <c r="C201" t="n">
-        <v>92.24280802636217</v>
+        <v>92.24281586478145</v>
       </c>
       <c r="D201" t="n">
-        <v>89.22075579004928</v>
+        <v>89.22076337166682</v>
       </c>
       <c r="E201" t="n">
-        <v>91.97047426173357</v>
+        <v>91.97048207701101</v>
       </c>
       <c r="F201" t="n">
         <v>566897</v>
@@ -4452,16 +4452,16 @@
         <v>44767</v>
       </c>
       <c r="B202" t="n">
-        <v>89.0802001953125</v>
+        <v>89.08021545410156</v>
       </c>
       <c r="C202" t="n">
-        <v>90.58243943087848</v>
+        <v>90.58245494699018</v>
       </c>
       <c r="D202" t="n">
-        <v>88.15776941968373</v>
+        <v>88.15778452046713</v>
       </c>
       <c r="E202" t="n">
-        <v>89.17683605570963</v>
+        <v>89.17685133105172</v>
       </c>
       <c r="F202" t="n">
         <v>343259</v>
@@ -4472,16 +4472,16 @@
         <v>44768</v>
       </c>
       <c r="B203" t="n">
-        <v>87.23534393310547</v>
+        <v>87.2353515625</v>
       </c>
       <c r="C203" t="n">
-        <v>88.80785828511767</v>
+        <v>88.80786605204057</v>
       </c>
       <c r="D203" t="n">
-        <v>86.86636760736479</v>
+        <v>86.86637520448954</v>
       </c>
       <c r="E203" t="n">
-        <v>88.1226270697279</v>
+        <v>88.12263477672209</v>
       </c>
       <c r="F203" t="n">
         <v>558437</v>
@@ -4492,16 +4492,16 @@
         <v>44769</v>
       </c>
       <c r="B204" t="n">
-        <v>92.2603759765625</v>
+        <v>92.26038360595703</v>
       </c>
       <c r="C204" t="n">
-        <v>92.55907046197431</v>
+        <v>92.55907811606914</v>
       </c>
       <c r="D204" t="n">
-        <v>87.46375071978201</v>
+        <v>87.46375795252364</v>
       </c>
       <c r="E204" t="n">
-        <v>87.46375071978201</v>
+        <v>87.46375795252364</v>
       </c>
       <c r="F204" t="n">
         <v>673546</v>
@@ -4552,16 +4552,16 @@
         <v>44774</v>
       </c>
       <c r="B207" t="n">
-        <v>100.1493453979492</v>
+        <v>100.1493377685547</v>
       </c>
       <c r="C207" t="n">
-        <v>102.284108028477</v>
+        <v>102.2841002364559</v>
       </c>
       <c r="D207" t="n">
-        <v>94.3512267417151</v>
+        <v>94.35121955402224</v>
       </c>
       <c r="E207" t="n">
-        <v>94.3512267417151</v>
+        <v>94.35121955402224</v>
       </c>
       <c r="F207" t="n">
         <v>942663</v>
@@ -4572,16 +4572,16 @@
         <v>44775</v>
       </c>
       <c r="B208" t="n">
-        <v>101.4671020507812</v>
+        <v>101.4670944213867</v>
       </c>
       <c r="C208" t="n">
-        <v>102.2050413939763</v>
+        <v>102.2050337090955</v>
       </c>
       <c r="D208" t="n">
-        <v>98.69981610890704</v>
+        <v>98.69980868758699</v>
       </c>
       <c r="E208" t="n">
-        <v>100.0439247000455</v>
+        <v>100.0439171776608</v>
       </c>
       <c r="F208" t="n">
         <v>737331</v>
@@ -4592,16 +4592,16 @@
         <v>44776</v>
       </c>
       <c r="B209" t="n">
-        <v>106.8523178100586</v>
+        <v>106.8523254394531</v>
       </c>
       <c r="C209" t="n">
-        <v>107.5990507243421</v>
+        <v>107.5990584070543</v>
       </c>
       <c r="D209" t="n">
-        <v>101.4670968161594</v>
+        <v>101.4671040610422</v>
       </c>
       <c r="E209" t="n">
-        <v>101.4670968161594</v>
+        <v>101.4671040610422</v>
       </c>
       <c r="F209" t="n">
         <v>990038</v>
@@ -4632,16 +4632,16 @@
         <v>44778</v>
       </c>
       <c r="B211" t="n">
-        <v>108.0119400024414</v>
+        <v>108.0119323730469</v>
       </c>
       <c r="C211" t="n">
-        <v>108.8728758822191</v>
+        <v>108.8728681920126</v>
       </c>
       <c r="D211" t="n">
-        <v>105.0953103420402</v>
+        <v>105.095302918661</v>
       </c>
       <c r="E211" t="n">
-        <v>107.3969905900615</v>
+        <v>107.3969830041038</v>
       </c>
       <c r="F211" t="n">
         <v>445839</v>
@@ -4712,16 +4712,16 @@
         <v>44784</v>
       </c>
       <c r="B215" t="n">
-        <v>84.59983825683594</v>
+        <v>84.59984588623047</v>
       </c>
       <c r="C215" t="n">
-        <v>92.06711346342773</v>
+        <v>92.06712176623714</v>
       </c>
       <c r="D215" t="n">
-        <v>83.26450999593463</v>
+        <v>83.26451750490639</v>
       </c>
       <c r="E215" t="n">
-        <v>90.87234889417739</v>
+        <v>90.87235708924037</v>
       </c>
       <c r="F215" t="n">
         <v>3127275</v>
@@ -4752,16 +4752,16 @@
         <v>44788</v>
       </c>
       <c r="B217" t="n">
-        <v>98.17270660400391</v>
+        <v>98.17271423339844</v>
       </c>
       <c r="C217" t="n">
-        <v>98.83158382953414</v>
+        <v>98.83159151013265</v>
       </c>
       <c r="D217" t="n">
-        <v>86.98058067634858</v>
+        <v>86.98058743595814</v>
       </c>
       <c r="E217" t="n">
-        <v>87.40225834731831</v>
+        <v>87.40226513969814</v>
       </c>
       <c r="F217" t="n">
         <v>1427504</v>
@@ -4772,16 +4772,16 @@
         <v>44789</v>
       </c>
       <c r="B218" t="n">
-        <v>94.96616363525391</v>
+        <v>94.96617126464844</v>
       </c>
       <c r="C218" t="n">
-        <v>98.40111324516731</v>
+        <v>98.40112115051892</v>
       </c>
       <c r="D218" t="n">
-        <v>92.85775530177888</v>
+        <v>92.85776276178804</v>
       </c>
       <c r="E218" t="n">
-        <v>98.18148751673127</v>
+        <v>98.18149540443858</v>
       </c>
       <c r="F218" t="n">
         <v>844810</v>
@@ -4852,16 +4852,16 @@
         <v>44795</v>
       </c>
       <c r="B222" t="n">
-        <v>88.45646667480469</v>
+        <v>88.45647430419922</v>
       </c>
       <c r="C222" t="n">
-        <v>92.04954062445751</v>
+        <v>92.04954856375565</v>
       </c>
       <c r="D222" t="n">
-        <v>88.03478229783688</v>
+        <v>88.03478989086102</v>
       </c>
       <c r="E222" t="n">
-        <v>92.04954062445751</v>
+        <v>92.04954856375565</v>
       </c>
       <c r="F222" t="n">
         <v>1074017</v>
@@ -4872,16 +4872,16 @@
         <v>44796</v>
       </c>
       <c r="B223" t="n">
-        <v>96.42449951171875</v>
+        <v>96.42449188232422</v>
       </c>
       <c r="C223" t="n">
-        <v>97.50505454197742</v>
+        <v>97.50504682708615</v>
       </c>
       <c r="D223" t="n">
-        <v>87.49890504115571</v>
+        <v>87.49889811798089</v>
       </c>
       <c r="E223" t="n">
-        <v>89.51946479721248</v>
+        <v>89.51945771416493</v>
       </c>
       <c r="F223" t="n">
         <v>1305076</v>
@@ -4892,16 +4892,16 @@
         <v>44797</v>
       </c>
       <c r="B224" t="n">
-        <v>101.0278472900391</v>
+        <v>101.0278396606445</v>
       </c>
       <c r="C224" t="n">
-        <v>102.855135180046</v>
+        <v>102.8551274126588</v>
       </c>
       <c r="D224" t="n">
-        <v>96.94280690695261</v>
+        <v>96.94279958605108</v>
       </c>
       <c r="E224" t="n">
-        <v>96.98673473892673</v>
+        <v>96.98672741470787</v>
       </c>
       <c r="F224" t="n">
         <v>1291806</v>
@@ -4912,16 +4912,16 @@
         <v>44798</v>
       </c>
       <c r="B225" t="n">
-        <v>99.56952667236328</v>
+        <v>99.56953430175781</v>
       </c>
       <c r="C225" t="n">
-        <v>103.1362534053532</v>
+        <v>103.1362613080438</v>
       </c>
       <c r="D225" t="n">
-        <v>98.69981058018772</v>
+        <v>98.6998181429413</v>
       </c>
       <c r="E225" t="n">
-        <v>101.9063478664755</v>
+        <v>101.9063556749261</v>
       </c>
       <c r="F225" t="n">
         <v>468543</v>
@@ -4992,16 +4992,16 @@
         <v>44804</v>
       </c>
       <c r="B229" t="n">
-        <v>87.36711120605469</v>
+        <v>87.36711883544922</v>
       </c>
       <c r="C229" t="n">
-        <v>91.33794808933241</v>
+        <v>91.33795606548307</v>
       </c>
       <c r="D229" t="n">
-        <v>87.36711120605469</v>
+        <v>87.36711883544922</v>
       </c>
       <c r="E229" t="n">
-        <v>89.35252964769354</v>
+        <v>89.35253745046614</v>
       </c>
       <c r="F229" t="n">
         <v>588012</v>
@@ -5032,16 +5032,16 @@
         <v>44806</v>
       </c>
       <c r="B231" t="n">
-        <v>88.0260009765625</v>
+        <v>88.02600860595703</v>
       </c>
       <c r="C231" t="n">
-        <v>91.19739745291511</v>
+        <v>91.1974053571811</v>
       </c>
       <c r="D231" t="n">
-        <v>86.98936713245767</v>
+        <v>86.98937467200503</v>
       </c>
       <c r="E231" t="n">
-        <v>89.50188633592451</v>
+        <v>89.50189409323706</v>
       </c>
       <c r="F231" t="n">
         <v>344726</v>
@@ -5052,16 +5052,16 @@
         <v>44809</v>
       </c>
       <c r="B232" t="n">
-        <v>89.43160247802734</v>
+        <v>89.43161010742188</v>
       </c>
       <c r="C232" t="n">
-        <v>89.82692612228165</v>
+        <v>89.82693378540118</v>
       </c>
       <c r="D232" t="n">
-        <v>88.03477931026735</v>
+        <v>88.03478682049915</v>
       </c>
       <c r="E232" t="n">
-        <v>88.81664639508718</v>
+        <v>88.81665397201991</v>
       </c>
       <c r="F232" t="n">
         <v>95765</v>
@@ -5092,16 +5092,16 @@
         <v>44812</v>
       </c>
       <c r="B234" t="n">
-        <v>88.28955841064453</v>
+        <v>88.28955078125</v>
       </c>
       <c r="C234" t="n">
-        <v>90.14320042192941</v>
+        <v>90.14319263235551</v>
       </c>
       <c r="D234" t="n">
-        <v>87.12993462797571</v>
+        <v>87.12992709878814</v>
       </c>
       <c r="E234" t="n">
-        <v>88.29834531801718</v>
+        <v>88.29833768786334</v>
       </c>
       <c r="F234" t="n">
         <v>707072</v>
@@ -5112,16 +5112,16 @@
         <v>44813</v>
       </c>
       <c r="B235" t="n">
-        <v>91.80356597900391</v>
+        <v>91.80357360839844</v>
       </c>
       <c r="C235" t="n">
-        <v>92.14618162206</v>
+        <v>92.14618927992782</v>
       </c>
       <c r="D235" t="n">
-        <v>88.81665435785808</v>
+        <v>88.8166617390234</v>
       </c>
       <c r="E235" t="n">
-        <v>88.81665435785808</v>
+        <v>88.8166617390234</v>
       </c>
       <c r="F235" t="n">
         <v>540504</v>
@@ -5132,16 +5132,16 @@
         <v>44816</v>
       </c>
       <c r="B236" t="n">
-        <v>94.79048156738281</v>
+        <v>94.79046630859375</v>
       </c>
       <c r="C236" t="n">
-        <v>94.79048156738281</v>
+        <v>94.79046630859375</v>
       </c>
       <c r="D236" t="n">
-        <v>91.34675117884834</v>
+        <v>91.34673647440984</v>
       </c>
       <c r="E236" t="n">
-        <v>91.34675117884834</v>
+        <v>91.34673647440984</v>
       </c>
       <c r="F236" t="n">
         <v>423751</v>
@@ -5192,16 +5192,16 @@
         <v>44819</v>
       </c>
       <c r="B239" t="n">
-        <v>90.22225189208984</v>
+        <v>90.22226715087891</v>
       </c>
       <c r="C239" t="n">
-        <v>93.36729411773216</v>
+        <v>93.36730990842477</v>
       </c>
       <c r="D239" t="n">
-        <v>89.21197884353981</v>
+        <v>89.21199393146699</v>
       </c>
       <c r="E239" t="n">
-        <v>89.60730249710758</v>
+        <v>89.60731765189367</v>
       </c>
       <c r="F239" t="n">
         <v>512054</v>
@@ -5212,16 +5212,16 @@
         <v>44820</v>
       </c>
       <c r="B240" t="n">
-        <v>87.80637359619141</v>
+        <v>87.80636596679688</v>
       </c>
       <c r="C240" t="n">
-        <v>89.46674375698272</v>
+        <v>89.46673598332055</v>
       </c>
       <c r="D240" t="n">
-        <v>86.15479034222778</v>
+        <v>86.15478285633742</v>
       </c>
       <c r="E240" t="n">
-        <v>89.33497366679777</v>
+        <v>89.33496590458495</v>
       </c>
       <c r="F240" t="n">
         <v>454254</v>
@@ -5232,16 +5232,16 @@
         <v>44823</v>
       </c>
       <c r="B241" t="n">
-        <v>88.99236297607422</v>
+        <v>88.99235534667969</v>
       </c>
       <c r="C241" t="n">
-        <v>89.82693820506938</v>
+        <v>89.82693050412597</v>
       </c>
       <c r="D241" t="n">
-        <v>86.69946944510852</v>
+        <v>86.69946201228579</v>
       </c>
       <c r="E241" t="n">
-        <v>87.393487669275</v>
+        <v>87.39348017695347</v>
       </c>
       <c r="F241" t="n">
         <v>601912</v>
@@ -5252,16 +5252,16 @@
         <v>44824</v>
       </c>
       <c r="B242" t="n">
-        <v>89.88842010498047</v>
+        <v>89.88843536376953</v>
       </c>
       <c r="C242" t="n">
-        <v>91.25010233617633</v>
+        <v>91.25011782611443</v>
       </c>
       <c r="D242" t="n">
-        <v>88.50917076414814</v>
+        <v>88.50918578880611</v>
       </c>
       <c r="E242" t="n">
-        <v>88.77272432581363</v>
+        <v>88.77273939521048</v>
       </c>
       <c r="F242" t="n">
         <v>415549</v>
@@ -5292,16 +5292,16 @@
         <v>44826</v>
       </c>
       <c r="B244" t="n">
-        <v>89.0802001953125</v>
+        <v>89.08021545410156</v>
       </c>
       <c r="C244" t="n">
-        <v>91.53122422253455</v>
+        <v>91.53123990116616</v>
       </c>
       <c r="D244" t="n">
-        <v>86.27777364868685</v>
+        <v>86.27778842744067</v>
       </c>
       <c r="E244" t="n">
-        <v>89.43160271471611</v>
+        <v>89.43161803369786</v>
       </c>
       <c r="F244" t="n">
         <v>985794</v>
@@ -5392,16 +5392,16 @@
         <v>44833</v>
       </c>
       <c r="B249" t="n">
-        <v>87.27049255371094</v>
+        <v>87.27048492431641</v>
       </c>
       <c r="C249" t="n">
-        <v>87.79759976248249</v>
+        <v>87.79759208700698</v>
       </c>
       <c r="D249" t="n">
-        <v>84.51199342491191</v>
+        <v>84.51198603667193</v>
       </c>
       <c r="E249" t="n">
-        <v>85.399283410401</v>
+        <v>85.39927594459202</v>
       </c>
       <c r="F249" t="n">
         <v>546314</v>
@@ -5412,16 +5412,16 @@
         <v>44834</v>
       </c>
       <c r="B250" t="n">
-        <v>90.31011962890625</v>
+        <v>90.31010437011719</v>
       </c>
       <c r="C250" t="n">
-        <v>91.1886227120573</v>
+        <v>91.18860730483644</v>
       </c>
       <c r="D250" t="n">
-        <v>85.89124349060133</v>
+        <v>85.89122897842515</v>
       </c>
       <c r="E250" t="n">
-        <v>86.97180523195362</v>
+        <v>86.97179053720583</v>
       </c>
       <c r="F250" t="n">
         <v>846019</v>
@@ -5432,16 +5432,16 @@
         <v>44837</v>
       </c>
       <c r="B251" t="n">
-        <v>94.77289581298828</v>
+        <v>94.77290344238281</v>
       </c>
       <c r="C251" t="n">
-        <v>95.68653968508768</v>
+        <v>95.68654738803224</v>
       </c>
       <c r="D251" t="n">
-        <v>90.92505530568604</v>
+        <v>90.92506262532224</v>
       </c>
       <c r="E251" t="n">
-        <v>91.36430678059274</v>
+        <v>91.36431413558951</v>
       </c>
       <c r="F251" t="n">
         <v>814581</v>
@@ -5492,16 +5492,16 @@
         <v>44840</v>
       </c>
       <c r="B254" t="n">
-        <v>99.09514617919922</v>
+        <v>99.09513854980469</v>
       </c>
       <c r="C254" t="n">
-        <v>99.89458046505639</v>
+        <v>99.89457277411294</v>
       </c>
       <c r="D254" t="n">
-        <v>94.70263095321427</v>
+        <v>94.70262366200211</v>
       </c>
       <c r="E254" t="n">
-        <v>95.71290409323375</v>
+        <v>95.71289672424005</v>
       </c>
       <c r="F254" t="n">
         <v>1317655</v>
@@ -5552,16 +5552,16 @@
         <v>44845</v>
       </c>
       <c r="B257" t="n">
-        <v>88.64973449707031</v>
+        <v>88.64974212646484</v>
       </c>
       <c r="C257" t="n">
-        <v>96.94279765600854</v>
+        <v>96.94280599912264</v>
       </c>
       <c r="D257" t="n">
-        <v>87.13870837462035</v>
+        <v>87.1387158739726</v>
       </c>
       <c r="E257" t="n">
-        <v>96.52112000005931</v>
+        <v>96.5211283068829</v>
       </c>
       <c r="F257" t="n">
         <v>1649810</v>
@@ -5672,16 +5672,16 @@
         <v>44854</v>
       </c>
       <c r="B263" t="n">
-        <v>77.81779479980469</v>
+        <v>77.81780242919922</v>
       </c>
       <c r="C263" t="n">
-        <v>80.72563748978079</v>
+        <v>80.72564540426539</v>
       </c>
       <c r="D263" t="n">
-        <v>76.50004034296538</v>
+        <v>76.50004784316492</v>
       </c>
       <c r="E263" t="n">
-        <v>80.4708708238317</v>
+        <v>80.47087871333852</v>
       </c>
       <c r="F263" t="n">
         <v>1064344</v>
@@ -5692,16 +5692,16 @@
         <v>44855</v>
       </c>
       <c r="B264" t="n">
-        <v>82.25423431396484</v>
+        <v>82.25422668457031</v>
       </c>
       <c r="C264" t="n">
-        <v>85.73310542506498</v>
+        <v>85.73309747299184</v>
       </c>
       <c r="D264" t="n">
-        <v>75.13836128205794</v>
+        <v>75.13835431268782</v>
       </c>
       <c r="E264" t="n">
-        <v>77.967142043229</v>
+        <v>77.96713481147866</v>
       </c>
       <c r="F264" t="n">
         <v>1421863</v>
@@ -5732,16 +5732,16 @@
         <v>44859</v>
       </c>
       <c r="B266" t="n">
-        <v>82.92189025878906</v>
+        <v>82.92189788818359</v>
       </c>
       <c r="C266" t="n">
-        <v>85.30263237275399</v>
+        <v>85.30264022119347</v>
       </c>
       <c r="D266" t="n">
-        <v>81.31422830318635</v>
+        <v>81.31423578466473</v>
       </c>
       <c r="E266" t="n">
-        <v>82.03460043101913</v>
+        <v>82.03460797877678</v>
       </c>
       <c r="F266" t="n">
         <v>1189906</v>
@@ -5752,16 +5752,16 @@
         <v>44860</v>
       </c>
       <c r="B267" t="n">
-        <v>80.20732879638672</v>
+        <v>80.20732116699219</v>
       </c>
       <c r="C267" t="n">
-        <v>84.20451353532545</v>
+        <v>84.20450552571505</v>
       </c>
       <c r="D267" t="n">
-        <v>80.07555200225771</v>
+        <v>80.07554438539792</v>
       </c>
       <c r="E267" t="n">
-        <v>82.57928428092416</v>
+        <v>82.57927642590705</v>
       </c>
       <c r="F267" t="n">
         <v>763965</v>
@@ -5772,16 +5772,16 @@
         <v>44861</v>
       </c>
       <c r="B268" t="n">
-        <v>78.95984649658203</v>
+        <v>78.95985412597656</v>
       </c>
       <c r="C268" t="n">
-        <v>81.79741410940505</v>
+        <v>81.79742201297594</v>
       </c>
       <c r="D268" t="n">
-        <v>78.12527133528192</v>
+        <v>78.12527888403669</v>
       </c>
       <c r="E268" t="n">
-        <v>80.63779042823175</v>
+        <v>80.63779821975547</v>
       </c>
       <c r="F268" t="n">
         <v>872704</v>
@@ -5792,16 +5792,16 @@
         <v>44862</v>
       </c>
       <c r="B269" t="n">
-        <v>81.43722534179688</v>
+        <v>81.43723297119141</v>
       </c>
       <c r="C269" t="n">
-        <v>82.14003042210881</v>
+        <v>82.14003811734518</v>
       </c>
       <c r="D269" t="n">
-        <v>78.40639267564933</v>
+        <v>78.40640002110223</v>
       </c>
       <c r="E269" t="n">
-        <v>79.04770281411741</v>
+        <v>79.04771021965105</v>
       </c>
       <c r="F269" t="n">
         <v>705309</v>
@@ -5812,16 +5812,16 @@
         <v>44865</v>
       </c>
       <c r="B270" t="n">
-        <v>83.36993408203125</v>
+        <v>83.36994171142578</v>
       </c>
       <c r="C270" t="n">
-        <v>84.17815521445814</v>
+        <v>84.17816291781504</v>
       </c>
       <c r="D270" t="n">
-        <v>79.07405504914219</v>
+        <v>79.07406228540991</v>
       </c>
       <c r="E270" t="n">
-        <v>79.07405504914219</v>
+        <v>79.07406228540991</v>
       </c>
       <c r="F270" t="n">
         <v>956071</v>
@@ -5872,16 +5872,16 @@
         <v>44869</v>
       </c>
       <c r="B273" t="n">
-        <v>83.48413848876953</v>
+        <v>83.484130859375</v>
       </c>
       <c r="C273" t="n">
-        <v>88.728802437938</v>
+        <v>88.72879432924752</v>
       </c>
       <c r="D273" t="n">
-        <v>82.78134011468907</v>
+        <v>82.78133254952142</v>
       </c>
       <c r="E273" t="n">
-        <v>87.59553277082331</v>
+        <v>87.59552476569932</v>
       </c>
       <c r="F273" t="n">
         <v>612180</v>
@@ -5952,16 +5952,16 @@
         <v>44875</v>
       </c>
       <c r="B277" t="n">
-        <v>90.49458312988281</v>
+        <v>90.49459838867188</v>
       </c>
       <c r="C277" t="n">
-        <v>94.21943344729159</v>
+        <v>94.21944933414814</v>
       </c>
       <c r="D277" t="n">
-        <v>85.65403040662872</v>
+        <v>85.65404484922558</v>
       </c>
       <c r="E277" t="n">
-        <v>85.67159751507221</v>
+        <v>85.67161196063115</v>
       </c>
       <c r="F277" t="n">
         <v>2820385</v>
@@ -5992,16 +5992,16 @@
         <v>44879</v>
       </c>
       <c r="B279" t="n">
-        <v>88.81664276123047</v>
+        <v>88.81665802001953</v>
       </c>
       <c r="C279" t="n">
-        <v>90.38916377266612</v>
+        <v>90.38917930161588</v>
       </c>
       <c r="D279" t="n">
-        <v>85.91758718293825</v>
+        <v>85.91760194366664</v>
       </c>
       <c r="E279" t="n">
-        <v>89.08019631491399</v>
+        <v>89.08021161898182</v>
       </c>
       <c r="F279" t="n">
         <v>689741</v>
@@ -6012,16 +6012,16 @@
         <v>44881</v>
       </c>
       <c r="B280" t="n">
-        <v>86.34806060791016</v>
+        <v>86.34806823730469</v>
       </c>
       <c r="C280" t="n">
-        <v>90.38917306431421</v>
+        <v>90.38918105076644</v>
       </c>
       <c r="D280" t="n">
-        <v>85.7594652069497</v>
+        <v>85.75947278433812</v>
       </c>
       <c r="E280" t="n">
-        <v>88.90450085067289</v>
+        <v>88.90450870594499</v>
       </c>
       <c r="F280" t="n">
         <v>1097230</v>
@@ -6032,16 +6032,16 @@
         <v>44882</v>
       </c>
       <c r="B281" t="n">
-        <v>84.07273864746094</v>
+        <v>84.07273101806641</v>
       </c>
       <c r="C281" t="n">
-        <v>86.65553974214566</v>
+        <v>86.65553187836828</v>
       </c>
       <c r="D281" t="n">
-        <v>78.95107099372555</v>
+        <v>78.95106382910978</v>
       </c>
       <c r="E281" t="n">
-        <v>86.26021605324125</v>
+        <v>86.26020822533852</v>
       </c>
       <c r="F281" t="n">
         <v>1328887</v>
@@ -6072,16 +6072,16 @@
         <v>44886</v>
       </c>
       <c r="B283" t="n">
-        <v>80.04039764404297</v>
+        <v>80.0404052734375</v>
       </c>
       <c r="C283" t="n">
-        <v>82.56170331342106</v>
+        <v>82.56171118314468</v>
       </c>
       <c r="D283" t="n">
-        <v>79.62750021954236</v>
+        <v>79.6275078095798</v>
       </c>
       <c r="E283" t="n">
-        <v>82.06973714473446</v>
+        <v>82.0697449675642</v>
       </c>
       <c r="F283" t="n">
         <v>597582</v>
@@ -6172,16 +6172,16 @@
         <v>44893</v>
       </c>
       <c r="B288" t="n">
-        <v>75.56881713867188</v>
+        <v>75.56883239746094</v>
       </c>
       <c r="C288" t="n">
-        <v>78.24825368697887</v>
+        <v>78.2482694867974</v>
       </c>
       <c r="D288" t="n">
-        <v>75.28769647642699</v>
+        <v>75.28771167845241</v>
       </c>
       <c r="E288" t="n">
-        <v>77.1413381470698</v>
+        <v>77.14135372338092</v>
       </c>
       <c r="F288" t="n">
         <v>519110</v>
@@ -6212,16 +6212,16 @@
         <v>44895</v>
       </c>
       <c r="B290" t="n">
-        <v>79.5396728515625</v>
+        <v>79.53966522216797</v>
       </c>
       <c r="C290" t="n">
-        <v>80.11948142230071</v>
+        <v>80.11947373729132</v>
       </c>
       <c r="D290" t="n">
-        <v>75.72696584646302</v>
+        <v>75.72695858278091</v>
       </c>
       <c r="E290" t="n">
-        <v>78.18677724991088</v>
+        <v>78.18676975028522</v>
       </c>
       <c r="F290" t="n">
         <v>577266</v>
@@ -6232,16 +6232,16 @@
         <v>44896</v>
       </c>
       <c r="B291" t="n">
-        <v>79.21462249755859</v>
+        <v>79.21460723876953</v>
       </c>
       <c r="C291" t="n">
-        <v>81.06826456490624</v>
+        <v>81.06824894905768</v>
       </c>
       <c r="D291" t="n">
-        <v>78.69630888848674</v>
+        <v>78.69629372953831</v>
       </c>
       <c r="E291" t="n">
-        <v>79.07406548757766</v>
+        <v>79.07405025586351</v>
       </c>
       <c r="F291" t="n">
         <v>741238</v>
@@ -6252,16 +6252,16 @@
         <v>44897</v>
       </c>
       <c r="B292" t="n">
-        <v>83.99367523193359</v>
+        <v>83.99366760253906</v>
       </c>
       <c r="C292" t="n">
-        <v>84.95124031743019</v>
+        <v>84.95123260105719</v>
       </c>
       <c r="D292" t="n">
-        <v>77.90564896612145</v>
+        <v>77.90564188972039</v>
       </c>
       <c r="E292" t="n">
-        <v>79.21461660409658</v>
+        <v>79.21460940879811</v>
       </c>
       <c r="F292" t="n">
         <v>680539</v>
@@ -6292,16 +6292,16 @@
         <v>44901</v>
       </c>
       <c r="B294" t="n">
-        <v>77.94956970214844</v>
+        <v>77.94957733154297</v>
       </c>
       <c r="C294" t="n">
-        <v>81.69198744336707</v>
+        <v>81.69199543905461</v>
       </c>
       <c r="D294" t="n">
-        <v>77.94956970214844</v>
+        <v>77.94957733154297</v>
       </c>
       <c r="E294" t="n">
-        <v>81.0418971370554</v>
+        <v>81.04190506911468</v>
       </c>
       <c r="F294" t="n">
         <v>575865</v>
@@ -6312,16 +6312,16 @@
         <v>44902</v>
       </c>
       <c r="B295" t="n">
-        <v>76.15742492675781</v>
+        <v>76.15743255615234</v>
       </c>
       <c r="C295" t="n">
-        <v>78.4327444112255</v>
+        <v>78.43275226855985</v>
       </c>
       <c r="D295" t="n">
-        <v>74.76060171345117</v>
+        <v>74.76060920291299</v>
       </c>
       <c r="E295" t="n">
-        <v>77.82657521465414</v>
+        <v>77.82658301126293</v>
       </c>
       <c r="F295" t="n">
         <v>782541</v>
@@ -6332,16 +6332,16 @@
         <v>44903</v>
       </c>
       <c r="B296" t="n">
-        <v>72.38865661621094</v>
+        <v>72.38864898681641</v>
       </c>
       <c r="C296" t="n">
-        <v>76.73724427036358</v>
+        <v>76.73723618265012</v>
       </c>
       <c r="D296" t="n">
-        <v>72.03725403651906</v>
+        <v>72.03724644416056</v>
       </c>
       <c r="E296" t="n">
-        <v>76.73724427036358</v>
+        <v>76.73723618265012</v>
       </c>
       <c r="F296" t="n">
         <v>1116650</v>
@@ -6372,16 +6372,16 @@
         <v>44907</v>
       </c>
       <c r="B298" t="n">
-        <v>72.23931121826172</v>
+        <v>72.23930358886719</v>
       </c>
       <c r="C298" t="n">
-        <v>74.02267139828965</v>
+        <v>74.02266358054949</v>
       </c>
       <c r="D298" t="n">
-        <v>70.51743928329</v>
+        <v>70.51743183574715</v>
       </c>
       <c r="E298" t="n">
-        <v>72.73127079828416</v>
+        <v>72.73126311693241</v>
       </c>
       <c r="F298" t="n">
         <v>769701</v>
@@ -6392,16 +6392,16 @@
         <v>44908</v>
       </c>
       <c r="B299" t="n">
-        <v>70.42079925537109</v>
+        <v>70.42080688476562</v>
       </c>
       <c r="C299" t="n">
-        <v>74.92751694822861</v>
+        <v>74.92752506588127</v>
       </c>
       <c r="D299" t="n">
-        <v>69.92883304873867</v>
+        <v>69.92884062483354</v>
       </c>
       <c r="E299" t="n">
-        <v>71.9581794084006</v>
+        <v>71.958187204355</v>
       </c>
       <c r="F299" t="n">
         <v>758036</v>
@@ -6432,16 +6432,16 @@
         <v>44910</v>
       </c>
       <c r="B301" t="n">
-        <v>65.86137390136719</v>
+        <v>65.86136627197266</v>
       </c>
       <c r="C301" t="n">
-        <v>68.8482855742363</v>
+        <v>68.84827759883733</v>
       </c>
       <c r="D301" t="n">
-        <v>65.81744606844191</v>
+        <v>65.81743844413599</v>
       </c>
       <c r="E301" t="n">
-        <v>68.30361127721578</v>
+        <v>68.30360336491199</v>
       </c>
       <c r="F301" t="n">
         <v>806063</v>
@@ -6452,16 +6452,16 @@
         <v>44911</v>
       </c>
       <c r="B302" t="n">
-        <v>64.96529388427734</v>
+        <v>64.96530151367188</v>
       </c>
       <c r="C302" t="n">
-        <v>66.81015553814807</v>
+        <v>66.81016338419947</v>
       </c>
       <c r="D302" t="n">
-        <v>63.87595204573682</v>
+        <v>63.87595954720123</v>
       </c>
       <c r="E302" t="n">
-        <v>66.32697620928745</v>
+        <v>66.32698399859524</v>
       </c>
       <c r="F302" t="n">
         <v>628655</v>
@@ -6492,16 +6492,16 @@
         <v>44915</v>
       </c>
       <c r="B304" t="n">
-        <v>69.59501647949219</v>
+        <v>69.59500885009766</v>
       </c>
       <c r="C304" t="n">
-        <v>69.88492411035084</v>
+        <v>69.88491644917501</v>
       </c>
       <c r="D304" t="n">
-        <v>65.00044232896225</v>
+        <v>65.0004352032506</v>
       </c>
       <c r="E304" t="n">
-        <v>65.79988336512761</v>
+        <v>65.79987615177677</v>
       </c>
       <c r="F304" t="n">
         <v>691729</v>
@@ -6572,16 +6572,16 @@
         <v>44921</v>
       </c>
       <c r="B308" t="n">
-        <v>68.78679656982422</v>
+        <v>68.78678131103516</v>
       </c>
       <c r="C308" t="n">
-        <v>71.15875229880567</v>
+        <v>71.15873651385208</v>
       </c>
       <c r="D308" t="n">
-        <v>68.39146614669608</v>
+        <v>68.39145097560208</v>
       </c>
       <c r="E308" t="n">
-        <v>71.15875229880567</v>
+        <v>71.15873651385208</v>
       </c>
       <c r="F308" t="n">
         <v>122344</v>
@@ -6592,16 +6592,16 @@
         <v>44922</v>
       </c>
       <c r="B309" t="n">
-        <v>67.8204345703125</v>
+        <v>67.82042694091797</v>
       </c>
       <c r="C309" t="n">
-        <v>70.45594378992226</v>
+        <v>70.45593586404866</v>
       </c>
       <c r="D309" t="n">
-        <v>67.38118303371087</v>
+        <v>67.38117545372953</v>
       </c>
       <c r="E309" t="n">
-        <v>68.96249124645534</v>
+        <v>68.96248348858624</v>
       </c>
       <c r="F309" t="n">
         <v>436455</v>
@@ -6632,16 +6632,16 @@
         <v>44924</v>
       </c>
       <c r="B311" t="n">
-        <v>70.66677856445312</v>
+        <v>70.66678619384766</v>
       </c>
       <c r="C311" t="n">
-        <v>70.66677856445312</v>
+        <v>70.66678619384766</v>
       </c>
       <c r="D311" t="n">
-        <v>67.35481873074851</v>
+        <v>67.35482600257404</v>
       </c>
       <c r="E311" t="n">
-        <v>68.52322924831307</v>
+        <v>68.52323664628368</v>
       </c>
       <c r="F311" t="n">
         <v>1109758</v>
@@ -6652,16 +6652,16 @@
         <v>44928</v>
       </c>
       <c r="B312" t="n">
-        <v>66.42361450195312</v>
+        <v>66.42360687255859</v>
       </c>
       <c r="C312" t="n">
-        <v>69.7707088947915</v>
+        <v>69.77070088095081</v>
       </c>
       <c r="D312" t="n">
-        <v>66.12491998707712</v>
+        <v>66.12491239199053</v>
       </c>
       <c r="E312" t="n">
-        <v>68.88342566202327</v>
+        <v>68.88341775009563</v>
       </c>
       <c r="F312" t="n">
         <v>452524</v>
@@ -6672,16 +6672,16 @@
         <v>44929</v>
       </c>
       <c r="B313" t="n">
-        <v>66.99464416503906</v>
+        <v>66.99463653564453</v>
       </c>
       <c r="C313" t="n">
-        <v>69.74435628615456</v>
+        <v>69.74434834362098</v>
       </c>
       <c r="D313" t="n">
-        <v>65.50118496536248</v>
+        <v>65.50117750604407</v>
       </c>
       <c r="E313" t="n">
-        <v>66.60810068001396</v>
+        <v>66.60809309463926</v>
       </c>
       <c r="F313" t="n">
         <v>913081</v>
@@ -6692,16 +6692,16 @@
         <v>44930</v>
       </c>
       <c r="B314" t="n">
-        <v>67.00341033935547</v>
+        <v>67.00341796875</v>
       </c>
       <c r="C314" t="n">
-        <v>68.40902028058885</v>
+        <v>68.40902807003422</v>
       </c>
       <c r="D314" t="n">
-        <v>66.33575298995903</v>
+        <v>66.33576054333025</v>
       </c>
       <c r="E314" t="n">
-        <v>66.52023778669582</v>
+        <v>66.52024536107352</v>
       </c>
       <c r="F314" t="n">
         <v>669125</v>
@@ -6712,16 +6712,16 @@
         <v>44931</v>
       </c>
       <c r="B315" t="n">
-        <v>65.422119140625</v>
+        <v>65.42211151123047</v>
       </c>
       <c r="C315" t="n">
-        <v>68.18061801001888</v>
+        <v>68.18061005893381</v>
       </c>
       <c r="D315" t="n">
-        <v>65.07071660197154</v>
+        <v>65.07070901355685</v>
       </c>
       <c r="E315" t="n">
-        <v>67.19669224227836</v>
+        <v>67.19668440593672</v>
       </c>
       <c r="F315" t="n">
         <v>721996</v>
@@ -6752,16 +6752,16 @@
         <v>44935</v>
       </c>
       <c r="B317" t="n">
-        <v>69.62136840820312</v>
+        <v>69.62136077880859</v>
       </c>
       <c r="C317" t="n">
-        <v>70.95669012764992</v>
+        <v>70.95668235192537</v>
       </c>
       <c r="D317" t="n">
-        <v>66.80137435331271</v>
+        <v>66.80136703294467</v>
       </c>
       <c r="E317" t="n">
-        <v>66.99464610141148</v>
+        <v>66.99463875986392</v>
       </c>
       <c r="F317" t="n">
         <v>604476</v>
@@ -6792,16 +6792,16 @@
         <v>44937</v>
       </c>
       <c r="B319" t="n">
-        <v>72.90696716308594</v>
+        <v>72.90695953369141</v>
       </c>
       <c r="C319" t="n">
-        <v>73.10902581621284</v>
+        <v>73.10901816567375</v>
       </c>
       <c r="D319" t="n">
-        <v>69.80585242983342</v>
+        <v>69.80584512495696</v>
       </c>
       <c r="E319" t="n">
-        <v>71.22024289438232</v>
+        <v>71.2202354414961</v>
       </c>
       <c r="F319" t="n">
         <v>824670</v>
@@ -6812,16 +6812,16 @@
         <v>44938</v>
       </c>
       <c r="B320" t="n">
-        <v>74.93630981445312</v>
+        <v>74.93630218505859</v>
       </c>
       <c r="C320" t="n">
-        <v>75.89387488304087</v>
+        <v>75.893867156155</v>
       </c>
       <c r="D320" t="n">
-        <v>71.29052096395313</v>
+        <v>71.29051370574263</v>
       </c>
       <c r="E320" t="n">
-        <v>72.90696329338618</v>
+        <v>72.90695587060291</v>
       </c>
       <c r="F320" t="n">
         <v>1386963</v>
@@ -6872,16 +6872,16 @@
         <v>44943</v>
       </c>
       <c r="B323" t="n">
-        <v>72.37985229492188</v>
+        <v>72.37985992431641</v>
       </c>
       <c r="C323" t="n">
-        <v>72.69611387031159</v>
+        <v>72.69612153304253</v>
       </c>
       <c r="D323" t="n">
-        <v>70.11331323877729</v>
+        <v>70.11332062926112</v>
       </c>
       <c r="E323" t="n">
-        <v>71.026957045187</v>
+        <v>71.02696453197595</v>
       </c>
       <c r="F323" t="n">
         <v>1038524</v>
@@ -6892,16 +6892,16 @@
         <v>44944</v>
       </c>
       <c r="B324" t="n">
-        <v>73.96995544433594</v>
+        <v>73.96994781494141</v>
       </c>
       <c r="C324" t="n">
-        <v>75.29649695010914</v>
+        <v>75.29648918389273</v>
       </c>
       <c r="D324" t="n">
-        <v>72.48528982109953</v>
+        <v>72.48528234483609</v>
       </c>
       <c r="E324" t="n">
-        <v>72.52043074801796</v>
+        <v>72.52042326813002</v>
       </c>
       <c r="F324" t="n">
         <v>881691</v>
@@ -6932,16 +6932,16 @@
         <v>44946</v>
       </c>
       <c r="B326" t="n">
-        <v>77.02713775634766</v>
+        <v>77.02714538574219</v>
       </c>
       <c r="C326" t="n">
-        <v>78.32732505171256</v>
+        <v>78.32733280988822</v>
       </c>
       <c r="D326" t="n">
-        <v>74.45312388377251</v>
+        <v>74.45313125821576</v>
       </c>
       <c r="E326" t="n">
-        <v>75.12078799233532</v>
+        <v>75.12079543290946</v>
       </c>
       <c r="F326" t="n">
         <v>766265</v>
@@ -6952,16 +6952,16 @@
         <v>44949</v>
       </c>
       <c r="B327" t="n">
-        <v>80.09310913085938</v>
+        <v>80.09311676025391</v>
       </c>
       <c r="C327" t="n">
-        <v>81.20881158598479</v>
+        <v>81.2088193216573</v>
       </c>
       <c r="D327" t="n">
-        <v>77.09741767677029</v>
+        <v>77.09742502080553</v>
       </c>
       <c r="E327" t="n">
-        <v>77.09741767677029</v>
+        <v>77.09742502080553</v>
       </c>
       <c r="F327" t="n">
         <v>1210224</v>
@@ -7032,16 +7032,16 @@
         <v>44953</v>
       </c>
       <c r="B331" t="n">
-        <v>81.18247222900391</v>
+        <v>81.18246459960938</v>
       </c>
       <c r="C331" t="n">
-        <v>81.18247222900391</v>
+        <v>81.18246459960938</v>
       </c>
       <c r="D331" t="n">
-        <v>75.7357491525274</v>
+        <v>75.73574203500689</v>
       </c>
       <c r="E331" t="n">
-        <v>78.99499475050509</v>
+        <v>78.99498732668607</v>
       </c>
       <c r="F331" t="n">
         <v>1276572</v>
@@ -7072,16 +7072,16 @@
         <v>44957</v>
       </c>
       <c r="B333" t="n">
-        <v>78.84564208984375</v>
+        <v>78.84564971923828</v>
       </c>
       <c r="C333" t="n">
-        <v>81.68320965117834</v>
+        <v>81.68321755514636</v>
       </c>
       <c r="D333" t="n">
-        <v>78.84564208984375</v>
+        <v>78.84564971923828</v>
       </c>
       <c r="E333" t="n">
-        <v>80.83984089613189</v>
+        <v>80.83984871849243</v>
       </c>
       <c r="F333" t="n">
         <v>714873</v>
@@ -7092,16 +7092,16 @@
         <v>44958</v>
       </c>
       <c r="B334" t="n">
-        <v>77.84414672851562</v>
+        <v>77.84415435791016</v>
       </c>
       <c r="C334" t="n">
-        <v>79.74170961019361</v>
+        <v>79.74171742556558</v>
       </c>
       <c r="D334" t="n">
-        <v>76.97443068701511</v>
+        <v>76.97443823117001</v>
       </c>
       <c r="E334" t="n">
-        <v>78.62601381573906</v>
+        <v>78.62602152176328</v>
       </c>
       <c r="F334" t="n">
         <v>624239</v>
@@ -7132,16 +7132,16 @@
         <v>44960</v>
       </c>
       <c r="B336" t="n">
-        <v>78.4327392578125</v>
+        <v>78.43274688720703</v>
       </c>
       <c r="C336" t="n">
-        <v>80.04918810831229</v>
+        <v>80.04919589494379</v>
       </c>
       <c r="D336" t="n">
-        <v>76.42975368198618</v>
+        <v>76.42976111654413</v>
       </c>
       <c r="E336" t="n">
-        <v>79.05647552379735</v>
+        <v>79.05648321386462</v>
       </c>
       <c r="F336" t="n">
         <v>709735</v>
@@ -7192,16 +7192,16 @@
         <v>44965</v>
       </c>
       <c r="B339" t="n">
-        <v>74.92752075195312</v>
+        <v>74.92751312255859</v>
       </c>
       <c r="C339" t="n">
-        <v>76.47368788960505</v>
+        <v>76.47368010277411</v>
       </c>
       <c r="D339" t="n">
-        <v>73.99630972819882</v>
+        <v>73.99630219362362</v>
       </c>
       <c r="E339" t="n">
-        <v>74.67275408079573</v>
+        <v>74.67274647734247</v>
       </c>
       <c r="F339" t="n">
         <v>806683</v>
@@ -7212,16 +7212,16 @@
         <v>44966</v>
       </c>
       <c r="B340" t="n">
-        <v>72.64341735839844</v>
+        <v>72.64340972900391</v>
       </c>
       <c r="C340" t="n">
-        <v>76.30677336791243</v>
+        <v>76.30676535377293</v>
       </c>
       <c r="D340" t="n">
-        <v>72.33593593736826</v>
+        <v>72.33592834026705</v>
       </c>
       <c r="E340" t="n">
-        <v>74.92752388531035</v>
+        <v>74.92751601602691</v>
       </c>
       <c r="F340" t="n">
         <v>904775</v>
@@ -7252,16 +7252,16 @@
         <v>44970</v>
       </c>
       <c r="B342" t="n">
-        <v>73.79424285888672</v>
+        <v>73.79425048828125</v>
       </c>
       <c r="C342" t="n">
-        <v>74.05779640721795</v>
+        <v>74.05780406386059</v>
       </c>
       <c r="D342" t="n">
-        <v>70.90396754262024</v>
+        <v>70.90397487319673</v>
       </c>
       <c r="E342" t="n">
-        <v>71.35200589380526</v>
+        <v>71.35201327070328</v>
       </c>
       <c r="F342" t="n">
         <v>400048</v>
@@ -7272,16 +7272,16 @@
         <v>44971</v>
       </c>
       <c r="B343" t="n">
-        <v>72.90696716308594</v>
+        <v>72.90695953369141</v>
       </c>
       <c r="C343" t="n">
-        <v>74.53219648561118</v>
+        <v>74.53218868614353</v>
       </c>
       <c r="D343" t="n">
-        <v>71.91426111693616</v>
+        <v>71.91425359142397</v>
       </c>
       <c r="E343" t="n">
-        <v>73.00360303600144</v>
+        <v>73.00359539649439</v>
       </c>
       <c r="F343" t="n">
         <v>472429</v>
@@ -7312,16 +7312,16 @@
         <v>44973</v>
       </c>
       <c r="B345" t="n">
-        <v>71.15874481201172</v>
+        <v>71.15873718261719</v>
       </c>
       <c r="C345" t="n">
-        <v>73.96995180261891</v>
+        <v>73.96994387181648</v>
       </c>
       <c r="D345" t="n">
-        <v>70.32416962173819</v>
+        <v>70.32416208182393</v>
       </c>
       <c r="E345" t="n">
-        <v>73.30229433137855</v>
+        <v>73.30228647216005</v>
       </c>
       <c r="F345" t="n">
         <v>1330447</v>
@@ -7332,16 +7332,16 @@
         <v>44974</v>
       </c>
       <c r="B346" t="n">
-        <v>58.2535285949707</v>
+        <v>58.25353240966797</v>
       </c>
       <c r="C346" t="n">
-        <v>64.91258257887556</v>
+        <v>64.91258682963696</v>
       </c>
       <c r="D346" t="n">
-        <v>57.36624543932376</v>
+        <v>57.36624919591782</v>
       </c>
       <c r="E346" t="n">
-        <v>64.68416993469967</v>
+        <v>64.68417417050361</v>
       </c>
       <c r="F346" t="n">
         <v>4993765</v>
@@ -7372,16 +7372,16 @@
         <v>44980</v>
       </c>
       <c r="B348" t="n">
-        <v>59.61521530151367</v>
+        <v>59.61521148681641</v>
       </c>
       <c r="C348" t="n">
-        <v>60.55521326210563</v>
+        <v>60.55520938725917</v>
       </c>
       <c r="D348" t="n">
-        <v>58.94755113155375</v>
+        <v>58.94754735957942</v>
       </c>
       <c r="E348" t="n">
-        <v>60.00175877398195</v>
+        <v>60.0017549345503</v>
       </c>
       <c r="F348" t="n">
         <v>572076</v>
@@ -7452,16 +7452,16 @@
         <v>44986</v>
       </c>
       <c r="B352" t="n">
-        <v>54.14214706420898</v>
+        <v>54.14213943481445</v>
       </c>
       <c r="C352" t="n">
-        <v>57.10270157685085</v>
+        <v>57.10269353027231</v>
       </c>
       <c r="D352" t="n">
-        <v>53.41298788164043</v>
+        <v>53.41298035499475</v>
       </c>
       <c r="E352" t="n">
-        <v>56.48775208700194</v>
+        <v>56.48774412707847</v>
       </c>
       <c r="F352" t="n">
         <v>634515</v>
@@ -7512,16 +7512,16 @@
         <v>44991</v>
       </c>
       <c r="B355" t="n">
-        <v>54.28269958496094</v>
+        <v>54.2827033996582</v>
       </c>
       <c r="C355" t="n">
-        <v>55.26662197781043</v>
+        <v>55.26662586165249</v>
       </c>
       <c r="D355" t="n">
-        <v>52.38513329456833</v>
+        <v>52.3851369759148</v>
       </c>
       <c r="E355" t="n">
-        <v>52.71017845670896</v>
+        <v>52.71018216089787</v>
       </c>
       <c r="F355" t="n">
         <v>1320672</v>
@@ -7532,16 +7532,16 @@
         <v>44992</v>
       </c>
       <c r="B356" t="n">
-        <v>54.52868270874023</v>
+        <v>54.52867889404297</v>
       </c>
       <c r="C356" t="n">
-        <v>54.57260718991888</v>
+        <v>54.57260337214876</v>
       </c>
       <c r="D356" t="n">
-        <v>53.0264433343582</v>
+        <v>53.02643962475403</v>
       </c>
       <c r="E356" t="n">
-        <v>54.28270293316135</v>
+        <v>54.28269913567225</v>
       </c>
       <c r="F356" t="n">
         <v>485619</v>
@@ -7552,16 +7552,16 @@
         <v>44993</v>
       </c>
       <c r="B357" t="n">
-        <v>58.67520904541016</v>
+        <v>58.67522048950195</v>
       </c>
       <c r="C357" t="n">
-        <v>58.67520904541016</v>
+        <v>58.67522048950195</v>
       </c>
       <c r="D357" t="n">
-        <v>53.97521655571307</v>
+        <v>53.975227083112</v>
       </c>
       <c r="E357" t="n">
-        <v>53.97521655571307</v>
+        <v>53.975227083112</v>
       </c>
       <c r="F357" t="n">
         <v>1672249</v>
@@ -7612,16 +7612,16 @@
         <v>44998</v>
       </c>
       <c r="B360" t="n">
-        <v>50.39093017578125</v>
+        <v>50.39093399047852</v>
       </c>
       <c r="C360" t="n">
-        <v>51.96345127391815</v>
+        <v>51.9634552076585</v>
       </c>
       <c r="D360" t="n">
-        <v>49.46850274069867</v>
+        <v>49.46850648556628</v>
       </c>
       <c r="E360" t="n">
-        <v>51.96345127391815</v>
+        <v>51.9634552076585</v>
       </c>
       <c r="F360" t="n">
         <v>1066340</v>
@@ -7672,16 +7672,16 @@
         <v>45001</v>
       </c>
       <c r="B363" t="n">
-        <v>53.81709289550781</v>
+        <v>53.81708908081055</v>
       </c>
       <c r="C363" t="n">
-        <v>54.24756084476554</v>
+        <v>54.24755699955558</v>
       </c>
       <c r="D363" t="n">
-        <v>50.10981247369315</v>
+        <v>50.10980892177768</v>
       </c>
       <c r="E363" t="n">
-        <v>50.68962432600123</v>
+        <v>50.68962073298718</v>
       </c>
       <c r="F363" t="n">
         <v>1144994</v>
@@ -7692,16 +7692,16 @@
         <v>45002</v>
       </c>
       <c r="B364" t="n">
-        <v>55.06456756591797</v>
+        <v>55.06457138061523</v>
       </c>
       <c r="C364" t="n">
-        <v>55.54774353916095</v>
+        <v>55.5477473873311</v>
       </c>
       <c r="D364" t="n">
-        <v>52.19186239249056</v>
+        <v>52.19186600817599</v>
       </c>
       <c r="E364" t="n">
-        <v>53.58868227771264</v>
+        <v>53.58868599016529</v>
       </c>
       <c r="F364" t="n">
         <v>1415773</v>
@@ -7712,16 +7712,16 @@
         <v>45005</v>
       </c>
       <c r="B365" t="n">
-        <v>52.49055480957031</v>
+        <v>52.49055099487305</v>
       </c>
       <c r="C365" t="n">
-        <v>55.60923982257214</v>
+        <v>55.60923578122764</v>
       </c>
       <c r="D365" t="n">
-        <v>52.18308009678171</v>
+        <v>52.18307630442985</v>
       </c>
       <c r="E365" t="n">
-        <v>54.03671863151492</v>
+        <v>54.03671470445178</v>
       </c>
       <c r="F365" t="n">
         <v>714391</v>
@@ -7772,16 +7772,16 @@
         <v>45008</v>
       </c>
       <c r="B368" t="n">
-        <v>49.1961669921875</v>
+        <v>49.19617080688477</v>
       </c>
       <c r="C368" t="n">
-        <v>53.29877430955613</v>
+        <v>53.29877844237178</v>
       </c>
       <c r="D368" t="n">
-        <v>48.85355136540186</v>
+        <v>48.85355515353253</v>
       </c>
       <c r="E368" t="n">
-        <v>52.56961857712928</v>
+        <v>52.56962265340579</v>
       </c>
       <c r="F368" t="n">
         <v>1208098</v>
@@ -7832,16 +7832,16 @@
         <v>45013</v>
       </c>
       <c r="B371" t="n">
-        <v>54.30905151367188</v>
+        <v>54.30905532836914</v>
       </c>
       <c r="C371" t="n">
-        <v>54.44961185010312</v>
+        <v>54.44961567467342</v>
       </c>
       <c r="D371" t="n">
-        <v>51.111301346444</v>
+        <v>51.11130493652956</v>
       </c>
       <c r="E371" t="n">
-        <v>51.83167348955698</v>
+        <v>51.83167713024186</v>
       </c>
       <c r="F371" t="n">
         <v>854484</v>
@@ -7872,16 +7872,16 @@
         <v>45015</v>
       </c>
       <c r="B373" t="n">
-        <v>54.20362854003906</v>
+        <v>54.20363235473633</v>
       </c>
       <c r="C373" t="n">
-        <v>56.39988239585843</v>
+        <v>56.3998863651218</v>
       </c>
       <c r="D373" t="n">
-        <v>53.7292361790246</v>
+        <v>53.72923996033548</v>
       </c>
       <c r="E373" t="n">
-        <v>54.03671084752145</v>
+        <v>54.03671465047152</v>
       </c>
       <c r="F373" t="n">
         <v>990197</v>
@@ -7892,16 +7892,16 @@
         <v>45016</v>
       </c>
       <c r="B374" t="n">
-        <v>52.33242416381836</v>
+        <v>52.33242034912109</v>
       </c>
       <c r="C374" t="n">
-        <v>54.73073698475589</v>
+        <v>54.73073299523703</v>
       </c>
       <c r="D374" t="n">
-        <v>51.94588404492639</v>
+        <v>51.94588025840541</v>
       </c>
       <c r="E374" t="n">
-        <v>54.20363651797383</v>
+        <v>54.20363256687721</v>
       </c>
       <c r="F374" t="n">
         <v>558868</v>
@@ -7912,16 +7912,16 @@
         <v>45019</v>
       </c>
       <c r="B375" t="n">
-        <v>49.41579437255859</v>
+        <v>49.41579055786133</v>
       </c>
       <c r="C375" t="n">
-        <v>52.67503973932627</v>
+        <v>52.67503567302858</v>
       </c>
       <c r="D375" t="n">
-        <v>49.41579437255859</v>
+        <v>49.41579055786133</v>
       </c>
       <c r="E375" t="n">
-        <v>52.34999456357366</v>
+        <v>52.34999052236814</v>
       </c>
       <c r="F375" t="n">
         <v>492395</v>
@@ -7932,16 +7932,16 @@
         <v>45020</v>
       </c>
       <c r="B376" t="n">
-        <v>48.90625762939453</v>
+        <v>48.9062614440918</v>
       </c>
       <c r="C376" t="n">
-        <v>50.48756562074401</v>
+        <v>50.48756955878359</v>
       </c>
       <c r="D376" t="n">
-        <v>48.55485846004571</v>
+        <v>48.55486224733378</v>
       </c>
       <c r="E376" t="n">
-        <v>49.59149220938691</v>
+        <v>49.5914960775326</v>
       </c>
       <c r="F376" t="n">
         <v>366364</v>
@@ -7952,16 +7952,16 @@
         <v>45021</v>
       </c>
       <c r="B377" t="n">
-        <v>48.90625762939453</v>
+        <v>48.9062614440918</v>
       </c>
       <c r="C377" t="n">
-        <v>49.20494876651357</v>
+        <v>49.2049526045088</v>
       </c>
       <c r="D377" t="n">
-        <v>47.2810285120021</v>
+        <v>47.2810321999312</v>
       </c>
       <c r="E377" t="n">
-        <v>48.94139855169625</v>
+        <v>48.94140236913452</v>
       </c>
       <c r="F377" t="n">
         <v>464516</v>
@@ -7972,16 +7972,16 @@
         <v>45022</v>
       </c>
       <c r="B378" t="n">
-        <v>48.04532623291016</v>
+        <v>48.04533004760742</v>
       </c>
       <c r="C378" t="n">
-        <v>49.56513596918133</v>
+        <v>49.56513990454828</v>
       </c>
       <c r="D378" t="n">
-        <v>47.88719543017925</v>
+        <v>47.88719923232127</v>
       </c>
       <c r="E378" t="n">
-        <v>48.64270852073295</v>
+        <v>48.64271238286111</v>
       </c>
       <c r="F378" t="n">
         <v>483494</v>
@@ -7992,16 +7992,16 @@
         <v>45026</v>
       </c>
       <c r="B379" t="n">
-        <v>48.75691604614258</v>
+        <v>48.75691223144531</v>
       </c>
       <c r="C379" t="n">
-        <v>49.21373800403698</v>
+        <v>49.21373415359837</v>
       </c>
       <c r="D379" t="n">
-        <v>48.01018984358273</v>
+        <v>48.01018608730865</v>
       </c>
       <c r="E379" t="n">
-        <v>48.3264481056115</v>
+        <v>48.32644432459367</v>
       </c>
       <c r="F379" t="n">
         <v>441343</v>
@@ -8012,16 +8012,16 @@
         <v>45027</v>
       </c>
       <c r="B380" t="n">
-        <v>54.63409805297852</v>
+        <v>54.63410186767578</v>
       </c>
       <c r="C380" t="n">
-        <v>54.63409805297852</v>
+        <v>54.63410186767578</v>
       </c>
       <c r="D380" t="n">
-        <v>48.85355030008497</v>
+        <v>48.8535537111691</v>
       </c>
       <c r="E380" t="n">
-        <v>48.85355030008497</v>
+        <v>48.8535537111691</v>
       </c>
       <c r="F380" t="n">
         <v>1223134</v>
@@ -8052,16 +8052,16 @@
         <v>45029</v>
       </c>
       <c r="B382" t="n">
-        <v>60.46735763549805</v>
+        <v>60.46736907958984</v>
       </c>
       <c r="C382" t="n">
-        <v>61.46006352292876</v>
+        <v>61.46007515490073</v>
       </c>
       <c r="D382" t="n">
-        <v>55.96063671432766</v>
+        <v>55.96064730547449</v>
       </c>
       <c r="E382" t="n">
-        <v>56.40867172931058</v>
+        <v>56.40868240525283</v>
       </c>
       <c r="F382" t="n">
         <v>2756815</v>
@@ -8072,16 +8072,16 @@
         <v>45030</v>
       </c>
       <c r="B383" t="n">
-        <v>60.44978713989258</v>
+        <v>60.44979476928711</v>
       </c>
       <c r="C383" t="n">
-        <v>62.15408504419084</v>
+        <v>62.15409288868556</v>
       </c>
       <c r="D383" t="n">
-        <v>59.10567866998549</v>
+        <v>59.1056861297395</v>
       </c>
       <c r="E383" t="n">
-        <v>60.45857404626561</v>
+        <v>60.45858167676914</v>
       </c>
       <c r="F383" t="n">
         <v>793877</v>
@@ -8092,16 +8092,16 @@
         <v>45033</v>
       </c>
       <c r="B384" t="n">
-        <v>59.95782470703125</v>
+        <v>59.95783615112305</v>
       </c>
       <c r="C384" t="n">
-        <v>60.7221246656276</v>
+        <v>60.72213625560059</v>
       </c>
       <c r="D384" t="n">
-        <v>59.16717073304285</v>
+        <v>59.16718202622329</v>
       </c>
       <c r="E384" t="n">
-        <v>60.35314834280274</v>
+        <v>60.35315986234957</v>
       </c>
       <c r="F384" t="n">
         <v>288592</v>
@@ -8112,16 +8112,16 @@
         <v>45034</v>
       </c>
       <c r="B385" t="n">
-        <v>61.49521255493164</v>
+        <v>61.49520874023438</v>
       </c>
       <c r="C385" t="n">
-        <v>61.49521255493164</v>
+        <v>61.49520874023438</v>
       </c>
       <c r="D385" t="n">
-        <v>59.16717816771997</v>
+        <v>59.16717449743633</v>
       </c>
       <c r="E385" t="n">
-        <v>59.16717816771997</v>
+        <v>59.16717449743633</v>
       </c>
       <c r="F385" t="n">
         <v>581190</v>
@@ -8132,16 +8132,16 @@
         <v>45035</v>
       </c>
       <c r="B386" t="n">
-        <v>58.84213256835938</v>
+        <v>58.84213638305664</v>
       </c>
       <c r="C386" t="n">
-        <v>61.27558287466414</v>
+        <v>61.2755868471204</v>
       </c>
       <c r="D386" t="n">
-        <v>58.30624521419173</v>
+        <v>58.30624899414777</v>
       </c>
       <c r="E386" t="n">
-        <v>61.27558287466414</v>
+        <v>61.2755868471204</v>
       </c>
       <c r="F386" t="n">
         <v>827950</v>
@@ -8152,16 +8152,16 @@
         <v>45036</v>
       </c>
       <c r="B387" t="n">
-        <v>60.80118942260742</v>
+        <v>60.80118560791016</v>
       </c>
       <c r="C387" t="n">
-        <v>60.80118942260742</v>
+        <v>60.80118560791016</v>
       </c>
       <c r="D387" t="n">
-        <v>58.21838855990702</v>
+        <v>58.21838490725599</v>
       </c>
       <c r="E387" t="n">
-        <v>58.78941682782696</v>
+        <v>58.78941313934933</v>
       </c>
       <c r="F387" t="n">
         <v>442904</v>
@@ -8172,16 +8172,16 @@
         <v>45040</v>
       </c>
       <c r="B388" t="n">
-        <v>60.99446487426758</v>
+        <v>60.99446868896484</v>
       </c>
       <c r="C388" t="n">
-        <v>61.2755855722359</v>
+        <v>61.27558940451494</v>
       </c>
       <c r="D388" t="n">
-        <v>59.73820528906153</v>
+        <v>59.73820902519019</v>
       </c>
       <c r="E388" t="n">
-        <v>60.27409266682086</v>
+        <v>60.27409643646482</v>
       </c>
       <c r="F388" t="n">
         <v>315786</v>
@@ -8252,16 +8252,16 @@
         <v>45044</v>
       </c>
       <c r="B392" t="n">
-        <v>63.67390441894531</v>
+        <v>63.67389297485352</v>
       </c>
       <c r="C392" t="n">
-        <v>63.75296647677501</v>
+        <v>63.75295501847341</v>
       </c>
       <c r="D392" t="n">
-        <v>60.61671083638181</v>
+        <v>60.6166999417585</v>
       </c>
       <c r="E392" t="n">
-        <v>61.50400079922254</v>
+        <v>61.50398974512687</v>
       </c>
       <c r="F392" t="n">
         <v>633625</v>
@@ -8312,16 +8312,16 @@
         <v>45050</v>
       </c>
       <c r="B395" t="n">
-        <v>60.79240798950195</v>
+        <v>60.79240417480469</v>
       </c>
       <c r="C395" t="n">
-        <v>61.56549495811417</v>
+        <v>61.56549109490604</v>
       </c>
       <c r="D395" t="n">
-        <v>58.60493728570287</v>
+        <v>58.60493360826845</v>
       </c>
       <c r="E395" t="n">
-        <v>58.60493728570287</v>
+        <v>58.60493360826845</v>
       </c>
       <c r="F395" t="n">
         <v>661928</v>
@@ -8352,16 +8352,16 @@
         <v>45054</v>
       </c>
       <c r="B397" t="n">
-        <v>65.16735076904297</v>
+        <v>65.1673583984375</v>
       </c>
       <c r="C397" t="n">
-        <v>65.74715924562913</v>
+        <v>65.74716694290409</v>
       </c>
       <c r="D397" t="n">
-        <v>63.59482964395288</v>
+        <v>63.59483708924626</v>
       </c>
       <c r="E397" t="n">
-        <v>63.76174735351282</v>
+        <v>63.7617548183479</v>
       </c>
       <c r="F397" t="n">
         <v>685640</v>
@@ -8412,16 +8412,16 @@
         <v>45057</v>
       </c>
       <c r="B400" t="n">
-        <v>67.00341033935547</v>
+        <v>67.00341796875</v>
       </c>
       <c r="C400" t="n">
-        <v>68.69892113120667</v>
+        <v>68.69892895366183</v>
       </c>
       <c r="D400" t="n">
-        <v>67.00341033935547</v>
+        <v>67.00341796875</v>
       </c>
       <c r="E400" t="n">
-        <v>67.38116683813408</v>
+        <v>67.38117451054214</v>
       </c>
       <c r="F400" t="n">
         <v>282491</v>
@@ -8432,16 +8432,16 @@
         <v>45058</v>
       </c>
       <c r="B401" t="n">
-        <v>66.23033905029297</v>
+        <v>66.23033142089844</v>
       </c>
       <c r="C401" t="n">
-        <v>67.00341925892872</v>
+        <v>67.00341154047932</v>
       </c>
       <c r="D401" t="n">
-        <v>65.81744157777364</v>
+        <v>65.81743399594278</v>
       </c>
       <c r="E401" t="n">
-        <v>66.79258042065457</v>
+        <v>66.79257272649272</v>
       </c>
       <c r="F401" t="n">
         <v>398348</v>
@@ -8492,16 +8492,16 @@
         <v>45063</v>
       </c>
       <c r="B404" t="n">
-        <v>72.32715606689453</v>
+        <v>72.3271484375</v>
       </c>
       <c r="C404" t="n">
-        <v>73.79425451837514</v>
+        <v>73.79424673422444</v>
       </c>
       <c r="D404" t="n">
-        <v>67.66230042003383</v>
+        <v>67.6622932827093</v>
       </c>
       <c r="E404" t="n">
-        <v>69.4105262754566</v>
+        <v>69.41051895372132</v>
       </c>
       <c r="F404" t="n">
         <v>1084227</v>
@@ -8512,16 +8512,16 @@
         <v>45064</v>
       </c>
       <c r="B405" t="n">
-        <v>71.18510437011719</v>
+        <v>71.18509674072266</v>
       </c>
       <c r="C405" t="n">
-        <v>71.99332560500903</v>
+        <v>71.99331788899191</v>
       </c>
       <c r="D405" t="n">
-        <v>69.86734973401003</v>
+        <v>69.86734224584828</v>
       </c>
       <c r="E405" t="n">
-        <v>71.15875034978652</v>
+        <v>71.15874272321652</v>
       </c>
       <c r="F405" t="n">
         <v>796674</v>
@@ -8552,16 +8552,16 @@
         <v>45068</v>
       </c>
       <c r="B407" t="n">
-        <v>77.76508331298828</v>
+        <v>77.76507568359375</v>
       </c>
       <c r="C407" t="n">
-        <v>78.30975759078616</v>
+        <v>78.3097499079546</v>
       </c>
       <c r="D407" t="n">
-        <v>75.07686625350173</v>
+        <v>75.0768588878434</v>
       </c>
       <c r="E407" t="n">
-        <v>75.45462281500996</v>
+        <v>75.45461541229061</v>
       </c>
       <c r="F407" t="n">
         <v>873661</v>
@@ -8632,16 +8632,16 @@
         <v>45072</v>
       </c>
       <c r="B411" t="n">
-        <v>82.75497436523438</v>
+        <v>82.75498199462891</v>
       </c>
       <c r="C411" t="n">
-        <v>84.15179752676379</v>
+        <v>84.15180528493505</v>
       </c>
       <c r="D411" t="n">
-        <v>80.38301910539758</v>
+        <v>80.38302651611544</v>
       </c>
       <c r="E411" t="n">
-        <v>81.70077351696148</v>
+        <v>81.70078104916651</v>
       </c>
       <c r="F411" t="n">
         <v>582166</v>
@@ -8652,16 +8652,16 @@
         <v>45075</v>
       </c>
       <c r="B412" t="n">
-        <v>81.52507781982422</v>
+        <v>81.52508544921875</v>
       </c>
       <c r="C412" t="n">
-        <v>83.1678740745439</v>
+        <v>83.1678818576769</v>
       </c>
       <c r="D412" t="n">
-        <v>80.73442381096265</v>
+        <v>80.73443136636509</v>
       </c>
       <c r="E412" t="n">
-        <v>82.66712765267252</v>
+        <v>82.66713538894396</v>
       </c>
       <c r="F412" t="n">
         <v>275309</v>
@@ -8672,16 +8672,16 @@
         <v>45076</v>
       </c>
       <c r="B413" t="n">
-        <v>80.55873107910156</v>
+        <v>80.5587158203125</v>
       </c>
       <c r="C413" t="n">
-        <v>84.13423840537149</v>
+        <v>84.13422246933848</v>
       </c>
       <c r="D413" t="n">
-        <v>79.3991072625396</v>
+        <v>79.39909222339719</v>
       </c>
       <c r="E413" t="n">
-        <v>82.54414994921937</v>
+        <v>82.54413431436818</v>
       </c>
       <c r="F413" t="n">
         <v>664894</v>
@@ -8692,16 +8692,16 @@
         <v>45077</v>
       </c>
       <c r="B414" t="n">
-        <v>78.81929016113281</v>
+        <v>78.81928253173828</v>
       </c>
       <c r="C414" t="n">
-        <v>80.38302442732773</v>
+        <v>80.38301664656991</v>
       </c>
       <c r="D414" t="n">
-        <v>78.53816946948481</v>
+        <v>78.53816186730164</v>
       </c>
       <c r="E414" t="n">
-        <v>79.97891385198659</v>
+        <v>79.97890611034508</v>
       </c>
       <c r="F414" t="n">
         <v>527775</v>
@@ -8732,16 +8732,16 @@
         <v>45079</v>
       </c>
       <c r="B416" t="n">
-        <v>82.84283447265625</v>
+        <v>82.84284210205078</v>
       </c>
       <c r="C416" t="n">
-        <v>84.02881216630033</v>
+        <v>84.02881990491723</v>
       </c>
       <c r="D416" t="n">
-        <v>78.89835122966686</v>
+        <v>78.89835849579498</v>
       </c>
       <c r="E416" t="n">
-        <v>78.89835122966686</v>
+        <v>78.89835849579498</v>
       </c>
       <c r="F416" t="n">
         <v>731024</v>
@@ -8792,16 +8792,16 @@
         <v>45084</v>
       </c>
       <c r="B419" t="n">
-        <v>86.52375793457031</v>
+        <v>86.52376556396484</v>
       </c>
       <c r="C419" t="n">
-        <v>86.60282668924023</v>
+        <v>86.60283432560681</v>
       </c>
       <c r="D419" t="n">
-        <v>82.88675607845614</v>
+        <v>82.88676338715122</v>
       </c>
       <c r="E419" t="n">
-        <v>84.3362873579094</v>
+        <v>84.33629479441962</v>
       </c>
       <c r="F419" t="n">
         <v>2805750</v>
@@ -8812,16 +8812,16 @@
         <v>45086</v>
       </c>
       <c r="B420" t="n">
-        <v>87.92935943603516</v>
+        <v>87.92936706542969</v>
       </c>
       <c r="C420" t="n">
-        <v>90.98655273412886</v>
+        <v>90.98656062878784</v>
       </c>
       <c r="D420" t="n">
-        <v>86.98058131812988</v>
+        <v>86.98058886520148</v>
       </c>
       <c r="E420" t="n">
-        <v>86.98058131812988</v>
+        <v>86.98058886520148</v>
       </c>
       <c r="F420" t="n">
         <v>1309381</v>
@@ -8852,16 +8852,16 @@
         <v>45090</v>
       </c>
       <c r="B422" t="n">
-        <v>86.91909027099609</v>
+        <v>86.91908264160156</v>
       </c>
       <c r="C422" t="n">
-        <v>91.17982854453695</v>
+        <v>91.17982054115261</v>
       </c>
       <c r="D422" t="n">
-        <v>86.91909027099609</v>
+        <v>86.91908264160156</v>
       </c>
       <c r="E422" t="n">
-        <v>90.48581035981377</v>
+        <v>90.48580241734746</v>
       </c>
       <c r="F422" t="n">
         <v>519950</v>
@@ -8892,16 +8892,16 @@
         <v>45092</v>
       </c>
       <c r="B424" t="n">
-        <v>91.97927093505859</v>
+        <v>91.97926330566406</v>
       </c>
       <c r="C424" t="n">
-        <v>92.26039165604509</v>
+        <v>92.26038400333246</v>
       </c>
       <c r="D424" t="n">
-        <v>89.18563083793495</v>
+        <v>89.18562344026418</v>
       </c>
       <c r="E424" t="n">
-        <v>89.43161733343898</v>
+        <v>89.43160991536439</v>
       </c>
       <c r="F424" t="n">
         <v>844482</v>
@@ -8912,16 +8912,16 @@
         <v>45093</v>
       </c>
       <c r="B425" t="n">
-        <v>94.66748046875</v>
+        <v>94.66748809814453</v>
       </c>
       <c r="C425" t="n">
-        <v>95.72168133556757</v>
+        <v>95.72168904992172</v>
       </c>
       <c r="D425" t="n">
-        <v>91.39066149194188</v>
+        <v>91.39066885725265</v>
       </c>
       <c r="E425" t="n">
-        <v>91.84748678268964</v>
+        <v>91.84749418481664</v>
       </c>
       <c r="F425" t="n">
         <v>1238876</v>
@@ -8932,16 +8932,16 @@
         <v>45096</v>
       </c>
       <c r="B426" t="n">
-        <v>98.03214263916016</v>
+        <v>98.03215026855469</v>
       </c>
       <c r="C426" t="n">
-        <v>98.33962403884159</v>
+        <v>98.33963169216599</v>
       </c>
       <c r="D426" t="n">
-        <v>94.14916114276463</v>
+        <v>94.14916846996442</v>
       </c>
       <c r="E426" t="n">
-        <v>94.61476664178524</v>
+        <v>94.61477400522099</v>
       </c>
       <c r="F426" t="n">
         <v>576522</v>
@@ -8992,16 +8992,16 @@
         <v>45099</v>
       </c>
       <c r="B429" t="n">
-        <v>99.27083587646484</v>
+        <v>99.27084350585938</v>
       </c>
       <c r="C429" t="n">
-        <v>104.858115316858</v>
+        <v>104.8581233756592</v>
       </c>
       <c r="D429" t="n">
-        <v>99.18298691971819</v>
+        <v>99.18299454236116</v>
       </c>
       <c r="E429" t="n">
-        <v>102.9605456793905</v>
+        <v>102.9605535923553</v>
       </c>
       <c r="F429" t="n">
         <v>1144936</v>
@@ -9012,16 +9012,16 @@
         <v>45100</v>
       </c>
       <c r="B430" t="n">
-        <v>98.56803131103516</v>
+        <v>98.56802368164062</v>
       </c>
       <c r="C430" t="n">
-        <v>100.544663008736</v>
+        <v>100.5446552263455</v>
       </c>
       <c r="D430" t="n">
-        <v>97.24149664189471</v>
+        <v>97.24148911517703</v>
       </c>
       <c r="E430" t="n">
-        <v>99.71008786179617</v>
+        <v>99.7100801440038</v>
       </c>
       <c r="F430" t="n">
         <v>1883788</v>
@@ -9032,16 +9032,16 @@
         <v>45103</v>
       </c>
       <c r="B431" t="n">
-        <v>97.00429534912109</v>
+        <v>97.00430297851562</v>
       </c>
       <c r="C431" t="n">
-        <v>99.27083459718358</v>
+        <v>99.27084240484157</v>
       </c>
       <c r="D431" t="n">
-        <v>95.75682275303549</v>
+        <v>95.75683028431621</v>
       </c>
       <c r="E431" t="n">
-        <v>98.46261348161649</v>
+        <v>98.46262122570784</v>
       </c>
       <c r="F431" t="n">
         <v>757098</v>
@@ -9052,16 +9052,16 @@
         <v>45104</v>
       </c>
       <c r="B432" t="n">
-        <v>94.86953735351562</v>
+        <v>94.86954498291016</v>
       </c>
       <c r="C432" t="n">
-        <v>98.3747691588906</v>
+        <v>98.37477707017537</v>
       </c>
       <c r="D432" t="n">
-        <v>91.40824008168553</v>
+        <v>91.40824743272303</v>
       </c>
       <c r="E432" t="n">
-        <v>96.9779458997876</v>
+        <v>96.97795369874004</v>
       </c>
       <c r="F432" t="n">
         <v>1484061</v>
@@ -9072,16 +9072,16 @@
         <v>45105</v>
       </c>
       <c r="B433" t="n">
-        <v>97.09215545654297</v>
+        <v>97.09214782714844</v>
       </c>
       <c r="C433" t="n">
-        <v>98.19028428396808</v>
+        <v>98.19027656828381</v>
       </c>
       <c r="D433" t="n">
-        <v>94.29851545147561</v>
+        <v>94.29850804160222</v>
       </c>
       <c r="E433" t="n">
-        <v>94.4742200853315</v>
+        <v>94.47421266165144</v>
       </c>
       <c r="F433" t="n">
         <v>538862</v>
@@ -9112,16 +9112,16 @@
         <v>45107</v>
       </c>
       <c r="B435" t="n">
-        <v>98.43625640869141</v>
+        <v>98.43626403808594</v>
       </c>
       <c r="C435" t="n">
-        <v>101.4758757552046</v>
+        <v>101.4758836201877</v>
       </c>
       <c r="D435" t="n">
-        <v>98.40111548704759</v>
+        <v>98.40112311371848</v>
       </c>
       <c r="E435" t="n">
-        <v>100.67643486831</v>
+        <v>100.6764426713316</v>
       </c>
       <c r="F435" t="n">
         <v>851232</v>
@@ -9132,16 +9132,16 @@
         <v>45110</v>
       </c>
       <c r="B436" t="n">
-        <v>100.8960800170898</v>
+        <v>100.8960647583008</v>
       </c>
       <c r="C436" t="n">
-        <v>101.4671083744049</v>
+        <v>101.4670930292576</v>
       </c>
       <c r="D436" t="n">
-        <v>98.26057070866375</v>
+        <v>98.26055584844994</v>
       </c>
       <c r="E436" t="n">
-        <v>98.46262937138633</v>
+        <v>98.46261448061463</v>
       </c>
       <c r="F436" t="n">
         <v>512630</v>
@@ -9252,16 +9252,16 @@
         <v>45118</v>
       </c>
       <c r="B442" t="n">
-        <v>99.71009063720703</v>
+        <v>99.7100830078125</v>
       </c>
       <c r="C442" t="n">
-        <v>99.71009063720703</v>
+        <v>99.7100830078125</v>
       </c>
       <c r="D442" t="n">
-        <v>94.7465473398877</v>
+        <v>94.74654009028252</v>
       </c>
       <c r="E442" t="n">
-        <v>97.71589177353913</v>
+        <v>97.71588429673227</v>
       </c>
       <c r="F442" t="n">
         <v>867229</v>
@@ -9292,16 +9292,16 @@
         <v>45120</v>
       </c>
       <c r="B444" t="n">
-        <v>97.98822021484375</v>
+        <v>97.98822784423828</v>
       </c>
       <c r="C444" t="n">
-        <v>101.0893345675846</v>
+        <v>101.0893424384329</v>
       </c>
       <c r="D444" t="n">
-        <v>97.21514002882437</v>
+        <v>97.21514759802663</v>
       </c>
       <c r="E444" t="n">
-        <v>99.32354175477643</v>
+        <v>99.32354948813953</v>
       </c>
       <c r="F444" t="n">
         <v>738822</v>
@@ -9312,16 +9312,16 @@
         <v>45121</v>
       </c>
       <c r="B445" t="n">
-        <v>96.74074554443359</v>
+        <v>96.74075317382812</v>
       </c>
       <c r="C445" t="n">
-        <v>98.69980333468348</v>
+        <v>98.69981111857781</v>
       </c>
       <c r="D445" t="n">
-        <v>95.02766080096731</v>
+        <v>95.02766829526057</v>
       </c>
       <c r="E445" t="n">
-        <v>98.69980333468348</v>
+        <v>98.69981111857781</v>
       </c>
       <c r="F445" t="n">
         <v>461646</v>
@@ -9332,16 +9332,16 @@
         <v>45124</v>
       </c>
       <c r="B446" t="n">
-        <v>99.48168182373047</v>
+        <v>99.48167419433594</v>
       </c>
       <c r="C446" t="n">
-        <v>99.48168182373047</v>
+        <v>99.48167419433594</v>
       </c>
       <c r="D446" t="n">
-        <v>95.75683083137832</v>
+        <v>95.75682348764802</v>
       </c>
       <c r="E446" t="n">
-        <v>96.44206212640412</v>
+        <v>96.44205473012244</v>
       </c>
       <c r="F446" t="n">
         <v>395417</v>
@@ -9352,16 +9352,16 @@
         <v>45125</v>
       </c>
       <c r="B447" t="n">
-        <v>101.4231643676758</v>
+        <v>101.4231719970703</v>
       </c>
       <c r="C447" t="n">
-        <v>103.6633496036482</v>
+        <v>103.663357401557</v>
       </c>
       <c r="D447" t="n">
-        <v>98.74373435277772</v>
+        <v>98.74374178061643</v>
       </c>
       <c r="E447" t="n">
-        <v>99.27083478993424</v>
+        <v>99.27084225742324</v>
       </c>
       <c r="F447" t="n">
         <v>594813</v>
@@ -9392,16 +9392,16 @@
         <v>45127</v>
       </c>
       <c r="B449" t="n">
-        <v>106.913818359375</v>
+        <v>106.9138107299805</v>
       </c>
       <c r="C449" t="n">
-        <v>107.2740078265619</v>
+        <v>107.2740001714642</v>
       </c>
       <c r="D449" t="n">
-        <v>100.3601864195351</v>
+        <v>100.3601792578093</v>
       </c>
       <c r="E449" t="n">
-        <v>100.4919632173461</v>
+        <v>100.4919560462166</v>
       </c>
       <c r="F449" t="n">
         <v>1906043</v>
@@ -9432,16 +9432,16 @@
         <v>45131</v>
       </c>
       <c r="B451" t="n">
-        <v>112.6240768432617</v>
+        <v>112.6240844726562</v>
       </c>
       <c r="C451" t="n">
-        <v>113.1160363563073</v>
+        <v>113.1160440190282</v>
       </c>
       <c r="D451" t="n">
-        <v>109.3033367253127</v>
+        <v>109.3033441297533</v>
       </c>
       <c r="E451" t="n">
-        <v>110.8582907186036</v>
+        <v>110.85829822838</v>
       </c>
       <c r="F451" t="n">
         <v>870351</v>
@@ -9472,16 +9472,16 @@
         <v>45133</v>
       </c>
       <c r="B453" t="n">
-        <v>113.8891296386719</v>
+        <v>113.8891372680664</v>
       </c>
       <c r="C453" t="n">
-        <v>113.9857655059323</v>
+        <v>113.9857731418005</v>
       </c>
       <c r="D453" t="n">
-        <v>110.5508155209108</v>
+        <v>110.5508229266728</v>
       </c>
       <c r="E453" t="n">
-        <v>111.0427817639948</v>
+        <v>111.0427892027134</v>
       </c>
       <c r="F453" t="n">
         <v>810223</v>
@@ -9512,16 +9512,16 @@
         <v>45135</v>
       </c>
       <c r="B455" t="n">
-        <v>109.8919448852539</v>
+        <v>109.8919372558594</v>
       </c>
       <c r="C455" t="n">
-        <v>111.9915733711529</v>
+        <v>111.9915655959889</v>
       </c>
       <c r="D455" t="n">
-        <v>108.0558767015642</v>
+        <v>108.0558691996412</v>
       </c>
       <c r="E455" t="n">
-        <v>110.6913858894073</v>
+        <v>110.6913782045105</v>
       </c>
       <c r="F455" t="n">
         <v>651013</v>
@@ -9552,16 +9552,16 @@
         <v>45139</v>
       </c>
       <c r="B457" t="n">
-        <v>113.2302474975586</v>
+        <v>113.2302551269531</v>
       </c>
       <c r="C457" t="n">
-        <v>113.6343647627333</v>
+        <v>113.6343724193571</v>
       </c>
       <c r="D457" t="n">
-        <v>109.1803482614203</v>
+        <v>109.1803556179347</v>
       </c>
       <c r="E457" t="n">
-        <v>111.5698774170749</v>
+        <v>111.5698849345946</v>
       </c>
       <c r="F457" t="n">
         <v>739423</v>
@@ -9572,16 +9572,16 @@
         <v>45140</v>
       </c>
       <c r="B458" t="n">
-        <v>112.2726898193359</v>
+        <v>112.2726821899414</v>
       </c>
       <c r="C458" t="n">
-        <v>112.4220337257216</v>
+        <v>112.4220260861785</v>
       </c>
       <c r="D458" t="n">
-        <v>108.6620418329161</v>
+        <v>108.66203444888</v>
       </c>
       <c r="E458" t="n">
-        <v>111.6928746028557</v>
+        <v>111.692867012862</v>
       </c>
       <c r="F458" t="n">
         <v>921444</v>
@@ -9612,16 +9612,16 @@
         <v>45142</v>
       </c>
       <c r="B460" t="n">
-        <v>113.1336212158203</v>
+        <v>113.1336135864258</v>
       </c>
       <c r="C460" t="n">
-        <v>114.6007196943687</v>
+        <v>114.6007119660374</v>
       </c>
       <c r="D460" t="n">
-        <v>110.9900716383365</v>
+        <v>110.9900641534965</v>
       </c>
       <c r="E460" t="n">
-        <v>114.2053960045622</v>
+        <v>114.2053883028904</v>
       </c>
       <c r="F460" t="n">
         <v>805649</v>
@@ -9632,16 +9632,16 @@
         <v>45145</v>
       </c>
       <c r="B461" t="n">
-        <v>112.9930572509766</v>
+        <v>112.9930419921875</v>
       </c>
       <c r="C461" t="n">
-        <v>117.7194079181516</v>
+        <v>117.7193920211075</v>
       </c>
       <c r="D461" t="n">
-        <v>111.6225946468615</v>
+        <v>111.6225795731422</v>
       </c>
       <c r="E461" t="n">
-        <v>113.326892697325</v>
+        <v>113.3268773934542</v>
       </c>
       <c r="F461" t="n">
         <v>579696</v>
@@ -9692,16 +9692,16 @@
         <v>45148</v>
       </c>
       <c r="B464" t="n">
-        <v>110.5156860351562</v>
+        <v>110.5156784057617</v>
       </c>
       <c r="C464" t="n">
-        <v>114.5919396385741</v>
+        <v>114.5919317277774</v>
       </c>
       <c r="D464" t="n">
-        <v>109.2857804284043</v>
+        <v>109.2857728839157</v>
       </c>
       <c r="E464" t="n">
-        <v>111.7455849394619</v>
+        <v>111.7455772251619</v>
       </c>
       <c r="F464" t="n">
         <v>733254</v>
@@ -9732,16 +9732,16 @@
         <v>45152</v>
       </c>
       <c r="B466" t="n">
-        <v>113.0633239746094</v>
+        <v>113.0633316040039</v>
       </c>
       <c r="C466" t="n">
-        <v>113.0633239746094</v>
+        <v>113.0633316040039</v>
       </c>
       <c r="D466" t="n">
-        <v>106.3779161668596</v>
+        <v>106.3779233451298</v>
       </c>
       <c r="E466" t="n">
-        <v>108.9431498064393</v>
+        <v>108.9431571578088</v>
       </c>
       <c r="F466" t="n">
         <v>1213584</v>
@@ -9772,16 +9772,16 @@
         <v>45154</v>
       </c>
       <c r="B468" t="n">
-        <v>108.6444702148438</v>
+        <v>108.6444625854492</v>
       </c>
       <c r="C468" t="n">
-        <v>111.8422207697557</v>
+        <v>111.842212915804</v>
       </c>
       <c r="D468" t="n">
-        <v>107.0983096778717</v>
+        <v>107.098302157054</v>
       </c>
       <c r="E468" t="n">
-        <v>108.2403596175138</v>
+        <v>108.2403520164973</v>
       </c>
       <c r="F468" t="n">
         <v>1047832</v>
@@ -9792,16 +9792,16 @@
         <v>45155</v>
       </c>
       <c r="B469" t="n">
-        <v>103.6633529663086</v>
+        <v>103.6633453369141</v>
       </c>
       <c r="C469" t="n">
-        <v>109.7689460744476</v>
+        <v>109.7689379956948</v>
       </c>
       <c r="D469" t="n">
-        <v>103.048403553419</v>
+        <v>103.0483959692834</v>
       </c>
       <c r="E469" t="n">
-        <v>108.9782987442884</v>
+        <v>108.9782907237255</v>
       </c>
       <c r="F469" t="n">
         <v>1841816</v>
@@ -9812,16 +9812,16 @@
         <v>45156</v>
       </c>
       <c r="B470" t="n">
-        <v>109.1539993286133</v>
+        <v>109.1539916992188</v>
       </c>
       <c r="C470" t="n">
-        <v>109.2242811782168</v>
+        <v>109.2242735439098</v>
       </c>
       <c r="D470" t="n">
-        <v>104.6912024154841</v>
+        <v>104.6911950980199</v>
       </c>
       <c r="E470" t="n">
-        <v>106.2549367057079</v>
+        <v>106.2549292789454</v>
       </c>
       <c r="F470" t="n">
         <v>1642163</v>
@@ -9852,16 +9852,16 @@
         <v>45160</v>
       </c>
       <c r="B472" t="n">
-        <v>113.9594116210938</v>
+        <v>113.9594039916992</v>
       </c>
       <c r="C472" t="n">
-        <v>114.0033394526074</v>
+        <v>114.003331820272</v>
       </c>
       <c r="D472" t="n">
-        <v>111.1745586857447</v>
+        <v>111.1745512427915</v>
       </c>
       <c r="E472" t="n">
-        <v>111.534741434862</v>
+        <v>111.5347339677951</v>
       </c>
       <c r="F472" t="n">
         <v>933012</v>
@@ -9872,16 +9872,16 @@
         <v>45161</v>
       </c>
       <c r="B473" t="n">
-        <v>117.4294891357422</v>
+        <v>117.4294967651367</v>
       </c>
       <c r="C473" t="n">
-        <v>117.9390224614812</v>
+        <v>117.9390301239801</v>
       </c>
       <c r="D473" t="n">
-        <v>112.9491320795816</v>
+        <v>112.9491394178873</v>
       </c>
       <c r="E473" t="n">
-        <v>114.0296869677586</v>
+        <v>114.0296943762679</v>
       </c>
       <c r="F473" t="n">
         <v>1193312</v>
@@ -9912,16 +9912,16 @@
         <v>45163</v>
       </c>
       <c r="B475" t="n">
-        <v>110.4278182983398</v>
+        <v>110.4278259277344</v>
       </c>
       <c r="C475" t="n">
-        <v>112.7997735858911</v>
+        <v>112.7997813791627</v>
       </c>
       <c r="D475" t="n">
-        <v>108.5917503472816</v>
+        <v>108.5917578498233</v>
       </c>
       <c r="E475" t="n">
-        <v>112.6240756766079</v>
+        <v>112.6240834577406</v>
       </c>
       <c r="F475" t="n">
         <v>1445522</v>
@@ -9952,16 +9952,16 @@
         <v>45167</v>
       </c>
       <c r="B477" t="n">
-        <v>113.318115234375</v>
+        <v>113.3181076049805</v>
       </c>
       <c r="C477" t="n">
-        <v>113.3620296637317</v>
+        <v>113.3620220313805</v>
       </c>
       <c r="D477" t="n">
-        <v>109.426339684017</v>
+        <v>109.426332316645</v>
       </c>
       <c r="E477" t="n">
-        <v>112.0091408411367</v>
+        <v>112.0091332998718</v>
       </c>
       <c r="F477" t="n">
         <v>768114</v>
@@ -10052,16 +10052,16 @@
         <v>45174</v>
       </c>
       <c r="B482" t="n">
-        <v>110.4717559814453</v>
+        <v>110.4717483520508</v>
       </c>
       <c r="C482" t="n">
-        <v>114.2053938575578</v>
+        <v>114.2053859703109</v>
       </c>
       <c r="D482" t="n">
-        <v>110.3839070189672</v>
+        <v>110.3838993956397</v>
       </c>
       <c r="E482" t="n">
-        <v>114.2053938575578</v>
+        <v>114.2053859703109</v>
       </c>
       <c r="F482" t="n">
         <v>645307</v>
@@ -10072,16 +10072,16 @@
         <v>45175</v>
       </c>
       <c r="B483" t="n">
-        <v>110.331184387207</v>
+        <v>110.3311920166016</v>
       </c>
       <c r="C483" t="n">
-        <v>113.1072569795688</v>
+        <v>113.1072648009286</v>
       </c>
       <c r="D483" t="n">
-        <v>108.3106315849618</v>
+        <v>108.3106390746352</v>
       </c>
       <c r="E483" t="n">
-        <v>110.471748079074</v>
+        <v>110.4717557181885</v>
       </c>
       <c r="F483" t="n">
         <v>1014845</v>
@@ -10232,16 +10232,16 @@
         <v>45188</v>
       </c>
       <c r="B491" t="n">
-        <v>111.9991912841797</v>
+        <v>111.9991989135742</v>
       </c>
       <c r="C491" t="n">
-        <v>115.957390144112</v>
+        <v>115.9573980431394</v>
       </c>
       <c r="D491" t="n">
-        <v>111.2705240431784</v>
+        <v>111.2705316229361</v>
       </c>
       <c r="E491" t="n">
-        <v>115.336683264999</v>
+        <v>115.3366911217438</v>
       </c>
       <c r="F491" t="n">
         <v>598810</v>
@@ -10272,16 +10272,16 @@
         <v>45190</v>
       </c>
       <c r="B493" t="n">
-        <v>104.1187591552734</v>
+        <v>104.118766784668</v>
       </c>
       <c r="C493" t="n">
-        <v>109.5343059543656</v>
+        <v>109.5343139805892</v>
       </c>
       <c r="D493" t="n">
-        <v>103.6509744115351</v>
+        <v>103.6509820066523</v>
       </c>
       <c r="E493" t="n">
-        <v>109.4353503014581</v>
+        <v>109.4353583204306</v>
       </c>
       <c r="F493" t="n">
         <v>1919322</v>
@@ -10312,16 +10312,16 @@
         <v>45194</v>
       </c>
       <c r="B495" t="n">
-        <v>103.525032043457</v>
+        <v>103.5250396728516</v>
       </c>
       <c r="C495" t="n">
-        <v>104.2986815857532</v>
+        <v>104.2986892721627</v>
       </c>
       <c r="D495" t="n">
-        <v>102.3825465471945</v>
+        <v>102.3825540923923</v>
       </c>
       <c r="E495" t="n">
-        <v>103.8938611340822</v>
+        <v>103.893868790658</v>
       </c>
       <c r="F495" t="n">
         <v>399935</v>
@@ -10332,16 +10332,16 @@
         <v>45195</v>
       </c>
       <c r="B496" t="n">
-        <v>101.5549240112305</v>
+        <v>101.554931640625</v>
       </c>
       <c r="C496" t="n">
-        <v>103.8129014901132</v>
+        <v>103.8129092891401</v>
       </c>
       <c r="D496" t="n">
-        <v>100.862241302414</v>
+        <v>100.8622488797702</v>
       </c>
       <c r="E496" t="n">
-        <v>101.6538796643958</v>
+        <v>101.6538873012245</v>
       </c>
       <c r="F496" t="n">
         <v>1664293</v>
@@ -10392,16 +10392,16 @@
         <v>45198</v>
       </c>
       <c r="B499" t="n">
-        <v>104.2177124023438</v>
+        <v>104.2177200317383</v>
       </c>
       <c r="C499" t="n">
-        <v>107.0514280468401</v>
+        <v>107.0514358836805</v>
       </c>
       <c r="D499" t="n">
-        <v>103.4080783805818</v>
+        <v>103.408085950706</v>
       </c>
       <c r="E499" t="n">
-        <v>107.0514280468401</v>
+        <v>107.0514358836805</v>
       </c>
       <c r="F499" t="n">
         <v>323662</v>
@@ -10452,16 +10452,16 @@
         <v>45203</v>
       </c>
       <c r="B502" t="n">
-        <v>101.7978210449219</v>
+        <v>101.7978286743164</v>
       </c>
       <c r="C502" t="n">
-        <v>102.1666501489935</v>
+        <v>102.1666578060305</v>
       </c>
       <c r="D502" t="n">
-        <v>98.96410523328106</v>
+        <v>98.96411265029839</v>
       </c>
       <c r="E502" t="n">
-        <v>99.85469927807969</v>
+        <v>99.85470676184396</v>
       </c>
       <c r="F502" t="n">
         <v>483635</v>
@@ -10592,16 +10592,16 @@
         <v>45215</v>
       </c>
       <c r="B509" t="n">
-        <v>96.91303253173828</v>
+        <v>96.91304016113281</v>
       </c>
       <c r="C509" t="n">
-        <v>98.87414302938409</v>
+        <v>98.87415081316534</v>
       </c>
       <c r="D509" t="n">
-        <v>96.44524092862584</v>
+        <v>96.44524852119388</v>
       </c>
       <c r="E509" t="n">
-        <v>97.20989262460226</v>
+        <v>97.20990027736684</v>
       </c>
       <c r="F509" t="n">
         <v>1010350</v>
@@ -10652,16 +10652,16 @@
         <v>45218</v>
       </c>
       <c r="B512" t="n">
-        <v>94.34919738769531</v>
+        <v>94.34918975830078</v>
       </c>
       <c r="C512" t="n">
-        <v>95.99545223608963</v>
+        <v>95.99544447357339</v>
       </c>
       <c r="D512" t="n">
-        <v>92.76592056203434</v>
+        <v>92.76591306066892</v>
       </c>
       <c r="E512" t="n">
-        <v>93.46760115621116</v>
+        <v>93.46759359810548</v>
       </c>
       <c r="F512" t="n">
         <v>760940</v>
@@ -10672,16 +10672,16 @@
         <v>45219</v>
       </c>
       <c r="B513" t="n">
-        <v>96.25634002685547</v>
+        <v>96.25633239746094</v>
       </c>
       <c r="C513" t="n">
-        <v>96.43625567409222</v>
+        <v>96.43624803043737</v>
       </c>
       <c r="D513" t="n">
-        <v>93.06278581333794</v>
+        <v>93.0627784370684</v>
       </c>
       <c r="E513" t="n">
-        <v>93.27869282603245</v>
+        <v>93.27868543264987</v>
       </c>
       <c r="F513" t="n">
         <v>605848</v>
@@ -10692,16 +10692,16 @@
         <v>45222</v>
       </c>
       <c r="B514" t="n">
-        <v>96.25634002685547</v>
+        <v>96.25633239746094</v>
       </c>
       <c r="C514" t="n">
-        <v>97.29087215682185</v>
+        <v>97.29086444542904</v>
       </c>
       <c r="D514" t="n">
-        <v>93.93539111545444</v>
+        <v>93.93538367002114</v>
       </c>
       <c r="E514" t="n">
-        <v>96.0764243796187</v>
+        <v>96.07641676448451</v>
       </c>
       <c r="F514" t="n">
         <v>469364</v>
@@ -10732,16 +10732,16 @@
         <v>45224</v>
       </c>
       <c r="B516" t="n">
-        <v>89.44641876220703</v>
+        <v>89.44642639160156</v>
       </c>
       <c r="C516" t="n">
-        <v>92.42406561747359</v>
+        <v>92.42407350084858</v>
       </c>
       <c r="D516" t="n">
-        <v>87.28739692921076</v>
+        <v>87.28740437445002</v>
       </c>
       <c r="E516" t="n">
-        <v>92.42406561747359</v>
+        <v>92.42407350084858</v>
       </c>
       <c r="F516" t="n">
         <v>1619426</v>
@@ -10772,16 +10772,16 @@
         <v>45226</v>
       </c>
       <c r="B518" t="n">
-        <v>90.64288330078125</v>
+        <v>90.64289093017578</v>
       </c>
       <c r="C518" t="n">
-        <v>93.4136211835644</v>
+        <v>93.41362904617142</v>
       </c>
       <c r="D518" t="n">
-        <v>90.64288330078125</v>
+        <v>90.64289093017578</v>
       </c>
       <c r="E518" t="n">
-        <v>92.37009813082983</v>
+        <v>92.37010590560371</v>
       </c>
       <c r="F518" t="n">
         <v>492223</v>
@@ -10812,16 +10812,16 @@
         <v>45230</v>
       </c>
       <c r="B520" t="n">
-        <v>91.32656097412109</v>
+        <v>91.32656860351562</v>
       </c>
       <c r="C520" t="n">
-        <v>91.32656097412109</v>
+        <v>91.32656860351562</v>
       </c>
       <c r="D520" t="n">
-        <v>88.72674109428142</v>
+        <v>88.72674850648775</v>
       </c>
       <c r="E520" t="n">
-        <v>89.94119557423609</v>
+        <v>89.94120308789761</v>
       </c>
       <c r="F520" t="n">
         <v>382337</v>
@@ -10852,16 +10852,16 @@
         <v>45233</v>
       </c>
       <c r="B522" t="n">
-        <v>94.61008453369141</v>
+        <v>94.61007690429688</v>
       </c>
       <c r="C522" t="n">
-        <v>97.14693357959244</v>
+        <v>97.14692574562541</v>
       </c>
       <c r="D522" t="n">
-        <v>92.08223332910212</v>
+        <v>92.08222590355452</v>
       </c>
       <c r="E522" t="n">
-        <v>92.70295397611622</v>
+        <v>92.70294650051345</v>
       </c>
       <c r="F522" t="n">
         <v>760712</v>
@@ -10872,16 +10872,16 @@
         <v>45236</v>
       </c>
       <c r="B523" t="n">
-        <v>92.2171630859375</v>
+        <v>92.21717071533203</v>
       </c>
       <c r="C523" t="n">
-        <v>95.9864482957361</v>
+        <v>95.98645623697459</v>
       </c>
       <c r="D523" t="n">
-        <v>91.38953336222757</v>
+        <v>91.38954092314988</v>
       </c>
       <c r="E523" t="n">
-        <v>95.13183877782029</v>
+        <v>95.13184664835444</v>
       </c>
       <c r="F523" t="n">
         <v>393989</v>
@@ -10932,16 +10932,16 @@
         <v>45239</v>
       </c>
       <c r="B526" t="n">
-        <v>95.28477478027344</v>
+        <v>95.28478240966797</v>
       </c>
       <c r="C526" t="n">
-        <v>97.73166590751246</v>
+        <v>97.73167373282809</v>
       </c>
       <c r="D526" t="n">
-        <v>94.73602315850255</v>
+        <v>94.73603074395886</v>
       </c>
       <c r="E526" t="n">
-        <v>97.21889878624117</v>
+        <v>97.21890657049985</v>
       </c>
       <c r="F526" t="n">
         <v>493995</v>
@@ -11012,16 +11012,16 @@
         <v>45246</v>
       </c>
       <c r="B530" t="n">
-        <v>101.6538848876953</v>
+        <v>101.6538925170898</v>
       </c>
       <c r="C530" t="n">
-        <v>103.6599778482697</v>
+        <v>103.6599856282268</v>
       </c>
       <c r="D530" t="n">
-        <v>99.45887845137312</v>
+        <v>99.45888591602659</v>
       </c>
       <c r="E530" t="n">
-        <v>100.4214415116168</v>
+        <v>100.4214490485131</v>
       </c>
       <c r="F530" t="n">
         <v>1796629</v>
@@ -11072,16 +11072,16 @@
         <v>45251</v>
       </c>
       <c r="B533" t="n">
-        <v>100.2595138549805</v>
+        <v>100.2595062255859</v>
       </c>
       <c r="C533" t="n">
-        <v>103.0932296941449</v>
+        <v>103.0932218491147</v>
       </c>
       <c r="D533" t="n">
-        <v>99.13502398732325</v>
+        <v>99.13501644349843</v>
       </c>
       <c r="E533" t="n">
-        <v>102.5804625890269</v>
+        <v>102.5804547830164</v>
       </c>
       <c r="F533" t="n">
         <v>1091156</v>
@@ -11332,16 +11332,16 @@
         <v>45268</v>
       </c>
       <c r="B546" t="n">
-        <v>105.4321594238281</v>
+        <v>105.4321670532227</v>
       </c>
       <c r="C546" t="n">
-        <v>108.7156709664404</v>
+        <v>108.7156788334399</v>
       </c>
       <c r="D546" t="n">
-        <v>105.2522438036881</v>
+        <v>105.2522514200634</v>
       </c>
       <c r="E546" t="n">
-        <v>106.961469648382</v>
+        <v>106.9614773884421</v>
       </c>
       <c r="F546" t="n">
         <v>678575</v>
@@ -24492,19 +24492,39 @@
         <v>46234</v>
       </c>
       <c r="B1204" t="n">
-        <v>86.56</v>
+        <v>86.55999755859375</v>
       </c>
       <c r="C1204" t="n">
         <v>87</v>
       </c>
       <c r="D1204" t="n">
-        <v>86.19</v>
+        <v>86.19000244140625</v>
       </c>
       <c r="E1204" t="n">
-        <v>86.31</v>
+        <v>86.30999755859375</v>
       </c>
       <c r="F1204" t="n">
         <v>256130</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B1205" t="n">
+        <v>86.75</v>
+      </c>
+      <c r="C1205" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>85.92</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="F1205" t="n">
+        <v>302511</v>
       </c>
     </row>
   </sheetData>

--- a/database/XPBR31.xlsx
+++ b/database/XPBR31.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1207"/>
+  <dimension ref="A1:F1208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>44473</v>
       </c>
       <c r="B2" t="n">
-        <v>196.6089630126953</v>
+        <v>196.6089782714844</v>
       </c>
       <c r="C2" t="n">
-        <v>203.5754849761604</v>
+        <v>203.5755007756201</v>
       </c>
       <c r="D2" t="n">
-        <v>191.4433613739322</v>
+        <v>191.4433762318198</v>
       </c>
       <c r="E2" t="n">
-        <v>191.9528946938346</v>
+        <v>191.9529095912669</v>
       </c>
       <c r="F2" t="n">
         <v>9950865</v>
@@ -472,16 +472,16 @@
         <v>44474</v>
       </c>
       <c r="B3" t="n">
-        <v>192.5414886474609</v>
+        <v>192.54150390625</v>
       </c>
       <c r="C3" t="n">
-        <v>198.9809168362223</v>
+        <v>198.9809326053319</v>
       </c>
       <c r="D3" t="n">
-        <v>187.7272962672212</v>
+        <v>187.7273111444886</v>
       </c>
       <c r="E3" t="n">
-        <v>197.6631624200884</v>
+        <v>197.6631780847668</v>
       </c>
       <c r="F3" t="n">
         <v>2636287</v>
@@ -532,16 +532,16 @@
         <v>44477</v>
       </c>
       <c r="B6" t="n">
-        <v>193.8241271972656</v>
+        <v>193.8241119384766</v>
       </c>
       <c r="C6" t="n">
-        <v>204.8669032795693</v>
+        <v>204.8668871514385</v>
       </c>
       <c r="D6" t="n">
-        <v>191.794787349043</v>
+        <v>191.7947722500135</v>
       </c>
       <c r="E6" t="n">
-        <v>200.9927017121121</v>
+        <v>200.9926858889775</v>
       </c>
       <c r="F6" t="n">
         <v>4982319</v>
@@ -552,16 +552,16 @@
         <v>44480</v>
       </c>
       <c r="B7" t="n">
-        <v>180.0931091308594</v>
+        <v>180.0931243896484</v>
       </c>
       <c r="C7" t="n">
-        <v>193.1125296009114</v>
+        <v>193.1125459627998</v>
       </c>
       <c r="D7" t="n">
-        <v>180.0931091308594</v>
+        <v>180.0931243896484</v>
       </c>
       <c r="E7" t="n">
-        <v>191.8738371941056</v>
+        <v>191.8738534510431</v>
       </c>
       <c r="F7" t="n">
         <v>2006205</v>
@@ -592,16 +592,16 @@
         <v>44483</v>
       </c>
       <c r="B9" t="n">
-        <v>164.7632446289062</v>
+        <v>164.7632293701172</v>
       </c>
       <c r="C9" t="n">
-        <v>173.8293888548571</v>
+        <v>173.8293727564489</v>
       </c>
       <c r="D9" t="n">
-        <v>164.2888454897918</v>
+        <v>164.2888302749371</v>
       </c>
       <c r="E9" t="n">
-        <v>171.8351966443599</v>
+        <v>171.8351807306346</v>
       </c>
       <c r="F9" t="n">
         <v>3205420</v>
@@ -612,16 +612,16 @@
         <v>44484</v>
       </c>
       <c r="B10" t="n">
-        <v>175.7005920410156</v>
+        <v>175.7006072998047</v>
       </c>
       <c r="C10" t="n">
-        <v>178.977404329211</v>
+        <v>178.9774198725761</v>
       </c>
       <c r="D10" t="n">
-        <v>166.9155624389649</v>
+        <v>166.9155769348145</v>
       </c>
       <c r="E10" t="n">
-        <v>166.9155624389649</v>
+        <v>166.9155769348145</v>
       </c>
       <c r="F10" t="n">
         <v>2643581</v>
@@ -632,16 +632,16 @@
         <v>44487</v>
       </c>
       <c r="B11" t="n">
-        <v>179.4166564941406</v>
+        <v>179.4166412353516</v>
       </c>
       <c r="C11" t="n">
-        <v>182.2717911257051</v>
+        <v>182.2717756240963</v>
       </c>
       <c r="D11" t="n">
-        <v>175.0680695055053</v>
+        <v>175.0680546165491</v>
       </c>
       <c r="E11" t="n">
-        <v>176.7547935869503</v>
+        <v>176.7547785545438</v>
       </c>
       <c r="F11" t="n">
         <v>1369949</v>
@@ -672,16 +672,16 @@
         <v>44489</v>
       </c>
       <c r="B13" t="n">
-        <v>174.3828430175781</v>
+        <v>174.3828582763672</v>
       </c>
       <c r="C13" t="n">
-        <v>178.4942305647025</v>
+        <v>178.4942461832448</v>
       </c>
       <c r="D13" t="n">
-        <v>169.8409841808207</v>
+        <v>169.8409990421895</v>
       </c>
       <c r="E13" t="n">
-        <v>176.5791004863134</v>
+        <v>176.5791159372786</v>
       </c>
       <c r="F13" t="n">
         <v>1907987</v>
@@ -692,16 +692,16 @@
         <v>44490</v>
       </c>
       <c r="B14" t="n">
-        <v>169.4193115234375</v>
+        <v>169.4192962646484</v>
       </c>
       <c r="C14" t="n">
-        <v>176.2189162691178</v>
+        <v>176.2189003979208</v>
       </c>
       <c r="D14" t="n">
-        <v>167.1615523442876</v>
+        <v>167.1615372888441</v>
       </c>
       <c r="E14" t="n">
-        <v>173.3989291023892</v>
+        <v>173.3989134851749</v>
       </c>
       <c r="F14" t="n">
         <v>1852525</v>
@@ -712,16 +712,16 @@
         <v>44491</v>
       </c>
       <c r="B15" t="n">
-        <v>166.0546264648438</v>
+        <v>166.0546417236328</v>
       </c>
       <c r="C15" t="n">
-        <v>170.8600385320068</v>
+        <v>170.8600542323661</v>
       </c>
       <c r="D15" t="n">
-        <v>159.8084701383689</v>
+        <v>159.8084848231975</v>
       </c>
       <c r="E15" t="n">
-        <v>169.5510643493521</v>
+        <v>169.5510799294295</v>
       </c>
       <c r="F15" t="n">
         <v>1387914</v>
@@ -732,16 +732,16 @@
         <v>44494</v>
       </c>
       <c r="B16" t="n">
-        <v>169.1206207275391</v>
+        <v>169.12060546875</v>
       </c>
       <c r="C16" t="n">
-        <v>174.5849108807135</v>
+        <v>174.5848951289127</v>
       </c>
       <c r="D16" t="n">
-        <v>167.3636145922391</v>
+        <v>167.3635994919746</v>
       </c>
       <c r="E16" t="n">
-        <v>167.7062302524268</v>
+        <v>167.7062151212502</v>
       </c>
       <c r="F16" t="n">
         <v>1203463</v>
@@ -792,16 +792,16 @@
         <v>44497</v>
       </c>
       <c r="B19" t="n">
-        <v>165.1673583984375</v>
+        <v>165.1673431396484</v>
       </c>
       <c r="C19" t="n">
-        <v>166.8101682649443</v>
+        <v>166.8101528543862</v>
       </c>
       <c r="D19" t="n">
-        <v>158.6664410017166</v>
+        <v>158.6664263435071</v>
       </c>
       <c r="E19" t="n">
-        <v>163.4103522474434</v>
+        <v>163.4103371509733</v>
       </c>
       <c r="F19" t="n">
         <v>1047427</v>
@@ -812,16 +812,16 @@
         <v>44498</v>
       </c>
       <c r="B20" t="n">
-        <v>162.5230712890625</v>
+        <v>162.5230560302734</v>
       </c>
       <c r="C20" t="n">
-        <v>167.3372644582008</v>
+        <v>167.337248747422</v>
       </c>
       <c r="D20" t="n">
-        <v>161.205316656989</v>
+        <v>161.2053015219199</v>
       </c>
       <c r="E20" t="n">
-        <v>166.1249393120207</v>
+        <v>166.1249237150633</v>
       </c>
       <c r="F20" t="n">
         <v>643563</v>
@@ -912,16 +912,16 @@
         <v>44508</v>
       </c>
       <c r="B25" t="n">
-        <v>166.9946441650391</v>
+        <v>166.99462890625</v>
       </c>
       <c r="C25" t="n">
-        <v>173.0651035525069</v>
+        <v>173.0650877390422</v>
       </c>
       <c r="D25" t="n">
-        <v>165.5890473060255</v>
+        <v>165.58903217567</v>
       </c>
       <c r="E25" t="n">
-        <v>173.0211757183424</v>
+        <v>173.0211599088915</v>
       </c>
       <c r="F25" t="n">
         <v>352216</v>
@@ -952,16 +952,16 @@
         <v>44510</v>
       </c>
       <c r="B27" t="n">
-        <v>158.5697937011719</v>
+        <v>158.5697784423828</v>
       </c>
       <c r="C27" t="n">
-        <v>165.99314147324</v>
+        <v>165.9931255001201</v>
       </c>
       <c r="D27" t="n">
-        <v>157.9109164420257</v>
+        <v>157.9109012466388</v>
       </c>
       <c r="E27" t="n">
-        <v>162.8305386722738</v>
+        <v>162.8305230034835</v>
       </c>
       <c r="F27" t="n">
         <v>596401</v>
@@ -972,16 +972,16 @@
         <v>44511</v>
       </c>
       <c r="B28" t="n">
-        <v>162.1804351806641</v>
+        <v>162.1804504394531</v>
       </c>
       <c r="C28" t="n">
-        <v>165.5099555665838</v>
+        <v>165.5099711386316</v>
       </c>
       <c r="D28" t="n">
-        <v>159.4658641978954</v>
+        <v>159.4658792012834</v>
       </c>
       <c r="E28" t="n">
-        <v>161.5566921686091</v>
+        <v>161.5567073687131</v>
       </c>
       <c r="F28" t="n">
         <v>479646</v>
@@ -1032,16 +1032,16 @@
         <v>44517</v>
       </c>
       <c r="B31" t="n">
-        <v>147.342529296875</v>
+        <v>147.3425140380859</v>
       </c>
       <c r="C31" t="n">
-        <v>157.708867734167</v>
+        <v>157.7088514018402</v>
       </c>
       <c r="D31" t="n">
-        <v>146.6045899686845</v>
+        <v>146.6045747863164</v>
       </c>
       <c r="E31" t="n">
-        <v>156.3735393748991</v>
+        <v>156.3735231808589</v>
       </c>
       <c r="F31" t="n">
         <v>1006563</v>
@@ -1052,16 +1052,16 @@
         <v>44518</v>
       </c>
       <c r="B32" t="n">
-        <v>141.1403045654297</v>
+        <v>141.1402893066406</v>
       </c>
       <c r="C32" t="n">
-        <v>149.7320634033205</v>
+        <v>149.7320472156696</v>
       </c>
       <c r="D32" t="n">
-        <v>141.1403045654297</v>
+        <v>141.1402893066406</v>
       </c>
       <c r="E32" t="n">
-        <v>147.8520673947305</v>
+        <v>147.8520514103275</v>
       </c>
       <c r="F32" t="n">
         <v>1135748</v>
@@ -1072,16 +1072,16 @@
         <v>44519</v>
       </c>
       <c r="B33" t="n">
-        <v>147.1931915283203</v>
+        <v>147.1931762695312</v>
       </c>
       <c r="C33" t="n">
-        <v>149.046833535527</v>
+        <v>149.0468180845801</v>
       </c>
       <c r="D33" t="n">
-        <v>140.5692708976831</v>
+        <v>140.5692563255631</v>
       </c>
       <c r="E33" t="n">
-        <v>142.5722568176638</v>
+        <v>142.5722420379041</v>
       </c>
       <c r="F33" t="n">
         <v>581745</v>
@@ -1092,16 +1092,16 @@
         <v>44522</v>
       </c>
       <c r="B34" t="n">
-        <v>140.0509338378906</v>
+        <v>140.0509490966797</v>
       </c>
       <c r="C34" t="n">
-        <v>150.6632507155369</v>
+        <v>150.6632671305561</v>
       </c>
       <c r="D34" t="n">
-        <v>139.9015899501414</v>
+        <v>139.9016051926592</v>
       </c>
       <c r="E34" t="n">
-        <v>145.9281205149585</v>
+        <v>145.9281364140771</v>
       </c>
       <c r="F34" t="n">
         <v>547961</v>
@@ -1112,16 +1112,16 @@
         <v>44523</v>
       </c>
       <c r="B35" t="n">
-        <v>144.9530029296875</v>
+        <v>144.9529876708984</v>
       </c>
       <c r="C35" t="n">
-        <v>147.2107621975469</v>
+        <v>147.2107467010899</v>
       </c>
       <c r="D35" t="n">
-        <v>136.3524639873455</v>
+        <v>136.3524496339106</v>
       </c>
       <c r="E35" t="n">
-        <v>142.3174937855114</v>
+        <v>142.3174788041548</v>
       </c>
       <c r="F35" t="n">
         <v>809322</v>
@@ -1132,16 +1132,16 @@
         <v>44524</v>
       </c>
       <c r="B36" t="n">
-        <v>148.7393493652344</v>
+        <v>148.7393646240234</v>
       </c>
       <c r="C36" t="n">
-        <v>150.2152414609149</v>
+        <v>150.215256871112</v>
       </c>
       <c r="D36" t="n">
-        <v>144.4171159644937</v>
+        <v>144.4171307798759</v>
       </c>
       <c r="E36" t="n">
-        <v>144.5225320410092</v>
+        <v>144.5225468672058</v>
       </c>
       <c r="F36" t="n">
         <v>231702</v>
@@ -1172,16 +1172,16 @@
         <v>44526</v>
       </c>
       <c r="B38" t="n">
-        <v>146.7363433837891</v>
+        <v>146.7363586425781</v>
       </c>
       <c r="C38" t="n">
-        <v>148.7305487890506</v>
+        <v>148.7305642552127</v>
       </c>
       <c r="D38" t="n">
-        <v>143.3716755519658</v>
+        <v>143.3716904608705</v>
       </c>
       <c r="E38" t="n">
-        <v>148.7305487890506</v>
+        <v>148.7305642552127</v>
       </c>
       <c r="F38" t="n">
         <v>241997</v>
@@ -1252,16 +1252,16 @@
         <v>44532</v>
       </c>
       <c r="B42" t="n">
-        <v>143.7845764160156</v>
+        <v>143.7845916748047</v>
       </c>
       <c r="C42" t="n">
-        <v>150.513912239461</v>
+        <v>150.5139282123845</v>
       </c>
       <c r="D42" t="n">
-        <v>143.0466371541728</v>
+        <v>143.0466523346498</v>
       </c>
       <c r="E42" t="n">
-        <v>145.8314899009227</v>
+        <v>145.8315053769355</v>
       </c>
       <c r="F42" t="n">
         <v>584287</v>
@@ -1272,16 +1272,16 @@
         <v>44533</v>
       </c>
       <c r="B43" t="n">
-        <v>144.0657348632812</v>
+        <v>144.0657196044922</v>
       </c>
       <c r="C43" t="n">
-        <v>149.3455339129111</v>
+        <v>149.3455180949097</v>
       </c>
       <c r="D43" t="n">
-        <v>142.6776982924445</v>
+        <v>142.67768318067</v>
       </c>
       <c r="E43" t="n">
-        <v>143.5649816387535</v>
+        <v>143.564966433002</v>
       </c>
       <c r="F43" t="n">
         <v>471453</v>
@@ -1332,16 +1332,16 @@
         <v>44538</v>
       </c>
       <c r="B46" t="n">
-        <v>146.3498229980469</v>
+        <v>146.3498077392578</v>
       </c>
       <c r="C46" t="n">
-        <v>150.2240247482011</v>
+        <v>150.2240090854783</v>
       </c>
       <c r="D46" t="n">
-        <v>145.9984271325229</v>
+        <v>145.9984119103712</v>
       </c>
       <c r="E46" t="n">
-        <v>148.2473928436195</v>
+        <v>148.2473773869852</v>
       </c>
       <c r="F46" t="n">
         <v>297967</v>
@@ -1352,16 +1352,16 @@
         <v>44539</v>
       </c>
       <c r="B47" t="n">
-        <v>146.6836547851562</v>
+        <v>146.6836395263672</v>
       </c>
       <c r="C47" t="n">
-        <v>148.8974862162897</v>
+        <v>148.8974707272065</v>
       </c>
       <c r="D47" t="n">
-        <v>143.7318840119426</v>
+        <v>143.7318690602119</v>
       </c>
       <c r="E47" t="n">
-        <v>146.4464552091688</v>
+        <v>146.4464399750544</v>
       </c>
       <c r="F47" t="n">
         <v>319045</v>
@@ -1372,16 +1372,16 @@
         <v>44540</v>
       </c>
       <c r="B48" t="n">
-        <v>148.2210083007812</v>
+        <v>148.2210388183594</v>
       </c>
       <c r="C48" t="n">
-        <v>150.2239938125575</v>
+        <v>150.2240247425351</v>
       </c>
       <c r="D48" t="n">
-        <v>146.332232453983</v>
+        <v>146.3322625826765</v>
       </c>
       <c r="E48" t="n">
-        <v>148.115592243811</v>
+        <v>148.1156227396848</v>
       </c>
       <c r="F48" t="n">
         <v>506410</v>
@@ -1412,16 +1412,16 @@
         <v>44544</v>
       </c>
       <c r="B50" t="n">
-        <v>147.2283020019531</v>
+        <v>147.2283325195312</v>
       </c>
       <c r="C50" t="n">
-        <v>150.9268052148167</v>
+        <v>150.926836499023</v>
       </c>
       <c r="D50" t="n">
-        <v>141.1227093534192</v>
+        <v>141.1227386054261</v>
       </c>
       <c r="E50" t="n">
-        <v>150.6632516563057</v>
+        <v>150.6632828858824</v>
       </c>
       <c r="F50" t="n">
         <v>995575</v>
@@ -1472,16 +1472,16 @@
         <v>44547</v>
       </c>
       <c r="B53" t="n">
-        <v>144.9530029296875</v>
+        <v>144.9529876708984</v>
       </c>
       <c r="C53" t="n">
-        <v>147.4128141452304</v>
+        <v>147.4127986275041</v>
       </c>
       <c r="D53" t="n">
-        <v>141.8255342233813</v>
+        <v>141.825519293812</v>
       </c>
       <c r="E53" t="n">
-        <v>144.0744998816288</v>
+        <v>144.0744847153172</v>
       </c>
       <c r="F53" t="n">
         <v>507335</v>
@@ -1532,16 +1532,16 @@
         <v>44552</v>
       </c>
       <c r="B56" t="n">
-        <v>146.2268371582031</v>
+        <v>146.226806640625</v>
       </c>
       <c r="C56" t="n">
-        <v>148.9502021086343</v>
+        <v>148.9501710226892</v>
       </c>
       <c r="D56" t="n">
-        <v>144.0745072611944</v>
+        <v>144.0744771928081</v>
       </c>
       <c r="E56" t="n">
-        <v>147.7202897354198</v>
+        <v>147.7202589061577</v>
       </c>
       <c r="F56" t="n">
         <v>439793</v>
@@ -1552,16 +1552,16 @@
         <v>44553</v>
       </c>
       <c r="B57" t="n">
-        <v>148.923828125</v>
+        <v>148.9238128662109</v>
       </c>
       <c r="C57" t="n">
-        <v>149.7759770834253</v>
+        <v>149.7759617373248</v>
       </c>
       <c r="D57" t="n">
-        <v>144.0832681520062</v>
+        <v>144.0832533891827</v>
       </c>
       <c r="E57" t="n">
-        <v>146.2268175565032</v>
+        <v>146.2268025740509</v>
       </c>
       <c r="F57" t="n">
         <v>381841</v>
@@ -1592,16 +1592,16 @@
         <v>44558</v>
       </c>
       <c r="B59" t="n">
-        <v>141.7025451660156</v>
+        <v>141.7025299072266</v>
       </c>
       <c r="C59" t="n">
-        <v>151.4539210138668</v>
+        <v>151.4539047050317</v>
       </c>
       <c r="D59" t="n">
-        <v>141.0963759145082</v>
+        <v>141.0963607209925</v>
       </c>
       <c r="E59" t="n">
-        <v>150.487575698256</v>
+        <v>150.4875594934788</v>
       </c>
       <c r="F59" t="n">
         <v>577682</v>
@@ -1652,16 +1652,16 @@
         <v>44564</v>
       </c>
       <c r="B62" t="n">
-        <v>144.8124237060547</v>
+        <v>144.8124389648438</v>
       </c>
       <c r="C62" t="n">
-        <v>144.8124237060547</v>
+        <v>144.8124389648438</v>
       </c>
       <c r="D62" t="n">
-        <v>138.7946865146767</v>
+        <v>138.7947011393807</v>
       </c>
       <c r="E62" t="n">
-        <v>142.1769148443119</v>
+        <v>142.1769298253991</v>
       </c>
       <c r="F62" t="n">
         <v>369633</v>
@@ -1672,16 +1672,16 @@
         <v>44565</v>
       </c>
       <c r="B63" t="n">
-        <v>140.2969207763672</v>
+        <v>140.2969055175781</v>
       </c>
       <c r="C63" t="n">
-        <v>146.4991495621347</v>
+        <v>146.499133628787</v>
       </c>
       <c r="D63" t="n">
-        <v>138.6629047258906</v>
+        <v>138.6628896448183</v>
       </c>
       <c r="E63" t="n">
-        <v>144.8124254785607</v>
+        <v>144.8124097286623</v>
       </c>
       <c r="F63" t="n">
         <v>382138</v>
@@ -1712,16 +1712,16 @@
         <v>44567</v>
       </c>
       <c r="B65" t="n">
-        <v>135.2718811035156</v>
+        <v>135.2718963623047</v>
       </c>
       <c r="C65" t="n">
-        <v>137.0288870115152</v>
+        <v>137.0289024684961</v>
       </c>
       <c r="D65" t="n">
-        <v>129.5879659187458</v>
+        <v>129.5879805363842</v>
       </c>
       <c r="E65" t="n">
-        <v>134.8502034389653</v>
+        <v>134.8502186501887</v>
       </c>
       <c r="F65" t="n">
         <v>814212</v>
@@ -1772,16 +1772,16 @@
         <v>44572</v>
       </c>
       <c r="B68" t="n">
-        <v>146.3849487304688</v>
+        <v>146.3849639892578</v>
       </c>
       <c r="C68" t="n">
-        <v>149.0116639338405</v>
+        <v>149.0116794664315</v>
       </c>
       <c r="D68" t="n">
-        <v>133.6290823276248</v>
+        <v>133.6290962567753</v>
       </c>
       <c r="E68" t="n">
-        <v>137.573565341825</v>
+        <v>137.5735796821382</v>
       </c>
       <c r="F68" t="n">
         <v>715197</v>
@@ -1792,16 +1792,16 @@
         <v>44573</v>
       </c>
       <c r="B69" t="n">
-        <v>149.4421539306641</v>
+        <v>149.442138671875</v>
       </c>
       <c r="C69" t="n">
-        <v>150.7950427255186</v>
+        <v>150.7950273285929</v>
       </c>
       <c r="D69" t="n">
-        <v>145.5591720697106</v>
+        <v>145.5591572073933</v>
       </c>
       <c r="E69" t="n">
-        <v>146.4464553218307</v>
+        <v>146.4464403689174</v>
       </c>
       <c r="F69" t="n">
         <v>416574</v>
@@ -1832,16 +1832,16 @@
         <v>44575</v>
       </c>
       <c r="B71" t="n">
-        <v>139.0494384765625</v>
+        <v>139.0494537353516</v>
       </c>
       <c r="C71" t="n">
-        <v>143.731860560231</v>
+        <v>143.7318763328524</v>
       </c>
       <c r="D71" t="n">
-        <v>136.396355954948</v>
+        <v>136.3963709225973</v>
       </c>
       <c r="E71" t="n">
-        <v>142.9675673238445</v>
+        <v>142.9675830125951</v>
       </c>
       <c r="F71" t="n">
         <v>386316</v>
@@ -1852,16 +1852,16 @@
         <v>44578</v>
       </c>
       <c r="B72" t="n">
-        <v>138.803466796875</v>
+        <v>138.8034820556641</v>
       </c>
       <c r="C72" t="n">
-        <v>140.2705651221538</v>
+        <v>140.2705805422223</v>
       </c>
       <c r="D72" t="n">
-        <v>136.9058971981742</v>
+        <v>136.9059122483617</v>
       </c>
       <c r="E72" t="n">
-        <v>138.065527532344</v>
+        <v>138.0655427100108</v>
       </c>
       <c r="F72" t="n">
         <v>75291</v>
@@ -1872,16 +1872,16 @@
         <v>44579</v>
       </c>
       <c r="B73" t="n">
-        <v>133.1722717285156</v>
+        <v>133.1722564697266</v>
       </c>
       <c r="C73" t="n">
-        <v>138.8034793945444</v>
+        <v>138.8034634905354</v>
       </c>
       <c r="D73" t="n">
-        <v>133.1722717285156</v>
+        <v>133.1722564697266</v>
       </c>
       <c r="E73" t="n">
-        <v>138.1885299516231</v>
+        <v>138.1885141180745</v>
       </c>
       <c r="F73" t="n">
         <v>435258</v>
@@ -1892,16 +1892,16 @@
         <v>44580</v>
       </c>
       <c r="B74" t="n">
-        <v>139.6117095947266</v>
+        <v>139.6116790771484</v>
       </c>
       <c r="C74" t="n">
-        <v>141.6937576305562</v>
+        <v>141.6937266578653</v>
       </c>
       <c r="D74" t="n">
-        <v>133.0492904334303</v>
+        <v>133.0492613503245</v>
       </c>
       <c r="E74" t="n">
-        <v>133.5324698143952</v>
+        <v>133.5324406256718</v>
       </c>
       <c r="F74" t="n">
         <v>381153</v>
@@ -1912,16 +1912,16 @@
         <v>44581</v>
       </c>
       <c r="B75" t="n">
-        <v>145.2868347167969</v>
+        <v>145.2868194580078</v>
       </c>
       <c r="C75" t="n">
-        <v>149.2488785379507</v>
+        <v>149.2488628630469</v>
       </c>
       <c r="D75" t="n">
-        <v>138.1094666035888</v>
+        <v>138.1094520986048</v>
       </c>
       <c r="E75" t="n">
-        <v>138.1094666035888</v>
+        <v>138.1094520986048</v>
       </c>
       <c r="F75" t="n">
         <v>666913</v>
@@ -1992,16 +1992,16 @@
         <v>44587</v>
       </c>
       <c r="B79" t="n">
-        <v>151.7789611816406</v>
+        <v>151.7789764404297</v>
       </c>
       <c r="C79" t="n">
-        <v>157.1466148398293</v>
+        <v>157.1466306382445</v>
       </c>
       <c r="D79" t="n">
-        <v>148.2122412846406</v>
+        <v>148.2122561848568</v>
       </c>
       <c r="E79" t="n">
-        <v>148.5987713295526</v>
+        <v>148.5987862686278</v>
       </c>
       <c r="F79" t="n">
         <v>671208</v>
@@ -2012,16 +2012,16 @@
         <v>44588</v>
       </c>
       <c r="B80" t="n">
-        <v>149.4860687255859</v>
+        <v>149.486083984375</v>
       </c>
       <c r="C80" t="n">
-        <v>156.5668005253132</v>
+        <v>156.5668165068679</v>
       </c>
       <c r="D80" t="n">
-        <v>147.3249455193078</v>
+        <v>147.3249605575002</v>
       </c>
       <c r="E80" t="n">
-        <v>151.5417624600439</v>
+        <v>151.5417779286678</v>
       </c>
       <c r="F80" t="n">
         <v>697237</v>
@@ -2032,16 +2032,16 @@
         <v>44589</v>
       </c>
       <c r="B81" t="n">
-        <v>147.5533752441406</v>
+        <v>147.5533599853516</v>
       </c>
       <c r="C81" t="n">
-        <v>149.9253307510293</v>
+        <v>149.9253152469516</v>
       </c>
       <c r="D81" t="n">
-        <v>142.7479625837369</v>
+        <v>142.7479478218851</v>
       </c>
       <c r="E81" t="n">
-        <v>149.4948594393217</v>
+        <v>149.4948439797599</v>
       </c>
       <c r="F81" t="n">
         <v>1084942</v>
@@ -2072,16 +2072,16 @@
         <v>44593</v>
       </c>
       <c r="B83" t="n">
-        <v>155.5828857421875</v>
+        <v>155.5828704833984</v>
       </c>
       <c r="C83" t="n">
-        <v>157.3574521401745</v>
+        <v>157.3574367073448</v>
       </c>
       <c r="D83" t="n">
-        <v>151.1200889199835</v>
+        <v>151.1200740988831</v>
       </c>
       <c r="E83" t="n">
-        <v>152.4378434121932</v>
+        <v>152.4378284618541</v>
       </c>
       <c r="F83" t="n">
         <v>577815</v>
@@ -2172,16 +2172,16 @@
         <v>44600</v>
       </c>
       <c r="B88" t="n">
-        <v>149.3191680908203</v>
+        <v>149.3191528320312</v>
       </c>
       <c r="C88" t="n">
-        <v>149.3191680908203</v>
+        <v>149.3191528320312</v>
       </c>
       <c r="D88" t="n">
-        <v>144.2326278016086</v>
+        <v>144.2326130626084</v>
       </c>
       <c r="E88" t="n">
-        <v>147.6763716371699</v>
+        <v>147.6763565462567</v>
       </c>
       <c r="F88" t="n">
         <v>326666</v>
@@ -2232,16 +2232,16 @@
         <v>44603</v>
       </c>
       <c r="B91" t="n">
-        <v>156.0045623779297</v>
+        <v>156.0045471191406</v>
       </c>
       <c r="C91" t="n">
-        <v>160.1510975579418</v>
+        <v>160.1510818935806</v>
       </c>
       <c r="D91" t="n">
-        <v>151.3309200426192</v>
+        <v>151.3309052409586</v>
       </c>
       <c r="E91" t="n">
-        <v>152.3763407441961</v>
+        <v>152.376325840283</v>
       </c>
       <c r="F91" t="n">
         <v>740597</v>
@@ -2252,16 +2252,16 @@
         <v>44606</v>
       </c>
       <c r="B92" t="n">
-        <v>152.9473876953125</v>
+        <v>152.9473724365234</v>
       </c>
       <c r="C92" t="n">
-        <v>157.9197048137788</v>
+        <v>157.9196890589268</v>
       </c>
       <c r="D92" t="n">
-        <v>152.0688846376827</v>
+        <v>152.0688694665374</v>
       </c>
       <c r="E92" t="n">
-        <v>156.0045745824943</v>
+        <v>156.0045590187052</v>
       </c>
       <c r="F92" t="n">
         <v>409040</v>
@@ -2272,16 +2272,16 @@
         <v>44607</v>
       </c>
       <c r="B93" t="n">
-        <v>161.1438140869141</v>
+        <v>161.143798828125</v>
       </c>
       <c r="C93" t="n">
-        <v>161.8202652142218</v>
+        <v>161.8202498913792</v>
       </c>
       <c r="D93" t="n">
-        <v>154.6253228193754</v>
+        <v>154.6253081778255</v>
       </c>
       <c r="E93" t="n">
-        <v>156.2769129050486</v>
+        <v>156.2768981071088</v>
       </c>
       <c r="F93" t="n">
         <v>501987</v>
@@ -2292,16 +2292,16 @@
         <v>44608</v>
       </c>
       <c r="B94" t="n">
-        <v>160.8099670410156</v>
+        <v>160.8099975585938</v>
       </c>
       <c r="C94" t="n">
-        <v>164.6841682523319</v>
+        <v>164.6841995051333</v>
       </c>
       <c r="D94" t="n">
-        <v>158.0690287325549</v>
+        <v>158.0690587299737</v>
       </c>
       <c r="E94" t="n">
-        <v>161.1437890453663</v>
+        <v>161.1438196262952</v>
       </c>
       <c r="F94" t="n">
         <v>383335</v>
@@ -2352,16 +2352,16 @@
         <v>44613</v>
       </c>
       <c r="B97" t="n">
-        <v>150.3118896484375</v>
+        <v>150.3118591308594</v>
       </c>
       <c r="C97" t="n">
-        <v>155.6883244695276</v>
+        <v>155.6882928603806</v>
       </c>
       <c r="D97" t="n">
-        <v>149.5827304480456</v>
+        <v>149.5827000785075</v>
       </c>
       <c r="E97" t="n">
-        <v>154.6165495874955</v>
+        <v>154.6165181959493</v>
       </c>
       <c r="F97" t="n">
         <v>185476</v>
@@ -2372,16 +2372,16 @@
         <v>44614</v>
       </c>
       <c r="B98" t="n">
-        <v>150.3557739257812</v>
+        <v>150.3557891845703</v>
       </c>
       <c r="C98" t="n">
-        <v>155.0557700513334</v>
+        <v>155.0557857870995</v>
       </c>
       <c r="D98" t="n">
-        <v>149.6793363085237</v>
+        <v>149.6793514986648</v>
       </c>
       <c r="E98" t="n">
-        <v>150.5314852389875</v>
+        <v>150.5315005156085</v>
       </c>
       <c r="F98" t="n">
         <v>352471</v>
@@ -2412,16 +2412,16 @@
         <v>44616</v>
       </c>
       <c r="B100" t="n">
-        <v>148.1067962646484</v>
+        <v>148.1068115234375</v>
       </c>
       <c r="C100" t="n">
-        <v>148.1067962646484</v>
+        <v>148.1068115234375</v>
       </c>
       <c r="D100" t="n">
-        <v>139.2427054859054</v>
+        <v>139.2427198314664</v>
       </c>
       <c r="E100" t="n">
-        <v>143.3277384867851</v>
+        <v>143.327753253209</v>
       </c>
       <c r="F100" t="n">
         <v>704723</v>
@@ -2432,16 +2432,16 @@
         <v>44617</v>
       </c>
       <c r="B101" t="n">
-        <v>145.1374816894531</v>
+        <v>145.1374969482422</v>
       </c>
       <c r="C101" t="n">
-        <v>149.1698071078465</v>
+        <v>149.1698227905674</v>
       </c>
       <c r="D101" t="n">
-        <v>141.2457065586561</v>
+        <v>141.2457214082899</v>
       </c>
       <c r="E101" t="n">
-        <v>145.8754209676771</v>
+        <v>145.8754363040482</v>
       </c>
       <c r="F101" t="n">
         <v>765160</v>
@@ -2492,16 +2492,16 @@
         <v>44624</v>
       </c>
       <c r="B104" t="n">
-        <v>129.4034881591797</v>
+        <v>129.4035034179688</v>
       </c>
       <c r="C104" t="n">
-        <v>139.2163645736173</v>
+        <v>139.216380989505</v>
       </c>
       <c r="D104" t="n">
-        <v>128.5864734391812</v>
+        <v>128.5864886016308</v>
       </c>
       <c r="E104" t="n">
-        <v>134.2440346232008</v>
+        <v>134.2440504527695</v>
       </c>
       <c r="F104" t="n">
         <v>615045</v>
@@ -2512,16 +2512,16 @@
         <v>44627</v>
       </c>
       <c r="B105" t="n">
-        <v>117.0781021118164</v>
+        <v>117.0780944824219</v>
       </c>
       <c r="C105" t="n">
-        <v>130.2644277157113</v>
+        <v>130.2644192270299</v>
       </c>
       <c r="D105" t="n">
-        <v>117.0781021118164</v>
+        <v>117.0780944824219</v>
       </c>
       <c r="E105" t="n">
-        <v>129.5791964273345</v>
+        <v>129.5791879833061</v>
       </c>
       <c r="F105" t="n">
         <v>1053703</v>
@@ -2612,16 +2612,16 @@
         <v>44634</v>
       </c>
       <c r="B110" t="n">
-        <v>126.6801223754883</v>
+        <v>126.6801376342773</v>
       </c>
       <c r="C110" t="n">
-        <v>133.8311358334649</v>
+        <v>133.831151953603</v>
       </c>
       <c r="D110" t="n">
-        <v>126.6801223754883</v>
+        <v>126.6801376342773</v>
       </c>
       <c r="E110" t="n">
-        <v>131.6173180568153</v>
+        <v>131.6173339102961</v>
       </c>
       <c r="F110" t="n">
         <v>265850</v>
@@ -2632,16 +2632,16 @@
         <v>44635</v>
       </c>
       <c r="B111" t="n">
-        <v>131.4855346679688</v>
+        <v>131.4855499267578</v>
       </c>
       <c r="C111" t="n">
-        <v>132.1971199113335</v>
+        <v>132.1971352527014</v>
       </c>
       <c r="D111" t="n">
-        <v>124.3520950170941</v>
+        <v>124.3521094480533</v>
       </c>
       <c r="E111" t="n">
-        <v>126.9876038620842</v>
+        <v>126.987618598892</v>
       </c>
       <c r="F111" t="n">
         <v>302237</v>
@@ -2692,16 +2692,16 @@
         <v>44638</v>
       </c>
       <c r="B114" t="n">
-        <v>142.3174743652344</v>
+        <v>142.3174896240234</v>
       </c>
       <c r="C114" t="n">
-        <v>145.1199008509126</v>
+        <v>145.1199164101681</v>
       </c>
       <c r="D114" t="n">
-        <v>137.1518728579682</v>
+        <v>137.1518875629193</v>
       </c>
       <c r="E114" t="n">
-        <v>138.6189711394427</v>
+        <v>138.618986001691</v>
       </c>
       <c r="F114" t="n">
         <v>570545</v>
@@ -2712,16 +2712,16 @@
         <v>44641</v>
       </c>
       <c r="B115" t="n">
-        <v>139.7698211669922</v>
+        <v>139.7698364257812</v>
       </c>
       <c r="C115" t="n">
-        <v>143.0642071460549</v>
+        <v>143.0642227644949</v>
       </c>
       <c r="D115" t="n">
-        <v>138.4169191515182</v>
+        <v>138.4169342626098</v>
       </c>
       <c r="E115" t="n">
-        <v>141.4828991951266</v>
+        <v>141.4829146409339</v>
       </c>
       <c r="F115" t="n">
         <v>351500</v>
@@ -2732,16 +2732,16 @@
         <v>44642</v>
       </c>
       <c r="B116" t="n">
-        <v>143.4683380126953</v>
+        <v>143.4683074951172</v>
       </c>
       <c r="C116" t="n">
-        <v>146.8330064684024</v>
+        <v>146.8329752351156</v>
       </c>
       <c r="D116" t="n">
-        <v>139.7698474968835</v>
+        <v>139.7698177660223</v>
       </c>
       <c r="E116" t="n">
-        <v>139.7698474968835</v>
+        <v>139.7698177660223</v>
       </c>
       <c r="F116" t="n">
         <v>384464</v>
@@ -2772,16 +2772,16 @@
         <v>44644</v>
       </c>
       <c r="B118" t="n">
-        <v>136.2733764648438</v>
+        <v>136.2733612060547</v>
       </c>
       <c r="C118" t="n">
-        <v>137.2660891108588</v>
+        <v>137.2660737409138</v>
       </c>
       <c r="D118" t="n">
-        <v>132.4870308075925</v>
+        <v>132.4870159727677</v>
       </c>
       <c r="E118" t="n">
-        <v>133.2776915238059</v>
+        <v>133.2776766004494</v>
       </c>
       <c r="F118" t="n">
         <v>438667</v>
@@ -2792,16 +2792,16 @@
         <v>44645</v>
       </c>
       <c r="B119" t="n">
-        <v>133.9277801513672</v>
+        <v>133.9277954101562</v>
       </c>
       <c r="C119" t="n">
-        <v>140.0333733423783</v>
+        <v>140.0333892967957</v>
       </c>
       <c r="D119" t="n">
-        <v>133.418246800945</v>
+        <v>133.4182620016815</v>
       </c>
       <c r="E119" t="n">
-        <v>135.3070363006828</v>
+        <v>135.3070517166146</v>
       </c>
       <c r="F119" t="n">
         <v>403765</v>
@@ -2832,16 +2832,16 @@
         <v>44649</v>
       </c>
       <c r="B121" t="n">
-        <v>139.5765533447266</v>
+        <v>139.5765686035156</v>
       </c>
       <c r="C121" t="n">
-        <v>140.4638365007489</v>
+        <v>140.4638518565375</v>
       </c>
       <c r="D121" t="n">
-        <v>135.1576845672471</v>
+        <v>135.1576993429566</v>
       </c>
       <c r="E121" t="n">
-        <v>137.9249635049115</v>
+        <v>137.9249785831454</v>
       </c>
       <c r="F121" t="n">
         <v>830631</v>
@@ -2872,16 +2872,16 @@
         <v>44651</v>
       </c>
       <c r="B123" t="n">
-        <v>126.0651779174805</v>
+        <v>126.065185546875</v>
       </c>
       <c r="C123" t="n">
-        <v>132.1707709614254</v>
+        <v>132.170778960327</v>
       </c>
       <c r="D123" t="n">
-        <v>123.4735968015489</v>
+        <v>123.4736042741024</v>
       </c>
       <c r="E123" t="n">
-        <v>131.6788114362862</v>
+        <v>131.6788194054147</v>
       </c>
       <c r="F123" t="n">
         <v>791956</v>
@@ -2892,16 +2892,16 @@
         <v>44652</v>
       </c>
       <c r="B124" t="n">
-        <v>127.382926940918</v>
+        <v>127.3829345703125</v>
       </c>
       <c r="C124" t="n">
-        <v>129.1047986101335</v>
+        <v>129.1048063426568</v>
       </c>
       <c r="D124" t="n">
-        <v>124.615648027951</v>
+        <v>124.6156554916039</v>
       </c>
       <c r="E124" t="n">
-        <v>126.5044239964978</v>
+        <v>126.5044315732759</v>
       </c>
       <c r="F124" t="n">
         <v>526406</v>
@@ -2952,16 +2952,16 @@
         <v>44657</v>
       </c>
       <c r="B127" t="n">
-        <v>125.0197601318359</v>
+        <v>125.0197448730469</v>
       </c>
       <c r="C127" t="n">
-        <v>127.3829353531706</v>
+        <v>127.3829198059536</v>
       </c>
       <c r="D127" t="n">
-        <v>122.6917325373382</v>
+        <v>122.6917175626873</v>
       </c>
       <c r="E127" t="n">
-        <v>127.1720898068249</v>
+        <v>127.1720742853418</v>
       </c>
       <c r="F127" t="n">
         <v>694358</v>
@@ -2972,16 +2972,16 @@
         <v>44658</v>
       </c>
       <c r="B128" t="n">
-        <v>126.9524459838867</v>
+        <v>126.9524612426758</v>
       </c>
       <c r="C128" t="n">
-        <v>128.604035682919</v>
+        <v>128.6040511402175</v>
       </c>
       <c r="D128" t="n">
-        <v>122.9991830356934</v>
+        <v>122.9991978193282</v>
       </c>
       <c r="E128" t="n">
-        <v>124.756188790446</v>
+        <v>124.7562037852604</v>
       </c>
       <c r="F128" t="n">
         <v>544395</v>
@@ -3012,16 +3012,16 @@
         <v>44662</v>
       </c>
       <c r="B130" t="n">
-        <v>121.8659362792969</v>
+        <v>121.8659515380859</v>
       </c>
       <c r="C130" t="n">
-        <v>123.5702342307505</v>
+        <v>123.5702497029341</v>
       </c>
       <c r="D130" t="n">
-        <v>119.3621973869214</v>
+        <v>119.3622123322183</v>
       </c>
       <c r="E130" t="n">
-        <v>122.9904190381111</v>
+        <v>122.9904344376963</v>
       </c>
       <c r="F130" t="n">
         <v>348006</v>
@@ -3092,16 +3092,16 @@
         <v>44669</v>
       </c>
       <c r="B134" t="n">
-        <v>112.4483947753906</v>
+        <v>112.4483871459961</v>
       </c>
       <c r="C134" t="n">
-        <v>115.1366120682069</v>
+        <v>115.1366042564223</v>
       </c>
       <c r="D134" t="n">
-        <v>112.053071068487</v>
+        <v>112.0530634659144</v>
       </c>
       <c r="E134" t="n">
-        <v>114.2054009437561</v>
+        <v>114.2053931951523</v>
       </c>
       <c r="F134" t="n">
         <v>589431</v>
@@ -3132,16 +3132,16 @@
         <v>44671</v>
       </c>
       <c r="B136" t="n">
-        <v>113.9945449829102</v>
+        <v>113.9945526123047</v>
       </c>
       <c r="C136" t="n">
-        <v>116.5597721462199</v>
+        <v>116.5597799472992</v>
       </c>
       <c r="D136" t="n">
-        <v>112.975491685902</v>
+        <v>112.9754992470936</v>
       </c>
       <c r="E136" t="n">
-        <v>114.5128719430319</v>
+        <v>114.5128796071169</v>
       </c>
       <c r="F136" t="n">
         <v>232622</v>
@@ -3172,16 +3172,16 @@
         <v>44676</v>
       </c>
       <c r="B138" t="n">
-        <v>111.5347366333008</v>
+        <v>111.5347442626953</v>
       </c>
       <c r="C138" t="n">
-        <v>111.8334311293538</v>
+        <v>111.8334387791802</v>
       </c>
       <c r="D138" t="n">
-        <v>105.9474571895508</v>
+        <v>105.9474644367544</v>
       </c>
       <c r="E138" t="n">
-        <v>106.2988597191943</v>
+        <v>106.2988669904352</v>
       </c>
       <c r="F138" t="n">
         <v>607459</v>
@@ -3212,16 +3212,16 @@
         <v>44678</v>
       </c>
       <c r="B140" t="n">
-        <v>104.5418472290039</v>
+        <v>104.5418548583984</v>
       </c>
       <c r="C140" t="n">
-        <v>110.4717419247667</v>
+        <v>110.471749986921</v>
       </c>
       <c r="D140" t="n">
-        <v>104.0938088641949</v>
+        <v>104.0938164608919</v>
       </c>
       <c r="E140" t="n">
-        <v>109.5493111800033</v>
+        <v>109.5493191748392</v>
       </c>
       <c r="F140" t="n">
         <v>1036983</v>
@@ -3272,16 +3272,16 @@
         <v>44683</v>
       </c>
       <c r="B143" t="n">
-        <v>107.1685791015625</v>
+        <v>107.168586730957</v>
       </c>
       <c r="C143" t="n">
-        <v>108.5566154502563</v>
+        <v>108.556623178466</v>
       </c>
       <c r="D143" t="n">
-        <v>104.4627949552132</v>
+        <v>104.4628023919814</v>
       </c>
       <c r="E143" t="n">
-        <v>107.1861529149336</v>
+        <v>107.1861605455792</v>
       </c>
       <c r="F143" t="n">
         <v>497573</v>
@@ -3292,16 +3292,16 @@
         <v>44684</v>
       </c>
       <c r="B144" t="n">
-        <v>102.7848587036133</v>
+        <v>102.7848510742188</v>
       </c>
       <c r="C144" t="n">
-        <v>107.1773740328275</v>
+        <v>107.1773660773905</v>
       </c>
       <c r="D144" t="n">
-        <v>101.809719764332</v>
+        <v>101.8097122073189</v>
       </c>
       <c r="E144" t="n">
-        <v>107.1422331059002</v>
+        <v>107.1422251530716</v>
       </c>
       <c r="F144" t="n">
         <v>541792</v>
@@ -3312,16 +3312,16 @@
         <v>44685</v>
       </c>
       <c r="B145" t="n">
-        <v>94.52692413330078</v>
+        <v>94.52691650390625</v>
       </c>
       <c r="C145" t="n">
-        <v>100.4128984212591</v>
+        <v>100.4128903167997</v>
       </c>
       <c r="D145" t="n">
-        <v>84.54712923481648</v>
+        <v>84.54712241090455</v>
       </c>
       <c r="E145" t="n">
-        <v>100.4128984212591</v>
+        <v>100.4128903167997</v>
       </c>
       <c r="F145" t="n">
         <v>3193940</v>
@@ -3332,16 +3332,16 @@
         <v>44686</v>
       </c>
       <c r="B146" t="n">
-        <v>93.73626708984375</v>
+        <v>93.73627471923828</v>
       </c>
       <c r="C146" t="n">
-        <v>95.51084689698163</v>
+        <v>95.51085467081299</v>
       </c>
       <c r="D146" t="n">
-        <v>91.46094754500817</v>
+        <v>91.4609549892096</v>
       </c>
       <c r="E146" t="n">
-        <v>94.43907216835407</v>
+        <v>94.4390798549514</v>
       </c>
       <c r="F146" t="n">
         <v>1265698</v>
@@ -3412,16 +3412,16 @@
         <v>44692</v>
       </c>
       <c r="B150" t="n">
-        <v>81.85890960693359</v>
+        <v>81.85890197753906</v>
       </c>
       <c r="C150" t="n">
-        <v>86.58525332243828</v>
+        <v>86.58524525254019</v>
       </c>
       <c r="D150" t="n">
-        <v>81.52508088063452</v>
+        <v>81.5250732823534</v>
       </c>
       <c r="E150" t="n">
-        <v>84.51198571133756</v>
+        <v>84.51197783467165</v>
       </c>
       <c r="F150" t="n">
         <v>624829</v>
@@ -3452,16 +3452,16 @@
         <v>44694</v>
       </c>
       <c r="B152" t="n">
-        <v>89.78300476074219</v>
+        <v>89.78299713134766</v>
       </c>
       <c r="C152" t="n">
-        <v>92.42730069221749</v>
+        <v>92.42729283812145</v>
       </c>
       <c r="D152" t="n">
-        <v>87.90300885931281</v>
+        <v>87.90300138967268</v>
       </c>
       <c r="E152" t="n">
-        <v>90.57365880864381</v>
+        <v>90.57365111206272</v>
       </c>
       <c r="F152" t="n">
         <v>780406</v>
@@ -3492,16 +3492,16 @@
         <v>44698</v>
       </c>
       <c r="B154" t="n">
-        <v>86.98058319091797</v>
+        <v>86.9805908203125</v>
       </c>
       <c r="C154" t="n">
-        <v>88.24562294284463</v>
+        <v>88.24563068320056</v>
       </c>
       <c r="D154" t="n">
-        <v>84.59105397819015</v>
+        <v>84.59106139799007</v>
       </c>
       <c r="E154" t="n">
-        <v>85.39048821633966</v>
+        <v>85.39049570626096</v>
       </c>
       <c r="F154" t="n">
         <v>1257850</v>
@@ -3512,16 +3512,16 @@
         <v>44699</v>
       </c>
       <c r="B155" t="n">
-        <v>84.09909820556641</v>
+        <v>84.09909057617188</v>
       </c>
       <c r="C155" t="n">
-        <v>87.19142592924517</v>
+        <v>87.19141801931744</v>
       </c>
       <c r="D155" t="n">
-        <v>83.82675770797285</v>
+        <v>83.82675010328479</v>
       </c>
       <c r="E155" t="n">
-        <v>86.83123646893756</v>
+        <v>86.83122859168591</v>
       </c>
       <c r="F155" t="n">
         <v>617555</v>
@@ -3532,16 +3532,16 @@
         <v>44700</v>
       </c>
       <c r="B156" t="n">
-        <v>89.60731506347656</v>
+        <v>89.60730743408203</v>
       </c>
       <c r="C156" t="n">
-        <v>90.45067722448628</v>
+        <v>90.45066952328574</v>
       </c>
       <c r="D156" t="n">
-        <v>82.86041107295223</v>
+        <v>82.86040401800625</v>
       </c>
       <c r="E156" t="n">
-        <v>83.85311715048053</v>
+        <v>83.85311001101303</v>
       </c>
       <c r="F156" t="n">
         <v>889253</v>
@@ -3552,16 +3552,16 @@
         <v>44701</v>
       </c>
       <c r="B157" t="n">
-        <v>91.24131774902344</v>
+        <v>91.24132537841797</v>
       </c>
       <c r="C157" t="n">
-        <v>92.66449495378507</v>
+        <v>92.66450270218249</v>
       </c>
       <c r="D157" t="n">
-        <v>87.70095190087078</v>
+        <v>87.70095923422785</v>
       </c>
       <c r="E157" t="n">
-        <v>89.60730171103826</v>
+        <v>89.60730920380003</v>
       </c>
       <c r="F157" t="n">
         <v>709088</v>
@@ -3572,16 +3572,16 @@
         <v>44704</v>
       </c>
       <c r="B158" t="n">
-        <v>91.02169036865234</v>
+        <v>91.02169799804688</v>
       </c>
       <c r="C158" t="n">
-        <v>92.67327348694673</v>
+        <v>92.67328125477616</v>
       </c>
       <c r="D158" t="n">
-        <v>90.09925959845417</v>
+        <v>90.09926715053099</v>
       </c>
       <c r="E158" t="n">
-        <v>90.31010513032238</v>
+        <v>90.31011270007218</v>
       </c>
       <c r="F158" t="n">
         <v>925415</v>
@@ -3592,16 +3592,16 @@
         <v>44705</v>
       </c>
       <c r="B159" t="n">
-        <v>87.67460632324219</v>
+        <v>87.67459106445312</v>
       </c>
       <c r="C159" t="n">
-        <v>90.02020783815051</v>
+        <v>90.02019217113561</v>
       </c>
       <c r="D159" t="n">
-        <v>85.55741077362453</v>
+        <v>85.55739588330977</v>
       </c>
       <c r="E159" t="n">
-        <v>88.43011947599447</v>
+        <v>88.43010408571675</v>
       </c>
       <c r="F159" t="n">
         <v>569845</v>
@@ -3632,16 +3632,16 @@
         <v>44707</v>
       </c>
       <c r="B161" t="n">
-        <v>94.81683349609375</v>
+        <v>94.81684112548828</v>
       </c>
       <c r="C161" t="n">
-        <v>96.2663648544297</v>
+        <v>96.26637260046013</v>
       </c>
       <c r="D161" t="n">
-        <v>89.0099278581001</v>
+        <v>89.00993502024454</v>
       </c>
       <c r="E161" t="n">
-        <v>89.41403845272137</v>
+        <v>89.41404564738239</v>
       </c>
       <c r="F161" t="n">
         <v>700096</v>
@@ -3652,16 +3652,16 @@
         <v>44708</v>
       </c>
       <c r="B162" t="n">
-        <v>96.65289306640625</v>
+        <v>96.65290832519531</v>
       </c>
       <c r="C162" t="n">
-        <v>97.42597996362124</v>
+        <v>97.42599534445911</v>
       </c>
       <c r="D162" t="n">
-        <v>93.57813269507206</v>
+        <v>93.57814746844244</v>
       </c>
       <c r="E162" t="n">
-        <v>94.57084533309663</v>
+        <v>94.57086026318858</v>
       </c>
       <c r="F162" t="n">
         <v>410015</v>
@@ -3672,16 +3672,16 @@
         <v>44711</v>
       </c>
       <c r="B163" t="n">
-        <v>96.54747772216797</v>
+        <v>96.5474853515625</v>
       </c>
       <c r="C163" t="n">
-        <v>99.64859213319181</v>
+        <v>99.64860000764324</v>
       </c>
       <c r="D163" t="n">
-        <v>94.96616969553888</v>
+        <v>94.96617719997496</v>
       </c>
       <c r="E163" t="n">
-        <v>94.96616969553888</v>
+        <v>94.96617719997496</v>
       </c>
       <c r="F163" t="n">
         <v>123810</v>
@@ -3692,16 +3692,16 @@
         <v>44712</v>
       </c>
       <c r="B164" t="n">
-        <v>93.95589447021484</v>
+        <v>93.95590209960938</v>
       </c>
       <c r="C164" t="n">
-        <v>98.17271160959186</v>
+        <v>98.17271958139983</v>
       </c>
       <c r="D164" t="n">
-        <v>93.12131928963522</v>
+        <v>93.12132685126069</v>
       </c>
       <c r="E164" t="n">
-        <v>96.72318029902813</v>
+        <v>96.72318815313145</v>
       </c>
       <c r="F164" t="n">
         <v>435642</v>
@@ -3712,16 +3712,16 @@
         <v>44713</v>
       </c>
       <c r="B165" t="n">
-        <v>92.17253112792969</v>
+        <v>92.17253875732422</v>
       </c>
       <c r="C165" t="n">
-        <v>96.28392534576922</v>
+        <v>96.28393331547606</v>
       </c>
       <c r="D165" t="n">
-        <v>91.18861207909531</v>
+        <v>91.18861962704793</v>
       </c>
       <c r="E165" t="n">
-        <v>95.12430167932452</v>
+        <v>95.12430955304588</v>
       </c>
       <c r="F165" t="n">
         <v>372179</v>
@@ -3772,16 +3772,16 @@
         <v>44718</v>
       </c>
       <c r="B168" t="n">
-        <v>94.98374176025391</v>
+        <v>94.98374938964844</v>
       </c>
       <c r="C168" t="n">
-        <v>97.48747383763394</v>
+        <v>97.48748166813617</v>
       </c>
       <c r="D168" t="n">
-        <v>94.69383417696631</v>
+        <v>94.69384178307456</v>
       </c>
       <c r="E168" t="n">
-        <v>95.18579368622116</v>
+        <v>95.18580133184516</v>
       </c>
       <c r="F168" t="n">
         <v>540320</v>
@@ -3792,16 +3792,16 @@
         <v>44719</v>
       </c>
       <c r="B169" t="n">
-        <v>100.5710296630859</v>
+        <v>100.5710220336914</v>
       </c>
       <c r="C169" t="n">
-        <v>101.2035462136224</v>
+        <v>101.2035385362447</v>
       </c>
       <c r="D169" t="n">
-        <v>93.36730080710669</v>
+        <v>93.36729372419249</v>
       </c>
       <c r="E169" t="n">
-        <v>94.36001351898909</v>
+        <v>94.36000636076696</v>
       </c>
       <c r="F169" t="n">
         <v>669503</v>
@@ -3812,16 +3812,16 @@
         <v>44720</v>
       </c>
       <c r="B170" t="n">
-        <v>97.07457733154297</v>
+        <v>97.0745849609375</v>
       </c>
       <c r="C170" t="n">
-        <v>100.0439149311568</v>
+        <v>100.0439227939208</v>
       </c>
       <c r="D170" t="n">
-        <v>97.07457733154297</v>
+        <v>97.0745849609375</v>
       </c>
       <c r="E170" t="n">
-        <v>98.75252120666485</v>
+        <v>98.75252896793423</v>
       </c>
       <c r="F170" t="n">
         <v>671896</v>
@@ -3832,16 +3832,16 @@
         <v>44721</v>
       </c>
       <c r="B171" t="n">
-        <v>95.02766418457031</v>
+        <v>95.02767181396484</v>
       </c>
       <c r="C171" t="n">
-        <v>97.41719332349938</v>
+        <v>97.41720114473972</v>
       </c>
       <c r="D171" t="n">
-        <v>94.52691776225399</v>
+        <v>94.52692535144557</v>
       </c>
       <c r="E171" t="n">
-        <v>97.1185055323561</v>
+        <v>97.11851332961599</v>
       </c>
       <c r="F171" t="n">
         <v>459814</v>
@@ -3852,16 +3852,16 @@
         <v>44722</v>
       </c>
       <c r="B172" t="n">
-        <v>88.72880554199219</v>
+        <v>88.72879791259766</v>
       </c>
       <c r="C172" t="n">
-        <v>95.2297292687264</v>
+        <v>95.22972108034641</v>
       </c>
       <c r="D172" t="n">
-        <v>88.72880554199219</v>
+        <v>88.72879791259766</v>
       </c>
       <c r="E172" t="n">
-        <v>93.59571310571778</v>
+        <v>93.59570505783955</v>
       </c>
       <c r="F172" t="n">
         <v>588546</v>
@@ -3872,16 +3872,16 @@
         <v>44725</v>
       </c>
       <c r="B173" t="n">
-        <v>85.03908538818359</v>
+        <v>85.03910064697266</v>
       </c>
       <c r="C173" t="n">
-        <v>87.61309921343133</v>
+        <v>87.61311493408253</v>
       </c>
       <c r="D173" t="n">
-        <v>84.30992635555765</v>
+        <v>84.30994148351176</v>
       </c>
       <c r="E173" t="n">
-        <v>87.4110405926337</v>
+        <v>87.41105627702898</v>
       </c>
       <c r="F173" t="n">
         <v>846744</v>
@@ -3912,16 +3912,16 @@
         <v>44727</v>
       </c>
       <c r="B175" t="n">
-        <v>86.62918853759766</v>
+        <v>86.62918090820312</v>
       </c>
       <c r="C175" t="n">
-        <v>88.47404364983063</v>
+        <v>88.47403585796052</v>
       </c>
       <c r="D175" t="n">
-        <v>85.29386011368575</v>
+        <v>85.29385260189301</v>
       </c>
       <c r="E175" t="n">
-        <v>86.10208803445202</v>
+        <v>86.102080451479</v>
       </c>
       <c r="F175" t="n">
         <v>817586</v>
@@ -4032,16 +4032,16 @@
         <v>44736</v>
       </c>
       <c r="B181" t="n">
-        <v>91.10076141357422</v>
+        <v>91.10075378417969</v>
       </c>
       <c r="C181" t="n">
-        <v>92.33066699449137</v>
+        <v>92.33065926209622</v>
       </c>
       <c r="D181" t="n">
-        <v>89.34375535582006</v>
+        <v>89.34374787356913</v>
       </c>
       <c r="E181" t="n">
-        <v>89.34375535582006</v>
+        <v>89.34374787356913</v>
       </c>
       <c r="F181" t="n">
         <v>487883</v>
@@ -4052,16 +4052,16 @@
         <v>44739</v>
       </c>
       <c r="B182" t="n">
-        <v>91.08319854736328</v>
+        <v>91.08319091796875</v>
       </c>
       <c r="C182" t="n">
-        <v>92.33067129792501</v>
+        <v>92.33066356403852</v>
       </c>
       <c r="D182" t="n">
-        <v>88.45647624527705</v>
+        <v>88.45646883590445</v>
       </c>
       <c r="E182" t="n">
-        <v>91.46095513548509</v>
+        <v>91.46094747444857</v>
       </c>
       <c r="F182" t="n">
         <v>388597</v>
@@ -4072,16 +4072,16 @@
         <v>44740</v>
       </c>
       <c r="B183" t="n">
-        <v>85.97909545898438</v>
+        <v>85.97908782958984</v>
       </c>
       <c r="C183" t="n">
-        <v>92.55908139179482</v>
+        <v>92.55907317852221</v>
       </c>
       <c r="D183" t="n">
-        <v>85.97909545898438</v>
+        <v>85.97908782958984</v>
       </c>
       <c r="E183" t="n">
-        <v>91.55758845631833</v>
+        <v>91.55758033191366</v>
       </c>
       <c r="F183" t="n">
         <v>484787</v>
@@ -4112,16 +4112,16 @@
         <v>44742</v>
       </c>
       <c r="B185" t="n">
-        <v>82.69348907470703</v>
+        <v>82.6934814453125</v>
       </c>
       <c r="C185" t="n">
-        <v>84.4680689760099</v>
+        <v>84.46806118289064</v>
       </c>
       <c r="D185" t="n">
-        <v>79.82078707143653</v>
+        <v>79.82077970708073</v>
       </c>
       <c r="E185" t="n">
-        <v>82.4914371280648</v>
+        <v>82.49142951731181</v>
       </c>
       <c r="F185" t="n">
         <v>710009</v>
@@ -4132,16 +4132,16 @@
         <v>44743</v>
       </c>
       <c r="B186" t="n">
-        <v>83.40507507324219</v>
+        <v>83.40506744384766</v>
       </c>
       <c r="C186" t="n">
-        <v>85.39048698245399</v>
+        <v>85.39047917144593</v>
       </c>
       <c r="D186" t="n">
-        <v>81.92918979861589</v>
+        <v>81.92918230422647</v>
       </c>
       <c r="E186" t="n">
-        <v>82.6232079571698</v>
+        <v>82.62320039929577</v>
       </c>
       <c r="F186" t="n">
         <v>500037</v>
@@ -4152,16 +4152,16 @@
         <v>44746</v>
       </c>
       <c r="B187" t="n">
-        <v>82.66713714599609</v>
+        <v>82.66712951660156</v>
       </c>
       <c r="C187" t="n">
-        <v>84.16059637922834</v>
+        <v>84.16058861200165</v>
       </c>
       <c r="D187" t="n">
-        <v>82.21909870578178</v>
+        <v>82.21909111773695</v>
       </c>
       <c r="E187" t="n">
-        <v>82.59685529214944</v>
+        <v>82.59684766924126</v>
       </c>
       <c r="F187" t="n">
         <v>102674</v>
@@ -4192,16 +4192,16 @@
         <v>44748</v>
       </c>
       <c r="B189" t="n">
-        <v>86.62040710449219</v>
+        <v>86.62039947509766</v>
       </c>
       <c r="C189" t="n">
-        <v>88.46526233331782</v>
+        <v>88.46525454143122</v>
       </c>
       <c r="D189" t="n">
-        <v>84.60863413651694</v>
+        <v>84.60862668431632</v>
       </c>
       <c r="E189" t="n">
-        <v>87.84152591655733</v>
+        <v>87.8415181796085</v>
       </c>
       <c r="F189" t="n">
         <v>788696</v>
@@ -4212,16 +4212,16 @@
         <v>44749</v>
       </c>
       <c r="B190" t="n">
-        <v>86.40077209472656</v>
+        <v>86.40076446533203</v>
       </c>
       <c r="C190" t="n">
-        <v>88.54432164349438</v>
+        <v>88.54431382481931</v>
       </c>
       <c r="D190" t="n">
-        <v>86.18993324315069</v>
+        <v>86.18992563237374</v>
       </c>
       <c r="E190" t="n">
-        <v>87.14749833349438</v>
+        <v>87.14749063816215</v>
       </c>
       <c r="F190" t="n">
         <v>483378</v>
@@ -4232,16 +4232,16 @@
         <v>44750</v>
       </c>
       <c r="B191" t="n">
-        <v>85.69796752929688</v>
+        <v>85.69797515869141</v>
       </c>
       <c r="C191" t="n">
-        <v>88.1489849210145</v>
+        <v>88.14899276861466</v>
       </c>
       <c r="D191" t="n">
-        <v>84.96880845454787</v>
+        <v>84.9688160190279</v>
       </c>
       <c r="E191" t="n">
-        <v>86.35684475775652</v>
+        <v>86.35685244580863</v>
       </c>
       <c r="F191" t="n">
         <v>710031</v>
@@ -4272,16 +4272,16 @@
         <v>44754</v>
       </c>
       <c r="B193" t="n">
-        <v>86.32170867919922</v>
+        <v>86.32170104980469</v>
       </c>
       <c r="C193" t="n">
-        <v>86.32170867919922</v>
+        <v>86.32170104980469</v>
       </c>
       <c r="D193" t="n">
-        <v>81.2966703290714</v>
+        <v>81.29666314380617</v>
       </c>
       <c r="E193" t="n">
-        <v>82.6232117668371</v>
+        <v>82.6232044643278</v>
       </c>
       <c r="F193" t="n">
         <v>730233</v>
@@ -4292,16 +4292,16 @@
         <v>44755</v>
       </c>
       <c r="B194" t="n">
-        <v>84.68768310546875</v>
+        <v>84.68769073486328</v>
       </c>
       <c r="C194" t="n">
-        <v>86.91908133386021</v>
+        <v>86.91908916427828</v>
       </c>
       <c r="D194" t="n">
-        <v>83.45777767295714</v>
+        <v>83.45778519155122</v>
       </c>
       <c r="E194" t="n">
-        <v>84.37142151703875</v>
+        <v>84.37142911794173</v>
       </c>
       <c r="F194" t="n">
         <v>1885043</v>
@@ -4332,16 +4332,16 @@
         <v>44757</v>
       </c>
       <c r="B196" t="n">
-        <v>82.85160827636719</v>
+        <v>82.85162353515625</v>
       </c>
       <c r="C196" t="n">
-        <v>84.72282378634415</v>
+        <v>84.72283938975517</v>
       </c>
       <c r="D196" t="n">
-        <v>81.20881210481942</v>
+        <v>81.20882706105454</v>
       </c>
       <c r="E196" t="n">
-        <v>82.27179983418721</v>
+        <v>82.27181498619288</v>
       </c>
       <c r="F196" t="n">
         <v>1850084</v>
@@ -4372,16 +4372,16 @@
         <v>44761</v>
       </c>
       <c r="B198" t="n">
-        <v>86.85759735107422</v>
+        <v>86.85758972167969</v>
       </c>
       <c r="C198" t="n">
-        <v>87.15628516534521</v>
+        <v>87.15627750971456</v>
       </c>
       <c r="D198" t="n">
-        <v>83.45778819792039</v>
+        <v>83.45778086715818</v>
       </c>
       <c r="E198" t="n">
-        <v>83.45778819792039</v>
+        <v>83.45778086715818</v>
       </c>
       <c r="F198" t="n">
         <v>493807</v>
@@ -4412,16 +4412,16 @@
         <v>44763</v>
       </c>
       <c r="B200" t="n">
-        <v>91.97048187255859</v>
+        <v>91.97047424316406</v>
       </c>
       <c r="C200" t="n">
-        <v>92.62057222052319</v>
+        <v>92.62056453720052</v>
       </c>
       <c r="D200" t="n">
-        <v>87.41104912516667</v>
+        <v>87.41104187399904</v>
       </c>
       <c r="E200" t="n">
-        <v>87.41104912516667</v>
+        <v>87.41104187399904</v>
       </c>
       <c r="F200" t="n">
         <v>453688</v>
@@ -4432,16 +4432,16 @@
         <v>44764</v>
       </c>
       <c r="B201" t="n">
-        <v>89.78300476074219</v>
+        <v>89.78299713134766</v>
       </c>
       <c r="C201" t="n">
-        <v>92.24281586478145</v>
+        <v>92.24280802636217</v>
       </c>
       <c r="D201" t="n">
-        <v>89.22076337166682</v>
+        <v>89.22075579004928</v>
       </c>
       <c r="E201" t="n">
-        <v>91.97048207701101</v>
+        <v>91.97047426173357</v>
       </c>
       <c r="F201" t="n">
         <v>566897</v>
@@ -4452,16 +4452,16 @@
         <v>44767</v>
       </c>
       <c r="B202" t="n">
-        <v>89.08020782470703</v>
+        <v>89.08021545410156</v>
       </c>
       <c r="C202" t="n">
-        <v>90.58244718893432</v>
+        <v>90.58245494699018</v>
       </c>
       <c r="D202" t="n">
-        <v>88.15777697007543</v>
+        <v>88.15778452046713</v>
       </c>
       <c r="E202" t="n">
-        <v>89.17684369338068</v>
+        <v>89.17685133105172</v>
       </c>
       <c r="F202" t="n">
         <v>343259</v>
@@ -4472,16 +4472,16 @@
         <v>44768</v>
       </c>
       <c r="B203" t="n">
-        <v>87.23533630371094</v>
+        <v>87.23534393310547</v>
       </c>
       <c r="C203" t="n">
-        <v>88.80785051819481</v>
+        <v>88.80785828511767</v>
       </c>
       <c r="D203" t="n">
-        <v>86.86636001024006</v>
+        <v>86.86636760736479</v>
       </c>
       <c r="E203" t="n">
-        <v>88.1226193627337</v>
+        <v>88.1226270697279</v>
       </c>
       <c r="F203" t="n">
         <v>558437</v>
@@ -4492,16 +4492,16 @@
         <v>44769</v>
       </c>
       <c r="B204" t="n">
-        <v>92.2603759765625</v>
+        <v>92.26038360595703</v>
       </c>
       <c r="C204" t="n">
-        <v>92.55907046197431</v>
+        <v>92.55907811606914</v>
       </c>
       <c r="D204" t="n">
-        <v>87.46375071978201</v>
+        <v>87.46375795252364</v>
       </c>
       <c r="E204" t="n">
-        <v>87.46375071978201</v>
+        <v>87.46375795252364</v>
       </c>
       <c r="F204" t="n">
         <v>673546</v>
@@ -4512,16 +4512,16 @@
         <v>44770</v>
       </c>
       <c r="B205" t="n">
-        <v>93.02468109130859</v>
+        <v>93.02468872070312</v>
       </c>
       <c r="C205" t="n">
-        <v>93.68355833392478</v>
+        <v>93.68356601735695</v>
       </c>
       <c r="D205" t="n">
-        <v>89.02748980512536</v>
+        <v>89.0274971066913</v>
       </c>
       <c r="E205" t="n">
-        <v>90.33646408621723</v>
+        <v>90.33647149513835</v>
       </c>
       <c r="F205" t="n">
         <v>529910</v>
@@ -4552,16 +4552,16 @@
         <v>44774</v>
       </c>
       <c r="B207" t="n">
-        <v>100.1493453979492</v>
+        <v>100.1493377685547</v>
       </c>
       <c r="C207" t="n">
-        <v>102.284108028477</v>
+        <v>102.2841002364559</v>
       </c>
       <c r="D207" t="n">
-        <v>94.3512267417151</v>
+        <v>94.35121955402224</v>
       </c>
       <c r="E207" t="n">
-        <v>94.3512267417151</v>
+        <v>94.35121955402224</v>
       </c>
       <c r="F207" t="n">
         <v>942663</v>
@@ -4592,16 +4592,16 @@
         <v>44776</v>
       </c>
       <c r="B209" t="n">
-        <v>106.8523254394531</v>
+        <v>106.8523178100586</v>
       </c>
       <c r="C209" t="n">
-        <v>107.5990584070543</v>
+        <v>107.5990507243421</v>
       </c>
       <c r="D209" t="n">
-        <v>101.4671040610422</v>
+        <v>101.4670968161594</v>
       </c>
       <c r="E209" t="n">
-        <v>101.4671040610422</v>
+        <v>101.4670968161594</v>
       </c>
       <c r="F209" t="n">
         <v>990038</v>
@@ -4612,16 +4612,16 @@
         <v>44777</v>
       </c>
       <c r="B210" t="n">
-        <v>107.695671081543</v>
+        <v>107.6956787109375</v>
       </c>
       <c r="C210" t="n">
-        <v>114.1966008131186</v>
+        <v>114.196608903053</v>
       </c>
       <c r="D210" t="n">
-        <v>104.9811002422437</v>
+        <v>104.9811076793322</v>
       </c>
       <c r="E210" t="n">
-        <v>106.8610959781686</v>
+        <v>106.86110354844</v>
       </c>
       <c r="F210" t="n">
         <v>1242592</v>
@@ -4652,16 +4652,16 @@
         <v>44781</v>
       </c>
       <c r="B212" t="n">
-        <v>110.4893264770508</v>
+        <v>110.4893188476562</v>
       </c>
       <c r="C212" t="n">
-        <v>113.2829664650746</v>
+        <v>113.2829586427765</v>
       </c>
       <c r="D212" t="n">
-        <v>108.4511996538819</v>
+        <v>108.451192165222</v>
       </c>
       <c r="E212" t="n">
-        <v>108.9343790159798</v>
+        <v>108.9343714939558</v>
       </c>
       <c r="F212" t="n">
         <v>1248783</v>
@@ -4712,16 +4712,16 @@
         <v>44784</v>
       </c>
       <c r="B215" t="n">
-        <v>84.59984588623047</v>
+        <v>84.59983825683594</v>
       </c>
       <c r="C215" t="n">
-        <v>92.06712176623714</v>
+        <v>92.06711346342773</v>
       </c>
       <c r="D215" t="n">
-        <v>83.26451750490639</v>
+        <v>83.26450999593463</v>
       </c>
       <c r="E215" t="n">
-        <v>90.87235708924037</v>
+        <v>90.87234889417739</v>
       </c>
       <c r="F215" t="n">
         <v>3127275</v>
@@ -4812,16 +4812,16 @@
         <v>44791</v>
       </c>
       <c r="B220" t="n">
-        <v>96.89887237548828</v>
+        <v>96.89888000488281</v>
       </c>
       <c r="C220" t="n">
-        <v>97.7861554771208</v>
+        <v>97.78616317637614</v>
       </c>
       <c r="D220" t="n">
-        <v>95.8095239557006</v>
+        <v>95.80953149932459</v>
       </c>
       <c r="E220" t="n">
-        <v>96.51232895540586</v>
+        <v>96.51233655436566</v>
       </c>
       <c r="F220" t="n">
         <v>225811</v>
@@ -4832,16 +4832,16 @@
         <v>44792</v>
       </c>
       <c r="B221" t="n">
-        <v>92.81383514404297</v>
+        <v>92.81385040283203</v>
       </c>
       <c r="C221" t="n">
-        <v>96.35420085090701</v>
+        <v>96.35421669173961</v>
       </c>
       <c r="D221" t="n">
-        <v>92.34822966730141</v>
+        <v>92.34824484954395</v>
       </c>
       <c r="E221" t="n">
-        <v>95.79195951645167</v>
+        <v>95.79197526485062</v>
       </c>
       <c r="F221" t="n">
         <v>610732</v>
@@ -4872,16 +4872,16 @@
         <v>44796</v>
       </c>
       <c r="B223" t="n">
-        <v>96.42449188232422</v>
+        <v>96.42449951171875</v>
       </c>
       <c r="C223" t="n">
-        <v>97.50504682708615</v>
+        <v>97.50505454197742</v>
       </c>
       <c r="D223" t="n">
-        <v>87.49889811798089</v>
+        <v>87.49890504115571</v>
       </c>
       <c r="E223" t="n">
-        <v>89.51945771416493</v>
+        <v>89.51946479721248</v>
       </c>
       <c r="F223" t="n">
         <v>1305076</v>
@@ -4892,16 +4892,16 @@
         <v>44797</v>
       </c>
       <c r="B224" t="n">
-        <v>101.0278472900391</v>
+        <v>101.0278396606445</v>
       </c>
       <c r="C224" t="n">
-        <v>102.855135180046</v>
+        <v>102.8551274126588</v>
       </c>
       <c r="D224" t="n">
-        <v>96.94280690695261</v>
+        <v>96.94279958605108</v>
       </c>
       <c r="E224" t="n">
-        <v>96.98673473892673</v>
+        <v>96.98672741470787</v>
       </c>
       <c r="F224" t="n">
         <v>1291806</v>
@@ -4912,16 +4912,16 @@
         <v>44798</v>
       </c>
       <c r="B225" t="n">
-        <v>99.56952667236328</v>
+        <v>99.56953430175781</v>
       </c>
       <c r="C225" t="n">
-        <v>103.1362534053532</v>
+        <v>103.1362613080438</v>
       </c>
       <c r="D225" t="n">
-        <v>98.69981058018772</v>
+        <v>98.6998181429413</v>
       </c>
       <c r="E225" t="n">
-        <v>101.9063478664755</v>
+        <v>101.9063556749261</v>
       </c>
       <c r="F225" t="n">
         <v>468543</v>
@@ -4932,16 +4932,16 @@
         <v>44799</v>
       </c>
       <c r="B226" t="n">
-        <v>95.02766418457031</v>
+        <v>95.02767181396484</v>
       </c>
       <c r="C226" t="n">
-        <v>100.773074384142</v>
+        <v>100.7730824748128</v>
       </c>
       <c r="D226" t="n">
-        <v>94.66748145393015</v>
+        <v>94.66748905440703</v>
       </c>
       <c r="E226" t="n">
-        <v>100.3601769179005</v>
+        <v>100.3601849754213</v>
       </c>
       <c r="F226" t="n">
         <v>448340</v>
@@ -4992,16 +4992,16 @@
         <v>44804</v>
       </c>
       <c r="B229" t="n">
-        <v>87.36711883544922</v>
+        <v>87.36712646484375</v>
       </c>
       <c r="C229" t="n">
-        <v>91.33795606548307</v>
+        <v>91.33796404163374</v>
       </c>
       <c r="D229" t="n">
-        <v>87.36711883544922</v>
+        <v>87.36712646484375</v>
       </c>
       <c r="E229" t="n">
-        <v>89.35253745046614</v>
+        <v>89.35254525323874</v>
       </c>
       <c r="F229" t="n">
         <v>588012</v>
@@ -5012,16 +5012,16 @@
         <v>44805</v>
       </c>
       <c r="B230" t="n">
-        <v>88.58823394775391</v>
+        <v>88.58824157714844</v>
       </c>
       <c r="C230" t="n">
-        <v>89.21197693820172</v>
+        <v>89.21198462131423</v>
       </c>
       <c r="D230" t="n">
-        <v>84.33628290195425</v>
+        <v>84.33629016516232</v>
       </c>
       <c r="E230" t="n">
-        <v>87.39347610622615</v>
+        <v>87.39348363272576</v>
       </c>
       <c r="F230" t="n">
         <v>1016578</v>
@@ -5052,16 +5052,16 @@
         <v>44809</v>
       </c>
       <c r="B232" t="n">
-        <v>89.43161773681641</v>
+        <v>89.43161010742188</v>
       </c>
       <c r="C232" t="n">
-        <v>89.8269414485207</v>
+        <v>89.82693378540118</v>
       </c>
       <c r="D232" t="n">
-        <v>88.03479433073093</v>
+        <v>88.03478682049915</v>
       </c>
       <c r="E232" t="n">
-        <v>88.81666154895264</v>
+        <v>88.81665397201991</v>
       </c>
       <c r="F232" t="n">
         <v>95765</v>
@@ -5072,16 +5072,16 @@
         <v>44810</v>
       </c>
       <c r="B233" t="n">
-        <v>86.71702575683594</v>
+        <v>86.71703338623047</v>
       </c>
       <c r="C233" t="n">
-        <v>89.31739369553651</v>
+        <v>89.31740155371233</v>
       </c>
       <c r="D233" t="n">
-        <v>85.2059996040562</v>
+        <v>85.20600710051012</v>
       </c>
       <c r="E233" t="n">
-        <v>88.73758523135686</v>
+        <v>88.73759303852093</v>
       </c>
       <c r="F233" t="n">
         <v>519096</v>
@@ -5092,16 +5092,16 @@
         <v>44812</v>
       </c>
       <c r="B234" t="n">
-        <v>88.28955078125</v>
+        <v>88.28955841064453</v>
       </c>
       <c r="C234" t="n">
-        <v>90.14319263235551</v>
+        <v>90.14320042192941</v>
       </c>
       <c r="D234" t="n">
-        <v>87.12992709878814</v>
+        <v>87.12993462797571</v>
       </c>
       <c r="E234" t="n">
-        <v>88.29833768786334</v>
+        <v>88.29834531801718</v>
       </c>
       <c r="F234" t="n">
         <v>707072</v>
@@ -5132,16 +5132,16 @@
         <v>44816</v>
       </c>
       <c r="B236" t="n">
-        <v>94.79048156738281</v>
+        <v>94.79047393798828</v>
       </c>
       <c r="C236" t="n">
-        <v>94.79048156738281</v>
+        <v>94.79047393798828</v>
       </c>
       <c r="D236" t="n">
-        <v>91.34675117884834</v>
+        <v>91.34674382662909</v>
       </c>
       <c r="E236" t="n">
-        <v>91.34675117884834</v>
+        <v>91.34674382662909</v>
       </c>
       <c r="F236" t="n">
         <v>423751</v>
@@ -5152,16 +5152,16 @@
         <v>44817</v>
       </c>
       <c r="B237" t="n">
-        <v>90.74935913085938</v>
+        <v>90.74937438964844</v>
       </c>
       <c r="C237" t="n">
-        <v>92.94561654736182</v>
+        <v>92.94563217543426</v>
       </c>
       <c r="D237" t="n">
-        <v>90.4858055599008</v>
+        <v>90.4858207743754</v>
       </c>
       <c r="E237" t="n">
-        <v>91.36430852650177</v>
+        <v>91.36432388868973</v>
       </c>
       <c r="F237" t="n">
         <v>548480</v>
@@ -5212,16 +5212,16 @@
         <v>44820</v>
       </c>
       <c r="B240" t="n">
-        <v>87.80636596679688</v>
+        <v>87.80637359619141</v>
       </c>
       <c r="C240" t="n">
-        <v>89.46673598332055</v>
+        <v>89.46674375698272</v>
       </c>
       <c r="D240" t="n">
-        <v>86.15478285633742</v>
+        <v>86.15479034222778</v>
       </c>
       <c r="E240" t="n">
-        <v>89.33496590458495</v>
+        <v>89.33497366679777</v>
       </c>
       <c r="F240" t="n">
         <v>454254</v>
@@ -5252,16 +5252,16 @@
         <v>44824</v>
       </c>
       <c r="B242" t="n">
-        <v>89.88842010498047</v>
+        <v>89.88843536376953</v>
       </c>
       <c r="C242" t="n">
-        <v>91.25010233617633</v>
+        <v>91.25011782611443</v>
       </c>
       <c r="D242" t="n">
-        <v>88.50917076414814</v>
+        <v>88.50918578880611</v>
       </c>
       <c r="E242" t="n">
-        <v>88.77272432581363</v>
+        <v>88.77273939521048</v>
       </c>
       <c r="F242" t="n">
         <v>415549</v>
@@ -5292,16 +5292,16 @@
         <v>44826</v>
       </c>
       <c r="B244" t="n">
-        <v>89.08020782470703</v>
+        <v>89.08021545410156</v>
       </c>
       <c r="C244" t="n">
-        <v>91.53123206185035</v>
+        <v>91.53123990116616</v>
       </c>
       <c r="D244" t="n">
-        <v>86.27778103806376</v>
+        <v>86.27778842744067</v>
       </c>
       <c r="E244" t="n">
-        <v>89.43161037420698</v>
+        <v>89.43161803369786</v>
       </c>
       <c r="F244" t="n">
         <v>985794</v>
@@ -5332,16 +5332,16 @@
         <v>44830</v>
       </c>
       <c r="B246" t="n">
-        <v>84.33628845214844</v>
+        <v>84.33628082275391</v>
       </c>
       <c r="C246" t="n">
-        <v>89.18562208907072</v>
+        <v>89.18561402098628</v>
       </c>
       <c r="D246" t="n">
-        <v>84.24843949216665</v>
+        <v>84.24843187071929</v>
       </c>
       <c r="E246" t="n">
-        <v>88.13142116439727</v>
+        <v>88.13141319168002</v>
       </c>
       <c r="F246" t="n">
         <v>548585</v>
@@ -5372,16 +5372,16 @@
         <v>44832</v>
       </c>
       <c r="B248" t="n">
-        <v>86.94544219970703</v>
+        <v>86.94544982910156</v>
       </c>
       <c r="C248" t="n">
-        <v>88.52674356400453</v>
+        <v>88.52675133215702</v>
       </c>
       <c r="D248" t="n">
-        <v>85.29385228500924</v>
+        <v>85.29385976947805</v>
       </c>
       <c r="E248" t="n">
-        <v>86.5501118317982</v>
+        <v>86.5501194265028</v>
       </c>
       <c r="F248" t="n">
         <v>626382</v>
@@ -5392,16 +5392,16 @@
         <v>44833</v>
       </c>
       <c r="B249" t="n">
-        <v>87.27049255371094</v>
+        <v>87.27048492431641</v>
       </c>
       <c r="C249" t="n">
-        <v>87.79759976248249</v>
+        <v>87.79759208700698</v>
       </c>
       <c r="D249" t="n">
-        <v>84.51199342491191</v>
+        <v>84.51198603667193</v>
       </c>
       <c r="E249" t="n">
-        <v>85.399283410401</v>
+        <v>85.39927594459202</v>
       </c>
       <c r="F249" t="n">
         <v>546314</v>
@@ -5452,16 +5452,16 @@
         <v>44838</v>
       </c>
       <c r="B252" t="n">
-        <v>94.43907928466797</v>
+        <v>94.43906402587891</v>
       </c>
       <c r="C252" t="n">
-        <v>96.46841921567656</v>
+        <v>96.46840362900132</v>
       </c>
       <c r="D252" t="n">
-        <v>92.77870903157975</v>
+        <v>92.77869404106141</v>
       </c>
       <c r="E252" t="n">
-        <v>93.47272725573275</v>
+        <v>93.47271215307993</v>
       </c>
       <c r="F252" t="n">
         <v>828067</v>
@@ -5472,16 +5472,16 @@
         <v>44839</v>
       </c>
       <c r="B253" t="n">
-        <v>95.75682067871094</v>
+        <v>95.7568359375</v>
       </c>
       <c r="C253" t="n">
-        <v>97.74223920433043</v>
+        <v>97.74225477949469</v>
       </c>
       <c r="D253" t="n">
-        <v>93.46392746387826</v>
+        <v>93.46394235729625</v>
       </c>
       <c r="E253" t="n">
-        <v>94.30728948391106</v>
+        <v>94.30730451171824</v>
       </c>
       <c r="F253" t="n">
         <v>556734</v>
@@ -5552,16 +5552,16 @@
         <v>44845</v>
       </c>
       <c r="B257" t="n">
-        <v>88.64974975585938</v>
+        <v>88.64974212646484</v>
       </c>
       <c r="C257" t="n">
-        <v>96.94281434223674</v>
+        <v>96.94280599912264</v>
       </c>
       <c r="D257" t="n">
-        <v>87.13872337332482</v>
+        <v>87.1387158739726</v>
       </c>
       <c r="E257" t="n">
-        <v>96.52113661370647</v>
+        <v>96.5211283068829</v>
       </c>
       <c r="F257" t="n">
         <v>1649810</v>
@@ -5612,16 +5612,16 @@
         <v>44851</v>
       </c>
       <c r="B260" t="n">
-        <v>83.01853179931641</v>
+        <v>83.01852416992188</v>
       </c>
       <c r="C260" t="n">
-        <v>85.90880741440093</v>
+        <v>85.90879951939036</v>
       </c>
       <c r="D260" t="n">
-        <v>82.82526007088433</v>
+        <v>82.82525245925146</v>
       </c>
       <c r="E260" t="n">
-        <v>84.32749936581655</v>
+        <v>84.32749161612804</v>
       </c>
       <c r="F260" t="n">
         <v>630186</v>
@@ -5632,16 +5632,16 @@
         <v>44852</v>
       </c>
       <c r="B261" t="n">
-        <v>80.54116058349609</v>
+        <v>80.54115295410156</v>
       </c>
       <c r="C261" t="n">
-        <v>85.61012027643372</v>
+        <v>85.61011216687361</v>
       </c>
       <c r="D261" t="n">
-        <v>79.24097310925836</v>
+        <v>79.24096560302623</v>
       </c>
       <c r="E261" t="n">
-        <v>84.42414248924207</v>
+        <v>84.42413449202566</v>
       </c>
       <c r="F261" t="n">
         <v>1514560</v>
@@ -5672,16 +5672,16 @@
         <v>44854</v>
       </c>
       <c r="B263" t="n">
-        <v>77.81778717041016</v>
+        <v>77.81779479980469</v>
       </c>
       <c r="C263" t="n">
-        <v>80.72562957529622</v>
+        <v>80.72563748978079</v>
       </c>
       <c r="D263" t="n">
-        <v>76.50003284276583</v>
+        <v>76.50004034296538</v>
       </c>
       <c r="E263" t="n">
-        <v>80.4708629343249</v>
+        <v>80.4708708238317</v>
       </c>
       <c r="F263" t="n">
         <v>1064344</v>
@@ -5692,16 +5692,16 @@
         <v>44855</v>
       </c>
       <c r="B264" t="n">
-        <v>82.25422668457031</v>
+        <v>82.25423431396484</v>
       </c>
       <c r="C264" t="n">
-        <v>85.73309747299184</v>
+        <v>85.73310542506498</v>
       </c>
       <c r="D264" t="n">
-        <v>75.13835431268782</v>
+        <v>75.13836128205794</v>
       </c>
       <c r="E264" t="n">
-        <v>77.96713481147866</v>
+        <v>77.967142043229</v>
       </c>
       <c r="F264" t="n">
         <v>1421863</v>
@@ -5712,16 +5712,16 @@
         <v>44858</v>
       </c>
       <c r="B265" t="n">
-        <v>82.40358734130859</v>
+        <v>82.40357971191406</v>
       </c>
       <c r="C265" t="n">
-        <v>83.41386046932367</v>
+        <v>83.41385274639228</v>
       </c>
       <c r="D265" t="n">
-        <v>80.20732975441281</v>
+        <v>80.20732232836033</v>
       </c>
       <c r="E265" t="n">
-        <v>81.73592315820733</v>
+        <v>81.73591559062895</v>
       </c>
       <c r="F265" t="n">
         <v>718180</v>
@@ -5732,16 +5732,16 @@
         <v>44859</v>
       </c>
       <c r="B266" t="n">
-        <v>82.92189788818359</v>
+        <v>82.92189025878906</v>
       </c>
       <c r="C266" t="n">
-        <v>85.30264022119347</v>
+        <v>85.30263237275399</v>
       </c>
       <c r="D266" t="n">
-        <v>81.31423578466473</v>
+        <v>81.31422830318635</v>
       </c>
       <c r="E266" t="n">
-        <v>82.03460797877678</v>
+        <v>82.03460043101913</v>
       </c>
       <c r="F266" t="n">
         <v>1189906</v>
@@ -5772,16 +5772,16 @@
         <v>44861</v>
       </c>
       <c r="B268" t="n">
-        <v>78.9598388671875</v>
+        <v>78.95984649658203</v>
       </c>
       <c r="C268" t="n">
-        <v>81.79740620583418</v>
+        <v>81.79741410940505</v>
       </c>
       <c r="D268" t="n">
-        <v>78.12526378652716</v>
+        <v>78.12527133528192</v>
       </c>
       <c r="E268" t="n">
-        <v>80.63778263670802</v>
+        <v>80.63779042823175</v>
       </c>
       <c r="F268" t="n">
         <v>872704</v>
@@ -5812,16 +5812,16 @@
         <v>44865</v>
       </c>
       <c r="B270" t="n">
-        <v>83.36994171142578</v>
+        <v>83.36994934082031</v>
       </c>
       <c r="C270" t="n">
-        <v>84.17816291781504</v>
+        <v>84.17817062117196</v>
       </c>
       <c r="D270" t="n">
-        <v>79.07406228540991</v>
+        <v>79.07406952167764</v>
       </c>
       <c r="E270" t="n">
-        <v>79.07406228540991</v>
+        <v>79.07406952167764</v>
       </c>
       <c r="F270" t="n">
         <v>956071</v>
@@ -5832,16 +5832,16 @@
         <v>44866</v>
       </c>
       <c r="B271" t="n">
-        <v>87.10356903076172</v>
+        <v>87.10357666015625</v>
       </c>
       <c r="C271" t="n">
-        <v>87.84150829326336</v>
+        <v>87.84151598729392</v>
       </c>
       <c r="D271" t="n">
-        <v>83.65983906752952</v>
+        <v>83.65984639528801</v>
       </c>
       <c r="E271" t="n">
-        <v>83.65983906752952</v>
+        <v>83.65984639528801</v>
       </c>
       <c r="F271" t="n">
         <v>1461617</v>
@@ -5852,16 +5852,16 @@
         <v>44868</v>
       </c>
       <c r="B272" t="n">
-        <v>86.58524322509766</v>
+        <v>86.58525848388672</v>
       </c>
       <c r="C272" t="n">
-        <v>88.4652388850419</v>
+        <v>88.4652544751398</v>
       </c>
       <c r="D272" t="n">
-        <v>84.0463703936091</v>
+        <v>84.04638520497635</v>
       </c>
       <c r="E272" t="n">
-        <v>85.59253736618446</v>
+        <v>85.59255245003042</v>
       </c>
       <c r="F272" t="n">
         <v>991113</v>
@@ -5872,16 +5872,16 @@
         <v>44869</v>
       </c>
       <c r="B273" t="n">
-        <v>83.48413848876953</v>
+        <v>83.484130859375</v>
       </c>
       <c r="C273" t="n">
-        <v>88.728802437938</v>
+        <v>88.72879432924752</v>
       </c>
       <c r="D273" t="n">
-        <v>82.78134011468907</v>
+        <v>82.78133254952142</v>
       </c>
       <c r="E273" t="n">
-        <v>87.59553277082331</v>
+        <v>87.59552476569932</v>
       </c>
       <c r="F273" t="n">
         <v>612180</v>
@@ -5892,16 +5892,16 @@
         <v>44872</v>
       </c>
       <c r="B274" t="n">
-        <v>83.19423675537109</v>
+        <v>83.19422912597656</v>
       </c>
       <c r="C274" t="n">
-        <v>84.51199133989617</v>
+        <v>84.51198358965588</v>
       </c>
       <c r="D274" t="n">
-        <v>82.28059947491988</v>
+        <v>82.2805919293112</v>
       </c>
       <c r="E274" t="n">
-        <v>83.03610593713023</v>
+        <v>83.03609832223721</v>
       </c>
       <c r="F274" t="n">
         <v>752715</v>
@@ -5912,16 +5912,16 @@
         <v>44873</v>
       </c>
       <c r="B275" t="n">
-        <v>83.45779418945312</v>
+        <v>83.45777893066406</v>
       </c>
       <c r="C275" t="n">
-        <v>84.66134584485553</v>
+        <v>84.66133036601822</v>
       </c>
       <c r="D275" t="n">
-        <v>81.31424448864632</v>
+        <v>81.31422962176761</v>
       </c>
       <c r="E275" t="n">
-        <v>82.71106789772105</v>
+        <v>82.71105277545774</v>
       </c>
       <c r="F275" t="n">
         <v>953385</v>
@@ -5932,16 +5932,16 @@
         <v>44874</v>
       </c>
       <c r="B276" t="n">
-        <v>90.18712615966797</v>
+        <v>90.18711853027344</v>
       </c>
       <c r="C276" t="n">
-        <v>93.10375601205598</v>
+        <v>93.10374813592868</v>
       </c>
       <c r="D276" t="n">
-        <v>83.46657649938446</v>
+        <v>83.4665694385159</v>
       </c>
       <c r="E276" t="n">
-        <v>83.89704111638565</v>
+        <v>83.89703401910188</v>
       </c>
       <c r="F276" t="n">
         <v>2468383</v>
@@ -5952,16 +5952,16 @@
         <v>44875</v>
       </c>
       <c r="B277" t="n">
-        <v>90.49459838867188</v>
+        <v>90.49459075927734</v>
       </c>
       <c r="C277" t="n">
-        <v>94.21944933414814</v>
+        <v>94.21944139071987</v>
       </c>
       <c r="D277" t="n">
-        <v>85.65404484922558</v>
+        <v>85.65403762792715</v>
       </c>
       <c r="E277" t="n">
-        <v>85.67161196063115</v>
+        <v>85.67160473785169</v>
       </c>
       <c r="F277" t="n">
         <v>2820385</v>
@@ -5992,16 +5992,16 @@
         <v>44879</v>
       </c>
       <c r="B279" t="n">
-        <v>88.81665802001953</v>
+        <v>88.816650390625</v>
       </c>
       <c r="C279" t="n">
-        <v>90.38917930161588</v>
+        <v>90.389171537141</v>
       </c>
       <c r="D279" t="n">
-        <v>85.91760194366664</v>
+        <v>85.91759456330244</v>
       </c>
       <c r="E279" t="n">
-        <v>89.08021161898182</v>
+        <v>89.08020396694791</v>
       </c>
       <c r="F279" t="n">
         <v>689741</v>
@@ -6052,16 +6052,16 @@
         <v>44883</v>
       </c>
       <c r="B282" t="n">
-        <v>82.07853698730469</v>
+        <v>82.07852935791016</v>
       </c>
       <c r="C282" t="n">
-        <v>86.70824492884405</v>
+        <v>86.7082368691072</v>
       </c>
       <c r="D282" t="n">
-        <v>81.44601374389941</v>
+        <v>81.44600617329941</v>
       </c>
       <c r="E282" t="n">
-        <v>85.21479248381745</v>
+        <v>85.21478456290053</v>
       </c>
       <c r="F282" t="n">
         <v>750376</v>
@@ -6072,16 +6072,16 @@
         <v>44886</v>
       </c>
       <c r="B283" t="n">
-        <v>80.04041290283203</v>
+        <v>80.0404052734375</v>
       </c>
       <c r="C283" t="n">
-        <v>82.5617190528683</v>
+        <v>82.56171118314468</v>
       </c>
       <c r="D283" t="n">
-        <v>79.62751539961722</v>
+        <v>79.6275078095798</v>
       </c>
       <c r="E283" t="n">
-        <v>82.06975279039395</v>
+        <v>82.0697449675642</v>
       </c>
       <c r="F283" t="n">
         <v>597582</v>
@@ -6092,16 +6092,16 @@
         <v>44887</v>
       </c>
       <c r="B284" t="n">
-        <v>78.23069763183594</v>
+        <v>78.23069000244141</v>
       </c>
       <c r="C284" t="n">
-        <v>80.67293498688288</v>
+        <v>80.67292711931084</v>
       </c>
       <c r="D284" t="n">
-        <v>76.6493894942427</v>
+        <v>76.64938201906415</v>
       </c>
       <c r="E284" t="n">
-        <v>80.04919863884506</v>
+        <v>80.04919083210247</v>
       </c>
       <c r="F284" t="n">
         <v>724710</v>
@@ -6112,16 +6112,16 @@
         <v>44888</v>
       </c>
       <c r="B285" t="n">
-        <v>77.27311706542969</v>
+        <v>77.27312469482422</v>
       </c>
       <c r="C285" t="n">
-        <v>78.72264824317485</v>
+        <v>78.7226560156857</v>
       </c>
       <c r="D285" t="n">
-        <v>75.99929049548588</v>
+        <v>75.99929799911189</v>
       </c>
       <c r="E285" t="n">
-        <v>78.02863012286181</v>
+        <v>78.0286378268503</v>
       </c>
       <c r="F285" t="n">
         <v>751617</v>
@@ -6172,16 +6172,16 @@
         <v>44893</v>
       </c>
       <c r="B288" t="n">
-        <v>75.56882476806641</v>
+        <v>75.56883239746094</v>
       </c>
       <c r="C288" t="n">
-        <v>78.24826158688813</v>
+        <v>78.2482694867974</v>
       </c>
       <c r="D288" t="n">
-        <v>75.2877040774397</v>
+        <v>75.28771167845241</v>
       </c>
       <c r="E288" t="n">
-        <v>77.14134593522536</v>
+        <v>77.14135372338092</v>
       </c>
       <c r="F288" t="n">
         <v>519110</v>
@@ -6312,16 +6312,16 @@
         <v>44902</v>
       </c>
       <c r="B295" t="n">
-        <v>76.15742492675781</v>
+        <v>76.15743255615234</v>
       </c>
       <c r="C295" t="n">
-        <v>78.4327444112255</v>
+        <v>78.43275226855985</v>
       </c>
       <c r="D295" t="n">
-        <v>74.76060171345117</v>
+        <v>74.76060920291299</v>
       </c>
       <c r="E295" t="n">
-        <v>77.82657521465414</v>
+        <v>77.82658301126293</v>
       </c>
       <c r="F295" t="n">
         <v>782541</v>
@@ -6352,16 +6352,16 @@
         <v>44904</v>
       </c>
       <c r="B297" t="n">
-        <v>72.71368408203125</v>
+        <v>72.71369171142578</v>
       </c>
       <c r="C297" t="n">
-        <v>74.76059750386545</v>
+        <v>74.76060534802988</v>
       </c>
       <c r="D297" t="n">
-        <v>70.93032421841735</v>
+        <v>70.93033166069503</v>
       </c>
       <c r="E297" t="n">
-        <v>72.96845073432544</v>
+        <v>72.96845839045105</v>
       </c>
       <c r="F297" t="n">
         <v>602365</v>
@@ -6372,16 +6372,16 @@
         <v>44907</v>
       </c>
       <c r="B298" t="n">
-        <v>72.23931121826172</v>
+        <v>72.23930358886719</v>
       </c>
       <c r="C298" t="n">
-        <v>74.02267139828965</v>
+        <v>74.02266358054949</v>
       </c>
       <c r="D298" t="n">
-        <v>70.51743928329</v>
+        <v>70.51743183574715</v>
       </c>
       <c r="E298" t="n">
-        <v>72.73127079828416</v>
+        <v>72.73126311693241</v>
       </c>
       <c r="F298" t="n">
         <v>769701</v>
@@ -6392,16 +6392,16 @@
         <v>44908</v>
       </c>
       <c r="B299" t="n">
-        <v>70.42079925537109</v>
+        <v>70.42080688476562</v>
       </c>
       <c r="C299" t="n">
-        <v>74.92751694822861</v>
+        <v>74.92752506588127</v>
       </c>
       <c r="D299" t="n">
-        <v>69.92883304873867</v>
+        <v>69.92884062483354</v>
       </c>
       <c r="E299" t="n">
-        <v>71.9581794084006</v>
+        <v>71.958187204355</v>
       </c>
       <c r="F299" t="n">
         <v>758036</v>
@@ -6412,16 +6412,16 @@
         <v>44909</v>
       </c>
       <c r="B300" t="n">
-        <v>68.19818878173828</v>
+        <v>68.19818115234375</v>
       </c>
       <c r="C300" t="n">
-        <v>70.5174362779243</v>
+        <v>70.51742838907342</v>
       </c>
       <c r="D300" t="n">
-        <v>66.81893927300305</v>
+        <v>66.81893179790644</v>
       </c>
       <c r="E300" t="n">
-        <v>70.43837422126734</v>
+        <v>70.43836634126119</v>
       </c>
       <c r="F300" t="n">
         <v>1355188</v>
@@ -6432,16 +6432,16 @@
         <v>44910</v>
       </c>
       <c r="B301" t="n">
-        <v>65.86138153076172</v>
+        <v>65.86137390136719</v>
       </c>
       <c r="C301" t="n">
-        <v>68.84829354963527</v>
+        <v>68.8482855742363</v>
       </c>
       <c r="D301" t="n">
-        <v>65.81745369274783</v>
+        <v>65.81744606844191</v>
       </c>
       <c r="E301" t="n">
-        <v>68.30361918951958</v>
+        <v>68.30361127721578</v>
       </c>
       <c r="F301" t="n">
         <v>806063</v>
@@ -6472,16 +6472,16 @@
         <v>44914</v>
       </c>
       <c r="B303" t="n">
-        <v>66.36210632324219</v>
+        <v>66.36211395263672</v>
       </c>
       <c r="C303" t="n">
-        <v>66.73107591293393</v>
+        <v>66.73108358474747</v>
       </c>
       <c r="D303" t="n">
-        <v>64.41182891709317</v>
+        <v>64.41183632227187</v>
       </c>
       <c r="E303" t="n">
-        <v>66.09855278635102</v>
+        <v>66.09856038544582</v>
       </c>
       <c r="F303" t="n">
         <v>945079</v>
@@ -6512,16 +6512,16 @@
         <v>44916</v>
       </c>
       <c r="B305" t="n">
-        <v>69.76192474365234</v>
+        <v>69.76193237304688</v>
       </c>
       <c r="C305" t="n">
-        <v>70.19238932645592</v>
+        <v>70.19239700292748</v>
       </c>
       <c r="D305" t="n">
-        <v>66.63444958235912</v>
+        <v>66.63445686972265</v>
       </c>
       <c r="E305" t="n">
-        <v>69.57743322000499</v>
+        <v>69.57744082922292</v>
       </c>
       <c r="F305" t="n">
         <v>349356</v>
@@ -6572,16 +6572,16 @@
         <v>44921</v>
       </c>
       <c r="B308" t="n">
-        <v>68.78679656982422</v>
+        <v>68.78678131103516</v>
       </c>
       <c r="C308" t="n">
-        <v>71.15875229880567</v>
+        <v>71.15873651385208</v>
       </c>
       <c r="D308" t="n">
-        <v>68.39146614669608</v>
+        <v>68.39145097560208</v>
       </c>
       <c r="E308" t="n">
-        <v>71.15875229880567</v>
+        <v>71.15873651385208</v>
       </c>
       <c r="F308" t="n">
         <v>122344</v>
@@ -6612,16 +6612,16 @@
         <v>44923</v>
       </c>
       <c r="B310" t="n">
-        <v>68.39144897460938</v>
+        <v>68.39145660400391</v>
       </c>
       <c r="C310" t="n">
-        <v>70.26266442886484</v>
+        <v>70.26267226700244</v>
       </c>
       <c r="D310" t="n">
-        <v>67.17911739346478</v>
+        <v>67.17912488761789</v>
       </c>
       <c r="E310" t="n">
-        <v>67.82042075287674</v>
+        <v>67.82042831857034</v>
       </c>
       <c r="F310" t="n">
         <v>543744</v>
@@ -6632,16 +6632,16 @@
         <v>44924</v>
       </c>
       <c r="B311" t="n">
-        <v>70.66677856445312</v>
+        <v>70.66678619384766</v>
       </c>
       <c r="C311" t="n">
-        <v>70.66677856445312</v>
+        <v>70.66678619384766</v>
       </c>
       <c r="D311" t="n">
-        <v>67.35481873074851</v>
+        <v>67.35482600257404</v>
       </c>
       <c r="E311" t="n">
-        <v>68.52322924831307</v>
+        <v>68.52323664628368</v>
       </c>
       <c r="F311" t="n">
         <v>1109758</v>
@@ -6652,16 +6652,16 @@
         <v>44928</v>
       </c>
       <c r="B312" t="n">
-        <v>66.42360687255859</v>
+        <v>66.42361450195312</v>
       </c>
       <c r="C312" t="n">
-        <v>69.77070088095081</v>
+        <v>69.7707088947915</v>
       </c>
       <c r="D312" t="n">
-        <v>66.12491239199053</v>
+        <v>66.12491998707712</v>
       </c>
       <c r="E312" t="n">
-        <v>68.88341775009563</v>
+        <v>68.88342566202327</v>
       </c>
       <c r="F312" t="n">
         <v>452524</v>
@@ -6692,16 +6692,16 @@
         <v>44930</v>
       </c>
       <c r="B314" t="n">
-        <v>67.00342559814453</v>
+        <v>67.00341796875</v>
       </c>
       <c r="C314" t="n">
-        <v>68.40903585947962</v>
+        <v>68.40902807003422</v>
       </c>
       <c r="D314" t="n">
-        <v>66.33576809670147</v>
+        <v>66.33576054333025</v>
       </c>
       <c r="E314" t="n">
-        <v>66.52025293545124</v>
+        <v>66.52024536107352</v>
       </c>
       <c r="F314" t="n">
         <v>669125</v>
@@ -6732,16 +6732,16 @@
         <v>44932</v>
       </c>
       <c r="B316" t="n">
-        <v>68.31239318847656</v>
+        <v>68.31240081787109</v>
       </c>
       <c r="C316" t="n">
-        <v>68.31239318847656</v>
+        <v>68.31240081787109</v>
       </c>
       <c r="D316" t="n">
-        <v>65.62416952826607</v>
+        <v>65.62417685742929</v>
       </c>
       <c r="E316" t="n">
-        <v>65.99314587149411</v>
+        <v>65.99315324186605</v>
       </c>
       <c r="F316" t="n">
         <v>775272</v>
@@ -6772,16 +6772,16 @@
         <v>44936</v>
       </c>
       <c r="B318" t="n">
-        <v>71.22024536132812</v>
+        <v>71.22023773193359</v>
       </c>
       <c r="C318" t="n">
-        <v>71.73856567059647</v>
+        <v>71.73855798567742</v>
       </c>
       <c r="D318" t="n">
-        <v>69.26118051816475</v>
+        <v>69.26117309863299</v>
       </c>
       <c r="E318" t="n">
-        <v>69.26118051816475</v>
+        <v>69.26117309863299</v>
       </c>
       <c r="F318" t="n">
         <v>559538</v>
@@ -6792,16 +6792,16 @@
         <v>44937</v>
       </c>
       <c r="B319" t="n">
-        <v>72.90696716308594</v>
+        <v>72.90695953369141</v>
       </c>
       <c r="C319" t="n">
-        <v>73.10902581621284</v>
+        <v>73.10901816567375</v>
       </c>
       <c r="D319" t="n">
-        <v>69.80585242983342</v>
+        <v>69.80584512495696</v>
       </c>
       <c r="E319" t="n">
-        <v>71.22024289438232</v>
+        <v>71.2202354414961</v>
       </c>
       <c r="F319" t="n">
         <v>824670</v>
@@ -6812,16 +6812,16 @@
         <v>44938</v>
       </c>
       <c r="B320" t="n">
-        <v>74.93631744384766</v>
+        <v>74.93630981445312</v>
       </c>
       <c r="C320" t="n">
-        <v>75.89388260992675</v>
+        <v>75.89387488304087</v>
       </c>
       <c r="D320" t="n">
-        <v>71.29052822216363</v>
+        <v>71.29052096395313</v>
       </c>
       <c r="E320" t="n">
-        <v>72.90697071616947</v>
+        <v>72.90696329338618</v>
       </c>
       <c r="F320" t="n">
         <v>1386963</v>
@@ -6892,16 +6892,16 @@
         <v>44944</v>
       </c>
       <c r="B324" t="n">
-        <v>73.96994781494141</v>
+        <v>73.96994018554688</v>
       </c>
       <c r="C324" t="n">
-        <v>75.29648918389273</v>
+        <v>75.29648141767632</v>
       </c>
       <c r="D324" t="n">
-        <v>72.48528234483609</v>
+        <v>72.48527486857265</v>
       </c>
       <c r="E324" t="n">
-        <v>72.52042326813002</v>
+        <v>72.52041578824208</v>
       </c>
       <c r="F324" t="n">
         <v>881691</v>
@@ -6952,16 +6952,16 @@
         <v>44949</v>
       </c>
       <c r="B327" t="n">
-        <v>80.09310913085938</v>
+        <v>80.09311676025391</v>
       </c>
       <c r="C327" t="n">
-        <v>81.20881158598479</v>
+        <v>81.2088193216573</v>
       </c>
       <c r="D327" t="n">
-        <v>77.09741767677029</v>
+        <v>77.09742502080553</v>
       </c>
       <c r="E327" t="n">
-        <v>77.09741767677029</v>
+        <v>77.09742502080553</v>
       </c>
       <c r="F327" t="n">
         <v>1210224</v>
@@ -6972,16 +6972,16 @@
         <v>44950</v>
       </c>
       <c r="B328" t="n">
-        <v>80.33030700683594</v>
+        <v>80.33031463623047</v>
       </c>
       <c r="C328" t="n">
-        <v>81.2966588525702</v>
+        <v>81.29666657374428</v>
       </c>
       <c r="D328" t="n">
-        <v>78.64357635156964</v>
+        <v>78.64358382076644</v>
       </c>
       <c r="E328" t="n">
-        <v>81.2966588525702</v>
+        <v>81.29666657374428</v>
       </c>
       <c r="F328" t="n">
         <v>788120</v>
@@ -6992,16 +6992,16 @@
         <v>44951</v>
       </c>
       <c r="B329" t="n">
-        <v>77.85294342041016</v>
+        <v>77.85293579101562</v>
       </c>
       <c r="C329" t="n">
-        <v>79.94377828577274</v>
+        <v>79.94377045148158</v>
       </c>
       <c r="D329" t="n">
-        <v>77.15892520022911</v>
+        <v>77.15891763884663</v>
       </c>
       <c r="E329" t="n">
-        <v>79.94377828577274</v>
+        <v>79.94377045148158</v>
       </c>
       <c r="F329" t="n">
         <v>568888</v>
@@ -7032,16 +7032,16 @@
         <v>44953</v>
       </c>
       <c r="B331" t="n">
-        <v>81.18247222900391</v>
+        <v>81.18246459960938</v>
       </c>
       <c r="C331" t="n">
-        <v>81.18247222900391</v>
+        <v>81.18246459960938</v>
       </c>
       <c r="D331" t="n">
-        <v>75.7357491525274</v>
+        <v>75.73574203500689</v>
       </c>
       <c r="E331" t="n">
-        <v>78.99499475050509</v>
+        <v>78.99498732668607</v>
       </c>
       <c r="F331" t="n">
         <v>1276572</v>
@@ -7052,16 +7052,16 @@
         <v>44956</v>
       </c>
       <c r="B332" t="n">
-        <v>80.84862518310547</v>
+        <v>80.84864044189453</v>
       </c>
       <c r="C332" t="n">
-        <v>81.99068169579233</v>
+        <v>81.99069717012495</v>
       </c>
       <c r="D332" t="n">
-        <v>78.90713447349425</v>
+        <v>78.90714936586031</v>
       </c>
       <c r="E332" t="n">
-        <v>81.17367368654911</v>
+        <v>81.17368900668549</v>
       </c>
       <c r="F332" t="n">
         <v>515927</v>
@@ -7072,16 +7072,16 @@
         <v>44957</v>
       </c>
       <c r="B333" t="n">
-        <v>78.84564208984375</v>
+        <v>78.84564971923828</v>
       </c>
       <c r="C333" t="n">
-        <v>81.68320965117834</v>
+        <v>81.68321755514636</v>
       </c>
       <c r="D333" t="n">
-        <v>78.84564208984375</v>
+        <v>78.84564971923828</v>
       </c>
       <c r="E333" t="n">
-        <v>80.83984089613189</v>
+        <v>80.83984871849243</v>
       </c>
       <c r="F333" t="n">
         <v>714873</v>
@@ -7092,16 +7092,16 @@
         <v>44958</v>
       </c>
       <c r="B334" t="n">
-        <v>77.84415435791016</v>
+        <v>77.84414672851562</v>
       </c>
       <c r="C334" t="n">
-        <v>79.74171742556558</v>
+        <v>79.74170961019361</v>
       </c>
       <c r="D334" t="n">
-        <v>76.97443823117001</v>
+        <v>76.97443068701511</v>
       </c>
       <c r="E334" t="n">
-        <v>78.62602152176328</v>
+        <v>78.62601381573906</v>
       </c>
       <c r="F334" t="n">
         <v>624239</v>
@@ -7172,16 +7172,16 @@
         <v>44964</v>
       </c>
       <c r="B338" t="n">
-        <v>74.67276000976562</v>
+        <v>74.67275238037109</v>
       </c>
       <c r="C338" t="n">
-        <v>78.23948028427274</v>
+        <v>78.23947229046264</v>
       </c>
       <c r="D338" t="n">
-        <v>74.45313424503101</v>
+        <v>74.45312663807589</v>
       </c>
       <c r="E338" t="n">
-        <v>76.98322064189294</v>
+        <v>76.98321277643622</v>
       </c>
       <c r="F338" t="n">
         <v>1089766</v>
@@ -7192,16 +7192,16 @@
         <v>44965</v>
       </c>
       <c r="B339" t="n">
-        <v>74.92752838134766</v>
+        <v>74.92752075195312</v>
       </c>
       <c r="C339" t="n">
-        <v>76.47369567643597</v>
+        <v>76.47368788960505</v>
       </c>
       <c r="D339" t="n">
-        <v>73.99631726277404</v>
+        <v>73.99630972819882</v>
       </c>
       <c r="E339" t="n">
-        <v>74.67276168424898</v>
+        <v>74.67275408079573</v>
       </c>
       <c r="F339" t="n">
         <v>806683</v>
@@ -7212,16 +7212,16 @@
         <v>44966</v>
       </c>
       <c r="B340" t="n">
-        <v>72.64341735839844</v>
+        <v>72.64340972900391</v>
       </c>
       <c r="C340" t="n">
-        <v>76.30677336791243</v>
+        <v>76.30676535377293</v>
       </c>
       <c r="D340" t="n">
-        <v>72.33593593736826</v>
+        <v>72.33592834026705</v>
       </c>
       <c r="E340" t="n">
-        <v>74.92752388531035</v>
+        <v>74.92751601602691</v>
       </c>
       <c r="F340" t="n">
         <v>904775</v>
@@ -7232,16 +7232,16 @@
         <v>44967</v>
       </c>
       <c r="B341" t="n">
-        <v>71.36080932617188</v>
+        <v>71.36080169677734</v>
       </c>
       <c r="C341" t="n">
-        <v>73.24958561767697</v>
+        <v>73.24957778634779</v>
       </c>
       <c r="D341" t="n">
-        <v>70.52622736480184</v>
+        <v>70.52621982463492</v>
       </c>
       <c r="E341" t="n">
-        <v>72.74005891664892</v>
+        <v>72.74005113979474</v>
       </c>
       <c r="F341" t="n">
         <v>649433</v>
@@ -7252,16 +7252,16 @@
         <v>44970</v>
       </c>
       <c r="B342" t="n">
-        <v>73.79425811767578</v>
+        <v>73.79425048828125</v>
       </c>
       <c r="C342" t="n">
-        <v>74.05781172050324</v>
+        <v>74.05780406386059</v>
       </c>
       <c r="D342" t="n">
-        <v>70.90398220377323</v>
+        <v>70.90397487319673</v>
       </c>
       <c r="E342" t="n">
-        <v>71.35202064760129</v>
+        <v>71.35201327070328</v>
       </c>
       <c r="F342" t="n">
         <v>400048</v>
@@ -7272,16 +7272,16 @@
         <v>44971</v>
       </c>
       <c r="B343" t="n">
-        <v>72.90696716308594</v>
+        <v>72.90695953369141</v>
       </c>
       <c r="C343" t="n">
-        <v>74.53219648561118</v>
+        <v>74.53218868614353</v>
       </c>
       <c r="D343" t="n">
-        <v>71.91426111693616</v>
+        <v>71.91425359142397</v>
       </c>
       <c r="E343" t="n">
-        <v>73.00360303600144</v>
+        <v>73.00359539649439</v>
       </c>
       <c r="F343" t="n">
         <v>472429</v>
@@ -7292,16 +7292,16 @@
         <v>44972</v>
       </c>
       <c r="B344" t="n">
-        <v>73.78546905517578</v>
+        <v>73.78546142578125</v>
       </c>
       <c r="C344" t="n">
-        <v>74.93631260463282</v>
+        <v>74.93630485624141</v>
       </c>
       <c r="D344" t="n">
-        <v>71.65070638245331</v>
+        <v>71.65069897379257</v>
       </c>
       <c r="E344" t="n">
-        <v>72.23930851791685</v>
+        <v>72.23930104839484</v>
       </c>
       <c r="F344" t="n">
         <v>619864</v>
@@ -7312,16 +7312,16 @@
         <v>44973</v>
       </c>
       <c r="B345" t="n">
-        <v>71.15873718261719</v>
+        <v>71.15874481201172</v>
       </c>
       <c r="C345" t="n">
-        <v>73.96994387181648</v>
+        <v>73.96995180261891</v>
       </c>
       <c r="D345" t="n">
-        <v>70.32416208182393</v>
+        <v>70.32416962173819</v>
       </c>
       <c r="E345" t="n">
-        <v>73.30228647216005</v>
+        <v>73.30229433137855</v>
       </c>
       <c r="F345" t="n">
         <v>1330447</v>
@@ -7352,16 +7352,16 @@
         <v>44979</v>
       </c>
       <c r="B347" t="n">
-        <v>59.92268753051758</v>
+        <v>59.92269515991211</v>
       </c>
       <c r="C347" t="n">
-        <v>60.25651625042154</v>
+        <v>60.25652392231935</v>
       </c>
       <c r="D347" t="n">
-        <v>58.28867144964006</v>
+        <v>58.28867887099064</v>
       </c>
       <c r="E347" t="n">
-        <v>58.85969972778687</v>
+        <v>58.85970722184112</v>
       </c>
       <c r="F347" t="n">
         <v>1166573</v>
@@ -7372,16 +7372,16 @@
         <v>44980</v>
       </c>
       <c r="B348" t="n">
-        <v>59.61521530151367</v>
+        <v>59.61521148681641</v>
       </c>
       <c r="C348" t="n">
-        <v>60.55521326210563</v>
+        <v>60.55520938725917</v>
       </c>
       <c r="D348" t="n">
-        <v>58.94755113155375</v>
+        <v>58.94754735957942</v>
       </c>
       <c r="E348" t="n">
-        <v>60.00175877398195</v>
+        <v>60.0017549345503</v>
       </c>
       <c r="F348" t="n">
         <v>572076</v>
@@ -7392,16 +7392,16 @@
         <v>44981</v>
       </c>
       <c r="B349" t="n">
-        <v>58.85091781616211</v>
+        <v>58.85091018676758</v>
       </c>
       <c r="C349" t="n">
-        <v>59.79970272476828</v>
+        <v>59.79969497237389</v>
       </c>
       <c r="D349" t="n">
-        <v>57.98998857507038</v>
+        <v>57.98998105728616</v>
       </c>
       <c r="E349" t="n">
-        <v>59.56250984883994</v>
+        <v>59.56250212719508</v>
       </c>
       <c r="F349" t="n">
         <v>780666</v>
@@ -7452,16 +7452,16 @@
         <v>44986</v>
       </c>
       <c r="B352" t="n">
-        <v>54.14213943481445</v>
+        <v>54.14214324951172</v>
       </c>
       <c r="C352" t="n">
-        <v>57.10269353027231</v>
+        <v>57.10269755356158</v>
       </c>
       <c r="D352" t="n">
-        <v>53.41298035499475</v>
+        <v>53.4129841183176</v>
       </c>
       <c r="E352" t="n">
-        <v>56.48774412707847</v>
+        <v>56.4877481070402</v>
       </c>
       <c r="F352" t="n">
         <v>634515</v>
@@ -7492,16 +7492,16 @@
         <v>44988</v>
       </c>
       <c r="B354" t="n">
-        <v>52.3587760925293</v>
+        <v>52.35877990722656</v>
       </c>
       <c r="C354" t="n">
-        <v>54.11578204665744</v>
+        <v>54.11578598936467</v>
       </c>
       <c r="D354" t="n">
-        <v>52.3587760925293</v>
+        <v>52.35877990722656</v>
       </c>
       <c r="E354" t="n">
-        <v>53.14943011237612</v>
+        <v>53.14943398467798</v>
       </c>
       <c r="F354" t="n">
         <v>443497</v>
@@ -7532,16 +7532,16 @@
         <v>44992</v>
       </c>
       <c r="B356" t="n">
-        <v>54.52868270874023</v>
+        <v>54.52867889404297</v>
       </c>
       <c r="C356" t="n">
-        <v>54.57260718991888</v>
+        <v>54.57260337214876</v>
       </c>
       <c r="D356" t="n">
-        <v>53.0264433343582</v>
+        <v>53.02643962475403</v>
       </c>
       <c r="E356" t="n">
-        <v>54.28270293316135</v>
+        <v>54.28269913567225</v>
       </c>
       <c r="F356" t="n">
         <v>485619</v>
@@ -7552,16 +7552,16 @@
         <v>44993</v>
       </c>
       <c r="B357" t="n">
-        <v>58.67521286010742</v>
+        <v>58.67522048950195</v>
       </c>
       <c r="C357" t="n">
-        <v>58.67521286010742</v>
+        <v>58.67522048950195</v>
       </c>
       <c r="D357" t="n">
-        <v>53.97522006484605</v>
+        <v>53.975227083112</v>
       </c>
       <c r="E357" t="n">
-        <v>53.97522006484605</v>
+        <v>53.975227083112</v>
       </c>
       <c r="F357" t="n">
         <v>1672249</v>
@@ -7592,16 +7592,16 @@
         <v>44995</v>
       </c>
       <c r="B359" t="n">
-        <v>52.01615905761719</v>
+        <v>52.01616668701172</v>
       </c>
       <c r="C359" t="n">
-        <v>56.08362866950537</v>
+        <v>56.08363689549009</v>
       </c>
       <c r="D359" t="n">
-        <v>51.79653331930479</v>
+        <v>51.79654091648602</v>
       </c>
       <c r="E359" t="n">
-        <v>55.52138731562125</v>
+        <v>55.52139545914005</v>
       </c>
       <c r="F359" t="n">
         <v>846843</v>
@@ -7612,16 +7612,16 @@
         <v>44998</v>
       </c>
       <c r="B360" t="n">
-        <v>50.39093017578125</v>
+        <v>50.39093399047852</v>
       </c>
       <c r="C360" t="n">
-        <v>51.96345127391815</v>
+        <v>51.9634552076585</v>
       </c>
       <c r="D360" t="n">
-        <v>49.46850274069867</v>
+        <v>49.46850648556628</v>
       </c>
       <c r="E360" t="n">
-        <v>51.96345127391815</v>
+        <v>51.9634552076585</v>
       </c>
       <c r="F360" t="n">
         <v>1066340</v>
@@ -7632,16 +7632,16 @@
         <v>44999</v>
       </c>
       <c r="B361" t="n">
-        <v>50.32943725585938</v>
+        <v>50.32944107055664</v>
       </c>
       <c r="C361" t="n">
-        <v>52.78924496516417</v>
+        <v>52.78924896630146</v>
       </c>
       <c r="D361" t="n">
-        <v>49.55635368394428</v>
+        <v>49.55635744004602</v>
       </c>
       <c r="E361" t="n">
-        <v>50.84775415559906</v>
+        <v>50.84775800958192</v>
       </c>
       <c r="F361" t="n">
         <v>730632</v>
@@ -7752,16 +7752,16 @@
         <v>45007</v>
       </c>
       <c r="B367" t="n">
-        <v>52.56961822509766</v>
+        <v>52.56962203979492</v>
       </c>
       <c r="C367" t="n">
-        <v>55.1260617515593</v>
+        <v>55.12606575176405</v>
       </c>
       <c r="D367" t="n">
-        <v>52.56961822509766</v>
+        <v>52.56962203979492</v>
       </c>
       <c r="E367" t="n">
-        <v>53.85223176594004</v>
+        <v>53.85223567370974</v>
       </c>
       <c r="F367" t="n">
         <v>930770</v>
@@ -7772,16 +7772,16 @@
         <v>45008</v>
       </c>
       <c r="B368" t="n">
-        <v>49.1961669921875</v>
+        <v>49.19617080688477</v>
       </c>
       <c r="C368" t="n">
-        <v>53.29877430955613</v>
+        <v>53.29877844237178</v>
       </c>
       <c r="D368" t="n">
-        <v>48.85355136540186</v>
+        <v>48.85355515353253</v>
       </c>
       <c r="E368" t="n">
-        <v>52.56961857712928</v>
+        <v>52.56962265340579</v>
       </c>
       <c r="F368" t="n">
         <v>1208098</v>
@@ -7792,16 +7792,16 @@
         <v>45009</v>
       </c>
       <c r="B369" t="n">
-        <v>50.40850448608398</v>
+        <v>50.40850067138672</v>
       </c>
       <c r="C369" t="n">
-        <v>51.3660729168746</v>
+        <v>51.3660690297127</v>
       </c>
       <c r="D369" t="n">
-        <v>48.82719971216801</v>
+        <v>48.82719601713704</v>
       </c>
       <c r="E369" t="n">
-        <v>50.05710193578128</v>
+        <v>50.05709814767665</v>
       </c>
       <c r="F369" t="n">
         <v>598427</v>
@@ -7852,16 +7852,16 @@
         <v>45014</v>
       </c>
       <c r="B372" t="n">
-        <v>53.88737106323242</v>
+        <v>53.88737487792969</v>
       </c>
       <c r="C372" t="n">
-        <v>54.64288413609415</v>
+        <v>54.64288800427434</v>
       </c>
       <c r="D372" t="n">
-        <v>52.91223225296775</v>
+        <v>52.91223599863476</v>
       </c>
       <c r="E372" t="n">
-        <v>54.38811747641328</v>
+        <v>54.38812132655848</v>
       </c>
       <c r="F372" t="n">
         <v>332515</v>
@@ -7872,16 +7872,16 @@
         <v>45015</v>
       </c>
       <c r="B373" t="n">
-        <v>54.20363616943359</v>
+        <v>54.20363235473633</v>
       </c>
       <c r="C373" t="n">
-        <v>56.39989033438518</v>
+        <v>56.3998863651218</v>
       </c>
       <c r="D373" t="n">
-        <v>53.72924374164636</v>
+        <v>53.72923996033548</v>
       </c>
       <c r="E373" t="n">
-        <v>54.0367184534216</v>
+        <v>54.03671465047152</v>
       </c>
       <c r="F373" t="n">
         <v>990197</v>
@@ -7912,16 +7912,16 @@
         <v>45019</v>
       </c>
       <c r="B375" t="n">
-        <v>49.41579437255859</v>
+        <v>49.41579055786133</v>
       </c>
       <c r="C375" t="n">
-        <v>52.67503973932627</v>
+        <v>52.67503567302858</v>
       </c>
       <c r="D375" t="n">
-        <v>49.41579437255859</v>
+        <v>49.41579055786133</v>
       </c>
       <c r="E375" t="n">
-        <v>52.34999456357366</v>
+        <v>52.34999052236814</v>
       </c>
       <c r="F375" t="n">
         <v>492395</v>
@@ -7932,16 +7932,16 @@
         <v>45020</v>
       </c>
       <c r="B376" t="n">
-        <v>48.9062614440918</v>
+        <v>48.90625762939453</v>
       </c>
       <c r="C376" t="n">
-        <v>50.48756955878359</v>
+        <v>50.48756562074401</v>
       </c>
       <c r="D376" t="n">
-        <v>48.55486224733378</v>
+        <v>48.55485846004571</v>
       </c>
       <c r="E376" t="n">
-        <v>49.5914960775326</v>
+        <v>49.59149220938691</v>
       </c>
       <c r="F376" t="n">
         <v>366364</v>
@@ -7952,16 +7952,16 @@
         <v>45021</v>
       </c>
       <c r="B377" t="n">
-        <v>48.9062614440918</v>
+        <v>48.90625762939453</v>
       </c>
       <c r="C377" t="n">
-        <v>49.2049526045088</v>
+        <v>49.20494876651357</v>
       </c>
       <c r="D377" t="n">
-        <v>47.2810321999312</v>
+        <v>47.2810285120021</v>
       </c>
       <c r="E377" t="n">
-        <v>48.94140236913452</v>
+        <v>48.94139855169625</v>
       </c>
       <c r="F377" t="n">
         <v>464516</v>
@@ -7972,16 +7972,16 @@
         <v>45022</v>
       </c>
       <c r="B378" t="n">
-        <v>48.04532623291016</v>
+        <v>48.04533004760742</v>
       </c>
       <c r="C378" t="n">
-        <v>49.56513596918133</v>
+        <v>49.56513990454828</v>
       </c>
       <c r="D378" t="n">
-        <v>47.88719543017925</v>
+        <v>47.88719923232127</v>
       </c>
       <c r="E378" t="n">
-        <v>48.64270852073295</v>
+        <v>48.64271238286111</v>
       </c>
       <c r="F378" t="n">
         <v>483494</v>
@@ -7992,16 +7992,16 @@
         <v>45026</v>
       </c>
       <c r="B379" t="n">
-        <v>48.75691604614258</v>
+        <v>48.75691986083984</v>
       </c>
       <c r="C379" t="n">
-        <v>49.21373800403698</v>
+        <v>49.21374185447558</v>
       </c>
       <c r="D379" t="n">
-        <v>48.01018984358273</v>
+        <v>48.01019359985681</v>
       </c>
       <c r="E379" t="n">
-        <v>48.3264481056115</v>
+        <v>48.32645188662934</v>
       </c>
       <c r="F379" t="n">
         <v>441343</v>
@@ -8012,16 +8012,16 @@
         <v>45027</v>
       </c>
       <c r="B380" t="n">
-        <v>54.63410568237305</v>
+        <v>54.63410186767578</v>
       </c>
       <c r="C380" t="n">
-        <v>54.63410568237305</v>
+        <v>54.63410186767578</v>
       </c>
       <c r="D380" t="n">
-        <v>48.85355712225322</v>
+        <v>48.8535537111691</v>
       </c>
       <c r="E380" t="n">
-        <v>48.85355712225322</v>
+        <v>48.8535537111691</v>
       </c>
       <c r="F380" t="n">
         <v>1223134</v>
@@ -8032,16 +8032,16 @@
         <v>45028</v>
       </c>
       <c r="B381" t="n">
-        <v>56.73373031616211</v>
+        <v>56.73372268676758</v>
       </c>
       <c r="C381" t="n">
-        <v>57.69129545283193</v>
+        <v>57.69128769466669</v>
       </c>
       <c r="D381" t="n">
-        <v>54.30905994717439</v>
+        <v>54.3090526438428</v>
       </c>
       <c r="E381" t="n">
-        <v>54.55503973632089</v>
+        <v>54.55503239991062</v>
       </c>
       <c r="F381" t="n">
         <v>1443641</v>
@@ -8052,16 +8052,16 @@
         <v>45029</v>
       </c>
       <c r="B382" t="n">
-        <v>60.46735763549805</v>
+        <v>60.46736145019531</v>
       </c>
       <c r="C382" t="n">
-        <v>61.46006352292876</v>
+        <v>61.46006740025275</v>
       </c>
       <c r="D382" t="n">
-        <v>55.96063671432766</v>
+        <v>55.96064024470993</v>
       </c>
       <c r="E382" t="n">
-        <v>56.40867172931058</v>
+        <v>56.408675287958</v>
       </c>
       <c r="F382" t="n">
         <v>2756815</v>
@@ -8092,16 +8092,16 @@
         <v>45033</v>
       </c>
       <c r="B384" t="n">
-        <v>59.95782470703125</v>
+        <v>59.95783233642578</v>
       </c>
       <c r="C384" t="n">
-        <v>60.7221246656276</v>
+        <v>60.72213239227627</v>
       </c>
       <c r="D384" t="n">
-        <v>59.16717073304285</v>
+        <v>59.16717826182981</v>
       </c>
       <c r="E384" t="n">
-        <v>60.35314834280274</v>
+        <v>60.35315602250063</v>
       </c>
       <c r="F384" t="n">
         <v>288592</v>
@@ -8112,16 +8112,16 @@
         <v>45034</v>
       </c>
       <c r="B385" t="n">
-        <v>61.49520111083984</v>
+        <v>61.49521255493164</v>
       </c>
       <c r="C385" t="n">
-        <v>61.49520111083984</v>
+        <v>61.49521255493164</v>
       </c>
       <c r="D385" t="n">
-        <v>59.16716715686905</v>
+        <v>59.16717816771997</v>
       </c>
       <c r="E385" t="n">
-        <v>59.16716715686905</v>
+        <v>59.16717816771997</v>
       </c>
       <c r="F385" t="n">
         <v>581190</v>
@@ -8152,16 +8152,16 @@
         <v>45036</v>
       </c>
       <c r="B387" t="n">
-        <v>60.80119705200195</v>
+        <v>60.80119323730469</v>
       </c>
       <c r="C387" t="n">
-        <v>60.80119705200195</v>
+        <v>60.80119323730469</v>
       </c>
       <c r="D387" t="n">
-        <v>58.2183958652091</v>
+        <v>58.21839221255807</v>
       </c>
       <c r="E387" t="n">
-        <v>58.78942420478224</v>
+        <v>58.78942051630461</v>
       </c>
       <c r="F387" t="n">
         <v>442904</v>
@@ -8172,16 +8172,16 @@
         <v>45040</v>
       </c>
       <c r="B388" t="n">
-        <v>60.99446868896484</v>
+        <v>60.99446487426758</v>
       </c>
       <c r="C388" t="n">
-        <v>61.27558940451494</v>
+        <v>61.2755855722359</v>
       </c>
       <c r="D388" t="n">
-        <v>59.73820902519019</v>
+        <v>59.73820528906153</v>
       </c>
       <c r="E388" t="n">
-        <v>60.27409643646482</v>
+        <v>60.27409266682086</v>
       </c>
       <c r="F388" t="n">
         <v>315786</v>
@@ -8192,16 +8192,16 @@
         <v>45041</v>
       </c>
       <c r="B389" t="n">
-        <v>60.50251007080078</v>
+        <v>60.50250244140625</v>
       </c>
       <c r="C389" t="n">
-        <v>61.2843772827617</v>
+        <v>61.28436955477335</v>
       </c>
       <c r="D389" t="n">
-        <v>59.0090508000448</v>
+        <v>59.00904335897617</v>
       </c>
       <c r="E389" t="n">
-        <v>61.2843772827617</v>
+        <v>61.28436955477335</v>
       </c>
       <c r="F389" t="n">
         <v>695154</v>
@@ -8212,16 +8212,16 @@
         <v>45042</v>
       </c>
       <c r="B390" t="n">
-        <v>59.31652069091797</v>
+        <v>59.3165168762207</v>
       </c>
       <c r="C390" t="n">
-        <v>60.01932578469255</v>
+        <v>60.01932192479727</v>
       </c>
       <c r="D390" t="n">
-        <v>56.9533521355543</v>
+        <v>56.95334847283447</v>
       </c>
       <c r="E390" t="n">
-        <v>59.30774048651921</v>
+        <v>59.30773667238661</v>
       </c>
       <c r="F390" t="n">
         <v>963997</v>
@@ -8232,16 +8232,16 @@
         <v>45043</v>
       </c>
       <c r="B391" t="n">
-        <v>61.50400161743164</v>
+        <v>61.50399780273438</v>
       </c>
       <c r="C391" t="n">
-        <v>62.82175621836179</v>
+        <v>62.82175232193269</v>
       </c>
       <c r="D391" t="n">
-        <v>58.44680799419723</v>
+        <v>58.446804369118</v>
       </c>
       <c r="E391" t="n">
-        <v>58.59615190704881</v>
+        <v>58.59614827270675</v>
       </c>
       <c r="F391" t="n">
         <v>723893</v>
@@ -8252,16 +8252,16 @@
         <v>45044</v>
       </c>
       <c r="B392" t="n">
-        <v>63.67390060424805</v>
+        <v>63.67389297485352</v>
       </c>
       <c r="C392" t="n">
-        <v>63.75296265734114</v>
+        <v>63.75295501847341</v>
       </c>
       <c r="D392" t="n">
-        <v>60.61670720484071</v>
+        <v>60.6166999417585</v>
       </c>
       <c r="E392" t="n">
-        <v>61.50399711452398</v>
+        <v>61.50398974512687</v>
       </c>
       <c r="F392" t="n">
         <v>633625</v>
@@ -8272,16 +8272,16 @@
         <v>45048</v>
       </c>
       <c r="B393" t="n">
-        <v>58.38531112670898</v>
+        <v>58.38530731201172</v>
       </c>
       <c r="C393" t="n">
-        <v>63.16436980030091</v>
+        <v>63.16436567335623</v>
       </c>
       <c r="D393" t="n">
-        <v>58.38531112670898</v>
+        <v>58.38530731201172</v>
       </c>
       <c r="E393" t="n">
-        <v>63.16436980030091</v>
+        <v>63.16436567335623</v>
       </c>
       <c r="F393" t="n">
         <v>808928</v>
@@ -8292,16 +8292,16 @@
         <v>45049</v>
       </c>
       <c r="B394" t="n">
-        <v>58.85091781616211</v>
+        <v>58.85091018676758</v>
       </c>
       <c r="C394" t="n">
-        <v>60.08082343445384</v>
+        <v>60.08081564561515</v>
       </c>
       <c r="D394" t="n">
-        <v>58.7718557583348</v>
+        <v>58.77184813918982</v>
       </c>
       <c r="E394" t="n">
-        <v>59.12325832105335</v>
+        <v>59.12325065635277</v>
       </c>
       <c r="F394" t="n">
         <v>320277</v>
@@ -8312,16 +8312,16 @@
         <v>45050</v>
       </c>
       <c r="B395" t="n">
-        <v>60.79240417480469</v>
+        <v>60.79240798950195</v>
       </c>
       <c r="C395" t="n">
-        <v>61.56549109490604</v>
+        <v>61.56549495811417</v>
       </c>
       <c r="D395" t="n">
-        <v>58.60493360826845</v>
+        <v>58.60493728570287</v>
       </c>
       <c r="E395" t="n">
-        <v>58.60493360826845</v>
+        <v>58.60493728570287</v>
       </c>
       <c r="F395" t="n">
         <v>661928</v>
@@ -8332,16 +8332,16 @@
         <v>45051</v>
       </c>
       <c r="B396" t="n">
-        <v>64.07801818847656</v>
+        <v>64.07801055908203</v>
       </c>
       <c r="C396" t="n">
-        <v>64.75446262565779</v>
+        <v>64.75445491572299</v>
       </c>
       <c r="D396" t="n">
-        <v>60.79241177231987</v>
+        <v>60.79240453412326</v>
       </c>
       <c r="E396" t="n">
-        <v>60.79241177231987</v>
+        <v>60.79240453412326</v>
       </c>
       <c r="F396" t="n">
         <v>739601</v>
@@ -8352,16 +8352,16 @@
         <v>45054</v>
       </c>
       <c r="B397" t="n">
-        <v>65.16735076904297</v>
+        <v>65.16734313964844</v>
       </c>
       <c r="C397" t="n">
-        <v>65.74715924562913</v>
+        <v>65.74715154835417</v>
       </c>
       <c r="D397" t="n">
-        <v>63.59482964395288</v>
+        <v>63.59482219865949</v>
       </c>
       <c r="E397" t="n">
-        <v>63.76174735351282</v>
+        <v>63.76173988867773</v>
       </c>
       <c r="F397" t="n">
         <v>685640</v>
@@ -8392,16 +8392,16 @@
         <v>45056</v>
       </c>
       <c r="B399" t="n">
-        <v>68.46173858642578</v>
+        <v>68.46174621582031</v>
       </c>
       <c r="C399" t="n">
-        <v>68.48809260385286</v>
+        <v>68.48810023618428</v>
       </c>
       <c r="D399" t="n">
-        <v>66.1864123468299</v>
+        <v>66.18641972266146</v>
       </c>
       <c r="E399" t="n">
-        <v>66.78379465081203</v>
+        <v>66.78380209321604</v>
       </c>
       <c r="F399" t="n">
         <v>406791</v>
@@ -8412,16 +8412,16 @@
         <v>45057</v>
       </c>
       <c r="B400" t="n">
-        <v>67.00342559814453</v>
+        <v>67.00341796875</v>
       </c>
       <c r="C400" t="n">
-        <v>68.69893677611699</v>
+        <v>68.69892895366183</v>
       </c>
       <c r="D400" t="n">
-        <v>67.00342559814453</v>
+        <v>67.00341796875</v>
       </c>
       <c r="E400" t="n">
-        <v>67.3811821829502</v>
+        <v>67.38117451054214</v>
       </c>
       <c r="F400" t="n">
         <v>282491</v>
@@ -8532,16 +8532,16 @@
         <v>45065</v>
       </c>
       <c r="B406" t="n">
-        <v>75.91144561767578</v>
+        <v>75.91145324707031</v>
       </c>
       <c r="C406" t="n">
-        <v>76.42975915801013</v>
+        <v>76.42976683949719</v>
       </c>
       <c r="D406" t="n">
-        <v>71.19388220849052</v>
+        <v>71.19388936375165</v>
       </c>
       <c r="E406" t="n">
-        <v>71.19388220849052</v>
+        <v>71.19388936375165</v>
       </c>
       <c r="F406" t="n">
         <v>1201246</v>
@@ -8552,16 +8552,16 @@
         <v>45068</v>
       </c>
       <c r="B407" t="n">
-        <v>77.76507568359375</v>
+        <v>77.76508331298828</v>
       </c>
       <c r="C407" t="n">
-        <v>78.3097499079546</v>
+        <v>78.30975759078616</v>
       </c>
       <c r="D407" t="n">
-        <v>75.0768588878434</v>
+        <v>75.07686625350173</v>
       </c>
       <c r="E407" t="n">
-        <v>75.45461541229061</v>
+        <v>75.45462281500996</v>
       </c>
       <c r="F407" t="n">
         <v>873661</v>
@@ -8572,16 +8572,16 @@
         <v>45069</v>
       </c>
       <c r="B408" t="n">
-        <v>77.132568359375</v>
+        <v>77.13256072998047</v>
       </c>
       <c r="C408" t="n">
-        <v>80.43573491118516</v>
+        <v>80.43572695506535</v>
       </c>
       <c r="D408" t="n">
-        <v>76.42976325763665</v>
+        <v>76.42975569775851</v>
       </c>
       <c r="E408" t="n">
-        <v>77.74751779656141</v>
+        <v>77.74751010634054</v>
       </c>
       <c r="F408" t="n">
         <v>970823</v>
@@ -8612,16 +8612,16 @@
         <v>45071</v>
       </c>
       <c r="B410" t="n">
-        <v>81.90283966064453</v>
+        <v>81.90283203125</v>
       </c>
       <c r="C410" t="n">
-        <v>81.90283966064453</v>
+        <v>81.90283203125</v>
       </c>
       <c r="D410" t="n">
-        <v>77.75630432590624</v>
+        <v>77.75629708276882</v>
       </c>
       <c r="E410" t="n">
-        <v>77.75630432590624</v>
+        <v>77.75629708276882</v>
       </c>
       <c r="F410" t="n">
         <v>1153989</v>
@@ -8632,16 +8632,16 @@
         <v>45072</v>
       </c>
       <c r="B411" t="n">
-        <v>82.75498199462891</v>
+        <v>82.75497436523438</v>
       </c>
       <c r="C411" t="n">
-        <v>84.15180528493505</v>
+        <v>84.15179752676379</v>
       </c>
       <c r="D411" t="n">
-        <v>80.38302651611544</v>
+        <v>80.38301910539758</v>
       </c>
       <c r="E411" t="n">
-        <v>81.70078104916651</v>
+        <v>81.70077351696148</v>
       </c>
       <c r="F411" t="n">
         <v>582166</v>
@@ -8672,16 +8672,16 @@
         <v>45076</v>
       </c>
       <c r="B413" t="n">
-        <v>80.55872344970703</v>
+        <v>80.5587158203125</v>
       </c>
       <c r="C413" t="n">
-        <v>84.13423043735499</v>
+        <v>84.13422246933848</v>
       </c>
       <c r="D413" t="n">
-        <v>79.3990997429684</v>
+        <v>79.39909222339719</v>
       </c>
       <c r="E413" t="n">
-        <v>82.54414213179378</v>
+        <v>82.54413431436818</v>
       </c>
       <c r="F413" t="n">
         <v>664894</v>
@@ -8792,16 +8792,16 @@
         <v>45084</v>
       </c>
       <c r="B419" t="n">
-        <v>86.52375793457031</v>
+        <v>86.52376556396484</v>
       </c>
       <c r="C419" t="n">
-        <v>86.60282668924023</v>
+        <v>86.60283432560681</v>
       </c>
       <c r="D419" t="n">
-        <v>82.88675607845614</v>
+        <v>82.88676338715122</v>
       </c>
       <c r="E419" t="n">
-        <v>84.3362873579094</v>
+        <v>84.33629479441962</v>
       </c>
       <c r="F419" t="n">
         <v>2805750</v>
@@ -8812,16 +8812,16 @@
         <v>45086</v>
       </c>
       <c r="B420" t="n">
-        <v>87.92936706542969</v>
+        <v>87.92935943603516</v>
       </c>
       <c r="C420" t="n">
-        <v>90.98656062878784</v>
+        <v>90.98655273412886</v>
       </c>
       <c r="D420" t="n">
-        <v>86.98058886520148</v>
+        <v>86.98058131812988</v>
       </c>
       <c r="E420" t="n">
-        <v>86.98058886520148</v>
+        <v>86.98058131812988</v>
       </c>
       <c r="F420" t="n">
         <v>1309381</v>
@@ -8832,16 +8832,16 @@
         <v>45089</v>
       </c>
       <c r="B421" t="n">
-        <v>90.35403442382812</v>
+        <v>90.35404205322266</v>
       </c>
       <c r="C421" t="n">
-        <v>91.34674712772208</v>
+        <v>91.34675484094018</v>
       </c>
       <c r="D421" t="n">
-        <v>87.95572492842221</v>
+        <v>87.95573235530614</v>
       </c>
       <c r="E421" t="n">
-        <v>87.95572492842221</v>
+        <v>87.95573235530614</v>
       </c>
       <c r="F421" t="n">
         <v>1071620</v>
@@ -8892,16 +8892,16 @@
         <v>45092</v>
       </c>
       <c r="B424" t="n">
-        <v>91.97927093505859</v>
+        <v>91.97925567626953</v>
       </c>
       <c r="C424" t="n">
-        <v>92.26039165604509</v>
+        <v>92.26037635061984</v>
       </c>
       <c r="D424" t="n">
-        <v>89.18563083793495</v>
+        <v>89.18561604259341</v>
       </c>
       <c r="E424" t="n">
-        <v>89.43161733343898</v>
+        <v>89.4316024972898</v>
       </c>
       <c r="F424" t="n">
         <v>844482</v>
@@ -8912,16 +8912,16 @@
         <v>45093</v>
       </c>
       <c r="B425" t="n">
-        <v>94.66748809814453</v>
+        <v>94.66748046875</v>
       </c>
       <c r="C425" t="n">
-        <v>95.72168904992172</v>
+        <v>95.72168133556757</v>
       </c>
       <c r="D425" t="n">
-        <v>91.39066885725265</v>
+        <v>91.39066149194188</v>
       </c>
       <c r="E425" t="n">
-        <v>91.84749418481664</v>
+        <v>91.84748678268964</v>
       </c>
       <c r="F425" t="n">
         <v>1238876</v>
@@ -8932,16 +8932,16 @@
         <v>45096</v>
       </c>
       <c r="B426" t="n">
-        <v>98.03213500976562</v>
+        <v>98.03215026855469</v>
       </c>
       <c r="C426" t="n">
-        <v>98.33961638551717</v>
+        <v>98.33963169216599</v>
       </c>
       <c r="D426" t="n">
-        <v>94.14915381556483</v>
+        <v>94.14916846996442</v>
       </c>
       <c r="E426" t="n">
-        <v>94.6147592783495</v>
+        <v>94.61477400522099</v>
       </c>
       <c r="F426" t="n">
         <v>576522</v>
@@ -8952,16 +8952,16 @@
         <v>45097</v>
       </c>
       <c r="B427" t="n">
-        <v>99.66616058349609</v>
+        <v>99.66616821289062</v>
       </c>
       <c r="C427" t="n">
-        <v>100.1493399043639</v>
+        <v>100.1493475707456</v>
       </c>
       <c r="D427" t="n">
-        <v>95.20337053073942</v>
+        <v>95.20337781850962</v>
       </c>
       <c r="E427" t="n">
-        <v>97.85644658614729</v>
+        <v>97.8564540770091</v>
       </c>
       <c r="F427" t="n">
         <v>1047570</v>
@@ -8992,16 +8992,16 @@
         <v>45099</v>
       </c>
       <c r="B429" t="n">
-        <v>99.27084350585938</v>
+        <v>99.27083587646484</v>
       </c>
       <c r="C429" t="n">
-        <v>104.8581233756592</v>
+        <v>104.858115316858</v>
       </c>
       <c r="D429" t="n">
-        <v>99.18299454236116</v>
+        <v>99.18298691971819</v>
       </c>
       <c r="E429" t="n">
-        <v>102.9605535923553</v>
+        <v>102.9605456793905</v>
       </c>
       <c r="F429" t="n">
         <v>1144936</v>
@@ -9052,16 +9052,16 @@
         <v>45104</v>
       </c>
       <c r="B432" t="n">
-        <v>94.86952209472656</v>
+        <v>94.86954498291016</v>
       </c>
       <c r="C432" t="n">
-        <v>98.37475333632106</v>
+        <v>98.37477707017537</v>
       </c>
       <c r="D432" t="n">
-        <v>91.40822537961051</v>
+        <v>91.40824743272303</v>
       </c>
       <c r="E432" t="n">
-        <v>96.97793030188271</v>
+        <v>96.97795369874004</v>
       </c>
       <c r="F432" t="n">
         <v>1484061</v>
@@ -9132,16 +9132,16 @@
         <v>45110</v>
       </c>
       <c r="B436" t="n">
-        <v>100.8960723876953</v>
+        <v>100.8960647583008</v>
       </c>
       <c r="C436" t="n">
-        <v>101.4671007018312</v>
+        <v>101.4670930292576</v>
       </c>
       <c r="D436" t="n">
-        <v>98.26056327855684</v>
+        <v>98.26055584844994</v>
       </c>
       <c r="E436" t="n">
-        <v>98.46262192600048</v>
+        <v>98.46261448061463</v>
       </c>
       <c r="F436" t="n">
         <v>512630</v>
@@ -9152,16 +9152,16 @@
         <v>45111</v>
       </c>
       <c r="B437" t="n">
-        <v>100.6764450073242</v>
+        <v>100.6764526367188</v>
       </c>
       <c r="C437" t="n">
-        <v>101.1508374436232</v>
+        <v>101.1508451089678</v>
       </c>
       <c r="D437" t="n">
-        <v>99.42018541743428</v>
+        <v>99.4201929516278</v>
       </c>
       <c r="E437" t="n">
-        <v>101.0278475567063</v>
+        <v>101.0278552127306</v>
       </c>
       <c r="F437" t="n">
         <v>210288</v>
@@ -9172,16 +9172,16 @@
         <v>45112</v>
       </c>
       <c r="B438" t="n">
-        <v>101.2386932373047</v>
+        <v>101.2386856079102</v>
       </c>
       <c r="C438" t="n">
-        <v>101.7042987981171</v>
+        <v>101.7042911336343</v>
       </c>
       <c r="D438" t="n">
-        <v>99.13028450117518</v>
+        <v>99.13027703067131</v>
       </c>
       <c r="E438" t="n">
-        <v>99.53440181682589</v>
+        <v>99.53439431586756</v>
       </c>
       <c r="F438" t="n">
         <v>519657</v>
@@ -9192,16 +9192,16 @@
         <v>45113</v>
       </c>
       <c r="B439" t="n">
-        <v>99.2093505859375</v>
+        <v>99.20934295654297</v>
       </c>
       <c r="C439" t="n">
-        <v>100.1405616824272</v>
+        <v>100.1405539814207</v>
       </c>
       <c r="D439" t="n">
-        <v>97.71589806864876</v>
+        <v>97.71589055410367</v>
       </c>
       <c r="E439" t="n">
-        <v>100.1405616824272</v>
+        <v>100.1405539814207</v>
       </c>
       <c r="F439" t="n">
         <v>463942</v>
@@ -9212,16 +9212,16 @@
         <v>45114</v>
       </c>
       <c r="B440" t="n">
-        <v>101.2386932373047</v>
+        <v>101.2386856079102</v>
       </c>
       <c r="C440" t="n">
-        <v>102.0820553912672</v>
+        <v>102.0820476983165</v>
       </c>
       <c r="D440" t="n">
-        <v>98.16393245199608</v>
+        <v>98.16392505431695</v>
       </c>
       <c r="E440" t="n">
-        <v>98.73496079547128</v>
+        <v>98.73495335475918</v>
       </c>
       <c r="F440" t="n">
         <v>1239341</v>
@@ -9252,16 +9252,16 @@
         <v>45118</v>
       </c>
       <c r="B442" t="n">
-        <v>99.71009063720703</v>
+        <v>99.7100830078125</v>
       </c>
       <c r="C442" t="n">
-        <v>99.71009063720703</v>
+        <v>99.7100830078125</v>
       </c>
       <c r="D442" t="n">
-        <v>94.7465473398877</v>
+        <v>94.74654009028252</v>
       </c>
       <c r="E442" t="n">
-        <v>97.71589177353913</v>
+        <v>97.71588429673227</v>
       </c>
       <c r="F442" t="n">
         <v>867229</v>
@@ -9312,16 +9312,16 @@
         <v>45121</v>
       </c>
       <c r="B445" t="n">
-        <v>96.74075317382812</v>
+        <v>96.74074554443359</v>
       </c>
       <c r="C445" t="n">
-        <v>98.69981111857781</v>
+        <v>98.69980333468348</v>
       </c>
       <c r="D445" t="n">
-        <v>95.02766829526057</v>
+        <v>95.02766080096731</v>
       </c>
       <c r="E445" t="n">
-        <v>98.69981111857781</v>
+        <v>98.69980333468348</v>
       </c>
       <c r="F445" t="n">
         <v>461646</v>
@@ -9332,16 +9332,16 @@
         <v>45124</v>
       </c>
       <c r="B446" t="n">
-        <v>99.48168182373047</v>
+        <v>99.48167419433594</v>
       </c>
       <c r="C446" t="n">
-        <v>99.48168182373047</v>
+        <v>99.48167419433594</v>
       </c>
       <c r="D446" t="n">
-        <v>95.75683083137832</v>
+        <v>95.75682348764802</v>
       </c>
       <c r="E446" t="n">
-        <v>96.44206212640412</v>
+        <v>96.44205473012244</v>
       </c>
       <c r="F446" t="n">
         <v>395417</v>
@@ -9352,16 +9352,16 @@
         <v>45125</v>
       </c>
       <c r="B447" t="n">
-        <v>101.4231719970703</v>
+        <v>101.4231643676758</v>
       </c>
       <c r="C447" t="n">
-        <v>103.663357401557</v>
+        <v>103.6633496036482</v>
       </c>
       <c r="D447" t="n">
-        <v>98.74374178061643</v>
+        <v>98.74373435277772</v>
       </c>
       <c r="E447" t="n">
-        <v>99.27084225742324</v>
+        <v>99.27083478993424</v>
       </c>
       <c r="F447" t="n">
         <v>594813</v>
@@ -9372,16 +9372,16 @@
         <v>45126</v>
       </c>
       <c r="B448" t="n">
-        <v>101.06298828125</v>
+        <v>101.0629806518555</v>
       </c>
       <c r="C448" t="n">
-        <v>101.2650402225924</v>
+        <v>101.2650325779447</v>
       </c>
       <c r="D448" t="n">
-        <v>99.00728772803575</v>
+        <v>99.00728025382909</v>
       </c>
       <c r="E448" t="n">
-        <v>100.8257887123484</v>
+        <v>100.8257811008604</v>
       </c>
       <c r="F448" t="n">
         <v>1189852</v>
@@ -9452,16 +9452,16 @@
         <v>45132</v>
       </c>
       <c r="B452" t="n">
-        <v>112.1584701538086</v>
+        <v>112.1584777832031</v>
       </c>
       <c r="C452" t="n">
-        <v>115.3298663433468</v>
+        <v>115.3298741884703</v>
       </c>
       <c r="D452" t="n">
-        <v>110.5859490671098</v>
+        <v>110.5859565895362</v>
       </c>
       <c r="E452" t="n">
-        <v>112.9491308527013</v>
+        <v>112.9491385358792</v>
       </c>
       <c r="F452" t="n">
         <v>603712</v>
@@ -9472,16 +9472,16 @@
         <v>45133</v>
       </c>
       <c r="B453" t="n">
-        <v>113.8891296386719</v>
+        <v>113.8891372680664</v>
       </c>
       <c r="C453" t="n">
-        <v>113.9857655059323</v>
+        <v>113.9857731418005</v>
       </c>
       <c r="D453" t="n">
-        <v>110.5508155209108</v>
+        <v>110.5508229266728</v>
       </c>
       <c r="E453" t="n">
-        <v>111.0427817639948</v>
+        <v>111.0427892027134</v>
       </c>
       <c r="F453" t="n">
         <v>810223</v>
@@ -9532,16 +9532,16 @@
         <v>45138</v>
       </c>
       <c r="B456" t="n">
-        <v>111.8246459960938</v>
+        <v>111.8246383666992</v>
       </c>
       <c r="C456" t="n">
-        <v>115.0838912728874</v>
+        <v>115.0838834211262</v>
       </c>
       <c r="D456" t="n">
-        <v>110.7792252970001</v>
+        <v>110.7792177389309</v>
       </c>
       <c r="E456" t="n">
-        <v>112.6416540419304</v>
+        <v>112.6416463567943</v>
       </c>
       <c r="F456" t="n">
         <v>524630</v>
@@ -9612,16 +9612,16 @@
         <v>45142</v>
       </c>
       <c r="B460" t="n">
-        <v>113.1336059570312</v>
+        <v>113.1336135864258</v>
       </c>
       <c r="C460" t="n">
-        <v>114.6007042377062</v>
+        <v>114.6007119660374</v>
       </c>
       <c r="D460" t="n">
-        <v>110.9900566686566</v>
+        <v>110.9900641534965</v>
       </c>
       <c r="E460" t="n">
-        <v>114.2053806012186</v>
+        <v>114.2053883028904</v>
       </c>
       <c r="F460" t="n">
         <v>805649</v>
@@ -9632,16 +9632,16 @@
         <v>45145</v>
       </c>
       <c r="B461" t="n">
-        <v>112.9930572509766</v>
+        <v>112.993049621582</v>
       </c>
       <c r="C461" t="n">
-        <v>117.7194079181516</v>
+        <v>117.7193999696295</v>
       </c>
       <c r="D461" t="n">
-        <v>111.6225946468615</v>
+        <v>111.6225871100018</v>
       </c>
       <c r="E461" t="n">
-        <v>113.326892697325</v>
+        <v>113.3268850453896</v>
       </c>
       <c r="F461" t="n">
         <v>579696</v>
@@ -9652,16 +9652,16 @@
         <v>45146</v>
       </c>
       <c r="B462" t="n">
-        <v>113.590446472168</v>
+        <v>113.5904388427734</v>
       </c>
       <c r="C462" t="n">
-        <v>113.590446472168</v>
+        <v>113.5904388427734</v>
       </c>
       <c r="D462" t="n">
-        <v>109.3033473202589</v>
+        <v>109.3033399788109</v>
       </c>
       <c r="E462" t="n">
-        <v>111.8685746047133</v>
+        <v>111.8685670909697</v>
       </c>
       <c r="F462" t="n">
         <v>457201</v>
@@ -9672,16 +9672,16 @@
         <v>45147</v>
       </c>
       <c r="B463" t="n">
-        <v>112.4483947753906</v>
+        <v>112.4483871459961</v>
       </c>
       <c r="C463" t="n">
-        <v>114.126338883354</v>
+        <v>114.1263311401144</v>
       </c>
       <c r="D463" t="n">
-        <v>110.6123265466231</v>
+        <v>110.612319041802</v>
       </c>
       <c r="E463" t="n">
-        <v>113.7397953815307</v>
+        <v>113.7397876645173</v>
       </c>
       <c r="F463" t="n">
         <v>434571</v>
@@ -9732,16 +9732,16 @@
         <v>45152</v>
       </c>
       <c r="B466" t="n">
-        <v>113.0633239746094</v>
+        <v>113.0633392333984</v>
       </c>
       <c r="C466" t="n">
-        <v>113.0633239746094</v>
+        <v>113.0633392333984</v>
       </c>
       <c r="D466" t="n">
-        <v>106.3779161668596</v>
+        <v>106.3779305234</v>
       </c>
       <c r="E466" t="n">
-        <v>108.9431498064393</v>
+        <v>108.9431645091783</v>
       </c>
       <c r="F466" t="n">
         <v>1213584</v>
@@ -9752,16 +9752,16 @@
         <v>45153</v>
       </c>
       <c r="B467" t="n">
-        <v>107.739616394043</v>
+        <v>107.7396087646484</v>
       </c>
       <c r="C467" t="n">
-        <v>113.3268964775016</v>
+        <v>113.3268884524535</v>
       </c>
       <c r="D467" t="n">
-        <v>104.9899041869657</v>
+        <v>104.9898967522873</v>
       </c>
       <c r="E467" t="n">
-        <v>112.7910090664897</v>
+        <v>112.7910010793896</v>
       </c>
       <c r="F467" t="n">
         <v>1563395</v>
@@ -9792,16 +9792,16 @@
         <v>45155</v>
       </c>
       <c r="B469" t="n">
-        <v>103.6633605957031</v>
+        <v>103.6633529663086</v>
       </c>
       <c r="C469" t="n">
-        <v>109.7689541532003</v>
+        <v>109.7689460744476</v>
       </c>
       <c r="D469" t="n">
-        <v>103.0484111375546</v>
+        <v>103.048403553419</v>
       </c>
       <c r="E469" t="n">
-        <v>108.9783067648512</v>
+        <v>108.9782987442884</v>
       </c>
       <c r="F469" t="n">
         <v>1841816</v>
@@ -9852,16 +9852,16 @@
         <v>45160</v>
       </c>
       <c r="B472" t="n">
-        <v>113.9594039916992</v>
+        <v>113.9594116210938</v>
       </c>
       <c r="C472" t="n">
-        <v>114.003331820272</v>
+        <v>114.0033394526074</v>
       </c>
       <c r="D472" t="n">
-        <v>111.1745512427915</v>
+        <v>111.1745586857447</v>
       </c>
       <c r="E472" t="n">
-        <v>111.5347339677951</v>
+        <v>111.534741434862</v>
       </c>
       <c r="F472" t="n">
         <v>933012</v>
@@ -9972,16 +9972,16 @@
         <v>45168</v>
       </c>
       <c r="B478" t="n">
-        <v>112.4483947753906</v>
+        <v>112.4483871459961</v>
       </c>
       <c r="C478" t="n">
-        <v>113.8540050720403</v>
+        <v>113.853997347278</v>
       </c>
       <c r="D478" t="n">
-        <v>110.8231654101419</v>
+        <v>110.8231578910159</v>
       </c>
       <c r="E478" t="n">
-        <v>113.0721378633134</v>
+        <v>113.0721301915992</v>
       </c>
       <c r="F478" t="n">
         <v>547646</v>
@@ -9992,16 +9992,16 @@
         <v>45169</v>
       </c>
       <c r="B479" t="n">
-        <v>110.4102630615234</v>
+        <v>110.4102554321289</v>
       </c>
       <c r="C479" t="n">
-        <v>112.4396029524886</v>
+        <v>112.4395951828659</v>
       </c>
       <c r="D479" t="n">
-        <v>108.8465287124293</v>
+        <v>108.8465211910895</v>
       </c>
       <c r="E479" t="n">
-        <v>111.7455847420302</v>
+        <v>111.7455770203644</v>
       </c>
       <c r="F479" t="n">
         <v>854216</v>
@@ -10012,16 +10012,16 @@
         <v>45170</v>
       </c>
       <c r="B480" t="n">
-        <v>113.7397918701172</v>
+        <v>113.7397842407227</v>
       </c>
       <c r="C480" t="n">
-        <v>115.5670798373918</v>
+        <v>115.5670720854272</v>
       </c>
       <c r="D480" t="n">
-        <v>109.3209225654903</v>
+        <v>109.320915232503</v>
       </c>
       <c r="E480" t="n">
-        <v>110.260920568448</v>
+        <v>110.2609131724079</v>
       </c>
       <c r="F480" t="n">
         <v>5149038</v>
@@ -10072,16 +10072,16 @@
         <v>45175</v>
       </c>
       <c r="B483" t="n">
-        <v>110.3311920166016</v>
+        <v>110.3311996459961</v>
       </c>
       <c r="C483" t="n">
-        <v>113.1072648009286</v>
+        <v>113.1072726222884</v>
       </c>
       <c r="D483" t="n">
-        <v>108.3106390746352</v>
+        <v>108.3106465643086</v>
       </c>
       <c r="E483" t="n">
-        <v>110.4717557181885</v>
+        <v>110.471763357303</v>
       </c>
       <c r="F483" t="n">
         <v>1014845</v>
@@ -10092,16 +10092,16 @@
         <v>45177</v>
       </c>
       <c r="B484" t="n">
-        <v>108.5126953125</v>
+        <v>108.5126800537109</v>
       </c>
       <c r="C484" t="n">
-        <v>110.7968086365694</v>
+        <v>110.7967930565939</v>
       </c>
       <c r="D484" t="n">
-        <v>106.7293351683192</v>
+        <v>106.7293201603019</v>
       </c>
       <c r="E484" t="n">
-        <v>109.8128827938557</v>
+        <v>109.8128673522375</v>
       </c>
       <c r="F484" t="n">
         <v>972821</v>
@@ -10252,16 +10252,16 @@
         <v>45189</v>
       </c>
       <c r="B492" t="n">
-        <v>110.0200958251953</v>
+        <v>110.0201034545898</v>
       </c>
       <c r="C492" t="n">
-        <v>112.5479469531647</v>
+        <v>112.5479547578543</v>
       </c>
       <c r="D492" t="n">
-        <v>110.0200958251953</v>
+        <v>110.0201034545898</v>
       </c>
       <c r="E492" t="n">
-        <v>111.7113261834204</v>
+        <v>111.711333930094</v>
       </c>
       <c r="F492" t="n">
         <v>472827</v>
@@ -10292,16 +10292,16 @@
         <v>45191</v>
       </c>
       <c r="B494" t="n">
-        <v>103.8129043579102</v>
+        <v>103.8129119873047</v>
       </c>
       <c r="C494" t="n">
-        <v>105.8639727468323</v>
+        <v>105.8639805269635</v>
       </c>
       <c r="D494" t="n">
-        <v>103.2011816047806</v>
+        <v>103.2011891892186</v>
       </c>
       <c r="E494" t="n">
-        <v>105.0903231807173</v>
+        <v>105.0903309039916</v>
       </c>
       <c r="F494" t="n">
         <v>394595</v>
@@ -10312,16 +10312,16 @@
         <v>45194</v>
       </c>
       <c r="B495" t="n">
-        <v>103.5250473022461</v>
+        <v>103.5250396728516</v>
       </c>
       <c r="C495" t="n">
-        <v>104.2986969585722</v>
+        <v>104.2986892721627</v>
       </c>
       <c r="D495" t="n">
-        <v>102.38256163759</v>
+        <v>102.3825540923923</v>
       </c>
       <c r="E495" t="n">
-        <v>103.8938764472339</v>
+        <v>103.893868790658</v>
       </c>
       <c r="F495" t="n">
         <v>399935</v>
@@ -10332,16 +10332,16 @@
         <v>45195</v>
       </c>
       <c r="B496" t="n">
-        <v>101.554931640625</v>
+        <v>101.5549240112305</v>
       </c>
       <c r="C496" t="n">
-        <v>103.8129092891401</v>
+        <v>103.8129014901132</v>
       </c>
       <c r="D496" t="n">
-        <v>100.8622488797702</v>
+        <v>100.862241302414</v>
       </c>
       <c r="E496" t="n">
-        <v>101.6538873012245</v>
+        <v>101.6538796643958</v>
       </c>
       <c r="F496" t="n">
         <v>1664293</v>
@@ -10352,16 +10352,16 @@
         <v>45196</v>
       </c>
       <c r="B497" t="n">
-        <v>100.0346221923828</v>
+        <v>100.0346145629883</v>
       </c>
       <c r="C497" t="n">
-        <v>103.4440765098144</v>
+        <v>103.4440686203892</v>
       </c>
       <c r="D497" t="n">
-        <v>98.69423210730918</v>
+        <v>98.6942245801429</v>
       </c>
       <c r="E497" t="n">
-        <v>101.6628882905459</v>
+        <v>101.6628805369675</v>
       </c>
       <c r="F497" t="n">
         <v>938220</v>
@@ -10392,16 +10392,16 @@
         <v>45198</v>
       </c>
       <c r="B499" t="n">
-        <v>104.2177200317383</v>
+        <v>104.2177124023438</v>
       </c>
       <c r="C499" t="n">
-        <v>107.0514358836805</v>
+        <v>107.0514280468401</v>
       </c>
       <c r="D499" t="n">
-        <v>103.408085950706</v>
+        <v>103.4080783805818</v>
       </c>
       <c r="E499" t="n">
-        <v>107.0514358836805</v>
+        <v>107.0514280468401</v>
       </c>
       <c r="F499" t="n">
         <v>323662</v>
@@ -10452,16 +10452,16 @@
         <v>45203</v>
       </c>
       <c r="B502" t="n">
-        <v>101.7978134155273</v>
+        <v>101.7978210449219</v>
       </c>
       <c r="C502" t="n">
-        <v>102.1666424919565</v>
+        <v>102.1666501489935</v>
       </c>
       <c r="D502" t="n">
-        <v>98.96409781626373</v>
+        <v>98.96410523328106</v>
       </c>
       <c r="E502" t="n">
-        <v>99.85469179431541</v>
+        <v>99.85469927807969</v>
       </c>
       <c r="F502" t="n">
         <v>483635</v>
@@ -10512,16 +10512,16 @@
         <v>45208</v>
       </c>
       <c r="B505" t="n">
-        <v>100.9612045288086</v>
+        <v>100.9611968994141</v>
       </c>
       <c r="C505" t="n">
-        <v>101.6718761081721</v>
+        <v>101.6718684250738</v>
       </c>
       <c r="D505" t="n">
-        <v>99.18900734252807</v>
+        <v>99.18899984705422</v>
       </c>
       <c r="E505" t="n">
-        <v>101.1051356675376</v>
+        <v>101.1051280272665</v>
       </c>
       <c r="F505" t="n">
         <v>728058</v>
@@ -10532,16 +10532,16 @@
         <v>45209</v>
       </c>
       <c r="B506" t="n">
-        <v>101.8338012695312</v>
+        <v>101.8337936401367</v>
       </c>
       <c r="C506" t="n">
-        <v>103.0932313137615</v>
+        <v>103.0932235900104</v>
       </c>
       <c r="D506" t="n">
-        <v>100.4574267480303</v>
+        <v>100.4574192217539</v>
       </c>
       <c r="E506" t="n">
-        <v>100.4574267480303</v>
+        <v>100.4574192217539</v>
       </c>
       <c r="F506" t="n">
         <v>501957</v>
@@ -10572,16 +10572,16 @@
         <v>45212</v>
       </c>
       <c r="B508" t="n">
-        <v>97.1649169921875</v>
+        <v>97.16492462158203</v>
       </c>
       <c r="C508" t="n">
-        <v>98.87414286845593</v>
+        <v>98.87415063205897</v>
       </c>
       <c r="D508" t="n">
-        <v>95.72557141445554</v>
+        <v>95.72557893083258</v>
       </c>
       <c r="E508" t="n">
-        <v>97.9475575039293</v>
+        <v>97.9475651947768</v>
       </c>
       <c r="F508" t="n">
         <v>544401</v>
@@ -10612,16 +10612,16 @@
         <v>45216</v>
       </c>
       <c r="B510" t="n">
-        <v>97.14692687988281</v>
+        <v>97.14693450927734</v>
       </c>
       <c r="C510" t="n">
-        <v>97.86660314166811</v>
+        <v>97.86661082758212</v>
       </c>
       <c r="D510" t="n">
-        <v>95.20381195440891</v>
+        <v>95.20381943120169</v>
       </c>
       <c r="E510" t="n">
-        <v>96.69713093210238</v>
+        <v>96.69713852617237</v>
       </c>
       <c r="F510" t="n">
         <v>593712</v>
@@ -10652,16 +10652,16 @@
         <v>45218</v>
       </c>
       <c r="B512" t="n">
-        <v>94.34920501708984</v>
+        <v>94.34919738769531</v>
       </c>
       <c r="C512" t="n">
-        <v>95.9954599986059</v>
+        <v>95.99545223608963</v>
       </c>
       <c r="D512" t="n">
-        <v>92.76592806339976</v>
+        <v>92.76592056203434</v>
       </c>
       <c r="E512" t="n">
-        <v>93.46760871431685</v>
+        <v>93.46760115621116</v>
       </c>
       <c r="F512" t="n">
         <v>760940</v>
@@ -10672,16 +10672,16 @@
         <v>45219</v>
       </c>
       <c r="B513" t="n">
-        <v>96.25632476806641</v>
+        <v>96.25633239746094</v>
       </c>
       <c r="C513" t="n">
-        <v>96.4362403867825</v>
+        <v>96.43624803043737</v>
       </c>
       <c r="D513" t="n">
-        <v>93.06277106079887</v>
+        <v>93.0627784370684</v>
       </c>
       <c r="E513" t="n">
-        <v>93.27867803926728</v>
+        <v>93.27868543264987</v>
       </c>
       <c r="F513" t="n">
         <v>605848</v>
@@ -10692,16 +10692,16 @@
         <v>45222</v>
       </c>
       <c r="B514" t="n">
-        <v>96.25632476806641</v>
+        <v>96.25633239746094</v>
       </c>
       <c r="C514" t="n">
-        <v>97.29085673403624</v>
+        <v>97.29086444542904</v>
       </c>
       <c r="D514" t="n">
-        <v>93.93537622458784</v>
+        <v>93.93538367002114</v>
       </c>
       <c r="E514" t="n">
-        <v>96.07640914935031</v>
+        <v>96.07641676448451</v>
       </c>
       <c r="F514" t="n">
         <v>469364</v>
@@ -10732,16 +10732,16 @@
         <v>45224</v>
       </c>
       <c r="B516" t="n">
-        <v>89.44643402099609</v>
+        <v>89.44642639160156</v>
       </c>
       <c r="C516" t="n">
-        <v>92.42408138422357</v>
+        <v>92.42407350084858</v>
       </c>
       <c r="D516" t="n">
-        <v>87.28741181968928</v>
+        <v>87.28740437445002</v>
       </c>
       <c r="E516" t="n">
-        <v>92.42408138422357</v>
+        <v>92.42407350084858</v>
       </c>
       <c r="F516" t="n">
         <v>1619426</v>
@@ -10812,16 +10812,16 @@
         <v>45230</v>
       </c>
       <c r="B520" t="n">
-        <v>91.32656097412109</v>
+        <v>91.32656860351562</v>
       </c>
       <c r="C520" t="n">
-        <v>91.32656097412109</v>
+        <v>91.32656860351562</v>
       </c>
       <c r="D520" t="n">
-        <v>88.72674109428142</v>
+        <v>88.72674850648775</v>
       </c>
       <c r="E520" t="n">
-        <v>89.94119557423609</v>
+        <v>89.94120308789761</v>
       </c>
       <c r="F520" t="n">
         <v>382337</v>
@@ -10852,16 +10852,16 @@
         <v>45233</v>
       </c>
       <c r="B522" t="n">
-        <v>94.61007690429688</v>
+        <v>94.61008453369141</v>
       </c>
       <c r="C522" t="n">
-        <v>97.14692574562541</v>
+        <v>97.14693357959244</v>
       </c>
       <c r="D522" t="n">
-        <v>92.08222590355452</v>
+        <v>92.08223332910212</v>
       </c>
       <c r="E522" t="n">
-        <v>92.70294650051345</v>
+        <v>92.70295397611622</v>
       </c>
       <c r="F522" t="n">
         <v>760712</v>
@@ -10872,16 +10872,16 @@
         <v>45236</v>
       </c>
       <c r="B523" t="n">
-        <v>92.21717071533203</v>
+        <v>92.2171630859375</v>
       </c>
       <c r="C523" t="n">
-        <v>95.98645623697459</v>
+        <v>95.9864482957361</v>
       </c>
       <c r="D523" t="n">
-        <v>91.38954092314988</v>
+        <v>91.38953336222757</v>
       </c>
       <c r="E523" t="n">
-        <v>95.13184664835444</v>
+        <v>95.13183877782029</v>
       </c>
       <c r="F523" t="n">
         <v>393989</v>
@@ -10892,16 +10892,16 @@
         <v>45237</v>
       </c>
       <c r="B524" t="n">
-        <v>97.12893676757812</v>
+        <v>97.12894439697266</v>
       </c>
       <c r="C524" t="n">
-        <v>97.12893676757812</v>
+        <v>97.12894439697266</v>
       </c>
       <c r="D524" t="n">
-        <v>91.57845649313083</v>
+        <v>91.57846368653991</v>
       </c>
       <c r="E524" t="n">
-        <v>92.02825243491765</v>
+        <v>92.02825966365781</v>
       </c>
       <c r="F524" t="n">
         <v>722184</v>
@@ -10932,16 +10932,16 @@
         <v>45239</v>
       </c>
       <c r="B526" t="n">
-        <v>95.28477478027344</v>
+        <v>95.28478240966797</v>
       </c>
       <c r="C526" t="n">
-        <v>97.73166590751246</v>
+        <v>97.73167373282809</v>
       </c>
       <c r="D526" t="n">
-        <v>94.73602315850255</v>
+        <v>94.73603074395886</v>
       </c>
       <c r="E526" t="n">
-        <v>97.21889878624117</v>
+        <v>97.21890657049985</v>
       </c>
       <c r="F526" t="n">
         <v>493995</v>
@@ -10972,16 +10972,16 @@
         <v>45243</v>
       </c>
       <c r="B528" t="n">
-        <v>98.83815765380859</v>
+        <v>98.83816528320312</v>
       </c>
       <c r="C528" t="n">
-        <v>100.3134877181948</v>
+        <v>100.3134954614712</v>
       </c>
       <c r="D528" t="n">
-        <v>96.80507817938725</v>
+        <v>96.80508565184681</v>
       </c>
       <c r="E528" t="n">
-        <v>98.95510212187712</v>
+        <v>98.9551097602987</v>
       </c>
       <c r="F528" t="n">
         <v>702632</v>
@@ -10992,16 +10992,16 @@
         <v>45244</v>
       </c>
       <c r="B529" t="n">
-        <v>97.60572814941406</v>
+        <v>97.60572052001953</v>
       </c>
       <c r="C529" t="n">
-        <v>106.6286344553219</v>
+        <v>106.628626120648</v>
       </c>
       <c r="D529" t="n">
-        <v>97.06597434337603</v>
+        <v>97.06596675617159</v>
       </c>
       <c r="E529" t="n">
-        <v>99.73776357610761</v>
+        <v>99.7377557800616</v>
       </c>
       <c r="F529" t="n">
         <v>2031591</v>
@@ -11052,16 +11052,16 @@
         <v>45250</v>
       </c>
       <c r="B532" t="n">
-        <v>102.5534820556641</v>
+        <v>102.5534744262695</v>
       </c>
       <c r="C532" t="n">
-        <v>104.5685660971273</v>
+        <v>104.5685583178221</v>
       </c>
       <c r="D532" t="n">
-        <v>100.9881939881291</v>
+        <v>100.9881864751831</v>
       </c>
       <c r="E532" t="n">
-        <v>103.6329896477554</v>
+        <v>103.6329819380516</v>
       </c>
       <c r="F532" t="n">
         <v>946377</v>
@@ -11072,16 +11072,16 @@
         <v>45251</v>
       </c>
       <c r="B533" t="n">
-        <v>100.259521484375</v>
+        <v>100.2595138549805</v>
       </c>
       <c r="C533" t="n">
-        <v>103.0932375391752</v>
+        <v>103.0932296941449</v>
       </c>
       <c r="D533" t="n">
-        <v>99.13503153114809</v>
+        <v>99.13502398732325</v>
       </c>
       <c r="E533" t="n">
-        <v>102.5804703950374</v>
+        <v>102.5804625890269</v>
       </c>
       <c r="F533" t="n">
         <v>1091156</v>
@@ -11132,16 +11132,16 @@
         <v>45254</v>
       </c>
       <c r="B536" t="n">
-        <v>103.5430221557617</v>
+        <v>103.5430297851562</v>
       </c>
       <c r="C536" t="n">
-        <v>104.3526562058894</v>
+        <v>104.3526638949405</v>
       </c>
       <c r="D536" t="n">
-        <v>100.9522000586942</v>
+        <v>100.9522074971883</v>
       </c>
       <c r="E536" t="n">
-        <v>103.2731487146133</v>
+        <v>103.2731563241227</v>
       </c>
       <c r="F536" t="n">
         <v>447021</v>
@@ -11192,16 +11192,16 @@
         <v>45259</v>
       </c>
       <c r="B539" t="n">
-        <v>101.671875</v>
+        <v>101.6718673706055</v>
       </c>
       <c r="C539" t="n">
-        <v>104.7844690591067</v>
+        <v>104.784461196145</v>
       </c>
       <c r="D539" t="n">
-        <v>101.671875</v>
+        <v>101.6718673706055</v>
       </c>
       <c r="E539" t="n">
-        <v>103.6329856451169</v>
+        <v>103.6329778685619</v>
       </c>
       <c r="F539" t="n">
         <v>3224073</v>
@@ -11252,16 +11252,16 @@
         <v>45264</v>
       </c>
       <c r="B542" t="n">
-        <v>101.1591033935547</v>
+        <v>101.1591110229492</v>
       </c>
       <c r="C542" t="n">
-        <v>105.2972315008476</v>
+        <v>105.2972394423387</v>
       </c>
       <c r="D542" t="n">
-        <v>100.3674650159607</v>
+        <v>100.3674725856501</v>
       </c>
       <c r="E542" t="n">
-        <v>105.2522491618521</v>
+        <v>105.2522570999507</v>
       </c>
       <c r="F542" t="n">
         <v>887105</v>
@@ -11292,16 +11292,16 @@
         <v>45266</v>
       </c>
       <c r="B544" t="n">
-        <v>104.0737838745117</v>
+        <v>104.0737915039062</v>
       </c>
       <c r="C544" t="n">
-        <v>106.4217191645265</v>
+        <v>106.4217269660424</v>
       </c>
       <c r="D544" t="n">
-        <v>102.9043117179754</v>
+        <v>102.9043192616387</v>
       </c>
       <c r="E544" t="n">
-        <v>106.1608367030425</v>
+        <v>106.1608444854338</v>
       </c>
       <c r="F544" t="n">
         <v>811001</v>
@@ -11452,16 +11452,16 @@
         <v>45278</v>
       </c>
       <c r="B552" t="n">
-        <v>118.341552734375</v>
+        <v>118.3415603637695</v>
       </c>
       <c r="C552" t="n">
-        <v>120.6714417856362</v>
+        <v>120.671449565237</v>
       </c>
       <c r="D552" t="n">
-        <v>114.5543313282876</v>
+        <v>114.5543387135227</v>
       </c>
       <c r="E552" t="n">
-        <v>114.8049535144115</v>
+        <v>114.804960915804</v>
       </c>
       <c r="F552" t="n">
         <v>1013443</v>
@@ -11632,16 +11632,16 @@
         <v>45294</v>
       </c>
       <c r="B561" t="n">
-        <v>113.2455062866211</v>
+        <v>113.2455139160156</v>
       </c>
       <c r="C561" t="n">
-        <v>116.2437305936984</v>
+        <v>116.2437384250845</v>
       </c>
       <c r="D561" t="n">
-        <v>113.2455062866211</v>
+        <v>113.2455139160156</v>
       </c>
       <c r="E561" t="n">
-        <v>115.7517564618344</v>
+        <v>115.7517642600759</v>
       </c>
       <c r="F561" t="n">
         <v>798887</v>
@@ -11752,16 +11752,16 @@
         <v>45302</v>
       </c>
       <c r="B567" t="n">
-        <v>114.4150924682617</v>
+        <v>114.4151000976562</v>
       </c>
       <c r="C567" t="n">
-        <v>114.7306912980884</v>
+        <v>114.7306989485276</v>
       </c>
       <c r="D567" t="n">
-        <v>112.1965950122623</v>
+        <v>112.1966024937236</v>
       </c>
       <c r="E567" t="n">
-        <v>113.9788176654469</v>
+        <v>113.9788252657498</v>
       </c>
       <c r="F567" t="n">
         <v>442933</v>
@@ -11772,16 +11772,16 @@
         <v>45303</v>
       </c>
       <c r="B568" t="n">
-        <v>116.6800003051758</v>
+        <v>116.6800079345703</v>
       </c>
       <c r="C568" t="n">
-        <v>117.7010720284054</v>
+        <v>117.7010797245651</v>
       </c>
       <c r="D568" t="n">
-        <v>112.8649256503406</v>
+        <v>112.8649330302776</v>
       </c>
       <c r="E568" t="n">
-        <v>114.6378710225635</v>
+        <v>114.6378785184286</v>
       </c>
       <c r="F568" t="n">
         <v>693991</v>
@@ -11792,16 +11792,16 @@
         <v>45306</v>
       </c>
       <c r="B569" t="n">
-        <v>118.2580261230469</v>
+        <v>118.2580184936523</v>
       </c>
       <c r="C569" t="n">
-        <v>120.5786239215518</v>
+        <v>120.5786161424443</v>
       </c>
       <c r="D569" t="n">
-        <v>115.6589458241968</v>
+        <v>115.6589383624814</v>
       </c>
       <c r="E569" t="n">
-        <v>116.6707332346643</v>
+        <v>116.6707257076737</v>
       </c>
       <c r="F569" t="n">
         <v>875695</v>
@@ -11832,16 +11832,16 @@
         <v>45308</v>
       </c>
       <c r="B571" t="n">
-        <v>115.8167343139648</v>
+        <v>115.8167419433594</v>
       </c>
       <c r="C571" t="n">
-        <v>117.2926425610734</v>
+        <v>117.292650287693</v>
       </c>
       <c r="D571" t="n">
-        <v>114.0530804370092</v>
+        <v>114.0530879502235</v>
       </c>
       <c r="E571" t="n">
-        <v>116.568615039894</v>
+        <v>116.5686227188185</v>
       </c>
       <c r="F571" t="n">
         <v>474098</v>
@@ -11912,16 +11912,16 @@
         <v>45314</v>
       </c>
       <c r="B575" t="n">
-        <v>115.8445816040039</v>
+        <v>115.8445892333984</v>
       </c>
       <c r="C575" t="n">
-        <v>119.5111339486896</v>
+        <v>119.5111418195592</v>
       </c>
       <c r="D575" t="n">
-        <v>115.3526074921376</v>
+        <v>115.3526150891313</v>
       </c>
       <c r="E575" t="n">
-        <v>117.0605761181597</v>
+        <v>117.0605838276382</v>
       </c>
       <c r="F575" t="n">
         <v>383026</v>
@@ -11952,16 +11952,16 @@
         <v>45316</v>
       </c>
       <c r="B577" t="n">
-        <v>115.4268798828125</v>
+        <v>115.426872253418</v>
       </c>
       <c r="C577" t="n">
-        <v>117.7289229314847</v>
+        <v>117.7289151499315</v>
       </c>
       <c r="D577" t="n">
-        <v>112.8742146349412</v>
+        <v>112.8742071742708</v>
       </c>
       <c r="E577" t="n">
-        <v>116.95848044792</v>
+        <v>116.958472717291</v>
       </c>
       <c r="F577" t="n">
         <v>983228</v>
@@ -12092,16 +12092,16 @@
         <v>45327</v>
       </c>
       <c r="B584" t="n">
-        <v>117.5711135864258</v>
+        <v>117.5711212158203</v>
       </c>
       <c r="C584" t="n">
-        <v>121.3026355450343</v>
+        <v>121.3026434165738</v>
       </c>
       <c r="D584" t="n">
-        <v>116.2065969632262</v>
+        <v>116.2066045040748</v>
       </c>
       <c r="E584" t="n">
-        <v>119.7246272668129</v>
+        <v>119.7246350359527</v>
       </c>
       <c r="F584" t="n">
         <v>563930</v>
@@ -12112,16 +12112,16 @@
         <v>45328</v>
       </c>
       <c r="B585" t="n">
-        <v>115.9374084472656</v>
+        <v>115.9374160766602</v>
       </c>
       <c r="C585" t="n">
-        <v>119.5946765194815</v>
+        <v>119.5946843895468</v>
       </c>
       <c r="D585" t="n">
-        <v>115.1205510870751</v>
+        <v>115.1205586627154</v>
       </c>
       <c r="E585" t="n">
-        <v>117.8867149153073</v>
+        <v>117.8867226729782</v>
       </c>
       <c r="F585" t="n">
         <v>714734</v>
@@ -12132,16 +12132,16 @@
         <v>45329</v>
       </c>
       <c r="B586" t="n">
-        <v>114.9070587158203</v>
+        <v>114.9070663452148</v>
       </c>
       <c r="C586" t="n">
-        <v>116.3179832026201</v>
+        <v>116.3179909256947</v>
       </c>
       <c r="D586" t="n">
-        <v>111.8160116757133</v>
+        <v>111.816019099874</v>
       </c>
       <c r="E586" t="n">
-        <v>115.1019886532248</v>
+        <v>115.101996295562</v>
       </c>
       <c r="F586" t="n">
         <v>998662</v>
@@ -12172,16 +12172,16 @@
         <v>45331</v>
       </c>
       <c r="B588" t="n">
-        <v>114.2201614379883</v>
+        <v>114.2201690673828</v>
       </c>
       <c r="C588" t="n">
-        <v>115.8445846607362</v>
+        <v>115.8445923986349</v>
       </c>
       <c r="D588" t="n">
-        <v>113.561103498381</v>
+        <v>113.5611110837534</v>
       </c>
       <c r="E588" t="n">
-        <v>114.9070584178118</v>
+        <v>114.9070660930879</v>
       </c>
       <c r="F588" t="n">
         <v>354486</v>
@@ -12212,16 +12212,16 @@
         <v>45337</v>
       </c>
       <c r="B590" t="n">
-        <v>115.7517623901367</v>
+        <v>115.7517547607422</v>
       </c>
       <c r="C590" t="n">
-        <v>116.4015359709352</v>
+        <v>116.4015282987129</v>
       </c>
       <c r="D590" t="n">
-        <v>114.4986372383505</v>
+        <v>114.4986296915515</v>
       </c>
       <c r="E590" t="n">
-        <v>115.6589396162866</v>
+        <v>115.6589319930101</v>
       </c>
       <c r="F590" t="n">
         <v>464925</v>
@@ -12352,16 +12352,16 @@
         <v>45348</v>
       </c>
       <c r="B597" t="n">
-        <v>111.2776260375977</v>
+        <v>111.2776336669922</v>
       </c>
       <c r="C597" t="n">
-        <v>113.0227251791686</v>
+        <v>113.0227329282103</v>
       </c>
       <c r="D597" t="n">
-        <v>110.5164680339092</v>
+        <v>110.5164756111173</v>
       </c>
       <c r="E597" t="n">
-        <v>111.6674929814756</v>
+        <v>111.6675006376001</v>
       </c>
       <c r="F597" t="n">
         <v>306480</v>
@@ -12392,16 +12392,16 @@
         <v>45350</v>
       </c>
       <c r="B599" t="n">
-        <v>110.507194519043</v>
+        <v>110.5072021484375</v>
       </c>
       <c r="C599" t="n">
-        <v>112.8556452546146</v>
+        <v>112.8556530461457</v>
       </c>
       <c r="D599" t="n">
-        <v>103.0348448313849</v>
+        <v>103.03485194489</v>
       </c>
       <c r="E599" t="n">
-        <v>112.8556452546146</v>
+        <v>112.8556530461457</v>
       </c>
       <c r="F599" t="n">
         <v>1284448</v>
@@ -12552,16 +12552,16 @@
         <v>45362</v>
       </c>
       <c r="B607" t="n">
-        <v>116.9120559692383</v>
+        <v>116.9120635986328</v>
       </c>
       <c r="C607" t="n">
-        <v>117.9052744467247</v>
+        <v>117.9052821409343</v>
       </c>
       <c r="D607" t="n">
-        <v>116.1044901074035</v>
+        <v>116.1044976840983</v>
       </c>
       <c r="E607" t="n">
-        <v>116.1230518280071</v>
+        <v>116.1230594059132</v>
       </c>
       <c r="F607" t="n">
         <v>387232</v>
@@ -12612,16 +12612,16 @@
         <v>45365</v>
       </c>
       <c r="B610" t="n">
-        <v>117.5711135864258</v>
+        <v>117.5711212158203</v>
       </c>
       <c r="C610" t="n">
-        <v>120.7642677478222</v>
+        <v>120.7642755844261</v>
       </c>
       <c r="D610" t="n">
-        <v>115.937405982697</v>
+        <v>115.9374135060774</v>
       </c>
       <c r="E610" t="n">
-        <v>120.662160579969</v>
+        <v>120.662168409947</v>
       </c>
       <c r="F610" t="n">
         <v>644367</v>
@@ -12672,16 +12672,16 @@
         <v>45370</v>
       </c>
       <c r="B613" t="n">
-        <v>116.4108200073242</v>
+        <v>116.4108123779297</v>
       </c>
       <c r="C613" t="n">
-        <v>118.248735002326</v>
+        <v>118.2487272524772</v>
       </c>
       <c r="D613" t="n">
-        <v>115.566116479516</v>
+        <v>115.5661089054821</v>
       </c>
       <c r="E613" t="n">
-        <v>117.2369547312665</v>
+        <v>117.2369470477283</v>
       </c>
       <c r="F613" t="n">
         <v>379495</v>
@@ -12692,16 +12692,16 @@
         <v>45371</v>
       </c>
       <c r="B614" t="n">
-        <v>118.1744766235352</v>
+        <v>118.1744689941406</v>
       </c>
       <c r="C614" t="n">
-        <v>119.5854083084638</v>
+        <v>119.5854005879789</v>
       </c>
       <c r="D614" t="n">
-        <v>115.1019981331325</v>
+        <v>115.1019907020985</v>
       </c>
       <c r="E614" t="n">
-        <v>115.9374172779029</v>
+        <v>115.9374097929339</v>
       </c>
       <c r="F614" t="n">
         <v>596704</v>
@@ -12872,16 +12872,16 @@
         <v>45385</v>
       </c>
       <c r="B623" t="n">
-        <v>117.4597320556641</v>
+        <v>117.4597244262695</v>
       </c>
       <c r="C623" t="n">
-        <v>118.1002212393131</v>
+        <v>118.1002135683167</v>
       </c>
       <c r="D623" t="n">
-        <v>116.0395230675065</v>
+        <v>116.0395155303591</v>
       </c>
       <c r="E623" t="n">
-        <v>117.7196386571669</v>
+        <v>117.7196310108906</v>
       </c>
       <c r="F623" t="n">
         <v>818287</v>
@@ -12992,16 +12992,16 @@
         <v>45393</v>
       </c>
       <c r="B629" t="n">
-        <v>113.9509811401367</v>
+        <v>113.9509735107422</v>
       </c>
       <c r="C629" t="n">
-        <v>114.4522326314215</v>
+        <v>114.4522249684666</v>
       </c>
       <c r="D629" t="n">
-        <v>112.3915344167808</v>
+        <v>112.3915268917964</v>
       </c>
       <c r="E629" t="n">
-        <v>114.025235112164</v>
+        <v>114.025227477798</v>
       </c>
       <c r="F629" t="n">
         <v>445667</v>
@@ -13132,16 +13132,16 @@
         <v>45404</v>
       </c>
       <c r="B636" t="n">
-        <v>100.9462966918945</v>
+        <v>100.9463043212891</v>
       </c>
       <c r="C636" t="n">
-        <v>102.5243049338492</v>
+        <v>102.5243126825076</v>
       </c>
       <c r="D636" t="n">
-        <v>100.4357608643617</v>
+        <v>100.4357684551706</v>
       </c>
       <c r="E636" t="n">
-        <v>101.1783571440598</v>
+        <v>101.1783647909932</v>
       </c>
       <c r="F636" t="n">
         <v>363945</v>
@@ -13232,16 +13232,16 @@
         <v>45412</v>
       </c>
       <c r="B641" t="n">
-        <v>98.4678955078125</v>
+        <v>98.46790313720703</v>
       </c>
       <c r="C641" t="n">
-        <v>100.4821785891058</v>
+        <v>100.482186374569</v>
       </c>
       <c r="D641" t="n">
-        <v>96.76921125094019</v>
+        <v>96.7692187487189</v>
       </c>
       <c r="E641" t="n">
-        <v>99.31259189464512</v>
+        <v>99.3125995894876</v>
       </c>
       <c r="F641" t="n">
         <v>1108924</v>
@@ -13252,16 +13252,16 @@
         <v>45414</v>
       </c>
       <c r="B642" t="n">
-        <v>99.81385040283203</v>
+        <v>99.8138427734375</v>
       </c>
       <c r="C642" t="n">
-        <v>101.3454509546608</v>
+        <v>101.3454432081965</v>
       </c>
       <c r="D642" t="n">
-        <v>98.76493960502044</v>
+        <v>98.7649320558007</v>
       </c>
       <c r="E642" t="n">
-        <v>100.7142461792009</v>
+        <v>100.7142384809835</v>
       </c>
       <c r="F642" t="n">
         <v>433847</v>
@@ -13272,16 +13272,16 @@
         <v>45415</v>
       </c>
       <c r="B643" t="n">
-        <v>105.9123992919922</v>
+        <v>105.9123916625977</v>
       </c>
       <c r="C643" t="n">
-        <v>106.3765202416345</v>
+        <v>106.3765125788071</v>
       </c>
       <c r="D643" t="n">
-        <v>100.073756895661</v>
+        <v>100.0737496868528</v>
       </c>
       <c r="E643" t="n">
-        <v>100.073756895661</v>
+        <v>100.0737496868528</v>
       </c>
       <c r="F643" t="n">
         <v>813358</v>
@@ -13452,16 +13452,16 @@
         <v>45428</v>
       </c>
       <c r="B652" t="n">
-        <v>104.6407012939453</v>
+        <v>104.6407089233398</v>
       </c>
       <c r="C652" t="n">
-        <v>104.9377383868498</v>
+        <v>104.9377460379014</v>
       </c>
       <c r="D652" t="n">
-        <v>103.322592554879</v>
+        <v>103.3226000881697</v>
       </c>
       <c r="E652" t="n">
-        <v>104.1487271908296</v>
+        <v>104.1487347843541</v>
       </c>
       <c r="F652" t="n">
         <v>283646</v>
@@ -13572,16 +13572,16 @@
         <v>45436</v>
       </c>
       <c r="B658" t="n">
-        <v>90.03946685791016</v>
+        <v>90.03945922851562</v>
       </c>
       <c r="C658" t="n">
-        <v>91.06053156053261</v>
+        <v>91.0605238446193</v>
       </c>
       <c r="D658" t="n">
-        <v>88.15513688048645</v>
+        <v>88.15512941075855</v>
       </c>
       <c r="E658" t="n">
-        <v>89.29687048404443</v>
+        <v>89.29686291757299</v>
       </c>
       <c r="F658" t="n">
         <v>574555</v>
@@ -13612,16 +13612,16 @@
         <v>45440</v>
       </c>
       <c r="B660" t="n">
-        <v>90.68922424316406</v>
+        <v>90.68923187255859</v>
       </c>
       <c r="C660" t="n">
-        <v>92.44360074082222</v>
+        <v>92.44360851780684</v>
       </c>
       <c r="D660" t="n">
-        <v>90.07658831603928</v>
+        <v>90.07659589389471</v>
       </c>
       <c r="E660" t="n">
-        <v>90.96769962580825</v>
+        <v>90.96770727863003</v>
       </c>
       <c r="F660" t="n">
         <v>449350</v>
@@ -13652,16 +13652,16 @@
         <v>45443</v>
       </c>
       <c r="B662" t="n">
-        <v>92.63854217529297</v>
+        <v>92.63853454589844</v>
       </c>
       <c r="C662" t="n">
-        <v>93.37184702617216</v>
+        <v>93.37183933638515</v>
       </c>
       <c r="D662" t="n">
-        <v>88.71207591877693</v>
+        <v>88.71206861275279</v>
       </c>
       <c r="E662" t="n">
-        <v>90.0394620864207</v>
+        <v>90.03945467107755</v>
       </c>
       <c r="F662" t="n">
         <v>991405</v>
@@ -13672,16 +13672,16 @@
         <v>45446</v>
       </c>
       <c r="B663" t="n">
-        <v>92.43431854248047</v>
+        <v>92.434326171875</v>
       </c>
       <c r="C663" t="n">
-        <v>93.60389809123609</v>
+        <v>93.60390581716601</v>
       </c>
       <c r="D663" t="n">
-        <v>90.53142005267401</v>
+        <v>90.53142752500605</v>
       </c>
       <c r="E663" t="n">
-        <v>92.64781018690546</v>
+        <v>92.64781783392128</v>
       </c>
       <c r="F663" t="n">
         <v>373105</v>
@@ -13712,16 +13712,16 @@
         <v>45448</v>
       </c>
       <c r="B665" t="n">
-        <v>92.92630004882812</v>
+        <v>92.92629241943359</v>
       </c>
       <c r="C665" t="n">
-        <v>93.79884972802287</v>
+        <v>93.79884202699066</v>
       </c>
       <c r="D665" t="n">
-        <v>92.39720243274542</v>
+        <v>92.39719484679063</v>
       </c>
       <c r="E665" t="n">
-        <v>93.18620665575664</v>
+        <v>93.18619900502337</v>
       </c>
       <c r="F665" t="n">
         <v>402887</v>
@@ -13772,16 +13772,16 @@
         <v>45453</v>
       </c>
       <c r="B668" t="n">
-        <v>92.53643798828125</v>
+        <v>92.53643035888672</v>
       </c>
       <c r="C668" t="n">
-        <v>93.24189673871706</v>
+        <v>93.24188905115926</v>
       </c>
       <c r="D668" t="n">
-        <v>90.78206135035421</v>
+        <v>90.78205386560359</v>
       </c>
       <c r="E668" t="n">
-        <v>92.0351865085987</v>
+        <v>92.0351789205311</v>
       </c>
       <c r="F668" t="n">
         <v>279796</v>
@@ -13812,16 +13812,16 @@
         <v>45455</v>
       </c>
       <c r="B670" t="n">
-        <v>90.15085601806641</v>
+        <v>90.15084838867188</v>
       </c>
       <c r="C670" t="n">
-        <v>93.86382362385611</v>
+        <v>93.8638156802361</v>
       </c>
       <c r="D670" t="n">
-        <v>90.1415716161133</v>
+        <v>90.1415639875045</v>
       </c>
       <c r="E670" t="n">
-        <v>93.15835779581742</v>
+        <v>93.15834991190043</v>
       </c>
       <c r="F670" t="n">
         <v>421382</v>
@@ -13852,16 +13852,16 @@
         <v>45457</v>
       </c>
       <c r="B672" t="n">
-        <v>85.38896942138672</v>
+        <v>85.38897705078125</v>
       </c>
       <c r="C672" t="n">
-        <v>86.81846278086709</v>
+        <v>86.81847053798501</v>
       </c>
       <c r="D672" t="n">
-        <v>84.95269460026903</v>
+        <v>84.95270219068296</v>
       </c>
       <c r="E672" t="n">
-        <v>86.81846278086709</v>
+        <v>86.81847053798501</v>
       </c>
       <c r="F672" t="n">
         <v>481131</v>
@@ -13872,16 +13872,16 @@
         <v>45460</v>
       </c>
       <c r="B673" t="n">
-        <v>85.58390045166016</v>
+        <v>85.58389282226562</v>
       </c>
       <c r="C673" t="n">
-        <v>86.70707938412349</v>
+        <v>86.70707165460294</v>
       </c>
       <c r="D673" t="n">
-        <v>83.36540287450703</v>
+        <v>83.36539544288092</v>
       </c>
       <c r="E673" t="n">
-        <v>85.12906390304379</v>
+        <v>85.12905631419575</v>
       </c>
       <c r="F673" t="n">
         <v>650145</v>
@@ -13892,16 +13892,16 @@
         <v>45461</v>
       </c>
       <c r="B674" t="n">
-        <v>87.54248046875</v>
+        <v>87.54248809814453</v>
       </c>
       <c r="C674" t="n">
-        <v>87.54248046875</v>
+        <v>87.54248809814453</v>
       </c>
       <c r="D674" t="n">
-        <v>84.9712538405923</v>
+        <v>84.97126124590245</v>
       </c>
       <c r="E674" t="n">
-        <v>85.57461241716906</v>
+        <v>85.57461987506238</v>
       </c>
       <c r="F674" t="n">
         <v>348422</v>
@@ -13972,16 +13972,16 @@
         <v>45467</v>
       </c>
       <c r="B678" t="n">
-        <v>89.74241638183594</v>
+        <v>89.74242401123047</v>
       </c>
       <c r="C678" t="n">
-        <v>90.60568152828682</v>
+        <v>90.6056892310713</v>
       </c>
       <c r="D678" t="n">
-        <v>88.23866213520195</v>
+        <v>88.23866963675577</v>
       </c>
       <c r="E678" t="n">
-        <v>88.92556615757213</v>
+        <v>88.92557371752265</v>
       </c>
       <c r="F678" t="n">
         <v>235914</v>
@@ -14052,16 +14052,16 @@
         <v>45471</v>
       </c>
       <c r="B682" t="n">
-        <v>90.78206634521484</v>
+        <v>90.78205871582031</v>
       </c>
       <c r="C682" t="n">
-        <v>92.4436132183085</v>
+        <v>92.44360544927629</v>
       </c>
       <c r="D682" t="n">
-        <v>89.58463336929955</v>
+        <v>89.58462584053821</v>
       </c>
       <c r="E682" t="n">
-        <v>91.15335746295753</v>
+        <v>91.15334980235941</v>
       </c>
       <c r="F682" t="n">
         <v>273815</v>
@@ -14092,16 +14092,16 @@
         <v>45475</v>
       </c>
       <c r="B684" t="n">
-        <v>87.69101715087891</v>
+        <v>87.69100952148438</v>
       </c>
       <c r="C684" t="n">
-        <v>88.647105215382</v>
+        <v>88.6470975028048</v>
       </c>
       <c r="D684" t="n">
-        <v>87.28258843131488</v>
+        <v>87.28258083745493</v>
       </c>
       <c r="E684" t="n">
-        <v>88.03446213603596</v>
+        <v>88.03445447676063</v>
       </c>
       <c r="F684" t="n">
         <v>181372</v>
@@ -14132,16 +14132,16 @@
         <v>45477</v>
       </c>
       <c r="B686" t="n">
-        <v>88.32221984863281</v>
+        <v>88.32221221923828</v>
       </c>
       <c r="C686" t="n">
-        <v>89.04624741102846</v>
+        <v>89.04623971909143</v>
       </c>
       <c r="D686" t="n">
-        <v>86.80918099098282</v>
+        <v>86.80917349228666</v>
       </c>
       <c r="E686" t="n">
-        <v>87.44038577803201</v>
+        <v>87.44037822481152</v>
       </c>
       <c r="F686" t="n">
         <v>119657</v>
@@ -14172,16 +14172,16 @@
         <v>45481</v>
       </c>
       <c r="B688" t="n">
-        <v>87.11549377441406</v>
+        <v>87.11550140380859</v>
       </c>
       <c r="C688" t="n">
-        <v>88.26651165334657</v>
+        <v>88.26651938354486</v>
       </c>
       <c r="D688" t="n">
-        <v>86.17796754914521</v>
+        <v>86.17797509643314</v>
       </c>
       <c r="E688" t="n">
-        <v>86.32648964032262</v>
+        <v>86.32649720061781</v>
       </c>
       <c r="F688" t="n">
         <v>189187</v>
@@ -14212,16 +14212,16 @@
         <v>45483</v>
       </c>
       <c r="B690" t="n">
-        <v>91.15335083007812</v>
+        <v>91.15334320068359</v>
       </c>
       <c r="C690" t="n">
-        <v>92.08159272073848</v>
+        <v>92.08158501365153</v>
       </c>
       <c r="D690" t="n">
-        <v>86.83703170404632</v>
+        <v>86.83702443592102</v>
       </c>
       <c r="E690" t="n">
-        <v>86.83703170404632</v>
+        <v>86.83702443592102</v>
       </c>
       <c r="F690" t="n">
         <v>604684</v>
@@ -14272,16 +14272,16 @@
         <v>45488</v>
       </c>
       <c r="B693" t="n">
-        <v>93.75243377685547</v>
+        <v>93.75242614746094</v>
       </c>
       <c r="C693" t="n">
-        <v>94.8756056485097</v>
+        <v>94.87559792771359</v>
       </c>
       <c r="D693" t="n">
-        <v>92.54571644992839</v>
+        <v>92.54570891873422</v>
       </c>
       <c r="E693" t="n">
-        <v>92.83347626039723</v>
+        <v>92.83346870578572</v>
       </c>
       <c r="F693" t="n">
         <v>284490</v>
@@ -14292,16 +14292,16 @@
         <v>45489</v>
       </c>
       <c r="B694" t="n">
-        <v>93.74314117431641</v>
+        <v>93.74314880371094</v>
       </c>
       <c r="C694" t="n">
-        <v>95.46038715708933</v>
+        <v>95.46039492624392</v>
       </c>
       <c r="D694" t="n">
-        <v>92.9262909069122</v>
+        <v>92.92629846982642</v>
       </c>
       <c r="E694" t="n">
-        <v>92.9262909069122</v>
+        <v>92.92629846982642</v>
       </c>
       <c r="F694" t="n">
         <v>218776</v>
@@ -14412,16 +14412,16 @@
         <v>45497</v>
       </c>
       <c r="B700" t="n">
-        <v>91.80311584472656</v>
+        <v>91.80312347412109</v>
       </c>
       <c r="C700" t="n">
-        <v>94.77348678516967</v>
+        <v>94.77349466141999</v>
       </c>
       <c r="D700" t="n">
-        <v>91.78454704276713</v>
+        <v>91.78455467061849</v>
       </c>
       <c r="E700" t="n">
-        <v>94.36506520706058</v>
+        <v>94.3650730493686</v>
       </c>
       <c r="F700" t="n">
         <v>387734</v>
@@ -14432,16 +14432,16 @@
         <v>45498</v>
       </c>
       <c r="B701" t="n">
-        <v>92.38790893554688</v>
+        <v>92.38791656494141</v>
       </c>
       <c r="C701" t="n">
-        <v>93.65960280217031</v>
+        <v>93.65961053658134</v>
       </c>
       <c r="D701" t="n">
-        <v>91.01411498218737</v>
+        <v>91.01412249813397</v>
       </c>
       <c r="E701" t="n">
-        <v>92.36006281353492</v>
+        <v>92.36007044062993</v>
       </c>
       <c r="F701" t="n">
         <v>169675</v>
@@ -14472,16 +14472,16 @@
         <v>45502</v>
       </c>
       <c r="B703" t="n">
-        <v>91.94235229492188</v>
+        <v>91.94235992431641</v>
       </c>
       <c r="C703" t="n">
-        <v>94.07730416654506</v>
+        <v>94.07731197309832</v>
       </c>
       <c r="D703" t="n">
-        <v>91.71956916594331</v>
+        <v>91.71957677685126</v>
       </c>
       <c r="E703" t="n">
-        <v>93.10265453447454</v>
+        <v>93.10266226015118</v>
       </c>
       <c r="F703" t="n">
         <v>142991</v>
@@ -14512,16 +14512,16 @@
         <v>45504</v>
       </c>
       <c r="B705" t="n">
-        <v>90.49430847167969</v>
+        <v>90.49430084228516</v>
       </c>
       <c r="C705" t="n">
-        <v>91.8031330602639</v>
+        <v>91.80312532052498</v>
       </c>
       <c r="D705" t="n">
-        <v>89.90023417218629</v>
+        <v>89.90022659287696</v>
       </c>
       <c r="E705" t="n">
-        <v>90.59641565583551</v>
+        <v>90.59640801783253</v>
       </c>
       <c r="F705" t="n">
         <v>210335</v>
@@ -14552,16 +14552,16 @@
         <v>45506</v>
       </c>
       <c r="B707" t="n">
-        <v>86.47502136230469</v>
+        <v>86.47501373291016</v>
       </c>
       <c r="C707" t="n">
-        <v>88.66566579576077</v>
+        <v>88.6656579730932</v>
       </c>
       <c r="D707" t="n">
-        <v>85.23117349689625</v>
+        <v>85.23116597724216</v>
       </c>
       <c r="E707" t="n">
-        <v>87.72814654800261</v>
+        <v>87.72813880804915</v>
       </c>
       <c r="F707" t="n">
         <v>556592</v>
@@ -14632,16 +14632,16 @@
         <v>45512</v>
       </c>
       <c r="B711" t="n">
-        <v>90.37362670898438</v>
+        <v>90.37363433837891</v>
       </c>
       <c r="C711" t="n">
-        <v>91.72885895455157</v>
+        <v>91.7288666983556</v>
       </c>
       <c r="D711" t="n">
-        <v>86.83702754131875</v>
+        <v>86.83703487215151</v>
       </c>
       <c r="E711" t="n">
-        <v>86.83702754131875</v>
+        <v>86.83703487215151</v>
       </c>
       <c r="F711" t="n">
         <v>332071</v>
@@ -14652,16 +14652,16 @@
         <v>45513</v>
       </c>
       <c r="B712" t="n">
-        <v>92.08158874511719</v>
+        <v>92.08159637451172</v>
       </c>
       <c r="C712" t="n">
-        <v>93.99377177302711</v>
+        <v>93.99377956085505</v>
       </c>
       <c r="D712" t="n">
-        <v>90.03945950660274</v>
+        <v>90.03946696679722</v>
       </c>
       <c r="E712" t="n">
-        <v>91.29258458850585</v>
+        <v>91.29259215252766</v>
       </c>
       <c r="F712" t="n">
         <v>660502</v>
@@ -14672,16 +14672,16 @@
         <v>45516</v>
       </c>
       <c r="B713" t="n">
-        <v>92.40647888183594</v>
+        <v>92.40648651123047</v>
       </c>
       <c r="C713" t="n">
-        <v>93.94735666826095</v>
+        <v>93.94736442487562</v>
       </c>
       <c r="D713" t="n">
-        <v>91.91450475315092</v>
+        <v>91.91451234192638</v>
       </c>
       <c r="E713" t="n">
-        <v>93.43682790056926</v>
+        <v>93.43683561503292</v>
       </c>
       <c r="F713" t="n">
         <v>620479</v>
@@ -14812,16 +14812,16 @@
         <v>45525</v>
       </c>
       <c r="B720" t="n">
-        <v>98.78350067138672</v>
+        <v>98.78349304199219</v>
       </c>
       <c r="C720" t="n">
-        <v>100.407923986077</v>
+        <v>100.4079162312225</v>
       </c>
       <c r="D720" t="n">
-        <v>98.45861742483341</v>
+        <v>98.45860982053073</v>
       </c>
       <c r="E720" t="n">
-        <v>99.32188266963144</v>
+        <v>99.32187499865579</v>
       </c>
       <c r="F720" t="n">
         <v>477691</v>
@@ -14892,16 +14892,16 @@
         <v>45531</v>
       </c>
       <c r="B724" t="n">
-        <v>99.32187652587891</v>
+        <v>99.32188415527344</v>
       </c>
       <c r="C724" t="n">
-        <v>100.7977776468936</v>
+        <v>100.7977853896593</v>
       </c>
       <c r="D724" t="n">
-        <v>99.1547927119977</v>
+        <v>99.15480032855771</v>
       </c>
       <c r="E724" t="n">
-        <v>99.40541489185792</v>
+        <v>99.40542252766943</v>
       </c>
       <c r="F724" t="n">
         <v>203544</v>
@@ -14992,16 +14992,16 @@
         <v>45538</v>
       </c>
       <c r="B729" t="n">
-        <v>96.24940490722656</v>
+        <v>96.24939727783203</v>
       </c>
       <c r="C729" t="n">
-        <v>97.25190077727714</v>
+        <v>97.25189306841784</v>
       </c>
       <c r="D729" t="n">
-        <v>94.54143612809369</v>
+        <v>94.5414286340846</v>
       </c>
       <c r="E729" t="n">
-        <v>95.51609295616707</v>
+        <v>95.51608538489992</v>
       </c>
       <c r="F729" t="n">
         <v>703523</v>
@@ -15092,16 +15092,16 @@
         <v>45545</v>
       </c>
       <c r="B734" t="n">
-        <v>94.4393310546875</v>
+        <v>94.43932342529297</v>
       </c>
       <c r="C734" t="n">
-        <v>94.894174694939</v>
+        <v>94.89416702879937</v>
       </c>
       <c r="D734" t="n">
-        <v>92.1929873056461</v>
+        <v>92.19297985772515</v>
       </c>
       <c r="E734" t="n">
-        <v>93.78028014064265</v>
+        <v>93.78027256449035</v>
       </c>
       <c r="F734" t="n">
         <v>481370</v>
@@ -15132,16 +15132,16 @@
         <v>45547</v>
       </c>
       <c r="B736" t="n">
-        <v>96.86203765869141</v>
+        <v>96.86204528808594</v>
       </c>
       <c r="C736" t="n">
-        <v>97.36328911801471</v>
+        <v>97.3632967868906</v>
       </c>
       <c r="D736" t="n">
-        <v>95.41398260859528</v>
+        <v>95.41399012393292</v>
       </c>
       <c r="E736" t="n">
-        <v>95.98021071550178</v>
+        <v>95.9802182754387</v>
       </c>
       <c r="F736" t="n">
         <v>375743</v>
@@ -15152,16 +15152,16 @@
         <v>45548</v>
       </c>
       <c r="B737" t="n">
-        <v>98.87632751464844</v>
+        <v>98.87631988525391</v>
       </c>
       <c r="C737" t="n">
-        <v>99.46112446444116</v>
+        <v>99.46111678992312</v>
       </c>
       <c r="D737" t="n">
-        <v>96.32366220076925</v>
+        <v>96.32365476834089</v>
       </c>
       <c r="E737" t="n">
-        <v>96.32366220076925</v>
+        <v>96.32365476834089</v>
       </c>
       <c r="F737" t="n">
         <v>344396</v>
@@ -15192,16 +15192,16 @@
         <v>45552</v>
       </c>
       <c r="B739" t="n">
-        <v>100.3150939941406</v>
+        <v>100.3151016235352</v>
       </c>
       <c r="C739" t="n">
-        <v>100.7977766282958</v>
+        <v>100.7977842944004</v>
       </c>
       <c r="D739" t="n">
-        <v>98.70923251684773</v>
+        <v>98.70924002410959</v>
       </c>
       <c r="E739" t="n">
-        <v>99.17335343050286</v>
+        <v>99.17336097306311</v>
       </c>
       <c r="F739" t="n">
         <v>287351</v>
@@ -15252,16 +15252,16 @@
         <v>45555</v>
       </c>
       <c r="B742" t="n">
-        <v>93.28830718994141</v>
+        <v>93.28831481933594</v>
       </c>
       <c r="C742" t="n">
-        <v>100.0830373407975</v>
+        <v>100.0830455258852</v>
       </c>
       <c r="D742" t="n">
-        <v>91.71957617595477</v>
+        <v>91.71958367705382</v>
       </c>
       <c r="E742" t="n">
-        <v>99.79528462961119</v>
+        <v>99.79529279116565</v>
       </c>
       <c r="F742" t="n">
         <v>1020811</v>
@@ -15312,16 +15312,16 @@
         <v>45560</v>
       </c>
       <c r="B745" t="n">
-        <v>90.49430847167969</v>
+        <v>90.49430084228516</v>
       </c>
       <c r="C745" t="n">
-        <v>92.06303968105173</v>
+        <v>92.0630319194006</v>
       </c>
       <c r="D745" t="n">
-        <v>89.42682878036601</v>
+        <v>89.42682124096855</v>
       </c>
       <c r="E745" t="n">
-        <v>91.89595584169895</v>
+        <v>91.89594809413431</v>
       </c>
       <c r="F745" t="n">
         <v>511811</v>
@@ -15452,16 +15452,16 @@
         <v>45569</v>
       </c>
       <c r="B752" t="n">
-        <v>89.85381317138672</v>
+        <v>89.85382080078125</v>
       </c>
       <c r="C752" t="n">
-        <v>90.30864969119534</v>
+        <v>90.30865735920958</v>
       </c>
       <c r="D752" t="n">
-        <v>87.72813850259483</v>
+        <v>87.72814595150052</v>
       </c>
       <c r="E752" t="n">
-        <v>90.17869639982145</v>
+        <v>90.17870405680148</v>
       </c>
       <c r="F752" t="n">
         <v>695884</v>
@@ -15472,16 +15472,16 @@
         <v>45572</v>
       </c>
       <c r="B753" t="n">
-        <v>90.48501586914062</v>
+        <v>90.48502349853516</v>
       </c>
       <c r="C753" t="n">
-        <v>90.75419976526331</v>
+        <v>90.75420741735454</v>
       </c>
       <c r="D753" t="n">
-        <v>89.12049925852935</v>
+        <v>89.1205067728724</v>
       </c>
       <c r="E753" t="n">
-        <v>89.80739622344984</v>
+        <v>89.80740379570975</v>
       </c>
       <c r="F753" t="n">
         <v>295051</v>
@@ -15492,16 +15492,16 @@
         <v>45573</v>
       </c>
       <c r="B754" t="n">
-        <v>90.68922424316406</v>
+        <v>90.68923187255859</v>
       </c>
       <c r="C754" t="n">
-        <v>91.33899777535945</v>
+        <v>91.33900545941735</v>
       </c>
       <c r="D754" t="n">
-        <v>90.68922424316406</v>
+        <v>90.68923187255859</v>
       </c>
       <c r="E754" t="n">
-        <v>91.12549903774249</v>
+        <v>91.12550670383942</v>
       </c>
       <c r="F754" t="n">
         <v>183628</v>
@@ -15512,16 +15512,16 @@
         <v>45574</v>
       </c>
       <c r="B755" t="n">
-        <v>89.48251342773438</v>
+        <v>89.48252105712891</v>
       </c>
       <c r="C755" t="n">
-        <v>90.68922355217755</v>
+        <v>90.68923128445775</v>
       </c>
       <c r="D755" t="n">
-        <v>87.85809023250759</v>
+        <v>87.85809772340171</v>
       </c>
       <c r="E755" t="n">
-        <v>90.42003965477517</v>
+        <v>90.42004736410439</v>
       </c>
       <c r="F755" t="n">
         <v>305833</v>
@@ -15572,16 +15572,16 @@
         <v>45579</v>
       </c>
       <c r="B758" t="n">
-        <v>92.63854217529297</v>
+        <v>92.63853454589844</v>
       </c>
       <c r="C758" t="n">
-        <v>93.58534577396981</v>
+        <v>93.58533806659976</v>
       </c>
       <c r="D758" t="n">
-        <v>90.9677039636003</v>
+        <v>90.9676964718103</v>
       </c>
       <c r="E758" t="n">
-        <v>90.9677039636003</v>
+        <v>90.9676964718103</v>
       </c>
       <c r="F758" t="n">
         <v>855663</v>
@@ -15592,16 +15592,16 @@
         <v>45580</v>
       </c>
       <c r="B759" t="n">
-        <v>92.2208251953125</v>
+        <v>92.22083282470703</v>
       </c>
       <c r="C759" t="n">
-        <v>94.20726216221644</v>
+        <v>94.20726995594816</v>
       </c>
       <c r="D759" t="n">
-        <v>91.71029643353101</v>
+        <v>91.71030402068969</v>
       </c>
       <c r="E759" t="n">
-        <v>93.52964958630643</v>
+        <v>93.52965732397952</v>
       </c>
       <c r="F759" t="n">
         <v>238514</v>
@@ -15712,16 +15712,16 @@
         <v>45588</v>
       </c>
       <c r="B765" t="n">
-        <v>92.42504119873047</v>
+        <v>92.425048828125</v>
       </c>
       <c r="C765" t="n">
-        <v>95.40469670279386</v>
+        <v>95.40470457814952</v>
       </c>
       <c r="D765" t="n">
-        <v>92.36006455217171</v>
+        <v>92.36007217620262</v>
       </c>
       <c r="E765" t="n">
-        <v>93.76171173585173</v>
+        <v>93.76171947558419</v>
       </c>
       <c r="F765" t="n">
         <v>357512</v>
@@ -15732,16 +15732,16 @@
         <v>45589</v>
       </c>
       <c r="B766" t="n">
-        <v>93.28830718994141</v>
+        <v>93.28831481933594</v>
       </c>
       <c r="C766" t="n">
-        <v>93.98448858688127</v>
+        <v>93.98449627321158</v>
       </c>
       <c r="D766" t="n">
-        <v>92.43432637602346</v>
+        <v>92.4343339355769</v>
       </c>
       <c r="E766" t="n">
-        <v>92.82418625864817</v>
+        <v>92.82419385008551</v>
       </c>
       <c r="F766" t="n">
         <v>318309</v>
@@ -15752,16 +15752,16 @@
         <v>45590</v>
       </c>
       <c r="B767" t="n">
-        <v>93.17691040039062</v>
+        <v>93.17691802978516</v>
       </c>
       <c r="C767" t="n">
-        <v>93.91022228060997</v>
+        <v>93.91022997004863</v>
       </c>
       <c r="D767" t="n">
-        <v>92.02589253816214</v>
+        <v>92.02590007331048</v>
       </c>
       <c r="E767" t="n">
-        <v>93.29758636820173</v>
+        <v>93.29759400747731</v>
       </c>
       <c r="F767" t="n">
         <v>563664</v>
@@ -15872,16 +15872,16 @@
         <v>45600</v>
       </c>
       <c r="B773" t="n">
-        <v>94.235107421875</v>
+        <v>94.23511505126953</v>
       </c>
       <c r="C773" t="n">
-        <v>95.19120245514728</v>
+        <v>95.19121016194849</v>
       </c>
       <c r="D773" t="n">
-        <v>91.90522552863958</v>
+        <v>91.9052329694039</v>
       </c>
       <c r="E773" t="n">
-        <v>92.32293151917671</v>
+        <v>92.32293899375905</v>
       </c>
       <c r="F773" t="n">
         <v>289905</v>
@@ -15892,16 +15892,16 @@
         <v>45601</v>
       </c>
       <c r="B774" t="n">
-        <v>95.24690246582031</v>
+        <v>95.24689483642578</v>
       </c>
       <c r="C774" t="n">
-        <v>95.47896294213662</v>
+        <v>95.47895529415376</v>
       </c>
       <c r="D774" t="n">
-        <v>93.37184985130725</v>
+        <v>93.37184237210674</v>
       </c>
       <c r="E774" t="n">
-        <v>93.57606420357338</v>
+        <v>93.57605670801507</v>
       </c>
       <c r="F774" t="n">
         <v>229590</v>
@@ -15912,16 +15912,16 @@
         <v>45602</v>
       </c>
       <c r="B775" t="n">
-        <v>94.72709655761719</v>
+        <v>94.72708892822266</v>
       </c>
       <c r="C775" t="n">
-        <v>95.38614751126146</v>
+        <v>95.38613982878644</v>
       </c>
       <c r="D775" t="n">
-        <v>91.81241731725275</v>
+        <v>91.81240992260877</v>
       </c>
       <c r="E775" t="n">
-        <v>94.2165606376484</v>
+        <v>94.21655304937283</v>
       </c>
       <c r="F775" t="n">
         <v>484922</v>
@@ -16032,16 +16032,16 @@
         <v>45610</v>
       </c>
       <c r="B781" t="n">
-        <v>90.15085601806641</v>
+        <v>90.15084838867188</v>
       </c>
       <c r="C781" t="n">
-        <v>91.79384106758192</v>
+        <v>91.79383329914289</v>
       </c>
       <c r="D781" t="n">
-        <v>89.28759076644334</v>
+        <v>89.28758321010626</v>
       </c>
       <c r="E781" t="n">
-        <v>90.22510998792019</v>
+        <v>90.22510235224161</v>
       </c>
       <c r="F781" t="n">
         <v>249817</v>
@@ -16112,16 +16112,16 @@
         <v>45618</v>
       </c>
       <c r="B785" t="n">
-        <v>85.32398986816406</v>
+        <v>85.32399749755859</v>
       </c>
       <c r="C785" t="n">
-        <v>86.79061370312989</v>
+        <v>86.79062146366518</v>
       </c>
       <c r="D785" t="n">
-        <v>83.87593483623105</v>
+        <v>83.8759423361452</v>
       </c>
       <c r="E785" t="n">
-        <v>84.55354742653884</v>
+        <v>84.55355498704292</v>
       </c>
       <c r="F785" t="n">
         <v>285924</v>
@@ -16192,16 +16192,16 @@
         <v>45624</v>
       </c>
       <c r="B789" t="n">
-        <v>77.55461120605469</v>
+        <v>77.55461883544922</v>
       </c>
       <c r="C789" t="n">
-        <v>83.54176844519063</v>
+        <v>83.54177666356864</v>
       </c>
       <c r="D789" t="n">
-        <v>77.14618251632936</v>
+        <v>77.14619010554493</v>
       </c>
       <c r="E789" t="n">
-        <v>82.6135265735774</v>
+        <v>82.6135347006401</v>
       </c>
       <c r="F789" t="n">
         <v>741463</v>
@@ -16252,16 +16252,16 @@
         <v>45629</v>
       </c>
       <c r="B792" t="n">
-        <v>75.25257110595703</v>
+        <v>75.2525634765625</v>
       </c>
       <c r="C792" t="n">
-        <v>78.61280935828697</v>
+        <v>78.61280138821857</v>
       </c>
       <c r="D792" t="n">
-        <v>75.17831005374644</v>
+        <v>75.17830243188078</v>
       </c>
       <c r="E792" t="n">
-        <v>77.94447405223913</v>
+        <v>77.94446614992914</v>
       </c>
       <c r="F792" t="n">
         <v>1021625</v>
@@ -16272,16 +16272,16 @@
         <v>45630</v>
       </c>
       <c r="B793" t="n">
-        <v>75.2247314453125</v>
+        <v>75.22472381591797</v>
       </c>
       <c r="C793" t="n">
-        <v>76.09728117894873</v>
+        <v>76.09727346105902</v>
       </c>
       <c r="D793" t="n">
-        <v>74.39859664377688</v>
+        <v>74.39858909817006</v>
       </c>
       <c r="E793" t="n">
-        <v>75.41966141267126</v>
+        <v>75.41965376350666</v>
       </c>
       <c r="F793" t="n">
         <v>411810</v>
@@ -16312,16 +16312,16 @@
         <v>45632</v>
       </c>
       <c r="B795" t="n">
-        <v>75.78166198730469</v>
+        <v>75.78166961669922</v>
       </c>
       <c r="C795" t="n">
-        <v>75.78166198730469</v>
+        <v>75.78166961669922</v>
       </c>
       <c r="D795" t="n">
-        <v>74.25934596164483</v>
+        <v>74.25935343777866</v>
       </c>
       <c r="E795" t="n">
-        <v>75.65170869842567</v>
+        <v>75.651716314737</v>
       </c>
       <c r="F795" t="n">
         <v>1017781</v>
@@ -24552,19 +24552,39 @@
         <v>46239</v>
       </c>
       <c r="B1207" t="n">
-        <v>88.20999999999999</v>
+        <v>88.20999908447266</v>
       </c>
       <c r="C1207" t="n">
-        <v>88.7</v>
+        <v>88.69999694824219</v>
       </c>
       <c r="D1207" t="n">
-        <v>86.61</v>
+        <v>86.61000061035156</v>
       </c>
       <c r="E1207" t="n">
-        <v>86.61</v>
+        <v>86.61000061035156</v>
       </c>
       <c r="F1207" t="n">
         <v>496669</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B1208" t="n">
+        <v>85.23999999999999</v>
+      </c>
+      <c r="C1208" t="n">
+        <v>87.84</v>
+      </c>
+      <c r="D1208" t="n">
+        <v>85.04000000000001</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>87.22</v>
+      </c>
+      <c r="F1208" t="n">
+        <v>339464</v>
       </c>
     </row>
   </sheetData>

--- a/database/XPBR31.xlsx
+++ b/database/XPBR31.xlsx
@@ -452,16 +452,16 @@
         <v>44473</v>
       </c>
       <c r="B2" t="n">
-        <v>196.6089782714844</v>
+        <v>196.6089630126953</v>
       </c>
       <c r="C2" t="n">
-        <v>203.5755007756201</v>
+        <v>203.5754849761604</v>
       </c>
       <c r="D2" t="n">
-        <v>191.4433762318198</v>
+        <v>191.4433613739322</v>
       </c>
       <c r="E2" t="n">
-        <v>191.9529095912669</v>
+        <v>191.9528946938346</v>
       </c>
       <c r="F2" t="n">
         <v>9950865</v>
@@ -472,16 +472,16 @@
         <v>44474</v>
       </c>
       <c r="B3" t="n">
-        <v>192.54150390625</v>
+        <v>192.5414886474609</v>
       </c>
       <c r="C3" t="n">
-        <v>198.9809326053319</v>
+        <v>198.9809168362223</v>
       </c>
       <c r="D3" t="n">
-        <v>187.7273111444886</v>
+        <v>187.7272962672212</v>
       </c>
       <c r="E3" t="n">
-        <v>197.6631780847668</v>
+        <v>197.6631624200884</v>
       </c>
       <c r="F3" t="n">
         <v>2636287</v>
@@ -492,16 +492,16 @@
         <v>44475</v>
       </c>
       <c r="B4" t="n">
-        <v>189.4491577148438</v>
+        <v>189.4491729736328</v>
       </c>
       <c r="C4" t="n">
-        <v>191.0041117053844</v>
+        <v>191.004127089414</v>
       </c>
       <c r="D4" t="n">
-        <v>181.8501124827158</v>
+        <v>181.8501271294555</v>
       </c>
       <c r="E4" t="n">
-        <v>191.0041117053844</v>
+        <v>191.004127089414</v>
       </c>
       <c r="F4" t="n">
         <v>2556665</v>
@@ -552,16 +552,16 @@
         <v>44480</v>
       </c>
       <c r="B7" t="n">
-        <v>180.0931243896484</v>
+        <v>180.0931091308594</v>
       </c>
       <c r="C7" t="n">
-        <v>193.1125459627998</v>
+        <v>193.1125296009114</v>
       </c>
       <c r="D7" t="n">
-        <v>180.0931243896484</v>
+        <v>180.0931091308594</v>
       </c>
       <c r="E7" t="n">
-        <v>191.8738534510431</v>
+        <v>191.8738371941056</v>
       </c>
       <c r="F7" t="n">
         <v>2006205</v>
@@ -572,16 +572,16 @@
         <v>44482</v>
       </c>
       <c r="B8" t="n">
-        <v>169.5510711669922</v>
+        <v>169.5510559082031</v>
       </c>
       <c r="C8" t="n">
-        <v>178.8632078987421</v>
+        <v>178.8631918019051</v>
       </c>
       <c r="D8" t="n">
-        <v>169.5510711669922</v>
+        <v>169.5510559082031</v>
       </c>
       <c r="E8" t="n">
-        <v>174.4091914601629</v>
+        <v>174.4091757641661</v>
       </c>
       <c r="F8" t="n">
         <v>3487621</v>
@@ -612,16 +612,16 @@
         <v>44484</v>
       </c>
       <c r="B10" t="n">
-        <v>175.7006072998047</v>
+        <v>175.7005920410156</v>
       </c>
       <c r="C10" t="n">
-        <v>178.9774198725761</v>
+        <v>178.977404329211</v>
       </c>
       <c r="D10" t="n">
-        <v>166.9155769348145</v>
+        <v>166.9155624389649</v>
       </c>
       <c r="E10" t="n">
-        <v>166.9155769348145</v>
+        <v>166.9155624389649</v>
       </c>
       <c r="F10" t="n">
         <v>2643581</v>
@@ -632,16 +632,16 @@
         <v>44487</v>
       </c>
       <c r="B11" t="n">
-        <v>179.4166412353516</v>
+        <v>179.4166717529297</v>
       </c>
       <c r="C11" t="n">
-        <v>182.2717756240963</v>
+        <v>182.2718066273138</v>
       </c>
       <c r="D11" t="n">
-        <v>175.0680546165491</v>
+        <v>175.0680843944616</v>
       </c>
       <c r="E11" t="n">
-        <v>176.7547785545438</v>
+        <v>176.7548086193568</v>
       </c>
       <c r="F11" t="n">
         <v>1369949</v>
@@ -652,16 +652,16 @@
         <v>44488</v>
       </c>
       <c r="B12" t="n">
-        <v>175.0856475830078</v>
+        <v>175.0856628417969</v>
       </c>
       <c r="C12" t="n">
-        <v>179.4078806604117</v>
+        <v>179.4078962958852</v>
       </c>
       <c r="D12" t="n">
-        <v>174.3828425140635</v>
+        <v>174.3828577116028</v>
       </c>
       <c r="E12" t="n">
-        <v>177.5454586218672</v>
+        <v>177.5454740950298</v>
       </c>
       <c r="F12" t="n">
         <v>722779</v>
@@ -672,16 +672,16 @@
         <v>44489</v>
       </c>
       <c r="B13" t="n">
-        <v>174.3828582763672</v>
+        <v>174.3828430175781</v>
       </c>
       <c r="C13" t="n">
-        <v>178.4942461832448</v>
+        <v>178.4942305647025</v>
       </c>
       <c r="D13" t="n">
-        <v>169.8409990421895</v>
+        <v>169.8409841808207</v>
       </c>
       <c r="E13" t="n">
-        <v>176.5791159372786</v>
+        <v>176.5791004863134</v>
       </c>
       <c r="F13" t="n">
         <v>1907987</v>
@@ -692,16 +692,16 @@
         <v>44490</v>
       </c>
       <c r="B14" t="n">
-        <v>169.4192962646484</v>
+        <v>169.4193115234375</v>
       </c>
       <c r="C14" t="n">
-        <v>176.2189003979208</v>
+        <v>176.2189162691178</v>
       </c>
       <c r="D14" t="n">
-        <v>167.1615372888441</v>
+        <v>167.1615523442876</v>
       </c>
       <c r="E14" t="n">
-        <v>173.3989134851749</v>
+        <v>173.3989291023892</v>
       </c>
       <c r="F14" t="n">
         <v>1852525</v>
@@ -732,16 +732,16 @@
         <v>44494</v>
       </c>
       <c r="B16" t="n">
-        <v>169.12060546875</v>
+        <v>169.1206207275391</v>
       </c>
       <c r="C16" t="n">
-        <v>174.5848951289127</v>
+        <v>174.5849108807135</v>
       </c>
       <c r="D16" t="n">
-        <v>167.3635994919746</v>
+        <v>167.3636145922391</v>
       </c>
       <c r="E16" t="n">
-        <v>167.7062151212502</v>
+        <v>167.7062302524268</v>
       </c>
       <c r="F16" t="n">
         <v>1203463</v>
@@ -772,16 +772,16 @@
         <v>44496</v>
       </c>
       <c r="B18" t="n">
-        <v>163.83203125</v>
+        <v>163.8320465087891</v>
       </c>
       <c r="C18" t="n">
-        <v>168.5408079223634</v>
+        <v>168.5408236197128</v>
       </c>
       <c r="D18" t="n">
-        <v>163.83203125</v>
+        <v>163.8320465087891</v>
       </c>
       <c r="E18" t="n">
-        <v>166.9155719910203</v>
+        <v>166.9155875370005</v>
       </c>
       <c r="F18" t="n">
         <v>503418</v>
@@ -792,16 +792,16 @@
         <v>44497</v>
       </c>
       <c r="B19" t="n">
-        <v>165.1673431396484</v>
+        <v>165.1673583984375</v>
       </c>
       <c r="C19" t="n">
-        <v>166.8101528543862</v>
+        <v>166.8101682649443</v>
       </c>
       <c r="D19" t="n">
-        <v>158.6664263435071</v>
+        <v>158.6664410017166</v>
       </c>
       <c r="E19" t="n">
-        <v>163.4103371509733</v>
+        <v>163.4103522474434</v>
       </c>
       <c r="F19" t="n">
         <v>1047427</v>
@@ -832,16 +832,16 @@
         <v>44501</v>
       </c>
       <c r="B21" t="n">
-        <v>169.7267761230469</v>
+        <v>169.7267913818359</v>
       </c>
       <c r="C21" t="n">
-        <v>171.2026681266692</v>
+        <v>171.2026835181439</v>
       </c>
       <c r="D21" t="n">
-        <v>161.9344588391563</v>
+        <v>161.9344733973998</v>
       </c>
       <c r="E21" t="n">
-        <v>162.5230542378089</v>
+        <v>162.5230688489684</v>
       </c>
       <c r="F21" t="n">
         <v>466029</v>
@@ -892,16 +892,16 @@
         <v>44505</v>
       </c>
       <c r="B24" t="n">
-        <v>170.4735107421875</v>
+        <v>170.4735260009766</v>
       </c>
       <c r="C24" t="n">
-        <v>171.30808591567</v>
+        <v>171.3081012491605</v>
       </c>
       <c r="D24" t="n">
-        <v>159.1408139386772</v>
+        <v>159.1408281830961</v>
       </c>
       <c r="E24" t="n">
-        <v>160.9417477792819</v>
+        <v>160.9417621848993</v>
       </c>
       <c r="F24" t="n">
         <v>806903</v>
@@ -932,16 +932,16 @@
         <v>44509</v>
       </c>
       <c r="B26" t="n">
-        <v>163.7705230712891</v>
+        <v>163.7705383300781</v>
       </c>
       <c r="C26" t="n">
-        <v>169.8497620526857</v>
+        <v>169.8497778778882</v>
       </c>
       <c r="D26" t="n">
-        <v>162.0837989670482</v>
+        <v>162.0838140686822</v>
       </c>
       <c r="E26" t="n">
-        <v>167.3548168196352</v>
+        <v>167.3548324123792</v>
       </c>
       <c r="F26" t="n">
         <v>336270</v>
@@ -952,16 +952,16 @@
         <v>44510</v>
       </c>
       <c r="B27" t="n">
-        <v>158.5697784423828</v>
+        <v>158.5697937011719</v>
       </c>
       <c r="C27" t="n">
-        <v>165.9931255001201</v>
+        <v>165.99314147324</v>
       </c>
       <c r="D27" t="n">
-        <v>157.9109012466388</v>
+        <v>157.9109164420257</v>
       </c>
       <c r="E27" t="n">
-        <v>162.8305230034835</v>
+        <v>162.8305386722738</v>
       </c>
       <c r="F27" t="n">
         <v>596401</v>
@@ -972,16 +972,16 @@
         <v>44511</v>
       </c>
       <c r="B28" t="n">
-        <v>162.1804504394531</v>
+        <v>162.1804351806641</v>
       </c>
       <c r="C28" t="n">
-        <v>165.5099711386316</v>
+        <v>165.5099555665838</v>
       </c>
       <c r="D28" t="n">
-        <v>159.4658792012834</v>
+        <v>159.4658641978954</v>
       </c>
       <c r="E28" t="n">
-        <v>161.5567073687131</v>
+        <v>161.5566921686091</v>
       </c>
       <c r="F28" t="n">
         <v>479646</v>
@@ -1032,16 +1032,16 @@
         <v>44517</v>
       </c>
       <c r="B31" t="n">
-        <v>147.3425140380859</v>
+        <v>147.342529296875</v>
       </c>
       <c r="C31" t="n">
-        <v>157.7088514018402</v>
+        <v>157.708867734167</v>
       </c>
       <c r="D31" t="n">
-        <v>146.6045747863164</v>
+        <v>146.6045899686845</v>
       </c>
       <c r="E31" t="n">
-        <v>156.3735231808589</v>
+        <v>156.3735393748991</v>
       </c>
       <c r="F31" t="n">
         <v>1006563</v>
@@ -1052,16 +1052,16 @@
         <v>44518</v>
       </c>
       <c r="B32" t="n">
-        <v>141.1402893066406</v>
+        <v>141.1403045654297</v>
       </c>
       <c r="C32" t="n">
-        <v>149.7320472156696</v>
+        <v>149.7320634033205</v>
       </c>
       <c r="D32" t="n">
-        <v>141.1402893066406</v>
+        <v>141.1403045654297</v>
       </c>
       <c r="E32" t="n">
-        <v>147.8520514103275</v>
+        <v>147.8520673947305</v>
       </c>
       <c r="F32" t="n">
         <v>1135748</v>
@@ -1092,16 +1092,16 @@
         <v>44522</v>
       </c>
       <c r="B34" t="n">
-        <v>140.0509490966797</v>
+        <v>140.0509338378906</v>
       </c>
       <c r="C34" t="n">
-        <v>150.6632671305561</v>
+        <v>150.6632507155369</v>
       </c>
       <c r="D34" t="n">
-        <v>139.9016051926592</v>
+        <v>139.9015899501414</v>
       </c>
       <c r="E34" t="n">
-        <v>145.9281364140771</v>
+        <v>145.9281205149585</v>
       </c>
       <c r="F34" t="n">
         <v>547961</v>
@@ -1112,16 +1112,16 @@
         <v>44523</v>
       </c>
       <c r="B35" t="n">
-        <v>144.9529876708984</v>
+        <v>144.9530029296875</v>
       </c>
       <c r="C35" t="n">
-        <v>147.2107467010899</v>
+        <v>147.2107621975469</v>
       </c>
       <c r="D35" t="n">
-        <v>136.3524496339106</v>
+        <v>136.3524639873455</v>
       </c>
       <c r="E35" t="n">
-        <v>142.3174788041548</v>
+        <v>142.3174937855114</v>
       </c>
       <c r="F35" t="n">
         <v>809322</v>
@@ -1132,16 +1132,16 @@
         <v>44524</v>
       </c>
       <c r="B36" t="n">
-        <v>148.7393646240234</v>
+        <v>148.7393493652344</v>
       </c>
       <c r="C36" t="n">
-        <v>150.215256871112</v>
+        <v>150.2152414609149</v>
       </c>
       <c r="D36" t="n">
-        <v>144.4171307798759</v>
+        <v>144.4171159644937</v>
       </c>
       <c r="E36" t="n">
-        <v>144.5225468672058</v>
+        <v>144.5225320410092</v>
       </c>
       <c r="F36" t="n">
         <v>231702</v>
@@ -1212,16 +1212,16 @@
         <v>44530</v>
       </c>
       <c r="B40" t="n">
-        <v>140.5604858398438</v>
+        <v>140.5604705810547</v>
       </c>
       <c r="C40" t="n">
-        <v>147.3073827258078</v>
+        <v>147.3073667345976</v>
       </c>
       <c r="D40" t="n">
-        <v>139.7610448594554</v>
+        <v>139.7610296874511</v>
       </c>
       <c r="E40" t="n">
-        <v>147.3073827258078</v>
+        <v>147.3073667345976</v>
       </c>
       <c r="F40" t="n">
         <v>711030</v>
@@ -1252,16 +1252,16 @@
         <v>44532</v>
       </c>
       <c r="B42" t="n">
-        <v>143.7845916748047</v>
+        <v>143.7845764160156</v>
       </c>
       <c r="C42" t="n">
-        <v>150.5139282123845</v>
+        <v>150.513912239461</v>
       </c>
       <c r="D42" t="n">
-        <v>143.0466523346498</v>
+        <v>143.0466371541728</v>
       </c>
       <c r="E42" t="n">
-        <v>145.8315053769355</v>
+        <v>145.8314899009227</v>
       </c>
       <c r="F42" t="n">
         <v>584287</v>
@@ -1292,16 +1292,16 @@
         <v>44536</v>
       </c>
       <c r="B44" t="n">
-        <v>147.7642059326172</v>
+        <v>147.7641906738281</v>
       </c>
       <c r="C44" t="n">
-        <v>149.3279402427002</v>
+        <v>149.327924822433</v>
       </c>
       <c r="D44" t="n">
-        <v>139.2427292821338</v>
+        <v>139.2427149033103</v>
       </c>
       <c r="E44" t="n">
-        <v>144.9617791417145</v>
+        <v>144.9617641723165</v>
       </c>
       <c r="F44" t="n">
         <v>521095</v>
@@ -1312,16 +1312,16 @@
         <v>44537</v>
       </c>
       <c r="B45" t="n">
-        <v>148.0277557373047</v>
+        <v>148.0277404785156</v>
       </c>
       <c r="C45" t="n">
-        <v>153.0440137734988</v>
+        <v>153.0439979976308</v>
       </c>
       <c r="D45" t="n">
-        <v>147.8871920399053</v>
+        <v>147.8871767956056</v>
       </c>
       <c r="E45" t="n">
-        <v>150.2240132408255</v>
+        <v>150.2239977556449</v>
       </c>
       <c r="F45" t="n">
         <v>560968</v>
@@ -1372,16 +1372,16 @@
         <v>44540</v>
       </c>
       <c r="B48" t="n">
-        <v>148.2210388183594</v>
+        <v>148.2210235595703</v>
       </c>
       <c r="C48" t="n">
-        <v>150.2240247425351</v>
+        <v>150.2240092775463</v>
       </c>
       <c r="D48" t="n">
-        <v>146.3322625826765</v>
+        <v>146.3322475183298</v>
       </c>
       <c r="E48" t="n">
-        <v>148.1156227396848</v>
+        <v>148.1156074917479</v>
       </c>
       <c r="F48" t="n">
         <v>506410</v>
@@ -1392,16 +1392,16 @@
         <v>44543</v>
       </c>
       <c r="B49" t="n">
-        <v>155.4950256347656</v>
+        <v>155.4950561523438</v>
       </c>
       <c r="C49" t="n">
-        <v>159.5537050651586</v>
+        <v>159.5537363792964</v>
       </c>
       <c r="D49" t="n">
-        <v>147.1580276266661</v>
+        <v>147.1580565080183</v>
       </c>
       <c r="E49" t="n">
-        <v>148.2034483053774</v>
+        <v>148.2034773919047</v>
       </c>
       <c r="F49" t="n">
         <v>707090</v>
@@ -1412,16 +1412,16 @@
         <v>44544</v>
       </c>
       <c r="B50" t="n">
-        <v>147.2283325195312</v>
+        <v>147.2283020019531</v>
       </c>
       <c r="C50" t="n">
-        <v>150.926836499023</v>
+        <v>150.9268052148167</v>
       </c>
       <c r="D50" t="n">
-        <v>141.1227386054261</v>
+        <v>141.1227093534192</v>
       </c>
       <c r="E50" t="n">
-        <v>150.6632828858824</v>
+        <v>150.6632516563057</v>
       </c>
       <c r="F50" t="n">
         <v>995575</v>
@@ -1432,16 +1432,16 @@
         <v>44545</v>
       </c>
       <c r="B51" t="n">
-        <v>150.6983947753906</v>
+        <v>150.6983795166016</v>
       </c>
       <c r="C51" t="n">
-        <v>151.5417635314571</v>
+        <v>151.5417481872738</v>
       </c>
       <c r="D51" t="n">
-        <v>142.2296266133646</v>
+        <v>142.2296122120707</v>
       </c>
       <c r="E51" t="n">
-        <v>145.8402743850054</v>
+        <v>145.8402596181196</v>
       </c>
       <c r="F51" t="n">
         <v>314440</v>
@@ -1472,16 +1472,16 @@
         <v>44547</v>
       </c>
       <c r="B53" t="n">
-        <v>144.9529876708984</v>
+        <v>144.9530029296875</v>
       </c>
       <c r="C53" t="n">
-        <v>147.4127986275041</v>
+        <v>147.4128141452304</v>
       </c>
       <c r="D53" t="n">
-        <v>141.825519293812</v>
+        <v>141.8255342233813</v>
       </c>
       <c r="E53" t="n">
-        <v>144.0744847153172</v>
+        <v>144.0744998816288</v>
       </c>
       <c r="F53" t="n">
         <v>507335</v>
@@ -1492,16 +1492,16 @@
         <v>44550</v>
       </c>
       <c r="B54" t="n">
-        <v>145.9105682373047</v>
+        <v>145.9105529785156</v>
       </c>
       <c r="C54" t="n">
-        <v>146.2883315190382</v>
+        <v>146.288316220744</v>
       </c>
       <c r="D54" t="n">
-        <v>139.2515135151951</v>
+        <v>139.2514989527854</v>
       </c>
       <c r="E54" t="n">
-        <v>144.6455217015624</v>
+        <v>144.6455065750673</v>
       </c>
       <c r="F54" t="n">
         <v>356146</v>
@@ -1532,16 +1532,16 @@
         <v>44552</v>
       </c>
       <c r="B56" t="n">
-        <v>146.226806640625</v>
+        <v>146.2268371582031</v>
       </c>
       <c r="C56" t="n">
-        <v>148.9501710226892</v>
+        <v>148.9502021086343</v>
       </c>
       <c r="D56" t="n">
-        <v>144.0744771928081</v>
+        <v>144.0745072611944</v>
       </c>
       <c r="E56" t="n">
-        <v>147.7202589061577</v>
+        <v>147.7202897354198</v>
       </c>
       <c r="F56" t="n">
         <v>439793</v>
@@ -1552,16 +1552,16 @@
         <v>44553</v>
       </c>
       <c r="B57" t="n">
-        <v>148.9238128662109</v>
+        <v>148.923828125</v>
       </c>
       <c r="C57" t="n">
-        <v>149.7759617373248</v>
+        <v>149.7759770834253</v>
       </c>
       <c r="D57" t="n">
-        <v>144.0832533891827</v>
+        <v>144.0832681520062</v>
       </c>
       <c r="E57" t="n">
-        <v>146.2268025740509</v>
+        <v>146.2268175565032</v>
       </c>
       <c r="F57" t="n">
         <v>381841</v>
@@ -1572,16 +1572,16 @@
         <v>44557</v>
       </c>
       <c r="B58" t="n">
-        <v>150.0483245849609</v>
+        <v>150.0483093261719</v>
       </c>
       <c r="C58" t="n">
-        <v>153.6941069039261</v>
+        <v>153.6940912743883</v>
       </c>
       <c r="D58" t="n">
-        <v>147.0438457432459</v>
+        <v>147.0438307899898</v>
       </c>
       <c r="E58" t="n">
-        <v>147.0438457432459</v>
+        <v>147.0438307899898</v>
       </c>
       <c r="F58" t="n">
         <v>232495</v>
@@ -1632,16 +1632,16 @@
         <v>44560</v>
       </c>
       <c r="B61" t="n">
-        <v>140.990966796875</v>
+        <v>140.9909515380859</v>
       </c>
       <c r="C61" t="n">
-        <v>141.2633006120338</v>
+        <v>141.2632853237713</v>
       </c>
       <c r="D61" t="n">
-        <v>136.7126476011728</v>
+        <v>136.7126328054061</v>
       </c>
       <c r="E61" t="n">
-        <v>140.0333882338771</v>
+        <v>140.0333730787222</v>
       </c>
       <c r="F61" t="n">
         <v>445854</v>
@@ -1652,16 +1652,16 @@
         <v>44564</v>
       </c>
       <c r="B62" t="n">
-        <v>144.8124389648438</v>
+        <v>144.8124237060547</v>
       </c>
       <c r="C62" t="n">
-        <v>144.8124389648438</v>
+        <v>144.8124237060547</v>
       </c>
       <c r="D62" t="n">
-        <v>138.7947011393807</v>
+        <v>138.7946865146767</v>
       </c>
       <c r="E62" t="n">
-        <v>142.1769298253991</v>
+        <v>142.1769148443119</v>
       </c>
       <c r="F62" t="n">
         <v>369633</v>
@@ -1672,16 +1672,16 @@
         <v>44565</v>
       </c>
       <c r="B63" t="n">
-        <v>140.2969055175781</v>
+        <v>140.2969207763672</v>
       </c>
       <c r="C63" t="n">
-        <v>146.499133628787</v>
+        <v>146.4991495621347</v>
       </c>
       <c r="D63" t="n">
-        <v>138.6628896448183</v>
+        <v>138.6629047258906</v>
       </c>
       <c r="E63" t="n">
-        <v>144.8124097286623</v>
+        <v>144.8124254785607</v>
       </c>
       <c r="F63" t="n">
         <v>382138</v>
@@ -1712,16 +1712,16 @@
         <v>44567</v>
       </c>
       <c r="B65" t="n">
-        <v>135.2718963623047</v>
+        <v>135.2718811035156</v>
       </c>
       <c r="C65" t="n">
-        <v>137.0289024684961</v>
+        <v>137.0288870115152</v>
       </c>
       <c r="D65" t="n">
-        <v>129.5879805363842</v>
+        <v>129.5879659187458</v>
       </c>
       <c r="E65" t="n">
-        <v>134.8502186501887</v>
+        <v>134.8502034389653</v>
       </c>
       <c r="F65" t="n">
         <v>814212</v>
@@ -1752,16 +1752,16 @@
         <v>44571</v>
       </c>
       <c r="B67" t="n">
-        <v>137.5208587646484</v>
+        <v>137.5208740234375</v>
       </c>
       <c r="C67" t="n">
-        <v>138.4696436480268</v>
+        <v>138.4696590120894</v>
       </c>
       <c r="D67" t="n">
-        <v>131.9072249249958</v>
+        <v>131.9072395609175</v>
       </c>
       <c r="E67" t="n">
-        <v>137.2309645603231</v>
+        <v>137.2309797869466</v>
       </c>
       <c r="F67" t="n">
         <v>730000</v>
@@ -1772,16 +1772,16 @@
         <v>44572</v>
       </c>
       <c r="B68" t="n">
-        <v>146.3849639892578</v>
+        <v>146.3849487304688</v>
       </c>
       <c r="C68" t="n">
-        <v>149.0116794664315</v>
+        <v>149.0116639338405</v>
       </c>
       <c r="D68" t="n">
-        <v>133.6290962567753</v>
+        <v>133.6290823276248</v>
       </c>
       <c r="E68" t="n">
-        <v>137.5735796821382</v>
+        <v>137.573565341825</v>
       </c>
       <c r="F68" t="n">
         <v>715197</v>
@@ -1792,16 +1792,16 @@
         <v>44573</v>
       </c>
       <c r="B69" t="n">
-        <v>149.442138671875</v>
+        <v>149.4421234130859</v>
       </c>
       <c r="C69" t="n">
-        <v>150.7950273285929</v>
+        <v>150.7950119316671</v>
       </c>
       <c r="D69" t="n">
-        <v>145.5591572073933</v>
+        <v>145.5591423450761</v>
       </c>
       <c r="E69" t="n">
-        <v>146.4464403689174</v>
+        <v>146.4464254160041</v>
       </c>
       <c r="F69" t="n">
         <v>416574</v>
@@ -1812,16 +1812,16 @@
         <v>44574</v>
       </c>
       <c r="B70" t="n">
-        <v>142.9675750732422</v>
+        <v>142.9675903320312</v>
       </c>
       <c r="C70" t="n">
-        <v>149.6529830666293</v>
+        <v>149.6529990389454</v>
       </c>
       <c r="D70" t="n">
-        <v>141.7201024913939</v>
+        <v>141.7201176170415</v>
       </c>
       <c r="E70" t="n">
-        <v>149.4860653611546</v>
+        <v>149.4860813156558</v>
       </c>
       <c r="F70" t="n">
         <v>401557</v>
@@ -1852,16 +1852,16 @@
         <v>44578</v>
       </c>
       <c r="B72" t="n">
-        <v>138.8034820556641</v>
+        <v>138.803466796875</v>
       </c>
       <c r="C72" t="n">
-        <v>140.2705805422223</v>
+        <v>140.2705651221538</v>
       </c>
       <c r="D72" t="n">
-        <v>136.9059122483617</v>
+        <v>136.9058971981742</v>
       </c>
       <c r="E72" t="n">
-        <v>138.0655427100108</v>
+        <v>138.065527532344</v>
       </c>
       <c r="F72" t="n">
         <v>75291</v>
@@ -1912,16 +1912,16 @@
         <v>44581</v>
       </c>
       <c r="B75" t="n">
-        <v>145.2868194580078</v>
+        <v>145.2868347167969</v>
       </c>
       <c r="C75" t="n">
-        <v>149.2488628630469</v>
+        <v>149.2488785379507</v>
       </c>
       <c r="D75" t="n">
-        <v>138.1094520986048</v>
+        <v>138.1094666035888</v>
       </c>
       <c r="E75" t="n">
-        <v>138.1094520986048</v>
+        <v>138.1094666035888</v>
       </c>
       <c r="F75" t="n">
         <v>666913</v>
@@ -1952,16 +1952,16 @@
         <v>44585</v>
       </c>
       <c r="B77" t="n">
-        <v>143.1696319580078</v>
+        <v>143.1696472167969</v>
       </c>
       <c r="C77" t="n">
-        <v>145.330741785616</v>
+        <v>145.3307572747327</v>
       </c>
       <c r="D77" t="n">
-        <v>136.4490895119325</v>
+        <v>136.449104054457</v>
       </c>
       <c r="E77" t="n">
-        <v>143.0202880597496</v>
+        <v>143.0203033026219</v>
       </c>
       <c r="F77" t="n">
         <v>940613</v>
@@ -1992,16 +1992,16 @@
         <v>44587</v>
       </c>
       <c r="B79" t="n">
-        <v>151.7789764404297</v>
+        <v>151.7789611816406</v>
       </c>
       <c r="C79" t="n">
-        <v>157.1466306382445</v>
+        <v>157.1466148398293</v>
       </c>
       <c r="D79" t="n">
-        <v>148.2122561848568</v>
+        <v>148.2122412846406</v>
       </c>
       <c r="E79" t="n">
-        <v>148.5987862686278</v>
+        <v>148.5987713295526</v>
       </c>
       <c r="F79" t="n">
         <v>671208</v>
@@ -2032,16 +2032,16 @@
         <v>44589</v>
       </c>
       <c r="B81" t="n">
-        <v>147.5533599853516</v>
+        <v>147.5533447265625</v>
       </c>
       <c r="C81" t="n">
-        <v>149.9253152469516</v>
+        <v>149.9252997428738</v>
       </c>
       <c r="D81" t="n">
-        <v>142.7479478218851</v>
+        <v>142.7479330600334</v>
       </c>
       <c r="E81" t="n">
-        <v>149.4948439797599</v>
+        <v>149.4948285201981</v>
       </c>
       <c r="F81" t="n">
         <v>1084942</v>
@@ -2052,16 +2052,16 @@
         <v>44592</v>
       </c>
       <c r="B82" t="n">
-        <v>155.0557861328125</v>
+        <v>155.0558013916016</v>
       </c>
       <c r="C82" t="n">
-        <v>155.3193397250649</v>
+        <v>155.3193550097899</v>
       </c>
       <c r="D82" t="n">
-        <v>145.8666384615764</v>
+        <v>145.8666528160763</v>
       </c>
       <c r="E82" t="n">
-        <v>147.0174887009155</v>
+        <v>147.0175031686687</v>
       </c>
       <c r="F82" t="n">
         <v>286473</v>
@@ -2072,16 +2072,16 @@
         <v>44593</v>
       </c>
       <c r="B83" t="n">
-        <v>155.5828704833984</v>
+        <v>155.5828857421875</v>
       </c>
       <c r="C83" t="n">
-        <v>157.3574367073448</v>
+        <v>157.3574521401745</v>
       </c>
       <c r="D83" t="n">
-        <v>151.1200740988831</v>
+        <v>151.1200889199835</v>
       </c>
       <c r="E83" t="n">
-        <v>152.4378284618541</v>
+        <v>152.4378434121932</v>
       </c>
       <c r="F83" t="n">
         <v>577815</v>
@@ -2092,16 +2092,16 @@
         <v>44594</v>
       </c>
       <c r="B84" t="n">
-        <v>148.9941101074219</v>
+        <v>148.9941253662109</v>
       </c>
       <c r="C84" t="n">
-        <v>158.1305356968381</v>
+        <v>158.1305518913071</v>
       </c>
       <c r="D84" t="n">
-        <v>148.9062544478559</v>
+        <v>148.9062696976475</v>
       </c>
       <c r="E84" t="n">
-        <v>155.8025081721468</v>
+        <v>155.8025241281978</v>
       </c>
       <c r="F84" t="n">
         <v>466282</v>
@@ -2112,16 +2112,16 @@
         <v>44595</v>
       </c>
       <c r="B85" t="n">
-        <v>146.270751953125</v>
+        <v>146.2707366943359</v>
       </c>
       <c r="C85" t="n">
-        <v>149.9604619340272</v>
+        <v>149.960446290332</v>
       </c>
       <c r="D85" t="n">
-        <v>145.5415928423091</v>
+        <v>145.5415776595851</v>
       </c>
       <c r="E85" t="n">
-        <v>149.2137424144391</v>
+        <v>149.2137268486408</v>
       </c>
       <c r="F85" t="n">
         <v>228387</v>
@@ -2172,16 +2172,16 @@
         <v>44600</v>
       </c>
       <c r="B88" t="n">
-        <v>149.3191528320312</v>
+        <v>149.3191680908203</v>
       </c>
       <c r="C88" t="n">
-        <v>149.3191528320312</v>
+        <v>149.3191680908203</v>
       </c>
       <c r="D88" t="n">
-        <v>144.2326130626084</v>
+        <v>144.2326278016086</v>
       </c>
       <c r="E88" t="n">
-        <v>147.6763565462567</v>
+        <v>147.6763716371699</v>
       </c>
       <c r="F88" t="n">
         <v>326666</v>
@@ -2292,16 +2292,16 @@
         <v>44608</v>
       </c>
       <c r="B94" t="n">
-        <v>160.8099975585938</v>
+        <v>160.8099822998047</v>
       </c>
       <c r="C94" t="n">
-        <v>164.6841995051333</v>
+        <v>164.6841838787326</v>
       </c>
       <c r="D94" t="n">
-        <v>158.0690587299737</v>
+        <v>158.0690437312643</v>
       </c>
       <c r="E94" t="n">
-        <v>161.1438196262952</v>
+        <v>161.1438043358308</v>
       </c>
       <c r="F94" t="n">
         <v>383335</v>
@@ -2332,16 +2332,16 @@
         <v>44610</v>
       </c>
       <c r="B96" t="n">
-        <v>155.4950256347656</v>
+        <v>155.4950561523438</v>
       </c>
       <c r="C96" t="n">
-        <v>159.5361446572868</v>
+        <v>159.5361759679781</v>
       </c>
       <c r="D96" t="n">
-        <v>153.4744661235051</v>
+        <v>153.4744962445266</v>
       </c>
       <c r="E96" t="n">
-        <v>156.9884780022568</v>
+        <v>156.9885088129411</v>
       </c>
       <c r="F96" t="n">
         <v>742998</v>
@@ -2352,16 +2352,16 @@
         <v>44613</v>
       </c>
       <c r="B97" t="n">
-        <v>150.3118591308594</v>
+        <v>150.3118743896484</v>
       </c>
       <c r="C97" t="n">
-        <v>155.6882928603806</v>
+        <v>155.6883086649541</v>
       </c>
       <c r="D97" t="n">
-        <v>149.5827000785075</v>
+        <v>149.5827152632765</v>
       </c>
       <c r="E97" t="n">
-        <v>154.6165181959493</v>
+        <v>154.6165338917224</v>
       </c>
       <c r="F97" t="n">
         <v>185476</v>
@@ -2372,16 +2372,16 @@
         <v>44614</v>
       </c>
       <c r="B98" t="n">
-        <v>150.3557891845703</v>
+        <v>150.3557739257812</v>
       </c>
       <c r="C98" t="n">
-        <v>155.0557857870995</v>
+        <v>155.0557700513334</v>
       </c>
       <c r="D98" t="n">
-        <v>149.6793514986648</v>
+        <v>149.6793363085237</v>
       </c>
       <c r="E98" t="n">
-        <v>150.5315005156085</v>
+        <v>150.5314852389875</v>
       </c>
       <c r="F98" t="n">
         <v>352471</v>
@@ -2412,16 +2412,16 @@
         <v>44616</v>
       </c>
       <c r="B100" t="n">
-        <v>148.1068115234375</v>
+        <v>148.1067962646484</v>
       </c>
       <c r="C100" t="n">
-        <v>148.1068115234375</v>
+        <v>148.1067962646484</v>
       </c>
       <c r="D100" t="n">
-        <v>139.2427198314664</v>
+        <v>139.2427054859054</v>
       </c>
       <c r="E100" t="n">
-        <v>143.327753253209</v>
+        <v>143.3277384867851</v>
       </c>
       <c r="F100" t="n">
         <v>704723</v>
@@ -2432,16 +2432,16 @@
         <v>44617</v>
       </c>
       <c r="B101" t="n">
-        <v>145.1374969482422</v>
+        <v>145.1374816894531</v>
       </c>
       <c r="C101" t="n">
-        <v>149.1698227905674</v>
+        <v>149.1698071078465</v>
       </c>
       <c r="D101" t="n">
-        <v>141.2457214082899</v>
+        <v>141.2457065586561</v>
       </c>
       <c r="E101" t="n">
-        <v>145.8754363040482</v>
+        <v>145.8754209676771</v>
       </c>
       <c r="F101" t="n">
         <v>765160</v>
@@ -2492,16 +2492,16 @@
         <v>44624</v>
       </c>
       <c r="B104" t="n">
-        <v>129.4035034179688</v>
+        <v>129.4034881591797</v>
       </c>
       <c r="C104" t="n">
-        <v>139.216380989505</v>
+        <v>139.2163645736173</v>
       </c>
       <c r="D104" t="n">
-        <v>128.5864886016308</v>
+        <v>128.5864734391812</v>
       </c>
       <c r="E104" t="n">
-        <v>134.2440504527695</v>
+        <v>134.2440346232008</v>
       </c>
       <c r="F104" t="n">
         <v>615045</v>
@@ -2512,16 +2512,16 @@
         <v>44627</v>
       </c>
       <c r="B105" t="n">
-        <v>117.0780944824219</v>
+        <v>117.0781021118164</v>
       </c>
       <c r="C105" t="n">
-        <v>130.2644192270299</v>
+        <v>130.2644277157113</v>
       </c>
       <c r="D105" t="n">
-        <v>117.0780944824219</v>
+        <v>117.0781021118164</v>
       </c>
       <c r="E105" t="n">
-        <v>129.5791879833061</v>
+        <v>129.5791964273345</v>
       </c>
       <c r="F105" t="n">
         <v>1053703</v>
@@ -2532,16 +2532,16 @@
         <v>44628</v>
       </c>
       <c r="B106" t="n">
-        <v>124.4399566650391</v>
+        <v>124.43994140625</v>
       </c>
       <c r="C106" t="n">
-        <v>125.6083673770213</v>
+        <v>125.6083519749621</v>
       </c>
       <c r="D106" t="n">
-        <v>115.8657713786687</v>
+        <v>115.8657571712436</v>
       </c>
       <c r="E106" t="n">
-        <v>118.3431565134491</v>
+        <v>118.3431420022477</v>
       </c>
       <c r="F106" t="n">
         <v>713320</v>
@@ -2572,16 +2572,16 @@
         <v>44630</v>
       </c>
       <c r="B108" t="n">
-        <v>135.7814178466797</v>
+        <v>135.7814331054688</v>
       </c>
       <c r="C108" t="n">
-        <v>139.163659666757</v>
+        <v>139.1636753056343</v>
       </c>
       <c r="D108" t="n">
-        <v>133.2425447818445</v>
+        <v>133.2425597553211</v>
       </c>
       <c r="E108" t="n">
-        <v>137.4857157651647</v>
+        <v>137.4857312154787</v>
       </c>
       <c r="F108" t="n">
         <v>543810</v>
@@ -2592,16 +2592,16 @@
         <v>44631</v>
       </c>
       <c r="B109" t="n">
-        <v>131.6173248291016</v>
+        <v>131.6173400878906</v>
       </c>
       <c r="C109" t="n">
-        <v>138.7156172153465</v>
+        <v>138.7156332970618</v>
       </c>
       <c r="D109" t="n">
-        <v>131.1341455020338</v>
+        <v>131.1341607048064</v>
       </c>
       <c r="E109" t="n">
-        <v>135.8077744536639</v>
+        <v>135.8077901982643</v>
       </c>
       <c r="F109" t="n">
         <v>422012</v>
@@ -2712,16 +2712,16 @@
         <v>44641</v>
       </c>
       <c r="B115" t="n">
-        <v>139.7698364257812</v>
+        <v>139.7698211669922</v>
       </c>
       <c r="C115" t="n">
-        <v>143.0642227644949</v>
+        <v>143.0642071460549</v>
       </c>
       <c r="D115" t="n">
-        <v>138.4169342626098</v>
+        <v>138.4169191515182</v>
       </c>
       <c r="E115" t="n">
-        <v>141.4829146409339</v>
+        <v>141.4828991951266</v>
       </c>
       <c r="F115" t="n">
         <v>351500</v>
@@ -2732,16 +2732,16 @@
         <v>44642</v>
       </c>
       <c r="B116" t="n">
-        <v>143.4683074951172</v>
+        <v>143.4683380126953</v>
       </c>
       <c r="C116" t="n">
-        <v>146.8329752351156</v>
+        <v>146.8330064684024</v>
       </c>
       <c r="D116" t="n">
-        <v>139.7698177660223</v>
+        <v>139.7698474968835</v>
       </c>
       <c r="E116" t="n">
-        <v>139.7698177660223</v>
+        <v>139.7698474968835</v>
       </c>
       <c r="F116" t="n">
         <v>384464</v>
@@ -2772,16 +2772,16 @@
         <v>44644</v>
       </c>
       <c r="B118" t="n">
-        <v>136.2733612060547</v>
+        <v>136.2733917236328</v>
       </c>
       <c r="C118" t="n">
-        <v>137.2660737409138</v>
+        <v>137.2661044808038</v>
       </c>
       <c r="D118" t="n">
-        <v>132.4870159727677</v>
+        <v>132.4870456424172</v>
       </c>
       <c r="E118" t="n">
-        <v>133.2776766004494</v>
+        <v>133.2777064471624</v>
       </c>
       <c r="F118" t="n">
         <v>438667</v>
@@ -2792,16 +2792,16 @@
         <v>44645</v>
       </c>
       <c r="B119" t="n">
-        <v>133.9277954101562</v>
+        <v>133.9277648925781</v>
       </c>
       <c r="C119" t="n">
-        <v>140.0333892967957</v>
+        <v>140.0333573879609</v>
       </c>
       <c r="D119" t="n">
-        <v>133.4182620016815</v>
+        <v>133.4182316002086</v>
       </c>
       <c r="E119" t="n">
-        <v>135.3070517166146</v>
+        <v>135.307020884751</v>
       </c>
       <c r="F119" t="n">
         <v>403765</v>
@@ -2832,16 +2832,16 @@
         <v>44649</v>
       </c>
       <c r="B121" t="n">
-        <v>139.5765686035156</v>
+        <v>139.5765533447266</v>
       </c>
       <c r="C121" t="n">
-        <v>140.4638518565375</v>
+        <v>140.4638365007489</v>
       </c>
       <c r="D121" t="n">
-        <v>135.1576993429566</v>
+        <v>135.1576845672471</v>
       </c>
       <c r="E121" t="n">
-        <v>137.9249785831454</v>
+        <v>137.9249635049115</v>
       </c>
       <c r="F121" t="n">
         <v>830631</v>
@@ -2852,16 +2852,16 @@
         <v>44650</v>
       </c>
       <c r="B122" t="n">
-        <v>130.6773223876953</v>
+        <v>130.6773376464844</v>
       </c>
       <c r="C122" t="n">
-        <v>139.2866545436278</v>
+        <v>139.2866708077021</v>
       </c>
       <c r="D122" t="n">
-        <v>130.6333945563345</v>
+        <v>130.6334098099942</v>
       </c>
       <c r="E122" t="n">
-        <v>137.9952540499933</v>
+        <v>137.9952701632747</v>
       </c>
       <c r="F122" t="n">
         <v>554943</v>
@@ -2892,16 +2892,16 @@
         <v>44652</v>
       </c>
       <c r="B124" t="n">
-        <v>127.3829345703125</v>
+        <v>127.382942199707</v>
       </c>
       <c r="C124" t="n">
-        <v>129.1048063426568</v>
+        <v>129.10481407518</v>
       </c>
       <c r="D124" t="n">
-        <v>124.6156554916039</v>
+        <v>124.6156629552567</v>
       </c>
       <c r="E124" t="n">
-        <v>126.5044315732759</v>
+        <v>126.5044391500539</v>
       </c>
       <c r="F124" t="n">
         <v>526406</v>
@@ -2912,16 +2912,16 @@
         <v>44655</v>
       </c>
       <c r="B125" t="n">
-        <v>129.0872344970703</v>
+        <v>129.0872192382812</v>
       </c>
       <c r="C125" t="n">
-        <v>129.0872344970703</v>
+        <v>129.0872192382812</v>
       </c>
       <c r="D125" t="n">
-        <v>125.6347106955444</v>
+        <v>125.6346958448618</v>
       </c>
       <c r="E125" t="n">
-        <v>127.3829365120573</v>
+        <v>127.3829214547252</v>
       </c>
       <c r="F125" t="n">
         <v>325077</v>
@@ -2932,16 +2932,16 @@
         <v>44656</v>
       </c>
       <c r="B126" t="n">
-        <v>128.0769500732422</v>
+        <v>128.0769348144531</v>
       </c>
       <c r="C126" t="n">
-        <v>130.1590113571142</v>
+        <v>130.1589958502732</v>
       </c>
       <c r="D126" t="n">
-        <v>125.6347127369603</v>
+        <v>125.6346977691337</v>
       </c>
       <c r="E126" t="n">
-        <v>128.2614416065824</v>
+        <v>128.2614263258134</v>
       </c>
       <c r="F126" t="n">
         <v>767000</v>
@@ -2952,16 +2952,16 @@
         <v>44657</v>
       </c>
       <c r="B127" t="n">
-        <v>125.0197448730469</v>
+        <v>125.019775390625</v>
       </c>
       <c r="C127" t="n">
-        <v>127.3829198059536</v>
+        <v>127.3829509003876</v>
       </c>
       <c r="D127" t="n">
-        <v>122.6917175626873</v>
+        <v>122.6917475119892</v>
       </c>
       <c r="E127" t="n">
-        <v>127.1720742853418</v>
+        <v>127.172105328308</v>
       </c>
       <c r="F127" t="n">
         <v>694358</v>
@@ -2972,16 +2972,16 @@
         <v>44658</v>
       </c>
       <c r="B128" t="n">
-        <v>126.9524612426758</v>
+        <v>126.9524536132812</v>
       </c>
       <c r="C128" t="n">
-        <v>128.6040511402175</v>
+        <v>128.6040434115682</v>
       </c>
       <c r="D128" t="n">
-        <v>122.9991978193282</v>
+        <v>122.9991904275108</v>
       </c>
       <c r="E128" t="n">
-        <v>124.7562037852604</v>
+        <v>124.7561962878532</v>
       </c>
       <c r="F128" t="n">
         <v>544395</v>
@@ -3012,16 +3012,16 @@
         <v>44662</v>
       </c>
       <c r="B130" t="n">
-        <v>121.8659515380859</v>
+        <v>121.8659210205078</v>
       </c>
       <c r="C130" t="n">
-        <v>123.5702497029341</v>
+        <v>123.570218758567</v>
       </c>
       <c r="D130" t="n">
-        <v>119.3622123322183</v>
+        <v>119.3621824416246</v>
       </c>
       <c r="E130" t="n">
-        <v>122.9904344376963</v>
+        <v>122.990403638526</v>
       </c>
       <c r="F130" t="n">
         <v>348006</v>
@@ -3072,16 +3072,16 @@
         <v>44665</v>
       </c>
       <c r="B133" t="n">
-        <v>115.6022109985352</v>
+        <v>115.6022033691406</v>
       </c>
       <c r="C133" t="n">
-        <v>120.003519776927</v>
+        <v>120.0035118570594</v>
       </c>
       <c r="D133" t="n">
-        <v>114.7061475555975</v>
+        <v>114.7061399853404</v>
       </c>
       <c r="E133" t="n">
-        <v>119.7751004090118</v>
+        <v>119.7750925042192</v>
       </c>
       <c r="F133" t="n">
         <v>497156</v>
@@ -3132,16 +3132,16 @@
         <v>44671</v>
       </c>
       <c r="B136" t="n">
-        <v>113.9945526123047</v>
+        <v>113.9945373535156</v>
       </c>
       <c r="C136" t="n">
-        <v>116.5597799472992</v>
+        <v>116.5597643451405</v>
       </c>
       <c r="D136" t="n">
-        <v>112.9754992470936</v>
+        <v>112.9754841247104</v>
       </c>
       <c r="E136" t="n">
-        <v>114.5128796071169</v>
+        <v>114.5128642789469</v>
       </c>
       <c r="F136" t="n">
         <v>232622</v>
@@ -3152,16 +3152,16 @@
         <v>44673</v>
       </c>
       <c r="B137" t="n">
-        <v>107.7923126220703</v>
+        <v>107.7923049926758</v>
       </c>
       <c r="C137" t="n">
-        <v>111.56987810503</v>
+        <v>111.5698702082644</v>
       </c>
       <c r="D137" t="n">
-        <v>106.2988602418002</v>
+        <v>106.2988527181102</v>
       </c>
       <c r="E137" t="n">
-        <v>111.56987810503</v>
+        <v>111.5698702082644</v>
       </c>
       <c r="F137" t="n">
         <v>509466</v>
@@ -3172,16 +3172,16 @@
         <v>44676</v>
       </c>
       <c r="B138" t="n">
-        <v>111.5347442626953</v>
+        <v>111.5347366333008</v>
       </c>
       <c r="C138" t="n">
-        <v>111.8334387791802</v>
+        <v>111.8334311293538</v>
       </c>
       <c r="D138" t="n">
-        <v>105.9474644367544</v>
+        <v>105.9474571895508</v>
       </c>
       <c r="E138" t="n">
-        <v>106.2988669904352</v>
+        <v>106.2988597191943</v>
       </c>
       <c r="F138" t="n">
         <v>607459</v>
@@ -3212,16 +3212,16 @@
         <v>44678</v>
       </c>
       <c r="B140" t="n">
-        <v>104.5418548583984</v>
+        <v>104.541862487793</v>
       </c>
       <c r="C140" t="n">
-        <v>110.471749986921</v>
+        <v>110.4717580490753</v>
       </c>
       <c r="D140" t="n">
-        <v>104.0938164608919</v>
+        <v>104.0938240575889</v>
       </c>
       <c r="E140" t="n">
-        <v>109.5493191748392</v>
+        <v>109.5493271696751</v>
       </c>
       <c r="F140" t="n">
         <v>1036983</v>
@@ -3252,16 +3252,16 @@
         <v>44680</v>
       </c>
       <c r="B142" t="n">
-        <v>107.6341857910156</v>
+        <v>107.6341781616211</v>
       </c>
       <c r="C142" t="n">
-        <v>112.0969826885324</v>
+        <v>112.0969747428031</v>
       </c>
       <c r="D142" t="n">
-        <v>107.1773671750833</v>
+        <v>107.1773595780693</v>
       </c>
       <c r="E142" t="n">
-        <v>108.1173651272915</v>
+        <v>108.117357463648</v>
       </c>
       <c r="F142" t="n">
         <v>762051</v>
@@ -3272,16 +3272,16 @@
         <v>44683</v>
       </c>
       <c r="B143" t="n">
-        <v>107.168586730957</v>
+        <v>107.1685791015625</v>
       </c>
       <c r="C143" t="n">
-        <v>108.556623178466</v>
+        <v>108.5566154502563</v>
       </c>
       <c r="D143" t="n">
-        <v>104.4628023919814</v>
+        <v>104.4627949552132</v>
       </c>
       <c r="E143" t="n">
-        <v>107.1861605455792</v>
+        <v>107.1861529149336</v>
       </c>
       <c r="F143" t="n">
         <v>497573</v>
@@ -3312,16 +3312,16 @@
         <v>44685</v>
       </c>
       <c r="B145" t="n">
-        <v>94.52691650390625</v>
+        <v>94.52693176269531</v>
       </c>
       <c r="C145" t="n">
-        <v>100.4128903167997</v>
+        <v>100.4129065257185</v>
       </c>
       <c r="D145" t="n">
-        <v>84.54712241090455</v>
+        <v>84.54713605872841</v>
       </c>
       <c r="E145" t="n">
-        <v>100.4128903167997</v>
+        <v>100.4129065257185</v>
       </c>
       <c r="F145" t="n">
         <v>3193940</v>
@@ -3352,16 +3352,16 @@
         <v>44687</v>
       </c>
       <c r="B147" t="n">
-        <v>90.31011199951172</v>
+        <v>90.31010437011719</v>
       </c>
       <c r="C147" t="n">
-        <v>95.44056635451888</v>
+        <v>95.44055829170378</v>
       </c>
       <c r="D147" t="n">
-        <v>90.31011199951172</v>
+        <v>90.31010437011719</v>
       </c>
       <c r="E147" t="n">
-        <v>93.73626837240195</v>
+        <v>93.73626045356588</v>
       </c>
       <c r="F147" t="n">
         <v>602571</v>
@@ -3392,16 +3392,16 @@
         <v>44691</v>
       </c>
       <c r="B149" t="n">
-        <v>84.51198577880859</v>
+        <v>84.51199340820312</v>
       </c>
       <c r="C149" t="n">
-        <v>89.03627756179158</v>
+        <v>89.03628559962057</v>
       </c>
       <c r="D149" t="n">
-        <v>83.46657176820631</v>
+        <v>83.46657930322515</v>
       </c>
       <c r="E149" t="n">
-        <v>85.83852718329263</v>
+        <v>85.83853493244185</v>
       </c>
       <c r="F149" t="n">
         <v>595901</v>
@@ -3432,16 +3432,16 @@
         <v>44693</v>
       </c>
       <c r="B151" t="n">
-        <v>89.44917297363281</v>
+        <v>89.44916534423828</v>
       </c>
       <c r="C151" t="n">
-        <v>96.8110255181841</v>
+        <v>96.81101726087455</v>
       </c>
       <c r="D151" t="n">
-        <v>80.67293009796164</v>
+        <v>80.67292321711979</v>
       </c>
       <c r="E151" t="n">
-        <v>80.98040479984731</v>
+        <v>80.98039789278</v>
       </c>
       <c r="F151" t="n">
         <v>2304224</v>
@@ -3552,16 +3552,16 @@
         <v>44701</v>
       </c>
       <c r="B157" t="n">
-        <v>91.24132537841797</v>
+        <v>91.24131774902344</v>
       </c>
       <c r="C157" t="n">
-        <v>92.66450270218249</v>
+        <v>92.66449495378507</v>
       </c>
       <c r="D157" t="n">
-        <v>87.70095923422785</v>
+        <v>87.70095190087078</v>
       </c>
       <c r="E157" t="n">
-        <v>89.60730920380003</v>
+        <v>89.60730171103826</v>
       </c>
       <c r="F157" t="n">
         <v>709088</v>
@@ -3572,16 +3572,16 @@
         <v>44704</v>
       </c>
       <c r="B158" t="n">
-        <v>91.02169799804688</v>
+        <v>91.02169036865234</v>
       </c>
       <c r="C158" t="n">
-        <v>92.67328125477616</v>
+        <v>92.67327348694673</v>
       </c>
       <c r="D158" t="n">
-        <v>90.09926715053099</v>
+        <v>90.09925959845417</v>
       </c>
       <c r="E158" t="n">
-        <v>90.31011270007218</v>
+        <v>90.31010513032238</v>
       </c>
       <c r="F158" t="n">
         <v>925415</v>
@@ -3592,16 +3592,16 @@
         <v>44705</v>
       </c>
       <c r="B159" t="n">
-        <v>87.67459106445312</v>
+        <v>87.67460632324219</v>
       </c>
       <c r="C159" t="n">
-        <v>90.02019217113561</v>
+        <v>90.02020783815051</v>
       </c>
       <c r="D159" t="n">
-        <v>85.55739588330977</v>
+        <v>85.55741077362453</v>
       </c>
       <c r="E159" t="n">
-        <v>88.43010408571675</v>
+        <v>88.43011947599447</v>
       </c>
       <c r="F159" t="n">
         <v>569845</v>
@@ -3612,16 +3612,16 @@
         <v>44706</v>
       </c>
       <c r="B160" t="n">
-        <v>89.92356872558594</v>
+        <v>89.92357635498047</v>
       </c>
       <c r="C160" t="n">
-        <v>90.73178988696996</v>
+        <v>90.73179758493647</v>
       </c>
       <c r="D160" t="n">
-        <v>85.75067942410486</v>
+        <v>85.75068669945851</v>
       </c>
       <c r="E160" t="n">
-        <v>86.97179807297417</v>
+        <v>86.97180545193132</v>
       </c>
       <c r="F160" t="n">
         <v>958832</v>
@@ -3632,16 +3632,16 @@
         <v>44707</v>
       </c>
       <c r="B161" t="n">
-        <v>94.81684112548828</v>
+        <v>94.81683349609375</v>
       </c>
       <c r="C161" t="n">
-        <v>96.26637260046013</v>
+        <v>96.2663648544297</v>
       </c>
       <c r="D161" t="n">
-        <v>89.00993502024454</v>
+        <v>89.0099278581001</v>
       </c>
       <c r="E161" t="n">
-        <v>89.41404564738239</v>
+        <v>89.41403845272137</v>
       </c>
       <c r="F161" t="n">
         <v>700096</v>
@@ -3652,16 +3652,16 @@
         <v>44708</v>
       </c>
       <c r="B162" t="n">
-        <v>96.65290832519531</v>
+        <v>96.65289306640625</v>
       </c>
       <c r="C162" t="n">
-        <v>97.42599534445911</v>
+        <v>97.42597996362124</v>
       </c>
       <c r="D162" t="n">
-        <v>93.57814746844244</v>
+        <v>93.57813269507206</v>
       </c>
       <c r="E162" t="n">
-        <v>94.57086026318858</v>
+        <v>94.57084533309663</v>
       </c>
       <c r="F162" t="n">
         <v>410015</v>
@@ -3672,16 +3672,16 @@
         <v>44711</v>
       </c>
       <c r="B163" t="n">
-        <v>96.5474853515625</v>
+        <v>96.54747772216797</v>
       </c>
       <c r="C163" t="n">
-        <v>99.64860000764324</v>
+        <v>99.64859213319181</v>
       </c>
       <c r="D163" t="n">
-        <v>94.96617719997496</v>
+        <v>94.96616969553888</v>
       </c>
       <c r="E163" t="n">
-        <v>94.96617719997496</v>
+        <v>94.96616969553888</v>
       </c>
       <c r="F163" t="n">
         <v>123810</v>
@@ -3692,16 +3692,16 @@
         <v>44712</v>
       </c>
       <c r="B164" t="n">
-        <v>93.95590209960938</v>
+        <v>93.95589447021484</v>
       </c>
       <c r="C164" t="n">
-        <v>98.17271958139983</v>
+        <v>98.17271160959186</v>
       </c>
       <c r="D164" t="n">
-        <v>93.12132685126069</v>
+        <v>93.12131928963522</v>
       </c>
       <c r="E164" t="n">
-        <v>96.72318815313145</v>
+        <v>96.72318029902813</v>
       </c>
       <c r="F164" t="n">
         <v>435642</v>
@@ -3712,16 +3712,16 @@
         <v>44713</v>
       </c>
       <c r="B165" t="n">
-        <v>92.17253875732422</v>
+        <v>92.17253112792969</v>
       </c>
       <c r="C165" t="n">
-        <v>96.28393331547606</v>
+        <v>96.28392534576922</v>
       </c>
       <c r="D165" t="n">
-        <v>91.18861962704793</v>
+        <v>91.18861207909531</v>
       </c>
       <c r="E165" t="n">
-        <v>95.12430955304588</v>
+        <v>95.12430167932452</v>
       </c>
       <c r="F165" t="n">
         <v>372179</v>
@@ -3732,16 +3732,16 @@
         <v>44714</v>
       </c>
       <c r="B166" t="n">
-        <v>97.39962768554688</v>
+        <v>97.39963531494141</v>
       </c>
       <c r="C166" t="n">
-        <v>97.77738423457956</v>
+        <v>97.77739189356407</v>
       </c>
       <c r="D166" t="n">
-        <v>91.3818769180002</v>
+        <v>91.38188407601926</v>
       </c>
       <c r="E166" t="n">
-        <v>91.3818769180002</v>
+        <v>91.38188407601926</v>
       </c>
       <c r="F166" t="n">
         <v>432233</v>
@@ -3752,16 +3752,16 @@
         <v>44715</v>
       </c>
       <c r="B167" t="n">
-        <v>94.96617889404297</v>
+        <v>94.96617126464844</v>
       </c>
       <c r="C167" t="n">
-        <v>97.28542642277941</v>
+        <v>97.28541860706112</v>
       </c>
       <c r="D167" t="n">
-        <v>93.93833192839882</v>
+        <v>93.93832438157946</v>
       </c>
       <c r="E167" t="n">
-        <v>96.63533603883948</v>
+        <v>96.63532827534817</v>
       </c>
       <c r="F167" t="n">
         <v>452357</v>
@@ -3772,16 +3772,16 @@
         <v>44718</v>
       </c>
       <c r="B168" t="n">
-        <v>94.98374938964844</v>
+        <v>94.98374176025391</v>
       </c>
       <c r="C168" t="n">
-        <v>97.48748166813617</v>
+        <v>97.48747383763394</v>
       </c>
       <c r="D168" t="n">
-        <v>94.69384178307456</v>
+        <v>94.69383417696631</v>
       </c>
       <c r="E168" t="n">
-        <v>95.18580133184516</v>
+        <v>95.18579368622116</v>
       </c>
       <c r="F168" t="n">
         <v>540320</v>
@@ -3792,16 +3792,16 @@
         <v>44719</v>
       </c>
       <c r="B169" t="n">
-        <v>100.5710220336914</v>
+        <v>100.5710296630859</v>
       </c>
       <c r="C169" t="n">
-        <v>101.2035385362447</v>
+        <v>101.2035462136224</v>
       </c>
       <c r="D169" t="n">
-        <v>93.36729372419249</v>
+        <v>93.36730080710669</v>
       </c>
       <c r="E169" t="n">
-        <v>94.36000636076696</v>
+        <v>94.36001351898909</v>
       </c>
       <c r="F169" t="n">
         <v>669503</v>
@@ -3832,16 +3832,16 @@
         <v>44721</v>
       </c>
       <c r="B171" t="n">
-        <v>95.02767181396484</v>
+        <v>95.02765655517578</v>
       </c>
       <c r="C171" t="n">
-        <v>97.41720114473972</v>
+        <v>97.41718550225902</v>
       </c>
       <c r="D171" t="n">
-        <v>94.52692535144557</v>
+        <v>94.5269101730624</v>
       </c>
       <c r="E171" t="n">
-        <v>97.11851332961599</v>
+        <v>97.11849773509621</v>
       </c>
       <c r="F171" t="n">
         <v>459814</v>
@@ -3852,16 +3852,16 @@
         <v>44722</v>
       </c>
       <c r="B172" t="n">
-        <v>88.72879791259766</v>
+        <v>88.72880554199219</v>
       </c>
       <c r="C172" t="n">
-        <v>95.22972108034641</v>
+        <v>95.2297292687264</v>
       </c>
       <c r="D172" t="n">
-        <v>88.72879791259766</v>
+        <v>88.72880554199219</v>
       </c>
       <c r="E172" t="n">
-        <v>93.59570505783955</v>
+        <v>93.59571310571778</v>
       </c>
       <c r="F172" t="n">
         <v>588546</v>
@@ -3872,16 +3872,16 @@
         <v>44725</v>
       </c>
       <c r="B173" t="n">
-        <v>85.03910064697266</v>
+        <v>85.03908538818359</v>
       </c>
       <c r="C173" t="n">
-        <v>87.61311493408253</v>
+        <v>87.61309921343133</v>
       </c>
       <c r="D173" t="n">
-        <v>84.30994148351176</v>
+        <v>84.30992635555765</v>
       </c>
       <c r="E173" t="n">
-        <v>87.41105627702898</v>
+        <v>87.4110405926337</v>
       </c>
       <c r="F173" t="n">
         <v>846744</v>
@@ -3892,16 +3892,16 @@
         <v>44726</v>
       </c>
       <c r="B174" t="n">
-        <v>85.73310852050781</v>
+        <v>85.73310089111328</v>
       </c>
       <c r="C174" t="n">
-        <v>86.47105455993147</v>
+        <v>86.47104686486708</v>
       </c>
       <c r="D174" t="n">
-        <v>84.07273830986246</v>
+        <v>84.07273082822437</v>
       </c>
       <c r="E174" t="n">
-        <v>86.10208489144279</v>
+        <v>86.10207722921302</v>
       </c>
       <c r="F174" t="n">
         <v>502449</v>
@@ -3912,16 +3912,16 @@
         <v>44727</v>
       </c>
       <c r="B175" t="n">
-        <v>86.62918090820312</v>
+        <v>86.62918853759766</v>
       </c>
       <c r="C175" t="n">
-        <v>88.47403585796052</v>
+        <v>88.47404364983063</v>
       </c>
       <c r="D175" t="n">
-        <v>85.29385260189301</v>
+        <v>85.29386011368575</v>
       </c>
       <c r="E175" t="n">
-        <v>86.102080451479</v>
+        <v>86.10208803445202</v>
       </c>
       <c r="F175" t="n">
         <v>817586</v>
@@ -3932,16 +3932,16 @@
         <v>44729</v>
       </c>
       <c r="B176" t="n">
-        <v>84.51198577880859</v>
+        <v>84.51199340820312</v>
       </c>
       <c r="C176" t="n">
-        <v>86.43590949039935</v>
+        <v>86.4359172934778</v>
       </c>
       <c r="D176" t="n">
-        <v>83.73011864630146</v>
+        <v>83.73012620511224</v>
       </c>
       <c r="E176" t="n">
-        <v>84.07273427953736</v>
+        <v>84.07274186927806</v>
       </c>
       <c r="F176" t="n">
         <v>418487</v>
@@ -3952,16 +3952,16 @@
         <v>44732</v>
       </c>
       <c r="B177" t="n">
-        <v>83.89703369140625</v>
+        <v>83.89704132080078</v>
       </c>
       <c r="C177" t="n">
-        <v>85.54861686323618</v>
+        <v>85.54862464282172</v>
       </c>
       <c r="D177" t="n">
-        <v>82.53535140601245</v>
+        <v>82.53535891157887</v>
       </c>
       <c r="E177" t="n">
-        <v>84.51198308984139</v>
+        <v>84.51199077515794</v>
       </c>
       <c r="F177" t="n">
         <v>143101</v>
@@ -4012,16 +4012,16 @@
         <v>44735</v>
       </c>
       <c r="B180" t="n">
-        <v>89.34375</v>
+        <v>89.34375762939453</v>
       </c>
       <c r="C180" t="n">
-        <v>90.31888883979336</v>
+        <v>90.31889655245861</v>
       </c>
       <c r="D180" t="n">
-        <v>86.62039211422531</v>
+        <v>86.6203995110622</v>
       </c>
       <c r="E180" t="n">
-        <v>86.84001785827886</v>
+        <v>86.8400252738704</v>
       </c>
       <c r="F180" t="n">
         <v>839900</v>
@@ -4032,16 +4032,16 @@
         <v>44736</v>
       </c>
       <c r="B181" t="n">
-        <v>91.10075378417969</v>
+        <v>91.10076141357422</v>
       </c>
       <c r="C181" t="n">
-        <v>92.33065926209622</v>
+        <v>92.33066699449137</v>
       </c>
       <c r="D181" t="n">
-        <v>89.34374787356913</v>
+        <v>89.34375535582006</v>
       </c>
       <c r="E181" t="n">
-        <v>89.34374787356913</v>
+        <v>89.34375535582006</v>
       </c>
       <c r="F181" t="n">
         <v>487883</v>
@@ -4112,16 +4112,16 @@
         <v>44742</v>
       </c>
       <c r="B185" t="n">
-        <v>82.6934814453125</v>
+        <v>82.69348907470703</v>
       </c>
       <c r="C185" t="n">
-        <v>84.46806118289064</v>
+        <v>84.4680689760099</v>
       </c>
       <c r="D185" t="n">
-        <v>79.82077970708073</v>
+        <v>79.82078707143653</v>
       </c>
       <c r="E185" t="n">
-        <v>82.49142951731181</v>
+        <v>82.4914371280648</v>
       </c>
       <c r="F185" t="n">
         <v>710009</v>
@@ -4132,16 +4132,16 @@
         <v>44743</v>
       </c>
       <c r="B186" t="n">
-        <v>83.40506744384766</v>
+        <v>83.40507507324219</v>
       </c>
       <c r="C186" t="n">
-        <v>85.39047917144593</v>
+        <v>85.39048698245399</v>
       </c>
       <c r="D186" t="n">
-        <v>81.92918230422647</v>
+        <v>81.92918979861589</v>
       </c>
       <c r="E186" t="n">
-        <v>82.62320039929577</v>
+        <v>82.6232079571698</v>
       </c>
       <c r="F186" t="n">
         <v>500037</v>
@@ -4152,16 +4152,16 @@
         <v>44746</v>
       </c>
       <c r="B187" t="n">
-        <v>82.66712951660156</v>
+        <v>82.66713714599609</v>
       </c>
       <c r="C187" t="n">
-        <v>84.16058861200165</v>
+        <v>84.16059637922834</v>
       </c>
       <c r="D187" t="n">
-        <v>82.21909111773695</v>
+        <v>82.21909870578178</v>
       </c>
       <c r="E187" t="n">
-        <v>82.59684766924126</v>
+        <v>82.59685529214944</v>
       </c>
       <c r="F187" t="n">
         <v>102674</v>
@@ -4192,16 +4192,16 @@
         <v>44748</v>
       </c>
       <c r="B189" t="n">
-        <v>86.62039947509766</v>
+        <v>86.62039184570312</v>
       </c>
       <c r="C189" t="n">
-        <v>88.46525454143122</v>
+        <v>88.46524674954465</v>
       </c>
       <c r="D189" t="n">
-        <v>84.60862668431632</v>
+        <v>84.60861923211571</v>
       </c>
       <c r="E189" t="n">
-        <v>87.8415181796085</v>
+        <v>87.84151044265967</v>
       </c>
       <c r="F189" t="n">
         <v>788696</v>
@@ -4212,16 +4212,16 @@
         <v>44749</v>
       </c>
       <c r="B190" t="n">
-        <v>86.40076446533203</v>
+        <v>86.40077209472656</v>
       </c>
       <c r="C190" t="n">
-        <v>88.54431382481931</v>
+        <v>88.54432164349438</v>
       </c>
       <c r="D190" t="n">
-        <v>86.18992563237374</v>
+        <v>86.18993324315069</v>
       </c>
       <c r="E190" t="n">
-        <v>87.14749063816215</v>
+        <v>87.14749833349438</v>
       </c>
       <c r="F190" t="n">
         <v>483378</v>
@@ -4252,16 +4252,16 @@
         <v>44753</v>
       </c>
       <c r="B192" t="n">
-        <v>81.78862762451172</v>
+        <v>81.78861999511719</v>
       </c>
       <c r="C192" t="n">
-        <v>85.20600374431876</v>
+        <v>85.20599579614506</v>
       </c>
       <c r="D192" t="n">
-        <v>81.43722508546183</v>
+        <v>81.43721748884678</v>
       </c>
       <c r="E192" t="n">
-        <v>85.0303058260168</v>
+        <v>85.03029789423252</v>
       </c>
       <c r="F192" t="n">
         <v>432674</v>
@@ -4272,16 +4272,16 @@
         <v>44754</v>
       </c>
       <c r="B193" t="n">
-        <v>86.32170104980469</v>
+        <v>86.32170867919922</v>
       </c>
       <c r="C193" t="n">
-        <v>86.32170104980469</v>
+        <v>86.32170867919922</v>
       </c>
       <c r="D193" t="n">
-        <v>81.29666314380617</v>
+        <v>81.2966703290714</v>
       </c>
       <c r="E193" t="n">
-        <v>82.6232044643278</v>
+        <v>82.6232117668371</v>
       </c>
       <c r="F193" t="n">
         <v>730233</v>
@@ -4292,16 +4292,16 @@
         <v>44755</v>
       </c>
       <c r="B194" t="n">
-        <v>84.68769073486328</v>
+        <v>84.68768310546875</v>
       </c>
       <c r="C194" t="n">
-        <v>86.91908916427828</v>
+        <v>86.91908133386021</v>
       </c>
       <c r="D194" t="n">
-        <v>83.45778519155122</v>
+        <v>83.45777767295714</v>
       </c>
       <c r="E194" t="n">
-        <v>84.37142911794173</v>
+        <v>84.37142151703875</v>
       </c>
       <c r="F194" t="n">
         <v>1885043</v>
@@ -4312,16 +4312,16 @@
         <v>44756</v>
       </c>
       <c r="B195" t="n">
-        <v>81.44600677490234</v>
+        <v>81.44601440429688</v>
       </c>
       <c r="C195" t="n">
-        <v>85.20599828625562</v>
+        <v>85.20600626786458</v>
       </c>
       <c r="D195" t="n">
-        <v>81.35815782137873</v>
+        <v>81.35816544254408</v>
       </c>
       <c r="E195" t="n">
-        <v>84.3362822522144</v>
+        <v>84.33629015235336</v>
       </c>
       <c r="F195" t="n">
         <v>647308</v>
@@ -4332,16 +4332,16 @@
         <v>44757</v>
       </c>
       <c r="B196" t="n">
-        <v>82.85162353515625</v>
+        <v>82.85160827636719</v>
       </c>
       <c r="C196" t="n">
-        <v>84.72283938975517</v>
+        <v>84.72282378634415</v>
       </c>
       <c r="D196" t="n">
-        <v>81.20882706105454</v>
+        <v>81.20881210481942</v>
       </c>
       <c r="E196" t="n">
-        <v>82.27181498619288</v>
+        <v>82.27179983418721</v>
       </c>
       <c r="F196" t="n">
         <v>1850084</v>
@@ -4372,16 +4372,16 @@
         <v>44761</v>
       </c>
       <c r="B198" t="n">
-        <v>86.85758972167969</v>
+        <v>86.85758209228516</v>
       </c>
       <c r="C198" t="n">
-        <v>87.15627750971456</v>
+        <v>87.15626985408389</v>
       </c>
       <c r="D198" t="n">
-        <v>83.45778086715818</v>
+        <v>83.45777353639596</v>
       </c>
       <c r="E198" t="n">
-        <v>83.45778086715818</v>
+        <v>83.45777353639596</v>
       </c>
       <c r="F198" t="n">
         <v>493807</v>
@@ -4452,16 +4452,16 @@
         <v>44767</v>
       </c>
       <c r="B202" t="n">
-        <v>89.08021545410156</v>
+        <v>89.08020782470703</v>
       </c>
       <c r="C202" t="n">
-        <v>90.58245494699018</v>
+        <v>90.58244718893432</v>
       </c>
       <c r="D202" t="n">
-        <v>88.15778452046713</v>
+        <v>88.15777697007543</v>
       </c>
       <c r="E202" t="n">
-        <v>89.17685133105172</v>
+        <v>89.17684369338068</v>
       </c>
       <c r="F202" t="n">
         <v>343259</v>
@@ -4492,16 +4492,16 @@
         <v>44769</v>
       </c>
       <c r="B204" t="n">
-        <v>92.26038360595703</v>
+        <v>92.2603759765625</v>
       </c>
       <c r="C204" t="n">
-        <v>92.55907811606914</v>
+        <v>92.55907046197431</v>
       </c>
       <c r="D204" t="n">
-        <v>87.46375795252364</v>
+        <v>87.46375071978201</v>
       </c>
       <c r="E204" t="n">
-        <v>87.46375795252364</v>
+        <v>87.46375071978201</v>
       </c>
       <c r="F204" t="n">
         <v>673546</v>
@@ -4512,16 +4512,16 @@
         <v>44770</v>
       </c>
       <c r="B205" t="n">
-        <v>93.02468872070312</v>
+        <v>93.02468109130859</v>
       </c>
       <c r="C205" t="n">
-        <v>93.68356601735695</v>
+        <v>93.68355833392478</v>
       </c>
       <c r="D205" t="n">
-        <v>89.0274971066913</v>
+        <v>89.02748980512536</v>
       </c>
       <c r="E205" t="n">
-        <v>90.33647149513835</v>
+        <v>90.33646408621723</v>
       </c>
       <c r="F205" t="n">
         <v>529910</v>
@@ -4552,16 +4552,16 @@
         <v>44774</v>
       </c>
       <c r="B207" t="n">
-        <v>100.1493377685547</v>
+        <v>100.1493453979492</v>
       </c>
       <c r="C207" t="n">
-        <v>102.2841002364559</v>
+        <v>102.284108028477</v>
       </c>
       <c r="D207" t="n">
-        <v>94.35121955402224</v>
+        <v>94.3512267417151</v>
       </c>
       <c r="E207" t="n">
-        <v>94.35121955402224</v>
+        <v>94.3512267417151</v>
       </c>
       <c r="F207" t="n">
         <v>942663</v>
@@ -4572,16 +4572,16 @@
         <v>44775</v>
       </c>
       <c r="B208" t="n">
-        <v>101.4670944213867</v>
+        <v>101.4670867919922</v>
       </c>
       <c r="C208" t="n">
-        <v>102.2050337090955</v>
+        <v>102.2050260242147</v>
       </c>
       <c r="D208" t="n">
-        <v>98.69980868758699</v>
+        <v>98.69980126626697</v>
       </c>
       <c r="E208" t="n">
-        <v>100.0439171776608</v>
+        <v>100.0439096552761</v>
       </c>
       <c r="F208" t="n">
         <v>737331</v>
@@ -4692,16 +4692,16 @@
         <v>44783</v>
       </c>
       <c r="B214" t="n">
-        <v>90.87235260009766</v>
+        <v>90.87236022949219</v>
       </c>
       <c r="C214" t="n">
-        <v>103.6457870434117</v>
+        <v>103.6457957452289</v>
       </c>
       <c r="D214" t="n">
-        <v>90.32767832640604</v>
+        <v>90.32768591007121</v>
       </c>
       <c r="E214" t="n">
-        <v>103.6457870434117</v>
+        <v>103.6457957452289</v>
       </c>
       <c r="F214" t="n">
         <v>2607483</v>
@@ -4752,16 +4752,16 @@
         <v>44788</v>
       </c>
       <c r="B217" t="n">
-        <v>98.17271423339844</v>
+        <v>98.17272186279297</v>
       </c>
       <c r="C217" t="n">
-        <v>98.83159151013265</v>
+        <v>98.83159919073117</v>
       </c>
       <c r="D217" t="n">
-        <v>86.98058743595814</v>
+        <v>86.9805941955677</v>
       </c>
       <c r="E217" t="n">
-        <v>87.40226513969814</v>
+        <v>87.40227193207797</v>
       </c>
       <c r="F217" t="n">
         <v>1427504</v>
@@ -4772,16 +4772,16 @@
         <v>44789</v>
       </c>
       <c r="B218" t="n">
-        <v>94.96617889404297</v>
+        <v>94.96617126464844</v>
       </c>
       <c r="C218" t="n">
-        <v>98.40112905587054</v>
+        <v>98.40112115051892</v>
       </c>
       <c r="D218" t="n">
-        <v>92.8577702217972</v>
+        <v>92.85776276178804</v>
       </c>
       <c r="E218" t="n">
-        <v>98.1815032921459</v>
+        <v>98.18149540443858</v>
       </c>
       <c r="F218" t="n">
         <v>844810</v>
@@ -4792,16 +4792,16 @@
         <v>44790</v>
       </c>
       <c r="B219" t="n">
-        <v>96.52112579345703</v>
+        <v>96.5211181640625</v>
       </c>
       <c r="C219" t="n">
-        <v>96.67046969296776</v>
+        <v>96.67046205176851</v>
       </c>
       <c r="D219" t="n">
-        <v>93.29701473066473</v>
+        <v>93.29700735611611</v>
       </c>
       <c r="E219" t="n">
-        <v>93.29701473066473</v>
+        <v>93.29700735611611</v>
       </c>
       <c r="F219" t="n">
         <v>484266</v>
@@ -4832,16 +4832,16 @@
         <v>44792</v>
       </c>
       <c r="B221" t="n">
-        <v>92.81385040283203</v>
+        <v>92.81383514404297</v>
       </c>
       <c r="C221" t="n">
-        <v>96.35421669173961</v>
+        <v>96.35420085090701</v>
       </c>
       <c r="D221" t="n">
-        <v>92.34824484954395</v>
+        <v>92.34822966730141</v>
       </c>
       <c r="E221" t="n">
-        <v>95.79197526485062</v>
+        <v>95.79195951645167</v>
       </c>
       <c r="F221" t="n">
         <v>610732</v>
@@ -4892,16 +4892,16 @@
         <v>44797</v>
       </c>
       <c r="B224" t="n">
-        <v>101.0278396606445</v>
+        <v>101.0278472900391</v>
       </c>
       <c r="C224" t="n">
-        <v>102.8551274126588</v>
+        <v>102.855135180046</v>
       </c>
       <c r="D224" t="n">
-        <v>96.94279958605108</v>
+        <v>96.94280690695261</v>
       </c>
       <c r="E224" t="n">
-        <v>96.98672741470787</v>
+        <v>96.98673473892673</v>
       </c>
       <c r="F224" t="n">
         <v>1291806</v>
@@ -4912,16 +4912,16 @@
         <v>44798</v>
       </c>
       <c r="B225" t="n">
-        <v>99.56953430175781</v>
+        <v>99.56952667236328</v>
       </c>
       <c r="C225" t="n">
-        <v>103.1362613080438</v>
+        <v>103.1362534053532</v>
       </c>
       <c r="D225" t="n">
-        <v>98.6998181429413</v>
+        <v>98.69981058018772</v>
       </c>
       <c r="E225" t="n">
-        <v>101.9063556749261</v>
+        <v>101.9063478664755</v>
       </c>
       <c r="F225" t="n">
         <v>468543</v>
@@ -4932,16 +4932,16 @@
         <v>44799</v>
       </c>
       <c r="B226" t="n">
-        <v>95.02767181396484</v>
+        <v>95.02765655517578</v>
       </c>
       <c r="C226" t="n">
-        <v>100.7730824748128</v>
+        <v>100.7730662934713</v>
       </c>
       <c r="D226" t="n">
-        <v>94.66748905440703</v>
+        <v>94.66747385345326</v>
       </c>
       <c r="E226" t="n">
-        <v>100.3601849754213</v>
+        <v>100.3601688603796</v>
       </c>
       <c r="F226" t="n">
         <v>448340</v>
@@ -4952,16 +4952,16 @@
         <v>44802</v>
       </c>
       <c r="B227" t="n">
-        <v>91.77720642089844</v>
+        <v>91.77721405029297</v>
       </c>
       <c r="C227" t="n">
-        <v>95.84467276233583</v>
+        <v>95.84468072985686</v>
       </c>
       <c r="D227" t="n">
-        <v>91.23253216618707</v>
+        <v>91.23253975030309</v>
       </c>
       <c r="E227" t="n">
-        <v>93.56056637901798</v>
+        <v>93.56057415666235</v>
       </c>
       <c r="F227" t="n">
         <v>661048</v>
@@ -4972,16 +4972,16 @@
         <v>44803</v>
       </c>
       <c r="B228" t="n">
-        <v>89.34375</v>
+        <v>89.34375762939453</v>
       </c>
       <c r="C228" t="n">
-        <v>93.80654672775484</v>
+        <v>93.80655473824415</v>
       </c>
       <c r="D228" t="n">
-        <v>88.50038794712792</v>
+        <v>88.50039550450462</v>
       </c>
       <c r="E228" t="n">
-        <v>92.65570997369696</v>
+        <v>92.65571788591205</v>
       </c>
       <c r="F228" t="n">
         <v>477437</v>
@@ -4992,16 +4992,16 @@
         <v>44804</v>
       </c>
       <c r="B229" t="n">
-        <v>87.36712646484375</v>
+        <v>87.36711120605469</v>
       </c>
       <c r="C229" t="n">
-        <v>91.33796404163374</v>
+        <v>91.33794808933241</v>
       </c>
       <c r="D229" t="n">
-        <v>87.36712646484375</v>
+        <v>87.36711120605469</v>
       </c>
       <c r="E229" t="n">
-        <v>89.35254525323874</v>
+        <v>89.35252964769354</v>
       </c>
       <c r="F229" t="n">
         <v>588012</v>
@@ -5012,16 +5012,16 @@
         <v>44805</v>
       </c>
       <c r="B230" t="n">
-        <v>88.58824157714844</v>
+        <v>88.58823394775391</v>
       </c>
       <c r="C230" t="n">
-        <v>89.21198462131423</v>
+        <v>89.21197693820172</v>
       </c>
       <c r="D230" t="n">
-        <v>84.33629016516232</v>
+        <v>84.33628290195425</v>
       </c>
       <c r="E230" t="n">
-        <v>87.39348363272576</v>
+        <v>87.39347610622615</v>
       </c>
       <c r="F230" t="n">
         <v>1016578</v>
@@ -5092,16 +5092,16 @@
         <v>44812</v>
       </c>
       <c r="B234" t="n">
-        <v>88.28955841064453</v>
+        <v>88.28955078125</v>
       </c>
       <c r="C234" t="n">
-        <v>90.14320042192941</v>
+        <v>90.14319263235551</v>
       </c>
       <c r="D234" t="n">
-        <v>87.12993462797571</v>
+        <v>87.12992709878814</v>
       </c>
       <c r="E234" t="n">
-        <v>88.29834531801718</v>
+        <v>88.29833768786334</v>
       </c>
       <c r="F234" t="n">
         <v>707072</v>
@@ -5112,16 +5112,16 @@
         <v>44813</v>
       </c>
       <c r="B235" t="n">
-        <v>91.80356597900391</v>
+        <v>91.80355834960938</v>
       </c>
       <c r="C235" t="n">
-        <v>92.14618162206</v>
+        <v>92.14617396419217</v>
       </c>
       <c r="D235" t="n">
-        <v>88.81665435785808</v>
+        <v>88.81664697669278</v>
       </c>
       <c r="E235" t="n">
-        <v>88.81665435785808</v>
+        <v>88.81664697669278</v>
       </c>
       <c r="F235" t="n">
         <v>540504</v>
@@ -5132,16 +5132,16 @@
         <v>44816</v>
       </c>
       <c r="B236" t="n">
-        <v>94.79047393798828</v>
+        <v>94.79048156738281</v>
       </c>
       <c r="C236" t="n">
-        <v>94.79047393798828</v>
+        <v>94.79048156738281</v>
       </c>
       <c r="D236" t="n">
-        <v>91.34674382662909</v>
+        <v>91.34675117884834</v>
       </c>
       <c r="E236" t="n">
-        <v>91.34674382662909</v>
+        <v>91.34675117884834</v>
       </c>
       <c r="F236" t="n">
         <v>423751</v>
@@ -5152,16 +5152,16 @@
         <v>44817</v>
       </c>
       <c r="B237" t="n">
-        <v>90.74937438964844</v>
+        <v>90.74936676025391</v>
       </c>
       <c r="C237" t="n">
-        <v>92.94563217543426</v>
+        <v>92.94562436139803</v>
       </c>
       <c r="D237" t="n">
-        <v>90.4858207743754</v>
+        <v>90.48581316713809</v>
       </c>
       <c r="E237" t="n">
-        <v>91.36432388868973</v>
+        <v>91.36431620759575</v>
       </c>
       <c r="F237" t="n">
         <v>548480</v>
@@ -5172,16 +5172,16 @@
         <v>44818</v>
       </c>
       <c r="B238" t="n">
-        <v>90.13440704345703</v>
+        <v>90.13441467285156</v>
       </c>
       <c r="C238" t="n">
-        <v>91.77721007698068</v>
+        <v>91.77721784542967</v>
       </c>
       <c r="D238" t="n">
-        <v>88.15777528065119</v>
+        <v>88.15778274273444</v>
       </c>
       <c r="E238" t="n">
-        <v>90.17833487472001</v>
+        <v>90.1783425078328</v>
       </c>
       <c r="F238" t="n">
         <v>962834</v>
@@ -5252,16 +5252,16 @@
         <v>44824</v>
       </c>
       <c r="B242" t="n">
-        <v>89.88843536376953</v>
+        <v>89.88842010498047</v>
       </c>
       <c r="C242" t="n">
-        <v>91.25011782611443</v>
+        <v>91.25010233617633</v>
       </c>
       <c r="D242" t="n">
-        <v>88.50918578880611</v>
+        <v>88.50917076414814</v>
       </c>
       <c r="E242" t="n">
-        <v>88.77273939521048</v>
+        <v>88.77272432581363</v>
       </c>
       <c r="F242" t="n">
         <v>415549</v>
@@ -5272,16 +5272,16 @@
         <v>44825</v>
       </c>
       <c r="B243" t="n">
-        <v>89.51065826416016</v>
+        <v>89.51066589355469</v>
       </c>
       <c r="C243" t="n">
-        <v>91.22373620601748</v>
+        <v>91.2237439814253</v>
       </c>
       <c r="D243" t="n">
-        <v>87.51645966767896</v>
+        <v>87.51646712709899</v>
       </c>
       <c r="E243" t="n">
-        <v>90.16953542678914</v>
+        <v>90.16954311234272</v>
       </c>
       <c r="F243" t="n">
         <v>553017</v>
@@ -5292,16 +5292,16 @@
         <v>44826</v>
       </c>
       <c r="B244" t="n">
-        <v>89.08021545410156</v>
+        <v>89.08020782470703</v>
       </c>
       <c r="C244" t="n">
-        <v>91.53123990116616</v>
+        <v>91.53123206185035</v>
       </c>
       <c r="D244" t="n">
-        <v>86.27778842744067</v>
+        <v>86.27778103806376</v>
       </c>
       <c r="E244" t="n">
-        <v>89.43161803369786</v>
+        <v>89.43161037420698</v>
       </c>
       <c r="F244" t="n">
         <v>985794</v>
@@ -5352,16 +5352,16 @@
         <v>44831</v>
       </c>
       <c r="B247" t="n">
-        <v>86.48862457275391</v>
+        <v>86.48861694335938</v>
       </c>
       <c r="C247" t="n">
-        <v>88.9045080155956</v>
+        <v>88.90450017308949</v>
       </c>
       <c r="D247" t="n">
-        <v>84.68769730046709</v>
+        <v>84.68768982993723</v>
       </c>
       <c r="E247" t="n">
-        <v>85.22358470943861</v>
+        <v>85.22357719163666</v>
       </c>
       <c r="F247" t="n">
         <v>891547</v>
@@ -5372,16 +5372,16 @@
         <v>44832</v>
       </c>
       <c r="B248" t="n">
-        <v>86.94544982910156</v>
+        <v>86.94544219970703</v>
       </c>
       <c r="C248" t="n">
-        <v>88.52675133215702</v>
+        <v>88.52674356400453</v>
       </c>
       <c r="D248" t="n">
-        <v>85.29385976947805</v>
+        <v>85.29385228500924</v>
       </c>
       <c r="E248" t="n">
-        <v>86.5501194265028</v>
+        <v>86.5501118317982</v>
       </c>
       <c r="F248" t="n">
         <v>626382</v>
@@ -5392,16 +5392,16 @@
         <v>44833</v>
       </c>
       <c r="B249" t="n">
-        <v>87.27048492431641</v>
+        <v>87.27049255371094</v>
       </c>
       <c r="C249" t="n">
-        <v>87.79759208700698</v>
+        <v>87.79759976248249</v>
       </c>
       <c r="D249" t="n">
-        <v>84.51198603667193</v>
+        <v>84.51199342491191</v>
       </c>
       <c r="E249" t="n">
-        <v>85.39927594459202</v>
+        <v>85.399283410401</v>
       </c>
       <c r="F249" t="n">
         <v>546314</v>
@@ -5412,16 +5412,16 @@
         <v>44834</v>
       </c>
       <c r="B250" t="n">
-        <v>90.31011199951172</v>
+        <v>90.31010437011719</v>
       </c>
       <c r="C250" t="n">
-        <v>91.18861500844686</v>
+        <v>91.18860730483644</v>
       </c>
       <c r="D250" t="n">
-        <v>85.89123623451323</v>
+        <v>85.89122897842515</v>
       </c>
       <c r="E250" t="n">
-        <v>86.97179788457973</v>
+        <v>86.97179053720583</v>
       </c>
       <c r="F250" t="n">
         <v>846019</v>
@@ -5452,16 +5452,16 @@
         <v>44838</v>
       </c>
       <c r="B252" t="n">
-        <v>94.43906402587891</v>
+        <v>94.43907165527344</v>
       </c>
       <c r="C252" t="n">
-        <v>96.46840362900132</v>
+        <v>96.46841142233895</v>
       </c>
       <c r="D252" t="n">
-        <v>92.77869404106141</v>
+        <v>92.77870153632058</v>
       </c>
       <c r="E252" t="n">
-        <v>93.47271215307993</v>
+        <v>93.47271970440633</v>
       </c>
       <c r="F252" t="n">
         <v>828067</v>
@@ -5472,16 +5472,16 @@
         <v>44839</v>
       </c>
       <c r="B253" t="n">
-        <v>95.7568359375</v>
+        <v>95.75682830810547</v>
       </c>
       <c r="C253" t="n">
-        <v>97.74225477949469</v>
+        <v>97.74224699191255</v>
       </c>
       <c r="D253" t="n">
-        <v>93.46394235729625</v>
+        <v>93.46393491058726</v>
       </c>
       <c r="E253" t="n">
-        <v>94.30730451171824</v>
+        <v>94.30729699781466</v>
       </c>
       <c r="F253" t="n">
         <v>556734</v>
@@ -5492,16 +5492,16 @@
         <v>44840</v>
       </c>
       <c r="B254" t="n">
-        <v>99.09514617919922</v>
+        <v>99.09513854980469</v>
       </c>
       <c r="C254" t="n">
-        <v>99.89458046505639</v>
+        <v>99.89457277411294</v>
       </c>
       <c r="D254" t="n">
-        <v>94.70263095321427</v>
+        <v>94.70262366200211</v>
       </c>
       <c r="E254" t="n">
-        <v>95.71290409323375</v>
+        <v>95.71289672424005</v>
       </c>
       <c r="F254" t="n">
         <v>1317655</v>
@@ -5532,16 +5532,16 @@
         <v>44844</v>
       </c>
       <c r="B256" t="n">
-        <v>96.52112579345703</v>
+        <v>96.5211181640625</v>
       </c>
       <c r="C256" t="n">
-        <v>97.95308325233714</v>
+        <v>97.95307550975528</v>
       </c>
       <c r="D256" t="n">
-        <v>94.96617174989328</v>
+        <v>94.96616424340819</v>
       </c>
       <c r="E256" t="n">
-        <v>97.16242922191877</v>
+        <v>97.1624215418332</v>
       </c>
       <c r="F256" t="n">
         <v>391665</v>
@@ -5572,16 +5572,16 @@
         <v>44847</v>
       </c>
       <c r="B258" t="n">
-        <v>86.48862457275391</v>
+        <v>86.48861694335938</v>
       </c>
       <c r="C258" t="n">
-        <v>88.2983454548735</v>
+        <v>88.29833766583862</v>
       </c>
       <c r="D258" t="n">
-        <v>84.90732306799816</v>
+        <v>84.9073155780945</v>
       </c>
       <c r="E258" t="n">
-        <v>86.97180394230085</v>
+        <v>86.97179627028378</v>
       </c>
       <c r="F258" t="n">
         <v>1120971</v>
@@ -5612,16 +5612,16 @@
         <v>44851</v>
       </c>
       <c r="B260" t="n">
-        <v>83.01852416992188</v>
+        <v>83.01853942871094</v>
       </c>
       <c r="C260" t="n">
-        <v>85.90879951939036</v>
+        <v>85.90881530941148</v>
       </c>
       <c r="D260" t="n">
-        <v>82.82525245925146</v>
+        <v>82.82526768251721</v>
       </c>
       <c r="E260" t="n">
-        <v>84.32749161612804</v>
+        <v>84.32750711550507</v>
       </c>
       <c r="F260" t="n">
         <v>630186</v>
@@ -5632,16 +5632,16 @@
         <v>44852</v>
       </c>
       <c r="B261" t="n">
-        <v>80.54115295410156</v>
+        <v>80.54116058349609</v>
       </c>
       <c r="C261" t="n">
-        <v>85.61011216687361</v>
+        <v>85.61012027643372</v>
       </c>
       <c r="D261" t="n">
-        <v>79.24096560302623</v>
+        <v>79.24097310925836</v>
       </c>
       <c r="E261" t="n">
-        <v>84.42413449202566</v>
+        <v>84.42414248924207</v>
       </c>
       <c r="F261" t="n">
         <v>1514560</v>
@@ -5652,16 +5652,16 @@
         <v>44853</v>
       </c>
       <c r="B262" t="n">
-        <v>80.47087097167969</v>
+        <v>80.47087860107422</v>
       </c>
       <c r="C262" t="n">
-        <v>81.52507856055549</v>
+        <v>81.52508628989879</v>
       </c>
       <c r="D262" t="n">
-        <v>79.10919538524473</v>
+        <v>79.10920288553962</v>
       </c>
       <c r="E262" t="n">
-        <v>80.38302201488482</v>
+        <v>80.38302963595044</v>
       </c>
       <c r="F262" t="n">
         <v>1204425</v>
@@ -5672,16 +5672,16 @@
         <v>44854</v>
       </c>
       <c r="B263" t="n">
-        <v>77.81779479980469</v>
+        <v>77.81778717041016</v>
       </c>
       <c r="C263" t="n">
-        <v>80.72563748978079</v>
+        <v>80.72562957529622</v>
       </c>
       <c r="D263" t="n">
-        <v>76.50004034296538</v>
+        <v>76.50003284276583</v>
       </c>
       <c r="E263" t="n">
-        <v>80.4708708238317</v>
+        <v>80.4708629343249</v>
       </c>
       <c r="F263" t="n">
         <v>1064344</v>
@@ -5692,16 +5692,16 @@
         <v>44855</v>
       </c>
       <c r="B264" t="n">
-        <v>82.25423431396484</v>
+        <v>82.25422668457031</v>
       </c>
       <c r="C264" t="n">
-        <v>85.73310542506498</v>
+        <v>85.73309747299184</v>
       </c>
       <c r="D264" t="n">
-        <v>75.13836128205794</v>
+        <v>75.13835431268782</v>
       </c>
       <c r="E264" t="n">
-        <v>77.967142043229</v>
+        <v>77.96713481147866</v>
       </c>
       <c r="F264" t="n">
         <v>1421863</v>
@@ -5712,16 +5712,16 @@
         <v>44858</v>
       </c>
       <c r="B265" t="n">
-        <v>82.40357971191406</v>
+        <v>82.40358734130859</v>
       </c>
       <c r="C265" t="n">
-        <v>83.41385274639228</v>
+        <v>83.41386046932367</v>
       </c>
       <c r="D265" t="n">
-        <v>80.20732232836033</v>
+        <v>80.20732975441281</v>
       </c>
       <c r="E265" t="n">
-        <v>81.73591559062895</v>
+        <v>81.73592315820733</v>
       </c>
       <c r="F265" t="n">
         <v>718180</v>
@@ -5792,16 +5792,16 @@
         <v>44862</v>
       </c>
       <c r="B269" t="n">
-        <v>81.43722534179688</v>
+        <v>81.43721771240234</v>
       </c>
       <c r="C269" t="n">
-        <v>82.14003042210881</v>
+        <v>82.14002272687244</v>
       </c>
       <c r="D269" t="n">
-        <v>78.40639267564933</v>
+        <v>78.40638533019641</v>
       </c>
       <c r="E269" t="n">
-        <v>79.04770281411741</v>
+        <v>79.04769540858378</v>
       </c>
       <c r="F269" t="n">
         <v>705309</v>
@@ -5812,16 +5812,16 @@
         <v>44865</v>
       </c>
       <c r="B270" t="n">
-        <v>83.36994934082031</v>
+        <v>83.36994171142578</v>
       </c>
       <c r="C270" t="n">
-        <v>84.17817062117196</v>
+        <v>84.17816291781504</v>
       </c>
       <c r="D270" t="n">
-        <v>79.07406952167764</v>
+        <v>79.07406228540991</v>
       </c>
       <c r="E270" t="n">
-        <v>79.07406952167764</v>
+        <v>79.07406228540991</v>
       </c>
       <c r="F270" t="n">
         <v>956071</v>
@@ -5832,16 +5832,16 @@
         <v>44866</v>
       </c>
       <c r="B271" t="n">
-        <v>87.10357666015625</v>
+        <v>87.10356903076172</v>
       </c>
       <c r="C271" t="n">
-        <v>87.84151598729392</v>
+        <v>87.84150829326336</v>
       </c>
       <c r="D271" t="n">
-        <v>83.65984639528801</v>
+        <v>83.65983906752952</v>
       </c>
       <c r="E271" t="n">
-        <v>83.65984639528801</v>
+        <v>83.65983906752952</v>
       </c>
       <c r="F271" t="n">
         <v>1461617</v>
@@ -5852,16 +5852,16 @@
         <v>44868</v>
       </c>
       <c r="B272" t="n">
-        <v>86.58525848388672</v>
+        <v>86.58525085449219</v>
       </c>
       <c r="C272" t="n">
-        <v>88.4652544751398</v>
+        <v>88.46524668009084</v>
       </c>
       <c r="D272" t="n">
-        <v>84.04638520497635</v>
+        <v>84.04637779929271</v>
       </c>
       <c r="E272" t="n">
-        <v>85.59255245003042</v>
+        <v>85.59254490810744</v>
       </c>
       <c r="F272" t="n">
         <v>991113</v>
@@ -5872,16 +5872,16 @@
         <v>44869</v>
       </c>
       <c r="B273" t="n">
-        <v>83.484130859375</v>
+        <v>83.48414611816406</v>
       </c>
       <c r="C273" t="n">
-        <v>88.72879432924752</v>
+        <v>88.72881054662849</v>
       </c>
       <c r="D273" t="n">
-        <v>82.78133254952142</v>
+        <v>82.78134767985672</v>
       </c>
       <c r="E273" t="n">
-        <v>87.59552476569932</v>
+        <v>87.59554077594728</v>
       </c>
       <c r="F273" t="n">
         <v>612180</v>
@@ -5912,16 +5912,16 @@
         <v>44873</v>
       </c>
       <c r="B275" t="n">
-        <v>83.45777893066406</v>
+        <v>83.45778656005859</v>
       </c>
       <c r="C275" t="n">
-        <v>84.66133036601822</v>
+        <v>84.66133810543688</v>
       </c>
       <c r="D275" t="n">
-        <v>81.31422962176761</v>
+        <v>81.31423705520696</v>
       </c>
       <c r="E275" t="n">
-        <v>82.71105277545774</v>
+        <v>82.7110603365894</v>
       </c>
       <c r="F275" t="n">
         <v>953385</v>
@@ -5952,16 +5952,16 @@
         <v>44875</v>
       </c>
       <c r="B277" t="n">
-        <v>90.49459075927734</v>
+        <v>90.49459838867188</v>
       </c>
       <c r="C277" t="n">
-        <v>94.21944139071987</v>
+        <v>94.21944933414814</v>
       </c>
       <c r="D277" t="n">
-        <v>85.65403762792715</v>
+        <v>85.65404484922558</v>
       </c>
       <c r="E277" t="n">
-        <v>85.67160473785169</v>
+        <v>85.67161196063115</v>
       </c>
       <c r="F277" t="n">
         <v>2820385</v>
@@ -5972,16 +5972,16 @@
         <v>44876</v>
       </c>
       <c r="B278" t="n">
-        <v>89.57216644287109</v>
+        <v>89.57217407226562</v>
       </c>
       <c r="C278" t="n">
-        <v>91.51365729821109</v>
+        <v>91.51366509297395</v>
       </c>
       <c r="D278" t="n">
-        <v>88.06114018741653</v>
+        <v>88.06114768810795</v>
       </c>
       <c r="E278" t="n">
-        <v>90.4858103811098</v>
+        <v>90.48581808832483</v>
       </c>
       <c r="F278" t="n">
         <v>1123849</v>
@@ -6032,16 +6032,16 @@
         <v>44882</v>
       </c>
       <c r="B281" t="n">
-        <v>84.07273101806641</v>
+        <v>84.07273864746094</v>
       </c>
       <c r="C281" t="n">
-        <v>86.65553187836828</v>
+        <v>86.65553974214566</v>
       </c>
       <c r="D281" t="n">
-        <v>78.95106382910978</v>
+        <v>78.95107099372555</v>
       </c>
       <c r="E281" t="n">
-        <v>86.26020822533852</v>
+        <v>86.26021605324125</v>
       </c>
       <c r="F281" t="n">
         <v>1328887</v>
@@ -6052,16 +6052,16 @@
         <v>44883</v>
       </c>
       <c r="B282" t="n">
-        <v>82.07852935791016</v>
+        <v>82.07853698730469</v>
       </c>
       <c r="C282" t="n">
-        <v>86.7082368691072</v>
+        <v>86.70824492884405</v>
       </c>
       <c r="D282" t="n">
-        <v>81.44600617329941</v>
+        <v>81.44601374389941</v>
       </c>
       <c r="E282" t="n">
-        <v>85.21478456290053</v>
+        <v>85.21479248381745</v>
       </c>
       <c r="F282" t="n">
         <v>750376</v>
@@ -6092,16 +6092,16 @@
         <v>44887</v>
       </c>
       <c r="B284" t="n">
-        <v>78.23069000244141</v>
+        <v>78.23070526123047</v>
       </c>
       <c r="C284" t="n">
-        <v>80.67292711931084</v>
+        <v>80.67294285445492</v>
       </c>
       <c r="D284" t="n">
-        <v>76.64938201906415</v>
+        <v>76.64939696942126</v>
       </c>
       <c r="E284" t="n">
-        <v>80.04919083210247</v>
+        <v>80.04920644558763</v>
       </c>
       <c r="F284" t="n">
         <v>724710</v>
@@ -6112,16 +6112,16 @@
         <v>44888</v>
       </c>
       <c r="B285" t="n">
-        <v>77.27312469482422</v>
+        <v>77.27311706542969</v>
       </c>
       <c r="C285" t="n">
-        <v>78.7226560156857</v>
+        <v>78.72264824317485</v>
       </c>
       <c r="D285" t="n">
-        <v>75.99929799911189</v>
+        <v>75.99929049548588</v>
       </c>
       <c r="E285" t="n">
-        <v>78.0286378268503</v>
+        <v>78.02863012286181</v>
       </c>
       <c r="F285" t="n">
         <v>751617</v>
@@ -6172,16 +6172,16 @@
         <v>44893</v>
       </c>
       <c r="B288" t="n">
-        <v>75.56883239746094</v>
+        <v>75.56881713867188</v>
       </c>
       <c r="C288" t="n">
-        <v>78.2482694867974</v>
+        <v>78.24825368697887</v>
       </c>
       <c r="D288" t="n">
-        <v>75.28771167845241</v>
+        <v>75.28769647642699</v>
       </c>
       <c r="E288" t="n">
-        <v>77.14135372338092</v>
+        <v>77.1413381470698</v>
       </c>
       <c r="F288" t="n">
         <v>519110</v>
@@ -6312,16 +6312,16 @@
         <v>44902</v>
       </c>
       <c r="B295" t="n">
-        <v>76.15743255615234</v>
+        <v>76.15742492675781</v>
       </c>
       <c r="C295" t="n">
-        <v>78.43275226855985</v>
+        <v>78.4327444112255</v>
       </c>
       <c r="D295" t="n">
-        <v>74.76060920291299</v>
+        <v>74.76060171345117</v>
       </c>
       <c r="E295" t="n">
-        <v>77.82658301126293</v>
+        <v>77.82657521465414</v>
       </c>
       <c r="F295" t="n">
         <v>782541</v>
@@ -6332,16 +6332,16 @@
         <v>44903</v>
       </c>
       <c r="B296" t="n">
-        <v>72.38864898681641</v>
+        <v>72.38865661621094</v>
       </c>
       <c r="C296" t="n">
-        <v>76.73723618265012</v>
+        <v>76.73724427036358</v>
       </c>
       <c r="D296" t="n">
-        <v>72.03724644416056</v>
+        <v>72.03725403651906</v>
       </c>
       <c r="E296" t="n">
-        <v>76.73723618265012</v>
+        <v>76.73724427036358</v>
       </c>
       <c r="F296" t="n">
         <v>1116650</v>
@@ -6432,16 +6432,16 @@
         <v>44910</v>
       </c>
       <c r="B301" t="n">
-        <v>65.86137390136719</v>
+        <v>65.86138153076172</v>
       </c>
       <c r="C301" t="n">
-        <v>68.8482855742363</v>
+        <v>68.84829354963527</v>
       </c>
       <c r="D301" t="n">
-        <v>65.81744606844191</v>
+        <v>65.81745369274783</v>
       </c>
       <c r="E301" t="n">
-        <v>68.30361127721578</v>
+        <v>68.30361918951958</v>
       </c>
       <c r="F301" t="n">
         <v>806063</v>
@@ -6512,16 +6512,16 @@
         <v>44916</v>
       </c>
       <c r="B305" t="n">
-        <v>69.76193237304688</v>
+        <v>69.76192474365234</v>
       </c>
       <c r="C305" t="n">
-        <v>70.19239700292748</v>
+        <v>70.19238932645592</v>
       </c>
       <c r="D305" t="n">
-        <v>66.63445686972265</v>
+        <v>66.63444958235912</v>
       </c>
       <c r="E305" t="n">
-        <v>69.57744082922292</v>
+        <v>69.57743322000499</v>
       </c>
       <c r="F305" t="n">
         <v>349356</v>
@@ -6552,16 +6552,16 @@
         <v>44918</v>
       </c>
       <c r="B307" t="n">
-        <v>70.72827911376953</v>
+        <v>70.72828674316406</v>
       </c>
       <c r="C307" t="n">
-        <v>70.85126899880341</v>
+        <v>70.85127664146475</v>
       </c>
       <c r="D307" t="n">
-        <v>68.02248823813217</v>
+        <v>68.02249557565553</v>
       </c>
       <c r="E307" t="n">
-        <v>68.52323468504038</v>
+        <v>68.52324207657881</v>
       </c>
       <c r="F307" t="n">
         <v>762496</v>
@@ -6572,16 +6572,16 @@
         <v>44921</v>
       </c>
       <c r="B308" t="n">
-        <v>68.78678131103516</v>
+        <v>68.78678894042969</v>
       </c>
       <c r="C308" t="n">
-        <v>71.15873651385208</v>
+        <v>71.15874440632886</v>
       </c>
       <c r="D308" t="n">
-        <v>68.39145097560208</v>
+        <v>68.39145856114908</v>
       </c>
       <c r="E308" t="n">
-        <v>71.15873651385208</v>
+        <v>71.15874440632886</v>
       </c>
       <c r="F308" t="n">
         <v>122344</v>
@@ -6612,16 +6612,16 @@
         <v>44923</v>
       </c>
       <c r="B310" t="n">
-        <v>68.39145660400391</v>
+        <v>68.39144897460938</v>
       </c>
       <c r="C310" t="n">
-        <v>70.26267226700244</v>
+        <v>70.26266442886484</v>
       </c>
       <c r="D310" t="n">
-        <v>67.17912488761789</v>
+        <v>67.17911739346478</v>
       </c>
       <c r="E310" t="n">
-        <v>67.82042831857034</v>
+        <v>67.82042075287674</v>
       </c>
       <c r="F310" t="n">
         <v>543744</v>
@@ -6632,16 +6632,16 @@
         <v>44924</v>
       </c>
       <c r="B311" t="n">
-        <v>70.66678619384766</v>
+        <v>70.66677856445312</v>
       </c>
       <c r="C311" t="n">
-        <v>70.66678619384766</v>
+        <v>70.66677856445312</v>
       </c>
       <c r="D311" t="n">
-        <v>67.35482600257404</v>
+        <v>67.35481873074851</v>
       </c>
       <c r="E311" t="n">
-        <v>68.52323664628368</v>
+        <v>68.52322924831307</v>
       </c>
       <c r="F311" t="n">
         <v>1109758</v>
@@ -6652,16 +6652,16 @@
         <v>44928</v>
       </c>
       <c r="B312" t="n">
-        <v>66.42361450195312</v>
+        <v>66.42360687255859</v>
       </c>
       <c r="C312" t="n">
-        <v>69.7707088947915</v>
+        <v>69.77070088095081</v>
       </c>
       <c r="D312" t="n">
-        <v>66.12491998707712</v>
+        <v>66.12491239199053</v>
       </c>
       <c r="E312" t="n">
-        <v>68.88342566202327</v>
+        <v>68.88341775009563</v>
       </c>
       <c r="F312" t="n">
         <v>452524</v>
@@ -6732,16 +6732,16 @@
         <v>44932</v>
       </c>
       <c r="B316" t="n">
-        <v>68.31240081787109</v>
+        <v>68.31238555908203</v>
       </c>
       <c r="C316" t="n">
-        <v>68.31240081787109</v>
+        <v>68.31238555908203</v>
       </c>
       <c r="D316" t="n">
-        <v>65.62417685742929</v>
+        <v>65.62416219910284</v>
       </c>
       <c r="E316" t="n">
-        <v>65.99315324186605</v>
+        <v>65.99313850112217</v>
       </c>
       <c r="F316" t="n">
         <v>775272</v>
@@ -6812,16 +6812,16 @@
         <v>44938</v>
       </c>
       <c r="B320" t="n">
-        <v>74.93630981445312</v>
+        <v>74.93631744384766</v>
       </c>
       <c r="C320" t="n">
-        <v>75.89387488304087</v>
+        <v>75.89388260992675</v>
       </c>
       <c r="D320" t="n">
-        <v>71.29052096395313</v>
+        <v>71.29052822216363</v>
       </c>
       <c r="E320" t="n">
-        <v>72.90696329338618</v>
+        <v>72.90697071616947</v>
       </c>
       <c r="F320" t="n">
         <v>1386963</v>
@@ -6872,16 +6872,16 @@
         <v>44943</v>
       </c>
       <c r="B323" t="n">
-        <v>72.37985992431641</v>
+        <v>72.37985229492188</v>
       </c>
       <c r="C323" t="n">
-        <v>72.69612153304253</v>
+        <v>72.69611387031159</v>
       </c>
       <c r="D323" t="n">
-        <v>70.11332062926112</v>
+        <v>70.11331323877729</v>
       </c>
       <c r="E323" t="n">
-        <v>71.02696453197595</v>
+        <v>71.026957045187</v>
       </c>
       <c r="F323" t="n">
         <v>1038524</v>
@@ -6892,16 +6892,16 @@
         <v>44944</v>
       </c>
       <c r="B324" t="n">
-        <v>73.96994018554688</v>
+        <v>73.96994781494141</v>
       </c>
       <c r="C324" t="n">
-        <v>75.29648141767632</v>
+        <v>75.29648918389273</v>
       </c>
       <c r="D324" t="n">
-        <v>72.48527486857265</v>
+        <v>72.48528234483609</v>
       </c>
       <c r="E324" t="n">
-        <v>72.52041578824208</v>
+        <v>72.52042326813002</v>
       </c>
       <c r="F324" t="n">
         <v>881691</v>
@@ -6912,16 +6912,16 @@
         <v>44945</v>
       </c>
       <c r="B325" t="n">
-        <v>75.39311981201172</v>
+        <v>75.39312744140625</v>
       </c>
       <c r="C325" t="n">
-        <v>76.09592482419572</v>
+        <v>76.09593252471049</v>
       </c>
       <c r="D325" t="n">
-        <v>72.74004396078551</v>
+        <v>72.74005132170247</v>
       </c>
       <c r="E325" t="n">
-        <v>73.78545787079142</v>
+        <v>73.78546533749886</v>
       </c>
       <c r="F325" t="n">
         <v>951207</v>
@@ -6932,16 +6932,16 @@
         <v>44946</v>
       </c>
       <c r="B326" t="n">
-        <v>77.02714538574219</v>
+        <v>77.02713775634766</v>
       </c>
       <c r="C326" t="n">
-        <v>78.32733280988822</v>
+        <v>78.32732505171256</v>
       </c>
       <c r="D326" t="n">
-        <v>74.45313125821576</v>
+        <v>74.45312388377251</v>
       </c>
       <c r="E326" t="n">
-        <v>75.12079543290946</v>
+        <v>75.12078799233532</v>
       </c>
       <c r="F326" t="n">
         <v>766265</v>
@@ -6952,16 +6952,16 @@
         <v>44949</v>
       </c>
       <c r="B327" t="n">
-        <v>80.09311676025391</v>
+        <v>80.09310913085938</v>
       </c>
       <c r="C327" t="n">
-        <v>81.2088193216573</v>
+        <v>81.20881158598479</v>
       </c>
       <c r="D327" t="n">
-        <v>77.09742502080553</v>
+        <v>77.09741767677029</v>
       </c>
       <c r="E327" t="n">
-        <v>77.09742502080553</v>
+        <v>77.09741767677029</v>
       </c>
       <c r="F327" t="n">
         <v>1210224</v>
@@ -6972,16 +6972,16 @@
         <v>44950</v>
       </c>
       <c r="B328" t="n">
-        <v>80.33031463623047</v>
+        <v>80.33030700683594</v>
       </c>
       <c r="C328" t="n">
-        <v>81.29666657374428</v>
+        <v>81.2966588525702</v>
       </c>
       <c r="D328" t="n">
-        <v>78.64358382076644</v>
+        <v>78.64357635156964</v>
       </c>
       <c r="E328" t="n">
-        <v>81.29666657374428</v>
+        <v>81.2966588525702</v>
       </c>
       <c r="F328" t="n">
         <v>788120</v>
@@ -7052,16 +7052,16 @@
         <v>44956</v>
       </c>
       <c r="B332" t="n">
-        <v>80.84864044189453</v>
+        <v>80.84862518310547</v>
       </c>
       <c r="C332" t="n">
-        <v>81.99069717012495</v>
+        <v>81.99068169579233</v>
       </c>
       <c r="D332" t="n">
-        <v>78.90714936586031</v>
+        <v>78.90713447349425</v>
       </c>
       <c r="E332" t="n">
-        <v>81.17368900668549</v>
+        <v>81.17367368654911</v>
       </c>
       <c r="F332" t="n">
         <v>515927</v>
@@ -7072,16 +7072,16 @@
         <v>44957</v>
       </c>
       <c r="B333" t="n">
-        <v>78.84564971923828</v>
+        <v>78.84563446044922</v>
       </c>
       <c r="C333" t="n">
-        <v>81.68321755514636</v>
+        <v>81.68320174721033</v>
       </c>
       <c r="D333" t="n">
-        <v>78.84564971923828</v>
+        <v>78.84563446044922</v>
       </c>
       <c r="E333" t="n">
-        <v>80.83984871849243</v>
+        <v>80.83983307377135</v>
       </c>
       <c r="F333" t="n">
         <v>714873</v>
@@ -7212,16 +7212,16 @@
         <v>44966</v>
       </c>
       <c r="B340" t="n">
-        <v>72.64340972900391</v>
+        <v>72.64341735839844</v>
       </c>
       <c r="C340" t="n">
-        <v>76.30676535377293</v>
+        <v>76.30677336791243</v>
       </c>
       <c r="D340" t="n">
-        <v>72.33592834026705</v>
+        <v>72.33593593736826</v>
       </c>
       <c r="E340" t="n">
-        <v>74.92751601602691</v>
+        <v>74.92752388531035</v>
       </c>
       <c r="F340" t="n">
         <v>904775</v>
@@ -7292,16 +7292,16 @@
         <v>44972</v>
       </c>
       <c r="B344" t="n">
-        <v>73.78546142578125</v>
+        <v>73.78546905517578</v>
       </c>
       <c r="C344" t="n">
-        <v>74.93630485624141</v>
+        <v>74.93631260463282</v>
       </c>
       <c r="D344" t="n">
-        <v>71.65069897379257</v>
+        <v>71.65070638245331</v>
       </c>
       <c r="E344" t="n">
-        <v>72.23930104839484</v>
+        <v>72.23930851791685</v>
       </c>
       <c r="F344" t="n">
         <v>619864</v>
@@ -7352,16 +7352,16 @@
         <v>44979</v>
       </c>
       <c r="B347" t="n">
-        <v>59.92269515991211</v>
+        <v>59.92268371582031</v>
       </c>
       <c r="C347" t="n">
-        <v>60.25652392231935</v>
+        <v>60.25651241447263</v>
       </c>
       <c r="D347" t="n">
-        <v>58.28867887099064</v>
+        <v>58.28866773896478</v>
       </c>
       <c r="E347" t="n">
-        <v>58.85970722184112</v>
+        <v>58.85969598075974</v>
       </c>
       <c r="F347" t="n">
         <v>1166573</v>
@@ -7372,16 +7372,16 @@
         <v>44980</v>
       </c>
       <c r="B348" t="n">
-        <v>59.61521148681641</v>
+        <v>59.61521911621094</v>
       </c>
       <c r="C348" t="n">
-        <v>60.55520938725917</v>
+        <v>60.5552171369521</v>
       </c>
       <c r="D348" t="n">
-        <v>58.94754735957942</v>
+        <v>58.94755490352809</v>
       </c>
       <c r="E348" t="n">
-        <v>60.0017549345503</v>
+        <v>60.00176261341363</v>
       </c>
       <c r="F348" t="n">
         <v>572076</v>
@@ -7392,16 +7392,16 @@
         <v>44981</v>
       </c>
       <c r="B349" t="n">
-        <v>58.85091018676758</v>
+        <v>58.85091781616211</v>
       </c>
       <c r="C349" t="n">
-        <v>59.79969497237389</v>
+        <v>59.79970272476828</v>
       </c>
       <c r="D349" t="n">
-        <v>57.98998105728616</v>
+        <v>57.98998857507038</v>
       </c>
       <c r="E349" t="n">
-        <v>59.56250212719508</v>
+        <v>59.56250984883994</v>
       </c>
       <c r="F349" t="n">
         <v>780666</v>
@@ -7432,16 +7432,16 @@
         <v>44985</v>
       </c>
       <c r="B351" t="n">
-        <v>56.48774337768555</v>
+        <v>56.48773956298828</v>
       </c>
       <c r="C351" t="n">
-        <v>57.19932863514759</v>
+        <v>57.19932477239597</v>
       </c>
       <c r="D351" t="n">
-        <v>55.53017165976352</v>
+        <v>55.53016790973243</v>
       </c>
       <c r="E351" t="n">
-        <v>56.82157209178407</v>
+        <v>56.82156825454288</v>
       </c>
       <c r="F351" t="n">
         <v>573942</v>
@@ -7452,16 +7452,16 @@
         <v>44986</v>
       </c>
       <c r="B352" t="n">
-        <v>54.14214324951172</v>
+        <v>54.14213943481445</v>
       </c>
       <c r="C352" t="n">
-        <v>57.10269755356158</v>
+        <v>57.10269353027231</v>
       </c>
       <c r="D352" t="n">
-        <v>53.4129841183176</v>
+        <v>53.41298035499475</v>
       </c>
       <c r="E352" t="n">
-        <v>56.4877481070402</v>
+        <v>56.48774412707847</v>
       </c>
       <c r="F352" t="n">
         <v>634515</v>
@@ -7492,16 +7492,16 @@
         <v>44988</v>
       </c>
       <c r="B354" t="n">
-        <v>52.35877990722656</v>
+        <v>52.35877227783203</v>
       </c>
       <c r="C354" t="n">
-        <v>54.11578598936467</v>
+        <v>54.11577810395019</v>
       </c>
       <c r="D354" t="n">
-        <v>52.35877990722656</v>
+        <v>52.35877227783203</v>
       </c>
       <c r="E354" t="n">
-        <v>53.14943398467798</v>
+        <v>53.14942624007427</v>
       </c>
       <c r="F354" t="n">
         <v>443497</v>
@@ -7512,16 +7512,16 @@
         <v>44991</v>
       </c>
       <c r="B355" t="n">
-        <v>54.2827033996582</v>
+        <v>54.28269958496094</v>
       </c>
       <c r="C355" t="n">
-        <v>55.26662586165249</v>
+        <v>55.26662197781043</v>
       </c>
       <c r="D355" t="n">
-        <v>52.3851369759148</v>
+        <v>52.38513329456833</v>
       </c>
       <c r="E355" t="n">
-        <v>52.71018216089787</v>
+        <v>52.71017845670896</v>
       </c>
       <c r="F355" t="n">
         <v>1320672</v>
@@ -7532,16 +7532,16 @@
         <v>44992</v>
       </c>
       <c r="B356" t="n">
-        <v>54.52867889404297</v>
+        <v>54.52868270874023</v>
       </c>
       <c r="C356" t="n">
-        <v>54.57260337214876</v>
+        <v>54.57260718991888</v>
       </c>
       <c r="D356" t="n">
-        <v>53.02643962475403</v>
+        <v>53.0264433343582</v>
       </c>
       <c r="E356" t="n">
-        <v>54.28269913567225</v>
+        <v>54.28270293316135</v>
       </c>
       <c r="F356" t="n">
         <v>485619</v>
@@ -7552,16 +7552,16 @@
         <v>44993</v>
       </c>
       <c r="B357" t="n">
-        <v>58.67522048950195</v>
+        <v>58.67521286010742</v>
       </c>
       <c r="C357" t="n">
-        <v>58.67522048950195</v>
+        <v>58.67521286010742</v>
       </c>
       <c r="D357" t="n">
-        <v>53.975227083112</v>
+        <v>53.97522006484605</v>
       </c>
       <c r="E357" t="n">
-        <v>53.975227083112</v>
+        <v>53.97522006484605</v>
       </c>
       <c r="F357" t="n">
         <v>1672249</v>
@@ -7592,16 +7592,16 @@
         <v>44995</v>
       </c>
       <c r="B359" t="n">
-        <v>52.01616668701172</v>
+        <v>52.01616287231445</v>
       </c>
       <c r="C359" t="n">
-        <v>56.08363689549009</v>
+        <v>56.08363278249773</v>
       </c>
       <c r="D359" t="n">
-        <v>51.79654091648602</v>
+        <v>51.7965371178954</v>
       </c>
       <c r="E359" t="n">
-        <v>55.52139545914005</v>
+        <v>55.52139138738065</v>
       </c>
       <c r="F359" t="n">
         <v>846843</v>
@@ -7612,16 +7612,16 @@
         <v>44998</v>
       </c>
       <c r="B360" t="n">
-        <v>50.39093399047852</v>
+        <v>50.39093017578125</v>
       </c>
       <c r="C360" t="n">
-        <v>51.9634552076585</v>
+        <v>51.96345127391815</v>
       </c>
       <c r="D360" t="n">
-        <v>49.46850648556628</v>
+        <v>49.46850274069867</v>
       </c>
       <c r="E360" t="n">
-        <v>51.9634552076585</v>
+        <v>51.96345127391815</v>
       </c>
       <c r="F360" t="n">
         <v>1066340</v>
@@ -7632,16 +7632,16 @@
         <v>44999</v>
       </c>
       <c r="B361" t="n">
-        <v>50.32944107055664</v>
+        <v>50.32943725585938</v>
       </c>
       <c r="C361" t="n">
-        <v>52.78924896630146</v>
+        <v>52.78924496516417</v>
       </c>
       <c r="D361" t="n">
-        <v>49.55635744004602</v>
+        <v>49.55635368394428</v>
       </c>
       <c r="E361" t="n">
-        <v>50.84775800958192</v>
+        <v>50.84775415559906</v>
       </c>
       <c r="F361" t="n">
         <v>730632</v>
@@ -7672,16 +7672,16 @@
         <v>45001</v>
       </c>
       <c r="B363" t="n">
-        <v>53.81709289550781</v>
+        <v>53.81708908081055</v>
       </c>
       <c r="C363" t="n">
-        <v>54.24756084476554</v>
+        <v>54.24755699955558</v>
       </c>
       <c r="D363" t="n">
-        <v>50.10981247369315</v>
+        <v>50.10980892177768</v>
       </c>
       <c r="E363" t="n">
-        <v>50.68962432600123</v>
+        <v>50.68962073298718</v>
       </c>
       <c r="F363" t="n">
         <v>1144994</v>
@@ -7692,16 +7692,16 @@
         <v>45002</v>
       </c>
       <c r="B364" t="n">
-        <v>55.06456756591797</v>
+        <v>55.06457138061523</v>
       </c>
       <c r="C364" t="n">
-        <v>55.54774353916095</v>
+        <v>55.5477473873311</v>
       </c>
       <c r="D364" t="n">
-        <v>52.19186239249056</v>
+        <v>52.19186600817599</v>
       </c>
       <c r="E364" t="n">
-        <v>53.58868227771264</v>
+        <v>53.58868599016529</v>
       </c>
       <c r="F364" t="n">
         <v>1415773</v>
@@ -7712,16 +7712,16 @@
         <v>45005</v>
       </c>
       <c r="B365" t="n">
-        <v>52.49055480957031</v>
+        <v>52.49055099487305</v>
       </c>
       <c r="C365" t="n">
-        <v>55.60923982257214</v>
+        <v>55.60923578122764</v>
       </c>
       <c r="D365" t="n">
-        <v>52.18308009678171</v>
+        <v>52.18307630442985</v>
       </c>
       <c r="E365" t="n">
-        <v>54.03671863151492</v>
+        <v>54.03671470445178</v>
       </c>
       <c r="F365" t="n">
         <v>714391</v>
@@ -7732,16 +7732,16 @@
         <v>45006</v>
       </c>
       <c r="B366" t="n">
-        <v>54.65166854858398</v>
+        <v>54.65167236328125</v>
       </c>
       <c r="C366" t="n">
-        <v>54.73073394933856</v>
+        <v>54.73073776955461</v>
       </c>
       <c r="D366" t="n">
-        <v>52.65746641952787</v>
+        <v>52.65747009502944</v>
       </c>
       <c r="E366" t="n">
-        <v>52.65746641952787</v>
+        <v>52.65747009502944</v>
       </c>
       <c r="F366" t="n">
         <v>534854</v>
@@ -7752,16 +7752,16 @@
         <v>45007</v>
       </c>
       <c r="B367" t="n">
-        <v>52.56962203979492</v>
+        <v>52.56961822509766</v>
       </c>
       <c r="C367" t="n">
-        <v>55.12606575176405</v>
+        <v>55.1260617515593</v>
       </c>
       <c r="D367" t="n">
-        <v>52.56962203979492</v>
+        <v>52.56961822509766</v>
       </c>
       <c r="E367" t="n">
-        <v>53.85223567370974</v>
+        <v>53.85223176594004</v>
       </c>
       <c r="F367" t="n">
         <v>930770</v>
@@ -7772,16 +7772,16 @@
         <v>45008</v>
       </c>
       <c r="B368" t="n">
-        <v>49.19617080688477</v>
+        <v>49.1961669921875</v>
       </c>
       <c r="C368" t="n">
-        <v>53.29877844237178</v>
+        <v>53.29877430955613</v>
       </c>
       <c r="D368" t="n">
-        <v>48.85355515353253</v>
+        <v>48.85355136540186</v>
       </c>
       <c r="E368" t="n">
-        <v>52.56962265340579</v>
+        <v>52.56961857712928</v>
       </c>
       <c r="F368" t="n">
         <v>1208098</v>
@@ -7792,16 +7792,16 @@
         <v>45009</v>
       </c>
       <c r="B369" t="n">
-        <v>50.40850067138672</v>
+        <v>50.40850448608398</v>
       </c>
       <c r="C369" t="n">
-        <v>51.3660690297127</v>
+        <v>51.3660729168746</v>
       </c>
       <c r="D369" t="n">
-        <v>48.82719601713704</v>
+        <v>48.82719971216801</v>
       </c>
       <c r="E369" t="n">
-        <v>50.05709814767665</v>
+        <v>50.05710193578128</v>
       </c>
       <c r="F369" t="n">
         <v>598427</v>
@@ -7832,16 +7832,16 @@
         <v>45013</v>
       </c>
       <c r="B371" t="n">
-        <v>54.30905532836914</v>
+        <v>54.30905151367188</v>
       </c>
       <c r="C371" t="n">
-        <v>54.44961567467342</v>
+        <v>54.44961185010312</v>
       </c>
       <c r="D371" t="n">
-        <v>51.11130493652956</v>
+        <v>51.111301346444</v>
       </c>
       <c r="E371" t="n">
-        <v>51.83167713024186</v>
+        <v>51.83167348955698</v>
       </c>
       <c r="F371" t="n">
         <v>854484</v>
@@ -7852,16 +7852,16 @@
         <v>45014</v>
       </c>
       <c r="B372" t="n">
-        <v>53.88737487792969</v>
+        <v>53.88737106323242</v>
       </c>
       <c r="C372" t="n">
-        <v>54.64288800427434</v>
+        <v>54.64288413609415</v>
       </c>
       <c r="D372" t="n">
-        <v>52.91223599863476</v>
+        <v>52.91223225296775</v>
       </c>
       <c r="E372" t="n">
-        <v>54.38812132655848</v>
+        <v>54.38811747641328</v>
       </c>
       <c r="F372" t="n">
         <v>332515</v>
@@ -7872,16 +7872,16 @@
         <v>45015</v>
       </c>
       <c r="B373" t="n">
-        <v>54.20363235473633</v>
+        <v>54.20363616943359</v>
       </c>
       <c r="C373" t="n">
-        <v>56.3998863651218</v>
+        <v>56.39989033438518</v>
       </c>
       <c r="D373" t="n">
-        <v>53.72923996033548</v>
+        <v>53.72924374164636</v>
       </c>
       <c r="E373" t="n">
-        <v>54.03671465047152</v>
+        <v>54.0367184534216</v>
       </c>
       <c r="F373" t="n">
         <v>990197</v>
@@ -7892,16 +7892,16 @@
         <v>45016</v>
       </c>
       <c r="B374" t="n">
-        <v>52.33242034912109</v>
+        <v>52.33242416381836</v>
       </c>
       <c r="C374" t="n">
-        <v>54.73073299523703</v>
+        <v>54.73073698475589</v>
       </c>
       <c r="D374" t="n">
-        <v>51.94588025840541</v>
+        <v>51.94588404492639</v>
       </c>
       <c r="E374" t="n">
-        <v>54.20363256687721</v>
+        <v>54.20363651797383</v>
       </c>
       <c r="F374" t="n">
         <v>558868</v>
@@ -7912,16 +7912,16 @@
         <v>45019</v>
       </c>
       <c r="B375" t="n">
-        <v>49.41579055786133</v>
+        <v>49.41579437255859</v>
       </c>
       <c r="C375" t="n">
-        <v>52.67503567302858</v>
+        <v>52.67503973932627</v>
       </c>
       <c r="D375" t="n">
-        <v>49.41579055786133</v>
+        <v>49.41579437255859</v>
       </c>
       <c r="E375" t="n">
-        <v>52.34999052236814</v>
+        <v>52.34999456357366</v>
       </c>
       <c r="F375" t="n">
         <v>492395</v>
@@ -7992,16 +7992,16 @@
         <v>45026</v>
       </c>
       <c r="B379" t="n">
-        <v>48.75691986083984</v>
+        <v>48.75691604614258</v>
       </c>
       <c r="C379" t="n">
-        <v>49.21374185447558</v>
+        <v>49.21373800403698</v>
       </c>
       <c r="D379" t="n">
-        <v>48.01019359985681</v>
+        <v>48.01018984358273</v>
       </c>
       <c r="E379" t="n">
-        <v>48.32645188662934</v>
+        <v>48.3264481056115</v>
       </c>
       <c r="F379" t="n">
         <v>441343</v>
@@ -8032,16 +8032,16 @@
         <v>45028</v>
       </c>
       <c r="B381" t="n">
-        <v>56.73372268676758</v>
+        <v>56.73372650146484</v>
       </c>
       <c r="C381" t="n">
-        <v>57.69128769466669</v>
+        <v>57.69129157374931</v>
       </c>
       <c r="D381" t="n">
-        <v>54.3090526438428</v>
+        <v>54.3090562955086</v>
       </c>
       <c r="E381" t="n">
-        <v>54.55503239991062</v>
+        <v>54.55503606811576</v>
       </c>
       <c r="F381" t="n">
         <v>1443641</v>
@@ -8092,16 +8092,16 @@
         <v>45033</v>
       </c>
       <c r="B384" t="n">
-        <v>59.95783233642578</v>
+        <v>59.95782470703125</v>
       </c>
       <c r="C384" t="n">
-        <v>60.72213239227627</v>
+        <v>60.7221246656276</v>
       </c>
       <c r="D384" t="n">
-        <v>59.16717826182981</v>
+        <v>59.16717073304285</v>
       </c>
       <c r="E384" t="n">
-        <v>60.35315602250063</v>
+        <v>60.35314834280274</v>
       </c>
       <c r="F384" t="n">
         <v>288592</v>
@@ -8112,16 +8112,16 @@
         <v>45034</v>
       </c>
       <c r="B385" t="n">
-        <v>61.49521255493164</v>
+        <v>61.49520492553711</v>
       </c>
       <c r="C385" t="n">
-        <v>61.49521255493164</v>
+        <v>61.49520492553711</v>
       </c>
       <c r="D385" t="n">
-        <v>59.16717816771997</v>
+        <v>59.16717082715269</v>
       </c>
       <c r="E385" t="n">
-        <v>59.16717816771997</v>
+        <v>59.16717082715269</v>
       </c>
       <c r="F385" t="n">
         <v>581190</v>
@@ -8172,16 +8172,16 @@
         <v>45040</v>
       </c>
       <c r="B388" t="n">
-        <v>60.99446487426758</v>
+        <v>60.99446868896484</v>
       </c>
       <c r="C388" t="n">
-        <v>61.2755855722359</v>
+        <v>61.27558940451494</v>
       </c>
       <c r="D388" t="n">
-        <v>59.73820528906153</v>
+        <v>59.73820902519019</v>
       </c>
       <c r="E388" t="n">
-        <v>60.27409266682086</v>
+        <v>60.27409643646482</v>
       </c>
       <c r="F388" t="n">
         <v>315786</v>
@@ -8192,16 +8192,16 @@
         <v>45041</v>
       </c>
       <c r="B389" t="n">
-        <v>60.50250244140625</v>
+        <v>60.50251007080078</v>
       </c>
       <c r="C389" t="n">
-        <v>61.28436955477335</v>
+        <v>61.2843772827617</v>
       </c>
       <c r="D389" t="n">
-        <v>59.00904335897617</v>
+        <v>59.0090508000448</v>
       </c>
       <c r="E389" t="n">
-        <v>61.28436955477335</v>
+        <v>61.2843772827617</v>
       </c>
       <c r="F389" t="n">
         <v>695154</v>
@@ -8232,16 +8232,16 @@
         <v>45043</v>
       </c>
       <c r="B391" t="n">
-        <v>61.50399780273438</v>
+        <v>61.50400161743164</v>
       </c>
       <c r="C391" t="n">
-        <v>62.82175232193269</v>
+        <v>62.82175621836179</v>
       </c>
       <c r="D391" t="n">
-        <v>58.446804369118</v>
+        <v>58.44680799419723</v>
       </c>
       <c r="E391" t="n">
-        <v>58.59614827270675</v>
+        <v>58.59615190704881</v>
       </c>
       <c r="F391" t="n">
         <v>723893</v>
@@ -8252,16 +8252,16 @@
         <v>45044</v>
       </c>
       <c r="B392" t="n">
-        <v>63.67389297485352</v>
+        <v>63.67390441894531</v>
       </c>
       <c r="C392" t="n">
-        <v>63.75295501847341</v>
+        <v>63.75296647677501</v>
       </c>
       <c r="D392" t="n">
-        <v>60.6166999417585</v>
+        <v>60.61671083638181</v>
       </c>
       <c r="E392" t="n">
-        <v>61.50398974512687</v>
+        <v>61.50400079922254</v>
       </c>
       <c r="F392" t="n">
         <v>633625</v>
@@ -8272,16 +8272,16 @@
         <v>45048</v>
       </c>
       <c r="B393" t="n">
-        <v>58.38530731201172</v>
+        <v>58.38531112670898</v>
       </c>
       <c r="C393" t="n">
-        <v>63.16436567335623</v>
+        <v>63.16436980030091</v>
       </c>
       <c r="D393" t="n">
-        <v>58.38530731201172</v>
+        <v>58.38531112670898</v>
       </c>
       <c r="E393" t="n">
-        <v>63.16436567335623</v>
+        <v>63.16436980030091</v>
       </c>
       <c r="F393" t="n">
         <v>808928</v>
@@ -8292,16 +8292,16 @@
         <v>45049</v>
       </c>
       <c r="B394" t="n">
-        <v>58.85091018676758</v>
+        <v>58.85091781616211</v>
       </c>
       <c r="C394" t="n">
-        <v>60.08081564561515</v>
+        <v>60.08082343445384</v>
       </c>
       <c r="D394" t="n">
-        <v>58.77184813918982</v>
+        <v>58.7718557583348</v>
       </c>
       <c r="E394" t="n">
-        <v>59.12325065635277</v>
+        <v>59.12325832105335</v>
       </c>
       <c r="F394" t="n">
         <v>320277</v>
@@ -8352,16 +8352,16 @@
         <v>45054</v>
       </c>
       <c r="B397" t="n">
-        <v>65.16734313964844</v>
+        <v>65.16735076904297</v>
       </c>
       <c r="C397" t="n">
-        <v>65.74715154835417</v>
+        <v>65.74715924562913</v>
       </c>
       <c r="D397" t="n">
-        <v>63.59482219865949</v>
+        <v>63.59482964395288</v>
       </c>
       <c r="E397" t="n">
-        <v>63.76173988867773</v>
+        <v>63.76174735351282</v>
       </c>
       <c r="F397" t="n">
         <v>685640</v>
@@ -8372,16 +8372,16 @@
         <v>45055</v>
       </c>
       <c r="B398" t="n">
-        <v>66.17762756347656</v>
+        <v>66.17763519287109</v>
       </c>
       <c r="C398" t="n">
-        <v>67.59201782205866</v>
+        <v>67.59202561451346</v>
       </c>
       <c r="D398" t="n">
-        <v>64.157068136232</v>
+        <v>64.15707553268307</v>
       </c>
       <c r="E398" t="n">
-        <v>65.00921705378778</v>
+        <v>65.00922454848022</v>
       </c>
       <c r="F398" t="n">
         <v>730723</v>
@@ -8392,16 +8392,16 @@
         <v>45056</v>
       </c>
       <c r="B399" t="n">
-        <v>68.46174621582031</v>
+        <v>68.46173858642578</v>
       </c>
       <c r="C399" t="n">
-        <v>68.48810023618428</v>
+        <v>68.48809260385286</v>
       </c>
       <c r="D399" t="n">
-        <v>66.18641972266146</v>
+        <v>66.1864123468299</v>
       </c>
       <c r="E399" t="n">
-        <v>66.78380209321604</v>
+        <v>66.78379465081203</v>
       </c>
       <c r="F399" t="n">
         <v>406791</v>
@@ -8452,16 +8452,16 @@
         <v>45061</v>
       </c>
       <c r="B402" t="n">
-        <v>68.41781616210938</v>
+        <v>68.41780853271484</v>
       </c>
       <c r="C402" t="n">
-        <v>69.17332933280035</v>
+        <v>69.17332161915719</v>
       </c>
       <c r="D402" t="n">
-        <v>66.23913231833025</v>
+        <v>66.2391249318847</v>
       </c>
       <c r="E402" t="n">
-        <v>66.23913231833025</v>
+        <v>66.2391249318847</v>
       </c>
       <c r="F402" t="n">
         <v>689284</v>
@@ -8492,16 +8492,16 @@
         <v>45063</v>
       </c>
       <c r="B404" t="n">
-        <v>72.3271484375</v>
+        <v>72.32715606689453</v>
       </c>
       <c r="C404" t="n">
-        <v>73.79424673422444</v>
+        <v>73.79425451837514</v>
       </c>
       <c r="D404" t="n">
-        <v>67.6622932827093</v>
+        <v>67.66230042003383</v>
       </c>
       <c r="E404" t="n">
-        <v>69.41051895372132</v>
+        <v>69.4105262754566</v>
       </c>
       <c r="F404" t="n">
         <v>1084227</v>
@@ -8512,16 +8512,16 @@
         <v>45064</v>
       </c>
       <c r="B405" t="n">
-        <v>71.18509674072266</v>
+        <v>71.18508911132812</v>
       </c>
       <c r="C405" t="n">
-        <v>71.99331788899191</v>
+        <v>71.99331017297479</v>
       </c>
       <c r="D405" t="n">
-        <v>69.86734224584828</v>
+        <v>69.86733475768652</v>
       </c>
       <c r="E405" t="n">
-        <v>71.15874272321652</v>
+        <v>71.15873509664654</v>
       </c>
       <c r="F405" t="n">
         <v>796674</v>
@@ -8552,16 +8552,16 @@
         <v>45068</v>
       </c>
       <c r="B407" t="n">
-        <v>77.76508331298828</v>
+        <v>77.76507568359375</v>
       </c>
       <c r="C407" t="n">
-        <v>78.30975759078616</v>
+        <v>78.3097499079546</v>
       </c>
       <c r="D407" t="n">
-        <v>75.07686625350173</v>
+        <v>75.0768588878434</v>
       </c>
       <c r="E407" t="n">
-        <v>75.45462281500996</v>
+        <v>75.45461541229061</v>
       </c>
       <c r="F407" t="n">
         <v>873661</v>
@@ -8572,16 +8572,16 @@
         <v>45069</v>
       </c>
       <c r="B408" t="n">
-        <v>77.13256072998047</v>
+        <v>77.132568359375</v>
       </c>
       <c r="C408" t="n">
-        <v>80.43572695506535</v>
+        <v>80.43573491118516</v>
       </c>
       <c r="D408" t="n">
-        <v>76.42975569775851</v>
+        <v>76.42976325763665</v>
       </c>
       <c r="E408" t="n">
-        <v>77.74751010634054</v>
+        <v>77.74751779656141</v>
       </c>
       <c r="F408" t="n">
         <v>970823</v>
@@ -8632,16 +8632,16 @@
         <v>45072</v>
       </c>
       <c r="B411" t="n">
-        <v>82.75497436523438</v>
+        <v>82.75498199462891</v>
       </c>
       <c r="C411" t="n">
-        <v>84.15179752676379</v>
+        <v>84.15180528493505</v>
       </c>
       <c r="D411" t="n">
-        <v>80.38301910539758</v>
+        <v>80.38302651611544</v>
       </c>
       <c r="E411" t="n">
-        <v>81.70077351696148</v>
+        <v>81.70078104916651</v>
       </c>
       <c r="F411" t="n">
         <v>582166</v>
@@ -8672,16 +8672,16 @@
         <v>45076</v>
       </c>
       <c r="B413" t="n">
-        <v>80.5587158203125</v>
+        <v>80.55873107910156</v>
       </c>
       <c r="C413" t="n">
-        <v>84.13422246933848</v>
+        <v>84.13423840537149</v>
       </c>
       <c r="D413" t="n">
-        <v>79.39909222339719</v>
+        <v>79.3991072625396</v>
       </c>
       <c r="E413" t="n">
-        <v>82.54413431436818</v>
+        <v>82.54414994921937</v>
       </c>
       <c r="F413" t="n">
         <v>664894</v>
@@ -8712,16 +8712,16 @@
         <v>45078</v>
       </c>
       <c r="B415" t="n">
-        <v>79.15312194824219</v>
+        <v>79.15311431884766</v>
       </c>
       <c r="C415" t="n">
-        <v>80.0579790000172</v>
+        <v>80.05797128340549</v>
       </c>
       <c r="D415" t="n">
-        <v>78.45910374774334</v>
+        <v>78.45909618524368</v>
       </c>
       <c r="E415" t="n">
-        <v>79.07405989243097</v>
+        <v>79.07405227065705</v>
       </c>
       <c r="F415" t="n">
         <v>974431</v>
@@ -8752,16 +8752,16 @@
         <v>45082</v>
       </c>
       <c r="B417" t="n">
-        <v>82.02583312988281</v>
+        <v>82.02582550048828</v>
       </c>
       <c r="C417" t="n">
-        <v>82.8867623753632</v>
+        <v>82.88675466589184</v>
       </c>
       <c r="D417" t="n">
-        <v>79.88228351857445</v>
+        <v>79.88227608855597</v>
       </c>
       <c r="E417" t="n">
-        <v>82.8867623753632</v>
+        <v>82.88675466589184</v>
       </c>
       <c r="F417" t="n">
         <v>409729</v>
@@ -8772,16 +8772,16 @@
         <v>45083</v>
       </c>
       <c r="B418" t="n">
-        <v>83.89703369140625</v>
+        <v>83.89704132080078</v>
       </c>
       <c r="C418" t="n">
-        <v>86.708240516318</v>
+        <v>86.70824840135691</v>
       </c>
       <c r="D418" t="n">
-        <v>81.92040200757731</v>
+        <v>81.92040945722171</v>
       </c>
       <c r="E418" t="n">
-        <v>82.01703787053793</v>
+        <v>82.01704532897017</v>
       </c>
       <c r="F418" t="n">
         <v>1573579</v>
@@ -8792,16 +8792,16 @@
         <v>45084</v>
       </c>
       <c r="B419" t="n">
-        <v>86.52376556396484</v>
+        <v>86.52375793457031</v>
       </c>
       <c r="C419" t="n">
-        <v>86.60283432560681</v>
+        <v>86.60282668924023</v>
       </c>
       <c r="D419" t="n">
-        <v>82.88676338715122</v>
+        <v>82.88675607845614</v>
       </c>
       <c r="E419" t="n">
-        <v>84.33629479441962</v>
+        <v>84.3362873579094</v>
       </c>
       <c r="F419" t="n">
         <v>2805750</v>
@@ -8812,16 +8812,16 @@
         <v>45086</v>
       </c>
       <c r="B420" t="n">
-        <v>87.92935943603516</v>
+        <v>87.92936706542969</v>
       </c>
       <c r="C420" t="n">
-        <v>90.98655273412886</v>
+        <v>90.98656062878784</v>
       </c>
       <c r="D420" t="n">
-        <v>86.98058131812988</v>
+        <v>86.98058886520148</v>
       </c>
       <c r="E420" t="n">
-        <v>86.98058131812988</v>
+        <v>86.98058886520148</v>
       </c>
       <c r="F420" t="n">
         <v>1309381</v>
@@ -8832,16 +8832,16 @@
         <v>45089</v>
       </c>
       <c r="B421" t="n">
-        <v>90.35404205322266</v>
+        <v>90.35403442382812</v>
       </c>
       <c r="C421" t="n">
-        <v>91.34675484094018</v>
+        <v>91.34674712772208</v>
       </c>
       <c r="D421" t="n">
-        <v>87.95573235530614</v>
+        <v>87.95572492842221</v>
       </c>
       <c r="E421" t="n">
-        <v>87.95573235530614</v>
+        <v>87.95572492842221</v>
       </c>
       <c r="F421" t="n">
         <v>1071620</v>
@@ -8872,16 +8872,16 @@
         <v>45091</v>
       </c>
       <c r="B423" t="n">
-        <v>89.40525054931641</v>
+        <v>89.40524291992188</v>
       </c>
       <c r="C423" t="n">
-        <v>89.44039147486313</v>
+        <v>89.44038384246984</v>
       </c>
       <c r="D423" t="n">
-        <v>87.26170771053611</v>
+        <v>87.26170026406075</v>
       </c>
       <c r="E423" t="n">
-        <v>87.54282841246366</v>
+        <v>87.54282094199888</v>
       </c>
       <c r="F423" t="n">
         <v>605932</v>
@@ -8892,16 +8892,16 @@
         <v>45092</v>
       </c>
       <c r="B424" t="n">
-        <v>91.97925567626953</v>
+        <v>91.97927093505859</v>
       </c>
       <c r="C424" t="n">
-        <v>92.26037635061984</v>
+        <v>92.26039165604509</v>
       </c>
       <c r="D424" t="n">
-        <v>89.18561604259341</v>
+        <v>89.18563083793495</v>
       </c>
       <c r="E424" t="n">
-        <v>89.4316024972898</v>
+        <v>89.43161733343898</v>
       </c>
       <c r="F424" t="n">
         <v>844482</v>
@@ -8932,16 +8932,16 @@
         <v>45096</v>
       </c>
       <c r="B426" t="n">
-        <v>98.03215026855469</v>
+        <v>98.03214263916016</v>
       </c>
       <c r="C426" t="n">
-        <v>98.33963169216599</v>
+        <v>98.33962403884159</v>
       </c>
       <c r="D426" t="n">
-        <v>94.14916846996442</v>
+        <v>94.14916114276463</v>
       </c>
       <c r="E426" t="n">
-        <v>94.61477400522099</v>
+        <v>94.61476664178524</v>
       </c>
       <c r="F426" t="n">
         <v>576522</v>
@@ -8992,16 +8992,16 @@
         <v>45099</v>
       </c>
       <c r="B429" t="n">
-        <v>99.27083587646484</v>
+        <v>99.27084350585938</v>
       </c>
       <c r="C429" t="n">
-        <v>104.858115316858</v>
+        <v>104.8581233756592</v>
       </c>
       <c r="D429" t="n">
-        <v>99.18298691971819</v>
+        <v>99.18299454236116</v>
       </c>
       <c r="E429" t="n">
-        <v>102.9605456793905</v>
+        <v>102.9605535923553</v>
       </c>
       <c r="F429" t="n">
         <v>1144936</v>
@@ -9032,16 +9032,16 @@
         <v>45103</v>
       </c>
       <c r="B431" t="n">
-        <v>97.00430297851562</v>
+        <v>97.00429534912109</v>
       </c>
       <c r="C431" t="n">
-        <v>99.27084240484157</v>
+        <v>99.27083459718358</v>
       </c>
       <c r="D431" t="n">
-        <v>95.75683028431621</v>
+        <v>95.75682275303549</v>
       </c>
       <c r="E431" t="n">
-        <v>98.46262122570784</v>
+        <v>98.46261348161649</v>
       </c>
       <c r="F431" t="n">
         <v>757098</v>
@@ -9052,16 +9052,16 @@
         <v>45104</v>
       </c>
       <c r="B432" t="n">
-        <v>94.86954498291016</v>
+        <v>94.86952972412109</v>
       </c>
       <c r="C432" t="n">
-        <v>98.37477707017537</v>
+        <v>98.37476124760583</v>
       </c>
       <c r="D432" t="n">
-        <v>91.40824743272303</v>
+        <v>91.40823273064802</v>
       </c>
       <c r="E432" t="n">
-        <v>96.97795369874004</v>
+        <v>96.97793810083515</v>
       </c>
       <c r="F432" t="n">
         <v>1484061</v>
@@ -9132,16 +9132,16 @@
         <v>45110</v>
       </c>
       <c r="B436" t="n">
-        <v>100.8960647583008</v>
+        <v>100.8960723876953</v>
       </c>
       <c r="C436" t="n">
-        <v>101.4670930292576</v>
+        <v>101.4671007018312</v>
       </c>
       <c r="D436" t="n">
-        <v>98.26055584844994</v>
+        <v>98.26056327855684</v>
       </c>
       <c r="E436" t="n">
-        <v>98.46261448061463</v>
+        <v>98.46262192600048</v>
       </c>
       <c r="F436" t="n">
         <v>512630</v>
@@ -9152,16 +9152,16 @@
         <v>45111</v>
       </c>
       <c r="B437" t="n">
-        <v>100.6764526367188</v>
+        <v>100.6764373779297</v>
       </c>
       <c r="C437" t="n">
-        <v>101.1508451089678</v>
+        <v>101.1508297782785</v>
       </c>
       <c r="D437" t="n">
-        <v>99.4201929516278</v>
+        <v>99.42017788324077</v>
       </c>
       <c r="E437" t="n">
-        <v>101.0278552127306</v>
+        <v>101.0278399006821</v>
       </c>
       <c r="F437" t="n">
         <v>210288</v>
@@ -9252,16 +9252,16 @@
         <v>45118</v>
       </c>
       <c r="B442" t="n">
-        <v>99.7100830078125</v>
+        <v>99.71009063720703</v>
       </c>
       <c r="C442" t="n">
-        <v>99.7100830078125</v>
+        <v>99.71009063720703</v>
       </c>
       <c r="D442" t="n">
-        <v>94.74654009028252</v>
+        <v>94.7465473398877</v>
       </c>
       <c r="E442" t="n">
-        <v>97.71588429673227</v>
+        <v>97.71589177353913</v>
       </c>
       <c r="F442" t="n">
         <v>867229</v>
@@ -9312,16 +9312,16 @@
         <v>45121</v>
       </c>
       <c r="B445" t="n">
-        <v>96.74074554443359</v>
+        <v>96.74075317382812</v>
       </c>
       <c r="C445" t="n">
-        <v>98.69980333468348</v>
+        <v>98.69981111857781</v>
       </c>
       <c r="D445" t="n">
-        <v>95.02766080096731</v>
+        <v>95.02766829526057</v>
       </c>
       <c r="E445" t="n">
-        <v>98.69980333468348</v>
+        <v>98.69981111857781</v>
       </c>
       <c r="F445" t="n">
         <v>461646</v>
@@ -9332,16 +9332,16 @@
         <v>45124</v>
       </c>
       <c r="B446" t="n">
-        <v>99.48167419433594</v>
+        <v>99.48168182373047</v>
       </c>
       <c r="C446" t="n">
-        <v>99.48167419433594</v>
+        <v>99.48168182373047</v>
       </c>
       <c r="D446" t="n">
-        <v>95.75682348764802</v>
+        <v>95.75683083137832</v>
       </c>
       <c r="E446" t="n">
-        <v>96.44205473012244</v>
+        <v>96.44206212640412</v>
       </c>
       <c r="F446" t="n">
         <v>395417</v>
@@ -9392,16 +9392,16 @@
         <v>45127</v>
       </c>
       <c r="B449" t="n">
-        <v>106.9138107299805</v>
+        <v>106.913818359375</v>
       </c>
       <c r="C449" t="n">
-        <v>107.2740001714642</v>
+        <v>107.2740078265619</v>
       </c>
       <c r="D449" t="n">
-        <v>100.3601792578093</v>
+        <v>100.3601864195351</v>
       </c>
       <c r="E449" t="n">
-        <v>100.4919560462166</v>
+        <v>100.4919632173461</v>
       </c>
       <c r="F449" t="n">
         <v>1906043</v>
@@ -9432,16 +9432,16 @@
         <v>45131</v>
       </c>
       <c r="B451" t="n">
-        <v>112.6240844726562</v>
+        <v>112.6240768432617</v>
       </c>
       <c r="C451" t="n">
-        <v>113.1160440190282</v>
+        <v>113.1160363563073</v>
       </c>
       <c r="D451" t="n">
-        <v>109.3033441297533</v>
+        <v>109.3033367253127</v>
       </c>
       <c r="E451" t="n">
-        <v>110.85829822838</v>
+        <v>110.8582907186036</v>
       </c>
       <c r="F451" t="n">
         <v>870351</v>
@@ -9452,16 +9452,16 @@
         <v>45132</v>
       </c>
       <c r="B452" t="n">
-        <v>112.1584777832031</v>
+        <v>112.1584701538086</v>
       </c>
       <c r="C452" t="n">
-        <v>115.3298741884703</v>
+        <v>115.3298663433468</v>
       </c>
       <c r="D452" t="n">
-        <v>110.5859565895362</v>
+        <v>110.5859490671098</v>
       </c>
       <c r="E452" t="n">
-        <v>112.9491385358792</v>
+        <v>112.9491308527013</v>
       </c>
       <c r="F452" t="n">
         <v>603712</v>
@@ -9472,16 +9472,16 @@
         <v>45133</v>
       </c>
       <c r="B453" t="n">
-        <v>113.8891372680664</v>
+        <v>113.8891296386719</v>
       </c>
       <c r="C453" t="n">
-        <v>113.9857731418005</v>
+        <v>113.9857655059323</v>
       </c>
       <c r="D453" t="n">
-        <v>110.5508229266728</v>
+        <v>110.5508155209108</v>
       </c>
       <c r="E453" t="n">
-        <v>111.0427892027134</v>
+        <v>111.0427817639948</v>
       </c>
       <c r="F453" t="n">
         <v>810223</v>
@@ -9492,16 +9492,16 @@
         <v>45134</v>
       </c>
       <c r="B454" t="n">
-        <v>110.7440872192383</v>
+        <v>110.7440948486328</v>
       </c>
       <c r="C454" t="n">
-        <v>114.6446427257238</v>
+        <v>114.6446506238359</v>
       </c>
       <c r="D454" t="n">
-        <v>109.7074534000573</v>
+        <v>109.7074609580359</v>
       </c>
       <c r="E454" t="n">
-        <v>113.5025861325351</v>
+        <v>113.5025939519685</v>
       </c>
       <c r="F454" t="n">
         <v>678181</v>
@@ -9532,16 +9532,16 @@
         <v>45138</v>
       </c>
       <c r="B456" t="n">
-        <v>111.8246383666992</v>
+        <v>111.8246459960938</v>
       </c>
       <c r="C456" t="n">
-        <v>115.0838834211262</v>
+        <v>115.0838912728874</v>
       </c>
       <c r="D456" t="n">
-        <v>110.7792177389309</v>
+        <v>110.7792252970001</v>
       </c>
       <c r="E456" t="n">
-        <v>112.6416463567943</v>
+        <v>112.6416540419304</v>
       </c>
       <c r="F456" t="n">
         <v>524630</v>
@@ -9612,16 +9612,16 @@
         <v>45142</v>
       </c>
       <c r="B460" t="n">
-        <v>113.1336135864258</v>
+        <v>113.1336059570312</v>
       </c>
       <c r="C460" t="n">
-        <v>114.6007119660374</v>
+        <v>114.6007042377062</v>
       </c>
       <c r="D460" t="n">
-        <v>110.9900641534965</v>
+        <v>110.9900566686566</v>
       </c>
       <c r="E460" t="n">
-        <v>114.2053883028904</v>
+        <v>114.2053806012186</v>
       </c>
       <c r="F460" t="n">
         <v>805649</v>
@@ -9692,16 +9692,16 @@
         <v>45148</v>
       </c>
       <c r="B464" t="n">
-        <v>110.5156784057617</v>
+        <v>110.5156860351562</v>
       </c>
       <c r="C464" t="n">
-        <v>114.5919317277774</v>
+        <v>114.5919396385741</v>
       </c>
       <c r="D464" t="n">
-        <v>109.2857728839157</v>
+        <v>109.2857804284043</v>
       </c>
       <c r="E464" t="n">
-        <v>111.7455772251619</v>
+        <v>111.7455849394619</v>
       </c>
       <c r="F464" t="n">
         <v>733254</v>
@@ -9732,16 +9732,16 @@
         <v>45152</v>
       </c>
       <c r="B466" t="n">
-        <v>113.0633392333984</v>
+        <v>113.0633316040039</v>
       </c>
       <c r="C466" t="n">
-        <v>113.0633392333984</v>
+        <v>113.0633316040039</v>
       </c>
       <c r="D466" t="n">
-        <v>106.3779305234</v>
+        <v>106.3779233451298</v>
       </c>
       <c r="E466" t="n">
-        <v>108.9431645091783</v>
+        <v>108.9431571578088</v>
       </c>
       <c r="F466" t="n">
         <v>1213584</v>
@@ -9812,16 +9812,16 @@
         <v>45156</v>
       </c>
       <c r="B470" t="n">
-        <v>109.1539993286133</v>
+        <v>109.1539916992188</v>
       </c>
       <c r="C470" t="n">
-        <v>109.2242811782168</v>
+        <v>109.2242735439098</v>
       </c>
       <c r="D470" t="n">
-        <v>104.6912024154841</v>
+        <v>104.6911950980199</v>
       </c>
       <c r="E470" t="n">
-        <v>106.2549367057079</v>
+        <v>106.2549292789454</v>
       </c>
       <c r="F470" t="n">
         <v>1642163</v>
@@ -9932,16 +9932,16 @@
         <v>45166</v>
       </c>
       <c r="B476" t="n">
-        <v>110.9549331665039</v>
+        <v>110.9549255371094</v>
       </c>
       <c r="C476" t="n">
-        <v>111.4820336335469</v>
+        <v>111.4820259679083</v>
       </c>
       <c r="D476" t="n">
-        <v>109.5493229844612</v>
+        <v>109.5493154517181</v>
       </c>
       <c r="E476" t="n">
-        <v>110.3399770362487</v>
+        <v>110.3399694491393</v>
       </c>
       <c r="F476" t="n">
         <v>1603475</v>
@@ -9952,16 +9952,16 @@
         <v>45167</v>
       </c>
       <c r="B477" t="n">
-        <v>113.3180999755859</v>
+        <v>113.3181076049805</v>
       </c>
       <c r="C477" t="n">
-        <v>113.3620143990293</v>
+        <v>113.3620220313805</v>
       </c>
       <c r="D477" t="n">
-        <v>109.4263249492729</v>
+        <v>109.426332316645</v>
       </c>
       <c r="E477" t="n">
-        <v>112.0091257586069</v>
+        <v>112.0091332998718</v>
       </c>
       <c r="F477" t="n">
         <v>768114</v>
@@ -10012,16 +10012,16 @@
         <v>45170</v>
       </c>
       <c r="B480" t="n">
-        <v>113.7397842407227</v>
+        <v>113.7397918701172</v>
       </c>
       <c r="C480" t="n">
-        <v>115.5670720854272</v>
+        <v>115.5670798373918</v>
       </c>
       <c r="D480" t="n">
-        <v>109.320915232503</v>
+        <v>109.3209225654903</v>
       </c>
       <c r="E480" t="n">
-        <v>110.2609131724079</v>
+        <v>110.260920568448</v>
       </c>
       <c r="F480" t="n">
         <v>5149038</v>
@@ -10032,16 +10032,16 @@
         <v>45173</v>
       </c>
       <c r="B481" t="n">
-        <v>113.3268890380859</v>
+        <v>113.3268814086914</v>
       </c>
       <c r="C481" t="n">
-        <v>115.4704385414185</v>
+        <v>115.4704307677159</v>
       </c>
       <c r="D481" t="n">
-        <v>112.711939608005</v>
+        <v>112.7119320200101</v>
       </c>
       <c r="E481" t="n">
-        <v>114.3020279218186</v>
+        <v>114.3020202267758</v>
       </c>
       <c r="F481" t="n">
         <v>279175</v>
@@ -10072,16 +10072,16 @@
         <v>45175</v>
       </c>
       <c r="B483" t="n">
-        <v>110.3311996459961</v>
+        <v>110.3311920166016</v>
       </c>
       <c r="C483" t="n">
-        <v>113.1072726222884</v>
+        <v>113.1072648009286</v>
       </c>
       <c r="D483" t="n">
-        <v>108.3106465643086</v>
+        <v>108.3106390746352</v>
       </c>
       <c r="E483" t="n">
-        <v>110.471763357303</v>
+        <v>110.4717557181885</v>
       </c>
       <c r="F483" t="n">
         <v>1014845</v>
@@ -10092,16 +10092,16 @@
         <v>45177</v>
       </c>
       <c r="B484" t="n">
-        <v>108.5126800537109</v>
+        <v>108.5126953125</v>
       </c>
       <c r="C484" t="n">
-        <v>110.7967930565939</v>
+        <v>110.7968086365694</v>
       </c>
       <c r="D484" t="n">
-        <v>106.7293201603019</v>
+        <v>106.7293351683192</v>
       </c>
       <c r="E484" t="n">
-        <v>109.8128673522375</v>
+        <v>109.8128827938557</v>
       </c>
       <c r="F484" t="n">
         <v>972821</v>
@@ -10192,16 +10192,16 @@
         <v>45184</v>
       </c>
       <c r="B489" t="n">
-        <v>114.455078125</v>
+        <v>114.4550857543945</v>
       </c>
       <c r="C489" t="n">
-        <v>117.9365011778736</v>
+        <v>117.9365090393343</v>
       </c>
       <c r="D489" t="n">
-        <v>111.6573468239327</v>
+        <v>111.6573542668349</v>
       </c>
       <c r="E489" t="n">
-        <v>113.0697058036241</v>
+        <v>113.0697133406719</v>
       </c>
       <c r="F489" t="n">
         <v>1700134</v>
@@ -10252,16 +10252,16 @@
         <v>45189</v>
       </c>
       <c r="B492" t="n">
-        <v>110.0201034545898</v>
+        <v>110.0200958251953</v>
       </c>
       <c r="C492" t="n">
-        <v>112.5479547578543</v>
+        <v>112.5479469531647</v>
       </c>
       <c r="D492" t="n">
-        <v>110.0201034545898</v>
+        <v>110.0200958251953</v>
       </c>
       <c r="E492" t="n">
-        <v>111.711333930094</v>
+        <v>111.7113261834204</v>
       </c>
       <c r="F492" t="n">
         <v>472827</v>
@@ -10292,16 +10292,16 @@
         <v>45191</v>
       </c>
       <c r="B494" t="n">
-        <v>103.8129119873047</v>
+        <v>103.8129043579102</v>
       </c>
       <c r="C494" t="n">
-        <v>105.8639805269635</v>
+        <v>105.8639727468323</v>
       </c>
       <c r="D494" t="n">
-        <v>103.2011891892186</v>
+        <v>103.2011816047806</v>
       </c>
       <c r="E494" t="n">
-        <v>105.0903309039916</v>
+        <v>105.0903231807173</v>
       </c>
       <c r="F494" t="n">
         <v>394595</v>
@@ -10332,16 +10332,16 @@
         <v>45195</v>
       </c>
       <c r="B496" t="n">
-        <v>101.5549240112305</v>
+        <v>101.554931640625</v>
       </c>
       <c r="C496" t="n">
-        <v>103.8129014901132</v>
+        <v>103.8129092891401</v>
       </c>
       <c r="D496" t="n">
-        <v>100.862241302414</v>
+        <v>100.8622488797702</v>
       </c>
       <c r="E496" t="n">
-        <v>101.6538796643958</v>
+        <v>101.6538873012245</v>
       </c>
       <c r="F496" t="n">
         <v>1664293</v>
@@ -10352,16 +10352,16 @@
         <v>45196</v>
       </c>
       <c r="B497" t="n">
-        <v>100.0346145629883</v>
+        <v>100.0346221923828</v>
       </c>
       <c r="C497" t="n">
-        <v>103.4440686203892</v>
+        <v>103.4440765098144</v>
       </c>
       <c r="D497" t="n">
-        <v>98.6942245801429</v>
+        <v>98.69423210730918</v>
       </c>
       <c r="E497" t="n">
-        <v>101.6628805369675</v>
+        <v>101.6628882905459</v>
       </c>
       <c r="F497" t="n">
         <v>938220</v>
@@ -10372,16 +10372,16 @@
         <v>45197</v>
       </c>
       <c r="B498" t="n">
-        <v>104.352653503418</v>
+        <v>104.3526611328125</v>
       </c>
       <c r="C498" t="n">
-        <v>104.352653503418</v>
+        <v>104.3526611328125</v>
       </c>
       <c r="D498" t="n">
-        <v>99.09904044902891</v>
+        <v>99.09904769432313</v>
       </c>
       <c r="E498" t="n">
-        <v>100.7542861412311</v>
+        <v>100.7542935075431</v>
       </c>
       <c r="F498" t="n">
         <v>896625</v>
@@ -10392,16 +10392,16 @@
         <v>45198</v>
       </c>
       <c r="B499" t="n">
-        <v>104.2177124023438</v>
+        <v>104.2177200317383</v>
       </c>
       <c r="C499" t="n">
-        <v>107.0514280468401</v>
+        <v>107.0514358836805</v>
       </c>
       <c r="D499" t="n">
-        <v>103.4080783805818</v>
+        <v>103.408085950706</v>
       </c>
       <c r="E499" t="n">
-        <v>107.0514280468401</v>
+        <v>107.0514358836805</v>
       </c>
       <c r="F499" t="n">
         <v>323662</v>
@@ -10412,16 +10412,16 @@
         <v>45201</v>
       </c>
       <c r="B500" t="n">
-        <v>103.7769317626953</v>
+        <v>103.7769241333008</v>
       </c>
       <c r="C500" t="n">
-        <v>105.6570757137529</v>
+        <v>105.6570679461354</v>
       </c>
       <c r="D500" t="n">
-        <v>102.1396746273053</v>
+        <v>102.1396671182774</v>
       </c>
       <c r="E500" t="n">
-        <v>104.2267277544326</v>
+        <v>104.2267200919703</v>
       </c>
       <c r="F500" t="n">
         <v>495726</v>
@@ -10452,16 +10452,16 @@
         <v>45203</v>
       </c>
       <c r="B502" t="n">
-        <v>101.7978210449219</v>
+        <v>101.7978134155273</v>
       </c>
       <c r="C502" t="n">
-        <v>102.1666501489935</v>
+        <v>102.1666424919565</v>
       </c>
       <c r="D502" t="n">
-        <v>98.96410523328106</v>
+        <v>98.96409781626373</v>
       </c>
       <c r="E502" t="n">
-        <v>99.85469927807969</v>
+        <v>99.85469179431541</v>
       </c>
       <c r="F502" t="n">
         <v>483635</v>
@@ -10512,16 +10512,16 @@
         <v>45208</v>
       </c>
       <c r="B505" t="n">
-        <v>100.9611968994141</v>
+        <v>100.9612045288086</v>
       </c>
       <c r="C505" t="n">
-        <v>101.6718684250738</v>
+        <v>101.6718761081721</v>
       </c>
       <c r="D505" t="n">
-        <v>99.18899984705422</v>
+        <v>99.18900734252807</v>
       </c>
       <c r="E505" t="n">
-        <v>101.1051280272665</v>
+        <v>101.1051356675376</v>
       </c>
       <c r="F505" t="n">
         <v>728058</v>
@@ -10532,16 +10532,16 @@
         <v>45209</v>
       </c>
       <c r="B506" t="n">
-        <v>101.8337936401367</v>
+        <v>101.8338012695312</v>
       </c>
       <c r="C506" t="n">
-        <v>103.0932235900104</v>
+        <v>103.0932313137615</v>
       </c>
       <c r="D506" t="n">
-        <v>100.4574192217539</v>
+        <v>100.4574267480303</v>
       </c>
       <c r="E506" t="n">
-        <v>100.4574192217539</v>
+        <v>100.4574267480303</v>
       </c>
       <c r="F506" t="n">
         <v>501957</v>
@@ -10612,16 +10612,16 @@
         <v>45216</v>
       </c>
       <c r="B510" t="n">
-        <v>97.14693450927734</v>
+        <v>97.14691925048828</v>
       </c>
       <c r="C510" t="n">
-        <v>97.86661082758212</v>
+        <v>97.86659545575409</v>
       </c>
       <c r="D510" t="n">
-        <v>95.20381943120169</v>
+        <v>95.20380447761612</v>
       </c>
       <c r="E510" t="n">
-        <v>96.69713852617237</v>
+        <v>96.69712333803238</v>
       </c>
       <c r="F510" t="n">
         <v>593712</v>
@@ -10632,16 +10632,16 @@
         <v>45217</v>
       </c>
       <c r="B511" t="n">
-        <v>93.69249725341797</v>
+        <v>93.6925048828125</v>
       </c>
       <c r="C511" t="n">
-        <v>96.61617091268285</v>
+        <v>96.61617878015257</v>
       </c>
       <c r="D511" t="n">
-        <v>92.6759540193504</v>
+        <v>92.67596156596765</v>
       </c>
       <c r="E511" t="n">
-        <v>96.61617091268285</v>
+        <v>96.61617878015257</v>
       </c>
       <c r="F511" t="n">
         <v>964239</v>
@@ -10652,16 +10652,16 @@
         <v>45218</v>
       </c>
       <c r="B512" t="n">
-        <v>94.34919738769531</v>
+        <v>94.34920501708984</v>
       </c>
       <c r="C512" t="n">
-        <v>95.99545223608963</v>
+        <v>95.9954599986059</v>
       </c>
       <c r="D512" t="n">
-        <v>92.76592056203434</v>
+        <v>92.76592806339976</v>
       </c>
       <c r="E512" t="n">
-        <v>93.46760115621116</v>
+        <v>93.46760871431685</v>
       </c>
       <c r="F512" t="n">
         <v>760940</v>
@@ -10812,16 +10812,16 @@
         <v>45230</v>
       </c>
       <c r="B520" t="n">
-        <v>91.32656860351562</v>
+        <v>91.32656097412109</v>
       </c>
       <c r="C520" t="n">
-        <v>91.32656860351562</v>
+        <v>91.32656097412109</v>
       </c>
       <c r="D520" t="n">
-        <v>88.72674850648775</v>
+        <v>88.72674109428142</v>
       </c>
       <c r="E520" t="n">
-        <v>89.94120308789761</v>
+        <v>89.94119557423609</v>
       </c>
       <c r="F520" t="n">
         <v>382337</v>
@@ -10852,16 +10852,16 @@
         <v>45233</v>
       </c>
       <c r="B522" t="n">
-        <v>94.61008453369141</v>
+        <v>94.61007690429688</v>
       </c>
       <c r="C522" t="n">
-        <v>97.14693357959244</v>
+        <v>97.14692574562541</v>
       </c>
       <c r="D522" t="n">
-        <v>92.08223332910212</v>
+        <v>92.08222590355452</v>
       </c>
       <c r="E522" t="n">
-        <v>92.70295397611622</v>
+        <v>92.70294650051345</v>
       </c>
       <c r="F522" t="n">
         <v>760712</v>
@@ -10872,16 +10872,16 @@
         <v>45236</v>
       </c>
       <c r="B523" t="n">
-        <v>92.2171630859375</v>
+        <v>92.21717071533203</v>
       </c>
       <c r="C523" t="n">
-        <v>95.9864482957361</v>
+        <v>95.98645623697459</v>
       </c>
       <c r="D523" t="n">
-        <v>91.38953336222757</v>
+        <v>91.38954092314988</v>
       </c>
       <c r="E523" t="n">
-        <v>95.13183877782029</v>
+        <v>95.13184664835444</v>
       </c>
       <c r="F523" t="n">
         <v>393989</v>
@@ -10892,16 +10892,16 @@
         <v>45237</v>
       </c>
       <c r="B524" t="n">
-        <v>97.12894439697266</v>
+        <v>97.12893676757812</v>
       </c>
       <c r="C524" t="n">
-        <v>97.12894439697266</v>
+        <v>97.12893676757812</v>
       </c>
       <c r="D524" t="n">
-        <v>91.57846368653991</v>
+        <v>91.57845649313083</v>
       </c>
       <c r="E524" t="n">
-        <v>92.02825966365781</v>
+        <v>92.02825243491765</v>
       </c>
       <c r="F524" t="n">
         <v>722184</v>
@@ -10912,16 +10912,16 @@
         <v>45238</v>
       </c>
       <c r="B525" t="n">
-        <v>96.40927124023438</v>
+        <v>96.40926361083984</v>
       </c>
       <c r="C525" t="n">
-        <v>98.50532220933374</v>
+        <v>98.50531441406719</v>
       </c>
       <c r="D525" t="n">
-        <v>95.54566375953443</v>
+        <v>95.54565619848189</v>
       </c>
       <c r="E525" t="n">
-        <v>97.11095188934421</v>
+        <v>97.11094420442183</v>
       </c>
       <c r="F525" t="n">
         <v>449324</v>
@@ -10932,16 +10932,16 @@
         <v>45239</v>
       </c>
       <c r="B526" t="n">
-        <v>95.28478240966797</v>
+        <v>95.28476715087891</v>
       </c>
       <c r="C526" t="n">
-        <v>97.73167373282809</v>
+        <v>97.73165808219684</v>
       </c>
       <c r="D526" t="n">
-        <v>94.73603074395886</v>
+        <v>94.73601557304625</v>
       </c>
       <c r="E526" t="n">
-        <v>97.21890657049985</v>
+        <v>97.2188910019825</v>
       </c>
       <c r="F526" t="n">
         <v>493995</v>
@@ -10952,16 +10952,16 @@
         <v>45240</v>
       </c>
       <c r="B527" t="n">
-        <v>98.95511627197266</v>
+        <v>98.95510864257812</v>
       </c>
       <c r="C527" t="n">
-        <v>99.84571039668464</v>
+        <v>99.84570269862571</v>
       </c>
       <c r="D527" t="n">
-        <v>95.0418925920676</v>
+        <v>95.04188526438084</v>
       </c>
       <c r="E527" t="n">
-        <v>95.0418925920676</v>
+        <v>95.04188526438084</v>
       </c>
       <c r="F527" t="n">
         <v>655787</v>
@@ -10972,16 +10972,16 @@
         <v>45243</v>
       </c>
       <c r="B528" t="n">
-        <v>98.83816528320312</v>
+        <v>98.83815765380859</v>
       </c>
       <c r="C528" t="n">
-        <v>100.3134954614712</v>
+        <v>100.3134877181948</v>
       </c>
       <c r="D528" t="n">
-        <v>96.80508565184681</v>
+        <v>96.80507817938725</v>
       </c>
       <c r="E528" t="n">
-        <v>98.9551097602987</v>
+        <v>98.95510212187712</v>
       </c>
       <c r="F528" t="n">
         <v>702632</v>
@@ -10992,16 +10992,16 @@
         <v>45244</v>
       </c>
       <c r="B529" t="n">
-        <v>97.60572052001953</v>
+        <v>97.60572814941406</v>
       </c>
       <c r="C529" t="n">
-        <v>106.628626120648</v>
+        <v>106.6286344553219</v>
       </c>
       <c r="D529" t="n">
-        <v>97.06596675617159</v>
+        <v>97.06597434337603</v>
       </c>
       <c r="E529" t="n">
-        <v>99.7377557800616</v>
+        <v>99.73776357610761</v>
       </c>
       <c r="F529" t="n">
         <v>2031591</v>
@@ -11052,16 +11052,16 @@
         <v>45250</v>
       </c>
       <c r="B532" t="n">
-        <v>102.5534744262695</v>
+        <v>102.5534820556641</v>
       </c>
       <c r="C532" t="n">
-        <v>104.5685583178221</v>
+        <v>104.5685660971273</v>
       </c>
       <c r="D532" t="n">
-        <v>100.9881864751831</v>
+        <v>100.9881939881291</v>
       </c>
       <c r="E532" t="n">
-        <v>103.6329819380516</v>
+        <v>103.6329896477554</v>
       </c>
       <c r="F532" t="n">
         <v>946377</v>
@@ -11072,16 +11072,16 @@
         <v>45251</v>
       </c>
       <c r="B533" t="n">
-        <v>100.2595138549805</v>
+        <v>100.259521484375</v>
       </c>
       <c r="C533" t="n">
-        <v>103.0932296941449</v>
+        <v>103.0932375391752</v>
       </c>
       <c r="D533" t="n">
-        <v>99.13502398732325</v>
+        <v>99.13503153114809</v>
       </c>
       <c r="E533" t="n">
-        <v>102.5804625890269</v>
+        <v>102.5804703950374</v>
       </c>
       <c r="F533" t="n">
         <v>1091156</v>
@@ -11132,16 +11132,16 @@
         <v>45254</v>
       </c>
       <c r="B536" t="n">
-        <v>103.5430297851562</v>
+        <v>103.5430145263672</v>
       </c>
       <c r="C536" t="n">
-        <v>104.3526638949405</v>
+        <v>104.3526485168384</v>
       </c>
       <c r="D536" t="n">
-        <v>100.9522074971883</v>
+        <v>100.9521926202001</v>
       </c>
       <c r="E536" t="n">
-        <v>103.2731563241227</v>
+        <v>103.2731411051039</v>
       </c>
       <c r="F536" t="n">
         <v>447021</v>
@@ -11152,16 +11152,16 @@
         <v>45257</v>
       </c>
       <c r="B537" t="n">
-        <v>102.1036758422852</v>
+        <v>102.1036834716797</v>
       </c>
       <c r="C537" t="n">
-        <v>103.9028595575677</v>
+        <v>103.9028673214009</v>
       </c>
       <c r="D537" t="n">
-        <v>101.4739642872727</v>
+        <v>101.4739718696139</v>
       </c>
       <c r="E537" t="n">
-        <v>102.8233520737347</v>
+        <v>102.8233597569049</v>
       </c>
       <c r="F537" t="n">
         <v>311562</v>
@@ -11172,16 +11172,16 @@
         <v>45258</v>
       </c>
       <c r="B538" t="n">
-        <v>102.9852828979492</v>
+        <v>102.9852905273438</v>
       </c>
       <c r="C538" t="n">
-        <v>105.4501627622543</v>
+        <v>105.450170574253</v>
       </c>
       <c r="D538" t="n">
-        <v>101.8337995100664</v>
+        <v>101.8338070541564</v>
       </c>
       <c r="E538" t="n">
-        <v>102.0946819825549</v>
+        <v>102.0946895459716</v>
       </c>
       <c r="F538" t="n">
         <v>492581</v>
@@ -11192,16 +11192,16 @@
         <v>45259</v>
       </c>
       <c r="B539" t="n">
-        <v>101.6718673706055</v>
+        <v>101.671875</v>
       </c>
       <c r="C539" t="n">
-        <v>104.784461196145</v>
+        <v>104.7844690591067</v>
       </c>
       <c r="D539" t="n">
-        <v>101.6718673706055</v>
+        <v>101.671875</v>
       </c>
       <c r="E539" t="n">
-        <v>103.6329778685619</v>
+        <v>103.6329856451169</v>
       </c>
       <c r="F539" t="n">
         <v>3224073</v>
@@ -11252,16 +11252,16 @@
         <v>45264</v>
       </c>
       <c r="B542" t="n">
-        <v>101.1591110229492</v>
+        <v>101.1591033935547</v>
       </c>
       <c r="C542" t="n">
-        <v>105.2972394423387</v>
+        <v>105.2972315008476</v>
       </c>
       <c r="D542" t="n">
-        <v>100.3674725856501</v>
+        <v>100.3674650159607</v>
       </c>
       <c r="E542" t="n">
-        <v>105.2522570999507</v>
+        <v>105.2522491618521</v>
       </c>
       <c r="F542" t="n">
         <v>887105</v>
@@ -11312,16 +11312,16 @@
         <v>45267</v>
       </c>
       <c r="B545" t="n">
-        <v>106.6016387939453</v>
+        <v>106.6016464233398</v>
       </c>
       <c r="C545" t="n">
-        <v>107.0514347382236</v>
+        <v>107.0514423998096</v>
       </c>
       <c r="D545" t="n">
-        <v>103.6959539740376</v>
+        <v>103.6959613954746</v>
       </c>
       <c r="E545" t="n">
-        <v>105.4231756162056</v>
+        <v>105.4231831612584</v>
       </c>
       <c r="F545" t="n">
         <v>599154</v>
@@ -11332,16 +11332,16 @@
         <v>45268</v>
       </c>
       <c r="B546" t="n">
-        <v>105.4321670532227</v>
+        <v>105.4321594238281</v>
       </c>
       <c r="C546" t="n">
-        <v>108.7156788334399</v>
+        <v>108.7156709664404</v>
       </c>
       <c r="D546" t="n">
-        <v>105.2522514200634</v>
+        <v>105.2522438036881</v>
       </c>
       <c r="E546" t="n">
-        <v>106.9614773884421</v>
+        <v>106.961469648382</v>
       </c>
       <c r="F546" t="n">
         <v>678575</v>
@@ -11352,16 +11352,16 @@
         <v>45271</v>
       </c>
       <c r="B547" t="n">
-        <v>103.1921844482422</v>
+        <v>103.1921920776367</v>
       </c>
       <c r="C547" t="n">
-        <v>106.4127250482224</v>
+        <v>106.4127329157239</v>
       </c>
       <c r="D547" t="n">
-        <v>103.1921844482422</v>
+        <v>103.1921920776367</v>
       </c>
       <c r="E547" t="n">
-        <v>105.3781930063656</v>
+        <v>105.3782007973801</v>
       </c>
       <c r="F547" t="n">
         <v>558243</v>
@@ -11452,16 +11452,16 @@
         <v>45278</v>
       </c>
       <c r="B552" t="n">
-        <v>118.3415603637695</v>
+        <v>118.341552734375</v>
       </c>
       <c r="C552" t="n">
-        <v>120.671449565237</v>
+        <v>120.6714417856362</v>
       </c>
       <c r="D552" t="n">
-        <v>114.5543387135227</v>
+        <v>114.5543313282876</v>
       </c>
       <c r="E552" t="n">
-        <v>114.804960915804</v>
+        <v>114.8049535144115</v>
       </c>
       <c r="F552" t="n">
         <v>1013443</v>
@@ -11632,16 +11632,16 @@
         <v>45294</v>
       </c>
       <c r="B561" t="n">
-        <v>113.2455139160156</v>
+        <v>113.2455062866211</v>
       </c>
       <c r="C561" t="n">
-        <v>116.2437384250845</v>
+        <v>116.2437305936984</v>
       </c>
       <c r="D561" t="n">
-        <v>113.2455139160156</v>
+        <v>113.2455062866211</v>
       </c>
       <c r="E561" t="n">
-        <v>115.7517642600759</v>
+        <v>115.7517564618344</v>
       </c>
       <c r="F561" t="n">
         <v>798887</v>
@@ -11752,16 +11752,16 @@
         <v>45302</v>
       </c>
       <c r="B567" t="n">
-        <v>114.4151000976562</v>
+        <v>114.4150924682617</v>
       </c>
       <c r="C567" t="n">
-        <v>114.7306989485276</v>
+        <v>114.7306912980884</v>
       </c>
       <c r="D567" t="n">
-        <v>112.1966024937236</v>
+        <v>112.1965950122623</v>
       </c>
       <c r="E567" t="n">
-        <v>113.9788252657498</v>
+        <v>113.9788176654469</v>
       </c>
       <c r="F567" t="n">
         <v>442933</v>
@@ -11772,16 +11772,16 @@
         <v>45303</v>
       </c>
       <c r="B568" t="n">
-        <v>116.6800079345703</v>
+        <v>116.6800003051758</v>
       </c>
       <c r="C568" t="n">
-        <v>117.7010797245651</v>
+        <v>117.7010720284054</v>
       </c>
       <c r="D568" t="n">
-        <v>112.8649330302776</v>
+        <v>112.8649256503406</v>
       </c>
       <c r="E568" t="n">
-        <v>114.6378785184286</v>
+        <v>114.6378710225635</v>
       </c>
       <c r="F568" t="n">
         <v>693991</v>
@@ -11792,16 +11792,16 @@
         <v>45306</v>
       </c>
       <c r="B569" t="n">
-        <v>118.2580184936523</v>
+        <v>118.2580261230469</v>
       </c>
       <c r="C569" t="n">
-        <v>120.5786161424443</v>
+        <v>120.5786239215518</v>
       </c>
       <c r="D569" t="n">
-        <v>115.6589383624814</v>
+        <v>115.6589458241968</v>
       </c>
       <c r="E569" t="n">
-        <v>116.6707257076737</v>
+        <v>116.6707332346643</v>
       </c>
       <c r="F569" t="n">
         <v>875695</v>
@@ -11832,16 +11832,16 @@
         <v>45308</v>
       </c>
       <c r="B571" t="n">
-        <v>115.8167419433594</v>
+        <v>115.8167343139648</v>
       </c>
       <c r="C571" t="n">
-        <v>117.292650287693</v>
+        <v>117.2926425610734</v>
       </c>
       <c r="D571" t="n">
-        <v>114.0530879502235</v>
+        <v>114.0530804370092</v>
       </c>
       <c r="E571" t="n">
-        <v>116.5686227188185</v>
+        <v>116.568615039894</v>
       </c>
       <c r="F571" t="n">
         <v>474098</v>
@@ -11912,16 +11912,16 @@
         <v>45314</v>
       </c>
       <c r="B575" t="n">
-        <v>115.8445892333984</v>
+        <v>115.8445816040039</v>
       </c>
       <c r="C575" t="n">
-        <v>119.5111418195592</v>
+        <v>119.5111339486896</v>
       </c>
       <c r="D575" t="n">
-        <v>115.3526150891313</v>
+        <v>115.3526074921376</v>
       </c>
       <c r="E575" t="n">
-        <v>117.0605838276382</v>
+        <v>117.0605761181597</v>
       </c>
       <c r="F575" t="n">
         <v>383026</v>
@@ -11952,16 +11952,16 @@
         <v>45316</v>
       </c>
       <c r="B577" t="n">
-        <v>115.426872253418</v>
+        <v>115.4268798828125</v>
       </c>
       <c r="C577" t="n">
-        <v>117.7289151499315</v>
+        <v>117.7289229314847</v>
       </c>
       <c r="D577" t="n">
-        <v>112.8742071742708</v>
+        <v>112.8742146349412</v>
       </c>
       <c r="E577" t="n">
-        <v>116.958472717291</v>
+        <v>116.95848044792</v>
       </c>
       <c r="F577" t="n">
         <v>983228</v>
@@ -12092,16 +12092,16 @@
         <v>45327</v>
       </c>
       <c r="B584" t="n">
-        <v>117.5711212158203</v>
+        <v>117.5711135864258</v>
       </c>
       <c r="C584" t="n">
-        <v>121.3026434165738</v>
+        <v>121.3026355450343</v>
       </c>
       <c r="D584" t="n">
-        <v>116.2066045040748</v>
+        <v>116.2065969632262</v>
       </c>
       <c r="E584" t="n">
-        <v>119.7246350359527</v>
+        <v>119.7246272668129</v>
       </c>
       <c r="F584" t="n">
         <v>563930</v>
@@ -12112,16 +12112,16 @@
         <v>45328</v>
       </c>
       <c r="B585" t="n">
-        <v>115.9374160766602</v>
+        <v>115.9374084472656</v>
       </c>
       <c r="C585" t="n">
-        <v>119.5946843895468</v>
+        <v>119.5946765194815</v>
       </c>
       <c r="D585" t="n">
-        <v>115.1205586627154</v>
+        <v>115.1205510870751</v>
       </c>
       <c r="E585" t="n">
-        <v>117.8867226729782</v>
+        <v>117.8867149153073</v>
       </c>
       <c r="F585" t="n">
         <v>714734</v>
@@ -12132,16 +12132,16 @@
         <v>45329</v>
       </c>
       <c r="B586" t="n">
-        <v>114.9070663452148</v>
+        <v>114.9070587158203</v>
       </c>
       <c r="C586" t="n">
-        <v>116.3179909256947</v>
+        <v>116.3179832026201</v>
       </c>
       <c r="D586" t="n">
-        <v>111.816019099874</v>
+        <v>111.8160116757133</v>
       </c>
       <c r="E586" t="n">
-        <v>115.101996295562</v>
+        <v>115.1019886532248</v>
       </c>
       <c r="F586" t="n">
         <v>998662</v>
@@ -12172,16 +12172,16 @@
         <v>45331</v>
       </c>
       <c r="B588" t="n">
-        <v>114.2201690673828</v>
+        <v>114.2201614379883</v>
       </c>
       <c r="C588" t="n">
-        <v>115.8445923986349</v>
+        <v>115.8445846607362</v>
       </c>
       <c r="D588" t="n">
-        <v>113.5611110837534</v>
+        <v>113.561103498381</v>
       </c>
       <c r="E588" t="n">
-        <v>114.9070660930879</v>
+        <v>114.9070584178118</v>
       </c>
       <c r="F588" t="n">
         <v>354486</v>
@@ -12212,16 +12212,16 @@
         <v>45337</v>
       </c>
       <c r="B590" t="n">
-        <v>115.7517547607422</v>
+        <v>115.7517623901367</v>
       </c>
       <c r="C590" t="n">
-        <v>116.4015282987129</v>
+        <v>116.4015359709352</v>
       </c>
       <c r="D590" t="n">
-        <v>114.4986296915515</v>
+        <v>114.4986372383505</v>
       </c>
       <c r="E590" t="n">
-        <v>115.6589319930101</v>
+        <v>115.6589396162866</v>
       </c>
       <c r="F590" t="n">
         <v>464925</v>
@@ -12352,16 +12352,16 @@
         <v>45348</v>
       </c>
       <c r="B597" t="n">
-        <v>111.2776336669922</v>
+        <v>111.2776260375977</v>
       </c>
       <c r="C597" t="n">
-        <v>113.0227329282103</v>
+        <v>113.0227251791686</v>
       </c>
       <c r="D597" t="n">
-        <v>110.5164756111173</v>
+        <v>110.5164680339092</v>
       </c>
       <c r="E597" t="n">
-        <v>111.6675006376001</v>
+        <v>111.6674929814756</v>
       </c>
       <c r="F597" t="n">
         <v>306480</v>
@@ -12392,16 +12392,16 @@
         <v>45350</v>
       </c>
       <c r="B599" t="n">
-        <v>110.5072021484375</v>
+        <v>110.507194519043</v>
       </c>
       <c r="C599" t="n">
-        <v>112.8556530461457</v>
+        <v>112.8556452546146</v>
       </c>
       <c r="D599" t="n">
-        <v>103.03485194489</v>
+        <v>103.0348448313849</v>
       </c>
       <c r="E599" t="n">
-        <v>112.8556530461457</v>
+        <v>112.8556452546146</v>
       </c>
       <c r="F599" t="n">
         <v>1284448</v>
@@ -12552,16 +12552,16 @@
         <v>45362</v>
       </c>
       <c r="B607" t="n">
-        <v>116.9120635986328</v>
+        <v>116.9120559692383</v>
       </c>
       <c r="C607" t="n">
-        <v>117.9052821409343</v>
+        <v>117.9052744467247</v>
       </c>
       <c r="D607" t="n">
-        <v>116.1044976840983</v>
+        <v>116.1044901074035</v>
       </c>
       <c r="E607" t="n">
-        <v>116.1230594059132</v>
+        <v>116.1230518280071</v>
       </c>
       <c r="F607" t="n">
         <v>387232</v>
@@ -12612,16 +12612,16 @@
         <v>45365</v>
       </c>
       <c r="B610" t="n">
-        <v>117.5711212158203</v>
+        <v>117.5711135864258</v>
       </c>
       <c r="C610" t="n">
-        <v>120.7642755844261</v>
+        <v>120.7642677478222</v>
       </c>
       <c r="D610" t="n">
-        <v>115.9374135060774</v>
+        <v>115.937405982697</v>
       </c>
       <c r="E610" t="n">
-        <v>120.662168409947</v>
+        <v>120.662160579969</v>
       </c>
       <c r="F610" t="n">
         <v>644367</v>
@@ -12672,16 +12672,16 @@
         <v>45370</v>
       </c>
       <c r="B613" t="n">
-        <v>116.4108123779297</v>
+        <v>116.4108200073242</v>
       </c>
       <c r="C613" t="n">
-        <v>118.2487272524772</v>
+        <v>118.248735002326</v>
       </c>
       <c r="D613" t="n">
-        <v>115.5661089054821</v>
+        <v>115.566116479516</v>
       </c>
       <c r="E613" t="n">
-        <v>117.2369470477283</v>
+        <v>117.2369547312665</v>
       </c>
       <c r="F613" t="n">
         <v>379495</v>
@@ -12692,16 +12692,16 @@
         <v>45371</v>
       </c>
       <c r="B614" t="n">
-        <v>118.1744689941406</v>
+        <v>118.1744766235352</v>
       </c>
       <c r="C614" t="n">
-        <v>119.5854005879789</v>
+        <v>119.5854083084638</v>
       </c>
       <c r="D614" t="n">
-        <v>115.1019907020985</v>
+        <v>115.1019981331325</v>
       </c>
       <c r="E614" t="n">
-        <v>115.9374097929339</v>
+        <v>115.9374172779029</v>
       </c>
       <c r="F614" t="n">
         <v>596704</v>
@@ -12872,16 +12872,16 @@
         <v>45385</v>
       </c>
       <c r="B623" t="n">
-        <v>117.4597244262695</v>
+        <v>117.4597320556641</v>
       </c>
       <c r="C623" t="n">
-        <v>118.1002135683167</v>
+        <v>118.1002212393131</v>
       </c>
       <c r="D623" t="n">
-        <v>116.0395155303591</v>
+        <v>116.0395230675065</v>
       </c>
       <c r="E623" t="n">
-        <v>117.7196310108906</v>
+        <v>117.7196386571669</v>
       </c>
       <c r="F623" t="n">
         <v>818287</v>
@@ -12992,16 +12992,16 @@
         <v>45393</v>
       </c>
       <c r="B629" t="n">
-        <v>113.9509735107422</v>
+        <v>113.9509811401367</v>
       </c>
       <c r="C629" t="n">
-        <v>114.4522249684666</v>
+        <v>114.4522326314215</v>
       </c>
       <c r="D629" t="n">
-        <v>112.3915268917964</v>
+        <v>112.3915344167808</v>
       </c>
       <c r="E629" t="n">
-        <v>114.025227477798</v>
+        <v>114.025235112164</v>
       </c>
       <c r="F629" t="n">
         <v>445667</v>
@@ -13132,16 +13132,16 @@
         <v>45404</v>
       </c>
       <c r="B636" t="n">
-        <v>100.9463043212891</v>
+        <v>100.9462966918945</v>
       </c>
       <c r="C636" t="n">
-        <v>102.5243126825076</v>
+        <v>102.5243049338492</v>
       </c>
       <c r="D636" t="n">
-        <v>100.4357684551706</v>
+        <v>100.4357608643617</v>
       </c>
       <c r="E636" t="n">
-        <v>101.1783647909932</v>
+        <v>101.1783571440598</v>
       </c>
       <c r="F636" t="n">
         <v>363945</v>
@@ -13232,16 +13232,16 @@
         <v>45412</v>
       </c>
       <c r="B641" t="n">
-        <v>98.46790313720703</v>
+        <v>98.4678955078125</v>
       </c>
       <c r="C641" t="n">
-        <v>100.482186374569</v>
+        <v>100.4821785891058</v>
       </c>
       <c r="D641" t="n">
-        <v>96.7692187487189</v>
+        <v>96.76921125094019</v>
       </c>
       <c r="E641" t="n">
-        <v>99.3125995894876</v>
+        <v>99.31259189464512</v>
       </c>
       <c r="F641" t="n">
         <v>1108924</v>
@@ -13252,16 +13252,16 @@
         <v>45414</v>
       </c>
       <c r="B642" t="n">
-        <v>99.8138427734375</v>
+        <v>99.81385040283203</v>
       </c>
       <c r="C642" t="n">
-        <v>101.3454432081965</v>
+        <v>101.3454509546608</v>
       </c>
       <c r="D642" t="n">
-        <v>98.7649320558007</v>
+        <v>98.76493960502044</v>
       </c>
       <c r="E642" t="n">
-        <v>100.7142384809835</v>
+        <v>100.7142461792009</v>
       </c>
       <c r="F642" t="n">
         <v>433847</v>
@@ -13272,16 +13272,16 @@
         <v>45415</v>
       </c>
       <c r="B643" t="n">
-        <v>105.9123916625977</v>
+        <v>105.9123992919922</v>
       </c>
       <c r="C643" t="n">
-        <v>106.3765125788071</v>
+        <v>106.3765202416345</v>
       </c>
       <c r="D643" t="n">
-        <v>100.0737496868528</v>
+        <v>100.073756895661</v>
       </c>
       <c r="E643" t="n">
-        <v>100.0737496868528</v>
+        <v>100.073756895661</v>
       </c>
       <c r="F643" t="n">
         <v>813358</v>
@@ -13452,16 +13452,16 @@
         <v>45428</v>
       </c>
       <c r="B652" t="n">
-        <v>104.6407089233398</v>
+        <v>104.6407012939453</v>
       </c>
       <c r="C652" t="n">
-        <v>104.9377460379014</v>
+        <v>104.9377383868498</v>
       </c>
       <c r="D652" t="n">
-        <v>103.3226000881697</v>
+        <v>103.322592554879</v>
       </c>
       <c r="E652" t="n">
-        <v>104.1487347843541</v>
+        <v>104.1487271908296</v>
       </c>
       <c r="F652" t="n">
         <v>283646</v>
@@ -13572,16 +13572,16 @@
         <v>45436</v>
       </c>
       <c r="B658" t="n">
-        <v>90.03945922851562</v>
+        <v>90.03946685791016</v>
       </c>
       <c r="C658" t="n">
-        <v>91.0605238446193</v>
+        <v>91.06053156053261</v>
       </c>
       <c r="D658" t="n">
-        <v>88.15512941075855</v>
+        <v>88.15513688048645</v>
       </c>
       <c r="E658" t="n">
-        <v>89.29686291757299</v>
+        <v>89.29687048404443</v>
       </c>
       <c r="F658" t="n">
         <v>574555</v>
@@ -13612,16 +13612,16 @@
         <v>45440</v>
       </c>
       <c r="B660" t="n">
-        <v>90.68923187255859</v>
+        <v>90.68922424316406</v>
       </c>
       <c r="C660" t="n">
-        <v>92.44360851780684</v>
+        <v>92.44360074082222</v>
       </c>
       <c r="D660" t="n">
-        <v>90.07659589389471</v>
+        <v>90.07658831603928</v>
       </c>
       <c r="E660" t="n">
-        <v>90.96770727863003</v>
+        <v>90.96769962580825</v>
       </c>
       <c r="F660" t="n">
         <v>449350</v>
@@ -13652,16 +13652,16 @@
         <v>45443</v>
       </c>
       <c r="B662" t="n">
-        <v>92.63853454589844</v>
+        <v>92.63854217529297</v>
       </c>
       <c r="C662" t="n">
-        <v>93.37183933638515</v>
+        <v>93.37184702617216</v>
       </c>
       <c r="D662" t="n">
-        <v>88.71206861275279</v>
+        <v>88.71207591877693</v>
       </c>
       <c r="E662" t="n">
-        <v>90.03945467107755</v>
+        <v>90.0394620864207</v>
       </c>
       <c r="F662" t="n">
         <v>991405</v>
@@ -13672,16 +13672,16 @@
         <v>45446</v>
       </c>
       <c r="B663" t="n">
-        <v>92.434326171875</v>
+        <v>92.43431854248047</v>
       </c>
       <c r="C663" t="n">
-        <v>93.60390581716601</v>
+        <v>93.60389809123609</v>
       </c>
       <c r="D663" t="n">
-        <v>90.53142752500605</v>
+        <v>90.53142005267401</v>
       </c>
       <c r="E663" t="n">
-        <v>92.64781783392128</v>
+        <v>92.64781018690546</v>
       </c>
       <c r="F663" t="n">
         <v>373105</v>
@@ -13712,16 +13712,16 @@
         <v>45448</v>
       </c>
       <c r="B665" t="n">
-        <v>92.92629241943359</v>
+        <v>92.92630004882812</v>
       </c>
       <c r="C665" t="n">
-        <v>93.79884202699066</v>
+        <v>93.79884972802287</v>
       </c>
       <c r="D665" t="n">
-        <v>92.39719484679063</v>
+        <v>92.39720243274542</v>
       </c>
       <c r="E665" t="n">
-        <v>93.18619900502337</v>
+        <v>93.18620665575664</v>
       </c>
       <c r="F665" t="n">
         <v>402887</v>
@@ -13772,16 +13772,16 @@
         <v>45453</v>
       </c>
       <c r="B668" t="n">
-        <v>92.53643035888672</v>
+        <v>92.53643798828125</v>
       </c>
       <c r="C668" t="n">
-        <v>93.24188905115926</v>
+        <v>93.24189673871706</v>
       </c>
       <c r="D668" t="n">
-        <v>90.78205386560359</v>
+        <v>90.78206135035421</v>
       </c>
       <c r="E668" t="n">
-        <v>92.0351789205311</v>
+        <v>92.0351865085987</v>
       </c>
       <c r="F668" t="n">
         <v>279796</v>
@@ -13812,16 +13812,16 @@
         <v>45455</v>
       </c>
       <c r="B670" t="n">
-        <v>90.15084838867188</v>
+        <v>90.15085601806641</v>
       </c>
       <c r="C670" t="n">
-        <v>93.8638156802361</v>
+        <v>93.86382362385611</v>
       </c>
       <c r="D670" t="n">
-        <v>90.1415639875045</v>
+        <v>90.1415716161133</v>
       </c>
       <c r="E670" t="n">
-        <v>93.15834991190043</v>
+        <v>93.15835779581742</v>
       </c>
       <c r="F670" t="n">
         <v>421382</v>
@@ -13852,16 +13852,16 @@
         <v>45457</v>
       </c>
       <c r="B672" t="n">
-        <v>85.38897705078125</v>
+        <v>85.38896942138672</v>
       </c>
       <c r="C672" t="n">
-        <v>86.81847053798501</v>
+        <v>86.81846278086709</v>
       </c>
       <c r="D672" t="n">
-        <v>84.95270219068296</v>
+        <v>84.95269460026903</v>
       </c>
       <c r="E672" t="n">
-        <v>86.81847053798501</v>
+        <v>86.81846278086709</v>
       </c>
       <c r="F672" t="n">
         <v>481131</v>
@@ -13872,16 +13872,16 @@
         <v>45460</v>
       </c>
       <c r="B673" t="n">
-        <v>85.58389282226562</v>
+        <v>85.58390045166016</v>
       </c>
       <c r="C673" t="n">
-        <v>86.70707165460294</v>
+        <v>86.70707938412349</v>
       </c>
       <c r="D673" t="n">
-        <v>83.36539544288092</v>
+        <v>83.36540287450703</v>
       </c>
       <c r="E673" t="n">
-        <v>85.12905631419575</v>
+        <v>85.12906390304379</v>
       </c>
       <c r="F673" t="n">
         <v>650145</v>
@@ -13892,16 +13892,16 @@
         <v>45461</v>
       </c>
       <c r="B674" t="n">
-        <v>87.54248809814453</v>
+        <v>87.54248046875</v>
       </c>
       <c r="C674" t="n">
-        <v>87.54248809814453</v>
+        <v>87.54248046875</v>
       </c>
       <c r="D674" t="n">
-        <v>84.97126124590245</v>
+        <v>84.9712538405923</v>
       </c>
       <c r="E674" t="n">
-        <v>85.57461987506238</v>
+        <v>85.57461241716906</v>
       </c>
       <c r="F674" t="n">
         <v>348422</v>
@@ -13972,16 +13972,16 @@
         <v>45467</v>
       </c>
       <c r="B678" t="n">
-        <v>89.74242401123047</v>
+        <v>89.74241638183594</v>
       </c>
       <c r="C678" t="n">
-        <v>90.6056892310713</v>
+        <v>90.60568152828682</v>
       </c>
       <c r="D678" t="n">
-        <v>88.23866963675577</v>
+        <v>88.23866213520195</v>
       </c>
       <c r="E678" t="n">
-        <v>88.92557371752265</v>
+        <v>88.92556615757213</v>
       </c>
       <c r="F678" t="n">
         <v>235914</v>
@@ -14052,16 +14052,16 @@
         <v>45471</v>
       </c>
       <c r="B682" t="n">
-        <v>90.78205871582031</v>
+        <v>90.78206634521484</v>
       </c>
       <c r="C682" t="n">
-        <v>92.44360544927629</v>
+        <v>92.4436132183085</v>
       </c>
       <c r="D682" t="n">
-        <v>89.58462584053821</v>
+        <v>89.58463336929955</v>
       </c>
       <c r="E682" t="n">
-        <v>91.15334980235941</v>
+        <v>91.15335746295753</v>
       </c>
       <c r="F682" t="n">
         <v>273815</v>
@@ -14092,16 +14092,16 @@
         <v>45475</v>
       </c>
       <c r="B684" t="n">
-        <v>87.69100952148438</v>
+        <v>87.69101715087891</v>
       </c>
       <c r="C684" t="n">
-        <v>88.6470975028048</v>
+        <v>88.647105215382</v>
       </c>
       <c r="D684" t="n">
-        <v>87.28258083745493</v>
+        <v>87.28258843131488</v>
       </c>
       <c r="E684" t="n">
-        <v>88.03445447676063</v>
+        <v>88.03446213603596</v>
       </c>
       <c r="F684" t="n">
         <v>181372</v>
@@ -14132,16 +14132,16 @@
         <v>45477</v>
       </c>
       <c r="B686" t="n">
-        <v>88.32221221923828</v>
+        <v>88.32221984863281</v>
       </c>
       <c r="C686" t="n">
-        <v>89.04623971909143</v>
+        <v>89.04624741102846</v>
       </c>
       <c r="D686" t="n">
-        <v>86.80917349228666</v>
+        <v>86.80918099098282</v>
       </c>
       <c r="E686" t="n">
-        <v>87.44037822481152</v>
+        <v>87.44038577803201</v>
       </c>
       <c r="F686" t="n">
         <v>119657</v>
@@ -14172,16 +14172,16 @@
         <v>45481</v>
       </c>
       <c r="B688" t="n">
-        <v>87.11550140380859</v>
+        <v>87.11549377441406</v>
       </c>
       <c r="C688" t="n">
-        <v>88.26651938354486</v>
+        <v>88.26651165334657</v>
       </c>
       <c r="D688" t="n">
-        <v>86.17797509643314</v>
+        <v>86.17796754914521</v>
       </c>
       <c r="E688" t="n">
-        <v>86.32649720061781</v>
+        <v>86.32648964032262</v>
       </c>
       <c r="F688" t="n">
         <v>189187</v>
@@ -14212,16 +14212,16 @@
         <v>45483</v>
       </c>
       <c r="B690" t="n">
-        <v>91.15334320068359</v>
+        <v>91.15335083007812</v>
       </c>
       <c r="C690" t="n">
-        <v>92.08158501365153</v>
+        <v>92.08159272073848</v>
       </c>
       <c r="D690" t="n">
-        <v>86.83702443592102</v>
+        <v>86.83703170404632</v>
       </c>
       <c r="E690" t="n">
-        <v>86.83702443592102</v>
+        <v>86.83703170404632</v>
       </c>
       <c r="F690" t="n">
         <v>604684</v>
@@ -14272,16 +14272,16 @@
         <v>45488</v>
       </c>
       <c r="B693" t="n">
-        <v>93.75242614746094</v>
+        <v>93.75243377685547</v>
       </c>
       <c r="C693" t="n">
-        <v>94.87559792771359</v>
+        <v>94.8756056485097</v>
       </c>
       <c r="D693" t="n">
-        <v>92.54570891873422</v>
+        <v>92.54571644992839</v>
       </c>
       <c r="E693" t="n">
-        <v>92.83346870578572</v>
+        <v>92.83347626039723</v>
       </c>
       <c r="F693" t="n">
         <v>284490</v>
@@ -14292,16 +14292,16 @@
         <v>45489</v>
       </c>
       <c r="B694" t="n">
-        <v>93.74314880371094</v>
+        <v>93.74314117431641</v>
       </c>
       <c r="C694" t="n">
-        <v>95.46039492624392</v>
+        <v>95.46038715708933</v>
       </c>
       <c r="D694" t="n">
-        <v>92.92629846982642</v>
+        <v>92.9262909069122</v>
       </c>
       <c r="E694" t="n">
-        <v>92.92629846982642</v>
+        <v>92.9262909069122</v>
       </c>
       <c r="F694" t="n">
         <v>218776</v>
@@ -14412,16 +14412,16 @@
         <v>45497</v>
       </c>
       <c r="B700" t="n">
-        <v>91.80312347412109</v>
+        <v>91.80311584472656</v>
       </c>
       <c r="C700" t="n">
-        <v>94.77349466141999</v>
+        <v>94.77348678516967</v>
       </c>
       <c r="D700" t="n">
-        <v>91.78455467061849</v>
+        <v>91.78454704276713</v>
       </c>
       <c r="E700" t="n">
-        <v>94.3650730493686</v>
+        <v>94.36506520706058</v>
       </c>
       <c r="F700" t="n">
         <v>387734</v>
@@ -14432,16 +14432,16 @@
         <v>45498</v>
       </c>
       <c r="B701" t="n">
-        <v>92.38791656494141</v>
+        <v>92.38790893554688</v>
       </c>
       <c r="C701" t="n">
-        <v>93.65961053658134</v>
+        <v>93.65960280217031</v>
       </c>
       <c r="D701" t="n">
-        <v>91.01412249813397</v>
+        <v>91.01411498218737</v>
       </c>
       <c r="E701" t="n">
-        <v>92.36007044062993</v>
+        <v>92.36006281353492</v>
       </c>
       <c r="F701" t="n">
         <v>169675</v>
@@ -14472,16 +14472,16 @@
         <v>45502</v>
       </c>
       <c r="B703" t="n">
-        <v>91.94235992431641</v>
+        <v>91.94235229492188</v>
       </c>
       <c r="C703" t="n">
-        <v>94.07731197309832</v>
+        <v>94.07730416654506</v>
       </c>
       <c r="D703" t="n">
-        <v>91.71957677685126</v>
+        <v>91.71956916594331</v>
       </c>
       <c r="E703" t="n">
-        <v>93.10266226015118</v>
+        <v>93.10265453447454</v>
       </c>
       <c r="F703" t="n">
         <v>142991</v>
@@ -14512,16 +14512,16 @@
         <v>45504</v>
       </c>
       <c r="B705" t="n">
-        <v>90.49430084228516</v>
+        <v>90.49430847167969</v>
       </c>
       <c r="C705" t="n">
-        <v>91.80312532052498</v>
+        <v>91.8031330602639</v>
       </c>
       <c r="D705" t="n">
-        <v>89.90022659287696</v>
+        <v>89.90023417218629</v>
       </c>
       <c r="E705" t="n">
-        <v>90.59640801783253</v>
+        <v>90.59641565583551</v>
       </c>
       <c r="F705" t="n">
         <v>210335</v>
@@ -14552,16 +14552,16 @@
         <v>45506</v>
       </c>
       <c r="B707" t="n">
-        <v>86.47501373291016</v>
+        <v>86.47502136230469</v>
       </c>
       <c r="C707" t="n">
-        <v>88.6656579730932</v>
+        <v>88.66566579576077</v>
       </c>
       <c r="D707" t="n">
-        <v>85.23116597724216</v>
+        <v>85.23117349689625</v>
       </c>
       <c r="E707" t="n">
-        <v>87.72813880804915</v>
+        <v>87.72814654800261</v>
       </c>
       <c r="F707" t="n">
         <v>556592</v>
@@ -14632,16 +14632,16 @@
         <v>45512</v>
       </c>
       <c r="B711" t="n">
-        <v>90.37363433837891</v>
+        <v>90.37362670898438</v>
       </c>
       <c r="C711" t="n">
-        <v>91.7288666983556</v>
+        <v>91.72885895455157</v>
       </c>
       <c r="D711" t="n">
-        <v>86.83703487215151</v>
+        <v>86.83702754131875</v>
       </c>
       <c r="E711" t="n">
-        <v>86.83703487215151</v>
+        <v>86.83702754131875</v>
       </c>
       <c r="F711" t="n">
         <v>332071</v>
@@ -14652,16 +14652,16 @@
         <v>45513</v>
       </c>
       <c r="B712" t="n">
-        <v>92.08159637451172</v>
+        <v>92.08158874511719</v>
       </c>
       <c r="C712" t="n">
-        <v>93.99377956085505</v>
+        <v>93.99377177302711</v>
       </c>
       <c r="D712" t="n">
-        <v>90.03946696679722</v>
+        <v>90.03945950660274</v>
       </c>
       <c r="E712" t="n">
-        <v>91.29259215252766</v>
+        <v>91.29258458850585</v>
       </c>
       <c r="F712" t="n">
         <v>660502</v>
@@ -14672,16 +14672,16 @@
         <v>45516</v>
       </c>
       <c r="B713" t="n">
-        <v>92.40648651123047</v>
+        <v>92.40647888183594</v>
       </c>
       <c r="C713" t="n">
-        <v>93.94736442487562</v>
+        <v>93.94735666826095</v>
       </c>
       <c r="D713" t="n">
-        <v>91.91451234192638</v>
+        <v>91.91450475315092</v>
       </c>
       <c r="E713" t="n">
-        <v>93.43683561503292</v>
+        <v>93.43682790056926</v>
       </c>
       <c r="F713" t="n">
         <v>620479</v>
@@ -14812,16 +14812,16 @@
         <v>45525</v>
       </c>
       <c r="B720" t="n">
-        <v>98.78349304199219</v>
+        <v>98.78350067138672</v>
       </c>
       <c r="C720" t="n">
-        <v>100.4079162312225</v>
+        <v>100.407923986077</v>
       </c>
       <c r="D720" t="n">
-        <v>98.45860982053073</v>
+        <v>98.45861742483341</v>
       </c>
       <c r="E720" t="n">
-        <v>99.32187499865579</v>
+        <v>99.32188266963144</v>
       </c>
       <c r="F720" t="n">
         <v>477691</v>
@@ -14892,16 +14892,16 @@
         <v>45531</v>
       </c>
       <c r="B724" t="n">
-        <v>99.32188415527344</v>
+        <v>99.32187652587891</v>
       </c>
       <c r="C724" t="n">
-        <v>100.7977853896593</v>
+        <v>100.7977776468936</v>
       </c>
       <c r="D724" t="n">
-        <v>99.15480032855771</v>
+        <v>99.1547927119977</v>
       </c>
       <c r="E724" t="n">
-        <v>99.40542252766943</v>
+        <v>99.40541489185792</v>
       </c>
       <c r="F724" t="n">
         <v>203544</v>
@@ -14992,16 +14992,16 @@
         <v>45538</v>
       </c>
       <c r="B729" t="n">
-        <v>96.24939727783203</v>
+        <v>96.24940490722656</v>
       </c>
       <c r="C729" t="n">
-        <v>97.25189306841784</v>
+        <v>97.25190077727714</v>
       </c>
       <c r="D729" t="n">
-        <v>94.5414286340846</v>
+        <v>94.54143612809369</v>
       </c>
       <c r="E729" t="n">
-        <v>95.51608538489992</v>
+        <v>95.51609295616707</v>
       </c>
       <c r="F729" t="n">
         <v>703523</v>
@@ -15092,16 +15092,16 @@
         <v>45545</v>
       </c>
       <c r="B734" t="n">
-        <v>94.43932342529297</v>
+        <v>94.4393310546875</v>
       </c>
       <c r="C734" t="n">
-        <v>94.89416702879937</v>
+        <v>94.894174694939</v>
       </c>
       <c r="D734" t="n">
-        <v>92.19297985772515</v>
+        <v>92.1929873056461</v>
       </c>
       <c r="E734" t="n">
-        <v>93.78027256449035</v>
+        <v>93.78028014064265</v>
       </c>
       <c r="F734" t="n">
         <v>481370</v>
@@ -15132,16 +15132,16 @@
         <v>45547</v>
       </c>
       <c r="B736" t="n">
-        <v>96.86204528808594</v>
+        <v>96.86203765869141</v>
       </c>
       <c r="C736" t="n">
-        <v>97.3632967868906</v>
+        <v>97.36328911801471</v>
       </c>
       <c r="D736" t="n">
-        <v>95.41399012393292</v>
+        <v>95.41398260859528</v>
       </c>
       <c r="E736" t="n">
-        <v>95.9802182754387</v>
+        <v>95.98021071550178</v>
       </c>
       <c r="F736" t="n">
         <v>375743</v>
@@ -15152,16 +15152,16 @@
         <v>45548</v>
       </c>
       <c r="B737" t="n">
-        <v>98.87631988525391</v>
+        <v>98.87632751464844</v>
       </c>
       <c r="C737" t="n">
-        <v>99.46111678992312</v>
+        <v>99.46112446444116</v>
       </c>
       <c r="D737" t="n">
-        <v>96.32365476834089</v>
+        <v>96.32366220076925</v>
       </c>
       <c r="E737" t="n">
-        <v>96.32365476834089</v>
+        <v>96.32366220076925</v>
       </c>
       <c r="F737" t="n">
         <v>344396</v>
@@ -15192,16 +15192,16 @@
         <v>45552</v>
       </c>
       <c r="B739" t="n">
-        <v>100.3151016235352</v>
+        <v>100.3150939941406</v>
       </c>
       <c r="C739" t="n">
-        <v>100.7977842944004</v>
+        <v>100.7977766282958</v>
       </c>
       <c r="D739" t="n">
-        <v>98.70924002410959</v>
+        <v>98.70923251684773</v>
       </c>
       <c r="E739" t="n">
-        <v>99.17336097306311</v>
+        <v>99.17335343050286</v>
       </c>
       <c r="F739" t="n">
         <v>287351</v>
@@ -15252,16 +15252,16 @@
         <v>45555</v>
       </c>
       <c r="B742" t="n">
-        <v>93.28831481933594</v>
+        <v>93.28830718994141</v>
       </c>
       <c r="C742" t="n">
-        <v>100.0830455258852</v>
+        <v>100.0830373407975</v>
       </c>
       <c r="D742" t="n">
-        <v>91.71958367705382</v>
+        <v>91.71957617595477</v>
       </c>
       <c r="E742" t="n">
-        <v>99.79529279116565</v>
+        <v>99.79528462961119</v>
       </c>
       <c r="F742" t="n">
         <v>1020811</v>
@@ -15312,16 +15312,16 @@
         <v>45560</v>
       </c>
       <c r="B745" t="n">
-        <v>90.49430084228516</v>
+        <v>90.49430847167969</v>
       </c>
       <c r="C745" t="n">
-        <v>92.0630319194006</v>
+        <v>92.06303968105173</v>
       </c>
       <c r="D745" t="n">
-        <v>89.42682124096855</v>
+        <v>89.42682878036601</v>
       </c>
       <c r="E745" t="n">
-        <v>91.89594809413431</v>
+        <v>91.89595584169895</v>
       </c>
       <c r="F745" t="n">
         <v>511811</v>
@@ -15452,16 +15452,16 @@
         <v>45569</v>
       </c>
       <c r="B752" t="n">
-        <v>89.85382080078125</v>
+        <v>89.85381317138672</v>
       </c>
       <c r="C752" t="n">
-        <v>90.30865735920958</v>
+        <v>90.30864969119534</v>
       </c>
       <c r="D752" t="n">
-        <v>87.72814595150052</v>
+        <v>87.72813850259483</v>
       </c>
       <c r="E752" t="n">
-        <v>90.17870405680148</v>
+        <v>90.17869639982145</v>
       </c>
       <c r="F752" t="n">
         <v>695884</v>
@@ -15472,16 +15472,16 @@
         <v>45572</v>
       </c>
       <c r="B753" t="n">
-        <v>90.48502349853516</v>
+        <v>90.48501586914062</v>
       </c>
       <c r="C753" t="n">
-        <v>90.75420741735454</v>
+        <v>90.75419976526331</v>
       </c>
       <c r="D753" t="n">
-        <v>89.1205067728724</v>
+        <v>89.12049925852935</v>
       </c>
       <c r="E753" t="n">
-        <v>89.80740379570975</v>
+        <v>89.80739622344984</v>
       </c>
       <c r="F753" t="n">
         <v>295051</v>
@@ -15492,16 +15492,16 @@
         <v>45573</v>
       </c>
       <c r="B754" t="n">
-        <v>90.68923187255859</v>
+        <v>90.68922424316406</v>
       </c>
       <c r="C754" t="n">
-        <v>91.33900545941735</v>
+        <v>91.33899777535945</v>
       </c>
       <c r="D754" t="n">
-        <v>90.68923187255859</v>
+        <v>90.68922424316406</v>
       </c>
       <c r="E754" t="n">
-        <v>91.12550670383942</v>
+        <v>91.12549903774249</v>
       </c>
       <c r="F754" t="n">
         <v>183628</v>
@@ -15512,16 +15512,16 @@
         <v>45574</v>
       </c>
       <c r="B755" t="n">
-        <v>89.48252105712891</v>
+        <v>89.48251342773438</v>
       </c>
       <c r="C755" t="n">
-        <v>90.68923128445775</v>
+        <v>90.68922355217755</v>
       </c>
       <c r="D755" t="n">
-        <v>87.85809772340171</v>
+        <v>87.85809023250759</v>
       </c>
       <c r="E755" t="n">
-        <v>90.42004736410439</v>
+        <v>90.42003965477517</v>
       </c>
       <c r="F755" t="n">
         <v>305833</v>
@@ -15572,16 +15572,16 @@
         <v>45579</v>
       </c>
       <c r="B758" t="n">
-        <v>92.63853454589844</v>
+        <v>92.63854217529297</v>
       </c>
       <c r="C758" t="n">
-        <v>93.58533806659976</v>
+        <v>93.58534577396981</v>
       </c>
       <c r="D758" t="n">
-        <v>90.9676964718103</v>
+        <v>90.9677039636003</v>
       </c>
       <c r="E758" t="n">
-        <v>90.9676964718103</v>
+        <v>90.9677039636003</v>
       </c>
       <c r="F758" t="n">
         <v>855663</v>
@@ -15592,16 +15592,16 @@
         <v>45580</v>
       </c>
       <c r="B759" t="n">
-        <v>92.22083282470703</v>
+        <v>92.2208251953125</v>
       </c>
       <c r="C759" t="n">
-        <v>94.20726995594816</v>
+        <v>94.20726216221644</v>
       </c>
       <c r="D759" t="n">
-        <v>91.71030402068969</v>
+        <v>91.71029643353101</v>
       </c>
       <c r="E759" t="n">
-        <v>93.52965732397952</v>
+        <v>93.52964958630643</v>
       </c>
       <c r="F759" t="n">
         <v>238514</v>
@@ -15712,16 +15712,16 @@
         <v>45588</v>
       </c>
       <c r="B765" t="n">
-        <v>92.425048828125</v>
+        <v>92.42504119873047</v>
       </c>
       <c r="C765" t="n">
-        <v>95.40470457814952</v>
+        <v>95.40469670279386</v>
       </c>
       <c r="D765" t="n">
-        <v>92.36007217620262</v>
+        <v>92.36006455217171</v>
       </c>
       <c r="E765" t="n">
-        <v>93.76171947558419</v>
+        <v>93.76171173585173</v>
       </c>
       <c r="F765" t="n">
         <v>357512</v>
@@ -15732,16 +15732,16 @@
         <v>45589</v>
       </c>
       <c r="B766" t="n">
-        <v>93.28831481933594</v>
+        <v>93.28830718994141</v>
       </c>
       <c r="C766" t="n">
-        <v>93.98449627321158</v>
+        <v>93.98448858688127</v>
       </c>
       <c r="D766" t="n">
-        <v>92.4343339355769</v>
+        <v>92.43432637602346</v>
       </c>
       <c r="E766" t="n">
-        <v>92.82419385008551</v>
+        <v>92.82418625864817</v>
       </c>
       <c r="F766" t="n">
         <v>318309</v>
@@ -15752,16 +15752,16 @@
         <v>45590</v>
       </c>
       <c r="B767" t="n">
-        <v>93.17691802978516</v>
+        <v>93.17691040039062</v>
       </c>
       <c r="C767" t="n">
-        <v>93.91022997004863</v>
+        <v>93.91022228060997</v>
       </c>
       <c r="D767" t="n">
-        <v>92.02590007331048</v>
+        <v>92.02589253816214</v>
       </c>
       <c r="E767" t="n">
-        <v>93.29759400747731</v>
+        <v>93.29758636820173</v>
       </c>
       <c r="F767" t="n">
         <v>563664</v>
@@ -15872,16 +15872,16 @@
         <v>45600</v>
       </c>
       <c r="B773" t="n">
-        <v>94.23511505126953</v>
+        <v>94.235107421875</v>
       </c>
       <c r="C773" t="n">
-        <v>95.19121016194849</v>
+        <v>95.19120245514728</v>
       </c>
       <c r="D773" t="n">
-        <v>91.9052329694039</v>
+        <v>91.90522552863958</v>
       </c>
       <c r="E773" t="n">
-        <v>92.32293899375905</v>
+        <v>92.32293151917671</v>
       </c>
       <c r="F773" t="n">
         <v>289905</v>
@@ -15892,16 +15892,16 @@
         <v>45601</v>
       </c>
       <c r="B774" t="n">
-        <v>95.24689483642578</v>
+        <v>95.24690246582031</v>
       </c>
       <c r="C774" t="n">
-        <v>95.47895529415376</v>
+        <v>95.47896294213662</v>
       </c>
       <c r="D774" t="n">
-        <v>93.37184237210674</v>
+        <v>93.37184985130725</v>
       </c>
       <c r="E774" t="n">
-        <v>93.57605670801507</v>
+        <v>93.57606420357338</v>
       </c>
       <c r="F774" t="n">
         <v>229590</v>
@@ -15912,16 +15912,16 @@
         <v>45602</v>
       </c>
       <c r="B775" t="n">
-        <v>94.72708892822266</v>
+        <v>94.72709655761719</v>
       </c>
       <c r="C775" t="n">
-        <v>95.38613982878644</v>
+        <v>95.38614751126146</v>
       </c>
       <c r="D775" t="n">
-        <v>91.81240992260877</v>
+        <v>91.81241731725275</v>
       </c>
       <c r="E775" t="n">
-        <v>94.21655304937283</v>
+        <v>94.2165606376484</v>
       </c>
       <c r="F775" t="n">
         <v>484922</v>
@@ -16032,16 +16032,16 @@
         <v>45610</v>
       </c>
       <c r="B781" t="n">
-        <v>90.15084838867188</v>
+        <v>90.15085601806641</v>
       </c>
       <c r="C781" t="n">
-        <v>91.79383329914289</v>
+        <v>91.79384106758192</v>
       </c>
       <c r="D781" t="n">
-        <v>89.28758321010626</v>
+        <v>89.28759076644334</v>
       </c>
       <c r="E781" t="n">
-        <v>90.22510235224161</v>
+        <v>90.22510998792019</v>
       </c>
       <c r="F781" t="n">
         <v>249817</v>
@@ -16112,16 +16112,16 @@
         <v>45618</v>
       </c>
       <c r="B785" t="n">
-        <v>85.32399749755859</v>
+        <v>85.32398986816406</v>
       </c>
       <c r="C785" t="n">
-        <v>86.79062146366518</v>
+        <v>86.79061370312989</v>
       </c>
       <c r="D785" t="n">
-        <v>83.8759423361452</v>
+        <v>83.87593483623105</v>
       </c>
       <c r="E785" t="n">
-        <v>84.55355498704292</v>
+        <v>84.55354742653884</v>
       </c>
       <c r="F785" t="n">
         <v>285924</v>
@@ -16192,16 +16192,16 @@
         <v>45624</v>
       </c>
       <c r="B789" t="n">
-        <v>77.55461883544922</v>
+        <v>77.55461120605469</v>
       </c>
       <c r="C789" t="n">
-        <v>83.54177666356864</v>
+        <v>83.54176844519063</v>
       </c>
       <c r="D789" t="n">
-        <v>77.14619010554493</v>
+        <v>77.14618251632936</v>
       </c>
       <c r="E789" t="n">
-        <v>82.6135347006401</v>
+        <v>82.6135265735774</v>
       </c>
       <c r="F789" t="n">
         <v>741463</v>
@@ -16252,16 +16252,16 @@
         <v>45629</v>
       </c>
       <c r="B792" t="n">
-        <v>75.2525634765625</v>
+        <v>75.25257110595703</v>
       </c>
       <c r="C792" t="n">
-        <v>78.61280138821857</v>
+        <v>78.61280935828697</v>
       </c>
       <c r="D792" t="n">
-        <v>75.17830243188078</v>
+        <v>75.17831005374644</v>
       </c>
       <c r="E792" t="n">
-        <v>77.94446614992914</v>
+        <v>77.94447405223913</v>
       </c>
       <c r="F792" t="n">
         <v>1021625</v>
@@ -16272,16 +16272,16 @@
         <v>45630</v>
       </c>
       <c r="B793" t="n">
-        <v>75.22472381591797</v>
+        <v>75.2247314453125</v>
       </c>
       <c r="C793" t="n">
-        <v>76.09727346105902</v>
+        <v>76.09728117894873</v>
       </c>
       <c r="D793" t="n">
-        <v>74.39858909817006</v>
+        <v>74.39859664377688</v>
       </c>
       <c r="E793" t="n">
-        <v>75.41965376350666</v>
+        <v>75.41966141267126</v>
       </c>
       <c r="F793" t="n">
         <v>411810</v>
@@ -16312,16 +16312,16 @@
         <v>45632</v>
       </c>
       <c r="B795" t="n">
-        <v>75.78166961669922</v>
+        <v>75.78166198730469</v>
       </c>
       <c r="C795" t="n">
-        <v>75.78166961669922</v>
+        <v>75.78166198730469</v>
       </c>
       <c r="D795" t="n">
-        <v>74.25935343777866</v>
+        <v>74.25934596164483</v>
       </c>
       <c r="E795" t="n">
-        <v>75.651716314737</v>
+        <v>75.65170869842567</v>
       </c>
       <c r="F795" t="n">
         <v>1017781</v>

--- a/database/XPBR31.xlsx
+++ b/database/XPBR31.xlsx
@@ -452,16 +452,16 @@
         <v>44473</v>
       </c>
       <c r="B2" t="n">
-        <v>196.6089630126953</v>
+        <v>196.6089782714844</v>
       </c>
       <c r="C2" t="n">
-        <v>203.5754849761604</v>
+        <v>203.5755007756201</v>
       </c>
       <c r="D2" t="n">
-        <v>191.4433613739322</v>
+        <v>191.4433762318198</v>
       </c>
       <c r="E2" t="n">
-        <v>191.9528946938346</v>
+        <v>191.9529095912669</v>
       </c>
       <c r="F2" t="n">
         <v>9950865</v>
@@ -492,16 +492,16 @@
         <v>44475</v>
       </c>
       <c r="B4" t="n">
-        <v>189.4491729736328</v>
+        <v>189.4491577148438</v>
       </c>
       <c r="C4" t="n">
-        <v>191.004127089414</v>
+        <v>191.0041117053844</v>
       </c>
       <c r="D4" t="n">
-        <v>181.8501271294555</v>
+        <v>181.8501124827158</v>
       </c>
       <c r="E4" t="n">
-        <v>191.004127089414</v>
+        <v>191.0041117053844</v>
       </c>
       <c r="F4" t="n">
         <v>2556665</v>
@@ -532,16 +532,16 @@
         <v>44477</v>
       </c>
       <c r="B6" t="n">
-        <v>193.8241119384766</v>
+        <v>193.8241271972656</v>
       </c>
       <c r="C6" t="n">
-        <v>204.8668871514385</v>
+        <v>204.8669032795693</v>
       </c>
       <c r="D6" t="n">
-        <v>191.7947722500135</v>
+        <v>191.794787349043</v>
       </c>
       <c r="E6" t="n">
-        <v>200.9926858889775</v>
+        <v>200.9927017121121</v>
       </c>
       <c r="F6" t="n">
         <v>4982319</v>
@@ -572,16 +572,16 @@
         <v>44482</v>
       </c>
       <c r="B8" t="n">
-        <v>169.5510559082031</v>
+        <v>169.5510711669922</v>
       </c>
       <c r="C8" t="n">
-        <v>178.8631918019051</v>
+        <v>178.8632078987421</v>
       </c>
       <c r="D8" t="n">
-        <v>169.5510559082031</v>
+        <v>169.5510711669922</v>
       </c>
       <c r="E8" t="n">
-        <v>174.4091757641661</v>
+        <v>174.4091914601629</v>
       </c>
       <c r="F8" t="n">
         <v>3487621</v>
@@ -592,16 +592,16 @@
         <v>44483</v>
       </c>
       <c r="B9" t="n">
-        <v>164.7632293701172</v>
+        <v>164.7632446289062</v>
       </c>
       <c r="C9" t="n">
-        <v>173.8293727564489</v>
+        <v>173.8293888548571</v>
       </c>
       <c r="D9" t="n">
-        <v>164.2888302749371</v>
+        <v>164.2888454897918</v>
       </c>
       <c r="E9" t="n">
-        <v>171.8351807306346</v>
+        <v>171.8351966443599</v>
       </c>
       <c r="F9" t="n">
         <v>3205420</v>
@@ -672,16 +672,16 @@
         <v>44489</v>
       </c>
       <c r="B13" t="n">
-        <v>174.3828430175781</v>
+        <v>174.3828582763672</v>
       </c>
       <c r="C13" t="n">
-        <v>178.4942305647025</v>
+        <v>178.4942461832448</v>
       </c>
       <c r="D13" t="n">
-        <v>169.8409841808207</v>
+        <v>169.8409990421895</v>
       </c>
       <c r="E13" t="n">
-        <v>176.5791004863134</v>
+        <v>176.5791159372786</v>
       </c>
       <c r="F13" t="n">
         <v>1907987</v>
@@ -772,16 +772,16 @@
         <v>44496</v>
       </c>
       <c r="B18" t="n">
-        <v>163.8320465087891</v>
+        <v>163.8320159912109</v>
       </c>
       <c r="C18" t="n">
-        <v>168.5408236197128</v>
+        <v>168.540792225014</v>
       </c>
       <c r="D18" t="n">
-        <v>163.8320465087891</v>
+        <v>163.8320159912109</v>
       </c>
       <c r="E18" t="n">
-        <v>166.9155875370005</v>
+        <v>166.9155564450402</v>
       </c>
       <c r="F18" t="n">
         <v>503418</v>
@@ -792,16 +792,16 @@
         <v>44497</v>
       </c>
       <c r="B19" t="n">
-        <v>165.1673583984375</v>
+        <v>165.1673431396484</v>
       </c>
       <c r="C19" t="n">
-        <v>166.8101682649443</v>
+        <v>166.8101528543862</v>
       </c>
       <c r="D19" t="n">
-        <v>158.6664410017166</v>
+        <v>158.6664263435071</v>
       </c>
       <c r="E19" t="n">
-        <v>163.4103522474434</v>
+        <v>163.4103371509733</v>
       </c>
       <c r="F19" t="n">
         <v>1047427</v>
@@ -832,16 +832,16 @@
         <v>44501</v>
       </c>
       <c r="B21" t="n">
-        <v>169.7267913818359</v>
+        <v>169.7267761230469</v>
       </c>
       <c r="C21" t="n">
-        <v>171.2026835181439</v>
+        <v>171.2026681266692</v>
       </c>
       <c r="D21" t="n">
-        <v>161.9344733973998</v>
+        <v>161.9344588391563</v>
       </c>
       <c r="E21" t="n">
-        <v>162.5230688489684</v>
+        <v>162.5230542378089</v>
       </c>
       <c r="F21" t="n">
         <v>466029</v>
@@ -892,16 +892,16 @@
         <v>44505</v>
       </c>
       <c r="B24" t="n">
-        <v>170.4735260009766</v>
+        <v>170.4735107421875</v>
       </c>
       <c r="C24" t="n">
-        <v>171.3081012491605</v>
+        <v>171.30808591567</v>
       </c>
       <c r="D24" t="n">
-        <v>159.1408281830961</v>
+        <v>159.1408139386772</v>
       </c>
       <c r="E24" t="n">
-        <v>160.9417621848993</v>
+        <v>160.9417477792819</v>
       </c>
       <c r="F24" t="n">
         <v>806903</v>
@@ -932,16 +932,16 @@
         <v>44509</v>
       </c>
       <c r="B26" t="n">
-        <v>163.7705383300781</v>
+        <v>163.7705230712891</v>
       </c>
       <c r="C26" t="n">
-        <v>169.8497778778882</v>
+        <v>169.8497620526857</v>
       </c>
       <c r="D26" t="n">
-        <v>162.0838140686822</v>
+        <v>162.0837989670482</v>
       </c>
       <c r="E26" t="n">
-        <v>167.3548324123792</v>
+        <v>167.3548168196352</v>
       </c>
       <c r="F26" t="n">
         <v>336270</v>
@@ -952,16 +952,16 @@
         <v>44510</v>
       </c>
       <c r="B27" t="n">
-        <v>158.5697937011719</v>
+        <v>158.5697784423828</v>
       </c>
       <c r="C27" t="n">
-        <v>165.99314147324</v>
+        <v>165.9931255001201</v>
       </c>
       <c r="D27" t="n">
-        <v>157.9109164420257</v>
+        <v>157.9109012466388</v>
       </c>
       <c r="E27" t="n">
-        <v>162.8305386722738</v>
+        <v>162.8305230034835</v>
       </c>
       <c r="F27" t="n">
         <v>596401</v>
@@ -992,16 +992,16 @@
         <v>44512</v>
       </c>
       <c r="B29" t="n">
-        <v>161.6533355712891</v>
+        <v>161.6533203125</v>
       </c>
       <c r="C29" t="n">
-        <v>162.5230583851655</v>
+        <v>162.5230430442815</v>
       </c>
       <c r="D29" t="n">
-        <v>157.4277381980575</v>
+        <v>157.4277233381312</v>
       </c>
       <c r="E29" t="n">
-        <v>162.1804427442249</v>
+        <v>162.1804274356811</v>
       </c>
       <c r="F29" t="n">
         <v>339439</v>
@@ -1052,16 +1052,16 @@
         <v>44518</v>
       </c>
       <c r="B32" t="n">
-        <v>141.1403045654297</v>
+        <v>141.1402893066406</v>
       </c>
       <c r="C32" t="n">
-        <v>149.7320634033205</v>
+        <v>149.7320472156696</v>
       </c>
       <c r="D32" t="n">
-        <v>141.1403045654297</v>
+        <v>141.1402893066406</v>
       </c>
       <c r="E32" t="n">
-        <v>147.8520673947305</v>
+        <v>147.8520514103275</v>
       </c>
       <c r="F32" t="n">
         <v>1135748</v>
@@ -1092,16 +1092,16 @@
         <v>44522</v>
       </c>
       <c r="B34" t="n">
-        <v>140.0509338378906</v>
+        <v>140.0509490966797</v>
       </c>
       <c r="C34" t="n">
-        <v>150.6632507155369</v>
+        <v>150.6632671305561</v>
       </c>
       <c r="D34" t="n">
-        <v>139.9015899501414</v>
+        <v>139.9016051926592</v>
       </c>
       <c r="E34" t="n">
-        <v>145.9281205149585</v>
+        <v>145.9281364140771</v>
       </c>
       <c r="F34" t="n">
         <v>547961</v>
@@ -1132,16 +1132,16 @@
         <v>44524</v>
       </c>
       <c r="B36" t="n">
-        <v>148.7393493652344</v>
+        <v>148.7393341064453</v>
       </c>
       <c r="C36" t="n">
-        <v>150.2152414609149</v>
+        <v>150.2152260507179</v>
       </c>
       <c r="D36" t="n">
-        <v>144.4171159644937</v>
+        <v>144.4171011491115</v>
       </c>
       <c r="E36" t="n">
-        <v>144.5225320410092</v>
+        <v>144.5225172148126</v>
       </c>
       <c r="F36" t="n">
         <v>231702</v>
@@ -1152,16 +1152,16 @@
         <v>44525</v>
       </c>
       <c r="B37" t="n">
-        <v>151.3133697509766</v>
+        <v>151.3133850097656</v>
       </c>
       <c r="C37" t="n">
-        <v>152.8507500843435</v>
+        <v>152.8507654981656</v>
       </c>
       <c r="D37" t="n">
-        <v>148.0716913604085</v>
+        <v>148.0717062922993</v>
       </c>
       <c r="E37" t="n">
-        <v>148.0716913604085</v>
+        <v>148.0717062922993</v>
       </c>
       <c r="F37" t="n">
         <v>222385</v>
@@ -1172,16 +1172,16 @@
         <v>44526</v>
       </c>
       <c r="B38" t="n">
-        <v>146.7363586425781</v>
+        <v>146.7363739013672</v>
       </c>
       <c r="C38" t="n">
-        <v>148.7305642552127</v>
+        <v>148.7305797213747</v>
       </c>
       <c r="D38" t="n">
-        <v>143.3716904608705</v>
+        <v>143.3717053697751</v>
       </c>
       <c r="E38" t="n">
-        <v>148.7305642552127</v>
+        <v>148.7305797213747</v>
       </c>
       <c r="F38" t="n">
         <v>241997</v>
@@ -1192,16 +1192,16 @@
         <v>44529</v>
       </c>
       <c r="B39" t="n">
-        <v>147.0174865722656</v>
+        <v>147.0174713134766</v>
       </c>
       <c r="C39" t="n">
-        <v>150.434862802775</v>
+        <v>150.4348471893001</v>
       </c>
       <c r="D39" t="n">
-        <v>146.0247738646084</v>
+        <v>146.0247587088519</v>
       </c>
       <c r="E39" t="n">
-        <v>148.730564789764</v>
+        <v>148.7305493531764</v>
       </c>
       <c r="F39" t="n">
         <v>333389</v>
@@ -1212,16 +1212,16 @@
         <v>44530</v>
       </c>
       <c r="B40" t="n">
-        <v>140.5604705810547</v>
+        <v>140.5604858398438</v>
       </c>
       <c r="C40" t="n">
-        <v>147.3073667345976</v>
+        <v>147.3073827258078</v>
       </c>
       <c r="D40" t="n">
-        <v>139.7610296874511</v>
+        <v>139.7610448594554</v>
       </c>
       <c r="E40" t="n">
-        <v>147.3073667345976</v>
+        <v>147.3073827258078</v>
       </c>
       <c r="F40" t="n">
         <v>711030</v>
@@ -1232,16 +1232,16 @@
         <v>44531</v>
       </c>
       <c r="B41" t="n">
-        <v>144.3116912841797</v>
+        <v>144.3116760253906</v>
       </c>
       <c r="C41" t="n">
-        <v>151.2342857954605</v>
+        <v>151.2342698047112</v>
       </c>
       <c r="D41" t="n">
-        <v>141.4477629305895</v>
+        <v>141.4477479746177</v>
       </c>
       <c r="E41" t="n">
-        <v>142.317485724668</v>
+        <v>142.3174706767361</v>
       </c>
       <c r="F41" t="n">
         <v>941983</v>
@@ -1272,16 +1272,16 @@
         <v>44533</v>
       </c>
       <c r="B43" t="n">
-        <v>144.0657196044922</v>
+        <v>144.0657348632812</v>
       </c>
       <c r="C43" t="n">
-        <v>149.3455180949097</v>
+        <v>149.3455339129111</v>
       </c>
       <c r="D43" t="n">
-        <v>142.67768318067</v>
+        <v>142.6776982924445</v>
       </c>
       <c r="E43" t="n">
-        <v>143.564966433002</v>
+        <v>143.5649816387535</v>
       </c>
       <c r="F43" t="n">
         <v>471453</v>
@@ -1312,16 +1312,16 @@
         <v>44537</v>
       </c>
       <c r="B45" t="n">
-        <v>148.0277404785156</v>
+        <v>148.0277557373047</v>
       </c>
       <c r="C45" t="n">
-        <v>153.0439979976308</v>
+        <v>153.0440137734988</v>
       </c>
       <c r="D45" t="n">
-        <v>147.8871767956056</v>
+        <v>147.8871920399053</v>
       </c>
       <c r="E45" t="n">
-        <v>150.2239977556449</v>
+        <v>150.2240132408255</v>
       </c>
       <c r="F45" t="n">
         <v>560968</v>
@@ -1352,16 +1352,16 @@
         <v>44539</v>
       </c>
       <c r="B47" t="n">
-        <v>146.6836395263672</v>
+        <v>146.6836547851562</v>
       </c>
       <c r="C47" t="n">
-        <v>148.8974707272065</v>
+        <v>148.8974862162897</v>
       </c>
       <c r="D47" t="n">
-        <v>143.7318690602119</v>
+        <v>143.7318840119426</v>
       </c>
       <c r="E47" t="n">
-        <v>146.4464399750544</v>
+        <v>146.4464552091688</v>
       </c>
       <c r="F47" t="n">
         <v>319045</v>
@@ -1372,16 +1372,16 @@
         <v>44540</v>
       </c>
       <c r="B48" t="n">
-        <v>148.2210235595703</v>
+        <v>148.2210388183594</v>
       </c>
       <c r="C48" t="n">
-        <v>150.2240092775463</v>
+        <v>150.2240247425351</v>
       </c>
       <c r="D48" t="n">
-        <v>146.3322475183298</v>
+        <v>146.3322625826765</v>
       </c>
       <c r="E48" t="n">
-        <v>148.1156074917479</v>
+        <v>148.1156227396848</v>
       </c>
       <c r="F48" t="n">
         <v>506410</v>
@@ -1392,16 +1392,16 @@
         <v>44543</v>
       </c>
       <c r="B49" t="n">
-        <v>155.4950561523438</v>
+        <v>155.4950408935547</v>
       </c>
       <c r="C49" t="n">
-        <v>159.5537363792964</v>
+        <v>159.5537207222275</v>
       </c>
       <c r="D49" t="n">
-        <v>147.1580565080183</v>
+        <v>147.1580420673422</v>
       </c>
       <c r="E49" t="n">
-        <v>148.2034773919047</v>
+        <v>148.2034628486411</v>
       </c>
       <c r="F49" t="n">
         <v>707090</v>
@@ -1412,16 +1412,16 @@
         <v>44544</v>
       </c>
       <c r="B50" t="n">
-        <v>147.2283020019531</v>
+        <v>147.2283172607422</v>
       </c>
       <c r="C50" t="n">
-        <v>150.9268052148167</v>
+        <v>150.9268208569199</v>
       </c>
       <c r="D50" t="n">
-        <v>141.1227093534192</v>
+        <v>141.1227239794226</v>
       </c>
       <c r="E50" t="n">
-        <v>150.6632516563057</v>
+        <v>150.663267271094</v>
       </c>
       <c r="F50" t="n">
         <v>995575</v>
@@ -1432,16 +1432,16 @@
         <v>44545</v>
       </c>
       <c r="B51" t="n">
-        <v>150.6983795166016</v>
+        <v>150.6983947753906</v>
       </c>
       <c r="C51" t="n">
-        <v>151.5417481872738</v>
+        <v>151.5417635314571</v>
       </c>
       <c r="D51" t="n">
-        <v>142.2296122120707</v>
+        <v>142.2296266133646</v>
       </c>
       <c r="E51" t="n">
-        <v>145.8402596181196</v>
+        <v>145.8402743850054</v>
       </c>
       <c r="F51" t="n">
         <v>314440</v>
@@ -1512,16 +1512,16 @@
         <v>44551</v>
       </c>
       <c r="B55" t="n">
-        <v>148.9853363037109</v>
+        <v>148.9853210449219</v>
       </c>
       <c r="C55" t="n">
-        <v>149.6442136233681</v>
+        <v>149.6441982970981</v>
       </c>
       <c r="D55" t="n">
-        <v>144.7948862022144</v>
+        <v>144.7948713726031</v>
       </c>
       <c r="E55" t="n">
-        <v>146.3146927995202</v>
+        <v>146.3146778142533</v>
       </c>
       <c r="F55" t="n">
         <v>221674</v>
@@ -1532,16 +1532,16 @@
         <v>44552</v>
       </c>
       <c r="B56" t="n">
-        <v>146.2268371582031</v>
+        <v>146.2268218994141</v>
       </c>
       <c r="C56" t="n">
-        <v>148.9502021086343</v>
+        <v>148.9501865656617</v>
       </c>
       <c r="D56" t="n">
-        <v>144.0745072611944</v>
+        <v>144.0744922270013</v>
       </c>
       <c r="E56" t="n">
-        <v>147.7202897354198</v>
+        <v>147.7202743207887</v>
       </c>
       <c r="F56" t="n">
         <v>439793</v>
@@ -1572,16 +1572,16 @@
         <v>44557</v>
       </c>
       <c r="B58" t="n">
-        <v>150.0483093261719</v>
+        <v>150.0483245849609</v>
       </c>
       <c r="C58" t="n">
-        <v>153.6940912743883</v>
+        <v>153.6941069039261</v>
       </c>
       <c r="D58" t="n">
-        <v>147.0438307899898</v>
+        <v>147.0438457432459</v>
       </c>
       <c r="E58" t="n">
-        <v>147.0438307899898</v>
+        <v>147.0438457432459</v>
       </c>
       <c r="F58" t="n">
         <v>232495</v>
@@ -1632,16 +1632,16 @@
         <v>44560</v>
       </c>
       <c r="B61" t="n">
-        <v>140.9909515380859</v>
+        <v>140.9909362792969</v>
       </c>
       <c r="C61" t="n">
-        <v>141.2632853237713</v>
+        <v>141.2632700355088</v>
       </c>
       <c r="D61" t="n">
-        <v>136.7126328054061</v>
+        <v>136.7126180096394</v>
       </c>
       <c r="E61" t="n">
-        <v>140.0333730787222</v>
+        <v>140.0333579235674</v>
       </c>
       <c r="F61" t="n">
         <v>445854</v>
@@ -1652,16 +1652,16 @@
         <v>44564</v>
       </c>
       <c r="B62" t="n">
-        <v>144.8124237060547</v>
+        <v>144.8124389648438</v>
       </c>
       <c r="C62" t="n">
-        <v>144.8124237060547</v>
+        <v>144.8124389648438</v>
       </c>
       <c r="D62" t="n">
-        <v>138.7946865146767</v>
+        <v>138.7947011393807</v>
       </c>
       <c r="E62" t="n">
-        <v>142.1769148443119</v>
+        <v>142.1769298253991</v>
       </c>
       <c r="F62" t="n">
         <v>369633</v>
@@ -1732,16 +1732,16 @@
         <v>44568</v>
       </c>
       <c r="B66" t="n">
-        <v>137.23974609375</v>
+        <v>137.2397308349609</v>
       </c>
       <c r="C66" t="n">
-        <v>142.1857225025721</v>
+        <v>142.1857066938723</v>
       </c>
       <c r="D66" t="n">
-        <v>134.2001196747043</v>
+        <v>134.2001047538714</v>
       </c>
       <c r="E66" t="n">
-        <v>137.9249773931206</v>
+        <v>137.9249620581452</v>
       </c>
       <c r="F66" t="n">
         <v>686988</v>
@@ -1772,16 +1772,16 @@
         <v>44572</v>
       </c>
       <c r="B68" t="n">
-        <v>146.3849487304688</v>
+        <v>146.3849639892578</v>
       </c>
       <c r="C68" t="n">
-        <v>149.0116639338405</v>
+        <v>149.0116794664315</v>
       </c>
       <c r="D68" t="n">
-        <v>133.6290823276248</v>
+        <v>133.6290962567753</v>
       </c>
       <c r="E68" t="n">
-        <v>137.573565341825</v>
+        <v>137.5735796821382</v>
       </c>
       <c r="F68" t="n">
         <v>715197</v>
@@ -1792,16 +1792,16 @@
         <v>44573</v>
       </c>
       <c r="B69" t="n">
-        <v>149.4421234130859</v>
+        <v>149.4421539306641</v>
       </c>
       <c r="C69" t="n">
-        <v>150.7950119316671</v>
+        <v>150.7950427255186</v>
       </c>
       <c r="D69" t="n">
-        <v>145.5591423450761</v>
+        <v>145.5591720697106</v>
       </c>
       <c r="E69" t="n">
-        <v>146.4464254160041</v>
+        <v>146.4464553218307</v>
       </c>
       <c r="F69" t="n">
         <v>416574</v>
@@ -1812,16 +1812,16 @@
         <v>44574</v>
       </c>
       <c r="B70" t="n">
-        <v>142.9675903320312</v>
+        <v>142.9675750732422</v>
       </c>
       <c r="C70" t="n">
-        <v>149.6529990389454</v>
+        <v>149.6529830666293</v>
       </c>
       <c r="D70" t="n">
-        <v>141.7201176170415</v>
+        <v>141.7201024913939</v>
       </c>
       <c r="E70" t="n">
-        <v>149.4860813156558</v>
+        <v>149.4860653611546</v>
       </c>
       <c r="F70" t="n">
         <v>401557</v>
@@ -1872,16 +1872,16 @@
         <v>44579</v>
       </c>
       <c r="B73" t="n">
-        <v>133.1722564697266</v>
+        <v>133.1722412109375</v>
       </c>
       <c r="C73" t="n">
-        <v>138.8034634905354</v>
+        <v>138.8034475865263</v>
       </c>
       <c r="D73" t="n">
-        <v>133.1722564697266</v>
+        <v>133.1722412109375</v>
       </c>
       <c r="E73" t="n">
-        <v>138.1885141180745</v>
+        <v>138.188498284526</v>
       </c>
       <c r="F73" t="n">
         <v>435258</v>
@@ -1892,16 +1892,16 @@
         <v>44580</v>
       </c>
       <c r="B74" t="n">
-        <v>139.6116790771484</v>
+        <v>139.6116943359375</v>
       </c>
       <c r="C74" t="n">
-        <v>141.6937266578653</v>
+        <v>141.6937421442108</v>
       </c>
       <c r="D74" t="n">
-        <v>133.0492613503245</v>
+        <v>133.0492758918774</v>
       </c>
       <c r="E74" t="n">
-        <v>133.5324406256718</v>
+        <v>133.5324552200335</v>
       </c>
       <c r="F74" t="n">
         <v>381153</v>
@@ -2012,16 +2012,16 @@
         <v>44588</v>
       </c>
       <c r="B80" t="n">
-        <v>149.486083984375</v>
+        <v>149.4860992431641</v>
       </c>
       <c r="C80" t="n">
-        <v>156.5668165068679</v>
+        <v>156.5668324884226</v>
       </c>
       <c r="D80" t="n">
-        <v>147.3249605575002</v>
+        <v>147.3249755956927</v>
       </c>
       <c r="E80" t="n">
-        <v>151.5417779286678</v>
+        <v>151.5417933972918</v>
       </c>
       <c r="F80" t="n">
         <v>697237</v>
@@ -2032,16 +2032,16 @@
         <v>44589</v>
       </c>
       <c r="B81" t="n">
-        <v>147.5533447265625</v>
+        <v>147.5533752441406</v>
       </c>
       <c r="C81" t="n">
-        <v>149.9252997428738</v>
+        <v>149.9253307510293</v>
       </c>
       <c r="D81" t="n">
-        <v>142.7479330600334</v>
+        <v>142.7479625837369</v>
       </c>
       <c r="E81" t="n">
-        <v>149.4948285201981</v>
+        <v>149.4948594393217</v>
       </c>
       <c r="F81" t="n">
         <v>1084942</v>
@@ -2052,16 +2052,16 @@
         <v>44592</v>
       </c>
       <c r="B82" t="n">
-        <v>155.0558013916016</v>
+        <v>155.0557861328125</v>
       </c>
       <c r="C82" t="n">
-        <v>155.3193550097899</v>
+        <v>155.3193397250649</v>
       </c>
       <c r="D82" t="n">
-        <v>145.8666528160763</v>
+        <v>145.8666384615764</v>
       </c>
       <c r="E82" t="n">
-        <v>147.0175031686687</v>
+        <v>147.0174887009155</v>
       </c>
       <c r="F82" t="n">
         <v>286473</v>
@@ -2092,16 +2092,16 @@
         <v>44594</v>
       </c>
       <c r="B84" t="n">
-        <v>148.9941253662109</v>
+        <v>148.9941101074219</v>
       </c>
       <c r="C84" t="n">
-        <v>158.1305518913071</v>
+        <v>158.1305356968381</v>
       </c>
       <c r="D84" t="n">
-        <v>148.9062696976475</v>
+        <v>148.9062544478559</v>
       </c>
       <c r="E84" t="n">
-        <v>155.8025241281978</v>
+        <v>155.8025081721468</v>
       </c>
       <c r="F84" t="n">
         <v>466282</v>
@@ -2152,16 +2152,16 @@
         <v>44599</v>
       </c>
       <c r="B87" t="n">
-        <v>147.1228942871094</v>
+        <v>147.1228790283203</v>
       </c>
       <c r="C87" t="n">
-        <v>152.183066597055</v>
+        <v>152.1830508134523</v>
       </c>
       <c r="D87" t="n">
-        <v>146.709996816492</v>
+        <v>146.7099816005264</v>
       </c>
       <c r="E87" t="n">
-        <v>149.5651314850764</v>
+        <v>149.5651159729917</v>
       </c>
       <c r="F87" t="n">
         <v>353300</v>
@@ -2172,16 +2172,16 @@
         <v>44600</v>
       </c>
       <c r="B88" t="n">
-        <v>149.3191680908203</v>
+        <v>149.3191528320312</v>
       </c>
       <c r="C88" t="n">
-        <v>149.3191680908203</v>
+        <v>149.3191528320312</v>
       </c>
       <c r="D88" t="n">
-        <v>144.2326278016086</v>
+        <v>144.2326130626084</v>
       </c>
       <c r="E88" t="n">
-        <v>147.6763716371699</v>
+        <v>147.6763565462567</v>
       </c>
       <c r="F88" t="n">
         <v>326666</v>
@@ -2192,16 +2192,16 @@
         <v>44601</v>
       </c>
       <c r="B89" t="n">
-        <v>157.5155944824219</v>
+        <v>157.5156097412109</v>
       </c>
       <c r="C89" t="n">
-        <v>159.7996942960607</v>
+        <v>159.7997097761142</v>
       </c>
       <c r="D89" t="n">
-        <v>151.4275615710859</v>
+        <v>151.4275762401174</v>
       </c>
       <c r="E89" t="n">
-        <v>153.7380288078784</v>
+        <v>153.7380437007286</v>
       </c>
       <c r="F89" t="n">
         <v>1361639</v>
@@ -2212,16 +2212,16 @@
         <v>44602</v>
       </c>
       <c r="B90" t="n">
-        <v>152.6311187744141</v>
+        <v>152.631103515625</v>
       </c>
       <c r="C90" t="n">
-        <v>163.1380073355108</v>
+        <v>163.1379910263304</v>
       </c>
       <c r="D90" t="n">
-        <v>151.2870102327762</v>
+        <v>151.2869951083599</v>
       </c>
       <c r="E90" t="n">
-        <v>157.5155933969532</v>
+        <v>157.515577649855</v>
       </c>
       <c r="F90" t="n">
         <v>704053</v>
@@ -2232,16 +2232,16 @@
         <v>44603</v>
       </c>
       <c r="B91" t="n">
-        <v>156.0045471191406</v>
+        <v>156.0045623779297</v>
       </c>
       <c r="C91" t="n">
-        <v>160.1510818935806</v>
+        <v>160.1510975579418</v>
       </c>
       <c r="D91" t="n">
-        <v>151.3309052409586</v>
+        <v>151.3309200426192</v>
       </c>
       <c r="E91" t="n">
-        <v>152.376325840283</v>
+        <v>152.3763407441961</v>
       </c>
       <c r="F91" t="n">
         <v>740597</v>
@@ -2252,16 +2252,16 @@
         <v>44606</v>
       </c>
       <c r="B92" t="n">
-        <v>152.9473724365234</v>
+        <v>152.9473571777344</v>
       </c>
       <c r="C92" t="n">
-        <v>157.9196890589268</v>
+        <v>157.9196733040747</v>
       </c>
       <c r="D92" t="n">
-        <v>152.0688694665374</v>
+        <v>152.0688542953922</v>
       </c>
       <c r="E92" t="n">
-        <v>156.0045590187052</v>
+        <v>156.004543454916</v>
       </c>
       <c r="F92" t="n">
         <v>409040</v>
@@ -2312,16 +2312,16 @@
         <v>44609</v>
       </c>
       <c r="B95" t="n">
-        <v>156.6282958984375</v>
+        <v>156.6282806396484</v>
       </c>
       <c r="C95" t="n">
-        <v>161.1877286693031</v>
+        <v>161.1877129663323</v>
       </c>
       <c r="D95" t="n">
-        <v>156.1626903751017</v>
+        <v>156.1626751616721</v>
       </c>
       <c r="E95" t="n">
-        <v>160.8011851997657</v>
+        <v>160.8011695344521</v>
       </c>
       <c r="F95" t="n">
         <v>315564</v>
@@ -2332,16 +2332,16 @@
         <v>44610</v>
       </c>
       <c r="B96" t="n">
-        <v>155.4950561523438</v>
+        <v>155.4950408935547</v>
       </c>
       <c r="C96" t="n">
-        <v>159.5361759679781</v>
+        <v>159.5361603126324</v>
       </c>
       <c r="D96" t="n">
-        <v>153.4744962445266</v>
+        <v>153.4744811840158</v>
       </c>
       <c r="E96" t="n">
-        <v>156.9885088129411</v>
+        <v>156.988493407599</v>
       </c>
       <c r="F96" t="n">
         <v>742998</v>
@@ -2352,16 +2352,16 @@
         <v>44613</v>
       </c>
       <c r="B97" t="n">
-        <v>150.3118743896484</v>
+        <v>150.3118591308594</v>
       </c>
       <c r="C97" t="n">
-        <v>155.6883086649541</v>
+        <v>155.6882928603806</v>
       </c>
       <c r="D97" t="n">
-        <v>149.5827152632765</v>
+        <v>149.5827000785075</v>
       </c>
       <c r="E97" t="n">
-        <v>154.6165338917224</v>
+        <v>154.6165181959493</v>
       </c>
       <c r="F97" t="n">
         <v>185476</v>
@@ -2372,16 +2372,16 @@
         <v>44614</v>
       </c>
       <c r="B98" t="n">
-        <v>150.3557739257812</v>
+        <v>150.3557586669922</v>
       </c>
       <c r="C98" t="n">
-        <v>155.0557700513334</v>
+        <v>155.0557543155673</v>
       </c>
       <c r="D98" t="n">
-        <v>149.6793363085237</v>
+        <v>149.6793211183826</v>
       </c>
       <c r="E98" t="n">
-        <v>150.5314852389875</v>
+        <v>150.5314699623664</v>
       </c>
       <c r="F98" t="n">
         <v>352471</v>
@@ -2412,16 +2412,16 @@
         <v>44616</v>
       </c>
       <c r="B100" t="n">
-        <v>148.1067962646484</v>
+        <v>148.1068267822266</v>
       </c>
       <c r="C100" t="n">
-        <v>148.1067962646484</v>
+        <v>148.1068267822266</v>
       </c>
       <c r="D100" t="n">
-        <v>139.2427054859054</v>
+        <v>139.2427341770273</v>
       </c>
       <c r="E100" t="n">
-        <v>143.3277384867851</v>
+        <v>143.3277680196328</v>
       </c>
       <c r="F100" t="n">
         <v>704723</v>
@@ -2512,16 +2512,16 @@
         <v>44627</v>
       </c>
       <c r="B105" t="n">
-        <v>117.0781021118164</v>
+        <v>117.0780868530273</v>
       </c>
       <c r="C105" t="n">
-        <v>130.2644277157113</v>
+        <v>130.2644107383485</v>
       </c>
       <c r="D105" t="n">
-        <v>117.0781021118164</v>
+        <v>117.0780868530273</v>
       </c>
       <c r="E105" t="n">
-        <v>129.5791964273345</v>
+        <v>129.5791795392778</v>
       </c>
       <c r="F105" t="n">
         <v>1053703</v>
@@ -2532,16 +2532,16 @@
         <v>44628</v>
       </c>
       <c r="B106" t="n">
-        <v>124.43994140625</v>
+        <v>124.4399261474609</v>
       </c>
       <c r="C106" t="n">
-        <v>125.6083519749621</v>
+        <v>125.6083365729028</v>
       </c>
       <c r="D106" t="n">
-        <v>115.8657571712436</v>
+        <v>115.8657429638185</v>
       </c>
       <c r="E106" t="n">
-        <v>118.3431420022477</v>
+        <v>118.3431274910464</v>
       </c>
       <c r="F106" t="n">
         <v>713320</v>
@@ -2572,16 +2572,16 @@
         <v>44630</v>
       </c>
       <c r="B108" t="n">
-        <v>135.7814331054688</v>
+        <v>135.7814178466797</v>
       </c>
       <c r="C108" t="n">
-        <v>139.1636753056343</v>
+        <v>139.163659666757</v>
       </c>
       <c r="D108" t="n">
-        <v>133.2425597553211</v>
+        <v>133.2425447818445</v>
       </c>
       <c r="E108" t="n">
-        <v>137.4857312154787</v>
+        <v>137.4857157651647</v>
       </c>
       <c r="F108" t="n">
         <v>543810</v>
@@ -2612,16 +2612,16 @@
         <v>44634</v>
       </c>
       <c r="B110" t="n">
-        <v>126.6801376342773</v>
+        <v>126.6801223754883</v>
       </c>
       <c r="C110" t="n">
-        <v>133.831151953603</v>
+        <v>133.8311358334649</v>
       </c>
       <c r="D110" t="n">
-        <v>126.6801376342773</v>
+        <v>126.6801223754883</v>
       </c>
       <c r="E110" t="n">
-        <v>131.6173339102961</v>
+        <v>131.6173180568153</v>
       </c>
       <c r="F110" t="n">
         <v>265850</v>
@@ -2652,16 +2652,16 @@
         <v>44636</v>
       </c>
       <c r="B112" t="n">
-        <v>139.4887084960938</v>
+        <v>139.4887237548828</v>
       </c>
       <c r="C112" t="n">
-        <v>142.3438433121762</v>
+        <v>142.3438588832909</v>
       </c>
       <c r="D112" t="n">
-        <v>132.6539560702938</v>
+        <v>132.6539705814235</v>
       </c>
       <c r="E112" t="n">
-        <v>132.6539560702938</v>
+        <v>132.6539705814235</v>
       </c>
       <c r="F112" t="n">
         <v>861619</v>
@@ -2732,16 +2732,16 @@
         <v>44642</v>
       </c>
       <c r="B116" t="n">
-        <v>143.4683380126953</v>
+        <v>143.4683227539062</v>
       </c>
       <c r="C116" t="n">
-        <v>146.8330064684024</v>
+        <v>146.832990851759</v>
       </c>
       <c r="D116" t="n">
-        <v>139.7698474968835</v>
+        <v>139.7698326314529</v>
       </c>
       <c r="E116" t="n">
-        <v>139.7698474968835</v>
+        <v>139.7698326314529</v>
       </c>
       <c r="F116" t="n">
         <v>384464</v>
@@ -2812,16 +2812,16 @@
         <v>44648</v>
       </c>
       <c r="B120" t="n">
-        <v>134.9380645751953</v>
+        <v>134.9380798339844</v>
       </c>
       <c r="C120" t="n">
-        <v>139.8488930702739</v>
+        <v>139.8489088843792</v>
       </c>
       <c r="D120" t="n">
-        <v>132.4782535231423</v>
+        <v>132.478268503776</v>
       </c>
       <c r="E120" t="n">
-        <v>134.762353253348</v>
+        <v>134.7623684922676</v>
       </c>
       <c r="F120" t="n">
         <v>527873</v>
@@ -2832,16 +2832,16 @@
         <v>44649</v>
       </c>
       <c r="B121" t="n">
-        <v>139.5765533447266</v>
+        <v>139.5765686035156</v>
       </c>
       <c r="C121" t="n">
-        <v>140.4638365007489</v>
+        <v>140.4638518565375</v>
       </c>
       <c r="D121" t="n">
-        <v>135.1576845672471</v>
+        <v>135.1576993429566</v>
       </c>
       <c r="E121" t="n">
-        <v>137.9249635049115</v>
+        <v>137.9249785831454</v>
       </c>
       <c r="F121" t="n">
         <v>830631</v>
@@ -2852,16 +2852,16 @@
         <v>44650</v>
       </c>
       <c r="B122" t="n">
-        <v>130.6773376464844</v>
+        <v>130.6773223876953</v>
       </c>
       <c r="C122" t="n">
-        <v>139.2866708077021</v>
+        <v>139.2866545436278</v>
       </c>
       <c r="D122" t="n">
-        <v>130.6334098099942</v>
+        <v>130.6333945563345</v>
       </c>
       <c r="E122" t="n">
-        <v>137.9952701632747</v>
+        <v>137.9952540499933</v>
       </c>
       <c r="F122" t="n">
         <v>554943</v>
@@ -2872,16 +2872,16 @@
         <v>44651</v>
       </c>
       <c r="B123" t="n">
-        <v>126.065185546875</v>
+        <v>126.0651702880859</v>
       </c>
       <c r="C123" t="n">
-        <v>132.170778960327</v>
+        <v>132.1707629625238</v>
       </c>
       <c r="D123" t="n">
-        <v>123.4736042741024</v>
+        <v>123.4735893289954</v>
       </c>
       <c r="E123" t="n">
-        <v>131.6788194054147</v>
+        <v>131.6788034671577</v>
       </c>
       <c r="F123" t="n">
         <v>791956</v>
@@ -2892,16 +2892,16 @@
         <v>44652</v>
       </c>
       <c r="B124" t="n">
-        <v>127.382942199707</v>
+        <v>127.382926940918</v>
       </c>
       <c r="C124" t="n">
-        <v>129.10481407518</v>
+        <v>129.1047986101335</v>
       </c>
       <c r="D124" t="n">
-        <v>124.6156629552567</v>
+        <v>124.615648027951</v>
       </c>
       <c r="E124" t="n">
-        <v>126.5044391500539</v>
+        <v>126.5044239964978</v>
       </c>
       <c r="F124" t="n">
         <v>526406</v>
@@ -2932,16 +2932,16 @@
         <v>44656</v>
       </c>
       <c r="B126" t="n">
-        <v>128.0769348144531</v>
+        <v>128.0769500732422</v>
       </c>
       <c r="C126" t="n">
-        <v>130.1589958502732</v>
+        <v>130.1590113571142</v>
       </c>
       <c r="D126" t="n">
-        <v>125.6346977691337</v>
+        <v>125.6347127369603</v>
       </c>
       <c r="E126" t="n">
-        <v>128.2614263258134</v>
+        <v>128.2614416065824</v>
       </c>
       <c r="F126" t="n">
         <v>767000</v>
@@ -2972,16 +2972,16 @@
         <v>44658</v>
       </c>
       <c r="B128" t="n">
-        <v>126.9524536132812</v>
+        <v>126.9524688720703</v>
       </c>
       <c r="C128" t="n">
-        <v>128.6040434115682</v>
+        <v>128.6040588688667</v>
       </c>
       <c r="D128" t="n">
-        <v>122.9991904275108</v>
+        <v>122.9992052111455</v>
       </c>
       <c r="E128" t="n">
-        <v>124.7561962878532</v>
+        <v>124.7562112826676</v>
       </c>
       <c r="F128" t="n">
         <v>544395</v>
@@ -2992,16 +2992,16 @@
         <v>44659</v>
       </c>
       <c r="B129" t="n">
-        <v>123.5790023803711</v>
+        <v>123.5790176391602</v>
       </c>
       <c r="C129" t="n">
-        <v>128.0857265850804</v>
+        <v>128.0857424003326</v>
       </c>
       <c r="D129" t="n">
-        <v>123.5790023803711</v>
+        <v>123.5790176391602</v>
       </c>
       <c r="E129" t="n">
-        <v>126.7943262387589</v>
+        <v>126.7943418945568</v>
       </c>
       <c r="F129" t="n">
         <v>403536</v>
@@ -3012,16 +3012,16 @@
         <v>44662</v>
       </c>
       <c r="B130" t="n">
-        <v>121.8659210205078</v>
+        <v>121.8659286499023</v>
       </c>
       <c r="C130" t="n">
-        <v>123.570218758567</v>
+        <v>123.5702264946588</v>
       </c>
       <c r="D130" t="n">
-        <v>119.3621824416246</v>
+        <v>119.362189914273</v>
       </c>
       <c r="E130" t="n">
-        <v>122.990403638526</v>
+        <v>122.9904113383186</v>
       </c>
       <c r="F130" t="n">
         <v>348006</v>
@@ -3032,16 +3032,16 @@
         <v>44663</v>
       </c>
       <c r="B131" t="n">
-        <v>118.2025833129883</v>
+        <v>118.2025909423828</v>
       </c>
       <c r="C131" t="n">
-        <v>125.1691057854541</v>
+        <v>125.1691138645034</v>
       </c>
       <c r="D131" t="n">
-        <v>118.1762292949377</v>
+        <v>118.1762369226312</v>
       </c>
       <c r="E131" t="n">
-        <v>122.9904220622919</v>
+        <v>122.9904300007179</v>
       </c>
       <c r="F131" t="n">
         <v>576598</v>
@@ -3052,16 +3052,16 @@
         <v>44664</v>
       </c>
       <c r="B132" t="n">
-        <v>119.7751007080078</v>
+        <v>119.7750930786133</v>
       </c>
       <c r="C132" t="n">
-        <v>120.794167446916</v>
+        <v>120.7941597526093</v>
       </c>
       <c r="D132" t="n">
-        <v>117.7545410442809</v>
+        <v>117.7545335435913</v>
       </c>
       <c r="E132" t="n">
-        <v>118.8351094300559</v>
+        <v>118.8351018605366</v>
       </c>
       <c r="F132" t="n">
         <v>714435</v>
@@ -3092,16 +3092,16 @@
         <v>44669</v>
       </c>
       <c r="B134" t="n">
-        <v>112.4483871459961</v>
+        <v>112.4483795166016</v>
       </c>
       <c r="C134" t="n">
-        <v>115.1366042564223</v>
+        <v>115.1365964446377</v>
       </c>
       <c r="D134" t="n">
-        <v>112.0530634659144</v>
+        <v>112.0530558633418</v>
       </c>
       <c r="E134" t="n">
-        <v>114.2053931951523</v>
+        <v>114.2053854465485</v>
       </c>
       <c r="F134" t="n">
         <v>589431</v>
@@ -3132,16 +3132,16 @@
         <v>44671</v>
       </c>
       <c r="B136" t="n">
-        <v>113.9945373535156</v>
+        <v>113.9945449829102</v>
       </c>
       <c r="C136" t="n">
-        <v>116.5597643451405</v>
+        <v>116.5597721462199</v>
       </c>
       <c r="D136" t="n">
-        <v>112.9754841247104</v>
+        <v>112.975491685902</v>
       </c>
       <c r="E136" t="n">
-        <v>114.5128642789469</v>
+        <v>114.5128719430319</v>
       </c>
       <c r="F136" t="n">
         <v>232622</v>
@@ -3152,16 +3152,16 @@
         <v>44673</v>
       </c>
       <c r="B137" t="n">
-        <v>107.7923049926758</v>
+        <v>107.7923202514648</v>
       </c>
       <c r="C137" t="n">
-        <v>111.5698702082644</v>
+        <v>111.5698860017955</v>
       </c>
       <c r="D137" t="n">
-        <v>106.2988527181102</v>
+        <v>106.2988677654902</v>
       </c>
       <c r="E137" t="n">
-        <v>111.5698702082644</v>
+        <v>111.5698860017955</v>
       </c>
       <c r="F137" t="n">
         <v>509466</v>
@@ -3192,16 +3192,16 @@
         <v>44677</v>
       </c>
       <c r="B139" t="n">
-        <v>107.4057846069336</v>
+        <v>107.4057769775391</v>
       </c>
       <c r="C139" t="n">
-        <v>112.6943700108434</v>
+        <v>112.6943620057829</v>
       </c>
       <c r="D139" t="n">
-        <v>106.3427967223379</v>
+        <v>106.342789168451</v>
       </c>
       <c r="E139" t="n">
-        <v>109.9270840670474</v>
+        <v>109.9270762585565</v>
       </c>
       <c r="F139" t="n">
         <v>615417</v>
@@ -3252,16 +3252,16 @@
         <v>44680</v>
       </c>
       <c r="B142" t="n">
-        <v>107.6341781616211</v>
+        <v>107.6341857910156</v>
       </c>
       <c r="C142" t="n">
-        <v>112.0969747428031</v>
+        <v>112.0969826885324</v>
       </c>
       <c r="D142" t="n">
-        <v>107.1773595780693</v>
+        <v>107.1773671750833</v>
       </c>
       <c r="E142" t="n">
-        <v>108.117357463648</v>
+        <v>108.1173651272915</v>
       </c>
       <c r="F142" t="n">
         <v>762051</v>
@@ -3312,16 +3312,16 @@
         <v>44685</v>
       </c>
       <c r="B145" t="n">
-        <v>94.52693176269531</v>
+        <v>94.52692413330078</v>
       </c>
       <c r="C145" t="n">
-        <v>100.4129065257185</v>
+        <v>100.4128984212591</v>
       </c>
       <c r="D145" t="n">
-        <v>84.54713605872841</v>
+        <v>84.54712923481648</v>
       </c>
       <c r="E145" t="n">
-        <v>100.4129065257185</v>
+        <v>100.4128984212591</v>
       </c>
       <c r="F145" t="n">
         <v>3193940</v>
@@ -3332,16 +3332,16 @@
         <v>44686</v>
       </c>
       <c r="B146" t="n">
-        <v>93.73627471923828</v>
+        <v>93.73626708984375</v>
       </c>
       <c r="C146" t="n">
-        <v>95.51085467081299</v>
+        <v>95.51084689698163</v>
       </c>
       <c r="D146" t="n">
-        <v>91.4609549892096</v>
+        <v>91.46094754500817</v>
       </c>
       <c r="E146" t="n">
-        <v>94.4390798549514</v>
+        <v>94.43907216835407</v>
       </c>
       <c r="F146" t="n">
         <v>1265698</v>
@@ -3352,16 +3352,16 @@
         <v>44687</v>
       </c>
       <c r="B147" t="n">
-        <v>90.31010437011719</v>
+        <v>90.31011199951172</v>
       </c>
       <c r="C147" t="n">
-        <v>95.44055829170378</v>
+        <v>95.44056635451888</v>
       </c>
       <c r="D147" t="n">
-        <v>90.31010437011719</v>
+        <v>90.31011199951172</v>
       </c>
       <c r="E147" t="n">
-        <v>93.73626045356588</v>
+        <v>93.73626837240195</v>
       </c>
       <c r="F147" t="n">
         <v>602571</v>
@@ -3372,16 +3372,16 @@
         <v>44690</v>
       </c>
       <c r="B148" t="n">
-        <v>85.645263671875</v>
+        <v>85.64525604248047</v>
       </c>
       <c r="C148" t="n">
-        <v>90.7405842334737</v>
+        <v>90.7405761501812</v>
       </c>
       <c r="D148" t="n">
-        <v>83.37873081194138</v>
+        <v>83.37872338445261</v>
       </c>
       <c r="E148" t="n">
-        <v>88.64096240162083</v>
+        <v>88.64095450536544</v>
       </c>
       <c r="F148" t="n">
         <v>1267170</v>
@@ -3392,16 +3392,16 @@
         <v>44691</v>
       </c>
       <c r="B149" t="n">
-        <v>84.51199340820312</v>
+        <v>84.51198577880859</v>
       </c>
       <c r="C149" t="n">
-        <v>89.03628559962057</v>
+        <v>89.03627756179158</v>
       </c>
       <c r="D149" t="n">
-        <v>83.46657930322515</v>
+        <v>83.46657176820631</v>
       </c>
       <c r="E149" t="n">
-        <v>85.83853493244185</v>
+        <v>85.83852718329263</v>
       </c>
       <c r="F149" t="n">
         <v>595901</v>
@@ -3432,16 +3432,16 @@
         <v>44693</v>
       </c>
       <c r="B151" t="n">
-        <v>89.44916534423828</v>
+        <v>89.44918060302734</v>
       </c>
       <c r="C151" t="n">
-        <v>96.81101726087455</v>
+        <v>96.81103377549363</v>
       </c>
       <c r="D151" t="n">
-        <v>80.67292321711979</v>
+        <v>80.67293697880346</v>
       </c>
       <c r="E151" t="n">
-        <v>80.98039789278</v>
+        <v>80.98041170691459</v>
       </c>
       <c r="F151" t="n">
         <v>2304224</v>
@@ -3492,16 +3492,16 @@
         <v>44698</v>
       </c>
       <c r="B154" t="n">
-        <v>86.9805908203125</v>
+        <v>86.98058319091797</v>
       </c>
       <c r="C154" t="n">
-        <v>88.24563068320056</v>
+        <v>88.24562294284463</v>
       </c>
       <c r="D154" t="n">
-        <v>84.59106139799007</v>
+        <v>84.59105397819015</v>
       </c>
       <c r="E154" t="n">
-        <v>85.39049570626096</v>
+        <v>85.39048821633966</v>
       </c>
       <c r="F154" t="n">
         <v>1257850</v>
@@ -3552,16 +3552,16 @@
         <v>44701</v>
       </c>
       <c r="B157" t="n">
-        <v>91.24131774902344</v>
+        <v>91.24132537841797</v>
       </c>
       <c r="C157" t="n">
-        <v>92.66449495378507</v>
+        <v>92.66450270218249</v>
       </c>
       <c r="D157" t="n">
-        <v>87.70095190087078</v>
+        <v>87.70095923422785</v>
       </c>
       <c r="E157" t="n">
-        <v>89.60730171103826</v>
+        <v>89.60730920380003</v>
       </c>
       <c r="F157" t="n">
         <v>709088</v>
@@ -3572,16 +3572,16 @@
         <v>44704</v>
       </c>
       <c r="B158" t="n">
-        <v>91.02169036865234</v>
+        <v>91.02169799804688</v>
       </c>
       <c r="C158" t="n">
-        <v>92.67327348694673</v>
+        <v>92.67328125477616</v>
       </c>
       <c r="D158" t="n">
-        <v>90.09925959845417</v>
+        <v>90.09926715053099</v>
       </c>
       <c r="E158" t="n">
-        <v>90.31010513032238</v>
+        <v>90.31011270007218</v>
       </c>
       <c r="F158" t="n">
         <v>925415</v>
@@ -3612,16 +3612,16 @@
         <v>44706</v>
       </c>
       <c r="B160" t="n">
-        <v>89.92357635498047</v>
+        <v>89.92356872558594</v>
       </c>
       <c r="C160" t="n">
-        <v>90.73179758493647</v>
+        <v>90.73178988696996</v>
       </c>
       <c r="D160" t="n">
-        <v>85.75068669945851</v>
+        <v>85.75067942410486</v>
       </c>
       <c r="E160" t="n">
-        <v>86.97180545193132</v>
+        <v>86.97179807297417</v>
       </c>
       <c r="F160" t="n">
         <v>958832</v>
@@ -3692,16 +3692,16 @@
         <v>44712</v>
       </c>
       <c r="B164" t="n">
-        <v>93.95589447021484</v>
+        <v>93.95588684082031</v>
       </c>
       <c r="C164" t="n">
-        <v>98.17271160959186</v>
+        <v>98.17270363778388</v>
       </c>
       <c r="D164" t="n">
-        <v>93.12131928963522</v>
+        <v>93.12131172800976</v>
       </c>
       <c r="E164" t="n">
-        <v>96.72318029902813</v>
+        <v>96.72317244492481</v>
       </c>
       <c r="F164" t="n">
         <v>435642</v>
@@ -3732,16 +3732,16 @@
         <v>44714</v>
       </c>
       <c r="B166" t="n">
-        <v>97.39963531494141</v>
+        <v>97.39962768554688</v>
       </c>
       <c r="C166" t="n">
-        <v>97.77739189356407</v>
+        <v>97.77738423457956</v>
       </c>
       <c r="D166" t="n">
-        <v>91.38188407601926</v>
+        <v>91.3818769180002</v>
       </c>
       <c r="E166" t="n">
-        <v>91.38188407601926</v>
+        <v>91.3818769180002</v>
       </c>
       <c r="F166" t="n">
         <v>432233</v>
@@ -3772,16 +3772,16 @@
         <v>44718</v>
       </c>
       <c r="B168" t="n">
-        <v>94.98374176025391</v>
+        <v>94.98374938964844</v>
       </c>
       <c r="C168" t="n">
-        <v>97.48747383763394</v>
+        <v>97.48748166813617</v>
       </c>
       <c r="D168" t="n">
-        <v>94.69383417696631</v>
+        <v>94.69384178307456</v>
       </c>
       <c r="E168" t="n">
-        <v>95.18579368622116</v>
+        <v>95.18580133184516</v>
       </c>
       <c r="F168" t="n">
         <v>540320</v>
@@ -3872,16 +3872,16 @@
         <v>44725</v>
       </c>
       <c r="B173" t="n">
-        <v>85.03908538818359</v>
+        <v>85.03909301757812</v>
       </c>
       <c r="C173" t="n">
-        <v>87.61309921343133</v>
+        <v>87.61310707375694</v>
       </c>
       <c r="D173" t="n">
-        <v>84.30992635555765</v>
+        <v>84.30993391953471</v>
       </c>
       <c r="E173" t="n">
-        <v>87.4110405926337</v>
+        <v>87.41104843483134</v>
       </c>
       <c r="F173" t="n">
         <v>846744</v>
@@ -3932,16 +3932,16 @@
         <v>44729</v>
       </c>
       <c r="B176" t="n">
-        <v>84.51199340820312</v>
+        <v>84.51198577880859</v>
       </c>
       <c r="C176" t="n">
-        <v>86.4359172934778</v>
+        <v>86.43590949039935</v>
       </c>
       <c r="D176" t="n">
-        <v>83.73012620511224</v>
+        <v>83.73011864630146</v>
       </c>
       <c r="E176" t="n">
-        <v>84.07274186927806</v>
+        <v>84.07273427953736</v>
       </c>
       <c r="F176" t="n">
         <v>418487</v>
@@ -3992,16 +3992,16 @@
         <v>44734</v>
       </c>
       <c r="B179" t="n">
-        <v>86.53254699707031</v>
+        <v>86.53253936767578</v>
       </c>
       <c r="C179" t="n">
-        <v>87.41105001226899</v>
+        <v>87.41104230541869</v>
       </c>
       <c r="D179" t="n">
-        <v>84.59105613777476</v>
+        <v>84.59104867955743</v>
       </c>
       <c r="E179" t="n">
-        <v>84.95123888873424</v>
+        <v>84.95123139876036</v>
       </c>
       <c r="F179" t="n">
         <v>352268</v>
@@ -4032,16 +4032,16 @@
         <v>44736</v>
       </c>
       <c r="B181" t="n">
-        <v>91.10076141357422</v>
+        <v>91.10075378417969</v>
       </c>
       <c r="C181" t="n">
-        <v>92.33066699449137</v>
+        <v>92.33065926209622</v>
       </c>
       <c r="D181" t="n">
-        <v>89.34375535582006</v>
+        <v>89.34374787356913</v>
       </c>
       <c r="E181" t="n">
-        <v>89.34375535582006</v>
+        <v>89.34374787356913</v>
       </c>
       <c r="F181" t="n">
         <v>487883</v>
@@ -4052,16 +4052,16 @@
         <v>44739</v>
       </c>
       <c r="B182" t="n">
-        <v>91.08319091796875</v>
+        <v>91.08318328857422</v>
       </c>
       <c r="C182" t="n">
-        <v>92.33066356403852</v>
+        <v>92.33065583015203</v>
       </c>
       <c r="D182" t="n">
-        <v>88.45646883590445</v>
+        <v>88.45646142653185</v>
       </c>
       <c r="E182" t="n">
-        <v>91.46094747444857</v>
+        <v>91.46093981341205</v>
       </c>
       <c r="F182" t="n">
         <v>388597</v>
@@ -4212,16 +4212,16 @@
         <v>44749</v>
       </c>
       <c r="B190" t="n">
-        <v>86.40077209472656</v>
+        <v>86.40076446533203</v>
       </c>
       <c r="C190" t="n">
-        <v>88.54432164349438</v>
+        <v>88.54431382481931</v>
       </c>
       <c r="D190" t="n">
-        <v>86.18993324315069</v>
+        <v>86.18992563237374</v>
       </c>
       <c r="E190" t="n">
-        <v>87.14749833349438</v>
+        <v>87.14749063816215</v>
       </c>
       <c r="F190" t="n">
         <v>483378</v>
@@ -4292,16 +4292,16 @@
         <v>44755</v>
       </c>
       <c r="B194" t="n">
-        <v>84.68768310546875</v>
+        <v>84.68769836425781</v>
       </c>
       <c r="C194" t="n">
-        <v>86.91908133386021</v>
+        <v>86.91909699469635</v>
       </c>
       <c r="D194" t="n">
-        <v>83.45777767295714</v>
+        <v>83.4577927101453</v>
       </c>
       <c r="E194" t="n">
-        <v>84.37142151703875</v>
+        <v>84.37143671884469</v>
       </c>
       <c r="F194" t="n">
         <v>1885043</v>
@@ -4332,16 +4332,16 @@
         <v>44757</v>
       </c>
       <c r="B196" t="n">
-        <v>82.85160827636719</v>
+        <v>82.85161590576172</v>
       </c>
       <c r="C196" t="n">
-        <v>84.72282378634415</v>
+        <v>84.72283158804966</v>
       </c>
       <c r="D196" t="n">
-        <v>81.20881210481942</v>
+        <v>81.20881958293697</v>
       </c>
       <c r="E196" t="n">
-        <v>82.27179983418721</v>
+        <v>82.27180741019004</v>
       </c>
       <c r="F196" t="n">
         <v>1850084</v>
@@ -4372,16 +4372,16 @@
         <v>44761</v>
       </c>
       <c r="B198" t="n">
-        <v>86.85758209228516</v>
+        <v>86.85758972167969</v>
       </c>
       <c r="C198" t="n">
-        <v>87.15626985408389</v>
+        <v>87.15627750971456</v>
       </c>
       <c r="D198" t="n">
-        <v>83.45777353639596</v>
+        <v>83.45778086715818</v>
       </c>
       <c r="E198" t="n">
-        <v>83.45777353639596</v>
+        <v>83.45778086715818</v>
       </c>
       <c r="F198" t="n">
         <v>493807</v>
@@ -4412,16 +4412,16 @@
         <v>44763</v>
       </c>
       <c r="B200" t="n">
-        <v>91.97047424316406</v>
+        <v>91.97048187255859</v>
       </c>
       <c r="C200" t="n">
-        <v>92.62056453720052</v>
+        <v>92.62057222052319</v>
       </c>
       <c r="D200" t="n">
-        <v>87.41104187399904</v>
+        <v>87.41104912516667</v>
       </c>
       <c r="E200" t="n">
-        <v>87.41104187399904</v>
+        <v>87.41104912516667</v>
       </c>
       <c r="F200" t="n">
         <v>453688</v>
@@ -4452,16 +4452,16 @@
         <v>44767</v>
       </c>
       <c r="B202" t="n">
-        <v>89.08020782470703</v>
+        <v>89.0802001953125</v>
       </c>
       <c r="C202" t="n">
-        <v>90.58244718893432</v>
+        <v>90.58243943087848</v>
       </c>
       <c r="D202" t="n">
-        <v>88.15777697007543</v>
+        <v>88.15776941968373</v>
       </c>
       <c r="E202" t="n">
-        <v>89.17684369338068</v>
+        <v>89.17683605570963</v>
       </c>
       <c r="F202" t="n">
         <v>343259</v>
@@ -4492,16 +4492,16 @@
         <v>44769</v>
       </c>
       <c r="B204" t="n">
-        <v>92.2603759765625</v>
+        <v>92.26038360595703</v>
       </c>
       <c r="C204" t="n">
-        <v>92.55907046197431</v>
+        <v>92.55907811606914</v>
       </c>
       <c r="D204" t="n">
-        <v>87.46375071978201</v>
+        <v>87.46375795252364</v>
       </c>
       <c r="E204" t="n">
-        <v>87.46375071978201</v>
+        <v>87.46375795252364</v>
       </c>
       <c r="F204" t="n">
         <v>673546</v>
@@ -4572,16 +4572,16 @@
         <v>44775</v>
       </c>
       <c r="B208" t="n">
-        <v>101.4670867919922</v>
+        <v>101.4671020507812</v>
       </c>
       <c r="C208" t="n">
-        <v>102.2050260242147</v>
+        <v>102.2050413939763</v>
       </c>
       <c r="D208" t="n">
-        <v>98.69980126626697</v>
+        <v>98.69981610890704</v>
       </c>
       <c r="E208" t="n">
-        <v>100.0439096552761</v>
+        <v>100.0439247000455</v>
       </c>
       <c r="F208" t="n">
         <v>737331</v>
@@ -4652,16 +4652,16 @@
         <v>44781</v>
       </c>
       <c r="B212" t="n">
-        <v>110.4893188476562</v>
+        <v>110.4893264770508</v>
       </c>
       <c r="C212" t="n">
-        <v>113.2829586427765</v>
+        <v>113.2829664650746</v>
       </c>
       <c r="D212" t="n">
-        <v>108.451192165222</v>
+        <v>108.4511996538819</v>
       </c>
       <c r="E212" t="n">
-        <v>108.9343714939558</v>
+        <v>108.9343790159798</v>
       </c>
       <c r="F212" t="n">
         <v>1248783</v>
@@ -4692,16 +4692,16 @@
         <v>44783</v>
       </c>
       <c r="B214" t="n">
-        <v>90.87236022949219</v>
+        <v>90.87235260009766</v>
       </c>
       <c r="C214" t="n">
-        <v>103.6457957452289</v>
+        <v>103.6457870434117</v>
       </c>
       <c r="D214" t="n">
-        <v>90.32768591007121</v>
+        <v>90.32767832640604</v>
       </c>
       <c r="E214" t="n">
-        <v>103.6457957452289</v>
+        <v>103.6457870434117</v>
       </c>
       <c r="F214" t="n">
         <v>2607483</v>
@@ -4712,16 +4712,16 @@
         <v>44784</v>
       </c>
       <c r="B215" t="n">
-        <v>84.59983825683594</v>
+        <v>84.59984588623047</v>
       </c>
       <c r="C215" t="n">
-        <v>92.06711346342773</v>
+        <v>92.06712176623714</v>
       </c>
       <c r="D215" t="n">
-        <v>83.26450999593463</v>
+        <v>83.26451750490639</v>
       </c>
       <c r="E215" t="n">
-        <v>90.87234889417739</v>
+        <v>90.87235708924037</v>
       </c>
       <c r="F215" t="n">
         <v>3127275</v>
@@ -4752,16 +4752,16 @@
         <v>44788</v>
       </c>
       <c r="B217" t="n">
-        <v>98.17272186279297</v>
+        <v>98.17270660400391</v>
       </c>
       <c r="C217" t="n">
-        <v>98.83159919073117</v>
+        <v>98.83158382953414</v>
       </c>
       <c r="D217" t="n">
-        <v>86.9805941955677</v>
+        <v>86.98058067634858</v>
       </c>
       <c r="E217" t="n">
-        <v>87.40227193207797</v>
+        <v>87.40225834731831</v>
       </c>
       <c r="F217" t="n">
         <v>1427504</v>
@@ -4792,16 +4792,16 @@
         <v>44790</v>
       </c>
       <c r="B219" t="n">
-        <v>96.5211181640625</v>
+        <v>96.52112579345703</v>
       </c>
       <c r="C219" t="n">
-        <v>96.67046205176851</v>
+        <v>96.67046969296776</v>
       </c>
       <c r="D219" t="n">
-        <v>93.29700735611611</v>
+        <v>93.29701473066473</v>
       </c>
       <c r="E219" t="n">
-        <v>93.29700735611611</v>
+        <v>93.29701473066473</v>
       </c>
       <c r="F219" t="n">
         <v>484266</v>
@@ -4812,16 +4812,16 @@
         <v>44791</v>
       </c>
       <c r="B220" t="n">
-        <v>96.89888000488281</v>
+        <v>96.89888763427734</v>
       </c>
       <c r="C220" t="n">
-        <v>97.78616317637614</v>
+        <v>97.78617087563147</v>
       </c>
       <c r="D220" t="n">
-        <v>95.80953149932459</v>
+        <v>95.80953904294859</v>
       </c>
       <c r="E220" t="n">
-        <v>96.51233655436566</v>
+        <v>96.51234415332544</v>
       </c>
       <c r="F220" t="n">
         <v>225811</v>
@@ -4832,16 +4832,16 @@
         <v>44792</v>
       </c>
       <c r="B221" t="n">
-        <v>92.81383514404297</v>
+        <v>92.8138427734375</v>
       </c>
       <c r="C221" t="n">
-        <v>96.35420085090701</v>
+        <v>96.3542087713233</v>
       </c>
       <c r="D221" t="n">
-        <v>92.34822966730141</v>
+        <v>92.34823725842267</v>
       </c>
       <c r="E221" t="n">
-        <v>95.79195951645167</v>
+        <v>95.79196739065114</v>
       </c>
       <c r="F221" t="n">
         <v>610732</v>
@@ -4852,16 +4852,16 @@
         <v>44795</v>
       </c>
       <c r="B222" t="n">
-        <v>88.45646667480469</v>
+        <v>88.45647430419922</v>
       </c>
       <c r="C222" t="n">
-        <v>92.04954062445751</v>
+        <v>92.04954856375565</v>
       </c>
       <c r="D222" t="n">
-        <v>88.03478229783688</v>
+        <v>88.03478989086102</v>
       </c>
       <c r="E222" t="n">
-        <v>92.04954062445751</v>
+        <v>92.04954856375565</v>
       </c>
       <c r="F222" t="n">
         <v>1074017</v>
@@ -4892,16 +4892,16 @@
         <v>44797</v>
       </c>
       <c r="B224" t="n">
-        <v>101.0278472900391</v>
+        <v>101.0278396606445</v>
       </c>
       <c r="C224" t="n">
-        <v>102.855135180046</v>
+        <v>102.8551274126588</v>
       </c>
       <c r="D224" t="n">
-        <v>96.94280690695261</v>
+        <v>96.94279958605108</v>
       </c>
       <c r="E224" t="n">
-        <v>96.98673473892673</v>
+        <v>96.98672741470787</v>
       </c>
       <c r="F224" t="n">
         <v>1291806</v>
@@ -4952,16 +4952,16 @@
         <v>44802</v>
       </c>
       <c r="B227" t="n">
-        <v>91.77721405029297</v>
+        <v>91.77720642089844</v>
       </c>
       <c r="C227" t="n">
-        <v>95.84468072985686</v>
+        <v>95.84467276233583</v>
       </c>
       <c r="D227" t="n">
-        <v>91.23253975030309</v>
+        <v>91.23253216618707</v>
       </c>
       <c r="E227" t="n">
-        <v>93.56057415666235</v>
+        <v>93.56056637901798</v>
       </c>
       <c r="F227" t="n">
         <v>661048</v>
@@ -4992,16 +4992,16 @@
         <v>44804</v>
       </c>
       <c r="B229" t="n">
-        <v>87.36711120605469</v>
+        <v>87.36711883544922</v>
       </c>
       <c r="C229" t="n">
-        <v>91.33794808933241</v>
+        <v>91.33795606548307</v>
       </c>
       <c r="D229" t="n">
-        <v>87.36711120605469</v>
+        <v>87.36711883544922</v>
       </c>
       <c r="E229" t="n">
-        <v>89.35252964769354</v>
+        <v>89.35253745046614</v>
       </c>
       <c r="F229" t="n">
         <v>588012</v>
@@ -5012,16 +5012,16 @@
         <v>44805</v>
       </c>
       <c r="B230" t="n">
-        <v>88.58823394775391</v>
+        <v>88.58824157714844</v>
       </c>
       <c r="C230" t="n">
-        <v>89.21197693820172</v>
+        <v>89.21198462131423</v>
       </c>
       <c r="D230" t="n">
-        <v>84.33628290195425</v>
+        <v>84.33629016516232</v>
       </c>
       <c r="E230" t="n">
-        <v>87.39347610622615</v>
+        <v>87.39348363272576</v>
       </c>
       <c r="F230" t="n">
         <v>1016578</v>
@@ -5032,16 +5032,16 @@
         <v>44806</v>
       </c>
       <c r="B231" t="n">
-        <v>88.0260009765625</v>
+        <v>88.02600860595703</v>
       </c>
       <c r="C231" t="n">
-        <v>91.19739745291511</v>
+        <v>91.1974053571811</v>
       </c>
       <c r="D231" t="n">
-        <v>86.98936713245767</v>
+        <v>86.98937467200503</v>
       </c>
       <c r="E231" t="n">
-        <v>89.50188633592451</v>
+        <v>89.50189409323706</v>
       </c>
       <c r="F231" t="n">
         <v>344726</v>
@@ -5052,16 +5052,16 @@
         <v>44809</v>
       </c>
       <c r="B232" t="n">
-        <v>89.43161010742188</v>
+        <v>89.43160247802734</v>
       </c>
       <c r="C232" t="n">
-        <v>89.82693378540118</v>
+        <v>89.82692612228165</v>
       </c>
       <c r="D232" t="n">
-        <v>88.03478682049915</v>
+        <v>88.03477931026735</v>
       </c>
       <c r="E232" t="n">
-        <v>88.81665397201991</v>
+        <v>88.81664639508718</v>
       </c>
       <c r="F232" t="n">
         <v>95765</v>
@@ -5092,16 +5092,16 @@
         <v>44812</v>
       </c>
       <c r="B234" t="n">
-        <v>88.28955078125</v>
+        <v>88.28955841064453</v>
       </c>
       <c r="C234" t="n">
-        <v>90.14319263235551</v>
+        <v>90.14320042192941</v>
       </c>
       <c r="D234" t="n">
-        <v>87.12992709878814</v>
+        <v>87.12993462797571</v>
       </c>
       <c r="E234" t="n">
-        <v>88.29833768786334</v>
+        <v>88.29834531801718</v>
       </c>
       <c r="F234" t="n">
         <v>707072</v>
@@ -5132,16 +5132,16 @@
         <v>44816</v>
       </c>
       <c r="B236" t="n">
-        <v>94.79048156738281</v>
+        <v>94.79047393798828</v>
       </c>
       <c r="C236" t="n">
-        <v>94.79048156738281</v>
+        <v>94.79047393798828</v>
       </c>
       <c r="D236" t="n">
-        <v>91.34675117884834</v>
+        <v>91.34674382662909</v>
       </c>
       <c r="E236" t="n">
-        <v>91.34675117884834</v>
+        <v>91.34674382662909</v>
       </c>
       <c r="F236" t="n">
         <v>423751</v>
@@ -5172,16 +5172,16 @@
         <v>44818</v>
       </c>
       <c r="B238" t="n">
-        <v>90.13441467285156</v>
+        <v>90.13440704345703</v>
       </c>
       <c r="C238" t="n">
-        <v>91.77721784542967</v>
+        <v>91.77721007698068</v>
       </c>
       <c r="D238" t="n">
-        <v>88.15778274273444</v>
+        <v>88.15777528065119</v>
       </c>
       <c r="E238" t="n">
-        <v>90.1783425078328</v>
+        <v>90.17833487472001</v>
       </c>
       <c r="F238" t="n">
         <v>962834</v>
@@ -5232,16 +5232,16 @@
         <v>44823</v>
       </c>
       <c r="B241" t="n">
-        <v>88.99235534667969</v>
+        <v>88.99236297607422</v>
       </c>
       <c r="C241" t="n">
-        <v>89.82693050412597</v>
+        <v>89.82693820506938</v>
       </c>
       <c r="D241" t="n">
-        <v>86.69946201228579</v>
+        <v>86.69946944510852</v>
       </c>
       <c r="E241" t="n">
-        <v>87.39348017695347</v>
+        <v>87.393487669275</v>
       </c>
       <c r="F241" t="n">
         <v>601912</v>
@@ -5252,16 +5252,16 @@
         <v>44824</v>
       </c>
       <c r="B242" t="n">
-        <v>89.88842010498047</v>
+        <v>89.888427734375</v>
       </c>
       <c r="C242" t="n">
-        <v>91.25010233617633</v>
+        <v>91.25011008114538</v>
       </c>
       <c r="D242" t="n">
-        <v>88.50917076414814</v>
+        <v>88.50917827647712</v>
       </c>
       <c r="E242" t="n">
-        <v>88.77272432581363</v>
+        <v>88.77273186051205</v>
       </c>
       <c r="F242" t="n">
         <v>415549</v>
@@ -5292,16 +5292,16 @@
         <v>44826</v>
       </c>
       <c r="B244" t="n">
-        <v>89.08020782470703</v>
+        <v>89.0802001953125</v>
       </c>
       <c r="C244" t="n">
-        <v>91.53123206185035</v>
+        <v>91.53122422253455</v>
       </c>
       <c r="D244" t="n">
-        <v>86.27778103806376</v>
+        <v>86.27777364868685</v>
       </c>
       <c r="E244" t="n">
-        <v>89.43161037420698</v>
+        <v>89.43160271471611</v>
       </c>
       <c r="F244" t="n">
         <v>985794</v>
@@ -5332,16 +5332,16 @@
         <v>44830</v>
       </c>
       <c r="B246" t="n">
-        <v>84.33628082275391</v>
+        <v>84.33629608154297</v>
       </c>
       <c r="C246" t="n">
-        <v>89.18561402098628</v>
+        <v>89.18563015715517</v>
       </c>
       <c r="D246" t="n">
-        <v>84.24843187071929</v>
+        <v>84.24844711361402</v>
       </c>
       <c r="E246" t="n">
-        <v>88.13141319168002</v>
+        <v>88.13142913711454</v>
       </c>
       <c r="F246" t="n">
         <v>548585</v>
@@ -5372,16 +5372,16 @@
         <v>44832</v>
       </c>
       <c r="B248" t="n">
-        <v>86.94544219970703</v>
+        <v>86.94544982910156</v>
       </c>
       <c r="C248" t="n">
-        <v>88.52674356400453</v>
+        <v>88.52675133215702</v>
       </c>
       <c r="D248" t="n">
-        <v>85.29385228500924</v>
+        <v>85.29385976947805</v>
       </c>
       <c r="E248" t="n">
-        <v>86.5501118317982</v>
+        <v>86.5501194265028</v>
       </c>
       <c r="F248" t="n">
         <v>626382</v>
@@ -5412,16 +5412,16 @@
         <v>44834</v>
       </c>
       <c r="B250" t="n">
-        <v>90.31010437011719</v>
+        <v>90.31011199951172</v>
       </c>
       <c r="C250" t="n">
-        <v>91.18860730483644</v>
+        <v>91.18861500844686</v>
       </c>
       <c r="D250" t="n">
-        <v>85.89122897842515</v>
+        <v>85.89123623451323</v>
       </c>
       <c r="E250" t="n">
-        <v>86.97179053720583</v>
+        <v>86.97179788457973</v>
       </c>
       <c r="F250" t="n">
         <v>846019</v>
@@ -5432,16 +5432,16 @@
         <v>44837</v>
       </c>
       <c r="B251" t="n">
-        <v>94.77290344238281</v>
+        <v>94.77289581298828</v>
       </c>
       <c r="C251" t="n">
-        <v>95.68654738803224</v>
+        <v>95.68653968508768</v>
       </c>
       <c r="D251" t="n">
-        <v>90.92506262532224</v>
+        <v>90.92505530568604</v>
       </c>
       <c r="E251" t="n">
-        <v>91.36431413558951</v>
+        <v>91.36430678059274</v>
       </c>
       <c r="F251" t="n">
         <v>814581</v>
@@ -5512,16 +5512,16 @@
         <v>44841</v>
       </c>
       <c r="B255" t="n">
-        <v>96.81102752685547</v>
+        <v>96.81101989746094</v>
       </c>
       <c r="C255" t="n">
-        <v>98.87551493044936</v>
+        <v>98.87550713835859</v>
       </c>
       <c r="D255" t="n">
-        <v>95.87102958876109</v>
+        <v>95.87102203344506</v>
       </c>
       <c r="E255" t="n">
-        <v>97.69831742994607</v>
+        <v>97.69830973062682</v>
       </c>
       <c r="F255" t="n">
         <v>390672</v>
@@ -5532,16 +5532,16 @@
         <v>44844</v>
       </c>
       <c r="B256" t="n">
-        <v>96.5211181640625</v>
+        <v>96.52112579345703</v>
       </c>
       <c r="C256" t="n">
-        <v>97.95307550975528</v>
+        <v>97.95308325233714</v>
       </c>
       <c r="D256" t="n">
-        <v>94.96616424340819</v>
+        <v>94.96617174989328</v>
       </c>
       <c r="E256" t="n">
-        <v>97.1624215418332</v>
+        <v>97.16242922191877</v>
       </c>
       <c r="F256" t="n">
         <v>391665</v>
@@ -5552,16 +5552,16 @@
         <v>44845</v>
       </c>
       <c r="B257" t="n">
-        <v>88.64974212646484</v>
+        <v>88.64974975585938</v>
       </c>
       <c r="C257" t="n">
-        <v>96.94280599912264</v>
+        <v>96.94281434223674</v>
       </c>
       <c r="D257" t="n">
-        <v>87.1387158739726</v>
+        <v>87.13872337332482</v>
       </c>
       <c r="E257" t="n">
-        <v>96.5211283068829</v>
+        <v>96.52113661370647</v>
       </c>
       <c r="F257" t="n">
         <v>1649810</v>
@@ -5592,16 +5592,16 @@
         <v>44848</v>
       </c>
       <c r="B259" t="n">
-        <v>82.71984100341797</v>
+        <v>82.71985626220703</v>
       </c>
       <c r="C259" t="n">
-        <v>90.16954226733124</v>
+        <v>90.16955890031807</v>
       </c>
       <c r="D259" t="n">
-        <v>82.66712626874587</v>
+        <v>82.667141517811</v>
       </c>
       <c r="E259" t="n">
-        <v>86.64674356053986</v>
+        <v>86.64675954369901</v>
       </c>
       <c r="F259" t="n">
         <v>951929</v>
@@ -5632,16 +5632,16 @@
         <v>44852</v>
       </c>
       <c r="B261" t="n">
-        <v>80.54116058349609</v>
+        <v>80.54115295410156</v>
       </c>
       <c r="C261" t="n">
-        <v>85.61012027643372</v>
+        <v>85.61011216687361</v>
       </c>
       <c r="D261" t="n">
-        <v>79.24097310925836</v>
+        <v>79.24096560302623</v>
       </c>
       <c r="E261" t="n">
-        <v>84.42414248924207</v>
+        <v>84.42413449202566</v>
       </c>
       <c r="F261" t="n">
         <v>1514560</v>
@@ -5652,16 +5652,16 @@
         <v>44853</v>
       </c>
       <c r="B262" t="n">
-        <v>80.47087860107422</v>
+        <v>80.47087097167969</v>
       </c>
       <c r="C262" t="n">
-        <v>81.52508628989879</v>
+        <v>81.52507856055549</v>
       </c>
       <c r="D262" t="n">
-        <v>79.10920288553962</v>
+        <v>79.10919538524473</v>
       </c>
       <c r="E262" t="n">
-        <v>80.38302963595044</v>
+        <v>80.38302201488482</v>
       </c>
       <c r="F262" t="n">
         <v>1204425</v>
@@ -5692,16 +5692,16 @@
         <v>44855</v>
       </c>
       <c r="B264" t="n">
-        <v>82.25422668457031</v>
+        <v>82.25423431396484</v>
       </c>
       <c r="C264" t="n">
-        <v>85.73309747299184</v>
+        <v>85.73310542506498</v>
       </c>
       <c r="D264" t="n">
-        <v>75.13835431268782</v>
+        <v>75.13836128205794</v>
       </c>
       <c r="E264" t="n">
-        <v>77.96713481147866</v>
+        <v>77.967142043229</v>
       </c>
       <c r="F264" t="n">
         <v>1421863</v>
@@ -5732,16 +5732,16 @@
         <v>44859</v>
       </c>
       <c r="B266" t="n">
-        <v>82.92189025878906</v>
+        <v>82.92189788818359</v>
       </c>
       <c r="C266" t="n">
-        <v>85.30263237275399</v>
+        <v>85.30264022119347</v>
       </c>
       <c r="D266" t="n">
-        <v>81.31422830318635</v>
+        <v>81.31423578466473</v>
       </c>
       <c r="E266" t="n">
-        <v>82.03460043101913</v>
+        <v>82.03460797877678</v>
       </c>
       <c r="F266" t="n">
         <v>1189906</v>
@@ -5792,16 +5792,16 @@
         <v>44862</v>
       </c>
       <c r="B269" t="n">
-        <v>81.43721771240234</v>
+        <v>81.43722534179688</v>
       </c>
       <c r="C269" t="n">
-        <v>82.14002272687244</v>
+        <v>82.14003042210881</v>
       </c>
       <c r="D269" t="n">
-        <v>78.40638533019641</v>
+        <v>78.40639267564933</v>
       </c>
       <c r="E269" t="n">
-        <v>79.04769540858378</v>
+        <v>79.04770281411741</v>
       </c>
       <c r="F269" t="n">
         <v>705309</v>
@@ -5832,16 +5832,16 @@
         <v>44866</v>
       </c>
       <c r="B271" t="n">
-        <v>87.10356903076172</v>
+        <v>87.10357666015625</v>
       </c>
       <c r="C271" t="n">
-        <v>87.84150829326336</v>
+        <v>87.84151598729392</v>
       </c>
       <c r="D271" t="n">
-        <v>83.65983906752952</v>
+        <v>83.65984639528801</v>
       </c>
       <c r="E271" t="n">
-        <v>83.65983906752952</v>
+        <v>83.65984639528801</v>
       </c>
       <c r="F271" t="n">
         <v>1461617</v>
@@ -5872,16 +5872,16 @@
         <v>44869</v>
       </c>
       <c r="B273" t="n">
-        <v>83.48414611816406</v>
+        <v>83.484130859375</v>
       </c>
       <c r="C273" t="n">
-        <v>88.72881054662849</v>
+        <v>88.72879432924752</v>
       </c>
       <c r="D273" t="n">
-        <v>82.78134767985672</v>
+        <v>82.78133254952142</v>
       </c>
       <c r="E273" t="n">
-        <v>87.59554077594728</v>
+        <v>87.59552476569932</v>
       </c>
       <c r="F273" t="n">
         <v>612180</v>
@@ -5892,16 +5892,16 @@
         <v>44872</v>
       </c>
       <c r="B274" t="n">
-        <v>83.19422912597656</v>
+        <v>83.19422149658203</v>
       </c>
       <c r="C274" t="n">
-        <v>84.51198358965588</v>
+        <v>84.51197583941561</v>
       </c>
       <c r="D274" t="n">
-        <v>82.2805919293112</v>
+        <v>82.2805843837025</v>
       </c>
       <c r="E274" t="n">
-        <v>83.03609832223721</v>
+        <v>83.03609070734419</v>
       </c>
       <c r="F274" t="n">
         <v>752715</v>
@@ -5952,16 +5952,16 @@
         <v>44875</v>
       </c>
       <c r="B277" t="n">
-        <v>90.49459838867188</v>
+        <v>90.49459075927734</v>
       </c>
       <c r="C277" t="n">
-        <v>94.21944933414814</v>
+        <v>94.21944139071987</v>
       </c>
       <c r="D277" t="n">
-        <v>85.65404484922558</v>
+        <v>85.65403762792715</v>
       </c>
       <c r="E277" t="n">
-        <v>85.67161196063115</v>
+        <v>85.67160473785169</v>
       </c>
       <c r="F277" t="n">
         <v>2820385</v>
@@ -5972,16 +5972,16 @@
         <v>44876</v>
       </c>
       <c r="B278" t="n">
-        <v>89.57217407226562</v>
+        <v>89.57216644287109</v>
       </c>
       <c r="C278" t="n">
-        <v>91.51366509297395</v>
+        <v>91.51365729821109</v>
       </c>
       <c r="D278" t="n">
-        <v>88.06114768810795</v>
+        <v>88.06114018741653</v>
       </c>
       <c r="E278" t="n">
-        <v>90.48581808832483</v>
+        <v>90.4858103811098</v>
       </c>
       <c r="F278" t="n">
         <v>1123849</v>
@@ -6032,16 +6032,16 @@
         <v>44882</v>
       </c>
       <c r="B281" t="n">
-        <v>84.07273864746094</v>
+        <v>84.07273101806641</v>
       </c>
       <c r="C281" t="n">
-        <v>86.65553974214566</v>
+        <v>86.65553187836828</v>
       </c>
       <c r="D281" t="n">
-        <v>78.95107099372555</v>
+        <v>78.95106382910978</v>
       </c>
       <c r="E281" t="n">
-        <v>86.26021605324125</v>
+        <v>86.26020822533852</v>
       </c>
       <c r="F281" t="n">
         <v>1328887</v>
@@ -6092,16 +6092,16 @@
         <v>44887</v>
       </c>
       <c r="B284" t="n">
-        <v>78.23070526123047</v>
+        <v>78.23069763183594</v>
       </c>
       <c r="C284" t="n">
-        <v>80.67294285445492</v>
+        <v>80.67293498688288</v>
       </c>
       <c r="D284" t="n">
-        <v>76.64939696942126</v>
+        <v>76.6493894942427</v>
       </c>
       <c r="E284" t="n">
-        <v>80.04920644558763</v>
+        <v>80.04919863884506</v>
       </c>
       <c r="F284" t="n">
         <v>724710</v>
@@ -6112,16 +6112,16 @@
         <v>44888</v>
       </c>
       <c r="B285" t="n">
-        <v>77.27311706542969</v>
+        <v>77.27313232421875</v>
       </c>
       <c r="C285" t="n">
-        <v>78.72264824317485</v>
+        <v>78.72266378819657</v>
       </c>
       <c r="D285" t="n">
-        <v>75.99929049548588</v>
+        <v>75.9993055027379</v>
       </c>
       <c r="E285" t="n">
-        <v>78.02863012286181</v>
+        <v>78.02864553083879</v>
       </c>
       <c r="F285" t="n">
         <v>751617</v>
@@ -6132,16 +6132,16 @@
         <v>44889</v>
       </c>
       <c r="B286" t="n">
-        <v>78.80171203613281</v>
+        <v>78.80170440673828</v>
       </c>
       <c r="C286" t="n">
-        <v>79.50451707802175</v>
+        <v>79.5045093805833</v>
       </c>
       <c r="D286" t="n">
-        <v>77.19405672940827</v>
+        <v>77.1940492556631</v>
       </c>
       <c r="E286" t="n">
-        <v>77.52788543796044</v>
+        <v>77.52787793189476</v>
       </c>
       <c r="F286" t="n">
         <v>618983</v>
@@ -6172,16 +6172,16 @@
         <v>44893</v>
       </c>
       <c r="B288" t="n">
-        <v>75.56881713867188</v>
+        <v>75.56882476806641</v>
       </c>
       <c r="C288" t="n">
-        <v>78.24825368697887</v>
+        <v>78.24826158688813</v>
       </c>
       <c r="D288" t="n">
-        <v>75.28769647642699</v>
+        <v>75.2877040774397</v>
       </c>
       <c r="E288" t="n">
-        <v>77.1413381470698</v>
+        <v>77.14134593522536</v>
       </c>
       <c r="F288" t="n">
         <v>519110</v>
@@ -6232,16 +6232,16 @@
         <v>44896</v>
       </c>
       <c r="B291" t="n">
-        <v>79.21461486816406</v>
+        <v>79.21462249755859</v>
       </c>
       <c r="C291" t="n">
-        <v>81.06825675698197</v>
+        <v>81.06826456490624</v>
       </c>
       <c r="D291" t="n">
-        <v>78.69630130901254</v>
+        <v>78.69630888848674</v>
       </c>
       <c r="E291" t="n">
-        <v>79.0740578717206</v>
+        <v>79.07406548757766</v>
       </c>
       <c r="F291" t="n">
         <v>741238</v>
@@ -6312,16 +6312,16 @@
         <v>44902</v>
       </c>
       <c r="B295" t="n">
-        <v>76.15742492675781</v>
+        <v>76.15741729736328</v>
       </c>
       <c r="C295" t="n">
-        <v>78.4327444112255</v>
+        <v>78.43273655389115</v>
       </c>
       <c r="D295" t="n">
-        <v>74.76060171345117</v>
+        <v>74.76059422398934</v>
       </c>
       <c r="E295" t="n">
-        <v>77.82657521465414</v>
+        <v>77.82656741804537</v>
       </c>
       <c r="F295" t="n">
         <v>782541</v>
@@ -6332,16 +6332,16 @@
         <v>44903</v>
       </c>
       <c r="B296" t="n">
-        <v>72.38865661621094</v>
+        <v>72.38864898681641</v>
       </c>
       <c r="C296" t="n">
-        <v>76.73724427036358</v>
+        <v>76.73723618265012</v>
       </c>
       <c r="D296" t="n">
-        <v>72.03725403651906</v>
+        <v>72.03724644416056</v>
       </c>
       <c r="E296" t="n">
-        <v>76.73724427036358</v>
+        <v>76.73723618265012</v>
       </c>
       <c r="F296" t="n">
         <v>1116650</v>
@@ -6372,16 +6372,16 @@
         <v>44907</v>
       </c>
       <c r="B298" t="n">
-        <v>72.23930358886719</v>
+        <v>72.23931121826172</v>
       </c>
       <c r="C298" t="n">
-        <v>74.02266358054949</v>
+        <v>74.02267139828965</v>
       </c>
       <c r="D298" t="n">
-        <v>70.51743183574715</v>
+        <v>70.51743928329</v>
       </c>
       <c r="E298" t="n">
-        <v>72.73126311693241</v>
+        <v>72.73127079828416</v>
       </c>
       <c r="F298" t="n">
         <v>769701</v>
@@ -6412,16 +6412,16 @@
         <v>44909</v>
       </c>
       <c r="B300" t="n">
-        <v>68.19818115234375</v>
+        <v>68.19818878173828</v>
       </c>
       <c r="C300" t="n">
-        <v>70.51742838907342</v>
+        <v>70.5174362779243</v>
       </c>
       <c r="D300" t="n">
-        <v>66.81893179790644</v>
+        <v>66.81893927300305</v>
       </c>
       <c r="E300" t="n">
-        <v>70.43836634126119</v>
+        <v>70.43837422126734</v>
       </c>
       <c r="F300" t="n">
         <v>1355188</v>
@@ -6432,16 +6432,16 @@
         <v>44910</v>
       </c>
       <c r="B301" t="n">
-        <v>65.86138153076172</v>
+        <v>65.86137390136719</v>
       </c>
       <c r="C301" t="n">
-        <v>68.84829354963527</v>
+        <v>68.8482855742363</v>
       </c>
       <c r="D301" t="n">
-        <v>65.81745369274783</v>
+        <v>65.81744606844191</v>
       </c>
       <c r="E301" t="n">
-        <v>68.30361918951958</v>
+        <v>68.30361127721578</v>
       </c>
       <c r="F301" t="n">
         <v>806063</v>
@@ -6532,16 +6532,16 @@
         <v>44917</v>
       </c>
       <c r="B306" t="n">
-        <v>67.46903228759766</v>
+        <v>67.46903991699219</v>
       </c>
       <c r="C306" t="n">
-        <v>72.45014263043683</v>
+        <v>72.45015082309504</v>
       </c>
       <c r="D306" t="n">
-        <v>64.56996974070987</v>
+        <v>64.56997704227857</v>
       </c>
       <c r="E306" t="n">
-        <v>70.28023917356177</v>
+        <v>70.28024712084742</v>
       </c>
       <c r="F306" t="n">
         <v>477342</v>
@@ -6592,16 +6592,16 @@
         <v>44922</v>
       </c>
       <c r="B309" t="n">
-        <v>67.82042694091797</v>
+        <v>67.8204345703125</v>
       </c>
       <c r="C309" t="n">
-        <v>70.45593586404866</v>
+        <v>70.45594378992226</v>
       </c>
       <c r="D309" t="n">
-        <v>67.38117545372953</v>
+        <v>67.38118303371087</v>
       </c>
       <c r="E309" t="n">
-        <v>68.96248348858624</v>
+        <v>68.96249124645534</v>
       </c>
       <c r="F309" t="n">
         <v>436455</v>
@@ -6612,16 +6612,16 @@
         <v>44923</v>
       </c>
       <c r="B310" t="n">
-        <v>68.39144897460938</v>
+        <v>68.39145660400391</v>
       </c>
       <c r="C310" t="n">
-        <v>70.26266442886484</v>
+        <v>70.26267226700244</v>
       </c>
       <c r="D310" t="n">
-        <v>67.17911739346478</v>
+        <v>67.17912488761789</v>
       </c>
       <c r="E310" t="n">
-        <v>67.82042075287674</v>
+        <v>67.82042831857034</v>
       </c>
       <c r="F310" t="n">
         <v>543744</v>
@@ -6652,16 +6652,16 @@
         <v>44928</v>
       </c>
       <c r="B312" t="n">
-        <v>66.42360687255859</v>
+        <v>66.42362213134766</v>
       </c>
       <c r="C312" t="n">
-        <v>69.77070088095081</v>
+        <v>69.7707169086322</v>
       </c>
       <c r="D312" t="n">
-        <v>66.12491239199053</v>
+        <v>66.12492758216369</v>
       </c>
       <c r="E312" t="n">
-        <v>68.88341775009563</v>
+        <v>68.8834335739509</v>
       </c>
       <c r="F312" t="n">
         <v>452524</v>
@@ -6692,16 +6692,16 @@
         <v>44930</v>
       </c>
       <c r="B314" t="n">
-        <v>67.00341796875</v>
+        <v>67.00341033935547</v>
       </c>
       <c r="C314" t="n">
-        <v>68.40902807003422</v>
+        <v>68.40902028058885</v>
       </c>
       <c r="D314" t="n">
-        <v>66.33576054333025</v>
+        <v>66.33575298995903</v>
       </c>
       <c r="E314" t="n">
-        <v>66.52024536107352</v>
+        <v>66.52023778669582</v>
       </c>
       <c r="F314" t="n">
         <v>669125</v>
@@ -6712,16 +6712,16 @@
         <v>44931</v>
       </c>
       <c r="B315" t="n">
-        <v>65.422119140625</v>
+        <v>65.42212677001953</v>
       </c>
       <c r="C315" t="n">
-        <v>68.18061801001888</v>
+        <v>68.18062596110393</v>
       </c>
       <c r="D315" t="n">
-        <v>65.07071660197154</v>
+        <v>65.07072419038622</v>
       </c>
       <c r="E315" t="n">
-        <v>67.19669224227836</v>
+        <v>67.19670007862</v>
       </c>
       <c r="F315" t="n">
         <v>721996</v>
@@ -6732,16 +6732,16 @@
         <v>44932</v>
       </c>
       <c r="B316" t="n">
-        <v>68.31238555908203</v>
+        <v>68.31239318847656</v>
       </c>
       <c r="C316" t="n">
-        <v>68.31238555908203</v>
+        <v>68.31239318847656</v>
       </c>
       <c r="D316" t="n">
-        <v>65.62416219910284</v>
+        <v>65.62416952826607</v>
       </c>
       <c r="E316" t="n">
-        <v>65.99313850112217</v>
+        <v>65.99314587149411</v>
       </c>
       <c r="F316" t="n">
         <v>775272</v>
@@ -6832,16 +6832,16 @@
         <v>44939</v>
       </c>
       <c r="B321" t="n">
-        <v>74.85723876953125</v>
+        <v>74.85724639892578</v>
       </c>
       <c r="C321" t="n">
-        <v>76.07835738610657</v>
+        <v>76.07836513995662</v>
       </c>
       <c r="D321" t="n">
-        <v>73.63612015295593</v>
+        <v>73.63612765789495</v>
       </c>
       <c r="E321" t="n">
-        <v>74.82209784573354</v>
+        <v>74.82210547154654</v>
       </c>
       <c r="F321" t="n">
         <v>628080</v>
@@ -6852,16 +6852,16 @@
         <v>44942</v>
       </c>
       <c r="B322" t="n">
-        <v>70.13089752197266</v>
+        <v>70.13088989257812</v>
       </c>
       <c r="C322" t="n">
-        <v>72.91575047990735</v>
+        <v>72.91574254755446</v>
       </c>
       <c r="D322" t="n">
-        <v>69.55108231303058</v>
+        <v>69.55107474671294</v>
       </c>
       <c r="E322" t="n">
-        <v>72.91575047990735</v>
+        <v>72.91574254755446</v>
       </c>
       <c r="F322" t="n">
         <v>636220</v>
@@ -6872,16 +6872,16 @@
         <v>44943</v>
       </c>
       <c r="B323" t="n">
-        <v>72.37985229492188</v>
+        <v>72.37985992431641</v>
       </c>
       <c r="C323" t="n">
-        <v>72.69611387031159</v>
+        <v>72.69612153304253</v>
       </c>
       <c r="D323" t="n">
-        <v>70.11331323877729</v>
+        <v>70.11332062926112</v>
       </c>
       <c r="E323" t="n">
-        <v>71.026957045187</v>
+        <v>71.02696453197595</v>
       </c>
       <c r="F323" t="n">
         <v>1038524</v>
@@ -6912,16 +6912,16 @@
         <v>44945</v>
       </c>
       <c r="B325" t="n">
-        <v>75.39312744140625</v>
+        <v>75.39313507080078</v>
       </c>
       <c r="C325" t="n">
-        <v>76.09593252471049</v>
+        <v>76.09594022522526</v>
       </c>
       <c r="D325" t="n">
-        <v>72.74005132170247</v>
+        <v>72.74005868261941</v>
       </c>
       <c r="E325" t="n">
-        <v>73.78546533749886</v>
+        <v>73.78547280420629</v>
       </c>
       <c r="F325" t="n">
         <v>951207</v>
@@ -6972,16 +6972,16 @@
         <v>44950</v>
       </c>
       <c r="B328" t="n">
-        <v>80.33030700683594</v>
+        <v>80.33031463623047</v>
       </c>
       <c r="C328" t="n">
-        <v>81.2966588525702</v>
+        <v>81.29666657374428</v>
       </c>
       <c r="D328" t="n">
-        <v>78.64357635156964</v>
+        <v>78.64358382076644</v>
       </c>
       <c r="E328" t="n">
-        <v>81.2966588525702</v>
+        <v>81.29666657374428</v>
       </c>
       <c r="F328" t="n">
         <v>788120</v>
@@ -7012,16 +7012,16 @@
         <v>44952</v>
       </c>
       <c r="B330" t="n">
-        <v>79.52208709716797</v>
+        <v>79.52207946777344</v>
       </c>
       <c r="C330" t="n">
-        <v>80.04919424909092</v>
+        <v>80.04918656912542</v>
       </c>
       <c r="D330" t="n">
-        <v>77.41368529925958</v>
+        <v>77.41367787214632</v>
       </c>
       <c r="E330" t="n">
-        <v>77.87929080800512</v>
+        <v>77.87928333622141</v>
       </c>
       <c r="F330" t="n">
         <v>392968</v>
@@ -7052,16 +7052,16 @@
         <v>44956</v>
       </c>
       <c r="B332" t="n">
-        <v>80.84862518310547</v>
+        <v>80.8486328125</v>
       </c>
       <c r="C332" t="n">
-        <v>81.99068169579233</v>
+        <v>81.99068943295865</v>
       </c>
       <c r="D332" t="n">
-        <v>78.90713447349425</v>
+        <v>78.90714191967729</v>
       </c>
       <c r="E332" t="n">
-        <v>81.17367368654911</v>
+        <v>81.1736813466173</v>
       </c>
       <c r="F332" t="n">
         <v>515927</v>
@@ -7072,16 +7072,16 @@
         <v>44957</v>
       </c>
       <c r="B333" t="n">
-        <v>78.84563446044922</v>
+        <v>78.84564208984375</v>
       </c>
       <c r="C333" t="n">
-        <v>81.68320174721033</v>
+        <v>81.68320965117834</v>
       </c>
       <c r="D333" t="n">
-        <v>78.84563446044922</v>
+        <v>78.84564208984375</v>
       </c>
       <c r="E333" t="n">
-        <v>80.83983307377135</v>
+        <v>80.83984089613189</v>
       </c>
       <c r="F333" t="n">
         <v>714873</v>
@@ -7172,16 +7172,16 @@
         <v>44964</v>
       </c>
       <c r="B338" t="n">
-        <v>74.67275238037109</v>
+        <v>74.67276000976562</v>
       </c>
       <c r="C338" t="n">
-        <v>78.23947229046264</v>
+        <v>78.23948028427274</v>
       </c>
       <c r="D338" t="n">
-        <v>74.45312663807589</v>
+        <v>74.45313424503101</v>
       </c>
       <c r="E338" t="n">
-        <v>76.98321277643622</v>
+        <v>76.98322064189294</v>
       </c>
       <c r="F338" t="n">
         <v>1089766</v>
@@ -7252,16 +7252,16 @@
         <v>44970</v>
       </c>
       <c r="B342" t="n">
-        <v>73.79425048828125</v>
+        <v>73.79424285888672</v>
       </c>
       <c r="C342" t="n">
-        <v>74.05780406386059</v>
+        <v>74.05779640721795</v>
       </c>
       <c r="D342" t="n">
-        <v>70.90397487319673</v>
+        <v>70.90396754262024</v>
       </c>
       <c r="E342" t="n">
-        <v>71.35201327070328</v>
+        <v>71.35200589380526</v>
       </c>
       <c r="F342" t="n">
         <v>400048</v>
@@ -7332,16 +7332,16 @@
         <v>44974</v>
       </c>
       <c r="B346" t="n">
-        <v>58.25353240966797</v>
+        <v>58.25353622436523</v>
       </c>
       <c r="C346" t="n">
-        <v>64.91258682963696</v>
+        <v>64.91259108039837</v>
       </c>
       <c r="D346" t="n">
-        <v>57.36624919591782</v>
+        <v>57.36625295251188</v>
       </c>
       <c r="E346" t="n">
-        <v>64.68417417050361</v>
+        <v>64.68417840630755</v>
       </c>
       <c r="F346" t="n">
         <v>4993765</v>
@@ -7352,16 +7352,16 @@
         <v>44979</v>
       </c>
       <c r="B347" t="n">
-        <v>59.92268371582031</v>
+        <v>59.92268753051758</v>
       </c>
       <c r="C347" t="n">
-        <v>60.25651241447263</v>
+        <v>60.25651625042154</v>
       </c>
       <c r="D347" t="n">
-        <v>58.28866773896478</v>
+        <v>58.28867144964006</v>
       </c>
       <c r="E347" t="n">
-        <v>58.85969598075974</v>
+        <v>58.85969972778687</v>
       </c>
       <c r="F347" t="n">
         <v>1166573</v>
@@ -7372,16 +7372,16 @@
         <v>44980</v>
       </c>
       <c r="B348" t="n">
-        <v>59.61521911621094</v>
+        <v>59.61521530151367</v>
       </c>
       <c r="C348" t="n">
-        <v>60.5552171369521</v>
+        <v>60.55521326210563</v>
       </c>
       <c r="D348" t="n">
-        <v>58.94755490352809</v>
+        <v>58.94755113155375</v>
       </c>
       <c r="E348" t="n">
-        <v>60.00176261341363</v>
+        <v>60.00175877398195</v>
       </c>
       <c r="F348" t="n">
         <v>572076</v>
@@ -7392,16 +7392,16 @@
         <v>44981</v>
       </c>
       <c r="B349" t="n">
-        <v>58.85091781616211</v>
+        <v>58.85091400146484</v>
       </c>
       <c r="C349" t="n">
-        <v>59.79970272476828</v>
+        <v>59.79969884857108</v>
       </c>
       <c r="D349" t="n">
-        <v>57.98998857507038</v>
+        <v>57.98998481617827</v>
       </c>
       <c r="E349" t="n">
-        <v>59.56250984883994</v>
+        <v>59.56250598801751</v>
       </c>
       <c r="F349" t="n">
         <v>780666</v>
@@ -7432,16 +7432,16 @@
         <v>44985</v>
       </c>
       <c r="B351" t="n">
-        <v>56.48773956298828</v>
+        <v>56.48774337768555</v>
       </c>
       <c r="C351" t="n">
-        <v>57.19932477239597</v>
+        <v>57.19932863514759</v>
       </c>
       <c r="D351" t="n">
-        <v>55.53016790973243</v>
+        <v>55.53017165976352</v>
       </c>
       <c r="E351" t="n">
-        <v>56.82156825454288</v>
+        <v>56.82157209178407</v>
       </c>
       <c r="F351" t="n">
         <v>573942</v>
@@ -7552,16 +7552,16 @@
         <v>44993</v>
       </c>
       <c r="B357" t="n">
-        <v>58.67521286010742</v>
+        <v>58.67520904541016</v>
       </c>
       <c r="C357" t="n">
-        <v>58.67521286010742</v>
+        <v>58.67520904541016</v>
       </c>
       <c r="D357" t="n">
-        <v>53.97522006484605</v>
+        <v>53.97521655571307</v>
       </c>
       <c r="E357" t="n">
-        <v>53.97522006484605</v>
+        <v>53.97521655571307</v>
       </c>
       <c r="F357" t="n">
         <v>1672249</v>
@@ -7632,16 +7632,16 @@
         <v>44999</v>
       </c>
       <c r="B361" t="n">
-        <v>50.32943725585938</v>
+        <v>50.32944107055664</v>
       </c>
       <c r="C361" t="n">
-        <v>52.78924496516417</v>
+        <v>52.78924896630146</v>
       </c>
       <c r="D361" t="n">
-        <v>49.55635368394428</v>
+        <v>49.55635744004602</v>
       </c>
       <c r="E361" t="n">
-        <v>50.84775415559906</v>
+        <v>50.84775800958192</v>
       </c>
       <c r="F361" t="n">
         <v>730632</v>
@@ -7652,16 +7652,16 @@
         <v>45000</v>
       </c>
       <c r="B362" t="n">
-        <v>50.43485641479492</v>
+        <v>50.43486022949219</v>
       </c>
       <c r="C362" t="n">
-        <v>50.90924883268146</v>
+        <v>50.90925268325992</v>
       </c>
       <c r="D362" t="n">
-        <v>48.08925504506086</v>
+        <v>48.08925868234591</v>
       </c>
       <c r="E362" t="n">
-        <v>49.89896905583676</v>
+        <v>49.89897283000158</v>
       </c>
       <c r="F362" t="n">
         <v>1072440</v>
@@ -7672,16 +7672,16 @@
         <v>45001</v>
       </c>
       <c r="B363" t="n">
-        <v>53.81708908081055</v>
+        <v>53.81709289550781</v>
       </c>
       <c r="C363" t="n">
-        <v>54.24755699955558</v>
+        <v>54.24756084476554</v>
       </c>
       <c r="D363" t="n">
-        <v>50.10980892177768</v>
+        <v>50.10981247369315</v>
       </c>
       <c r="E363" t="n">
-        <v>50.68962073298718</v>
+        <v>50.68962432600123</v>
       </c>
       <c r="F363" t="n">
         <v>1144994</v>
@@ -7692,16 +7692,16 @@
         <v>45002</v>
       </c>
       <c r="B364" t="n">
-        <v>55.06457138061523</v>
+        <v>55.06456756591797</v>
       </c>
       <c r="C364" t="n">
-        <v>55.5477473873311</v>
+        <v>55.54774353916095</v>
       </c>
       <c r="D364" t="n">
-        <v>52.19186600817599</v>
+        <v>52.19186239249056</v>
       </c>
       <c r="E364" t="n">
-        <v>53.58868599016529</v>
+        <v>53.58868227771264</v>
       </c>
       <c r="F364" t="n">
         <v>1415773</v>
@@ -7752,16 +7752,16 @@
         <v>45007</v>
       </c>
       <c r="B367" t="n">
-        <v>52.56961822509766</v>
+        <v>52.56962203979492</v>
       </c>
       <c r="C367" t="n">
-        <v>55.1260617515593</v>
+        <v>55.12606575176405</v>
       </c>
       <c r="D367" t="n">
-        <v>52.56961822509766</v>
+        <v>52.56962203979492</v>
       </c>
       <c r="E367" t="n">
-        <v>53.85223176594004</v>
+        <v>53.85223567370974</v>
       </c>
       <c r="F367" t="n">
         <v>930770</v>
@@ -7792,16 +7792,16 @@
         <v>45009</v>
       </c>
       <c r="B369" t="n">
-        <v>50.40850448608398</v>
+        <v>50.40850830078125</v>
       </c>
       <c r="C369" t="n">
-        <v>51.3660729168746</v>
+        <v>51.3660768040365</v>
       </c>
       <c r="D369" t="n">
-        <v>48.82719971216801</v>
+        <v>48.82720340719898</v>
       </c>
       <c r="E369" t="n">
-        <v>50.05710193578128</v>
+        <v>50.05710572388593</v>
       </c>
       <c r="F369" t="n">
         <v>598427</v>
@@ -7852,16 +7852,16 @@
         <v>45014</v>
       </c>
       <c r="B372" t="n">
-        <v>53.88737106323242</v>
+        <v>53.88737487792969</v>
       </c>
       <c r="C372" t="n">
-        <v>54.64288413609415</v>
+        <v>54.64288800427434</v>
       </c>
       <c r="D372" t="n">
-        <v>52.91223225296775</v>
+        <v>52.91223599863476</v>
       </c>
       <c r="E372" t="n">
-        <v>54.38811747641328</v>
+        <v>54.38812132655848</v>
       </c>
       <c r="F372" t="n">
         <v>332515</v>
@@ -7872,16 +7872,16 @@
         <v>45015</v>
       </c>
       <c r="B373" t="n">
-        <v>54.20363616943359</v>
+        <v>54.20363235473633</v>
       </c>
       <c r="C373" t="n">
-        <v>56.39989033438518</v>
+        <v>56.3998863651218</v>
       </c>
       <c r="D373" t="n">
-        <v>53.72924374164636</v>
+        <v>53.72923996033548</v>
       </c>
       <c r="E373" t="n">
-        <v>54.0367184534216</v>
+        <v>54.03671465047152</v>
       </c>
       <c r="F373" t="n">
         <v>990197</v>
@@ -7972,16 +7972,16 @@
         <v>45022</v>
       </c>
       <c r="B378" t="n">
-        <v>48.04533004760742</v>
+        <v>48.04532623291016</v>
       </c>
       <c r="C378" t="n">
-        <v>49.56513990454828</v>
+        <v>49.56513596918133</v>
       </c>
       <c r="D378" t="n">
-        <v>47.88719923232127</v>
+        <v>47.88719543017925</v>
       </c>
       <c r="E378" t="n">
-        <v>48.64271238286111</v>
+        <v>48.64270852073295</v>
       </c>
       <c r="F378" t="n">
         <v>483494</v>
@@ -8012,16 +8012,16 @@
         <v>45027</v>
       </c>
       <c r="B380" t="n">
-        <v>54.63410186767578</v>
+        <v>54.63409805297852</v>
       </c>
       <c r="C380" t="n">
-        <v>54.63410186767578</v>
+        <v>54.63409805297852</v>
       </c>
       <c r="D380" t="n">
-        <v>48.8535537111691</v>
+        <v>48.85355030008497</v>
       </c>
       <c r="E380" t="n">
-        <v>48.8535537111691</v>
+        <v>48.85355030008497</v>
       </c>
       <c r="F380" t="n">
         <v>1223134</v>
@@ -8052,16 +8052,16 @@
         <v>45029</v>
       </c>
       <c r="B382" t="n">
-        <v>60.46736145019531</v>
+        <v>60.46736526489258</v>
       </c>
       <c r="C382" t="n">
-        <v>61.46006740025275</v>
+        <v>61.46007127757674</v>
       </c>
       <c r="D382" t="n">
-        <v>55.96064024470993</v>
+        <v>55.96064377509221</v>
       </c>
       <c r="E382" t="n">
-        <v>56.408675287958</v>
+        <v>56.4086788466054</v>
       </c>
       <c r="F382" t="n">
         <v>2756815</v>
@@ -8072,16 +8072,16 @@
         <v>45030</v>
       </c>
       <c r="B383" t="n">
-        <v>60.44979095458984</v>
+        <v>60.44978713989258</v>
       </c>
       <c r="C383" t="n">
-        <v>62.1540889664382</v>
+        <v>62.15408504419084</v>
       </c>
       <c r="D383" t="n">
-        <v>59.1056823998625</v>
+        <v>59.10567866998549</v>
       </c>
       <c r="E383" t="n">
-        <v>60.45857786151738</v>
+        <v>60.45857404626561</v>
       </c>
       <c r="F383" t="n">
         <v>793877</v>
@@ -8092,16 +8092,16 @@
         <v>45033</v>
       </c>
       <c r="B384" t="n">
-        <v>59.95782470703125</v>
+        <v>59.95783233642578</v>
       </c>
       <c r="C384" t="n">
-        <v>60.7221246656276</v>
+        <v>60.72213239227627</v>
       </c>
       <c r="D384" t="n">
-        <v>59.16717073304285</v>
+        <v>59.16717826182981</v>
       </c>
       <c r="E384" t="n">
-        <v>60.35314834280274</v>
+        <v>60.35315602250063</v>
       </c>
       <c r="F384" t="n">
         <v>288592</v>
@@ -8112,16 +8112,16 @@
         <v>45034</v>
       </c>
       <c r="B385" t="n">
-        <v>61.49520492553711</v>
+        <v>61.49521255493164</v>
       </c>
       <c r="C385" t="n">
-        <v>61.49520492553711</v>
+        <v>61.49521255493164</v>
       </c>
       <c r="D385" t="n">
-        <v>59.16717082715269</v>
+        <v>59.16717816771997</v>
       </c>
       <c r="E385" t="n">
-        <v>59.16717082715269</v>
+        <v>59.16717816771997</v>
       </c>
       <c r="F385" t="n">
         <v>581190</v>
@@ -8132,16 +8132,16 @@
         <v>45035</v>
       </c>
       <c r="B386" t="n">
-        <v>58.84213256835938</v>
+        <v>58.84213638305664</v>
       </c>
       <c r="C386" t="n">
-        <v>61.27558287466414</v>
+        <v>61.2755868471204</v>
       </c>
       <c r="D386" t="n">
-        <v>58.30624521419173</v>
+        <v>58.30624899414777</v>
       </c>
       <c r="E386" t="n">
-        <v>61.27558287466414</v>
+        <v>61.2755868471204</v>
       </c>
       <c r="F386" t="n">
         <v>827950</v>
@@ -8152,16 +8152,16 @@
         <v>45036</v>
       </c>
       <c r="B387" t="n">
-        <v>60.80119323730469</v>
+        <v>60.80118942260742</v>
       </c>
       <c r="C387" t="n">
-        <v>60.80119323730469</v>
+        <v>60.80118942260742</v>
       </c>
       <c r="D387" t="n">
-        <v>58.21839221255807</v>
+        <v>58.21838855990702</v>
       </c>
       <c r="E387" t="n">
-        <v>58.78942051630461</v>
+        <v>58.78941682782696</v>
       </c>
       <c r="F387" t="n">
         <v>442904</v>
@@ -8172,16 +8172,16 @@
         <v>45040</v>
       </c>
       <c r="B388" t="n">
-        <v>60.99446868896484</v>
+        <v>60.99446487426758</v>
       </c>
       <c r="C388" t="n">
-        <v>61.27558940451494</v>
+        <v>61.2755855722359</v>
       </c>
       <c r="D388" t="n">
-        <v>59.73820902519019</v>
+        <v>59.73820528906153</v>
       </c>
       <c r="E388" t="n">
-        <v>60.27409643646482</v>
+        <v>60.27409266682086</v>
       </c>
       <c r="F388" t="n">
         <v>315786</v>
@@ -8192,16 +8192,16 @@
         <v>45041</v>
       </c>
       <c r="B389" t="n">
-        <v>60.50251007080078</v>
+        <v>60.50250625610352</v>
       </c>
       <c r="C389" t="n">
-        <v>61.2843772827617</v>
+        <v>61.28437341876753</v>
       </c>
       <c r="D389" t="n">
-        <v>59.0090508000448</v>
+        <v>59.00904707951048</v>
       </c>
       <c r="E389" t="n">
-        <v>61.2843772827617</v>
+        <v>61.28437341876753</v>
       </c>
       <c r="F389" t="n">
         <v>695154</v>
@@ -8212,16 +8212,16 @@
         <v>45042</v>
       </c>
       <c r="B390" t="n">
-        <v>59.3165168762207</v>
+        <v>59.31652069091797</v>
       </c>
       <c r="C390" t="n">
-        <v>60.01932192479727</v>
+        <v>60.01932578469255</v>
       </c>
       <c r="D390" t="n">
-        <v>56.95334847283447</v>
+        <v>56.9533521355543</v>
       </c>
       <c r="E390" t="n">
-        <v>59.30773667238661</v>
+        <v>59.30774048651921</v>
       </c>
       <c r="F390" t="n">
         <v>963997</v>
@@ -8232,16 +8232,16 @@
         <v>45043</v>
       </c>
       <c r="B391" t="n">
-        <v>61.50400161743164</v>
+        <v>61.50400543212891</v>
       </c>
       <c r="C391" t="n">
-        <v>62.82175621836179</v>
+        <v>62.82176011479089</v>
       </c>
       <c r="D391" t="n">
-        <v>58.44680799419723</v>
+        <v>58.44681161927646</v>
       </c>
       <c r="E391" t="n">
-        <v>58.59615190704881</v>
+        <v>58.59615554139089</v>
       </c>
       <c r="F391" t="n">
         <v>723893</v>
@@ -8252,16 +8252,16 @@
         <v>45044</v>
       </c>
       <c r="B392" t="n">
-        <v>63.67390441894531</v>
+        <v>63.67389678955078</v>
       </c>
       <c r="C392" t="n">
-        <v>63.75296647677501</v>
+        <v>63.75295883790729</v>
       </c>
       <c r="D392" t="n">
-        <v>60.61671083638181</v>
+        <v>60.6167035732996</v>
       </c>
       <c r="E392" t="n">
-        <v>61.50400079922254</v>
+        <v>61.50399342982543</v>
       </c>
       <c r="F392" t="n">
         <v>633625</v>
@@ -8272,16 +8272,16 @@
         <v>45048</v>
       </c>
       <c r="B393" t="n">
-        <v>58.38531112670898</v>
+        <v>58.38530731201172</v>
       </c>
       <c r="C393" t="n">
-        <v>63.16436980030091</v>
+        <v>63.16436567335623</v>
       </c>
       <c r="D393" t="n">
-        <v>58.38531112670898</v>
+        <v>58.38530731201172</v>
       </c>
       <c r="E393" t="n">
-        <v>63.16436980030091</v>
+        <v>63.16436567335623</v>
       </c>
       <c r="F393" t="n">
         <v>808928</v>
@@ -8292,16 +8292,16 @@
         <v>45049</v>
       </c>
       <c r="B394" t="n">
-        <v>58.85091781616211</v>
+        <v>58.85091400146484</v>
       </c>
       <c r="C394" t="n">
-        <v>60.08082343445384</v>
+        <v>60.08081954003449</v>
       </c>
       <c r="D394" t="n">
-        <v>58.7718557583348</v>
+        <v>58.77185194876231</v>
       </c>
       <c r="E394" t="n">
-        <v>59.12325832105335</v>
+        <v>59.12325448870306</v>
       </c>
       <c r="F394" t="n">
         <v>320277</v>
@@ -8332,16 +8332,16 @@
         <v>45051</v>
       </c>
       <c r="B396" t="n">
-        <v>64.07801055908203</v>
+        <v>64.07801818847656</v>
       </c>
       <c r="C396" t="n">
-        <v>64.75445491572299</v>
+        <v>64.75446262565779</v>
       </c>
       <c r="D396" t="n">
-        <v>60.79240453412326</v>
+        <v>60.79241177231987</v>
       </c>
       <c r="E396" t="n">
-        <v>60.79240453412326</v>
+        <v>60.79241177231987</v>
       </c>
       <c r="F396" t="n">
         <v>739601</v>
@@ -8412,16 +8412,16 @@
         <v>45057</v>
       </c>
       <c r="B400" t="n">
-        <v>67.00341796875</v>
+        <v>67.00341033935547</v>
       </c>
       <c r="C400" t="n">
-        <v>68.69892895366183</v>
+        <v>68.69892113120667</v>
       </c>
       <c r="D400" t="n">
-        <v>67.00341796875</v>
+        <v>67.00341033935547</v>
       </c>
       <c r="E400" t="n">
-        <v>67.38117451054214</v>
+        <v>67.38116683813408</v>
       </c>
       <c r="F400" t="n">
         <v>282491</v>
@@ -8512,16 +8512,16 @@
         <v>45064</v>
       </c>
       <c r="B405" t="n">
-        <v>71.18508911132812</v>
+        <v>71.18510437011719</v>
       </c>
       <c r="C405" t="n">
-        <v>71.99331017297479</v>
+        <v>71.99332560500903</v>
       </c>
       <c r="D405" t="n">
-        <v>69.86733475768652</v>
+        <v>69.86734973401003</v>
       </c>
       <c r="E405" t="n">
-        <v>71.15873509664654</v>
+        <v>71.15875034978652</v>
       </c>
       <c r="F405" t="n">
         <v>796674</v>
@@ -8532,16 +8532,16 @@
         <v>45065</v>
       </c>
       <c r="B406" t="n">
-        <v>75.91145324707031</v>
+        <v>75.91144561767578</v>
       </c>
       <c r="C406" t="n">
-        <v>76.42976683949719</v>
+        <v>76.42975915801013</v>
       </c>
       <c r="D406" t="n">
-        <v>71.19388936375165</v>
+        <v>71.19388220849052</v>
       </c>
       <c r="E406" t="n">
-        <v>71.19388936375165</v>
+        <v>71.19388220849052</v>
       </c>
       <c r="F406" t="n">
         <v>1201246</v>
@@ -8552,16 +8552,16 @@
         <v>45068</v>
       </c>
       <c r="B407" t="n">
-        <v>77.76507568359375</v>
+        <v>77.76508331298828</v>
       </c>
       <c r="C407" t="n">
-        <v>78.3097499079546</v>
+        <v>78.30975759078616</v>
       </c>
       <c r="D407" t="n">
-        <v>75.0768588878434</v>
+        <v>75.07686625350173</v>
       </c>
       <c r="E407" t="n">
-        <v>75.45461541229061</v>
+        <v>75.45462281500996</v>
       </c>
       <c r="F407" t="n">
         <v>873661</v>
@@ -8572,16 +8572,16 @@
         <v>45069</v>
       </c>
       <c r="B408" t="n">
-        <v>77.132568359375</v>
+        <v>77.13256072998047</v>
       </c>
       <c r="C408" t="n">
-        <v>80.43573491118516</v>
+        <v>80.43572695506535</v>
       </c>
       <c r="D408" t="n">
-        <v>76.42976325763665</v>
+        <v>76.42975569775851</v>
       </c>
       <c r="E408" t="n">
-        <v>77.74751779656141</v>
+        <v>77.74751010634054</v>
       </c>
       <c r="F408" t="n">
         <v>970823</v>
@@ -8592,16 +8592,16 @@
         <v>45070</v>
       </c>
       <c r="B409" t="n">
-        <v>77.30826568603516</v>
+        <v>77.30825805664062</v>
       </c>
       <c r="C409" t="n">
-        <v>78.27461766662137</v>
+        <v>78.27460994185954</v>
       </c>
       <c r="D409" t="n">
-        <v>75.96415713911252</v>
+        <v>75.96414964236531</v>
       </c>
       <c r="E409" t="n">
-        <v>76.61424749660561</v>
+        <v>76.61423993570233</v>
       </c>
       <c r="F409" t="n">
         <v>567398</v>
@@ -8632,16 +8632,16 @@
         <v>45072</v>
       </c>
       <c r="B411" t="n">
-        <v>82.75498199462891</v>
+        <v>82.75497436523438</v>
       </c>
       <c r="C411" t="n">
-        <v>84.15180528493505</v>
+        <v>84.15179752676379</v>
       </c>
       <c r="D411" t="n">
-        <v>80.38302651611544</v>
+        <v>80.38301910539758</v>
       </c>
       <c r="E411" t="n">
-        <v>81.70078104916651</v>
+        <v>81.70077351696148</v>
       </c>
       <c r="F411" t="n">
         <v>582166</v>
@@ -8672,16 +8672,16 @@
         <v>45076</v>
       </c>
       <c r="B413" t="n">
-        <v>80.55873107910156</v>
+        <v>80.55872344970703</v>
       </c>
       <c r="C413" t="n">
-        <v>84.13423840537149</v>
+        <v>84.13423043735499</v>
       </c>
       <c r="D413" t="n">
-        <v>79.3991072625396</v>
+        <v>79.3990997429684</v>
       </c>
       <c r="E413" t="n">
-        <v>82.54414994921937</v>
+        <v>82.54414213179378</v>
       </c>
       <c r="F413" t="n">
         <v>664894</v>
@@ -8732,16 +8732,16 @@
         <v>45079</v>
       </c>
       <c r="B416" t="n">
-        <v>82.84283447265625</v>
+        <v>82.84282684326172</v>
       </c>
       <c r="C416" t="n">
-        <v>84.02881216630033</v>
+        <v>84.0288044276834</v>
       </c>
       <c r="D416" t="n">
-        <v>78.89835122966686</v>
+        <v>78.89834396353872</v>
       </c>
       <c r="E416" t="n">
-        <v>78.89835122966686</v>
+        <v>78.89834396353872</v>
       </c>
       <c r="F416" t="n">
         <v>731024</v>
@@ -8752,16 +8752,16 @@
         <v>45082</v>
       </c>
       <c r="B417" t="n">
-        <v>82.02582550048828</v>
+        <v>82.02583312988281</v>
       </c>
       <c r="C417" t="n">
-        <v>82.88675466589184</v>
+        <v>82.8867623753632</v>
       </c>
       <c r="D417" t="n">
-        <v>79.88227608855597</v>
+        <v>79.88228351857445</v>
       </c>
       <c r="E417" t="n">
-        <v>82.88675466589184</v>
+        <v>82.8867623753632</v>
       </c>
       <c r="F417" t="n">
         <v>409729</v>
@@ -8812,16 +8812,16 @@
         <v>45086</v>
       </c>
       <c r="B420" t="n">
-        <v>87.92936706542969</v>
+        <v>87.92935943603516</v>
       </c>
       <c r="C420" t="n">
-        <v>90.98656062878784</v>
+        <v>90.98655273412886</v>
       </c>
       <c r="D420" t="n">
-        <v>86.98058886520148</v>
+        <v>86.98058131812988</v>
       </c>
       <c r="E420" t="n">
-        <v>86.98058886520148</v>
+        <v>86.98058131812988</v>
       </c>
       <c r="F420" t="n">
         <v>1309381</v>
@@ -8832,16 +8832,16 @@
         <v>45089</v>
       </c>
       <c r="B421" t="n">
-        <v>90.35403442382812</v>
+        <v>90.35404205322266</v>
       </c>
       <c r="C421" t="n">
-        <v>91.34674712772208</v>
+        <v>91.34675484094018</v>
       </c>
       <c r="D421" t="n">
-        <v>87.95572492842221</v>
+        <v>87.95573235530614</v>
       </c>
       <c r="E421" t="n">
-        <v>87.95572492842221</v>
+        <v>87.95573235530614</v>
       </c>
       <c r="F421" t="n">
         <v>1071620</v>
@@ -8972,16 +8972,16 @@
         <v>45098</v>
       </c>
       <c r="B428" t="n">
-        <v>102.9605484008789</v>
+        <v>102.9605560302734</v>
       </c>
       <c r="C428" t="n">
-        <v>103.6457863674851</v>
+        <v>103.6457940476559</v>
       </c>
       <c r="D428" t="n">
-        <v>97.65439620573426</v>
+        <v>97.65440344194199</v>
       </c>
       <c r="E428" t="n">
-        <v>99.25327138959017</v>
+        <v>99.25327874427484</v>
       </c>
       <c r="F428" t="n">
         <v>1080781</v>
@@ -9012,16 +9012,16 @@
         <v>45100</v>
       </c>
       <c r="B430" t="n">
-        <v>98.56803131103516</v>
+        <v>98.56803894042969</v>
       </c>
       <c r="C430" t="n">
-        <v>100.544663008736</v>
+        <v>100.5446707911264</v>
       </c>
       <c r="D430" t="n">
-        <v>97.24149664189471</v>
+        <v>97.24150416861238</v>
       </c>
       <c r="E430" t="n">
-        <v>99.71008786179617</v>
+        <v>99.71009557958853</v>
       </c>
       <c r="F430" t="n">
         <v>1883788</v>
@@ -9052,16 +9052,16 @@
         <v>45104</v>
       </c>
       <c r="B432" t="n">
-        <v>94.86952972412109</v>
+        <v>94.86954498291016</v>
       </c>
       <c r="C432" t="n">
-        <v>98.37476124760583</v>
+        <v>98.37477707017537</v>
       </c>
       <c r="D432" t="n">
-        <v>91.40823273064802</v>
+        <v>91.40824743272303</v>
       </c>
       <c r="E432" t="n">
-        <v>96.97793810083515</v>
+        <v>96.97795369874004</v>
       </c>
       <c r="F432" t="n">
         <v>1484061</v>
@@ -9072,16 +9072,16 @@
         <v>45105</v>
       </c>
       <c r="B433" t="n">
-        <v>97.09215545654297</v>
+        <v>97.09214782714844</v>
       </c>
       <c r="C433" t="n">
-        <v>98.19028428396808</v>
+        <v>98.19027656828381</v>
       </c>
       <c r="D433" t="n">
-        <v>94.29851545147561</v>
+        <v>94.29850804160222</v>
       </c>
       <c r="E433" t="n">
-        <v>94.4742200853315</v>
+        <v>94.47421266165144</v>
       </c>
       <c r="F433" t="n">
         <v>538862</v>
@@ -9092,16 +9092,16 @@
         <v>45106</v>
       </c>
       <c r="B434" t="n">
-        <v>99.08635711669922</v>
+        <v>99.08634948730469</v>
       </c>
       <c r="C434" t="n">
-        <v>99.83308334838433</v>
+        <v>99.83307566149379</v>
       </c>
       <c r="D434" t="n">
-        <v>97.4259869335896</v>
+        <v>97.4259794320393</v>
       </c>
       <c r="E434" t="n">
-        <v>97.53140300715454</v>
+        <v>97.53139549748747</v>
       </c>
       <c r="F434" t="n">
         <v>506881</v>
@@ -9132,16 +9132,16 @@
         <v>45110</v>
       </c>
       <c r="B436" t="n">
-        <v>100.8960723876953</v>
+        <v>100.8960800170898</v>
       </c>
       <c r="C436" t="n">
-        <v>101.4671007018312</v>
+        <v>101.4671083744049</v>
       </c>
       <c r="D436" t="n">
-        <v>98.26056327855684</v>
+        <v>98.26057070866375</v>
       </c>
       <c r="E436" t="n">
-        <v>98.46262192600048</v>
+        <v>98.46262937138633</v>
       </c>
       <c r="F436" t="n">
         <v>512630</v>
@@ -9172,16 +9172,16 @@
         <v>45112</v>
       </c>
       <c r="B438" t="n">
-        <v>101.2386856079102</v>
+        <v>101.2386779785156</v>
       </c>
       <c r="C438" t="n">
-        <v>101.7042911336343</v>
+        <v>101.7042834691515</v>
       </c>
       <c r="D438" t="n">
-        <v>99.13027703067131</v>
+        <v>99.13026956016742</v>
       </c>
       <c r="E438" t="n">
-        <v>99.53439431586756</v>
+        <v>99.5343868149092</v>
       </c>
       <c r="F438" t="n">
         <v>519657</v>
@@ -9192,16 +9192,16 @@
         <v>45113</v>
       </c>
       <c r="B439" t="n">
-        <v>99.20934295654297</v>
+        <v>99.2093505859375</v>
       </c>
       <c r="C439" t="n">
-        <v>100.1405539814207</v>
+        <v>100.1405616824272</v>
       </c>
       <c r="D439" t="n">
-        <v>97.71589055410367</v>
+        <v>97.71589806864876</v>
       </c>
       <c r="E439" t="n">
-        <v>100.1405539814207</v>
+        <v>100.1405616824272</v>
       </c>
       <c r="F439" t="n">
         <v>463942</v>
@@ -9212,16 +9212,16 @@
         <v>45114</v>
       </c>
       <c r="B440" t="n">
-        <v>101.2386856079102</v>
+        <v>101.2386779785156</v>
       </c>
       <c r="C440" t="n">
-        <v>102.0820476983165</v>
+        <v>102.0820400053658</v>
       </c>
       <c r="D440" t="n">
-        <v>98.16392505431695</v>
+        <v>98.16391765663779</v>
       </c>
       <c r="E440" t="n">
-        <v>98.73495335475918</v>
+        <v>98.73494591404707</v>
       </c>
       <c r="F440" t="n">
         <v>1239341</v>
@@ -9272,16 +9272,16 @@
         <v>45119</v>
       </c>
       <c r="B443" t="n">
-        <v>99.29718780517578</v>
+        <v>99.29719543457031</v>
       </c>
       <c r="C443" t="n">
-        <v>102.0644734504011</v>
+        <v>102.0644812924171</v>
       </c>
       <c r="D443" t="n">
-        <v>98.57681565108831</v>
+        <v>98.57682322513379</v>
       </c>
       <c r="E443" t="n">
-        <v>99.10391608292989</v>
+        <v>99.10392369747458</v>
       </c>
       <c r="F443" t="n">
         <v>690662</v>
@@ -9312,16 +9312,16 @@
         <v>45121</v>
       </c>
       <c r="B445" t="n">
-        <v>96.74075317382812</v>
+        <v>96.74074554443359</v>
       </c>
       <c r="C445" t="n">
-        <v>98.69981111857781</v>
+        <v>98.69980333468348</v>
       </c>
       <c r="D445" t="n">
-        <v>95.02766829526057</v>
+        <v>95.02766080096731</v>
       </c>
       <c r="E445" t="n">
-        <v>98.69981111857781</v>
+        <v>98.69980333468348</v>
       </c>
       <c r="F445" t="n">
         <v>461646</v>
@@ -9372,16 +9372,16 @@
         <v>45126</v>
       </c>
       <c r="B448" t="n">
-        <v>101.0629806518555</v>
+        <v>101.06298828125</v>
       </c>
       <c r="C448" t="n">
-        <v>101.2650325779447</v>
+        <v>101.2650402225924</v>
       </c>
       <c r="D448" t="n">
-        <v>99.00728025382909</v>
+        <v>99.00728772803575</v>
       </c>
       <c r="E448" t="n">
-        <v>100.8257811008604</v>
+        <v>100.8257887123484</v>
       </c>
       <c r="F448" t="n">
         <v>1189852</v>
@@ -9452,16 +9452,16 @@
         <v>45132</v>
       </c>
       <c r="B452" t="n">
-        <v>112.1584701538086</v>
+        <v>112.1584777832031</v>
       </c>
       <c r="C452" t="n">
-        <v>115.3298663433468</v>
+        <v>115.3298741884703</v>
       </c>
       <c r="D452" t="n">
-        <v>110.5859490671098</v>
+        <v>110.5859565895362</v>
       </c>
       <c r="E452" t="n">
-        <v>112.9491308527013</v>
+        <v>112.9491385358792</v>
       </c>
       <c r="F452" t="n">
         <v>603712</v>
@@ -9492,16 +9492,16 @@
         <v>45134</v>
       </c>
       <c r="B454" t="n">
-        <v>110.7440948486328</v>
+        <v>110.7440872192383</v>
       </c>
       <c r="C454" t="n">
-        <v>114.6446506238359</v>
+        <v>114.6446427257238</v>
       </c>
       <c r="D454" t="n">
-        <v>109.7074609580359</v>
+        <v>109.7074534000573</v>
       </c>
       <c r="E454" t="n">
-        <v>113.5025939519685</v>
+        <v>113.5025861325351</v>
       </c>
       <c r="F454" t="n">
         <v>678181</v>
@@ -9592,16 +9592,16 @@
         <v>45141</v>
       </c>
       <c r="B459" t="n">
-        <v>114.7939834594727</v>
+        <v>114.7939910888672</v>
       </c>
       <c r="C459" t="n">
-        <v>117.3065025331647</v>
+        <v>117.3065103295453</v>
       </c>
       <c r="D459" t="n">
-        <v>111.8597867062838</v>
+        <v>111.8597941406668</v>
       </c>
       <c r="E459" t="n">
-        <v>112.9227678115621</v>
+        <v>112.9227753165926</v>
       </c>
       <c r="F459" t="n">
         <v>1277901</v>
@@ -9612,16 +9612,16 @@
         <v>45142</v>
       </c>
       <c r="B460" t="n">
-        <v>113.1336059570312</v>
+        <v>113.1336135864258</v>
       </c>
       <c r="C460" t="n">
-        <v>114.6007042377062</v>
+        <v>114.6007119660374</v>
       </c>
       <c r="D460" t="n">
-        <v>110.9900566686566</v>
+        <v>110.9900641534965</v>
       </c>
       <c r="E460" t="n">
-        <v>114.2053806012186</v>
+        <v>114.2053883028904</v>
       </c>
       <c r="F460" t="n">
         <v>805649</v>
@@ -9632,16 +9632,16 @@
         <v>45145</v>
       </c>
       <c r="B461" t="n">
-        <v>112.993049621582</v>
+        <v>112.9930572509766</v>
       </c>
       <c r="C461" t="n">
-        <v>117.7193999696295</v>
+        <v>117.7194079181516</v>
       </c>
       <c r="D461" t="n">
-        <v>111.6225871100018</v>
+        <v>111.6225946468615</v>
       </c>
       <c r="E461" t="n">
-        <v>113.3268850453896</v>
+        <v>113.326892697325</v>
       </c>
       <c r="F461" t="n">
         <v>579696</v>
@@ -9672,16 +9672,16 @@
         <v>45147</v>
       </c>
       <c r="B463" t="n">
-        <v>112.4483871459961</v>
+        <v>112.4483795166016</v>
       </c>
       <c r="C463" t="n">
-        <v>114.1263311401144</v>
+        <v>114.1263233968748</v>
       </c>
       <c r="D463" t="n">
-        <v>110.612319041802</v>
+        <v>110.612311536981</v>
       </c>
       <c r="E463" t="n">
-        <v>113.7397876645173</v>
+        <v>113.7397799475038</v>
       </c>
       <c r="F463" t="n">
         <v>434571</v>
@@ -9712,16 +9712,16 @@
         <v>45149</v>
       </c>
       <c r="B465" t="n">
-        <v>109.812873840332</v>
+        <v>109.8128814697266</v>
       </c>
       <c r="C465" t="n">
-        <v>111.9915642064004</v>
+        <v>111.9915719871623</v>
       </c>
       <c r="D465" t="n">
-        <v>108.1261497067316</v>
+        <v>108.1261572189387</v>
       </c>
       <c r="E465" t="n">
-        <v>110.7353046615692</v>
+        <v>110.7353123550508</v>
       </c>
       <c r="F465" t="n">
         <v>577766</v>
@@ -9772,16 +9772,16 @@
         <v>45154</v>
       </c>
       <c r="B468" t="n">
-        <v>108.6444625854492</v>
+        <v>108.6444549560547</v>
       </c>
       <c r="C468" t="n">
-        <v>111.842212915804</v>
+        <v>111.8422050618522</v>
       </c>
       <c r="D468" t="n">
-        <v>107.098302157054</v>
+        <v>107.0982946362363</v>
       </c>
       <c r="E468" t="n">
-        <v>108.2403520164973</v>
+        <v>108.2403444154809</v>
       </c>
       <c r="F468" t="n">
         <v>1047832</v>
@@ -9792,16 +9792,16 @@
         <v>45155</v>
       </c>
       <c r="B469" t="n">
-        <v>103.6633529663086</v>
+        <v>103.6633453369141</v>
       </c>
       <c r="C469" t="n">
-        <v>109.7689460744476</v>
+        <v>109.7689379956948</v>
       </c>
       <c r="D469" t="n">
-        <v>103.048403553419</v>
+        <v>103.0483959692834</v>
       </c>
       <c r="E469" t="n">
-        <v>108.9782987442884</v>
+        <v>108.9782907237255</v>
       </c>
       <c r="F469" t="n">
         <v>1841816</v>
@@ -9812,16 +9812,16 @@
         <v>45156</v>
       </c>
       <c r="B470" t="n">
-        <v>109.1539916992188</v>
+        <v>109.1539993286133</v>
       </c>
       <c r="C470" t="n">
-        <v>109.2242735439098</v>
+        <v>109.2242811782168</v>
       </c>
       <c r="D470" t="n">
-        <v>104.6911950980199</v>
+        <v>104.6912024154841</v>
       </c>
       <c r="E470" t="n">
-        <v>106.2549292789454</v>
+        <v>106.2549367057079</v>
       </c>
       <c r="F470" t="n">
         <v>1642163</v>
@@ -9872,16 +9872,16 @@
         <v>45161</v>
       </c>
       <c r="B473" t="n">
-        <v>117.4294967651367</v>
+        <v>117.4294891357422</v>
       </c>
       <c r="C473" t="n">
-        <v>117.9390301239801</v>
+        <v>117.9390224614812</v>
       </c>
       <c r="D473" t="n">
-        <v>112.9491394178873</v>
+        <v>112.9491320795816</v>
       </c>
       <c r="E473" t="n">
-        <v>114.0296943762679</v>
+        <v>114.0296869677586</v>
       </c>
       <c r="F473" t="n">
         <v>1193312</v>
@@ -9972,16 +9972,16 @@
         <v>45168</v>
       </c>
       <c r="B478" t="n">
-        <v>112.4483871459961</v>
+        <v>112.4483795166016</v>
       </c>
       <c r="C478" t="n">
-        <v>113.853997347278</v>
+        <v>113.8539896225157</v>
       </c>
       <c r="D478" t="n">
-        <v>110.8231578910159</v>
+        <v>110.8231503718898</v>
       </c>
       <c r="E478" t="n">
-        <v>113.0721301915992</v>
+        <v>113.0721225198849</v>
       </c>
       <c r="F478" t="n">
         <v>547646</v>
@@ -9992,16 +9992,16 @@
         <v>45169</v>
       </c>
       <c r="B479" t="n">
-        <v>110.4102554321289</v>
+        <v>110.4102630615234</v>
       </c>
       <c r="C479" t="n">
-        <v>112.4395951828659</v>
+        <v>112.4396029524886</v>
       </c>
       <c r="D479" t="n">
-        <v>108.8465211910895</v>
+        <v>108.8465287124293</v>
       </c>
       <c r="E479" t="n">
-        <v>111.7455770203644</v>
+        <v>111.7455847420302</v>
       </c>
       <c r="F479" t="n">
         <v>854216</v>
@@ -10092,16 +10092,16 @@
         <v>45177</v>
       </c>
       <c r="B484" t="n">
-        <v>108.5126953125</v>
+        <v>108.5126876831055</v>
       </c>
       <c r="C484" t="n">
-        <v>110.7968086365694</v>
+        <v>110.7968008465816</v>
       </c>
       <c r="D484" t="n">
-        <v>106.7293351683192</v>
+        <v>106.7293276643105</v>
       </c>
       <c r="E484" t="n">
-        <v>109.8128827938557</v>
+        <v>109.8128750730466</v>
       </c>
       <c r="F484" t="n">
         <v>972821</v>
@@ -10172,16 +10172,16 @@
         <v>45183</v>
       </c>
       <c r="B488" t="n">
-        <v>112.4759826660156</v>
+        <v>112.4759750366211</v>
       </c>
       <c r="C488" t="n">
-        <v>114.2481799411909</v>
+        <v>114.2481721915859</v>
       </c>
       <c r="D488" t="n">
-        <v>110.6048297252885</v>
+        <v>110.6048222228168</v>
       </c>
       <c r="E488" t="n">
-        <v>114.2481799411909</v>
+        <v>114.2481721915859</v>
       </c>
       <c r="F488" t="n">
         <v>682177</v>
@@ -10232,16 +10232,16 @@
         <v>45188</v>
       </c>
       <c r="B491" t="n">
-        <v>111.9991912841797</v>
+        <v>111.9991836547852</v>
       </c>
       <c r="C491" t="n">
-        <v>115.957390144112</v>
+        <v>115.9573822450846</v>
       </c>
       <c r="D491" t="n">
-        <v>111.2705240431784</v>
+        <v>111.2705164634207</v>
       </c>
       <c r="E491" t="n">
-        <v>115.336683264999</v>
+        <v>115.3366754082542</v>
       </c>
       <c r="F491" t="n">
         <v>598810</v>
@@ -10272,16 +10272,16 @@
         <v>45190</v>
       </c>
       <c r="B493" t="n">
-        <v>104.118766784668</v>
+        <v>104.1187591552734</v>
       </c>
       <c r="C493" t="n">
-        <v>109.5343139805892</v>
+        <v>109.5343059543656</v>
       </c>
       <c r="D493" t="n">
-        <v>103.6509820066523</v>
+        <v>103.6509744115351</v>
       </c>
       <c r="E493" t="n">
-        <v>109.4353583204306</v>
+        <v>109.4353503014581</v>
       </c>
       <c r="F493" t="n">
         <v>1919322</v>
@@ -10332,16 +10332,16 @@
         <v>45195</v>
       </c>
       <c r="B496" t="n">
-        <v>101.554931640625</v>
+        <v>101.5549240112305</v>
       </c>
       <c r="C496" t="n">
-        <v>103.8129092891401</v>
+        <v>103.8129014901132</v>
       </c>
       <c r="D496" t="n">
-        <v>100.8622488797702</v>
+        <v>100.862241302414</v>
       </c>
       <c r="E496" t="n">
-        <v>101.6538873012245</v>
+        <v>101.6538796643958</v>
       </c>
       <c r="F496" t="n">
         <v>1664293</v>
@@ -10372,16 +10372,16 @@
         <v>45197</v>
       </c>
       <c r="B498" t="n">
-        <v>104.3526611328125</v>
+        <v>104.352668762207</v>
       </c>
       <c r="C498" t="n">
-        <v>104.3526611328125</v>
+        <v>104.352668762207</v>
       </c>
       <c r="D498" t="n">
-        <v>99.09904769432313</v>
+        <v>99.09905493961736</v>
       </c>
       <c r="E498" t="n">
-        <v>100.7542935075431</v>
+        <v>100.7543008738551</v>
       </c>
       <c r="F498" t="n">
         <v>896625</v>
@@ -10472,16 +10472,16 @@
         <v>45204</v>
       </c>
       <c r="B503" t="n">
-        <v>102.8683395385742</v>
+        <v>102.8683319091797</v>
       </c>
       <c r="C503" t="n">
-        <v>103.4170911847632</v>
+        <v>103.4170835146696</v>
       </c>
       <c r="D503" t="n">
-        <v>100.7542997993806</v>
+        <v>100.7542923267772</v>
       </c>
       <c r="E503" t="n">
-        <v>101.2490781240894</v>
+        <v>101.24907061479</v>
       </c>
       <c r="F503" t="n">
         <v>554198</v>
@@ -10612,16 +10612,16 @@
         <v>45216</v>
       </c>
       <c r="B510" t="n">
-        <v>97.14691925048828</v>
+        <v>97.14693450927734</v>
       </c>
       <c r="C510" t="n">
-        <v>97.86659545575409</v>
+        <v>97.86661082758212</v>
       </c>
       <c r="D510" t="n">
-        <v>95.20380447761612</v>
+        <v>95.20381943120169</v>
       </c>
       <c r="E510" t="n">
-        <v>96.69712333803238</v>
+        <v>96.69713852617237</v>
       </c>
       <c r="F510" t="n">
         <v>593712</v>
@@ -10632,16 +10632,16 @@
         <v>45217</v>
       </c>
       <c r="B511" t="n">
-        <v>93.6925048828125</v>
+        <v>93.69249725341797</v>
       </c>
       <c r="C511" t="n">
-        <v>96.61617878015257</v>
+        <v>96.61617091268285</v>
       </c>
       <c r="D511" t="n">
-        <v>92.67596156596765</v>
+        <v>92.6759540193504</v>
       </c>
       <c r="E511" t="n">
-        <v>96.61617878015257</v>
+        <v>96.61617091268285</v>
       </c>
       <c r="F511" t="n">
         <v>964239</v>
@@ -10672,16 +10672,16 @@
         <v>45219</v>
       </c>
       <c r="B513" t="n">
-        <v>96.25633239746094</v>
+        <v>96.25634002685547</v>
       </c>
       <c r="C513" t="n">
-        <v>96.43624803043737</v>
+        <v>96.43625567409222</v>
       </c>
       <c r="D513" t="n">
-        <v>93.0627784370684</v>
+        <v>93.06278581333794</v>
       </c>
       <c r="E513" t="n">
-        <v>93.27868543264987</v>
+        <v>93.27869282603245</v>
       </c>
       <c r="F513" t="n">
         <v>605848</v>
@@ -10692,16 +10692,16 @@
         <v>45222</v>
       </c>
       <c r="B514" t="n">
-        <v>96.25633239746094</v>
+        <v>96.25634002685547</v>
       </c>
       <c r="C514" t="n">
-        <v>97.29086444542904</v>
+        <v>97.29087215682185</v>
       </c>
       <c r="D514" t="n">
-        <v>93.93538367002114</v>
+        <v>93.93539111545444</v>
       </c>
       <c r="E514" t="n">
-        <v>96.07641676448451</v>
+        <v>96.0764243796187</v>
       </c>
       <c r="F514" t="n">
         <v>469364</v>
@@ -10712,16 +10712,16 @@
         <v>45223</v>
       </c>
       <c r="B515" t="n">
-        <v>93.5125732421875</v>
+        <v>93.51258087158203</v>
       </c>
       <c r="C515" t="n">
-        <v>98.39735742833496</v>
+        <v>98.39736545626356</v>
       </c>
       <c r="D515" t="n">
-        <v>93.38663092797195</v>
+        <v>93.38663854709125</v>
       </c>
       <c r="E515" t="n">
-        <v>96.71512500416665</v>
+        <v>96.71513289484724</v>
       </c>
       <c r="F515" t="n">
         <v>956700</v>
@@ -10732,16 +10732,16 @@
         <v>45224</v>
       </c>
       <c r="B516" t="n">
-        <v>89.44642639160156</v>
+        <v>89.44641876220703</v>
       </c>
       <c r="C516" t="n">
-        <v>92.42407350084858</v>
+        <v>92.42406561747359</v>
       </c>
       <c r="D516" t="n">
-        <v>87.28740437445002</v>
+        <v>87.28739692921076</v>
       </c>
       <c r="E516" t="n">
-        <v>92.42407350084858</v>
+        <v>92.42406561747359</v>
       </c>
       <c r="F516" t="n">
         <v>1619426</v>
@@ -10792,16 +10792,16 @@
         <v>45229</v>
       </c>
       <c r="B519" t="n">
-        <v>89.12256622314453</v>
+        <v>89.12257385253906</v>
       </c>
       <c r="C519" t="n">
-        <v>92.43306457692978</v>
+        <v>92.43307248972164</v>
       </c>
       <c r="D519" t="n">
-        <v>88.60979913214193</v>
+        <v>88.60980671764069</v>
       </c>
       <c r="E519" t="n">
-        <v>91.38054373697832</v>
+        <v>91.38055155966848</v>
       </c>
       <c r="F519" t="n">
         <v>688103</v>
@@ -10812,16 +10812,16 @@
         <v>45230</v>
       </c>
       <c r="B520" t="n">
-        <v>91.32656097412109</v>
+        <v>91.32656860351562</v>
       </c>
       <c r="C520" t="n">
-        <v>91.32656097412109</v>
+        <v>91.32656860351562</v>
       </c>
       <c r="D520" t="n">
-        <v>88.72674109428142</v>
+        <v>88.72674850648775</v>
       </c>
       <c r="E520" t="n">
-        <v>89.94119557423609</v>
+        <v>89.94120308789761</v>
       </c>
       <c r="F520" t="n">
         <v>382337</v>
@@ -10852,16 +10852,16 @@
         <v>45233</v>
       </c>
       <c r="B522" t="n">
-        <v>94.61007690429688</v>
+        <v>94.61008453369141</v>
       </c>
       <c r="C522" t="n">
-        <v>97.14692574562541</v>
+        <v>97.14693357959244</v>
       </c>
       <c r="D522" t="n">
-        <v>92.08222590355452</v>
+        <v>92.08223332910212</v>
       </c>
       <c r="E522" t="n">
-        <v>92.70294650051345</v>
+        <v>92.70295397611622</v>
       </c>
       <c r="F522" t="n">
         <v>760712</v>
@@ -10872,16 +10872,16 @@
         <v>45236</v>
       </c>
       <c r="B523" t="n">
-        <v>92.21717071533203</v>
+        <v>92.2171630859375</v>
       </c>
       <c r="C523" t="n">
-        <v>95.98645623697459</v>
+        <v>95.9864482957361</v>
       </c>
       <c r="D523" t="n">
-        <v>91.38954092314988</v>
+        <v>91.38953336222757</v>
       </c>
       <c r="E523" t="n">
-        <v>95.13184664835444</v>
+        <v>95.13183877782029</v>
       </c>
       <c r="F523" t="n">
         <v>393989</v>
@@ -10912,16 +10912,16 @@
         <v>45238</v>
       </c>
       <c r="B525" t="n">
-        <v>96.40926361083984</v>
+        <v>96.40925598144531</v>
       </c>
       <c r="C525" t="n">
-        <v>98.50531441406719</v>
+        <v>98.50530661880065</v>
       </c>
       <c r="D525" t="n">
-        <v>95.54565619848189</v>
+        <v>95.54564863742937</v>
       </c>
       <c r="E525" t="n">
-        <v>97.11094420442183</v>
+        <v>97.11093651949946</v>
       </c>
       <c r="F525" t="n">
         <v>449324</v>
@@ -10972,16 +10972,16 @@
         <v>45243</v>
       </c>
       <c r="B528" t="n">
-        <v>98.83815765380859</v>
+        <v>98.83816528320312</v>
       </c>
       <c r="C528" t="n">
-        <v>100.3134877181948</v>
+        <v>100.3134954614712</v>
       </c>
       <c r="D528" t="n">
-        <v>96.80507817938725</v>
+        <v>96.80508565184681</v>
       </c>
       <c r="E528" t="n">
-        <v>98.95510212187712</v>
+        <v>98.9551097602987</v>
       </c>
       <c r="F528" t="n">
         <v>702632</v>
@@ -10992,16 +10992,16 @@
         <v>45244</v>
       </c>
       <c r="B529" t="n">
-        <v>97.60572814941406</v>
+        <v>97.60572052001953</v>
       </c>
       <c r="C529" t="n">
-        <v>106.6286344553219</v>
+        <v>106.628626120648</v>
       </c>
       <c r="D529" t="n">
-        <v>97.06597434337603</v>
+        <v>97.06596675617159</v>
       </c>
       <c r="E529" t="n">
-        <v>99.73776357610761</v>
+        <v>99.7377557800616</v>
       </c>
       <c r="F529" t="n">
         <v>2031591</v>
@@ -11052,16 +11052,16 @@
         <v>45250</v>
       </c>
       <c r="B532" t="n">
-        <v>102.5534820556641</v>
+        <v>102.5534744262695</v>
       </c>
       <c r="C532" t="n">
-        <v>104.5685660971273</v>
+        <v>104.5685583178221</v>
       </c>
       <c r="D532" t="n">
-        <v>100.9881939881291</v>
+        <v>100.9881864751831</v>
       </c>
       <c r="E532" t="n">
-        <v>103.6329896477554</v>
+        <v>103.6329819380516</v>
       </c>
       <c r="F532" t="n">
         <v>946377</v>
@@ -11072,16 +11072,16 @@
         <v>45251</v>
       </c>
       <c r="B533" t="n">
-        <v>100.259521484375</v>
+        <v>100.2595138549805</v>
       </c>
       <c r="C533" t="n">
-        <v>103.0932375391752</v>
+        <v>103.0932296941449</v>
       </c>
       <c r="D533" t="n">
-        <v>99.13503153114809</v>
+        <v>99.13502398732325</v>
       </c>
       <c r="E533" t="n">
-        <v>102.5804703950374</v>
+        <v>102.5804625890269</v>
       </c>
       <c r="F533" t="n">
         <v>1091156</v>
@@ -11112,16 +11112,16 @@
         <v>45253</v>
       </c>
       <c r="B535" t="n">
-        <v>103.4440689086914</v>
+        <v>103.4440765380859</v>
       </c>
       <c r="C535" t="n">
-        <v>104.5955454230704</v>
+        <v>104.5955531373908</v>
       </c>
       <c r="D535" t="n">
-        <v>101.9327542677336</v>
+        <v>101.9327617856629</v>
       </c>
       <c r="E535" t="n">
-        <v>102.8683306515019</v>
+        <v>102.8683382384335</v>
       </c>
       <c r="F535" t="n">
         <v>270469</v>
@@ -11132,16 +11132,16 @@
         <v>45254</v>
       </c>
       <c r="B536" t="n">
-        <v>103.5430145263672</v>
+        <v>103.5430221557617</v>
       </c>
       <c r="C536" t="n">
-        <v>104.3526485168384</v>
+        <v>104.3526562058894</v>
       </c>
       <c r="D536" t="n">
-        <v>100.9521926202001</v>
+        <v>100.9522000586942</v>
       </c>
       <c r="E536" t="n">
-        <v>103.2731411051039</v>
+        <v>103.2731487146133</v>
       </c>
       <c r="F536" t="n">
         <v>447021</v>
@@ -11212,16 +11212,16 @@
         <v>45260</v>
       </c>
       <c r="B540" t="n">
-        <v>103.2731552124023</v>
+        <v>103.2731475830078</v>
       </c>
       <c r="C540" t="n">
-        <v>103.5250398519922</v>
+        <v>103.5250322039895</v>
       </c>
       <c r="D540" t="n">
-        <v>101.2310777095213</v>
+        <v>101.231070230987</v>
       </c>
       <c r="E540" t="n">
-        <v>102.643436750086</v>
+        <v>102.6434291672124</v>
       </c>
       <c r="F540" t="n">
         <v>702061</v>
@@ -11232,16 +11232,16 @@
         <v>45261</v>
       </c>
       <c r="B541" t="n">
-        <v>105.3062210083008</v>
+        <v>105.3062286376953</v>
       </c>
       <c r="C541" t="n">
-        <v>105.9179437480583</v>
+        <v>105.9179514217719</v>
       </c>
       <c r="D541" t="n">
-        <v>102.004720527015</v>
+        <v>102.0047279172171</v>
       </c>
       <c r="E541" t="n">
-        <v>103.2731483448977</v>
+        <v>103.2731558269969</v>
       </c>
       <c r="F541" t="n">
         <v>1785577</v>
@@ -11272,16 +11272,16 @@
         <v>45265</v>
       </c>
       <c r="B543" t="n">
-        <v>106.1338577270508</v>
+        <v>106.1338500976562</v>
       </c>
       <c r="C543" t="n">
-        <v>107.825088065618</v>
+        <v>107.82508031465</v>
       </c>
       <c r="D543" t="n">
-        <v>103.021263644533</v>
+        <v>103.0212562388862</v>
       </c>
       <c r="E543" t="n">
-        <v>103.426084126483</v>
+        <v>103.4260766917358</v>
       </c>
       <c r="F543" t="n">
         <v>1056803</v>
@@ -11312,16 +11312,16 @@
         <v>45267</v>
       </c>
       <c r="B545" t="n">
-        <v>106.6016464233398</v>
+        <v>106.6016387939453</v>
       </c>
       <c r="C545" t="n">
-        <v>107.0514423998096</v>
+        <v>107.0514347382236</v>
       </c>
       <c r="D545" t="n">
-        <v>103.6959613954746</v>
+        <v>103.6959539740376</v>
       </c>
       <c r="E545" t="n">
-        <v>105.4231831612584</v>
+        <v>105.4231756162056</v>
       </c>
       <c r="F545" t="n">
         <v>599154</v>
@@ -11332,16 +11332,16 @@
         <v>45268</v>
       </c>
       <c r="B546" t="n">
-        <v>105.4321594238281</v>
+        <v>105.4321670532227</v>
       </c>
       <c r="C546" t="n">
-        <v>108.7156709664404</v>
+        <v>108.7156788334399</v>
       </c>
       <c r="D546" t="n">
-        <v>105.2522438036881</v>
+        <v>105.2522514200634</v>
       </c>
       <c r="E546" t="n">
-        <v>106.961469648382</v>
+        <v>106.9614773884421</v>
       </c>
       <c r="F546" t="n">
         <v>678575</v>
@@ -11352,16 +11352,16 @@
         <v>45271</v>
       </c>
       <c r="B547" t="n">
-        <v>103.1921920776367</v>
+        <v>103.1921844482422</v>
       </c>
       <c r="C547" t="n">
-        <v>106.4127329157239</v>
+        <v>106.4127250482224</v>
       </c>
       <c r="D547" t="n">
-        <v>103.1921920776367</v>
+        <v>103.1921844482422</v>
       </c>
       <c r="E547" t="n">
-        <v>105.3782007973801</v>
+        <v>105.3781930063656</v>
       </c>
       <c r="F547" t="n">
         <v>558243</v>
@@ -11452,16 +11452,16 @@
         <v>45278</v>
       </c>
       <c r="B552" t="n">
-        <v>118.341552734375</v>
+        <v>118.3415603637695</v>
       </c>
       <c r="C552" t="n">
-        <v>120.6714417856362</v>
+        <v>120.671449565237</v>
       </c>
       <c r="D552" t="n">
-        <v>114.5543313282876</v>
+        <v>114.5543387135227</v>
       </c>
       <c r="E552" t="n">
-        <v>114.8049535144115</v>
+        <v>114.804960915804</v>
       </c>
       <c r="F552" t="n">
         <v>1013443</v>
@@ -11472,16 +11472,16 @@
         <v>45279</v>
       </c>
       <c r="B553" t="n">
-        <v>120.4950790405273</v>
+        <v>120.4950714111328</v>
       </c>
       <c r="C553" t="n">
-        <v>122.0638101212287</v>
+        <v>122.0638023925067</v>
       </c>
       <c r="D553" t="n">
-        <v>117.4226006109158</v>
+        <v>117.4225931760616</v>
       </c>
       <c r="E553" t="n">
-        <v>118.1187820374627</v>
+        <v>118.1187745585284</v>
       </c>
       <c r="F553" t="n">
         <v>921758</v>
@@ -11612,16 +11612,16 @@
         <v>45293</v>
       </c>
       <c r="B560" t="n">
-        <v>116.4015350341797</v>
+        <v>116.4015274047852</v>
       </c>
       <c r="C560" t="n">
-        <v>119.000608090686</v>
+        <v>119.0006002909384</v>
       </c>
       <c r="D560" t="n">
-        <v>115.1948177380679</v>
+        <v>115.1948101877661</v>
       </c>
       <c r="E560" t="n">
-        <v>119.000608090686</v>
+        <v>119.0006002909384</v>
       </c>
       <c r="F560" t="n">
         <v>900041</v>
@@ -11632,16 +11632,16 @@
         <v>45294</v>
       </c>
       <c r="B561" t="n">
-        <v>113.2455062866211</v>
+        <v>113.2455139160156</v>
       </c>
       <c r="C561" t="n">
-        <v>116.2437305936984</v>
+        <v>116.2437384250845</v>
       </c>
       <c r="D561" t="n">
-        <v>113.2455062866211</v>
+        <v>113.2455139160156</v>
       </c>
       <c r="E561" t="n">
-        <v>115.7517564618344</v>
+        <v>115.7517642600759</v>
       </c>
       <c r="F561" t="n">
         <v>798887</v>
@@ -11672,16 +11672,16 @@
         <v>45296</v>
       </c>
       <c r="B563" t="n">
-        <v>115.6310882568359</v>
+        <v>115.6310958862305</v>
       </c>
       <c r="C563" t="n">
-        <v>115.6310882568359</v>
+        <v>115.6310958862305</v>
       </c>
       <c r="D563" t="n">
-        <v>109.7181850571025</v>
+        <v>109.7181922963609</v>
       </c>
       <c r="E563" t="n">
-        <v>110.1823059872627</v>
+        <v>110.182313257144</v>
       </c>
       <c r="F563" t="n">
         <v>1732820</v>
@@ -11712,16 +11712,16 @@
         <v>45300</v>
       </c>
       <c r="B565" t="n">
-        <v>114.0345153808594</v>
+        <v>114.0345077514648</v>
       </c>
       <c r="C565" t="n">
-        <v>117.7938978882632</v>
+        <v>117.79389000735</v>
       </c>
       <c r="D565" t="n">
-        <v>113.3847488871488</v>
+        <v>113.3847413012264</v>
       </c>
       <c r="E565" t="n">
-        <v>117.7938978882632</v>
+        <v>117.79389000735</v>
       </c>
       <c r="F565" t="n">
         <v>842892</v>
@@ -11772,16 +11772,16 @@
         <v>45303</v>
       </c>
       <c r="B568" t="n">
-        <v>116.6800003051758</v>
+        <v>116.6800079345703</v>
       </c>
       <c r="C568" t="n">
-        <v>117.7010720284054</v>
+        <v>117.7010797245651</v>
       </c>
       <c r="D568" t="n">
-        <v>112.8649256503406</v>
+        <v>112.8649330302776</v>
       </c>
       <c r="E568" t="n">
-        <v>114.6378710225635</v>
+        <v>114.6378785184286</v>
       </c>
       <c r="F568" t="n">
         <v>693991</v>
@@ -11792,16 +11792,16 @@
         <v>45306</v>
       </c>
       <c r="B569" t="n">
-        <v>118.2580261230469</v>
+        <v>118.2580184936523</v>
       </c>
       <c r="C569" t="n">
-        <v>120.5786239215518</v>
+        <v>120.5786161424443</v>
       </c>
       <c r="D569" t="n">
-        <v>115.6589458241968</v>
+        <v>115.6589383624814</v>
       </c>
       <c r="E569" t="n">
-        <v>116.6707332346643</v>
+        <v>116.6707257076737</v>
       </c>
       <c r="F569" t="n">
         <v>875695</v>
@@ -11892,16 +11892,16 @@
         <v>45313</v>
       </c>
       <c r="B574" t="n">
-        <v>116.9677658081055</v>
+        <v>116.9677581787109</v>
       </c>
       <c r="C574" t="n">
-        <v>118.313713753421</v>
+        <v>118.313706036235</v>
       </c>
       <c r="D574" t="n">
-        <v>114.8792214972839</v>
+        <v>114.8792140041177</v>
       </c>
       <c r="E574" t="n">
-        <v>115.7332023602692</v>
+        <v>115.7331948114009</v>
       </c>
       <c r="F574" t="n">
         <v>856226</v>
@@ -11912,16 +11912,16 @@
         <v>45314</v>
       </c>
       <c r="B575" t="n">
-        <v>115.8445816040039</v>
+        <v>115.8445892333984</v>
       </c>
       <c r="C575" t="n">
-        <v>119.5111339486896</v>
+        <v>119.5111418195592</v>
       </c>
       <c r="D575" t="n">
-        <v>115.3526074921376</v>
+        <v>115.3526150891313</v>
       </c>
       <c r="E575" t="n">
-        <v>117.0605761181597</v>
+        <v>117.0605838276382</v>
       </c>
       <c r="F575" t="n">
         <v>383026</v>
@@ -11972,16 +11972,16 @@
         <v>45317</v>
       </c>
       <c r="B578" t="n">
-        <v>116.6614379882812</v>
+        <v>116.6614456176758</v>
       </c>
       <c r="C578" t="n">
-        <v>119.0841427428836</v>
+        <v>119.0841505307175</v>
       </c>
       <c r="D578" t="n">
-        <v>113.3383304087349</v>
+        <v>113.3383378208057</v>
       </c>
       <c r="E578" t="n">
-        <v>113.6817824486065</v>
+        <v>113.6817898831383</v>
       </c>
       <c r="F578" t="n">
         <v>753916</v>
@@ -12032,16 +12032,16 @@
         <v>45322</v>
       </c>
       <c r="B581" t="n">
-        <v>112.7256927490234</v>
+        <v>112.725700378418</v>
       </c>
       <c r="C581" t="n">
-        <v>117.5618319470799</v>
+        <v>117.5618399037895</v>
       </c>
       <c r="D581" t="n">
-        <v>112.252287421666</v>
+        <v>112.25229501902</v>
       </c>
       <c r="E581" t="n">
-        <v>115.1205513444103</v>
+        <v>115.1205591358914</v>
       </c>
       <c r="F581" t="n">
         <v>967870</v>
@@ -12072,16 +12072,16 @@
         <v>45324</v>
       </c>
       <c r="B583" t="n">
-        <v>119.7431945800781</v>
+        <v>119.7432022094727</v>
       </c>
       <c r="C583" t="n">
-        <v>120.7642662459118</v>
+        <v>120.7642739403636</v>
       </c>
       <c r="D583" t="n">
-        <v>114.2758508359602</v>
+        <v>114.2758581170049</v>
       </c>
       <c r="E583" t="n">
-        <v>114.7492561463083</v>
+        <v>114.7492634575158</v>
       </c>
       <c r="F583" t="n">
         <v>1061152</v>
@@ -12132,16 +12132,16 @@
         <v>45329</v>
       </c>
       <c r="B586" t="n">
-        <v>114.9070587158203</v>
+        <v>114.9070663452148</v>
       </c>
       <c r="C586" t="n">
-        <v>116.3179832026201</v>
+        <v>116.3179909256947</v>
       </c>
       <c r="D586" t="n">
-        <v>111.8160116757133</v>
+        <v>111.816019099874</v>
       </c>
       <c r="E586" t="n">
-        <v>115.1019886532248</v>
+        <v>115.101996295562</v>
       </c>
       <c r="F586" t="n">
         <v>998662</v>
@@ -12192,16 +12192,16 @@
         <v>45336</v>
       </c>
       <c r="B589" t="n">
-        <v>115.5289840698242</v>
+        <v>115.5289916992188</v>
       </c>
       <c r="C589" t="n">
-        <v>116.3644031820766</v>
+        <v>116.3644108666412</v>
       </c>
       <c r="D589" t="n">
-        <v>114.8699331818039</v>
+        <v>114.8699407676755</v>
       </c>
       <c r="E589" t="n">
-        <v>115.055578725894</v>
+        <v>115.0555863240254</v>
       </c>
       <c r="F589" t="n">
         <v>421454</v>
@@ -12212,16 +12212,16 @@
         <v>45337</v>
       </c>
       <c r="B590" t="n">
-        <v>115.7517623901367</v>
+        <v>115.7517547607422</v>
       </c>
       <c r="C590" t="n">
-        <v>116.4015359709352</v>
+        <v>116.4015282987129</v>
       </c>
       <c r="D590" t="n">
-        <v>114.4986372383505</v>
+        <v>114.4986296915515</v>
       </c>
       <c r="E590" t="n">
-        <v>115.6589396162866</v>
+        <v>115.6589319930101</v>
       </c>
       <c r="F590" t="n">
         <v>464925</v>
@@ -12272,16 +12272,16 @@
         <v>45342</v>
       </c>
       <c r="B593" t="n">
-        <v>114.7306976318359</v>
+        <v>114.7306900024414</v>
       </c>
       <c r="C593" t="n">
-        <v>116.0302377105792</v>
+        <v>116.0302299947675</v>
       </c>
       <c r="D593" t="n">
-        <v>113.338334779309</v>
+        <v>113.3383272425042</v>
       </c>
       <c r="E593" t="n">
-        <v>113.4218802330609</v>
+        <v>113.4218726907005</v>
       </c>
       <c r="F593" t="n">
         <v>900047</v>
@@ -12332,16 +12332,16 @@
         <v>45345</v>
       </c>
       <c r="B596" t="n">
-        <v>111.5561065673828</v>
+        <v>111.5561141967773</v>
       </c>
       <c r="C596" t="n">
-        <v>114.0437950254093</v>
+        <v>114.0438028249385</v>
       </c>
       <c r="D596" t="n">
-        <v>111.5561065673828</v>
+        <v>111.5561141967773</v>
       </c>
       <c r="E596" t="n">
-        <v>113.3476136332219</v>
+        <v>113.3476213851388</v>
       </c>
       <c r="F596" t="n">
         <v>783111</v>
@@ -12352,16 +12352,16 @@
         <v>45348</v>
       </c>
       <c r="B597" t="n">
-        <v>111.2776260375977</v>
+        <v>111.2776336669922</v>
       </c>
       <c r="C597" t="n">
-        <v>113.0227251791686</v>
+        <v>113.0227329282103</v>
       </c>
       <c r="D597" t="n">
-        <v>110.5164680339092</v>
+        <v>110.5164756111173</v>
       </c>
       <c r="E597" t="n">
-        <v>111.6674929814756</v>
+        <v>111.6675006376001</v>
       </c>
       <c r="F597" t="n">
         <v>306480</v>
@@ -12372,16 +12372,16 @@
         <v>45349</v>
       </c>
       <c r="B598" t="n">
-        <v>112.976318359375</v>
+        <v>112.9763259887695</v>
       </c>
       <c r="C598" t="n">
-        <v>113.941690764358</v>
+        <v>113.941698458945</v>
       </c>
       <c r="D598" t="n">
-        <v>107.7039041979591</v>
+        <v>107.7039114713027</v>
       </c>
       <c r="E598" t="n">
-        <v>111.8717082560142</v>
+        <v>111.8717158108134</v>
       </c>
       <c r="F598" t="n">
         <v>631455</v>
@@ -12392,16 +12392,16 @@
         <v>45350</v>
       </c>
       <c r="B599" t="n">
-        <v>110.507194519043</v>
+        <v>110.5072021484375</v>
       </c>
       <c r="C599" t="n">
-        <v>112.8556452546146</v>
+        <v>112.8556530461457</v>
       </c>
       <c r="D599" t="n">
-        <v>103.0348448313849</v>
+        <v>103.03485194489</v>
       </c>
       <c r="E599" t="n">
-        <v>112.8556452546146</v>
+        <v>112.8556530461457</v>
       </c>
       <c r="F599" t="n">
         <v>1284448</v>
@@ -12552,16 +12552,16 @@
         <v>45362</v>
       </c>
       <c r="B607" t="n">
-        <v>116.9120559692383</v>
+        <v>116.9120635986328</v>
       </c>
       <c r="C607" t="n">
-        <v>117.9052744467247</v>
+        <v>117.9052821409343</v>
       </c>
       <c r="D607" t="n">
-        <v>116.1044901074035</v>
+        <v>116.1044976840983</v>
       </c>
       <c r="E607" t="n">
-        <v>116.1230518280071</v>
+        <v>116.1230594059132</v>
       </c>
       <c r="F607" t="n">
         <v>387232</v>
@@ -12652,16 +12652,16 @@
         <v>45369</v>
       </c>
       <c r="B612" t="n">
-        <v>117.8867263793945</v>
+        <v>117.88671875</v>
       </c>
       <c r="C612" t="n">
-        <v>119.5946881496622</v>
+        <v>119.5946804097318</v>
       </c>
       <c r="D612" t="n">
-        <v>116.3644101643563</v>
+        <v>116.364402633483</v>
       </c>
       <c r="E612" t="n">
-        <v>118.8799520538364</v>
+        <v>118.8799443601623</v>
       </c>
       <c r="F612" t="n">
         <v>649560</v>
@@ -12792,16 +12792,16 @@
         <v>45378</v>
       </c>
       <c r="B619" t="n">
-        <v>116.8099594116211</v>
+        <v>116.8099517822266</v>
       </c>
       <c r="C619" t="n">
-        <v>118.6571659250514</v>
+        <v>118.6571581750073</v>
       </c>
       <c r="D619" t="n">
-        <v>116.7821132872247</v>
+        <v>116.7821056596489</v>
       </c>
       <c r="E619" t="n">
-        <v>116.9399197953439</v>
+        <v>116.9399121574611</v>
       </c>
       <c r="F619" t="n">
         <v>350637</v>
@@ -12812,16 +12812,16 @@
         <v>45379</v>
       </c>
       <c r="B620" t="n">
-        <v>118.9077835083008</v>
+        <v>118.9077911376953</v>
       </c>
       <c r="C620" t="n">
-        <v>120.5693301438005</v>
+        <v>120.5693378798037</v>
       </c>
       <c r="D620" t="n">
-        <v>116.5964562638948</v>
+        <v>116.5964637449893</v>
       </c>
       <c r="E620" t="n">
-        <v>117.0698615778232</v>
+        <v>117.0698690892924</v>
       </c>
       <c r="F620" t="n">
         <v>712173</v>
@@ -12892,16 +12892,16 @@
         <v>45386</v>
       </c>
       <c r="B624" t="n">
-        <v>117.4225921630859</v>
+        <v>117.4225997924805</v>
       </c>
       <c r="C624" t="n">
-        <v>118.7963931953485</v>
+        <v>118.7964009140041</v>
       </c>
       <c r="D624" t="n">
-        <v>116.104490456648</v>
+        <v>116.1044980004005</v>
       </c>
       <c r="E624" t="n">
-        <v>117.5525454534715</v>
+        <v>117.5525530913096</v>
       </c>
       <c r="F624" t="n">
         <v>491773</v>
@@ -12932,16 +12932,16 @@
         <v>45390</v>
       </c>
       <c r="B626" t="n">
-        <v>116.2251663208008</v>
+        <v>116.2251586914062</v>
       </c>
       <c r="C626" t="n">
-        <v>117.2926459118219</v>
+        <v>117.2926382123546</v>
       </c>
       <c r="D626" t="n">
-        <v>115.334054955283</v>
+        <v>115.3340473843839</v>
       </c>
       <c r="E626" t="n">
-        <v>116.2158819189523</v>
+        <v>116.2158742901672</v>
       </c>
       <c r="F626" t="n">
         <v>333012</v>
@@ -12992,16 +12992,16 @@
         <v>45393</v>
       </c>
       <c r="B629" t="n">
-        <v>113.9509811401367</v>
+        <v>113.9509735107422</v>
       </c>
       <c r="C629" t="n">
-        <v>114.4522326314215</v>
+        <v>114.4522249684666</v>
       </c>
       <c r="D629" t="n">
-        <v>112.3915344167808</v>
+        <v>112.3915268917964</v>
       </c>
       <c r="E629" t="n">
-        <v>114.025235112164</v>
+        <v>114.025227477798</v>
       </c>
       <c r="F629" t="n">
         <v>445667</v>
@@ -13052,16 +13052,16 @@
         <v>45398</v>
       </c>
       <c r="B632" t="n">
-        <v>104.48291015625</v>
+        <v>104.4829025268555</v>
       </c>
       <c r="C632" t="n">
-        <v>108.7713904544259</v>
+        <v>108.7713825118844</v>
       </c>
       <c r="D632" t="n">
-        <v>104.48291015625</v>
+        <v>104.4829025268555</v>
       </c>
       <c r="E632" t="n">
-        <v>107.5832419082449</v>
+        <v>107.5832340524626</v>
       </c>
       <c r="F632" t="n">
         <v>811680</v>
@@ -13092,16 +13092,16 @@
         <v>45400</v>
       </c>
       <c r="B634" t="n">
-        <v>102.4036483764648</v>
+        <v>102.4036407470703</v>
       </c>
       <c r="C634" t="n">
-        <v>105.3647423687916</v>
+        <v>105.3647345187862</v>
       </c>
       <c r="D634" t="n">
-        <v>102.0509189962012</v>
+        <v>102.0509113930862</v>
       </c>
       <c r="E634" t="n">
-        <v>103.7867268549386</v>
+        <v>103.7867191225003</v>
       </c>
       <c r="F634" t="n">
         <v>749923</v>
@@ -13132,16 +13132,16 @@
         <v>45404</v>
       </c>
       <c r="B636" t="n">
-        <v>100.9462966918945</v>
+        <v>100.9463043212891</v>
       </c>
       <c r="C636" t="n">
-        <v>102.5243049338492</v>
+        <v>102.5243126825076</v>
       </c>
       <c r="D636" t="n">
-        <v>100.4357608643617</v>
+        <v>100.4357684551706</v>
       </c>
       <c r="E636" t="n">
-        <v>101.1783571440598</v>
+        <v>101.1783647909932</v>
       </c>
       <c r="F636" t="n">
         <v>363945</v>
@@ -13232,16 +13232,16 @@
         <v>45412</v>
       </c>
       <c r="B641" t="n">
-        <v>98.4678955078125</v>
+        <v>98.46790313720703</v>
       </c>
       <c r="C641" t="n">
-        <v>100.4821785891058</v>
+        <v>100.482186374569</v>
       </c>
       <c r="D641" t="n">
-        <v>96.76921125094019</v>
+        <v>96.7692187487189</v>
       </c>
       <c r="E641" t="n">
-        <v>99.31259189464512</v>
+        <v>99.3125995894876</v>
       </c>
       <c r="F641" t="n">
         <v>1108924</v>
@@ -13292,16 +13292,16 @@
         <v>45418</v>
       </c>
       <c r="B644" t="n">
-        <v>105.7267532348633</v>
+        <v>105.7267456054688</v>
       </c>
       <c r="C644" t="n">
-        <v>107.1655239226594</v>
+        <v>107.1655161894411</v>
       </c>
       <c r="D644" t="n">
-        <v>105.2255017618369</v>
+        <v>105.2254941686134</v>
       </c>
       <c r="E644" t="n">
-        <v>105.8195760079592</v>
+        <v>105.8195683718665</v>
       </c>
       <c r="F644" t="n">
         <v>262476</v>
@@ -13332,16 +13332,16 @@
         <v>45420</v>
       </c>
       <c r="B646" t="n">
-        <v>105.9495239257812</v>
+        <v>105.9495315551758</v>
       </c>
       <c r="C646" t="n">
-        <v>105.9959388509337</v>
+        <v>105.9959464836706</v>
       </c>
       <c r="D646" t="n">
-        <v>102.301533181186</v>
+        <v>102.3015405478897</v>
       </c>
       <c r="E646" t="n">
-        <v>103.6846115512664</v>
+        <v>103.6846190175652</v>
       </c>
       <c r="F646" t="n">
         <v>426813</v>
@@ -13352,16 +13352,16 @@
         <v>45421</v>
       </c>
       <c r="B647" t="n">
-        <v>102.5428848266602</v>
+        <v>102.5428771972656</v>
       </c>
       <c r="C647" t="n">
-        <v>105.9402465312093</v>
+        <v>105.9402386490443</v>
       </c>
       <c r="D647" t="n">
-        <v>101.9395261693882</v>
+        <v>101.9395185848848</v>
       </c>
       <c r="E647" t="n">
-        <v>105.9402465312093</v>
+        <v>105.9402386490443</v>
       </c>
       <c r="F647" t="n">
         <v>474171</v>
@@ -13392,16 +13392,16 @@
         <v>45425</v>
       </c>
       <c r="B649" t="n">
-        <v>103.5732345581055</v>
+        <v>103.5732269287109</v>
       </c>
       <c r="C649" t="n">
-        <v>105.0955507318979</v>
+        <v>105.0955429903668</v>
       </c>
       <c r="D649" t="n">
-        <v>102.8027920691221</v>
+        <v>102.8027844964798</v>
       </c>
       <c r="E649" t="n">
-        <v>102.8027920691221</v>
+        <v>102.8027844964798</v>
       </c>
       <c r="F649" t="n">
         <v>135742</v>
@@ -13452,16 +13452,16 @@
         <v>45428</v>
       </c>
       <c r="B652" t="n">
-        <v>104.6407012939453</v>
+        <v>104.6407165527344</v>
       </c>
       <c r="C652" t="n">
-        <v>104.9377383868498</v>
+        <v>104.937753688953</v>
       </c>
       <c r="D652" t="n">
-        <v>103.322592554879</v>
+        <v>103.3226076214604</v>
       </c>
       <c r="E652" t="n">
-        <v>104.1487271908296</v>
+        <v>104.1487423778786</v>
       </c>
       <c r="F652" t="n">
         <v>283646</v>
@@ -13492,16 +13492,16 @@
         <v>45432</v>
       </c>
       <c r="B654" t="n">
-        <v>102.5243072509766</v>
+        <v>102.5243148803711</v>
       </c>
       <c r="C654" t="n">
-        <v>103.3504419128024</v>
+        <v>103.3504496036741</v>
       </c>
       <c r="D654" t="n">
-        <v>101.2340516743307</v>
+        <v>101.2340592077103</v>
       </c>
       <c r="E654" t="n">
-        <v>103.0162813695012</v>
+        <v>103.0162890355063</v>
       </c>
       <c r="F654" t="n">
         <v>409635</v>
@@ -13552,16 +13552,16 @@
         <v>45435</v>
       </c>
       <c r="B657" t="n">
-        <v>88.36862182617188</v>
+        <v>88.36862945556641</v>
       </c>
       <c r="C657" t="n">
-        <v>90.96770185479242</v>
+        <v>90.96770970858115</v>
       </c>
       <c r="D657" t="n">
-        <v>87.70957095848325</v>
+        <v>87.70957853097796</v>
       </c>
       <c r="E657" t="n">
-        <v>88.18297628780898</v>
+        <v>88.18298390117562</v>
       </c>
       <c r="F657" t="n">
         <v>1960163</v>
@@ -13592,16 +13592,16 @@
         <v>45439</v>
       </c>
       <c r="B659" t="n">
-        <v>90.40147399902344</v>
+        <v>90.40148162841797</v>
       </c>
       <c r="C659" t="n">
-        <v>90.78205656018962</v>
+        <v>90.78206422170325</v>
       </c>
       <c r="D659" t="n">
-        <v>89.20404115217451</v>
+        <v>89.2040486805122</v>
       </c>
       <c r="E659" t="n">
-        <v>90.08587516657443</v>
+        <v>90.08588276933413</v>
       </c>
       <c r="F659" t="n">
         <v>176378</v>
@@ -13632,16 +13632,16 @@
         <v>45441</v>
       </c>
       <c r="B661" t="n">
-        <v>88.13656616210938</v>
+        <v>88.13655853271484</v>
       </c>
       <c r="C661" t="n">
-        <v>90.68923140419381</v>
+        <v>90.68922355383208</v>
       </c>
       <c r="D661" t="n">
-        <v>87.62603736284672</v>
+        <v>87.62602977764526</v>
       </c>
       <c r="E661" t="n">
-        <v>90.68923140419381</v>
+        <v>90.68922355383208</v>
       </c>
       <c r="F661" t="n">
         <v>430434</v>
@@ -13672,16 +13672,16 @@
         <v>45446</v>
       </c>
       <c r="B663" t="n">
-        <v>92.43431854248047</v>
+        <v>92.43433380126953</v>
       </c>
       <c r="C663" t="n">
-        <v>93.60389809123609</v>
+        <v>93.60391354309594</v>
       </c>
       <c r="D663" t="n">
-        <v>90.53142005267401</v>
+        <v>90.53143499733811</v>
       </c>
       <c r="E663" t="n">
-        <v>92.64781018690546</v>
+        <v>92.6478254809371</v>
       </c>
       <c r="F663" t="n">
         <v>373105</v>
@@ -13692,16 +13692,16 @@
         <v>45447</v>
       </c>
       <c r="B664" t="n">
-        <v>93.03768920898438</v>
+        <v>93.03768157958984</v>
       </c>
       <c r="C664" t="n">
-        <v>94.17013838371813</v>
+        <v>94.17013066145907</v>
       </c>
       <c r="D664" t="n">
-        <v>92.17442395447692</v>
+        <v>92.17441639587297</v>
       </c>
       <c r="E664" t="n">
-        <v>92.18370127453734</v>
+        <v>92.18369371517262</v>
       </c>
       <c r="F664" t="n">
         <v>382317</v>
@@ -13712,16 +13712,16 @@
         <v>45448</v>
       </c>
       <c r="B665" t="n">
-        <v>92.92630004882812</v>
+        <v>92.92629241943359</v>
       </c>
       <c r="C665" t="n">
-        <v>93.79884972802287</v>
+        <v>93.79884202699066</v>
       </c>
       <c r="D665" t="n">
-        <v>92.39720243274542</v>
+        <v>92.39719484679063</v>
       </c>
       <c r="E665" t="n">
-        <v>93.18620665575664</v>
+        <v>93.18619900502337</v>
       </c>
       <c r="F665" t="n">
         <v>402887</v>
@@ -13772,16 +13772,16 @@
         <v>45453</v>
       </c>
       <c r="B668" t="n">
-        <v>92.53643798828125</v>
+        <v>92.53644561767578</v>
       </c>
       <c r="C668" t="n">
-        <v>93.24189673871706</v>
+        <v>93.24190442627489</v>
       </c>
       <c r="D668" t="n">
-        <v>90.78206135035421</v>
+        <v>90.78206883510484</v>
       </c>
       <c r="E668" t="n">
-        <v>92.0351865085987</v>
+        <v>92.03519409666633</v>
       </c>
       <c r="F668" t="n">
         <v>279796</v>
@@ -13892,16 +13892,16 @@
         <v>45461</v>
       </c>
       <c r="B674" t="n">
-        <v>87.54248046875</v>
+        <v>87.54248809814453</v>
       </c>
       <c r="C674" t="n">
-        <v>87.54248046875</v>
+        <v>87.54248809814453</v>
       </c>
       <c r="D674" t="n">
-        <v>84.9712538405923</v>
+        <v>84.97126124590245</v>
       </c>
       <c r="E674" t="n">
-        <v>85.57461241716906</v>
+        <v>85.57461987506238</v>
       </c>
       <c r="F674" t="n">
         <v>348422</v>
@@ -13952,16 +13952,16 @@
         <v>45464</v>
       </c>
       <c r="B677" t="n">
-        <v>88.75849151611328</v>
+        <v>88.75848388671875</v>
       </c>
       <c r="C677" t="n">
-        <v>91.33900282106455</v>
+        <v>91.33899496985757</v>
       </c>
       <c r="D677" t="n">
-        <v>86.98554611797962</v>
+        <v>86.98553864098177</v>
       </c>
       <c r="E677" t="n">
-        <v>91.33900282106455</v>
+        <v>91.33899496985757</v>
       </c>
       <c r="F677" t="n">
         <v>813524</v>
@@ -13972,16 +13972,16 @@
         <v>45467</v>
       </c>
       <c r="B678" t="n">
-        <v>89.74241638183594</v>
+        <v>89.74242401123047</v>
       </c>
       <c r="C678" t="n">
-        <v>90.60568152828682</v>
+        <v>90.6056892310713</v>
       </c>
       <c r="D678" t="n">
-        <v>88.23866213520195</v>
+        <v>88.23866963675577</v>
       </c>
       <c r="E678" t="n">
-        <v>88.92556615757213</v>
+        <v>88.92557371752265</v>
       </c>
       <c r="F678" t="n">
         <v>235914</v>
@@ -13992,16 +13992,16 @@
         <v>45468</v>
       </c>
       <c r="B679" t="n">
-        <v>90.97698211669922</v>
+        <v>90.97698974609375</v>
       </c>
       <c r="C679" t="n">
-        <v>90.97698211669922</v>
+        <v>90.97698974609375</v>
       </c>
       <c r="D679" t="n">
-        <v>89.11121408877702</v>
+        <v>89.1112215617069</v>
       </c>
       <c r="E679" t="n">
-        <v>90.03017150112908</v>
+        <v>90.0301790511234</v>
       </c>
       <c r="F679" t="n">
         <v>300759</v>
@@ -14052,16 +14052,16 @@
         <v>45471</v>
       </c>
       <c r="B682" t="n">
-        <v>90.78206634521484</v>
+        <v>90.78205871582031</v>
       </c>
       <c r="C682" t="n">
-        <v>92.4436132183085</v>
+        <v>92.44360544927629</v>
       </c>
       <c r="D682" t="n">
-        <v>89.58463336929955</v>
+        <v>89.58462584053821</v>
       </c>
       <c r="E682" t="n">
-        <v>91.15335746295753</v>
+        <v>91.15334980235941</v>
       </c>
       <c r="F682" t="n">
         <v>273815</v>
@@ -14072,16 +14072,16 @@
         <v>45474</v>
       </c>
       <c r="B683" t="n">
-        <v>87.969482421875</v>
+        <v>87.96947479248047</v>
       </c>
       <c r="C683" t="n">
-        <v>91.70101885438143</v>
+        <v>91.70101090135917</v>
       </c>
       <c r="D683" t="n">
-        <v>87.85809792545159</v>
+        <v>87.85809030571718</v>
       </c>
       <c r="E683" t="n">
-        <v>90.31794039570877</v>
+        <v>90.31793256263779</v>
       </c>
       <c r="F683" t="n">
         <v>154542</v>
@@ -14172,16 +14172,16 @@
         <v>45481</v>
       </c>
       <c r="B688" t="n">
-        <v>87.11549377441406</v>
+        <v>87.11550140380859</v>
       </c>
       <c r="C688" t="n">
-        <v>88.26651165334657</v>
+        <v>88.26651938354486</v>
       </c>
       <c r="D688" t="n">
-        <v>86.17796754914521</v>
+        <v>86.17797509643314</v>
       </c>
       <c r="E688" t="n">
-        <v>86.32648964032262</v>
+        <v>86.32649720061781</v>
       </c>
       <c r="F688" t="n">
         <v>189187</v>
@@ -14232,16 +14232,16 @@
         <v>45484</v>
       </c>
       <c r="B691" t="n">
-        <v>92.32294464111328</v>
+        <v>92.32293701171875</v>
       </c>
       <c r="C691" t="n">
-        <v>92.6014200623334</v>
+        <v>92.60141240992618</v>
       </c>
       <c r="D691" t="n">
-        <v>89.85382470611971</v>
+        <v>89.85381728076861</v>
       </c>
       <c r="E691" t="n">
-        <v>90.12300864286192</v>
+        <v>90.12300119526596</v>
       </c>
       <c r="F691" t="n">
         <v>274684</v>
@@ -14312,16 +14312,16 @@
         <v>45490</v>
       </c>
       <c r="B695" t="n">
-        <v>94.36507415771484</v>
+        <v>94.36506652832031</v>
       </c>
       <c r="C695" t="n">
-        <v>94.84775682559884</v>
+        <v>94.84774915717952</v>
       </c>
       <c r="D695" t="n">
-        <v>93.13051074146198</v>
+        <v>93.13050321188162</v>
       </c>
       <c r="E695" t="n">
-        <v>93.47395570913518</v>
+        <v>93.47394815178737</v>
       </c>
       <c r="F695" t="n">
         <v>165974</v>
@@ -14332,16 +14332,16 @@
         <v>45491</v>
       </c>
       <c r="B696" t="n">
-        <v>91.96092224121094</v>
+        <v>91.96092987060547</v>
       </c>
       <c r="C696" t="n">
-        <v>94.96842393223361</v>
+        <v>94.96843181114083</v>
       </c>
       <c r="D696" t="n">
-        <v>91.20904858893614</v>
+        <v>91.20905615595265</v>
       </c>
       <c r="E696" t="n">
-        <v>94.88488556283573</v>
+        <v>94.88489343481233</v>
       </c>
       <c r="F696" t="n">
         <v>265514</v>
@@ -14372,16 +14372,16 @@
         <v>45495</v>
       </c>
       <c r="B698" t="n">
-        <v>94.53215026855469</v>
+        <v>94.53214263916016</v>
       </c>
       <c r="C698" t="n">
-        <v>95.24690048663403</v>
+        <v>95.24689279955425</v>
       </c>
       <c r="D698" t="n">
-        <v>92.54571319911821</v>
+        <v>92.54570573004281</v>
       </c>
       <c r="E698" t="n">
-        <v>92.54571319911821</v>
+        <v>92.54570573004281</v>
       </c>
       <c r="F698" t="n">
         <v>202118</v>
@@ -14392,16 +14392,16 @@
         <v>45496</v>
       </c>
       <c r="B699" t="n">
-        <v>94.27224731445312</v>
+        <v>94.27223968505859</v>
       </c>
       <c r="C699" t="n">
-        <v>94.9405826312758</v>
+        <v>94.94057494779331</v>
       </c>
       <c r="D699" t="n">
-        <v>93.76171850660302</v>
+        <v>93.76171091852527</v>
       </c>
       <c r="E699" t="n">
-        <v>93.76171850660302</v>
+        <v>93.76171091852527</v>
       </c>
       <c r="F699" t="n">
         <v>121190</v>
@@ -14412,16 +14412,16 @@
         <v>45497</v>
       </c>
       <c r="B700" t="n">
-        <v>91.80311584472656</v>
+        <v>91.80312347412109</v>
       </c>
       <c r="C700" t="n">
-        <v>94.77348678516967</v>
+        <v>94.77349466141999</v>
       </c>
       <c r="D700" t="n">
-        <v>91.78454704276713</v>
+        <v>91.78455467061849</v>
       </c>
       <c r="E700" t="n">
-        <v>94.36506520706058</v>
+        <v>94.3650730493686</v>
       </c>
       <c r="F700" t="n">
         <v>387734</v>
@@ -14452,16 +14452,16 @@
         <v>45499</v>
       </c>
       <c r="B702" t="n">
-        <v>93.1026611328125</v>
+        <v>93.10266876220703</v>
       </c>
       <c r="C702" t="n">
-        <v>94.93129164313034</v>
+        <v>94.9312994223739</v>
       </c>
       <c r="D702" t="n">
-        <v>92.04446598189828</v>
+        <v>92.04447352457791</v>
       </c>
       <c r="E702" t="n">
-        <v>93.00055396194153</v>
+        <v>93.00056158296879</v>
       </c>
       <c r="F702" t="n">
         <v>291332</v>
@@ -14472,16 +14472,16 @@
         <v>45502</v>
       </c>
       <c r="B703" t="n">
-        <v>91.94235229492188</v>
+        <v>91.94235992431641</v>
       </c>
       <c r="C703" t="n">
-        <v>94.07730416654506</v>
+        <v>94.07731197309832</v>
       </c>
       <c r="D703" t="n">
-        <v>91.71956916594331</v>
+        <v>91.71957677685126</v>
       </c>
       <c r="E703" t="n">
-        <v>93.10265453447454</v>
+        <v>93.10266226015118</v>
       </c>
       <c r="F703" t="n">
         <v>142991</v>
@@ -14492,16 +14492,16 @@
         <v>45503</v>
       </c>
       <c r="B704" t="n">
-        <v>90.27152252197266</v>
+        <v>90.27151489257812</v>
       </c>
       <c r="C704" t="n">
-        <v>93.12122480057187</v>
+        <v>93.1212169303317</v>
       </c>
       <c r="D704" t="n">
-        <v>90.05802377425481</v>
+        <v>90.05801616290437</v>
       </c>
       <c r="E704" t="n">
-        <v>91.94236073304077</v>
+        <v>91.94235296243356</v>
       </c>
       <c r="F704" t="n">
         <v>198691</v>
@@ -14512,16 +14512,16 @@
         <v>45504</v>
       </c>
       <c r="B705" t="n">
-        <v>90.49430847167969</v>
+        <v>90.49430084228516</v>
       </c>
       <c r="C705" t="n">
-        <v>91.8031330602639</v>
+        <v>91.80312532052498</v>
       </c>
       <c r="D705" t="n">
-        <v>89.90023417218629</v>
+        <v>89.90022659287696</v>
       </c>
       <c r="E705" t="n">
-        <v>90.59641565583551</v>
+        <v>90.59640801783253</v>
       </c>
       <c r="F705" t="n">
         <v>210335</v>
@@ -14532,16 +14532,16 @@
         <v>45505</v>
       </c>
       <c r="B706" t="n">
-        <v>88.00661468505859</v>
+        <v>88.00660705566406</v>
       </c>
       <c r="C706" t="n">
-        <v>91.76599731587329</v>
+        <v>91.76598936057357</v>
       </c>
       <c r="D706" t="n">
-        <v>87.55177812453009</v>
+        <v>87.55177053456586</v>
       </c>
       <c r="E706" t="n">
-        <v>90.96770869343818</v>
+        <v>90.96770080734302</v>
       </c>
       <c r="F706" t="n">
         <v>831618</v>
@@ -14592,16 +14592,16 @@
         <v>45510</v>
       </c>
       <c r="B709" t="n">
-        <v>85.04552459716797</v>
+        <v>85.0455322265625</v>
       </c>
       <c r="C709" t="n">
-        <v>86.18725815714363</v>
+        <v>86.18726588896256</v>
       </c>
       <c r="D709" t="n">
-        <v>83.79239237886372</v>
+        <v>83.79239989584035</v>
       </c>
       <c r="E709" t="n">
-        <v>85.21260842081362</v>
+        <v>85.21261606519718</v>
       </c>
       <c r="F709" t="n">
         <v>246819</v>
@@ -14612,16 +14612,16 @@
         <v>45511</v>
       </c>
       <c r="B710" t="n">
-        <v>87.3104248046875</v>
+        <v>87.31043243408203</v>
       </c>
       <c r="C710" t="n">
-        <v>88.45216537870958</v>
+        <v>88.45217310787214</v>
       </c>
       <c r="D710" t="n">
-        <v>85.49107165644291</v>
+        <v>85.491079126858</v>
       </c>
       <c r="E710" t="n">
-        <v>85.49107165644291</v>
+        <v>85.491079126858</v>
       </c>
       <c r="F710" t="n">
         <v>332645</v>
@@ -14692,16 +14692,16 @@
         <v>45517</v>
       </c>
       <c r="B714" t="n">
-        <v>93.46467590332031</v>
+        <v>93.46468353271484</v>
       </c>
       <c r="C714" t="n">
-        <v>94.6806704835107</v>
+        <v>94.6806782121652</v>
       </c>
       <c r="D714" t="n">
-        <v>92.62925680619877</v>
+        <v>92.62926436739917</v>
       </c>
       <c r="E714" t="n">
-        <v>92.62925680619877</v>
+        <v>92.62926436739917</v>
       </c>
       <c r="F714" t="n">
         <v>783941</v>
@@ -14712,16 +14712,16 @@
         <v>45518</v>
       </c>
       <c r="B715" t="n">
-        <v>100.250129699707</v>
+        <v>100.2501220703125</v>
       </c>
       <c r="C715" t="n">
-        <v>101.4382782519291</v>
+        <v>101.4382705321122</v>
       </c>
       <c r="D715" t="n">
-        <v>98.41220753916585</v>
+        <v>98.41220004964379</v>
       </c>
       <c r="E715" t="n">
-        <v>100.0644841441438</v>
+        <v>100.0644765288776</v>
       </c>
       <c r="F715" t="n">
         <v>1420295</v>
@@ -14772,16 +14772,16 @@
         <v>45523</v>
       </c>
       <c r="B718" t="n">
-        <v>100.5471572875977</v>
+        <v>100.5471649169922</v>
       </c>
       <c r="C718" t="n">
-        <v>102.0787577622536</v>
+        <v>102.0787655078641</v>
       </c>
       <c r="D718" t="n">
-        <v>99.86026029894786</v>
+        <v>99.8602678762215</v>
       </c>
       <c r="E718" t="n">
-        <v>101.3640075691833</v>
+        <v>101.3640152605594</v>
       </c>
       <c r="F718" t="n">
         <v>372762</v>
@@ -14792,16 +14792,16 @@
         <v>45524</v>
       </c>
       <c r="B719" t="n">
-        <v>99.72102355957031</v>
+        <v>99.72103118896484</v>
       </c>
       <c r="C719" t="n">
-        <v>101.0948246319502</v>
+        <v>101.0948323664506</v>
       </c>
       <c r="D719" t="n">
-        <v>99.31259487390432</v>
+        <v>99.31260247205103</v>
       </c>
       <c r="E719" t="n">
-        <v>100.5935731764301</v>
+        <v>100.5935808725811</v>
       </c>
       <c r="F719" t="n">
         <v>300080</v>
@@ -14812,16 +14812,16 @@
         <v>45525</v>
       </c>
       <c r="B720" t="n">
-        <v>98.78350067138672</v>
+        <v>98.78350830078125</v>
       </c>
       <c r="C720" t="n">
-        <v>100.407923986077</v>
+        <v>100.4079317409314</v>
       </c>
       <c r="D720" t="n">
-        <v>98.45861742483341</v>
+        <v>98.45862502913606</v>
       </c>
       <c r="E720" t="n">
-        <v>99.32188266963144</v>
+        <v>99.32189034060708</v>
       </c>
       <c r="F720" t="n">
         <v>477691</v>
@@ -14872,16 +14872,16 @@
         <v>45530</v>
       </c>
       <c r="B723" t="n">
-        <v>99.94380187988281</v>
+        <v>99.94379425048828</v>
       </c>
       <c r="C723" t="n">
-        <v>102.6635508813548</v>
+        <v>102.6635430443433</v>
       </c>
       <c r="D723" t="n">
-        <v>99.06197492347634</v>
+        <v>99.06196736139771</v>
       </c>
       <c r="E723" t="n">
-        <v>100.2594078028197</v>
+        <v>100.2594001493328</v>
       </c>
       <c r="F723" t="n">
         <v>725758</v>
@@ -14892,16 +14892,16 @@
         <v>45531</v>
       </c>
       <c r="B724" t="n">
-        <v>99.32187652587891</v>
+        <v>99.32188415527344</v>
       </c>
       <c r="C724" t="n">
-        <v>100.7977776468936</v>
+        <v>100.7977853896593</v>
       </c>
       <c r="D724" t="n">
-        <v>99.1547927119977</v>
+        <v>99.15480032855771</v>
       </c>
       <c r="E724" t="n">
-        <v>99.40541489185792</v>
+        <v>99.40542252766943</v>
       </c>
       <c r="F724" t="n">
         <v>203544</v>
@@ -14912,16 +14912,16 @@
         <v>45532</v>
       </c>
       <c r="B725" t="n">
-        <v>98.89488983154297</v>
+        <v>98.89488220214844</v>
       </c>
       <c r="C725" t="n">
-        <v>100.2222759909589</v>
+        <v>100.2222682591612</v>
       </c>
       <c r="D725" t="n">
-        <v>98.33794612507214</v>
+        <v>98.33793853864385</v>
       </c>
       <c r="E725" t="n">
-        <v>100.1851454662711</v>
+        <v>100.1851377373378</v>
       </c>
       <c r="F725" t="n">
         <v>251737</v>
@@ -14992,16 +14992,16 @@
         <v>45538</v>
       </c>
       <c r="B729" t="n">
-        <v>96.24940490722656</v>
+        <v>96.24939727783203</v>
       </c>
       <c r="C729" t="n">
-        <v>97.25190077727714</v>
+        <v>97.25189306841784</v>
       </c>
       <c r="D729" t="n">
-        <v>94.54143612809369</v>
+        <v>94.5414286340846</v>
       </c>
       <c r="E729" t="n">
-        <v>95.51609295616707</v>
+        <v>95.51608538489992</v>
       </c>
       <c r="F729" t="n">
         <v>703523</v>
@@ -15052,16 +15052,16 @@
         <v>45541</v>
       </c>
       <c r="B732" t="n">
-        <v>93.76171112060547</v>
+        <v>93.76171875</v>
       </c>
       <c r="C732" t="n">
-        <v>96.95485826444198</v>
+        <v>96.95486615366303</v>
       </c>
       <c r="D732" t="n">
-        <v>93.10266025785589</v>
+        <v>93.10266783362343</v>
       </c>
       <c r="E732" t="n">
-        <v>96.5835671904987</v>
+        <v>96.58357504950779</v>
       </c>
       <c r="F732" t="n">
         <v>627234</v>
@@ -15072,16 +15072,16 @@
         <v>45544</v>
       </c>
       <c r="B733" t="n">
-        <v>93.68745422363281</v>
+        <v>93.68744659423828</v>
       </c>
       <c r="C733" t="n">
-        <v>95.05197093478797</v>
+        <v>95.05196319427465</v>
       </c>
       <c r="D733" t="n">
-        <v>93.37184829849096</v>
+        <v>93.37184069479765</v>
       </c>
       <c r="E733" t="n">
-        <v>93.77099259439402</v>
+        <v>93.77098495819658</v>
       </c>
       <c r="F733" t="n">
         <v>200739</v>
@@ -15092,16 +15092,16 @@
         <v>45545</v>
       </c>
       <c r="B734" t="n">
-        <v>94.4393310546875</v>
+        <v>94.43932342529297</v>
       </c>
       <c r="C734" t="n">
-        <v>94.894174694939</v>
+        <v>94.89416702879937</v>
       </c>
       <c r="D734" t="n">
-        <v>92.1929873056461</v>
+        <v>92.19297985772515</v>
       </c>
       <c r="E734" t="n">
-        <v>93.78028014064265</v>
+        <v>93.78027256449035</v>
       </c>
       <c r="F734" t="n">
         <v>481370</v>
@@ -15292,16 +15292,16 @@
         <v>45559</v>
       </c>
       <c r="B744" t="n">
-        <v>91.52465057373047</v>
+        <v>91.52464294433594</v>
       </c>
       <c r="C744" t="n">
-        <v>93.45539543910657</v>
+        <v>93.45538764876726</v>
       </c>
       <c r="D744" t="n">
-        <v>90.05802666165111</v>
+        <v>90.05801915451273</v>
       </c>
       <c r="E744" t="n">
-        <v>90.96770684615915</v>
+        <v>90.96769926319082</v>
       </c>
       <c r="F744" t="n">
         <v>524613</v>
@@ -15312,16 +15312,16 @@
         <v>45560</v>
       </c>
       <c r="B745" t="n">
-        <v>90.49430847167969</v>
+        <v>90.49430084228516</v>
       </c>
       <c r="C745" t="n">
-        <v>92.06303968105173</v>
+        <v>92.0630319194006</v>
       </c>
       <c r="D745" t="n">
-        <v>89.42682878036601</v>
+        <v>89.42682124096855</v>
       </c>
       <c r="E745" t="n">
-        <v>91.89595584169895</v>
+        <v>91.89594809413431</v>
       </c>
       <c r="F745" t="n">
         <v>511811</v>
@@ -15352,16 +15352,16 @@
         <v>45562</v>
       </c>
       <c r="B747" t="n">
-        <v>91.98876953125</v>
+        <v>91.98876190185547</v>
       </c>
       <c r="C747" t="n">
-        <v>93.64103895603112</v>
+        <v>93.64103118960014</v>
       </c>
       <c r="D747" t="n">
-        <v>90.51286833111075</v>
+        <v>90.512860824125</v>
       </c>
       <c r="E747" t="n">
-        <v>91.71957853434738</v>
+        <v>91.71957092727911</v>
       </c>
       <c r="F747" t="n">
         <v>582331</v>
@@ -15372,16 +15372,16 @@
         <v>45565</v>
       </c>
       <c r="B748" t="n">
-        <v>90.47573852539062</v>
+        <v>90.47573089599609</v>
       </c>
       <c r="C748" t="n">
-        <v>92.6663899613996</v>
+        <v>92.66638214727772</v>
       </c>
       <c r="D748" t="n">
-        <v>90.05802542400984</v>
+        <v>90.05801782983909</v>
       </c>
       <c r="E748" t="n">
-        <v>91.98877026285227</v>
+        <v>91.98876250587087</v>
       </c>
       <c r="F748" t="n">
         <v>340494</v>
@@ -15412,16 +15412,16 @@
         <v>45567</v>
       </c>
       <c r="B750" t="n">
-        <v>90.91201019287109</v>
+        <v>90.91201782226562</v>
       </c>
       <c r="C750" t="n">
-        <v>93.24189216654202</v>
+        <v>93.24189999146175</v>
       </c>
       <c r="D750" t="n">
-        <v>90.61497308043096</v>
+        <v>90.61498068489794</v>
       </c>
       <c r="E750" t="n">
-        <v>90.96770243835256</v>
+        <v>90.96771007242083</v>
       </c>
       <c r="F750" t="n">
         <v>338550</v>
@@ -15472,16 +15472,16 @@
         <v>45572</v>
       </c>
       <c r="B753" t="n">
-        <v>90.48501586914062</v>
+        <v>90.48502349853516</v>
       </c>
       <c r="C753" t="n">
-        <v>90.75419976526331</v>
+        <v>90.75420741735454</v>
       </c>
       <c r="D753" t="n">
-        <v>89.12049925852935</v>
+        <v>89.1205067728724</v>
       </c>
       <c r="E753" t="n">
-        <v>89.80739622344984</v>
+        <v>89.80740379570975</v>
       </c>
       <c r="F753" t="n">
         <v>295051</v>
@@ -15512,16 +15512,16 @@
         <v>45574</v>
       </c>
       <c r="B755" t="n">
-        <v>89.48251342773438</v>
+        <v>89.48252105712891</v>
       </c>
       <c r="C755" t="n">
-        <v>90.68922355217755</v>
+        <v>90.68923128445775</v>
       </c>
       <c r="D755" t="n">
-        <v>87.85809023250759</v>
+        <v>87.85809772340171</v>
       </c>
       <c r="E755" t="n">
-        <v>90.42003965477517</v>
+        <v>90.42004736410439</v>
       </c>
       <c r="F755" t="n">
         <v>305833</v>
@@ -15592,16 +15592,16 @@
         <v>45580</v>
       </c>
       <c r="B759" t="n">
-        <v>92.2208251953125</v>
+        <v>92.22083282470703</v>
       </c>
       <c r="C759" t="n">
-        <v>94.20726216221644</v>
+        <v>94.20726995594816</v>
       </c>
       <c r="D759" t="n">
-        <v>91.71029643353101</v>
+        <v>91.71030402068969</v>
       </c>
       <c r="E759" t="n">
-        <v>93.52964958630643</v>
+        <v>93.52965732397952</v>
       </c>
       <c r="F759" t="n">
         <v>238514</v>
@@ -15612,16 +15612,16 @@
         <v>45581</v>
       </c>
       <c r="B760" t="n">
-        <v>95.37684631347656</v>
+        <v>95.37685394287109</v>
       </c>
       <c r="C760" t="n">
-        <v>95.37684631347656</v>
+        <v>95.37685394287109</v>
       </c>
       <c r="D760" t="n">
-        <v>91.53392577309324</v>
+        <v>91.53393309508448</v>
       </c>
       <c r="E760" t="n">
-        <v>91.53392577309324</v>
+        <v>91.53393309508448</v>
       </c>
       <c r="F760" t="n">
         <v>473040</v>
@@ -15712,16 +15712,16 @@
         <v>45588</v>
       </c>
       <c r="B765" t="n">
-        <v>92.42504119873047</v>
+        <v>92.425048828125</v>
       </c>
       <c r="C765" t="n">
-        <v>95.40469670279386</v>
+        <v>95.40470457814952</v>
       </c>
       <c r="D765" t="n">
-        <v>92.36006455217171</v>
+        <v>92.36007217620262</v>
       </c>
       <c r="E765" t="n">
-        <v>93.76171173585173</v>
+        <v>93.76171947558419</v>
       </c>
       <c r="F765" t="n">
         <v>357512</v>
@@ -15752,16 +15752,16 @@
         <v>45590</v>
       </c>
       <c r="B767" t="n">
-        <v>93.17691040039062</v>
+        <v>93.17691802978516</v>
       </c>
       <c r="C767" t="n">
-        <v>93.91022228060997</v>
+        <v>93.91022997004863</v>
       </c>
       <c r="D767" t="n">
-        <v>92.02589253816214</v>
+        <v>92.02590007331048</v>
       </c>
       <c r="E767" t="n">
-        <v>93.29758636820173</v>
+        <v>93.29759400747731</v>
       </c>
       <c r="F767" t="n">
         <v>563664</v>
@@ -15832,16 +15832,16 @@
         <v>45596</v>
       </c>
       <c r="B771" t="n">
-        <v>93.83596801757812</v>
+        <v>93.83597564697266</v>
       </c>
       <c r="C771" t="n">
-        <v>95.56249847665784</v>
+        <v>95.56250624642907</v>
       </c>
       <c r="D771" t="n">
-        <v>93.23261646261058</v>
+        <v>93.23262404294924</v>
       </c>
       <c r="E771" t="n">
-        <v>95.47896010698793</v>
+        <v>95.47896786996702</v>
       </c>
       <c r="F771" t="n">
         <v>253528</v>
@@ -15872,16 +15872,16 @@
         <v>45600</v>
       </c>
       <c r="B773" t="n">
-        <v>94.235107421875</v>
+        <v>94.23511505126953</v>
       </c>
       <c r="C773" t="n">
-        <v>95.19120245514728</v>
+        <v>95.19121016194849</v>
       </c>
       <c r="D773" t="n">
-        <v>91.90522552863958</v>
+        <v>91.9052329694039</v>
       </c>
       <c r="E773" t="n">
-        <v>92.32293151917671</v>
+        <v>92.32293899375905</v>
       </c>
       <c r="F773" t="n">
         <v>289905</v>
@@ -15912,16 +15912,16 @@
         <v>45602</v>
       </c>
       <c r="B775" t="n">
-        <v>94.72709655761719</v>
+        <v>94.72708129882812</v>
       </c>
       <c r="C775" t="n">
-        <v>95.38614751126146</v>
+        <v>95.38613214631143</v>
       </c>
       <c r="D775" t="n">
-        <v>91.81241731725275</v>
+        <v>91.81240252796478</v>
       </c>
       <c r="E775" t="n">
-        <v>94.2165606376484</v>
+        <v>94.21654546109727</v>
       </c>
       <c r="F775" t="n">
         <v>484922</v>
@@ -15932,16 +15932,16 @@
         <v>45603</v>
       </c>
       <c r="B776" t="n">
-        <v>93.40898132324219</v>
+        <v>93.40897369384766</v>
       </c>
       <c r="C776" t="n">
-        <v>96.03590764140573</v>
+        <v>96.03589979745092</v>
       </c>
       <c r="D776" t="n">
-        <v>92.91701424157758</v>
+        <v>92.91700665236559</v>
       </c>
       <c r="E776" t="n">
-        <v>94.72709022432851</v>
+        <v>94.72708248727439</v>
       </c>
       <c r="F776" t="n">
         <v>397597</v>
@@ -15952,16 +15952,16 @@
         <v>45604</v>
       </c>
       <c r="B777" t="n">
-        <v>91.02339172363281</v>
+        <v>91.02339935302734</v>
       </c>
       <c r="C777" t="n">
-        <v>93.79883989858776</v>
+        <v>93.79884776061469</v>
       </c>
       <c r="D777" t="n">
-        <v>89.98376540486406</v>
+        <v>89.98377294711923</v>
       </c>
       <c r="E777" t="n">
-        <v>93.39969562779672</v>
+        <v>93.39970345636819</v>
       </c>
       <c r="F777" t="n">
         <v>477120</v>
@@ -15972,16 +15972,16 @@
         <v>45607</v>
       </c>
       <c r="B778" t="n">
-        <v>92.10945129394531</v>
+        <v>92.10944366455078</v>
       </c>
       <c r="C778" t="n">
-        <v>93.48324540630318</v>
+        <v>93.48323766311775</v>
       </c>
       <c r="D778" t="n">
-        <v>90.58712798917934</v>
+        <v>90.58712048587832</v>
       </c>
       <c r="E778" t="n">
-        <v>91.52465433631919</v>
+        <v>91.52464675536318</v>
       </c>
       <c r="F778" t="n">
         <v>447451</v>
@@ -15992,16 +15992,16 @@
         <v>45608</v>
       </c>
       <c r="B779" t="n">
-        <v>89.94663238525391</v>
+        <v>89.94664001464844</v>
       </c>
       <c r="C779" t="n">
-        <v>92.870595489481</v>
+        <v>92.87060336689002</v>
       </c>
       <c r="D779" t="n">
-        <v>89.7888329779525</v>
+        <v>89.78884059396226</v>
       </c>
       <c r="E779" t="n">
-        <v>92.82418056642861</v>
+        <v>92.82418843990065</v>
       </c>
       <c r="F779" t="n">
         <v>488207</v>
@@ -16072,16 +16072,16 @@
         <v>45615</v>
       </c>
       <c r="B783" t="n">
-        <v>89.11121368408203</v>
+        <v>89.11122131347656</v>
       </c>
       <c r="C783" t="n">
-        <v>90.45716147466617</v>
+        <v>90.45716921929609</v>
       </c>
       <c r="D783" t="n">
-        <v>88.56355441597165</v>
+        <v>88.56356199847747</v>
       </c>
       <c r="E783" t="n">
-        <v>89.87237168435665</v>
+        <v>89.87237937891889</v>
       </c>
       <c r="F783" t="n">
         <v>517590</v>
@@ -16092,16 +16092,16 @@
         <v>45617</v>
       </c>
       <c r="B784" t="n">
-        <v>83.69029998779297</v>
+        <v>83.69029235839844</v>
       </c>
       <c r="C784" t="n">
-        <v>85.30543904371771</v>
+        <v>85.30543126708351</v>
       </c>
       <c r="D784" t="n">
-        <v>83.30043297546001</v>
+        <v>83.30042538160664</v>
       </c>
       <c r="E784" t="n">
-        <v>85.1662013308791</v>
+        <v>85.16619356693812</v>
       </c>
       <c r="F784" t="n">
         <v>1016945</v>
@@ -16132,16 +16132,16 @@
         <v>45621</v>
       </c>
       <c r="B786" t="n">
-        <v>85.59317779541016</v>
+        <v>85.59318542480469</v>
       </c>
       <c r="C786" t="n">
-        <v>86.31720528548094</v>
+        <v>86.31721297941206</v>
       </c>
       <c r="D786" t="n">
-        <v>84.42359111349106</v>
+        <v>84.42359863863385</v>
       </c>
       <c r="E786" t="n">
-        <v>85.32398681644892</v>
+        <v>85.32399442184897</v>
       </c>
       <c r="F786" t="n">
         <v>384525</v>
@@ -16212,16 +16212,16 @@
         <v>45625</v>
       </c>
       <c r="B790" t="n">
-        <v>76.31076812744141</v>
+        <v>76.31076049804688</v>
       </c>
       <c r="C790" t="n">
-        <v>79.70813698664587</v>
+        <v>79.70812901758936</v>
       </c>
       <c r="D790" t="n">
-        <v>73.81379507240612</v>
+        <v>73.81378769265385</v>
       </c>
       <c r="E790" t="n">
-        <v>78.53855017325635</v>
+        <v>78.53854232113272</v>
       </c>
       <c r="F790" t="n">
         <v>1718056</v>
@@ -16272,16 +16272,16 @@
         <v>45630</v>
       </c>
       <c r="B793" t="n">
-        <v>75.2247314453125</v>
+        <v>75.22471618652344</v>
       </c>
       <c r="C793" t="n">
-        <v>76.09728117894873</v>
+        <v>76.0972657431693</v>
       </c>
       <c r="D793" t="n">
-        <v>74.39859664377688</v>
+        <v>74.39858155256324</v>
       </c>
       <c r="E793" t="n">
-        <v>75.41966141267126</v>
+        <v>75.41964611434207</v>
       </c>
       <c r="F793" t="n">
         <v>411810</v>
@@ -16292,16 +16292,16 @@
         <v>45631</v>
       </c>
       <c r="B794" t="n">
-        <v>75.51248168945312</v>
+        <v>75.51247406005859</v>
       </c>
       <c r="C794" t="n">
-        <v>77.57317996447813</v>
+        <v>77.5731721268812</v>
       </c>
       <c r="D794" t="n">
-        <v>74.09227263015862</v>
+        <v>74.09226514425474</v>
       </c>
       <c r="E794" t="n">
-        <v>75.65171939921073</v>
+        <v>75.65171175574832</v>
       </c>
       <c r="F794" t="n">
         <v>973742</v>
@@ -16312,16 +16312,16 @@
         <v>45632</v>
       </c>
       <c r="B795" t="n">
-        <v>75.78166198730469</v>
+        <v>75.78166961669922</v>
       </c>
       <c r="C795" t="n">
-        <v>75.78166198730469</v>
+        <v>75.78166961669922</v>
       </c>
       <c r="D795" t="n">
-        <v>74.25934596164483</v>
+        <v>74.25935343777866</v>
       </c>
       <c r="E795" t="n">
-        <v>75.65170869842567</v>
+        <v>75.651716314737</v>
       </c>
       <c r="F795" t="n">
         <v>1017781</v>
@@ -16332,16 +16332,16 @@
         <v>45635</v>
       </c>
       <c r="B796" t="n">
-        <v>75.51248168945312</v>
+        <v>75.51247406005859</v>
       </c>
       <c r="C796" t="n">
-        <v>78.0651470679541</v>
+        <v>78.06513918065133</v>
       </c>
       <c r="D796" t="n">
-        <v>75.51248168945312</v>
+        <v>75.51247406005859</v>
       </c>
       <c r="E796" t="n">
-        <v>76.11584037711999</v>
+        <v>76.11583268676519</v>
       </c>
       <c r="F796" t="n">
         <v>291521</v>
@@ -16452,16 +16452,16 @@
         <v>45643</v>
       </c>
       <c r="B802" t="n">
-        <v>77.18950653076172</v>
+        <v>77.18951416015625</v>
       </c>
       <c r="C802" t="n">
-        <v>78.9191654754832</v>
+        <v>78.91917327583685</v>
       </c>
       <c r="D802" t="n">
-        <v>75.78233483874901</v>
+        <v>75.78234232905898</v>
       </c>
       <c r="E802" t="n">
-        <v>76.12435547724201</v>
+        <v>76.12436300135722</v>
       </c>
       <c r="F802" t="n">
         <v>713503</v>
@@ -16492,16 +16492,16 @@
         <v>45645</v>
       </c>
       <c r="B804" t="n">
-        <v>72.4598388671875</v>
+        <v>72.45983123779297</v>
       </c>
       <c r="C804" t="n">
-        <v>73.96473726095877</v>
+        <v>73.96472947311145</v>
       </c>
       <c r="D804" t="n">
-        <v>71.17969371703964</v>
+        <v>71.17968622243332</v>
       </c>
       <c r="E804" t="n">
-        <v>72.37188643518905</v>
+        <v>72.37187881505514</v>
       </c>
       <c r="F804" t="n">
         <v>633891</v>
@@ -16532,16 +16532,16 @@
         <v>45649</v>
       </c>
       <c r="B806" t="n">
-        <v>72.79207611083984</v>
+        <v>72.79208374023438</v>
       </c>
       <c r="C806" t="n">
-        <v>73.45657651880434</v>
+        <v>73.45658421784569</v>
       </c>
       <c r="D806" t="n">
-        <v>71.0721988418062</v>
+        <v>71.07220629093905</v>
       </c>
       <c r="E806" t="n">
-        <v>72.32302138491811</v>
+        <v>72.32302896515064</v>
       </c>
       <c r="F806" t="n">
         <v>510211</v>
@@ -16572,16 +16572,16 @@
         <v>45653</v>
       </c>
       <c r="B808" t="n">
-        <v>72.35234832763672</v>
+        <v>72.35234069824219</v>
       </c>
       <c r="C808" t="n">
-        <v>73.83769847912376</v>
+        <v>73.83769069310235</v>
       </c>
       <c r="D808" t="n">
-        <v>72.35234832763672</v>
+        <v>72.35234069824219</v>
       </c>
       <c r="E808" t="n">
-        <v>73.29046538996933</v>
+        <v>73.29045766165243</v>
       </c>
       <c r="F808" t="n">
         <v>193425</v>
@@ -16612,16 +16612,16 @@
         <v>45659</v>
       </c>
       <c r="B810" t="n">
-        <v>70.56405639648438</v>
+        <v>70.56404876708984</v>
       </c>
       <c r="C810" t="n">
-        <v>72.74322942844815</v>
+        <v>72.74322156344115</v>
       </c>
       <c r="D810" t="n">
-        <v>69.73343264596139</v>
+        <v>69.733425106374</v>
       </c>
       <c r="E810" t="n">
-        <v>71.88328323031399</v>
+        <v>71.8832754582845</v>
       </c>
       <c r="F810" t="n">
         <v>241349</v>
@@ -16732,16 +16732,16 @@
         <v>45667</v>
       </c>
       <c r="B816" t="n">
-        <v>66.62591552734375</v>
+        <v>66.62590789794922</v>
       </c>
       <c r="C816" t="n">
-        <v>67.14383359335977</v>
+        <v>67.14382590465797</v>
       </c>
       <c r="D816" t="n">
-        <v>65.19919544467032</v>
+        <v>65.19918797865081</v>
       </c>
       <c r="E816" t="n">
-        <v>65.58030524628556</v>
+        <v>65.58029773662483</v>
       </c>
       <c r="F816" t="n">
         <v>598954</v>
@@ -16752,16 +16752,16 @@
         <v>45670</v>
       </c>
       <c r="B817" t="n">
-        <v>67.87673187255859</v>
+        <v>67.87673950195312</v>
       </c>
       <c r="C817" t="n">
-        <v>68.63895140467909</v>
+        <v>68.63895911974765</v>
       </c>
       <c r="D817" t="n">
-        <v>65.75619651668684</v>
+        <v>65.75620390773163</v>
       </c>
       <c r="E817" t="n">
-        <v>66.57704602651182</v>
+        <v>66.5770535098207</v>
       </c>
       <c r="F817" t="n">
         <v>512624</v>
@@ -16792,16 +16792,16 @@
         <v>45672</v>
       </c>
       <c r="B819" t="n">
-        <v>69.77251434326172</v>
+        <v>69.77252197265625</v>
       </c>
       <c r="C819" t="n">
-        <v>69.96795257353654</v>
+        <v>69.96796022430158</v>
       </c>
       <c r="D819" t="n">
-        <v>66.75294373372894</v>
+        <v>66.75295103294337</v>
       </c>
       <c r="E819" t="n">
-        <v>66.75294373372894</v>
+        <v>66.75295103294337</v>
       </c>
       <c r="F819" t="n">
         <v>444557</v>
@@ -17032,16 +17032,16 @@
         <v>45688</v>
       </c>
       <c r="B831" t="n">
-        <v>77.98104858398438</v>
+        <v>77.98105621337891</v>
       </c>
       <c r="C831" t="n">
-        <v>80.18952896866313</v>
+        <v>80.18953681412769</v>
       </c>
       <c r="D831" t="n">
-        <v>77.37517812716173</v>
+        <v>77.37518569728</v>
       </c>
       <c r="E831" t="n">
-        <v>79.74001506411371</v>
+        <v>79.7400228655994</v>
       </c>
       <c r="F831" t="n">
         <v>229217</v>
@@ -17072,16 +17072,16 @@
         <v>45692</v>
       </c>
       <c r="B833" t="n">
-        <v>78.51851654052734</v>
+        <v>78.51850891113281</v>
       </c>
       <c r="C833" t="n">
-        <v>79.76933928144435</v>
+        <v>79.76933153051134</v>
       </c>
       <c r="D833" t="n">
-        <v>77.01361810052045</v>
+        <v>77.01361061735211</v>
       </c>
       <c r="E833" t="n">
-        <v>78.95826380304736</v>
+        <v>78.95825613092398</v>
       </c>
       <c r="F833" t="n">
         <v>404279</v>
@@ -17252,16 +17252,16 @@
         <v>45705</v>
       </c>
       <c r="B842" t="n">
-        <v>81.79215240478516</v>
+        <v>81.79214477539062</v>
       </c>
       <c r="C842" t="n">
-        <v>84.23516779866155</v>
+        <v>84.23515994138785</v>
       </c>
       <c r="D842" t="n">
-        <v>80.99084365381336</v>
+        <v>80.99083609916316</v>
       </c>
       <c r="E842" t="n">
-        <v>82.28075548356044</v>
+        <v>82.28074780859008</v>
       </c>
       <c r="F842" t="n">
         <v>317686</v>
@@ -17412,16 +17412,16 @@
         <v>45715</v>
       </c>
       <c r="B850" t="n">
-        <v>82.19281005859375</v>
+        <v>82.19280242919922</v>
       </c>
       <c r="C850" t="n">
-        <v>84.69445542248718</v>
+        <v>84.69444756088208</v>
       </c>
       <c r="D850" t="n">
-        <v>81.9387343714823</v>
+        <v>81.93872676567187</v>
       </c>
       <c r="E850" t="n">
-        <v>82.2612141910286</v>
+        <v>82.2612065552846</v>
       </c>
       <c r="F850" t="n">
         <v>386526</v>
@@ -17492,16 +17492,16 @@
         <v>45723</v>
       </c>
       <c r="B854" t="n">
-        <v>86.96157073974609</v>
+        <v>86.96156311035156</v>
       </c>
       <c r="C854" t="n">
-        <v>87.2058722703318</v>
+        <v>87.20586461950396</v>
       </c>
       <c r="D854" t="n">
-        <v>81.6358003551744</v>
+        <v>81.63579319302536</v>
       </c>
       <c r="E854" t="n">
-        <v>82.23189668624276</v>
+        <v>82.23188947179645</v>
       </c>
       <c r="F854" t="n">
         <v>477946</v>
@@ -17512,16 +17512,16 @@
         <v>45726</v>
       </c>
       <c r="B855" t="n">
-        <v>86.60977935791016</v>
+        <v>86.60977172851562</v>
       </c>
       <c r="C855" t="n">
-        <v>87.33291728494093</v>
+        <v>87.33290959184569</v>
       </c>
       <c r="D855" t="n">
-        <v>85.90619718466415</v>
+        <v>85.90618961724768</v>
       </c>
       <c r="E855" t="n">
-        <v>85.90619718466415</v>
+        <v>85.90618961724768</v>
       </c>
       <c r="F855" t="n">
         <v>418727</v>
@@ -17552,16 +17552,16 @@
         <v>45728</v>
       </c>
       <c r="B857" t="n">
-        <v>80.08203887939453</v>
+        <v>80.08203125</v>
       </c>
       <c r="C857" t="n">
-        <v>84.72376796838242</v>
+        <v>84.72375989677158</v>
       </c>
       <c r="D857" t="n">
-        <v>77.38495534511513</v>
+        <v>77.38494797267103</v>
       </c>
       <c r="E857" t="n">
-        <v>84.29380234355746</v>
+        <v>84.29379431290934</v>
       </c>
       <c r="F857" t="n">
         <v>1616980</v>
@@ -17732,16 +17732,16 @@
         <v>45741</v>
       </c>
       <c r="B866" t="n">
-        <v>82.01691436767578</v>
+        <v>82.01690673828125</v>
       </c>
       <c r="C866" t="n">
-        <v>84.42084065770479</v>
+        <v>84.42083280469173</v>
       </c>
       <c r="D866" t="n">
-        <v>80.61950924258466</v>
+        <v>80.61950174317984</v>
       </c>
       <c r="E866" t="n">
-        <v>83.08206551721464</v>
+        <v>83.0820577887374</v>
       </c>
       <c r="F866" t="n">
         <v>769467</v>
@@ -17752,16 +17752,16 @@
         <v>45742</v>
       </c>
       <c r="B867" t="n">
-        <v>82.81822204589844</v>
+        <v>82.81821441650391</v>
       </c>
       <c r="C867" t="n">
-        <v>83.15046856160603</v>
+        <v>83.15046090160423</v>
       </c>
       <c r="D867" t="n">
-        <v>81.10811126618962</v>
+        <v>81.10810379433421</v>
       </c>
       <c r="E867" t="n">
-        <v>81.59671434610642</v>
+        <v>81.59670682923984</v>
       </c>
       <c r="F867" t="n">
         <v>621808</v>
@@ -17792,16 +17792,16 @@
         <v>45744</v>
       </c>
       <c r="B869" t="n">
-        <v>83.47294616699219</v>
+        <v>83.47293853759766</v>
       </c>
       <c r="C869" t="n">
-        <v>83.74656269160093</v>
+        <v>83.74655503719795</v>
       </c>
       <c r="D869" t="n">
-        <v>80.22862210071933</v>
+        <v>80.22861476785475</v>
       </c>
       <c r="E869" t="n">
-        <v>81.59671217925415</v>
+        <v>81.59670472134668</v>
       </c>
       <c r="F869" t="n">
         <v>1013438</v>
@@ -17832,16 +17832,16 @@
         <v>45748</v>
       </c>
       <c r="B871" t="n">
-        <v>78.28398132324219</v>
+        <v>78.28398895263672</v>
       </c>
       <c r="C871" t="n">
-        <v>79.3882215330526</v>
+        <v>79.3882292700641</v>
       </c>
       <c r="D871" t="n">
-        <v>76.88657630102644</v>
+        <v>76.88658379423278</v>
       </c>
       <c r="E871" t="n">
-        <v>77.56085089626417</v>
+        <v>77.5608584551839</v>
       </c>
       <c r="F871" t="n">
         <v>960198</v>
@@ -17852,16 +17852,16 @@
         <v>45749</v>
       </c>
       <c r="B872" t="n">
-        <v>78.16670989990234</v>
+        <v>78.16671752929688</v>
       </c>
       <c r="C872" t="n">
-        <v>78.76280618720718</v>
+        <v>78.76281387478318</v>
       </c>
       <c r="D872" t="n">
-        <v>76.86703151877802</v>
+        <v>76.86703902131858</v>
       </c>
       <c r="E872" t="n">
-        <v>78.09830577458001</v>
+        <v>78.09831339729801</v>
       </c>
       <c r="F872" t="n">
         <v>373719</v>
@@ -17872,16 +17872,16 @@
         <v>45750</v>
       </c>
       <c r="B873" t="n">
-        <v>78.32307434082031</v>
+        <v>78.32306671142578</v>
       </c>
       <c r="C873" t="n">
-        <v>79.06575310166777</v>
+        <v>79.06574539992943</v>
       </c>
       <c r="D873" t="n">
-        <v>75.8214215294108</v>
+        <v>75.82141414370047</v>
       </c>
       <c r="E873" t="n">
-        <v>77.10156665445534</v>
+        <v>77.10155914404699</v>
       </c>
       <c r="F873" t="n">
         <v>721024</v>
@@ -17892,16 +17892,16 @@
         <v>45751</v>
       </c>
       <c r="B874" t="n">
-        <v>73.78883361816406</v>
+        <v>73.78884124755859</v>
       </c>
       <c r="C874" t="n">
-        <v>77.65856882284673</v>
+        <v>77.65857685235244</v>
       </c>
       <c r="D874" t="n">
-        <v>72.93866163963507</v>
+        <v>72.9386691811261</v>
       </c>
       <c r="E874" t="n">
-        <v>76.71067772684667</v>
+        <v>76.7106856583452</v>
       </c>
       <c r="F874" t="n">
         <v>1192804</v>
@@ -17912,16 +17912,16 @@
         <v>45754</v>
       </c>
       <c r="B875" t="n">
-        <v>73.09501647949219</v>
+        <v>73.09502410888672</v>
       </c>
       <c r="C875" t="n">
-        <v>76.01686051972106</v>
+        <v>76.01686845408716</v>
       </c>
       <c r="D875" t="n">
-        <v>70.59336388899551</v>
+        <v>70.59337125727656</v>
       </c>
       <c r="E875" t="n">
-        <v>72.17644039470501</v>
+        <v>72.17644792822188</v>
       </c>
       <c r="F875" t="n">
         <v>726435</v>
@@ -17932,16 +17932,16 @@
         <v>45755</v>
       </c>
       <c r="B876" t="n">
-        <v>75.0494384765625</v>
+        <v>75.04943084716797</v>
       </c>
       <c r="C876" t="n">
-        <v>77.47290565599279</v>
+        <v>77.47289778023283</v>
       </c>
       <c r="D876" t="n">
-        <v>74.10154727809095</v>
+        <v>74.10153974505738</v>
       </c>
       <c r="E876" t="n">
-        <v>76.22208292396535</v>
+        <v>76.22207517536182</v>
       </c>
       <c r="F876" t="n">
         <v>1315177</v>
@@ -18052,16 +18052,16 @@
         <v>45763</v>
       </c>
       <c r="B882" t="n">
-        <v>78.49897003173828</v>
+        <v>78.49896240234375</v>
       </c>
       <c r="C882" t="n">
-        <v>79.83773765524597</v>
+        <v>79.83772989573525</v>
       </c>
       <c r="D882" t="n">
-        <v>77.92241453950848</v>
+        <v>77.92240696614996</v>
       </c>
       <c r="E882" t="n">
-        <v>79.15369634801512</v>
+        <v>79.15368865498706</v>
       </c>
       <c r="F882" t="n">
         <v>449643</v>
@@ -18112,16 +18112,16 @@
         <v>45770</v>
       </c>
       <c r="B885" t="n">
-        <v>84.3328857421875</v>
+        <v>84.33289337158203</v>
       </c>
       <c r="C885" t="n">
-        <v>85.00715285211088</v>
+        <v>85.00716054250474</v>
       </c>
       <c r="D885" t="n">
-        <v>81.96804141692802</v>
+        <v>81.96804883238075</v>
       </c>
       <c r="E885" t="n">
-        <v>82.60322684538413</v>
+        <v>82.60323431830055</v>
       </c>
       <c r="F885" t="n">
         <v>698539</v>
@@ -18192,16 +18192,16 @@
         <v>45776</v>
       </c>
       <c r="B889" t="n">
-        <v>88.583740234375</v>
+        <v>88.58373260498047</v>
       </c>
       <c r="C889" t="n">
-        <v>90.62609753796141</v>
+        <v>90.62608973266609</v>
       </c>
       <c r="D889" t="n">
-        <v>88.583740234375</v>
+        <v>88.58373260498047</v>
       </c>
       <c r="E889" t="n">
-        <v>89.41436398245803</v>
+        <v>89.4143562815249</v>
       </c>
       <c r="F889" t="n">
         <v>288735</v>
@@ -18272,16 +18272,16 @@
         <v>45783</v>
       </c>
       <c r="B893" t="n">
-        <v>88.32966613769531</v>
+        <v>88.32965850830078</v>
       </c>
       <c r="C893" t="n">
-        <v>90.03000280574344</v>
+        <v>90.02999502948387</v>
       </c>
       <c r="D893" t="n">
-        <v>87.9485563233999</v>
+        <v>87.94854872692339</v>
       </c>
       <c r="E893" t="n">
-        <v>87.9485563233999</v>
+        <v>87.94854872692339</v>
       </c>
       <c r="F893" t="n">
         <v>191886</v>
@@ -18292,16 +18292,16 @@
         <v>45784</v>
       </c>
       <c r="B894" t="n">
-        <v>89.16028594970703</v>
+        <v>89.1602783203125</v>
       </c>
       <c r="C894" t="n">
-        <v>89.26777922133371</v>
+        <v>89.26777158274103</v>
       </c>
       <c r="D894" t="n">
-        <v>87.0983804019461</v>
+        <v>87.09837294898765</v>
       </c>
       <c r="E894" t="n">
-        <v>88.43715549507488</v>
+        <v>88.43714792755821</v>
       </c>
       <c r="F894" t="n">
         <v>251191</v>
@@ -18312,16 +18312,16 @@
         <v>45785</v>
       </c>
       <c r="B895" t="n">
-        <v>97.71083068847656</v>
+        <v>97.71083831787109</v>
       </c>
       <c r="C895" t="n">
-        <v>97.71083068847656</v>
+        <v>97.71083831787109</v>
       </c>
       <c r="D895" t="n">
-        <v>88.50555150219621</v>
+        <v>88.50555841283003</v>
       </c>
       <c r="E895" t="n">
-        <v>88.50555150219621</v>
+        <v>88.50555841283003</v>
       </c>
       <c r="F895" t="n">
         <v>1207326</v>
@@ -18332,16 +18332,16 @@
         <v>45786</v>
       </c>
       <c r="B896" t="n">
-        <v>98.40464782714844</v>
+        <v>98.40465545654297</v>
       </c>
       <c r="C896" t="n">
-        <v>99.0789223981929</v>
+        <v>99.07893007986451</v>
       </c>
       <c r="D896" t="n">
-        <v>97.23200353058388</v>
+        <v>97.23201106906231</v>
       </c>
       <c r="E896" t="n">
-        <v>97.67174327792293</v>
+        <v>97.67175085049476</v>
       </c>
       <c r="F896" t="n">
         <v>488440</v>
@@ -18372,16 +18372,16 @@
         <v>45790</v>
       </c>
       <c r="B898" t="n">
-        <v>101.4242248535156</v>
+        <v>101.4242172241211</v>
       </c>
       <c r="C898" t="n">
-        <v>102.2548485706747</v>
+        <v>102.2548408787985</v>
       </c>
       <c r="D898" t="n">
-        <v>99.1375586386342</v>
+        <v>99.13755118124867</v>
       </c>
       <c r="E898" t="n">
-        <v>99.62616170231497</v>
+        <v>99.62615420817545</v>
       </c>
       <c r="F898" t="n">
         <v>527476</v>
@@ -18392,16 +18392,16 @@
         <v>45791</v>
       </c>
       <c r="B899" t="n">
-        <v>103.1538696289062</v>
+        <v>103.1538772583008</v>
       </c>
       <c r="C899" t="n">
-        <v>104.561048745443</v>
+        <v>104.5610564789144</v>
       </c>
       <c r="D899" t="n">
-        <v>100.3590596921682</v>
+        <v>100.359067114855</v>
       </c>
       <c r="E899" t="n">
-        <v>101.3362657552098</v>
+        <v>101.3362732501719</v>
       </c>
       <c r="F899" t="n">
         <v>818733</v>
@@ -18432,16 +18432,16 @@
         <v>45793</v>
       </c>
       <c r="B901" t="n">
-        <v>103.593620300293</v>
+        <v>103.5936279296875</v>
       </c>
       <c r="C901" t="n">
-        <v>104.0235859126987</v>
+        <v>104.0235935737591</v>
       </c>
       <c r="D901" t="n">
-        <v>102.3721126805784</v>
+        <v>102.3721202200121</v>
       </c>
       <c r="E901" t="n">
-        <v>103.29068134087</v>
+        <v>103.2906889479539</v>
       </c>
       <c r="F901" t="n">
         <v>726672</v>
@@ -18452,16 +18452,16 @@
         <v>45796</v>
       </c>
       <c r="B902" t="n">
-        <v>102.2157592773438</v>
+        <v>102.2157516479492</v>
       </c>
       <c r="C902" t="n">
-        <v>103.7499725967766</v>
+        <v>103.7499648528683</v>
       </c>
       <c r="D902" t="n">
-        <v>101.6685262326006</v>
+        <v>101.6685186440516</v>
       </c>
       <c r="E902" t="n">
-        <v>103.5643085025908</v>
+        <v>103.5643007725404</v>
       </c>
       <c r="F902" t="n">
         <v>1026194</v>
@@ -18512,16 +18512,16 @@
         <v>45799</v>
       </c>
       <c r="B905" t="n">
-        <v>103.8770065307617</v>
+        <v>103.8770141601562</v>
       </c>
       <c r="C905" t="n">
-        <v>104.6099110713208</v>
+        <v>104.6099187545445</v>
       </c>
       <c r="D905" t="n">
-        <v>102.3232450279215</v>
+        <v>102.3232525431978</v>
       </c>
       <c r="E905" t="n">
-        <v>103.5838417323419</v>
+        <v>103.5838493402045</v>
       </c>
       <c r="F905" t="n">
         <v>1088124</v>
@@ -18532,16 +18532,16 @@
         <v>45800</v>
       </c>
       <c r="B906" t="n">
-        <v>103.2906799316406</v>
+        <v>103.2906875610352</v>
       </c>
       <c r="C906" t="n">
-        <v>104.3851534279493</v>
+        <v>104.3851611381853</v>
       </c>
       <c r="D906" t="n">
-        <v>100.8769871706277</v>
+        <v>100.8769946217388</v>
       </c>
       <c r="E906" t="n">
-        <v>102.7043577732752</v>
+        <v>102.704365359362</v>
       </c>
       <c r="F906" t="n">
         <v>895232</v>
@@ -18552,16 +18552,16 @@
         <v>45803</v>
       </c>
       <c r="B907" t="n">
-        <v>103.798828125</v>
+        <v>103.7988357543945</v>
       </c>
       <c r="C907" t="n">
-        <v>104.6587667675181</v>
+        <v>104.6587744601196</v>
       </c>
       <c r="D907" t="n">
-        <v>102.997519459895</v>
+        <v>102.997527030392</v>
       </c>
       <c r="E907" t="n">
-        <v>102.997519459895</v>
+        <v>102.997527030392</v>
       </c>
       <c r="F907" t="n">
         <v>188218</v>
@@ -18612,16 +18612,16 @@
         <v>45806</v>
       </c>
       <c r="B910" t="n">
-        <v>107.2679061889648</v>
+        <v>107.2679138183594</v>
       </c>
       <c r="C910" t="n">
-        <v>108.8021194087094</v>
+        <v>108.8021271472243</v>
       </c>
       <c r="D910" t="n">
-        <v>106.3981933898703</v>
+        <v>106.3982009574068</v>
       </c>
       <c r="E910" t="n">
-        <v>108.2353455586916</v>
+        <v>108.235353256895</v>
       </c>
       <c r="F910" t="n">
         <v>645105</v>
@@ -18652,16 +18652,16 @@
         <v>45810</v>
       </c>
       <c r="B912" t="n">
-        <v>107.4047317504883</v>
+        <v>107.4047241210938</v>
       </c>
       <c r="C912" t="n">
-        <v>109.2027874916251</v>
+        <v>109.2027797345073</v>
       </c>
       <c r="D912" t="n">
-        <v>106.7402312688744</v>
+        <v>106.740223686682</v>
       </c>
       <c r="E912" t="n">
-        <v>108.5480611590693</v>
+        <v>108.5480534484594</v>
       </c>
       <c r="F912" t="n">
         <v>325434</v>
@@ -18712,16 +18712,16 @@
         <v>45813</v>
       </c>
       <c r="B915" t="n">
-        <v>108.3917007446289</v>
+        <v>108.3916931152344</v>
       </c>
       <c r="C915" t="n">
-        <v>108.7532696920168</v>
+        <v>108.7532620371724</v>
       </c>
       <c r="D915" t="n">
-        <v>107.0529331354047</v>
+        <v>107.0529256002424</v>
       </c>
       <c r="E915" t="n">
-        <v>107.8835568440347</v>
+        <v>107.8835492504071</v>
       </c>
       <c r="F915" t="n">
         <v>989620</v>
@@ -18732,16 +18732,16 @@
         <v>45814</v>
       </c>
       <c r="B916" t="n">
-        <v>107.5513076782227</v>
+        <v>107.5513000488281</v>
       </c>
       <c r="C916" t="n">
-        <v>108.9584869356147</v>
+        <v>108.9584792063988</v>
       </c>
       <c r="D916" t="n">
-        <v>106.4861565415238</v>
+        <v>106.4861489876882</v>
       </c>
       <c r="E916" t="n">
-        <v>108.3721647301985</v>
+        <v>108.3721570425746</v>
       </c>
       <c r="F916" t="n">
         <v>400888</v>
@@ -18752,16 +18752,16 @@
         <v>45817</v>
       </c>
       <c r="B917" t="n">
-        <v>106.2809371948242</v>
+        <v>106.2809448242188</v>
       </c>
       <c r="C917" t="n">
-        <v>108.2744385273175</v>
+        <v>108.2744462998158</v>
       </c>
       <c r="D917" t="n">
-        <v>105.772785849321</v>
+        <v>105.7727934422378</v>
       </c>
       <c r="E917" t="n">
-        <v>107.1995058562494</v>
+        <v>107.1995135515835</v>
       </c>
       <c r="F917" t="n">
         <v>436201</v>
@@ -18772,16 +18772,16 @@
         <v>45818</v>
       </c>
       <c r="B918" t="n">
-        <v>108.6848678588867</v>
+        <v>108.6848602294922</v>
       </c>
       <c r="C918" t="n">
-        <v>109.7109298304698</v>
+        <v>109.7109221290484</v>
       </c>
       <c r="D918" t="n">
-        <v>106.8086338632852</v>
+        <v>106.8086263655974</v>
       </c>
       <c r="E918" t="n">
-        <v>106.8086338632852</v>
+        <v>106.8086263655974</v>
       </c>
       <c r="F918" t="n">
         <v>299047</v>
@@ -18872,16 +18872,16 @@
         <v>45825</v>
       </c>
       <c r="B923" t="n">
-        <v>107.5903930664062</v>
+        <v>107.5903854370117</v>
       </c>
       <c r="C923" t="n">
-        <v>107.8444687469043</v>
+        <v>107.8444610994928</v>
       </c>
       <c r="D923" t="n">
-        <v>105.7630223808585</v>
+        <v>105.7630148810455</v>
       </c>
       <c r="E923" t="n">
-        <v>107.7858387650551</v>
+        <v>107.7858311218013</v>
       </c>
       <c r="F923" t="n">
         <v>359643</v>
@@ -18892,16 +18892,16 @@
         <v>45826</v>
       </c>
       <c r="B924" t="n">
-        <v>106.9845275878906</v>
+        <v>106.9845352172852</v>
       </c>
       <c r="C924" t="n">
-        <v>107.6881097204315</v>
+        <v>107.6881174000007</v>
       </c>
       <c r="D924" t="n">
-        <v>105.8314240865031</v>
+        <v>105.8314316336663</v>
       </c>
       <c r="E924" t="n">
-        <v>107.0040684295622</v>
+        <v>107.0040760603503</v>
       </c>
       <c r="F924" t="n">
         <v>439989</v>
@@ -18912,16 +18912,16 @@
         <v>45828</v>
       </c>
       <c r="B925" t="n">
-        <v>104.7076416015625</v>
+        <v>104.707633972168</v>
       </c>
       <c r="C925" t="n">
-        <v>107.0040745879219</v>
+        <v>107.0040667912006</v>
       </c>
       <c r="D925" t="n">
-        <v>104.629463319395</v>
+        <v>104.6294556956968</v>
       </c>
       <c r="E925" t="n">
-        <v>107.0040745879219</v>
+        <v>107.0040667912006</v>
       </c>
       <c r="F925" t="n">
         <v>336419</v>
@@ -18952,16 +18952,16 @@
         <v>45832</v>
       </c>
       <c r="B927" t="n">
-        <v>103.593620300293</v>
+        <v>103.5936279296875</v>
       </c>
       <c r="C927" t="n">
-        <v>106.0854913712162</v>
+        <v>106.0854991841304</v>
       </c>
       <c r="D927" t="n">
-        <v>103.1050172524071</v>
+        <v>103.1050248458173</v>
       </c>
       <c r="E927" t="n">
-        <v>103.1050172524071</v>
+        <v>103.1050248458173</v>
       </c>
       <c r="F927" t="n">
         <v>471744</v>
@@ -19072,16 +19072,16 @@
         <v>45840</v>
       </c>
       <c r="B933" t="n">
-        <v>103.3004531860352</v>
+        <v>103.3004608154297</v>
       </c>
       <c r="C933" t="n">
-        <v>106.0952631540645</v>
+        <v>106.0952709898735</v>
       </c>
       <c r="D933" t="n">
-        <v>103.2418232073532</v>
+        <v>103.2418308324176</v>
       </c>
       <c r="E933" t="n">
-        <v>106.0561740164463</v>
+        <v>106.0561818493683</v>
       </c>
       <c r="F933" t="n">
         <v>463221</v>
@@ -19112,16 +19112,16 @@
         <v>45842</v>
       </c>
       <c r="B935" t="n">
-        <v>103.593620300293</v>
+        <v>103.5936279296875</v>
       </c>
       <c r="C935" t="n">
-        <v>104.736949643028</v>
+        <v>104.7369573566257</v>
       </c>
       <c r="D935" t="n">
-        <v>102.899804866954</v>
+        <v>102.8998124452508</v>
       </c>
       <c r="E935" t="n">
-        <v>102.9095715599583</v>
+        <v>102.9095791389745</v>
       </c>
       <c r="F935" t="n">
         <v>75389</v>
@@ -19132,16 +19132,16 @@
         <v>45845</v>
       </c>
       <c r="B936" t="n">
-        <v>104.4535675048828</v>
+        <v>104.4535598754883</v>
       </c>
       <c r="C936" t="n">
-        <v>104.8444514661891</v>
+        <v>104.844443808244</v>
       </c>
       <c r="D936" t="n">
-        <v>103.5740804558166</v>
+        <v>103.5740728906607</v>
       </c>
       <c r="E936" t="n">
-        <v>104.3167592367493</v>
+        <v>104.3167516173474</v>
       </c>
       <c r="F936" t="n">
         <v>614814</v>
@@ -19152,16 +19152,16 @@
         <v>45846</v>
       </c>
       <c r="B937" t="n">
-        <v>102.8998031616211</v>
+        <v>102.8998107910156</v>
       </c>
       <c r="C937" t="n">
-        <v>104.9323861409677</v>
+        <v>104.9323939210659</v>
       </c>
       <c r="D937" t="n">
-        <v>102.616412503885</v>
+        <v>102.6164201122678</v>
       </c>
       <c r="E937" t="n">
-        <v>103.5936185834616</v>
+        <v>103.5936262642984</v>
       </c>
       <c r="F937" t="n">
         <v>319689</v>
@@ -19192,16 +19192,16 @@
         <v>45848</v>
       </c>
       <c r="B939" t="n">
-        <v>100.8379058837891</v>
+        <v>100.8378982543945</v>
       </c>
       <c r="C939" t="n">
-        <v>103.2222838408521</v>
+        <v>103.2222760310556</v>
       </c>
       <c r="D939" t="n">
-        <v>99.47958991988082</v>
+        <v>99.47958239325645</v>
       </c>
       <c r="E939" t="n">
-        <v>102.8802631764672</v>
+        <v>102.8802553925479</v>
       </c>
       <c r="F939" t="n">
         <v>532452</v>
@@ -19232,16 +19232,16 @@
         <v>45852</v>
       </c>
       <c r="B941" t="n">
-        <v>98.11148834228516</v>
+        <v>98.11149597167969</v>
       </c>
       <c r="C941" t="n">
-        <v>99.43071501103869</v>
+        <v>99.43072274301957</v>
       </c>
       <c r="D941" t="n">
-        <v>97.74991942190482</v>
+        <v>97.74992702318283</v>
       </c>
       <c r="E941" t="n">
-        <v>98.94211198887142</v>
+        <v>98.94211968285731</v>
       </c>
       <c r="F941" t="n">
         <v>223357</v>
@@ -19252,16 +19252,16 @@
         <v>45853</v>
       </c>
       <c r="B942" t="n">
-        <v>98.70758819580078</v>
+        <v>98.70759582519531</v>
       </c>
       <c r="C942" t="n">
-        <v>99.33299949035536</v>
+        <v>99.33300716808975</v>
       </c>
       <c r="D942" t="n">
-        <v>97.82810123299254</v>
+        <v>97.82810879440898</v>
       </c>
       <c r="E942" t="n">
-        <v>98.12126603909219</v>
+        <v>98.12127362316819</v>
       </c>
       <c r="F942" t="n">
         <v>259679</v>
@@ -19272,16 +19272,16 @@
         <v>45854</v>
       </c>
       <c r="B943" t="n">
-        <v>99.80205535888672</v>
+        <v>99.80206298828125</v>
       </c>
       <c r="C943" t="n">
-        <v>100.0365901886073</v>
+        <v>100.0365978359309</v>
       </c>
       <c r="D943" t="n">
-        <v>97.96491059235345</v>
+        <v>97.96491808130695</v>
       </c>
       <c r="E943" t="n">
-        <v>98.71735600177402</v>
+        <v>98.71736354824841</v>
       </c>
       <c r="F943" t="n">
         <v>444283</v>
@@ -19332,16 +19332,16 @@
         <v>45859</v>
       </c>
       <c r="B946" t="n">
-        <v>92.297119140625</v>
+        <v>92.29711151123047</v>
       </c>
       <c r="C946" t="n">
-        <v>93.63589426831037</v>
+        <v>93.63588652825102</v>
       </c>
       <c r="D946" t="n">
-        <v>91.88669434136077</v>
+        <v>91.88668674589246</v>
       </c>
       <c r="E946" t="n">
-        <v>93.03002376309314</v>
+        <v>93.0300160731158</v>
       </c>
       <c r="F946" t="n">
         <v>459254</v>
@@ -19372,16 +19372,16 @@
         <v>45861</v>
       </c>
       <c r="B948" t="n">
-        <v>91.75965881347656</v>
+        <v>91.75965118408203</v>
       </c>
       <c r="C948" t="n">
-        <v>92.32644016878999</v>
+        <v>92.32643249227019</v>
       </c>
       <c r="D948" t="n">
-        <v>91.07561003639412</v>
+        <v>91.0756024638751</v>
       </c>
       <c r="E948" t="n">
-        <v>92.26780273015984</v>
+        <v>92.26779505851549</v>
       </c>
       <c r="F948" t="n">
         <v>201915</v>
@@ -19392,16 +19392,16 @@
         <v>45862</v>
       </c>
       <c r="B949" t="n">
-        <v>90.00068664550781</v>
+        <v>90.00067901611328</v>
       </c>
       <c r="C949" t="n">
-        <v>92.03327726570676</v>
+        <v>92.0332694640087</v>
       </c>
       <c r="D949" t="n">
-        <v>89.64889182833909</v>
+        <v>89.64888422876635</v>
       </c>
       <c r="E949" t="n">
-        <v>92.03327726570676</v>
+        <v>92.0332694640087</v>
       </c>
       <c r="F949" t="n">
         <v>148443</v>
@@ -19412,16 +19412,16 @@
         <v>45863</v>
       </c>
       <c r="B950" t="n">
-        <v>89.61956787109375</v>
+        <v>89.61957550048828</v>
       </c>
       <c r="C950" t="n">
-        <v>90.68472636527164</v>
+        <v>90.68473408534409</v>
       </c>
       <c r="D950" t="n">
-        <v>89.27754723736346</v>
+        <v>89.27755483764147</v>
       </c>
       <c r="E950" t="n">
-        <v>89.46321877659875</v>
+        <v>89.46322639268315</v>
       </c>
       <c r="F950" t="n">
         <v>133512</v>
@@ -19572,16 +19572,16 @@
         <v>45875</v>
       </c>
       <c r="B958" t="n">
-        <v>91.05606842041016</v>
+        <v>91.05606079101562</v>
       </c>
       <c r="C958" t="n">
-        <v>91.3101441043393</v>
+        <v>91.3101364536563</v>
       </c>
       <c r="D958" t="n">
-        <v>90.09840312282569</v>
+        <v>90.09839557367191</v>
       </c>
       <c r="E958" t="n">
-        <v>90.09840312282569</v>
+        <v>90.09839557367191</v>
       </c>
       <c r="F958" t="n">
         <v>142081</v>
@@ -19752,16 +19752,16 @@
         <v>45888</v>
       </c>
       <c r="B967" t="n">
-        <v>85.65211486816406</v>
+        <v>85.65212249755859</v>
       </c>
       <c r="C967" t="n">
-        <v>90.97788505088515</v>
+        <v>90.97789315466845</v>
       </c>
       <c r="D967" t="n">
-        <v>85.40781334683759</v>
+        <v>85.40782095447115</v>
       </c>
       <c r="E967" t="n">
-        <v>90.97788505088515</v>
+        <v>90.97789315466845</v>
       </c>
       <c r="F967" t="n">
         <v>1451209</v>
@@ -19772,16 +19772,16 @@
         <v>45889</v>
       </c>
       <c r="B968" t="n">
-        <v>86.38502502441406</v>
+        <v>86.38501739501953</v>
       </c>
       <c r="C968" t="n">
-        <v>87.58698441207628</v>
+        <v>87.58697667652652</v>
       </c>
       <c r="D968" t="n">
-        <v>85.41759302487036</v>
+        <v>85.41758548091796</v>
       </c>
       <c r="E968" t="n">
-        <v>86.15049763629555</v>
+        <v>86.15049002761413</v>
       </c>
       <c r="F968" t="n">
         <v>1048687</v>
@@ -19832,16 +19832,16 @@
         <v>45894</v>
       </c>
       <c r="B971" t="n">
-        <v>88.92575073242188</v>
+        <v>88.92575836181641</v>
       </c>
       <c r="C971" t="n">
-        <v>89.54138786120821</v>
+        <v>89.5413955434214</v>
       </c>
       <c r="D971" t="n">
-        <v>87.15701016405045</v>
+        <v>87.15701764169569</v>
       </c>
       <c r="E971" t="n">
-        <v>87.15701016405045</v>
+        <v>87.15701764169569</v>
       </c>
       <c r="F971" t="n">
         <v>788338</v>
@@ -19872,16 +19872,16 @@
         <v>45896</v>
       </c>
       <c r="B973" t="n">
-        <v>90.80199432373047</v>
+        <v>90.80198669433594</v>
       </c>
       <c r="C973" t="n">
-        <v>90.80199432373047</v>
+        <v>90.80198669433594</v>
       </c>
       <c r="D973" t="n">
-        <v>88.61305461947694</v>
+        <v>88.61304717400222</v>
       </c>
       <c r="E973" t="n">
-        <v>88.91598614240509</v>
+        <v>88.91597867147736</v>
       </c>
       <c r="F973" t="n">
         <v>1220015</v>
@@ -19932,16 +19932,16 @@
         <v>45901</v>
       </c>
       <c r="B976" t="n">
-        <v>96.010498046875</v>
+        <v>96.01050567626953</v>
       </c>
       <c r="C976" t="n">
-        <v>96.44047111090812</v>
+        <v>96.44047877447011</v>
       </c>
       <c r="D976" t="n">
-        <v>95.27759348163168</v>
+        <v>95.27760105278657</v>
       </c>
       <c r="E976" t="n">
-        <v>95.287367630039</v>
+        <v>95.28737520197058</v>
       </c>
       <c r="F976" t="n">
         <v>152929</v>
@@ -19952,16 +19952,16 @@
         <v>45902</v>
       </c>
       <c r="B977" t="n">
-        <v>95.76620483398438</v>
+        <v>95.76619720458984</v>
       </c>
       <c r="C977" t="n">
-        <v>95.76620483398438</v>
+        <v>95.76619720458984</v>
       </c>
       <c r="D977" t="n">
-        <v>93.71407336435442</v>
+        <v>93.7140658984468</v>
       </c>
       <c r="E977" t="n">
-        <v>95.75643068472903</v>
+        <v>95.75642305611316</v>
       </c>
       <c r="F977" t="n">
         <v>684271</v>
@@ -19972,16 +19972,16 @@
         <v>45903</v>
       </c>
       <c r="B978" t="n">
-        <v>95.60984039306641</v>
+        <v>95.60984802246094</v>
       </c>
       <c r="C978" t="n">
-        <v>96.16685502237223</v>
+        <v>96.16686269621496</v>
       </c>
       <c r="D978" t="n">
-        <v>94.76945001360953</v>
+        <v>94.76945757594329</v>
       </c>
       <c r="E978" t="n">
-        <v>95.75642279785789</v>
+        <v>95.75643043894929</v>
       </c>
       <c r="F978" t="n">
         <v>439208</v>
@@ -20052,16 +20052,16 @@
         <v>45909</v>
       </c>
       <c r="B982" t="n">
-        <v>96.98770141601562</v>
+        <v>96.98770904541016</v>
       </c>
       <c r="C982" t="n">
-        <v>99.08869593526924</v>
+        <v>99.0887037299354</v>
       </c>
       <c r="D982" t="n">
-        <v>96.87043400488615</v>
+        <v>96.87044162505602</v>
       </c>
       <c r="E982" t="n">
-        <v>97.86718836076022</v>
+        <v>97.8671960593383</v>
       </c>
       <c r="F982" t="n">
         <v>316824</v>
@@ -20112,16 +20112,16 @@
         <v>45912</v>
       </c>
       <c r="B985" t="n">
-        <v>98.69781494140625</v>
+        <v>98.69782257080078</v>
       </c>
       <c r="C985" t="n">
-        <v>100.2027132123995</v>
+        <v>100.2027209581235</v>
       </c>
       <c r="D985" t="n">
-        <v>97.80855382220949</v>
+        <v>97.80856138286366</v>
       </c>
       <c r="E985" t="n">
-        <v>99.11801385769326</v>
+        <v>99.1180215195694</v>
       </c>
       <c r="F985" t="n">
         <v>599879</v>
@@ -20132,16 +20132,16 @@
         <v>45915</v>
       </c>
       <c r="B986" t="n">
-        <v>98.02354431152344</v>
+        <v>98.02353668212891</v>
       </c>
       <c r="C986" t="n">
-        <v>99.64571006259945</v>
+        <v>99.6457023069481</v>
       </c>
       <c r="D986" t="n">
-        <v>97.52517455420922</v>
+        <v>97.52516696360394</v>
       </c>
       <c r="E986" t="n">
-        <v>98.69781892558407</v>
+        <v>98.69781124370924</v>
       </c>
       <c r="F986" t="n">
         <v>461876</v>
@@ -20152,16 +20152,16 @@
         <v>45916</v>
       </c>
       <c r="B987" t="n">
-        <v>99.60661315917969</v>
+        <v>99.60662078857422</v>
       </c>
       <c r="C987" t="n">
-        <v>100.4861000969065</v>
+        <v>100.4861077936656</v>
       </c>
       <c r="D987" t="n">
-        <v>97.60333777077366</v>
+        <v>97.60334524672678</v>
       </c>
       <c r="E987" t="n">
-        <v>98.11148909278937</v>
+        <v>98.11149660766448</v>
       </c>
       <c r="F987" t="n">
         <v>502898</v>
@@ -20172,16 +20172,16 @@
         <v>45917</v>
       </c>
       <c r="B988" t="n">
-        <v>102.8998031616211</v>
+        <v>102.8998107910156</v>
       </c>
       <c r="C988" t="n">
-        <v>104.8444411724413</v>
+        <v>104.8444489460189</v>
       </c>
       <c r="D988" t="n">
-        <v>98.74667732342019</v>
+        <v>98.7466846448857</v>
       </c>
       <c r="E988" t="n">
-        <v>99.22550621487537</v>
+        <v>99.22551357184312</v>
       </c>
       <c r="F988" t="n">
         <v>607209</v>
@@ -20192,16 +20192,16 @@
         <v>45918</v>
       </c>
       <c r="B989" t="n">
-        <v>104.0919876098633</v>
+        <v>104.0919952392578</v>
       </c>
       <c r="C989" t="n">
-        <v>104.7858104824872</v>
+        <v>104.7858181627353</v>
       </c>
       <c r="D989" t="n">
-        <v>102.0691713370833</v>
+        <v>102.069178818216</v>
       </c>
       <c r="E989" t="n">
-        <v>103.5936178806138</v>
+        <v>103.5936254734804</v>
       </c>
       <c r="F989" t="n">
         <v>323487</v>
@@ -20212,16 +20212,16 @@
         <v>45919</v>
       </c>
       <c r="B990" t="n">
-        <v>102.1180419921875</v>
+        <v>102.118034362793</v>
       </c>
       <c r="C990" t="n">
-        <v>105.0203454311598</v>
+        <v>105.0203375849298</v>
       </c>
       <c r="D990" t="n">
-        <v>101.4437673674388</v>
+        <v>101.4437597884204</v>
       </c>
       <c r="E990" t="n">
-        <v>104.3753857978366</v>
+        <v>104.3753779997924</v>
       </c>
       <c r="F990" t="n">
         <v>805829</v>
@@ -20252,16 +20252,16 @@
         <v>45923</v>
       </c>
       <c r="B992" t="n">
-        <v>101.2385559082031</v>
+        <v>101.2385482788086</v>
       </c>
       <c r="C992" t="n">
-        <v>102.5577827229838</v>
+        <v>102.5577749941716</v>
       </c>
       <c r="D992" t="n">
-        <v>100.4079321696739</v>
+        <v>100.4079246028757</v>
       </c>
       <c r="E992" t="n">
-        <v>101.2287817591405</v>
+        <v>101.2287741304826</v>
       </c>
       <c r="F992" t="n">
         <v>578829</v>
@@ -20372,16 +20372,16 @@
         <v>45931</v>
       </c>
       <c r="B998" t="n">
-        <v>95.22872924804688</v>
+        <v>95.22873687744141</v>
       </c>
       <c r="C998" t="n">
-        <v>99.3623142353271</v>
+        <v>99.3623221958901</v>
       </c>
       <c r="D998" t="n">
-        <v>95.01375017365902</v>
+        <v>95.01375778583019</v>
       </c>
       <c r="E998" t="n">
-        <v>97.5544844834704</v>
+        <v>97.55449229919635</v>
       </c>
       <c r="F998" t="n">
         <v>911140</v>
@@ -20392,16 +20392,16 @@
         <v>45932</v>
       </c>
       <c r="B999" t="n">
-        <v>92.09189605712891</v>
+        <v>92.09190368652344</v>
       </c>
       <c r="C999" t="n">
-        <v>96.53818656647101</v>
+        <v>96.53819456422049</v>
       </c>
       <c r="D999" t="n">
-        <v>91.47625892965451</v>
+        <v>91.47626650804631</v>
       </c>
       <c r="E999" t="n">
-        <v>95.22872658272024</v>
+        <v>95.22873447198691</v>
       </c>
       <c r="F999" t="n">
         <v>1326713</v>
@@ -20452,16 +20452,16 @@
         <v>45937</v>
       </c>
       <c r="B1002" t="n">
-        <v>85.994140625</v>
+        <v>85.99413299560547</v>
       </c>
       <c r="C1002" t="n">
-        <v>88.49578596651554</v>
+        <v>88.4957781151752</v>
       </c>
       <c r="D1002" t="n">
-        <v>85.55440084263682</v>
+        <v>85.55439325225598</v>
       </c>
       <c r="E1002" t="n">
-        <v>88.24171773716807</v>
+        <v>88.24170990836865</v>
       </c>
       <c r="F1002" t="n">
         <v>845675</v>
@@ -20512,16 +20512,16 @@
         <v>45940</v>
       </c>
       <c r="B1005" t="n">
-        <v>85.34917449951172</v>
+        <v>85.34918212890625</v>
       </c>
       <c r="C1005" t="n">
-        <v>86.7465794765927</v>
+        <v>86.74658723090178</v>
       </c>
       <c r="D1005" t="n">
-        <v>84.66513323331431</v>
+        <v>84.66514080156213</v>
       </c>
       <c r="E1005" t="n">
-        <v>85.31009281757814</v>
+        <v>85.31010044347914</v>
       </c>
       <c r="F1005" t="n">
         <v>848390</v>
@@ -20572,16 +20572,16 @@
         <v>45945</v>
       </c>
       <c r="B1008" t="n">
-        <v>88.33943176269531</v>
+        <v>88.33943939208984</v>
       </c>
       <c r="C1008" t="n">
-        <v>89.01369889304345</v>
+        <v>89.01370658067076</v>
       </c>
       <c r="D1008" t="n">
-        <v>85.47621762934537</v>
+        <v>85.47622501145973</v>
       </c>
       <c r="E1008" t="n">
-        <v>85.85732740686544</v>
+        <v>85.85733482189416</v>
       </c>
       <c r="F1008" t="n">
         <v>892096</v>
@@ -20672,16 +20672,16 @@
         <v>45952</v>
       </c>
       <c r="B1013" t="n">
-        <v>88.34920501708984</v>
+        <v>88.34921264648438</v>
       </c>
       <c r="C1013" t="n">
-        <v>90.32315801259118</v>
+        <v>90.32316581244639</v>
       </c>
       <c r="D1013" t="n">
-        <v>88.0658143600468</v>
+        <v>88.06582196496913</v>
       </c>
       <c r="E1013" t="n">
-        <v>89.41435606258787</v>
+        <v>89.41436378396349</v>
       </c>
       <c r="F1013" t="n">
         <v>342955</v>
@@ -20812,16 +20812,16 @@
         <v>45961</v>
       </c>
       <c r="B1020" t="n">
-        <v>95.01374816894531</v>
+        <v>95.01375579833984</v>
       </c>
       <c r="C1020" t="n">
-        <v>95.64892614137838</v>
+        <v>95.64893382177631</v>
       </c>
       <c r="D1020" t="n">
-        <v>94.12448707875414</v>
+        <v>94.12449463674297</v>
       </c>
       <c r="E1020" t="n">
-        <v>94.39810358173895</v>
+        <v>94.39811116169858</v>
       </c>
       <c r="F1020" t="n">
         <v>181142</v>
@@ -20872,16 +20872,16 @@
         <v>45966</v>
       </c>
       <c r="B1023" t="n">
-        <v>96.762939453125</v>
+        <v>96.76294708251953</v>
       </c>
       <c r="C1023" t="n">
-        <v>97.71083051119773</v>
+        <v>97.7108382153299</v>
       </c>
       <c r="D1023" t="n">
-        <v>95.01374719055691</v>
+        <v>95.0137546820342</v>
       </c>
       <c r="E1023" t="n">
-        <v>95.33621951975952</v>
+        <v>95.33622703666254</v>
       </c>
       <c r="F1023" t="n">
         <v>404214</v>
@@ -20892,16 +20892,16 @@
         <v>45967</v>
       </c>
       <c r="B1024" t="n">
-        <v>97.85741424560547</v>
+        <v>97.857421875</v>
       </c>
       <c r="C1024" t="n">
-        <v>98.36556557184718</v>
+        <v>98.36557324085943</v>
       </c>
       <c r="D1024" t="n">
-        <v>96.37206431491778</v>
+        <v>96.3720718285079</v>
       </c>
       <c r="E1024" t="n">
-        <v>96.76294077449994</v>
+        <v>96.76294831856451</v>
       </c>
       <c r="F1024" t="n">
         <v>244412</v>
@@ -20972,16 +20972,16 @@
         <v>45973</v>
       </c>
       <c r="B1028" t="n">
-        <v>99.68479156494141</v>
+        <v>99.68479919433594</v>
       </c>
       <c r="C1028" t="n">
-        <v>103.0659236140314</v>
+        <v>103.0659315022015</v>
       </c>
       <c r="D1028" t="n">
-        <v>98.06262593814901</v>
+        <v>98.06263344339078</v>
       </c>
       <c r="E1028" t="n">
-        <v>101.6294295230862</v>
+        <v>101.629437301314</v>
       </c>
       <c r="F1028" t="n">
         <v>452005</v>
@@ -21032,16 +21032,16 @@
         <v>45978</v>
       </c>
       <c r="B1031" t="n">
-        <v>94.49583435058594</v>
+        <v>94.49582672119141</v>
       </c>
       <c r="C1031" t="n">
-        <v>97.72061771745865</v>
+        <v>97.72060982770191</v>
       </c>
       <c r="D1031" t="n">
-        <v>94.08540954549056</v>
+        <v>94.08540194923286</v>
       </c>
       <c r="E1031" t="n">
-        <v>96.85090481621259</v>
+        <v>96.85089699667463</v>
       </c>
       <c r="F1031" t="n">
         <v>742213</v>
@@ -21132,16 +21132,16 @@
         <v>45986</v>
       </c>
       <c r="B1036" t="n">
-        <v>95.0723876953125</v>
+        <v>95.07238006591797</v>
       </c>
       <c r="C1036" t="n">
-        <v>95.32646338309848</v>
+        <v>95.32645573331483</v>
       </c>
       <c r="D1036" t="n">
-        <v>93.23524280826224</v>
+        <v>93.23523532629541</v>
       </c>
       <c r="E1036" t="n">
-        <v>93.61635261219558</v>
+        <v>93.61634509964536</v>
       </c>
       <c r="F1036" t="n">
         <v>322148</v>
@@ -21292,16 +21292,16 @@
         <v>45996</v>
       </c>
       <c r="B1044" t="n">
-        <v>95.47303771972656</v>
+        <v>95.47303009033203</v>
       </c>
       <c r="C1044" t="n">
-        <v>104.336297187796</v>
+        <v>104.336288850125</v>
       </c>
       <c r="D1044" t="n">
-        <v>94.21244834908003</v>
+        <v>94.21244082042111</v>
       </c>
       <c r="E1044" t="n">
-        <v>101.6392135860741</v>
+        <v>101.6392054639311</v>
       </c>
       <c r="F1044" t="n">
         <v>1178496</v>
@@ -24489,102 +24489,102 @@
     </row>
     <row r="1204">
       <c r="A1204" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B1204" t="n">
-        <v>86.55999755859375</v>
+        <v>86.75</v>
       </c>
       <c r="C1204" t="n">
-        <v>87</v>
+        <v>87.69999694824219</v>
       </c>
       <c r="D1204" t="n">
-        <v>86.19000244140625</v>
+        <v>85.91999816894531</v>
       </c>
       <c r="E1204" t="n">
-        <v>86.30999755859375</v>
+        <v>86.40000152587891</v>
       </c>
       <c r="F1204" t="n">
-        <v>256130</v>
+        <v>302511</v>
       </c>
     </row>
     <row r="1205">
       <c r="A1205" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B1205" t="n">
-        <v>86.75</v>
+        <v>87.19999694824219</v>
       </c>
       <c r="C1205" t="n">
-        <v>87.69999694824219</v>
+        <v>88.87999725341797</v>
       </c>
       <c r="D1205" t="n">
-        <v>85.91999816894531</v>
+        <v>86.55000305175781</v>
       </c>
       <c r="E1205" t="n">
-        <v>86.40000152587891</v>
+        <v>87.08999633789062</v>
       </c>
       <c r="F1205" t="n">
-        <v>302511</v>
+        <v>395841</v>
       </c>
     </row>
     <row r="1206">
       <c r="A1206" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B1206" t="n">
-        <v>87.19999694824219</v>
+        <v>88.20999908447266</v>
       </c>
       <c r="C1206" t="n">
-        <v>88.87999725341797</v>
+        <v>88.69999694824219</v>
       </c>
       <c r="D1206" t="n">
-        <v>86.55000305175781</v>
+        <v>86.61000061035156</v>
       </c>
       <c r="E1206" t="n">
-        <v>87.08999633789062</v>
+        <v>86.61000061035156</v>
       </c>
       <c r="F1206" t="n">
-        <v>395841</v>
+        <v>496669</v>
       </c>
     </row>
     <row r="1207">
       <c r="A1207" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B1207" t="n">
-        <v>88.20999908447266</v>
+        <v>85.23999786376953</v>
       </c>
       <c r="C1207" t="n">
-        <v>88.69999694824219</v>
+        <v>87.83999633789062</v>
       </c>
       <c r="D1207" t="n">
-        <v>86.61000061035156</v>
+        <v>85.04000091552734</v>
       </c>
       <c r="E1207" t="n">
-        <v>86.61000061035156</v>
+        <v>87.22000122070312</v>
       </c>
       <c r="F1207" t="n">
-        <v>496669</v>
+        <v>339464</v>
       </c>
     </row>
     <row r="1208">
       <c r="A1208" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B1208" t="n">
-        <v>85.23999999999999</v>
+        <v>83.19</v>
       </c>
       <c r="C1208" t="n">
-        <v>87.84</v>
+        <v>86.13</v>
       </c>
       <c r="D1208" t="n">
-        <v>85.04000000000001</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="E1208" t="n">
-        <v>87.22</v>
+        <v>85.11</v>
       </c>
       <c r="F1208" t="n">
-        <v>339464</v>
+        <v>589226</v>
       </c>
     </row>
   </sheetData>

--- a/database/XPBR31.xlsx
+++ b/database/XPBR31.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1208"/>
+  <dimension ref="A1:F1210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>44474</v>
       </c>
       <c r="B3" t="n">
-        <v>192.5414886474609</v>
+        <v>192.54150390625</v>
       </c>
       <c r="C3" t="n">
-        <v>198.9809168362223</v>
+        <v>198.9809326053319</v>
       </c>
       <c r="D3" t="n">
-        <v>187.7272962672212</v>
+        <v>187.7273111444886</v>
       </c>
       <c r="E3" t="n">
-        <v>197.6631624200884</v>
+        <v>197.6631780847668</v>
       </c>
       <c r="F3" t="n">
         <v>2636287</v>
@@ -512,16 +512,16 @@
         <v>44476</v>
       </c>
       <c r="B5" t="n">
-        <v>203.3734283447266</v>
+        <v>203.3734436035156</v>
       </c>
       <c r="C5" t="n">
-        <v>203.3734283447266</v>
+        <v>203.3734436035156</v>
       </c>
       <c r="D5" t="n">
-        <v>190.9426172441435</v>
+        <v>190.9426315702683</v>
       </c>
       <c r="E5" t="n">
-        <v>190.9426172441435</v>
+        <v>190.9426315702683</v>
       </c>
       <c r="F5" t="n">
         <v>12157101</v>
@@ -532,16 +532,16 @@
         <v>44477</v>
       </c>
       <c r="B6" t="n">
-        <v>193.8241271972656</v>
+        <v>193.8241119384766</v>
       </c>
       <c r="C6" t="n">
-        <v>204.8669032795693</v>
+        <v>204.8668871514385</v>
       </c>
       <c r="D6" t="n">
-        <v>191.794787349043</v>
+        <v>191.7947722500135</v>
       </c>
       <c r="E6" t="n">
-        <v>200.9927017121121</v>
+        <v>200.9926858889775</v>
       </c>
       <c r="F6" t="n">
         <v>4982319</v>
@@ -572,16 +572,16 @@
         <v>44482</v>
       </c>
       <c r="B8" t="n">
-        <v>169.5510711669922</v>
+        <v>169.5510864257812</v>
       </c>
       <c r="C8" t="n">
-        <v>178.8632078987421</v>
+        <v>178.8632239955791</v>
       </c>
       <c r="D8" t="n">
-        <v>169.5510711669922</v>
+        <v>169.5510864257812</v>
       </c>
       <c r="E8" t="n">
-        <v>174.4091914601629</v>
+        <v>174.4092071561597</v>
       </c>
       <c r="F8" t="n">
         <v>3487621</v>
@@ -632,16 +632,16 @@
         <v>44487</v>
       </c>
       <c r="B11" t="n">
-        <v>179.4166717529297</v>
+        <v>179.4166564941406</v>
       </c>
       <c r="C11" t="n">
-        <v>182.2718066273138</v>
+        <v>182.2717911257051</v>
       </c>
       <c r="D11" t="n">
-        <v>175.0680843944616</v>
+        <v>175.0680695055053</v>
       </c>
       <c r="E11" t="n">
-        <v>176.7548086193568</v>
+        <v>176.7547935869503</v>
       </c>
       <c r="F11" t="n">
         <v>1369949</v>
@@ -652,16 +652,16 @@
         <v>44488</v>
       </c>
       <c r="B12" t="n">
-        <v>175.0856628417969</v>
+        <v>175.0856475830078</v>
       </c>
       <c r="C12" t="n">
-        <v>179.4078962958852</v>
+        <v>179.4078806604117</v>
       </c>
       <c r="D12" t="n">
-        <v>174.3828577116028</v>
+        <v>174.3828425140635</v>
       </c>
       <c r="E12" t="n">
-        <v>177.5454740950298</v>
+        <v>177.5454586218672</v>
       </c>
       <c r="F12" t="n">
         <v>722779</v>
@@ -672,16 +672,16 @@
         <v>44489</v>
       </c>
       <c r="B13" t="n">
-        <v>174.3828582763672</v>
+        <v>174.3828430175781</v>
       </c>
       <c r="C13" t="n">
-        <v>178.4942461832448</v>
+        <v>178.4942305647025</v>
       </c>
       <c r="D13" t="n">
-        <v>169.8409990421895</v>
+        <v>169.8409841808207</v>
       </c>
       <c r="E13" t="n">
-        <v>176.5791159372786</v>
+        <v>176.5791004863134</v>
       </c>
       <c r="F13" t="n">
         <v>1907987</v>
@@ -692,16 +692,16 @@
         <v>44490</v>
       </c>
       <c r="B14" t="n">
-        <v>169.4193115234375</v>
+        <v>169.4193267822266</v>
       </c>
       <c r="C14" t="n">
-        <v>176.2189162691178</v>
+        <v>176.2189321403148</v>
       </c>
       <c r="D14" t="n">
-        <v>167.1615523442876</v>
+        <v>167.161567399731</v>
       </c>
       <c r="E14" t="n">
-        <v>173.3989291023892</v>
+        <v>173.3989447196034</v>
       </c>
       <c r="F14" t="n">
         <v>1852525</v>
@@ -712,16 +712,16 @@
         <v>44491</v>
       </c>
       <c r="B15" t="n">
-        <v>166.0546417236328</v>
+        <v>166.0546264648438</v>
       </c>
       <c r="C15" t="n">
-        <v>170.8600542323661</v>
+        <v>170.8600385320068</v>
       </c>
       <c r="D15" t="n">
-        <v>159.8084848231975</v>
+        <v>159.8084701383689</v>
       </c>
       <c r="E15" t="n">
-        <v>169.5510799294295</v>
+        <v>169.5510643493521</v>
       </c>
       <c r="F15" t="n">
         <v>1387914</v>
@@ -732,16 +732,16 @@
         <v>44494</v>
       </c>
       <c r="B16" t="n">
-        <v>169.1206207275391</v>
+        <v>169.12060546875</v>
       </c>
       <c r="C16" t="n">
-        <v>174.5849108807135</v>
+        <v>174.5848951289127</v>
       </c>
       <c r="D16" t="n">
-        <v>167.3636145922391</v>
+        <v>167.3635994919746</v>
       </c>
       <c r="E16" t="n">
-        <v>167.7062302524268</v>
+        <v>167.7062151212502</v>
       </c>
       <c r="F16" t="n">
         <v>1203463</v>
@@ -772,16 +772,16 @@
         <v>44496</v>
       </c>
       <c r="B18" t="n">
-        <v>163.8320159912109</v>
+        <v>163.83203125</v>
       </c>
       <c r="C18" t="n">
-        <v>168.540792225014</v>
+        <v>168.5408079223634</v>
       </c>
       <c r="D18" t="n">
-        <v>163.8320159912109</v>
+        <v>163.83203125</v>
       </c>
       <c r="E18" t="n">
-        <v>166.9155564450402</v>
+        <v>166.9155719910203</v>
       </c>
       <c r="F18" t="n">
         <v>503418</v>
@@ -832,16 +832,16 @@
         <v>44501</v>
       </c>
       <c r="B21" t="n">
-        <v>169.7267761230469</v>
+        <v>169.7267913818359</v>
       </c>
       <c r="C21" t="n">
-        <v>171.2026681266692</v>
+        <v>171.2026835181439</v>
       </c>
       <c r="D21" t="n">
-        <v>161.9344588391563</v>
+        <v>161.9344733973998</v>
       </c>
       <c r="E21" t="n">
-        <v>162.5230542378089</v>
+        <v>162.5230688489684</v>
       </c>
       <c r="F21" t="n">
         <v>466029</v>
@@ -872,16 +872,16 @@
         <v>44504</v>
       </c>
       <c r="B23" t="n">
-        <v>160.3707275390625</v>
+        <v>160.3707427978516</v>
       </c>
       <c r="C23" t="n">
-        <v>170.4208041422209</v>
+        <v>170.4208203572443</v>
       </c>
       <c r="D23" t="n">
-        <v>158.7630654183402</v>
+        <v>158.763080524165</v>
       </c>
       <c r="E23" t="n">
-        <v>168.2333268163413</v>
+        <v>168.2333428232328</v>
       </c>
       <c r="F23" t="n">
         <v>1051127</v>
@@ -992,16 +992,16 @@
         <v>44512</v>
       </c>
       <c r="B29" t="n">
-        <v>161.6533203125</v>
+        <v>161.6533355712891</v>
       </c>
       <c r="C29" t="n">
-        <v>162.5230430442815</v>
+        <v>162.5230583851655</v>
       </c>
       <c r="D29" t="n">
-        <v>157.4277233381312</v>
+        <v>157.4277381980575</v>
       </c>
       <c r="E29" t="n">
-        <v>162.1804274356811</v>
+        <v>162.1804427442249</v>
       </c>
       <c r="F29" t="n">
         <v>339439</v>
@@ -1072,16 +1072,16 @@
         <v>44519</v>
       </c>
       <c r="B33" t="n">
-        <v>147.1931762695312</v>
+        <v>147.1931915283203</v>
       </c>
       <c r="C33" t="n">
-        <v>149.0468180845801</v>
+        <v>149.046833535527</v>
       </c>
       <c r="D33" t="n">
-        <v>140.5692563255631</v>
+        <v>140.5692708976831</v>
       </c>
       <c r="E33" t="n">
-        <v>142.5722420379041</v>
+        <v>142.5722568176638</v>
       </c>
       <c r="F33" t="n">
         <v>581745</v>
@@ -1092,16 +1092,16 @@
         <v>44522</v>
       </c>
       <c r="B34" t="n">
-        <v>140.0509490966797</v>
+        <v>140.0509643554688</v>
       </c>
       <c r="C34" t="n">
-        <v>150.6632671305561</v>
+        <v>150.6632835455752</v>
       </c>
       <c r="D34" t="n">
-        <v>139.9016051926592</v>
+        <v>139.901620435177</v>
       </c>
       <c r="E34" t="n">
-        <v>145.9281364140771</v>
+        <v>145.9281523131958</v>
       </c>
       <c r="F34" t="n">
         <v>547961</v>
@@ -1112,16 +1112,16 @@
         <v>44523</v>
       </c>
       <c r="B35" t="n">
-        <v>144.9530029296875</v>
+        <v>144.9529876708984</v>
       </c>
       <c r="C35" t="n">
-        <v>147.2107621975469</v>
+        <v>147.2107467010899</v>
       </c>
       <c r="D35" t="n">
-        <v>136.3524639873455</v>
+        <v>136.3524496339106</v>
       </c>
       <c r="E35" t="n">
-        <v>142.3174937855114</v>
+        <v>142.3174788041548</v>
       </c>
       <c r="F35" t="n">
         <v>809322</v>
@@ -1132,16 +1132,16 @@
         <v>44524</v>
       </c>
       <c r="B36" t="n">
-        <v>148.7393341064453</v>
+        <v>148.7393493652344</v>
       </c>
       <c r="C36" t="n">
-        <v>150.2152260507179</v>
+        <v>150.2152414609149</v>
       </c>
       <c r="D36" t="n">
-        <v>144.4171011491115</v>
+        <v>144.4171159644937</v>
       </c>
       <c r="E36" t="n">
-        <v>144.5225172148126</v>
+        <v>144.5225320410092</v>
       </c>
       <c r="F36" t="n">
         <v>231702</v>
@@ -1152,16 +1152,16 @@
         <v>44525</v>
       </c>
       <c r="B37" t="n">
-        <v>151.3133850097656</v>
+        <v>151.3133697509766</v>
       </c>
       <c r="C37" t="n">
-        <v>152.8507654981656</v>
+        <v>152.8507500843435</v>
       </c>
       <c r="D37" t="n">
-        <v>148.0717062922993</v>
+        <v>148.0716913604085</v>
       </c>
       <c r="E37" t="n">
-        <v>148.0717062922993</v>
+        <v>148.0716913604085</v>
       </c>
       <c r="F37" t="n">
         <v>222385</v>
@@ -1172,16 +1172,16 @@
         <v>44526</v>
       </c>
       <c r="B38" t="n">
-        <v>146.7363739013672</v>
+        <v>146.7363433837891</v>
       </c>
       <c r="C38" t="n">
-        <v>148.7305797213747</v>
+        <v>148.7305487890506</v>
       </c>
       <c r="D38" t="n">
-        <v>143.3717053697751</v>
+        <v>143.3716755519658</v>
       </c>
       <c r="E38" t="n">
-        <v>148.7305797213747</v>
+        <v>148.7305487890506</v>
       </c>
       <c r="F38" t="n">
         <v>241997</v>
@@ -1192,16 +1192,16 @@
         <v>44529</v>
       </c>
       <c r="B39" t="n">
-        <v>147.0174713134766</v>
+        <v>147.0174865722656</v>
       </c>
       <c r="C39" t="n">
-        <v>150.4348471893001</v>
+        <v>150.434862802775</v>
       </c>
       <c r="D39" t="n">
-        <v>146.0247587088519</v>
+        <v>146.0247738646084</v>
       </c>
       <c r="E39" t="n">
-        <v>148.7305493531764</v>
+        <v>148.730564789764</v>
       </c>
       <c r="F39" t="n">
         <v>333389</v>
@@ -1212,16 +1212,16 @@
         <v>44530</v>
       </c>
       <c r="B40" t="n">
-        <v>140.5604858398438</v>
+        <v>140.5604705810547</v>
       </c>
       <c r="C40" t="n">
-        <v>147.3073827258078</v>
+        <v>147.3073667345976</v>
       </c>
       <c r="D40" t="n">
-        <v>139.7610448594554</v>
+        <v>139.7610296874511</v>
       </c>
       <c r="E40" t="n">
-        <v>147.3073827258078</v>
+        <v>147.3073667345976</v>
       </c>
       <c r="F40" t="n">
         <v>711030</v>
@@ -1252,16 +1252,16 @@
         <v>44532</v>
       </c>
       <c r="B42" t="n">
-        <v>143.7845764160156</v>
+        <v>143.7846069335938</v>
       </c>
       <c r="C42" t="n">
-        <v>150.513912239461</v>
+        <v>150.513944185308</v>
       </c>
       <c r="D42" t="n">
-        <v>143.0466371541728</v>
+        <v>143.0466675151269</v>
       </c>
       <c r="E42" t="n">
-        <v>145.8314899009227</v>
+        <v>145.8315208529483</v>
       </c>
       <c r="F42" t="n">
         <v>584287</v>
@@ -1272,16 +1272,16 @@
         <v>44533</v>
       </c>
       <c r="B43" t="n">
-        <v>144.0657348632812</v>
+        <v>144.0657196044922</v>
       </c>
       <c r="C43" t="n">
-        <v>149.3455339129111</v>
+        <v>149.3455180949097</v>
       </c>
       <c r="D43" t="n">
-        <v>142.6776982924445</v>
+        <v>142.67768318067</v>
       </c>
       <c r="E43" t="n">
-        <v>143.5649816387535</v>
+        <v>143.564966433002</v>
       </c>
       <c r="F43" t="n">
         <v>471453</v>
@@ -1292,16 +1292,16 @@
         <v>44536</v>
       </c>
       <c r="B44" t="n">
-        <v>147.7641906738281</v>
+        <v>147.7642059326172</v>
       </c>
       <c r="C44" t="n">
-        <v>149.327924822433</v>
+        <v>149.3279402427002</v>
       </c>
       <c r="D44" t="n">
-        <v>139.2427149033103</v>
+        <v>139.2427292821338</v>
       </c>
       <c r="E44" t="n">
-        <v>144.9617641723165</v>
+        <v>144.9617791417145</v>
       </c>
       <c r="F44" t="n">
         <v>521095</v>
@@ -1432,16 +1432,16 @@
         <v>44545</v>
       </c>
       <c r="B51" t="n">
-        <v>150.6983947753906</v>
+        <v>150.6984100341797</v>
       </c>
       <c r="C51" t="n">
-        <v>151.5417635314571</v>
+        <v>151.5417788756405</v>
       </c>
       <c r="D51" t="n">
-        <v>142.2296266133646</v>
+        <v>142.2296410146585</v>
       </c>
       <c r="E51" t="n">
-        <v>145.8402743850054</v>
+        <v>145.8402891518912</v>
       </c>
       <c r="F51" t="n">
         <v>314440</v>
@@ -1452,16 +1452,16 @@
         <v>44546</v>
       </c>
       <c r="B52" t="n">
-        <v>145.72607421875</v>
+        <v>145.7260894775391</v>
       </c>
       <c r="C52" t="n">
-        <v>152.8595139117323</v>
+        <v>152.8595299174546</v>
       </c>
       <c r="D52" t="n">
-        <v>144.3028903187285</v>
+        <v>144.3029054284978</v>
       </c>
       <c r="E52" t="n">
-        <v>148.115603324704</v>
+        <v>148.1156188336976</v>
       </c>
       <c r="F52" t="n">
         <v>399045</v>
@@ -1472,16 +1472,16 @@
         <v>44547</v>
       </c>
       <c r="B53" t="n">
-        <v>144.9530029296875</v>
+        <v>144.9529876708984</v>
       </c>
       <c r="C53" t="n">
-        <v>147.4128141452304</v>
+        <v>147.4127986275041</v>
       </c>
       <c r="D53" t="n">
-        <v>141.8255342233813</v>
+        <v>141.825519293812</v>
       </c>
       <c r="E53" t="n">
-        <v>144.0744998816288</v>
+        <v>144.0744847153172</v>
       </c>
       <c r="F53" t="n">
         <v>507335</v>
@@ -1512,16 +1512,16 @@
         <v>44551</v>
       </c>
       <c r="B55" t="n">
-        <v>148.9853210449219</v>
+        <v>148.9853057861328</v>
       </c>
       <c r="C55" t="n">
-        <v>149.6441982970981</v>
+        <v>149.6441829708282</v>
       </c>
       <c r="D55" t="n">
-        <v>144.7948713726031</v>
+        <v>144.7948565429918</v>
       </c>
       <c r="E55" t="n">
-        <v>146.3146778142533</v>
+        <v>146.3146628289863</v>
       </c>
       <c r="F55" t="n">
         <v>221674</v>
@@ -1652,16 +1652,16 @@
         <v>44564</v>
       </c>
       <c r="B62" t="n">
-        <v>144.8124389648438</v>
+        <v>144.8124237060547</v>
       </c>
       <c r="C62" t="n">
-        <v>144.8124389648438</v>
+        <v>144.8124237060547</v>
       </c>
       <c r="D62" t="n">
-        <v>138.7947011393807</v>
+        <v>138.7946865146767</v>
       </c>
       <c r="E62" t="n">
-        <v>142.1769298253991</v>
+        <v>142.1769148443119</v>
       </c>
       <c r="F62" t="n">
         <v>369633</v>
@@ -1752,16 +1752,16 @@
         <v>44571</v>
       </c>
       <c r="B67" t="n">
-        <v>137.5208740234375</v>
+        <v>137.5208587646484</v>
       </c>
       <c r="C67" t="n">
-        <v>138.4696590120894</v>
+        <v>138.4696436480268</v>
       </c>
       <c r="D67" t="n">
-        <v>131.9072395609175</v>
+        <v>131.9072249249958</v>
       </c>
       <c r="E67" t="n">
-        <v>137.2309797869466</v>
+        <v>137.2309645603231</v>
       </c>
       <c r="F67" t="n">
         <v>730000</v>
@@ -1872,16 +1872,16 @@
         <v>44579</v>
       </c>
       <c r="B73" t="n">
-        <v>133.1722412109375</v>
+        <v>133.1722717285156</v>
       </c>
       <c r="C73" t="n">
-        <v>138.8034475865263</v>
+        <v>138.8034793945444</v>
       </c>
       <c r="D73" t="n">
-        <v>133.1722412109375</v>
+        <v>133.1722717285156</v>
       </c>
       <c r="E73" t="n">
-        <v>138.188498284526</v>
+        <v>138.1885299516231</v>
       </c>
       <c r="F73" t="n">
         <v>435258</v>
@@ -1932,16 +1932,16 @@
         <v>44582</v>
       </c>
       <c r="B76" t="n">
-        <v>143.1871948242188</v>
+        <v>143.1872100830078</v>
       </c>
       <c r="C76" t="n">
-        <v>145.5679302151781</v>
+        <v>145.567945727671</v>
       </c>
       <c r="D76" t="n">
-        <v>140.3320603528095</v>
+        <v>140.3320753073403</v>
       </c>
       <c r="E76" t="n">
-        <v>145.3043766599161</v>
+        <v>145.3043921443233</v>
       </c>
       <c r="F76" t="n">
         <v>292243</v>
@@ -1952,16 +1952,16 @@
         <v>44585</v>
       </c>
       <c r="B77" t="n">
-        <v>143.1696472167969</v>
+        <v>143.1696319580078</v>
       </c>
       <c r="C77" t="n">
-        <v>145.3307572747327</v>
+        <v>145.330741785616</v>
       </c>
       <c r="D77" t="n">
-        <v>136.449104054457</v>
+        <v>136.4490895119325</v>
       </c>
       <c r="E77" t="n">
-        <v>143.0203033026219</v>
+        <v>143.0202880597496</v>
       </c>
       <c r="F77" t="n">
         <v>940613</v>
@@ -1972,16 +1972,16 @@
         <v>44586</v>
       </c>
       <c r="B78" t="n">
-        <v>147.3161773681641</v>
+        <v>147.316162109375</v>
       </c>
       <c r="C78" t="n">
-        <v>149.5212151794752</v>
+        <v>149.5211996922916</v>
       </c>
       <c r="D78" t="n">
-        <v>140.1651631371207</v>
+        <v>140.165148619023</v>
       </c>
       <c r="E78" t="n">
-        <v>140.1651631371207</v>
+        <v>140.165148619023</v>
       </c>
       <c r="F78" t="n">
         <v>456302</v>
@@ -2012,16 +2012,16 @@
         <v>44588</v>
       </c>
       <c r="B80" t="n">
-        <v>149.4860992431641</v>
+        <v>149.486083984375</v>
       </c>
       <c r="C80" t="n">
-        <v>156.5668324884226</v>
+        <v>156.5668165068679</v>
       </c>
       <c r="D80" t="n">
-        <v>147.3249755956927</v>
+        <v>147.3249605575002</v>
       </c>
       <c r="E80" t="n">
-        <v>151.5417933972918</v>
+        <v>151.5417779286678</v>
       </c>
       <c r="F80" t="n">
         <v>697237</v>
@@ -2052,16 +2052,16 @@
         <v>44592</v>
       </c>
       <c r="B82" t="n">
-        <v>155.0557861328125</v>
+        <v>155.0557708740234</v>
       </c>
       <c r="C82" t="n">
-        <v>155.3193397250649</v>
+        <v>155.31932444034</v>
       </c>
       <c r="D82" t="n">
-        <v>145.8666384615764</v>
+        <v>145.8666241070765</v>
       </c>
       <c r="E82" t="n">
-        <v>147.0174887009155</v>
+        <v>147.0174742331623</v>
       </c>
       <c r="F82" t="n">
         <v>286473</v>
@@ -2092,16 +2092,16 @@
         <v>44594</v>
       </c>
       <c r="B84" t="n">
-        <v>148.9941101074219</v>
+        <v>148.9940948486328</v>
       </c>
       <c r="C84" t="n">
-        <v>158.1305356968381</v>
+        <v>158.1305195023691</v>
       </c>
       <c r="D84" t="n">
-        <v>148.9062544478559</v>
+        <v>148.9062391980643</v>
       </c>
       <c r="E84" t="n">
-        <v>155.8025081721468</v>
+        <v>155.8024922160959</v>
       </c>
       <c r="F84" t="n">
         <v>466282</v>
@@ -2112,16 +2112,16 @@
         <v>44595</v>
       </c>
       <c r="B85" t="n">
-        <v>146.2707366943359</v>
+        <v>146.270751953125</v>
       </c>
       <c r="C85" t="n">
-        <v>149.960446290332</v>
+        <v>149.9604619340272</v>
       </c>
       <c r="D85" t="n">
-        <v>145.5415776595851</v>
+        <v>145.5415928423091</v>
       </c>
       <c r="E85" t="n">
-        <v>149.2137268486408</v>
+        <v>149.2137424144391</v>
       </c>
       <c r="F85" t="n">
         <v>228387</v>
@@ -2132,16 +2132,16 @@
         <v>44596</v>
       </c>
       <c r="B86" t="n">
-        <v>149.6002655029297</v>
+        <v>149.6002807617188</v>
       </c>
       <c r="C86" t="n">
-        <v>151.0058756228975</v>
+        <v>151.0058910250547</v>
       </c>
       <c r="D86" t="n">
-        <v>143.5825281756291</v>
+        <v>143.5825428206266</v>
       </c>
       <c r="E86" t="n">
-        <v>149.3455055386924</v>
+        <v>149.3455207714968</v>
       </c>
       <c r="F86" t="n">
         <v>455710</v>
@@ -2152,16 +2152,16 @@
         <v>44599</v>
       </c>
       <c r="B87" t="n">
-        <v>147.1228790283203</v>
+        <v>147.1228942871094</v>
       </c>
       <c r="C87" t="n">
-        <v>152.1830508134523</v>
+        <v>152.183066597055</v>
       </c>
       <c r="D87" t="n">
-        <v>146.7099816005264</v>
+        <v>146.709996816492</v>
       </c>
       <c r="E87" t="n">
-        <v>149.5651159729917</v>
+        <v>149.5651314850764</v>
       </c>
       <c r="F87" t="n">
         <v>353300</v>
@@ -2172,16 +2172,16 @@
         <v>44600</v>
       </c>
       <c r="B88" t="n">
-        <v>149.3191528320312</v>
+        <v>149.3191680908203</v>
       </c>
       <c r="C88" t="n">
-        <v>149.3191528320312</v>
+        <v>149.3191680908203</v>
       </c>
       <c r="D88" t="n">
-        <v>144.2326130626084</v>
+        <v>144.2326278016086</v>
       </c>
       <c r="E88" t="n">
-        <v>147.6763565462567</v>
+        <v>147.6763716371699</v>
       </c>
       <c r="F88" t="n">
         <v>326666</v>
@@ -2192,16 +2192,16 @@
         <v>44601</v>
       </c>
       <c r="B89" t="n">
-        <v>157.5156097412109</v>
+        <v>157.5155944824219</v>
       </c>
       <c r="C89" t="n">
-        <v>159.7997097761142</v>
+        <v>159.7996942960607</v>
       </c>
       <c r="D89" t="n">
-        <v>151.4275762401174</v>
+        <v>151.4275615710859</v>
       </c>
       <c r="E89" t="n">
-        <v>153.7380437007286</v>
+        <v>153.7380288078784</v>
       </c>
       <c r="F89" t="n">
         <v>1361639</v>
@@ -2252,16 +2252,16 @@
         <v>44606</v>
       </c>
       <c r="B92" t="n">
-        <v>152.9473571777344</v>
+        <v>152.9473876953125</v>
       </c>
       <c r="C92" t="n">
-        <v>157.9196733040747</v>
+        <v>157.9197048137788</v>
       </c>
       <c r="D92" t="n">
-        <v>152.0688542953922</v>
+        <v>152.0688846376827</v>
       </c>
       <c r="E92" t="n">
-        <v>156.004543454916</v>
+        <v>156.0045745824943</v>
       </c>
       <c r="F92" t="n">
         <v>409040</v>
@@ -2312,16 +2312,16 @@
         <v>44609</v>
       </c>
       <c r="B95" t="n">
-        <v>156.6282806396484</v>
+        <v>156.6282958984375</v>
       </c>
       <c r="C95" t="n">
-        <v>161.1877129663323</v>
+        <v>161.1877286693031</v>
       </c>
       <c r="D95" t="n">
-        <v>156.1626751616721</v>
+        <v>156.1626903751017</v>
       </c>
       <c r="E95" t="n">
-        <v>160.8011695344521</v>
+        <v>160.8011851997657</v>
       </c>
       <c r="F95" t="n">
         <v>315564</v>
@@ -2352,16 +2352,16 @@
         <v>44613</v>
       </c>
       <c r="B97" t="n">
-        <v>150.3118591308594</v>
+        <v>150.3118743896484</v>
       </c>
       <c r="C97" t="n">
-        <v>155.6882928603806</v>
+        <v>155.6883086649541</v>
       </c>
       <c r="D97" t="n">
-        <v>149.5827000785075</v>
+        <v>149.5827152632765</v>
       </c>
       <c r="E97" t="n">
-        <v>154.6165181959493</v>
+        <v>154.6165338917224</v>
       </c>
       <c r="F97" t="n">
         <v>185476</v>
@@ -2372,16 +2372,16 @@
         <v>44614</v>
       </c>
       <c r="B98" t="n">
-        <v>150.3557586669922</v>
+        <v>150.3557891845703</v>
       </c>
       <c r="C98" t="n">
-        <v>155.0557543155673</v>
+        <v>155.0557857870995</v>
       </c>
       <c r="D98" t="n">
-        <v>149.6793211183826</v>
+        <v>149.6793514986648</v>
       </c>
       <c r="E98" t="n">
-        <v>150.5314699623664</v>
+        <v>150.5315005156085</v>
       </c>
       <c r="F98" t="n">
         <v>352471</v>
@@ -2392,16 +2392,16 @@
         <v>44615</v>
       </c>
       <c r="B99" t="n">
-        <v>147.2722473144531</v>
+        <v>147.2722625732422</v>
       </c>
       <c r="C99" t="n">
-        <v>153.5623322222181</v>
+        <v>153.5623481327191</v>
       </c>
       <c r="D99" t="n">
-        <v>146.9647658922019</v>
+        <v>146.964781119133</v>
       </c>
       <c r="E99" t="n">
-        <v>150.3557881219284</v>
+        <v>150.3558037002013</v>
       </c>
       <c r="F99" t="n">
         <v>373832</v>
@@ -2412,16 +2412,16 @@
         <v>44616</v>
       </c>
       <c r="B100" t="n">
-        <v>148.1068267822266</v>
+        <v>148.1068115234375</v>
       </c>
       <c r="C100" t="n">
-        <v>148.1068267822266</v>
+        <v>148.1068115234375</v>
       </c>
       <c r="D100" t="n">
-        <v>139.2427341770273</v>
+        <v>139.2427198314664</v>
       </c>
       <c r="E100" t="n">
-        <v>143.3277680196328</v>
+        <v>143.327753253209</v>
       </c>
       <c r="F100" t="n">
         <v>704723</v>
@@ -2432,16 +2432,16 @@
         <v>44617</v>
       </c>
       <c r="B101" t="n">
-        <v>145.1374816894531</v>
+        <v>145.1374969482422</v>
       </c>
       <c r="C101" t="n">
-        <v>149.1698071078465</v>
+        <v>149.1698227905674</v>
       </c>
       <c r="D101" t="n">
-        <v>141.2457065586561</v>
+        <v>141.2457214082899</v>
       </c>
       <c r="E101" t="n">
-        <v>145.8754209676771</v>
+        <v>145.8754363040482</v>
       </c>
       <c r="F101" t="n">
         <v>765160</v>
@@ -2472,16 +2472,16 @@
         <v>44623</v>
       </c>
       <c r="B103" t="n">
-        <v>136.16796875</v>
+        <v>136.1679534912109</v>
       </c>
       <c r="C103" t="n">
-        <v>143.3365566445935</v>
+        <v>143.3365405825027</v>
       </c>
       <c r="D103" t="n">
-        <v>135.4915176680011</v>
+        <v>135.4915024850142</v>
       </c>
       <c r="E103" t="n">
-        <v>142.5107616570688</v>
+        <v>142.5107456875154</v>
       </c>
       <c r="F103" t="n">
         <v>801826</v>
@@ -2512,16 +2512,16 @@
         <v>44627</v>
       </c>
       <c r="B105" t="n">
-        <v>117.0780868530273</v>
+        <v>117.0781021118164</v>
       </c>
       <c r="C105" t="n">
-        <v>130.2644107383485</v>
+        <v>130.2644277157113</v>
       </c>
       <c r="D105" t="n">
-        <v>117.0780868530273</v>
+        <v>117.0781021118164</v>
       </c>
       <c r="E105" t="n">
-        <v>129.5791795392778</v>
+        <v>129.5791964273345</v>
       </c>
       <c r="F105" t="n">
         <v>1053703</v>
@@ -2532,16 +2532,16 @@
         <v>44628</v>
       </c>
       <c r="B106" t="n">
-        <v>124.4399261474609</v>
+        <v>124.4399566650391</v>
       </c>
       <c r="C106" t="n">
-        <v>125.6083365729028</v>
+        <v>125.6083673770213</v>
       </c>
       <c r="D106" t="n">
-        <v>115.8657429638185</v>
+        <v>115.8657713786687</v>
       </c>
       <c r="E106" t="n">
-        <v>118.3431274910464</v>
+        <v>118.3431565134491</v>
       </c>
       <c r="F106" t="n">
         <v>713320</v>
@@ -2592,16 +2592,16 @@
         <v>44631</v>
       </c>
       <c r="B109" t="n">
-        <v>131.6173400878906</v>
+        <v>131.6173248291016</v>
       </c>
       <c r="C109" t="n">
-        <v>138.7156332970618</v>
+        <v>138.7156172153465</v>
       </c>
       <c r="D109" t="n">
-        <v>131.1341607048064</v>
+        <v>131.1341455020338</v>
       </c>
       <c r="E109" t="n">
-        <v>135.8077901982643</v>
+        <v>135.8077744536639</v>
       </c>
       <c r="F109" t="n">
         <v>422012</v>
@@ -2632,16 +2632,16 @@
         <v>44635</v>
       </c>
       <c r="B111" t="n">
-        <v>131.4855499267578</v>
+        <v>131.4855346679688</v>
       </c>
       <c r="C111" t="n">
-        <v>132.1971352527014</v>
+        <v>132.1971199113335</v>
       </c>
       <c r="D111" t="n">
-        <v>124.3521094480533</v>
+        <v>124.3520950170941</v>
       </c>
       <c r="E111" t="n">
-        <v>126.987618598892</v>
+        <v>126.9876038620842</v>
       </c>
       <c r="F111" t="n">
         <v>302237</v>
@@ -2652,16 +2652,16 @@
         <v>44636</v>
       </c>
       <c r="B112" t="n">
-        <v>139.4887237548828</v>
+        <v>139.4887084960938</v>
       </c>
       <c r="C112" t="n">
-        <v>142.3438588832909</v>
+        <v>142.3438433121762</v>
       </c>
       <c r="D112" t="n">
-        <v>132.6539705814235</v>
+        <v>132.6539560702938</v>
       </c>
       <c r="E112" t="n">
-        <v>132.6539705814235</v>
+        <v>132.6539560702938</v>
       </c>
       <c r="F112" t="n">
         <v>861619</v>
@@ -2672,16 +2672,16 @@
         <v>44637</v>
       </c>
       <c r="B113" t="n">
-        <v>138.6101989746094</v>
+        <v>138.6101837158203</v>
       </c>
       <c r="C113" t="n">
-        <v>142.0978568741435</v>
+        <v>142.0978412314185</v>
       </c>
       <c r="D113" t="n">
-        <v>135.7989921223744</v>
+        <v>135.7989771730547</v>
       </c>
       <c r="E113" t="n">
-        <v>140.0333695112333</v>
+        <v>140.0333540957757</v>
       </c>
       <c r="F113" t="n">
         <v>600068</v>
@@ -2712,16 +2712,16 @@
         <v>44641</v>
       </c>
       <c r="B115" t="n">
-        <v>139.7698211669922</v>
+        <v>139.7698364257812</v>
       </c>
       <c r="C115" t="n">
-        <v>143.0642071460549</v>
+        <v>143.0642227644949</v>
       </c>
       <c r="D115" t="n">
-        <v>138.4169191515182</v>
+        <v>138.4169342626098</v>
       </c>
       <c r="E115" t="n">
-        <v>141.4828991951266</v>
+        <v>141.4829146409339</v>
       </c>
       <c r="F115" t="n">
         <v>351500</v>
@@ -2732,16 +2732,16 @@
         <v>44642</v>
       </c>
       <c r="B116" t="n">
-        <v>143.4683227539062</v>
+        <v>143.4683380126953</v>
       </c>
       <c r="C116" t="n">
-        <v>146.832990851759</v>
+        <v>146.8330064684024</v>
       </c>
       <c r="D116" t="n">
-        <v>139.7698326314529</v>
+        <v>139.7698474968835</v>
       </c>
       <c r="E116" t="n">
-        <v>139.7698326314529</v>
+        <v>139.7698474968835</v>
       </c>
       <c r="F116" t="n">
         <v>384464</v>
@@ -2772,16 +2772,16 @@
         <v>44644</v>
       </c>
       <c r="B118" t="n">
-        <v>136.2733917236328</v>
+        <v>136.2733764648438</v>
       </c>
       <c r="C118" t="n">
-        <v>137.2661044808038</v>
+        <v>137.2660891108588</v>
       </c>
       <c r="D118" t="n">
-        <v>132.4870456424172</v>
+        <v>132.4870308075925</v>
       </c>
       <c r="E118" t="n">
-        <v>133.2777064471624</v>
+        <v>133.2776915238059</v>
       </c>
       <c r="F118" t="n">
         <v>438667</v>
@@ -2812,16 +2812,16 @@
         <v>44648</v>
       </c>
       <c r="B120" t="n">
-        <v>134.9380798339844</v>
+        <v>134.9380645751953</v>
       </c>
       <c r="C120" t="n">
-        <v>139.8489088843792</v>
+        <v>139.8488930702739</v>
       </c>
       <c r="D120" t="n">
-        <v>132.478268503776</v>
+        <v>132.4782535231423</v>
       </c>
       <c r="E120" t="n">
-        <v>134.7623684922676</v>
+        <v>134.762353253348</v>
       </c>
       <c r="F120" t="n">
         <v>527873</v>
@@ -2832,16 +2832,16 @@
         <v>44649</v>
       </c>
       <c r="B121" t="n">
-        <v>139.5765686035156</v>
+        <v>139.5765838623047</v>
       </c>
       <c r="C121" t="n">
-        <v>140.4638518565375</v>
+        <v>140.4638672123262</v>
       </c>
       <c r="D121" t="n">
-        <v>135.1576993429566</v>
+        <v>135.157714118666</v>
       </c>
       <c r="E121" t="n">
-        <v>137.9249785831454</v>
+        <v>137.9249936613793</v>
       </c>
       <c r="F121" t="n">
         <v>830631</v>
@@ -2852,16 +2852,16 @@
         <v>44650</v>
       </c>
       <c r="B122" t="n">
-        <v>130.6773223876953</v>
+        <v>130.6773071289062</v>
       </c>
       <c r="C122" t="n">
-        <v>139.2866545436278</v>
+        <v>139.2866382795535</v>
       </c>
       <c r="D122" t="n">
-        <v>130.6333945563345</v>
+        <v>130.6333793026747</v>
       </c>
       <c r="E122" t="n">
-        <v>137.9952540499933</v>
+        <v>137.9952379367119</v>
       </c>
       <c r="F122" t="n">
         <v>554943</v>
@@ -2872,16 +2872,16 @@
         <v>44651</v>
       </c>
       <c r="B123" t="n">
-        <v>126.0651702880859</v>
+        <v>126.0651779174805</v>
       </c>
       <c r="C123" t="n">
-        <v>132.1707629625238</v>
+        <v>132.1707709614254</v>
       </c>
       <c r="D123" t="n">
-        <v>123.4735893289954</v>
+        <v>123.4735968015489</v>
       </c>
       <c r="E123" t="n">
-        <v>131.6788034671577</v>
+        <v>131.6788114362862</v>
       </c>
       <c r="F123" t="n">
         <v>791956</v>
@@ -2892,16 +2892,16 @@
         <v>44652</v>
       </c>
       <c r="B124" t="n">
-        <v>127.382926940918</v>
+        <v>127.3829498291016</v>
       </c>
       <c r="C124" t="n">
-        <v>129.1047986101335</v>
+        <v>129.1048218077033</v>
       </c>
       <c r="D124" t="n">
-        <v>124.615648027951</v>
+        <v>124.6156704189095</v>
       </c>
       <c r="E124" t="n">
-        <v>126.5044239964978</v>
+        <v>126.5044467268319</v>
       </c>
       <c r="F124" t="n">
         <v>526406</v>
@@ -2912,16 +2912,16 @@
         <v>44655</v>
       </c>
       <c r="B125" t="n">
-        <v>129.0872192382812</v>
+        <v>129.0872344970703</v>
       </c>
       <c r="C125" t="n">
-        <v>129.0872192382812</v>
+        <v>129.0872344970703</v>
       </c>
       <c r="D125" t="n">
-        <v>125.6346958448618</v>
+        <v>125.6347106955444</v>
       </c>
       <c r="E125" t="n">
-        <v>127.3829214547252</v>
+        <v>127.3829365120573</v>
       </c>
       <c r="F125" t="n">
         <v>325077</v>
@@ -2932,16 +2932,16 @@
         <v>44656</v>
       </c>
       <c r="B126" t="n">
-        <v>128.0769500732422</v>
+        <v>128.0769653320312</v>
       </c>
       <c r="C126" t="n">
-        <v>130.1590113571142</v>
+        <v>130.1590268639552</v>
       </c>
       <c r="D126" t="n">
-        <v>125.6347127369603</v>
+        <v>125.6347277047869</v>
       </c>
       <c r="E126" t="n">
-        <v>128.2614416065824</v>
+        <v>128.2614568873513</v>
       </c>
       <c r="F126" t="n">
         <v>767000</v>
@@ -2952,16 +2952,16 @@
         <v>44657</v>
       </c>
       <c r="B127" t="n">
-        <v>125.019775390625</v>
+        <v>125.0197677612305</v>
       </c>
       <c r="C127" t="n">
-        <v>127.3829509003876</v>
+        <v>127.3829431267791</v>
       </c>
       <c r="D127" t="n">
-        <v>122.6917475119892</v>
+        <v>122.6917400246637</v>
       </c>
       <c r="E127" t="n">
-        <v>127.172105328308</v>
+        <v>127.1720975675664</v>
       </c>
       <c r="F127" t="n">
         <v>694358</v>
@@ -2972,16 +2972,16 @@
         <v>44658</v>
       </c>
       <c r="B128" t="n">
-        <v>126.9524688720703</v>
+        <v>126.9524536132812</v>
       </c>
       <c r="C128" t="n">
-        <v>128.6040588688667</v>
+        <v>128.6040434115682</v>
       </c>
       <c r="D128" t="n">
-        <v>122.9992052111455</v>
+        <v>122.9991904275108</v>
       </c>
       <c r="E128" t="n">
-        <v>124.7562112826676</v>
+        <v>124.7561962878532</v>
       </c>
       <c r="F128" t="n">
         <v>544395</v>
@@ -2992,16 +2992,16 @@
         <v>44659</v>
       </c>
       <c r="B129" t="n">
-        <v>123.5790176391602</v>
+        <v>123.5790100097656</v>
       </c>
       <c r="C129" t="n">
-        <v>128.0857424003326</v>
+        <v>128.0857344927065</v>
       </c>
       <c r="D129" t="n">
-        <v>123.5790176391602</v>
+        <v>123.5790100097656</v>
       </c>
       <c r="E129" t="n">
-        <v>126.7943418945568</v>
+        <v>126.7943340666578</v>
       </c>
       <c r="F129" t="n">
         <v>403536</v>
@@ -3012,16 +3012,16 @@
         <v>44662</v>
       </c>
       <c r="B130" t="n">
-        <v>121.8659286499023</v>
+        <v>121.8659362792969</v>
       </c>
       <c r="C130" t="n">
-        <v>123.5702264946588</v>
+        <v>123.5702342307505</v>
       </c>
       <c r="D130" t="n">
-        <v>119.362189914273</v>
+        <v>119.3621973869214</v>
       </c>
       <c r="E130" t="n">
-        <v>122.9904113383186</v>
+        <v>122.9904190381111</v>
       </c>
       <c r="F130" t="n">
         <v>348006</v>
@@ -3032,16 +3032,16 @@
         <v>44663</v>
       </c>
       <c r="B131" t="n">
-        <v>118.2025909423828</v>
+        <v>118.2025756835938</v>
       </c>
       <c r="C131" t="n">
-        <v>125.1691138645034</v>
+        <v>125.1690977064049</v>
       </c>
       <c r="D131" t="n">
-        <v>118.1762369226312</v>
+        <v>118.1762216672442</v>
       </c>
       <c r="E131" t="n">
-        <v>122.9904300007179</v>
+        <v>122.990414123866</v>
       </c>
       <c r="F131" t="n">
         <v>576598</v>
@@ -3052,16 +3052,16 @@
         <v>44664</v>
       </c>
       <c r="B132" t="n">
-        <v>119.7750930786133</v>
+        <v>119.7751007080078</v>
       </c>
       <c r="C132" t="n">
-        <v>120.7941597526093</v>
+        <v>120.794167446916</v>
       </c>
       <c r="D132" t="n">
-        <v>117.7545335435913</v>
+        <v>117.7545410442809</v>
       </c>
       <c r="E132" t="n">
-        <v>118.8351018605366</v>
+        <v>118.8351094300559</v>
       </c>
       <c r="F132" t="n">
         <v>714435</v>
@@ -3092,16 +3092,16 @@
         <v>44669</v>
       </c>
       <c r="B134" t="n">
-        <v>112.4483795166016</v>
+        <v>112.4483871459961</v>
       </c>
       <c r="C134" t="n">
-        <v>115.1365964446377</v>
+        <v>115.1366042564223</v>
       </c>
       <c r="D134" t="n">
-        <v>112.0530558633418</v>
+        <v>112.0530634659144</v>
       </c>
       <c r="E134" t="n">
-        <v>114.2053854465485</v>
+        <v>114.2053931951523</v>
       </c>
       <c r="F134" t="n">
         <v>589431</v>
@@ -3212,16 +3212,16 @@
         <v>44678</v>
       </c>
       <c r="B140" t="n">
-        <v>104.541862487793</v>
+        <v>104.5418548583984</v>
       </c>
       <c r="C140" t="n">
-        <v>110.4717580490753</v>
+        <v>110.471749986921</v>
       </c>
       <c r="D140" t="n">
-        <v>104.0938240575889</v>
+        <v>104.0938164608919</v>
       </c>
       <c r="E140" t="n">
-        <v>109.5493271696751</v>
+        <v>109.5493191748392</v>
       </c>
       <c r="F140" t="n">
         <v>1036983</v>
@@ -3232,16 +3232,16 @@
         <v>44679</v>
       </c>
       <c r="B141" t="n">
-        <v>108.4951248168945</v>
+        <v>108.4951324462891</v>
       </c>
       <c r="C141" t="n">
-        <v>109.5844667035533</v>
+        <v>109.5844744095505</v>
       </c>
       <c r="D141" t="n">
-        <v>104.0235475861498</v>
+        <v>104.0235549011023</v>
       </c>
       <c r="E141" t="n">
-        <v>104.5418611595988</v>
+        <v>104.5418685109992</v>
       </c>
       <c r="F141" t="n">
         <v>799584</v>
@@ -3312,16 +3312,16 @@
         <v>44685</v>
       </c>
       <c r="B145" t="n">
-        <v>94.52692413330078</v>
+        <v>94.52691650390625</v>
       </c>
       <c r="C145" t="n">
-        <v>100.4128984212591</v>
+        <v>100.4128903167997</v>
       </c>
       <c r="D145" t="n">
-        <v>84.54712923481648</v>
+        <v>84.54712241090455</v>
       </c>
       <c r="E145" t="n">
-        <v>100.4128984212591</v>
+        <v>100.4128903167997</v>
       </c>
       <c r="F145" t="n">
         <v>3193940</v>
@@ -3372,16 +3372,16 @@
         <v>44690</v>
       </c>
       <c r="B148" t="n">
-        <v>85.64525604248047</v>
+        <v>85.64524841308594</v>
       </c>
       <c r="C148" t="n">
-        <v>90.7405761501812</v>
+        <v>90.7405680668887</v>
       </c>
       <c r="D148" t="n">
-        <v>83.37872338445261</v>
+        <v>83.37871595696386</v>
       </c>
       <c r="E148" t="n">
-        <v>88.64095450536544</v>
+        <v>88.64094660911006</v>
       </c>
       <c r="F148" t="n">
         <v>1267170</v>
@@ -3412,16 +3412,16 @@
         <v>44692</v>
       </c>
       <c r="B150" t="n">
-        <v>81.85890197753906</v>
+        <v>81.85891723632812</v>
       </c>
       <c r="C150" t="n">
-        <v>86.58524525254019</v>
+        <v>86.58526139233636</v>
       </c>
       <c r="D150" t="n">
-        <v>81.5250732823534</v>
+        <v>81.52508847891562</v>
       </c>
       <c r="E150" t="n">
-        <v>84.51197783467165</v>
+        <v>84.51199358800345</v>
       </c>
       <c r="F150" t="n">
         <v>624829</v>
@@ -3432,16 +3432,16 @@
         <v>44693</v>
       </c>
       <c r="B151" t="n">
-        <v>89.44918060302734</v>
+        <v>89.44917297363281</v>
       </c>
       <c r="C151" t="n">
-        <v>96.81103377549363</v>
+        <v>96.8110255181841</v>
       </c>
       <c r="D151" t="n">
-        <v>80.67293697880346</v>
+        <v>80.67293009796164</v>
       </c>
       <c r="E151" t="n">
-        <v>80.98041170691459</v>
+        <v>80.98040479984731</v>
       </c>
       <c r="F151" t="n">
         <v>2304224</v>
@@ -3452,16 +3452,16 @@
         <v>44694</v>
       </c>
       <c r="B152" t="n">
-        <v>89.78299713134766</v>
+        <v>89.78300476074219</v>
       </c>
       <c r="C152" t="n">
-        <v>92.42729283812145</v>
+        <v>92.42730069221749</v>
       </c>
       <c r="D152" t="n">
-        <v>87.90300138967268</v>
+        <v>87.90300885931281</v>
       </c>
       <c r="E152" t="n">
-        <v>90.57365111206272</v>
+        <v>90.57365880864381</v>
       </c>
       <c r="F152" t="n">
         <v>780406</v>
@@ -3572,16 +3572,16 @@
         <v>44704</v>
       </c>
       <c r="B158" t="n">
-        <v>91.02169799804688</v>
+        <v>91.02169036865234</v>
       </c>
       <c r="C158" t="n">
-        <v>92.67328125477616</v>
+        <v>92.67327348694673</v>
       </c>
       <c r="D158" t="n">
-        <v>90.09926715053099</v>
+        <v>90.09925959845417</v>
       </c>
       <c r="E158" t="n">
-        <v>90.31011270007218</v>
+        <v>90.31010513032238</v>
       </c>
       <c r="F158" t="n">
         <v>925415</v>
@@ -3592,16 +3592,16 @@
         <v>44705</v>
       </c>
       <c r="B159" t="n">
-        <v>87.67460632324219</v>
+        <v>87.67459869384766</v>
       </c>
       <c r="C159" t="n">
-        <v>90.02020783815051</v>
+        <v>90.02020000464306</v>
       </c>
       <c r="D159" t="n">
-        <v>85.55741077362453</v>
+        <v>85.55740332846713</v>
       </c>
       <c r="E159" t="n">
-        <v>88.43011947599447</v>
+        <v>88.43011178085561</v>
       </c>
       <c r="F159" t="n">
         <v>569845</v>
@@ -3612,16 +3612,16 @@
         <v>44706</v>
       </c>
       <c r="B160" t="n">
-        <v>89.92356872558594</v>
+        <v>89.92356109619141</v>
       </c>
       <c r="C160" t="n">
-        <v>90.73178988696996</v>
+        <v>90.73178218900343</v>
       </c>
       <c r="D160" t="n">
-        <v>85.75067942410486</v>
+        <v>85.75067214875119</v>
       </c>
       <c r="E160" t="n">
-        <v>86.97179807297417</v>
+        <v>86.971790694017</v>
       </c>
       <c r="F160" t="n">
         <v>958832</v>
@@ -3692,16 +3692,16 @@
         <v>44712</v>
       </c>
       <c r="B164" t="n">
-        <v>93.95588684082031</v>
+        <v>93.95589447021484</v>
       </c>
       <c r="C164" t="n">
-        <v>98.17270363778388</v>
+        <v>98.17271160959186</v>
       </c>
       <c r="D164" t="n">
-        <v>93.12131172800976</v>
+        <v>93.12131928963522</v>
       </c>
       <c r="E164" t="n">
-        <v>96.72317244492481</v>
+        <v>96.72318029902813</v>
       </c>
       <c r="F164" t="n">
         <v>435642</v>
@@ -3732,16 +3732,16 @@
         <v>44714</v>
       </c>
       <c r="B166" t="n">
-        <v>97.39962768554688</v>
+        <v>97.39963531494141</v>
       </c>
       <c r="C166" t="n">
-        <v>97.77738423457956</v>
+        <v>97.77739189356407</v>
       </c>
       <c r="D166" t="n">
-        <v>91.3818769180002</v>
+        <v>91.38188407601926</v>
       </c>
       <c r="E166" t="n">
-        <v>91.3818769180002</v>
+        <v>91.38188407601926</v>
       </c>
       <c r="F166" t="n">
         <v>432233</v>
@@ -3832,16 +3832,16 @@
         <v>44721</v>
       </c>
       <c r="B171" t="n">
-        <v>95.02765655517578</v>
+        <v>95.02766418457031</v>
       </c>
       <c r="C171" t="n">
-        <v>97.41718550225902</v>
+        <v>97.41719332349938</v>
       </c>
       <c r="D171" t="n">
-        <v>94.5269101730624</v>
+        <v>94.52691776225399</v>
       </c>
       <c r="E171" t="n">
-        <v>97.11849773509621</v>
+        <v>97.1185055323561</v>
       </c>
       <c r="F171" t="n">
         <v>459814</v>
@@ -3852,16 +3852,16 @@
         <v>44722</v>
       </c>
       <c r="B172" t="n">
-        <v>88.72880554199219</v>
+        <v>88.72879791259766</v>
       </c>
       <c r="C172" t="n">
-        <v>95.2297292687264</v>
+        <v>95.22972108034641</v>
       </c>
       <c r="D172" t="n">
-        <v>88.72880554199219</v>
+        <v>88.72879791259766</v>
       </c>
       <c r="E172" t="n">
-        <v>93.59571310571778</v>
+        <v>93.59570505783955</v>
       </c>
       <c r="F172" t="n">
         <v>588546</v>
@@ -3892,16 +3892,16 @@
         <v>44726</v>
       </c>
       <c r="B174" t="n">
-        <v>85.73310089111328</v>
+        <v>85.73310852050781</v>
       </c>
       <c r="C174" t="n">
-        <v>86.47104686486708</v>
+        <v>86.47105455993147</v>
       </c>
       <c r="D174" t="n">
-        <v>84.07273082822437</v>
+        <v>84.07273830986246</v>
       </c>
       <c r="E174" t="n">
-        <v>86.10207722921302</v>
+        <v>86.10208489144279</v>
       </c>
       <c r="F174" t="n">
         <v>502449</v>
@@ -3912,16 +3912,16 @@
         <v>44727</v>
       </c>
       <c r="B175" t="n">
-        <v>86.62918853759766</v>
+        <v>86.62917327880859</v>
       </c>
       <c r="C175" t="n">
-        <v>88.47404364983063</v>
+        <v>88.47402806609041</v>
       </c>
       <c r="D175" t="n">
-        <v>85.29386011368575</v>
+        <v>85.29384509010026</v>
       </c>
       <c r="E175" t="n">
-        <v>86.10208803445202</v>
+        <v>86.10207286850599</v>
       </c>
       <c r="F175" t="n">
         <v>817586</v>
@@ -3952,16 +3952,16 @@
         <v>44732</v>
       </c>
       <c r="B177" t="n">
-        <v>83.89704132080078</v>
+        <v>83.89703369140625</v>
       </c>
       <c r="C177" t="n">
-        <v>85.54862464282172</v>
+        <v>85.54861686323618</v>
       </c>
       <c r="D177" t="n">
-        <v>82.53535891157887</v>
+        <v>82.53535140601245</v>
       </c>
       <c r="E177" t="n">
-        <v>84.51199077515794</v>
+        <v>84.51198308984139</v>
       </c>
       <c r="F177" t="n">
         <v>143101</v>
@@ -3972,16 +3972,16 @@
         <v>44733</v>
       </c>
       <c r="B178" t="n">
-        <v>85.99665832519531</v>
+        <v>85.99665069580078</v>
       </c>
       <c r="C178" t="n">
-        <v>87.58674661395143</v>
+        <v>87.5867388434885</v>
       </c>
       <c r="D178" t="n">
-        <v>85.37292199810067</v>
+        <v>85.37291442404235</v>
       </c>
       <c r="E178" t="n">
-        <v>85.5749806376266</v>
+        <v>85.57497304564218</v>
       </c>
       <c r="F178" t="n">
         <v>532289</v>
@@ -4032,16 +4032,16 @@
         <v>44736</v>
       </c>
       <c r="B181" t="n">
-        <v>91.10075378417969</v>
+        <v>91.10076141357422</v>
       </c>
       <c r="C181" t="n">
-        <v>92.33065926209622</v>
+        <v>92.33066699449137</v>
       </c>
       <c r="D181" t="n">
-        <v>89.34374787356913</v>
+        <v>89.34375535582006</v>
       </c>
       <c r="E181" t="n">
-        <v>89.34374787356913</v>
+        <v>89.34375535582006</v>
       </c>
       <c r="F181" t="n">
         <v>487883</v>
@@ -4052,16 +4052,16 @@
         <v>44739</v>
       </c>
       <c r="B182" t="n">
-        <v>91.08318328857422</v>
+        <v>91.08319091796875</v>
       </c>
       <c r="C182" t="n">
-        <v>92.33065583015203</v>
+        <v>92.33066356403852</v>
       </c>
       <c r="D182" t="n">
-        <v>88.45646142653185</v>
+        <v>88.45646883590445</v>
       </c>
       <c r="E182" t="n">
-        <v>91.46093981341205</v>
+        <v>91.46094747444857</v>
       </c>
       <c r="F182" t="n">
         <v>388597</v>
@@ -4112,16 +4112,16 @@
         <v>44742</v>
       </c>
       <c r="B185" t="n">
-        <v>82.69348907470703</v>
+        <v>82.6934814453125</v>
       </c>
       <c r="C185" t="n">
-        <v>84.4680689760099</v>
+        <v>84.46806118289064</v>
       </c>
       <c r="D185" t="n">
-        <v>79.82078707143653</v>
+        <v>79.82077970708073</v>
       </c>
       <c r="E185" t="n">
-        <v>82.4914371280648</v>
+        <v>82.49142951731181</v>
       </c>
       <c r="F185" t="n">
         <v>710009</v>
@@ -4212,16 +4212,16 @@
         <v>44749</v>
       </c>
       <c r="B190" t="n">
-        <v>86.40076446533203</v>
+        <v>86.4007568359375</v>
       </c>
       <c r="C190" t="n">
-        <v>88.54431382481931</v>
+        <v>88.54430600614423</v>
       </c>
       <c r="D190" t="n">
-        <v>86.18992563237374</v>
+        <v>86.18991802159677</v>
       </c>
       <c r="E190" t="n">
-        <v>87.14749063816215</v>
+        <v>87.14748294282991</v>
       </c>
       <c r="F190" t="n">
         <v>483378</v>
@@ -4252,16 +4252,16 @@
         <v>44753</v>
       </c>
       <c r="B192" t="n">
-        <v>81.78861999511719</v>
+        <v>81.78862762451172</v>
       </c>
       <c r="C192" t="n">
-        <v>85.20599579614506</v>
+        <v>85.20600374431876</v>
       </c>
       <c r="D192" t="n">
-        <v>81.43721748884678</v>
+        <v>81.43722508546183</v>
       </c>
       <c r="E192" t="n">
-        <v>85.03029789423252</v>
+        <v>85.0303058260168</v>
       </c>
       <c r="F192" t="n">
         <v>432674</v>
@@ -4272,16 +4272,16 @@
         <v>44754</v>
       </c>
       <c r="B193" t="n">
-        <v>86.32170867919922</v>
+        <v>86.32170104980469</v>
       </c>
       <c r="C193" t="n">
-        <v>86.32170867919922</v>
+        <v>86.32170104980469</v>
       </c>
       <c r="D193" t="n">
-        <v>81.2966703290714</v>
+        <v>81.29666314380617</v>
       </c>
       <c r="E193" t="n">
-        <v>82.6232117668371</v>
+        <v>82.6232044643278</v>
       </c>
       <c r="F193" t="n">
         <v>730233</v>
@@ -4292,16 +4292,16 @@
         <v>44755</v>
       </c>
       <c r="B194" t="n">
-        <v>84.68769836425781</v>
+        <v>84.68769073486328</v>
       </c>
       <c r="C194" t="n">
-        <v>86.91909699469635</v>
+        <v>86.91908916427828</v>
       </c>
       <c r="D194" t="n">
-        <v>83.4577927101453</v>
+        <v>83.45778519155122</v>
       </c>
       <c r="E194" t="n">
-        <v>84.37143671884469</v>
+        <v>84.37142911794173</v>
       </c>
       <c r="F194" t="n">
         <v>1885043</v>
@@ -4332,16 +4332,16 @@
         <v>44757</v>
       </c>
       <c r="B196" t="n">
-        <v>82.85161590576172</v>
+        <v>82.85160827636719</v>
       </c>
       <c r="C196" t="n">
-        <v>84.72283158804966</v>
+        <v>84.72282378634415</v>
       </c>
       <c r="D196" t="n">
-        <v>81.20881958293697</v>
+        <v>81.20881210481942</v>
       </c>
       <c r="E196" t="n">
-        <v>82.27180741019004</v>
+        <v>82.27179983418721</v>
       </c>
       <c r="F196" t="n">
         <v>1850084</v>
@@ -4352,16 +4352,16 @@
         <v>44760</v>
       </c>
       <c r="B197" t="n">
-        <v>83.74768829345703</v>
+        <v>83.74770355224609</v>
       </c>
       <c r="C197" t="n">
-        <v>86.46225920673785</v>
+        <v>86.46227496012044</v>
       </c>
       <c r="D197" t="n">
-        <v>82.93946718359145</v>
+        <v>82.93948229512301</v>
       </c>
       <c r="E197" t="n">
-        <v>82.93946718359145</v>
+        <v>82.93948229512301</v>
       </c>
       <c r="F197" t="n">
         <v>494919</v>
@@ -4372,16 +4372,16 @@
         <v>44761</v>
       </c>
       <c r="B198" t="n">
-        <v>86.85758972167969</v>
+        <v>86.85759735107422</v>
       </c>
       <c r="C198" t="n">
-        <v>87.15627750971456</v>
+        <v>87.15628516534521</v>
       </c>
       <c r="D198" t="n">
-        <v>83.45778086715818</v>
+        <v>83.45778819792039</v>
       </c>
       <c r="E198" t="n">
-        <v>83.45778086715818</v>
+        <v>83.45778819792039</v>
       </c>
       <c r="F198" t="n">
         <v>493807</v>
@@ -4412,16 +4412,16 @@
         <v>44763</v>
       </c>
       <c r="B200" t="n">
-        <v>91.97048187255859</v>
+        <v>91.97048950195312</v>
       </c>
       <c r="C200" t="n">
-        <v>92.62057222052319</v>
+        <v>92.62057990384585</v>
       </c>
       <c r="D200" t="n">
-        <v>87.41104912516667</v>
+        <v>87.41105637633429</v>
       </c>
       <c r="E200" t="n">
-        <v>87.41104912516667</v>
+        <v>87.41105637633429</v>
       </c>
       <c r="F200" t="n">
         <v>453688</v>
@@ -4432,16 +4432,16 @@
         <v>44764</v>
       </c>
       <c r="B201" t="n">
-        <v>89.78299713134766</v>
+        <v>89.78300476074219</v>
       </c>
       <c r="C201" t="n">
-        <v>92.24280802636217</v>
+        <v>92.24281586478145</v>
       </c>
       <c r="D201" t="n">
-        <v>89.22075579004928</v>
+        <v>89.22076337166682</v>
       </c>
       <c r="E201" t="n">
-        <v>91.97047426173357</v>
+        <v>91.97048207701101</v>
       </c>
       <c r="F201" t="n">
         <v>566897</v>
@@ -4452,16 +4452,16 @@
         <v>44767</v>
       </c>
       <c r="B202" t="n">
-        <v>89.0802001953125</v>
+        <v>89.08020782470703</v>
       </c>
       <c r="C202" t="n">
-        <v>90.58243943087848</v>
+        <v>90.58244718893432</v>
       </c>
       <c r="D202" t="n">
-        <v>88.15776941968373</v>
+        <v>88.15777697007543</v>
       </c>
       <c r="E202" t="n">
-        <v>89.17683605570963</v>
+        <v>89.17684369338068</v>
       </c>
       <c r="F202" t="n">
         <v>343259</v>
@@ -4472,16 +4472,16 @@
         <v>44768</v>
       </c>
       <c r="B203" t="n">
-        <v>87.23534393310547</v>
+        <v>87.2353515625</v>
       </c>
       <c r="C203" t="n">
-        <v>88.80785828511767</v>
+        <v>88.80786605204057</v>
       </c>
       <c r="D203" t="n">
-        <v>86.86636760736479</v>
+        <v>86.86637520448954</v>
       </c>
       <c r="E203" t="n">
-        <v>88.1226270697279</v>
+        <v>88.12263477672209</v>
       </c>
       <c r="F203" t="n">
         <v>558437</v>
@@ -4512,16 +4512,16 @@
         <v>44770</v>
       </c>
       <c r="B205" t="n">
-        <v>93.02468109130859</v>
+        <v>93.02468872070312</v>
       </c>
       <c r="C205" t="n">
-        <v>93.68355833392478</v>
+        <v>93.68356601735695</v>
       </c>
       <c r="D205" t="n">
-        <v>89.02748980512536</v>
+        <v>89.0274971066913</v>
       </c>
       <c r="E205" t="n">
-        <v>90.33646408621723</v>
+        <v>90.33647149513835</v>
       </c>
       <c r="F205" t="n">
         <v>529910</v>
@@ -4552,16 +4552,16 @@
         <v>44774</v>
       </c>
       <c r="B207" t="n">
-        <v>100.1493453979492</v>
+        <v>100.1493377685547</v>
       </c>
       <c r="C207" t="n">
-        <v>102.284108028477</v>
+        <v>102.2841002364559</v>
       </c>
       <c r="D207" t="n">
-        <v>94.3512267417151</v>
+        <v>94.35121955402224</v>
       </c>
       <c r="E207" t="n">
-        <v>94.3512267417151</v>
+        <v>94.35121955402224</v>
       </c>
       <c r="F207" t="n">
         <v>942663</v>
@@ -4572,16 +4572,16 @@
         <v>44775</v>
       </c>
       <c r="B208" t="n">
-        <v>101.4671020507812</v>
+        <v>101.4670944213867</v>
       </c>
       <c r="C208" t="n">
-        <v>102.2050413939763</v>
+        <v>102.2050337090955</v>
       </c>
       <c r="D208" t="n">
-        <v>98.69981610890704</v>
+        <v>98.69980868758699</v>
       </c>
       <c r="E208" t="n">
-        <v>100.0439247000455</v>
+        <v>100.0439171776608</v>
       </c>
       <c r="F208" t="n">
         <v>737331</v>
@@ -4652,16 +4652,16 @@
         <v>44781</v>
       </c>
       <c r="B212" t="n">
-        <v>110.4893264770508</v>
+        <v>110.4893188476562</v>
       </c>
       <c r="C212" t="n">
-        <v>113.2829664650746</v>
+        <v>113.2829586427765</v>
       </c>
       <c r="D212" t="n">
-        <v>108.4511996538819</v>
+        <v>108.451192165222</v>
       </c>
       <c r="E212" t="n">
-        <v>108.9343790159798</v>
+        <v>108.9343714939558</v>
       </c>
       <c r="F212" t="n">
         <v>1248783</v>
@@ -4732,16 +4732,16 @@
         <v>44785</v>
       </c>
       <c r="B216" t="n">
-        <v>88.11385345458984</v>
+        <v>88.11386108398438</v>
       </c>
       <c r="C216" t="n">
-        <v>88.11385345458984</v>
+        <v>88.11386108398438</v>
       </c>
       <c r="D216" t="n">
-        <v>84.52077270447177</v>
+        <v>84.52078002275709</v>
       </c>
       <c r="E216" t="n">
-        <v>84.52077270447177</v>
+        <v>84.52078002275709</v>
       </c>
       <c r="F216" t="n">
         <v>1008211</v>
@@ -4752,16 +4752,16 @@
         <v>44788</v>
       </c>
       <c r="B217" t="n">
-        <v>98.17270660400391</v>
+        <v>98.17271423339844</v>
       </c>
       <c r="C217" t="n">
-        <v>98.83158382953414</v>
+        <v>98.83159151013265</v>
       </c>
       <c r="D217" t="n">
-        <v>86.98058067634858</v>
+        <v>86.98058743595814</v>
       </c>
       <c r="E217" t="n">
-        <v>87.40225834731831</v>
+        <v>87.40226513969814</v>
       </c>
       <c r="F217" t="n">
         <v>1427504</v>
@@ -4792,16 +4792,16 @@
         <v>44790</v>
       </c>
       <c r="B219" t="n">
-        <v>96.52112579345703</v>
+        <v>96.52113342285156</v>
       </c>
       <c r="C219" t="n">
-        <v>96.67046969296776</v>
+        <v>96.67047733416699</v>
       </c>
       <c r="D219" t="n">
-        <v>93.29701473066473</v>
+        <v>93.29702210521333</v>
       </c>
       <c r="E219" t="n">
-        <v>93.29701473066473</v>
+        <v>93.29702210521333</v>
       </c>
       <c r="F219" t="n">
         <v>484266</v>
@@ -4812,16 +4812,16 @@
         <v>44791</v>
       </c>
       <c r="B220" t="n">
-        <v>96.89888763427734</v>
+        <v>96.89888000488281</v>
       </c>
       <c r="C220" t="n">
-        <v>97.78617087563147</v>
+        <v>97.78616317637614</v>
       </c>
       <c r="D220" t="n">
-        <v>95.80953904294859</v>
+        <v>95.80953149932459</v>
       </c>
       <c r="E220" t="n">
-        <v>96.51234415332544</v>
+        <v>96.51233655436566</v>
       </c>
       <c r="F220" t="n">
         <v>225811</v>
@@ -4852,16 +4852,16 @@
         <v>44795</v>
       </c>
       <c r="B222" t="n">
-        <v>88.45647430419922</v>
+        <v>88.45646667480469</v>
       </c>
       <c r="C222" t="n">
-        <v>92.04954856375565</v>
+        <v>92.04954062445751</v>
       </c>
       <c r="D222" t="n">
-        <v>88.03478989086102</v>
+        <v>88.03478229783688</v>
       </c>
       <c r="E222" t="n">
-        <v>92.04954856375565</v>
+        <v>92.04954062445751</v>
       </c>
       <c r="F222" t="n">
         <v>1074017</v>
@@ -4872,16 +4872,16 @@
         <v>44796</v>
       </c>
       <c r="B223" t="n">
-        <v>96.42449951171875</v>
+        <v>96.42449188232422</v>
       </c>
       <c r="C223" t="n">
-        <v>97.50505454197742</v>
+        <v>97.50504682708615</v>
       </c>
       <c r="D223" t="n">
-        <v>87.49890504115571</v>
+        <v>87.49889811798089</v>
       </c>
       <c r="E223" t="n">
-        <v>89.51946479721248</v>
+        <v>89.51945771416493</v>
       </c>
       <c r="F223" t="n">
         <v>1305076</v>
@@ -4892,16 +4892,16 @@
         <v>44797</v>
       </c>
       <c r="B224" t="n">
-        <v>101.0278396606445</v>
+        <v>101.0278472900391</v>
       </c>
       <c r="C224" t="n">
-        <v>102.8551274126588</v>
+        <v>102.855135180046</v>
       </c>
       <c r="D224" t="n">
-        <v>96.94279958605108</v>
+        <v>96.94280690695261</v>
       </c>
       <c r="E224" t="n">
-        <v>96.98672741470787</v>
+        <v>96.98673473892673</v>
       </c>
       <c r="F224" t="n">
         <v>1291806</v>
@@ -4932,16 +4932,16 @@
         <v>44799</v>
       </c>
       <c r="B226" t="n">
-        <v>95.02765655517578</v>
+        <v>95.02766418457031</v>
       </c>
       <c r="C226" t="n">
-        <v>100.7730662934713</v>
+        <v>100.773074384142</v>
       </c>
       <c r="D226" t="n">
-        <v>94.66747385345326</v>
+        <v>94.66748145393015</v>
       </c>
       <c r="E226" t="n">
-        <v>100.3601688603796</v>
+        <v>100.3601769179005</v>
       </c>
       <c r="F226" t="n">
         <v>448340</v>
@@ -4952,16 +4952,16 @@
         <v>44802</v>
       </c>
       <c r="B227" t="n">
-        <v>91.77720642089844</v>
+        <v>91.77721405029297</v>
       </c>
       <c r="C227" t="n">
-        <v>95.84467276233583</v>
+        <v>95.84468072985686</v>
       </c>
       <c r="D227" t="n">
-        <v>91.23253216618707</v>
+        <v>91.23253975030309</v>
       </c>
       <c r="E227" t="n">
-        <v>93.56056637901798</v>
+        <v>93.56057415666235</v>
       </c>
       <c r="F227" t="n">
         <v>661048</v>
@@ -5032,16 +5032,16 @@
         <v>44806</v>
       </c>
       <c r="B231" t="n">
-        <v>88.02600860595703</v>
+        <v>88.02599334716797</v>
       </c>
       <c r="C231" t="n">
-        <v>91.1974053571811</v>
+        <v>91.19738954864913</v>
       </c>
       <c r="D231" t="n">
-        <v>86.98937467200503</v>
+        <v>86.98935959291033</v>
       </c>
       <c r="E231" t="n">
-        <v>89.50189409323706</v>
+        <v>89.50187857861195</v>
       </c>
       <c r="F231" t="n">
         <v>344726</v>
@@ -5052,16 +5052,16 @@
         <v>44809</v>
       </c>
       <c r="B232" t="n">
-        <v>89.43160247802734</v>
+        <v>89.43161010742188</v>
       </c>
       <c r="C232" t="n">
-        <v>89.82692612228165</v>
+        <v>89.82693378540118</v>
       </c>
       <c r="D232" t="n">
-        <v>88.03477931026735</v>
+        <v>88.03478682049915</v>
       </c>
       <c r="E232" t="n">
-        <v>88.81664639508718</v>
+        <v>88.81665397201991</v>
       </c>
       <c r="F232" t="n">
         <v>95765</v>
@@ -5072,16 +5072,16 @@
         <v>44810</v>
       </c>
       <c r="B233" t="n">
-        <v>86.71703338623047</v>
+        <v>86.71702575683594</v>
       </c>
       <c r="C233" t="n">
-        <v>89.31740155371233</v>
+        <v>89.31739369553651</v>
       </c>
       <c r="D233" t="n">
-        <v>85.20600710051012</v>
+        <v>85.2059996040562</v>
       </c>
       <c r="E233" t="n">
-        <v>88.73759303852093</v>
+        <v>88.73758523135686</v>
       </c>
       <c r="F233" t="n">
         <v>519096</v>
@@ -5092,16 +5092,16 @@
         <v>44812</v>
       </c>
       <c r="B234" t="n">
-        <v>88.28955841064453</v>
+        <v>88.28954315185547</v>
       </c>
       <c r="C234" t="n">
-        <v>90.14320042192941</v>
+        <v>90.14318484278159</v>
       </c>
       <c r="D234" t="n">
-        <v>87.12993462797571</v>
+        <v>87.12991956960056</v>
       </c>
       <c r="E234" t="n">
-        <v>88.29834531801718</v>
+        <v>88.29833005770951</v>
       </c>
       <c r="F234" t="n">
         <v>707072</v>
@@ -5112,16 +5112,16 @@
         <v>44813</v>
       </c>
       <c r="B235" t="n">
-        <v>91.80355834960938</v>
+        <v>91.80356597900391</v>
       </c>
       <c r="C235" t="n">
-        <v>92.14617396419217</v>
+        <v>92.14618162206</v>
       </c>
       <c r="D235" t="n">
-        <v>88.81664697669278</v>
+        <v>88.81665435785808</v>
       </c>
       <c r="E235" t="n">
-        <v>88.81664697669278</v>
+        <v>88.81665435785808</v>
       </c>
       <c r="F235" t="n">
         <v>540504</v>
@@ -5152,16 +5152,16 @@
         <v>44817</v>
       </c>
       <c r="B237" t="n">
-        <v>90.74936676025391</v>
+        <v>90.74935913085938</v>
       </c>
       <c r="C237" t="n">
-        <v>92.94562436139803</v>
+        <v>92.94561654736182</v>
       </c>
       <c r="D237" t="n">
-        <v>90.48581316713809</v>
+        <v>90.4858055599008</v>
       </c>
       <c r="E237" t="n">
-        <v>91.36431620759575</v>
+        <v>91.36430852650177</v>
       </c>
       <c r="F237" t="n">
         <v>548480</v>
@@ -5192,16 +5192,16 @@
         <v>44819</v>
       </c>
       <c r="B239" t="n">
-        <v>90.22225189208984</v>
+        <v>90.22225952148438</v>
       </c>
       <c r="C239" t="n">
-        <v>93.36729411773216</v>
+        <v>93.36730201307846</v>
       </c>
       <c r="D239" t="n">
-        <v>89.21197884353981</v>
+        <v>89.2119863875034</v>
       </c>
       <c r="E239" t="n">
-        <v>89.60730249710758</v>
+        <v>89.60731007450063</v>
       </c>
       <c r="F239" t="n">
         <v>512054</v>
@@ -5232,16 +5232,16 @@
         <v>44823</v>
       </c>
       <c r="B241" t="n">
-        <v>88.99236297607422</v>
+        <v>88.99235534667969</v>
       </c>
       <c r="C241" t="n">
-        <v>89.82693820506938</v>
+        <v>89.82693050412597</v>
       </c>
       <c r="D241" t="n">
-        <v>86.69946944510852</v>
+        <v>86.69946201228579</v>
       </c>
       <c r="E241" t="n">
-        <v>87.393487669275</v>
+        <v>87.39348017695347</v>
       </c>
       <c r="F241" t="n">
         <v>601912</v>
@@ -5272,16 +5272,16 @@
         <v>44825</v>
       </c>
       <c r="B243" t="n">
-        <v>89.51066589355469</v>
+        <v>89.51067352294922</v>
       </c>
       <c r="C243" t="n">
-        <v>91.2237439814253</v>
+        <v>91.22375175683315</v>
       </c>
       <c r="D243" t="n">
-        <v>87.51646712709899</v>
+        <v>87.51647458651904</v>
       </c>
       <c r="E243" t="n">
-        <v>90.16954311234272</v>
+        <v>90.16955079789631</v>
       </c>
       <c r="F243" t="n">
         <v>553017</v>
@@ -5292,16 +5292,16 @@
         <v>44826</v>
       </c>
       <c r="B244" t="n">
-        <v>89.0802001953125</v>
+        <v>89.08020782470703</v>
       </c>
       <c r="C244" t="n">
-        <v>91.53122422253455</v>
+        <v>91.53123206185035</v>
       </c>
       <c r="D244" t="n">
-        <v>86.27777364868685</v>
+        <v>86.27778103806376</v>
       </c>
       <c r="E244" t="n">
-        <v>89.43160271471611</v>
+        <v>89.43161037420698</v>
       </c>
       <c r="F244" t="n">
         <v>985794</v>
@@ -5312,16 +5312,16 @@
         <v>44827</v>
       </c>
       <c r="B245" t="n">
-        <v>88.11385345458984</v>
+        <v>88.11386108398438</v>
       </c>
       <c r="C245" t="n">
-        <v>89.37011301088573</v>
+        <v>89.37012074905431</v>
       </c>
       <c r="D245" t="n">
-        <v>86.19871664923903</v>
+        <v>86.19872411281021</v>
       </c>
       <c r="E245" t="n">
-        <v>87.85029987398948</v>
+        <v>87.85030748056406</v>
       </c>
       <c r="F245" t="n">
         <v>433707</v>
@@ -5332,16 +5332,16 @@
         <v>44830</v>
       </c>
       <c r="B246" t="n">
-        <v>84.33629608154297</v>
+        <v>84.33628082275391</v>
       </c>
       <c r="C246" t="n">
-        <v>89.18563015715517</v>
+        <v>89.18561402098628</v>
       </c>
       <c r="D246" t="n">
-        <v>84.24844711361402</v>
+        <v>84.24843187071929</v>
       </c>
       <c r="E246" t="n">
-        <v>88.13142913711454</v>
+        <v>88.13141319168002</v>
       </c>
       <c r="F246" t="n">
         <v>548585</v>
@@ -5372,16 +5372,16 @@
         <v>44832</v>
       </c>
       <c r="B248" t="n">
-        <v>86.94544982910156</v>
+        <v>86.94544219970703</v>
       </c>
       <c r="C248" t="n">
-        <v>88.52675133215702</v>
+        <v>88.52674356400453</v>
       </c>
       <c r="D248" t="n">
-        <v>85.29385976947805</v>
+        <v>85.29385228500924</v>
       </c>
       <c r="E248" t="n">
-        <v>86.5501194265028</v>
+        <v>86.5501118317982</v>
       </c>
       <c r="F248" t="n">
         <v>626382</v>
@@ -5392,16 +5392,16 @@
         <v>44833</v>
       </c>
       <c r="B249" t="n">
-        <v>87.27049255371094</v>
+        <v>87.27047729492188</v>
       </c>
       <c r="C249" t="n">
-        <v>87.79759976248249</v>
+        <v>87.79758441153149</v>
       </c>
       <c r="D249" t="n">
-        <v>84.51199342491191</v>
+        <v>84.51197864843198</v>
       </c>
       <c r="E249" t="n">
-        <v>85.399283410401</v>
+        <v>85.39926847878306</v>
       </c>
       <c r="F249" t="n">
         <v>546314</v>
@@ -5432,16 +5432,16 @@
         <v>44837</v>
       </c>
       <c r="B251" t="n">
-        <v>94.77289581298828</v>
+        <v>94.77291107177734</v>
       </c>
       <c r="C251" t="n">
-        <v>95.68653968508768</v>
+        <v>95.68655509097681</v>
       </c>
       <c r="D251" t="n">
-        <v>90.92505530568604</v>
+        <v>90.92506994495847</v>
       </c>
       <c r="E251" t="n">
-        <v>91.36430678059274</v>
+        <v>91.36432149058628</v>
       </c>
       <c r="F251" t="n">
         <v>814581</v>
@@ -5492,16 +5492,16 @@
         <v>44840</v>
       </c>
       <c r="B254" t="n">
-        <v>99.09513854980469</v>
+        <v>99.09514617919922</v>
       </c>
       <c r="C254" t="n">
-        <v>99.89457277411294</v>
+        <v>99.89458046505639</v>
       </c>
       <c r="D254" t="n">
-        <v>94.70262366200211</v>
+        <v>94.70263095321427</v>
       </c>
       <c r="E254" t="n">
-        <v>95.71289672424005</v>
+        <v>95.71290409323375</v>
       </c>
       <c r="F254" t="n">
         <v>1317655</v>
@@ -5512,16 +5512,16 @@
         <v>44841</v>
       </c>
       <c r="B255" t="n">
-        <v>96.81101989746094</v>
+        <v>96.81102752685547</v>
       </c>
       <c r="C255" t="n">
-        <v>98.87550713835859</v>
+        <v>98.87551493044936</v>
       </c>
       <c r="D255" t="n">
-        <v>95.87102203344506</v>
+        <v>95.87102958876109</v>
       </c>
       <c r="E255" t="n">
-        <v>97.69830973062682</v>
+        <v>97.69831742994607</v>
       </c>
       <c r="F255" t="n">
         <v>390672</v>
@@ -5532,16 +5532,16 @@
         <v>44844</v>
       </c>
       <c r="B256" t="n">
-        <v>96.52112579345703</v>
+        <v>96.52113342285156</v>
       </c>
       <c r="C256" t="n">
-        <v>97.95308325233714</v>
+        <v>97.95309099491899</v>
       </c>
       <c r="D256" t="n">
-        <v>94.96617174989328</v>
+        <v>94.96617925637837</v>
       </c>
       <c r="E256" t="n">
-        <v>97.16242922191877</v>
+        <v>97.16243690200434</v>
       </c>
       <c r="F256" t="n">
         <v>391665</v>
@@ -5552,16 +5552,16 @@
         <v>44845</v>
       </c>
       <c r="B257" t="n">
-        <v>88.64974975585938</v>
+        <v>88.64974212646484</v>
       </c>
       <c r="C257" t="n">
-        <v>96.94281434223674</v>
+        <v>96.94280599912264</v>
       </c>
       <c r="D257" t="n">
-        <v>87.13872337332482</v>
+        <v>87.1387158739726</v>
       </c>
       <c r="E257" t="n">
-        <v>96.52113661370647</v>
+        <v>96.5211283068829</v>
       </c>
       <c r="F257" t="n">
         <v>1649810</v>
@@ -5592,16 +5592,16 @@
         <v>44848</v>
       </c>
       <c r="B259" t="n">
-        <v>82.71985626220703</v>
+        <v>82.71984100341797</v>
       </c>
       <c r="C259" t="n">
-        <v>90.16955890031807</v>
+        <v>90.16954226733124</v>
       </c>
       <c r="D259" t="n">
-        <v>82.667141517811</v>
+        <v>82.66712626874587</v>
       </c>
       <c r="E259" t="n">
-        <v>86.64675954369901</v>
+        <v>86.64674356053986</v>
       </c>
       <c r="F259" t="n">
         <v>951929</v>
@@ -5632,16 +5632,16 @@
         <v>44852</v>
       </c>
       <c r="B261" t="n">
-        <v>80.54115295410156</v>
+        <v>80.54116058349609</v>
       </c>
       <c r="C261" t="n">
-        <v>85.61011216687361</v>
+        <v>85.61012027643372</v>
       </c>
       <c r="D261" t="n">
-        <v>79.24096560302623</v>
+        <v>79.24097310925836</v>
       </c>
       <c r="E261" t="n">
-        <v>84.42413449202566</v>
+        <v>84.42414248924207</v>
       </c>
       <c r="F261" t="n">
         <v>1514560</v>
@@ -5652,16 +5652,16 @@
         <v>44853</v>
       </c>
       <c r="B262" t="n">
-        <v>80.47087097167969</v>
+        <v>80.47087860107422</v>
       </c>
       <c r="C262" t="n">
-        <v>81.52507856055549</v>
+        <v>81.52508628989879</v>
       </c>
       <c r="D262" t="n">
-        <v>79.10919538524473</v>
+        <v>79.10920288553962</v>
       </c>
       <c r="E262" t="n">
-        <v>80.38302201488482</v>
+        <v>80.38302963595044</v>
       </c>
       <c r="F262" t="n">
         <v>1204425</v>
@@ -5672,16 +5672,16 @@
         <v>44854</v>
       </c>
       <c r="B263" t="n">
-        <v>77.81778717041016</v>
+        <v>77.81779479980469</v>
       </c>
       <c r="C263" t="n">
-        <v>80.72562957529622</v>
+        <v>80.72563748978079</v>
       </c>
       <c r="D263" t="n">
-        <v>76.50003284276583</v>
+        <v>76.50004034296538</v>
       </c>
       <c r="E263" t="n">
-        <v>80.4708629343249</v>
+        <v>80.4708708238317</v>
       </c>
       <c r="F263" t="n">
         <v>1064344</v>
@@ -5692,16 +5692,16 @@
         <v>44855</v>
       </c>
       <c r="B264" t="n">
-        <v>82.25423431396484</v>
+        <v>82.25422668457031</v>
       </c>
       <c r="C264" t="n">
-        <v>85.73310542506498</v>
+        <v>85.73309747299184</v>
       </c>
       <c r="D264" t="n">
-        <v>75.13836128205794</v>
+        <v>75.13835431268782</v>
       </c>
       <c r="E264" t="n">
-        <v>77.967142043229</v>
+        <v>77.96713481147866</v>
       </c>
       <c r="F264" t="n">
         <v>1421863</v>
@@ -5772,16 +5772,16 @@
         <v>44861</v>
       </c>
       <c r="B268" t="n">
-        <v>78.95984649658203</v>
+        <v>78.95985412597656</v>
       </c>
       <c r="C268" t="n">
-        <v>81.79741410940505</v>
+        <v>81.79742201297594</v>
       </c>
       <c r="D268" t="n">
-        <v>78.12527133528192</v>
+        <v>78.12527888403669</v>
       </c>
       <c r="E268" t="n">
-        <v>80.63779042823175</v>
+        <v>80.63779821975547</v>
       </c>
       <c r="F268" t="n">
         <v>872704</v>
@@ -5792,16 +5792,16 @@
         <v>44862</v>
       </c>
       <c r="B269" t="n">
-        <v>81.43722534179688</v>
+        <v>81.43721771240234</v>
       </c>
       <c r="C269" t="n">
-        <v>82.14003042210881</v>
+        <v>82.14002272687244</v>
       </c>
       <c r="D269" t="n">
-        <v>78.40639267564933</v>
+        <v>78.40638533019641</v>
       </c>
       <c r="E269" t="n">
-        <v>79.04770281411741</v>
+        <v>79.04769540858378</v>
       </c>
       <c r="F269" t="n">
         <v>705309</v>
@@ -5812,16 +5812,16 @@
         <v>44865</v>
       </c>
       <c r="B270" t="n">
-        <v>83.36994171142578</v>
+        <v>83.36993408203125</v>
       </c>
       <c r="C270" t="n">
-        <v>84.17816291781504</v>
+        <v>84.17815521445814</v>
       </c>
       <c r="D270" t="n">
-        <v>79.07406228540991</v>
+        <v>79.07405504914219</v>
       </c>
       <c r="E270" t="n">
-        <v>79.07406228540991</v>
+        <v>79.07405504914219</v>
       </c>
       <c r="F270" t="n">
         <v>956071</v>
@@ -5852,16 +5852,16 @@
         <v>44868</v>
       </c>
       <c r="B272" t="n">
-        <v>86.58525085449219</v>
+        <v>86.58525848388672</v>
       </c>
       <c r="C272" t="n">
-        <v>88.46524668009084</v>
+        <v>88.4652544751398</v>
       </c>
       <c r="D272" t="n">
-        <v>84.04637779929271</v>
+        <v>84.04638520497635</v>
       </c>
       <c r="E272" t="n">
-        <v>85.59254490810744</v>
+        <v>85.59255245003042</v>
       </c>
       <c r="F272" t="n">
         <v>991113</v>
@@ -5872,16 +5872,16 @@
         <v>44869</v>
       </c>
       <c r="B273" t="n">
-        <v>83.484130859375</v>
+        <v>83.48413848876953</v>
       </c>
       <c r="C273" t="n">
-        <v>88.72879432924752</v>
+        <v>88.728802437938</v>
       </c>
       <c r="D273" t="n">
-        <v>82.78133254952142</v>
+        <v>82.78134011468907</v>
       </c>
       <c r="E273" t="n">
-        <v>87.59552476569932</v>
+        <v>87.59553277082331</v>
       </c>
       <c r="F273" t="n">
         <v>612180</v>
@@ -5892,16 +5892,16 @@
         <v>44872</v>
       </c>
       <c r="B274" t="n">
-        <v>83.19422149658203</v>
+        <v>83.19422912597656</v>
       </c>
       <c r="C274" t="n">
-        <v>84.51197583941561</v>
+        <v>84.51198358965588</v>
       </c>
       <c r="D274" t="n">
-        <v>82.2805843837025</v>
+        <v>82.2805919293112</v>
       </c>
       <c r="E274" t="n">
-        <v>83.03609070734419</v>
+        <v>83.03609832223721</v>
       </c>
       <c r="F274" t="n">
         <v>752715</v>
@@ -5932,16 +5932,16 @@
         <v>44874</v>
       </c>
       <c r="B276" t="n">
-        <v>90.18711853027344</v>
+        <v>90.18712615966797</v>
       </c>
       <c r="C276" t="n">
-        <v>93.10374813592868</v>
+        <v>93.10375601205598</v>
       </c>
       <c r="D276" t="n">
-        <v>83.4665694385159</v>
+        <v>83.46657649938446</v>
       </c>
       <c r="E276" t="n">
-        <v>83.89703401910188</v>
+        <v>83.89704111638565</v>
       </c>
       <c r="F276" t="n">
         <v>2468383</v>
@@ -5952,16 +5952,16 @@
         <v>44875</v>
       </c>
       <c r="B277" t="n">
-        <v>90.49459075927734</v>
+        <v>90.49459838867188</v>
       </c>
       <c r="C277" t="n">
-        <v>94.21944139071987</v>
+        <v>94.21944933414814</v>
       </c>
       <c r="D277" t="n">
-        <v>85.65403762792715</v>
+        <v>85.65404484922558</v>
       </c>
       <c r="E277" t="n">
-        <v>85.67160473785169</v>
+        <v>85.67161196063115</v>
       </c>
       <c r="F277" t="n">
         <v>2820385</v>
@@ -5972,16 +5972,16 @@
         <v>44876</v>
       </c>
       <c r="B278" t="n">
-        <v>89.57216644287109</v>
+        <v>89.57215881347656</v>
       </c>
       <c r="C278" t="n">
-        <v>91.51365729821109</v>
+        <v>91.51364950344822</v>
       </c>
       <c r="D278" t="n">
-        <v>88.06114018741653</v>
+        <v>88.06113268672509</v>
       </c>
       <c r="E278" t="n">
-        <v>90.4858103811098</v>
+        <v>90.48580267389478</v>
       </c>
       <c r="F278" t="n">
         <v>1123849</v>
@@ -5992,16 +5992,16 @@
         <v>44879</v>
       </c>
       <c r="B279" t="n">
-        <v>88.816650390625</v>
+        <v>88.81664276123047</v>
       </c>
       <c r="C279" t="n">
-        <v>90.389171537141</v>
+        <v>90.38916377266612</v>
       </c>
       <c r="D279" t="n">
-        <v>85.91759456330244</v>
+        <v>85.91758718293825</v>
       </c>
       <c r="E279" t="n">
-        <v>89.08020396694791</v>
+        <v>89.08019631491399</v>
       </c>
       <c r="F279" t="n">
         <v>689741</v>
@@ -6072,16 +6072,16 @@
         <v>44886</v>
       </c>
       <c r="B283" t="n">
-        <v>80.0404052734375</v>
+        <v>80.04041290283203</v>
       </c>
       <c r="C283" t="n">
-        <v>82.56171118314468</v>
+        <v>82.5617190528683</v>
       </c>
       <c r="D283" t="n">
-        <v>79.6275078095798</v>
+        <v>79.62751539961722</v>
       </c>
       <c r="E283" t="n">
-        <v>82.0697449675642</v>
+        <v>82.06975279039395</v>
       </c>
       <c r="F283" t="n">
         <v>597582</v>
@@ -6112,16 +6112,16 @@
         <v>44888</v>
       </c>
       <c r="B285" t="n">
-        <v>77.27313232421875</v>
+        <v>77.27312469482422</v>
       </c>
       <c r="C285" t="n">
-        <v>78.72266378819657</v>
+        <v>78.7226560156857</v>
       </c>
       <c r="D285" t="n">
-        <v>75.9993055027379</v>
+        <v>75.99929799911189</v>
       </c>
       <c r="E285" t="n">
-        <v>78.02864553083879</v>
+        <v>78.0286378268503</v>
       </c>
       <c r="F285" t="n">
         <v>751617</v>
@@ -6132,16 +6132,16 @@
         <v>44889</v>
       </c>
       <c r="B286" t="n">
-        <v>78.80170440673828</v>
+        <v>78.80171966552734</v>
       </c>
       <c r="C286" t="n">
-        <v>79.5045093805833</v>
+        <v>79.5045247754602</v>
       </c>
       <c r="D286" t="n">
-        <v>77.1940492556631</v>
+        <v>77.19406420315345</v>
       </c>
       <c r="E286" t="n">
-        <v>77.52787793189476</v>
+        <v>77.52789294402611</v>
       </c>
       <c r="F286" t="n">
         <v>618983</v>
@@ -6172,16 +6172,16 @@
         <v>44893</v>
       </c>
       <c r="B288" t="n">
-        <v>75.56882476806641</v>
+        <v>75.56881713867188</v>
       </c>
       <c r="C288" t="n">
-        <v>78.24826158688813</v>
+        <v>78.24825368697887</v>
       </c>
       <c r="D288" t="n">
-        <v>75.2877040774397</v>
+        <v>75.28769647642699</v>
       </c>
       <c r="E288" t="n">
-        <v>77.14134593522536</v>
+        <v>77.1413381470698</v>
       </c>
       <c r="F288" t="n">
         <v>519110</v>
@@ -6232,16 +6232,16 @@
         <v>44896</v>
       </c>
       <c r="B291" t="n">
-        <v>79.21462249755859</v>
+        <v>79.21460723876953</v>
       </c>
       <c r="C291" t="n">
-        <v>81.06826456490624</v>
+        <v>81.06824894905768</v>
       </c>
       <c r="D291" t="n">
-        <v>78.69630888848674</v>
+        <v>78.69629372953831</v>
       </c>
       <c r="E291" t="n">
-        <v>79.07406548757766</v>
+        <v>79.07405025586351</v>
       </c>
       <c r="F291" t="n">
         <v>741238</v>
@@ -6292,16 +6292,16 @@
         <v>44901</v>
       </c>
       <c r="B294" t="n">
-        <v>77.94957733154297</v>
+        <v>77.94956970214844</v>
       </c>
       <c r="C294" t="n">
-        <v>81.69199543905461</v>
+        <v>81.69198744336707</v>
       </c>
       <c r="D294" t="n">
-        <v>77.94957733154297</v>
+        <v>77.94956970214844</v>
       </c>
       <c r="E294" t="n">
-        <v>81.04190506911468</v>
+        <v>81.0418971370554</v>
       </c>
       <c r="F294" t="n">
         <v>575865</v>
@@ -6312,16 +6312,16 @@
         <v>44902</v>
       </c>
       <c r="B295" t="n">
-        <v>76.15741729736328</v>
+        <v>76.15742492675781</v>
       </c>
       <c r="C295" t="n">
-        <v>78.43273655389115</v>
+        <v>78.4327444112255</v>
       </c>
       <c r="D295" t="n">
-        <v>74.76059422398934</v>
+        <v>74.76060171345117</v>
       </c>
       <c r="E295" t="n">
-        <v>77.82656741804537</v>
+        <v>77.82657521465414</v>
       </c>
       <c r="F295" t="n">
         <v>782541</v>
@@ -6372,16 +6372,16 @@
         <v>44907</v>
       </c>
       <c r="B298" t="n">
-        <v>72.23931121826172</v>
+        <v>72.23929595947266</v>
       </c>
       <c r="C298" t="n">
-        <v>74.02267139828965</v>
+        <v>74.02265576280934</v>
       </c>
       <c r="D298" t="n">
-        <v>70.51743928329</v>
+        <v>70.5174243882043</v>
       </c>
       <c r="E298" t="n">
-        <v>72.73127079828416</v>
+        <v>72.73125543558065</v>
       </c>
       <c r="F298" t="n">
         <v>769701</v>
@@ -6392,16 +6392,16 @@
         <v>44908</v>
       </c>
       <c r="B299" t="n">
-        <v>70.42080688476562</v>
+        <v>70.42079925537109</v>
       </c>
       <c r="C299" t="n">
-        <v>74.92752506588127</v>
+        <v>74.92751694822861</v>
       </c>
       <c r="D299" t="n">
-        <v>69.92884062483354</v>
+        <v>69.92883304873867</v>
       </c>
       <c r="E299" t="n">
-        <v>71.958187204355</v>
+        <v>71.9581794084006</v>
       </c>
       <c r="F299" t="n">
         <v>758036</v>
@@ -6452,16 +6452,16 @@
         <v>44911</v>
       </c>
       <c r="B302" t="n">
-        <v>64.96529388427734</v>
+        <v>64.96530151367188</v>
       </c>
       <c r="C302" t="n">
-        <v>66.81015553814807</v>
+        <v>66.81016338419947</v>
       </c>
       <c r="D302" t="n">
-        <v>63.87595204573682</v>
+        <v>63.87595954720123</v>
       </c>
       <c r="E302" t="n">
-        <v>66.32697620928745</v>
+        <v>66.32698399859524</v>
       </c>
       <c r="F302" t="n">
         <v>628655</v>
@@ -6532,16 +6532,16 @@
         <v>44917</v>
       </c>
       <c r="B306" t="n">
-        <v>67.46903991699219</v>
+        <v>67.46903228759766</v>
       </c>
       <c r="C306" t="n">
-        <v>72.45015082309504</v>
+        <v>72.45014263043683</v>
       </c>
       <c r="D306" t="n">
-        <v>64.56997704227857</v>
+        <v>64.56996974070987</v>
       </c>
       <c r="E306" t="n">
-        <v>70.28024712084742</v>
+        <v>70.28023917356177</v>
       </c>
       <c r="F306" t="n">
         <v>477342</v>
@@ -6552,16 +6552,16 @@
         <v>44918</v>
       </c>
       <c r="B307" t="n">
-        <v>70.72828674316406</v>
+        <v>70.72827911376953</v>
       </c>
       <c r="C307" t="n">
-        <v>70.85127664146475</v>
+        <v>70.85126899880341</v>
       </c>
       <c r="D307" t="n">
-        <v>68.02249557565553</v>
+        <v>68.02248823813217</v>
       </c>
       <c r="E307" t="n">
-        <v>68.52324207657881</v>
+        <v>68.52323468504038</v>
       </c>
       <c r="F307" t="n">
         <v>762496</v>
@@ -6592,16 +6592,16 @@
         <v>44922</v>
       </c>
       <c r="B309" t="n">
-        <v>67.8204345703125</v>
+        <v>67.82042694091797</v>
       </c>
       <c r="C309" t="n">
-        <v>70.45594378992226</v>
+        <v>70.45593586404866</v>
       </c>
       <c r="D309" t="n">
-        <v>67.38118303371087</v>
+        <v>67.38117545372953</v>
       </c>
       <c r="E309" t="n">
-        <v>68.96249124645534</v>
+        <v>68.96248348858624</v>
       </c>
       <c r="F309" t="n">
         <v>436455</v>
@@ -6632,16 +6632,16 @@
         <v>44924</v>
       </c>
       <c r="B311" t="n">
-        <v>70.66677856445312</v>
+        <v>70.66678619384766</v>
       </c>
       <c r="C311" t="n">
-        <v>70.66677856445312</v>
+        <v>70.66678619384766</v>
       </c>
       <c r="D311" t="n">
-        <v>67.35481873074851</v>
+        <v>67.35482600257404</v>
       </c>
       <c r="E311" t="n">
-        <v>68.52322924831307</v>
+        <v>68.52323664628368</v>
       </c>
       <c r="F311" t="n">
         <v>1109758</v>
@@ -6652,16 +6652,16 @@
         <v>44928</v>
       </c>
       <c r="B312" t="n">
-        <v>66.42362213134766</v>
+        <v>66.42361450195312</v>
       </c>
       <c r="C312" t="n">
-        <v>69.7707169086322</v>
+        <v>69.7707088947915</v>
       </c>
       <c r="D312" t="n">
-        <v>66.12492758216369</v>
+        <v>66.12491998707712</v>
       </c>
       <c r="E312" t="n">
-        <v>68.8834335739509</v>
+        <v>68.88342566202327</v>
       </c>
       <c r="F312" t="n">
         <v>452524</v>
@@ -6672,16 +6672,16 @@
         <v>44929</v>
       </c>
       <c r="B313" t="n">
-        <v>66.99463653564453</v>
+        <v>66.99464416503906</v>
       </c>
       <c r="C313" t="n">
-        <v>69.74434834362098</v>
+        <v>69.74435628615456</v>
       </c>
       <c r="D313" t="n">
-        <v>65.50117750604407</v>
+        <v>65.50118496536248</v>
       </c>
       <c r="E313" t="n">
-        <v>66.60809309463926</v>
+        <v>66.60810068001396</v>
       </c>
       <c r="F313" t="n">
         <v>913081</v>
@@ -6692,16 +6692,16 @@
         <v>44930</v>
       </c>
       <c r="B314" t="n">
-        <v>67.00341033935547</v>
+        <v>67.00341796875</v>
       </c>
       <c r="C314" t="n">
-        <v>68.40902028058885</v>
+        <v>68.40902807003422</v>
       </c>
       <c r="D314" t="n">
-        <v>66.33575298995903</v>
+        <v>66.33576054333025</v>
       </c>
       <c r="E314" t="n">
-        <v>66.52023778669582</v>
+        <v>66.52024536107352</v>
       </c>
       <c r="F314" t="n">
         <v>669125</v>
@@ -6712,16 +6712,16 @@
         <v>44931</v>
       </c>
       <c r="B315" t="n">
-        <v>65.42212677001953</v>
+        <v>65.422119140625</v>
       </c>
       <c r="C315" t="n">
-        <v>68.18062596110393</v>
+        <v>68.18061801001888</v>
       </c>
       <c r="D315" t="n">
-        <v>65.07072419038622</v>
+        <v>65.07071660197154</v>
       </c>
       <c r="E315" t="n">
-        <v>67.19670007862</v>
+        <v>67.19669224227836</v>
       </c>
       <c r="F315" t="n">
         <v>721996</v>
@@ -6752,16 +6752,16 @@
         <v>44935</v>
       </c>
       <c r="B317" t="n">
-        <v>69.62136840820312</v>
+        <v>69.62136077880859</v>
       </c>
       <c r="C317" t="n">
-        <v>70.95669012764992</v>
+        <v>70.95668235192537</v>
       </c>
       <c r="D317" t="n">
-        <v>66.80137435331271</v>
+        <v>66.80136703294467</v>
       </c>
       <c r="E317" t="n">
-        <v>66.99464610141148</v>
+        <v>66.99463875986392</v>
       </c>
       <c r="F317" t="n">
         <v>604476</v>
@@ -6812,16 +6812,16 @@
         <v>44938</v>
       </c>
       <c r="B320" t="n">
-        <v>74.93631744384766</v>
+        <v>74.93630218505859</v>
       </c>
       <c r="C320" t="n">
-        <v>75.89388260992675</v>
+        <v>75.893867156155</v>
       </c>
       <c r="D320" t="n">
-        <v>71.29052822216363</v>
+        <v>71.29051370574263</v>
       </c>
       <c r="E320" t="n">
-        <v>72.90697071616947</v>
+        <v>72.90695587060291</v>
       </c>
       <c r="F320" t="n">
         <v>1386963</v>
@@ -6832,16 +6832,16 @@
         <v>44939</v>
       </c>
       <c r="B321" t="n">
-        <v>74.85724639892578</v>
+        <v>74.85723114013672</v>
       </c>
       <c r="C321" t="n">
-        <v>76.07836513995662</v>
+        <v>76.07834963225653</v>
       </c>
       <c r="D321" t="n">
-        <v>73.63612765789495</v>
+        <v>73.6361126480169</v>
       </c>
       <c r="E321" t="n">
-        <v>74.82210547154654</v>
+        <v>74.82209021992054</v>
       </c>
       <c r="F321" t="n">
         <v>628080</v>
@@ -6872,16 +6872,16 @@
         <v>44943</v>
       </c>
       <c r="B323" t="n">
-        <v>72.37985992431641</v>
+        <v>72.37986755371094</v>
       </c>
       <c r="C323" t="n">
-        <v>72.69612153304253</v>
+        <v>72.69612919577348</v>
       </c>
       <c r="D323" t="n">
-        <v>70.11332062926112</v>
+        <v>70.11332801974497</v>
       </c>
       <c r="E323" t="n">
-        <v>71.02696453197595</v>
+        <v>71.02697201876489</v>
       </c>
       <c r="F323" t="n">
         <v>1038524</v>
@@ -6992,16 +6992,16 @@
         <v>44951</v>
       </c>
       <c r="B329" t="n">
-        <v>77.85293579101562</v>
+        <v>77.85294342041016</v>
       </c>
       <c r="C329" t="n">
-        <v>79.94377045148158</v>
+        <v>79.94377828577274</v>
       </c>
       <c r="D329" t="n">
-        <v>77.15891763884663</v>
+        <v>77.15892520022911</v>
       </c>
       <c r="E329" t="n">
-        <v>79.94377045148158</v>
+        <v>79.94377828577274</v>
       </c>
       <c r="F329" t="n">
         <v>568888</v>
@@ -7012,16 +7012,16 @@
         <v>44952</v>
       </c>
       <c r="B330" t="n">
-        <v>79.52207946777344</v>
+        <v>79.5220947265625</v>
       </c>
       <c r="C330" t="n">
-        <v>80.04918656912542</v>
+        <v>80.04920192905641</v>
       </c>
       <c r="D330" t="n">
-        <v>77.41367787214632</v>
+        <v>77.41369272637284</v>
       </c>
       <c r="E330" t="n">
-        <v>77.87928333622141</v>
+        <v>77.87929827978883</v>
       </c>
       <c r="F330" t="n">
         <v>392968</v>
@@ -7032,16 +7032,16 @@
         <v>44953</v>
       </c>
       <c r="B331" t="n">
-        <v>81.18246459960938</v>
+        <v>81.18247222900391</v>
       </c>
       <c r="C331" t="n">
-        <v>81.18246459960938</v>
+        <v>81.18247222900391</v>
       </c>
       <c r="D331" t="n">
-        <v>75.73574203500689</v>
+        <v>75.7357491525274</v>
       </c>
       <c r="E331" t="n">
-        <v>78.99498732668607</v>
+        <v>78.99499475050509</v>
       </c>
       <c r="F331" t="n">
         <v>1276572</v>
@@ -7092,16 +7092,16 @@
         <v>44958</v>
       </c>
       <c r="B334" t="n">
-        <v>77.84414672851562</v>
+        <v>77.84415435791016</v>
       </c>
       <c r="C334" t="n">
-        <v>79.74170961019361</v>
+        <v>79.74171742556558</v>
       </c>
       <c r="D334" t="n">
-        <v>76.97443068701511</v>
+        <v>76.97443823117001</v>
       </c>
       <c r="E334" t="n">
-        <v>78.62601381573906</v>
+        <v>78.62602152176328</v>
       </c>
       <c r="F334" t="n">
         <v>624239</v>
@@ -7132,16 +7132,16 @@
         <v>44960</v>
       </c>
       <c r="B336" t="n">
-        <v>78.43274688720703</v>
+        <v>78.43275451660156</v>
       </c>
       <c r="C336" t="n">
-        <v>80.04919589494379</v>
+        <v>80.04920368157528</v>
       </c>
       <c r="D336" t="n">
-        <v>76.42976111654413</v>
+        <v>76.42976855110207</v>
       </c>
       <c r="E336" t="n">
-        <v>79.05648321386462</v>
+        <v>79.0564909039319</v>
       </c>
       <c r="F336" t="n">
         <v>709735</v>
@@ -7232,16 +7232,16 @@
         <v>44967</v>
       </c>
       <c r="B341" t="n">
-        <v>71.36080169677734</v>
+        <v>71.36079406738281</v>
       </c>
       <c r="C341" t="n">
-        <v>73.24957778634779</v>
+        <v>73.24956995501861</v>
       </c>
       <c r="D341" t="n">
-        <v>70.52621982463492</v>
+        <v>70.52621228446802</v>
       </c>
       <c r="E341" t="n">
-        <v>72.74005113979474</v>
+        <v>72.74004336294057</v>
       </c>
       <c r="F341" t="n">
         <v>649433</v>
@@ -7252,16 +7252,16 @@
         <v>44970</v>
       </c>
       <c r="B342" t="n">
-        <v>73.79424285888672</v>
+        <v>73.79425811767578</v>
       </c>
       <c r="C342" t="n">
-        <v>74.05779640721795</v>
+        <v>74.05781172050324</v>
       </c>
       <c r="D342" t="n">
-        <v>70.90396754262024</v>
+        <v>70.90398220377323</v>
       </c>
       <c r="E342" t="n">
-        <v>71.35200589380526</v>
+        <v>71.35202064760129</v>
       </c>
       <c r="F342" t="n">
         <v>400048</v>
@@ -7292,16 +7292,16 @@
         <v>44972</v>
       </c>
       <c r="B344" t="n">
-        <v>73.78546905517578</v>
+        <v>73.78546142578125</v>
       </c>
       <c r="C344" t="n">
-        <v>74.93631260463282</v>
+        <v>74.93630485624141</v>
       </c>
       <c r="D344" t="n">
-        <v>71.65070638245331</v>
+        <v>71.65069897379257</v>
       </c>
       <c r="E344" t="n">
-        <v>72.23930851791685</v>
+        <v>72.23930104839484</v>
       </c>
       <c r="F344" t="n">
         <v>619864</v>
@@ -7332,16 +7332,16 @@
         <v>44974</v>
       </c>
       <c r="B346" t="n">
-        <v>58.25353622436523</v>
+        <v>58.25353240966797</v>
       </c>
       <c r="C346" t="n">
-        <v>64.91259108039837</v>
+        <v>64.91258682963696</v>
       </c>
       <c r="D346" t="n">
-        <v>57.36625295251188</v>
+        <v>57.36624919591782</v>
       </c>
       <c r="E346" t="n">
-        <v>64.68417840630755</v>
+        <v>64.68417417050361</v>
       </c>
       <c r="F346" t="n">
         <v>4993765</v>
@@ -7412,16 +7412,16 @@
         <v>44984</v>
       </c>
       <c r="B350" t="n">
-        <v>56.37353515625</v>
+        <v>56.37353897094727</v>
       </c>
       <c r="C350" t="n">
-        <v>59.81726526214266</v>
+        <v>59.81726930987105</v>
       </c>
       <c r="D350" t="n">
-        <v>56.37353515625</v>
+        <v>56.37353897094727</v>
       </c>
       <c r="E350" t="n">
-        <v>59.69427537996406</v>
+        <v>59.69427941936994</v>
       </c>
       <c r="F350" t="n">
         <v>610901</v>
@@ -7432,16 +7432,16 @@
         <v>44985</v>
       </c>
       <c r="B351" t="n">
-        <v>56.48774337768555</v>
+        <v>56.48774719238281</v>
       </c>
       <c r="C351" t="n">
-        <v>57.19932863514759</v>
+        <v>57.19933249789922</v>
       </c>
       <c r="D351" t="n">
-        <v>55.53017165976352</v>
+        <v>55.53017540979462</v>
       </c>
       <c r="E351" t="n">
-        <v>56.82157209178407</v>
+        <v>56.82157592902526</v>
       </c>
       <c r="F351" t="n">
         <v>573942</v>
@@ -7492,16 +7492,16 @@
         <v>44988</v>
       </c>
       <c r="B354" t="n">
-        <v>52.35877227783203</v>
+        <v>52.3587760925293</v>
       </c>
       <c r="C354" t="n">
-        <v>54.11577810395019</v>
+        <v>54.11578204665744</v>
       </c>
       <c r="D354" t="n">
-        <v>52.35877227783203</v>
+        <v>52.3587760925293</v>
       </c>
       <c r="E354" t="n">
-        <v>53.14942624007427</v>
+        <v>53.14943011237612</v>
       </c>
       <c r="F354" t="n">
         <v>443497</v>
@@ -7512,16 +7512,16 @@
         <v>44991</v>
       </c>
       <c r="B355" t="n">
-        <v>54.28269958496094</v>
+        <v>54.2827033996582</v>
       </c>
       <c r="C355" t="n">
-        <v>55.26662197781043</v>
+        <v>55.26662586165249</v>
       </c>
       <c r="D355" t="n">
-        <v>52.38513329456833</v>
+        <v>52.3851369759148</v>
       </c>
       <c r="E355" t="n">
-        <v>52.71017845670896</v>
+        <v>52.71018216089787</v>
       </c>
       <c r="F355" t="n">
         <v>1320672</v>
@@ -7552,16 +7552,16 @@
         <v>44993</v>
       </c>
       <c r="B357" t="n">
-        <v>58.67520904541016</v>
+        <v>58.67521667480469</v>
       </c>
       <c r="C357" t="n">
-        <v>58.67520904541016</v>
+        <v>58.67521667480469</v>
       </c>
       <c r="D357" t="n">
-        <v>53.97521655571307</v>
+        <v>53.97522357397903</v>
       </c>
       <c r="E357" t="n">
-        <v>53.97521655571307</v>
+        <v>53.97522357397903</v>
       </c>
       <c r="F357" t="n">
         <v>1672249</v>
@@ -7592,16 +7592,16 @@
         <v>44995</v>
       </c>
       <c r="B359" t="n">
-        <v>52.01616287231445</v>
+        <v>52.01615905761719</v>
       </c>
       <c r="C359" t="n">
-        <v>56.08363278249773</v>
+        <v>56.08362866950537</v>
       </c>
       <c r="D359" t="n">
-        <v>51.7965371178954</v>
+        <v>51.79653331930479</v>
       </c>
       <c r="E359" t="n">
-        <v>55.52139138738065</v>
+        <v>55.52138731562125</v>
       </c>
       <c r="F359" t="n">
         <v>846843</v>
@@ -7612,16 +7612,16 @@
         <v>44998</v>
       </c>
       <c r="B360" t="n">
-        <v>50.39093017578125</v>
+        <v>50.39093399047852</v>
       </c>
       <c r="C360" t="n">
-        <v>51.96345127391815</v>
+        <v>51.9634552076585</v>
       </c>
       <c r="D360" t="n">
-        <v>49.46850274069867</v>
+        <v>49.46850648556628</v>
       </c>
       <c r="E360" t="n">
-        <v>51.96345127391815</v>
+        <v>51.9634552076585</v>
       </c>
       <c r="F360" t="n">
         <v>1066340</v>
@@ -7632,16 +7632,16 @@
         <v>44999</v>
       </c>
       <c r="B361" t="n">
-        <v>50.32944107055664</v>
+        <v>50.32943725585938</v>
       </c>
       <c r="C361" t="n">
-        <v>52.78924896630146</v>
+        <v>52.78924496516417</v>
       </c>
       <c r="D361" t="n">
-        <v>49.55635744004602</v>
+        <v>49.55635368394428</v>
       </c>
       <c r="E361" t="n">
-        <v>50.84775800958192</v>
+        <v>50.84775415559906</v>
       </c>
       <c r="F361" t="n">
         <v>730632</v>
@@ -7752,16 +7752,16 @@
         <v>45007</v>
       </c>
       <c r="B367" t="n">
-        <v>52.56962203979492</v>
+        <v>52.56961822509766</v>
       </c>
       <c r="C367" t="n">
-        <v>55.12606575176405</v>
+        <v>55.1260617515593</v>
       </c>
       <c r="D367" t="n">
-        <v>52.56962203979492</v>
+        <v>52.56961822509766</v>
       </c>
       <c r="E367" t="n">
-        <v>53.85223567370974</v>
+        <v>53.85223176594004</v>
       </c>
       <c r="F367" t="n">
         <v>930770</v>
@@ -7772,16 +7772,16 @@
         <v>45008</v>
       </c>
       <c r="B368" t="n">
-        <v>49.1961669921875</v>
+        <v>49.19617080688477</v>
       </c>
       <c r="C368" t="n">
-        <v>53.29877430955613</v>
+        <v>53.29877844237178</v>
       </c>
       <c r="D368" t="n">
-        <v>48.85355136540186</v>
+        <v>48.85355515353253</v>
       </c>
       <c r="E368" t="n">
-        <v>52.56961857712928</v>
+        <v>52.56962265340579</v>
       </c>
       <c r="F368" t="n">
         <v>1208098</v>
@@ -7792,16 +7792,16 @@
         <v>45009</v>
       </c>
       <c r="B369" t="n">
-        <v>50.40850830078125</v>
+        <v>50.40850448608398</v>
       </c>
       <c r="C369" t="n">
-        <v>51.3660768040365</v>
+        <v>51.3660729168746</v>
       </c>
       <c r="D369" t="n">
-        <v>48.82720340719898</v>
+        <v>48.82719971216801</v>
       </c>
       <c r="E369" t="n">
-        <v>50.05710572388593</v>
+        <v>50.05710193578128</v>
       </c>
       <c r="F369" t="n">
         <v>598427</v>
@@ -7852,16 +7852,16 @@
         <v>45014</v>
       </c>
       <c r="B372" t="n">
-        <v>53.88737487792969</v>
+        <v>53.88737106323242</v>
       </c>
       <c r="C372" t="n">
-        <v>54.64288800427434</v>
+        <v>54.64288413609415</v>
       </c>
       <c r="D372" t="n">
-        <v>52.91223599863476</v>
+        <v>52.91223225296775</v>
       </c>
       <c r="E372" t="n">
-        <v>54.38812132655848</v>
+        <v>54.38811747641328</v>
       </c>
       <c r="F372" t="n">
         <v>332515</v>
@@ -7932,16 +7932,16 @@
         <v>45020</v>
       </c>
       <c r="B376" t="n">
-        <v>48.90625762939453</v>
+        <v>48.9062614440918</v>
       </c>
       <c r="C376" t="n">
-        <v>50.48756562074401</v>
+        <v>50.48756955878359</v>
       </c>
       <c r="D376" t="n">
-        <v>48.55485846004571</v>
+        <v>48.55486224733378</v>
       </c>
       <c r="E376" t="n">
-        <v>49.59149220938691</v>
+        <v>49.5914960775326</v>
       </c>
       <c r="F376" t="n">
         <v>366364</v>
@@ -7952,16 +7952,16 @@
         <v>45021</v>
       </c>
       <c r="B377" t="n">
-        <v>48.90625762939453</v>
+        <v>48.9062614440918</v>
       </c>
       <c r="C377" t="n">
-        <v>49.20494876651357</v>
+        <v>49.2049526045088</v>
       </c>
       <c r="D377" t="n">
-        <v>47.2810285120021</v>
+        <v>47.2810321999312</v>
       </c>
       <c r="E377" t="n">
-        <v>48.94139855169625</v>
+        <v>48.94140236913452</v>
       </c>
       <c r="F377" t="n">
         <v>464516</v>
@@ -7992,16 +7992,16 @@
         <v>45026</v>
       </c>
       <c r="B379" t="n">
-        <v>48.75691604614258</v>
+        <v>48.75691986083984</v>
       </c>
       <c r="C379" t="n">
-        <v>49.21373800403698</v>
+        <v>49.21374185447558</v>
       </c>
       <c r="D379" t="n">
-        <v>48.01018984358273</v>
+        <v>48.01019359985681</v>
       </c>
       <c r="E379" t="n">
-        <v>48.3264481056115</v>
+        <v>48.32645188662934</v>
       </c>
       <c r="F379" t="n">
         <v>441343</v>
@@ -8012,16 +8012,16 @@
         <v>45027</v>
       </c>
       <c r="B380" t="n">
-        <v>54.63409805297852</v>
+        <v>54.63410186767578</v>
       </c>
       <c r="C380" t="n">
-        <v>54.63409805297852</v>
+        <v>54.63410186767578</v>
       </c>
       <c r="D380" t="n">
-        <v>48.85355030008497</v>
+        <v>48.8535537111691</v>
       </c>
       <c r="E380" t="n">
-        <v>48.85355030008497</v>
+        <v>48.8535537111691</v>
       </c>
       <c r="F380" t="n">
         <v>1223134</v>
@@ -8052,16 +8052,16 @@
         <v>45029</v>
       </c>
       <c r="B382" t="n">
-        <v>60.46736526489258</v>
+        <v>60.46736907958984</v>
       </c>
       <c r="C382" t="n">
-        <v>61.46007127757674</v>
+        <v>61.46007515490073</v>
       </c>
       <c r="D382" t="n">
-        <v>55.96064377509221</v>
+        <v>55.96064730547449</v>
       </c>
       <c r="E382" t="n">
-        <v>56.4086788466054</v>
+        <v>56.40868240525283</v>
       </c>
       <c r="F382" t="n">
         <v>2756815</v>
@@ -8092,16 +8092,16 @@
         <v>45033</v>
       </c>
       <c r="B384" t="n">
-        <v>59.95783233642578</v>
+        <v>59.95782852172852</v>
       </c>
       <c r="C384" t="n">
-        <v>60.72213239227627</v>
+        <v>60.72212852895193</v>
       </c>
       <c r="D384" t="n">
-        <v>59.16717826182981</v>
+        <v>59.16717449743633</v>
       </c>
       <c r="E384" t="n">
-        <v>60.35315602250063</v>
+        <v>60.35315218265168</v>
       </c>
       <c r="F384" t="n">
         <v>288592</v>
@@ -8132,16 +8132,16 @@
         <v>45035</v>
       </c>
       <c r="B386" t="n">
-        <v>58.84213638305664</v>
+        <v>58.84213256835938</v>
       </c>
       <c r="C386" t="n">
-        <v>61.2755868471204</v>
+        <v>61.27558287466414</v>
       </c>
       <c r="D386" t="n">
-        <v>58.30624899414777</v>
+        <v>58.30624521419173</v>
       </c>
       <c r="E386" t="n">
-        <v>61.2755868471204</v>
+        <v>61.27558287466414</v>
       </c>
       <c r="F386" t="n">
         <v>827950</v>
@@ -8152,16 +8152,16 @@
         <v>45036</v>
       </c>
       <c r="B387" t="n">
-        <v>60.80118942260742</v>
+        <v>60.80118560791016</v>
       </c>
       <c r="C387" t="n">
-        <v>60.80118942260742</v>
+        <v>60.80118560791016</v>
       </c>
       <c r="D387" t="n">
-        <v>58.21838855990702</v>
+        <v>58.21838490725599</v>
       </c>
       <c r="E387" t="n">
-        <v>58.78941682782696</v>
+        <v>58.78941313934933</v>
       </c>
       <c r="F387" t="n">
         <v>442904</v>
@@ -8172,16 +8172,16 @@
         <v>45040</v>
       </c>
       <c r="B388" t="n">
-        <v>60.99446487426758</v>
+        <v>60.99446105957031</v>
       </c>
       <c r="C388" t="n">
-        <v>61.2755855722359</v>
+        <v>61.27558173995688</v>
       </c>
       <c r="D388" t="n">
-        <v>59.73820528906153</v>
+        <v>59.73820155293286</v>
       </c>
       <c r="E388" t="n">
-        <v>60.27409266682086</v>
+        <v>60.2740888971769</v>
       </c>
       <c r="F388" t="n">
         <v>315786</v>
@@ -8192,16 +8192,16 @@
         <v>45041</v>
       </c>
       <c r="B389" t="n">
-        <v>60.50250625610352</v>
+        <v>60.50250244140625</v>
       </c>
       <c r="C389" t="n">
-        <v>61.28437341876753</v>
+        <v>61.28436955477335</v>
       </c>
       <c r="D389" t="n">
-        <v>59.00904707951048</v>
+        <v>59.00904335897617</v>
       </c>
       <c r="E389" t="n">
-        <v>61.28437341876753</v>
+        <v>61.28436955477335</v>
       </c>
       <c r="F389" t="n">
         <v>695154</v>
@@ -8212,16 +8212,16 @@
         <v>45042</v>
       </c>
       <c r="B390" t="n">
-        <v>59.31652069091797</v>
+        <v>59.3165168762207</v>
       </c>
       <c r="C390" t="n">
-        <v>60.01932578469255</v>
+        <v>60.01932192479727</v>
       </c>
       <c r="D390" t="n">
-        <v>56.9533521355543</v>
+        <v>56.95334847283447</v>
       </c>
       <c r="E390" t="n">
-        <v>59.30774048651921</v>
+        <v>59.30773667238661</v>
       </c>
       <c r="F390" t="n">
         <v>963997</v>
@@ -8232,16 +8232,16 @@
         <v>45043</v>
       </c>
       <c r="B391" t="n">
-        <v>61.50400543212891</v>
+        <v>61.50399780273438</v>
       </c>
       <c r="C391" t="n">
-        <v>62.82176011479089</v>
+        <v>62.82175232193269</v>
       </c>
       <c r="D391" t="n">
-        <v>58.44681161927646</v>
+        <v>58.446804369118</v>
       </c>
       <c r="E391" t="n">
-        <v>58.59615554139089</v>
+        <v>58.59614827270675</v>
       </c>
       <c r="F391" t="n">
         <v>723893</v>
@@ -8252,16 +8252,16 @@
         <v>45044</v>
       </c>
       <c r="B392" t="n">
-        <v>63.67389678955078</v>
+        <v>63.67390060424805</v>
       </c>
       <c r="C392" t="n">
-        <v>63.75295883790729</v>
+        <v>63.75296265734114</v>
       </c>
       <c r="D392" t="n">
-        <v>60.6167035732996</v>
+        <v>60.61670720484071</v>
       </c>
       <c r="E392" t="n">
-        <v>61.50399342982543</v>
+        <v>61.50399711452398</v>
       </c>
       <c r="F392" t="n">
         <v>633625</v>
@@ -8272,16 +8272,16 @@
         <v>45048</v>
       </c>
       <c r="B393" t="n">
-        <v>58.38530731201172</v>
+        <v>58.38531112670898</v>
       </c>
       <c r="C393" t="n">
-        <v>63.16436567335623</v>
+        <v>63.16436980030091</v>
       </c>
       <c r="D393" t="n">
-        <v>58.38530731201172</v>
+        <v>58.38531112670898</v>
       </c>
       <c r="E393" t="n">
-        <v>63.16436567335623</v>
+        <v>63.16436980030091</v>
       </c>
       <c r="F393" t="n">
         <v>808928</v>
@@ -8332,16 +8332,16 @@
         <v>45051</v>
       </c>
       <c r="B396" t="n">
-        <v>64.07801818847656</v>
+        <v>64.07801055908203</v>
       </c>
       <c r="C396" t="n">
-        <v>64.75446262565779</v>
+        <v>64.75445491572299</v>
       </c>
       <c r="D396" t="n">
-        <v>60.79241177231987</v>
+        <v>60.79240453412326</v>
       </c>
       <c r="E396" t="n">
-        <v>60.79241177231987</v>
+        <v>60.79240453412326</v>
       </c>
       <c r="F396" t="n">
         <v>739601</v>
@@ -8412,16 +8412,16 @@
         <v>45057</v>
       </c>
       <c r="B400" t="n">
-        <v>67.00341033935547</v>
+        <v>67.00341796875</v>
       </c>
       <c r="C400" t="n">
-        <v>68.69892113120667</v>
+        <v>68.69892895366183</v>
       </c>
       <c r="D400" t="n">
-        <v>67.00341033935547</v>
+        <v>67.00341796875</v>
       </c>
       <c r="E400" t="n">
-        <v>67.38116683813408</v>
+        <v>67.38117451054214</v>
       </c>
       <c r="F400" t="n">
         <v>282491</v>
@@ -8472,16 +8472,16 @@
         <v>45062</v>
       </c>
       <c r="B403" t="n">
-        <v>69.20846557617188</v>
+        <v>69.20847320556641</v>
       </c>
       <c r="C403" t="n">
-        <v>74.04023209771412</v>
+        <v>74.04024025975235</v>
       </c>
       <c r="D403" t="n">
-        <v>67.52174141723872</v>
+        <v>67.52174886069236</v>
       </c>
       <c r="E403" t="n">
-        <v>69.22603938961998</v>
+        <v>69.22604702095181</v>
       </c>
       <c r="F403" t="n">
         <v>1416795</v>
@@ -8572,16 +8572,16 @@
         <v>45069</v>
       </c>
       <c r="B408" t="n">
-        <v>77.13256072998047</v>
+        <v>77.132568359375</v>
       </c>
       <c r="C408" t="n">
-        <v>80.43572695506535</v>
+        <v>80.43573491118516</v>
       </c>
       <c r="D408" t="n">
-        <v>76.42975569775851</v>
+        <v>76.42976325763665</v>
       </c>
       <c r="E408" t="n">
-        <v>77.74751010634054</v>
+        <v>77.74751779656141</v>
       </c>
       <c r="F408" t="n">
         <v>970823</v>
@@ -8632,16 +8632,16 @@
         <v>45072</v>
       </c>
       <c r="B411" t="n">
-        <v>82.75497436523438</v>
+        <v>82.75498199462891</v>
       </c>
       <c r="C411" t="n">
-        <v>84.15179752676379</v>
+        <v>84.15180528493505</v>
       </c>
       <c r="D411" t="n">
-        <v>80.38301910539758</v>
+        <v>80.38302651611544</v>
       </c>
       <c r="E411" t="n">
-        <v>81.70077351696148</v>
+        <v>81.70078104916651</v>
       </c>
       <c r="F411" t="n">
         <v>582166</v>
@@ -8652,16 +8652,16 @@
         <v>45075</v>
       </c>
       <c r="B412" t="n">
-        <v>81.52507781982422</v>
+        <v>81.52508544921875</v>
       </c>
       <c r="C412" t="n">
-        <v>83.1678740745439</v>
+        <v>83.1678818576769</v>
       </c>
       <c r="D412" t="n">
-        <v>80.73442381096265</v>
+        <v>80.73443136636509</v>
       </c>
       <c r="E412" t="n">
-        <v>82.66712765267252</v>
+        <v>82.66713538894396</v>
       </c>
       <c r="F412" t="n">
         <v>275309</v>
@@ -8732,16 +8732,16 @@
         <v>45079</v>
       </c>
       <c r="B416" t="n">
-        <v>82.84282684326172</v>
+        <v>82.84284210205078</v>
       </c>
       <c r="C416" t="n">
-        <v>84.0288044276834</v>
+        <v>84.02881990491723</v>
       </c>
       <c r="D416" t="n">
-        <v>78.89834396353872</v>
+        <v>78.89835849579498</v>
       </c>
       <c r="E416" t="n">
-        <v>78.89834396353872</v>
+        <v>78.89835849579498</v>
       </c>
       <c r="F416" t="n">
         <v>731024</v>
@@ -8772,16 +8772,16 @@
         <v>45083</v>
       </c>
       <c r="B418" t="n">
-        <v>83.89704132080078</v>
+        <v>83.89703369140625</v>
       </c>
       <c r="C418" t="n">
-        <v>86.70824840135691</v>
+        <v>86.708240516318</v>
       </c>
       <c r="D418" t="n">
-        <v>81.92040945722171</v>
+        <v>81.92040200757731</v>
       </c>
       <c r="E418" t="n">
-        <v>82.01704532897017</v>
+        <v>82.01703787053793</v>
       </c>
       <c r="F418" t="n">
         <v>1573579</v>
@@ -8792,16 +8792,16 @@
         <v>45084</v>
       </c>
       <c r="B419" t="n">
-        <v>86.52375793457031</v>
+        <v>86.52376556396484</v>
       </c>
       <c r="C419" t="n">
-        <v>86.60282668924023</v>
+        <v>86.60283432560681</v>
       </c>
       <c r="D419" t="n">
-        <v>82.88675607845614</v>
+        <v>82.88676338715122</v>
       </c>
       <c r="E419" t="n">
-        <v>84.3362873579094</v>
+        <v>84.33629479441962</v>
       </c>
       <c r="F419" t="n">
         <v>2805750</v>
@@ -8832,16 +8832,16 @@
         <v>45089</v>
       </c>
       <c r="B421" t="n">
-        <v>90.35404205322266</v>
+        <v>90.35403442382812</v>
       </c>
       <c r="C421" t="n">
-        <v>91.34675484094018</v>
+        <v>91.34674712772208</v>
       </c>
       <c r="D421" t="n">
-        <v>87.95573235530614</v>
+        <v>87.95572492842221</v>
       </c>
       <c r="E421" t="n">
-        <v>87.95573235530614</v>
+        <v>87.95572492842221</v>
       </c>
       <c r="F421" t="n">
         <v>1071620</v>
@@ -8872,16 +8872,16 @@
         <v>45091</v>
       </c>
       <c r="B423" t="n">
-        <v>89.40524291992188</v>
+        <v>89.40525054931641</v>
       </c>
       <c r="C423" t="n">
-        <v>89.44038384246984</v>
+        <v>89.44039147486313</v>
       </c>
       <c r="D423" t="n">
-        <v>87.26170026406075</v>
+        <v>87.26170771053611</v>
       </c>
       <c r="E423" t="n">
-        <v>87.54282094199888</v>
+        <v>87.54282841246366</v>
       </c>
       <c r="F423" t="n">
         <v>605932</v>
@@ -8892,16 +8892,16 @@
         <v>45092</v>
       </c>
       <c r="B424" t="n">
-        <v>91.97927093505859</v>
+        <v>91.97926330566406</v>
       </c>
       <c r="C424" t="n">
-        <v>92.26039165604509</v>
+        <v>92.26038400333246</v>
       </c>
       <c r="D424" t="n">
-        <v>89.18563083793495</v>
+        <v>89.18562344026418</v>
       </c>
       <c r="E424" t="n">
-        <v>89.43161733343898</v>
+        <v>89.43160991536439</v>
       </c>
       <c r="F424" t="n">
         <v>844482</v>
@@ -8912,16 +8912,16 @@
         <v>45093</v>
       </c>
       <c r="B425" t="n">
-        <v>94.66748046875</v>
+        <v>94.66748809814453</v>
       </c>
       <c r="C425" t="n">
-        <v>95.72168133556757</v>
+        <v>95.72168904992172</v>
       </c>
       <c r="D425" t="n">
-        <v>91.39066149194188</v>
+        <v>91.39066885725265</v>
       </c>
       <c r="E425" t="n">
-        <v>91.84748678268964</v>
+        <v>91.84749418481664</v>
       </c>
       <c r="F425" t="n">
         <v>1238876</v>
@@ -8932,16 +8932,16 @@
         <v>45096</v>
       </c>
       <c r="B426" t="n">
-        <v>98.03214263916016</v>
+        <v>98.03215026855469</v>
       </c>
       <c r="C426" t="n">
-        <v>98.33962403884159</v>
+        <v>98.33963169216599</v>
       </c>
       <c r="D426" t="n">
-        <v>94.14916114276463</v>
+        <v>94.14916846996442</v>
       </c>
       <c r="E426" t="n">
-        <v>94.61476664178524</v>
+        <v>94.61477400522099</v>
       </c>
       <c r="F426" t="n">
         <v>576522</v>
@@ -8952,16 +8952,16 @@
         <v>45097</v>
       </c>
       <c r="B427" t="n">
-        <v>99.66616821289062</v>
+        <v>99.66616058349609</v>
       </c>
       <c r="C427" t="n">
-        <v>100.1493475707456</v>
+        <v>100.1493399043639</v>
       </c>
       <c r="D427" t="n">
-        <v>95.20337781850962</v>
+        <v>95.20337053073942</v>
       </c>
       <c r="E427" t="n">
-        <v>97.8564540770091</v>
+        <v>97.85644658614729</v>
       </c>
       <c r="F427" t="n">
         <v>1047570</v>
@@ -8972,16 +8972,16 @@
         <v>45098</v>
       </c>
       <c r="B428" t="n">
-        <v>102.9605560302734</v>
+        <v>102.9605484008789</v>
       </c>
       <c r="C428" t="n">
-        <v>103.6457940476559</v>
+        <v>103.6457863674851</v>
       </c>
       <c r="D428" t="n">
-        <v>97.65440344194199</v>
+        <v>97.65439620573426</v>
       </c>
       <c r="E428" t="n">
-        <v>99.25327874427484</v>
+        <v>99.25327138959017</v>
       </c>
       <c r="F428" t="n">
         <v>1080781</v>
@@ -9012,16 +9012,16 @@
         <v>45100</v>
       </c>
       <c r="B430" t="n">
-        <v>98.56803894042969</v>
+        <v>98.56803131103516</v>
       </c>
       <c r="C430" t="n">
-        <v>100.5446707911264</v>
+        <v>100.544663008736</v>
       </c>
       <c r="D430" t="n">
-        <v>97.24150416861238</v>
+        <v>97.24149664189471</v>
       </c>
       <c r="E430" t="n">
-        <v>99.71009557958853</v>
+        <v>99.71008786179617</v>
       </c>
       <c r="F430" t="n">
         <v>1883788</v>
@@ -9032,16 +9032,16 @@
         <v>45103</v>
       </c>
       <c r="B431" t="n">
-        <v>97.00429534912109</v>
+        <v>97.00430297851562</v>
       </c>
       <c r="C431" t="n">
-        <v>99.27083459718358</v>
+        <v>99.27084240484157</v>
       </c>
       <c r="D431" t="n">
-        <v>95.75682275303549</v>
+        <v>95.75683028431621</v>
       </c>
       <c r="E431" t="n">
-        <v>98.46261348161649</v>
+        <v>98.46262122570784</v>
       </c>
       <c r="F431" t="n">
         <v>757098</v>
@@ -9052,16 +9052,16 @@
         <v>45104</v>
       </c>
       <c r="B432" t="n">
-        <v>94.86954498291016</v>
+        <v>94.86953735351562</v>
       </c>
       <c r="C432" t="n">
-        <v>98.37477707017537</v>
+        <v>98.3747691588906</v>
       </c>
       <c r="D432" t="n">
-        <v>91.40824743272303</v>
+        <v>91.40824008168553</v>
       </c>
       <c r="E432" t="n">
-        <v>96.97795369874004</v>
+        <v>96.9779458997876</v>
       </c>
       <c r="F432" t="n">
         <v>1484061</v>
@@ -9112,16 +9112,16 @@
         <v>45107</v>
       </c>
       <c r="B435" t="n">
-        <v>98.43625640869141</v>
+        <v>98.43626403808594</v>
       </c>
       <c r="C435" t="n">
-        <v>101.4758757552046</v>
+        <v>101.4758836201877</v>
       </c>
       <c r="D435" t="n">
-        <v>98.40111548704759</v>
+        <v>98.40112311371848</v>
       </c>
       <c r="E435" t="n">
-        <v>100.67643486831</v>
+        <v>100.6764426713316</v>
       </c>
       <c r="F435" t="n">
         <v>851232</v>
@@ -9132,16 +9132,16 @@
         <v>45110</v>
       </c>
       <c r="B436" t="n">
-        <v>100.8960800170898</v>
+        <v>100.8960647583008</v>
       </c>
       <c r="C436" t="n">
-        <v>101.4671083744049</v>
+        <v>101.4670930292576</v>
       </c>
       <c r="D436" t="n">
-        <v>98.26057070866375</v>
+        <v>98.26055584844994</v>
       </c>
       <c r="E436" t="n">
-        <v>98.46262937138633</v>
+        <v>98.46261448061463</v>
       </c>
       <c r="F436" t="n">
         <v>512630</v>
@@ -9152,16 +9152,16 @@
         <v>45111</v>
       </c>
       <c r="B437" t="n">
-        <v>100.6764373779297</v>
+        <v>100.6764450073242</v>
       </c>
       <c r="C437" t="n">
-        <v>101.1508297782785</v>
+        <v>101.1508374436232</v>
       </c>
       <c r="D437" t="n">
-        <v>99.42017788324077</v>
+        <v>99.42018541743428</v>
       </c>
       <c r="E437" t="n">
-        <v>101.0278399006821</v>
+        <v>101.0278475567063</v>
       </c>
       <c r="F437" t="n">
         <v>210288</v>
@@ -9172,16 +9172,16 @@
         <v>45112</v>
       </c>
       <c r="B438" t="n">
-        <v>101.2386779785156</v>
+        <v>101.2386856079102</v>
       </c>
       <c r="C438" t="n">
-        <v>101.7042834691515</v>
+        <v>101.7042911336343</v>
       </c>
       <c r="D438" t="n">
-        <v>99.13026956016742</v>
+        <v>99.13027703067131</v>
       </c>
       <c r="E438" t="n">
-        <v>99.5343868149092</v>
+        <v>99.53439431586756</v>
       </c>
       <c r="F438" t="n">
         <v>519657</v>
@@ -9192,16 +9192,16 @@
         <v>45113</v>
       </c>
       <c r="B439" t="n">
-        <v>99.2093505859375</v>
+        <v>99.20934295654297</v>
       </c>
       <c r="C439" t="n">
-        <v>100.1405616824272</v>
+        <v>100.1405539814207</v>
       </c>
       <c r="D439" t="n">
-        <v>97.71589806864876</v>
+        <v>97.71589055410367</v>
       </c>
       <c r="E439" t="n">
-        <v>100.1405616824272</v>
+        <v>100.1405539814207</v>
       </c>
       <c r="F439" t="n">
         <v>463942</v>
@@ -9212,16 +9212,16 @@
         <v>45114</v>
       </c>
       <c r="B440" t="n">
-        <v>101.2386779785156</v>
+        <v>101.2386856079102</v>
       </c>
       <c r="C440" t="n">
-        <v>102.0820400053658</v>
+        <v>102.0820476983165</v>
       </c>
       <c r="D440" t="n">
-        <v>98.16391765663779</v>
+        <v>98.16392505431695</v>
       </c>
       <c r="E440" t="n">
-        <v>98.73494591404707</v>
+        <v>98.73495335475918</v>
       </c>
       <c r="F440" t="n">
         <v>1239341</v>
@@ -9312,16 +9312,16 @@
         <v>45121</v>
       </c>
       <c r="B445" t="n">
-        <v>96.74074554443359</v>
+        <v>96.74075317382812</v>
       </c>
       <c r="C445" t="n">
-        <v>98.69980333468348</v>
+        <v>98.69981111857781</v>
       </c>
       <c r="D445" t="n">
-        <v>95.02766080096731</v>
+        <v>95.02766829526057</v>
       </c>
       <c r="E445" t="n">
-        <v>98.69980333468348</v>
+        <v>98.69981111857781</v>
       </c>
       <c r="F445" t="n">
         <v>461646</v>
@@ -9332,16 +9332,16 @@
         <v>45124</v>
       </c>
       <c r="B446" t="n">
-        <v>99.48168182373047</v>
+        <v>99.48167419433594</v>
       </c>
       <c r="C446" t="n">
-        <v>99.48168182373047</v>
+        <v>99.48167419433594</v>
       </c>
       <c r="D446" t="n">
-        <v>95.75683083137832</v>
+        <v>95.75682348764802</v>
       </c>
       <c r="E446" t="n">
-        <v>96.44206212640412</v>
+        <v>96.44205473012244</v>
       </c>
       <c r="F446" t="n">
         <v>395417</v>
@@ -9372,16 +9372,16 @@
         <v>45126</v>
       </c>
       <c r="B448" t="n">
-        <v>101.06298828125</v>
+        <v>101.0629806518555</v>
       </c>
       <c r="C448" t="n">
-        <v>101.2650402225924</v>
+        <v>101.2650325779447</v>
       </c>
       <c r="D448" t="n">
-        <v>99.00728772803575</v>
+        <v>99.00728025382909</v>
       </c>
       <c r="E448" t="n">
-        <v>100.8257887123484</v>
+        <v>100.8257811008604</v>
       </c>
       <c r="F448" t="n">
         <v>1189852</v>
@@ -9412,16 +9412,16 @@
         <v>45128</v>
       </c>
       <c r="B450" t="n">
-        <v>111.3941802978516</v>
+        <v>111.3941879272461</v>
       </c>
       <c r="C450" t="n">
-        <v>111.3941802978516</v>
+        <v>111.3941879272461</v>
       </c>
       <c r="D450" t="n">
-        <v>106.0353067697835</v>
+        <v>106.0353140321484</v>
       </c>
       <c r="E450" t="n">
-        <v>106.7556789436875</v>
+        <v>106.7556862553908</v>
       </c>
       <c r="F450" t="n">
         <v>688364</v>
@@ -9432,16 +9432,16 @@
         <v>45131</v>
       </c>
       <c r="B451" t="n">
-        <v>112.6240768432617</v>
+        <v>112.6240844726562</v>
       </c>
       <c r="C451" t="n">
-        <v>113.1160363563073</v>
+        <v>113.1160440190282</v>
       </c>
       <c r="D451" t="n">
-        <v>109.3033367253127</v>
+        <v>109.3033441297533</v>
       </c>
       <c r="E451" t="n">
-        <v>110.8582907186036</v>
+        <v>110.85829822838</v>
       </c>
       <c r="F451" t="n">
         <v>870351</v>
@@ -9472,16 +9472,16 @@
         <v>45133</v>
       </c>
       <c r="B453" t="n">
-        <v>113.8891296386719</v>
+        <v>113.8891372680664</v>
       </c>
       <c r="C453" t="n">
-        <v>113.9857655059323</v>
+        <v>113.9857731418005</v>
       </c>
       <c r="D453" t="n">
-        <v>110.5508155209108</v>
+        <v>110.5508229266728</v>
       </c>
       <c r="E453" t="n">
-        <v>111.0427817639948</v>
+        <v>111.0427892027134</v>
       </c>
       <c r="F453" t="n">
         <v>810223</v>
@@ -9492,16 +9492,16 @@
         <v>45134</v>
       </c>
       <c r="B454" t="n">
-        <v>110.7440872192383</v>
+        <v>110.7440719604492</v>
       </c>
       <c r="C454" t="n">
-        <v>114.6446427257238</v>
+        <v>114.6446269294997</v>
       </c>
       <c r="D454" t="n">
-        <v>109.7074534000573</v>
+        <v>109.7074382841</v>
       </c>
       <c r="E454" t="n">
-        <v>113.5025861325351</v>
+        <v>113.5025704936684</v>
       </c>
       <c r="F454" t="n">
         <v>678181</v>
@@ -9512,16 +9512,16 @@
         <v>45135</v>
       </c>
       <c r="B455" t="n">
-        <v>109.8919448852539</v>
+        <v>109.8919372558594</v>
       </c>
       <c r="C455" t="n">
-        <v>111.9915733711529</v>
+        <v>111.9915655959889</v>
       </c>
       <c r="D455" t="n">
-        <v>108.0558767015642</v>
+        <v>108.0558691996412</v>
       </c>
       <c r="E455" t="n">
-        <v>110.6913858894073</v>
+        <v>110.6913782045105</v>
       </c>
       <c r="F455" t="n">
         <v>651013</v>
@@ -9592,16 +9592,16 @@
         <v>45141</v>
       </c>
       <c r="B459" t="n">
-        <v>114.7939910888672</v>
+        <v>114.7939834594727</v>
       </c>
       <c r="C459" t="n">
-        <v>117.3065103295453</v>
+        <v>117.3065025331647</v>
       </c>
       <c r="D459" t="n">
-        <v>111.8597941406668</v>
+        <v>111.8597867062838</v>
       </c>
       <c r="E459" t="n">
-        <v>112.9227753165926</v>
+        <v>112.9227678115621</v>
       </c>
       <c r="F459" t="n">
         <v>1277901</v>
@@ -9612,16 +9612,16 @@
         <v>45142</v>
       </c>
       <c r="B460" t="n">
-        <v>113.1336135864258</v>
+        <v>113.1336212158203</v>
       </c>
       <c r="C460" t="n">
-        <v>114.6007119660374</v>
+        <v>114.6007196943687</v>
       </c>
       <c r="D460" t="n">
-        <v>110.9900641534965</v>
+        <v>110.9900716383365</v>
       </c>
       <c r="E460" t="n">
-        <v>114.2053883028904</v>
+        <v>114.2053960045622</v>
       </c>
       <c r="F460" t="n">
         <v>805649</v>
@@ -9632,16 +9632,16 @@
         <v>45145</v>
       </c>
       <c r="B461" t="n">
-        <v>112.9930572509766</v>
+        <v>112.993049621582</v>
       </c>
       <c r="C461" t="n">
-        <v>117.7194079181516</v>
+        <v>117.7193999696295</v>
       </c>
       <c r="D461" t="n">
-        <v>111.6225946468615</v>
+        <v>111.6225871100018</v>
       </c>
       <c r="E461" t="n">
-        <v>113.326892697325</v>
+        <v>113.3268850453896</v>
       </c>
       <c r="F461" t="n">
         <v>579696</v>
@@ -9652,16 +9652,16 @@
         <v>45146</v>
       </c>
       <c r="B462" t="n">
-        <v>113.5904388427734</v>
+        <v>113.590446472168</v>
       </c>
       <c r="C462" t="n">
-        <v>113.5904388427734</v>
+        <v>113.590446472168</v>
       </c>
       <c r="D462" t="n">
-        <v>109.3033399788109</v>
+        <v>109.3033473202589</v>
       </c>
       <c r="E462" t="n">
-        <v>111.8685670909697</v>
+        <v>111.8685746047133</v>
       </c>
       <c r="F462" t="n">
         <v>457201</v>
@@ -9672,16 +9672,16 @@
         <v>45147</v>
       </c>
       <c r="B463" t="n">
-        <v>112.4483795166016</v>
+        <v>112.4483871459961</v>
       </c>
       <c r="C463" t="n">
-        <v>114.1263233968748</v>
+        <v>114.1263311401144</v>
       </c>
       <c r="D463" t="n">
-        <v>110.612311536981</v>
+        <v>110.612319041802</v>
       </c>
       <c r="E463" t="n">
-        <v>113.7397799475038</v>
+        <v>113.7397876645173</v>
       </c>
       <c r="F463" t="n">
         <v>434571</v>
@@ -9772,16 +9772,16 @@
         <v>45154</v>
       </c>
       <c r="B468" t="n">
-        <v>108.6444549560547</v>
+        <v>108.6444625854492</v>
       </c>
       <c r="C468" t="n">
-        <v>111.8422050618522</v>
+        <v>111.842212915804</v>
       </c>
       <c r="D468" t="n">
-        <v>107.0982946362363</v>
+        <v>107.098302157054</v>
       </c>
       <c r="E468" t="n">
-        <v>108.2403444154809</v>
+        <v>108.2403520164973</v>
       </c>
       <c r="F468" t="n">
         <v>1047832</v>
@@ -9792,16 +9792,16 @@
         <v>45155</v>
       </c>
       <c r="B469" t="n">
-        <v>103.6633453369141</v>
+        <v>103.6633529663086</v>
       </c>
       <c r="C469" t="n">
-        <v>109.7689379956948</v>
+        <v>109.7689460744476</v>
       </c>
       <c r="D469" t="n">
-        <v>103.0483959692834</v>
+        <v>103.048403553419</v>
       </c>
       <c r="E469" t="n">
-        <v>108.9782907237255</v>
+        <v>108.9782987442884</v>
       </c>
       <c r="F469" t="n">
         <v>1841816</v>
@@ -9832,16 +9832,16 @@
         <v>45159</v>
       </c>
       <c r="B471" t="n">
-        <v>111.3941802978516</v>
+        <v>111.3941879272461</v>
       </c>
       <c r="C471" t="n">
-        <v>111.4556752382173</v>
+        <v>111.4556828718236</v>
       </c>
       <c r="D471" t="n">
-        <v>108.0997941301601</v>
+        <v>108.0998015339219</v>
       </c>
       <c r="E471" t="n">
-        <v>109.153995022843</v>
+        <v>109.1540024988072</v>
       </c>
       <c r="F471" t="n">
         <v>967109</v>
@@ -9892,16 +9892,16 @@
         <v>45162</v>
       </c>
       <c r="B474" t="n">
-        <v>112.7470703125</v>
+        <v>112.7470779418945</v>
       </c>
       <c r="C474" t="n">
-        <v>117.7457544612085</v>
+        <v>117.7457624288552</v>
       </c>
       <c r="D474" t="n">
-        <v>111.5698795252345</v>
+        <v>111.5698870749707</v>
       </c>
       <c r="E474" t="n">
-        <v>117.4997746968513</v>
+        <v>117.499782647853</v>
       </c>
       <c r="F474" t="n">
         <v>930433</v>
@@ -9932,16 +9932,16 @@
         <v>45166</v>
       </c>
       <c r="B476" t="n">
-        <v>110.9549255371094</v>
+        <v>110.9549331665039</v>
       </c>
       <c r="C476" t="n">
-        <v>111.4820259679083</v>
+        <v>111.4820336335469</v>
       </c>
       <c r="D476" t="n">
-        <v>109.5493154517181</v>
+        <v>109.5493229844612</v>
       </c>
       <c r="E476" t="n">
-        <v>110.3399694491393</v>
+        <v>110.3399770362487</v>
       </c>
       <c r="F476" t="n">
         <v>1603475</v>
@@ -9972,16 +9972,16 @@
         <v>45168</v>
       </c>
       <c r="B478" t="n">
-        <v>112.4483795166016</v>
+        <v>112.4483871459961</v>
       </c>
       <c r="C478" t="n">
-        <v>113.8539896225157</v>
+        <v>113.853997347278</v>
       </c>
       <c r="D478" t="n">
-        <v>110.8231503718898</v>
+        <v>110.8231578910159</v>
       </c>
       <c r="E478" t="n">
-        <v>113.0721225198849</v>
+        <v>113.0721301915992</v>
       </c>
       <c r="F478" t="n">
         <v>547646</v>
@@ -9992,16 +9992,16 @@
         <v>45169</v>
       </c>
       <c r="B479" t="n">
-        <v>110.4102630615234</v>
+        <v>110.4102554321289</v>
       </c>
       <c r="C479" t="n">
-        <v>112.4396029524886</v>
+        <v>112.4395951828659</v>
       </c>
       <c r="D479" t="n">
-        <v>108.8465287124293</v>
+        <v>108.8465211910895</v>
       </c>
       <c r="E479" t="n">
-        <v>111.7455847420302</v>
+        <v>111.7455770203644</v>
       </c>
       <c r="F479" t="n">
         <v>854216</v>
@@ -10012,16 +10012,16 @@
         <v>45170</v>
       </c>
       <c r="B480" t="n">
-        <v>113.7397918701172</v>
+        <v>113.7397842407227</v>
       </c>
       <c r="C480" t="n">
-        <v>115.5670798373918</v>
+        <v>115.5670720854272</v>
       </c>
       <c r="D480" t="n">
-        <v>109.3209225654903</v>
+        <v>109.320915232503</v>
       </c>
       <c r="E480" t="n">
-        <v>110.260920568448</v>
+        <v>110.2609131724079</v>
       </c>
       <c r="F480" t="n">
         <v>5149038</v>
@@ -10132,16 +10132,16 @@
         <v>45181</v>
       </c>
       <c r="B486" t="n">
-        <v>112.4489898681641</v>
+        <v>112.4489974975586</v>
       </c>
       <c r="C486" t="n">
-        <v>113.6994220864307</v>
+        <v>113.6994298006641</v>
       </c>
       <c r="D486" t="n">
-        <v>109.6602562921019</v>
+        <v>109.6602637322876</v>
       </c>
       <c r="E486" t="n">
-        <v>109.7592119522533</v>
+        <v>109.7592193991528</v>
       </c>
       <c r="F486" t="n">
         <v>550963</v>
@@ -10232,16 +10232,16 @@
         <v>45188</v>
       </c>
       <c r="B491" t="n">
-        <v>111.9991836547852</v>
+        <v>111.9991912841797</v>
       </c>
       <c r="C491" t="n">
-        <v>115.9573822450846</v>
+        <v>115.957390144112</v>
       </c>
       <c r="D491" t="n">
-        <v>111.2705164634207</v>
+        <v>111.2705240431784</v>
       </c>
       <c r="E491" t="n">
-        <v>115.3366754082542</v>
+        <v>115.336683264999</v>
       </c>
       <c r="F491" t="n">
         <v>598810</v>
@@ -10252,16 +10252,16 @@
         <v>45189</v>
       </c>
       <c r="B492" t="n">
-        <v>110.0200958251953</v>
+        <v>110.0200881958008</v>
       </c>
       <c r="C492" t="n">
-        <v>112.5479469531647</v>
+        <v>112.5479391484752</v>
       </c>
       <c r="D492" t="n">
-        <v>110.0200958251953</v>
+        <v>110.0200881958008</v>
       </c>
       <c r="E492" t="n">
-        <v>111.7113261834204</v>
+        <v>111.7113184367467</v>
       </c>
       <c r="F492" t="n">
         <v>472827</v>
@@ -10272,16 +10272,16 @@
         <v>45190</v>
       </c>
       <c r="B493" t="n">
-        <v>104.1187591552734</v>
+        <v>104.118766784668</v>
       </c>
       <c r="C493" t="n">
-        <v>109.5343059543656</v>
+        <v>109.5343139805892</v>
       </c>
       <c r="D493" t="n">
-        <v>103.6509744115351</v>
+        <v>103.6509820066523</v>
       </c>
       <c r="E493" t="n">
-        <v>109.4353503014581</v>
+        <v>109.4353583204306</v>
       </c>
       <c r="F493" t="n">
         <v>1919322</v>
@@ -10332,16 +10332,16 @@
         <v>45195</v>
       </c>
       <c r="B496" t="n">
-        <v>101.5549240112305</v>
+        <v>101.554931640625</v>
       </c>
       <c r="C496" t="n">
-        <v>103.8129014901132</v>
+        <v>103.8129092891401</v>
       </c>
       <c r="D496" t="n">
-        <v>100.862241302414</v>
+        <v>100.8622488797702</v>
       </c>
       <c r="E496" t="n">
-        <v>101.6538796643958</v>
+        <v>101.6538873012245</v>
       </c>
       <c r="F496" t="n">
         <v>1664293</v>
@@ -10352,16 +10352,16 @@
         <v>45196</v>
       </c>
       <c r="B497" t="n">
-        <v>100.0346221923828</v>
+        <v>100.0346145629883</v>
       </c>
       <c r="C497" t="n">
-        <v>103.4440765098144</v>
+        <v>103.4440686203892</v>
       </c>
       <c r="D497" t="n">
-        <v>98.69423210730918</v>
+        <v>98.6942245801429</v>
       </c>
       <c r="E497" t="n">
-        <v>101.6628882905459</v>
+        <v>101.6628805369675</v>
       </c>
       <c r="F497" t="n">
         <v>938220</v>
@@ -10372,16 +10372,16 @@
         <v>45197</v>
       </c>
       <c r="B498" t="n">
-        <v>104.352668762207</v>
+        <v>104.3526611328125</v>
       </c>
       <c r="C498" t="n">
-        <v>104.352668762207</v>
+        <v>104.3526611328125</v>
       </c>
       <c r="D498" t="n">
-        <v>99.09905493961736</v>
+        <v>99.09904769432313</v>
       </c>
       <c r="E498" t="n">
-        <v>100.7543008738551</v>
+        <v>100.7542935075431</v>
       </c>
       <c r="F498" t="n">
         <v>896625</v>
@@ -10452,16 +10452,16 @@
         <v>45203</v>
       </c>
       <c r="B502" t="n">
-        <v>101.7978134155273</v>
+        <v>101.7978210449219</v>
       </c>
       <c r="C502" t="n">
-        <v>102.1666424919565</v>
+        <v>102.1666501489935</v>
       </c>
       <c r="D502" t="n">
-        <v>98.96409781626373</v>
+        <v>98.96410523328106</v>
       </c>
       <c r="E502" t="n">
-        <v>99.85469179431541</v>
+        <v>99.85469927807969</v>
       </c>
       <c r="F502" t="n">
         <v>483635</v>
@@ -10572,16 +10572,16 @@
         <v>45212</v>
       </c>
       <c r="B508" t="n">
-        <v>97.16492462158203</v>
+        <v>97.1649169921875</v>
       </c>
       <c r="C508" t="n">
-        <v>98.87415063205897</v>
+        <v>98.87414286845593</v>
       </c>
       <c r="D508" t="n">
-        <v>95.72557893083258</v>
+        <v>95.72557141445554</v>
       </c>
       <c r="E508" t="n">
-        <v>97.9475651947768</v>
+        <v>97.9475575039293</v>
       </c>
       <c r="F508" t="n">
         <v>544401</v>
@@ -10652,16 +10652,16 @@
         <v>45218</v>
       </c>
       <c r="B512" t="n">
-        <v>94.34920501708984</v>
+        <v>94.34919738769531</v>
       </c>
       <c r="C512" t="n">
-        <v>95.9954599986059</v>
+        <v>95.99545223608963</v>
       </c>
       <c r="D512" t="n">
-        <v>92.76592806339976</v>
+        <v>92.76592056203434</v>
       </c>
       <c r="E512" t="n">
-        <v>93.46760871431685</v>
+        <v>93.46760115621116</v>
       </c>
       <c r="F512" t="n">
         <v>760940</v>
@@ -10712,16 +10712,16 @@
         <v>45223</v>
       </c>
       <c r="B515" t="n">
-        <v>93.51258087158203</v>
+        <v>93.5125732421875</v>
       </c>
       <c r="C515" t="n">
-        <v>98.39736545626356</v>
+        <v>98.39735742833496</v>
       </c>
       <c r="D515" t="n">
-        <v>93.38663854709125</v>
+        <v>93.38663092797195</v>
       </c>
       <c r="E515" t="n">
-        <v>96.71513289484724</v>
+        <v>96.71512500416665</v>
       </c>
       <c r="F515" t="n">
         <v>956700</v>
@@ -10732,16 +10732,16 @@
         <v>45224</v>
       </c>
       <c r="B516" t="n">
-        <v>89.44641876220703</v>
+        <v>89.44642639160156</v>
       </c>
       <c r="C516" t="n">
-        <v>92.42406561747359</v>
+        <v>92.42407350084858</v>
       </c>
       <c r="D516" t="n">
-        <v>87.28739692921076</v>
+        <v>87.28740437445002</v>
       </c>
       <c r="E516" t="n">
-        <v>92.42406561747359</v>
+        <v>92.42407350084858</v>
       </c>
       <c r="F516" t="n">
         <v>1619426</v>
@@ -10752,16 +10752,16 @@
         <v>45225</v>
       </c>
       <c r="B517" t="n">
-        <v>92.35210418701172</v>
+        <v>92.35211181640625</v>
       </c>
       <c r="C517" t="n">
-        <v>92.90084891057617</v>
+        <v>92.90085658530361</v>
       </c>
       <c r="D517" t="n">
-        <v>89.23951029330274</v>
+        <v>89.23951766555959</v>
       </c>
       <c r="E517" t="n">
-        <v>89.23951029330274</v>
+        <v>89.23951766555959</v>
       </c>
       <c r="F517" t="n">
         <v>731795</v>
@@ -10852,16 +10852,16 @@
         <v>45233</v>
       </c>
       <c r="B522" t="n">
-        <v>94.61008453369141</v>
+        <v>94.61007690429688</v>
       </c>
       <c r="C522" t="n">
-        <v>97.14693357959244</v>
+        <v>97.14692574562541</v>
       </c>
       <c r="D522" t="n">
-        <v>92.08223332910212</v>
+        <v>92.08222590355452</v>
       </c>
       <c r="E522" t="n">
-        <v>92.70295397611622</v>
+        <v>92.70294650051345</v>
       </c>
       <c r="F522" t="n">
         <v>760712</v>
@@ -10872,16 +10872,16 @@
         <v>45236</v>
       </c>
       <c r="B523